--- a/data/ZUC.MI.xlsx
+++ b/data/ZUC.MI.xlsx
@@ -62886,6 +62886,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2719">
+      <c r="A2719" s="1" t="n">
+        <v>46279.2916666667</v>
+      </c>
+      <c r="B2719" t="n">
+        <v>300</v>
+      </c>
+      <c r="C2719" t="n">
+        <v>0.509999990463257</v>
+      </c>
+      <c r="D2719" t="n">
+        <v>0.509999990463257</v>
+      </c>
+      <c r="E2719" t="n">
+        <v>0.509999990463257</v>
+      </c>
+      <c r="F2719" t="n">
+        <v>0.509999990463257</v>
+      </c>
+      <c r="G2719" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ZUC.MI.xlsx
+++ b/data/ZUC.MI.xlsx
@@ -62909,6 +62909,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2720">
+      <c r="A2720" s="1" t="n">
+        <v>46280.2916666667</v>
+      </c>
+      <c r="B2720" t="n">
+        <v>1421</v>
+      </c>
+      <c r="C2720" t="n">
+        <v>0.519999980926514</v>
+      </c>
+      <c r="D2720" t="n">
+        <v>0.509999990463257</v>
+      </c>
+      <c r="E2720" t="n">
+        <v>0.509999990463257</v>
+      </c>
+      <c r="F2720" t="n">
+        <v>0.519999980926514</v>
+      </c>
+      <c r="G2720" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ZUC.MI.xlsx
+++ b/data/ZUC.MI.xlsx
@@ -62932,6 +62932,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2721">
+      <c r="A2721" s="1" t="n">
+        <v>46281.2916666667</v>
+      </c>
+      <c r="B2721" t="n">
+        <v>10000</v>
+      </c>
+      <c r="C2721" t="n">
+        <v>0.509999990463257</v>
+      </c>
+      <c r="D2721" t="n">
+        <v>0.509999990463257</v>
+      </c>
+      <c r="E2721" t="n">
+        <v>0.509999990463257</v>
+      </c>
+      <c r="F2721" t="n">
+        <v>0.509999990463257</v>
+      </c>
+      <c r="G2721" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ZUC.MI.xlsx
+++ b/data/ZUC.MI.xlsx
@@ -62955,6 +62955,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2722">
+      <c r="A2722" s="1" t="n">
+        <v>46282.2916666667</v>
+      </c>
+      <c r="B2722" t="n">
+        <v>10413</v>
+      </c>
+      <c r="C2722" t="n">
+        <v>0.545000016689301</v>
+      </c>
+      <c r="D2722" t="n">
+        <v>0.524999976158142</v>
+      </c>
+      <c r="E2722" t="n">
+        <v>0.524999976158142</v>
+      </c>
+      <c r="F2722" t="n">
+        <v>0.524999976158142</v>
+      </c>
+      <c r="G2722" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ZUC.MI.xlsx
+++ b/data/ZUC.MI.xlsx
@@ -62796,22 +62796,22 @@
     </row>
     <row r="2715">
       <c r="A2715" s="1" t="n">
-        <v>46273.2916666667</v>
+        <v>46272.2916666667</v>
       </c>
       <c r="B2715" t="n">
-        <v>1048</v>
+        <v>2230</v>
       </c>
       <c r="C2715" t="n">
-        <v>0.524999976158142</v>
+        <v>0.550000011920929</v>
       </c>
       <c r="D2715" t="n">
-        <v>0.524999976158142</v>
+        <v>0.545000016689301</v>
       </c>
       <c r="E2715" t="n">
-        <v>0.524999976158142</v>
+        <v>0.545000016689301</v>
       </c>
       <c r="F2715" t="n">
-        <v>0.524999976158142</v>
+        <v>0.550000011920929</v>
       </c>
       <c r="G2715" t="s">
         <v>7</v>
@@ -62819,22 +62819,22 @@
     </row>
     <row r="2716">
       <c r="A2716" s="1" t="n">
-        <v>46274.2916666667</v>
+        <v>46273.2916666667</v>
       </c>
       <c r="B2716" t="n">
-        <v>1760</v>
+        <v>1048</v>
       </c>
       <c r="C2716" t="n">
-        <v>0.540000021457672</v>
+        <v>0.524999976158142</v>
       </c>
       <c r="D2716" t="n">
-        <v>0.509999990463257</v>
+        <v>0.524999976158142</v>
       </c>
       <c r="E2716" t="n">
-        <v>0.519999980926514</v>
+        <v>0.524999976158142</v>
       </c>
       <c r="F2716" t="n">
-        <v>0.540000021457672</v>
+        <v>0.524999976158142</v>
       </c>
       <c r="G2716" t="s">
         <v>7</v>
@@ -62842,22 +62842,22 @@
     </row>
     <row r="2717">
       <c r="A2717" s="1" t="n">
-        <v>46275.2916666667</v>
+        <v>46274.2916666667</v>
       </c>
       <c r="B2717" t="n">
-        <v>2056</v>
+        <v>1760</v>
       </c>
       <c r="C2717" t="n">
-        <v>0.529999971389771</v>
+        <v>0.540000021457672</v>
       </c>
       <c r="D2717" t="n">
         <v>0.509999990463257</v>
       </c>
       <c r="E2717" t="n">
-        <v>0.509999990463257</v>
+        <v>0.519999980926514</v>
       </c>
       <c r="F2717" t="n">
-        <v>0.529999971389771</v>
+        <v>0.540000021457672</v>
       </c>
       <c r="G2717" t="s">
         <v>7</v>
@@ -62865,22 +62865,22 @@
     </row>
     <row r="2718">
       <c r="A2718" s="1" t="n">
-        <v>46276.2916666667</v>
+        <v>46275.2916666667</v>
       </c>
       <c r="B2718" t="n">
-        <v>691</v>
+        <v>2056</v>
       </c>
       <c r="C2718" t="n">
-        <v>0.560000002384186</v>
+        <v>0.529999971389771</v>
       </c>
       <c r="D2718" t="n">
-        <v>0.560000002384186</v>
+        <v>0.509999990463257</v>
       </c>
       <c r="E2718" t="n">
-        <v>0.560000002384186</v>
+        <v>0.509999990463257</v>
       </c>
       <c r="F2718" t="n">
-        <v>0.560000002384186</v>
+        <v>0.529999971389771</v>
       </c>
       <c r="G2718" t="s">
         <v>7</v>
@@ -62888,22 +62888,22 @@
     </row>
     <row r="2719">
       <c r="A2719" s="1" t="n">
-        <v>46279.2916666667</v>
+        <v>46276.2916666667</v>
       </c>
       <c r="B2719" t="n">
-        <v>300</v>
+        <v>691</v>
       </c>
       <c r="C2719" t="n">
-        <v>0.509999990463257</v>
+        <v>0.560000002384186</v>
       </c>
       <c r="D2719" t="n">
-        <v>0.509999990463257</v>
+        <v>0.560000002384186</v>
       </c>
       <c r="E2719" t="n">
-        <v>0.509999990463257</v>
+        <v>0.560000002384186</v>
       </c>
       <c r="F2719" t="n">
-        <v>0.509999990463257</v>
+        <v>0.560000002384186</v>
       </c>
       <c r="G2719" t="s">
         <v>7</v>
@@ -62911,13 +62911,13 @@
     </row>
     <row r="2720">
       <c r="A2720" s="1" t="n">
-        <v>46280.2916666667</v>
+        <v>46279.2916666667</v>
       </c>
       <c r="B2720" t="n">
-        <v>1421</v>
+        <v>300</v>
       </c>
       <c r="C2720" t="n">
-        <v>0.519999980926514</v>
+        <v>0.509999990463257</v>
       </c>
       <c r="D2720" t="n">
         <v>0.509999990463257</v>
@@ -62926,7 +62926,7 @@
         <v>0.509999990463257</v>
       </c>
       <c r="F2720" t="n">
-        <v>0.519999980926514</v>
+        <v>0.509999990463257</v>
       </c>
       <c r="G2720" t="s">
         <v>7</v>
@@ -62934,13 +62934,13 @@
     </row>
     <row r="2721">
       <c r="A2721" s="1" t="n">
-        <v>46281.2916666667</v>
+        <v>46280.2916666667</v>
       </c>
       <c r="B2721" t="n">
-        <v>10000</v>
+        <v>1421</v>
       </c>
       <c r="C2721" t="n">
-        <v>0.509999990463257</v>
+        <v>0.519999980926514</v>
       </c>
       <c r="D2721" t="n">
         <v>0.509999990463257</v>
@@ -62949,7 +62949,7 @@
         <v>0.509999990463257</v>
       </c>
       <c r="F2721" t="n">
-        <v>0.509999990463257</v>
+        <v>0.519999980926514</v>
       </c>
       <c r="G2721" t="s">
         <v>7</v>
@@ -62957,24 +62957,47 @@
     </row>
     <row r="2722">
       <c r="A2722" s="1" t="n">
-        <v>46282.2916666667</v>
+        <v>46281.2916666667</v>
       </c>
       <c r="B2722" t="n">
-        <v>10413</v>
+        <v>10000</v>
       </c>
       <c r="C2722" t="n">
-        <v>0.545000016689301</v>
+        <v>0.509999990463257</v>
       </c>
       <c r="D2722" t="n">
+        <v>0.509999990463257</v>
+      </c>
+      <c r="E2722" t="n">
+        <v>0.509999990463257</v>
+      </c>
+      <c r="F2722" t="n">
+        <v>0.509999990463257</v>
+      </c>
+      <c r="G2722" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2723">
+      <c r="A2723" s="1" t="n">
+        <v>46283.2916666667</v>
+      </c>
+      <c r="B2723" t="n">
+        <v>10</v>
+      </c>
+      <c r="C2723" t="n">
         <v>0.524999976158142</v>
       </c>
-      <c r="E2722" t="n">
+      <c r="D2723" t="n">
         <v>0.524999976158142</v>
       </c>
-      <c r="F2722" t="n">
+      <c r="E2723" t="n">
         <v>0.524999976158142</v>
       </c>
-      <c r="G2722" t="s">
+      <c r="F2723" t="n">
+        <v>0.524999976158142</v>
+      </c>
+      <c r="G2723" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/ZUC.MI.xlsx
+++ b/data/ZUC.MI.xlsx
@@ -62980,13 +62980,13 @@
     </row>
     <row r="2723">
       <c r="A2723" s="1" t="n">
-        <v>46283.2916666667</v>
+        <v>46282.2916666667</v>
       </c>
       <c r="B2723" t="n">
-        <v>10</v>
+        <v>10413</v>
       </c>
       <c r="C2723" t="n">
-        <v>0.524999976158142</v>
+        <v>0.545000016689301</v>
       </c>
       <c r="D2723" t="n">
         <v>0.524999976158142</v>
@@ -62998,6 +62998,29 @@
         <v>0.524999976158142</v>
       </c>
       <c r="G2723" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2724">
+      <c r="A2724" s="1" t="n">
+        <v>46283.2916666667</v>
+      </c>
+      <c r="B2724" t="n">
+        <v>10</v>
+      </c>
+      <c r="C2724" t="n">
+        <v>0.524999976158142</v>
+      </c>
+      <c r="D2724" t="n">
+        <v>0.524999976158142</v>
+      </c>
+      <c r="E2724" t="n">
+        <v>0.524999976158142</v>
+      </c>
+      <c r="F2724" t="n">
+        <v>0.524999976158142</v>
+      </c>
+      <c r="G2724" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/ZUC.MI.xlsx
+++ b/data/ZUC.MI.xlsx
@@ -421,7 +421,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G2" t="n">
-        <v>3.01633286476135</v>
+        <v>3.01633310317993</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -447,7 +447,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G3" t="n">
-        <v>3.07884764671326</v>
+        <v>3.07884788513184</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -473,7 +473,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G4" t="n">
-        <v>2.96163249015808</v>
+        <v>2.96163296699524</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -499,7 +499,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G5" t="n">
-        <v>2.8522322177887</v>
+        <v>2.85223197937012</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -525,7 +525,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G6" t="n">
-        <v>2.96944665908813</v>
+        <v>2.96944689750671</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -551,7 +551,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G7" t="n">
-        <v>2.84441757202148</v>
+        <v>2.84441781044006</v>
       </c>
       <c r="H7" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G8" t="n">
-        <v>2.8522322177887</v>
+        <v>2.85223197937012</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G9" t="n">
-        <v>2.8522322177887</v>
+        <v>2.85223197937012</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G11" t="n">
-        <v>2.77408862113953</v>
+        <v>2.77408838272095</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -681,7 +681,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G12" t="n">
-        <v>2.62561631202698</v>
+        <v>2.6256160736084</v>
       </c>
       <c r="H12" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G13" t="n">
-        <v>2.5084011554718</v>
+        <v>2.50840139389038</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -733,7 +733,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G14" t="n">
-        <v>2.39900064468384</v>
+        <v>2.39900016784668</v>
       </c>
       <c r="H14" t="s">
         <v>8</v>
@@ -759,7 +759,7 @@
         <v>3</v>
       </c>
       <c r="G15" t="n">
-        <v>2.34430003166199</v>
+        <v>2.34430027008057</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
@@ -785,7 +785,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G16" t="n">
-        <v>2.39118599891663</v>
+        <v>2.39118623733521</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>3</v>
       </c>
       <c r="G19" t="n">
-        <v>2.34430003166199</v>
+        <v>2.34430027008057</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G25" t="n">
-        <v>1.78948259353638</v>
+        <v>1.78948247432709</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G27" t="n">
-        <v>1.0158634185791</v>
+        <v>1.01586353778839</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G28" t="n">
-        <v>0.625146746635437</v>
+        <v>0.625146687030792</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>1.5</v>
       </c>
       <c r="G30" t="n">
-        <v>1.17215001583099</v>
+        <v>1.17215013504028</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G33" t="n">
-        <v>1.9926552772522</v>
+        <v>1.99265515804291</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>3</v>
       </c>
       <c r="G34" t="n">
-        <v>2.34430003166199</v>
+        <v>2.34430027008057</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G35" t="n">
-        <v>2.50058698654175</v>
+        <v>2.50058674812317</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>3</v>
       </c>
       <c r="G36" t="n">
-        <v>2.34430003166199</v>
+        <v>2.34430027008057</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G37" t="n">
-        <v>2.71157383918762</v>
+        <v>2.7115740776062</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G38" t="n">
-        <v>2.63343024253845</v>
+        <v>2.63343048095703</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1383,7 +1383,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G39" t="n">
-        <v>2.44588685035706</v>
+        <v>2.44588661193848</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G40" t="n">
-        <v>2.37555766105652</v>
+        <v>2.37555742263794</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1435,7 +1435,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G41" t="n">
-        <v>2.51621556282043</v>
+        <v>2.51621532440186</v>
       </c>
       <c r="H41" t="s">
         <v>8</v>
@@ -1487,7 +1487,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G43" t="n">
-        <v>2.43025755882263</v>
+        <v>2.43025779724121</v>
       </c>
       <c r="H43" t="s">
         <v>8</v>
@@ -1513,7 +1513,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G44" t="n">
-        <v>2.48495817184448</v>
+        <v>2.48495841026306</v>
       </c>
       <c r="H44" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G45" t="n">
-        <v>2.77408862113953</v>
+        <v>2.77408838272095</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G46" t="n">
-        <v>2.742830991745</v>
+        <v>2.74283123016357</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1591,7 +1591,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G47" t="n">
-        <v>2.50058698654175</v>
+        <v>2.50058674812317</v>
       </c>
       <c r="H47" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G48" t="n">
-        <v>2.52402997016907</v>
+        <v>2.52402973175049</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G51" t="n">
-        <v>2.54747295379639</v>
+        <v>2.54747271537781</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G52" t="n">
-        <v>2.50058698654175</v>
+        <v>2.50058674812317</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G53" t="n">
-        <v>2.43807196617126</v>
+        <v>2.43807220458984</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G54" t="n">
-        <v>2.43025755882263</v>
+        <v>2.43025779724121</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G58" t="n">
-        <v>2.27397155761719</v>
+        <v>2.27397131919861</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G59" t="n">
-        <v>2.22708511352539</v>
+        <v>2.22708535194397</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G61" t="n">
-        <v>2.08642721176147</v>
+        <v>2.08642745018005</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G62" t="n">
-        <v>2.0551700592041</v>
+        <v>2.05517029762268</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G63" t="n">
-        <v>2.07079887390137</v>
+        <v>2.07079839706421</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G64" t="n">
-        <v>2.01609826087952</v>
+        <v>2.01609802246094</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>2.5</v>
       </c>
       <c r="G65" t="n">
-        <v>1.9535835981369</v>
+        <v>1.95358347892761</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>2.5</v>
       </c>
       <c r="G66" t="n">
-        <v>1.9535835981369</v>
+        <v>1.95358347892761</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>2.5</v>
       </c>
       <c r="G67" t="n">
-        <v>1.9535835981369</v>
+        <v>1.95358347892761</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G68" t="n">
-        <v>1.86762595176697</v>
+        <v>1.86762571334839</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G69" t="n">
-        <v>1.83636868000031</v>
+        <v>1.83636832237244</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2189,7 +2189,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G70" t="n">
-        <v>1.82073974609375</v>
+        <v>1.82073962688446</v>
       </c>
       <c r="H70" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G72" t="n">
-        <v>1.80511116981506</v>
+        <v>1.80511105060577</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G74" t="n">
-        <v>1.91451191902161</v>
+        <v>1.91451215744019</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G75" t="n">
-        <v>1.84418272972107</v>
+        <v>1.84418261051178</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G77" t="n">
-        <v>1.80511116981506</v>
+        <v>1.80511105060577</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G79" t="n">
-        <v>1.75041091442108</v>
+        <v>1.7504106760025</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>2.25</v>
       </c>
       <c r="G80" t="n">
-        <v>1.75822520256042</v>
+        <v>1.75822532176971</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G81" t="n">
-        <v>1.75041091442108</v>
+        <v>1.7504106760025</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2501,7 +2501,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G82" t="n">
-        <v>1.85981166362762</v>
+        <v>1.85981178283691</v>
       </c>
       <c r="H82" t="s">
         <v>8</v>
@@ -2527,7 +2527,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G83" t="n">
-        <v>1.85981166362762</v>
+        <v>1.85981178283691</v>
       </c>
       <c r="H83" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G84" t="n">
-        <v>1.85981166362762</v>
+        <v>1.85981178283691</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G85" t="n">
-        <v>1.83636868000031</v>
+        <v>1.83636832237244</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2631,7 +2631,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G87" t="n">
-        <v>1.73478209972382</v>
+        <v>1.7347823381424</v>
       </c>
       <c r="H87" t="s">
         <v>8</v>
@@ -2657,7 +2657,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G88" t="n">
-        <v>1.73478209972382</v>
+        <v>1.7347823381424</v>
       </c>
       <c r="H88" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G89" t="n">
-        <v>1.78948259353638</v>
+        <v>1.78948247432709</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G90" t="n">
-        <v>1.70352506637573</v>
+        <v>1.70352482795715</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2761,7 +2761,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G92" t="n">
-        <v>1.6331958770752</v>
+        <v>1.63319575786591</v>
       </c>
       <c r="H92" t="s">
         <v>8</v>
@@ -2787,7 +2787,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G93" t="n">
-        <v>1.70352506637573</v>
+        <v>1.70352482795715</v>
       </c>
       <c r="H93" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G94" t="n">
-        <v>1.69571042060852</v>
+        <v>1.6957106590271</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G96" t="n">
-        <v>1.64882445335388</v>
+        <v>1.64882433414459</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G99" t="n">
-        <v>2.26615691184998</v>
+        <v>2.26615715026855</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G100" t="n">
-        <v>2.08642721176147</v>
+        <v>2.08642745018005</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G101" t="n">
-        <v>2.0317268371582</v>
+        <v>2.03172707557678</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3021,7 +3021,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G102" t="n">
-        <v>2.01609826087952</v>
+        <v>2.01609802246094</v>
       </c>
       <c r="H102" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G105" t="n">
-        <v>1.88325476646423</v>
+        <v>1.88325464725494</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G106" t="n">
-        <v>1.82855427265167</v>
+        <v>1.82855439186096</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G107" t="n">
-        <v>1.74259650707245</v>
+        <v>1.74259638786316</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G109" t="n">
-        <v>1.71133935451508</v>
+        <v>1.71133923530579</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>2.25</v>
       </c>
       <c r="G111" t="n">
-        <v>1.75822520256042</v>
+        <v>1.75822532176971</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3281,7 +3281,7 @@
         <v>2.25</v>
       </c>
       <c r="G112" t="n">
-        <v>1.75822520256042</v>
+        <v>1.75822532176971</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -3307,7 +3307,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G113" t="n">
-        <v>1.69571042060852</v>
+        <v>1.6957106590271</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -3333,7 +3333,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G114" t="n">
-        <v>1.64882445335388</v>
+        <v>1.64882433414459</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G115" t="n">
-        <v>1.58630967140198</v>
+        <v>1.58630979061127</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3385,7 +3385,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G116" t="n">
-        <v>1.60193848609924</v>
+        <v>1.60193836688995</v>
       </c>
       <c r="H116" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G120" t="n">
-        <v>1.57849550247192</v>
+        <v>1.57849538326263</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3515,7 +3515,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G121" t="n">
-        <v>1.57849550247192</v>
+        <v>1.57849538326263</v>
       </c>
       <c r="H121" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G122" t="n">
-        <v>1.57849550247192</v>
+        <v>1.57849538326263</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G123" t="n">
-        <v>1.57849550247192</v>
+        <v>1.57849538326263</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G124" t="n">
-        <v>1.46909475326538</v>
+        <v>1.46909487247467</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G125" t="n">
-        <v>1.40658009052277</v>
+        <v>1.40658020973206</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G129" t="n">
-        <v>1.40658009052277</v>
+        <v>1.40658020973206</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>2.25</v>
       </c>
       <c r="G130" t="n">
-        <v>1.75822520256042</v>
+        <v>1.75822532176971</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>1.75</v>
       </c>
       <c r="G134" t="n">
-        <v>1.36750841140747</v>
+        <v>1.36750853061676</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3931,7 +3931,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G137" t="n">
-        <v>1.42220878601074</v>
+        <v>1.42220890522003</v>
       </c>
       <c r="H137" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G141" t="n">
-        <v>1.47690904140472</v>
+        <v>1.47690916061401</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G142" t="n">
-        <v>1.46909475326538</v>
+        <v>1.46909487247467</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4087,7 +4087,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G143" t="n">
-        <v>1.42220878601074</v>
+        <v>1.42220890522003</v>
       </c>
       <c r="H143" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G144" t="n">
-        <v>1.40658009052277</v>
+        <v>1.40658020973206</v>
       </c>
       <c r="H144" t="s">
         <v>8</v>
@@ -4139,7 +4139,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G145" t="n">
-        <v>1.45346617698669</v>
+        <v>1.4534660577774</v>
       </c>
       <c r="H145" t="s">
         <v>8</v>
@@ -4165,7 +4165,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G146" t="n">
-        <v>1.43002307415009</v>
+        <v>1.43002319335938</v>
       </c>
       <c r="H146" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G148" t="n">
-        <v>1.43002307415009</v>
+        <v>1.43002319335938</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4243,7 +4243,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G149" t="n">
-        <v>1.40658009052277</v>
+        <v>1.40658020973206</v>
       </c>
       <c r="H149" t="s">
         <v>8</v>
@@ -4269,7 +4269,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G150" t="n">
-        <v>1.43002307415009</v>
+        <v>1.43002319335938</v>
       </c>
       <c r="H150" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G151" t="n">
-        <v>1.43002307415009</v>
+        <v>1.43002319335938</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4347,7 +4347,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G153" t="n">
-        <v>1.42220878601074</v>
+        <v>1.42220890522003</v>
       </c>
       <c r="H153" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G154" t="n">
-        <v>1.46909475326538</v>
+        <v>1.46909487247467</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G156" t="n">
-        <v>1.49253785610199</v>
+        <v>1.49253797531128</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4451,7 +4451,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G157" t="n">
-        <v>1.50816643238068</v>
+        <v>1.50816655158997</v>
       </c>
       <c r="H157" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G159" t="n">
-        <v>1.48472332954407</v>
+        <v>1.48472344875336</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4555,7 +4555,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G161" t="n">
-        <v>1.47690904140472</v>
+        <v>1.47690916061401</v>
       </c>
       <c r="H161" t="s">
         <v>8</v>
@@ -4607,7 +4607,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G163" t="n">
-        <v>1.46909475326538</v>
+        <v>1.46909487247467</v>
       </c>
       <c r="H163" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G165" t="n">
-        <v>1.45346617698669</v>
+        <v>1.4534660577774</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -4685,7 +4685,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G166" t="n">
-        <v>1.46909475326538</v>
+        <v>1.46909487247467</v>
       </c>
       <c r="H166" t="s">
         <v>8</v>
@@ -4711,7 +4711,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G167" t="n">
-        <v>1.46909475326538</v>
+        <v>1.46909487247467</v>
       </c>
       <c r="H167" t="s">
         <v>8</v>
@@ -4737,7 +4737,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G168" t="n">
-        <v>1.46909475326538</v>
+        <v>1.46909487247467</v>
       </c>
       <c r="H168" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G169" t="n">
-        <v>1.47690904140472</v>
+        <v>1.47690916061401</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -4789,7 +4789,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G170" t="n">
-        <v>1.48472332954407</v>
+        <v>1.48472344875336</v>
       </c>
       <c r="H170" t="s">
         <v>8</v>
@@ -4815,7 +4815,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G171" t="n">
-        <v>1.47690904140472</v>
+        <v>1.47690916061401</v>
       </c>
       <c r="H171" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G172" t="n">
-        <v>1.47690904140472</v>
+        <v>1.47690916061401</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G175" t="n">
-        <v>1.49253785610199</v>
+        <v>1.49253797531128</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -4971,7 +4971,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G177" t="n">
-        <v>1.52379512786865</v>
+        <v>1.52379536628723</v>
       </c>
       <c r="H177" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G178" t="n">
-        <v>1.49253785610199</v>
+        <v>1.49253797531128</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G179" t="n">
-        <v>1.48472332954407</v>
+        <v>1.48472344875336</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G182" t="n">
-        <v>1.47690904140472</v>
+        <v>1.47690916061401</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G184" t="n">
-        <v>1.45346617698669</v>
+        <v>1.4534660577774</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5231,7 +5231,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G187" t="n">
-        <v>1.60975277423859</v>
+        <v>1.60975289344788</v>
       </c>
       <c r="H187" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G188" t="n">
-        <v>1.66445326805115</v>
+        <v>1.66445302963257</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5283,7 +5283,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G189" t="n">
-        <v>1.62538135051727</v>
+        <v>1.62538146972656</v>
       </c>
       <c r="H189" t="s">
         <v>8</v>
@@ -5309,7 +5309,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G190" t="n">
-        <v>1.52379512786865</v>
+        <v>1.52379536628723</v>
       </c>
       <c r="H190" t="s">
         <v>8</v>
@@ -5335,7 +5335,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G191" t="n">
-        <v>1.52379512786865</v>
+        <v>1.52379536628723</v>
       </c>
       <c r="H191" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G192" t="n">
-        <v>1.48472332954407</v>
+        <v>1.48472344875336</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5387,7 +5387,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G193" t="n">
-        <v>1.48472332954407</v>
+        <v>1.48472344875336</v>
       </c>
       <c r="H193" t="s">
         <v>8</v>
@@ -5413,7 +5413,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G194" t="n">
-        <v>1.48472332954407</v>
+        <v>1.48472344875336</v>
       </c>
       <c r="H194" t="s">
         <v>8</v>
@@ -5465,7 +5465,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G196" t="n">
-        <v>1.48472332954407</v>
+        <v>1.48472344875336</v>
       </c>
       <c r="H196" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G197" t="n">
-        <v>1.48472332954407</v>
+        <v>1.48472344875336</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5517,7 +5517,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G198" t="n">
-        <v>1.46909475326538</v>
+        <v>1.46909487247467</v>
       </c>
       <c r="H198" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G199" t="n">
-        <v>1.48472332954407</v>
+        <v>1.48472344875336</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5569,7 +5569,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G200" t="n">
-        <v>1.48472332954407</v>
+        <v>1.48472344875336</v>
       </c>
       <c r="H200" t="s">
         <v>8</v>
@@ -5595,7 +5595,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G201" t="n">
-        <v>1.48472332954407</v>
+        <v>1.48472344875336</v>
       </c>
       <c r="H201" t="s">
         <v>8</v>
@@ -5621,7 +5621,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G202" t="n">
-        <v>1.47690904140472</v>
+        <v>1.47690916061401</v>
       </c>
       <c r="H202" t="s">
         <v>8</v>
@@ -5647,7 +5647,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G203" t="n">
-        <v>1.48472332954407</v>
+        <v>1.48472344875336</v>
       </c>
       <c r="H203" t="s">
         <v>8</v>
@@ -5699,7 +5699,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G205" t="n">
-        <v>1.50816643238068</v>
+        <v>1.50816655158997</v>
       </c>
       <c r="H205" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G206" t="n">
-        <v>1.48472332954407</v>
+        <v>1.48472344875336</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G207" t="n">
-        <v>1.48472332954407</v>
+        <v>1.48472344875336</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5829,7 +5829,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G210" t="n">
-        <v>1.52379512786865</v>
+        <v>1.52379536628723</v>
       </c>
       <c r="H210" t="s">
         <v>8</v>
@@ -5855,7 +5855,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G211" t="n">
-        <v>1.53942382335663</v>
+        <v>1.53942394256592</v>
       </c>
       <c r="H211" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G213" t="n">
-        <v>1.55505263805389</v>
+        <v>1.5550525188446</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G216" t="n">
-        <v>1.50816643238068</v>
+        <v>1.50816655158997</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6011,7 +6011,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G217" t="n">
-        <v>1.52379512786865</v>
+        <v>1.52379536628723</v>
       </c>
       <c r="H217" t="s">
         <v>8</v>
@@ -6167,7 +6167,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G223" t="n">
-        <v>1.57849550247192</v>
+        <v>1.57849538326263</v>
       </c>
       <c r="H223" t="s">
         <v>8</v>
@@ -6193,7 +6193,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G224" t="n">
-        <v>1.55505263805389</v>
+        <v>1.5550525188446</v>
       </c>
       <c r="H224" t="s">
         <v>8</v>
@@ -6219,7 +6219,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G225" t="n">
-        <v>1.58630967140198</v>
+        <v>1.58630979061127</v>
       </c>
       <c r="H225" t="s">
         <v>8</v>
@@ -6271,7 +6271,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G227" t="n">
-        <v>1.53942382335663</v>
+        <v>1.53942394256592</v>
       </c>
       <c r="H227" t="s">
         <v>8</v>
@@ -6297,7 +6297,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G228" t="n">
-        <v>1.53942382335663</v>
+        <v>1.53942394256592</v>
       </c>
       <c r="H228" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G229" t="n">
-        <v>1.46909475326538</v>
+        <v>1.46909487247467</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6349,7 +6349,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G230" t="n">
-        <v>1.49253785610199</v>
+        <v>1.49253797531128</v>
       </c>
       <c r="H230" t="s">
         <v>8</v>
@@ -6375,7 +6375,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G231" t="n">
-        <v>1.48472332954407</v>
+        <v>1.48472344875336</v>
       </c>
       <c r="H231" t="s">
         <v>8</v>
@@ -6427,7 +6427,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G233" t="n">
-        <v>1.52379512786865</v>
+        <v>1.52379536628723</v>
       </c>
       <c r="H233" t="s">
         <v>8</v>
@@ -6479,7 +6479,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G235" t="n">
-        <v>1.43002307415009</v>
+        <v>1.43002319335938</v>
       </c>
       <c r="H235" t="s">
         <v>8</v>
@@ -6531,7 +6531,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G237" t="n">
-        <v>1.47690904140472</v>
+        <v>1.47690916061401</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -6583,7 +6583,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G239" t="n">
-        <v>1.46909475326538</v>
+        <v>1.46909487247467</v>
       </c>
       <c r="H239" t="s">
         <v>8</v>
@@ -6635,7 +6635,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G241" t="n">
-        <v>1.52379512786865</v>
+        <v>1.52379536628723</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -6661,7 +6661,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G242" t="n">
-        <v>1.52379512786865</v>
+        <v>1.52379536628723</v>
       </c>
       <c r="H242" t="s">
         <v>8</v>
@@ -6739,7 +6739,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G245" t="n">
-        <v>1.49253785610199</v>
+        <v>1.49253797531128</v>
       </c>
       <c r="H245" t="s">
         <v>8</v>
@@ -6895,7 +6895,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G251" t="n">
-        <v>1.50816643238068</v>
+        <v>1.50816655158997</v>
       </c>
       <c r="H251" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G252" t="n">
-        <v>1.49253785610199</v>
+        <v>1.49253797531128</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -6947,7 +6947,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G253" t="n">
-        <v>1.47690904140472</v>
+        <v>1.47690916061401</v>
       </c>
       <c r="H253" t="s">
         <v>8</v>
@@ -6999,7 +6999,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G255" t="n">
-        <v>1.49253785610199</v>
+        <v>1.49253797531128</v>
       </c>
       <c r="H255" t="s">
         <v>8</v>
@@ -7025,7 +7025,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G256" t="n">
-        <v>1.53942382335663</v>
+        <v>1.53942394256592</v>
       </c>
       <c r="H256" t="s">
         <v>8</v>
@@ -7077,7 +7077,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G258" t="n">
-        <v>1.83636868000031</v>
+        <v>1.83636832237244</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -7129,7 +7129,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G260" t="n">
-        <v>1.76603960990906</v>
+        <v>1.76603949069977</v>
       </c>
       <c r="H260" t="s">
         <v>8</v>
@@ -7155,7 +7155,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G261" t="n">
-        <v>1.73478209972382</v>
+        <v>1.7347823381424</v>
       </c>
       <c r="H261" t="s">
         <v>8</v>
@@ -7207,7 +7207,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G263" t="n">
-        <v>1.67226755619049</v>
+        <v>1.67226767539978</v>
       </c>
       <c r="H263" t="s">
         <v>8</v>
@@ -7233,7 +7233,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G264" t="n">
-        <v>1.64882445335388</v>
+        <v>1.64882433414459</v>
       </c>
       <c r="H264" t="s">
         <v>8</v>
@@ -7259,7 +7259,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G265" t="n">
-        <v>1.6331958770752</v>
+        <v>1.63319575786591</v>
       </c>
       <c r="H265" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G266" t="n">
-        <v>1.60193848609924</v>
+        <v>1.60193836688995</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7311,7 +7311,7 @@
         <v>2.25</v>
       </c>
       <c r="G267" t="n">
-        <v>1.75822520256042</v>
+        <v>1.75822532176971</v>
       </c>
       <c r="H267" t="s">
         <v>8</v>
@@ -7337,7 +7337,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G268" t="n">
-        <v>1.71133935451508</v>
+        <v>1.71133923530579</v>
       </c>
       <c r="H268" t="s">
         <v>8</v>
@@ -7363,7 +7363,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G269" t="n">
-        <v>1.66445326805115</v>
+        <v>1.66445302963257</v>
       </c>
       <c r="H269" t="s">
         <v>8</v>
@@ -7415,7 +7415,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G271" t="n">
-        <v>1.79729676246643</v>
+        <v>1.79729688167572</v>
       </c>
       <c r="H271" t="s">
         <v>8</v>
@@ -7441,7 +7441,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G272" t="n">
-        <v>2.0317268371582</v>
+        <v>2.03172707557678</v>
       </c>
       <c r="H272" t="s">
         <v>8</v>
@@ -7467,7 +7467,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G273" t="n">
-        <v>2.54747295379639</v>
+        <v>2.54747271537781</v>
       </c>
       <c r="H273" t="s">
         <v>8</v>
@@ -7545,7 +7545,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G276" t="n">
-        <v>2.54747295379639</v>
+        <v>2.54747271537781</v>
       </c>
       <c r="H276" t="s">
         <v>8</v>
@@ -7571,7 +7571,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G277" t="n">
-        <v>2.31304287910461</v>
+        <v>2.31304264068604</v>
       </c>
       <c r="H277" t="s">
         <v>8</v>
@@ -7597,7 +7597,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G278" t="n">
-        <v>2.36774349212646</v>
+        <v>2.36774301528931</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -7623,7 +7623,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G279" t="n">
-        <v>2.32085752487183</v>
+        <v>2.32085728645325</v>
       </c>
       <c r="H279" t="s">
         <v>8</v>
@@ -7649,7 +7649,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G280" t="n">
-        <v>2.36774349212646</v>
+        <v>2.36774301528931</v>
       </c>
       <c r="H280" t="s">
         <v>8</v>
@@ -7675,7 +7675,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G281" t="n">
-        <v>2.26615691184998</v>
+        <v>2.26615715026855</v>
       </c>
       <c r="H281" t="s">
         <v>8</v>
@@ -7727,7 +7727,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G283" t="n">
-        <v>2.48495817184448</v>
+        <v>2.48495841026306</v>
       </c>
       <c r="H283" t="s">
         <v>8</v>
@@ -7805,7 +7805,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G286" t="n">
-        <v>2.63343024253845</v>
+        <v>2.63343048095703</v>
       </c>
       <c r="H286" t="s">
         <v>8</v>
@@ -7857,7 +7857,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G288" t="n">
-        <v>2.56310176849365</v>
+        <v>2.56310153007507</v>
       </c>
       <c r="H288" t="s">
         <v>8</v>
@@ -7883,7 +7883,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G289" t="n">
-        <v>2.5084011554718</v>
+        <v>2.50840139389038</v>
       </c>
       <c r="H289" t="s">
         <v>8</v>
@@ -7909,7 +7909,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G290" t="n">
-        <v>2.48495817184448</v>
+        <v>2.48495841026306</v>
       </c>
       <c r="H290" t="s">
         <v>8</v>
@@ -8039,7 +8039,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G295" t="n">
-        <v>2.2114565372467</v>
+        <v>2.21145677566528</v>
       </c>
       <c r="H295" t="s">
         <v>8</v>
@@ -8065,7 +8065,7 @@
         <v>2.75</v>
       </c>
       <c r="G296" t="n">
-        <v>2.1489417552948</v>
+        <v>2.14894199371338</v>
       </c>
       <c r="H296" t="s">
         <v>8</v>
@@ -8273,7 +8273,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G304" t="n">
-        <v>2.08642721176147</v>
+        <v>2.08642745018005</v>
       </c>
       <c r="H304" t="s">
         <v>8</v>
@@ -8299,7 +8299,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G305" t="n">
-        <v>2.08642721176147</v>
+        <v>2.08642745018005</v>
       </c>
       <c r="H305" t="s">
         <v>8</v>
@@ -8325,7 +8325,7 @@
         <v>2.75</v>
       </c>
       <c r="G306" t="n">
-        <v>2.1489417552948</v>
+        <v>2.14894199371338</v>
       </c>
       <c r="H306" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G311" t="n">
-        <v>2.13331294059753</v>
+        <v>2.13331317901611</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8481,7 +8481,7 @@
         <v>2.75</v>
       </c>
       <c r="G312" t="n">
-        <v>2.1489417552948</v>
+        <v>2.14894199371338</v>
       </c>
       <c r="H312" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G313" t="n">
-        <v>2.14112758636475</v>
+        <v>2.14112782478333</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8533,7 +8533,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G314" t="n">
-        <v>2.19582796096802</v>
+        <v>2.19582772254944</v>
       </c>
       <c r="H314" t="s">
         <v>8</v>
@@ -8559,7 +8559,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G315" t="n">
-        <v>2.2114565372467</v>
+        <v>2.21145677566528</v>
       </c>
       <c r="H315" t="s">
         <v>8</v>
@@ -8585,7 +8585,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G316" t="n">
-        <v>2.31304287910461</v>
+        <v>2.31304264068604</v>
       </c>
       <c r="H316" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>3</v>
       </c>
       <c r="G317" t="n">
-        <v>2.34430003166199</v>
+        <v>2.34430027008057</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8663,7 +8663,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G319" t="n">
-        <v>2.43025755882263</v>
+        <v>2.43025779724121</v>
       </c>
       <c r="H319" t="s">
         <v>8</v>
@@ -8715,7 +8715,7 @@
         <v>3</v>
       </c>
       <c r="G321" t="n">
-        <v>2.34430003166199</v>
+        <v>2.34430027008057</v>
       </c>
       <c r="H321" t="s">
         <v>8</v>
@@ -8741,7 +8741,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G322" t="n">
-        <v>2.32085752487183</v>
+        <v>2.32085728645325</v>
       </c>
       <c r="H322" t="s">
         <v>8</v>
@@ -8767,7 +8767,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G323" t="n">
-        <v>2.26615691184998</v>
+        <v>2.26615715026855</v>
       </c>
       <c r="H323" t="s">
         <v>8</v>
@@ -8819,7 +8819,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G325" t="n">
-        <v>2.36774349212646</v>
+        <v>2.36774301528931</v>
       </c>
       <c r="H325" t="s">
         <v>8</v>
@@ -8871,7 +8871,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G327" t="n">
-        <v>2.31304287910461</v>
+        <v>2.31304264068604</v>
       </c>
       <c r="H327" t="s">
         <v>8</v>
@@ -8897,7 +8897,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G328" t="n">
-        <v>2.27397155761719</v>
+        <v>2.27397131919861</v>
       </c>
       <c r="H328" t="s">
         <v>8</v>
@@ -8923,7 +8923,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G329" t="n">
-        <v>2.27397155761719</v>
+        <v>2.27397131919861</v>
       </c>
       <c r="H329" t="s">
         <v>8</v>
@@ -8949,7 +8949,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G330" t="n">
-        <v>2.26615691184998</v>
+        <v>2.26615715026855</v>
       </c>
       <c r="H330" t="s">
         <v>8</v>
@@ -8975,7 +8975,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G331" t="n">
-        <v>2.27397155761719</v>
+        <v>2.27397131919861</v>
       </c>
       <c r="H331" t="s">
         <v>8</v>
@@ -9001,7 +9001,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G332" t="n">
-        <v>2.19582796096802</v>
+        <v>2.19582772254944</v>
       </c>
       <c r="H332" t="s">
         <v>8</v>
@@ -9105,7 +9105,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G336" t="n">
-        <v>2.36774349212646</v>
+        <v>2.36774301528931</v>
       </c>
       <c r="H336" t="s">
         <v>8</v>
@@ -9157,7 +9157,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G338" t="n">
-        <v>2.31304287910461</v>
+        <v>2.31304264068604</v>
       </c>
       <c r="H338" t="s">
         <v>8</v>
@@ -9209,7 +9209,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G340" t="n">
-        <v>2.26615691184998</v>
+        <v>2.26615715026855</v>
       </c>
       <c r="H340" t="s">
         <v>8</v>
@@ -9313,7 +9313,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G344" t="n">
-        <v>2.5084011554718</v>
+        <v>2.50840139389038</v>
       </c>
       <c r="H344" t="s">
         <v>8</v>
@@ -9365,7 +9365,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G346" t="n">
-        <v>2.39900064468384</v>
+        <v>2.39900016784668</v>
       </c>
       <c r="H346" t="s">
         <v>8</v>
@@ -9547,7 +9547,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G353" t="n">
-        <v>2.26615691184998</v>
+        <v>2.26615715026855</v>
       </c>
       <c r="H353" t="s">
         <v>8</v>
@@ -9573,7 +9573,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G354" t="n">
-        <v>2.27397155761719</v>
+        <v>2.27397131919861</v>
       </c>
       <c r="H354" t="s">
         <v>8</v>
@@ -9625,7 +9625,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G356" t="n">
-        <v>2.35992908477783</v>
+        <v>2.35992884635925</v>
       </c>
       <c r="H356" t="s">
         <v>8</v>
@@ -9677,7 +9677,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G358" t="n">
-        <v>2.37555766105652</v>
+        <v>2.37555742263794</v>
       </c>
       <c r="H358" t="s">
         <v>8</v>
@@ -9729,7 +9729,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G360" t="n">
-        <v>2.31304287910461</v>
+        <v>2.31304264068604</v>
       </c>
       <c r="H360" t="s">
         <v>8</v>
@@ -9781,7 +9781,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G362" t="n">
-        <v>2.39900064468384</v>
+        <v>2.39900016784668</v>
       </c>
       <c r="H362" t="s">
         <v>8</v>
@@ -9859,7 +9859,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G365" t="n">
-        <v>2.19582796096802</v>
+        <v>2.19582772254944</v>
       </c>
       <c r="H365" t="s">
         <v>8</v>
@@ -9885,7 +9885,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G366" t="n">
-        <v>2.19582796096802</v>
+        <v>2.19582772254944</v>
       </c>
       <c r="H366" t="s">
         <v>8</v>
@@ -9911,7 +9911,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G367" t="n">
-        <v>2.22708511352539</v>
+        <v>2.22708535194397</v>
       </c>
       <c r="H367" t="s">
         <v>8</v>
@@ -9937,7 +9937,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G368" t="n">
-        <v>2.22708511352539</v>
+        <v>2.22708535194397</v>
       </c>
       <c r="H368" t="s">
         <v>8</v>
@@ -9963,7 +9963,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G369" t="n">
-        <v>2.19582796096802</v>
+        <v>2.19582772254944</v>
       </c>
       <c r="H369" t="s">
         <v>8</v>
@@ -9989,7 +9989,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G370" t="n">
-        <v>2.19582796096802</v>
+        <v>2.19582772254944</v>
       </c>
       <c r="H370" t="s">
         <v>8</v>
@@ -10015,7 +10015,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G371" t="n">
-        <v>2.20364212989807</v>
+        <v>2.20364236831665</v>
       </c>
       <c r="H371" t="s">
         <v>8</v>
@@ -10041,7 +10041,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G372" t="n">
-        <v>2.22708511352539</v>
+        <v>2.22708535194397</v>
       </c>
       <c r="H372" t="s">
         <v>8</v>
@@ -10067,7 +10067,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G373" t="n">
-        <v>2.20364212989807</v>
+        <v>2.20364236831665</v>
       </c>
       <c r="H373" t="s">
         <v>8</v>
@@ -10093,7 +10093,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G374" t="n">
-        <v>2.2114565372467</v>
+        <v>2.21145677566528</v>
       </c>
       <c r="H374" t="s">
         <v>8</v>
@@ -10119,7 +10119,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G375" t="n">
-        <v>2.20364212989807</v>
+        <v>2.20364236831665</v>
       </c>
       <c r="H375" t="s">
         <v>8</v>
@@ -10171,7 +10171,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G377" t="n">
-        <v>2.22708511352539</v>
+        <v>2.22708535194397</v>
       </c>
       <c r="H377" t="s">
         <v>8</v>
@@ -10223,7 +10223,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G379" t="n">
-        <v>2.22708511352539</v>
+        <v>2.22708535194397</v>
       </c>
       <c r="H379" t="s">
         <v>8</v>
@@ -10249,7 +10249,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G380" t="n">
-        <v>2.20364212989807</v>
+        <v>2.20364236831665</v>
       </c>
       <c r="H380" t="s">
         <v>8</v>
@@ -10301,7 +10301,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G382" t="n">
-        <v>2.2114565372467</v>
+        <v>2.21145677566528</v>
       </c>
       <c r="H382" t="s">
         <v>8</v>
@@ -10353,7 +10353,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G384" t="n">
-        <v>2.23489952087402</v>
+        <v>2.2348997592926</v>
       </c>
       <c r="H384" t="s">
         <v>8</v>
@@ -10379,7 +10379,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G385" t="n">
-        <v>2.23489952087402</v>
+        <v>2.2348997592926</v>
       </c>
       <c r="H385" t="s">
         <v>8</v>
@@ -10457,7 +10457,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G388" t="n">
-        <v>2.22708511352539</v>
+        <v>2.22708535194397</v>
       </c>
       <c r="H388" t="s">
         <v>8</v>
@@ -10483,7 +10483,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G389" t="n">
-        <v>2.18019890785217</v>
+        <v>2.18019938468933</v>
       </c>
       <c r="H389" t="s">
         <v>8</v>
@@ -10509,7 +10509,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G390" t="n">
-        <v>2.19582796096802</v>
+        <v>2.19582772254944</v>
       </c>
       <c r="H390" t="s">
         <v>8</v>
@@ -10535,7 +10535,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G391" t="n">
-        <v>2.23489952087402</v>
+        <v>2.2348997592926</v>
       </c>
       <c r="H391" t="s">
         <v>8</v>
@@ -10561,7 +10561,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G392" t="n">
-        <v>2.22708511352539</v>
+        <v>2.22708535194397</v>
       </c>
       <c r="H392" t="s">
         <v>8</v>
@@ -10613,7 +10613,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G394" t="n">
-        <v>2.25052833557129</v>
+        <v>2.25052809715271</v>
       </c>
       <c r="H394" t="s">
         <v>8</v>
@@ -10639,7 +10639,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G395" t="n">
-        <v>2.26615691184998</v>
+        <v>2.26615715026855</v>
       </c>
       <c r="H395" t="s">
         <v>8</v>
@@ -10665,7 +10665,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G396" t="n">
-        <v>2.22708511352539</v>
+        <v>2.22708535194397</v>
       </c>
       <c r="H396" t="s">
         <v>8</v>
@@ -10691,7 +10691,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G397" t="n">
-        <v>2.2114565372467</v>
+        <v>2.21145677566528</v>
       </c>
       <c r="H397" t="s">
         <v>8</v>
@@ -10717,7 +10717,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G398" t="n">
-        <v>2.23489952087402</v>
+        <v>2.2348997592926</v>
       </c>
       <c r="H398" t="s">
         <v>8</v>
@@ -10769,7 +10769,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G400" t="n">
-        <v>2.25052833557129</v>
+        <v>2.25052809715271</v>
       </c>
       <c r="H400" t="s">
         <v>8</v>
@@ -10795,7 +10795,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G401" t="n">
-        <v>2.27397155761719</v>
+        <v>2.27397131919861</v>
       </c>
       <c r="H401" t="s">
         <v>8</v>
@@ -10821,7 +10821,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G402" t="n">
-        <v>2.28178572654724</v>
+        <v>2.28178548812866</v>
       </c>
       <c r="H402" t="s">
         <v>8</v>
@@ -10873,7 +10873,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G404" t="n">
-        <v>2.28178572654724</v>
+        <v>2.28178548812866</v>
       </c>
       <c r="H404" t="s">
         <v>8</v>
@@ -10899,7 +10899,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G405" t="n">
-        <v>2.26615691184998</v>
+        <v>2.26615715026855</v>
       </c>
       <c r="H405" t="s">
         <v>8</v>
@@ -10951,7 +10951,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G407" t="n">
-        <v>2.26615691184998</v>
+        <v>2.26615715026855</v>
       </c>
       <c r="H407" t="s">
         <v>8</v>
@@ -11003,7 +11003,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G409" t="n">
-        <v>2.25052833557129</v>
+        <v>2.25052809715271</v>
       </c>
       <c r="H409" t="s">
         <v>8</v>
@@ -11029,7 +11029,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G410" t="n">
-        <v>2.27397155761719</v>
+        <v>2.27397131919861</v>
       </c>
       <c r="H410" t="s">
         <v>8</v>
@@ -11055,7 +11055,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G411" t="n">
-        <v>2.26615691184998</v>
+        <v>2.26615715026855</v>
       </c>
       <c r="H411" t="s">
         <v>8</v>
@@ -11081,7 +11081,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G412" t="n">
-        <v>2.25052833557129</v>
+        <v>2.25052809715271</v>
       </c>
       <c r="H412" t="s">
         <v>8</v>
@@ -11133,7 +11133,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G414" t="n">
-        <v>2.22708511352539</v>
+        <v>2.22708535194397</v>
       </c>
       <c r="H414" t="s">
         <v>8</v>
@@ -11159,7 +11159,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G415" t="n">
-        <v>2.22708511352539</v>
+        <v>2.22708535194397</v>
       </c>
       <c r="H415" t="s">
         <v>8</v>
@@ -11185,7 +11185,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G416" t="n">
-        <v>2.25052833557129</v>
+        <v>2.25052809715271</v>
       </c>
       <c r="H416" t="s">
         <v>8</v>
@@ -11237,7 +11237,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G418" t="n">
-        <v>2.27397155761719</v>
+        <v>2.27397131919861</v>
       </c>
       <c r="H418" t="s">
         <v>8</v>
@@ -11263,7 +11263,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G419" t="n">
-        <v>2.25052833557129</v>
+        <v>2.25052809715271</v>
       </c>
       <c r="H419" t="s">
         <v>8</v>
@@ -11315,7 +11315,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G421" t="n">
-        <v>2.25052833557129</v>
+        <v>2.25052809715271</v>
       </c>
       <c r="H421" t="s">
         <v>8</v>
@@ -11341,7 +11341,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G422" t="n">
-        <v>2.25052833557129</v>
+        <v>2.25052809715271</v>
       </c>
       <c r="H422" t="s">
         <v>8</v>
@@ -11497,7 +11497,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G428" t="n">
-        <v>2.28178572654724</v>
+        <v>2.28178548812866</v>
       </c>
       <c r="H428" t="s">
         <v>8</v>
@@ -11523,7 +11523,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G429" t="n">
-        <v>2.27397155761719</v>
+        <v>2.27397131919861</v>
       </c>
       <c r="H429" t="s">
         <v>8</v>
@@ -11549,7 +11549,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G430" t="n">
-        <v>2.26615691184998</v>
+        <v>2.26615715026855</v>
       </c>
       <c r="H430" t="s">
         <v>8</v>
@@ -11575,7 +11575,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G431" t="n">
-        <v>2.27397155761719</v>
+        <v>2.27397131919861</v>
       </c>
       <c r="H431" t="s">
         <v>8</v>
@@ -11705,7 +11705,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G436" t="n">
-        <v>2.28178572654724</v>
+        <v>2.28178548812866</v>
       </c>
       <c r="H436" t="s">
         <v>8</v>
@@ -11731,7 +11731,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G437" t="n">
-        <v>2.27397155761719</v>
+        <v>2.27397131919861</v>
       </c>
       <c r="H437" t="s">
         <v>8</v>
@@ -11757,7 +11757,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G438" t="n">
-        <v>2.28178572654724</v>
+        <v>2.28178548812866</v>
       </c>
       <c r="H438" t="s">
         <v>8</v>
@@ -11835,7 +11835,7 @@
         <v>3</v>
       </c>
       <c r="G441" t="n">
-        <v>2.34430003166199</v>
+        <v>2.34430027008057</v>
       </c>
       <c r="H441" t="s">
         <v>8</v>
@@ -11887,7 +11887,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G443" t="n">
-        <v>2.35992908477783</v>
+        <v>2.35992884635925</v>
       </c>
       <c r="H443" t="s">
         <v>8</v>
@@ -11939,7 +11939,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G445" t="n">
-        <v>2.32085752487183</v>
+        <v>2.32085728645325</v>
       </c>
       <c r="H445" t="s">
         <v>8</v>
@@ -12043,7 +12043,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G449" t="n">
-        <v>2.31304287910461</v>
+        <v>2.31304264068604</v>
       </c>
       <c r="H449" t="s">
         <v>8</v>
@@ -12095,7 +12095,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G451" t="n">
-        <v>2.28178572654724</v>
+        <v>2.28178548812866</v>
       </c>
       <c r="H451" t="s">
         <v>8</v>
@@ -12121,7 +12121,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G452" t="n">
-        <v>2.27397155761719</v>
+        <v>2.27397131919861</v>
       </c>
       <c r="H452" t="s">
         <v>8</v>
@@ -12199,7 +12199,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G455" t="n">
-        <v>2.25052833557129</v>
+        <v>2.25052809715271</v>
       </c>
       <c r="H455" t="s">
         <v>8</v>
@@ -12225,7 +12225,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G456" t="n">
-        <v>2.27397155761719</v>
+        <v>2.27397131919861</v>
       </c>
       <c r="H456" t="s">
         <v>8</v>
@@ -12251,7 +12251,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G457" t="n">
-        <v>2.26615691184998</v>
+        <v>2.26615715026855</v>
       </c>
       <c r="H457" t="s">
         <v>8</v>
@@ -12277,7 +12277,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G458" t="n">
-        <v>2.26615691184998</v>
+        <v>2.26615715026855</v>
       </c>
       <c r="H458" t="s">
         <v>8</v>
@@ -12303,7 +12303,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G459" t="n">
-        <v>2.27397155761719</v>
+        <v>2.27397131919861</v>
       </c>
       <c r="H459" t="s">
         <v>8</v>
@@ -12329,7 +12329,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G460" t="n">
-        <v>2.26615691184998</v>
+        <v>2.26615715026855</v>
       </c>
       <c r="H460" t="s">
         <v>8</v>
@@ -12355,7 +12355,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G461" t="n">
-        <v>2.27397155761719</v>
+        <v>2.27397131919861</v>
       </c>
       <c r="H461" t="s">
         <v>8</v>
@@ -12407,7 +12407,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G463" t="n">
-        <v>2.27397155761719</v>
+        <v>2.27397131919861</v>
       </c>
       <c r="H463" t="s">
         <v>8</v>
@@ -12459,7 +12459,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G465" t="n">
-        <v>2.25052833557129</v>
+        <v>2.25052809715271</v>
       </c>
       <c r="H465" t="s">
         <v>8</v>
@@ -12511,7 +12511,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G467" t="n">
-        <v>2.25052833557129</v>
+        <v>2.25052809715271</v>
       </c>
       <c r="H467" t="s">
         <v>8</v>
@@ -12589,7 +12589,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G470" t="n">
-        <v>2.25052833557129</v>
+        <v>2.25052809715271</v>
       </c>
       <c r="H470" t="s">
         <v>8</v>
@@ -12693,7 +12693,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G474" t="n">
-        <v>2.28178572654724</v>
+        <v>2.28178548812866</v>
       </c>
       <c r="H474" t="s">
         <v>8</v>
@@ -12719,7 +12719,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G475" t="n">
-        <v>2.26615691184998</v>
+        <v>2.26615715026855</v>
       </c>
       <c r="H475" t="s">
         <v>8</v>
@@ -12745,7 +12745,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G476" t="n">
-        <v>2.26615691184998</v>
+        <v>2.26615715026855</v>
       </c>
       <c r="H476" t="s">
         <v>8</v>
@@ -12771,7 +12771,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G477" t="n">
-        <v>2.26615691184998</v>
+        <v>2.26615715026855</v>
       </c>
       <c r="H477" t="s">
         <v>8</v>
@@ -12797,7 +12797,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G478" t="n">
-        <v>2.25052833557129</v>
+        <v>2.25052809715271</v>
       </c>
       <c r="H478" t="s">
         <v>8</v>
@@ -12901,7 +12901,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G482" t="n">
-        <v>2.0551700592041</v>
+        <v>2.05517029762268</v>
       </c>
       <c r="H482" t="s">
         <v>8</v>
@@ -12927,7 +12927,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G483" t="n">
-        <v>2.0551700592041</v>
+        <v>2.05517029762268</v>
       </c>
       <c r="H483" t="s">
         <v>8</v>
@@ -12979,7 +12979,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G485" t="n">
-        <v>2.04735541343689</v>
+        <v>2.04735517501831</v>
       </c>
       <c r="H485" t="s">
         <v>8</v>
@@ -13005,7 +13005,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G486" t="n">
-        <v>2.07079887390137</v>
+        <v>2.07079839706421</v>
       </c>
       <c r="H486" t="s">
         <v>8</v>
@@ -13031,7 +13031,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G487" t="n">
-        <v>2.0551700592041</v>
+        <v>2.05517029762268</v>
       </c>
       <c r="H487" t="s">
         <v>8</v>
@@ -13135,7 +13135,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G491" t="n">
-        <v>2.0551700592041</v>
+        <v>2.05517029762268</v>
       </c>
       <c r="H491" t="s">
         <v>8</v>
@@ -13161,7 +13161,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G492" t="n">
-        <v>1.9926552772522</v>
+        <v>1.99265515804291</v>
       </c>
       <c r="H492" t="s">
         <v>8</v>
@@ -13187,7 +13187,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G493" t="n">
-        <v>2.0082836151123</v>
+        <v>2.00828409194946</v>
       </c>
       <c r="H493" t="s">
         <v>8</v>
@@ -13213,7 +13213,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G494" t="n">
-        <v>2.02391219139099</v>
+        <v>2.02391242980957</v>
       </c>
       <c r="H494" t="s">
         <v>8</v>
@@ -13239,7 +13239,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G495" t="n">
-        <v>2.02391219139099</v>
+        <v>2.02391242980957</v>
       </c>
       <c r="H495" t="s">
         <v>8</v>
@@ -13265,7 +13265,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G496" t="n">
-        <v>2.01609826087952</v>
+        <v>2.01609802246094</v>
       </c>
       <c r="H496" t="s">
         <v>8</v>
@@ -13291,7 +13291,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G497" t="n">
-        <v>1.9926552772522</v>
+        <v>1.99265515804291</v>
       </c>
       <c r="H497" t="s">
         <v>8</v>
@@ -13369,7 +13369,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G500" t="n">
-        <v>2.0082836151123</v>
+        <v>2.00828409194946</v>
       </c>
       <c r="H500" t="s">
         <v>8</v>
@@ -13395,7 +13395,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G501" t="n">
-        <v>2.01609826087952</v>
+        <v>2.01609802246094</v>
       </c>
       <c r="H501" t="s">
         <v>8</v>
@@ -13447,7 +13447,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G503" t="n">
-        <v>2.01609826087952</v>
+        <v>2.01609802246094</v>
       </c>
       <c r="H503" t="s">
         <v>8</v>
@@ -13473,7 +13473,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G504" t="n">
-        <v>1.9926552772522</v>
+        <v>1.99265515804291</v>
       </c>
       <c r="H504" t="s">
         <v>8</v>
@@ -13525,7 +13525,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G506" t="n">
-        <v>2.0317268371582</v>
+        <v>2.03172707557678</v>
       </c>
       <c r="H506" t="s">
         <v>8</v>
@@ -13551,7 +13551,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G507" t="n">
-        <v>2.0317268371582</v>
+        <v>2.03172707557678</v>
       </c>
       <c r="H507" t="s">
         <v>8</v>
@@ -13577,7 +13577,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G508" t="n">
-        <v>2.01609826087952</v>
+        <v>2.01609802246094</v>
       </c>
       <c r="H508" t="s">
         <v>8</v>
@@ -13629,7 +13629,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G510" t="n">
-        <v>2.0082836151123</v>
+        <v>2.00828409194946</v>
       </c>
       <c r="H510" t="s">
         <v>8</v>
@@ -13707,7 +13707,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G513" t="n">
-        <v>2.0082836151123</v>
+        <v>2.00828409194946</v>
       </c>
       <c r="H513" t="s">
         <v>8</v>
@@ -13733,7 +13733,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G514" t="n">
-        <v>2.01609826087952</v>
+        <v>2.01609802246094</v>
       </c>
       <c r="H514" t="s">
         <v>8</v>
@@ -13759,7 +13759,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G515" t="n">
-        <v>2.0317268371582</v>
+        <v>2.03172707557678</v>
       </c>
       <c r="H515" t="s">
         <v>8</v>
@@ -13785,7 +13785,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G516" t="n">
-        <v>2.0317268371582</v>
+        <v>2.03172707557678</v>
       </c>
       <c r="H516" t="s">
         <v>8</v>
@@ -13811,7 +13811,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G517" t="n">
-        <v>2.01609826087952</v>
+        <v>2.01609802246094</v>
       </c>
       <c r="H517" t="s">
         <v>8</v>
@@ -13863,7 +13863,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G519" t="n">
-        <v>2.08642721176147</v>
+        <v>2.08642745018005</v>
       </c>
       <c r="H519" t="s">
         <v>8</v>
@@ -13941,7 +13941,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G522" t="n">
-        <v>2.0551700592041</v>
+        <v>2.05517029762268</v>
       </c>
       <c r="H522" t="s">
         <v>8</v>
@@ -13967,7 +13967,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G523" t="n">
-        <v>2.08642721176147</v>
+        <v>2.08642745018005</v>
       </c>
       <c r="H523" t="s">
         <v>8</v>
@@ -14019,7 +14019,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G525" t="n">
-        <v>2.0551700592041</v>
+        <v>2.05517029762268</v>
       </c>
       <c r="H525" t="s">
         <v>8</v>
@@ -14045,7 +14045,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G526" t="n">
-        <v>2.04735541343689</v>
+        <v>2.04735517501831</v>
       </c>
       <c r="H526" t="s">
         <v>8</v>
@@ -14071,7 +14071,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G527" t="n">
-        <v>2.04735541343689</v>
+        <v>2.04735517501831</v>
       </c>
       <c r="H527" t="s">
         <v>8</v>
@@ -14097,7 +14097,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G528" t="n">
-        <v>2.0551700592041</v>
+        <v>2.05517029762268</v>
       </c>
       <c r="H528" t="s">
         <v>8</v>
@@ -14123,7 +14123,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G529" t="n">
-        <v>2.04735541343689</v>
+        <v>2.04735517501831</v>
       </c>
       <c r="H529" t="s">
         <v>8</v>
@@ -14149,7 +14149,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G530" t="n">
-        <v>2.08642721176147</v>
+        <v>2.08642745018005</v>
       </c>
       <c r="H530" t="s">
         <v>8</v>
@@ -14253,7 +14253,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G534" t="n">
-        <v>2.0317268371582</v>
+        <v>2.03172707557678</v>
       </c>
       <c r="H534" t="s">
         <v>8</v>
@@ -14279,7 +14279,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G535" t="n">
-        <v>2.0317268371582</v>
+        <v>2.03172707557678</v>
       </c>
       <c r="H535" t="s">
         <v>8</v>
@@ -14383,7 +14383,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G539" t="n">
-        <v>1.98484075069427</v>
+        <v>1.98484086990356</v>
       </c>
       <c r="H539" t="s">
         <v>8</v>
@@ -14409,7 +14409,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G540" t="n">
-        <v>1.97702646255493</v>
+        <v>1.97702670097351</v>
       </c>
       <c r="H540" t="s">
         <v>8</v>
@@ -14435,7 +14435,7 @@
         <v>2.5</v>
       </c>
       <c r="G541" t="n">
-        <v>1.9535835981369</v>
+        <v>1.95358347892761</v>
       </c>
       <c r="H541" t="s">
         <v>8</v>
@@ -14461,7 +14461,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G542" t="n">
-        <v>1.89106905460358</v>
+        <v>1.89106869697571</v>
       </c>
       <c r="H542" t="s">
         <v>8</v>
@@ -14487,7 +14487,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G543" t="n">
-        <v>1.92232596874237</v>
+        <v>1.92232608795166</v>
       </c>
       <c r="H543" t="s">
         <v>8</v>
@@ -14513,7 +14513,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G544" t="n">
-        <v>1.89106905460358</v>
+        <v>1.89106869697571</v>
       </c>
       <c r="H544" t="s">
         <v>8</v>
@@ -14539,7 +14539,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G545" t="n">
-        <v>1.98484075069427</v>
+        <v>1.98484086990356</v>
       </c>
       <c r="H545" t="s">
         <v>8</v>
@@ -14565,7 +14565,7 @@
         <v>2.5</v>
       </c>
       <c r="G546" t="n">
-        <v>1.9535835981369</v>
+        <v>1.95358347892761</v>
       </c>
       <c r="H546" t="s">
         <v>8</v>
@@ -14591,7 +14591,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G547" t="n">
-        <v>1.96921241283417</v>
+        <v>1.96921217441559</v>
       </c>
       <c r="H547" t="s">
         <v>8</v>
@@ -14617,7 +14617,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G548" t="n">
-        <v>1.96921241283417</v>
+        <v>1.96921217441559</v>
       </c>
       <c r="H548" t="s">
         <v>8</v>
@@ -14669,7 +14669,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G550" t="n">
-        <v>2.04735541343689</v>
+        <v>2.04735517501831</v>
       </c>
       <c r="H550" t="s">
         <v>8</v>
@@ -14695,7 +14695,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G551" t="n">
-        <v>2.0082836151123</v>
+        <v>2.00828409194946</v>
       </c>
       <c r="H551" t="s">
         <v>8</v>
@@ -14721,7 +14721,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G552" t="n">
-        <v>2.02391219139099</v>
+        <v>2.02391242980957</v>
       </c>
       <c r="H552" t="s">
         <v>8</v>
@@ -14747,7 +14747,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G553" t="n">
-        <v>2.0082836151123</v>
+        <v>2.00828409194946</v>
       </c>
       <c r="H553" t="s">
         <v>8</v>
@@ -14773,7 +14773,7 @@
         <v>2.5</v>
       </c>
       <c r="G554" t="n">
-        <v>1.9535835981369</v>
+        <v>1.95358347892761</v>
       </c>
       <c r="H554" t="s">
         <v>8</v>
@@ -14825,7 +14825,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G556" t="n">
-        <v>1.86762595176697</v>
+        <v>1.86762571334839</v>
       </c>
       <c r="H556" t="s">
         <v>8</v>
@@ -14877,7 +14877,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G558" t="n">
-        <v>1.88325476646423</v>
+        <v>1.88325464725494</v>
       </c>
       <c r="H558" t="s">
         <v>8</v>
@@ -14929,7 +14929,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G560" t="n">
-        <v>1.89888310432434</v>
+        <v>1.89888322353363</v>
       </c>
       <c r="H560" t="s">
         <v>8</v>
@@ -14955,7 +14955,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G561" t="n">
-        <v>1.89888310432434</v>
+        <v>1.89888322353363</v>
       </c>
       <c r="H561" t="s">
         <v>8</v>
@@ -14981,7 +14981,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G562" t="n">
-        <v>1.88325476646423</v>
+        <v>1.88325464725494</v>
       </c>
       <c r="H562" t="s">
         <v>8</v>
@@ -15059,7 +15059,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G565" t="n">
-        <v>1.91451191902161</v>
+        <v>1.91451215744019</v>
       </c>
       <c r="H565" t="s">
         <v>8</v>
@@ -15137,7 +15137,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G568" t="n">
-        <v>1.86762595176697</v>
+        <v>1.86762571334839</v>
       </c>
       <c r="H568" t="s">
         <v>8</v>
@@ -15163,7 +15163,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G569" t="n">
-        <v>1.84418272972107</v>
+        <v>1.84418261051178</v>
       </c>
       <c r="H569" t="s">
         <v>8</v>
@@ -15189,7 +15189,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G570" t="n">
-        <v>1.92232596874237</v>
+        <v>1.92232608795166</v>
       </c>
       <c r="H570" t="s">
         <v>8</v>
@@ -15241,7 +15241,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G572" t="n">
-        <v>2.0082836151123</v>
+        <v>2.00828409194946</v>
       </c>
       <c r="H572" t="s">
         <v>8</v>
@@ -15267,7 +15267,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G573" t="n">
-        <v>2.0317268371582</v>
+        <v>2.03172707557678</v>
       </c>
       <c r="H573" t="s">
         <v>8</v>
@@ -15319,7 +15319,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G575" t="n">
-        <v>2.0317268371582</v>
+        <v>2.03172707557678</v>
       </c>
       <c r="H575" t="s">
         <v>8</v>
@@ -15345,7 +15345,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G576" t="n">
-        <v>2.01609826087952</v>
+        <v>2.01609802246094</v>
       </c>
       <c r="H576" t="s">
         <v>8</v>
@@ -15397,7 +15397,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G578" t="n">
-        <v>2.0551700592041</v>
+        <v>2.05517029762268</v>
       </c>
       <c r="H578" t="s">
         <v>8</v>
@@ -15449,7 +15449,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G580" t="n">
-        <v>2.04735541343689</v>
+        <v>2.04735517501831</v>
       </c>
       <c r="H580" t="s">
         <v>8</v>
@@ -15475,7 +15475,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G581" t="n">
-        <v>2.01609826087952</v>
+        <v>2.01609802246094</v>
       </c>
       <c r="H581" t="s">
         <v>8</v>
@@ -15501,7 +15501,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G582" t="n">
-        <v>1.98484075069427</v>
+        <v>1.98484086990356</v>
       </c>
       <c r="H582" t="s">
         <v>8</v>
@@ -15527,7 +15527,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G583" t="n">
-        <v>1.98484075069427</v>
+        <v>1.98484086990356</v>
       </c>
       <c r="H583" t="s">
         <v>8</v>
@@ -15553,7 +15553,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G584" t="n">
-        <v>1.96139788627625</v>
+        <v>1.96139800548553</v>
       </c>
       <c r="H584" t="s">
         <v>8</v>
@@ -15579,7 +15579,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G585" t="n">
-        <v>1.97702646255493</v>
+        <v>1.97702670097351</v>
       </c>
       <c r="H585" t="s">
         <v>8</v>
@@ -15605,7 +15605,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G586" t="n">
-        <v>2.02391219139099</v>
+        <v>2.02391242980957</v>
       </c>
       <c r="H586" t="s">
         <v>8</v>
@@ -15631,7 +15631,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G587" t="n">
-        <v>2.0082836151123</v>
+        <v>2.00828409194946</v>
       </c>
       <c r="H587" t="s">
         <v>8</v>
@@ -15657,7 +15657,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G588" t="n">
-        <v>1.96921241283417</v>
+        <v>1.96921217441559</v>
       </c>
       <c r="H588" t="s">
         <v>8</v>
@@ -15683,7 +15683,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G589" t="n">
-        <v>1.97702646255493</v>
+        <v>1.97702670097351</v>
       </c>
       <c r="H589" t="s">
         <v>8</v>
@@ -15709,7 +15709,7 @@
         <v>2.5</v>
       </c>
       <c r="G590" t="n">
-        <v>1.9535835981369</v>
+        <v>1.95358347892761</v>
       </c>
       <c r="H590" t="s">
         <v>8</v>
@@ -15761,7 +15761,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G592" t="n">
-        <v>1.96921241283417</v>
+        <v>1.96921217441559</v>
       </c>
       <c r="H592" t="s">
         <v>8</v>
@@ -15787,7 +15787,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G593" t="n">
-        <v>1.89888310432434</v>
+        <v>1.89888322353363</v>
       </c>
       <c r="H593" t="s">
         <v>8</v>
@@ -15813,7 +15813,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G594" t="n">
-        <v>1.96921241283417</v>
+        <v>1.96921217441559</v>
       </c>
       <c r="H594" t="s">
         <v>8</v>
@@ -15839,7 +15839,7 @@
         <v>2.5</v>
       </c>
       <c r="G595" t="n">
-        <v>1.9535835981369</v>
+        <v>1.95358347892761</v>
       </c>
       <c r="H595" t="s">
         <v>8</v>
@@ -15865,7 +15865,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G596" t="n">
-        <v>1.93014049530029</v>
+        <v>1.93014061450958</v>
       </c>
       <c r="H596" t="s">
         <v>8</v>
@@ -15891,7 +15891,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G597" t="n">
-        <v>1.93014049530029</v>
+        <v>1.93014061450958</v>
       </c>
       <c r="H597" t="s">
         <v>8</v>
@@ -15943,7 +15943,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G599" t="n">
-        <v>1.91451191902161</v>
+        <v>1.91451215744019</v>
       </c>
       <c r="H599" t="s">
         <v>8</v>
@@ -16021,7 +16021,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G602" t="n">
-        <v>1.89106905460358</v>
+        <v>1.89106869697571</v>
       </c>
       <c r="H602" t="s">
         <v>8</v>
@@ -16099,7 +16099,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G605" t="n">
-        <v>1.89106905460358</v>
+        <v>1.89106869697571</v>
       </c>
       <c r="H605" t="s">
         <v>8</v>
@@ -16203,7 +16203,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G609" t="n">
-        <v>1.8519971370697</v>
+        <v>1.85199725627899</v>
       </c>
       <c r="H609" t="s">
         <v>8</v>
@@ -16229,7 +16229,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G610" t="n">
-        <v>1.84418272972107</v>
+        <v>1.84418261051178</v>
       </c>
       <c r="H610" t="s">
         <v>8</v>
@@ -16255,7 +16255,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G611" t="n">
-        <v>1.84418272972107</v>
+        <v>1.84418261051178</v>
       </c>
       <c r="H611" t="s">
         <v>8</v>
@@ -16281,7 +16281,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G612" t="n">
-        <v>1.85981166362762</v>
+        <v>1.85981178283691</v>
       </c>
       <c r="H612" t="s">
         <v>8</v>
@@ -16333,7 +16333,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G614" t="n">
-        <v>1.79729676246643</v>
+        <v>1.79729688167572</v>
       </c>
       <c r="H614" t="s">
         <v>8</v>
@@ -16359,7 +16359,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G615" t="n">
-        <v>1.88325476646423</v>
+        <v>1.88325464725494</v>
       </c>
       <c r="H615" t="s">
         <v>8</v>
@@ -16385,7 +16385,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G616" t="n">
-        <v>1.88325476646423</v>
+        <v>1.88325464725494</v>
       </c>
       <c r="H616" t="s">
         <v>8</v>
@@ -16437,7 +16437,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G618" t="n">
-        <v>1.84418272972107</v>
+        <v>1.84418261051178</v>
       </c>
       <c r="H618" t="s">
         <v>8</v>
@@ -16463,7 +16463,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G619" t="n">
-        <v>1.89106905460358</v>
+        <v>1.89106869697571</v>
       </c>
       <c r="H619" t="s">
         <v>8</v>
@@ -16489,7 +16489,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G620" t="n">
-        <v>1.82073974609375</v>
+        <v>1.82073962688446</v>
       </c>
       <c r="H620" t="s">
         <v>8</v>
@@ -16515,7 +16515,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G621" t="n">
-        <v>1.86762595176697</v>
+        <v>1.86762571334839</v>
       </c>
       <c r="H621" t="s">
         <v>8</v>
@@ -16541,7 +16541,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G622" t="n">
-        <v>1.84418272972107</v>
+        <v>1.84418261051178</v>
       </c>
       <c r="H622" t="s">
         <v>8</v>
@@ -16567,7 +16567,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G623" t="n">
-        <v>1.92232596874237</v>
+        <v>1.92232608795166</v>
       </c>
       <c r="H623" t="s">
         <v>8</v>
@@ -16593,7 +16593,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G624" t="n">
-        <v>1.86762595176697</v>
+        <v>1.86762571334839</v>
       </c>
       <c r="H624" t="s">
         <v>8</v>
@@ -16619,7 +16619,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G625" t="n">
-        <v>1.91451191902161</v>
+        <v>1.91451215744019</v>
       </c>
       <c r="H625" t="s">
         <v>8</v>
@@ -16645,7 +16645,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G626" t="n">
-        <v>1.86762595176697</v>
+        <v>1.86762571334839</v>
       </c>
       <c r="H626" t="s">
         <v>8</v>
@@ -16671,7 +16671,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G627" t="n">
-        <v>1.82073974609375</v>
+        <v>1.82073962688446</v>
       </c>
       <c r="H627" t="s">
         <v>8</v>
@@ -16697,7 +16697,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G628" t="n">
-        <v>1.8519971370697</v>
+        <v>1.85199725627899</v>
       </c>
       <c r="H628" t="s">
         <v>8</v>
@@ -16723,7 +16723,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G629" t="n">
-        <v>1.83636868000031</v>
+        <v>1.83636832237244</v>
       </c>
       <c r="H629" t="s">
         <v>8</v>
@@ -16749,7 +16749,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G630" t="n">
-        <v>1.84418272972107</v>
+        <v>1.84418261051178</v>
       </c>
       <c r="H630" t="s">
         <v>8</v>
@@ -16775,7 +16775,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G631" t="n">
-        <v>1.79729676246643</v>
+        <v>1.79729688167572</v>
       </c>
       <c r="H631" t="s">
         <v>8</v>
@@ -16801,7 +16801,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G632" t="n">
-        <v>1.76603960990906</v>
+        <v>1.76603949069977</v>
       </c>
       <c r="H632" t="s">
         <v>8</v>
@@ -16827,7 +16827,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G633" t="n">
-        <v>1.76603960990906</v>
+        <v>1.76603949069977</v>
       </c>
       <c r="H633" t="s">
         <v>8</v>
@@ -16853,7 +16853,7 @@
         <v>2.25</v>
       </c>
       <c r="G634" t="n">
-        <v>1.75822520256042</v>
+        <v>1.75822532176971</v>
       </c>
       <c r="H634" t="s">
         <v>8</v>
@@ -16905,7 +16905,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G636" t="n">
-        <v>1.75041091442108</v>
+        <v>1.7504106760025</v>
       </c>
       <c r="H636" t="s">
         <v>8</v>
@@ -16957,7 +16957,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G638" t="n">
-        <v>1.82073974609375</v>
+        <v>1.82073962688446</v>
       </c>
       <c r="H638" t="s">
         <v>8</v>
@@ -16983,7 +16983,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G639" t="n">
-        <v>1.73478209972382</v>
+        <v>1.7347823381424</v>
       </c>
       <c r="H639" t="s">
         <v>8</v>
@@ -17061,7 +17061,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G642" t="n">
-        <v>1.75041091442108</v>
+        <v>1.7504106760025</v>
       </c>
       <c r="H642" t="s">
         <v>8</v>
@@ -17113,7 +17113,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G644" t="n">
-        <v>1.74259650707245</v>
+        <v>1.74259638786316</v>
       </c>
       <c r="H644" t="s">
         <v>8</v>
@@ -17243,7 +17243,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G649" t="n">
-        <v>1.70352506637573</v>
+        <v>1.70352482795715</v>
       </c>
       <c r="H649" t="s">
         <v>8</v>
@@ -17295,7 +17295,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G651" t="n">
-        <v>1.68008196353912</v>
+        <v>1.68008172512054</v>
       </c>
       <c r="H651" t="s">
         <v>8</v>
@@ -17321,7 +17321,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G652" t="n">
-        <v>1.68008196353912</v>
+        <v>1.68008172512054</v>
       </c>
       <c r="H652" t="s">
         <v>8</v>
@@ -17347,7 +17347,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G653" t="n">
-        <v>1.66445326805115</v>
+        <v>1.66445302963257</v>
       </c>
       <c r="H653" t="s">
         <v>8</v>
@@ -17373,7 +17373,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G654" t="n">
-        <v>1.66445326805115</v>
+        <v>1.66445302963257</v>
       </c>
       <c r="H654" t="s">
         <v>8</v>
@@ -17503,7 +17503,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G659" t="n">
-        <v>1.60193848609924</v>
+        <v>1.60193836688995</v>
       </c>
       <c r="H659" t="s">
         <v>8</v>
@@ -17555,7 +17555,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G661" t="n">
-        <v>1.60193848609924</v>
+        <v>1.60193836688995</v>
       </c>
       <c r="H661" t="s">
         <v>8</v>
@@ -17581,7 +17581,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G662" t="n">
-        <v>1.60975277423859</v>
+        <v>1.60975289344788</v>
       </c>
       <c r="H662" t="s">
         <v>8</v>
@@ -17607,7 +17607,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G663" t="n">
-        <v>1.48472332954407</v>
+        <v>1.48472344875336</v>
       </c>
       <c r="H663" t="s">
         <v>8</v>
@@ -17633,7 +17633,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G664" t="n">
-        <v>1.55505263805389</v>
+        <v>1.5550525188446</v>
       </c>
       <c r="H664" t="s">
         <v>8</v>
@@ -17685,7 +17685,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G666" t="n">
-        <v>1.92232596874237</v>
+        <v>1.92232608795166</v>
       </c>
       <c r="H666" t="s">
         <v>8</v>
@@ -17711,7 +17711,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G667" t="n">
-        <v>2.01609826087952</v>
+        <v>2.01609802246094</v>
       </c>
       <c r="H667" t="s">
         <v>8</v>
@@ -17737,7 +17737,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G668" t="n">
-        <v>1.88325476646423</v>
+        <v>1.88325464725494</v>
       </c>
       <c r="H668" t="s">
         <v>8</v>
@@ -17763,7 +17763,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G669" t="n">
-        <v>1.92232596874237</v>
+        <v>1.92232608795166</v>
       </c>
       <c r="H669" t="s">
         <v>8</v>
@@ -17789,7 +17789,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G670" t="n">
-        <v>1.9926552772522</v>
+        <v>1.99265515804291</v>
       </c>
       <c r="H670" t="s">
         <v>8</v>
@@ -17815,7 +17815,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G671" t="n">
-        <v>1.93014049530029</v>
+        <v>1.93014061450958</v>
       </c>
       <c r="H671" t="s">
         <v>8</v>
@@ -17841,7 +17841,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G672" t="n">
-        <v>1.89888310432434</v>
+        <v>1.89888322353363</v>
       </c>
       <c r="H672" t="s">
         <v>8</v>
@@ -17867,7 +17867,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G673" t="n">
-        <v>1.92232596874237</v>
+        <v>1.92232608795166</v>
       </c>
       <c r="H673" t="s">
         <v>8</v>
@@ -17893,7 +17893,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G674" t="n">
-        <v>1.97702646255493</v>
+        <v>1.97702670097351</v>
       </c>
       <c r="H674" t="s">
         <v>8</v>
@@ -17919,7 +17919,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G675" t="n">
-        <v>1.89106905460358</v>
+        <v>1.89106869697571</v>
       </c>
       <c r="H675" t="s">
         <v>8</v>
@@ -17945,7 +17945,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G676" t="n">
-        <v>1.91451191902161</v>
+        <v>1.91451215744019</v>
       </c>
       <c r="H676" t="s">
         <v>8</v>
@@ -17971,7 +17971,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G677" t="n">
-        <v>1.88325476646423</v>
+        <v>1.88325464725494</v>
       </c>
       <c r="H677" t="s">
         <v>8</v>
@@ -17997,7 +17997,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G678" t="n">
-        <v>1.82855427265167</v>
+        <v>1.82855439186096</v>
       </c>
       <c r="H678" t="s">
         <v>8</v>
@@ -18023,7 +18023,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G679" t="n">
-        <v>1.85981166362762</v>
+        <v>1.85981178283691</v>
       </c>
       <c r="H679" t="s">
         <v>8</v>
@@ -18049,7 +18049,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G680" t="n">
-        <v>1.82855427265167</v>
+        <v>1.82855439186096</v>
       </c>
       <c r="H680" t="s">
         <v>8</v>
@@ -18075,7 +18075,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G681" t="n">
-        <v>1.76603960990906</v>
+        <v>1.76603949069977</v>
       </c>
       <c r="H681" t="s">
         <v>8</v>
@@ -18101,7 +18101,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G682" t="n">
-        <v>1.70352506637573</v>
+        <v>1.70352482795715</v>
       </c>
       <c r="H682" t="s">
         <v>8</v>
@@ -18127,7 +18127,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G683" t="n">
-        <v>1.91451191902161</v>
+        <v>1.91451215744019</v>
       </c>
       <c r="H683" t="s">
         <v>8</v>
@@ -18153,7 +18153,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G684" t="n">
-        <v>1.82073974609375</v>
+        <v>1.82073962688446</v>
       </c>
       <c r="H684" t="s">
         <v>8</v>
@@ -18179,7 +18179,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G685" t="n">
-        <v>1.76603960990906</v>
+        <v>1.76603949069977</v>
       </c>
       <c r="H685" t="s">
         <v>8</v>
@@ -18231,7 +18231,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G687" t="n">
-        <v>1.76603960990906</v>
+        <v>1.76603949069977</v>
       </c>
       <c r="H687" t="s">
         <v>8</v>
@@ -18257,7 +18257,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G688" t="n">
-        <v>1.76603960990906</v>
+        <v>1.76603949069977</v>
       </c>
       <c r="H688" t="s">
         <v>8</v>
@@ -18309,7 +18309,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G690" t="n">
-        <v>1.75041091442108</v>
+        <v>1.7504106760025</v>
       </c>
       <c r="H690" t="s">
         <v>8</v>
@@ -18361,7 +18361,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G692" t="n">
-        <v>1.70352506637573</v>
+        <v>1.70352482795715</v>
       </c>
       <c r="H692" t="s">
         <v>8</v>
@@ -18387,7 +18387,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G693" t="n">
-        <v>1.66445326805115</v>
+        <v>1.66445302963257</v>
       </c>
       <c r="H693" t="s">
         <v>8</v>
@@ -18413,7 +18413,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G694" t="n">
-        <v>1.66445326805115</v>
+        <v>1.66445302963257</v>
       </c>
       <c r="H694" t="s">
         <v>8</v>
@@ -18439,7 +18439,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G695" t="n">
-        <v>1.64882445335388</v>
+        <v>1.64882433414459</v>
       </c>
       <c r="H695" t="s">
         <v>8</v>
@@ -18465,7 +18465,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G696" t="n">
-        <v>1.67226755619049</v>
+        <v>1.67226767539978</v>
       </c>
       <c r="H696" t="s">
         <v>8</v>
@@ -18491,7 +18491,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G697" t="n">
-        <v>1.68008196353912</v>
+        <v>1.68008172512054</v>
       </c>
       <c r="H697" t="s">
         <v>8</v>
@@ -18517,7 +18517,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G698" t="n">
-        <v>1.68008196353912</v>
+        <v>1.68008172512054</v>
       </c>
       <c r="H698" t="s">
         <v>8</v>
@@ -18543,7 +18543,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G699" t="n">
-        <v>1.74259650707245</v>
+        <v>1.74259638786316</v>
       </c>
       <c r="H699" t="s">
         <v>8</v>
@@ -18595,7 +18595,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G701" t="n">
-        <v>1.70352506637573</v>
+        <v>1.70352482795715</v>
       </c>
       <c r="H701" t="s">
         <v>8</v>
@@ -18621,7 +18621,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G702" t="n">
-        <v>1.69571042060852</v>
+        <v>1.6957106590271</v>
       </c>
       <c r="H702" t="s">
         <v>8</v>
@@ -18647,7 +18647,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G703" t="n">
-        <v>1.64882445335388</v>
+        <v>1.64882433414459</v>
       </c>
       <c r="H703" t="s">
         <v>8</v>
@@ -18673,7 +18673,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G704" t="n">
-        <v>1.71133935451508</v>
+        <v>1.71133923530579</v>
       </c>
       <c r="H704" t="s">
         <v>8</v>
@@ -18699,7 +18699,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G705" t="n">
-        <v>1.69571042060852</v>
+        <v>1.6957106590271</v>
       </c>
       <c r="H705" t="s">
         <v>8</v>
@@ -18725,7 +18725,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G706" t="n">
-        <v>1.68789625167847</v>
+        <v>1.68789637088776</v>
       </c>
       <c r="H706" t="s">
         <v>8</v>
@@ -18751,7 +18751,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G707" t="n">
-        <v>1.62538135051727</v>
+        <v>1.62538146972656</v>
       </c>
       <c r="H707" t="s">
         <v>8</v>
@@ -18803,7 +18803,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G709" t="n">
-        <v>1.68789625167847</v>
+        <v>1.68789637088776</v>
       </c>
       <c r="H709" t="s">
         <v>8</v>
@@ -18829,7 +18829,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G710" t="n">
-        <v>1.6331958770752</v>
+        <v>1.63319575786591</v>
       </c>
       <c r="H710" t="s">
         <v>8</v>
@@ -18855,7 +18855,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G711" t="n">
-        <v>1.68008196353912</v>
+        <v>1.68008172512054</v>
       </c>
       <c r="H711" t="s">
         <v>8</v>
@@ -18881,7 +18881,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G712" t="n">
-        <v>1.68008196353912</v>
+        <v>1.68008172512054</v>
       </c>
       <c r="H712" t="s">
         <v>8</v>
@@ -18907,7 +18907,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G713" t="n">
-        <v>1.6331958770752</v>
+        <v>1.63319575786591</v>
       </c>
       <c r="H713" t="s">
         <v>8</v>
@@ -19011,7 +19011,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G717" t="n">
-        <v>1.58630967140198</v>
+        <v>1.58630979061127</v>
       </c>
       <c r="H717" t="s">
         <v>8</v>
@@ -19167,7 +19167,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G723" t="n">
-        <v>1.60193848609924</v>
+        <v>1.60193836688995</v>
       </c>
       <c r="H723" t="s">
         <v>8</v>
@@ -19193,7 +19193,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G724" t="n">
-        <v>1.60193848609924</v>
+        <v>1.60193836688995</v>
       </c>
       <c r="H724" t="s">
         <v>8</v>
@@ -19219,7 +19219,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G725" t="n">
-        <v>1.60193848609924</v>
+        <v>1.60193836688995</v>
       </c>
       <c r="H725" t="s">
         <v>8</v>
@@ -19245,7 +19245,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G726" t="n">
-        <v>1.60193848609924</v>
+        <v>1.60193836688995</v>
       </c>
       <c r="H726" t="s">
         <v>8</v>
@@ -19271,7 +19271,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G727" t="n">
-        <v>1.60193848609924</v>
+        <v>1.60193836688995</v>
       </c>
       <c r="H727" t="s">
         <v>8</v>
@@ -19401,7 +19401,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G732" t="n">
-        <v>1.60193848609924</v>
+        <v>1.60193836688995</v>
       </c>
       <c r="H732" t="s">
         <v>8</v>
@@ -19479,7 +19479,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G735" t="n">
-        <v>1.55505263805389</v>
+        <v>1.5550525188446</v>
       </c>
       <c r="H735" t="s">
         <v>8</v>
@@ -19531,7 +19531,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G737" t="n">
-        <v>1.50816643238068</v>
+        <v>1.50816655158997</v>
       </c>
       <c r="H737" t="s">
         <v>8</v>
@@ -19583,7 +19583,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G739" t="n">
-        <v>1.49253785610199</v>
+        <v>1.49253797531128</v>
       </c>
       <c r="H739" t="s">
         <v>8</v>
@@ -19661,7 +19661,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G742" t="n">
-        <v>1.50816643238068</v>
+        <v>1.50816655158997</v>
       </c>
       <c r="H742" t="s">
         <v>8</v>
@@ -19687,7 +19687,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G743" t="n">
-        <v>1.60975277423859</v>
+        <v>1.60975289344788</v>
       </c>
       <c r="H743" t="s">
         <v>8</v>
@@ -19713,7 +19713,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G744" t="n">
-        <v>1.62538135051727</v>
+        <v>1.62538146972656</v>
       </c>
       <c r="H744" t="s">
         <v>8</v>
@@ -19791,7 +19791,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G747" t="n">
-        <v>1.58630967140198</v>
+        <v>1.58630979061127</v>
       </c>
       <c r="H747" t="s">
         <v>8</v>
@@ -19817,7 +19817,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G748" t="n">
-        <v>1.58630967140198</v>
+        <v>1.58630979061127</v>
       </c>
       <c r="H748" t="s">
         <v>8</v>
@@ -19843,7 +19843,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G749" t="n">
-        <v>1.58630967140198</v>
+        <v>1.58630979061127</v>
       </c>
       <c r="H749" t="s">
         <v>8</v>
@@ -19895,7 +19895,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G751" t="n">
-        <v>1.57849550247192</v>
+        <v>1.57849538326263</v>
       </c>
       <c r="H751" t="s">
         <v>8</v>
@@ -19921,7 +19921,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G752" t="n">
-        <v>1.52379512786865</v>
+        <v>1.52379536628723</v>
       </c>
       <c r="H752" t="s">
         <v>8</v>
@@ -19947,7 +19947,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G753" t="n">
-        <v>1.52379512786865</v>
+        <v>1.52379536628723</v>
       </c>
       <c r="H753" t="s">
         <v>8</v>
@@ -19973,7 +19973,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G754" t="n">
-        <v>1.52379512786865</v>
+        <v>1.52379536628723</v>
       </c>
       <c r="H754" t="s">
         <v>8</v>
@@ -20025,7 +20025,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G756" t="n">
-        <v>1.53942382335663</v>
+        <v>1.53942394256592</v>
       </c>
       <c r="H756" t="s">
         <v>8</v>
@@ -20051,7 +20051,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G757" t="n">
-        <v>1.50816643238068</v>
+        <v>1.50816655158997</v>
       </c>
       <c r="H757" t="s">
         <v>8</v>
@@ -20077,7 +20077,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G758" t="n">
-        <v>1.48472332954407</v>
+        <v>1.48472344875336</v>
       </c>
       <c r="H758" t="s">
         <v>8</v>
@@ -20103,7 +20103,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G759" t="n">
-        <v>1.48472332954407</v>
+        <v>1.48472344875336</v>
       </c>
       <c r="H759" t="s">
         <v>8</v>
@@ -20155,7 +20155,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G761" t="n">
-        <v>1.49253785610199</v>
+        <v>1.49253797531128</v>
       </c>
       <c r="H761" t="s">
         <v>8</v>
@@ -20181,7 +20181,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G762" t="n">
-        <v>1.47690904140472</v>
+        <v>1.47690916061401</v>
       </c>
       <c r="H762" t="s">
         <v>8</v>
@@ -20233,7 +20233,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G764" t="n">
-        <v>1.50816643238068</v>
+        <v>1.50816655158997</v>
       </c>
       <c r="H764" t="s">
         <v>8</v>
@@ -20259,7 +20259,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G765" t="n">
-        <v>1.74259650707245</v>
+        <v>1.74259638786316</v>
       </c>
       <c r="H765" t="s">
         <v>8</v>
@@ -20285,7 +20285,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G766" t="n">
-        <v>1.55505263805389</v>
+        <v>1.5550525188446</v>
       </c>
       <c r="H766" t="s">
         <v>8</v>
@@ -20311,7 +20311,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G767" t="n">
-        <v>1.58630967140198</v>
+        <v>1.58630979061127</v>
       </c>
       <c r="H767" t="s">
         <v>8</v>
@@ -20337,7 +20337,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G768" t="n">
-        <v>1.55505263805389</v>
+        <v>1.5550525188446</v>
       </c>
       <c r="H768" t="s">
         <v>8</v>
@@ -20363,7 +20363,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G769" t="n">
-        <v>1.58630967140198</v>
+        <v>1.58630979061127</v>
       </c>
       <c r="H769" t="s">
         <v>8</v>
@@ -20389,7 +20389,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G770" t="n">
-        <v>1.58630967140198</v>
+        <v>1.58630979061127</v>
       </c>
       <c r="H770" t="s">
         <v>8</v>
@@ -20415,7 +20415,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G771" t="n">
-        <v>1.58630967140198</v>
+        <v>1.58630979061127</v>
       </c>
       <c r="H771" t="s">
         <v>8</v>
@@ -20441,7 +20441,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G772" t="n">
-        <v>1.58630967140198</v>
+        <v>1.58630979061127</v>
       </c>
       <c r="H772" t="s">
         <v>8</v>
@@ -20467,7 +20467,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G773" t="n">
-        <v>1.55505263805389</v>
+        <v>1.5550525188446</v>
       </c>
       <c r="H773" t="s">
         <v>8</v>
@@ -20493,7 +20493,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G774" t="n">
-        <v>1.57849550247192</v>
+        <v>1.57849538326263</v>
       </c>
       <c r="H774" t="s">
         <v>8</v>
@@ -20519,7 +20519,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G775" t="n">
-        <v>1.55505263805389</v>
+        <v>1.5550525188446</v>
       </c>
       <c r="H775" t="s">
         <v>8</v>
@@ -20571,7 +20571,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G777" t="n">
-        <v>1.53942382335663</v>
+        <v>1.53942394256592</v>
       </c>
       <c r="H777" t="s">
         <v>8</v>
@@ -20597,7 +20597,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G778" t="n">
-        <v>1.53942382335663</v>
+        <v>1.53942394256592</v>
       </c>
       <c r="H778" t="s">
         <v>8</v>
@@ -20675,7 +20675,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G781" t="n">
-        <v>1.55505263805389</v>
+        <v>1.5550525188446</v>
       </c>
       <c r="H781" t="s">
         <v>8</v>
@@ -20805,7 +20805,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G786" t="n">
-        <v>1.55505263805389</v>
+        <v>1.5550525188446</v>
       </c>
       <c r="H786" t="s">
         <v>8</v>
@@ -20831,7 +20831,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G787" t="n">
-        <v>1.55505263805389</v>
+        <v>1.5550525188446</v>
       </c>
       <c r="H787" t="s">
         <v>8</v>
@@ -20909,7 +20909,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G790" t="n">
-        <v>1.55505263805389</v>
+        <v>1.5550525188446</v>
       </c>
       <c r="H790" t="s">
         <v>8</v>
@@ -21117,7 +21117,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G798" t="n">
-        <v>1.57849550247192</v>
+        <v>1.57849538326263</v>
       </c>
       <c r="H798" t="s">
         <v>8</v>
@@ -21169,7 +21169,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G800" t="n">
-        <v>1.53942382335663</v>
+        <v>1.53942394256592</v>
       </c>
       <c r="H800" t="s">
         <v>8</v>
@@ -21221,7 +21221,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G802" t="n">
-        <v>1.55505263805389</v>
+        <v>1.5550525188446</v>
       </c>
       <c r="H802" t="s">
         <v>8</v>
@@ -21247,7 +21247,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G803" t="n">
-        <v>1.58630967140198</v>
+        <v>1.58630979061127</v>
       </c>
       <c r="H803" t="s">
         <v>8</v>
@@ -21325,7 +21325,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G806" t="n">
-        <v>1.58630967140198</v>
+        <v>1.58630979061127</v>
       </c>
       <c r="H806" t="s">
         <v>8</v>
@@ -21351,7 +21351,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G807" t="n">
-        <v>1.60975277423859</v>
+        <v>1.60975289344788</v>
       </c>
       <c r="H807" t="s">
         <v>8</v>
@@ -21377,7 +21377,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G808" t="n">
-        <v>1.58630967140198</v>
+        <v>1.58630979061127</v>
       </c>
       <c r="H808" t="s">
         <v>8</v>
@@ -21455,7 +21455,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G811" t="n">
-        <v>1.55505263805389</v>
+        <v>1.5550525188446</v>
       </c>
       <c r="H811" t="s">
         <v>8</v>
@@ -21481,7 +21481,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G812" t="n">
-        <v>1.55505263805389</v>
+        <v>1.5550525188446</v>
       </c>
       <c r="H812" t="s">
         <v>8</v>
@@ -21611,7 +21611,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G817" t="n">
-        <v>1.68008196353912</v>
+        <v>1.68008172512054</v>
       </c>
       <c r="H817" t="s">
         <v>8</v>
@@ -21637,7 +21637,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G818" t="n">
-        <v>1.60975277423859</v>
+        <v>1.60975289344788</v>
       </c>
       <c r="H818" t="s">
         <v>8</v>
@@ -21663,7 +21663,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G819" t="n">
-        <v>1.58630967140198</v>
+        <v>1.58630979061127</v>
       </c>
       <c r="H819" t="s">
         <v>8</v>
@@ -21715,7 +21715,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G821" t="n">
-        <v>1.62538135051727</v>
+        <v>1.62538146972656</v>
       </c>
       <c r="H821" t="s">
         <v>8</v>
@@ -21767,7 +21767,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G823" t="n">
-        <v>1.57849550247192</v>
+        <v>1.57849538326263</v>
       </c>
       <c r="H823" t="s">
         <v>8</v>
@@ -21793,7 +21793,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G824" t="n">
-        <v>1.57849550247192</v>
+        <v>1.57849538326263</v>
       </c>
       <c r="H824" t="s">
         <v>8</v>
@@ -21819,7 +21819,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G825" t="n">
-        <v>1.58630967140198</v>
+        <v>1.58630979061127</v>
       </c>
       <c r="H825" t="s">
         <v>8</v>
@@ -21871,7 +21871,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G827" t="n">
-        <v>1.62538135051727</v>
+        <v>1.62538146972656</v>
       </c>
       <c r="H827" t="s">
         <v>8</v>
@@ -21897,7 +21897,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G828" t="n">
-        <v>1.89106905460358</v>
+        <v>1.89106869697571</v>
       </c>
       <c r="H828" t="s">
         <v>8</v>
@@ -21923,7 +21923,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G829" t="n">
-        <v>1.73478209972382</v>
+        <v>1.7347823381424</v>
       </c>
       <c r="H829" t="s">
         <v>8</v>
@@ -21949,7 +21949,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G830" t="n">
-        <v>1.67226755619049</v>
+        <v>1.67226767539978</v>
       </c>
       <c r="H830" t="s">
         <v>8</v>
@@ -21975,7 +21975,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G831" t="n">
-        <v>1.65663886070251</v>
+        <v>1.65663874149323</v>
       </c>
       <c r="H831" t="s">
         <v>8</v>
@@ -22001,7 +22001,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G832" t="n">
-        <v>1.65663886070251</v>
+        <v>1.65663874149323</v>
       </c>
       <c r="H832" t="s">
         <v>8</v>
@@ -22027,7 +22027,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G833" t="n">
-        <v>1.67226755619049</v>
+        <v>1.67226767539978</v>
       </c>
       <c r="H833" t="s">
         <v>8</v>
@@ -22079,7 +22079,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G835" t="n">
-        <v>1.60975277423859</v>
+        <v>1.60975289344788</v>
       </c>
       <c r="H835" t="s">
         <v>8</v>
@@ -22105,7 +22105,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G836" t="n">
-        <v>1.62538135051727</v>
+        <v>1.62538146972656</v>
       </c>
       <c r="H836" t="s">
         <v>8</v>
@@ -22131,7 +22131,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G837" t="n">
-        <v>1.67226755619049</v>
+        <v>1.67226767539978</v>
       </c>
       <c r="H837" t="s">
         <v>8</v>
@@ -22157,7 +22157,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G838" t="n">
-        <v>1.67226755619049</v>
+        <v>1.67226767539978</v>
       </c>
       <c r="H838" t="s">
         <v>8</v>
@@ -22287,7 +22287,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G843" t="n">
-        <v>1.57849550247192</v>
+        <v>1.57849538326263</v>
       </c>
       <c r="H843" t="s">
         <v>8</v>
@@ -22313,7 +22313,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G844" t="n">
-        <v>1.60975277423859</v>
+        <v>1.60975289344788</v>
       </c>
       <c r="H844" t="s">
         <v>8</v>
@@ -22339,7 +22339,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G845" t="n">
-        <v>1.62538135051727</v>
+        <v>1.62538146972656</v>
       </c>
       <c r="H845" t="s">
         <v>8</v>
@@ -22365,7 +22365,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G846" t="n">
-        <v>1.60975277423859</v>
+        <v>1.60975289344788</v>
       </c>
       <c r="H846" t="s">
         <v>8</v>
@@ -22391,7 +22391,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G847" t="n">
-        <v>1.62538135051727</v>
+        <v>1.62538146972656</v>
       </c>
       <c r="H847" t="s">
         <v>8</v>
@@ -22417,7 +22417,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G848" t="n">
-        <v>1.60975277423859</v>
+        <v>1.60975289344788</v>
       </c>
       <c r="H848" t="s">
         <v>8</v>
@@ -22495,7 +22495,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G851" t="n">
-        <v>1.57849550247192</v>
+        <v>1.57849538326263</v>
       </c>
       <c r="H851" t="s">
         <v>8</v>
@@ -22703,7 +22703,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G859" t="n">
-        <v>1.57849550247192</v>
+        <v>1.57849538326263</v>
       </c>
       <c r="H859" t="s">
         <v>8</v>
@@ -22937,7 +22937,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G868" t="n">
-        <v>1.46909475326538</v>
+        <v>1.46909487247467</v>
       </c>
       <c r="H868" t="s">
         <v>8</v>
@@ -22963,7 +22963,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G869" t="n">
-        <v>1.45346617698669</v>
+        <v>1.4534660577774</v>
       </c>
       <c r="H869" t="s">
         <v>8</v>
@@ -22989,7 +22989,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G870" t="n">
-        <v>1.46909475326538</v>
+        <v>1.46909487247467</v>
       </c>
       <c r="H870" t="s">
         <v>8</v>
@@ -23067,7 +23067,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G873" t="n">
-        <v>1.46909475326538</v>
+        <v>1.46909487247467</v>
       </c>
       <c r="H873" t="s">
         <v>8</v>
@@ -23093,7 +23093,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G874" t="n">
-        <v>1.48472332954407</v>
+        <v>1.48472344875336</v>
       </c>
       <c r="H874" t="s">
         <v>8</v>
@@ -23119,7 +23119,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G875" t="n">
-        <v>1.45346617698669</v>
+        <v>1.4534660577774</v>
       </c>
       <c r="H875" t="s">
         <v>8</v>
@@ -23145,7 +23145,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G876" t="n">
-        <v>1.45346617698669</v>
+        <v>1.4534660577774</v>
       </c>
       <c r="H876" t="s">
         <v>8</v>
@@ -23223,7 +23223,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G879" t="n">
-        <v>1.48472332954407</v>
+        <v>1.48472344875336</v>
       </c>
       <c r="H879" t="s">
         <v>8</v>
@@ -23249,7 +23249,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G880" t="n">
-        <v>1.46909475326538</v>
+        <v>1.46909487247467</v>
       </c>
       <c r="H880" t="s">
         <v>8</v>
@@ -23275,7 +23275,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G881" t="n">
-        <v>1.45346617698669</v>
+        <v>1.4534660577774</v>
       </c>
       <c r="H881" t="s">
         <v>8</v>
@@ -23327,7 +23327,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G883" t="n">
-        <v>1.45346617698669</v>
+        <v>1.4534660577774</v>
       </c>
       <c r="H883" t="s">
         <v>8</v>
@@ -23353,7 +23353,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G884" t="n">
-        <v>1.45346617698669</v>
+        <v>1.4534660577774</v>
       </c>
       <c r="H884" t="s">
         <v>8</v>
@@ -23405,7 +23405,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G886" t="n">
-        <v>1.46909475326538</v>
+        <v>1.46909487247467</v>
       </c>
       <c r="H886" t="s">
         <v>8</v>
@@ -23431,7 +23431,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G887" t="n">
-        <v>1.48472332954407</v>
+        <v>1.48472344875336</v>
       </c>
       <c r="H887" t="s">
         <v>8</v>
@@ -23457,7 +23457,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G888" t="n">
-        <v>1.48472332954407</v>
+        <v>1.48472344875336</v>
       </c>
       <c r="H888" t="s">
         <v>8</v>
@@ -23613,7 +23613,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G894" t="n">
-        <v>1.48472332954407</v>
+        <v>1.48472344875336</v>
       </c>
       <c r="H894" t="s">
         <v>8</v>
@@ -24055,7 +24055,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G911" t="n">
-        <v>1.48472332954407</v>
+        <v>1.48472344875336</v>
       </c>
       <c r="H911" t="s">
         <v>8</v>
@@ -24237,7 +24237,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G918" t="n">
-        <v>1.46909475326538</v>
+        <v>1.46909487247467</v>
       </c>
       <c r="H918" t="s">
         <v>8</v>
@@ -24263,7 +24263,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G919" t="n">
-        <v>1.45346617698669</v>
+        <v>1.4534660577774</v>
       </c>
       <c r="H919" t="s">
         <v>8</v>
@@ -24289,7 +24289,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G920" t="n">
-        <v>1.45346617698669</v>
+        <v>1.4534660577774</v>
       </c>
       <c r="H920" t="s">
         <v>8</v>
@@ -24315,7 +24315,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G921" t="n">
-        <v>1.48472332954407</v>
+        <v>1.48472344875336</v>
       </c>
       <c r="H921" t="s">
         <v>8</v>
@@ -24341,7 +24341,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G922" t="n">
-        <v>1.46909475326538</v>
+        <v>1.46909487247467</v>
       </c>
       <c r="H922" t="s">
         <v>8</v>
@@ -24367,7 +24367,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G923" t="n">
-        <v>1.46909475326538</v>
+        <v>1.46909487247467</v>
       </c>
       <c r="H923" t="s">
         <v>8</v>
@@ -24393,7 +24393,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G924" t="n">
-        <v>1.45346617698669</v>
+        <v>1.4534660577774</v>
       </c>
       <c r="H924" t="s">
         <v>8</v>
@@ -24419,7 +24419,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G925" t="n">
-        <v>1.48472332954407</v>
+        <v>1.48472344875336</v>
       </c>
       <c r="H925" t="s">
         <v>8</v>
@@ -24497,7 +24497,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G928" t="n">
-        <v>1.45346617698669</v>
+        <v>1.4534660577774</v>
       </c>
       <c r="H928" t="s">
         <v>8</v>
@@ -24523,7 +24523,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G929" t="n">
-        <v>1.45346617698669</v>
+        <v>1.4534660577774</v>
       </c>
       <c r="H929" t="s">
         <v>8</v>
@@ -24549,7 +24549,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G930" t="n">
-        <v>1.48472332954407</v>
+        <v>1.48472344875336</v>
       </c>
       <c r="H930" t="s">
         <v>8</v>
@@ -24575,7 +24575,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G931" t="n">
-        <v>1.48472332954407</v>
+        <v>1.48472344875336</v>
       </c>
       <c r="H931" t="s">
         <v>8</v>
@@ -24601,7 +24601,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G932" t="n">
-        <v>1.46909475326538</v>
+        <v>1.46909487247467</v>
       </c>
       <c r="H932" t="s">
         <v>8</v>
@@ -24653,7 +24653,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G934" t="n">
-        <v>1.46909475326538</v>
+        <v>1.46909487247467</v>
       </c>
       <c r="H934" t="s">
         <v>8</v>
@@ -24861,7 +24861,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G942" t="n">
-        <v>1.48472332954407</v>
+        <v>1.48472344875336</v>
       </c>
       <c r="H942" t="s">
         <v>8</v>
@@ -24991,7 +24991,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G947" t="n">
-        <v>1.48472332954407</v>
+        <v>1.48472344875336</v>
       </c>
       <c r="H947" t="s">
         <v>8</v>
@@ -25199,7 +25199,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G955" t="n">
-        <v>1.48472332954407</v>
+        <v>1.48472344875336</v>
       </c>
       <c r="H955" t="s">
         <v>8</v>
@@ -25225,7 +25225,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G956" t="n">
-        <v>1.46909475326538</v>
+        <v>1.46909487247467</v>
       </c>
       <c r="H956" t="s">
         <v>8</v>
@@ -25251,7 +25251,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G957" t="n">
-        <v>1.46909475326538</v>
+        <v>1.46909487247467</v>
       </c>
       <c r="H957" t="s">
         <v>8</v>
@@ -25277,7 +25277,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G958" t="n">
-        <v>1.45346617698669</v>
+        <v>1.4534660577774</v>
       </c>
       <c r="H958" t="s">
         <v>8</v>
@@ -25303,7 +25303,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G959" t="n">
-        <v>1.40658009052277</v>
+        <v>1.40658020973206</v>
       </c>
       <c r="H959" t="s">
         <v>8</v>
@@ -25329,7 +25329,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G960" t="n">
-        <v>1.46909475326538</v>
+        <v>1.46909487247467</v>
       </c>
       <c r="H960" t="s">
         <v>8</v>
@@ -25355,7 +25355,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G961" t="n">
-        <v>1.46909475326538</v>
+        <v>1.46909487247467</v>
       </c>
       <c r="H961" t="s">
         <v>8</v>
@@ -25381,7 +25381,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G962" t="n">
-        <v>1.45346617698669</v>
+        <v>1.4534660577774</v>
       </c>
       <c r="H962" t="s">
         <v>8</v>
@@ -25407,7 +25407,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G963" t="n">
-        <v>1.48472332954407</v>
+        <v>1.48472344875336</v>
       </c>
       <c r="H963" t="s">
         <v>8</v>
@@ -25433,7 +25433,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G964" t="n">
-        <v>1.48472332954407</v>
+        <v>1.48472344875336</v>
       </c>
       <c r="H964" t="s">
         <v>8</v>
@@ -25459,7 +25459,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G965" t="n">
-        <v>1.48472332954407</v>
+        <v>1.48472344875336</v>
       </c>
       <c r="H965" t="s">
         <v>8</v>
@@ -25485,7 +25485,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G966" t="n">
-        <v>1.46909475326538</v>
+        <v>1.46909487247467</v>
       </c>
       <c r="H966" t="s">
         <v>8</v>
@@ -25511,7 +25511,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G967" t="n">
-        <v>1.46909475326538</v>
+        <v>1.46909487247467</v>
       </c>
       <c r="H967" t="s">
         <v>8</v>
@@ -25537,7 +25537,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G968" t="n">
-        <v>1.46909475326538</v>
+        <v>1.46909487247467</v>
       </c>
       <c r="H968" t="s">
         <v>8</v>
@@ -25667,7 +25667,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G973" t="n">
-        <v>1.42220878601074</v>
+        <v>1.42220890522003</v>
       </c>
       <c r="H973" t="s">
         <v>8</v>
@@ -25693,7 +25693,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G974" t="n">
-        <v>1.45346617698669</v>
+        <v>1.4534660577774</v>
       </c>
       <c r="H974" t="s">
         <v>8</v>
@@ -25745,7 +25745,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G976" t="n">
-        <v>1.42220878601074</v>
+        <v>1.42220890522003</v>
       </c>
       <c r="H976" t="s">
         <v>8</v>
@@ -25771,7 +25771,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G977" t="n">
-        <v>1.42220878601074</v>
+        <v>1.42220890522003</v>
       </c>
       <c r="H977" t="s">
         <v>8</v>
@@ -25823,7 +25823,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G979" t="n">
-        <v>1.45346617698669</v>
+        <v>1.4534660577774</v>
       </c>
       <c r="H979" t="s">
         <v>8</v>
@@ -25901,7 +25901,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G982" t="n">
-        <v>1.45346617698669</v>
+        <v>1.4534660577774</v>
       </c>
       <c r="H982" t="s">
         <v>8</v>
@@ -25927,7 +25927,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G983" t="n">
-        <v>1.45346617698669</v>
+        <v>1.4534660577774</v>
       </c>
       <c r="H983" t="s">
         <v>8</v>
@@ -25953,7 +25953,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G984" t="n">
-        <v>1.42220878601074</v>
+        <v>1.42220890522003</v>
       </c>
       <c r="H984" t="s">
         <v>8</v>
@@ -25979,7 +25979,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G985" t="n">
-        <v>1.42220878601074</v>
+        <v>1.42220890522003</v>
       </c>
       <c r="H985" t="s">
         <v>8</v>
@@ -26005,7 +26005,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G986" t="n">
-        <v>1.42220878601074</v>
+        <v>1.42220890522003</v>
       </c>
       <c r="H986" t="s">
         <v>8</v>
@@ -26031,7 +26031,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G987" t="n">
-        <v>1.40658009052277</v>
+        <v>1.40658020973206</v>
       </c>
       <c r="H987" t="s">
         <v>8</v>
@@ -26083,7 +26083,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G989" t="n">
-        <v>1.40658009052277</v>
+        <v>1.40658020973206</v>
       </c>
       <c r="H989" t="s">
         <v>8</v>
@@ -26187,7 +26187,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G993" t="n">
-        <v>1.42220878601074</v>
+        <v>1.42220890522003</v>
       </c>
       <c r="H993" t="s">
         <v>8</v>
@@ -26213,7 +26213,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G994" t="n">
-        <v>1.42220878601074</v>
+        <v>1.42220890522003</v>
       </c>
       <c r="H994" t="s">
         <v>8</v>
@@ -26265,7 +26265,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G996" t="n">
-        <v>1.42220878601074</v>
+        <v>1.42220890522003</v>
       </c>
       <c r="H996" t="s">
         <v>8</v>
@@ -26291,7 +26291,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G997" t="n">
-        <v>1.40658009052277</v>
+        <v>1.40658020973206</v>
       </c>
       <c r="H997" t="s">
         <v>8</v>
@@ -26317,7 +26317,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G998" t="n">
-        <v>1.40658009052277</v>
+        <v>1.40658020973206</v>
       </c>
       <c r="H998" t="s">
         <v>8</v>
@@ -26369,7 +26369,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G1000" t="n">
-        <v>1.40658009052277</v>
+        <v>1.40658020973206</v>
       </c>
       <c r="H1000" t="s">
         <v>8</v>
@@ -26447,7 +26447,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1003" t="n">
-        <v>1.68789625167847</v>
+        <v>1.68789637088776</v>
       </c>
       <c r="H1003" t="s">
         <v>8</v>
@@ -26499,7 +26499,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G1005" t="n">
-        <v>1.48472332954407</v>
+        <v>1.48472344875336</v>
       </c>
       <c r="H1005" t="s">
         <v>8</v>
@@ -26551,7 +26551,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G1007" t="n">
-        <v>1.46909475326538</v>
+        <v>1.46909487247467</v>
       </c>
       <c r="H1007" t="s">
         <v>8</v>
@@ -26577,7 +26577,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G1008" t="n">
-        <v>1.42220878601074</v>
+        <v>1.42220890522003</v>
       </c>
       <c r="H1008" t="s">
         <v>8</v>
@@ -26603,7 +26603,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G1009" t="n">
-        <v>1.45346617698669</v>
+        <v>1.4534660577774</v>
       </c>
       <c r="H1009" t="s">
         <v>8</v>
@@ -26655,7 +26655,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G1011" t="n">
-        <v>1.45346617698669</v>
+        <v>1.4534660577774</v>
       </c>
       <c r="H1011" t="s">
         <v>8</v>
@@ -26733,7 +26733,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G1014" t="n">
-        <v>1.46909475326538</v>
+        <v>1.46909487247467</v>
       </c>
       <c r="H1014" t="s">
         <v>8</v>
@@ -26759,7 +26759,7 @@
         <v>1.86940002441406</v>
       </c>
       <c r="G1015" t="n">
-        <v>1.46081161499023</v>
+        <v>1.46081173419952</v>
       </c>
       <c r="H1015" t="s">
         <v>8</v>
@@ -26785,7 +26785,7 @@
         <v>1.84019994735718</v>
       </c>
       <c r="G1016" t="n">
-        <v>1.43799388408661</v>
+        <v>1.43799376487732</v>
       </c>
       <c r="H1016" t="s">
         <v>8</v>
@@ -26811,7 +26811,7 @@
         <v>1.80480003356934</v>
       </c>
       <c r="G1017" t="n">
-        <v>1.41033101081848</v>
+        <v>1.41033089160919</v>
       </c>
       <c r="H1017" t="s">
         <v>8</v>
@@ -26863,7 +26863,7 @@
         <v>1.76600003242493</v>
       </c>
       <c r="G1019" t="n">
-        <v>1.38001132011414</v>
+        <v>1.38001155853271</v>
       </c>
       <c r="H1019" t="s">
         <v>8</v>
@@ -26915,7 +26915,7 @@
         <v>1.77359998226166</v>
       </c>
       <c r="G1021" t="n">
-        <v>1.38595032691956</v>
+        <v>1.38595020771027</v>
       </c>
       <c r="H1021" t="s">
         <v>8</v>
@@ -26941,7 +26941,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G1022" t="n">
-        <v>1.43002307415009</v>
+        <v>1.43002319335938</v>
       </c>
       <c r="H1022" t="s">
         <v>8</v>
@@ -27071,7 +27071,7 @@
         <v>1.74600005149841</v>
       </c>
       <c r="G1027" t="n">
-        <v>1.36438262462616</v>
+        <v>1.36438286304474</v>
       </c>
       <c r="H1027" t="s">
         <v>8</v>
@@ -27149,7 +27149,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G1030" t="n">
-        <v>1.3362512588501</v>
+        <v>1.33625113964081</v>
       </c>
       <c r="H1030" t="s">
         <v>8</v>
@@ -27175,7 +27175,7 @@
         <v>1.73239994049072</v>
       </c>
       <c r="G1031" t="n">
-        <v>1.35375511646271</v>
+        <v>1.353755235672</v>
       </c>
       <c r="H1031" t="s">
         <v>8</v>
@@ -27201,7 +27201,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G1032" t="n">
-        <v>1.35187995433807</v>
+        <v>1.35187971591949</v>
       </c>
       <c r="H1032" t="s">
         <v>8</v>
@@ -27227,7 +27227,7 @@
         <v>1.70099997520447</v>
       </c>
       <c r="G1033" t="n">
-        <v>1.32921826839447</v>
+        <v>1.32921838760376</v>
       </c>
       <c r="H1033" t="s">
         <v>8</v>
@@ -27253,7 +27253,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G1034" t="n">
-        <v>1.3362512588501</v>
+        <v>1.33625113964081</v>
       </c>
       <c r="H1034" t="s">
         <v>8</v>
@@ -27279,7 +27279,7 @@
         <v>1.68099999427795</v>
       </c>
       <c r="G1035" t="n">
-        <v>1.31358957290649</v>
+        <v>1.3135894536972</v>
       </c>
       <c r="H1035" t="s">
         <v>8</v>
@@ -27331,7 +27331,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G1037" t="n">
-        <v>1.28155088424683</v>
+        <v>1.28155076503754</v>
       </c>
       <c r="H1037" t="s">
         <v>8</v>
@@ -27357,7 +27357,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1038" t="n">
-        <v>1.25029349327087</v>
+        <v>1.25029337406158</v>
       </c>
       <c r="H1038" t="s">
         <v>8</v>
@@ -27409,7 +27409,7 @@
         <v>1.52020001411438</v>
       </c>
       <c r="G1040" t="n">
-        <v>1.18793523311615</v>
+        <v>1.18793499469757</v>
       </c>
       <c r="H1040" t="s">
         <v>8</v>
@@ -27435,7 +27435,7 @@
         <v>1.57720005512238</v>
       </c>
       <c r="G1041" t="n">
-        <v>1.23247671127319</v>
+        <v>1.23247683048248</v>
       </c>
       <c r="H1041" t="s">
         <v>8</v>
@@ -27461,7 +27461,7 @@
         <v>1.60580003261566</v>
       </c>
       <c r="G1042" t="n">
-        <v>1.25482571125031</v>
+        <v>1.25482583045959</v>
       </c>
       <c r="H1042" t="s">
         <v>8</v>
@@ -27487,7 +27487,7 @@
         <v>1.61819994449615</v>
       </c>
       <c r="G1043" t="n">
-        <v>1.26451551914215</v>
+        <v>1.26451539993286</v>
       </c>
       <c r="H1043" t="s">
         <v>8</v>
@@ -27513,7 +27513,7 @@
         <v>1.63900005817413</v>
       </c>
       <c r="G1044" t="n">
-        <v>1.28076946735382</v>
+        <v>1.28076958656311</v>
       </c>
       <c r="H1044" t="s">
         <v>8</v>
@@ -27617,7 +27617,7 @@
         <v>1.68579995632172</v>
       </c>
       <c r="G1048" t="n">
-        <v>1.31734049320221</v>
+        <v>1.31734037399292</v>
       </c>
       <c r="H1048" t="s">
         <v>8</v>
@@ -27643,7 +27643,7 @@
         <v>1.67980003356934</v>
       </c>
       <c r="G1049" t="n">
-        <v>1.31265199184418</v>
+        <v>1.3126517534256</v>
       </c>
       <c r="H1049" t="s">
         <v>8</v>
@@ -27695,7 +27695,7 @@
         <v>1.65020000934601</v>
       </c>
       <c r="G1051" t="n">
-        <v>1.28952157497406</v>
+        <v>1.28952133655548</v>
       </c>
       <c r="H1051" t="s">
         <v>8</v>
@@ -27825,7 +27825,7 @@
         <v>1.54159998893738</v>
       </c>
       <c r="G1056" t="n">
-        <v>1.20465767383575</v>
+        <v>1.20465779304504</v>
       </c>
       <c r="H1056" t="s">
         <v>8</v>
@@ -27851,7 +27851,7 @@
         <v>1.58980000019073</v>
       </c>
       <c r="G1057" t="n">
-        <v>1.24232280254364</v>
+        <v>1.24232292175293</v>
       </c>
       <c r="H1057" t="s">
         <v>8</v>
@@ -27877,7 +27877,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G1058" t="n">
-        <v>1.17996454238892</v>
+        <v>1.17996442317963</v>
       </c>
       <c r="H1058" t="s">
         <v>8</v>
@@ -27903,7 +27903,7 @@
         <v>1.55980002880096</v>
       </c>
       <c r="G1059" t="n">
-        <v>1.21887981891632</v>
+        <v>1.21887993812561</v>
       </c>
       <c r="H1059" t="s">
         <v>8</v>
@@ -27929,7 +27929,7 @@
         <v>1.5</v>
       </c>
       <c r="G1060" t="n">
-        <v>1.17215001583099</v>
+        <v>1.17215013504028</v>
       </c>
       <c r="H1060" t="s">
         <v>8</v>
@@ -28007,7 +28007,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G1063" t="n">
-        <v>0.883019804954529</v>
+        <v>0.883019745349884</v>
       </c>
       <c r="H1063" t="s">
         <v>8</v>
@@ -28033,7 +28033,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G1064" t="n">
-        <v>0.883019804954529</v>
+        <v>0.883019745349884</v>
       </c>
       <c r="H1064" t="s">
         <v>8</v>
@@ -28059,7 +28059,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G1065" t="n">
-        <v>0.867391049861908</v>
+        <v>0.867391169071198</v>
       </c>
       <c r="H1065" t="s">
         <v>8</v>
@@ -28085,7 +28085,7 @@
         <v>0.939999997615814</v>
       </c>
       <c r="G1066" t="n">
-        <v>0.73454737663269</v>
+        <v>0.734547436237335</v>
       </c>
       <c r="H1066" t="s">
         <v>8</v>
@@ -28111,7 +28111,7 @@
         <v>0.997900009155273</v>
       </c>
       <c r="G1067" t="n">
-        <v>0.779792368412018</v>
+        <v>0.779792428016663</v>
       </c>
       <c r="H1067" t="s">
         <v>8</v>
@@ -28215,7 +28215,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G1071" t="n">
-        <v>0.789247751235962</v>
+        <v>0.789247691631317</v>
       </c>
       <c r="H1071" t="s">
         <v>8</v>
@@ -28371,7 +28371,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G1077" t="n">
-        <v>1.24247908592224</v>
+        <v>1.24247920513153</v>
       </c>
       <c r="H1077" t="s">
         <v>8</v>
@@ -28397,7 +28397,7 @@
         <v>1.61500000953674</v>
       </c>
       <c r="G1078" t="n">
-        <v>1.26201498508453</v>
+        <v>1.26201486587524</v>
       </c>
       <c r="H1078" t="s">
         <v>8</v>
@@ -28423,7 +28423,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1079" t="n">
-        <v>1.25029349327087</v>
+        <v>1.25029337406158</v>
       </c>
       <c r="H1079" t="s">
         <v>8</v>
@@ -28501,7 +28501,7 @@
         <v>1.49080002307892</v>
       </c>
       <c r="G1082" t="n">
-        <v>1.16496098041534</v>
+        <v>1.16496086120605</v>
       </c>
       <c r="H1082" t="s">
         <v>8</v>
@@ -28553,7 +28553,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G1084" t="n">
-        <v>1.25810778141022</v>
+        <v>1.25810766220093</v>
       </c>
       <c r="H1084" t="s">
         <v>8</v>
@@ -28579,7 +28579,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G1085" t="n">
-        <v>1.21903598308563</v>
+        <v>1.21903610229492</v>
       </c>
       <c r="H1085" t="s">
         <v>8</v>
@@ -28657,7 +28657,7 @@
         <v>1.52999997138977</v>
       </c>
       <c r="G1088" t="n">
-        <v>1.19559299945831</v>
+        <v>1.1955931186676</v>
       </c>
       <c r="H1088" t="s">
         <v>8</v>
@@ -28683,7 +28683,7 @@
         <v>1.60959994792938</v>
       </c>
       <c r="G1089" t="n">
-        <v>1.25779509544373</v>
+        <v>1.25779521465302</v>
       </c>
       <c r="H1089" t="s">
         <v>8</v>
@@ -28735,7 +28735,7 @@
         <v>1.53519999980927</v>
       </c>
       <c r="G1091" t="n">
-        <v>1.19965660572052</v>
+        <v>1.19965648651123</v>
       </c>
       <c r="H1091" t="s">
         <v>8</v>
@@ -28787,7 +28787,7 @@
         <v>1.53840005397797</v>
       </c>
       <c r="G1093" t="n">
-        <v>1.20215713977814</v>
+        <v>1.20215725898743</v>
       </c>
       <c r="H1093" t="s">
         <v>8</v>
@@ -28839,7 +28839,7 @@
         <v>1.42999994754791</v>
       </c>
       <c r="G1095" t="n">
-        <v>1.11744976043701</v>
+        <v>1.1174498796463</v>
       </c>
       <c r="H1095" t="s">
         <v>8</v>
@@ -28943,7 +28943,7 @@
         <v>1.42980003356934</v>
       </c>
       <c r="G1099" t="n">
-        <v>1.11729347705841</v>
+        <v>1.1172935962677</v>
       </c>
       <c r="H1099" t="s">
         <v>8</v>
@@ -28969,7 +28969,7 @@
         <v>1.42980003356934</v>
       </c>
       <c r="G1100" t="n">
-        <v>1.11729347705841</v>
+        <v>1.1172935962677</v>
       </c>
       <c r="H1100" t="s">
         <v>8</v>
@@ -28995,7 +28995,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G1101" t="n">
-        <v>1.06274938583374</v>
+        <v>1.06274950504303</v>
       </c>
       <c r="H1101" t="s">
         <v>8</v>
@@ -29099,7 +29099,7 @@
         <v>1.3782000541687</v>
       </c>
       <c r="G1105" t="n">
-        <v>1.0769716501236</v>
+        <v>1.07697153091431</v>
       </c>
       <c r="H1105" t="s">
         <v>8</v>
@@ -29177,7 +29177,7 @@
         <v>1.30019998550415</v>
       </c>
       <c r="G1108" t="n">
-        <v>1.01601958274841</v>
+        <v>1.01601982116699</v>
       </c>
       <c r="H1108" t="s">
         <v>8</v>
@@ -29203,7 +29203,7 @@
         <v>1.26440000534058</v>
       </c>
       <c r="G1109" t="n">
-        <v>0.988044500350952</v>
+        <v>0.988044440746307</v>
       </c>
       <c r="H1109" t="s">
         <v>8</v>
@@ -29229,7 +29229,7 @@
         <v>1.25279998779297</v>
       </c>
       <c r="G1110" t="n">
-        <v>0.978979766368866</v>
+        <v>0.978979825973511</v>
       </c>
       <c r="H1110" t="s">
         <v>8</v>
@@ -29359,7 +29359,7 @@
         <v>1.25</v>
       </c>
       <c r="G1115" t="n">
-        <v>0.976791799068451</v>
+        <v>0.976791739463806</v>
       </c>
       <c r="H1115" t="s">
         <v>8</v>
@@ -29437,7 +29437,7 @@
         <v>1.31719994544983</v>
       </c>
       <c r="G1118" t="n">
-        <v>1.02930402755737</v>
+        <v>1.02930414676666</v>
       </c>
       <c r="H1118" t="s">
         <v>8</v>
@@ -29463,7 +29463,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G1119" t="n">
-        <v>1.0158634185791</v>
+        <v>1.01586353778839</v>
       </c>
       <c r="H1119" t="s">
         <v>8</v>
@@ -29489,7 +29489,7 @@
         <v>1.2791999578476</v>
       </c>
       <c r="G1120" t="n">
-        <v>0.999609649181366</v>
+        <v>0.999609529972076</v>
       </c>
       <c r="H1120" t="s">
         <v>8</v>
@@ -29515,7 +29515,7 @@
         <v>1.2771999835968</v>
       </c>
       <c r="G1121" t="n">
-        <v>0.998046815395355</v>
+        <v>0.998046875</v>
       </c>
       <c r="H1121" t="s">
         <v>8</v>
@@ -29541,7 +29541,7 @@
         <v>1.33940005302429</v>
       </c>
       <c r="G1122" t="n">
-        <v>1.04665184020996</v>
+        <v>1.04665195941925</v>
       </c>
       <c r="H1122" t="s">
         <v>8</v>
@@ -29567,7 +29567,7 @@
         <v>1.31359994411469</v>
       </c>
       <c r="G1123" t="n">
-        <v>1.02649080753326</v>
+        <v>1.02649092674255</v>
       </c>
       <c r="H1123" t="s">
         <v>8</v>
@@ -29645,7 +29645,7 @@
         <v>1.35979998111725</v>
       </c>
       <c r="G1126" t="n">
-        <v>1.06259298324585</v>
+        <v>1.06259322166443</v>
       </c>
       <c r="H1126" t="s">
         <v>8</v>
@@ -29749,7 +29749,7 @@
         <v>1.29579997062683</v>
       </c>
       <c r="G1130" t="n">
-        <v>1.01258134841919</v>
+        <v>1.01258146762848</v>
       </c>
       <c r="H1130" t="s">
         <v>8</v>
@@ -29775,7 +29775,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1131" t="n">
-        <v>1.00804913043976</v>
+        <v>1.00804901123047</v>
       </c>
       <c r="H1131" t="s">
         <v>8</v>
@@ -29801,7 +29801,7 @@
         <v>1.32280004024506</v>
       </c>
       <c r="G1132" t="n">
-        <v>1.03368008136749</v>
+        <v>1.03368020057678</v>
       </c>
       <c r="H1132" t="s">
         <v>8</v>
@@ -29827,7 +29827,7 @@
         <v>1.29820001125336</v>
       </c>
       <c r="G1133" t="n">
-        <v>1.01445686817169</v>
+        <v>1.0144567489624</v>
       </c>
       <c r="H1133" t="s">
         <v>8</v>
@@ -29931,7 +29931,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G1137" t="n">
-        <v>1.0158634185791</v>
+        <v>1.01586353778839</v>
       </c>
       <c r="H1137" t="s">
         <v>8</v>
@@ -30035,7 +30035,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1141" t="n">
-        <v>1.00804913043976</v>
+        <v>1.00804901123047</v>
       </c>
       <c r="H1141" t="s">
         <v>8</v>
@@ -30061,7 +30061,7 @@
         <v>1.29200005531311</v>
       </c>
       <c r="G1142" t="n">
-        <v>1.00961196422577</v>
+        <v>1.00961208343506</v>
       </c>
       <c r="H1142" t="s">
         <v>8</v>
@@ -30087,7 +30087,7 @@
         <v>1.30900001525879</v>
       </c>
       <c r="G1143" t="n">
-        <v>1.02289640903473</v>
+        <v>1.02289628982544</v>
       </c>
       <c r="H1143" t="s">
         <v>8</v>
@@ -30191,7 +30191,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1147" t="n">
-        <v>0.992420375347137</v>
+        <v>0.992420434951782</v>
       </c>
       <c r="H1147" t="s">
         <v>8</v>
@@ -30217,7 +30217,7 @@
         <v>1.26499998569489</v>
       </c>
       <c r="G1148" t="n">
-        <v>0.988513231277466</v>
+        <v>0.988513350486755</v>
       </c>
       <c r="H1148" t="s">
         <v>8</v>
@@ -30243,7 +30243,7 @@
         <v>1.26240003108978</v>
       </c>
       <c r="G1149" t="n">
-        <v>0.986481487751007</v>
+        <v>0.986481547355652</v>
       </c>
       <c r="H1149" t="s">
         <v>8</v>
@@ -30321,7 +30321,7 @@
         <v>1.29180002212524</v>
       </c>
       <c r="G1152" t="n">
-        <v>1.00945568084717</v>
+        <v>1.00945556163788</v>
       </c>
       <c r="H1152" t="s">
         <v>8</v>
@@ -30347,7 +30347,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1153" t="n">
-        <v>0.992420375347137</v>
+        <v>0.992420434951782</v>
       </c>
       <c r="H1153" t="s">
         <v>8</v>
@@ -30373,7 +30373,7 @@
         <v>1.25440001487732</v>
       </c>
       <c r="G1154" t="n">
-        <v>0.980230033397675</v>
+        <v>0.980230093002319</v>
       </c>
       <c r="H1154" t="s">
         <v>8</v>
@@ -30399,7 +30399,7 @@
         <v>1.28880000114441</v>
       </c>
       <c r="G1155" t="n">
-        <v>1.00711143016815</v>
+        <v>1.00711131095886</v>
       </c>
       <c r="H1155" t="s">
         <v>8</v>
@@ -30425,7 +30425,7 @@
         <v>1.26199996471405</v>
       </c>
       <c r="G1156" t="n">
-        <v>0.986168920993805</v>
+        <v>0.98616886138916</v>
       </c>
       <c r="H1156" t="s">
         <v>8</v>
@@ -30451,7 +30451,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G1157" t="n">
-        <v>1.02367770671844</v>
+        <v>1.02367758750916</v>
       </c>
       <c r="H1157" t="s">
         <v>8</v>
@@ -30503,7 +30503,7 @@
         <v>1.29499995708466</v>
       </c>
       <c r="G1159" t="n">
-        <v>1.0119560956955</v>
+        <v>1.01195621490479</v>
       </c>
       <c r="H1159" t="s">
         <v>8</v>
@@ -30529,7 +30529,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1160" t="n">
-        <v>1.00804913043976</v>
+        <v>1.00804901123047</v>
       </c>
       <c r="H1160" t="s">
         <v>8</v>
@@ -30555,7 +30555,7 @@
         <v>1.28939998149872</v>
       </c>
       <c r="G1161" t="n">
-        <v>1.00758028030396</v>
+        <v>1.00758039951324</v>
       </c>
       <c r="H1161" t="s">
         <v>8</v>
@@ -30581,7 +30581,7 @@
         <v>1.29980003833771</v>
       </c>
       <c r="G1162" t="n">
-        <v>1.0157071352005</v>
+        <v>1.01570725440979</v>
       </c>
       <c r="H1162" t="s">
         <v>8</v>
@@ -30633,7 +30633,7 @@
         <v>1.23099994659424</v>
       </c>
       <c r="G1164" t="n">
-        <v>0.96194452047348</v>
+        <v>0.961944460868835</v>
       </c>
       <c r="H1164" t="s">
         <v>8</v>
@@ -30659,7 +30659,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1165" t="n">
-        <v>0.992420375347137</v>
+        <v>0.992420434951782</v>
       </c>
       <c r="H1165" t="s">
         <v>8</v>
@@ -30685,7 +30685,7 @@
         <v>1.27900004386902</v>
       </c>
       <c r="G1166" t="n">
-        <v>0.999453365802765</v>
+        <v>0.999453246593475</v>
       </c>
       <c r="H1166" t="s">
         <v>8</v>
@@ -30711,7 +30711,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1167" t="n">
-        <v>0.992420375347137</v>
+        <v>0.992420434951782</v>
       </c>
       <c r="H1167" t="s">
         <v>8</v>
@@ -30763,7 +30763,7 @@
         <v>1.25</v>
       </c>
       <c r="G1169" t="n">
-        <v>0.976791799068451</v>
+        <v>0.976791739463806</v>
       </c>
       <c r="H1169" t="s">
         <v>8</v>
@@ -30789,7 +30789,7 @@
         <v>1.25</v>
       </c>
       <c r="G1170" t="n">
-        <v>0.976791799068451</v>
+        <v>0.976791739463806</v>
       </c>
       <c r="H1170" t="s">
         <v>8</v>
@@ -30815,7 +30815,7 @@
         <v>1.24339997768402</v>
       </c>
       <c r="G1171" t="n">
-        <v>0.971634328365326</v>
+        <v>0.971634268760681</v>
       </c>
       <c r="H1171" t="s">
         <v>8</v>
@@ -30841,7 +30841,7 @@
         <v>1.22060000896454</v>
       </c>
       <c r="G1172" t="n">
-        <v>0.953817486763</v>
+        <v>0.95381760597229</v>
       </c>
       <c r="H1172" t="s">
         <v>8</v>
@@ -30867,7 +30867,7 @@
         <v>1.22060000896454</v>
       </c>
       <c r="G1173" t="n">
-        <v>0.953817486763</v>
+        <v>0.95381760597229</v>
       </c>
       <c r="H1173" t="s">
         <v>8</v>
@@ -30893,7 +30893,7 @@
         <v>1.24979996681213</v>
       </c>
       <c r="G1174" t="n">
-        <v>0.976635456085205</v>
+        <v>0.97663551568985</v>
       </c>
       <c r="H1174" t="s">
         <v>8</v>
@@ -30919,7 +30919,7 @@
         <v>1.22200000286102</v>
       </c>
       <c r="G1175" t="n">
-        <v>0.954911589622498</v>
+        <v>0.954911708831787</v>
       </c>
       <c r="H1175" t="s">
         <v>8</v>
@@ -30945,7 +30945,7 @@
         <v>1.22019994258881</v>
       </c>
       <c r="G1176" t="n">
-        <v>0.953504920005798</v>
+        <v>0.953505039215088</v>
       </c>
       <c r="H1176" t="s">
         <v>8</v>
@@ -30997,7 +30997,7 @@
         <v>1.23479998111725</v>
       </c>
       <c r="G1178" t="n">
-        <v>0.96491402387619</v>
+        <v>0.964913904666901</v>
       </c>
       <c r="H1178" t="s">
         <v>8</v>
@@ -31023,7 +31023,7 @@
         <v>1.21700000762939</v>
       </c>
       <c r="G1179" t="n">
-        <v>0.951004445552826</v>
+        <v>0.951004505157471</v>
       </c>
       <c r="H1179" t="s">
         <v>8</v>
@@ -31049,7 +31049,7 @@
         <v>1.19500005245209</v>
       </c>
       <c r="G1180" t="n">
-        <v>0.933812975883484</v>
+        <v>0.933812856674194</v>
       </c>
       <c r="H1180" t="s">
         <v>8</v>
@@ -31101,7 +31101,7 @@
         <v>1.24399995803833</v>
       </c>
       <c r="G1182" t="n">
-        <v>0.972103238105774</v>
+        <v>0.97210305929184</v>
       </c>
       <c r="H1182" t="s">
         <v>8</v>
@@ -31127,7 +31127,7 @@
         <v>1.24399995803833</v>
       </c>
       <c r="G1183" t="n">
-        <v>0.972103238105774</v>
+        <v>0.97210305929184</v>
       </c>
       <c r="H1183" t="s">
         <v>8</v>
@@ -31153,7 +31153,7 @@
         <v>1.20860004425049</v>
       </c>
       <c r="G1184" t="n">
-        <v>0.944440424442291</v>
+        <v>0.944440364837646</v>
       </c>
       <c r="H1184" t="s">
         <v>8</v>
@@ -31179,7 +31179,7 @@
         <v>1.20500004291534</v>
       </c>
       <c r="G1185" t="n">
-        <v>0.941627383232117</v>
+        <v>0.941627323627472</v>
       </c>
       <c r="H1185" t="s">
         <v>8</v>
@@ -31205,7 +31205,7 @@
         <v>1.20899999141693</v>
       </c>
       <c r="G1186" t="n">
-        <v>0.944752991199493</v>
+        <v>0.944752931594849</v>
       </c>
       <c r="H1186" t="s">
         <v>8</v>
@@ -31257,7 +31257,7 @@
         <v>1.20019996166229</v>
       </c>
       <c r="G1188" t="n">
-        <v>0.937876224517822</v>
+        <v>0.937876343727112</v>
       </c>
       <c r="H1188" t="s">
         <v>8</v>
@@ -31283,7 +31283,7 @@
         <v>1.22019994258881</v>
       </c>
       <c r="G1189" t="n">
-        <v>0.953504920005798</v>
+        <v>0.953505039215088</v>
       </c>
       <c r="H1189" t="s">
         <v>8</v>
@@ -31309,7 +31309,7 @@
         <v>1.26979994773865</v>
       </c>
       <c r="G1190" t="n">
-        <v>0.992264151573181</v>
+        <v>0.992264091968536</v>
       </c>
       <c r="H1190" t="s">
         <v>8</v>
@@ -31335,7 +31335,7 @@
         <v>1.23959994316101</v>
       </c>
       <c r="G1191" t="n">
-        <v>0.968664824962616</v>
+        <v>0.968664705753326</v>
       </c>
       <c r="H1191" t="s">
         <v>8</v>
@@ -31361,7 +31361,7 @@
         <v>1.24979996681213</v>
       </c>
       <c r="G1192" t="n">
-        <v>0.976635456085205</v>
+        <v>0.97663551568985</v>
       </c>
       <c r="H1192" t="s">
         <v>8</v>
@@ -31387,7 +31387,7 @@
         <v>1.21319997310638</v>
       </c>
       <c r="G1193" t="n">
-        <v>0.948034942150116</v>
+        <v>0.948034882545471</v>
       </c>
       <c r="H1193" t="s">
         <v>8</v>
@@ -31413,7 +31413,7 @@
         <v>1.22800004482269</v>
       </c>
       <c r="G1194" t="n">
-        <v>0.959600269794464</v>
+        <v>0.959600210189819</v>
       </c>
       <c r="H1194" t="s">
         <v>8</v>
@@ -31465,7 +31465,7 @@
         <v>1.24199998378754</v>
       </c>
       <c r="G1196" t="n">
-        <v>0.970540225505829</v>
+        <v>0.970540285110474</v>
       </c>
       <c r="H1196" t="s">
         <v>8</v>
@@ -31491,7 +31491,7 @@
         <v>1.24399995803833</v>
       </c>
       <c r="G1197" t="n">
-        <v>0.972103238105774</v>
+        <v>0.97210305929184</v>
       </c>
       <c r="H1197" t="s">
         <v>8</v>
@@ -31517,7 +31517,7 @@
         <v>1.23979997634888</v>
       </c>
       <c r="G1198" t="n">
-        <v>0.968821287155151</v>
+        <v>0.968821108341217</v>
       </c>
       <c r="H1198" t="s">
         <v>8</v>
@@ -31543,7 +31543,7 @@
         <v>1.23979997634888</v>
       </c>
       <c r="G1199" t="n">
-        <v>0.968821287155151</v>
+        <v>0.968821108341217</v>
       </c>
       <c r="H1199" t="s">
         <v>8</v>
@@ -31569,7 +31569,7 @@
         <v>1.19120001792908</v>
       </c>
       <c r="G1200" t="n">
-        <v>0.930843591690063</v>
+        <v>0.930843532085419</v>
       </c>
       <c r="H1200" t="s">
         <v>8</v>
@@ -31595,7 +31595,7 @@
         <v>1.19120001792908</v>
       </c>
       <c r="G1201" t="n">
-        <v>0.930843591690063</v>
+        <v>0.930843532085419</v>
       </c>
       <c r="H1201" t="s">
         <v>8</v>
@@ -31621,7 +31621,7 @@
         <v>1.22940003871918</v>
       </c>
       <c r="G1202" t="n">
-        <v>0.960694253444672</v>
+        <v>0.960694313049316</v>
       </c>
       <c r="H1202" t="s">
         <v>8</v>
@@ -31673,7 +31673,7 @@
         <v>1.22979998588562</v>
       </c>
       <c r="G1204" t="n">
-        <v>0.961006641387939</v>
+        <v>0.961006760597229</v>
       </c>
       <c r="H1204" t="s">
         <v>8</v>
@@ -31699,7 +31699,7 @@
         <v>1.24199998378754</v>
       </c>
       <c r="G1205" t="n">
-        <v>0.970540225505829</v>
+        <v>0.970540285110474</v>
       </c>
       <c r="H1205" t="s">
         <v>8</v>
@@ -31725,7 +31725,7 @@
         <v>1.2117999792099</v>
       </c>
       <c r="G1206" t="n">
-        <v>0.946940958499908</v>
+        <v>0.946940898895264</v>
       </c>
       <c r="H1206" t="s">
         <v>8</v>
@@ -31777,7 +31777,7 @@
         <v>1.19500005245209</v>
       </c>
       <c r="G1208" t="n">
-        <v>0.933812975883484</v>
+        <v>0.933812856674194</v>
       </c>
       <c r="H1208" t="s">
         <v>8</v>
@@ -31803,7 +31803,7 @@
         <v>1.19500005245209</v>
       </c>
       <c r="G1209" t="n">
-        <v>0.933812975883484</v>
+        <v>0.933812856674194</v>
       </c>
       <c r="H1209" t="s">
         <v>8</v>
@@ -31829,7 +31829,7 @@
         <v>1.19900000095367</v>
       </c>
       <c r="G1210" t="n">
-        <v>0.936938583850861</v>
+        <v>0.93693870306015</v>
       </c>
       <c r="H1210" t="s">
         <v>8</v>
@@ -31907,7 +31907,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1213" t="n">
-        <v>1.00804913043976</v>
+        <v>1.00804901123047</v>
       </c>
       <c r="H1213" t="s">
         <v>8</v>
@@ -31933,7 +31933,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G1214" t="n">
-        <v>1.02367770671844</v>
+        <v>1.02367758750916</v>
       </c>
       <c r="H1214" t="s">
         <v>8</v>
@@ -31959,7 +31959,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1215" t="n">
-        <v>0.984606206417084</v>
+        <v>0.984606087207794</v>
       </c>
       <c r="H1215" t="s">
         <v>8</v>
@@ -32011,7 +32011,7 @@
         <v>1.26540005207062</v>
       </c>
       <c r="G1217" t="n">
-        <v>0.988825798034668</v>
+        <v>0.988825738430023</v>
       </c>
       <c r="H1217" t="s">
         <v>8</v>
@@ -32037,7 +32037,7 @@
         <v>1.24020004272461</v>
       </c>
       <c r="G1218" t="n">
-        <v>0.969133734703064</v>
+        <v>0.969133853912354</v>
       </c>
       <c r="H1218" t="s">
         <v>8</v>
@@ -32063,7 +32063,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1219" t="n">
-        <v>1.00804913043976</v>
+        <v>1.00804901123047</v>
       </c>
       <c r="H1219" t="s">
         <v>8</v>
@@ -32089,7 +32089,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G1220" t="n">
-        <v>1.0158634185791</v>
+        <v>1.01586353778839</v>
       </c>
       <c r="H1220" t="s">
         <v>8</v>
@@ -32115,7 +32115,7 @@
         <v>1.25539994239807</v>
       </c>
       <c r="G1221" t="n">
-        <v>0.981011390686035</v>
+        <v>0.981011509895325</v>
       </c>
       <c r="H1221" t="s">
         <v>8</v>
@@ -32141,7 +32141,7 @@
         <v>1.22599995136261</v>
       </c>
       <c r="G1222" t="n">
-        <v>0.958037376403809</v>
+        <v>0.958037316799164</v>
       </c>
       <c r="H1222" t="s">
         <v>8</v>
@@ -32167,7 +32167,7 @@
         <v>1.22599995136261</v>
       </c>
       <c r="G1223" t="n">
-        <v>0.958037376403809</v>
+        <v>0.958037316799164</v>
       </c>
       <c r="H1223" t="s">
         <v>8</v>
@@ -32193,7 +32193,7 @@
         <v>1.22599995136261</v>
       </c>
       <c r="G1224" t="n">
-        <v>0.958037376403809</v>
+        <v>0.958037316799164</v>
       </c>
       <c r="H1224" t="s">
         <v>8</v>
@@ -32245,7 +32245,7 @@
         <v>1.25</v>
       </c>
       <c r="G1226" t="n">
-        <v>0.976791799068451</v>
+        <v>0.976791739463806</v>
       </c>
       <c r="H1226" t="s">
         <v>8</v>
@@ -32297,7 +32297,7 @@
         <v>1.17519998550415</v>
       </c>
       <c r="G1228" t="n">
-        <v>0.918340563774109</v>
+        <v>0.918340504169464</v>
       </c>
       <c r="H1228" t="s">
         <v>8</v>
@@ -32323,7 +32323,7 @@
         <v>1.192999958992</v>
       </c>
       <c r="G1229" t="n">
-        <v>0.932249963283539</v>
+        <v>0.932250082492828</v>
       </c>
       <c r="H1229" t="s">
         <v>8</v>
@@ -32349,7 +32349,7 @@
         <v>1.18219995498657</v>
       </c>
       <c r="G1230" t="n">
-        <v>0.923810482025146</v>
+        <v>0.923810541629791</v>
       </c>
       <c r="H1230" t="s">
         <v>8</v>
@@ -32375,7 +32375,7 @@
         <v>1.18219995498657</v>
       </c>
       <c r="G1231" t="n">
-        <v>0.923810482025146</v>
+        <v>0.923810541629791</v>
       </c>
       <c r="H1231" t="s">
         <v>8</v>
@@ -32401,7 +32401,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G1232" t="n">
-        <v>0.961162984371185</v>
+        <v>0.96116304397583</v>
       </c>
       <c r="H1232" t="s">
         <v>8</v>
@@ -32427,7 +32427,7 @@
         <v>1.19159996509552</v>
       </c>
       <c r="G1233" t="n">
-        <v>0.931156098842621</v>
+        <v>0.931155979633331</v>
       </c>
       <c r="H1233" t="s">
         <v>8</v>
@@ -32453,7 +32453,7 @@
         <v>1.19099998474121</v>
       </c>
       <c r="G1234" t="n">
-        <v>0.930687189102173</v>
+        <v>0.930687129497528</v>
       </c>
       <c r="H1234" t="s">
         <v>8</v>
@@ -32479,7 +32479,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G1235" t="n">
-        <v>0.961162984371185</v>
+        <v>0.96116304397583</v>
       </c>
       <c r="H1235" t="s">
         <v>8</v>
@@ -32505,7 +32505,7 @@
         <v>1.19799995422363</v>
       </c>
       <c r="G1236" t="n">
-        <v>0.936157166957855</v>
+        <v>0.93615710735321</v>
       </c>
       <c r="H1236" t="s">
         <v>8</v>
@@ -32583,7 +32583,7 @@
         <v>1.26800000667572</v>
       </c>
       <c r="G1239" t="n">
-        <v>0.990857481956482</v>
+        <v>0.990857660770416</v>
       </c>
       <c r="H1239" t="s">
         <v>8</v>
@@ -32635,7 +32635,7 @@
         <v>1.27320003509521</v>
       </c>
       <c r="G1241" t="n">
-        <v>0.994921088218689</v>
+        <v>0.994920969009399</v>
       </c>
       <c r="H1241" t="s">
         <v>8</v>
@@ -32661,7 +32661,7 @@
         <v>1.27320003509521</v>
       </c>
       <c r="G1242" t="n">
-        <v>0.994921088218689</v>
+        <v>0.994920969009399</v>
       </c>
       <c r="H1242" t="s">
         <v>8</v>
@@ -32713,7 +32713,7 @@
         <v>1.26639997959137</v>
       </c>
       <c r="G1244" t="n">
-        <v>0.989607214927673</v>
+        <v>0.989607334136963</v>
       </c>
       <c r="H1244" t="s">
         <v>8</v>
@@ -32791,7 +32791,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G1247" t="n">
-        <v>1.24247908592224</v>
+        <v>1.24247920513153</v>
       </c>
       <c r="H1247" t="s">
         <v>8</v>
@@ -32843,7 +32843,7 @@
         <v>1.59200000762939</v>
       </c>
       <c r="G1249" t="n">
-        <v>1.24404191970825</v>
+        <v>1.24404203891754</v>
       </c>
       <c r="H1249" t="s">
         <v>8</v>
@@ -32869,7 +32869,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G1250" t="n">
-        <v>1.3362512588501</v>
+        <v>1.33625113964081</v>
       </c>
       <c r="H1250" t="s">
         <v>8</v>
@@ -32895,7 +32895,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G1251" t="n">
-        <v>1.31280815601349</v>
+        <v>1.3128080368042</v>
       </c>
       <c r="H1251" t="s">
         <v>8</v>
@@ -32921,7 +32921,7 @@
         <v>1.67980003356934</v>
       </c>
       <c r="G1252" t="n">
-        <v>1.31265199184418</v>
+        <v>1.3126517534256</v>
       </c>
       <c r="H1252" t="s">
         <v>8</v>
@@ -32947,7 +32947,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G1253" t="n">
-        <v>1.31280815601349</v>
+        <v>1.3128080368042</v>
       </c>
       <c r="H1253" t="s">
         <v>8</v>
@@ -32999,7 +32999,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G1255" t="n">
-        <v>1.31280815601349</v>
+        <v>1.3128080368042</v>
       </c>
       <c r="H1255" t="s">
         <v>8</v>
@@ -33025,7 +33025,7 @@
         <v>1.72060000896454</v>
       </c>
       <c r="G1256" t="n">
-        <v>1.34453439712524</v>
+        <v>1.34453427791595</v>
       </c>
       <c r="H1256" t="s">
         <v>8</v>
@@ -33285,7 +33285,7 @@
         <v>1.72940003871918</v>
       </c>
       <c r="G1266" t="n">
-        <v>1.35141086578369</v>
+        <v>1.35141098499298</v>
       </c>
       <c r="H1266" t="s">
         <v>8</v>
@@ -33337,7 +33337,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G1268" t="n">
-        <v>1.45658135414124</v>
+        <v>1.45658147335052</v>
       </c>
       <c r="H1268" t="s">
         <v>8</v>
@@ -33363,7 +33363,7 @@
         <v>1.74979996681213</v>
       </c>
       <c r="G1269" t="n">
-        <v>1.46478497982025</v>
+        <v>1.46478509902954</v>
       </c>
       <c r="H1269" t="s">
         <v>8</v>
@@ -33389,7 +33389,7 @@
         <v>1.73800003528595</v>
       </c>
       <c r="G1270" t="n">
-        <v>1.45490717887878</v>
+        <v>1.45490729808807</v>
       </c>
       <c r="H1270" t="s">
         <v>8</v>
@@ -33415,7 +33415,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G1271" t="n">
-        <v>1.45658135414124</v>
+        <v>1.45658147335052</v>
       </c>
       <c r="H1271" t="s">
         <v>8</v>
@@ -33441,7 +33441,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G1272" t="n">
-        <v>1.43983912467957</v>
+        <v>1.43983924388885</v>
       </c>
       <c r="H1272" t="s">
         <v>8</v>
@@ -33467,7 +33467,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G1273" t="n">
-        <v>1.43983912467957</v>
+        <v>1.43983924388885</v>
       </c>
       <c r="H1273" t="s">
         <v>8</v>
@@ -33493,7 +33493,7 @@
         <v>1.69459998607635</v>
       </c>
       <c r="G1274" t="n">
-        <v>1.41857624053955</v>
+        <v>1.41857635974884</v>
       </c>
       <c r="H1274" t="s">
         <v>8</v>
@@ -33519,7 +33519,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G1275" t="n">
-        <v>1.43983912467957</v>
+        <v>1.43983924388885</v>
       </c>
       <c r="H1275" t="s">
         <v>8</v>
@@ -33597,7 +33597,7 @@
         <v>1.68599998950958</v>
       </c>
       <c r="G1278" t="n">
-        <v>1.41137707233429</v>
+        <v>1.41137719154358</v>
       </c>
       <c r="H1278" t="s">
         <v>8</v>
@@ -33805,7 +33805,7 @@
         <v>1.60060000419617</v>
       </c>
       <c r="G1286" t="n">
-        <v>1.33988749980927</v>
+        <v>1.33988761901855</v>
       </c>
       <c r="H1286" t="s">
         <v>8</v>
@@ -33883,7 +33883,7 @@
         <v>1.62999999523163</v>
       </c>
       <c r="G1289" t="n">
-        <v>1.36449861526489</v>
+        <v>1.3644984960556</v>
       </c>
       <c r="H1289" t="s">
         <v>8</v>
@@ -33935,7 +33935,7 @@
         <v>1.6418000459671</v>
       </c>
       <c r="G1291" t="n">
-        <v>1.37437665462494</v>
+        <v>1.37437677383423</v>
       </c>
       <c r="H1291" t="s">
         <v>8</v>
@@ -34117,7 +34117,7 @@
         <v>1.75419998168945</v>
       </c>
       <c r="G1298" t="n">
-        <v>1.46846830844879</v>
+        <v>1.46846842765808</v>
       </c>
       <c r="H1298" t="s">
         <v>8</v>
@@ -34143,7 +34143,7 @@
         <v>1.77939999103546</v>
       </c>
       <c r="G1299" t="n">
-        <v>1.48956370353699</v>
+        <v>1.48956382274628</v>
       </c>
       <c r="H1299" t="s">
         <v>8</v>
@@ -34195,7 +34195,7 @@
         <v>1.80540001392365</v>
       </c>
       <c r="G1301" t="n">
-        <v>1.51132869720459</v>
+        <v>1.51132881641388</v>
       </c>
       <c r="H1301" t="s">
         <v>8</v>
@@ -34273,7 +34273,7 @@
         <v>1.74399995803833</v>
       </c>
       <c r="G1304" t="n">
-        <v>1.45992982387543</v>
+        <v>1.45992970466614</v>
       </c>
       <c r="H1304" t="s">
         <v>8</v>
@@ -34533,7 +34533,7 @@
         <v>1.86160004138947</v>
       </c>
       <c r="G1314" t="n">
-        <v>1.5583747625351</v>
+        <v>1.55837464332581</v>
       </c>
       <c r="H1314" t="s">
         <v>8</v>
@@ -34559,7 +34559,7 @@
         <v>1.84019994735718</v>
       </c>
       <c r="G1315" t="n">
-        <v>1.54046046733856</v>
+        <v>1.54046034812927</v>
       </c>
       <c r="H1315" t="s">
         <v>8</v>
@@ -34637,7 +34637,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G1318" t="n">
-        <v>1.62400460243225</v>
+        <v>1.62400448322296</v>
       </c>
       <c r="H1318" t="s">
         <v>8</v>
@@ -34663,7 +34663,7 @@
         <v>1.97979998588562</v>
       </c>
       <c r="G1319" t="n">
-        <v>1.65732181072235</v>
+        <v>1.65732169151306</v>
       </c>
       <c r="H1319" t="s">
         <v>8</v>
@@ -34715,7 +34715,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G1321" t="n">
-        <v>1.65748929977417</v>
+        <v>1.65748918056488</v>
       </c>
       <c r="H1321" t="s">
         <v>8</v>
@@ -34819,7 +34819,7 @@
         <v>1.92120003700256</v>
       </c>
       <c r="G1325" t="n">
-        <v>1.60826683044434</v>
+        <v>1.60826671123505</v>
       </c>
       <c r="H1325" t="s">
         <v>8</v>
@@ -34923,7 +34923,7 @@
         <v>1.95959997177124</v>
       </c>
       <c r="G1329" t="n">
-        <v>1.64041197299957</v>
+        <v>1.64041185379028</v>
       </c>
       <c r="H1329" t="s">
         <v>8</v>
@@ -34975,7 +34975,7 @@
         <v>1.91620004177094</v>
       </c>
       <c r="G1331" t="n">
-        <v>1.60408115386963</v>
+        <v>1.60408127307892</v>
       </c>
       <c r="H1331" t="s">
         <v>8</v>
@@ -35027,7 +35027,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G1333" t="n">
-        <v>1.6323755979538</v>
+        <v>1.63237583637238</v>
       </c>
       <c r="H1333" t="s">
         <v>8</v>
@@ -35053,7 +35053,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G1334" t="n">
-        <v>1.6323755979538</v>
+        <v>1.63237583637238</v>
       </c>
       <c r="H1334" t="s">
         <v>8</v>
@@ -35079,7 +35079,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G1335" t="n">
-        <v>1.6323755979538</v>
+        <v>1.63237583637238</v>
       </c>
       <c r="H1335" t="s">
         <v>8</v>
@@ -35183,7 +35183,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G1339" t="n">
-        <v>1.607262134552</v>
+        <v>1.60726201534271</v>
       </c>
       <c r="H1339" t="s">
         <v>8</v>
@@ -35209,7 +35209,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G1340" t="n">
-        <v>1.607262134552</v>
+        <v>1.60726201534271</v>
       </c>
       <c r="H1340" t="s">
         <v>8</v>
@@ -35235,7 +35235,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G1341" t="n">
-        <v>1.607262134552</v>
+        <v>1.60726201534271</v>
       </c>
       <c r="H1341" t="s">
         <v>8</v>
@@ -35287,7 +35287,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G1343" t="n">
-        <v>1.607262134552</v>
+        <v>1.60726201534271</v>
       </c>
       <c r="H1343" t="s">
         <v>8</v>
@@ -35313,7 +35313,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G1344" t="n">
-        <v>1.69097375869751</v>
+        <v>1.69097363948822</v>
       </c>
       <c r="H1344" t="s">
         <v>8</v>
@@ -35339,7 +35339,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G1345" t="n">
-        <v>1.65748929977417</v>
+        <v>1.65748918056488</v>
       </c>
       <c r="H1345" t="s">
         <v>8</v>
@@ -35391,7 +35391,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G1347" t="n">
-        <v>1.69097375869751</v>
+        <v>1.69097363948822</v>
       </c>
       <c r="H1347" t="s">
         <v>8</v>
@@ -35443,7 +35443,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G1349" t="n">
-        <v>1.65748929977417</v>
+        <v>1.65748918056488</v>
       </c>
       <c r="H1349" t="s">
         <v>8</v>
@@ -35469,7 +35469,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G1350" t="n">
-        <v>1.607262134552</v>
+        <v>1.60726201534271</v>
       </c>
       <c r="H1350" t="s">
         <v>8</v>
@@ -35599,7 +35599,7 @@
         <v>1.89499998092651</v>
       </c>
       <c r="G1355" t="n">
-        <v>1.58633422851562</v>
+        <v>1.5863344669342</v>
       </c>
       <c r="H1355" t="s">
         <v>8</v>
@@ -35651,7 +35651,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G1357" t="n">
-        <v>1.5570353269577</v>
+        <v>1.55703520774841</v>
       </c>
       <c r="H1357" t="s">
         <v>8</v>
@@ -35755,7 +35755,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G1361" t="n">
-        <v>1.607262134552</v>
+        <v>1.60726201534271</v>
       </c>
       <c r="H1361" t="s">
         <v>8</v>
@@ -35963,7 +35963,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G1369" t="n">
-        <v>1.5570353269577</v>
+        <v>1.55703520774841</v>
       </c>
       <c r="H1369" t="s">
         <v>8</v>
@@ -35989,7 +35989,7 @@
         <v>1.89499998092651</v>
       </c>
       <c r="G1370" t="n">
-        <v>1.58633422851562</v>
+        <v>1.5863344669342</v>
       </c>
       <c r="H1370" t="s">
         <v>8</v>
@@ -36015,7 +36015,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G1371" t="n">
-        <v>1.5570353269577</v>
+        <v>1.55703520774841</v>
       </c>
       <c r="H1371" t="s">
         <v>8</v>
@@ -36067,7 +36067,7 @@
         <v>1.83500003814697</v>
       </c>
       <c r="G1373" t="n">
-        <v>1.53610730171204</v>
+        <v>1.53610754013062</v>
       </c>
       <c r="H1373" t="s">
         <v>8</v>
@@ -36093,7 +36093,7 @@
         <v>1.89499998092651</v>
       </c>
       <c r="G1374" t="n">
-        <v>1.58633422851562</v>
+        <v>1.5863344669342</v>
       </c>
       <c r="H1374" t="s">
         <v>8</v>
@@ -36119,7 +36119,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G1375" t="n">
-        <v>1.5570353269577</v>
+        <v>1.55703520774841</v>
       </c>
       <c r="H1375" t="s">
         <v>8</v>
@@ -36171,7 +36171,7 @@
         <v>1.86500000953674</v>
       </c>
       <c r="G1377" t="n">
-        <v>1.56122076511383</v>
+        <v>1.56122088432312</v>
       </c>
       <c r="H1377" t="s">
         <v>8</v>
@@ -36197,7 +36197,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G1378" t="n">
-        <v>1.82491254806519</v>
+        <v>1.82491230964661</v>
       </c>
       <c r="H1378" t="s">
         <v>8</v>
@@ -36223,7 +36223,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G1379" t="n">
-        <v>1.89188170433044</v>
+        <v>1.89188158512115</v>
       </c>
       <c r="H1379" t="s">
         <v>8</v>
@@ -36249,7 +36249,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1380" t="n">
-        <v>1.80817008018494</v>
+        <v>1.80817019939423</v>
       </c>
       <c r="H1380" t="s">
         <v>8</v>
@@ -36275,7 +36275,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G1381" t="n">
-        <v>1.90862369537354</v>
+        <v>1.90862381458282</v>
       </c>
       <c r="H1381" t="s">
         <v>8</v>
@@ -36301,7 +36301,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G1382" t="n">
-        <v>1.85839688777924</v>
+        <v>1.85839712619781</v>
       </c>
       <c r="H1382" t="s">
         <v>8</v>
@@ -36327,7 +36327,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G1383" t="n">
-        <v>1.87513935565948</v>
+        <v>1.87513911724091</v>
       </c>
       <c r="H1383" t="s">
         <v>8</v>
@@ -36379,7 +36379,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G1385" t="n">
-        <v>1.85839688777924</v>
+        <v>1.85839712619781</v>
       </c>
       <c r="H1385" t="s">
         <v>8</v>
@@ -36405,7 +36405,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G1386" t="n">
-        <v>1.85839688777924</v>
+        <v>1.85839712619781</v>
       </c>
       <c r="H1386" t="s">
         <v>8</v>
@@ -36457,7 +36457,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G1388" t="n">
-        <v>1.81654107570648</v>
+        <v>1.81654131412506</v>
       </c>
       <c r="H1388" t="s">
         <v>8</v>
@@ -36483,7 +36483,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G1389" t="n">
-        <v>1.78305661678314</v>
+        <v>1.78305649757385</v>
       </c>
       <c r="H1389" t="s">
         <v>8</v>
@@ -36509,7 +36509,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G1390" t="n">
-        <v>1.82491254806519</v>
+        <v>1.82491230964661</v>
       </c>
       <c r="H1390" t="s">
         <v>8</v>
@@ -36535,7 +36535,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1391" t="n">
-        <v>1.80817008018494</v>
+        <v>1.80817019939423</v>
       </c>
       <c r="H1391" t="s">
         <v>8</v>
@@ -36587,7 +36587,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1393" t="n">
-        <v>1.80817008018494</v>
+        <v>1.80817019939423</v>
       </c>
       <c r="H1393" t="s">
         <v>8</v>
@@ -36613,7 +36613,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G1394" t="n">
-        <v>1.78305661678314</v>
+        <v>1.78305649757385</v>
       </c>
       <c r="H1394" t="s">
         <v>8</v>
@@ -36639,7 +36639,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G1395" t="n">
-        <v>1.79142773151398</v>
+        <v>1.79142785072327</v>
       </c>
       <c r="H1395" t="s">
         <v>8</v>
@@ -36665,7 +36665,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1396" t="n">
-        <v>1.75794291496277</v>
+        <v>1.75794279575348</v>
       </c>
       <c r="H1396" t="s">
         <v>8</v>
@@ -36691,7 +36691,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1397" t="n">
-        <v>1.75794291496277</v>
+        <v>1.75794279575348</v>
       </c>
       <c r="H1397" t="s">
         <v>8</v>
@@ -36743,7 +36743,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1399" t="n">
-        <v>1.75794291496277</v>
+        <v>1.75794279575348</v>
       </c>
       <c r="H1399" t="s">
         <v>8</v>
@@ -36769,7 +36769,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G1400" t="n">
-        <v>1.74120056629181</v>
+        <v>1.7412006855011</v>
       </c>
       <c r="H1400" t="s">
         <v>8</v>
@@ -36795,7 +36795,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G1401" t="n">
-        <v>1.74120056629181</v>
+        <v>1.7412006855011</v>
       </c>
       <c r="H1401" t="s">
         <v>8</v>
@@ -36821,7 +36821,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G1402" t="n">
-        <v>1.7160872220993</v>
+        <v>1.71608710289001</v>
       </c>
       <c r="H1402" t="s">
         <v>8</v>
@@ -36873,7 +36873,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G1404" t="n">
-        <v>1.69934475421906</v>
+        <v>1.69934487342834</v>
       </c>
       <c r="H1404" t="s">
         <v>8</v>
@@ -36899,7 +36899,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G1405" t="n">
-        <v>1.74957191944122</v>
+        <v>1.74957180023193</v>
       </c>
       <c r="H1405" t="s">
         <v>8</v>
@@ -36951,7 +36951,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G1407" t="n">
-        <v>1.7160872220993</v>
+        <v>1.71608710289001</v>
       </c>
       <c r="H1407" t="s">
         <v>8</v>
@@ -36977,7 +36977,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G1408" t="n">
-        <v>1.70771622657776</v>
+        <v>1.70771610736847</v>
       </c>
       <c r="H1408" t="s">
         <v>8</v>
@@ -37003,7 +37003,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G1409" t="n">
-        <v>1.6323755979538</v>
+        <v>1.63237583637238</v>
       </c>
       <c r="H1409" t="s">
         <v>8</v>
@@ -37029,7 +37029,7 @@
         <v>1.9650000333786</v>
       </c>
       <c r="G1410" t="n">
-        <v>1.64493238925934</v>
+        <v>1.64493250846863</v>
       </c>
       <c r="H1410" t="s">
         <v>8</v>
@@ -37055,7 +37055,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G1411" t="n">
-        <v>1.70771622657776</v>
+        <v>1.70771610736847</v>
       </c>
       <c r="H1411" t="s">
         <v>8</v>
@@ -37081,7 +37081,7 @@
         <v>1.98500001430511</v>
       </c>
       <c r="G1412" t="n">
-        <v>1.66167485713959</v>
+        <v>1.6616747379303</v>
       </c>
       <c r="H1412" t="s">
         <v>8</v>
@@ -37133,7 +37133,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G1414" t="n">
-        <v>1.69934475421906</v>
+        <v>1.69934487342834</v>
       </c>
       <c r="H1414" t="s">
         <v>8</v>
@@ -37159,7 +37159,7 @@
         <v>1.99500000476837</v>
       </c>
       <c r="G1415" t="n">
-        <v>1.67004585266113</v>
+        <v>1.67004597187042</v>
       </c>
       <c r="H1415" t="s">
         <v>8</v>
@@ -37185,7 +37185,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G1416" t="n">
-        <v>1.65748929977417</v>
+        <v>1.65748918056488</v>
       </c>
       <c r="H1416" t="s">
         <v>8</v>
@@ -37211,7 +37211,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G1417" t="n">
-        <v>1.69097375869751</v>
+        <v>1.69097363948822</v>
       </c>
       <c r="H1417" t="s">
         <v>8</v>
@@ -37263,7 +37263,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G1419" t="n">
-        <v>1.77468538284302</v>
+        <v>1.77468526363373</v>
       </c>
       <c r="H1419" t="s">
         <v>8</v>
@@ -37315,7 +37315,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1421" t="n">
-        <v>1.80817008018494</v>
+        <v>1.80817019939423</v>
       </c>
       <c r="H1421" t="s">
         <v>8</v>
@@ -37341,7 +37341,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G1422" t="n">
-        <v>1.7997989654541</v>
+        <v>1.79979884624481</v>
       </c>
       <c r="H1422" t="s">
         <v>8</v>
@@ -37367,7 +37367,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G1423" t="n">
-        <v>1.81654107570648</v>
+        <v>1.81654131412506</v>
       </c>
       <c r="H1423" t="s">
         <v>8</v>
@@ -37393,7 +37393,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G1424" t="n">
-        <v>1.81654107570648</v>
+        <v>1.81654131412506</v>
       </c>
       <c r="H1424" t="s">
         <v>8</v>
@@ -37419,7 +37419,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G1425" t="n">
-        <v>1.81654107570648</v>
+        <v>1.81654131412506</v>
       </c>
       <c r="H1425" t="s">
         <v>8</v>
@@ -37445,7 +37445,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G1426" t="n">
-        <v>1.83328366279602</v>
+        <v>1.83328354358673</v>
       </c>
       <c r="H1426" t="s">
         <v>8</v>
@@ -37471,7 +37471,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G1427" t="n">
-        <v>1.85839688777924</v>
+        <v>1.85839712619781</v>
       </c>
       <c r="H1427" t="s">
         <v>8</v>
@@ -37497,7 +37497,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G1428" t="n">
-        <v>1.85839688777924</v>
+        <v>1.85839712619781</v>
       </c>
       <c r="H1428" t="s">
         <v>8</v>
@@ -37523,7 +37523,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G1429" t="n">
-        <v>1.85839688777924</v>
+        <v>1.85839712619781</v>
       </c>
       <c r="H1429" t="s">
         <v>8</v>
@@ -37549,7 +37549,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G1430" t="n">
-        <v>1.83328366279602</v>
+        <v>1.83328354358673</v>
       </c>
       <c r="H1430" t="s">
         <v>8</v>
@@ -37601,7 +37601,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G1432" t="n">
-        <v>1.78305661678314</v>
+        <v>1.78305649757385</v>
       </c>
       <c r="H1432" t="s">
         <v>8</v>
@@ -37627,7 +37627,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G1433" t="n">
-        <v>1.79142773151398</v>
+        <v>1.79142785072327</v>
       </c>
       <c r="H1433" t="s">
         <v>8</v>
@@ -37653,7 +37653,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G1434" t="n">
-        <v>1.81654107570648</v>
+        <v>1.81654131412506</v>
       </c>
       <c r="H1434" t="s">
         <v>8</v>
@@ -37679,7 +37679,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G1435" t="n">
-        <v>1.85839688777924</v>
+        <v>1.85839712619781</v>
       </c>
       <c r="H1435" t="s">
         <v>8</v>
@@ -37705,7 +37705,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G1436" t="n">
-        <v>1.85839688777924</v>
+        <v>1.85839712619781</v>
       </c>
       <c r="H1436" t="s">
         <v>8</v>
@@ -37757,7 +37757,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G1438" t="n">
-        <v>1.82491254806519</v>
+        <v>1.82491230964661</v>
       </c>
       <c r="H1438" t="s">
         <v>8</v>
@@ -37783,7 +37783,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G1439" t="n">
-        <v>1.7997989654541</v>
+        <v>1.79979884624481</v>
       </c>
       <c r="H1439" t="s">
         <v>8</v>
@@ -37809,7 +37809,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G1440" t="n">
-        <v>1.81654107570648</v>
+        <v>1.81654131412506</v>
       </c>
       <c r="H1440" t="s">
         <v>8</v>
@@ -37835,7 +37835,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G1441" t="n">
-        <v>1.82491254806519</v>
+        <v>1.82491230964661</v>
       </c>
       <c r="H1441" t="s">
         <v>8</v>
@@ -37861,7 +37861,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1442" t="n">
-        <v>1.80817008018494</v>
+        <v>1.80817019939423</v>
       </c>
       <c r="H1442" t="s">
         <v>8</v>
@@ -37887,7 +37887,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G1443" t="n">
-        <v>1.83328366279602</v>
+        <v>1.83328354358673</v>
       </c>
       <c r="H1443" t="s">
         <v>8</v>
@@ -37913,7 +37913,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G1444" t="n">
-        <v>1.83328366279602</v>
+        <v>1.83328354358673</v>
       </c>
       <c r="H1444" t="s">
         <v>8</v>
@@ -37939,7 +37939,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G1445" t="n">
-        <v>1.7997989654541</v>
+        <v>1.79979884624481</v>
       </c>
       <c r="H1445" t="s">
         <v>8</v>
@@ -37965,7 +37965,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G1446" t="n">
-        <v>1.7997989654541</v>
+        <v>1.79979884624481</v>
       </c>
       <c r="H1446" t="s">
         <v>8</v>
@@ -37991,7 +37991,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G1447" t="n">
-        <v>1.79142773151398</v>
+        <v>1.79142785072327</v>
       </c>
       <c r="H1447" t="s">
         <v>8</v>
@@ -38043,7 +38043,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G1449" t="n">
-        <v>1.7997989654541</v>
+        <v>1.79979884624481</v>
       </c>
       <c r="H1449" t="s">
         <v>8</v>
@@ -38069,7 +38069,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G1450" t="n">
-        <v>1.78305661678314</v>
+        <v>1.78305649757385</v>
       </c>
       <c r="H1450" t="s">
         <v>8</v>
@@ -38095,7 +38095,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G1451" t="n">
-        <v>1.7997989654541</v>
+        <v>1.79979884624481</v>
       </c>
       <c r="H1451" t="s">
         <v>8</v>
@@ -38121,7 +38121,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G1452" t="n">
-        <v>1.7997989654541</v>
+        <v>1.79979884624481</v>
       </c>
       <c r="H1452" t="s">
         <v>8</v>
@@ -38147,7 +38147,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G1453" t="n">
-        <v>1.77468538284302</v>
+        <v>1.77468526363373</v>
       </c>
       <c r="H1453" t="s">
         <v>8</v>
@@ -38173,7 +38173,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1454" t="n">
-        <v>1.75794291496277</v>
+        <v>1.75794279575348</v>
       </c>
       <c r="H1454" t="s">
         <v>8</v>
@@ -38199,7 +38199,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G1455" t="n">
-        <v>1.79142773151398</v>
+        <v>1.79142785072327</v>
       </c>
       <c r="H1455" t="s">
         <v>8</v>
@@ -38225,7 +38225,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G1456" t="n">
-        <v>1.83328366279602</v>
+        <v>1.83328354358673</v>
       </c>
       <c r="H1456" t="s">
         <v>8</v>
@@ -38277,7 +38277,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G1458" t="n">
-        <v>1.86676812171936</v>
+        <v>1.86676800251007</v>
       </c>
       <c r="H1458" t="s">
         <v>8</v>
@@ -38303,7 +38303,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G1459" t="n">
-        <v>1.87513935565948</v>
+        <v>1.87513911724091</v>
       </c>
       <c r="H1459" t="s">
         <v>8</v>
@@ -38329,7 +38329,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G1460" t="n">
-        <v>1.87513935565948</v>
+        <v>1.87513911724091</v>
       </c>
       <c r="H1460" t="s">
         <v>8</v>
@@ -38381,7 +38381,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G1462" t="n">
-        <v>2.1932430267334</v>
+        <v>2.19324278831482</v>
       </c>
       <c r="H1462" t="s">
         <v>8</v>
@@ -38433,7 +38433,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G1464" t="n">
-        <v>2.17650079727173</v>
+        <v>2.17650103569031</v>
       </c>
       <c r="H1464" t="s">
         <v>8</v>
@@ -38485,7 +38485,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G1466" t="n">
-        <v>2.1179027557373</v>
+        <v>2.11790299415588</v>
       </c>
       <c r="H1466" t="s">
         <v>8</v>
@@ -38589,7 +38589,7 @@
         <v>2.5</v>
       </c>
       <c r="G1470" t="n">
-        <v>2.0927894115448</v>
+        <v>2.09278917312622</v>
       </c>
       <c r="H1470" t="s">
         <v>8</v>
@@ -38641,7 +38641,7 @@
         <v>2.5</v>
       </c>
       <c r="G1472" t="n">
-        <v>2.0927894115448</v>
+        <v>2.09278917312622</v>
       </c>
       <c r="H1472" t="s">
         <v>8</v>
@@ -38667,7 +38667,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G1473" t="n">
-        <v>2.13464522361755</v>
+        <v>2.13464498519897</v>
       </c>
       <c r="H1473" t="s">
         <v>8</v>
@@ -38693,7 +38693,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G1474" t="n">
-        <v>2.10953187942505</v>
+        <v>2.10953164100647</v>
       </c>
       <c r="H1474" t="s">
         <v>8</v>
@@ -38719,7 +38719,7 @@
         <v>2.5</v>
       </c>
       <c r="G1475" t="n">
-        <v>2.0927894115448</v>
+        <v>2.09278917312622</v>
       </c>
       <c r="H1475" t="s">
         <v>8</v>
@@ -38745,7 +38745,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G1476" t="n">
-        <v>2.1179027557373</v>
+        <v>2.11790299415588</v>
       </c>
       <c r="H1476" t="s">
         <v>8</v>
@@ -38901,7 +38901,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G1482" t="n">
-        <v>2.1932430267334</v>
+        <v>2.19324278831482</v>
       </c>
       <c r="H1482" t="s">
         <v>8</v>
@@ -38927,7 +38927,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G1483" t="n">
-        <v>2.15975856781006</v>
+        <v>2.15975832939148</v>
       </c>
       <c r="H1483" t="s">
         <v>8</v>
@@ -39083,7 +39083,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G1489" t="n">
-        <v>2.17650079727173</v>
+        <v>2.17650103569031</v>
       </c>
       <c r="H1489" t="s">
         <v>8</v>
@@ -39109,7 +39109,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G1490" t="n">
-        <v>2.17650079727173</v>
+        <v>2.17650103569031</v>
       </c>
       <c r="H1490" t="s">
         <v>8</v>
@@ -39135,7 +39135,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G1491" t="n">
-        <v>2.13464522361755</v>
+        <v>2.13464498519897</v>
       </c>
       <c r="H1491" t="s">
         <v>8</v>
@@ -39161,7 +39161,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G1492" t="n">
-        <v>2.15138721466064</v>
+        <v>2.1513876914978</v>
       </c>
       <c r="H1492" t="s">
         <v>8</v>
@@ -39187,7 +39187,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G1493" t="n">
-        <v>2.28532576560974</v>
+        <v>2.28532600402832</v>
       </c>
       <c r="H1493" t="s">
         <v>8</v>
@@ -39317,7 +39317,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G1498" t="n">
-        <v>2.21835708618164</v>
+        <v>2.21835660934448</v>
       </c>
       <c r="H1498" t="s">
         <v>8</v>
@@ -39343,7 +39343,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G1499" t="n">
-        <v>2.21835708618164</v>
+        <v>2.21835660934448</v>
       </c>
       <c r="H1499" t="s">
         <v>8</v>
@@ -39369,7 +39369,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G1500" t="n">
-        <v>2.17650079727173</v>
+        <v>2.17650103569031</v>
       </c>
       <c r="H1500" t="s">
         <v>8</v>
@@ -39421,7 +39421,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G1502" t="n">
-        <v>2.27695465087891</v>
+        <v>2.27695488929749</v>
       </c>
       <c r="H1502" t="s">
         <v>8</v>
@@ -39499,7 +39499,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G1505" t="n">
-        <v>2.21835708618164</v>
+        <v>2.21835660934448</v>
       </c>
       <c r="H1505" t="s">
         <v>8</v>
@@ -39525,7 +39525,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G1506" t="n">
-        <v>2.26858377456665</v>
+        <v>2.26858353614807</v>
       </c>
       <c r="H1506" t="s">
         <v>8</v>
@@ -39551,7 +39551,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G1507" t="n">
-        <v>2.26858377456665</v>
+        <v>2.26858353614807</v>
       </c>
       <c r="H1507" t="s">
         <v>8</v>
@@ -39603,7 +39603,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G1509" t="n">
-        <v>2.26858377456665</v>
+        <v>2.26858353614807</v>
       </c>
       <c r="H1509" t="s">
         <v>8</v>
@@ -39655,7 +39655,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G1511" t="n">
-        <v>2.21835708618164</v>
+        <v>2.21835660934448</v>
       </c>
       <c r="H1511" t="s">
         <v>8</v>
@@ -39733,7 +39733,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G1514" t="n">
-        <v>2.26858377456665</v>
+        <v>2.26858353614807</v>
       </c>
       <c r="H1514" t="s">
         <v>8</v>
@@ -39759,7 +39759,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G1515" t="n">
-        <v>2.26858377456665</v>
+        <v>2.26858353614807</v>
       </c>
       <c r="H1515" t="s">
         <v>8</v>
@@ -39811,7 +39811,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G1517" t="n">
-        <v>2.54483199119568</v>
+        <v>2.5448317527771</v>
       </c>
       <c r="H1517" t="s">
         <v>8</v>
@@ -39837,7 +39837,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G1518" t="n">
-        <v>2.62017250061035</v>
+        <v>2.62017226219177</v>
       </c>
       <c r="H1518" t="s">
         <v>8</v>
@@ -39889,7 +39889,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G1520" t="n">
-        <v>2.67039942741394</v>
+        <v>2.67039918899536</v>
       </c>
       <c r="H1520" t="s">
         <v>8</v>
@@ -39915,7 +39915,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G1521" t="n">
-        <v>2.71225500106812</v>
+        <v>2.71225523948669</v>
       </c>
       <c r="H1521" t="s">
         <v>8</v>
@@ -39941,7 +39941,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G1522" t="n">
-        <v>2.67877054214478</v>
+        <v>2.6787703037262</v>
       </c>
       <c r="H1522" t="s">
         <v>8</v>
@@ -40019,7 +40019,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1525" t="n">
-        <v>3.26475119590759</v>
+        <v>3.26475167274475</v>
       </c>
       <c r="H1525" t="s">
         <v>8</v>
@@ -40149,7 +40149,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1530" t="n">
-        <v>3.01361656188965</v>
+        <v>3.01361680030823</v>
       </c>
       <c r="H1530" t="s">
         <v>8</v>
@@ -40201,7 +40201,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G1532" t="n">
-        <v>2.95501828193665</v>
+        <v>2.95501852035522</v>
       </c>
       <c r="H1532" t="s">
         <v>8</v>
@@ -40227,7 +40227,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G1533" t="n">
-        <v>2.92153406143188</v>
+        <v>2.92153358459473</v>
       </c>
       <c r="H1533" t="s">
         <v>8</v>
@@ -40253,7 +40253,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G1534" t="n">
-        <v>2.87967824935913</v>
+        <v>2.87967848777771</v>
       </c>
       <c r="H1534" t="s">
         <v>8</v>
@@ -40279,7 +40279,7 @@
         <v>3.5</v>
       </c>
       <c r="G1535" t="n">
-        <v>2.92990493774414</v>
+        <v>2.92990517616272</v>
       </c>
       <c r="H1535" t="s">
         <v>8</v>
@@ -40305,7 +40305,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G1536" t="n">
-        <v>2.89642071723938</v>
+        <v>2.89642024040222</v>
       </c>
       <c r="H1536" t="s">
         <v>8</v>
@@ -40357,7 +40357,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1538" t="n">
-        <v>2.84619331359863</v>
+        <v>2.84619355201721</v>
       </c>
       <c r="H1538" t="s">
         <v>8</v>
@@ -40409,7 +40409,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G1540" t="n">
-        <v>2.78759551048279</v>
+        <v>2.78759527206421</v>
       </c>
       <c r="H1540" t="s">
         <v>8</v>
@@ -40461,7 +40461,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G1542" t="n">
-        <v>2.89642071723938</v>
+        <v>2.89642024040222</v>
       </c>
       <c r="H1542" t="s">
         <v>8</v>
@@ -40487,7 +40487,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G1543" t="n">
-        <v>2.90479159355164</v>
+        <v>2.90479183197021</v>
       </c>
       <c r="H1543" t="s">
         <v>8</v>
@@ -40513,7 +40513,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G1544" t="n">
-        <v>2.97176098823547</v>
+        <v>2.97176074981689</v>
       </c>
       <c r="H1544" t="s">
         <v>8</v>
@@ -40539,7 +40539,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G1545" t="n">
-        <v>3.03873014450073</v>
+        <v>3.03873038291931</v>
       </c>
       <c r="H1545" t="s">
         <v>8</v>
@@ -40591,7 +40591,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G1547" t="n">
-        <v>3.04710125923157</v>
+        <v>3.04710149765015</v>
       </c>
       <c r="H1547" t="s">
         <v>8</v>
@@ -40617,7 +40617,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G1548" t="n">
-        <v>3.12244153022766</v>
+        <v>3.12244176864624</v>
       </c>
       <c r="H1548" t="s">
         <v>8</v>
@@ -40643,7 +40643,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G1549" t="n">
-        <v>3.1894109249115</v>
+        <v>3.18941068649292</v>
       </c>
       <c r="H1549" t="s">
         <v>8</v>
@@ -40669,7 +40669,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G1550" t="n">
-        <v>3.17266845703125</v>
+        <v>3.17266893386841</v>
       </c>
       <c r="H1550" t="s">
         <v>8</v>
@@ -40695,7 +40695,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G1551" t="n">
-        <v>3.22289562225342</v>
+        <v>3.22289538383484</v>
       </c>
       <c r="H1551" t="s">
         <v>8</v>
@@ -40825,7 +40825,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G1556" t="n">
-        <v>3.21806406974792</v>
+        <v>3.2180643081665</v>
       </c>
       <c r="H1556" t="s">
         <v>8</v>
@@ -40877,7 +40877,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G1558" t="n">
-        <v>3.16629910469055</v>
+        <v>3.16629934310913</v>
       </c>
       <c r="H1558" t="s">
         <v>8</v>
@@ -40903,7 +40903,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G1559" t="n">
-        <v>3.1749267578125</v>
+        <v>3.17492651939392</v>
       </c>
       <c r="H1559" t="s">
         <v>8</v>
@@ -40955,7 +40955,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G1561" t="n">
-        <v>3.1749267578125</v>
+        <v>3.17492651939392</v>
       </c>
       <c r="H1561" t="s">
         <v>8</v>
@@ -41033,7 +41033,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1564" t="n">
-        <v>3.10590624809265</v>
+        <v>3.10590648651123</v>
       </c>
       <c r="H1564" t="s">
         <v>8</v>
@@ -41085,7 +41085,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G1566" t="n">
-        <v>2.97649383544922</v>
+        <v>2.97649359703064</v>
       </c>
       <c r="H1566" t="s">
         <v>8</v>
@@ -41111,7 +41111,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G1567" t="n">
-        <v>2.9592387676239</v>
+        <v>2.95923852920532</v>
       </c>
       <c r="H1567" t="s">
         <v>8</v>
@@ -41319,7 +41319,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G1575" t="n">
-        <v>2.62276554107666</v>
+        <v>2.62276530265808</v>
       </c>
       <c r="H1575" t="s">
         <v>8</v>
@@ -41397,7 +41397,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G1578" t="n">
-        <v>2.83845329284668</v>
+        <v>2.83845353126526</v>
       </c>
       <c r="H1578" t="s">
         <v>8</v>
@@ -41423,7 +41423,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G1579" t="n">
-        <v>2.90747332572937</v>
+        <v>2.90747356414795</v>
       </c>
       <c r="H1579" t="s">
         <v>8</v>
@@ -41501,7 +41501,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G1582" t="n">
-        <v>2.96786618232727</v>
+        <v>2.96786642074585</v>
       </c>
       <c r="H1582" t="s">
         <v>8</v>
@@ -41579,7 +41579,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G1585" t="n">
-        <v>2.99374866485596</v>
+        <v>2.99374890327454</v>
       </c>
       <c r="H1585" t="s">
         <v>8</v>
@@ -41605,7 +41605,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G1586" t="n">
-        <v>2.9592387676239</v>
+        <v>2.95923852920532</v>
       </c>
       <c r="H1586" t="s">
         <v>8</v>
@@ -41787,7 +41787,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G1593" t="n">
-        <v>3.01100373268127</v>
+        <v>3.0110034942627</v>
       </c>
       <c r="H1593" t="s">
         <v>8</v>
@@ -41813,7 +41813,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1594" t="n">
-        <v>2.93335628509521</v>
+        <v>2.93335604667664</v>
       </c>
       <c r="H1594" t="s">
         <v>8</v>
@@ -41839,7 +41839,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1595" t="n">
-        <v>2.93335628509521</v>
+        <v>2.93335604667664</v>
       </c>
       <c r="H1595" t="s">
         <v>8</v>
@@ -41891,7 +41891,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G1597" t="n">
-        <v>2.9592387676239</v>
+        <v>2.95923852920532</v>
       </c>
       <c r="H1597" t="s">
         <v>8</v>
@@ -41917,7 +41917,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1598" t="n">
-        <v>2.93335628509521</v>
+        <v>2.93335604667664</v>
       </c>
       <c r="H1598" t="s">
         <v>8</v>
@@ -41943,7 +41943,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G1599" t="n">
-        <v>2.90747332572937</v>
+        <v>2.90747356414795</v>
       </c>
       <c r="H1599" t="s">
         <v>8</v>
@@ -41969,7 +41969,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G1600" t="n">
-        <v>2.9592387676239</v>
+        <v>2.95923852920532</v>
       </c>
       <c r="H1600" t="s">
         <v>8</v>
@@ -41995,7 +41995,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1601" t="n">
-        <v>2.93335628509521</v>
+        <v>2.93335604667664</v>
       </c>
       <c r="H1601" t="s">
         <v>8</v>
@@ -71300,6 +71300,32 @@
         <v>0.509999990463257</v>
       </c>
       <c r="H2728" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2729">
+      <c r="A2729" s="1" t="n">
+        <v>46290.2916666667</v>
+      </c>
+      <c r="B2729" t="n">
+        <v>34536</v>
+      </c>
+      <c r="C2729" t="n">
+        <v>0.535000026226044</v>
+      </c>
+      <c r="D2729" t="n">
+        <v>0.529999971389771</v>
+      </c>
+      <c r="E2729" t="n">
+        <v>0.529999971389771</v>
+      </c>
+      <c r="F2729" t="n">
+        <v>0.535000026226044</v>
+      </c>
+      <c r="G2729" t="n">
+        <v>0.535000026226044</v>
+      </c>
+      <c r="H2729" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/ZUC.MI.xlsx
+++ b/data/ZUC.MI.xlsx
@@ -63270,8 +63270,31 @@
       <c r="E2735" t="n">
         <v>0.416000008583069</v>
       </c>
-      <c r="F2735"/>
+      <c r="F2735" t="n">
+        <v>0.449999988079071</v>
+      </c>
       <c r="G2735" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2736">
+      <c r="A2736" s="1" t="n">
+        <v>46301.2916666667</v>
+      </c>
+      <c r="B2736" t="n">
+        <v>4960</v>
+      </c>
+      <c r="C2736" t="n">
+        <v>0.409999996423721</v>
+      </c>
+      <c r="D2736" t="n">
+        <v>0.409999996423721</v>
+      </c>
+      <c r="E2736" t="n">
+        <v>0.409999996423721</v>
+      </c>
+      <c r="F2736"/>
+      <c r="G2736" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/ZUC.MI.xlsx
+++ b/data/ZUC.MI.xlsx
@@ -63285,7 +63285,7 @@
         <v>4960</v>
       </c>
       <c r="C2736" t="n">
-        <v>0.409999996423721</v>
+        <v>0.419999986886978</v>
       </c>
       <c r="D2736" t="n">
         <v>0.409999996423721</v>
@@ -63293,8 +63293,31 @@
       <c r="E2736" t="n">
         <v>0.409999996423721</v>
       </c>
-      <c r="F2736"/>
+      <c r="F2736" t="n">
+        <v>0.419999986886978</v>
+      </c>
       <c r="G2736" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2737">
+      <c r="A2737" s="1" t="n">
+        <v>46302.2916666667</v>
+      </c>
+      <c r="B2737" t="n">
+        <v>6455</v>
+      </c>
+      <c r="C2737" t="n">
+        <v>0.456000000238419</v>
+      </c>
+      <c r="D2737" t="n">
+        <v>0.439999997615814</v>
+      </c>
+      <c r="E2737" t="n">
+        <v>0.439999997615814</v>
+      </c>
+      <c r="F2737"/>
+      <c r="G2737" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/ZUC.MI.xlsx
+++ b/data/ZUC.MI.xlsx
@@ -63311,13 +63311,36 @@
         <v>0.456000000238419</v>
       </c>
       <c r="D2737" t="n">
-        <v>0.439999997615814</v>
+        <v>0.412000000476837</v>
       </c>
       <c r="E2737" t="n">
         <v>0.439999997615814</v>
       </c>
-      <c r="F2737"/>
+      <c r="F2737" t="n">
+        <v>0.412000000476837</v>
+      </c>
       <c r="G2737" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2738">
+      <c r="A2738" s="1" t="n">
+        <v>46303.2916666667</v>
+      </c>
+      <c r="B2738" t="n">
+        <v>3700</v>
+      </c>
+      <c r="C2738" t="n">
+        <v>0.419999986886978</v>
+      </c>
+      <c r="D2738" t="n">
+        <v>0.419999986886978</v>
+      </c>
+      <c r="E2738" t="n">
+        <v>0.419999986886978</v>
+      </c>
+      <c r="F2738"/>
+      <c r="G2738" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/ZUC.MI.xlsx
+++ b/data/ZUC.MI.xlsx
@@ -63339,7 +63339,9 @@
       <c r="E2738" t="n">
         <v>0.419999986886978</v>
       </c>
-      <c r="F2738"/>
+      <c r="F2738" t="n">
+        <v>0.419999986886978</v>
+      </c>
       <c r="G2738" t="s">
         <v>7</v>
       </c>

--- a/data/ZUC.MI.xlsx
+++ b/data/ZUC.MI.xlsx
@@ -63369,6 +63369,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2740">
+      <c r="A2740" s="1" t="n">
+        <v>46307.2916666667</v>
+      </c>
+      <c r="B2740" t="n">
+        <v>12677</v>
+      </c>
+      <c r="C2740" t="n">
+        <v>0.419999986886978</v>
+      </c>
+      <c r="D2740" t="n">
+        <v>0.419999986886978</v>
+      </c>
+      <c r="E2740" t="n">
+        <v>0.419999986886978</v>
+      </c>
+      <c r="F2740" t="n">
+        <v>0.419999986886978</v>
+      </c>
+      <c r="G2740" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ZUC.MI.xlsx
+++ b/data/ZUC.MI.xlsx
@@ -421,7 +421,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G2" t="n">
-        <v>3.01633310317993</v>
+        <v>3.01633286476135</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -525,7 +525,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G6" t="n">
-        <v>2.96944689750671</v>
+        <v>2.96944713592529</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -629,7 +629,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G10" t="n">
-        <v>2.89130353927612</v>
+        <v>2.89130401611328</v>
       </c>
       <c r="H10" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G11" t="n">
-        <v>2.77408862113953</v>
+        <v>2.77408838272095</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -681,7 +681,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G12" t="n">
-        <v>2.62561631202698</v>
+        <v>2.6256160736084</v>
       </c>
       <c r="H12" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G13" t="n">
-        <v>2.5084011554718</v>
+        <v>2.50840139389038</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -733,7 +733,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G14" t="n">
-        <v>2.39900088310242</v>
+        <v>2.39900064468384</v>
       </c>
       <c r="H14" t="s">
         <v>8</v>
@@ -785,7 +785,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G16" t="n">
-        <v>2.39118623733521</v>
+        <v>2.39118599891663</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G20" t="n">
-        <v>2.29741454124451</v>
+        <v>2.29741430282593</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G23" t="n">
-        <v>2.29741454124451</v>
+        <v>2.29741430282593</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G24" t="n">
-        <v>2.16457056999207</v>
+        <v>2.16457033157349</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G25" t="n">
-        <v>1.78948271274567</v>
+        <v>1.7894823551178</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G26" t="n">
-        <v>1.44565176963806</v>
+        <v>1.44565200805664</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G27" t="n">
-        <v>1.01586329936981</v>
+        <v>1.0158634185791</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>1</v>
       </c>
       <c r="G29" t="n">
-        <v>0.781433403491974</v>
+        <v>0.781433463096619</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G33" t="n">
-        <v>1.9926552772522</v>
+        <v>1.99265515804291</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G38" t="n">
-        <v>2.63343024253845</v>
+        <v>2.63343071937561</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1513,7 +1513,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G44" t="n">
-        <v>2.48495841026306</v>
+        <v>2.4849579334259</v>
       </c>
       <c r="H44" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G45" t="n">
-        <v>2.77408862113953</v>
+        <v>2.77408838272095</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G46" t="n">
-        <v>2.74283146858215</v>
+        <v>2.742830991745</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G49" t="n">
-        <v>2.57091617584229</v>
+        <v>2.57091593742371</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G51" t="n">
-        <v>2.54747271537781</v>
+        <v>2.54747295379639</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G53" t="n">
-        <v>2.43807220458984</v>
+        <v>2.43807196617126</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1799,7 +1799,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G55" t="n">
-        <v>2.38337206840515</v>
+        <v>2.38337182998657</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G57" t="n">
-        <v>2.35211443901062</v>
+        <v>2.3521146774292</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G64" t="n">
-        <v>2.01609802246094</v>
+        <v>2.01609826087952</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>2.5</v>
       </c>
       <c r="G65" t="n">
-        <v>1.95358335971832</v>
+        <v>1.9535835981369</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>2.5</v>
       </c>
       <c r="G66" t="n">
-        <v>1.95358335971832</v>
+        <v>1.9535835981369</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>2.5</v>
       </c>
       <c r="G67" t="n">
-        <v>1.95358335971832</v>
+        <v>1.9535835981369</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G69" t="n">
-        <v>1.83636856079102</v>
+        <v>1.83636844158173</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2189,7 +2189,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G70" t="n">
-        <v>1.82073974609375</v>
+        <v>1.82073986530304</v>
       </c>
       <c r="H70" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G72" t="n">
-        <v>1.80511128902435</v>
+        <v>1.80511105060577</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G73" t="n">
-        <v>1.94576907157898</v>
+        <v>1.94576930999756</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G74" t="n">
-        <v>1.91451191902161</v>
+        <v>1.91451215744019</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G75" t="n">
-        <v>1.84418261051178</v>
+        <v>1.84418272972107</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G76" t="n">
-        <v>1.8754403591156</v>
+        <v>1.87544012069702</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G77" t="n">
-        <v>1.80511128902435</v>
+        <v>1.80511105060577</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G79" t="n">
-        <v>1.75041103363037</v>
+        <v>1.75041091442108</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>2.25</v>
       </c>
       <c r="G80" t="n">
-        <v>1.75822532176971</v>
+        <v>1.75822520256042</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G81" t="n">
-        <v>1.75041103363037</v>
+        <v>1.75041091442108</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G85" t="n">
-        <v>1.83636856079102</v>
+        <v>1.83636844158173</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2631,7 +2631,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G87" t="n">
-        <v>1.7347823381424</v>
+        <v>1.73478221893311</v>
       </c>
       <c r="H87" t="s">
         <v>8</v>
@@ -2657,7 +2657,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G88" t="n">
-        <v>1.7347823381424</v>
+        <v>1.73478221893311</v>
       </c>
       <c r="H88" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G89" t="n">
-        <v>1.78948271274567</v>
+        <v>1.7894823551178</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G90" t="n">
-        <v>1.70352506637573</v>
+        <v>1.70352494716644</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2787,7 +2787,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G93" t="n">
-        <v>1.70352506637573</v>
+        <v>1.70352494716644</v>
       </c>
       <c r="H93" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G94" t="n">
-        <v>1.69571053981781</v>
+        <v>1.69571042060852</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G96" t="n">
-        <v>1.64882433414459</v>
+        <v>1.64882445335388</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G101" t="n">
-        <v>2.03172659873962</v>
+        <v>2.0317268371582</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3021,7 +3021,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G102" t="n">
-        <v>2.01609802246094</v>
+        <v>2.01609826087952</v>
       </c>
       <c r="H102" t="s">
         <v>8</v>
@@ -3047,7 +3047,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G103" t="n">
-        <v>2.00046920776367</v>
+        <v>2.00046944618225</v>
       </c>
       <c r="H103" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G104" t="n">
-        <v>1.93795478343964</v>
+        <v>1.93795502185822</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G107" t="n">
-        <v>1.74259638786316</v>
+        <v>1.74259662628174</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>2.25</v>
       </c>
       <c r="G111" t="n">
-        <v>1.75822532176971</v>
+        <v>1.75822520256042</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3281,7 +3281,7 @@
         <v>2.25</v>
       </c>
       <c r="G112" t="n">
-        <v>1.75822532176971</v>
+        <v>1.75822520256042</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -3307,7 +3307,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G113" t="n">
-        <v>1.69571053981781</v>
+        <v>1.69571042060852</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -3333,7 +3333,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G114" t="n">
-        <v>1.64882433414459</v>
+        <v>1.64882445335388</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -3385,7 +3385,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G116" t="n">
-        <v>1.60193848609924</v>
+        <v>1.60193836688995</v>
       </c>
       <c r="H116" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G120" t="n">
-        <v>1.57849550247192</v>
+        <v>1.57849538326263</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3515,7 +3515,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G121" t="n">
-        <v>1.57849550247192</v>
+        <v>1.57849538326263</v>
       </c>
       <c r="H121" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G122" t="n">
-        <v>1.57849550247192</v>
+        <v>1.57849538326263</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G123" t="n">
-        <v>1.57849550247192</v>
+        <v>1.57849538326263</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G124" t="n">
-        <v>1.46909475326538</v>
+        <v>1.46909487247467</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3645,7 +3645,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G126" t="n">
-        <v>1.44565176963806</v>
+        <v>1.44565200805664</v>
       </c>
       <c r="H126" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G127" t="n">
-        <v>1.44565176963806</v>
+        <v>1.44565200805664</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>2.25</v>
       </c>
       <c r="G130" t="n">
-        <v>1.75822532176971</v>
+        <v>1.75822520256042</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>1.75</v>
       </c>
       <c r="G134" t="n">
-        <v>1.36750841140747</v>
+        <v>1.36750853061676</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3983,7 +3983,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G139" t="n">
-        <v>1.46128034591675</v>
+        <v>1.46128046512604</v>
       </c>
       <c r="H139" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G141" t="n">
-        <v>1.47690916061401</v>
+        <v>1.47690904140472</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G142" t="n">
-        <v>1.46909475326538</v>
+        <v>1.46909487247467</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4139,7 +4139,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G145" t="n">
-        <v>1.4534660577774</v>
+        <v>1.45346617698669</v>
       </c>
       <c r="H145" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G147" t="n">
-        <v>1.44565176963806</v>
+        <v>1.44565200805664</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4321,7 +4321,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G152" t="n">
-        <v>1.44565176963806</v>
+        <v>1.44565200805664</v>
       </c>
       <c r="H152" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G154" t="n">
-        <v>1.46909475326538</v>
+        <v>1.46909487247467</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4399,7 +4399,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G155" t="n">
-        <v>1.50035214424133</v>
+        <v>1.50035202503204</v>
       </c>
       <c r="H155" t="s">
         <v>8</v>
@@ -4451,7 +4451,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G157" t="n">
-        <v>1.50816655158997</v>
+        <v>1.50816643238068</v>
       </c>
       <c r="H157" t="s">
         <v>8</v>
@@ -4477,7 +4477,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G158" t="n">
-        <v>1.50035214424133</v>
+        <v>1.50035202503204</v>
       </c>
       <c r="H158" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G159" t="n">
-        <v>1.48472344875336</v>
+        <v>1.48472356796265</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4529,7 +4529,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G160" t="n">
-        <v>1.46128034591675</v>
+        <v>1.46128046512604</v>
       </c>
       <c r="H160" t="s">
         <v>8</v>
@@ -4555,7 +4555,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G161" t="n">
-        <v>1.47690916061401</v>
+        <v>1.47690904140472</v>
       </c>
       <c r="H161" t="s">
         <v>8</v>
@@ -4581,7 +4581,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G162" t="n">
-        <v>1.46128034591675</v>
+        <v>1.46128046512604</v>
       </c>
       <c r="H162" t="s">
         <v>8</v>
@@ -4607,7 +4607,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G163" t="n">
-        <v>1.46909475326538</v>
+        <v>1.46909487247467</v>
       </c>
       <c r="H163" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G164" t="n">
-        <v>1.44565176963806</v>
+        <v>1.44565200805664</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G165" t="n">
-        <v>1.4534660577774</v>
+        <v>1.45346617698669</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -4685,7 +4685,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G166" t="n">
-        <v>1.46909475326538</v>
+        <v>1.46909487247467</v>
       </c>
       <c r="H166" t="s">
         <v>8</v>
@@ -4711,7 +4711,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G167" t="n">
-        <v>1.46909475326538</v>
+        <v>1.46909487247467</v>
       </c>
       <c r="H167" t="s">
         <v>8</v>
@@ -4737,7 +4737,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G168" t="n">
-        <v>1.46909475326538</v>
+        <v>1.46909487247467</v>
       </c>
       <c r="H168" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G169" t="n">
-        <v>1.47690916061401</v>
+        <v>1.47690904140472</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -4789,7 +4789,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G170" t="n">
-        <v>1.48472344875336</v>
+        <v>1.48472356796265</v>
       </c>
       <c r="H170" t="s">
         <v>8</v>
@@ -4815,7 +4815,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G171" t="n">
-        <v>1.47690916061401</v>
+        <v>1.47690904140472</v>
       </c>
       <c r="H171" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G172" t="n">
-        <v>1.47690916061401</v>
+        <v>1.47690904140472</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -4867,7 +4867,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G173" t="n">
-        <v>1.46128034591675</v>
+        <v>1.46128046512604</v>
       </c>
       <c r="H173" t="s">
         <v>8</v>
@@ -4945,7 +4945,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G176" t="n">
-        <v>1.46128034591675</v>
+        <v>1.46128046512604</v>
       </c>
       <c r="H176" t="s">
         <v>8</v>
@@ -4971,7 +4971,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G177" t="n">
-        <v>1.52379524707794</v>
+        <v>1.52379512786865</v>
       </c>
       <c r="H177" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G179" t="n">
-        <v>1.48472344875336</v>
+        <v>1.48472356796265</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5049,7 +5049,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G180" t="n">
-        <v>1.51598107814789</v>
+        <v>1.51598083972931</v>
       </c>
       <c r="H180" t="s">
         <v>8</v>
@@ -5075,7 +5075,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G181" t="n">
-        <v>1.51598107814789</v>
+        <v>1.51598083972931</v>
       </c>
       <c r="H181" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G182" t="n">
-        <v>1.47690916061401</v>
+        <v>1.47690904140472</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G184" t="n">
-        <v>1.4534660577774</v>
+        <v>1.45346617698669</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5205,7 +5205,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G186" t="n">
-        <v>1.44565176963806</v>
+        <v>1.44565200805664</v>
       </c>
       <c r="H186" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G188" t="n">
-        <v>1.66445314884186</v>
+        <v>1.66445326805115</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5283,7 +5283,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G189" t="n">
-        <v>1.62538135051727</v>
+        <v>1.62538146972656</v>
       </c>
       <c r="H189" t="s">
         <v>8</v>
@@ -5309,7 +5309,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G190" t="n">
-        <v>1.52379524707794</v>
+        <v>1.52379512786865</v>
       </c>
       <c r="H190" t="s">
         <v>8</v>
@@ -5335,7 +5335,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G191" t="n">
-        <v>1.52379524707794</v>
+        <v>1.52379512786865</v>
       </c>
       <c r="H191" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G192" t="n">
-        <v>1.48472344875336</v>
+        <v>1.48472356796265</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5387,7 +5387,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G193" t="n">
-        <v>1.48472344875336</v>
+        <v>1.48472356796265</v>
       </c>
       <c r="H193" t="s">
         <v>8</v>
@@ -5413,7 +5413,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G194" t="n">
-        <v>1.48472344875336</v>
+        <v>1.48472356796265</v>
       </c>
       <c r="H194" t="s">
         <v>8</v>
@@ -5439,7 +5439,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G195" t="n">
-        <v>1.51598107814789</v>
+        <v>1.51598083972931</v>
       </c>
       <c r="H195" t="s">
         <v>8</v>
@@ -5465,7 +5465,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G196" t="n">
-        <v>1.48472344875336</v>
+        <v>1.48472356796265</v>
       </c>
       <c r="H196" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G197" t="n">
-        <v>1.48472344875336</v>
+        <v>1.48472356796265</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5517,7 +5517,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G198" t="n">
-        <v>1.46909475326538</v>
+        <v>1.46909487247467</v>
       </c>
       <c r="H198" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G199" t="n">
-        <v>1.48472344875336</v>
+        <v>1.48472356796265</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5569,7 +5569,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G200" t="n">
-        <v>1.48472344875336</v>
+        <v>1.48472356796265</v>
       </c>
       <c r="H200" t="s">
         <v>8</v>
@@ -5595,7 +5595,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G201" t="n">
-        <v>1.48472344875336</v>
+        <v>1.48472356796265</v>
       </c>
       <c r="H201" t="s">
         <v>8</v>
@@ -5621,7 +5621,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G202" t="n">
-        <v>1.47690916061401</v>
+        <v>1.47690904140472</v>
       </c>
       <c r="H202" t="s">
         <v>8</v>
@@ -5647,7 +5647,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G203" t="n">
-        <v>1.48472344875336</v>
+        <v>1.48472356796265</v>
       </c>
       <c r="H203" t="s">
         <v>8</v>
@@ -5673,7 +5673,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G204" t="n">
-        <v>1.53160953521729</v>
+        <v>1.531609416008</v>
       </c>
       <c r="H204" t="s">
         <v>8</v>
@@ -5699,7 +5699,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G205" t="n">
-        <v>1.50816655158997</v>
+        <v>1.50816643238068</v>
       </c>
       <c r="H205" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G206" t="n">
-        <v>1.48472344875336</v>
+        <v>1.48472356796265</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G207" t="n">
-        <v>1.48472344875336</v>
+        <v>1.48472356796265</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5829,7 +5829,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G210" t="n">
-        <v>1.52379524707794</v>
+        <v>1.52379512786865</v>
       </c>
       <c r="H210" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>2</v>
       </c>
       <c r="G215" t="n">
-        <v>1.56286680698395</v>
+        <v>1.56286692619324</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G216" t="n">
-        <v>1.50816655158997</v>
+        <v>1.50816643238068</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6011,7 +6011,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G217" t="n">
-        <v>1.52379524707794</v>
+        <v>1.52379512786865</v>
       </c>
       <c r="H217" t="s">
         <v>8</v>
@@ -6037,7 +6037,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G218" t="n">
-        <v>1.51598107814789</v>
+        <v>1.51598083972931</v>
       </c>
       <c r="H218" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G219" t="n">
-        <v>1.53160953521729</v>
+        <v>1.531609416008</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6089,7 +6089,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G220" t="n">
-        <v>1.51598107814789</v>
+        <v>1.51598083972931</v>
       </c>
       <c r="H220" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>2</v>
       </c>
       <c r="G221" t="n">
-        <v>1.56286680698395</v>
+        <v>1.56286692619324</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6141,7 +6141,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G222" t="n">
-        <v>1.61756706237793</v>
+        <v>1.61756694316864</v>
       </c>
       <c r="H222" t="s">
         <v>8</v>
@@ -6167,7 +6167,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G223" t="n">
-        <v>1.57849550247192</v>
+        <v>1.57849538326263</v>
       </c>
       <c r="H223" t="s">
         <v>8</v>
@@ -6245,7 +6245,7 @@
         <v>2</v>
       </c>
       <c r="G226" t="n">
-        <v>1.56286680698395</v>
+        <v>1.56286692619324</v>
       </c>
       <c r="H226" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G229" t="n">
-        <v>1.46909475326538</v>
+        <v>1.46909487247467</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6375,7 +6375,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G231" t="n">
-        <v>1.48472344875336</v>
+        <v>1.48472356796265</v>
       </c>
       <c r="H231" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G232" t="n">
-        <v>1.51598107814789</v>
+        <v>1.51598083972931</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6427,7 +6427,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G233" t="n">
-        <v>1.52379524707794</v>
+        <v>1.52379512786865</v>
       </c>
       <c r="H233" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G236" t="n">
-        <v>1.46128034591675</v>
+        <v>1.46128046512604</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6531,7 +6531,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G237" t="n">
-        <v>1.47690916061401</v>
+        <v>1.47690904140472</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -6583,7 +6583,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G239" t="n">
-        <v>1.46909475326538</v>
+        <v>1.46909487247467</v>
       </c>
       <c r="H239" t="s">
         <v>8</v>
@@ -6609,7 +6609,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G240" t="n">
-        <v>1.51598107814789</v>
+        <v>1.51598083972931</v>
       </c>
       <c r="H240" t="s">
         <v>8</v>
@@ -6635,7 +6635,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G241" t="n">
-        <v>1.52379524707794</v>
+        <v>1.52379512786865</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -6661,7 +6661,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G242" t="n">
-        <v>1.52379524707794</v>
+        <v>1.52379512786865</v>
       </c>
       <c r="H242" t="s">
         <v>8</v>
@@ -6687,7 +6687,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G243" t="n">
-        <v>1.50035214424133</v>
+        <v>1.50035202503204</v>
       </c>
       <c r="H243" t="s">
         <v>8</v>
@@ -6713,7 +6713,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G244" t="n">
-        <v>1.50035214424133</v>
+        <v>1.50035202503204</v>
       </c>
       <c r="H244" t="s">
         <v>8</v>
@@ -6765,7 +6765,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G246" t="n">
-        <v>1.50035214424133</v>
+        <v>1.50035202503204</v>
       </c>
       <c r="H246" t="s">
         <v>8</v>
@@ -6791,7 +6791,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G247" t="n">
-        <v>1.50035214424133</v>
+        <v>1.50035202503204</v>
       </c>
       <c r="H247" t="s">
         <v>8</v>
@@ -6817,7 +6817,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G248" t="n">
-        <v>1.50035214424133</v>
+        <v>1.50035202503204</v>
       </c>
       <c r="H248" t="s">
         <v>8</v>
@@ -6843,7 +6843,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G249" t="n">
-        <v>1.51598107814789</v>
+        <v>1.51598083972931</v>
       </c>
       <c r="H249" t="s">
         <v>8</v>
@@ -6869,7 +6869,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G250" t="n">
-        <v>1.50035214424133</v>
+        <v>1.50035202503204</v>
       </c>
       <c r="H250" t="s">
         <v>8</v>
@@ -6895,7 +6895,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G251" t="n">
-        <v>1.50816655158997</v>
+        <v>1.50816643238068</v>
       </c>
       <c r="H251" t="s">
         <v>8</v>
@@ -6947,7 +6947,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G253" t="n">
-        <v>1.47690916061401</v>
+        <v>1.47690904140472</v>
       </c>
       <c r="H253" t="s">
         <v>8</v>
@@ -6973,7 +6973,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G254" t="n">
-        <v>1.50035214424133</v>
+        <v>1.50035202503204</v>
       </c>
       <c r="H254" t="s">
         <v>8</v>
@@ -7077,7 +7077,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G258" t="n">
-        <v>1.83636856079102</v>
+        <v>1.83636844158173</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -7129,7 +7129,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G260" t="n">
-        <v>1.76603960990906</v>
+        <v>1.76603937149048</v>
       </c>
       <c r="H260" t="s">
         <v>8</v>
@@ -7155,7 +7155,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G261" t="n">
-        <v>1.7347823381424</v>
+        <v>1.73478221893311</v>
       </c>
       <c r="H261" t="s">
         <v>8</v>
@@ -7181,7 +7181,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G262" t="n">
-        <v>1.72696781158447</v>
+        <v>1.72696805000305</v>
       </c>
       <c r="H262" t="s">
         <v>8</v>
@@ -7233,7 +7233,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G264" t="n">
-        <v>1.64882433414459</v>
+        <v>1.64882445335388</v>
       </c>
       <c r="H264" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G266" t="n">
-        <v>1.60193848609924</v>
+        <v>1.60193836688995</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7311,7 +7311,7 @@
         <v>2.25</v>
       </c>
       <c r="G267" t="n">
-        <v>1.75822532176971</v>
+        <v>1.75822520256042</v>
       </c>
       <c r="H267" t="s">
         <v>8</v>
@@ -7363,7 +7363,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G269" t="n">
-        <v>1.66445314884186</v>
+        <v>1.66445326805115</v>
       </c>
       <c r="H269" t="s">
         <v>8</v>
@@ -7441,7 +7441,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G272" t="n">
-        <v>2.03172659873962</v>
+        <v>2.0317268371582</v>
       </c>
       <c r="H272" t="s">
         <v>8</v>
@@ -7467,7 +7467,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G273" t="n">
-        <v>2.54747271537781</v>
+        <v>2.54747295379639</v>
       </c>
       <c r="H273" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G274" t="n">
-        <v>2.78190302848816</v>
+        <v>2.78190279006958</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7545,7 +7545,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G276" t="n">
-        <v>2.54747271537781</v>
+        <v>2.54747295379639</v>
       </c>
       <c r="H276" t="s">
         <v>8</v>
@@ -7623,7 +7623,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G279" t="n">
-        <v>2.32085728645325</v>
+        <v>2.32085752487183</v>
       </c>
       <c r="H279" t="s">
         <v>8</v>
@@ -7727,7 +7727,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G283" t="n">
-        <v>2.48495841026306</v>
+        <v>2.4849579334259</v>
       </c>
       <c r="H283" t="s">
         <v>8</v>
@@ -7805,7 +7805,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G286" t="n">
-        <v>2.63343024253845</v>
+        <v>2.63343071937561</v>
       </c>
       <c r="H286" t="s">
         <v>8</v>
@@ -7831,7 +7831,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G287" t="n">
-        <v>2.53184390068054</v>
+        <v>2.5318443775177</v>
       </c>
       <c r="H287" t="s">
         <v>8</v>
@@ -7883,7 +7883,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G289" t="n">
-        <v>2.5084011554718</v>
+        <v>2.50840139389038</v>
       </c>
       <c r="H289" t="s">
         <v>8</v>
@@ -7909,7 +7909,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G290" t="n">
-        <v>2.48495841026306</v>
+        <v>2.4849579334259</v>
       </c>
       <c r="H290" t="s">
         <v>8</v>
@@ -7961,7 +7961,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G292" t="n">
-        <v>2.35211443901062</v>
+        <v>2.3521146774292</v>
       </c>
       <c r="H292" t="s">
         <v>8</v>
@@ -8039,7 +8039,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G295" t="n">
-        <v>2.21145677566528</v>
+        <v>2.2114565372467</v>
       </c>
       <c r="H295" t="s">
         <v>8</v>
@@ -8065,7 +8065,7 @@
         <v>2.75</v>
       </c>
       <c r="G296" t="n">
-        <v>2.1489417552948</v>
+        <v>2.14894151687622</v>
       </c>
       <c r="H296" t="s">
         <v>8</v>
@@ -8091,7 +8091,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G297" t="n">
-        <v>2.07861304283142</v>
+        <v>2.07861280441284</v>
       </c>
       <c r="H297" t="s">
         <v>8</v>
@@ -8169,7 +8169,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G300" t="n">
-        <v>2.16457056999207</v>
+        <v>2.16457033157349</v>
       </c>
       <c r="H300" t="s">
         <v>8</v>
@@ -8325,7 +8325,7 @@
         <v>2.75</v>
       </c>
       <c r="G306" t="n">
-        <v>2.1489417552948</v>
+        <v>2.14894151687622</v>
       </c>
       <c r="H306" t="s">
         <v>8</v>
@@ -8403,7 +8403,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G309" t="n">
-        <v>2.16457056999207</v>
+        <v>2.16457033157349</v>
       </c>
       <c r="H309" t="s">
         <v>8</v>
@@ -8481,7 +8481,7 @@
         <v>2.75</v>
       </c>
       <c r="G312" t="n">
-        <v>2.1489417552948</v>
+        <v>2.14894151687622</v>
       </c>
       <c r="H312" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G313" t="n">
-        <v>2.14112758636475</v>
+        <v>2.14112782478333</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8533,7 +8533,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G314" t="n">
-        <v>2.1958281993866</v>
+        <v>2.19582772254944</v>
       </c>
       <c r="H314" t="s">
         <v>8</v>
@@ -8559,7 +8559,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G315" t="n">
-        <v>2.21145677566528</v>
+        <v>2.2114565372467</v>
       </c>
       <c r="H315" t="s">
         <v>8</v>
@@ -8689,7 +8689,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G320" t="n">
-        <v>2.35211443901062</v>
+        <v>2.3521146774292</v>
       </c>
       <c r="H320" t="s">
         <v>8</v>
@@ -8741,7 +8741,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G322" t="n">
-        <v>2.32085728645325</v>
+        <v>2.32085752487183</v>
       </c>
       <c r="H322" t="s">
         <v>8</v>
@@ -9001,7 +9001,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G332" t="n">
-        <v>2.1958281993866</v>
+        <v>2.19582772254944</v>
       </c>
       <c r="H332" t="s">
         <v>8</v>
@@ -9079,7 +9079,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G335" t="n">
-        <v>2.29741454124451</v>
+        <v>2.29741430282593</v>
       </c>
       <c r="H335" t="s">
         <v>8</v>
@@ -9287,7 +9287,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G343" t="n">
-        <v>2.29741454124451</v>
+        <v>2.29741430282593</v>
       </c>
       <c r="H343" t="s">
         <v>8</v>
@@ -9313,7 +9313,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G344" t="n">
-        <v>2.5084011554718</v>
+        <v>2.50840139389038</v>
       </c>
       <c r="H344" t="s">
         <v>8</v>
@@ -9365,7 +9365,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G346" t="n">
-        <v>2.39900088310242</v>
+        <v>2.39900064468384</v>
       </c>
       <c r="H346" t="s">
         <v>8</v>
@@ -9417,7 +9417,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G348" t="n">
-        <v>2.35211443901062</v>
+        <v>2.3521146774292</v>
       </c>
       <c r="H348" t="s">
         <v>8</v>
@@ -9443,7 +9443,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G349" t="n">
-        <v>2.28959989547729</v>
+        <v>2.28959965705872</v>
       </c>
       <c r="H349" t="s">
         <v>8</v>
@@ -9781,7 +9781,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G362" t="n">
-        <v>2.39900088310242</v>
+        <v>2.39900064468384</v>
       </c>
       <c r="H362" t="s">
         <v>8</v>
@@ -9807,7 +9807,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G363" t="n">
-        <v>2.29741454124451</v>
+        <v>2.29741430282593</v>
       </c>
       <c r="H363" t="s">
         <v>8</v>
@@ -9833,7 +9833,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G364" t="n">
-        <v>2.28959989547729</v>
+        <v>2.28959965705872</v>
       </c>
       <c r="H364" t="s">
         <v>8</v>
@@ -9859,7 +9859,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G365" t="n">
-        <v>2.1958281993866</v>
+        <v>2.19582772254944</v>
       </c>
       <c r="H365" t="s">
         <v>8</v>
@@ -9885,7 +9885,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G366" t="n">
-        <v>2.1958281993866</v>
+        <v>2.19582772254944</v>
       </c>
       <c r="H366" t="s">
         <v>8</v>
@@ -9963,7 +9963,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G369" t="n">
-        <v>2.1958281993866</v>
+        <v>2.19582772254944</v>
       </c>
       <c r="H369" t="s">
         <v>8</v>
@@ -9989,7 +9989,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G370" t="n">
-        <v>2.1958281993866</v>
+        <v>2.19582772254944</v>
       </c>
       <c r="H370" t="s">
         <v>8</v>
@@ -10093,7 +10093,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G374" t="n">
-        <v>2.21145677566528</v>
+        <v>2.2114565372467</v>
       </c>
       <c r="H374" t="s">
         <v>8</v>
@@ -10301,7 +10301,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G382" t="n">
-        <v>2.21145677566528</v>
+        <v>2.2114565372467</v>
       </c>
       <c r="H382" t="s">
         <v>8</v>
@@ -10483,7 +10483,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G389" t="n">
-        <v>2.18019938468933</v>
+        <v>2.18019914627075</v>
       </c>
       <c r="H389" t="s">
         <v>8</v>
@@ -10509,7 +10509,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G390" t="n">
-        <v>2.1958281993866</v>
+        <v>2.19582772254944</v>
       </c>
       <c r="H390" t="s">
         <v>8</v>
@@ -10587,7 +10587,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G393" t="n">
-        <v>2.28959989547729</v>
+        <v>2.28959965705872</v>
       </c>
       <c r="H393" t="s">
         <v>8</v>
@@ -10613,7 +10613,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G394" t="n">
-        <v>2.25052833557129</v>
+        <v>2.25052857398987</v>
       </c>
       <c r="H394" t="s">
         <v>8</v>
@@ -10691,7 +10691,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G397" t="n">
-        <v>2.21145677566528</v>
+        <v>2.2114565372467</v>
       </c>
       <c r="H397" t="s">
         <v>8</v>
@@ -10769,7 +10769,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G400" t="n">
-        <v>2.25052833557129</v>
+        <v>2.25052857398987</v>
       </c>
       <c r="H400" t="s">
         <v>8</v>
@@ -10847,7 +10847,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G403" t="n">
-        <v>2.28959989547729</v>
+        <v>2.28959965705872</v>
       </c>
       <c r="H403" t="s">
         <v>8</v>
@@ -10977,7 +10977,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G408" t="n">
-        <v>2.28959989547729</v>
+        <v>2.28959965705872</v>
       </c>
       <c r="H408" t="s">
         <v>8</v>
@@ -11003,7 +11003,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G409" t="n">
-        <v>2.25052833557129</v>
+        <v>2.25052857398987</v>
       </c>
       <c r="H409" t="s">
         <v>8</v>
@@ -11081,7 +11081,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G412" t="n">
-        <v>2.25052833557129</v>
+        <v>2.25052857398987</v>
       </c>
       <c r="H412" t="s">
         <v>8</v>
@@ -11185,7 +11185,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G416" t="n">
-        <v>2.25052833557129</v>
+        <v>2.25052857398987</v>
       </c>
       <c r="H416" t="s">
         <v>8</v>
@@ -11263,7 +11263,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G419" t="n">
-        <v>2.25052833557129</v>
+        <v>2.25052857398987</v>
       </c>
       <c r="H419" t="s">
         <v>8</v>
@@ -11315,7 +11315,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G421" t="n">
-        <v>2.25052833557129</v>
+        <v>2.25052857398987</v>
       </c>
       <c r="H421" t="s">
         <v>8</v>
@@ -11341,7 +11341,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G422" t="n">
-        <v>2.25052833557129</v>
+        <v>2.25052857398987</v>
       </c>
       <c r="H422" t="s">
         <v>8</v>
@@ -11445,7 +11445,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G426" t="n">
-        <v>2.28959989547729</v>
+        <v>2.28959965705872</v>
       </c>
       <c r="H426" t="s">
         <v>8</v>
@@ -11471,7 +11471,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G427" t="n">
-        <v>2.28959989547729</v>
+        <v>2.28959965705872</v>
       </c>
       <c r="H427" t="s">
         <v>8</v>
@@ -11601,7 +11601,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G432" t="n">
-        <v>2.28959989547729</v>
+        <v>2.28959965705872</v>
       </c>
       <c r="H432" t="s">
         <v>8</v>
@@ -11627,7 +11627,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G433" t="n">
-        <v>2.28959989547729</v>
+        <v>2.28959965705872</v>
       </c>
       <c r="H433" t="s">
         <v>8</v>
@@ -11679,7 +11679,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G435" t="n">
-        <v>2.28959989547729</v>
+        <v>2.28959965705872</v>
       </c>
       <c r="H435" t="s">
         <v>8</v>
@@ -11809,7 +11809,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G440" t="n">
-        <v>2.29741454124451</v>
+        <v>2.29741430282593</v>
       </c>
       <c r="H440" t="s">
         <v>8</v>
@@ -11939,7 +11939,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G445" t="n">
-        <v>2.32085728645325</v>
+        <v>2.32085752487183</v>
       </c>
       <c r="H445" t="s">
         <v>8</v>
@@ -11991,7 +11991,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G447" t="n">
-        <v>2.28959989547729</v>
+        <v>2.28959965705872</v>
       </c>
       <c r="H447" t="s">
         <v>8</v>
@@ -12017,7 +12017,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G448" t="n">
-        <v>2.29741454124451</v>
+        <v>2.29741430282593</v>
       </c>
       <c r="H448" t="s">
         <v>8</v>
@@ -12069,7 +12069,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G450" t="n">
-        <v>2.28959989547729</v>
+        <v>2.28959965705872</v>
       </c>
       <c r="H450" t="s">
         <v>8</v>
@@ -12199,7 +12199,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G455" t="n">
-        <v>2.25052833557129</v>
+        <v>2.25052857398987</v>
       </c>
       <c r="H455" t="s">
         <v>8</v>
@@ -12459,7 +12459,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G465" t="n">
-        <v>2.25052833557129</v>
+        <v>2.25052857398987</v>
       </c>
       <c r="H465" t="s">
         <v>8</v>
@@ -12511,7 +12511,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G467" t="n">
-        <v>2.25052833557129</v>
+        <v>2.25052857398987</v>
       </c>
       <c r="H467" t="s">
         <v>8</v>
@@ -12589,7 +12589,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G470" t="n">
-        <v>2.25052833557129</v>
+        <v>2.25052857398987</v>
       </c>
       <c r="H470" t="s">
         <v>8</v>
@@ -12797,7 +12797,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G478" t="n">
-        <v>2.25052833557129</v>
+        <v>2.25052857398987</v>
       </c>
       <c r="H478" t="s">
         <v>8</v>
@@ -12979,7 +12979,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G485" t="n">
-        <v>2.04735517501831</v>
+        <v>2.04735541343689</v>
       </c>
       <c r="H485" t="s">
         <v>8</v>
@@ -13057,7 +13057,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G488" t="n">
-        <v>2.09424185752869</v>
+        <v>2.09424161911011</v>
       </c>
       <c r="H488" t="s">
         <v>8</v>
@@ -13109,7 +13109,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G490" t="n">
-        <v>2.03954100608826</v>
+        <v>2.03954124450684</v>
       </c>
       <c r="H490" t="s">
         <v>8</v>
@@ -13161,7 +13161,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G492" t="n">
-        <v>1.9926552772522</v>
+        <v>1.99265515804291</v>
       </c>
       <c r="H492" t="s">
         <v>8</v>
@@ -13187,7 +13187,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G493" t="n">
-        <v>2.00828385353088</v>
+        <v>2.0082836151123</v>
       </c>
       <c r="H493" t="s">
         <v>8</v>
@@ -13265,7 +13265,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G496" t="n">
-        <v>2.01609802246094</v>
+        <v>2.01609826087952</v>
       </c>
       <c r="H496" t="s">
         <v>8</v>
@@ -13291,7 +13291,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G497" t="n">
-        <v>1.9926552772522</v>
+        <v>1.99265515804291</v>
       </c>
       <c r="H497" t="s">
         <v>8</v>
@@ -13317,7 +13317,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G498" t="n">
-        <v>2.00046920776367</v>
+        <v>2.00046944618225</v>
       </c>
       <c r="H498" t="s">
         <v>8</v>
@@ -13343,7 +13343,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G499" t="n">
-        <v>2.00046920776367</v>
+        <v>2.00046944618225</v>
       </c>
       <c r="H499" t="s">
         <v>8</v>
@@ -13369,7 +13369,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G500" t="n">
-        <v>2.00828385353088</v>
+        <v>2.0082836151123</v>
       </c>
       <c r="H500" t="s">
         <v>8</v>
@@ -13395,7 +13395,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G501" t="n">
-        <v>2.01609802246094</v>
+        <v>2.01609826087952</v>
       </c>
       <c r="H501" t="s">
         <v>8</v>
@@ -13421,7 +13421,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G502" t="n">
-        <v>2.00046920776367</v>
+        <v>2.00046944618225</v>
       </c>
       <c r="H502" t="s">
         <v>8</v>
@@ -13447,7 +13447,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G503" t="n">
-        <v>2.01609802246094</v>
+        <v>2.01609826087952</v>
       </c>
       <c r="H503" t="s">
         <v>8</v>
@@ -13473,7 +13473,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G504" t="n">
-        <v>1.9926552772522</v>
+        <v>1.99265515804291</v>
       </c>
       <c r="H504" t="s">
         <v>8</v>
@@ -13499,7 +13499,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G505" t="n">
-        <v>2.00046920776367</v>
+        <v>2.00046944618225</v>
       </c>
       <c r="H505" t="s">
         <v>8</v>
@@ -13525,7 +13525,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G506" t="n">
-        <v>2.03172659873962</v>
+        <v>2.0317268371582</v>
       </c>
       <c r="H506" t="s">
         <v>8</v>
@@ -13551,7 +13551,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G507" t="n">
-        <v>2.03172659873962</v>
+        <v>2.0317268371582</v>
       </c>
       <c r="H507" t="s">
         <v>8</v>
@@ -13577,7 +13577,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G508" t="n">
-        <v>2.01609802246094</v>
+        <v>2.01609826087952</v>
       </c>
       <c r="H508" t="s">
         <v>8</v>
@@ -13603,7 +13603,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G509" t="n">
-        <v>2.00046920776367</v>
+        <v>2.00046944618225</v>
       </c>
       <c r="H509" t="s">
         <v>8</v>
@@ -13629,7 +13629,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G510" t="n">
-        <v>2.00828385353088</v>
+        <v>2.0082836151123</v>
       </c>
       <c r="H510" t="s">
         <v>8</v>
@@ -13655,7 +13655,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G511" t="n">
-        <v>2.00046920776367</v>
+        <v>2.00046944618225</v>
       </c>
       <c r="H511" t="s">
         <v>8</v>
@@ -13681,7 +13681,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G512" t="n">
-        <v>2.00046920776367</v>
+        <v>2.00046944618225</v>
       </c>
       <c r="H512" t="s">
         <v>8</v>
@@ -13707,7 +13707,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G513" t="n">
-        <v>2.00828385353088</v>
+        <v>2.0082836151123</v>
       </c>
       <c r="H513" t="s">
         <v>8</v>
@@ -13733,7 +13733,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G514" t="n">
-        <v>2.01609802246094</v>
+        <v>2.01609826087952</v>
       </c>
       <c r="H514" t="s">
         <v>8</v>
@@ -13759,7 +13759,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G515" t="n">
-        <v>2.03172659873962</v>
+        <v>2.0317268371582</v>
       </c>
       <c r="H515" t="s">
         <v>8</v>
@@ -13785,7 +13785,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G516" t="n">
-        <v>2.03172659873962</v>
+        <v>2.0317268371582</v>
       </c>
       <c r="H516" t="s">
         <v>8</v>
@@ -13811,7 +13811,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G517" t="n">
-        <v>2.01609802246094</v>
+        <v>2.01609826087952</v>
       </c>
       <c r="H517" t="s">
         <v>8</v>
@@ -13837,7 +13837,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G518" t="n">
-        <v>2.09424185752869</v>
+        <v>2.09424161911011</v>
       </c>
       <c r="H518" t="s">
         <v>8</v>
@@ -13889,7 +13889,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G520" t="n">
-        <v>2.07861304283142</v>
+        <v>2.07861280441284</v>
       </c>
       <c r="H520" t="s">
         <v>8</v>
@@ -14045,7 +14045,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G526" t="n">
-        <v>2.04735517501831</v>
+        <v>2.04735541343689</v>
       </c>
       <c r="H526" t="s">
         <v>8</v>
@@ -14071,7 +14071,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G527" t="n">
-        <v>2.04735517501831</v>
+        <v>2.04735541343689</v>
       </c>
       <c r="H527" t="s">
         <v>8</v>
@@ -14123,7 +14123,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G529" t="n">
-        <v>2.04735517501831</v>
+        <v>2.04735541343689</v>
       </c>
       <c r="H529" t="s">
         <v>8</v>
@@ -14175,7 +14175,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G531" t="n">
-        <v>2.07861304283142</v>
+        <v>2.07861280441284</v>
       </c>
       <c r="H531" t="s">
         <v>8</v>
@@ -14201,7 +14201,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G532" t="n">
-        <v>2.03954100608826</v>
+        <v>2.03954124450684</v>
       </c>
       <c r="H532" t="s">
         <v>8</v>
@@ -14227,7 +14227,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G533" t="n">
-        <v>2.03954100608826</v>
+        <v>2.03954124450684</v>
       </c>
       <c r="H533" t="s">
         <v>8</v>
@@ -14253,7 +14253,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G534" t="n">
-        <v>2.03172659873962</v>
+        <v>2.0317268371582</v>
       </c>
       <c r="H534" t="s">
         <v>8</v>
@@ -14279,7 +14279,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G535" t="n">
-        <v>2.03172659873962</v>
+        <v>2.0317268371582</v>
       </c>
       <c r="H535" t="s">
         <v>8</v>
@@ -14305,7 +14305,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G536" t="n">
-        <v>2.00046920776367</v>
+        <v>2.00046944618225</v>
       </c>
       <c r="H536" t="s">
         <v>8</v>
@@ -14331,7 +14331,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G537" t="n">
-        <v>2.00046920776367</v>
+        <v>2.00046944618225</v>
       </c>
       <c r="H537" t="s">
         <v>8</v>
@@ -14357,7 +14357,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G538" t="n">
-        <v>2.00046920776367</v>
+        <v>2.00046944618225</v>
       </c>
       <c r="H538" t="s">
         <v>8</v>
@@ -14435,7 +14435,7 @@
         <v>2.5</v>
       </c>
       <c r="G541" t="n">
-        <v>1.95358335971832</v>
+        <v>1.9535835981369</v>
       </c>
       <c r="H541" t="s">
         <v>8</v>
@@ -14461,7 +14461,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G542" t="n">
-        <v>1.89106917381287</v>
+        <v>1.89106893539429</v>
       </c>
       <c r="H542" t="s">
         <v>8</v>
@@ -14513,7 +14513,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G544" t="n">
-        <v>1.89106917381287</v>
+        <v>1.89106893539429</v>
       </c>
       <c r="H544" t="s">
         <v>8</v>
@@ -14565,7 +14565,7 @@
         <v>2.5</v>
       </c>
       <c r="G546" t="n">
-        <v>1.95358335971832</v>
+        <v>1.9535835981369</v>
       </c>
       <c r="H546" t="s">
         <v>8</v>
@@ -14591,7 +14591,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G547" t="n">
-        <v>1.96921217441559</v>
+        <v>1.96921193599701</v>
       </c>
       <c r="H547" t="s">
         <v>8</v>
@@ -14617,7 +14617,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G548" t="n">
-        <v>1.96921217441559</v>
+        <v>1.96921193599701</v>
       </c>
       <c r="H548" t="s">
         <v>8</v>
@@ -14643,7 +14643,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G549" t="n">
-        <v>1.93795478343964</v>
+        <v>1.93795502185822</v>
       </c>
       <c r="H549" t="s">
         <v>8</v>
@@ -14669,7 +14669,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G550" t="n">
-        <v>2.04735517501831</v>
+        <v>2.04735541343689</v>
       </c>
       <c r="H550" t="s">
         <v>8</v>
@@ -14695,7 +14695,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G551" t="n">
-        <v>2.00828385353088</v>
+        <v>2.0082836151123</v>
       </c>
       <c r="H551" t="s">
         <v>8</v>
@@ -14747,7 +14747,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G553" t="n">
-        <v>2.00828385353088</v>
+        <v>2.0082836151123</v>
       </c>
       <c r="H553" t="s">
         <v>8</v>
@@ -14773,7 +14773,7 @@
         <v>2.5</v>
       </c>
       <c r="G554" t="n">
-        <v>1.95358335971832</v>
+        <v>1.9535835981369</v>
       </c>
       <c r="H554" t="s">
         <v>8</v>
@@ -14799,7 +14799,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G555" t="n">
-        <v>1.8754403591156</v>
+        <v>1.87544012069702</v>
       </c>
       <c r="H555" t="s">
         <v>8</v>
@@ -14851,7 +14851,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G557" t="n">
-        <v>1.8754403591156</v>
+        <v>1.87544012069702</v>
       </c>
       <c r="H557" t="s">
         <v>8</v>
@@ -14903,7 +14903,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G559" t="n">
-        <v>1.8754403591156</v>
+        <v>1.87544012069702</v>
       </c>
       <c r="H559" t="s">
         <v>8</v>
@@ -14929,7 +14929,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G560" t="n">
-        <v>1.89888322353363</v>
+        <v>1.89888310432434</v>
       </c>
       <c r="H560" t="s">
         <v>8</v>
@@ -14955,7 +14955,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G561" t="n">
-        <v>1.89888322353363</v>
+        <v>1.89888310432434</v>
       </c>
       <c r="H561" t="s">
         <v>8</v>
@@ -15059,7 +15059,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G565" t="n">
-        <v>1.91451191902161</v>
+        <v>1.91451215744019</v>
       </c>
       <c r="H565" t="s">
         <v>8</v>
@@ -15085,7 +15085,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G566" t="n">
-        <v>1.8754403591156</v>
+        <v>1.87544012069702</v>
       </c>
       <c r="H566" t="s">
         <v>8</v>
@@ -15111,7 +15111,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G567" t="n">
-        <v>1.8754403591156</v>
+        <v>1.87544012069702</v>
       </c>
       <c r="H567" t="s">
         <v>8</v>
@@ -15163,7 +15163,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G569" t="n">
-        <v>1.84418261051178</v>
+        <v>1.84418272972107</v>
       </c>
       <c r="H569" t="s">
         <v>8</v>
@@ -15215,7 +15215,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G571" t="n">
-        <v>2.00046920776367</v>
+        <v>2.00046944618225</v>
       </c>
       <c r="H571" t="s">
         <v>8</v>
@@ -15241,7 +15241,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G572" t="n">
-        <v>2.00828385353088</v>
+        <v>2.0082836151123</v>
       </c>
       <c r="H572" t="s">
         <v>8</v>
@@ -15267,7 +15267,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G573" t="n">
-        <v>2.03172659873962</v>
+        <v>2.0317268371582</v>
       </c>
       <c r="H573" t="s">
         <v>8</v>
@@ -15293,7 +15293,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G574" t="n">
-        <v>2.03954100608826</v>
+        <v>2.03954124450684</v>
       </c>
       <c r="H574" t="s">
         <v>8</v>
@@ -15319,7 +15319,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G575" t="n">
-        <v>2.03172659873962</v>
+        <v>2.0317268371582</v>
       </c>
       <c r="H575" t="s">
         <v>8</v>
@@ -15345,7 +15345,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G576" t="n">
-        <v>2.01609802246094</v>
+        <v>2.01609826087952</v>
       </c>
       <c r="H576" t="s">
         <v>8</v>
@@ -15423,7 +15423,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G579" t="n">
-        <v>2.03954100608826</v>
+        <v>2.03954124450684</v>
       </c>
       <c r="H579" t="s">
         <v>8</v>
@@ -15449,7 +15449,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G580" t="n">
-        <v>2.04735517501831</v>
+        <v>2.04735541343689</v>
       </c>
       <c r="H580" t="s">
         <v>8</v>
@@ -15475,7 +15475,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G581" t="n">
-        <v>2.01609802246094</v>
+        <v>2.01609826087952</v>
       </c>
       <c r="H581" t="s">
         <v>8</v>
@@ -15631,7 +15631,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G587" t="n">
-        <v>2.00828385353088</v>
+        <v>2.0082836151123</v>
       </c>
       <c r="H587" t="s">
         <v>8</v>
@@ -15657,7 +15657,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G588" t="n">
-        <v>1.96921217441559</v>
+        <v>1.96921193599701</v>
       </c>
       <c r="H588" t="s">
         <v>8</v>
@@ -15709,7 +15709,7 @@
         <v>2.5</v>
       </c>
       <c r="G590" t="n">
-        <v>1.95358335971832</v>
+        <v>1.9535835981369</v>
       </c>
       <c r="H590" t="s">
         <v>8</v>
@@ -15735,7 +15735,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G591" t="n">
-        <v>1.93795478343964</v>
+        <v>1.93795502185822</v>
       </c>
       <c r="H591" t="s">
         <v>8</v>
@@ -15761,7 +15761,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G592" t="n">
-        <v>1.96921217441559</v>
+        <v>1.96921193599701</v>
       </c>
       <c r="H592" t="s">
         <v>8</v>
@@ -15787,7 +15787,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G593" t="n">
-        <v>1.89888322353363</v>
+        <v>1.89888310432434</v>
       </c>
       <c r="H593" t="s">
         <v>8</v>
@@ -15813,7 +15813,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G594" t="n">
-        <v>1.96921217441559</v>
+        <v>1.96921193599701</v>
       </c>
       <c r="H594" t="s">
         <v>8</v>
@@ -15839,7 +15839,7 @@
         <v>2.5</v>
       </c>
       <c r="G595" t="n">
-        <v>1.95358335971832</v>
+        <v>1.9535835981369</v>
       </c>
       <c r="H595" t="s">
         <v>8</v>
@@ -15865,7 +15865,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G596" t="n">
-        <v>1.93014049530029</v>
+        <v>1.93014073371887</v>
       </c>
       <c r="H596" t="s">
         <v>8</v>
@@ -15891,7 +15891,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G597" t="n">
-        <v>1.93014049530029</v>
+        <v>1.93014073371887</v>
       </c>
       <c r="H597" t="s">
         <v>8</v>
@@ -15917,7 +15917,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G598" t="n">
-        <v>1.93795478343964</v>
+        <v>1.93795502185822</v>
       </c>
       <c r="H598" t="s">
         <v>8</v>
@@ -15943,7 +15943,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G599" t="n">
-        <v>1.91451191902161</v>
+        <v>1.91451215744019</v>
       </c>
       <c r="H599" t="s">
         <v>8</v>
@@ -15969,7 +15969,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G600" t="n">
-        <v>1.94576907157898</v>
+        <v>1.94576930999756</v>
       </c>
       <c r="H600" t="s">
         <v>8</v>
@@ -15995,7 +15995,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G601" t="n">
-        <v>1.94576907157898</v>
+        <v>1.94576930999756</v>
       </c>
       <c r="H601" t="s">
         <v>8</v>
@@ -16021,7 +16021,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G602" t="n">
-        <v>1.89106917381287</v>
+        <v>1.89106893539429</v>
       </c>
       <c r="H602" t="s">
         <v>8</v>
@@ -16047,7 +16047,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G603" t="n">
-        <v>1.94576907157898</v>
+        <v>1.94576930999756</v>
       </c>
       <c r="H603" t="s">
         <v>8</v>
@@ -16073,7 +16073,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G604" t="n">
-        <v>1.93795478343964</v>
+        <v>1.93795502185822</v>
       </c>
       <c r="H604" t="s">
         <v>8</v>
@@ -16099,7 +16099,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G605" t="n">
-        <v>1.89106917381287</v>
+        <v>1.89106893539429</v>
       </c>
       <c r="H605" t="s">
         <v>8</v>
@@ -16125,7 +16125,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G606" t="n">
-        <v>1.8754403591156</v>
+        <v>1.87544012069702</v>
       </c>
       <c r="H606" t="s">
         <v>8</v>
@@ -16151,7 +16151,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G607" t="n">
-        <v>1.8754403591156</v>
+        <v>1.87544012069702</v>
       </c>
       <c r="H607" t="s">
         <v>8</v>
@@ -16177,7 +16177,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G608" t="n">
-        <v>1.8754403591156</v>
+        <v>1.87544012069702</v>
       </c>
       <c r="H608" t="s">
         <v>8</v>
@@ -16229,7 +16229,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G610" t="n">
-        <v>1.84418261051178</v>
+        <v>1.84418272972107</v>
       </c>
       <c r="H610" t="s">
         <v>8</v>
@@ -16255,7 +16255,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G611" t="n">
-        <v>1.84418261051178</v>
+        <v>1.84418272972107</v>
       </c>
       <c r="H611" t="s">
         <v>8</v>
@@ -16411,7 +16411,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G617" t="n">
-        <v>1.8754403591156</v>
+        <v>1.87544012069702</v>
       </c>
       <c r="H617" t="s">
         <v>8</v>
@@ -16437,7 +16437,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G618" t="n">
-        <v>1.84418261051178</v>
+        <v>1.84418272972107</v>
       </c>
       <c r="H618" t="s">
         <v>8</v>
@@ -16463,7 +16463,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G619" t="n">
-        <v>1.89106917381287</v>
+        <v>1.89106893539429</v>
       </c>
       <c r="H619" t="s">
         <v>8</v>
@@ -16489,7 +16489,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G620" t="n">
-        <v>1.82073974609375</v>
+        <v>1.82073986530304</v>
       </c>
       <c r="H620" t="s">
         <v>8</v>
@@ -16541,7 +16541,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G622" t="n">
-        <v>1.84418261051178</v>
+        <v>1.84418272972107</v>
       </c>
       <c r="H622" t="s">
         <v>8</v>
@@ -16619,7 +16619,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G625" t="n">
-        <v>1.91451191902161</v>
+        <v>1.91451215744019</v>
       </c>
       <c r="H625" t="s">
         <v>8</v>
@@ -16671,7 +16671,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G627" t="n">
-        <v>1.82073974609375</v>
+        <v>1.82073986530304</v>
       </c>
       <c r="H627" t="s">
         <v>8</v>
@@ -16723,7 +16723,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G629" t="n">
-        <v>1.83636856079102</v>
+        <v>1.83636844158173</v>
       </c>
       <c r="H629" t="s">
         <v>8</v>
@@ -16749,7 +16749,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G630" t="n">
-        <v>1.84418261051178</v>
+        <v>1.84418272972107</v>
       </c>
       <c r="H630" t="s">
         <v>8</v>
@@ -16801,7 +16801,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G632" t="n">
-        <v>1.76603960990906</v>
+        <v>1.76603937149048</v>
       </c>
       <c r="H632" t="s">
         <v>8</v>
@@ -16827,7 +16827,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G633" t="n">
-        <v>1.76603960990906</v>
+        <v>1.76603937149048</v>
       </c>
       <c r="H633" t="s">
         <v>8</v>
@@ -16853,7 +16853,7 @@
         <v>2.25</v>
       </c>
       <c r="G634" t="n">
-        <v>1.75822532176971</v>
+        <v>1.75822520256042</v>
       </c>
       <c r="H634" t="s">
         <v>8</v>
@@ -16879,7 +16879,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G635" t="n">
-        <v>1.72696781158447</v>
+        <v>1.72696805000305</v>
       </c>
       <c r="H635" t="s">
         <v>8</v>
@@ -16905,7 +16905,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G636" t="n">
-        <v>1.75041103363037</v>
+        <v>1.75041091442108</v>
       </c>
       <c r="H636" t="s">
         <v>8</v>
@@ -16957,7 +16957,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G638" t="n">
-        <v>1.82073974609375</v>
+        <v>1.82073986530304</v>
       </c>
       <c r="H638" t="s">
         <v>8</v>
@@ -16983,7 +16983,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G639" t="n">
-        <v>1.7347823381424</v>
+        <v>1.73478221893311</v>
       </c>
       <c r="H639" t="s">
         <v>8</v>
@@ -17061,7 +17061,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G642" t="n">
-        <v>1.75041103363037</v>
+        <v>1.75041091442108</v>
       </c>
       <c r="H642" t="s">
         <v>8</v>
@@ -17113,7 +17113,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G644" t="n">
-        <v>1.74259638786316</v>
+        <v>1.74259662628174</v>
       </c>
       <c r="H644" t="s">
         <v>8</v>
@@ -17243,7 +17243,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G649" t="n">
-        <v>1.70352506637573</v>
+        <v>1.70352494716644</v>
       </c>
       <c r="H649" t="s">
         <v>8</v>
@@ -17295,7 +17295,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G651" t="n">
-        <v>1.68008196353912</v>
+        <v>1.68008184432983</v>
       </c>
       <c r="H651" t="s">
         <v>8</v>
@@ -17321,7 +17321,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G652" t="n">
-        <v>1.68008196353912</v>
+        <v>1.68008184432983</v>
       </c>
       <c r="H652" t="s">
         <v>8</v>
@@ -17347,7 +17347,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G653" t="n">
-        <v>1.66445314884186</v>
+        <v>1.66445326805115</v>
       </c>
       <c r="H653" t="s">
         <v>8</v>
@@ -17373,7 +17373,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G654" t="n">
-        <v>1.66445314884186</v>
+        <v>1.66445326805115</v>
       </c>
       <c r="H654" t="s">
         <v>8</v>
@@ -17399,7 +17399,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G655" t="n">
-        <v>1.61756706237793</v>
+        <v>1.61756694316864</v>
       </c>
       <c r="H655" t="s">
         <v>8</v>
@@ -17425,7 +17425,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G656" t="n">
-        <v>1.61756706237793</v>
+        <v>1.61756694316864</v>
       </c>
       <c r="H656" t="s">
         <v>8</v>
@@ -17451,7 +17451,7 @@
         <v>2</v>
       </c>
       <c r="G657" t="n">
-        <v>1.56286680698395</v>
+        <v>1.56286692619324</v>
       </c>
       <c r="H657" t="s">
         <v>8</v>
@@ -17477,7 +17477,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G658" t="n">
-        <v>1.5941241979599</v>
+        <v>1.59412407875061</v>
       </c>
       <c r="H658" t="s">
         <v>8</v>
@@ -17503,7 +17503,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G659" t="n">
-        <v>1.60193848609924</v>
+        <v>1.60193836688995</v>
       </c>
       <c r="H659" t="s">
         <v>8</v>
@@ -17555,7 +17555,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G661" t="n">
-        <v>1.60193848609924</v>
+        <v>1.60193836688995</v>
       </c>
       <c r="H661" t="s">
         <v>8</v>
@@ -17607,7 +17607,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G663" t="n">
-        <v>1.48472344875336</v>
+        <v>1.48472356796265</v>
       </c>
       <c r="H663" t="s">
         <v>8</v>
@@ -17711,7 +17711,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G667" t="n">
-        <v>2.01609802246094</v>
+        <v>2.01609826087952</v>
       </c>
       <c r="H667" t="s">
         <v>8</v>
@@ -17789,7 +17789,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G670" t="n">
-        <v>1.9926552772522</v>
+        <v>1.99265515804291</v>
       </c>
       <c r="H670" t="s">
         <v>8</v>
@@ -17815,7 +17815,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G671" t="n">
-        <v>1.93014049530029</v>
+        <v>1.93014073371887</v>
       </c>
       <c r="H671" t="s">
         <v>8</v>
@@ -17841,7 +17841,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G672" t="n">
-        <v>1.89888322353363</v>
+        <v>1.89888310432434</v>
       </c>
       <c r="H672" t="s">
         <v>8</v>
@@ -17919,7 +17919,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G675" t="n">
-        <v>1.89106917381287</v>
+        <v>1.89106893539429</v>
       </c>
       <c r="H675" t="s">
         <v>8</v>
@@ -17945,7 +17945,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G676" t="n">
-        <v>1.91451191902161</v>
+        <v>1.91451215744019</v>
       </c>
       <c r="H676" t="s">
         <v>8</v>
@@ -18075,7 +18075,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G681" t="n">
-        <v>1.76603960990906</v>
+        <v>1.76603937149048</v>
       </c>
       <c r="H681" t="s">
         <v>8</v>
@@ -18101,7 +18101,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G682" t="n">
-        <v>1.70352506637573</v>
+        <v>1.70352494716644</v>
       </c>
       <c r="H682" t="s">
         <v>8</v>
@@ -18127,7 +18127,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G683" t="n">
-        <v>1.91451191902161</v>
+        <v>1.91451215744019</v>
       </c>
       <c r="H683" t="s">
         <v>8</v>
@@ -18153,7 +18153,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G684" t="n">
-        <v>1.82073974609375</v>
+        <v>1.82073986530304</v>
       </c>
       <c r="H684" t="s">
         <v>8</v>
@@ -18179,7 +18179,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G685" t="n">
-        <v>1.76603960990906</v>
+        <v>1.76603937149048</v>
       </c>
       <c r="H685" t="s">
         <v>8</v>
@@ -18231,7 +18231,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G687" t="n">
-        <v>1.76603960990906</v>
+        <v>1.76603937149048</v>
       </c>
       <c r="H687" t="s">
         <v>8</v>
@@ -18257,7 +18257,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G688" t="n">
-        <v>1.76603960990906</v>
+        <v>1.76603937149048</v>
       </c>
       <c r="H688" t="s">
         <v>8</v>
@@ -18309,7 +18309,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G690" t="n">
-        <v>1.75041103363037</v>
+        <v>1.75041091442108</v>
       </c>
       <c r="H690" t="s">
         <v>8</v>
@@ -18361,7 +18361,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G692" t="n">
-        <v>1.70352506637573</v>
+        <v>1.70352494716644</v>
       </c>
       <c r="H692" t="s">
         <v>8</v>
@@ -18387,7 +18387,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G693" t="n">
-        <v>1.66445314884186</v>
+        <v>1.66445326805115</v>
       </c>
       <c r="H693" t="s">
         <v>8</v>
@@ -18413,7 +18413,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G694" t="n">
-        <v>1.66445314884186</v>
+        <v>1.66445326805115</v>
       </c>
       <c r="H694" t="s">
         <v>8</v>
@@ -18439,7 +18439,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G695" t="n">
-        <v>1.64882433414459</v>
+        <v>1.64882445335388</v>
       </c>
       <c r="H695" t="s">
         <v>8</v>
@@ -18491,7 +18491,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G697" t="n">
-        <v>1.68008196353912</v>
+        <v>1.68008184432983</v>
       </c>
       <c r="H697" t="s">
         <v>8</v>
@@ -18517,7 +18517,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G698" t="n">
-        <v>1.68008196353912</v>
+        <v>1.68008184432983</v>
       </c>
       <c r="H698" t="s">
         <v>8</v>
@@ -18543,7 +18543,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G699" t="n">
-        <v>1.74259638786316</v>
+        <v>1.74259662628174</v>
       </c>
       <c r="H699" t="s">
         <v>8</v>
@@ -18595,7 +18595,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G701" t="n">
-        <v>1.70352506637573</v>
+        <v>1.70352494716644</v>
       </c>
       <c r="H701" t="s">
         <v>8</v>
@@ -18621,7 +18621,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G702" t="n">
-        <v>1.69571053981781</v>
+        <v>1.69571042060852</v>
       </c>
       <c r="H702" t="s">
         <v>8</v>
@@ -18647,7 +18647,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G703" t="n">
-        <v>1.64882433414459</v>
+        <v>1.64882445335388</v>
       </c>
       <c r="H703" t="s">
         <v>8</v>
@@ -18699,7 +18699,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G705" t="n">
-        <v>1.69571053981781</v>
+        <v>1.69571042060852</v>
       </c>
       <c r="H705" t="s">
         <v>8</v>
@@ -18725,7 +18725,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G706" t="n">
-        <v>1.68789637088776</v>
+        <v>1.68789613246918</v>
       </c>
       <c r="H706" t="s">
         <v>8</v>
@@ -18751,7 +18751,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G707" t="n">
-        <v>1.62538135051727</v>
+        <v>1.62538146972656</v>
       </c>
       <c r="H707" t="s">
         <v>8</v>
@@ -18803,7 +18803,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G709" t="n">
-        <v>1.68789637088776</v>
+        <v>1.68789613246918</v>
       </c>
       <c r="H709" t="s">
         <v>8</v>
@@ -18855,7 +18855,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G711" t="n">
-        <v>1.68008196353912</v>
+        <v>1.68008184432983</v>
       </c>
       <c r="H711" t="s">
         <v>8</v>
@@ -18881,7 +18881,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G712" t="n">
-        <v>1.68008196353912</v>
+        <v>1.68008184432983</v>
       </c>
       <c r="H712" t="s">
         <v>8</v>
@@ -18959,7 +18959,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G715" t="n">
-        <v>1.61756706237793</v>
+        <v>1.61756694316864</v>
       </c>
       <c r="H715" t="s">
         <v>8</v>
@@ -18985,7 +18985,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G716" t="n">
-        <v>1.61756706237793</v>
+        <v>1.61756694316864</v>
       </c>
       <c r="H716" t="s">
         <v>8</v>
@@ -19037,7 +19037,7 @@
         <v>2</v>
       </c>
       <c r="G718" t="n">
-        <v>1.56286680698395</v>
+        <v>1.56286692619324</v>
       </c>
       <c r="H718" t="s">
         <v>8</v>
@@ -19141,7 +19141,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G722" t="n">
-        <v>1.61756706237793</v>
+        <v>1.61756694316864</v>
       </c>
       <c r="H722" t="s">
         <v>8</v>
@@ -19167,7 +19167,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G723" t="n">
-        <v>1.60193848609924</v>
+        <v>1.60193836688995</v>
       </c>
       <c r="H723" t="s">
         <v>8</v>
@@ -19193,7 +19193,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G724" t="n">
-        <v>1.60193848609924</v>
+        <v>1.60193836688995</v>
       </c>
       <c r="H724" t="s">
         <v>8</v>
@@ -19219,7 +19219,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G725" t="n">
-        <v>1.60193848609924</v>
+        <v>1.60193836688995</v>
       </c>
       <c r="H725" t="s">
         <v>8</v>
@@ -19245,7 +19245,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G726" t="n">
-        <v>1.60193848609924</v>
+        <v>1.60193836688995</v>
       </c>
       <c r="H726" t="s">
         <v>8</v>
@@ -19271,7 +19271,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G727" t="n">
-        <v>1.60193848609924</v>
+        <v>1.60193836688995</v>
       </c>
       <c r="H727" t="s">
         <v>8</v>
@@ -19297,7 +19297,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G728" t="n">
-        <v>1.5941241979599</v>
+        <v>1.59412407875061</v>
       </c>
       <c r="H728" t="s">
         <v>8</v>
@@ -19401,7 +19401,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G732" t="n">
-        <v>1.60193848609924</v>
+        <v>1.60193836688995</v>
       </c>
       <c r="H732" t="s">
         <v>8</v>
@@ -19453,7 +19453,7 @@
         <v>2</v>
       </c>
       <c r="G734" t="n">
-        <v>1.56286680698395</v>
+        <v>1.56286692619324</v>
       </c>
       <c r="H734" t="s">
         <v>8</v>
@@ -19505,7 +19505,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G736" t="n">
-        <v>1.53160953521729</v>
+        <v>1.531609416008</v>
       </c>
       <c r="H736" t="s">
         <v>8</v>
@@ -19531,7 +19531,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G737" t="n">
-        <v>1.50816655158997</v>
+        <v>1.50816643238068</v>
       </c>
       <c r="H737" t="s">
         <v>8</v>
@@ -19557,7 +19557,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G738" t="n">
-        <v>1.50035214424133</v>
+        <v>1.50035202503204</v>
       </c>
       <c r="H738" t="s">
         <v>8</v>
@@ -19609,7 +19609,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G740" t="n">
-        <v>1.53160953521729</v>
+        <v>1.531609416008</v>
       </c>
       <c r="H740" t="s">
         <v>8</v>
@@ -19635,7 +19635,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G741" t="n">
-        <v>1.50035214424133</v>
+        <v>1.50035202503204</v>
       </c>
       <c r="H741" t="s">
         <v>8</v>
@@ -19661,7 +19661,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G742" t="n">
-        <v>1.50816655158997</v>
+        <v>1.50816643238068</v>
       </c>
       <c r="H742" t="s">
         <v>8</v>
@@ -19713,7 +19713,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G744" t="n">
-        <v>1.62538135051727</v>
+        <v>1.62538146972656</v>
       </c>
       <c r="H744" t="s">
         <v>8</v>
@@ -19765,7 +19765,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G746" t="n">
-        <v>1.5941241979599</v>
+        <v>1.59412407875061</v>
       </c>
       <c r="H746" t="s">
         <v>8</v>
@@ -19869,7 +19869,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G750" t="n">
-        <v>1.51598107814789</v>
+        <v>1.51598083972931</v>
       </c>
       <c r="H750" t="s">
         <v>8</v>
@@ -19895,7 +19895,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G751" t="n">
-        <v>1.57849550247192</v>
+        <v>1.57849538326263</v>
       </c>
       <c r="H751" t="s">
         <v>8</v>
@@ -19921,7 +19921,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G752" t="n">
-        <v>1.52379524707794</v>
+        <v>1.52379512786865</v>
       </c>
       <c r="H752" t="s">
         <v>8</v>
@@ -19947,7 +19947,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G753" t="n">
-        <v>1.52379524707794</v>
+        <v>1.52379512786865</v>
       </c>
       <c r="H753" t="s">
         <v>8</v>
@@ -19973,7 +19973,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G754" t="n">
-        <v>1.52379524707794</v>
+        <v>1.52379512786865</v>
       </c>
       <c r="H754" t="s">
         <v>8</v>
@@ -19999,7 +19999,7 @@
         <v>2</v>
       </c>
       <c r="G755" t="n">
-        <v>1.56286680698395</v>
+        <v>1.56286692619324</v>
       </c>
       <c r="H755" t="s">
         <v>8</v>
@@ -20051,7 +20051,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G757" t="n">
-        <v>1.50816655158997</v>
+        <v>1.50816643238068</v>
       </c>
       <c r="H757" t="s">
         <v>8</v>
@@ -20077,7 +20077,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G758" t="n">
-        <v>1.48472344875336</v>
+        <v>1.48472356796265</v>
       </c>
       <c r="H758" t="s">
         <v>8</v>
@@ -20103,7 +20103,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G759" t="n">
-        <v>1.48472344875336</v>
+        <v>1.48472356796265</v>
       </c>
       <c r="H759" t="s">
         <v>8</v>
@@ -20181,7 +20181,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G762" t="n">
-        <v>1.47690916061401</v>
+        <v>1.47690904140472</v>
       </c>
       <c r="H762" t="s">
         <v>8</v>
@@ -20207,7 +20207,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G763" t="n">
-        <v>1.51598107814789</v>
+        <v>1.51598083972931</v>
       </c>
       <c r="H763" t="s">
         <v>8</v>
@@ -20233,7 +20233,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G764" t="n">
-        <v>1.50816655158997</v>
+        <v>1.50816643238068</v>
       </c>
       <c r="H764" t="s">
         <v>8</v>
@@ -20259,7 +20259,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G765" t="n">
-        <v>1.74259638786316</v>
+        <v>1.74259662628174</v>
       </c>
       <c r="H765" t="s">
         <v>8</v>
@@ -20493,7 +20493,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G774" t="n">
-        <v>1.57849550247192</v>
+        <v>1.57849538326263</v>
       </c>
       <c r="H774" t="s">
         <v>8</v>
@@ -20545,7 +20545,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G776" t="n">
-        <v>1.53160953521729</v>
+        <v>1.531609416008</v>
       </c>
       <c r="H776" t="s">
         <v>8</v>
@@ -20623,7 +20623,7 @@
         <v>2</v>
       </c>
       <c r="G779" t="n">
-        <v>1.56286680698395</v>
+        <v>1.56286692619324</v>
       </c>
       <c r="H779" t="s">
         <v>8</v>
@@ -20649,7 +20649,7 @@
         <v>2</v>
       </c>
       <c r="G780" t="n">
-        <v>1.56286680698395</v>
+        <v>1.56286692619324</v>
       </c>
       <c r="H780" t="s">
         <v>8</v>
@@ -20701,7 +20701,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G782" t="n">
-        <v>1.53160953521729</v>
+        <v>1.531609416008</v>
       </c>
       <c r="H782" t="s">
         <v>8</v>
@@ -20727,7 +20727,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G783" t="n">
-        <v>1.53160953521729</v>
+        <v>1.531609416008</v>
       </c>
       <c r="H783" t="s">
         <v>8</v>
@@ -20753,7 +20753,7 @@
         <v>2</v>
       </c>
       <c r="G784" t="n">
-        <v>1.56286680698395</v>
+        <v>1.56286692619324</v>
       </c>
       <c r="H784" t="s">
         <v>8</v>
@@ -20779,7 +20779,7 @@
         <v>2</v>
       </c>
       <c r="G785" t="n">
-        <v>1.56286680698395</v>
+        <v>1.56286692619324</v>
       </c>
       <c r="H785" t="s">
         <v>8</v>
@@ -20857,7 +20857,7 @@
         <v>2</v>
       </c>
       <c r="G788" t="n">
-        <v>1.56286680698395</v>
+        <v>1.56286692619324</v>
       </c>
       <c r="H788" t="s">
         <v>8</v>
@@ -20883,7 +20883,7 @@
         <v>2</v>
       </c>
       <c r="G789" t="n">
-        <v>1.56286680698395</v>
+        <v>1.56286692619324</v>
       </c>
       <c r="H789" t="s">
         <v>8</v>
@@ -20935,7 +20935,7 @@
         <v>2</v>
       </c>
       <c r="G791" t="n">
-        <v>1.56286680698395</v>
+        <v>1.56286692619324</v>
       </c>
       <c r="H791" t="s">
         <v>8</v>
@@ -21039,7 +21039,7 @@
         <v>2</v>
       </c>
       <c r="G795" t="n">
-        <v>1.56286680698395</v>
+        <v>1.56286692619324</v>
       </c>
       <c r="H795" t="s">
         <v>8</v>
@@ -21065,7 +21065,7 @@
         <v>2</v>
       </c>
       <c r="G796" t="n">
-        <v>1.56286680698395</v>
+        <v>1.56286692619324</v>
       </c>
       <c r="H796" t="s">
         <v>8</v>
@@ -21117,7 +21117,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G798" t="n">
-        <v>1.57849550247192</v>
+        <v>1.57849538326263</v>
       </c>
       <c r="H798" t="s">
         <v>8</v>
@@ -21143,7 +21143,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G799" t="n">
-        <v>1.5941241979599</v>
+        <v>1.59412407875061</v>
       </c>
       <c r="H799" t="s">
         <v>8</v>
@@ -21273,7 +21273,7 @@
         <v>2</v>
       </c>
       <c r="G804" t="n">
-        <v>1.56286680698395</v>
+        <v>1.56286692619324</v>
       </c>
       <c r="H804" t="s">
         <v>8</v>
@@ -21299,7 +21299,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G805" t="n">
-        <v>1.5941241979599</v>
+        <v>1.59412407875061</v>
       </c>
       <c r="H805" t="s">
         <v>8</v>
@@ -21403,7 +21403,7 @@
         <v>2</v>
       </c>
       <c r="G809" t="n">
-        <v>1.56286680698395</v>
+        <v>1.56286692619324</v>
       </c>
       <c r="H809" t="s">
         <v>8</v>
@@ -21429,7 +21429,7 @@
         <v>2</v>
       </c>
       <c r="G810" t="n">
-        <v>1.56286680698395</v>
+        <v>1.56286692619324</v>
       </c>
       <c r="H810" t="s">
         <v>8</v>
@@ -21507,7 +21507,7 @@
         <v>2</v>
       </c>
       <c r="G813" t="n">
-        <v>1.56286680698395</v>
+        <v>1.56286692619324</v>
       </c>
       <c r="H813" t="s">
         <v>8</v>
@@ -21559,7 +21559,7 @@
         <v>2</v>
       </c>
       <c r="G815" t="n">
-        <v>1.56286680698395</v>
+        <v>1.56286692619324</v>
       </c>
       <c r="H815" t="s">
         <v>8</v>
@@ -21585,7 +21585,7 @@
         <v>2</v>
       </c>
       <c r="G816" t="n">
-        <v>1.56286680698395</v>
+        <v>1.56286692619324</v>
       </c>
       <c r="H816" t="s">
         <v>8</v>
@@ -21611,7 +21611,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G817" t="n">
-        <v>1.68008196353912</v>
+        <v>1.68008184432983</v>
       </c>
       <c r="H817" t="s">
         <v>8</v>
@@ -21715,7 +21715,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G821" t="n">
-        <v>1.62538135051727</v>
+        <v>1.62538146972656</v>
       </c>
       <c r="H821" t="s">
         <v>8</v>
@@ -21741,7 +21741,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G822" t="n">
-        <v>1.61756706237793</v>
+        <v>1.61756694316864</v>
       </c>
       <c r="H822" t="s">
         <v>8</v>
@@ -21767,7 +21767,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G823" t="n">
-        <v>1.57849550247192</v>
+        <v>1.57849538326263</v>
       </c>
       <c r="H823" t="s">
         <v>8</v>
@@ -21793,7 +21793,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G824" t="n">
-        <v>1.57849550247192</v>
+        <v>1.57849538326263</v>
       </c>
       <c r="H824" t="s">
         <v>8</v>
@@ -21845,7 +21845,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G826" t="n">
-        <v>1.5941241979599</v>
+        <v>1.59412407875061</v>
       </c>
       <c r="H826" t="s">
         <v>8</v>
@@ -21871,7 +21871,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G827" t="n">
-        <v>1.62538135051727</v>
+        <v>1.62538146972656</v>
       </c>
       <c r="H827" t="s">
         <v>8</v>
@@ -21897,7 +21897,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G828" t="n">
-        <v>1.89106917381287</v>
+        <v>1.89106893539429</v>
       </c>
       <c r="H828" t="s">
         <v>8</v>
@@ -21923,7 +21923,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G829" t="n">
-        <v>1.7347823381424</v>
+        <v>1.73478221893311</v>
       </c>
       <c r="H829" t="s">
         <v>8</v>
@@ -22105,7 +22105,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G836" t="n">
-        <v>1.62538135051727</v>
+        <v>1.62538146972656</v>
       </c>
       <c r="H836" t="s">
         <v>8</v>
@@ -22209,7 +22209,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G840" t="n">
-        <v>1.5941241979599</v>
+        <v>1.59412407875061</v>
       </c>
       <c r="H840" t="s">
         <v>8</v>
@@ -22261,7 +22261,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G842" t="n">
-        <v>1.5941241979599</v>
+        <v>1.59412407875061</v>
       </c>
       <c r="H842" t="s">
         <v>8</v>
@@ -22287,7 +22287,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G843" t="n">
-        <v>1.57849550247192</v>
+        <v>1.57849538326263</v>
       </c>
       <c r="H843" t="s">
         <v>8</v>
@@ -22339,7 +22339,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G845" t="n">
-        <v>1.62538135051727</v>
+        <v>1.62538146972656</v>
       </c>
       <c r="H845" t="s">
         <v>8</v>
@@ -22391,7 +22391,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G847" t="n">
-        <v>1.62538135051727</v>
+        <v>1.62538146972656</v>
       </c>
       <c r="H847" t="s">
         <v>8</v>
@@ -22443,7 +22443,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G849" t="n">
-        <v>1.5941241979599</v>
+        <v>1.59412407875061</v>
       </c>
       <c r="H849" t="s">
         <v>8</v>
@@ -22469,7 +22469,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G850" t="n">
-        <v>1.5941241979599</v>
+        <v>1.59412407875061</v>
       </c>
       <c r="H850" t="s">
         <v>8</v>
@@ -22495,7 +22495,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G851" t="n">
-        <v>1.57849550247192</v>
+        <v>1.57849538326263</v>
       </c>
       <c r="H851" t="s">
         <v>8</v>
@@ -22521,7 +22521,7 @@
         <v>2</v>
       </c>
       <c r="G852" t="n">
-        <v>1.56286680698395</v>
+        <v>1.56286692619324</v>
       </c>
       <c r="H852" t="s">
         <v>8</v>
@@ -22547,7 +22547,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G853" t="n">
-        <v>1.53160953521729</v>
+        <v>1.531609416008</v>
       </c>
       <c r="H853" t="s">
         <v>8</v>
@@ -22573,7 +22573,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G854" t="n">
-        <v>1.5941241979599</v>
+        <v>1.59412407875061</v>
       </c>
       <c r="H854" t="s">
         <v>8</v>
@@ -22599,7 +22599,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G855" t="n">
-        <v>1.53160953521729</v>
+        <v>1.531609416008</v>
       </c>
       <c r="H855" t="s">
         <v>8</v>
@@ -22651,7 +22651,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G857" t="n">
-        <v>1.53160953521729</v>
+        <v>1.531609416008</v>
       </c>
       <c r="H857" t="s">
         <v>8</v>
@@ -22677,7 +22677,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G858" t="n">
-        <v>1.51598107814789</v>
+        <v>1.51598083972931</v>
       </c>
       <c r="H858" t="s">
         <v>8</v>
@@ -22703,7 +22703,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G859" t="n">
-        <v>1.57849550247192</v>
+        <v>1.57849538326263</v>
       </c>
       <c r="H859" t="s">
         <v>8</v>
@@ -22729,7 +22729,7 @@
         <v>2</v>
       </c>
       <c r="G860" t="n">
-        <v>1.56286680698395</v>
+        <v>1.56286692619324</v>
       </c>
       <c r="H860" t="s">
         <v>8</v>
@@ -22755,7 +22755,7 @@
         <v>2</v>
       </c>
       <c r="G861" t="n">
-        <v>1.56286680698395</v>
+        <v>1.56286692619324</v>
       </c>
       <c r="H861" t="s">
         <v>8</v>
@@ -22781,7 +22781,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G862" t="n">
-        <v>1.51598107814789</v>
+        <v>1.51598083972931</v>
       </c>
       <c r="H862" t="s">
         <v>8</v>
@@ -22807,7 +22807,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G863" t="n">
-        <v>1.51598107814789</v>
+        <v>1.51598083972931</v>
       </c>
       <c r="H863" t="s">
         <v>8</v>
@@ -22833,7 +22833,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G864" t="n">
-        <v>1.51598107814789</v>
+        <v>1.51598083972931</v>
       </c>
       <c r="H864" t="s">
         <v>8</v>
@@ -22859,7 +22859,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G865" t="n">
-        <v>1.50035214424133</v>
+        <v>1.50035202503204</v>
       </c>
       <c r="H865" t="s">
         <v>8</v>
@@ -22885,7 +22885,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G866" t="n">
-        <v>1.50035214424133</v>
+        <v>1.50035202503204</v>
       </c>
       <c r="H866" t="s">
         <v>8</v>
@@ -22911,7 +22911,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G867" t="n">
-        <v>1.53160953521729</v>
+        <v>1.531609416008</v>
       </c>
       <c r="H867" t="s">
         <v>8</v>
@@ -22937,7 +22937,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G868" t="n">
-        <v>1.46909475326538</v>
+        <v>1.46909487247467</v>
       </c>
       <c r="H868" t="s">
         <v>8</v>
@@ -22963,7 +22963,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G869" t="n">
-        <v>1.4534660577774</v>
+        <v>1.45346617698669</v>
       </c>
       <c r="H869" t="s">
         <v>8</v>
@@ -22989,7 +22989,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G870" t="n">
-        <v>1.46909475326538</v>
+        <v>1.46909487247467</v>
       </c>
       <c r="H870" t="s">
         <v>8</v>
@@ -23015,7 +23015,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G871" t="n">
-        <v>1.50035214424133</v>
+        <v>1.50035202503204</v>
       </c>
       <c r="H871" t="s">
         <v>8</v>
@@ -23041,7 +23041,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G872" t="n">
-        <v>1.50035214424133</v>
+        <v>1.50035202503204</v>
       </c>
       <c r="H872" t="s">
         <v>8</v>
@@ -23067,7 +23067,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G873" t="n">
-        <v>1.46909475326538</v>
+        <v>1.46909487247467</v>
       </c>
       <c r="H873" t="s">
         <v>8</v>
@@ -23093,7 +23093,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G874" t="n">
-        <v>1.48472344875336</v>
+        <v>1.48472356796265</v>
       </c>
       <c r="H874" t="s">
         <v>8</v>
@@ -23119,7 +23119,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G875" t="n">
-        <v>1.4534660577774</v>
+        <v>1.45346617698669</v>
       </c>
       <c r="H875" t="s">
         <v>8</v>
@@ -23145,7 +23145,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G876" t="n">
-        <v>1.4534660577774</v>
+        <v>1.45346617698669</v>
       </c>
       <c r="H876" t="s">
         <v>8</v>
@@ -23171,7 +23171,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G877" t="n">
-        <v>1.51598107814789</v>
+        <v>1.51598083972931</v>
       </c>
       <c r="H877" t="s">
         <v>8</v>
@@ -23197,7 +23197,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G878" t="n">
-        <v>1.53160953521729</v>
+        <v>1.531609416008</v>
       </c>
       <c r="H878" t="s">
         <v>8</v>
@@ -23223,7 +23223,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G879" t="n">
-        <v>1.48472344875336</v>
+        <v>1.48472356796265</v>
       </c>
       <c r="H879" t="s">
         <v>8</v>
@@ -23249,7 +23249,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G880" t="n">
-        <v>1.46909475326538</v>
+        <v>1.46909487247467</v>
       </c>
       <c r="H880" t="s">
         <v>8</v>
@@ -23275,7 +23275,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G881" t="n">
-        <v>1.4534660577774</v>
+        <v>1.45346617698669</v>
       </c>
       <c r="H881" t="s">
         <v>8</v>
@@ -23327,7 +23327,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G883" t="n">
-        <v>1.4534660577774</v>
+        <v>1.45346617698669</v>
       </c>
       <c r="H883" t="s">
         <v>8</v>
@@ -23353,7 +23353,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G884" t="n">
-        <v>1.4534660577774</v>
+        <v>1.45346617698669</v>
       </c>
       <c r="H884" t="s">
         <v>8</v>
@@ -23405,7 +23405,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G886" t="n">
-        <v>1.46909475326538</v>
+        <v>1.46909487247467</v>
       </c>
       <c r="H886" t="s">
         <v>8</v>
@@ -23431,7 +23431,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G887" t="n">
-        <v>1.48472344875336</v>
+        <v>1.48472356796265</v>
       </c>
       <c r="H887" t="s">
         <v>8</v>
@@ -23457,7 +23457,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G888" t="n">
-        <v>1.48472344875336</v>
+        <v>1.48472356796265</v>
       </c>
       <c r="H888" t="s">
         <v>8</v>
@@ -23483,7 +23483,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G889" t="n">
-        <v>1.51598107814789</v>
+        <v>1.51598083972931</v>
       </c>
       <c r="H889" t="s">
         <v>8</v>
@@ -23509,7 +23509,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G890" t="n">
-        <v>1.51598107814789</v>
+        <v>1.51598083972931</v>
       </c>
       <c r="H890" t="s">
         <v>8</v>
@@ -23535,7 +23535,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G891" t="n">
-        <v>1.51598107814789</v>
+        <v>1.51598083972931</v>
       </c>
       <c r="H891" t="s">
         <v>8</v>
@@ -23561,7 +23561,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G892" t="n">
-        <v>1.53160953521729</v>
+        <v>1.531609416008</v>
       </c>
       <c r="H892" t="s">
         <v>8</v>
@@ -23587,7 +23587,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G893" t="n">
-        <v>1.51598107814789</v>
+        <v>1.51598083972931</v>
       </c>
       <c r="H893" t="s">
         <v>8</v>
@@ -23613,7 +23613,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G894" t="n">
-        <v>1.48472344875336</v>
+        <v>1.48472356796265</v>
       </c>
       <c r="H894" t="s">
         <v>8</v>
@@ -23639,7 +23639,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G895" t="n">
-        <v>1.53160953521729</v>
+        <v>1.531609416008</v>
       </c>
       <c r="H895" t="s">
         <v>8</v>
@@ -23665,7 +23665,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G896" t="n">
-        <v>1.53160953521729</v>
+        <v>1.531609416008</v>
       </c>
       <c r="H896" t="s">
         <v>8</v>
@@ -23717,7 +23717,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G898" t="n">
-        <v>1.50035214424133</v>
+        <v>1.50035202503204</v>
       </c>
       <c r="H898" t="s">
         <v>8</v>
@@ -23743,7 +23743,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G899" t="n">
-        <v>1.50035214424133</v>
+        <v>1.50035202503204</v>
       </c>
       <c r="H899" t="s">
         <v>8</v>
@@ -23769,7 +23769,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G900" t="n">
-        <v>1.50035214424133</v>
+        <v>1.50035202503204</v>
       </c>
       <c r="H900" t="s">
         <v>8</v>
@@ -23821,7 +23821,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G902" t="n">
-        <v>1.51598107814789</v>
+        <v>1.51598083972931</v>
       </c>
       <c r="H902" t="s">
         <v>8</v>
@@ -23847,7 +23847,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G903" t="n">
-        <v>1.51598107814789</v>
+        <v>1.51598083972931</v>
       </c>
       <c r="H903" t="s">
         <v>8</v>
@@ -23873,7 +23873,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G904" t="n">
-        <v>1.53160953521729</v>
+        <v>1.531609416008</v>
       </c>
       <c r="H904" t="s">
         <v>8</v>
@@ -23899,7 +23899,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G905" t="n">
-        <v>1.53160953521729</v>
+        <v>1.531609416008</v>
       </c>
       <c r="H905" t="s">
         <v>8</v>
@@ -23925,7 +23925,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G906" t="n">
-        <v>1.50035214424133</v>
+        <v>1.50035202503204</v>
       </c>
       <c r="H906" t="s">
         <v>8</v>
@@ -23951,7 +23951,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G907" t="n">
-        <v>1.50035214424133</v>
+        <v>1.50035202503204</v>
       </c>
       <c r="H907" t="s">
         <v>8</v>
@@ -23977,7 +23977,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G908" t="n">
-        <v>1.51598107814789</v>
+        <v>1.51598083972931</v>
       </c>
       <c r="H908" t="s">
         <v>8</v>
@@ -24003,7 +24003,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G909" t="n">
-        <v>1.51598107814789</v>
+        <v>1.51598083972931</v>
       </c>
       <c r="H909" t="s">
         <v>8</v>
@@ -24029,7 +24029,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G910" t="n">
-        <v>1.50035214424133</v>
+        <v>1.50035202503204</v>
       </c>
       <c r="H910" t="s">
         <v>8</v>
@@ -24055,7 +24055,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G911" t="n">
-        <v>1.48472344875336</v>
+        <v>1.48472356796265</v>
       </c>
       <c r="H911" t="s">
         <v>8</v>
@@ -24081,7 +24081,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G912" t="n">
-        <v>1.51598107814789</v>
+        <v>1.51598083972931</v>
       </c>
       <c r="H912" t="s">
         <v>8</v>
@@ -24107,7 +24107,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G913" t="n">
-        <v>1.50035214424133</v>
+        <v>1.50035202503204</v>
       </c>
       <c r="H913" t="s">
         <v>8</v>
@@ -24133,7 +24133,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G914" t="n">
-        <v>1.51598107814789</v>
+        <v>1.51598083972931</v>
       </c>
       <c r="H914" t="s">
         <v>8</v>
@@ -24159,7 +24159,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G915" t="n">
-        <v>1.51598107814789</v>
+        <v>1.51598083972931</v>
       </c>
       <c r="H915" t="s">
         <v>8</v>
@@ -24185,7 +24185,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G916" t="n">
-        <v>1.50035214424133</v>
+        <v>1.50035202503204</v>
       </c>
       <c r="H916" t="s">
         <v>8</v>
@@ -24211,7 +24211,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G917" t="n">
-        <v>1.50035214424133</v>
+        <v>1.50035202503204</v>
       </c>
       <c r="H917" t="s">
         <v>8</v>
@@ -24237,7 +24237,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G918" t="n">
-        <v>1.46909475326538</v>
+        <v>1.46909487247467</v>
       </c>
       <c r="H918" t="s">
         <v>8</v>
@@ -24263,7 +24263,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G919" t="n">
-        <v>1.4534660577774</v>
+        <v>1.45346617698669</v>
       </c>
       <c r="H919" t="s">
         <v>8</v>
@@ -24289,7 +24289,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G920" t="n">
-        <v>1.4534660577774</v>
+        <v>1.45346617698669</v>
       </c>
       <c r="H920" t="s">
         <v>8</v>
@@ -24315,7 +24315,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G921" t="n">
-        <v>1.48472344875336</v>
+        <v>1.48472356796265</v>
       </c>
       <c r="H921" t="s">
         <v>8</v>
@@ -24341,7 +24341,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G922" t="n">
-        <v>1.46909475326538</v>
+        <v>1.46909487247467</v>
       </c>
       <c r="H922" t="s">
         <v>8</v>
@@ -24367,7 +24367,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G923" t="n">
-        <v>1.46909475326538</v>
+        <v>1.46909487247467</v>
       </c>
       <c r="H923" t="s">
         <v>8</v>
@@ -24393,7 +24393,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G924" t="n">
-        <v>1.4534660577774</v>
+        <v>1.45346617698669</v>
       </c>
       <c r="H924" t="s">
         <v>8</v>
@@ -24419,7 +24419,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G925" t="n">
-        <v>1.48472344875336</v>
+        <v>1.48472356796265</v>
       </c>
       <c r="H925" t="s">
         <v>8</v>
@@ -24445,7 +24445,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G926" t="n">
-        <v>1.50035214424133</v>
+        <v>1.50035202503204</v>
       </c>
       <c r="H926" t="s">
         <v>8</v>
@@ -24471,7 +24471,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G927" t="n">
-        <v>1.50035214424133</v>
+        <v>1.50035202503204</v>
       </c>
       <c r="H927" t="s">
         <v>8</v>
@@ -24497,7 +24497,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G928" t="n">
-        <v>1.4534660577774</v>
+        <v>1.45346617698669</v>
       </c>
       <c r="H928" t="s">
         <v>8</v>
@@ -24523,7 +24523,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G929" t="n">
-        <v>1.4534660577774</v>
+        <v>1.45346617698669</v>
       </c>
       <c r="H929" t="s">
         <v>8</v>
@@ -24549,7 +24549,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G930" t="n">
-        <v>1.48472344875336</v>
+        <v>1.48472356796265</v>
       </c>
       <c r="H930" t="s">
         <v>8</v>
@@ -24575,7 +24575,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G931" t="n">
-        <v>1.48472344875336</v>
+        <v>1.48472356796265</v>
       </c>
       <c r="H931" t="s">
         <v>8</v>
@@ -24601,7 +24601,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G932" t="n">
-        <v>1.46909475326538</v>
+        <v>1.46909487247467</v>
       </c>
       <c r="H932" t="s">
         <v>8</v>
@@ -24627,7 +24627,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G933" t="n">
-        <v>1.50035214424133</v>
+        <v>1.50035202503204</v>
       </c>
       <c r="H933" t="s">
         <v>8</v>
@@ -24653,7 +24653,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G934" t="n">
-        <v>1.46909475326538</v>
+        <v>1.46909487247467</v>
       </c>
       <c r="H934" t="s">
         <v>8</v>
@@ -24679,7 +24679,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G935" t="n">
-        <v>1.51598107814789</v>
+        <v>1.51598083972931</v>
       </c>
       <c r="H935" t="s">
         <v>8</v>
@@ -24705,7 +24705,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G936" t="n">
-        <v>1.51598107814789</v>
+        <v>1.51598083972931</v>
       </c>
       <c r="H936" t="s">
         <v>8</v>
@@ -24731,7 +24731,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G937" t="n">
-        <v>1.51598107814789</v>
+        <v>1.51598083972931</v>
       </c>
       <c r="H937" t="s">
         <v>8</v>
@@ -24757,7 +24757,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G938" t="n">
-        <v>1.51598107814789</v>
+        <v>1.51598083972931</v>
       </c>
       <c r="H938" t="s">
         <v>8</v>
@@ -24783,7 +24783,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G939" t="n">
-        <v>1.51598107814789</v>
+        <v>1.51598083972931</v>
       </c>
       <c r="H939" t="s">
         <v>8</v>
@@ -24809,7 +24809,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G940" t="n">
-        <v>1.50035214424133</v>
+        <v>1.50035202503204</v>
       </c>
       <c r="H940" t="s">
         <v>8</v>
@@ -24835,7 +24835,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G941" t="n">
-        <v>1.53160953521729</v>
+        <v>1.531609416008</v>
       </c>
       <c r="H941" t="s">
         <v>8</v>
@@ -24861,7 +24861,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G942" t="n">
-        <v>1.48472344875336</v>
+        <v>1.48472356796265</v>
       </c>
       <c r="H942" t="s">
         <v>8</v>
@@ -24887,7 +24887,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G943" t="n">
-        <v>1.51598107814789</v>
+        <v>1.51598083972931</v>
       </c>
       <c r="H943" t="s">
         <v>8</v>
@@ -24913,7 +24913,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G944" t="n">
-        <v>1.51598107814789</v>
+        <v>1.51598083972931</v>
       </c>
       <c r="H944" t="s">
         <v>8</v>
@@ -24939,7 +24939,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G945" t="n">
-        <v>1.51598107814789</v>
+        <v>1.51598083972931</v>
       </c>
       <c r="H945" t="s">
         <v>8</v>
@@ -24965,7 +24965,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G946" t="n">
-        <v>1.51598107814789</v>
+        <v>1.51598083972931</v>
       </c>
       <c r="H946" t="s">
         <v>8</v>
@@ -24991,7 +24991,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G947" t="n">
-        <v>1.48472344875336</v>
+        <v>1.48472356796265</v>
       </c>
       <c r="H947" t="s">
         <v>8</v>
@@ -25017,7 +25017,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G948" t="n">
-        <v>1.51598107814789</v>
+        <v>1.51598083972931</v>
       </c>
       <c r="H948" t="s">
         <v>8</v>
@@ -25043,7 +25043,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G949" t="n">
-        <v>1.50035214424133</v>
+        <v>1.50035202503204</v>
       </c>
       <c r="H949" t="s">
         <v>8</v>
@@ -25069,7 +25069,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G950" t="n">
-        <v>1.50035214424133</v>
+        <v>1.50035202503204</v>
       </c>
       <c r="H950" t="s">
         <v>8</v>
@@ -25095,7 +25095,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G951" t="n">
-        <v>1.50035214424133</v>
+        <v>1.50035202503204</v>
       </c>
       <c r="H951" t="s">
         <v>8</v>
@@ -25121,7 +25121,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G952" t="n">
-        <v>1.50035214424133</v>
+        <v>1.50035202503204</v>
       </c>
       <c r="H952" t="s">
         <v>8</v>
@@ -25147,7 +25147,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G953" t="n">
-        <v>1.50035214424133</v>
+        <v>1.50035202503204</v>
       </c>
       <c r="H953" t="s">
         <v>8</v>
@@ -25173,7 +25173,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G954" t="n">
-        <v>1.50035214424133</v>
+        <v>1.50035202503204</v>
       </c>
       <c r="H954" t="s">
         <v>8</v>
@@ -25199,7 +25199,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G955" t="n">
-        <v>1.48472344875336</v>
+        <v>1.48472356796265</v>
       </c>
       <c r="H955" t="s">
         <v>8</v>
@@ -25225,7 +25225,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G956" t="n">
-        <v>1.46909475326538</v>
+        <v>1.46909487247467</v>
       </c>
       <c r="H956" t="s">
         <v>8</v>
@@ -25251,7 +25251,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G957" t="n">
-        <v>1.46909475326538</v>
+        <v>1.46909487247467</v>
       </c>
       <c r="H957" t="s">
         <v>8</v>
@@ -25277,7 +25277,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G958" t="n">
-        <v>1.4534660577774</v>
+        <v>1.45346617698669</v>
       </c>
       <c r="H958" t="s">
         <v>8</v>
@@ -25329,7 +25329,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G960" t="n">
-        <v>1.46909475326538</v>
+        <v>1.46909487247467</v>
       </c>
       <c r="H960" t="s">
         <v>8</v>
@@ -25355,7 +25355,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G961" t="n">
-        <v>1.46909475326538</v>
+        <v>1.46909487247467</v>
       </c>
       <c r="H961" t="s">
         <v>8</v>
@@ -25381,7 +25381,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G962" t="n">
-        <v>1.4534660577774</v>
+        <v>1.45346617698669</v>
       </c>
       <c r="H962" t="s">
         <v>8</v>
@@ -25407,7 +25407,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G963" t="n">
-        <v>1.48472344875336</v>
+        <v>1.48472356796265</v>
       </c>
       <c r="H963" t="s">
         <v>8</v>
@@ -25433,7 +25433,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G964" t="n">
-        <v>1.48472344875336</v>
+        <v>1.48472356796265</v>
       </c>
       <c r="H964" t="s">
         <v>8</v>
@@ -25459,7 +25459,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G965" t="n">
-        <v>1.48472344875336</v>
+        <v>1.48472356796265</v>
       </c>
       <c r="H965" t="s">
         <v>8</v>
@@ -25485,7 +25485,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G966" t="n">
-        <v>1.46909475326538</v>
+        <v>1.46909487247467</v>
       </c>
       <c r="H966" t="s">
         <v>8</v>
@@ -25511,7 +25511,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G967" t="n">
-        <v>1.46909475326538</v>
+        <v>1.46909487247467</v>
       </c>
       <c r="H967" t="s">
         <v>8</v>
@@ -25537,7 +25537,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G968" t="n">
-        <v>1.46909475326538</v>
+        <v>1.46909487247467</v>
       </c>
       <c r="H968" t="s">
         <v>8</v>
@@ -25693,7 +25693,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G974" t="n">
-        <v>1.4534660577774</v>
+        <v>1.45346617698669</v>
       </c>
       <c r="H974" t="s">
         <v>8</v>
@@ -25823,7 +25823,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G979" t="n">
-        <v>1.4534660577774</v>
+        <v>1.45346617698669</v>
       </c>
       <c r="H979" t="s">
         <v>8</v>
@@ -25901,7 +25901,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G982" t="n">
-        <v>1.4534660577774</v>
+        <v>1.45346617698669</v>
       </c>
       <c r="H982" t="s">
         <v>8</v>
@@ -25927,7 +25927,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G983" t="n">
-        <v>1.4534660577774</v>
+        <v>1.45346617698669</v>
       </c>
       <c r="H983" t="s">
         <v>8</v>
@@ -26239,7 +26239,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G995" t="n">
-        <v>1.39095151424408</v>
+        <v>1.39095139503479</v>
       </c>
       <c r="H995" t="s">
         <v>8</v>
@@ -26447,7 +26447,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1003" t="n">
-        <v>1.68789637088776</v>
+        <v>1.68789613246918</v>
       </c>
       <c r="H1003" t="s">
         <v>8</v>
@@ -26473,7 +26473,7 @@
         <v>2</v>
       </c>
       <c r="G1004" t="n">
-        <v>1.56286680698395</v>
+        <v>1.56286692619324</v>
       </c>
       <c r="H1004" t="s">
         <v>8</v>
@@ -26499,7 +26499,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G1005" t="n">
-        <v>1.48472344875336</v>
+        <v>1.48472356796265</v>
       </c>
       <c r="H1005" t="s">
         <v>8</v>
@@ -26525,7 +26525,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G1006" t="n">
-        <v>1.51598107814789</v>
+        <v>1.51598083972931</v>
       </c>
       <c r="H1006" t="s">
         <v>8</v>
@@ -26551,7 +26551,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G1007" t="n">
-        <v>1.46909475326538</v>
+        <v>1.46909487247467</v>
       </c>
       <c r="H1007" t="s">
         <v>8</v>
@@ -26603,7 +26603,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G1009" t="n">
-        <v>1.4534660577774</v>
+        <v>1.45346617698669</v>
       </c>
       <c r="H1009" t="s">
         <v>8</v>
@@ -26629,7 +26629,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G1010" t="n">
-        <v>1.51598107814789</v>
+        <v>1.51598083972931</v>
       </c>
       <c r="H1010" t="s">
         <v>8</v>
@@ -26655,7 +26655,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G1011" t="n">
-        <v>1.4534660577774</v>
+        <v>1.45346617698669</v>
       </c>
       <c r="H1011" t="s">
         <v>8</v>
@@ -26733,7 +26733,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G1014" t="n">
-        <v>1.46909475326538</v>
+        <v>1.46909487247467</v>
       </c>
       <c r="H1014" t="s">
         <v>8</v>
@@ -26759,7 +26759,7 @@
         <v>1.86940002441406</v>
       </c>
       <c r="G1015" t="n">
-        <v>1.46081185340881</v>
+        <v>1.46081161499023</v>
       </c>
       <c r="H1015" t="s">
         <v>8</v>
@@ -26785,7 +26785,7 @@
         <v>1.84019994735718</v>
       </c>
       <c r="G1016" t="n">
-        <v>1.43799364566803</v>
+        <v>1.43799376487732</v>
       </c>
       <c r="H1016" t="s">
         <v>8</v>
@@ -26811,7 +26811,7 @@
         <v>1.80480003356934</v>
       </c>
       <c r="G1017" t="n">
-        <v>1.41033101081848</v>
+        <v>1.41033113002777</v>
       </c>
       <c r="H1017" t="s">
         <v>8</v>
@@ -26863,7 +26863,7 @@
         <v>1.76600003242493</v>
       </c>
       <c r="G1019" t="n">
-        <v>1.38001143932343</v>
+        <v>1.38001132011414</v>
       </c>
       <c r="H1019" t="s">
         <v>8</v>
@@ -26915,7 +26915,7 @@
         <v>1.77359998226166</v>
       </c>
       <c r="G1021" t="n">
-        <v>1.38595044612885</v>
+        <v>1.38595032691956</v>
       </c>
       <c r="H1021" t="s">
         <v>8</v>
@@ -27123,7 +27123,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G1029" t="n">
-        <v>1.34406542778015</v>
+        <v>1.34406554698944</v>
       </c>
       <c r="H1029" t="s">
         <v>8</v>
@@ -27149,7 +27149,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G1030" t="n">
-        <v>1.3362512588501</v>
+        <v>1.33625113964081</v>
       </c>
       <c r="H1030" t="s">
         <v>8</v>
@@ -27175,7 +27175,7 @@
         <v>1.73239994049072</v>
       </c>
       <c r="G1031" t="n">
-        <v>1.35375511646271</v>
+        <v>1.353755235672</v>
       </c>
       <c r="H1031" t="s">
         <v>8</v>
@@ -27201,7 +27201,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G1032" t="n">
-        <v>1.35187983512878</v>
+        <v>1.35187995433807</v>
       </c>
       <c r="H1032" t="s">
         <v>8</v>
@@ -27253,7 +27253,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G1034" t="n">
-        <v>1.3362512588501</v>
+        <v>1.33625113964081</v>
       </c>
       <c r="H1034" t="s">
         <v>8</v>
@@ -27279,7 +27279,7 @@
         <v>1.68099999427795</v>
       </c>
       <c r="G1035" t="n">
-        <v>1.31358957290649</v>
+        <v>1.3135894536972</v>
       </c>
       <c r="H1035" t="s">
         <v>8</v>
@@ -27305,7 +27305,7 @@
         <v>1.66919994354248</v>
       </c>
       <c r="G1036" t="n">
-        <v>1.30436873435974</v>
+        <v>1.30436849594116</v>
       </c>
       <c r="H1036" t="s">
         <v>8</v>
@@ -27409,7 +27409,7 @@
         <v>1.52020001411438</v>
       </c>
       <c r="G1040" t="n">
-        <v>1.18793511390686</v>
+        <v>1.18793499469757</v>
       </c>
       <c r="H1040" t="s">
         <v>8</v>
@@ -27435,7 +27435,7 @@
         <v>1.57720005512238</v>
       </c>
       <c r="G1041" t="n">
-        <v>1.23247671127319</v>
+        <v>1.23247683048248</v>
       </c>
       <c r="H1041" t="s">
         <v>8</v>
@@ -27487,7 +27487,7 @@
         <v>1.61819994449615</v>
       </c>
       <c r="G1043" t="n">
-        <v>1.26451551914215</v>
+        <v>1.26451539993286</v>
       </c>
       <c r="H1043" t="s">
         <v>8</v>
@@ -27539,7 +27539,7 @@
         <v>1.62979996204376</v>
       </c>
       <c r="G1045" t="n">
-        <v>1.27358019351959</v>
+        <v>1.2735800743103</v>
       </c>
       <c r="H1045" t="s">
         <v>8</v>
@@ -27565,7 +27565,7 @@
         <v>1.63779997825623</v>
       </c>
       <c r="G1046" t="n">
-        <v>1.27983152866364</v>
+        <v>1.27983164787292</v>
       </c>
       <c r="H1046" t="s">
         <v>8</v>
@@ -27591,7 +27591,7 @@
         <v>1.66260004043579</v>
       </c>
       <c r="G1047" t="n">
-        <v>1.29921138286591</v>
+        <v>1.29921126365662</v>
       </c>
       <c r="H1047" t="s">
         <v>8</v>
@@ -27617,7 +27617,7 @@
         <v>1.68579995632172</v>
       </c>
       <c r="G1048" t="n">
-        <v>1.31734049320221</v>
+        <v>1.31734037399292</v>
       </c>
       <c r="H1048" t="s">
         <v>8</v>
@@ -27643,7 +27643,7 @@
         <v>1.67980003356934</v>
       </c>
       <c r="G1049" t="n">
-        <v>1.31265187263489</v>
+        <v>1.3126517534256</v>
       </c>
       <c r="H1049" t="s">
         <v>8</v>
@@ -27669,7 +27669,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1050" t="n">
-        <v>1.30499374866486</v>
+        <v>1.30499386787415</v>
       </c>
       <c r="H1050" t="s">
         <v>8</v>
@@ -27721,7 +27721,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1052" t="n">
-        <v>1.30499374866486</v>
+        <v>1.30499386787415</v>
       </c>
       <c r="H1052" t="s">
         <v>8</v>
@@ -27747,7 +27747,7 @@
         <v>1.58379995822906</v>
       </c>
       <c r="G1053" t="n">
-        <v>1.23763430118561</v>
+        <v>1.23763418197632</v>
       </c>
       <c r="H1053" t="s">
         <v>8</v>
@@ -27773,7 +27773,7 @@
         <v>1.58379995822906</v>
       </c>
       <c r="G1054" t="n">
-        <v>1.23763430118561</v>
+        <v>1.23763418197632</v>
       </c>
       <c r="H1054" t="s">
         <v>8</v>
@@ -27799,7 +27799,7 @@
         <v>1.61479997634888</v>
       </c>
       <c r="G1055" t="n">
-        <v>1.26185870170593</v>
+        <v>1.26185858249664</v>
       </c>
       <c r="H1055" t="s">
         <v>8</v>
@@ -27825,7 +27825,7 @@
         <v>1.54159998893738</v>
       </c>
       <c r="G1056" t="n">
-        <v>1.20465767383575</v>
+        <v>1.20465779304504</v>
       </c>
       <c r="H1056" t="s">
         <v>8</v>
@@ -27851,7 +27851,7 @@
         <v>1.58980000019073</v>
       </c>
       <c r="G1057" t="n">
-        <v>1.24232280254364</v>
+        <v>1.24232292175293</v>
       </c>
       <c r="H1057" t="s">
         <v>8</v>
@@ -27903,7 +27903,7 @@
         <v>1.55980002880096</v>
       </c>
       <c r="G1059" t="n">
-        <v>1.21887981891632</v>
+        <v>1.2188800573349</v>
       </c>
       <c r="H1059" t="s">
         <v>8</v>
@@ -28007,7 +28007,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G1063" t="n">
-        <v>0.883019804954529</v>
+        <v>0.883019685745239</v>
       </c>
       <c r="H1063" t="s">
         <v>8</v>
@@ -28033,7 +28033,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G1064" t="n">
-        <v>0.883019804954529</v>
+        <v>0.883019685745239</v>
       </c>
       <c r="H1064" t="s">
         <v>8</v>
@@ -28059,7 +28059,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G1065" t="n">
-        <v>0.867391169071198</v>
+        <v>0.867391109466553</v>
       </c>
       <c r="H1065" t="s">
         <v>8</v>
@@ -28085,7 +28085,7 @@
         <v>0.939999997615814</v>
       </c>
       <c r="G1066" t="n">
-        <v>0.73454737663269</v>
+        <v>0.734547436237335</v>
       </c>
       <c r="H1066" t="s">
         <v>8</v>
@@ -28215,7 +28215,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G1071" t="n">
-        <v>0.789247751235962</v>
+        <v>0.789247691631317</v>
       </c>
       <c r="H1071" t="s">
         <v>8</v>
@@ -28267,7 +28267,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G1073" t="n">
-        <v>0.968977391719818</v>
+        <v>0.968977510929108</v>
       </c>
       <c r="H1073" t="s">
         <v>8</v>
@@ -28345,7 +28345,7 @@
         <v>1.5958000421524</v>
       </c>
       <c r="G1076" t="n">
-        <v>1.24701130390167</v>
+        <v>1.24701154232025</v>
       </c>
       <c r="H1076" t="s">
         <v>8</v>
@@ -28371,7 +28371,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G1077" t="n">
-        <v>1.24247920513153</v>
+        <v>1.24247896671295</v>
       </c>
       <c r="H1077" t="s">
         <v>8</v>
@@ -28501,7 +28501,7 @@
         <v>1.49080002307892</v>
       </c>
       <c r="G1082" t="n">
-        <v>1.16496109962463</v>
+        <v>1.16496086120605</v>
       </c>
       <c r="H1082" t="s">
         <v>8</v>
@@ -28579,7 +28579,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G1085" t="n">
-        <v>1.21903610229492</v>
+        <v>1.21903598308563</v>
       </c>
       <c r="H1085" t="s">
         <v>8</v>
@@ -28605,7 +28605,7 @@
         <v>1.52499997615814</v>
       </c>
       <c r="G1086" t="n">
-        <v>1.19168603420258</v>
+        <v>1.19168591499329</v>
       </c>
       <c r="H1086" t="s">
         <v>8</v>
@@ -28631,7 +28631,7 @@
         <v>1.52119994163513</v>
       </c>
       <c r="G1087" t="n">
-        <v>1.18871653079987</v>
+        <v>1.18871641159058</v>
       </c>
       <c r="H1087" t="s">
         <v>8</v>
@@ -28657,7 +28657,7 @@
         <v>1.52999997138977</v>
       </c>
       <c r="G1088" t="n">
-        <v>1.1955931186676</v>
+        <v>1.19559299945831</v>
       </c>
       <c r="H1088" t="s">
         <v>8</v>
@@ -28735,7 +28735,7 @@
         <v>1.53519999980927</v>
       </c>
       <c r="G1091" t="n">
-        <v>1.19965648651123</v>
+        <v>1.19965660572052</v>
       </c>
       <c r="H1091" t="s">
         <v>8</v>
@@ -28761,7 +28761,7 @@
         <v>1.51059997081757</v>
       </c>
       <c r="G1092" t="n">
-        <v>1.18043339252472</v>
+        <v>1.18043315410614</v>
       </c>
       <c r="H1092" t="s">
         <v>8</v>
@@ -28787,7 +28787,7 @@
         <v>1.53840005397797</v>
       </c>
       <c r="G1093" t="n">
-        <v>1.20215725898743</v>
+        <v>1.20215713977814</v>
       </c>
       <c r="H1093" t="s">
         <v>8</v>
@@ -28813,7 +28813,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G1094" t="n">
-        <v>1.14870727062225</v>
+        <v>1.14870715141296</v>
       </c>
       <c r="H1094" t="s">
         <v>8</v>
@@ -29073,7 +29073,7 @@
         <v>1.37020003795624</v>
       </c>
       <c r="G1104" t="n">
-        <v>1.07072007656097</v>
+        <v>1.07071995735168</v>
       </c>
       <c r="H1104" t="s">
         <v>8</v>
@@ -29099,7 +29099,7 @@
         <v>1.3782000541687</v>
       </c>
       <c r="G1105" t="n">
-        <v>1.0769716501236</v>
+        <v>1.07697153091431</v>
       </c>
       <c r="H1105" t="s">
         <v>8</v>
@@ -29125,7 +29125,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1106" t="n">
-        <v>1.04712092876434</v>
+        <v>1.04712080955505</v>
       </c>
       <c r="H1106" t="s">
         <v>8</v>
@@ -29151,7 +29151,7 @@
         <v>1.34080004692078</v>
       </c>
       <c r="G1107" t="n">
-        <v>1.04774594306946</v>
+        <v>1.04774582386017</v>
       </c>
       <c r="H1107" t="s">
         <v>8</v>
@@ -29177,7 +29177,7 @@
         <v>1.30019998550415</v>
       </c>
       <c r="G1108" t="n">
-        <v>1.0160197019577</v>
+        <v>1.01601982116699</v>
       </c>
       <c r="H1108" t="s">
         <v>8</v>
@@ -29229,7 +29229,7 @@
         <v>1.25279998779297</v>
       </c>
       <c r="G1110" t="n">
-        <v>0.978979825973511</v>
+        <v>0.978979766368866</v>
       </c>
       <c r="H1110" t="s">
         <v>8</v>
@@ -29255,7 +29255,7 @@
         <v>1.24500000476837</v>
       </c>
       <c r="G1111" t="n">
-        <v>0.97288453578949</v>
+        <v>0.972884654998779</v>
       </c>
       <c r="H1111" t="s">
         <v>8</v>
@@ -29281,7 +29281,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1112" t="n">
-        <v>1.00023460388184</v>
+        <v>1.00023472309113</v>
       </c>
       <c r="H1112" t="s">
         <v>8</v>
@@ -29307,7 +29307,7 @@
         <v>1.23800003528595</v>
       </c>
       <c r="G1113" t="n">
-        <v>0.967414498329163</v>
+        <v>0.967414617538452</v>
       </c>
       <c r="H1113" t="s">
         <v>8</v>
@@ -29359,7 +29359,7 @@
         <v>1.25</v>
       </c>
       <c r="G1115" t="n">
-        <v>0.976791679859161</v>
+        <v>0.976791799068451</v>
       </c>
       <c r="H1115" t="s">
         <v>8</v>
@@ -29411,7 +29411,7 @@
         <v>1.3367999792099</v>
       </c>
       <c r="G1117" t="n">
-        <v>1.04462027549744</v>
+        <v>1.04462003707886</v>
       </c>
       <c r="H1117" t="s">
         <v>8</v>
@@ -29437,7 +29437,7 @@
         <v>1.31719994544983</v>
       </c>
       <c r="G1118" t="n">
-        <v>1.02930390834808</v>
+        <v>1.02930414676666</v>
       </c>
       <c r="H1118" t="s">
         <v>8</v>
@@ -29463,7 +29463,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G1119" t="n">
-        <v>1.01586329936981</v>
+        <v>1.0158634185791</v>
       </c>
       <c r="H1119" t="s">
         <v>8</v>
@@ -29489,7 +29489,7 @@
         <v>1.2791999578476</v>
       </c>
       <c r="G1120" t="n">
-        <v>0.999609589576721</v>
+        <v>0.999609470367432</v>
       </c>
       <c r="H1120" t="s">
         <v>8</v>
@@ -29515,7 +29515,7 @@
         <v>1.2771999835968</v>
       </c>
       <c r="G1121" t="n">
-        <v>0.99804675579071</v>
+        <v>0.998046696186066</v>
       </c>
       <c r="H1121" t="s">
         <v>8</v>
@@ -29567,7 +29567,7 @@
         <v>1.31359994411469</v>
       </c>
       <c r="G1123" t="n">
-        <v>1.02649092674255</v>
+        <v>1.02649080753326</v>
       </c>
       <c r="H1123" t="s">
         <v>8</v>
@@ -29749,7 +29749,7 @@
         <v>1.29579997062683</v>
       </c>
       <c r="G1130" t="n">
-        <v>1.01258146762848</v>
+        <v>1.0125812292099</v>
       </c>
       <c r="H1130" t="s">
         <v>8</v>
@@ -29775,7 +29775,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1131" t="n">
-        <v>1.00804901123047</v>
+        <v>1.00804913043976</v>
       </c>
       <c r="H1131" t="s">
         <v>8</v>
@@ -29801,7 +29801,7 @@
         <v>1.32280004024506</v>
       </c>
       <c r="G1132" t="n">
-        <v>1.03368008136749</v>
+        <v>1.03368020057678</v>
       </c>
       <c r="H1132" t="s">
         <v>8</v>
@@ -29827,7 +29827,7 @@
         <v>1.29820001125336</v>
       </c>
       <c r="G1133" t="n">
-        <v>1.01445686817169</v>
+        <v>1.01445698738098</v>
       </c>
       <c r="H1133" t="s">
         <v>8</v>
@@ -29853,7 +29853,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1134" t="n">
-        <v>1.04712092876434</v>
+        <v>1.04712080955505</v>
       </c>
       <c r="H1134" t="s">
         <v>8</v>
@@ -29931,7 +29931,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G1137" t="n">
-        <v>1.01586329936981</v>
+        <v>1.0158634185791</v>
       </c>
       <c r="H1137" t="s">
         <v>8</v>
@@ -29957,7 +29957,7 @@
         <v>1.33980000019073</v>
       </c>
       <c r="G1138" t="n">
-        <v>1.04696440696716</v>
+        <v>1.04696452617645</v>
       </c>
       <c r="H1138" t="s">
         <v>8</v>
@@ -30009,7 +30009,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1140" t="n">
-        <v>1.03930652141571</v>
+        <v>1.03930640220642</v>
       </c>
       <c r="H1140" t="s">
         <v>8</v>
@@ -30035,7 +30035,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1141" t="n">
-        <v>1.00804901123047</v>
+        <v>1.00804913043976</v>
       </c>
       <c r="H1141" t="s">
         <v>8</v>
@@ -30113,7 +30113,7 @@
         <v>1.30499994754791</v>
       </c>
       <c r="G1144" t="n">
-        <v>1.01977050304413</v>
+        <v>1.01977062225342</v>
       </c>
       <c r="H1144" t="s">
         <v>8</v>
@@ -30165,7 +30165,7 @@
         <v>1.3257999420166</v>
       </c>
       <c r="G1146" t="n">
-        <v>1.0360244512558</v>
+        <v>1.03602433204651</v>
       </c>
       <c r="H1146" t="s">
         <v>8</v>
@@ -30321,7 +30321,7 @@
         <v>1.29180002212524</v>
       </c>
       <c r="G1152" t="n">
-        <v>1.00945556163788</v>
+        <v>1.00945568084717</v>
       </c>
       <c r="H1152" t="s">
         <v>8</v>
@@ -30373,7 +30373,7 @@
         <v>1.25440001487732</v>
       </c>
       <c r="G1154" t="n">
-        <v>0.980230033397675</v>
+        <v>0.980230212211609</v>
       </c>
       <c r="H1154" t="s">
         <v>8</v>
@@ -30399,7 +30399,7 @@
         <v>1.28880000114441</v>
       </c>
       <c r="G1155" t="n">
-        <v>1.00711143016815</v>
+        <v>1.00711131095886</v>
       </c>
       <c r="H1155" t="s">
         <v>8</v>
@@ -30451,7 +30451,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G1157" t="n">
-        <v>1.02367758750916</v>
+        <v>1.02367770671844</v>
       </c>
       <c r="H1157" t="s">
         <v>8</v>
@@ -30529,7 +30529,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1160" t="n">
-        <v>1.00804901123047</v>
+        <v>1.00804913043976</v>
       </c>
       <c r="H1160" t="s">
         <v>8</v>
@@ -30555,7 +30555,7 @@
         <v>1.28939998149872</v>
       </c>
       <c r="G1161" t="n">
-        <v>1.00758028030396</v>
+        <v>1.00758016109467</v>
       </c>
       <c r="H1161" t="s">
         <v>8</v>
@@ -30581,7 +30581,7 @@
         <v>1.29980003833771</v>
       </c>
       <c r="G1162" t="n">
-        <v>1.01570725440979</v>
+        <v>1.01570701599121</v>
       </c>
       <c r="H1162" t="s">
         <v>8</v>
@@ -30607,7 +30607,7 @@
         <v>1.23080003261566</v>
       </c>
       <c r="G1163" t="n">
-        <v>0.961788415908813</v>
+        <v>0.961788237094879</v>
       </c>
       <c r="H1163" t="s">
         <v>8</v>
@@ -30633,7 +30633,7 @@
         <v>1.23099994659424</v>
       </c>
       <c r="G1164" t="n">
-        <v>0.96194452047348</v>
+        <v>0.961944460868835</v>
       </c>
       <c r="H1164" t="s">
         <v>8</v>
@@ -30685,7 +30685,7 @@
         <v>1.27900004386902</v>
       </c>
       <c r="G1166" t="n">
-        <v>0.999453365802765</v>
+        <v>0.99945342540741</v>
       </c>
       <c r="H1166" t="s">
         <v>8</v>
@@ -30763,7 +30763,7 @@
         <v>1.25</v>
       </c>
       <c r="G1169" t="n">
-        <v>0.976791679859161</v>
+        <v>0.976791799068451</v>
       </c>
       <c r="H1169" t="s">
         <v>8</v>
@@ -30789,7 +30789,7 @@
         <v>1.25</v>
       </c>
       <c r="G1170" t="n">
-        <v>0.976791679859161</v>
+        <v>0.976791799068451</v>
       </c>
       <c r="H1170" t="s">
         <v>8</v>
@@ -30815,7 +30815,7 @@
         <v>1.24339997768402</v>
       </c>
       <c r="G1171" t="n">
-        <v>0.971634268760681</v>
+        <v>0.971634328365326</v>
       </c>
       <c r="H1171" t="s">
         <v>8</v>
@@ -30893,7 +30893,7 @@
         <v>1.24979996681213</v>
       </c>
       <c r="G1174" t="n">
-        <v>0.976635456085205</v>
+        <v>0.97663539648056</v>
       </c>
       <c r="H1174" t="s">
         <v>8</v>
@@ -30919,7 +30919,7 @@
         <v>1.22200000286102</v>
       </c>
       <c r="G1175" t="n">
-        <v>0.954911589622498</v>
+        <v>0.954911708831787</v>
       </c>
       <c r="H1175" t="s">
         <v>8</v>
@@ -30945,7 +30945,7 @@
         <v>1.22019994258881</v>
       </c>
       <c r="G1176" t="n">
-        <v>0.953505098819733</v>
+        <v>0.953505039215088</v>
       </c>
       <c r="H1176" t="s">
         <v>8</v>
@@ -31023,7 +31023,7 @@
         <v>1.21700000762939</v>
       </c>
       <c r="G1179" t="n">
-        <v>0.951004445552826</v>
+        <v>0.951004326343536</v>
       </c>
       <c r="H1179" t="s">
         <v>8</v>
@@ -31075,7 +31075,7 @@
         <v>1.23580002784729</v>
       </c>
       <c r="G1181" t="n">
-        <v>0.96569550037384</v>
+        <v>0.965695381164551</v>
       </c>
       <c r="H1181" t="s">
         <v>8</v>
@@ -31205,7 +31205,7 @@
         <v>1.20899999141693</v>
       </c>
       <c r="G1186" t="n">
-        <v>0.944753050804138</v>
+        <v>0.944752991199493</v>
       </c>
       <c r="H1186" t="s">
         <v>8</v>
@@ -31257,7 +31257,7 @@
         <v>1.20019996166229</v>
       </c>
       <c r="G1188" t="n">
-        <v>0.937876403331757</v>
+        <v>0.937876462936401</v>
       </c>
       <c r="H1188" t="s">
         <v>8</v>
@@ -31283,7 +31283,7 @@
         <v>1.22019994258881</v>
       </c>
       <c r="G1189" t="n">
-        <v>0.953505098819733</v>
+        <v>0.953505039215088</v>
       </c>
       <c r="H1189" t="s">
         <v>8</v>
@@ -31335,7 +31335,7 @@
         <v>1.23959994316101</v>
       </c>
       <c r="G1191" t="n">
-        <v>0.968664705753326</v>
+        <v>0.968664824962616</v>
       </c>
       <c r="H1191" t="s">
         <v>8</v>
@@ -31361,7 +31361,7 @@
         <v>1.24979996681213</v>
       </c>
       <c r="G1192" t="n">
-        <v>0.976635456085205</v>
+        <v>0.97663539648056</v>
       </c>
       <c r="H1192" t="s">
         <v>8</v>
@@ -31439,7 +31439,7 @@
         <v>1.24279999732971</v>
       </c>
       <c r="G1195" t="n">
-        <v>0.971165418624878</v>
+        <v>0.971165359020233</v>
       </c>
       <c r="H1195" t="s">
         <v>8</v>
@@ -31465,7 +31465,7 @@
         <v>1.24199998378754</v>
       </c>
       <c r="G1196" t="n">
-        <v>0.970540285110474</v>
+        <v>0.970540404319763</v>
       </c>
       <c r="H1196" t="s">
         <v>8</v>
@@ -31517,7 +31517,7 @@
         <v>1.23979997634888</v>
       </c>
       <c r="G1198" t="n">
-        <v>0.968821167945862</v>
+        <v>0.968821048736572</v>
       </c>
       <c r="H1198" t="s">
         <v>8</v>
@@ -31543,7 +31543,7 @@
         <v>1.23979997634888</v>
       </c>
       <c r="G1199" t="n">
-        <v>0.968821167945862</v>
+        <v>0.968821048736572</v>
       </c>
       <c r="H1199" t="s">
         <v>8</v>
@@ -31569,7 +31569,7 @@
         <v>1.19120001792908</v>
       </c>
       <c r="G1200" t="n">
-        <v>0.930843472480774</v>
+        <v>0.930843412876129</v>
       </c>
       <c r="H1200" t="s">
         <v>8</v>
@@ -31595,7 +31595,7 @@
         <v>1.19120001792908</v>
       </c>
       <c r="G1201" t="n">
-        <v>0.930843472480774</v>
+        <v>0.930843412876129</v>
       </c>
       <c r="H1201" t="s">
         <v>8</v>
@@ -31699,7 +31699,7 @@
         <v>1.24199998378754</v>
       </c>
       <c r="G1205" t="n">
-        <v>0.970540285110474</v>
+        <v>0.970540404319763</v>
       </c>
       <c r="H1205" t="s">
         <v>8</v>
@@ -31725,7 +31725,7 @@
         <v>1.2117999792099</v>
       </c>
       <c r="G1206" t="n">
-        <v>0.946940958499908</v>
+        <v>0.946941018104553</v>
       </c>
       <c r="H1206" t="s">
         <v>8</v>
@@ -31751,7 +31751,7 @@
         <v>1.21119999885559</v>
       </c>
       <c r="G1207" t="n">
-        <v>0.94647204875946</v>
+        <v>0.94647216796875</v>
       </c>
       <c r="H1207" t="s">
         <v>8</v>
@@ -31829,7 +31829,7 @@
         <v>1.19900000095367</v>
       </c>
       <c r="G1210" t="n">
-        <v>0.936938643455505</v>
+        <v>0.93693870306015</v>
       </c>
       <c r="H1210" t="s">
         <v>8</v>
@@ -31855,7 +31855,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G1211" t="n">
-        <v>0.968977391719818</v>
+        <v>0.968977510929108</v>
       </c>
       <c r="H1211" t="s">
         <v>8</v>
@@ -31881,7 +31881,7 @@
         <v>1.20060002803802</v>
       </c>
       <c r="G1212" t="n">
-        <v>0.938188970088959</v>
+        <v>0.938188910484314</v>
       </c>
       <c r="H1212" t="s">
         <v>8</v>
@@ -31907,7 +31907,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1213" t="n">
-        <v>1.00804901123047</v>
+        <v>1.00804913043976</v>
       </c>
       <c r="H1213" t="s">
         <v>8</v>
@@ -31933,7 +31933,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G1214" t="n">
-        <v>1.02367758750916</v>
+        <v>1.02367770671844</v>
       </c>
       <c r="H1214" t="s">
         <v>8</v>
@@ -31959,7 +31959,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1215" t="n">
-        <v>0.984606087207794</v>
+        <v>0.984605967998505</v>
       </c>
       <c r="H1215" t="s">
         <v>8</v>
@@ -31985,7 +31985,7 @@
         <v>1.26579999923706</v>
       </c>
       <c r="G1216" t="n">
-        <v>0.98913848400116</v>
+        <v>0.98913836479187</v>
       </c>
       <c r="H1216" t="s">
         <v>8</v>
@@ -32011,7 +32011,7 @@
         <v>1.26540005207062</v>
       </c>
       <c r="G1217" t="n">
-        <v>0.988825798034668</v>
+        <v>0.988825917243958</v>
       </c>
       <c r="H1217" t="s">
         <v>8</v>
@@ -32063,7 +32063,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1219" t="n">
-        <v>1.00804901123047</v>
+        <v>1.00804913043976</v>
       </c>
       <c r="H1219" t="s">
         <v>8</v>
@@ -32089,7 +32089,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G1220" t="n">
-        <v>1.01586329936981</v>
+        <v>1.0158634185791</v>
       </c>
       <c r="H1220" t="s">
         <v>8</v>
@@ -32141,7 +32141,7 @@
         <v>1.22599995136261</v>
       </c>
       <c r="G1222" t="n">
-        <v>0.958037257194519</v>
+        <v>0.958037376403809</v>
       </c>
       <c r="H1222" t="s">
         <v>8</v>
@@ -32167,7 +32167,7 @@
         <v>1.22599995136261</v>
       </c>
       <c r="G1223" t="n">
-        <v>0.958037257194519</v>
+        <v>0.958037376403809</v>
       </c>
       <c r="H1223" t="s">
         <v>8</v>
@@ -32193,7 +32193,7 @@
         <v>1.22599995136261</v>
       </c>
       <c r="G1224" t="n">
-        <v>0.958037257194519</v>
+        <v>0.958037376403809</v>
       </c>
       <c r="H1224" t="s">
         <v>8</v>
@@ -32245,7 +32245,7 @@
         <v>1.25</v>
       </c>
       <c r="G1226" t="n">
-        <v>0.976791679859161</v>
+        <v>0.976791799068451</v>
       </c>
       <c r="H1226" t="s">
         <v>8</v>
@@ -32271,7 +32271,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1227" t="n">
-        <v>0.9377201795578</v>
+        <v>0.937720060348511</v>
       </c>
       <c r="H1227" t="s">
         <v>8</v>
@@ -32297,7 +32297,7 @@
         <v>1.17519998550415</v>
       </c>
       <c r="G1228" t="n">
-        <v>0.918340504169464</v>
+        <v>0.918340444564819</v>
       </c>
       <c r="H1228" t="s">
         <v>8</v>
@@ -32349,7 +32349,7 @@
         <v>1.18219995498657</v>
       </c>
       <c r="G1230" t="n">
-        <v>0.923810601234436</v>
+        <v>0.923810482025146</v>
       </c>
       <c r="H1230" t="s">
         <v>8</v>
@@ -32375,7 +32375,7 @@
         <v>1.18219995498657</v>
       </c>
       <c r="G1231" t="n">
-        <v>0.923810601234436</v>
+        <v>0.923810482025146</v>
       </c>
       <c r="H1231" t="s">
         <v>8</v>
@@ -32453,7 +32453,7 @@
         <v>1.19099998474121</v>
       </c>
       <c r="G1234" t="n">
-        <v>0.930687189102173</v>
+        <v>0.930687129497528</v>
       </c>
       <c r="H1234" t="s">
         <v>8</v>
@@ -32505,7 +32505,7 @@
         <v>1.19799995422363</v>
       </c>
       <c r="G1236" t="n">
-        <v>0.936157286167145</v>
+        <v>0.936157166957855</v>
       </c>
       <c r="H1236" t="s">
         <v>8</v>
@@ -32531,7 +32531,7 @@
         <v>1.23800003528595</v>
       </c>
       <c r="G1237" t="n">
-        <v>0.967414498329163</v>
+        <v>0.967414617538452</v>
       </c>
       <c r="H1237" t="s">
         <v>8</v>
@@ -32583,7 +32583,7 @@
         <v>1.26800000667572</v>
       </c>
       <c r="G1239" t="n">
-        <v>0.990857481956482</v>
+        <v>0.990857541561127</v>
       </c>
       <c r="H1239" t="s">
         <v>8</v>
@@ -32635,7 +32635,7 @@
         <v>1.27320003509521</v>
       </c>
       <c r="G1241" t="n">
-        <v>0.994920969009399</v>
+        <v>0.994921088218689</v>
       </c>
       <c r="H1241" t="s">
         <v>8</v>
@@ -32661,7 +32661,7 @@
         <v>1.27320003509521</v>
       </c>
       <c r="G1242" t="n">
-        <v>0.994920969009399</v>
+        <v>0.994921088218689</v>
       </c>
       <c r="H1242" t="s">
         <v>8</v>
@@ -32687,7 +32687,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1243" t="n">
-        <v>1.00023460388184</v>
+        <v>1.00023472309113</v>
       </c>
       <c r="H1243" t="s">
         <v>8</v>
@@ -32713,7 +32713,7 @@
         <v>1.26639997959137</v>
       </c>
       <c r="G1244" t="n">
-        <v>0.989607274532318</v>
+        <v>0.989607214927673</v>
       </c>
       <c r="H1244" t="s">
         <v>8</v>
@@ -32791,7 +32791,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G1247" t="n">
-        <v>1.24247920513153</v>
+        <v>1.24247896671295</v>
       </c>
       <c r="H1247" t="s">
         <v>8</v>
@@ -32817,7 +32817,7 @@
         <v>1.61300003528595</v>
       </c>
       <c r="G1248" t="n">
-        <v>1.26045215129852</v>
+        <v>1.26045227050781</v>
       </c>
       <c r="H1248" t="s">
         <v>8</v>
@@ -32869,7 +32869,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G1250" t="n">
-        <v>1.3362512588501</v>
+        <v>1.33625113964081</v>
       </c>
       <c r="H1250" t="s">
         <v>8</v>
@@ -32895,7 +32895,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G1251" t="n">
-        <v>1.31280815601349</v>
+        <v>1.3128080368042</v>
       </c>
       <c r="H1251" t="s">
         <v>8</v>
@@ -32921,7 +32921,7 @@
         <v>1.67980003356934</v>
       </c>
       <c r="G1252" t="n">
-        <v>1.31265187263489</v>
+        <v>1.3126517534256</v>
       </c>
       <c r="H1252" t="s">
         <v>8</v>
@@ -32947,7 +32947,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G1253" t="n">
-        <v>1.31280815601349</v>
+        <v>1.3128080368042</v>
       </c>
       <c r="H1253" t="s">
         <v>8</v>
@@ -32973,7 +32973,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1254" t="n">
-        <v>1.30499374866486</v>
+        <v>1.30499386787415</v>
       </c>
       <c r="H1254" t="s">
         <v>8</v>
@@ -32999,7 +32999,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G1255" t="n">
-        <v>1.31280815601349</v>
+        <v>1.3128080368042</v>
       </c>
       <c r="H1255" t="s">
         <v>8</v>
@@ -33155,7 +33155,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G1261" t="n">
-        <v>1.34406542778015</v>
+        <v>1.34406554698944</v>
       </c>
       <c r="H1261" t="s">
         <v>8</v>
@@ -33207,7 +33207,7 @@
         <v>1.7208000421524</v>
       </c>
       <c r="G1263" t="n">
-        <v>1.34469068050385</v>
+        <v>1.34469056129456</v>
       </c>
       <c r="H1263" t="s">
         <v>8</v>
@@ -33233,7 +33233,7 @@
         <v>1.71019995212555</v>
       </c>
       <c r="G1264" t="n">
-        <v>1.33640730381012</v>
+        <v>1.33640742301941</v>
       </c>
       <c r="H1264" t="s">
         <v>8</v>
@@ -33259,7 +33259,7 @@
         <v>1.67920005321503</v>
       </c>
       <c r="G1265" t="n">
-        <v>1.31218302249908</v>
+        <v>1.31218290328979</v>
       </c>
       <c r="H1265" t="s">
         <v>8</v>
@@ -33311,7 +33311,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G1267" t="n">
-        <v>1.39095151424408</v>
+        <v>1.39095139503479</v>
       </c>
       <c r="H1267" t="s">
         <v>8</v>
@@ -33363,7 +33363,7 @@
         <v>1.74979996681213</v>
       </c>
       <c r="G1269" t="n">
-        <v>1.46478509902954</v>
+        <v>1.46478521823883</v>
       </c>
       <c r="H1269" t="s">
         <v>8</v>
@@ -33441,7 +33441,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G1272" t="n">
-        <v>1.43983900547028</v>
+        <v>1.43983912467957</v>
       </c>
       <c r="H1272" t="s">
         <v>8</v>
@@ -33467,7 +33467,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G1273" t="n">
-        <v>1.43983900547028</v>
+        <v>1.43983912467957</v>
       </c>
       <c r="H1273" t="s">
         <v>8</v>
@@ -33519,7 +33519,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G1275" t="n">
-        <v>1.43983900547028</v>
+        <v>1.43983912467957</v>
       </c>
       <c r="H1275" t="s">
         <v>8</v>
@@ -33649,7 +33649,7 @@
         <v>1.66600000858307</v>
       </c>
       <c r="G1280" t="n">
-        <v>1.39463484287262</v>
+        <v>1.39463496208191</v>
       </c>
       <c r="H1280" t="s">
         <v>8</v>
@@ -33857,7 +33857,7 @@
         <v>1.60199999809265</v>
       </c>
       <c r="G1288" t="n">
-        <v>1.34105944633484</v>
+        <v>1.34105932712555</v>
       </c>
       <c r="H1288" t="s">
         <v>8</v>
@@ -33935,7 +33935,7 @@
         <v>1.6418000459671</v>
       </c>
       <c r="G1291" t="n">
-        <v>1.37437653541565</v>
+        <v>1.37437665462494</v>
       </c>
       <c r="H1291" t="s">
         <v>8</v>
@@ -33987,7 +33987,7 @@
         <v>1.60199999809265</v>
       </c>
       <c r="G1293" t="n">
-        <v>1.34105944633484</v>
+        <v>1.34105932712555</v>
       </c>
       <c r="H1293" t="s">
         <v>8</v>
@@ -34065,7 +34065,7 @@
         <v>1.71039998531342</v>
       </c>
       <c r="G1296" t="n">
-        <v>1.4318026304245</v>
+        <v>1.43180274963379</v>
       </c>
       <c r="H1296" t="s">
         <v>8</v>
@@ -34117,7 +34117,7 @@
         <v>1.75419998168945</v>
       </c>
       <c r="G1298" t="n">
-        <v>1.46846830844879</v>
+        <v>1.46846854686737</v>
       </c>
       <c r="H1298" t="s">
         <v>8</v>
@@ -34143,7 +34143,7 @@
         <v>1.77939999103546</v>
       </c>
       <c r="G1299" t="n">
-        <v>1.48956370353699</v>
+        <v>1.48956382274628</v>
       </c>
       <c r="H1299" t="s">
         <v>8</v>
@@ -34195,7 +34195,7 @@
         <v>1.80540001392365</v>
       </c>
       <c r="G1301" t="n">
-        <v>1.51132881641388</v>
+        <v>1.51132869720459</v>
       </c>
       <c r="H1301" t="s">
         <v>8</v>
@@ -34221,7 +34221,7 @@
         <v>1.7688000202179</v>
       </c>
       <c r="G1302" t="n">
-        <v>1.48069024085999</v>
+        <v>1.48069036006927</v>
       </c>
       <c r="H1302" t="s">
         <v>8</v>
@@ -34247,7 +34247,7 @@
         <v>1.76760005950928</v>
       </c>
       <c r="G1303" t="n">
-        <v>1.47968578338623</v>
+        <v>1.47968590259552</v>
       </c>
       <c r="H1303" t="s">
         <v>8</v>
@@ -34325,7 +34325,7 @@
         <v>1.83259999752045</v>
       </c>
       <c r="G1306" t="n">
-        <v>1.53409814834595</v>
+        <v>1.53409826755524</v>
       </c>
       <c r="H1306" t="s">
         <v>8</v>
@@ -34351,7 +34351,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G1307" t="n">
-        <v>1.57377743721008</v>
+        <v>1.57377755641937</v>
       </c>
       <c r="H1307" t="s">
         <v>8</v>
@@ -34377,7 +34377,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G1308" t="n">
-        <v>1.57377743721008</v>
+        <v>1.57377755641937</v>
       </c>
       <c r="H1308" t="s">
         <v>8</v>
@@ -34455,7 +34455,7 @@
         <v>1.87479996681213</v>
       </c>
       <c r="G1311" t="n">
-        <v>1.56942462921143</v>
+        <v>1.56942451000214</v>
       </c>
       <c r="H1311" t="s">
         <v>8</v>
@@ -34481,7 +34481,7 @@
         <v>1.88979995250702</v>
       </c>
       <c r="G1312" t="n">
-        <v>1.58198130130768</v>
+        <v>1.58198142051697</v>
       </c>
       <c r="H1312" t="s">
         <v>8</v>
@@ -34507,7 +34507,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G1313" t="n">
-        <v>1.57377743721008</v>
+        <v>1.57377755641937</v>
       </c>
       <c r="H1313" t="s">
         <v>8</v>
@@ -34585,7 +34585,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G1316" t="n">
-        <v>1.57377743721008</v>
+        <v>1.57377755641937</v>
       </c>
       <c r="H1316" t="s">
         <v>8</v>
@@ -34637,7 +34637,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G1318" t="n">
-        <v>1.62400472164154</v>
+        <v>1.62400448322296</v>
       </c>
       <c r="H1318" t="s">
         <v>8</v>
@@ -34663,7 +34663,7 @@
         <v>1.97979998588562</v>
       </c>
       <c r="G1319" t="n">
-        <v>1.65732169151306</v>
+        <v>1.65732181072235</v>
       </c>
       <c r="H1319" t="s">
         <v>8</v>
@@ -34689,7 +34689,7 @@
         <v>1.97780001163483</v>
       </c>
       <c r="G1320" t="n">
-        <v>1.65564751625061</v>
+        <v>1.65564739704132</v>
       </c>
       <c r="H1320" t="s">
         <v>8</v>
@@ -34793,7 +34793,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G1324" t="n">
-        <v>1.61563336849213</v>
+        <v>1.61563324928284</v>
       </c>
       <c r="H1324" t="s">
         <v>8</v>
@@ -34949,7 +34949,7 @@
         <v>1.91499996185303</v>
       </c>
       <c r="G1330" t="n">
-        <v>1.60307645797729</v>
+        <v>1.60307669639587</v>
       </c>
       <c r="H1330" t="s">
         <v>8</v>
@@ -35001,7 +35001,7 @@
         <v>1.95860004425049</v>
       </c>
       <c r="G1332" t="n">
-        <v>1.63957488536835</v>
+        <v>1.63957500457764</v>
       </c>
       <c r="H1332" t="s">
         <v>8</v>
@@ -35105,7 +35105,7 @@
         <v>1.91499996185303</v>
       </c>
       <c r="G1336" t="n">
-        <v>1.60307645797729</v>
+        <v>1.60307669639587</v>
       </c>
       <c r="H1336" t="s">
         <v>8</v>
@@ -35131,7 +35131,7 @@
         <v>1.91499996185303</v>
       </c>
       <c r="G1337" t="n">
-        <v>1.60307645797729</v>
+        <v>1.60307669639587</v>
       </c>
       <c r="H1337" t="s">
         <v>8</v>
@@ -35183,7 +35183,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G1339" t="n">
-        <v>1.607262134552</v>
+        <v>1.60726225376129</v>
       </c>
       <c r="H1339" t="s">
         <v>8</v>
@@ -35209,7 +35209,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G1340" t="n">
-        <v>1.607262134552</v>
+        <v>1.60726225376129</v>
       </c>
       <c r="H1340" t="s">
         <v>8</v>
@@ -35235,7 +35235,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G1341" t="n">
-        <v>1.607262134552</v>
+        <v>1.60726225376129</v>
       </c>
       <c r="H1341" t="s">
         <v>8</v>
@@ -35261,7 +35261,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G1342" t="n">
-        <v>1.61563336849213</v>
+        <v>1.61563324928284</v>
       </c>
       <c r="H1342" t="s">
         <v>8</v>
@@ -35287,7 +35287,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G1343" t="n">
-        <v>1.607262134552</v>
+        <v>1.60726225376129</v>
       </c>
       <c r="H1343" t="s">
         <v>8</v>
@@ -35313,7 +35313,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G1344" t="n">
-        <v>1.69097375869751</v>
+        <v>1.6909738779068</v>
       </c>
       <c r="H1344" t="s">
         <v>8</v>
@@ -35391,7 +35391,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G1347" t="n">
-        <v>1.69097375869751</v>
+        <v>1.6909738779068</v>
       </c>
       <c r="H1347" t="s">
         <v>8</v>
@@ -35469,7 +35469,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G1350" t="n">
-        <v>1.607262134552</v>
+        <v>1.60726225376129</v>
       </c>
       <c r="H1350" t="s">
         <v>8</v>
@@ -35495,7 +35495,7 @@
         <v>1.91499996185303</v>
       </c>
       <c r="G1351" t="n">
-        <v>1.60307645797729</v>
+        <v>1.60307669639587</v>
       </c>
       <c r="H1351" t="s">
         <v>8</v>
@@ -35547,7 +35547,7 @@
         <v>1.85500001907349</v>
       </c>
       <c r="G1353" t="n">
-        <v>1.55284976959229</v>
+        <v>1.552849650383</v>
       </c>
       <c r="H1353" t="s">
         <v>8</v>
@@ -35599,7 +35599,7 @@
         <v>1.89499998092651</v>
       </c>
       <c r="G1355" t="n">
-        <v>1.58633410930634</v>
+        <v>1.58633434772491</v>
       </c>
       <c r="H1355" t="s">
         <v>8</v>
@@ -35625,7 +35625,7 @@
         <v>1.88499999046326</v>
       </c>
       <c r="G1356" t="n">
-        <v>1.57796311378479</v>
+        <v>1.57796323299408</v>
       </c>
       <c r="H1356" t="s">
         <v>8</v>
@@ -35677,7 +35677,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G1358" t="n">
-        <v>1.54866409301758</v>
+        <v>1.54866421222687</v>
       </c>
       <c r="H1358" t="s">
         <v>8</v>
@@ -35755,7 +35755,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G1361" t="n">
-        <v>1.607262134552</v>
+        <v>1.60726225376129</v>
       </c>
       <c r="H1361" t="s">
         <v>8</v>
@@ -35885,7 +35885,7 @@
         <v>1.85500001907349</v>
       </c>
       <c r="G1366" t="n">
-        <v>1.55284976959229</v>
+        <v>1.552849650383</v>
       </c>
       <c r="H1366" t="s">
         <v>8</v>
@@ -35989,7 +35989,7 @@
         <v>1.89499998092651</v>
       </c>
       <c r="G1370" t="n">
-        <v>1.58633410930634</v>
+        <v>1.58633434772491</v>
       </c>
       <c r="H1370" t="s">
         <v>8</v>
@@ -36093,7 +36093,7 @@
         <v>1.89499998092651</v>
       </c>
       <c r="G1374" t="n">
-        <v>1.58633410930634</v>
+        <v>1.58633434772491</v>
       </c>
       <c r="H1374" t="s">
         <v>8</v>
@@ -36145,7 +36145,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G1376" t="n">
-        <v>1.54866409301758</v>
+        <v>1.54866421222687</v>
       </c>
       <c r="H1376" t="s">
         <v>8</v>
@@ -36197,7 +36197,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G1378" t="n">
-        <v>1.8249124288559</v>
+        <v>1.82491230964661</v>
       </c>
       <c r="H1378" t="s">
         <v>8</v>
@@ -36249,7 +36249,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1380" t="n">
-        <v>1.80817019939423</v>
+        <v>1.80817008018494</v>
       </c>
       <c r="H1380" t="s">
         <v>8</v>
@@ -36275,7 +36275,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G1381" t="n">
-        <v>1.90862393379211</v>
+        <v>1.90862381458282</v>
       </c>
       <c r="H1381" t="s">
         <v>8</v>
@@ -36301,7 +36301,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G1382" t="n">
-        <v>1.85839712619781</v>
+        <v>1.85839688777924</v>
       </c>
       <c r="H1382" t="s">
         <v>8</v>
@@ -36327,7 +36327,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G1383" t="n">
-        <v>1.87513947486877</v>
+        <v>1.87513935565948</v>
       </c>
       <c r="H1383" t="s">
         <v>8</v>
@@ -36353,7 +36353,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G1384" t="n">
-        <v>1.90025281906128</v>
+        <v>1.90025269985199</v>
       </c>
       <c r="H1384" t="s">
         <v>8</v>
@@ -36379,7 +36379,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G1385" t="n">
-        <v>1.85839712619781</v>
+        <v>1.85839688777924</v>
       </c>
       <c r="H1385" t="s">
         <v>8</v>
@@ -36405,7 +36405,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G1386" t="n">
-        <v>1.85839712619781</v>
+        <v>1.85839688777924</v>
       </c>
       <c r="H1386" t="s">
         <v>8</v>
@@ -36457,7 +36457,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G1388" t="n">
-        <v>1.81654107570648</v>
+        <v>1.81654119491577</v>
       </c>
       <c r="H1388" t="s">
         <v>8</v>
@@ -36509,7 +36509,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G1390" t="n">
-        <v>1.8249124288559</v>
+        <v>1.82491230964661</v>
       </c>
       <c r="H1390" t="s">
         <v>8</v>
@@ -36535,7 +36535,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1391" t="n">
-        <v>1.80817019939423</v>
+        <v>1.80817008018494</v>
       </c>
       <c r="H1391" t="s">
         <v>8</v>
@@ -36587,7 +36587,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1393" t="n">
-        <v>1.80817019939423</v>
+        <v>1.80817008018494</v>
       </c>
       <c r="H1393" t="s">
         <v>8</v>
@@ -36639,7 +36639,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G1395" t="n">
-        <v>1.79142785072327</v>
+        <v>1.79142773151398</v>
       </c>
       <c r="H1395" t="s">
         <v>8</v>
@@ -36665,7 +36665,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1396" t="n">
-        <v>1.75794279575348</v>
+        <v>1.75794291496277</v>
       </c>
       <c r="H1396" t="s">
         <v>8</v>
@@ -36691,7 +36691,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1397" t="n">
-        <v>1.75794279575348</v>
+        <v>1.75794291496277</v>
       </c>
       <c r="H1397" t="s">
         <v>8</v>
@@ -36743,7 +36743,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1399" t="n">
-        <v>1.75794279575348</v>
+        <v>1.75794291496277</v>
       </c>
       <c r="H1399" t="s">
         <v>8</v>
@@ -36769,7 +36769,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G1400" t="n">
-        <v>1.74120056629181</v>
+        <v>1.7412006855011</v>
       </c>
       <c r="H1400" t="s">
         <v>8</v>
@@ -36795,7 +36795,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G1401" t="n">
-        <v>1.74120056629181</v>
+        <v>1.7412006855011</v>
       </c>
       <c r="H1401" t="s">
         <v>8</v>
@@ -36847,7 +36847,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G1403" t="n">
-        <v>1.73282945156097</v>
+        <v>1.73282957077026</v>
       </c>
       <c r="H1403" t="s">
         <v>8</v>
@@ -36873,7 +36873,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G1404" t="n">
-        <v>1.69934487342834</v>
+        <v>1.69934499263763</v>
       </c>
       <c r="H1404" t="s">
         <v>8</v>
@@ -36925,7 +36925,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G1406" t="n">
-        <v>1.72445833683014</v>
+        <v>1.72445845603943</v>
       </c>
       <c r="H1406" t="s">
         <v>8</v>
@@ -37029,7 +37029,7 @@
         <v>1.9650000333786</v>
       </c>
       <c r="G1410" t="n">
-        <v>1.64493250846863</v>
+        <v>1.64493238925934</v>
       </c>
       <c r="H1410" t="s">
         <v>8</v>
@@ -37107,7 +37107,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G1413" t="n">
-        <v>1.72445833683014</v>
+        <v>1.72445845603943</v>
       </c>
       <c r="H1413" t="s">
         <v>8</v>
@@ -37133,7 +37133,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G1414" t="n">
-        <v>1.69934487342834</v>
+        <v>1.69934499263763</v>
       </c>
       <c r="H1414" t="s">
         <v>8</v>
@@ -37211,7 +37211,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G1417" t="n">
-        <v>1.69097375869751</v>
+        <v>1.6909738779068</v>
       </c>
       <c r="H1417" t="s">
         <v>8</v>
@@ -37237,7 +37237,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G1418" t="n">
-        <v>1.72445833683014</v>
+        <v>1.72445845603943</v>
       </c>
       <c r="H1418" t="s">
         <v>8</v>
@@ -37289,7 +37289,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G1420" t="n">
-        <v>1.73282945156097</v>
+        <v>1.73282957077026</v>
       </c>
       <c r="H1420" t="s">
         <v>8</v>
@@ -37315,7 +37315,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1421" t="n">
-        <v>1.80817019939423</v>
+        <v>1.80817008018494</v>
       </c>
       <c r="H1421" t="s">
         <v>8</v>
@@ -37341,7 +37341,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G1422" t="n">
-        <v>1.7997989654541</v>
+        <v>1.79979884624481</v>
       </c>
       <c r="H1422" t="s">
         <v>8</v>
@@ -37367,7 +37367,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G1423" t="n">
-        <v>1.81654107570648</v>
+        <v>1.81654119491577</v>
       </c>
       <c r="H1423" t="s">
         <v>8</v>
@@ -37393,7 +37393,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G1424" t="n">
-        <v>1.81654107570648</v>
+        <v>1.81654119491577</v>
       </c>
       <c r="H1424" t="s">
         <v>8</v>
@@ -37419,7 +37419,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G1425" t="n">
-        <v>1.81654107570648</v>
+        <v>1.81654119491577</v>
       </c>
       <c r="H1425" t="s">
         <v>8</v>
@@ -37471,7 +37471,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G1427" t="n">
-        <v>1.85839712619781</v>
+        <v>1.85839688777924</v>
       </c>
       <c r="H1427" t="s">
         <v>8</v>
@@ -37497,7 +37497,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G1428" t="n">
-        <v>1.85839712619781</v>
+        <v>1.85839688777924</v>
       </c>
       <c r="H1428" t="s">
         <v>8</v>
@@ -37523,7 +37523,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G1429" t="n">
-        <v>1.85839712619781</v>
+        <v>1.85839688777924</v>
       </c>
       <c r="H1429" t="s">
         <v>8</v>
@@ -37627,7 +37627,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G1433" t="n">
-        <v>1.79142785072327</v>
+        <v>1.79142773151398</v>
       </c>
       <c r="H1433" t="s">
         <v>8</v>
@@ -37653,7 +37653,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G1434" t="n">
-        <v>1.81654107570648</v>
+        <v>1.81654119491577</v>
       </c>
       <c r="H1434" t="s">
         <v>8</v>
@@ -37679,7 +37679,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G1435" t="n">
-        <v>1.85839712619781</v>
+        <v>1.85839688777924</v>
       </c>
       <c r="H1435" t="s">
         <v>8</v>
@@ -37705,7 +37705,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G1436" t="n">
-        <v>1.85839712619781</v>
+        <v>1.85839688777924</v>
       </c>
       <c r="H1436" t="s">
         <v>8</v>
@@ -37757,7 +37757,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G1438" t="n">
-        <v>1.8249124288559</v>
+        <v>1.82491230964661</v>
       </c>
       <c r="H1438" t="s">
         <v>8</v>
@@ -37783,7 +37783,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G1439" t="n">
-        <v>1.7997989654541</v>
+        <v>1.79979884624481</v>
       </c>
       <c r="H1439" t="s">
         <v>8</v>
@@ -37809,7 +37809,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G1440" t="n">
-        <v>1.81654107570648</v>
+        <v>1.81654119491577</v>
       </c>
       <c r="H1440" t="s">
         <v>8</v>
@@ -37835,7 +37835,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G1441" t="n">
-        <v>1.8249124288559</v>
+        <v>1.82491230964661</v>
       </c>
       <c r="H1441" t="s">
         <v>8</v>
@@ -37861,7 +37861,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1442" t="n">
-        <v>1.80817019939423</v>
+        <v>1.80817008018494</v>
       </c>
       <c r="H1442" t="s">
         <v>8</v>
@@ -37939,7 +37939,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G1445" t="n">
-        <v>1.7997989654541</v>
+        <v>1.79979884624481</v>
       </c>
       <c r="H1445" t="s">
         <v>8</v>
@@ -37965,7 +37965,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G1446" t="n">
-        <v>1.7997989654541</v>
+        <v>1.79979884624481</v>
       </c>
       <c r="H1446" t="s">
         <v>8</v>
@@ -37991,7 +37991,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G1447" t="n">
-        <v>1.79142785072327</v>
+        <v>1.79142773151398</v>
       </c>
       <c r="H1447" t="s">
         <v>8</v>
@@ -38043,7 +38043,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G1449" t="n">
-        <v>1.7997989654541</v>
+        <v>1.79979884624481</v>
       </c>
       <c r="H1449" t="s">
         <v>8</v>
@@ -38095,7 +38095,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G1451" t="n">
-        <v>1.7997989654541</v>
+        <v>1.79979884624481</v>
       </c>
       <c r="H1451" t="s">
         <v>8</v>
@@ -38121,7 +38121,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G1452" t="n">
-        <v>1.7997989654541</v>
+        <v>1.79979884624481</v>
       </c>
       <c r="H1452" t="s">
         <v>8</v>
@@ -38173,7 +38173,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1454" t="n">
-        <v>1.75794279575348</v>
+        <v>1.75794291496277</v>
       </c>
       <c r="H1454" t="s">
         <v>8</v>
@@ -38199,7 +38199,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G1455" t="n">
-        <v>1.79142785072327</v>
+        <v>1.79142773151398</v>
       </c>
       <c r="H1455" t="s">
         <v>8</v>
@@ -38277,7 +38277,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G1458" t="n">
-        <v>1.86676800251007</v>
+        <v>1.86676812171936</v>
       </c>
       <c r="H1458" t="s">
         <v>8</v>
@@ -38303,7 +38303,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G1459" t="n">
-        <v>1.87513947486877</v>
+        <v>1.87513935565948</v>
       </c>
       <c r="H1459" t="s">
         <v>8</v>
@@ -38329,7 +38329,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G1460" t="n">
-        <v>1.87513947486877</v>
+        <v>1.87513935565948</v>
       </c>
       <c r="H1460" t="s">
         <v>8</v>
@@ -38355,7 +38355,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G1461" t="n">
-        <v>1.90025281906128</v>
+        <v>1.90025269985199</v>
       </c>
       <c r="H1461" t="s">
         <v>8</v>
@@ -38381,7 +38381,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G1462" t="n">
-        <v>2.1932430267334</v>
+        <v>2.19324326515198</v>
       </c>
       <c r="H1462" t="s">
         <v>8</v>
@@ -38407,7 +38407,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G1463" t="n">
-        <v>2.20161437988281</v>
+        <v>2.20161461830139</v>
       </c>
       <c r="H1463" t="s">
         <v>8</v>
@@ -38537,7 +38537,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G1468" t="n">
-        <v>2.01744890213013</v>
+        <v>2.01744914054871</v>
       </c>
       <c r="H1468" t="s">
         <v>8</v>
@@ -38667,7 +38667,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G1473" t="n">
-        <v>2.13464522361755</v>
+        <v>2.13464498519897</v>
       </c>
       <c r="H1473" t="s">
         <v>8</v>
@@ -38693,7 +38693,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G1474" t="n">
-        <v>2.10953164100647</v>
+        <v>2.10953140258789</v>
       </c>
       <c r="H1474" t="s">
         <v>8</v>
@@ -38771,7 +38771,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G1477" t="n">
-        <v>2.18487191200256</v>
+        <v>2.18487215042114</v>
       </c>
       <c r="H1477" t="s">
         <v>8</v>
@@ -38797,7 +38797,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G1478" t="n">
-        <v>2.20161437988281</v>
+        <v>2.20161461830139</v>
       </c>
       <c r="H1478" t="s">
         <v>8</v>
@@ -38849,7 +38849,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G1480" t="n">
-        <v>2.20998549461365</v>
+        <v>2.20998573303223</v>
       </c>
       <c r="H1480" t="s">
         <v>8</v>
@@ -38875,7 +38875,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G1481" t="n">
-        <v>2.20998549461365</v>
+        <v>2.20998573303223</v>
       </c>
       <c r="H1481" t="s">
         <v>8</v>
@@ -38901,7 +38901,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G1482" t="n">
-        <v>2.1932430267334</v>
+        <v>2.19324326515198</v>
       </c>
       <c r="H1482" t="s">
         <v>8</v>
@@ -38927,7 +38927,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G1483" t="n">
-        <v>2.15975856781006</v>
+        <v>2.15975880622864</v>
       </c>
       <c r="H1483" t="s">
         <v>8</v>
@@ -38953,7 +38953,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G1484" t="n">
-        <v>2.18487191200256</v>
+        <v>2.18487215042114</v>
       </c>
       <c r="H1484" t="s">
         <v>8</v>
@@ -38979,7 +38979,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G1485" t="n">
-        <v>2.18487191200256</v>
+        <v>2.18487215042114</v>
       </c>
       <c r="H1485" t="s">
         <v>8</v>
@@ -39005,7 +39005,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G1486" t="n">
-        <v>2.18487191200256</v>
+        <v>2.18487215042114</v>
       </c>
       <c r="H1486" t="s">
         <v>8</v>
@@ -39031,7 +39031,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G1487" t="n">
-        <v>2.18487191200256</v>
+        <v>2.18487215042114</v>
       </c>
       <c r="H1487" t="s">
         <v>8</v>
@@ -39135,7 +39135,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G1491" t="n">
-        <v>2.13464522361755</v>
+        <v>2.13464498519897</v>
       </c>
       <c r="H1491" t="s">
         <v>8</v>
@@ -39161,7 +39161,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G1492" t="n">
-        <v>2.15138745307922</v>
+        <v>2.15138721466064</v>
       </c>
       <c r="H1492" t="s">
         <v>8</v>
@@ -39239,7 +39239,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G1495" t="n">
-        <v>2.26021265983582</v>
+        <v>2.26021242141724</v>
       </c>
       <c r="H1495" t="s">
         <v>8</v>
@@ -39265,7 +39265,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G1496" t="n">
-        <v>2.23509907722473</v>
+        <v>2.23509883880615</v>
       </c>
       <c r="H1496" t="s">
         <v>8</v>
@@ -39291,7 +39291,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G1497" t="n">
-        <v>2.23509907722473</v>
+        <v>2.23509883880615</v>
       </c>
       <c r="H1497" t="s">
         <v>8</v>
@@ -39317,7 +39317,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G1498" t="n">
-        <v>2.21835684776306</v>
+        <v>2.21835660934448</v>
       </c>
       <c r="H1498" t="s">
         <v>8</v>
@@ -39343,7 +39343,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G1499" t="n">
-        <v>2.21835684776306</v>
+        <v>2.21835660934448</v>
       </c>
       <c r="H1499" t="s">
         <v>8</v>
@@ -39473,7 +39473,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G1504" t="n">
-        <v>2.24347043037415</v>
+        <v>2.24347019195557</v>
       </c>
       <c r="H1504" t="s">
         <v>8</v>
@@ -39499,7 +39499,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G1505" t="n">
-        <v>2.21835684776306</v>
+        <v>2.21835660934448</v>
       </c>
       <c r="H1505" t="s">
         <v>8</v>
@@ -39525,7 +39525,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G1506" t="n">
-        <v>2.26858377456665</v>
+        <v>2.26858353614807</v>
       </c>
       <c r="H1506" t="s">
         <v>8</v>
@@ -39551,7 +39551,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G1507" t="n">
-        <v>2.26858377456665</v>
+        <v>2.26858353614807</v>
       </c>
       <c r="H1507" t="s">
         <v>8</v>
@@ -39577,7 +39577,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G1508" t="n">
-        <v>2.26021265983582</v>
+        <v>2.26021242141724</v>
       </c>
       <c r="H1508" t="s">
         <v>8</v>
@@ -39603,7 +39603,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G1509" t="n">
-        <v>2.26858377456665</v>
+        <v>2.26858353614807</v>
       </c>
       <c r="H1509" t="s">
         <v>8</v>
@@ -39629,7 +39629,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G1510" t="n">
-        <v>2.26021265983582</v>
+        <v>2.26021242141724</v>
       </c>
       <c r="H1510" t="s">
         <v>8</v>
@@ -39655,7 +39655,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G1511" t="n">
-        <v>2.21835684776306</v>
+        <v>2.21835660934448</v>
       </c>
       <c r="H1511" t="s">
         <v>8</v>
@@ -39733,7 +39733,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G1514" t="n">
-        <v>2.26858377456665</v>
+        <v>2.26858353614807</v>
       </c>
       <c r="H1514" t="s">
         <v>8</v>
@@ -39759,7 +39759,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G1515" t="n">
-        <v>2.26858377456665</v>
+        <v>2.26858353614807</v>
       </c>
       <c r="H1515" t="s">
         <v>8</v>
@@ -39785,7 +39785,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G1516" t="n">
-        <v>2.26021265983582</v>
+        <v>2.26021242141724</v>
       </c>
       <c r="H1516" t="s">
         <v>8</v>
@@ -39811,7 +39811,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G1517" t="n">
-        <v>2.5448317527771</v>
+        <v>2.54483199119568</v>
       </c>
       <c r="H1517" t="s">
         <v>8</v>
@@ -39837,7 +39837,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G1518" t="n">
-        <v>2.62017250061035</v>
+        <v>2.62017226219177</v>
       </c>
       <c r="H1518" t="s">
         <v>8</v>
@@ -39863,7 +39863,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G1519" t="n">
-        <v>2.59505891799927</v>
+        <v>2.59505867958069</v>
       </c>
       <c r="H1519" t="s">
         <v>8</v>
@@ -39915,7 +39915,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G1521" t="n">
-        <v>2.71225476264954</v>
+        <v>2.71225500106812</v>
       </c>
       <c r="H1521" t="s">
         <v>8</v>
@@ -39967,7 +39967,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G1523" t="n">
-        <v>2.75411081314087</v>
+        <v>2.75411105155945</v>
       </c>
       <c r="H1523" t="s">
         <v>8</v>
@@ -40045,7 +40045,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G1526" t="n">
-        <v>3.20615291595459</v>
+        <v>3.20615339279175</v>
       </c>
       <c r="H1526" t="s">
         <v>8</v>
@@ -40071,7 +40071,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G1527" t="n">
-        <v>3.10569953918457</v>
+        <v>3.10569930076599</v>
       </c>
       <c r="H1527" t="s">
         <v>8</v>
@@ -40149,7 +40149,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1530" t="n">
-        <v>3.01361656188965</v>
+        <v>3.01361680030823</v>
       </c>
       <c r="H1530" t="s">
         <v>8</v>
@@ -40227,7 +40227,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G1533" t="n">
-        <v>2.92153406143188</v>
+        <v>2.92153382301331</v>
       </c>
       <c r="H1533" t="s">
         <v>8</v>
@@ -40253,7 +40253,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G1534" t="n">
-        <v>2.87967801094055</v>
+        <v>2.87967824935913</v>
       </c>
       <c r="H1534" t="s">
         <v>8</v>
@@ -40279,7 +40279,7 @@
         <v>3.5</v>
       </c>
       <c r="G1535" t="n">
-        <v>2.92990493774414</v>
+        <v>2.92990517616272</v>
       </c>
       <c r="H1535" t="s">
         <v>8</v>
@@ -40357,7 +40357,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1538" t="n">
-        <v>2.84619355201721</v>
+        <v>2.84619331359863</v>
       </c>
       <c r="H1538" t="s">
         <v>8</v>
@@ -40409,7 +40409,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G1540" t="n">
-        <v>2.78759527206421</v>
+        <v>2.78759551048279</v>
       </c>
       <c r="H1540" t="s">
         <v>8</v>
@@ -40513,7 +40513,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G1544" t="n">
-        <v>2.97176074981689</v>
+        <v>2.97176098823547</v>
       </c>
       <c r="H1544" t="s">
         <v>8</v>
@@ -40591,7 +40591,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G1547" t="n">
-        <v>3.04710149765015</v>
+        <v>3.04710125923157</v>
       </c>
       <c r="H1547" t="s">
         <v>8</v>
@@ -40669,7 +40669,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G1550" t="n">
-        <v>3.17266821861267</v>
+        <v>3.17266869544983</v>
       </c>
       <c r="H1550" t="s">
         <v>8</v>
@@ -40695,7 +40695,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G1551" t="n">
-        <v>3.22289538383484</v>
+        <v>3.22289562225342</v>
       </c>
       <c r="H1551" t="s">
         <v>8</v>
@@ -40773,7 +40773,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G1554" t="n">
-        <v>3.08865118026733</v>
+        <v>3.08865141868591</v>
       </c>
       <c r="H1554" t="s">
         <v>8</v>
@@ -40799,7 +40799,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G1555" t="n">
-        <v>3.05414128303528</v>
+        <v>3.05414152145386</v>
       </c>
       <c r="H1555" t="s">
         <v>8</v>
@@ -40825,7 +40825,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G1556" t="n">
-        <v>3.21806406974792</v>
+        <v>3.2180643081665</v>
       </c>
       <c r="H1556" t="s">
         <v>8</v>
@@ -40851,7 +40851,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G1557" t="n">
-        <v>3.15767168998718</v>
+        <v>3.1576714515686</v>
       </c>
       <c r="H1557" t="s">
         <v>8</v>
@@ -40877,7 +40877,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G1558" t="n">
-        <v>3.16629934310913</v>
+        <v>3.16629910469055</v>
       </c>
       <c r="H1558" t="s">
         <v>8</v>
@@ -40929,7 +40929,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G1560" t="n">
-        <v>3.1317892074585</v>
+        <v>3.13178896903992</v>
       </c>
       <c r="H1560" t="s">
         <v>8</v>
@@ -40981,7 +40981,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G1562" t="n">
-        <v>3.1317892074585</v>
+        <v>3.13178896903992</v>
       </c>
       <c r="H1562" t="s">
         <v>8</v>
@@ -41007,7 +41007,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G1563" t="n">
-        <v>3.1317892074585</v>
+        <v>3.13178896903992</v>
       </c>
       <c r="H1563" t="s">
         <v>8</v>
@@ -41163,7 +41163,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G1569" t="n">
-        <v>3.03688621520996</v>
+        <v>3.03688645362854</v>
       </c>
       <c r="H1569" t="s">
         <v>8</v>
@@ -41293,7 +41293,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G1574" t="n">
-        <v>2.66590309143066</v>
+        <v>2.66590285301208</v>
       </c>
       <c r="H1574" t="s">
         <v>8</v>
@@ -41319,7 +41319,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G1575" t="n">
-        <v>2.62276530265808</v>
+        <v>2.62276554107666</v>
       </c>
       <c r="H1575" t="s">
         <v>8</v>
@@ -41475,7 +41475,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G1581" t="n">
-        <v>3.00237631797791</v>
+        <v>3.00237607955933</v>
       </c>
       <c r="H1581" t="s">
         <v>8</v>
@@ -41501,7 +41501,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G1582" t="n">
-        <v>2.96786642074585</v>
+        <v>2.96786618232727</v>
       </c>
       <c r="H1582" t="s">
         <v>8</v>
@@ -41579,7 +41579,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G1585" t="n">
-        <v>2.99374890327454</v>
+        <v>2.99374866485596</v>
       </c>
       <c r="H1585" t="s">
         <v>8</v>
@@ -41657,7 +41657,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G1588" t="n">
-        <v>3.00237631797791</v>
+        <v>3.00237607955933</v>
       </c>
       <c r="H1588" t="s">
         <v>8</v>
@@ -41683,7 +41683,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G1589" t="n">
-        <v>3.08865118026733</v>
+        <v>3.08865141868591</v>
       </c>
       <c r="H1589" t="s">
         <v>8</v>
@@ -42125,7 +42125,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1606" t="n">
-        <v>2.89021825790405</v>
+        <v>2.89021849632263</v>
       </c>
       <c r="H1606" t="s">
         <v>8</v>
@@ -71664,6 +71664,32 @@
         <v>0.428000003099442</v>
       </c>
       <c r="H2742" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2743">
+      <c r="A2743" s="1" t="n">
+        <v>46310.2916666667</v>
+      </c>
+      <c r="B2743" t="n">
+        <v>798</v>
+      </c>
+      <c r="C2743" t="n">
+        <v>0.428000003099442</v>
+      </c>
+      <c r="D2743" t="n">
+        <v>0.400000005960464</v>
+      </c>
+      <c r="E2743" t="n">
+        <v>0.428000003099442</v>
+      </c>
+      <c r="F2743" t="n">
+        <v>0.400000005960464</v>
+      </c>
+      <c r="G2743" t="n">
+        <v>0.400000005960464</v>
+      </c>
+      <c r="H2743" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/ZUC.MI.xlsx
+++ b/data/ZUC.MI.xlsx
@@ -421,7 +421,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G2" t="n">
-        <v>3.01633286476135</v>
+        <v>3.01633310317993</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -473,7 +473,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G4" t="n">
-        <v>2.96163249015808</v>
+        <v>2.96163272857666</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -551,7 +551,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G7" t="n">
-        <v>2.84441781044006</v>
+        <v>2.84441757202148</v>
       </c>
       <c r="H7" t="s">
         <v>8</v>
@@ -629,7 +629,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G10" t="n">
-        <v>2.89130401611328</v>
+        <v>2.8913037776947</v>
       </c>
       <c r="H10" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G11" t="n">
-        <v>2.77408838272095</v>
+        <v>2.77408862113953</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G13" t="n">
-        <v>2.50840139389038</v>
+        <v>2.5084011554718</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -759,7 +759,7 @@
         <v>3</v>
       </c>
       <c r="G15" t="n">
-        <v>2.34430003166199</v>
+        <v>2.34430027008057</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
@@ -785,7 +785,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G16" t="n">
-        <v>2.39118599891663</v>
+        <v>2.39118623733521</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>3</v>
       </c>
       <c r="G19" t="n">
-        <v>2.34430003166199</v>
+        <v>2.34430027008057</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -915,7 +915,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G21" t="n">
-        <v>2.3286714553833</v>
+        <v>2.32867169380188</v>
       </c>
       <c r="H21" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G24" t="n">
-        <v>2.16457033157349</v>
+        <v>2.16457056999207</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G26" t="n">
-        <v>1.44565200805664</v>
+        <v>1.44565188884735</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>1.5</v>
       </c>
       <c r="G30" t="n">
-        <v>1.17215001583099</v>
+        <v>1.17215013504028</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>3</v>
       </c>
       <c r="G34" t="n">
-        <v>2.34430003166199</v>
+        <v>2.34430027008057</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>3</v>
       </c>
       <c r="G36" t="n">
-        <v>2.34430003166199</v>
+        <v>2.34430027008057</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G37" t="n">
-        <v>2.7115740776062</v>
+        <v>2.71157383918762</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1435,7 +1435,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G41" t="n">
-        <v>2.51621556282043</v>
+        <v>2.51621532440186</v>
       </c>
       <c r="H41" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G45" t="n">
-        <v>2.77408838272095</v>
+        <v>2.77408862113953</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G46" t="n">
-        <v>2.742830991745</v>
+        <v>2.74283123016357</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G49" t="n">
-        <v>2.57091593742371</v>
+        <v>2.57091569900513</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G51" t="n">
-        <v>2.54747295379639</v>
+        <v>2.54747319221497</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G53" t="n">
-        <v>2.43807196617126</v>
+        <v>2.43807220458984</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G62" t="n">
-        <v>2.05516982078552</v>
+        <v>2.0551700592041</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2189,7 +2189,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G70" t="n">
-        <v>1.82073986530304</v>
+        <v>1.82073974609375</v>
       </c>
       <c r="H70" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G71" t="n">
-        <v>1.8129255771637</v>
+        <v>1.81292569637299</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G74" t="n">
-        <v>1.91451215744019</v>
+        <v>1.91451191902161</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G79" t="n">
-        <v>1.75041091442108</v>
+        <v>1.75041079521179</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G81" t="n">
-        <v>1.75041091442108</v>
+        <v>1.75041079521179</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G99" t="n">
-        <v>2.26615715026855</v>
+        <v>2.26615691184998</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G104" t="n">
-        <v>1.93795502185822</v>
+        <v>1.9379551410675</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G105" t="n">
-        <v>1.88325464725494</v>
+        <v>1.88325452804565</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G106" t="n">
-        <v>1.82855403423309</v>
+        <v>1.82855415344238</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G117" t="n">
-        <v>1.57068109512329</v>
+        <v>1.57068121433258</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G120" t="n">
-        <v>1.57849538326263</v>
+        <v>1.57849550247192</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3515,7 +3515,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G121" t="n">
-        <v>1.57849538326263</v>
+        <v>1.57849550247192</v>
       </c>
       <c r="H121" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G122" t="n">
-        <v>1.57849538326263</v>
+        <v>1.57849550247192</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G123" t="n">
-        <v>1.57849538326263</v>
+        <v>1.57849550247192</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -3645,7 +3645,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G126" t="n">
-        <v>1.44565200805664</v>
+        <v>1.44565188884735</v>
       </c>
       <c r="H126" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G127" t="n">
-        <v>1.44565200805664</v>
+        <v>1.44565188884735</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3775,7 +3775,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G131" t="n">
-        <v>1.57068109512329</v>
+        <v>1.57068121433258</v>
       </c>
       <c r="H131" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>1.75</v>
       </c>
       <c r="G134" t="n">
-        <v>1.36750853061676</v>
+        <v>1.36750841140747</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3931,7 +3931,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G137" t="n">
-        <v>1.42220890522003</v>
+        <v>1.42220878601074</v>
       </c>
       <c r="H137" t="s">
         <v>8</v>
@@ -3983,7 +3983,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G139" t="n">
-        <v>1.46128046512604</v>
+        <v>1.46128034591675</v>
       </c>
       <c r="H139" t="s">
         <v>8</v>
@@ -4087,7 +4087,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G143" t="n">
-        <v>1.42220890522003</v>
+        <v>1.42220878601074</v>
       </c>
       <c r="H143" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G147" t="n">
-        <v>1.44565200805664</v>
+        <v>1.44565188884735</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4321,7 +4321,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G152" t="n">
-        <v>1.44565200805664</v>
+        <v>1.44565188884735</v>
       </c>
       <c r="H152" t="s">
         <v>8</v>
@@ -4347,7 +4347,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G153" t="n">
-        <v>1.42220890522003</v>
+        <v>1.42220878601074</v>
       </c>
       <c r="H153" t="s">
         <v>8</v>
@@ -4399,7 +4399,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G155" t="n">
-        <v>1.50035202503204</v>
+        <v>1.50035214424133</v>
       </c>
       <c r="H155" t="s">
         <v>8</v>
@@ -4451,7 +4451,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G157" t="n">
-        <v>1.50816643238068</v>
+        <v>1.50816655158997</v>
       </c>
       <c r="H157" t="s">
         <v>8</v>
@@ -4477,7 +4477,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G158" t="n">
-        <v>1.50035202503204</v>
+        <v>1.50035214424133</v>
       </c>
       <c r="H158" t="s">
         <v>8</v>
@@ -4529,7 +4529,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G160" t="n">
-        <v>1.46128046512604</v>
+        <v>1.46128034591675</v>
       </c>
       <c r="H160" t="s">
         <v>8</v>
@@ -4581,7 +4581,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G162" t="n">
-        <v>1.46128046512604</v>
+        <v>1.46128034591675</v>
       </c>
       <c r="H162" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G164" t="n">
-        <v>1.44565200805664</v>
+        <v>1.44565188884735</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4867,7 +4867,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G173" t="n">
-        <v>1.46128046512604</v>
+        <v>1.46128034591675</v>
       </c>
       <c r="H173" t="s">
         <v>8</v>
@@ -4945,7 +4945,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G176" t="n">
-        <v>1.46128046512604</v>
+        <v>1.46128034591675</v>
       </c>
       <c r="H176" t="s">
         <v>8</v>
@@ -4971,7 +4971,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G177" t="n">
-        <v>1.52379512786865</v>
+        <v>1.52379524707794</v>
       </c>
       <c r="H177" t="s">
         <v>8</v>
@@ -5205,7 +5205,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G186" t="n">
-        <v>1.44565200805664</v>
+        <v>1.44565188884735</v>
       </c>
       <c r="H186" t="s">
         <v>8</v>
@@ -5309,7 +5309,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G190" t="n">
-        <v>1.52379512786865</v>
+        <v>1.52379524707794</v>
       </c>
       <c r="H190" t="s">
         <v>8</v>
@@ -5335,7 +5335,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G191" t="n">
-        <v>1.52379512786865</v>
+        <v>1.52379524707794</v>
       </c>
       <c r="H191" t="s">
         <v>8</v>
@@ -5699,7 +5699,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G205" t="n">
-        <v>1.50816643238068</v>
+        <v>1.50816655158997</v>
       </c>
       <c r="H205" t="s">
         <v>8</v>
@@ -5829,7 +5829,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G210" t="n">
-        <v>1.52379512786865</v>
+        <v>1.52379524707794</v>
       </c>
       <c r="H210" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G214" t="n">
-        <v>1.57068109512329</v>
+        <v>1.57068121433258</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G216" t="n">
-        <v>1.50816643238068</v>
+        <v>1.50816655158997</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6011,7 +6011,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G217" t="n">
-        <v>1.52379512786865</v>
+        <v>1.52379524707794</v>
       </c>
       <c r="H217" t="s">
         <v>8</v>
@@ -6141,7 +6141,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G222" t="n">
-        <v>1.61756694316864</v>
+        <v>1.61756706237793</v>
       </c>
       <c r="H222" t="s">
         <v>8</v>
@@ -6167,7 +6167,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G223" t="n">
-        <v>1.57849538326263</v>
+        <v>1.57849550247192</v>
       </c>
       <c r="H223" t="s">
         <v>8</v>
@@ -6427,7 +6427,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G233" t="n">
-        <v>1.52379512786865</v>
+        <v>1.52379524707794</v>
       </c>
       <c r="H233" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G236" t="n">
-        <v>1.46128046512604</v>
+        <v>1.46128034591675</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6635,7 +6635,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G241" t="n">
-        <v>1.52379512786865</v>
+        <v>1.52379524707794</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -6661,7 +6661,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G242" t="n">
-        <v>1.52379512786865</v>
+        <v>1.52379524707794</v>
       </c>
       <c r="H242" t="s">
         <v>8</v>
@@ -6687,7 +6687,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G243" t="n">
-        <v>1.50035202503204</v>
+        <v>1.50035214424133</v>
       </c>
       <c r="H243" t="s">
         <v>8</v>
@@ -6713,7 +6713,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G244" t="n">
-        <v>1.50035202503204</v>
+        <v>1.50035214424133</v>
       </c>
       <c r="H244" t="s">
         <v>8</v>
@@ -6765,7 +6765,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G246" t="n">
-        <v>1.50035202503204</v>
+        <v>1.50035214424133</v>
       </c>
       <c r="H246" t="s">
         <v>8</v>
@@ -6791,7 +6791,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G247" t="n">
-        <v>1.50035202503204</v>
+        <v>1.50035214424133</v>
       </c>
       <c r="H247" t="s">
         <v>8</v>
@@ -6817,7 +6817,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G248" t="n">
-        <v>1.50035202503204</v>
+        <v>1.50035214424133</v>
       </c>
       <c r="H248" t="s">
         <v>8</v>
@@ -6869,7 +6869,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G250" t="n">
-        <v>1.50035202503204</v>
+        <v>1.50035214424133</v>
       </c>
       <c r="H250" t="s">
         <v>8</v>
@@ -6895,7 +6895,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G251" t="n">
-        <v>1.50816643238068</v>
+        <v>1.50816655158997</v>
       </c>
       <c r="H251" t="s">
         <v>8</v>
@@ -6973,7 +6973,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G254" t="n">
-        <v>1.50035202503204</v>
+        <v>1.50035214424133</v>
       </c>
       <c r="H254" t="s">
         <v>8</v>
@@ -7129,7 +7129,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G260" t="n">
-        <v>1.76603937149048</v>
+        <v>1.76603925228119</v>
       </c>
       <c r="H260" t="s">
         <v>8</v>
@@ -7181,7 +7181,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G262" t="n">
-        <v>1.72696805000305</v>
+        <v>1.72696793079376</v>
       </c>
       <c r="H262" t="s">
         <v>8</v>
@@ -7467,7 +7467,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G273" t="n">
-        <v>2.54747295379639</v>
+        <v>2.54747319221497</v>
       </c>
       <c r="H273" t="s">
         <v>8</v>
@@ -7545,7 +7545,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G276" t="n">
-        <v>2.54747295379639</v>
+        <v>2.54747319221497</v>
       </c>
       <c r="H276" t="s">
         <v>8</v>
@@ -7623,7 +7623,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G279" t="n">
-        <v>2.32085752487183</v>
+        <v>2.32085728645325</v>
       </c>
       <c r="H279" t="s">
         <v>8</v>
@@ -7675,7 +7675,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G281" t="n">
-        <v>2.26615715026855</v>
+        <v>2.26615691184998</v>
       </c>
       <c r="H281" t="s">
         <v>8</v>
@@ -7883,7 +7883,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G289" t="n">
-        <v>2.50840139389038</v>
+        <v>2.5084011554718</v>
       </c>
       <c r="H289" t="s">
         <v>8</v>
@@ -8065,7 +8065,7 @@
         <v>2.75</v>
       </c>
       <c r="G296" t="n">
-        <v>2.14894151687622</v>
+        <v>2.1489417552948</v>
       </c>
       <c r="H296" t="s">
         <v>8</v>
@@ -8169,7 +8169,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G300" t="n">
-        <v>2.16457033157349</v>
+        <v>2.16457056999207</v>
       </c>
       <c r="H300" t="s">
         <v>8</v>
@@ -8325,7 +8325,7 @@
         <v>2.75</v>
       </c>
       <c r="G306" t="n">
-        <v>2.14894151687622</v>
+        <v>2.1489417552948</v>
       </c>
       <c r="H306" t="s">
         <v>8</v>
@@ -8403,7 +8403,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G309" t="n">
-        <v>2.16457033157349</v>
+        <v>2.16457056999207</v>
       </c>
       <c r="H309" t="s">
         <v>8</v>
@@ -8481,7 +8481,7 @@
         <v>2.75</v>
       </c>
       <c r="G312" t="n">
-        <v>2.14894151687622</v>
+        <v>2.1489417552948</v>
       </c>
       <c r="H312" t="s">
         <v>8</v>
@@ -8533,7 +8533,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G314" t="n">
-        <v>2.19582772254944</v>
+        <v>2.19582796096802</v>
       </c>
       <c r="H314" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>3</v>
       </c>
       <c r="G317" t="n">
-        <v>2.34430003166199</v>
+        <v>2.34430027008057</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8715,7 +8715,7 @@
         <v>3</v>
       </c>
       <c r="G321" t="n">
-        <v>2.34430003166199</v>
+        <v>2.34430027008057</v>
       </c>
       <c r="H321" t="s">
         <v>8</v>
@@ -8741,7 +8741,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G322" t="n">
-        <v>2.32085752487183</v>
+        <v>2.32085728645325</v>
       </c>
       <c r="H322" t="s">
         <v>8</v>
@@ -8767,7 +8767,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G323" t="n">
-        <v>2.26615715026855</v>
+        <v>2.26615691184998</v>
       </c>
       <c r="H323" t="s">
         <v>8</v>
@@ -8793,7 +8793,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G324" t="n">
-        <v>2.24271368980408</v>
+        <v>2.24271392822266</v>
       </c>
       <c r="H324" t="s">
         <v>8</v>
@@ -8845,7 +8845,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G326" t="n">
-        <v>2.3286714553833</v>
+        <v>2.32867169380188</v>
       </c>
       <c r="H326" t="s">
         <v>8</v>
@@ -8949,7 +8949,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G330" t="n">
-        <v>2.26615715026855</v>
+        <v>2.26615691184998</v>
       </c>
       <c r="H330" t="s">
         <v>8</v>
@@ -9001,7 +9001,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G332" t="n">
-        <v>2.19582772254944</v>
+        <v>2.19582796096802</v>
       </c>
       <c r="H332" t="s">
         <v>8</v>
@@ -9183,7 +9183,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G339" t="n">
-        <v>2.3286714553833</v>
+        <v>2.32867169380188</v>
       </c>
       <c r="H339" t="s">
         <v>8</v>
@@ -9209,7 +9209,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G340" t="n">
-        <v>2.26615715026855</v>
+        <v>2.26615691184998</v>
       </c>
       <c r="H340" t="s">
         <v>8</v>
@@ -9313,7 +9313,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G344" t="n">
-        <v>2.50840139389038</v>
+        <v>2.5084011554718</v>
       </c>
       <c r="H344" t="s">
         <v>8</v>
@@ -9469,7 +9469,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G350" t="n">
-        <v>2.33648586273193</v>
+        <v>2.33648610115051</v>
       </c>
       <c r="H350" t="s">
         <v>8</v>
@@ -9547,7 +9547,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G353" t="n">
-        <v>2.26615715026855</v>
+        <v>2.26615691184998</v>
       </c>
       <c r="H353" t="s">
         <v>8</v>
@@ -9625,7 +9625,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G356" t="n">
-        <v>2.35992860794067</v>
+        <v>2.35992884635925</v>
       </c>
       <c r="H356" t="s">
         <v>8</v>
@@ -9651,7 +9651,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G357" t="n">
-        <v>2.3286714553833</v>
+        <v>2.32867169380188</v>
       </c>
       <c r="H357" t="s">
         <v>8</v>
@@ -9859,7 +9859,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G365" t="n">
-        <v>2.19582772254944</v>
+        <v>2.19582796096802</v>
       </c>
       <c r="H365" t="s">
         <v>8</v>
@@ -9885,7 +9885,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G366" t="n">
-        <v>2.19582772254944</v>
+        <v>2.19582796096802</v>
       </c>
       <c r="H366" t="s">
         <v>8</v>
@@ -9963,7 +9963,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G369" t="n">
-        <v>2.19582772254944</v>
+        <v>2.19582796096802</v>
       </c>
       <c r="H369" t="s">
         <v>8</v>
@@ -9989,7 +9989,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G370" t="n">
-        <v>2.19582772254944</v>
+        <v>2.19582796096802</v>
       </c>
       <c r="H370" t="s">
         <v>8</v>
@@ -10353,7 +10353,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G384" t="n">
-        <v>2.23489952087402</v>
+        <v>2.23489928245544</v>
       </c>
       <c r="H384" t="s">
         <v>8</v>
@@ -10379,7 +10379,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G385" t="n">
-        <v>2.23489952087402</v>
+        <v>2.23489928245544</v>
       </c>
       <c r="H385" t="s">
         <v>8</v>
@@ -10431,7 +10431,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G387" t="n">
-        <v>2.24271368980408</v>
+        <v>2.24271392822266</v>
       </c>
       <c r="H387" t="s">
         <v>8</v>
@@ -10509,7 +10509,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G390" t="n">
-        <v>2.19582772254944</v>
+        <v>2.19582796096802</v>
       </c>
       <c r="H390" t="s">
         <v>8</v>
@@ -10535,7 +10535,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G391" t="n">
-        <v>2.23489952087402</v>
+        <v>2.23489928245544</v>
       </c>
       <c r="H391" t="s">
         <v>8</v>
@@ -10639,7 +10639,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G395" t="n">
-        <v>2.26615715026855</v>
+        <v>2.26615691184998</v>
       </c>
       <c r="H395" t="s">
         <v>8</v>
@@ -10717,7 +10717,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G398" t="n">
-        <v>2.23489952087402</v>
+        <v>2.23489928245544</v>
       </c>
       <c r="H398" t="s">
         <v>8</v>
@@ -10821,7 +10821,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G402" t="n">
-        <v>2.28178572654724</v>
+        <v>2.28178548812866</v>
       </c>
       <c r="H402" t="s">
         <v>8</v>
@@ -10873,7 +10873,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G404" t="n">
-        <v>2.28178572654724</v>
+        <v>2.28178548812866</v>
       </c>
       <c r="H404" t="s">
         <v>8</v>
@@ -10899,7 +10899,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G405" t="n">
-        <v>2.26615715026855</v>
+        <v>2.26615691184998</v>
       </c>
       <c r="H405" t="s">
         <v>8</v>
@@ -10925,7 +10925,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G406" t="n">
-        <v>2.24271368980408</v>
+        <v>2.24271392822266</v>
       </c>
       <c r="H406" t="s">
         <v>8</v>
@@ -10951,7 +10951,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G407" t="n">
-        <v>2.26615715026855</v>
+        <v>2.26615691184998</v>
       </c>
       <c r="H407" t="s">
         <v>8</v>
@@ -11055,7 +11055,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G411" t="n">
-        <v>2.26615715026855</v>
+        <v>2.26615691184998</v>
       </c>
       <c r="H411" t="s">
         <v>8</v>
@@ -11107,7 +11107,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G413" t="n">
-        <v>2.24271368980408</v>
+        <v>2.24271392822266</v>
       </c>
       <c r="H413" t="s">
         <v>8</v>
@@ -11289,7 +11289,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G420" t="n">
-        <v>2.24271368980408</v>
+        <v>2.24271392822266</v>
       </c>
       <c r="H420" t="s">
         <v>8</v>
@@ -11419,7 +11419,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G425" t="n">
-        <v>2.24271368980408</v>
+        <v>2.24271392822266</v>
       </c>
       <c r="H425" t="s">
         <v>8</v>
@@ -11497,7 +11497,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G428" t="n">
-        <v>2.28178572654724</v>
+        <v>2.28178548812866</v>
       </c>
       <c r="H428" t="s">
         <v>8</v>
@@ -11549,7 +11549,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G430" t="n">
-        <v>2.26615715026855</v>
+        <v>2.26615691184998</v>
       </c>
       <c r="H430" t="s">
         <v>8</v>
@@ -11705,7 +11705,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G436" t="n">
-        <v>2.28178572654724</v>
+        <v>2.28178548812866</v>
       </c>
       <c r="H436" t="s">
         <v>8</v>
@@ -11757,7 +11757,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G438" t="n">
-        <v>2.28178572654724</v>
+        <v>2.28178548812866</v>
       </c>
       <c r="H438" t="s">
         <v>8</v>
@@ -11835,7 +11835,7 @@
         <v>3</v>
       </c>
       <c r="G441" t="n">
-        <v>2.34430003166199</v>
+        <v>2.34430027008057</v>
       </c>
       <c r="H441" t="s">
         <v>8</v>
@@ -11861,7 +11861,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G442" t="n">
-        <v>2.33648586273193</v>
+        <v>2.33648610115051</v>
       </c>
       <c r="H442" t="s">
         <v>8</v>
@@ -11887,7 +11887,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G443" t="n">
-        <v>2.35992860794067</v>
+        <v>2.35992884635925</v>
       </c>
       <c r="H443" t="s">
         <v>8</v>
@@ -11939,7 +11939,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G445" t="n">
-        <v>2.32085752487183</v>
+        <v>2.32085728645325</v>
       </c>
       <c r="H445" t="s">
         <v>8</v>
@@ -11965,7 +11965,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G446" t="n">
-        <v>2.3286714553833</v>
+        <v>2.32867169380188</v>
       </c>
       <c r="H446" t="s">
         <v>8</v>
@@ -12095,7 +12095,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G451" t="n">
-        <v>2.28178572654724</v>
+        <v>2.28178548812866</v>
       </c>
       <c r="H451" t="s">
         <v>8</v>
@@ -12251,7 +12251,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G457" t="n">
-        <v>2.26615715026855</v>
+        <v>2.26615691184998</v>
       </c>
       <c r="H457" t="s">
         <v>8</v>
@@ -12277,7 +12277,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G458" t="n">
-        <v>2.26615715026855</v>
+        <v>2.26615691184998</v>
       </c>
       <c r="H458" t="s">
         <v>8</v>
@@ -12329,7 +12329,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G460" t="n">
-        <v>2.26615715026855</v>
+        <v>2.26615691184998</v>
       </c>
       <c r="H460" t="s">
         <v>8</v>
@@ -12485,7 +12485,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G466" t="n">
-        <v>2.24271368980408</v>
+        <v>2.24271392822266</v>
       </c>
       <c r="H466" t="s">
         <v>8</v>
@@ -12537,7 +12537,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G468" t="n">
-        <v>2.24271368980408</v>
+        <v>2.24271392822266</v>
       </c>
       <c r="H468" t="s">
         <v>8</v>
@@ -12563,7 +12563,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G469" t="n">
-        <v>2.24271368980408</v>
+        <v>2.24271392822266</v>
       </c>
       <c r="H469" t="s">
         <v>8</v>
@@ -12641,7 +12641,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G472" t="n">
-        <v>2.24271368980408</v>
+        <v>2.24271392822266</v>
       </c>
       <c r="H472" t="s">
         <v>8</v>
@@ -12693,7 +12693,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G474" t="n">
-        <v>2.28178572654724</v>
+        <v>2.28178548812866</v>
       </c>
       <c r="H474" t="s">
         <v>8</v>
@@ -12719,7 +12719,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G475" t="n">
-        <v>2.26615715026855</v>
+        <v>2.26615691184998</v>
       </c>
       <c r="H475" t="s">
         <v>8</v>
@@ -12745,7 +12745,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G476" t="n">
-        <v>2.26615715026855</v>
+        <v>2.26615691184998</v>
       </c>
       <c r="H476" t="s">
         <v>8</v>
@@ -12771,7 +12771,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G477" t="n">
-        <v>2.26615715026855</v>
+        <v>2.26615691184998</v>
       </c>
       <c r="H477" t="s">
         <v>8</v>
@@ -12901,7 +12901,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G482" t="n">
-        <v>2.05516982078552</v>
+        <v>2.0551700592041</v>
       </c>
       <c r="H482" t="s">
         <v>8</v>
@@ -12927,7 +12927,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G483" t="n">
-        <v>2.05516982078552</v>
+        <v>2.0551700592041</v>
       </c>
       <c r="H483" t="s">
         <v>8</v>
@@ -12979,7 +12979,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G485" t="n">
-        <v>2.04735541343689</v>
+        <v>2.04735517501831</v>
       </c>
       <c r="H485" t="s">
         <v>8</v>
@@ -13031,7 +13031,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G487" t="n">
-        <v>2.05516982078552</v>
+        <v>2.0551700592041</v>
       </c>
       <c r="H487" t="s">
         <v>8</v>
@@ -13057,7 +13057,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G488" t="n">
-        <v>2.09424161911011</v>
+        <v>2.09424138069153</v>
       </c>
       <c r="H488" t="s">
         <v>8</v>
@@ -13135,7 +13135,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G491" t="n">
-        <v>2.05516982078552</v>
+        <v>2.0551700592041</v>
       </c>
       <c r="H491" t="s">
         <v>8</v>
@@ -13187,7 +13187,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G493" t="n">
-        <v>2.0082836151123</v>
+        <v>2.00828385353088</v>
       </c>
       <c r="H493" t="s">
         <v>8</v>
@@ -13213,7 +13213,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G494" t="n">
-        <v>2.02391242980957</v>
+        <v>2.02391266822815</v>
       </c>
       <c r="H494" t="s">
         <v>8</v>
@@ -13239,7 +13239,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G495" t="n">
-        <v>2.02391242980957</v>
+        <v>2.02391266822815</v>
       </c>
       <c r="H495" t="s">
         <v>8</v>
@@ -13369,7 +13369,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G500" t="n">
-        <v>2.0082836151123</v>
+        <v>2.00828385353088</v>
       </c>
       <c r="H500" t="s">
         <v>8</v>
@@ -13629,7 +13629,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G510" t="n">
-        <v>2.0082836151123</v>
+        <v>2.00828385353088</v>
       </c>
       <c r="H510" t="s">
         <v>8</v>
@@ -13707,7 +13707,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G513" t="n">
-        <v>2.0082836151123</v>
+        <v>2.00828385353088</v>
       </c>
       <c r="H513" t="s">
         <v>8</v>
@@ -13837,7 +13837,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G518" t="n">
-        <v>2.09424161911011</v>
+        <v>2.09424138069153</v>
       </c>
       <c r="H518" t="s">
         <v>8</v>
@@ -13941,7 +13941,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G522" t="n">
-        <v>2.05516982078552</v>
+        <v>2.0551700592041</v>
       </c>
       <c r="H522" t="s">
         <v>8</v>
@@ -14019,7 +14019,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G525" t="n">
-        <v>2.05516982078552</v>
+        <v>2.0551700592041</v>
       </c>
       <c r="H525" t="s">
         <v>8</v>
@@ -14045,7 +14045,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G526" t="n">
-        <v>2.04735541343689</v>
+        <v>2.04735517501831</v>
       </c>
       <c r="H526" t="s">
         <v>8</v>
@@ -14071,7 +14071,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G527" t="n">
-        <v>2.04735541343689</v>
+        <v>2.04735517501831</v>
       </c>
       <c r="H527" t="s">
         <v>8</v>
@@ -14097,7 +14097,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G528" t="n">
-        <v>2.05516982078552</v>
+        <v>2.0551700592041</v>
       </c>
       <c r="H528" t="s">
         <v>8</v>
@@ -14123,7 +14123,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G529" t="n">
-        <v>2.04735541343689</v>
+        <v>2.04735517501831</v>
       </c>
       <c r="H529" t="s">
         <v>8</v>
@@ -14461,7 +14461,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G542" t="n">
-        <v>1.89106893539429</v>
+        <v>1.891068816185</v>
       </c>
       <c r="H542" t="s">
         <v>8</v>
@@ -14513,7 +14513,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G544" t="n">
-        <v>1.89106893539429</v>
+        <v>1.891068816185</v>
       </c>
       <c r="H544" t="s">
         <v>8</v>
@@ -14591,7 +14591,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G547" t="n">
-        <v>1.96921193599701</v>
+        <v>1.96921217441559</v>
       </c>
       <c r="H547" t="s">
         <v>8</v>
@@ -14617,7 +14617,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G548" t="n">
-        <v>1.96921193599701</v>
+        <v>1.96921217441559</v>
       </c>
       <c r="H548" t="s">
         <v>8</v>
@@ -14643,7 +14643,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G549" t="n">
-        <v>1.93795502185822</v>
+        <v>1.9379551410675</v>
       </c>
       <c r="H549" t="s">
         <v>8</v>
@@ -14669,7 +14669,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G550" t="n">
-        <v>2.04735541343689</v>
+        <v>2.04735517501831</v>
       </c>
       <c r="H550" t="s">
         <v>8</v>
@@ -14695,7 +14695,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G551" t="n">
-        <v>2.0082836151123</v>
+        <v>2.00828385353088</v>
       </c>
       <c r="H551" t="s">
         <v>8</v>
@@ -14721,7 +14721,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G552" t="n">
-        <v>2.02391242980957</v>
+        <v>2.02391266822815</v>
       </c>
       <c r="H552" t="s">
         <v>8</v>
@@ -14747,7 +14747,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G553" t="n">
-        <v>2.0082836151123</v>
+        <v>2.00828385353088</v>
       </c>
       <c r="H553" t="s">
         <v>8</v>
@@ -14877,7 +14877,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G558" t="n">
-        <v>1.88325464725494</v>
+        <v>1.88325452804565</v>
       </c>
       <c r="H558" t="s">
         <v>8</v>
@@ -14929,7 +14929,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G560" t="n">
-        <v>1.89888310432434</v>
+        <v>1.89888298511505</v>
       </c>
       <c r="H560" t="s">
         <v>8</v>
@@ -14955,7 +14955,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G561" t="n">
-        <v>1.89888310432434</v>
+        <v>1.89888298511505</v>
       </c>
       <c r="H561" t="s">
         <v>8</v>
@@ -14981,7 +14981,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G562" t="n">
-        <v>1.88325464725494</v>
+        <v>1.88325452804565</v>
       </c>
       <c r="H562" t="s">
         <v>8</v>
@@ -15059,7 +15059,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G565" t="n">
-        <v>1.91451215744019</v>
+        <v>1.91451191902161</v>
       </c>
       <c r="H565" t="s">
         <v>8</v>
@@ -15241,7 +15241,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G572" t="n">
-        <v>2.0082836151123</v>
+        <v>2.00828385353088</v>
       </c>
       <c r="H572" t="s">
         <v>8</v>
@@ -15397,7 +15397,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G578" t="n">
-        <v>2.05516982078552</v>
+        <v>2.0551700592041</v>
       </c>
       <c r="H578" t="s">
         <v>8</v>
@@ -15449,7 +15449,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G580" t="n">
-        <v>2.04735541343689</v>
+        <v>2.04735517501831</v>
       </c>
       <c r="H580" t="s">
         <v>8</v>
@@ -15605,7 +15605,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G586" t="n">
-        <v>2.02391242980957</v>
+        <v>2.02391266822815</v>
       </c>
       <c r="H586" t="s">
         <v>8</v>
@@ -15631,7 +15631,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G587" t="n">
-        <v>2.0082836151123</v>
+        <v>2.00828385353088</v>
       </c>
       <c r="H587" t="s">
         <v>8</v>
@@ -15657,7 +15657,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G588" t="n">
-        <v>1.96921193599701</v>
+        <v>1.96921217441559</v>
       </c>
       <c r="H588" t="s">
         <v>8</v>
@@ -15735,7 +15735,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G591" t="n">
-        <v>1.93795502185822</v>
+        <v>1.9379551410675</v>
       </c>
       <c r="H591" t="s">
         <v>8</v>
@@ -15761,7 +15761,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G592" t="n">
-        <v>1.96921193599701</v>
+        <v>1.96921217441559</v>
       </c>
       <c r="H592" t="s">
         <v>8</v>
@@ -15787,7 +15787,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G593" t="n">
-        <v>1.89888310432434</v>
+        <v>1.89888298511505</v>
       </c>
       <c r="H593" t="s">
         <v>8</v>
@@ -15813,7 +15813,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G594" t="n">
-        <v>1.96921193599701</v>
+        <v>1.96921217441559</v>
       </c>
       <c r="H594" t="s">
         <v>8</v>
@@ -15917,7 +15917,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G598" t="n">
-        <v>1.93795502185822</v>
+        <v>1.9379551410675</v>
       </c>
       <c r="H598" t="s">
         <v>8</v>
@@ -15943,7 +15943,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G599" t="n">
-        <v>1.91451215744019</v>
+        <v>1.91451191902161</v>
       </c>
       <c r="H599" t="s">
         <v>8</v>
@@ -16021,7 +16021,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G602" t="n">
-        <v>1.89106893539429</v>
+        <v>1.891068816185</v>
       </c>
       <c r="H602" t="s">
         <v>8</v>
@@ -16073,7 +16073,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G604" t="n">
-        <v>1.93795502185822</v>
+        <v>1.9379551410675</v>
       </c>
       <c r="H604" t="s">
         <v>8</v>
@@ -16099,7 +16099,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G605" t="n">
-        <v>1.89106893539429</v>
+        <v>1.891068816185</v>
       </c>
       <c r="H605" t="s">
         <v>8</v>
@@ -16359,7 +16359,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G615" t="n">
-        <v>1.88325464725494</v>
+        <v>1.88325452804565</v>
       </c>
       <c r="H615" t="s">
         <v>8</v>
@@ -16385,7 +16385,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G616" t="n">
-        <v>1.88325464725494</v>
+        <v>1.88325452804565</v>
       </c>
       <c r="H616" t="s">
         <v>8</v>
@@ -16463,7 +16463,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G619" t="n">
-        <v>1.89106893539429</v>
+        <v>1.891068816185</v>
       </c>
       <c r="H619" t="s">
         <v>8</v>
@@ -16489,7 +16489,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G620" t="n">
-        <v>1.82073986530304</v>
+        <v>1.82073974609375</v>
       </c>
       <c r="H620" t="s">
         <v>8</v>
@@ -16619,7 +16619,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G625" t="n">
-        <v>1.91451215744019</v>
+        <v>1.91451191902161</v>
       </c>
       <c r="H625" t="s">
         <v>8</v>
@@ -16671,7 +16671,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G627" t="n">
-        <v>1.82073986530304</v>
+        <v>1.82073974609375</v>
       </c>
       <c r="H627" t="s">
         <v>8</v>
@@ -16801,7 +16801,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G632" t="n">
-        <v>1.76603937149048</v>
+        <v>1.76603925228119</v>
       </c>
       <c r="H632" t="s">
         <v>8</v>
@@ -16827,7 +16827,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G633" t="n">
-        <v>1.76603937149048</v>
+        <v>1.76603925228119</v>
       </c>
       <c r="H633" t="s">
         <v>8</v>
@@ -16879,7 +16879,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G635" t="n">
-        <v>1.72696805000305</v>
+        <v>1.72696793079376</v>
       </c>
       <c r="H635" t="s">
         <v>8</v>
@@ -16905,7 +16905,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G636" t="n">
-        <v>1.75041091442108</v>
+        <v>1.75041079521179</v>
       </c>
       <c r="H636" t="s">
         <v>8</v>
@@ -16957,7 +16957,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G638" t="n">
-        <v>1.82073986530304</v>
+        <v>1.82073974609375</v>
       </c>
       <c r="H638" t="s">
         <v>8</v>
@@ -17061,7 +17061,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G642" t="n">
-        <v>1.75041091442108</v>
+        <v>1.75041079521179</v>
       </c>
       <c r="H642" t="s">
         <v>8</v>
@@ -17399,7 +17399,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G655" t="n">
-        <v>1.61756694316864</v>
+        <v>1.61756706237793</v>
       </c>
       <c r="H655" t="s">
         <v>8</v>
@@ -17425,7 +17425,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G656" t="n">
-        <v>1.61756694316864</v>
+        <v>1.61756706237793</v>
       </c>
       <c r="H656" t="s">
         <v>8</v>
@@ -17477,7 +17477,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G658" t="n">
-        <v>1.59412407875061</v>
+        <v>1.5941241979599</v>
       </c>
       <c r="H658" t="s">
         <v>8</v>
@@ -17737,7 +17737,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G668" t="n">
-        <v>1.88325464725494</v>
+        <v>1.88325452804565</v>
       </c>
       <c r="H668" t="s">
         <v>8</v>
@@ -17841,7 +17841,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G672" t="n">
-        <v>1.89888310432434</v>
+        <v>1.89888298511505</v>
       </c>
       <c r="H672" t="s">
         <v>8</v>
@@ -17919,7 +17919,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G675" t="n">
-        <v>1.89106893539429</v>
+        <v>1.891068816185</v>
       </c>
       <c r="H675" t="s">
         <v>8</v>
@@ -17945,7 +17945,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G676" t="n">
-        <v>1.91451215744019</v>
+        <v>1.91451191902161</v>
       </c>
       <c r="H676" t="s">
         <v>8</v>
@@ -17971,7 +17971,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G677" t="n">
-        <v>1.88325464725494</v>
+        <v>1.88325452804565</v>
       </c>
       <c r="H677" t="s">
         <v>8</v>
@@ -17997,7 +17997,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G678" t="n">
-        <v>1.82855403423309</v>
+        <v>1.82855415344238</v>
       </c>
       <c r="H678" t="s">
         <v>8</v>
@@ -18049,7 +18049,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G680" t="n">
-        <v>1.82855403423309</v>
+        <v>1.82855415344238</v>
       </c>
       <c r="H680" t="s">
         <v>8</v>
@@ -18075,7 +18075,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G681" t="n">
-        <v>1.76603937149048</v>
+        <v>1.76603925228119</v>
       </c>
       <c r="H681" t="s">
         <v>8</v>
@@ -18127,7 +18127,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G683" t="n">
-        <v>1.91451215744019</v>
+        <v>1.91451191902161</v>
       </c>
       <c r="H683" t="s">
         <v>8</v>
@@ -18153,7 +18153,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G684" t="n">
-        <v>1.82073986530304</v>
+        <v>1.82073974609375</v>
       </c>
       <c r="H684" t="s">
         <v>8</v>
@@ -18179,7 +18179,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G685" t="n">
-        <v>1.76603937149048</v>
+        <v>1.76603925228119</v>
       </c>
       <c r="H685" t="s">
         <v>8</v>
@@ -18231,7 +18231,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G687" t="n">
-        <v>1.76603937149048</v>
+        <v>1.76603925228119</v>
       </c>
       <c r="H687" t="s">
         <v>8</v>
@@ -18257,7 +18257,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G688" t="n">
-        <v>1.76603937149048</v>
+        <v>1.76603925228119</v>
       </c>
       <c r="H688" t="s">
         <v>8</v>
@@ -18309,7 +18309,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G690" t="n">
-        <v>1.75041091442108</v>
+        <v>1.75041079521179</v>
       </c>
       <c r="H690" t="s">
         <v>8</v>
@@ -18725,7 +18725,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G706" t="n">
-        <v>1.68789613246918</v>
+        <v>1.68789625167847</v>
       </c>
       <c r="H706" t="s">
         <v>8</v>
@@ -18803,7 +18803,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G709" t="n">
-        <v>1.68789613246918</v>
+        <v>1.68789625167847</v>
       </c>
       <c r="H709" t="s">
         <v>8</v>
@@ -18959,7 +18959,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G715" t="n">
-        <v>1.61756694316864</v>
+        <v>1.61756706237793</v>
       </c>
       <c r="H715" t="s">
         <v>8</v>
@@ -18985,7 +18985,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G716" t="n">
-        <v>1.61756694316864</v>
+        <v>1.61756706237793</v>
       </c>
       <c r="H716" t="s">
         <v>8</v>
@@ -19089,7 +19089,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G720" t="n">
-        <v>1.57068109512329</v>
+        <v>1.57068121433258</v>
       </c>
       <c r="H720" t="s">
         <v>8</v>
@@ -19141,7 +19141,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G722" t="n">
-        <v>1.61756694316864</v>
+        <v>1.61756706237793</v>
       </c>
       <c r="H722" t="s">
         <v>8</v>
@@ -19297,7 +19297,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G728" t="n">
-        <v>1.59412407875061</v>
+        <v>1.5941241979599</v>
       </c>
       <c r="H728" t="s">
         <v>8</v>
@@ -19323,7 +19323,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G729" t="n">
-        <v>1.57068109512329</v>
+        <v>1.57068121433258</v>
       </c>
       <c r="H729" t="s">
         <v>8</v>
@@ -19349,7 +19349,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G730" t="n">
-        <v>1.57068109512329</v>
+        <v>1.57068121433258</v>
       </c>
       <c r="H730" t="s">
         <v>8</v>
@@ -19531,7 +19531,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G737" t="n">
-        <v>1.50816643238068</v>
+        <v>1.50816655158997</v>
       </c>
       <c r="H737" t="s">
         <v>8</v>
@@ -19557,7 +19557,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G738" t="n">
-        <v>1.50035202503204</v>
+        <v>1.50035214424133</v>
       </c>
       <c r="H738" t="s">
         <v>8</v>
@@ -19635,7 +19635,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G741" t="n">
-        <v>1.50035202503204</v>
+        <v>1.50035214424133</v>
       </c>
       <c r="H741" t="s">
         <v>8</v>
@@ -19661,7 +19661,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G742" t="n">
-        <v>1.50816643238068</v>
+        <v>1.50816655158997</v>
       </c>
       <c r="H742" t="s">
         <v>8</v>
@@ -19765,7 +19765,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G746" t="n">
-        <v>1.59412407875061</v>
+        <v>1.5941241979599</v>
       </c>
       <c r="H746" t="s">
         <v>8</v>
@@ -19895,7 +19895,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G751" t="n">
-        <v>1.57849538326263</v>
+        <v>1.57849550247192</v>
       </c>
       <c r="H751" t="s">
         <v>8</v>
@@ -19921,7 +19921,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G752" t="n">
-        <v>1.52379512786865</v>
+        <v>1.52379524707794</v>
       </c>
       <c r="H752" t="s">
         <v>8</v>
@@ -19947,7 +19947,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G753" t="n">
-        <v>1.52379512786865</v>
+        <v>1.52379524707794</v>
       </c>
       <c r="H753" t="s">
         <v>8</v>
@@ -19973,7 +19973,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G754" t="n">
-        <v>1.52379512786865</v>
+        <v>1.52379524707794</v>
       </c>
       <c r="H754" t="s">
         <v>8</v>
@@ -20051,7 +20051,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G757" t="n">
-        <v>1.50816643238068</v>
+        <v>1.50816655158997</v>
       </c>
       <c r="H757" t="s">
         <v>8</v>
@@ -20129,7 +20129,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G760" t="n">
-        <v>1.57068109512329</v>
+        <v>1.57068121433258</v>
       </c>
       <c r="H760" t="s">
         <v>8</v>
@@ -20233,7 +20233,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G764" t="n">
-        <v>1.50816643238068</v>
+        <v>1.50816655158997</v>
       </c>
       <c r="H764" t="s">
         <v>8</v>
@@ -20493,7 +20493,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G774" t="n">
-        <v>1.57849538326263</v>
+        <v>1.57849550247192</v>
       </c>
       <c r="H774" t="s">
         <v>8</v>
@@ -21091,7 +21091,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G797" t="n">
-        <v>1.57068109512329</v>
+        <v>1.57068121433258</v>
       </c>
       <c r="H797" t="s">
         <v>8</v>
@@ -21117,7 +21117,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G798" t="n">
-        <v>1.57849538326263</v>
+        <v>1.57849550247192</v>
       </c>
       <c r="H798" t="s">
         <v>8</v>
@@ -21143,7 +21143,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G799" t="n">
-        <v>1.59412407875061</v>
+        <v>1.5941241979599</v>
       </c>
       <c r="H799" t="s">
         <v>8</v>
@@ -21299,7 +21299,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G805" t="n">
-        <v>1.59412407875061</v>
+        <v>1.5941241979599</v>
       </c>
       <c r="H805" t="s">
         <v>8</v>
@@ -21533,7 +21533,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G814" t="n">
-        <v>1.57068109512329</v>
+        <v>1.57068121433258</v>
       </c>
       <c r="H814" t="s">
         <v>8</v>
@@ -21741,7 +21741,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G822" t="n">
-        <v>1.61756694316864</v>
+        <v>1.61756706237793</v>
       </c>
       <c r="H822" t="s">
         <v>8</v>
@@ -21767,7 +21767,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G823" t="n">
-        <v>1.57849538326263</v>
+        <v>1.57849550247192</v>
       </c>
       <c r="H823" t="s">
         <v>8</v>
@@ -21793,7 +21793,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G824" t="n">
-        <v>1.57849538326263</v>
+        <v>1.57849550247192</v>
       </c>
       <c r="H824" t="s">
         <v>8</v>
@@ -21845,7 +21845,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G826" t="n">
-        <v>1.59412407875061</v>
+        <v>1.5941241979599</v>
       </c>
       <c r="H826" t="s">
         <v>8</v>
@@ -21897,7 +21897,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G828" t="n">
-        <v>1.89106893539429</v>
+        <v>1.891068816185</v>
       </c>
       <c r="H828" t="s">
         <v>8</v>
@@ -21975,7 +21975,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G831" t="n">
-        <v>1.65663874149323</v>
+        <v>1.65663862228394</v>
       </c>
       <c r="H831" t="s">
         <v>8</v>
@@ -22001,7 +22001,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G832" t="n">
-        <v>1.65663874149323</v>
+        <v>1.65663862228394</v>
       </c>
       <c r="H832" t="s">
         <v>8</v>
@@ -22209,7 +22209,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G840" t="n">
-        <v>1.59412407875061</v>
+        <v>1.5941241979599</v>
       </c>
       <c r="H840" t="s">
         <v>8</v>
@@ -22261,7 +22261,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G842" t="n">
-        <v>1.59412407875061</v>
+        <v>1.5941241979599</v>
       </c>
       <c r="H842" t="s">
         <v>8</v>
@@ -22287,7 +22287,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G843" t="n">
-        <v>1.57849538326263</v>
+        <v>1.57849550247192</v>
       </c>
       <c r="H843" t="s">
         <v>8</v>
@@ -22443,7 +22443,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G849" t="n">
-        <v>1.59412407875061</v>
+        <v>1.5941241979599</v>
       </c>
       <c r="H849" t="s">
         <v>8</v>
@@ -22469,7 +22469,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G850" t="n">
-        <v>1.59412407875061</v>
+        <v>1.5941241979599</v>
       </c>
       <c r="H850" t="s">
         <v>8</v>
@@ -22495,7 +22495,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G851" t="n">
-        <v>1.57849538326263</v>
+        <v>1.57849550247192</v>
       </c>
       <c r="H851" t="s">
         <v>8</v>
@@ -22573,7 +22573,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G854" t="n">
-        <v>1.59412407875061</v>
+        <v>1.5941241979599</v>
       </c>
       <c r="H854" t="s">
         <v>8</v>
@@ -22703,7 +22703,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G859" t="n">
-        <v>1.57849538326263</v>
+        <v>1.57849550247192</v>
       </c>
       <c r="H859" t="s">
         <v>8</v>
@@ -22859,7 +22859,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G865" t="n">
-        <v>1.50035202503204</v>
+        <v>1.50035214424133</v>
       </c>
       <c r="H865" t="s">
         <v>8</v>
@@ -22885,7 +22885,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G866" t="n">
-        <v>1.50035202503204</v>
+        <v>1.50035214424133</v>
       </c>
       <c r="H866" t="s">
         <v>8</v>
@@ -23015,7 +23015,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G871" t="n">
-        <v>1.50035202503204</v>
+        <v>1.50035214424133</v>
       </c>
       <c r="H871" t="s">
         <v>8</v>
@@ -23041,7 +23041,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G872" t="n">
-        <v>1.50035202503204</v>
+        <v>1.50035214424133</v>
       </c>
       <c r="H872" t="s">
         <v>8</v>
@@ -23717,7 +23717,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G898" t="n">
-        <v>1.50035202503204</v>
+        <v>1.50035214424133</v>
       </c>
       <c r="H898" t="s">
         <v>8</v>
@@ -23743,7 +23743,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G899" t="n">
-        <v>1.50035202503204</v>
+        <v>1.50035214424133</v>
       </c>
       <c r="H899" t="s">
         <v>8</v>
@@ -23769,7 +23769,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G900" t="n">
-        <v>1.50035202503204</v>
+        <v>1.50035214424133</v>
       </c>
       <c r="H900" t="s">
         <v>8</v>
@@ -23925,7 +23925,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G906" t="n">
-        <v>1.50035202503204</v>
+        <v>1.50035214424133</v>
       </c>
       <c r="H906" t="s">
         <v>8</v>
@@ -23951,7 +23951,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G907" t="n">
-        <v>1.50035202503204</v>
+        <v>1.50035214424133</v>
       </c>
       <c r="H907" t="s">
         <v>8</v>
@@ -24029,7 +24029,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G910" t="n">
-        <v>1.50035202503204</v>
+        <v>1.50035214424133</v>
       </c>
       <c r="H910" t="s">
         <v>8</v>
@@ -24107,7 +24107,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G913" t="n">
-        <v>1.50035202503204</v>
+        <v>1.50035214424133</v>
       </c>
       <c r="H913" t="s">
         <v>8</v>
@@ -24185,7 +24185,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G916" t="n">
-        <v>1.50035202503204</v>
+        <v>1.50035214424133</v>
       </c>
       <c r="H916" t="s">
         <v>8</v>
@@ -24211,7 +24211,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G917" t="n">
-        <v>1.50035202503204</v>
+        <v>1.50035214424133</v>
       </c>
       <c r="H917" t="s">
         <v>8</v>
@@ -24445,7 +24445,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G926" t="n">
-        <v>1.50035202503204</v>
+        <v>1.50035214424133</v>
       </c>
       <c r="H926" t="s">
         <v>8</v>
@@ -24471,7 +24471,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G927" t="n">
-        <v>1.50035202503204</v>
+        <v>1.50035214424133</v>
       </c>
       <c r="H927" t="s">
         <v>8</v>
@@ -24627,7 +24627,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G933" t="n">
-        <v>1.50035202503204</v>
+        <v>1.50035214424133</v>
       </c>
       <c r="H933" t="s">
         <v>8</v>
@@ -24809,7 +24809,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G940" t="n">
-        <v>1.50035202503204</v>
+        <v>1.50035214424133</v>
       </c>
       <c r="H940" t="s">
         <v>8</v>
@@ -25043,7 +25043,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G949" t="n">
-        <v>1.50035202503204</v>
+        <v>1.50035214424133</v>
       </c>
       <c r="H949" t="s">
         <v>8</v>
@@ -25069,7 +25069,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G950" t="n">
-        <v>1.50035202503204</v>
+        <v>1.50035214424133</v>
       </c>
       <c r="H950" t="s">
         <v>8</v>
@@ -25095,7 +25095,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G951" t="n">
-        <v>1.50035202503204</v>
+        <v>1.50035214424133</v>
       </c>
       <c r="H951" t="s">
         <v>8</v>
@@ -25121,7 +25121,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G952" t="n">
-        <v>1.50035202503204</v>
+        <v>1.50035214424133</v>
       </c>
       <c r="H952" t="s">
         <v>8</v>
@@ -25147,7 +25147,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G953" t="n">
-        <v>1.50035202503204</v>
+        <v>1.50035214424133</v>
       </c>
       <c r="H953" t="s">
         <v>8</v>
@@ -25173,7 +25173,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G954" t="n">
-        <v>1.50035202503204</v>
+        <v>1.50035214424133</v>
       </c>
       <c r="H954" t="s">
         <v>8</v>
@@ -25667,7 +25667,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G973" t="n">
-        <v>1.42220890522003</v>
+        <v>1.42220878601074</v>
       </c>
       <c r="H973" t="s">
         <v>8</v>
@@ -25745,7 +25745,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G976" t="n">
-        <v>1.42220890522003</v>
+        <v>1.42220878601074</v>
       </c>
       <c r="H976" t="s">
         <v>8</v>
@@ -25771,7 +25771,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G977" t="n">
-        <v>1.42220890522003</v>
+        <v>1.42220878601074</v>
       </c>
       <c r="H977" t="s">
         <v>8</v>
@@ -25953,7 +25953,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G984" t="n">
-        <v>1.42220890522003</v>
+        <v>1.42220878601074</v>
       </c>
       <c r="H984" t="s">
         <v>8</v>
@@ -25979,7 +25979,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G985" t="n">
-        <v>1.42220890522003</v>
+        <v>1.42220878601074</v>
       </c>
       <c r="H985" t="s">
         <v>8</v>
@@ -26005,7 +26005,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G986" t="n">
-        <v>1.42220890522003</v>
+        <v>1.42220878601074</v>
       </c>
       <c r="H986" t="s">
         <v>8</v>
@@ -26187,7 +26187,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G993" t="n">
-        <v>1.42220890522003</v>
+        <v>1.42220878601074</v>
       </c>
       <c r="H993" t="s">
         <v>8</v>
@@ -26213,7 +26213,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G994" t="n">
-        <v>1.42220890522003</v>
+        <v>1.42220878601074</v>
       </c>
       <c r="H994" t="s">
         <v>8</v>
@@ -26265,7 +26265,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G996" t="n">
-        <v>1.42220890522003</v>
+        <v>1.42220878601074</v>
       </c>
       <c r="H996" t="s">
         <v>8</v>
@@ -26447,7 +26447,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1003" t="n">
-        <v>1.68789613246918</v>
+        <v>1.68789625167847</v>
       </c>
       <c r="H1003" t="s">
         <v>8</v>
@@ -26577,7 +26577,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G1008" t="n">
-        <v>1.42220890522003</v>
+        <v>1.42220878601074</v>
       </c>
       <c r="H1008" t="s">
         <v>8</v>
@@ -26759,7 +26759,7 @@
         <v>1.86940002441406</v>
       </c>
       <c r="G1015" t="n">
-        <v>1.46081161499023</v>
+        <v>1.46081149578094</v>
       </c>
       <c r="H1015" t="s">
         <v>8</v>
@@ -26811,7 +26811,7 @@
         <v>1.80480003356934</v>
       </c>
       <c r="G1017" t="n">
-        <v>1.41033113002777</v>
+        <v>1.41033101081848</v>
       </c>
       <c r="H1017" t="s">
         <v>8</v>
@@ -26889,7 +26889,7 @@
         <v>1.81679999828339</v>
       </c>
       <c r="G1020" t="n">
-        <v>1.41970825195312</v>
+        <v>1.41970837116241</v>
       </c>
       <c r="H1020" t="s">
         <v>8</v>
@@ -27045,7 +27045,7 @@
         <v>1.74119997024536</v>
       </c>
       <c r="G1026" t="n">
-        <v>1.36063182353973</v>
+        <v>1.36063170433044</v>
       </c>
       <c r="H1026" t="s">
         <v>8</v>
@@ -27201,7 +27201,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G1032" t="n">
-        <v>1.35187995433807</v>
+        <v>1.35187983512878</v>
       </c>
       <c r="H1032" t="s">
         <v>8</v>
@@ -27461,7 +27461,7 @@
         <v>1.60580003261566</v>
       </c>
       <c r="G1042" t="n">
-        <v>1.25482571125031</v>
+        <v>1.25482583045959</v>
       </c>
       <c r="H1042" t="s">
         <v>8</v>
@@ -27487,7 +27487,7 @@
         <v>1.61819994449615</v>
       </c>
       <c r="G1043" t="n">
-        <v>1.26451539993286</v>
+        <v>1.26451551914215</v>
       </c>
       <c r="H1043" t="s">
         <v>8</v>
@@ -27513,7 +27513,7 @@
         <v>1.63900005817413</v>
       </c>
       <c r="G1044" t="n">
-        <v>1.28076946735382</v>
+        <v>1.28076934814453</v>
       </c>
       <c r="H1044" t="s">
         <v>8</v>
@@ -27539,7 +27539,7 @@
         <v>1.62979996204376</v>
       </c>
       <c r="G1045" t="n">
-        <v>1.2735800743103</v>
+        <v>1.27358019351959</v>
       </c>
       <c r="H1045" t="s">
         <v>8</v>
@@ -27591,7 +27591,7 @@
         <v>1.66260004043579</v>
       </c>
       <c r="G1047" t="n">
-        <v>1.29921126365662</v>
+        <v>1.29921114444733</v>
       </c>
       <c r="H1047" t="s">
         <v>8</v>
@@ -27695,7 +27695,7 @@
         <v>1.65020000934601</v>
       </c>
       <c r="G1051" t="n">
-        <v>1.28952145576477</v>
+        <v>1.28952133655548</v>
       </c>
       <c r="H1051" t="s">
         <v>8</v>
@@ -27747,7 +27747,7 @@
         <v>1.58379995822906</v>
       </c>
       <c r="G1053" t="n">
-        <v>1.23763418197632</v>
+        <v>1.23763406276703</v>
       </c>
       <c r="H1053" t="s">
         <v>8</v>
@@ -27773,7 +27773,7 @@
         <v>1.58379995822906</v>
       </c>
       <c r="G1054" t="n">
-        <v>1.23763418197632</v>
+        <v>1.23763406276703</v>
       </c>
       <c r="H1054" t="s">
         <v>8</v>
@@ -27825,7 +27825,7 @@
         <v>1.54159998893738</v>
       </c>
       <c r="G1056" t="n">
-        <v>1.20465779304504</v>
+        <v>1.20465767383575</v>
       </c>
       <c r="H1056" t="s">
         <v>8</v>
@@ -27877,7 +27877,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G1058" t="n">
-        <v>1.17996430397034</v>
+        <v>1.17996442317963</v>
       </c>
       <c r="H1058" t="s">
         <v>8</v>
@@ -27903,7 +27903,7 @@
         <v>1.55980002880096</v>
       </c>
       <c r="G1059" t="n">
-        <v>1.2188800573349</v>
+        <v>1.21887993812561</v>
       </c>
       <c r="H1059" t="s">
         <v>8</v>
@@ -27929,7 +27929,7 @@
         <v>1.5</v>
       </c>
       <c r="G1060" t="n">
-        <v>1.17215001583099</v>
+        <v>1.17215013504028</v>
       </c>
       <c r="H1060" t="s">
         <v>8</v>
@@ -28007,7 +28007,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G1063" t="n">
-        <v>0.883019685745239</v>
+        <v>0.883019626140594</v>
       </c>
       <c r="H1063" t="s">
         <v>8</v>
@@ -28033,7 +28033,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G1064" t="n">
-        <v>0.883019685745239</v>
+        <v>0.883019626140594</v>
       </c>
       <c r="H1064" t="s">
         <v>8</v>
@@ -28111,7 +28111,7 @@
         <v>0.997900009155273</v>
       </c>
       <c r="G1067" t="n">
-        <v>0.779792428016663</v>
+        <v>0.779792487621307</v>
       </c>
       <c r="H1067" t="s">
         <v>8</v>
@@ -28215,7 +28215,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G1071" t="n">
-        <v>0.789247691631317</v>
+        <v>0.789247751235962</v>
       </c>
       <c r="H1071" t="s">
         <v>8</v>
@@ -28267,7 +28267,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G1073" t="n">
-        <v>0.968977510929108</v>
+        <v>0.968977570533752</v>
       </c>
       <c r="H1073" t="s">
         <v>8</v>
@@ -28553,7 +28553,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G1084" t="n">
-        <v>1.25810778141022</v>
+        <v>1.25810766220093</v>
       </c>
       <c r="H1084" t="s">
         <v>8</v>
@@ -28579,7 +28579,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G1085" t="n">
-        <v>1.21903598308563</v>
+        <v>1.21903610229492</v>
       </c>
       <c r="H1085" t="s">
         <v>8</v>
@@ -28631,7 +28631,7 @@
         <v>1.52119994163513</v>
       </c>
       <c r="G1087" t="n">
-        <v>1.18871641159058</v>
+        <v>1.18871653079987</v>
       </c>
       <c r="H1087" t="s">
         <v>8</v>
@@ -28657,7 +28657,7 @@
         <v>1.52999997138977</v>
       </c>
       <c r="G1088" t="n">
-        <v>1.19559299945831</v>
+        <v>1.1955931186676</v>
       </c>
       <c r="H1088" t="s">
         <v>8</v>
@@ -28735,7 +28735,7 @@
         <v>1.53519999980927</v>
       </c>
       <c r="G1091" t="n">
-        <v>1.19965660572052</v>
+        <v>1.19965648651123</v>
       </c>
       <c r="H1091" t="s">
         <v>8</v>
@@ -28761,7 +28761,7 @@
         <v>1.51059997081757</v>
       </c>
       <c r="G1092" t="n">
-        <v>1.18043315410614</v>
+        <v>1.18043327331543</v>
       </c>
       <c r="H1092" t="s">
         <v>8</v>
@@ -28787,7 +28787,7 @@
         <v>1.53840005397797</v>
       </c>
       <c r="G1093" t="n">
-        <v>1.20215713977814</v>
+        <v>1.20215725898743</v>
       </c>
       <c r="H1093" t="s">
         <v>8</v>
@@ -28839,7 +28839,7 @@
         <v>1.42999994754791</v>
       </c>
       <c r="G1095" t="n">
-        <v>1.11744976043701</v>
+        <v>1.11744964122772</v>
       </c>
       <c r="H1095" t="s">
         <v>8</v>
@@ -28995,7 +28995,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G1101" t="n">
-        <v>1.06274950504303</v>
+        <v>1.06274938583374</v>
       </c>
       <c r="H1101" t="s">
         <v>8</v>
@@ -29125,7 +29125,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1106" t="n">
-        <v>1.04712080955505</v>
+        <v>1.04712069034576</v>
       </c>
       <c r="H1106" t="s">
         <v>8</v>
@@ -29151,7 +29151,7 @@
         <v>1.34080004692078</v>
       </c>
       <c r="G1107" t="n">
-        <v>1.04774582386017</v>
+        <v>1.04774594306946</v>
       </c>
       <c r="H1107" t="s">
         <v>8</v>
@@ -29177,7 +29177,7 @@
         <v>1.30019998550415</v>
       </c>
       <c r="G1108" t="n">
-        <v>1.01601982116699</v>
+        <v>1.0160197019577</v>
       </c>
       <c r="H1108" t="s">
         <v>8</v>
@@ -29307,7 +29307,7 @@
         <v>1.23800003528595</v>
       </c>
       <c r="G1113" t="n">
-        <v>0.967414617538452</v>
+        <v>0.967414677143097</v>
       </c>
       <c r="H1113" t="s">
         <v>8</v>
@@ -29333,7 +29333,7 @@
         <v>1.23039996623993</v>
       </c>
       <c r="G1114" t="n">
-        <v>0.961475670337677</v>
+        <v>0.961475729942322</v>
       </c>
       <c r="H1114" t="s">
         <v>8</v>
@@ -29437,7 +29437,7 @@
         <v>1.31719994544983</v>
       </c>
       <c r="G1118" t="n">
-        <v>1.02930414676666</v>
+        <v>1.02930402755737</v>
       </c>
       <c r="H1118" t="s">
         <v>8</v>
@@ -29541,7 +29541,7 @@
         <v>1.33940005302429</v>
       </c>
       <c r="G1122" t="n">
-        <v>1.04665195941925</v>
+        <v>1.04665184020996</v>
       </c>
       <c r="H1122" t="s">
         <v>8</v>
@@ -29645,7 +29645,7 @@
         <v>1.35979998111725</v>
       </c>
       <c r="G1126" t="n">
-        <v>1.06259310245514</v>
+        <v>1.06259322166443</v>
       </c>
       <c r="H1126" t="s">
         <v>8</v>
@@ -29749,7 +29749,7 @@
         <v>1.29579997062683</v>
       </c>
       <c r="G1130" t="n">
-        <v>1.0125812292099</v>
+        <v>1.01258134841919</v>
       </c>
       <c r="H1130" t="s">
         <v>8</v>
@@ -29801,7 +29801,7 @@
         <v>1.32280004024506</v>
       </c>
       <c r="G1132" t="n">
-        <v>1.03368020057678</v>
+        <v>1.03368008136749</v>
       </c>
       <c r="H1132" t="s">
         <v>8</v>
@@ -29827,7 +29827,7 @@
         <v>1.29820001125336</v>
       </c>
       <c r="G1133" t="n">
-        <v>1.01445698738098</v>
+        <v>1.01445686817169</v>
       </c>
       <c r="H1133" t="s">
         <v>8</v>
@@ -29853,7 +29853,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1134" t="n">
-        <v>1.04712080955505</v>
+        <v>1.04712069034576</v>
       </c>
       <c r="H1134" t="s">
         <v>8</v>
@@ -30087,7 +30087,7 @@
         <v>1.30900001525879</v>
       </c>
       <c r="G1143" t="n">
-        <v>1.02289640903473</v>
+        <v>1.02289628982544</v>
       </c>
       <c r="H1143" t="s">
         <v>8</v>
@@ -30165,7 +30165,7 @@
         <v>1.3257999420166</v>
       </c>
       <c r="G1146" t="n">
-        <v>1.03602433204651</v>
+        <v>1.0360244512558</v>
       </c>
       <c r="H1146" t="s">
         <v>8</v>
@@ -30373,7 +30373,7 @@
         <v>1.25440001487732</v>
       </c>
       <c r="G1154" t="n">
-        <v>0.980230212211609</v>
+        <v>0.980230093002319</v>
       </c>
       <c r="H1154" t="s">
         <v>8</v>
@@ -30451,7 +30451,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G1157" t="n">
-        <v>1.02367770671844</v>
+        <v>1.02367758750916</v>
       </c>
       <c r="H1157" t="s">
         <v>8</v>
@@ -30503,7 +30503,7 @@
         <v>1.29499995708466</v>
       </c>
       <c r="G1159" t="n">
-        <v>1.01195621490479</v>
+        <v>1.01195633411407</v>
       </c>
       <c r="H1159" t="s">
         <v>8</v>
@@ -30633,7 +30633,7 @@
         <v>1.23099994659424</v>
       </c>
       <c r="G1164" t="n">
-        <v>0.961944460868835</v>
+        <v>0.961944580078125</v>
       </c>
       <c r="H1164" t="s">
         <v>8</v>
@@ -30737,7 +30737,7 @@
         <v>1.22819995880127</v>
       </c>
       <c r="G1168" t="n">
-        <v>0.95975649356842</v>
+        <v>0.959756553173065</v>
       </c>
       <c r="H1168" t="s">
         <v>8</v>
@@ -30841,7 +30841,7 @@
         <v>1.22060000896454</v>
       </c>
       <c r="G1172" t="n">
-        <v>0.953817665576935</v>
+        <v>0.95381760597229</v>
       </c>
       <c r="H1172" t="s">
         <v>8</v>
@@ -30867,7 +30867,7 @@
         <v>1.22060000896454</v>
       </c>
       <c r="G1173" t="n">
-        <v>0.953817665576935</v>
+        <v>0.95381760597229</v>
       </c>
       <c r="H1173" t="s">
         <v>8</v>
@@ -31023,7 +31023,7 @@
         <v>1.21700000762939</v>
       </c>
       <c r="G1179" t="n">
-        <v>0.951004326343536</v>
+        <v>0.951004385948181</v>
       </c>
       <c r="H1179" t="s">
         <v>8</v>
@@ -31153,7 +31153,7 @@
         <v>1.20860004425049</v>
       </c>
       <c r="G1184" t="n">
-        <v>0.944440484046936</v>
+        <v>0.944440603256226</v>
       </c>
       <c r="H1184" t="s">
         <v>8</v>
@@ -31179,7 +31179,7 @@
         <v>1.20500004291534</v>
       </c>
       <c r="G1185" t="n">
-        <v>0.941627323627472</v>
+        <v>0.941627264022827</v>
       </c>
       <c r="H1185" t="s">
         <v>8</v>
@@ -31205,7 +31205,7 @@
         <v>1.20899999141693</v>
       </c>
       <c r="G1186" t="n">
-        <v>0.944752991199493</v>
+        <v>0.944752931594849</v>
       </c>
       <c r="H1186" t="s">
         <v>8</v>
@@ -31257,7 +31257,7 @@
         <v>1.20019996166229</v>
       </c>
       <c r="G1188" t="n">
-        <v>0.937876462936401</v>
+        <v>0.937876403331757</v>
       </c>
       <c r="H1188" t="s">
         <v>8</v>
@@ -31309,7 +31309,7 @@
         <v>1.26979994773865</v>
       </c>
       <c r="G1190" t="n">
-        <v>0.992264032363892</v>
+        <v>0.992264151573181</v>
       </c>
       <c r="H1190" t="s">
         <v>8</v>
@@ -31335,7 +31335,7 @@
         <v>1.23959994316101</v>
       </c>
       <c r="G1191" t="n">
-        <v>0.968664824962616</v>
+        <v>0.968664765357971</v>
       </c>
       <c r="H1191" t="s">
         <v>8</v>
@@ -31439,7 +31439,7 @@
         <v>1.24279999732971</v>
       </c>
       <c r="G1195" t="n">
-        <v>0.971165359020233</v>
+        <v>0.971165478229523</v>
       </c>
       <c r="H1195" t="s">
         <v>8</v>
@@ -31517,7 +31517,7 @@
         <v>1.23979997634888</v>
       </c>
       <c r="G1198" t="n">
-        <v>0.968821048736572</v>
+        <v>0.968821108341217</v>
       </c>
       <c r="H1198" t="s">
         <v>8</v>
@@ -31543,7 +31543,7 @@
         <v>1.23979997634888</v>
       </c>
       <c r="G1199" t="n">
-        <v>0.968821048736572</v>
+        <v>0.968821108341217</v>
       </c>
       <c r="H1199" t="s">
         <v>8</v>
@@ -31569,7 +31569,7 @@
         <v>1.19120001792908</v>
       </c>
       <c r="G1200" t="n">
-        <v>0.930843412876129</v>
+        <v>0.930843472480774</v>
       </c>
       <c r="H1200" t="s">
         <v>8</v>
@@ -31595,7 +31595,7 @@
         <v>1.19120001792908</v>
       </c>
       <c r="G1201" t="n">
-        <v>0.930843412876129</v>
+        <v>0.930843472480774</v>
       </c>
       <c r="H1201" t="s">
         <v>8</v>
@@ -31621,7 +31621,7 @@
         <v>1.22940003871918</v>
       </c>
       <c r="G1202" t="n">
-        <v>0.960694193840027</v>
+        <v>0.960694253444672</v>
       </c>
       <c r="H1202" t="s">
         <v>8</v>
@@ -31647,7 +31647,7 @@
         <v>1.19140005111694</v>
       </c>
       <c r="G1203" t="n">
-        <v>0.93099981546402</v>
+        <v>0.930999934673309</v>
       </c>
       <c r="H1203" t="s">
         <v>8</v>
@@ -31673,7 +31673,7 @@
         <v>1.22979998588562</v>
       </c>
       <c r="G1204" t="n">
-        <v>0.961006760597229</v>
+        <v>0.961006820201874</v>
       </c>
       <c r="H1204" t="s">
         <v>8</v>
@@ -31725,7 +31725,7 @@
         <v>1.2117999792099</v>
       </c>
       <c r="G1206" t="n">
-        <v>0.946941018104553</v>
+        <v>0.946940958499908</v>
       </c>
       <c r="H1206" t="s">
         <v>8</v>
@@ -31855,7 +31855,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G1211" t="n">
-        <v>0.968977510929108</v>
+        <v>0.968977570533752</v>
       </c>
       <c r="H1211" t="s">
         <v>8</v>
@@ -31933,7 +31933,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G1214" t="n">
-        <v>1.02367770671844</v>
+        <v>1.02367758750916</v>
       </c>
       <c r="H1214" t="s">
         <v>8</v>
@@ -31959,7 +31959,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1215" t="n">
-        <v>0.984605967998505</v>
+        <v>0.984606087207794</v>
       </c>
       <c r="H1215" t="s">
         <v>8</v>
@@ -32037,7 +32037,7 @@
         <v>1.24020004272461</v>
       </c>
       <c r="G1218" t="n">
-        <v>0.969133734703064</v>
+        <v>0.969133675098419</v>
       </c>
       <c r="H1218" t="s">
         <v>8</v>
@@ -32219,7 +32219,7 @@
         <v>1.23039996623993</v>
       </c>
       <c r="G1225" t="n">
-        <v>0.961475670337677</v>
+        <v>0.961475729942322</v>
       </c>
       <c r="H1225" t="s">
         <v>8</v>
@@ -32297,7 +32297,7 @@
         <v>1.17519998550415</v>
       </c>
       <c r="G1228" t="n">
-        <v>0.918340444564819</v>
+        <v>0.918340504169464</v>
       </c>
       <c r="H1228" t="s">
         <v>8</v>
@@ -32323,7 +32323,7 @@
         <v>1.192999958992</v>
       </c>
       <c r="G1229" t="n">
-        <v>0.932249963283539</v>
+        <v>0.932250022888184</v>
       </c>
       <c r="H1229" t="s">
         <v>8</v>
@@ -32427,7 +32427,7 @@
         <v>1.19159996509552</v>
       </c>
       <c r="G1233" t="n">
-        <v>0.931155979633331</v>
+        <v>0.931155920028687</v>
       </c>
       <c r="H1233" t="s">
         <v>8</v>
@@ -32453,7 +32453,7 @@
         <v>1.19099998474121</v>
       </c>
       <c r="G1234" t="n">
-        <v>0.930687129497528</v>
+        <v>0.930687069892883</v>
       </c>
       <c r="H1234" t="s">
         <v>8</v>
@@ -32531,7 +32531,7 @@
         <v>1.23800003528595</v>
       </c>
       <c r="G1237" t="n">
-        <v>0.967414617538452</v>
+        <v>0.967414677143097</v>
       </c>
       <c r="H1237" t="s">
         <v>8</v>
@@ -33025,7 +33025,7 @@
         <v>1.72060000896454</v>
       </c>
       <c r="G1256" t="n">
-        <v>1.34453439712524</v>
+        <v>1.34453427791595</v>
       </c>
       <c r="H1256" t="s">
         <v>8</v>
@@ -33181,7 +33181,7 @@
         <v>1.74119997024536</v>
       </c>
       <c r="G1262" t="n">
-        <v>1.36063182353973</v>
+        <v>1.36063170433044</v>
       </c>
       <c r="H1262" t="s">
         <v>8</v>
@@ -33285,7 +33285,7 @@
         <v>1.72940003871918</v>
       </c>
       <c r="G1266" t="n">
-        <v>1.35141098499298</v>
+        <v>1.35141086578369</v>
       </c>
       <c r="H1266" t="s">
         <v>8</v>
@@ -33389,7 +33389,7 @@
         <v>1.73800003528595</v>
       </c>
       <c r="G1270" t="n">
-        <v>1.45490729808807</v>
+        <v>1.45490717887878</v>
       </c>
       <c r="H1270" t="s">
         <v>8</v>
@@ -33545,7 +33545,7 @@
         <v>1.67279994487762</v>
       </c>
       <c r="G1276" t="n">
-        <v>1.40032708644867</v>
+        <v>1.40032720565796</v>
       </c>
       <c r="H1276" t="s">
         <v>8</v>
@@ -33571,7 +33571,7 @@
         <v>1.68700003623962</v>
       </c>
       <c r="G1277" t="n">
-        <v>1.4122142791748</v>
+        <v>1.41221415996552</v>
       </c>
       <c r="H1277" t="s">
         <v>8</v>
@@ -33623,7 +33623,7 @@
         <v>1.62020003795624</v>
       </c>
       <c r="G1279" t="n">
-        <v>1.35629498958588</v>
+        <v>1.35629487037659</v>
       </c>
       <c r="H1279" t="s">
         <v>8</v>
@@ -33649,7 +33649,7 @@
         <v>1.66600000858307</v>
       </c>
       <c r="G1280" t="n">
-        <v>1.39463496208191</v>
+        <v>1.39463484287262</v>
       </c>
       <c r="H1280" t="s">
         <v>8</v>
@@ -33701,7 +33701,7 @@
         <v>1.62020003795624</v>
       </c>
       <c r="G1282" t="n">
-        <v>1.35629498958588</v>
+        <v>1.35629487037659</v>
       </c>
       <c r="H1282" t="s">
         <v>8</v>
@@ -33727,7 +33727,7 @@
         <v>1.64800000190735</v>
       </c>
       <c r="G1283" t="n">
-        <v>1.37956666946411</v>
+        <v>1.3795667886734</v>
       </c>
       <c r="H1283" t="s">
         <v>8</v>
@@ -33805,7 +33805,7 @@
         <v>1.60060000419617</v>
       </c>
       <c r="G1286" t="n">
-        <v>1.33988749980927</v>
+        <v>1.33988738059998</v>
       </c>
       <c r="H1286" t="s">
         <v>8</v>
@@ -33831,7 +33831,7 @@
         <v>1.6088000535965</v>
       </c>
       <c r="G1287" t="n">
-        <v>1.34675180912018</v>
+        <v>1.34675192832947</v>
       </c>
       <c r="H1287" t="s">
         <v>8</v>
@@ -33883,7 +33883,7 @@
         <v>1.62999999523163</v>
       </c>
       <c r="G1289" t="n">
-        <v>1.36449861526489</v>
+        <v>1.36449873447418</v>
       </c>
       <c r="H1289" t="s">
         <v>8</v>
@@ -33961,7 +33961,7 @@
         <v>1.60599994659424</v>
       </c>
       <c r="G1292" t="n">
-        <v>1.34440779685974</v>
+        <v>1.34440791606903</v>
       </c>
       <c r="H1292" t="s">
         <v>8</v>
@@ -34065,7 +34065,7 @@
         <v>1.71039998531342</v>
       </c>
       <c r="G1296" t="n">
-        <v>1.43180274963379</v>
+        <v>1.4318026304245</v>
       </c>
       <c r="H1296" t="s">
         <v>8</v>
@@ -34117,7 +34117,7 @@
         <v>1.75419998168945</v>
       </c>
       <c r="G1298" t="n">
-        <v>1.46846854686737</v>
+        <v>1.46846842765808</v>
       </c>
       <c r="H1298" t="s">
         <v>8</v>
@@ -34169,7 +34169,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G1300" t="n">
-        <v>1.49006605148315</v>
+        <v>1.49006593227386</v>
       </c>
       <c r="H1300" t="s">
         <v>8</v>
@@ -34221,7 +34221,7 @@
         <v>1.7688000202179</v>
       </c>
       <c r="G1302" t="n">
-        <v>1.48069036006927</v>
+        <v>1.48069024085999</v>
       </c>
       <c r="H1302" t="s">
         <v>8</v>
@@ -34247,7 +34247,7 @@
         <v>1.76760005950928</v>
       </c>
       <c r="G1303" t="n">
-        <v>1.47968590259552</v>
+        <v>1.47968578338623</v>
       </c>
       <c r="H1303" t="s">
         <v>8</v>
@@ -34481,7 +34481,7 @@
         <v>1.88979995250702</v>
       </c>
       <c r="G1312" t="n">
-        <v>1.58198142051697</v>
+        <v>1.58198130130768</v>
       </c>
       <c r="H1312" t="s">
         <v>8</v>
@@ -34533,7 +34533,7 @@
         <v>1.86160004138947</v>
       </c>
       <c r="G1314" t="n">
-        <v>1.5583747625351</v>
+        <v>1.55837464332581</v>
       </c>
       <c r="H1314" t="s">
         <v>8</v>
@@ -34689,7 +34689,7 @@
         <v>1.97780001163483</v>
       </c>
       <c r="G1320" t="n">
-        <v>1.65564739704132</v>
+        <v>1.65564751625061</v>
       </c>
       <c r="H1320" t="s">
         <v>8</v>
@@ -34897,7 +34897,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G1328" t="n">
-        <v>1.64074683189392</v>
+        <v>1.64074695110321</v>
       </c>
       <c r="H1328" t="s">
         <v>8</v>
@@ -34949,7 +34949,7 @@
         <v>1.91499996185303</v>
       </c>
       <c r="G1330" t="n">
-        <v>1.60307669639587</v>
+        <v>1.60307657718658</v>
       </c>
       <c r="H1330" t="s">
         <v>8</v>
@@ -34975,7 +34975,7 @@
         <v>1.91620004177094</v>
       </c>
       <c r="G1331" t="n">
-        <v>1.60408115386963</v>
+        <v>1.60408127307892</v>
       </c>
       <c r="H1331" t="s">
         <v>8</v>
@@ -35105,7 +35105,7 @@
         <v>1.91499996185303</v>
       </c>
       <c r="G1336" t="n">
-        <v>1.60307669639587</v>
+        <v>1.60307657718658</v>
       </c>
       <c r="H1336" t="s">
         <v>8</v>
@@ -35131,7 +35131,7 @@
         <v>1.91499996185303</v>
       </c>
       <c r="G1337" t="n">
-        <v>1.60307669639587</v>
+        <v>1.60307657718658</v>
       </c>
       <c r="H1337" t="s">
         <v>8</v>
@@ -35365,7 +35365,7 @@
         <v>2</v>
       </c>
       <c r="G1346" t="n">
-        <v>1.67423152923584</v>
+        <v>1.67423141002655</v>
       </c>
       <c r="H1346" t="s">
         <v>8</v>
@@ -35417,7 +35417,7 @@
         <v>2</v>
       </c>
       <c r="G1348" t="n">
-        <v>1.67423152923584</v>
+        <v>1.67423141002655</v>
       </c>
       <c r="H1348" t="s">
         <v>8</v>
@@ -35495,7 +35495,7 @@
         <v>1.91499996185303</v>
       </c>
       <c r="G1351" t="n">
-        <v>1.60307669639587</v>
+        <v>1.60307657718658</v>
       </c>
       <c r="H1351" t="s">
         <v>8</v>
@@ -35521,7 +35521,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G1352" t="n">
-        <v>1.59889101982117</v>
+        <v>1.59889113903046</v>
       </c>
       <c r="H1352" t="s">
         <v>8</v>
@@ -35547,7 +35547,7 @@
         <v>1.85500001907349</v>
       </c>
       <c r="G1353" t="n">
-        <v>1.552849650383</v>
+        <v>1.55284976959229</v>
       </c>
       <c r="H1353" t="s">
         <v>8</v>
@@ -35573,7 +35573,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G1354" t="n">
-        <v>1.59051978588104</v>
+        <v>1.59051990509033</v>
       </c>
       <c r="H1354" t="s">
         <v>8</v>
@@ -35729,7 +35729,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G1360" t="n">
-        <v>1.59051978588104</v>
+        <v>1.59051990509033</v>
       </c>
       <c r="H1360" t="s">
         <v>8</v>
@@ -35781,7 +35781,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G1362" t="n">
-        <v>1.59051978588104</v>
+        <v>1.59051990509033</v>
       </c>
       <c r="H1362" t="s">
         <v>8</v>
@@ -35807,7 +35807,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G1363" t="n">
-        <v>1.58214867115021</v>
+        <v>1.5821487903595</v>
       </c>
       <c r="H1363" t="s">
         <v>8</v>
@@ -35833,7 +35833,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G1364" t="n">
-        <v>1.59051978588104</v>
+        <v>1.59051990509033</v>
       </c>
       <c r="H1364" t="s">
         <v>8</v>
@@ -35859,7 +35859,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G1365" t="n">
-        <v>1.59051978588104</v>
+        <v>1.59051990509033</v>
       </c>
       <c r="H1365" t="s">
         <v>8</v>
@@ -35885,7 +35885,7 @@
         <v>1.85500001907349</v>
       </c>
       <c r="G1366" t="n">
-        <v>1.552849650383</v>
+        <v>1.55284976959229</v>
       </c>
       <c r="H1366" t="s">
         <v>8</v>
@@ -35911,7 +35911,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G1367" t="n">
-        <v>1.54029297828674</v>
+        <v>1.54029309749603</v>
       </c>
       <c r="H1367" t="s">
         <v>8</v>
@@ -35937,7 +35937,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G1368" t="n">
-        <v>1.59051978588104</v>
+        <v>1.59051990509033</v>
       </c>
       <c r="H1368" t="s">
         <v>8</v>
@@ -36041,7 +36041,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G1372" t="n">
-        <v>1.54029297828674</v>
+        <v>1.54029309749603</v>
       </c>
       <c r="H1372" t="s">
         <v>8</v>
@@ -36197,7 +36197,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G1378" t="n">
-        <v>1.82491230964661</v>
+        <v>1.8249124288559</v>
       </c>
       <c r="H1378" t="s">
         <v>8</v>
@@ -36223,7 +36223,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G1379" t="n">
-        <v>1.89188170433044</v>
+        <v>1.89188158512115</v>
       </c>
       <c r="H1379" t="s">
         <v>8</v>
@@ -36249,7 +36249,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1380" t="n">
-        <v>1.80817008018494</v>
+        <v>1.80817019939423</v>
       </c>
       <c r="H1380" t="s">
         <v>8</v>
@@ -36457,7 +36457,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G1388" t="n">
-        <v>1.81654119491577</v>
+        <v>1.81654131412506</v>
       </c>
       <c r="H1388" t="s">
         <v>8</v>
@@ -36509,7 +36509,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G1390" t="n">
-        <v>1.82491230964661</v>
+        <v>1.8249124288559</v>
       </c>
       <c r="H1390" t="s">
         <v>8</v>
@@ -36535,7 +36535,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1391" t="n">
-        <v>1.80817008018494</v>
+        <v>1.80817019939423</v>
       </c>
       <c r="H1391" t="s">
         <v>8</v>
@@ -36587,7 +36587,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1393" t="n">
-        <v>1.80817008018494</v>
+        <v>1.80817019939423</v>
       </c>
       <c r="H1393" t="s">
         <v>8</v>
@@ -36821,7 +36821,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G1402" t="n">
-        <v>1.7160872220993</v>
+        <v>1.71608710289001</v>
       </c>
       <c r="H1402" t="s">
         <v>8</v>
@@ -36847,7 +36847,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G1403" t="n">
-        <v>1.73282957077026</v>
+        <v>1.73282945156097</v>
       </c>
       <c r="H1403" t="s">
         <v>8</v>
@@ -36925,7 +36925,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G1406" t="n">
-        <v>1.72445845603943</v>
+        <v>1.72445833683014</v>
       </c>
       <c r="H1406" t="s">
         <v>8</v>
@@ -36951,7 +36951,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G1407" t="n">
-        <v>1.7160872220993</v>
+        <v>1.71608710289001</v>
       </c>
       <c r="H1407" t="s">
         <v>8</v>
@@ -37081,7 +37081,7 @@
         <v>1.98500001430511</v>
       </c>
       <c r="G1412" t="n">
-        <v>1.66167485713959</v>
+        <v>1.6616747379303</v>
       </c>
       <c r="H1412" t="s">
         <v>8</v>
@@ -37107,7 +37107,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G1413" t="n">
-        <v>1.72445845603943</v>
+        <v>1.72445833683014</v>
       </c>
       <c r="H1413" t="s">
         <v>8</v>
@@ -37237,7 +37237,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G1418" t="n">
-        <v>1.72445845603943</v>
+        <v>1.72445833683014</v>
       </c>
       <c r="H1418" t="s">
         <v>8</v>
@@ -37289,7 +37289,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G1420" t="n">
-        <v>1.73282957077026</v>
+        <v>1.73282945156097</v>
       </c>
       <c r="H1420" t="s">
         <v>8</v>
@@ -37315,7 +37315,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1421" t="n">
-        <v>1.80817008018494</v>
+        <v>1.80817019939423</v>
       </c>
       <c r="H1421" t="s">
         <v>8</v>
@@ -37341,7 +37341,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G1422" t="n">
-        <v>1.79979884624481</v>
+        <v>1.7997989654541</v>
       </c>
       <c r="H1422" t="s">
         <v>8</v>
@@ -37367,7 +37367,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G1423" t="n">
-        <v>1.81654119491577</v>
+        <v>1.81654131412506</v>
       </c>
       <c r="H1423" t="s">
         <v>8</v>
@@ -37393,7 +37393,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G1424" t="n">
-        <v>1.81654119491577</v>
+        <v>1.81654131412506</v>
       </c>
       <c r="H1424" t="s">
         <v>8</v>
@@ -37419,7 +37419,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G1425" t="n">
-        <v>1.81654119491577</v>
+        <v>1.81654131412506</v>
       </c>
       <c r="H1425" t="s">
         <v>8</v>
@@ -37653,7 +37653,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G1434" t="n">
-        <v>1.81654119491577</v>
+        <v>1.81654131412506</v>
       </c>
       <c r="H1434" t="s">
         <v>8</v>
@@ -37757,7 +37757,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G1438" t="n">
-        <v>1.82491230964661</v>
+        <v>1.8249124288559</v>
       </c>
       <c r="H1438" t="s">
         <v>8</v>
@@ -37783,7 +37783,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G1439" t="n">
-        <v>1.79979884624481</v>
+        <v>1.7997989654541</v>
       </c>
       <c r="H1439" t="s">
         <v>8</v>
@@ -37809,7 +37809,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G1440" t="n">
-        <v>1.81654119491577</v>
+        <v>1.81654131412506</v>
       </c>
       <c r="H1440" t="s">
         <v>8</v>
@@ -37835,7 +37835,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G1441" t="n">
-        <v>1.82491230964661</v>
+        <v>1.8249124288559</v>
       </c>
       <c r="H1441" t="s">
         <v>8</v>
@@ -37861,7 +37861,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1442" t="n">
-        <v>1.80817008018494</v>
+        <v>1.80817019939423</v>
       </c>
       <c r="H1442" t="s">
         <v>8</v>
@@ -37939,7 +37939,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G1445" t="n">
-        <v>1.79979884624481</v>
+        <v>1.7997989654541</v>
       </c>
       <c r="H1445" t="s">
         <v>8</v>
@@ -37965,7 +37965,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G1446" t="n">
-        <v>1.79979884624481</v>
+        <v>1.7997989654541</v>
       </c>
       <c r="H1446" t="s">
         <v>8</v>
@@ -38043,7 +38043,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G1449" t="n">
-        <v>1.79979884624481</v>
+        <v>1.7997989654541</v>
       </c>
       <c r="H1449" t="s">
         <v>8</v>
@@ -38095,7 +38095,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G1451" t="n">
-        <v>1.79979884624481</v>
+        <v>1.7997989654541</v>
       </c>
       <c r="H1451" t="s">
         <v>8</v>
@@ -38121,7 +38121,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G1452" t="n">
-        <v>1.79979884624481</v>
+        <v>1.7997989654541</v>
       </c>
       <c r="H1452" t="s">
         <v>8</v>
@@ -38277,7 +38277,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G1458" t="n">
-        <v>1.86676812171936</v>
+        <v>1.86676824092865</v>
       </c>
       <c r="H1458" t="s">
         <v>8</v>
@@ -38615,7 +38615,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G1471" t="n">
-        <v>2.04256248474121</v>
+        <v>2.04256224632263</v>
       </c>
       <c r="H1471" t="s">
         <v>8</v>
@@ -38667,7 +38667,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G1473" t="n">
-        <v>2.13464498519897</v>
+        <v>2.13464522361755</v>
       </c>
       <c r="H1473" t="s">
         <v>8</v>
@@ -39135,7 +39135,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G1491" t="n">
-        <v>2.13464498519897</v>
+        <v>2.13464522361755</v>
       </c>
       <c r="H1491" t="s">
         <v>8</v>
@@ -39161,7 +39161,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G1492" t="n">
-        <v>2.15138721466064</v>
+        <v>2.15138745307922</v>
       </c>
       <c r="H1492" t="s">
         <v>8</v>
@@ -39213,7 +39213,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G1494" t="n">
-        <v>2.2518413066864</v>
+        <v>2.25184154510498</v>
       </c>
       <c r="H1494" t="s">
         <v>8</v>
@@ -39265,7 +39265,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G1496" t="n">
-        <v>2.23509883880615</v>
+        <v>2.23509907722473</v>
       </c>
       <c r="H1496" t="s">
         <v>8</v>
@@ -39291,7 +39291,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G1497" t="n">
-        <v>2.23509883880615</v>
+        <v>2.23509907722473</v>
       </c>
       <c r="H1497" t="s">
         <v>8</v>
@@ -39317,7 +39317,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G1498" t="n">
-        <v>2.21835660934448</v>
+        <v>2.21835684776306</v>
       </c>
       <c r="H1498" t="s">
         <v>8</v>
@@ -39343,7 +39343,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G1499" t="n">
-        <v>2.21835660934448</v>
+        <v>2.21835684776306</v>
       </c>
       <c r="H1499" t="s">
         <v>8</v>
@@ -39395,7 +39395,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G1501" t="n">
-        <v>2.2518413066864</v>
+        <v>2.25184154510498</v>
       </c>
       <c r="H1501" t="s">
         <v>8</v>
@@ -39447,7 +39447,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G1503" t="n">
-        <v>2.2518413066864</v>
+        <v>2.25184154510498</v>
       </c>
       <c r="H1503" t="s">
         <v>8</v>
@@ -39499,7 +39499,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G1505" t="n">
-        <v>2.21835660934448</v>
+        <v>2.21835684776306</v>
       </c>
       <c r="H1505" t="s">
         <v>8</v>
@@ -39525,7 +39525,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G1506" t="n">
-        <v>2.26858353614807</v>
+        <v>2.26858377456665</v>
       </c>
       <c r="H1506" t="s">
         <v>8</v>
@@ -39551,7 +39551,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G1507" t="n">
-        <v>2.26858353614807</v>
+        <v>2.26858377456665</v>
       </c>
       <c r="H1507" t="s">
         <v>8</v>
@@ -39603,7 +39603,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G1509" t="n">
-        <v>2.26858353614807</v>
+        <v>2.26858377456665</v>
       </c>
       <c r="H1509" t="s">
         <v>8</v>
@@ -39655,7 +39655,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G1511" t="n">
-        <v>2.21835660934448</v>
+        <v>2.21835684776306</v>
       </c>
       <c r="H1511" t="s">
         <v>8</v>
@@ -39681,7 +39681,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G1512" t="n">
-        <v>2.2518413066864</v>
+        <v>2.25184154510498</v>
       </c>
       <c r="H1512" t="s">
         <v>8</v>
@@ -39707,7 +39707,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G1513" t="n">
-        <v>2.2518413066864</v>
+        <v>2.25184154510498</v>
       </c>
       <c r="H1513" t="s">
         <v>8</v>
@@ -39733,7 +39733,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G1514" t="n">
-        <v>2.26858353614807</v>
+        <v>2.26858377456665</v>
       </c>
       <c r="H1514" t="s">
         <v>8</v>
@@ -39759,7 +39759,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G1515" t="n">
-        <v>2.26858353614807</v>
+        <v>2.26858377456665</v>
       </c>
       <c r="H1515" t="s">
         <v>8</v>
@@ -39811,7 +39811,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G1517" t="n">
-        <v>2.54483199119568</v>
+        <v>2.5448317527771</v>
       </c>
       <c r="H1517" t="s">
         <v>8</v>
@@ -39889,7 +39889,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G1520" t="n">
-        <v>2.67039918899536</v>
+        <v>2.67039942741394</v>
       </c>
       <c r="H1520" t="s">
         <v>8</v>
@@ -39967,7 +39967,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G1523" t="n">
-        <v>2.75411105155945</v>
+        <v>2.75411081314087</v>
       </c>
       <c r="H1523" t="s">
         <v>8</v>
@@ -40045,7 +40045,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G1526" t="n">
-        <v>3.20615339279175</v>
+        <v>3.20615315437317</v>
       </c>
       <c r="H1526" t="s">
         <v>8</v>
@@ -40071,7 +40071,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G1527" t="n">
-        <v>3.10569930076599</v>
+        <v>3.10569953918457</v>
       </c>
       <c r="H1527" t="s">
         <v>8</v>
@@ -40097,7 +40097,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G1528" t="n">
-        <v>2.99687433242798</v>
+        <v>2.9968740940094</v>
       </c>
       <c r="H1528" t="s">
         <v>8</v>
@@ -40123,7 +40123,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G1529" t="n">
-        <v>3.0303590297699</v>
+        <v>3.03035879135132</v>
       </c>
       <c r="H1529" t="s">
         <v>8</v>
@@ -40149,7 +40149,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1530" t="n">
-        <v>3.01361680030823</v>
+        <v>3.01361656188965</v>
       </c>
       <c r="H1530" t="s">
         <v>8</v>
@@ -40175,7 +40175,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G1531" t="n">
-        <v>2.99687433242798</v>
+        <v>2.9968740940094</v>
       </c>
       <c r="H1531" t="s">
         <v>8</v>
@@ -40357,7 +40357,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1538" t="n">
-        <v>2.84619331359863</v>
+        <v>2.84619355201721</v>
       </c>
       <c r="H1538" t="s">
         <v>8</v>
@@ -40513,7 +40513,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G1544" t="n">
-        <v>2.97176098823547</v>
+        <v>2.97176074981689</v>
       </c>
       <c r="H1544" t="s">
         <v>8</v>
@@ -71690,6 +71690,32 @@
         <v>0.400000005960464</v>
       </c>
       <c r="H2743" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2744">
+      <c r="A2744" s="1" t="n">
+        <v>46311.2916666667</v>
+      </c>
+      <c r="B2744" t="n">
+        <v>1100</v>
+      </c>
+      <c r="C2744" t="n">
+        <v>0.412000000476837</v>
+      </c>
+      <c r="D2744" t="n">
+        <v>0.412000000476837</v>
+      </c>
+      <c r="E2744" t="n">
+        <v>0.412000000476837</v>
+      </c>
+      <c r="F2744" t="n">
+        <v>0.412000000476837</v>
+      </c>
+      <c r="G2744" t="n">
+        <v>0.412000000476837</v>
+      </c>
+      <c r="H2744" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/ZUC.MI.xlsx
+++ b/data/ZUC.MI.xlsx
@@ -485,7 +485,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G4" t="n">
-        <v>2.96163249015808</v>
+        <v>2.96163272857666</v>
       </c>
       <c r="H4" t="n">
         <v>12680</v>
@@ -514,7 +514,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G5" t="n">
-        <v>2.8522322177887</v>
+        <v>2.85223197937012</v>
       </c>
       <c r="H5" t="n">
         <v>41852</v>
@@ -601,7 +601,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G8" t="n">
-        <v>2.8522322177887</v>
+        <v>2.85223197937012</v>
       </c>
       <c r="H8" t="n">
         <v>11271</v>
@@ -630,7 +630,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G9" t="n">
-        <v>2.8522322177887</v>
+        <v>2.85223197937012</v>
       </c>
       <c r="H9" t="n">
         <v>22577</v>
@@ -659,7 +659,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G10" t="n">
-        <v>2.8913037776947</v>
+        <v>2.89130353927612</v>
       </c>
       <c r="H10" t="n">
         <v>21901</v>
@@ -688,7 +688,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G11" t="n">
-        <v>2.77408862113953</v>
+        <v>2.77408838272095</v>
       </c>
       <c r="H11" t="n">
         <v>14530</v>
@@ -717,7 +717,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G12" t="n">
-        <v>2.6256160736084</v>
+        <v>2.62561631202698</v>
       </c>
       <c r="H12" t="n">
         <v>16207</v>
@@ -746,7 +746,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G13" t="n">
-        <v>2.50840139389038</v>
+        <v>2.5084011554718</v>
       </c>
       <c r="H13" t="n">
         <v>22831</v>
@@ -804,7 +804,7 @@
         <v>3</v>
       </c>
       <c r="G15" t="n">
-        <v>2.34430003166199</v>
+        <v>2.34430027008057</v>
       </c>
       <c r="H15" t="n">
         <v>26367</v>
@@ -862,7 +862,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G17" t="n">
-        <v>2.41462922096252</v>
+        <v>2.41462898254395</v>
       </c>
       <c r="H17" t="n">
         <v>14217</v>
@@ -891,7 +891,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G18" t="n">
-        <v>2.41462922096252</v>
+        <v>2.41462898254395</v>
       </c>
       <c r="H18" t="n">
         <v>18543</v>
@@ -920,7 +920,7 @@
         <v>3</v>
       </c>
       <c r="G19" t="n">
-        <v>2.34430003166199</v>
+        <v>2.34430027008057</v>
       </c>
       <c r="H19" t="n">
         <v>7546</v>
@@ -949,7 +949,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G20" t="n">
-        <v>2.29741430282593</v>
+        <v>2.29741406440735</v>
       </c>
       <c r="H20" t="n">
         <v>9023</v>
@@ -978,7 +978,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G21" t="n">
-        <v>2.32867169380188</v>
+        <v>2.3286714553833</v>
       </c>
       <c r="H21" t="n">
         <v>6070</v>
@@ -1007,7 +1007,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G22" t="n">
-        <v>2.30522847175598</v>
+        <v>2.30522871017456</v>
       </c>
       <c r="H22" t="n">
         <v>7688</v>
@@ -1036,7 +1036,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G23" t="n">
-        <v>2.29741430282593</v>
+        <v>2.29741406440735</v>
       </c>
       <c r="H23" t="n">
         <v>6069</v>
@@ -1094,7 +1094,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G25" t="n">
-        <v>1.7894823551178</v>
+        <v>1.78948259353638</v>
       </c>
       <c r="H25" t="n">
         <v>29015</v>
@@ -1123,7 +1123,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G26" t="n">
-        <v>1.44565188884735</v>
+        <v>1.44565176963806</v>
       </c>
       <c r="H26" t="n">
         <v>34743</v>
@@ -1210,7 +1210,7 @@
         <v>1</v>
       </c>
       <c r="G29" t="n">
-        <v>0.781433463096619</v>
+        <v>0.781433403491974</v>
       </c>
       <c r="H29" t="n">
         <v>16056</v>
@@ -1239,7 +1239,7 @@
         <v>1.5</v>
       </c>
       <c r="G30" t="n">
-        <v>1.17215001583099</v>
+        <v>1.17215013504028</v>
       </c>
       <c r="H30" t="n">
         <v>11792</v>
@@ -1268,7 +1268,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G31" t="n">
-        <v>1.71915364265442</v>
+        <v>1.71915352344513</v>
       </c>
       <c r="H31" t="n">
         <v>23390</v>
@@ -1355,7 +1355,7 @@
         <v>3</v>
       </c>
       <c r="G34" t="n">
-        <v>2.34430003166199</v>
+        <v>2.34430027008057</v>
       </c>
       <c r="H34" t="n">
         <v>65915</v>
@@ -1413,7 +1413,7 @@
         <v>3</v>
       </c>
       <c r="G36" t="n">
-        <v>2.34430003166199</v>
+        <v>2.34430027008057</v>
       </c>
       <c r="H36" t="n">
         <v>20892</v>
@@ -1442,7 +1442,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G37" t="n">
-        <v>2.7115740776062</v>
+        <v>2.71157383918762</v>
       </c>
       <c r="H37" t="n">
         <v>25045</v>
@@ -1500,7 +1500,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G39" t="n">
-        <v>2.4458863735199</v>
+        <v>2.44588661193848</v>
       </c>
       <c r="H39" t="n">
         <v>23320</v>
@@ -1558,7 +1558,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G41" t="n">
-        <v>2.51621580123901</v>
+        <v>2.51621556282043</v>
       </c>
       <c r="H41" t="n">
         <v>12434</v>
@@ -1587,7 +1587,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G42" t="n">
-        <v>2.45370101928711</v>
+        <v>2.45370078086853</v>
       </c>
       <c r="H42" t="n">
         <v>6497</v>
@@ -1616,7 +1616,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G43" t="n">
-        <v>2.43025779724121</v>
+        <v>2.43025803565979</v>
       </c>
       <c r="H43" t="n">
         <v>31886</v>
@@ -1645,7 +1645,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G44" t="n">
-        <v>2.4849579334259</v>
+        <v>2.48495841026306</v>
       </c>
       <c r="H44" t="n">
         <v>10570</v>
@@ -1674,7 +1674,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G45" t="n">
-        <v>2.77408862113953</v>
+        <v>2.77408838272095</v>
       </c>
       <c r="H45" t="n">
         <v>276654</v>
@@ -1790,7 +1790,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G49" t="n">
-        <v>2.57091569900513</v>
+        <v>2.57091593742371</v>
       </c>
       <c r="H49" t="n">
         <v>6727</v>
@@ -1935,7 +1935,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G54" t="n">
-        <v>2.43025779724121</v>
+        <v>2.43025803565979</v>
       </c>
       <c r="H54" t="n">
         <v>6029</v>
@@ -1993,7 +1993,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G56" t="n">
-        <v>2.41462922096252</v>
+        <v>2.41462898254395</v>
       </c>
       <c r="H56" t="n">
         <v>6905</v>
@@ -2051,7 +2051,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G58" t="n">
-        <v>2.27397108078003</v>
+        <v>2.27397131919861</v>
       </c>
       <c r="H58" t="n">
         <v>5139</v>
@@ -2138,7 +2138,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G61" t="n">
-        <v>2.08642721176147</v>
+        <v>2.08642745018005</v>
       </c>
       <c r="H61" t="n">
         <v>24791</v>
@@ -2167,7 +2167,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G62" t="n">
-        <v>2.0551700592041</v>
+        <v>2.05516982078552</v>
       </c>
       <c r="H62" t="n">
         <v>7073</v>
@@ -2254,7 +2254,7 @@
         <v>2.5</v>
       </c>
       <c r="G65" t="n">
-        <v>1.9535835981369</v>
+        <v>1.95358347892761</v>
       </c>
       <c r="H65" t="n">
         <v>4420</v>
@@ -2283,7 +2283,7 @@
         <v>2.5</v>
       </c>
       <c r="G66" t="n">
-        <v>1.9535835981369</v>
+        <v>1.95358347892761</v>
       </c>
       <c r="H66" t="n">
         <v>8536</v>
@@ -2312,7 +2312,7 @@
         <v>2.5</v>
       </c>
       <c r="G67" t="n">
-        <v>1.9535835981369</v>
+        <v>1.95358347892761</v>
       </c>
       <c r="H67" t="n">
         <v>400</v>
@@ -2399,7 +2399,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G70" t="n">
-        <v>1.82073986530304</v>
+        <v>1.82073962688446</v>
       </c>
       <c r="H70" t="n">
         <v>19067</v>
@@ -2428,7 +2428,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G71" t="n">
-        <v>1.81292545795441</v>
+        <v>1.81292533874512</v>
       </c>
       <c r="H71" t="n">
         <v>7528</v>
@@ -2515,7 +2515,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G74" t="n">
-        <v>1.91451215744019</v>
+        <v>1.9145120382309</v>
       </c>
       <c r="H74" t="n">
         <v>27553</v>
@@ -2544,7 +2544,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G75" t="n">
-        <v>1.84418296813965</v>
+        <v>1.84418284893036</v>
       </c>
       <c r="H75" t="n">
         <v>12321</v>
@@ -2573,7 +2573,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G76" t="n">
-        <v>1.87544023990631</v>
+        <v>1.8754403591156</v>
       </c>
       <c r="H76" t="n">
         <v>16625</v>
@@ -2660,7 +2660,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G79" t="n">
-        <v>1.75041091442108</v>
+        <v>1.7504106760025</v>
       </c>
       <c r="H79" t="n">
         <v>18881</v>
@@ -2689,7 +2689,7 @@
         <v>2.25</v>
       </c>
       <c r="G80" t="n">
-        <v>1.75822508335114</v>
+        <v>1.75822532176971</v>
       </c>
       <c r="H80" t="n">
         <v>4825</v>
@@ -2718,7 +2718,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G81" t="n">
-        <v>1.75041091442108</v>
+        <v>1.7504106760025</v>
       </c>
       <c r="H81" t="n">
         <v>11995</v>
@@ -2863,7 +2863,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G86" t="n">
-        <v>1.78166806697845</v>
+        <v>1.78166818618774</v>
       </c>
       <c r="H86" t="n">
         <v>2070</v>
@@ -2892,7 +2892,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G87" t="n">
-        <v>1.73478221893311</v>
+        <v>1.73478209972382</v>
       </c>
       <c r="H87" t="n">
         <v>11269</v>
@@ -2921,7 +2921,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G88" t="n">
-        <v>1.73478221893311</v>
+        <v>1.73478209972382</v>
       </c>
       <c r="H88" t="n">
         <v>9381</v>
@@ -2950,7 +2950,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G89" t="n">
-        <v>1.7894823551178</v>
+        <v>1.78948259353638</v>
       </c>
       <c r="H89" t="n">
         <v>13120</v>
@@ -2979,7 +2979,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G90" t="n">
-        <v>1.70352482795715</v>
+        <v>1.70352494716644</v>
       </c>
       <c r="H90" t="n">
         <v>5489</v>
@@ -3008,7 +3008,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G91" t="n">
-        <v>1.71915364265442</v>
+        <v>1.71915352344513</v>
       </c>
       <c r="H91" t="n">
         <v>12134</v>
@@ -3066,7 +3066,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G93" t="n">
-        <v>1.70352482795715</v>
+        <v>1.70352494716644</v>
       </c>
       <c r="H93" t="n">
         <v>5250</v>
@@ -3095,7 +3095,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G94" t="n">
-        <v>1.69571042060852</v>
+        <v>1.6957106590271</v>
       </c>
       <c r="H94" t="n">
         <v>7592</v>
@@ -3124,7 +3124,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G95" t="n">
-        <v>1.71915364265442</v>
+        <v>1.71915352344513</v>
       </c>
       <c r="H95" t="n">
         <v>1431</v>
@@ -3153,7 +3153,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G96" t="n">
-        <v>1.64882445335388</v>
+        <v>1.64882433414459</v>
       </c>
       <c r="H96" t="n">
         <v>2615</v>
@@ -3182,7 +3182,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G97" t="n">
-        <v>1.71915364265442</v>
+        <v>1.71915352344513</v>
       </c>
       <c r="H97" t="n">
         <v>10382</v>
@@ -3269,7 +3269,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G100" t="n">
-        <v>2.08642721176147</v>
+        <v>2.08642745018005</v>
       </c>
       <c r="H100" t="n">
         <v>131201</v>
@@ -3385,7 +3385,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G104" t="n">
-        <v>1.93795478343964</v>
+        <v>1.93795502185822</v>
       </c>
       <c r="H104" t="n">
         <v>28640</v>
@@ -3443,7 +3443,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G106" t="n">
-        <v>1.82855403423309</v>
+        <v>1.8285539150238</v>
       </c>
       <c r="H106" t="n">
         <v>48556</v>
@@ -3472,7 +3472,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G107" t="n">
-        <v>1.74259662628174</v>
+        <v>1.74259638786316</v>
       </c>
       <c r="H107" t="n">
         <v>29505</v>
@@ -3501,7 +3501,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G108" t="n">
-        <v>1.71915364265442</v>
+        <v>1.71915352344513</v>
       </c>
       <c r="H108" t="n">
         <v>19258</v>
@@ -3559,7 +3559,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G110" t="n">
-        <v>1.71915364265442</v>
+        <v>1.71915352344513</v>
       </c>
       <c r="H110" t="n">
         <v>31434</v>
@@ -3588,7 +3588,7 @@
         <v>2.25</v>
       </c>
       <c r="G111" t="n">
-        <v>1.75822508335114</v>
+        <v>1.75822532176971</v>
       </c>
       <c r="H111" t="n">
         <v>12997</v>
@@ -3617,7 +3617,7 @@
         <v>2.25</v>
       </c>
       <c r="G112" t="n">
-        <v>1.75822508335114</v>
+        <v>1.75822532176971</v>
       </c>
       <c r="H112" t="n">
         <v>6892</v>
@@ -3646,7 +3646,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G113" t="n">
-        <v>1.69571042060852</v>
+        <v>1.6957106590271</v>
       </c>
       <c r="H113" t="n">
         <v>7676</v>
@@ -3675,7 +3675,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G114" t="n">
-        <v>1.64882445335388</v>
+        <v>1.64882433414459</v>
       </c>
       <c r="H114" t="n">
         <v>16400</v>
@@ -3791,7 +3791,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G118" t="n">
-        <v>1.54723811149597</v>
+        <v>1.54723823070526</v>
       </c>
       <c r="H118" t="n">
         <v>2966</v>
@@ -3849,7 +3849,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G120" t="n">
-        <v>1.57849538326263</v>
+        <v>1.57849550247192</v>
       </c>
       <c r="H120" t="n">
         <v>26546</v>
@@ -3878,7 +3878,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G121" t="n">
-        <v>1.57849538326263</v>
+        <v>1.57849550247192</v>
       </c>
       <c r="H121" t="n">
         <v>5793</v>
@@ -3907,7 +3907,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G122" t="n">
-        <v>1.57849538326263</v>
+        <v>1.57849550247192</v>
       </c>
       <c r="H122" t="n">
         <v>255</v>
@@ -3936,7 +3936,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G123" t="n">
-        <v>1.57849538326263</v>
+        <v>1.57849550247192</v>
       </c>
       <c r="H123" t="n">
         <v>12438</v>
@@ -3965,7 +3965,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G124" t="n">
-        <v>1.46909487247467</v>
+        <v>1.46909475326538</v>
       </c>
       <c r="H124" t="n">
         <v>33327</v>
@@ -4023,7 +4023,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G126" t="n">
-        <v>1.44565188884735</v>
+        <v>1.44565176963806</v>
       </c>
       <c r="H126" t="n">
         <v>4514</v>
@@ -4052,7 +4052,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G127" t="n">
-        <v>1.44565188884735</v>
+        <v>1.44565176963806</v>
       </c>
       <c r="H127" t="n">
         <v>0</v>
@@ -4139,7 +4139,7 @@
         <v>2.25</v>
       </c>
       <c r="G130" t="n">
-        <v>1.75822508335114</v>
+        <v>1.75822532176971</v>
       </c>
       <c r="H130" t="n">
         <v>83797</v>
@@ -4255,7 +4255,7 @@
         <v>1.75</v>
       </c>
       <c r="G134" t="n">
-        <v>1.36750841140747</v>
+        <v>1.36750853061676</v>
       </c>
       <c r="H134" t="n">
         <v>31791</v>
@@ -4313,7 +4313,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G136" t="n">
-        <v>1.4143944978714</v>
+        <v>1.41439437866211</v>
       </c>
       <c r="H136" t="n">
         <v>17202</v>
@@ -4371,7 +4371,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G138" t="n">
-        <v>1.4143944978714</v>
+        <v>1.41439437866211</v>
       </c>
       <c r="H138" t="n">
         <v>9467</v>
@@ -4429,7 +4429,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G140" t="n">
-        <v>1.4143944978714</v>
+        <v>1.41439437866211</v>
       </c>
       <c r="H140" t="n">
         <v>22023</v>
@@ -4458,7 +4458,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G141" t="n">
-        <v>1.47690904140472</v>
+        <v>1.47690916061401</v>
       </c>
       <c r="H141" t="n">
         <v>16351</v>
@@ -4487,7 +4487,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G142" t="n">
-        <v>1.46909487247467</v>
+        <v>1.46909475326538</v>
       </c>
       <c r="H142" t="n">
         <v>23001</v>
@@ -4574,7 +4574,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G145" t="n">
-        <v>1.4534660577774</v>
+        <v>1.45346617698669</v>
       </c>
       <c r="H145" t="n">
         <v>20080</v>
@@ -4603,7 +4603,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G146" t="n">
-        <v>1.43002307415009</v>
+        <v>1.43002319335938</v>
       </c>
       <c r="H146" t="n">
         <v>5668</v>
@@ -4632,7 +4632,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G147" t="n">
-        <v>1.44565188884735</v>
+        <v>1.44565176963806</v>
       </c>
       <c r="H147" t="n">
         <v>3897</v>
@@ -4661,7 +4661,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G148" t="n">
-        <v>1.43002307415009</v>
+        <v>1.43002319335938</v>
       </c>
       <c r="H148" t="n">
         <v>3047</v>
@@ -4719,7 +4719,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G150" t="n">
-        <v>1.43002307415009</v>
+        <v>1.43002319335938</v>
       </c>
       <c r="H150" t="n">
         <v>3668</v>
@@ -4748,7 +4748,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G151" t="n">
-        <v>1.43002307415009</v>
+        <v>1.43002319335938</v>
       </c>
       <c r="H151" t="n">
         <v>20454</v>
@@ -4777,7 +4777,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G152" t="n">
-        <v>1.44565188884735</v>
+        <v>1.44565176963806</v>
       </c>
       <c r="H152" t="n">
         <v>3895</v>
@@ -4835,7 +4835,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G154" t="n">
-        <v>1.46909487247467</v>
+        <v>1.46909475326538</v>
       </c>
       <c r="H154" t="n">
         <v>6731</v>
@@ -4864,7 +4864,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G155" t="n">
-        <v>1.50035214424133</v>
+        <v>1.50035226345062</v>
       </c>
       <c r="H155" t="n">
         <v>11333</v>
@@ -4951,7 +4951,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G158" t="n">
-        <v>1.50035214424133</v>
+        <v>1.50035226345062</v>
       </c>
       <c r="H158" t="n">
         <v>230</v>
@@ -5038,7 +5038,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G161" t="n">
-        <v>1.47690904140472</v>
+        <v>1.47690916061401</v>
       </c>
       <c r="H161" t="n">
         <v>4796</v>
@@ -5096,7 +5096,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G163" t="n">
-        <v>1.46909487247467</v>
+        <v>1.46909475326538</v>
       </c>
       <c r="H163" t="n">
         <v>3375</v>
@@ -5125,7 +5125,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G164" t="n">
-        <v>1.44565188884735</v>
+        <v>1.44565176963806</v>
       </c>
       <c r="H164" t="n">
         <v>2612</v>
@@ -5154,7 +5154,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G165" t="n">
-        <v>1.4534660577774</v>
+        <v>1.45346617698669</v>
       </c>
       <c r="H165" t="n">
         <v>815</v>
@@ -5183,7 +5183,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G166" t="n">
-        <v>1.46909487247467</v>
+        <v>1.46909475326538</v>
       </c>
       <c r="H166" t="n">
         <v>3815</v>
@@ -5212,7 +5212,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G167" t="n">
-        <v>1.46909487247467</v>
+        <v>1.46909475326538</v>
       </c>
       <c r="H167" t="n">
         <v>100</v>
@@ -5241,7 +5241,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G168" t="n">
-        <v>1.46909487247467</v>
+        <v>1.46909475326538</v>
       </c>
       <c r="H168" t="n">
         <v>600</v>
@@ -5270,7 +5270,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G169" t="n">
-        <v>1.47690904140472</v>
+        <v>1.47690916061401</v>
       </c>
       <c r="H169" t="n">
         <v>12338</v>
@@ -5328,7 +5328,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G171" t="n">
-        <v>1.47690904140472</v>
+        <v>1.47690916061401</v>
       </c>
       <c r="H171" t="n">
         <v>7601</v>
@@ -5357,7 +5357,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G172" t="n">
-        <v>1.47690904140472</v>
+        <v>1.47690916061401</v>
       </c>
       <c r="H172" t="n">
         <v>2406</v>
@@ -5415,7 +5415,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G174" t="n">
-        <v>1.54723811149597</v>
+        <v>1.54723823070526</v>
       </c>
       <c r="H174" t="n">
         <v>47810</v>
@@ -5502,7 +5502,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G177" t="n">
-        <v>1.52379500865936</v>
+        <v>1.52379524707794</v>
       </c>
       <c r="H177" t="n">
         <v>51119</v>
@@ -5647,7 +5647,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G182" t="n">
-        <v>1.47690904140472</v>
+        <v>1.47690916061401</v>
       </c>
       <c r="H182" t="n">
         <v>1510</v>
@@ -5676,7 +5676,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G183" t="n">
-        <v>1.4143944978714</v>
+        <v>1.41439437866211</v>
       </c>
       <c r="H183" t="n">
         <v>13615</v>
@@ -5705,7 +5705,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G184" t="n">
-        <v>1.4534660577774</v>
+        <v>1.45346617698669</v>
       </c>
       <c r="H184" t="n">
         <v>3021</v>
@@ -5734,7 +5734,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G185" t="n">
-        <v>1.43783748149872</v>
+        <v>1.43783760070801</v>
       </c>
       <c r="H185" t="n">
         <v>3980</v>
@@ -5763,7 +5763,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G186" t="n">
-        <v>1.44565188884735</v>
+        <v>1.44565176963806</v>
       </c>
       <c r="H186" t="n">
         <v>5051</v>
@@ -5792,7 +5792,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G187" t="n">
-        <v>1.60975277423859</v>
+        <v>1.60975289344788</v>
       </c>
       <c r="H187" t="n">
         <v>206627</v>
@@ -5879,7 +5879,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G190" t="n">
-        <v>1.52379500865936</v>
+        <v>1.52379524707794</v>
       </c>
       <c r="H190" t="n">
         <v>29552</v>
@@ -5908,7 +5908,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G191" t="n">
-        <v>1.52379500865936</v>
+        <v>1.52379524707794</v>
       </c>
       <c r="H191" t="n">
         <v>10729</v>
@@ -6111,7 +6111,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G198" t="n">
-        <v>1.46909487247467</v>
+        <v>1.46909475326538</v>
       </c>
       <c r="H198" t="n">
         <v>7517</v>
@@ -6227,7 +6227,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G202" t="n">
-        <v>1.47690904140472</v>
+        <v>1.47690916061401</v>
       </c>
       <c r="H202" t="n">
         <v>7610</v>
@@ -6285,7 +6285,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G204" t="n">
-        <v>1.53160953521729</v>
+        <v>1.531609416008</v>
       </c>
       <c r="H204" t="n">
         <v>8646</v>
@@ -6401,7 +6401,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G208" t="n">
-        <v>1.54723811149597</v>
+        <v>1.54723823070526</v>
       </c>
       <c r="H208" t="n">
         <v>30696</v>
@@ -6430,7 +6430,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G209" t="n">
-        <v>1.54723811149597</v>
+        <v>1.54723823070526</v>
       </c>
       <c r="H209" t="n">
         <v>5243</v>
@@ -6459,7 +6459,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G210" t="n">
-        <v>1.52379500865936</v>
+        <v>1.52379524707794</v>
       </c>
       <c r="H210" t="n">
         <v>3092</v>
@@ -6517,7 +6517,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G212" t="n">
-        <v>1.54723811149597</v>
+        <v>1.54723823070526</v>
       </c>
       <c r="H212" t="n">
         <v>600</v>
@@ -6604,7 +6604,7 @@
         <v>2</v>
       </c>
       <c r="G215" t="n">
-        <v>1.56286692619324</v>
+        <v>1.56286680698395</v>
       </c>
       <c r="H215" t="n">
         <v>7270</v>
@@ -6662,7 +6662,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G217" t="n">
-        <v>1.52379500865936</v>
+        <v>1.52379524707794</v>
       </c>
       <c r="H217" t="n">
         <v>9361</v>
@@ -6720,7 +6720,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G219" t="n">
-        <v>1.53160953521729</v>
+        <v>1.531609416008</v>
       </c>
       <c r="H219" t="n">
         <v>16116</v>
@@ -6778,7 +6778,7 @@
         <v>2</v>
       </c>
       <c r="G221" t="n">
-        <v>1.56286692619324</v>
+        <v>1.56286680698395</v>
       </c>
       <c r="H221" t="n">
         <v>25291</v>
@@ -6807,7 +6807,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G222" t="n">
-        <v>1.61756706237793</v>
+        <v>1.61756718158722</v>
       </c>
       <c r="H222" t="n">
         <v>33429</v>
@@ -6836,7 +6836,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G223" t="n">
-        <v>1.57849538326263</v>
+        <v>1.57849550247192</v>
       </c>
       <c r="H223" t="n">
         <v>95323</v>
@@ -6923,7 +6923,7 @@
         <v>2</v>
       </c>
       <c r="G226" t="n">
-        <v>1.56286692619324</v>
+        <v>1.56286680698395</v>
       </c>
       <c r="H226" t="n">
         <v>13694</v>
@@ -7010,7 +7010,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G229" t="n">
-        <v>1.46909487247467</v>
+        <v>1.46909475326538</v>
       </c>
       <c r="H229" t="n">
         <v>18045</v>
@@ -7126,7 +7126,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G233" t="n">
-        <v>1.52379500865936</v>
+        <v>1.52379524707794</v>
       </c>
       <c r="H233" t="n">
         <v>6905</v>
@@ -7155,7 +7155,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G234" t="n">
-        <v>1.4143944978714</v>
+        <v>1.41439437866211</v>
       </c>
       <c r="H234" t="n">
         <v>15984</v>
@@ -7184,7 +7184,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G235" t="n">
-        <v>1.43002307415009</v>
+        <v>1.43002319335938</v>
       </c>
       <c r="H235" t="n">
         <v>7002</v>
@@ -7242,7 +7242,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G237" t="n">
-        <v>1.47690904140472</v>
+        <v>1.47690916061401</v>
       </c>
       <c r="H237" t="n">
         <v>3415</v>
@@ -7271,7 +7271,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G238" t="n">
-        <v>1.43783748149872</v>
+        <v>1.43783760070801</v>
       </c>
       <c r="H238" t="n">
         <v>1692</v>
@@ -7300,7 +7300,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G239" t="n">
-        <v>1.46909487247467</v>
+        <v>1.46909475326538</v>
       </c>
       <c r="H239" t="n">
         <v>4746</v>
@@ -7358,7 +7358,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G241" t="n">
-        <v>1.52379500865936</v>
+        <v>1.52379524707794</v>
       </c>
       <c r="H241" t="n">
         <v>5500</v>
@@ -7387,7 +7387,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G242" t="n">
-        <v>1.52379500865936</v>
+        <v>1.52379524707794</v>
       </c>
       <c r="H242" t="n">
         <v>6897</v>
@@ -7416,7 +7416,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G243" t="n">
-        <v>1.50035214424133</v>
+        <v>1.50035226345062</v>
       </c>
       <c r="H243" t="n">
         <v>2774</v>
@@ -7445,7 +7445,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G244" t="n">
-        <v>1.50035214424133</v>
+        <v>1.50035226345062</v>
       </c>
       <c r="H244" t="n">
         <v>2142</v>
@@ -7503,7 +7503,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G246" t="n">
-        <v>1.50035214424133</v>
+        <v>1.50035226345062</v>
       </c>
       <c r="H246" t="n">
         <v>6837</v>
@@ -7532,7 +7532,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G247" t="n">
-        <v>1.50035214424133</v>
+        <v>1.50035226345062</v>
       </c>
       <c r="H247" t="n">
         <v>9596</v>
@@ -7561,7 +7561,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G248" t="n">
-        <v>1.50035214424133</v>
+        <v>1.50035226345062</v>
       </c>
       <c r="H248" t="n">
         <v>3796</v>
@@ -7619,7 +7619,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G250" t="n">
-        <v>1.50035214424133</v>
+        <v>1.50035226345062</v>
       </c>
       <c r="H250" t="n">
         <v>16130</v>
@@ -7706,7 +7706,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G253" t="n">
-        <v>1.47690904140472</v>
+        <v>1.47690916061401</v>
       </c>
       <c r="H253" t="n">
         <v>5630</v>
@@ -7735,7 +7735,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G254" t="n">
-        <v>1.50035214424133</v>
+        <v>1.50035226345062</v>
       </c>
       <c r="H254" t="n">
         <v>10860</v>
@@ -7822,7 +7822,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G257" t="n">
-        <v>1.54723811149597</v>
+        <v>1.54723823070526</v>
       </c>
       <c r="H257" t="n">
         <v>41048</v>
@@ -7909,7 +7909,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G260" t="n">
-        <v>1.76603937149048</v>
+        <v>1.76603949069977</v>
       </c>
       <c r="H260" t="n">
         <v>45306</v>
@@ -7938,7 +7938,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G261" t="n">
-        <v>1.73478221893311</v>
+        <v>1.73478209972382</v>
       </c>
       <c r="H261" t="n">
         <v>35690</v>
@@ -7967,7 +7967,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G262" t="n">
-        <v>1.72696793079376</v>
+        <v>1.72696781158447</v>
       </c>
       <c r="H262" t="n">
         <v>17933</v>
@@ -7996,7 +7996,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G263" t="n">
-        <v>1.67226755619049</v>
+        <v>1.67226767539978</v>
       </c>
       <c r="H263" t="n">
         <v>45589</v>
@@ -8025,7 +8025,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G264" t="n">
-        <v>1.64882445335388</v>
+        <v>1.64882433414459</v>
       </c>
       <c r="H264" t="n">
         <v>11388</v>
@@ -8112,7 +8112,7 @@
         <v>2.25</v>
       </c>
       <c r="G267" t="n">
-        <v>1.75822508335114</v>
+        <v>1.75822532176971</v>
       </c>
       <c r="H267" t="n">
         <v>48617</v>
@@ -8228,7 +8228,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G271" t="n">
-        <v>1.79729664325714</v>
+        <v>1.79729688167572</v>
       </c>
       <c r="H271" t="n">
         <v>110444</v>
@@ -8315,7 +8315,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G274" t="n">
-        <v>2.78190279006958</v>
+        <v>2.78190302848816</v>
       </c>
       <c r="H274" t="n">
         <v>248750</v>
@@ -8402,7 +8402,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G277" t="n">
-        <v>2.31304311752319</v>
+        <v>2.31304287910461</v>
       </c>
       <c r="H277" t="n">
         <v>178115</v>
@@ -8431,7 +8431,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G278" t="n">
-        <v>2.36774325370789</v>
+        <v>2.36774301528931</v>
       </c>
       <c r="H278" t="n">
         <v>155933</v>
@@ -8489,7 +8489,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G280" t="n">
-        <v>2.36774325370789</v>
+        <v>2.36774301528931</v>
       </c>
       <c r="H280" t="n">
         <v>42641</v>
@@ -8576,7 +8576,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G283" t="n">
-        <v>2.4849579334259</v>
+        <v>2.48495841026306</v>
       </c>
       <c r="H283" t="n">
         <v>174485</v>
@@ -8605,7 +8605,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G284" t="n">
-        <v>2.41462922096252</v>
+        <v>2.41462898254395</v>
       </c>
       <c r="H284" t="n">
         <v>141085</v>
@@ -8634,7 +8634,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G285" t="n">
-        <v>2.41462922096252</v>
+        <v>2.41462898254395</v>
       </c>
       <c r="H285" t="n">
         <v>32999</v>
@@ -8721,7 +8721,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G288" t="n">
-        <v>2.56310176849365</v>
+        <v>2.56310153007507</v>
       </c>
       <c r="H288" t="n">
         <v>73109</v>
@@ -8750,7 +8750,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G289" t="n">
-        <v>2.50840139389038</v>
+        <v>2.5084011554718</v>
       </c>
       <c r="H289" t="n">
         <v>75755</v>
@@ -8779,7 +8779,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G290" t="n">
-        <v>2.4849579334259</v>
+        <v>2.48495841026306</v>
       </c>
       <c r="H290" t="n">
         <v>43039</v>
@@ -8808,7 +8808,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G291" t="n">
-        <v>2.45370101928711</v>
+        <v>2.45370078086853</v>
       </c>
       <c r="H291" t="n">
         <v>62585</v>
@@ -8866,7 +8866,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G293" t="n">
-        <v>2.30522847175598</v>
+        <v>2.30522871017456</v>
       </c>
       <c r="H293" t="n">
         <v>63123</v>
@@ -8924,7 +8924,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G295" t="n">
-        <v>2.2114565372467</v>
+        <v>2.21145629882812</v>
       </c>
       <c r="H295" t="n">
         <v>127250</v>
@@ -8953,7 +8953,7 @@
         <v>2.75</v>
       </c>
       <c r="G296" t="n">
-        <v>2.14894151687622</v>
+        <v>2.14894199371338</v>
       </c>
       <c r="H296" t="n">
         <v>145249</v>
@@ -9127,7 +9127,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G302" t="n">
-        <v>2.10987043380737</v>
+        <v>2.10987019538879</v>
       </c>
       <c r="H302" t="n">
         <v>17255</v>
@@ -9185,7 +9185,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G304" t="n">
-        <v>2.08642721176147</v>
+        <v>2.08642745018005</v>
       </c>
       <c r="H304" t="n">
         <v>19530</v>
@@ -9214,7 +9214,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G305" t="n">
-        <v>2.08642721176147</v>
+        <v>2.08642745018005</v>
       </c>
       <c r="H305" t="n">
         <v>13542</v>
@@ -9243,7 +9243,7 @@
         <v>2.75</v>
       </c>
       <c r="G306" t="n">
-        <v>2.14894151687622</v>
+        <v>2.14894199371338</v>
       </c>
       <c r="H306" t="n">
         <v>29862</v>
@@ -9388,7 +9388,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G311" t="n">
-        <v>2.13331317901611</v>
+        <v>2.13331294059753</v>
       </c>
       <c r="H311" t="n">
         <v>20423</v>
@@ -9417,7 +9417,7 @@
         <v>2.75</v>
       </c>
       <c r="G312" t="n">
-        <v>2.14894151687622</v>
+        <v>2.14894199371338</v>
       </c>
       <c r="H312" t="n">
         <v>12417</v>
@@ -9446,7 +9446,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G313" t="n">
-        <v>2.14112782478333</v>
+        <v>2.14112758636475</v>
       </c>
       <c r="H313" t="n">
         <v>5822</v>
@@ -9475,7 +9475,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G314" t="n">
-        <v>2.19582772254944</v>
+        <v>2.19582796096802</v>
       </c>
       <c r="H314" t="n">
         <v>90558</v>
@@ -9504,7 +9504,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G315" t="n">
-        <v>2.2114565372467</v>
+        <v>2.21145629882812</v>
       </c>
       <c r="H315" t="n">
         <v>24918</v>
@@ -9533,7 +9533,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G316" t="n">
-        <v>2.31304311752319</v>
+        <v>2.31304287910461</v>
       </c>
       <c r="H316" t="n">
         <v>166647</v>
@@ -9562,7 +9562,7 @@
         <v>3</v>
       </c>
       <c r="G317" t="n">
-        <v>2.34430003166199</v>
+        <v>2.34430027008057</v>
       </c>
       <c r="H317" t="n">
         <v>64269</v>
@@ -9620,7 +9620,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G319" t="n">
-        <v>2.43025779724121</v>
+        <v>2.43025803565979</v>
       </c>
       <c r="H319" t="n">
         <v>373672</v>
@@ -9678,7 +9678,7 @@
         <v>3</v>
       </c>
       <c r="G321" t="n">
-        <v>2.34430003166199</v>
+        <v>2.34430027008057</v>
       </c>
       <c r="H321" t="n">
         <v>14413</v>
@@ -9794,7 +9794,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G325" t="n">
-        <v>2.36774325370789</v>
+        <v>2.36774301528931</v>
       </c>
       <c r="H325" t="n">
         <v>123555</v>
@@ -9823,7 +9823,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G326" t="n">
-        <v>2.32867169380188</v>
+        <v>2.3286714553833</v>
       </c>
       <c r="H326" t="n">
         <v>34122</v>
@@ -9852,7 +9852,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G327" t="n">
-        <v>2.31304311752319</v>
+        <v>2.31304287910461</v>
       </c>
       <c r="H327" t="n">
         <v>15378</v>
@@ -9881,7 +9881,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G328" t="n">
-        <v>2.27397108078003</v>
+        <v>2.27397131919861</v>
       </c>
       <c r="H328" t="n">
         <v>24472</v>
@@ -9910,7 +9910,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G329" t="n">
-        <v>2.27397108078003</v>
+        <v>2.27397131919861</v>
       </c>
       <c r="H329" t="n">
         <v>19303</v>
@@ -9968,7 +9968,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G331" t="n">
-        <v>2.27397108078003</v>
+        <v>2.27397131919861</v>
       </c>
       <c r="H331" t="n">
         <v>11915</v>
@@ -9997,7 +9997,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G332" t="n">
-        <v>2.19582772254944</v>
+        <v>2.19582796096802</v>
       </c>
       <c r="H332" t="n">
         <v>23745</v>
@@ -10026,7 +10026,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G333" t="n">
-        <v>2.25834250450134</v>
+        <v>2.25834274291992</v>
       </c>
       <c r="H333" t="n">
         <v>41046</v>
@@ -10055,7 +10055,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G334" t="n">
-        <v>2.30522847175598</v>
+        <v>2.30522871017456</v>
       </c>
       <c r="H334" t="n">
         <v>27597</v>
@@ -10084,7 +10084,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G335" t="n">
-        <v>2.29741430282593</v>
+        <v>2.29741406440735</v>
       </c>
       <c r="H335" t="n">
         <v>14756</v>
@@ -10113,7 +10113,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G336" t="n">
-        <v>2.36774325370789</v>
+        <v>2.36774301528931</v>
       </c>
       <c r="H336" t="n">
         <v>60523</v>
@@ -10142,7 +10142,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G337" t="n">
-        <v>2.30522847175598</v>
+        <v>2.30522871017456</v>
       </c>
       <c r="H337" t="n">
         <v>70691</v>
@@ -10171,7 +10171,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G338" t="n">
-        <v>2.31304311752319</v>
+        <v>2.31304287910461</v>
       </c>
       <c r="H338" t="n">
         <v>35872</v>
@@ -10200,7 +10200,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G339" t="n">
-        <v>2.32867169380188</v>
+        <v>2.3286714553833</v>
       </c>
       <c r="H339" t="n">
         <v>58353</v>
@@ -10258,7 +10258,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G341" t="n">
-        <v>2.25834250450134</v>
+        <v>2.25834274291992</v>
       </c>
       <c r="H341" t="n">
         <v>19671</v>
@@ -10287,7 +10287,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G342" t="n">
-        <v>2.25834250450134</v>
+        <v>2.25834274291992</v>
       </c>
       <c r="H342" t="n">
         <v>9250</v>
@@ -10316,7 +10316,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G343" t="n">
-        <v>2.29741430282593</v>
+        <v>2.29741406440735</v>
       </c>
       <c r="H343" t="n">
         <v>68674</v>
@@ -10345,7 +10345,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G344" t="n">
-        <v>2.50840139389038</v>
+        <v>2.5084011554718</v>
       </c>
       <c r="H344" t="n">
         <v>306118</v>
@@ -10432,7 +10432,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G347" t="n">
-        <v>2.41462922096252</v>
+        <v>2.41462898254395</v>
       </c>
       <c r="H347" t="n">
         <v>25889</v>
@@ -10548,7 +10548,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G351" t="n">
-        <v>2.30522847175598</v>
+        <v>2.30522871017456</v>
       </c>
       <c r="H351" t="n">
         <v>10524</v>
@@ -10577,7 +10577,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G352" t="n">
-        <v>2.25834250450134</v>
+        <v>2.25834274291992</v>
       </c>
       <c r="H352" t="n">
         <v>34161</v>
@@ -10635,7 +10635,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G354" t="n">
-        <v>2.27397108078003</v>
+        <v>2.27397131919861</v>
       </c>
       <c r="H354" t="n">
         <v>5260</v>
@@ -10664,7 +10664,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G355" t="n">
-        <v>2.30522847175598</v>
+        <v>2.30522871017456</v>
       </c>
       <c r="H355" t="n">
         <v>6469</v>
@@ -10693,7 +10693,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G356" t="n">
-        <v>2.35992860794067</v>
+        <v>2.35992884635925</v>
       </c>
       <c r="H356" t="n">
         <v>37071</v>
@@ -10722,7 +10722,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G357" t="n">
-        <v>2.32867169380188</v>
+        <v>2.3286714553833</v>
       </c>
       <c r="H357" t="n">
         <v>14916</v>
@@ -10780,7 +10780,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G359" t="n">
-        <v>2.30522847175598</v>
+        <v>2.30522871017456</v>
       </c>
       <c r="H359" t="n">
         <v>21418</v>
@@ -10809,7 +10809,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G360" t="n">
-        <v>2.31304311752319</v>
+        <v>2.31304287910461</v>
       </c>
       <c r="H360" t="n">
         <v>6391</v>
@@ -10838,7 +10838,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G361" t="n">
-        <v>2.30522847175598</v>
+        <v>2.30522871017456</v>
       </c>
       <c r="H361" t="n">
         <v>12853</v>
@@ -10896,7 +10896,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G363" t="n">
-        <v>2.29741430282593</v>
+        <v>2.29741406440735</v>
       </c>
       <c r="H363" t="n">
         <v>67201</v>
@@ -10954,7 +10954,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G365" t="n">
-        <v>2.19582772254944</v>
+        <v>2.19582796096802</v>
       </c>
       <c r="H365" t="n">
         <v>66685</v>
@@ -10983,7 +10983,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G366" t="n">
-        <v>2.19582772254944</v>
+        <v>2.19582796096802</v>
       </c>
       <c r="H366" t="n">
         <v>21330</v>
@@ -11070,7 +11070,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G369" t="n">
-        <v>2.19582772254944</v>
+        <v>2.19582796096802</v>
       </c>
       <c r="H369" t="n">
         <v>25375</v>
@@ -11099,7 +11099,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G370" t="n">
-        <v>2.19582772254944</v>
+        <v>2.19582796096802</v>
       </c>
       <c r="H370" t="n">
         <v>2922</v>
@@ -11215,7 +11215,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G374" t="n">
-        <v>2.2114565372467</v>
+        <v>2.21145629882812</v>
       </c>
       <c r="H374" t="n">
         <v>1201</v>
@@ -11447,7 +11447,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G382" t="n">
-        <v>2.2114565372467</v>
+        <v>2.21145629882812</v>
       </c>
       <c r="H382" t="n">
         <v>7415</v>
@@ -11476,7 +11476,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G383" t="n">
-        <v>2.25834250450134</v>
+        <v>2.25834274291992</v>
       </c>
       <c r="H383" t="n">
         <v>38535</v>
@@ -11505,7 +11505,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G384" t="n">
-        <v>2.23489928245544</v>
+        <v>2.23489952087402</v>
       </c>
       <c r="H384" t="n">
         <v>7914</v>
@@ -11534,7 +11534,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G385" t="n">
-        <v>2.23489928245544</v>
+        <v>2.23489952087402</v>
       </c>
       <c r="H385" t="n">
         <v>2794</v>
@@ -11563,7 +11563,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G386" t="n">
-        <v>2.25834250450134</v>
+        <v>2.25834274291992</v>
       </c>
       <c r="H386" t="n">
         <v>100</v>
@@ -11679,7 +11679,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G390" t="n">
-        <v>2.19582772254944</v>
+        <v>2.19582796096802</v>
       </c>
       <c r="H390" t="n">
         <v>6870</v>
@@ -11708,7 +11708,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G391" t="n">
-        <v>2.23489928245544</v>
+        <v>2.23489952087402</v>
       </c>
       <c r="H391" t="n">
         <v>13073</v>
@@ -11882,7 +11882,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G397" t="n">
-        <v>2.2114565372467</v>
+        <v>2.21145629882812</v>
       </c>
       <c r="H397" t="n">
         <v>14364</v>
@@ -11911,7 +11911,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G398" t="n">
-        <v>2.23489928245544</v>
+        <v>2.23489952087402</v>
       </c>
       <c r="H398" t="n">
         <v>19480</v>
@@ -11940,7 +11940,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G399" t="n">
-        <v>2.25834250450134</v>
+        <v>2.25834274291992</v>
       </c>
       <c r="H399" t="n">
         <v>9326</v>
@@ -11998,7 +11998,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G401" t="n">
-        <v>2.27397108078003</v>
+        <v>2.27397131919861</v>
       </c>
       <c r="H401" t="n">
         <v>8887</v>
@@ -12259,7 +12259,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G410" t="n">
-        <v>2.27397108078003</v>
+        <v>2.27397131919861</v>
       </c>
       <c r="H410" t="n">
         <v>12237</v>
@@ -12462,7 +12462,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G417" t="n">
-        <v>2.25834250450134</v>
+        <v>2.25834274291992</v>
       </c>
       <c r="H417" t="n">
         <v>1700</v>
@@ -12491,7 +12491,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G418" t="n">
-        <v>2.27397108078003</v>
+        <v>2.27397131919861</v>
       </c>
       <c r="H418" t="n">
         <v>7095</v>
@@ -12636,7 +12636,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G423" t="n">
-        <v>2.25834250450134</v>
+        <v>2.25834274291992</v>
       </c>
       <c r="H423" t="n">
         <v>19254</v>
@@ -12665,7 +12665,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G424" t="n">
-        <v>2.25834250450134</v>
+        <v>2.25834274291992</v>
       </c>
       <c r="H424" t="n">
         <v>2892</v>
@@ -12810,7 +12810,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G429" t="n">
-        <v>2.27397108078003</v>
+        <v>2.27397131919861</v>
       </c>
       <c r="H429" t="n">
         <v>3175</v>
@@ -12868,7 +12868,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G431" t="n">
-        <v>2.27397108078003</v>
+        <v>2.27397131919861</v>
       </c>
       <c r="H431" t="n">
         <v>5595</v>
@@ -12955,7 +12955,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G434" t="n">
-        <v>2.30522847175598</v>
+        <v>2.30522871017456</v>
       </c>
       <c r="H434" t="n">
         <v>3559</v>
@@ -13042,7 +13042,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G437" t="n">
-        <v>2.27397108078003</v>
+        <v>2.27397131919861</v>
       </c>
       <c r="H437" t="n">
         <v>4699</v>
@@ -13100,7 +13100,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G439" t="n">
-        <v>2.30522847175598</v>
+        <v>2.30522871017456</v>
       </c>
       <c r="H439" t="n">
         <v>7059</v>
@@ -13129,7 +13129,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G440" t="n">
-        <v>2.29741430282593</v>
+        <v>2.29741406440735</v>
       </c>
       <c r="H440" t="n">
         <v>7441</v>
@@ -13158,7 +13158,7 @@
         <v>3</v>
       </c>
       <c r="G441" t="n">
-        <v>2.34430003166199</v>
+        <v>2.34430027008057</v>
       </c>
       <c r="H441" t="n">
         <v>42286</v>
@@ -13216,7 +13216,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G443" t="n">
-        <v>2.35992860794067</v>
+        <v>2.35992884635925</v>
       </c>
       <c r="H443" t="n">
         <v>25888</v>
@@ -13245,7 +13245,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G444" t="n">
-        <v>2.42244362831116</v>
+        <v>2.42244338989258</v>
       </c>
       <c r="H444" t="n">
         <v>158865</v>
@@ -13303,7 +13303,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G446" t="n">
-        <v>2.32867169380188</v>
+        <v>2.3286714553833</v>
       </c>
       <c r="H446" t="n">
         <v>38929</v>
@@ -13361,7 +13361,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G448" t="n">
-        <v>2.29741430282593</v>
+        <v>2.29741406440735</v>
       </c>
       <c r="H448" t="n">
         <v>19867</v>
@@ -13390,7 +13390,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G449" t="n">
-        <v>2.31304311752319</v>
+        <v>2.31304287910461</v>
       </c>
       <c r="H449" t="n">
         <v>8698</v>
@@ -13477,7 +13477,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G452" t="n">
-        <v>2.27397108078003</v>
+        <v>2.27397131919861</v>
       </c>
       <c r="H452" t="n">
         <v>4236</v>
@@ -13506,7 +13506,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G453" t="n">
-        <v>2.25834250450134</v>
+        <v>2.25834274291992</v>
       </c>
       <c r="H453" t="n">
         <v>12264</v>
@@ -13535,7 +13535,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G454" t="n">
-        <v>2.25834250450134</v>
+        <v>2.25834274291992</v>
       </c>
       <c r="H454" t="n">
         <v>3217</v>
@@ -13593,7 +13593,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G456" t="n">
-        <v>2.27397108078003</v>
+        <v>2.27397131919861</v>
       </c>
       <c r="H456" t="n">
         <v>23276</v>
@@ -13680,7 +13680,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G459" t="n">
-        <v>2.27397108078003</v>
+        <v>2.27397131919861</v>
       </c>
       <c r="H459" t="n">
         <v>4372</v>
@@ -13738,7 +13738,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G461" t="n">
-        <v>2.27397108078003</v>
+        <v>2.27397131919861</v>
       </c>
       <c r="H461" t="n">
         <v>2391</v>
@@ -13767,7 +13767,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G462" t="n">
-        <v>2.25834250450134</v>
+        <v>2.25834274291992</v>
       </c>
       <c r="H462" t="n">
         <v>11311</v>
@@ -13796,7 +13796,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G463" t="n">
-        <v>2.27397108078003</v>
+        <v>2.27397131919861</v>
       </c>
       <c r="H463" t="n">
         <v>891</v>
@@ -13825,7 +13825,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G464" t="n">
-        <v>2.25834250450134</v>
+        <v>2.25834274291992</v>
       </c>
       <c r="H464" t="n">
         <v>893</v>
@@ -14028,7 +14028,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G471" t="n">
-        <v>2.25834250450134</v>
+        <v>2.25834274291992</v>
       </c>
       <c r="H471" t="n">
         <v>5598</v>
@@ -14086,7 +14086,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G473" t="n">
-        <v>2.25834250450134</v>
+        <v>2.25834274291992</v>
       </c>
       <c r="H473" t="n">
         <v>2692</v>
@@ -14347,7 +14347,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G482" t="n">
-        <v>2.0551700592041</v>
+        <v>2.05516982078552</v>
       </c>
       <c r="H482" t="n">
         <v>33954</v>
@@ -14376,7 +14376,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G483" t="n">
-        <v>2.0551700592041</v>
+        <v>2.05516982078552</v>
       </c>
       <c r="H483" t="n">
         <v>1310</v>
@@ -14405,7 +14405,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G484" t="n">
-        <v>2.06298398971558</v>
+        <v>2.06298422813416</v>
       </c>
       <c r="H484" t="n">
         <v>4500</v>
@@ -14434,7 +14434,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G485" t="n">
-        <v>2.04735541343689</v>
+        <v>2.04735517501831</v>
       </c>
       <c r="H485" t="n">
         <v>5465</v>
@@ -14492,7 +14492,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G487" t="n">
-        <v>2.0551700592041</v>
+        <v>2.05516982078552</v>
       </c>
       <c r="H487" t="n">
         <v>7884</v>
@@ -14521,7 +14521,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G488" t="n">
-        <v>2.09424138069153</v>
+        <v>2.09424161911011</v>
       </c>
       <c r="H488" t="n">
         <v>6344</v>
@@ -14579,7 +14579,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G490" t="n">
-        <v>2.03954148292542</v>
+        <v>2.03954100608826</v>
       </c>
       <c r="H490" t="n">
         <v>11032</v>
@@ -14608,7 +14608,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G491" t="n">
-        <v>2.0551700592041</v>
+        <v>2.05516982078552</v>
       </c>
       <c r="H491" t="n">
         <v>4461</v>
@@ -14666,7 +14666,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G493" t="n">
-        <v>2.0082836151123</v>
+        <v>2.00828385353088</v>
       </c>
       <c r="H493" t="n">
         <v>38338</v>
@@ -14695,7 +14695,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G494" t="n">
-        <v>2.02391242980957</v>
+        <v>2.02391266822815</v>
       </c>
       <c r="H494" t="n">
         <v>4454</v>
@@ -14724,7 +14724,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G495" t="n">
-        <v>2.02391242980957</v>
+        <v>2.02391266822815</v>
       </c>
       <c r="H495" t="n">
         <v>1453</v>
@@ -14869,7 +14869,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G500" t="n">
-        <v>2.0082836151123</v>
+        <v>2.00828385353088</v>
       </c>
       <c r="H500" t="n">
         <v>1488</v>
@@ -15159,7 +15159,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G510" t="n">
-        <v>2.0082836151123</v>
+        <v>2.00828385353088</v>
       </c>
       <c r="H510" t="n">
         <v>2371</v>
@@ -15246,7 +15246,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G513" t="n">
-        <v>2.0082836151123</v>
+        <v>2.00828385353088</v>
       </c>
       <c r="H513" t="n">
         <v>4130</v>
@@ -15391,7 +15391,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G518" t="n">
-        <v>2.09424138069153</v>
+        <v>2.09424161911011</v>
       </c>
       <c r="H518" t="n">
         <v>112388</v>
@@ -15420,7 +15420,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G519" t="n">
-        <v>2.08642721176147</v>
+        <v>2.08642745018005</v>
       </c>
       <c r="H519" t="n">
         <v>11274</v>
@@ -15478,7 +15478,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G521" t="n">
-        <v>2.06298398971558</v>
+        <v>2.06298422813416</v>
       </c>
       <c r="H521" t="n">
         <v>14270</v>
@@ -15507,7 +15507,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G522" t="n">
-        <v>2.0551700592041</v>
+        <v>2.05516982078552</v>
       </c>
       <c r="H522" t="n">
         <v>2500</v>
@@ -15536,7 +15536,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G523" t="n">
-        <v>2.08642721176147</v>
+        <v>2.08642745018005</v>
       </c>
       <c r="H523" t="n">
         <v>9758</v>
@@ -15594,7 +15594,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G525" t="n">
-        <v>2.0551700592041</v>
+        <v>2.05516982078552</v>
       </c>
       <c r="H525" t="n">
         <v>14380</v>
@@ -15623,7 +15623,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G526" t="n">
-        <v>2.04735541343689</v>
+        <v>2.04735517501831</v>
       </c>
       <c r="H526" t="n">
         <v>13140</v>
@@ -15652,7 +15652,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G527" t="n">
-        <v>2.04735541343689</v>
+        <v>2.04735517501831</v>
       </c>
       <c r="H527" t="n">
         <v>1930</v>
@@ -15681,7 +15681,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G528" t="n">
-        <v>2.0551700592041</v>
+        <v>2.05516982078552</v>
       </c>
       <c r="H528" t="n">
         <v>4970</v>
@@ -15710,7 +15710,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G529" t="n">
-        <v>2.04735541343689</v>
+        <v>2.04735517501831</v>
       </c>
       <c r="H529" t="n">
         <v>6486</v>
@@ -15739,7 +15739,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G530" t="n">
-        <v>2.08642721176147</v>
+        <v>2.08642745018005</v>
       </c>
       <c r="H530" t="n">
         <v>11459</v>
@@ -15797,7 +15797,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G532" t="n">
-        <v>2.03954148292542</v>
+        <v>2.03954100608826</v>
       </c>
       <c r="H532" t="n">
         <v>7408</v>
@@ -15826,7 +15826,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G533" t="n">
-        <v>2.03954148292542</v>
+        <v>2.03954100608826</v>
       </c>
       <c r="H533" t="n">
         <v>1950</v>
@@ -16000,7 +16000,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G539" t="n">
-        <v>1.98484075069427</v>
+        <v>1.98484063148499</v>
       </c>
       <c r="H539" t="n">
         <v>4051</v>
@@ -16058,7 +16058,7 @@
         <v>2.5</v>
       </c>
       <c r="G541" t="n">
-        <v>1.9535835981369</v>
+        <v>1.95358347892761</v>
       </c>
       <c r="H541" t="n">
         <v>1628</v>
@@ -16087,7 +16087,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G542" t="n">
-        <v>1.89106893539429</v>
+        <v>1.891068816185</v>
       </c>
       <c r="H542" t="n">
         <v>4966</v>
@@ -16116,7 +16116,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G543" t="n">
-        <v>1.92232620716095</v>
+        <v>1.92232632637024</v>
       </c>
       <c r="H543" t="n">
         <v>2000</v>
@@ -16145,7 +16145,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G544" t="n">
-        <v>1.89106893539429</v>
+        <v>1.891068816185</v>
       </c>
       <c r="H544" t="n">
         <v>1977</v>
@@ -16174,7 +16174,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G545" t="n">
-        <v>1.98484075069427</v>
+        <v>1.98484063148499</v>
       </c>
       <c r="H545" t="n">
         <v>7157</v>
@@ -16203,7 +16203,7 @@
         <v>2.5</v>
       </c>
       <c r="G546" t="n">
-        <v>1.9535835981369</v>
+        <v>1.95358347892761</v>
       </c>
       <c r="H546" t="n">
         <v>13540</v>
@@ -16232,7 +16232,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G547" t="n">
-        <v>1.96921217441559</v>
+        <v>1.96921193599701</v>
       </c>
       <c r="H547" t="n">
         <v>4409</v>
@@ -16261,7 +16261,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G548" t="n">
-        <v>1.96921217441559</v>
+        <v>1.96921193599701</v>
       </c>
       <c r="H548" t="n">
         <v>2935</v>
@@ -16290,7 +16290,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G549" t="n">
-        <v>1.93795478343964</v>
+        <v>1.93795502185822</v>
       </c>
       <c r="H549" t="n">
         <v>78</v>
@@ -16319,7 +16319,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G550" t="n">
-        <v>2.04735541343689</v>
+        <v>2.04735517501831</v>
       </c>
       <c r="H550" t="n">
         <v>12782</v>
@@ -16348,7 +16348,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G551" t="n">
-        <v>2.0082836151123</v>
+        <v>2.00828385353088</v>
       </c>
       <c r="H551" t="n">
         <v>4912</v>
@@ -16377,7 +16377,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G552" t="n">
-        <v>2.02391242980957</v>
+        <v>2.02391266822815</v>
       </c>
       <c r="H552" t="n">
         <v>3342</v>
@@ -16406,7 +16406,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G553" t="n">
-        <v>2.0082836151123</v>
+        <v>2.00828385353088</v>
       </c>
       <c r="H553" t="n">
         <v>3184</v>
@@ -16435,7 +16435,7 @@
         <v>2.5</v>
       </c>
       <c r="G554" t="n">
-        <v>1.9535835981369</v>
+        <v>1.95358347892761</v>
       </c>
       <c r="H554" t="n">
         <v>801</v>
@@ -16464,7 +16464,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G555" t="n">
-        <v>1.87544023990631</v>
+        <v>1.8754403591156</v>
       </c>
       <c r="H555" t="n">
         <v>11021</v>
@@ -16522,7 +16522,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G557" t="n">
-        <v>1.87544023990631</v>
+        <v>1.8754403591156</v>
       </c>
       <c r="H557" t="n">
         <v>9292</v>
@@ -16580,7 +16580,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G559" t="n">
-        <v>1.87544023990631</v>
+        <v>1.8754403591156</v>
       </c>
       <c r="H559" t="n">
         <v>2957</v>
@@ -16609,7 +16609,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G560" t="n">
-        <v>1.89888310432434</v>
+        <v>1.89888322353363</v>
       </c>
       <c r="H560" t="n">
         <v>4094</v>
@@ -16638,7 +16638,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G561" t="n">
-        <v>1.89888310432434</v>
+        <v>1.89888322353363</v>
       </c>
       <c r="H561" t="n">
         <v>2899</v>
@@ -16696,7 +16696,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G563" t="n">
-        <v>1.90669763088226</v>
+        <v>1.90669739246368</v>
       </c>
       <c r="H563" t="n">
         <v>3670</v>
@@ -16725,7 +16725,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G564" t="n">
-        <v>1.90669763088226</v>
+        <v>1.90669739246368</v>
       </c>
       <c r="H564" t="n">
         <v>290</v>
@@ -16754,7 +16754,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G565" t="n">
-        <v>1.91451215744019</v>
+        <v>1.9145120382309</v>
       </c>
       <c r="H565" t="n">
         <v>930</v>
@@ -16783,7 +16783,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G566" t="n">
-        <v>1.87544023990631</v>
+        <v>1.8754403591156</v>
       </c>
       <c r="H566" t="n">
         <v>3211</v>
@@ -16812,7 +16812,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G567" t="n">
-        <v>1.87544023990631</v>
+        <v>1.8754403591156</v>
       </c>
       <c r="H567" t="n">
         <v>2215</v>
@@ -16870,7 +16870,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G569" t="n">
-        <v>1.84418296813965</v>
+        <v>1.84418284893036</v>
       </c>
       <c r="H569" t="n">
         <v>2584</v>
@@ -16899,7 +16899,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G570" t="n">
-        <v>1.92232620716095</v>
+        <v>1.92232632637024</v>
       </c>
       <c r="H570" t="n">
         <v>34637</v>
@@ -16957,7 +16957,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G572" t="n">
-        <v>2.0082836151123</v>
+        <v>2.00828385353088</v>
       </c>
       <c r="H572" t="n">
         <v>19963</v>
@@ -17015,7 +17015,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G574" t="n">
-        <v>2.03954148292542</v>
+        <v>2.03954100608826</v>
       </c>
       <c r="H574" t="n">
         <v>1270</v>
@@ -17102,7 +17102,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G577" t="n">
-        <v>2.06298398971558</v>
+        <v>2.06298422813416</v>
       </c>
       <c r="H577" t="n">
         <v>25388</v>
@@ -17131,7 +17131,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G578" t="n">
-        <v>2.0551700592041</v>
+        <v>2.05516982078552</v>
       </c>
       <c r="H578" t="n">
         <v>3757</v>
@@ -17160,7 +17160,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G579" t="n">
-        <v>2.03954148292542</v>
+        <v>2.03954100608826</v>
       </c>
       <c r="H579" t="n">
         <v>4138</v>
@@ -17189,7 +17189,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G580" t="n">
-        <v>2.04735541343689</v>
+        <v>2.04735517501831</v>
       </c>
       <c r="H580" t="n">
         <v>2057</v>
@@ -17247,7 +17247,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G582" t="n">
-        <v>1.98484075069427</v>
+        <v>1.98484063148499</v>
       </c>
       <c r="H582" t="n">
         <v>5772</v>
@@ -17276,7 +17276,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G583" t="n">
-        <v>1.98484075069427</v>
+        <v>1.98484063148499</v>
       </c>
       <c r="H583" t="n">
         <v>817</v>
@@ -17305,7 +17305,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G584" t="n">
-        <v>1.96139764785767</v>
+        <v>1.96139800548553</v>
       </c>
       <c r="H584" t="n">
         <v>534</v>
@@ -17363,7 +17363,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G586" t="n">
-        <v>2.02391242980957</v>
+        <v>2.02391266822815</v>
       </c>
       <c r="H586" t="n">
         <v>4748</v>
@@ -17392,7 +17392,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G587" t="n">
-        <v>2.0082836151123</v>
+        <v>2.00828385353088</v>
       </c>
       <c r="H587" t="n">
         <v>4400</v>
@@ -17421,7 +17421,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G588" t="n">
-        <v>1.96921217441559</v>
+        <v>1.96921193599701</v>
       </c>
       <c r="H588" t="n">
         <v>1223</v>
@@ -17479,7 +17479,7 @@
         <v>2.5</v>
       </c>
       <c r="G590" t="n">
-        <v>1.9535835981369</v>
+        <v>1.95358347892761</v>
       </c>
       <c r="H590" t="n">
         <v>6559</v>
@@ -17508,7 +17508,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G591" t="n">
-        <v>1.93795478343964</v>
+        <v>1.93795502185822</v>
       </c>
       <c r="H591" t="n">
         <v>11871</v>
@@ -17537,7 +17537,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G592" t="n">
-        <v>1.96921217441559</v>
+        <v>1.96921193599701</v>
       </c>
       <c r="H592" t="n">
         <v>100</v>
@@ -17566,7 +17566,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G593" t="n">
-        <v>1.89888310432434</v>
+        <v>1.89888322353363</v>
       </c>
       <c r="H593" t="n">
         <v>219</v>
@@ -17595,7 +17595,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G594" t="n">
-        <v>1.96921217441559</v>
+        <v>1.96921193599701</v>
       </c>
       <c r="H594" t="n">
         <v>28</v>
@@ -17624,7 +17624,7 @@
         <v>2.5</v>
       </c>
       <c r="G595" t="n">
-        <v>1.9535835981369</v>
+        <v>1.95358347892761</v>
       </c>
       <c r="H595" t="n">
         <v>2570</v>
@@ -17711,7 +17711,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G598" t="n">
-        <v>1.93795478343964</v>
+        <v>1.93795502185822</v>
       </c>
       <c r="H598" t="n">
         <v>301</v>
@@ -17740,7 +17740,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G599" t="n">
-        <v>1.91451215744019</v>
+        <v>1.9145120382309</v>
       </c>
       <c r="H599" t="n">
         <v>16585</v>
@@ -17827,7 +17827,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G602" t="n">
-        <v>1.89106893539429</v>
+        <v>1.891068816185</v>
       </c>
       <c r="H602" t="n">
         <v>3186</v>
@@ -17885,7 +17885,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G604" t="n">
-        <v>1.93795478343964</v>
+        <v>1.93795502185822</v>
       </c>
       <c r="H604" t="n">
         <v>100</v>
@@ -17914,7 +17914,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G605" t="n">
-        <v>1.89106893539429</v>
+        <v>1.891068816185</v>
       </c>
       <c r="H605" t="n">
         <v>12977</v>
@@ -17943,7 +17943,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G606" t="n">
-        <v>1.87544023990631</v>
+        <v>1.8754403591156</v>
       </c>
       <c r="H606" t="n">
         <v>311</v>
@@ -17972,7 +17972,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G607" t="n">
-        <v>1.87544023990631</v>
+        <v>1.8754403591156</v>
       </c>
       <c r="H607" t="n">
         <v>1604</v>
@@ -18001,7 +18001,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G608" t="n">
-        <v>1.87544023990631</v>
+        <v>1.8754403591156</v>
       </c>
       <c r="H608" t="n">
         <v>5380</v>
@@ -18030,7 +18030,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G609" t="n">
-        <v>1.8519971370697</v>
+        <v>1.85199725627899</v>
       </c>
       <c r="H609" t="n">
         <v>700</v>
@@ -18059,7 +18059,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G610" t="n">
-        <v>1.84418296813965</v>
+        <v>1.84418284893036</v>
       </c>
       <c r="H610" t="n">
         <v>4036</v>
@@ -18088,7 +18088,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G611" t="n">
-        <v>1.84418296813965</v>
+        <v>1.84418284893036</v>
       </c>
       <c r="H611" t="n">
         <v>937</v>
@@ -18146,7 +18146,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G613" t="n">
-        <v>1.78166806697845</v>
+        <v>1.78166818618774</v>
       </c>
       <c r="H613" t="n">
         <v>2844</v>
@@ -18175,7 +18175,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G614" t="n">
-        <v>1.79729664325714</v>
+        <v>1.79729688167572</v>
       </c>
       <c r="H614" t="n">
         <v>10850</v>
@@ -18262,7 +18262,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G617" t="n">
-        <v>1.87544023990631</v>
+        <v>1.8754403591156</v>
       </c>
       <c r="H617" t="n">
         <v>1865</v>
@@ -18291,7 +18291,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G618" t="n">
-        <v>1.84418296813965</v>
+        <v>1.84418284893036</v>
       </c>
       <c r="H618" t="n">
         <v>2111</v>
@@ -18320,7 +18320,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G619" t="n">
-        <v>1.89106893539429</v>
+        <v>1.891068816185</v>
       </c>
       <c r="H619" t="n">
         <v>4395</v>
@@ -18349,7 +18349,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G620" t="n">
-        <v>1.82073986530304</v>
+        <v>1.82073962688446</v>
       </c>
       <c r="H620" t="n">
         <v>2510</v>
@@ -18407,7 +18407,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G622" t="n">
-        <v>1.84418296813965</v>
+        <v>1.84418284893036</v>
       </c>
       <c r="H622" t="n">
         <v>1654</v>
@@ -18436,7 +18436,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G623" t="n">
-        <v>1.92232620716095</v>
+        <v>1.92232632637024</v>
       </c>
       <c r="H623" t="n">
         <v>678</v>
@@ -18494,7 +18494,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G625" t="n">
-        <v>1.91451215744019</v>
+        <v>1.9145120382309</v>
       </c>
       <c r="H625" t="n">
         <v>1010</v>
@@ -18552,7 +18552,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G627" t="n">
-        <v>1.82073986530304</v>
+        <v>1.82073962688446</v>
       </c>
       <c r="H627" t="n">
         <v>5337</v>
@@ -18581,7 +18581,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G628" t="n">
-        <v>1.8519971370697</v>
+        <v>1.85199725627899</v>
       </c>
       <c r="H628" t="n">
         <v>767</v>
@@ -18639,7 +18639,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G630" t="n">
-        <v>1.84418296813965</v>
+        <v>1.84418284893036</v>
       </c>
       <c r="H630" t="n">
         <v>470</v>
@@ -18668,7 +18668,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G631" t="n">
-        <v>1.79729664325714</v>
+        <v>1.79729688167572</v>
       </c>
       <c r="H631" t="n">
         <v>1387</v>
@@ -18697,7 +18697,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G632" t="n">
-        <v>1.76603937149048</v>
+        <v>1.76603949069977</v>
       </c>
       <c r="H632" t="n">
         <v>2150</v>
@@ -18726,7 +18726,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G633" t="n">
-        <v>1.76603937149048</v>
+        <v>1.76603949069977</v>
       </c>
       <c r="H633" t="n">
         <v>0</v>
@@ -18755,7 +18755,7 @@
         <v>2.25</v>
       </c>
       <c r="G634" t="n">
-        <v>1.75822508335114</v>
+        <v>1.75822532176971</v>
       </c>
       <c r="H634" t="n">
         <v>3308</v>
@@ -18784,7 +18784,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G635" t="n">
-        <v>1.72696793079376</v>
+        <v>1.72696781158447</v>
       </c>
       <c r="H635" t="n">
         <v>2340</v>
@@ -18813,7 +18813,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G636" t="n">
-        <v>1.75041091442108</v>
+        <v>1.7504106760025</v>
       </c>
       <c r="H636" t="n">
         <v>116</v>
@@ -18842,7 +18842,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G637" t="n">
-        <v>1.78166806697845</v>
+        <v>1.78166818618774</v>
       </c>
       <c r="H637" t="n">
         <v>4216</v>
@@ -18871,7 +18871,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G638" t="n">
-        <v>1.82073986530304</v>
+        <v>1.82073962688446</v>
       </c>
       <c r="H638" t="n">
         <v>1300</v>
@@ -18900,7 +18900,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G639" t="n">
-        <v>1.73478221893311</v>
+        <v>1.73478209972382</v>
       </c>
       <c r="H639" t="n">
         <v>17652</v>
@@ -18929,7 +18929,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G640" t="n">
-        <v>1.71915364265442</v>
+        <v>1.71915352344513</v>
       </c>
       <c r="H640" t="n">
         <v>7930</v>
@@ -18958,7 +18958,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G641" t="n">
-        <v>1.71915364265442</v>
+        <v>1.71915352344513</v>
       </c>
       <c r="H641" t="n">
         <v>7808</v>
@@ -18987,7 +18987,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G642" t="n">
-        <v>1.75041091442108</v>
+        <v>1.7504106760025</v>
       </c>
       <c r="H642" t="n">
         <v>870</v>
@@ -19016,7 +19016,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G643" t="n">
-        <v>1.71915364265442</v>
+        <v>1.71915352344513</v>
       </c>
       <c r="H643" t="n">
         <v>3579</v>
@@ -19045,7 +19045,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G644" t="n">
-        <v>1.74259662628174</v>
+        <v>1.74259638786316</v>
       </c>
       <c r="H644" t="n">
         <v>1986</v>
@@ -19074,7 +19074,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G645" t="n">
-        <v>1.71915364265442</v>
+        <v>1.71915352344513</v>
       </c>
       <c r="H645" t="n">
         <v>380</v>
@@ -19103,7 +19103,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G646" t="n">
-        <v>1.71915364265442</v>
+        <v>1.71915352344513</v>
       </c>
       <c r="H646" t="n">
         <v>7131</v>
@@ -19132,7 +19132,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G647" t="n">
-        <v>1.71915364265442</v>
+        <v>1.71915352344513</v>
       </c>
       <c r="H647" t="n">
         <v>1204</v>
@@ -19161,7 +19161,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G648" t="n">
-        <v>1.71915364265442</v>
+        <v>1.71915352344513</v>
       </c>
       <c r="H648" t="n">
         <v>4223</v>
@@ -19190,7 +19190,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G649" t="n">
-        <v>1.70352482795715</v>
+        <v>1.70352494716644</v>
       </c>
       <c r="H649" t="n">
         <v>1910</v>
@@ -19219,7 +19219,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G650" t="n">
-        <v>1.71915364265442</v>
+        <v>1.71915352344513</v>
       </c>
       <c r="H650" t="n">
         <v>1700</v>
@@ -19248,7 +19248,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G651" t="n">
-        <v>1.68008196353912</v>
+        <v>1.68008184432983</v>
       </c>
       <c r="H651" t="n">
         <v>2312</v>
@@ -19277,7 +19277,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G652" t="n">
-        <v>1.68008196353912</v>
+        <v>1.68008184432983</v>
       </c>
       <c r="H652" t="n">
         <v>3142</v>
@@ -19364,7 +19364,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G655" t="n">
-        <v>1.61756706237793</v>
+        <v>1.61756718158722</v>
       </c>
       <c r="H655" t="n">
         <v>2957</v>
@@ -19393,7 +19393,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G656" t="n">
-        <v>1.61756706237793</v>
+        <v>1.61756718158722</v>
       </c>
       <c r="H656" t="n">
         <v>4076</v>
@@ -19422,7 +19422,7 @@
         <v>2</v>
       </c>
       <c r="G657" t="n">
-        <v>1.56286692619324</v>
+        <v>1.56286680698395</v>
       </c>
       <c r="H657" t="n">
         <v>7242</v>
@@ -19567,7 +19567,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G662" t="n">
-        <v>1.60975277423859</v>
+        <v>1.60975289344788</v>
       </c>
       <c r="H662" t="n">
         <v>1581</v>
@@ -19654,7 +19654,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G665" t="n">
-        <v>2.06298398971558</v>
+        <v>2.06298422813416</v>
       </c>
       <c r="H665" t="n">
         <v>130384</v>
@@ -19683,7 +19683,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G666" t="n">
-        <v>1.92232620716095</v>
+        <v>1.92232632637024</v>
       </c>
       <c r="H666" t="n">
         <v>446846</v>
@@ -19770,7 +19770,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G669" t="n">
-        <v>1.92232620716095</v>
+        <v>1.92232632637024</v>
       </c>
       <c r="H669" t="n">
         <v>32286</v>
@@ -19857,7 +19857,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G672" t="n">
-        <v>1.89888310432434</v>
+        <v>1.89888322353363</v>
       </c>
       <c r="H672" t="n">
         <v>10847</v>
@@ -19886,7 +19886,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G673" t="n">
-        <v>1.92232620716095</v>
+        <v>1.92232632637024</v>
       </c>
       <c r="H673" t="n">
         <v>37391</v>
@@ -19944,7 +19944,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G675" t="n">
-        <v>1.89106893539429</v>
+        <v>1.891068816185</v>
       </c>
       <c r="H675" t="n">
         <v>16914</v>
@@ -19973,7 +19973,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G676" t="n">
-        <v>1.91451215744019</v>
+        <v>1.9145120382309</v>
       </c>
       <c r="H676" t="n">
         <v>18044</v>
@@ -20031,7 +20031,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G678" t="n">
-        <v>1.82855403423309</v>
+        <v>1.8285539150238</v>
       </c>
       <c r="H678" t="n">
         <v>7847</v>
@@ -20089,7 +20089,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G680" t="n">
-        <v>1.82855403423309</v>
+        <v>1.8285539150238</v>
       </c>
       <c r="H680" t="n">
         <v>4199</v>
@@ -20118,7 +20118,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G681" t="n">
-        <v>1.76603937149048</v>
+        <v>1.76603949069977</v>
       </c>
       <c r="H681" t="n">
         <v>6126</v>
@@ -20147,7 +20147,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G682" t="n">
-        <v>1.70352482795715</v>
+        <v>1.70352494716644</v>
       </c>
       <c r="H682" t="n">
         <v>21460</v>
@@ -20176,7 +20176,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G683" t="n">
-        <v>1.91451215744019</v>
+        <v>1.9145120382309</v>
       </c>
       <c r="H683" t="n">
         <v>82840</v>
@@ -20205,7 +20205,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G684" t="n">
-        <v>1.82073986530304</v>
+        <v>1.82073962688446</v>
       </c>
       <c r="H684" t="n">
         <v>79297</v>
@@ -20234,7 +20234,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G685" t="n">
-        <v>1.76603937149048</v>
+        <v>1.76603949069977</v>
       </c>
       <c r="H685" t="n">
         <v>13837</v>
@@ -20263,7 +20263,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G686" t="n">
-        <v>1.78166806697845</v>
+        <v>1.78166818618774</v>
       </c>
       <c r="H686" t="n">
         <v>16568</v>
@@ -20292,7 +20292,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G687" t="n">
-        <v>1.76603937149048</v>
+        <v>1.76603949069977</v>
       </c>
       <c r="H687" t="n">
         <v>11052</v>
@@ -20321,7 +20321,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G688" t="n">
-        <v>1.76603937149048</v>
+        <v>1.76603949069977</v>
       </c>
       <c r="H688" t="n">
         <v>8342</v>
@@ -20350,7 +20350,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G689" t="n">
-        <v>1.78166806697845</v>
+        <v>1.78166818618774</v>
       </c>
       <c r="H689" t="n">
         <v>4504</v>
@@ -20379,7 +20379,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G690" t="n">
-        <v>1.75041091442108</v>
+        <v>1.7504106760025</v>
       </c>
       <c r="H690" t="n">
         <v>2392</v>
@@ -20408,7 +20408,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G691" t="n">
-        <v>1.71915364265442</v>
+        <v>1.71915352344513</v>
       </c>
       <c r="H691" t="n">
         <v>22928</v>
@@ -20437,7 +20437,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G692" t="n">
-        <v>1.70352482795715</v>
+        <v>1.70352494716644</v>
       </c>
       <c r="H692" t="n">
         <v>29415</v>
@@ -20524,7 +20524,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G695" t="n">
-        <v>1.64882445335388</v>
+        <v>1.64882433414459</v>
       </c>
       <c r="H695" t="n">
         <v>5710</v>
@@ -20553,7 +20553,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G696" t="n">
-        <v>1.67226755619049</v>
+        <v>1.67226767539978</v>
       </c>
       <c r="H696" t="n">
         <v>11489</v>
@@ -20582,7 +20582,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G697" t="n">
-        <v>1.68008196353912</v>
+        <v>1.68008184432983</v>
       </c>
       <c r="H697" t="n">
         <v>5973</v>
@@ -20611,7 +20611,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G698" t="n">
-        <v>1.68008196353912</v>
+        <v>1.68008184432983</v>
       </c>
       <c r="H698" t="n">
         <v>6783</v>
@@ -20640,7 +20640,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G699" t="n">
-        <v>1.74259662628174</v>
+        <v>1.74259638786316</v>
       </c>
       <c r="H699" t="n">
         <v>125437</v>
@@ -20669,7 +20669,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G700" t="n">
-        <v>1.78166806697845</v>
+        <v>1.78166818618774</v>
       </c>
       <c r="H700" t="n">
         <v>16469</v>
@@ -20698,7 +20698,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G701" t="n">
-        <v>1.70352482795715</v>
+        <v>1.70352494716644</v>
       </c>
       <c r="H701" t="n">
         <v>20038</v>
@@ -20727,7 +20727,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G702" t="n">
-        <v>1.69571042060852</v>
+        <v>1.6957106590271</v>
       </c>
       <c r="H702" t="n">
         <v>42863</v>
@@ -20756,7 +20756,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G703" t="n">
-        <v>1.64882445335388</v>
+        <v>1.64882433414459</v>
       </c>
       <c r="H703" t="n">
         <v>2626</v>
@@ -20814,7 +20814,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G705" t="n">
-        <v>1.69571042060852</v>
+        <v>1.6957106590271</v>
       </c>
       <c r="H705" t="n">
         <v>9685</v>
@@ -20843,7 +20843,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G706" t="n">
-        <v>1.68789613246918</v>
+        <v>1.68789625167847</v>
       </c>
       <c r="H706" t="n">
         <v>4340</v>
@@ -20930,7 +20930,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G709" t="n">
-        <v>1.68789613246918</v>
+        <v>1.68789625167847</v>
       </c>
       <c r="H709" t="n">
         <v>23100</v>
@@ -20988,7 +20988,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G711" t="n">
-        <v>1.68008196353912</v>
+        <v>1.68008184432983</v>
       </c>
       <c r="H711" t="n">
         <v>1343</v>
@@ -21017,7 +21017,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G712" t="n">
-        <v>1.68008196353912</v>
+        <v>1.68008184432983</v>
       </c>
       <c r="H712" t="n">
         <v>1105</v>
@@ -21104,7 +21104,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G715" t="n">
-        <v>1.61756706237793</v>
+        <v>1.61756718158722</v>
       </c>
       <c r="H715" t="n">
         <v>5893</v>
@@ -21133,7 +21133,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G716" t="n">
-        <v>1.61756706237793</v>
+        <v>1.61756718158722</v>
       </c>
       <c r="H716" t="n">
         <v>15324</v>
@@ -21191,7 +21191,7 @@
         <v>2</v>
       </c>
       <c r="G718" t="n">
-        <v>1.56286692619324</v>
+        <v>1.56286680698395</v>
       </c>
       <c r="H718" t="n">
         <v>6637</v>
@@ -21220,7 +21220,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G719" t="n">
-        <v>1.54723811149597</v>
+        <v>1.54723823070526</v>
       </c>
       <c r="H719" t="n">
         <v>9044</v>
@@ -21278,7 +21278,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G721" t="n">
-        <v>1.54723811149597</v>
+        <v>1.54723823070526</v>
       </c>
       <c r="H721" t="n">
         <v>4279</v>
@@ -21307,7 +21307,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G722" t="n">
-        <v>1.61756706237793</v>
+        <v>1.61756718158722</v>
       </c>
       <c r="H722" t="n">
         <v>3905</v>
@@ -21568,7 +21568,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G731" t="n">
-        <v>1.54723811149597</v>
+        <v>1.54723823070526</v>
       </c>
       <c r="H731" t="n">
         <v>2640</v>
@@ -21626,7 +21626,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G733" t="n">
-        <v>1.54723811149597</v>
+        <v>1.54723823070526</v>
       </c>
       <c r="H733" t="n">
         <v>10612</v>
@@ -21655,7 +21655,7 @@
         <v>2</v>
       </c>
       <c r="G734" t="n">
-        <v>1.56286692619324</v>
+        <v>1.56286680698395</v>
       </c>
       <c r="H734" t="n">
         <v>1000</v>
@@ -21713,7 +21713,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G736" t="n">
-        <v>1.53160953521729</v>
+        <v>1.531609416008</v>
       </c>
       <c r="H736" t="n">
         <v>1180</v>
@@ -21771,7 +21771,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G738" t="n">
-        <v>1.50035214424133</v>
+        <v>1.50035226345062</v>
       </c>
       <c r="H738" t="n">
         <v>3783</v>
@@ -21829,7 +21829,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G740" t="n">
-        <v>1.53160953521729</v>
+        <v>1.531609416008</v>
       </c>
       <c r="H740" t="n">
         <v>1201</v>
@@ -21858,7 +21858,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G741" t="n">
-        <v>1.50035214424133</v>
+        <v>1.50035226345062</v>
       </c>
       <c r="H741" t="n">
         <v>1657</v>
@@ -21916,7 +21916,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G743" t="n">
-        <v>1.60975277423859</v>
+        <v>1.60975289344788</v>
       </c>
       <c r="H743" t="n">
         <v>83441</v>
@@ -21974,7 +21974,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G745" t="n">
-        <v>1.54723811149597</v>
+        <v>1.54723823070526</v>
       </c>
       <c r="H745" t="n">
         <v>6604</v>
@@ -22148,7 +22148,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G751" t="n">
-        <v>1.57849538326263</v>
+        <v>1.57849550247192</v>
       </c>
       <c r="H751" t="n">
         <v>40</v>
@@ -22177,7 +22177,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G752" t="n">
-        <v>1.52379500865936</v>
+        <v>1.52379524707794</v>
       </c>
       <c r="H752" t="n">
         <v>2112</v>
@@ -22206,7 +22206,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G753" t="n">
-        <v>1.52379500865936</v>
+        <v>1.52379524707794</v>
       </c>
       <c r="H753" t="n">
         <v>2730</v>
@@ -22235,7 +22235,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G754" t="n">
-        <v>1.52379500865936</v>
+        <v>1.52379524707794</v>
       </c>
       <c r="H754" t="n">
         <v>116</v>
@@ -22264,7 +22264,7 @@
         <v>2</v>
       </c>
       <c r="G755" t="n">
-        <v>1.56286692619324</v>
+        <v>1.56286680698395</v>
       </c>
       <c r="H755" t="n">
         <v>4200</v>
@@ -22467,7 +22467,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G762" t="n">
-        <v>1.47690904140472</v>
+        <v>1.47690916061401</v>
       </c>
       <c r="H762" t="n">
         <v>4134</v>
@@ -22554,7 +22554,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G765" t="n">
-        <v>1.74259662628174</v>
+        <v>1.74259638786316</v>
       </c>
       <c r="H765" t="n">
         <v>62191</v>
@@ -22815,7 +22815,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G774" t="n">
-        <v>1.57849538326263</v>
+        <v>1.57849550247192</v>
       </c>
       <c r="H774" t="n">
         <v>305</v>
@@ -22873,7 +22873,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G776" t="n">
-        <v>1.53160953521729</v>
+        <v>1.531609416008</v>
       </c>
       <c r="H776" t="n">
         <v>5415</v>
@@ -22960,7 +22960,7 @@
         <v>2</v>
       </c>
       <c r="G779" t="n">
-        <v>1.56286692619324</v>
+        <v>1.56286680698395</v>
       </c>
       <c r="H779" t="n">
         <v>770</v>
@@ -22989,7 +22989,7 @@
         <v>2</v>
       </c>
       <c r="G780" t="n">
-        <v>1.56286692619324</v>
+        <v>1.56286680698395</v>
       </c>
       <c r="H780" t="n">
         <v>1385</v>
@@ -23047,7 +23047,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G782" t="n">
-        <v>1.53160953521729</v>
+        <v>1.531609416008</v>
       </c>
       <c r="H782" t="n">
         <v>5650</v>
@@ -23076,7 +23076,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G783" t="n">
-        <v>1.53160953521729</v>
+        <v>1.531609416008</v>
       </c>
       <c r="H783" t="n">
         <v>9208</v>
@@ -23105,7 +23105,7 @@
         <v>2</v>
       </c>
       <c r="G784" t="n">
-        <v>1.56286692619324</v>
+        <v>1.56286680698395</v>
       </c>
       <c r="H784" t="n">
         <v>1630</v>
@@ -23134,7 +23134,7 @@
         <v>2</v>
       </c>
       <c r="G785" t="n">
-        <v>1.56286692619324</v>
+        <v>1.56286680698395</v>
       </c>
       <c r="H785" t="n">
         <v>3493</v>
@@ -23221,7 +23221,7 @@
         <v>2</v>
       </c>
       <c r="G788" t="n">
-        <v>1.56286692619324</v>
+        <v>1.56286680698395</v>
       </c>
       <c r="H788" t="n">
         <v>400</v>
@@ -23250,7 +23250,7 @@
         <v>2</v>
       </c>
       <c r="G789" t="n">
-        <v>1.56286692619324</v>
+        <v>1.56286680698395</v>
       </c>
       <c r="H789" t="n">
         <v>540</v>
@@ -23308,7 +23308,7 @@
         <v>2</v>
       </c>
       <c r="G791" t="n">
-        <v>1.56286692619324</v>
+        <v>1.56286680698395</v>
       </c>
       <c r="H791" t="n">
         <v>88</v>
@@ -23337,7 +23337,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G792" t="n">
-        <v>1.54723811149597</v>
+        <v>1.54723823070526</v>
       </c>
       <c r="H792" t="n">
         <v>3760</v>
@@ -23366,7 +23366,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G793" t="n">
-        <v>1.54723811149597</v>
+        <v>1.54723823070526</v>
       </c>
       <c r="H793" t="n">
         <v>1646</v>
@@ -23395,7 +23395,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G794" t="n">
-        <v>1.54723811149597</v>
+        <v>1.54723823070526</v>
       </c>
       <c r="H794" t="n">
         <v>3700</v>
@@ -23424,7 +23424,7 @@
         <v>2</v>
       </c>
       <c r="G795" t="n">
-        <v>1.56286692619324</v>
+        <v>1.56286680698395</v>
       </c>
       <c r="H795" t="n">
         <v>8735</v>
@@ -23453,7 +23453,7 @@
         <v>2</v>
       </c>
       <c r="G796" t="n">
-        <v>1.56286692619324</v>
+        <v>1.56286680698395</v>
       </c>
       <c r="H796" t="n">
         <v>8350</v>
@@ -23511,7 +23511,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G798" t="n">
-        <v>1.57849538326263</v>
+        <v>1.57849550247192</v>
       </c>
       <c r="H798" t="n">
         <v>382</v>
@@ -23598,7 +23598,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G801" t="n">
-        <v>1.54723811149597</v>
+        <v>1.54723823070526</v>
       </c>
       <c r="H801" t="n">
         <v>4800</v>
@@ -23685,7 +23685,7 @@
         <v>2</v>
       </c>
       <c r="G804" t="n">
-        <v>1.56286692619324</v>
+        <v>1.56286680698395</v>
       </c>
       <c r="H804" t="n">
         <v>715</v>
@@ -23772,7 +23772,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G807" t="n">
-        <v>1.60975277423859</v>
+        <v>1.60975289344788</v>
       </c>
       <c r="H807" t="n">
         <v>6800</v>
@@ -23830,7 +23830,7 @@
         <v>2</v>
       </c>
       <c r="G809" t="n">
-        <v>1.56286692619324</v>
+        <v>1.56286680698395</v>
       </c>
       <c r="H809" t="n">
         <v>100</v>
@@ -23859,7 +23859,7 @@
         <v>2</v>
       </c>
       <c r="G810" t="n">
-        <v>1.56286692619324</v>
+        <v>1.56286680698395</v>
       </c>
       <c r="H810" t="n">
         <v>2902</v>
@@ -23946,7 +23946,7 @@
         <v>2</v>
       </c>
       <c r="G813" t="n">
-        <v>1.56286692619324</v>
+        <v>1.56286680698395</v>
       </c>
       <c r="H813" t="n">
         <v>3779</v>
@@ -24004,7 +24004,7 @@
         <v>2</v>
       </c>
       <c r="G815" t="n">
-        <v>1.56286692619324</v>
+        <v>1.56286680698395</v>
       </c>
       <c r="H815" t="n">
         <v>4107</v>
@@ -24033,7 +24033,7 @@
         <v>2</v>
       </c>
       <c r="G816" t="n">
-        <v>1.56286692619324</v>
+        <v>1.56286680698395</v>
       </c>
       <c r="H816" t="n">
         <v>8835</v>
@@ -24062,7 +24062,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G817" t="n">
-        <v>1.68008196353912</v>
+        <v>1.68008184432983</v>
       </c>
       <c r="H817" t="n">
         <v>78580</v>
@@ -24091,7 +24091,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G818" t="n">
-        <v>1.60975277423859</v>
+        <v>1.60975289344788</v>
       </c>
       <c r="H818" t="n">
         <v>32403</v>
@@ -24207,7 +24207,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G822" t="n">
-        <v>1.61756706237793</v>
+        <v>1.61756718158722</v>
       </c>
       <c r="H822" t="n">
         <v>271</v>
@@ -24236,7 +24236,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G823" t="n">
-        <v>1.57849538326263</v>
+        <v>1.57849550247192</v>
       </c>
       <c r="H823" t="n">
         <v>2086</v>
@@ -24265,7 +24265,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G824" t="n">
-        <v>1.57849538326263</v>
+        <v>1.57849550247192</v>
       </c>
       <c r="H824" t="n">
         <v>3797</v>
@@ -24381,7 +24381,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G828" t="n">
-        <v>1.89106893539429</v>
+        <v>1.891068816185</v>
       </c>
       <c r="H828" t="n">
         <v>164712</v>
@@ -24410,7 +24410,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G829" t="n">
-        <v>1.73478221893311</v>
+        <v>1.73478209972382</v>
       </c>
       <c r="H829" t="n">
         <v>220051</v>
@@ -24439,7 +24439,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G830" t="n">
-        <v>1.67226755619049</v>
+        <v>1.67226767539978</v>
       </c>
       <c r="H830" t="n">
         <v>111394</v>
@@ -24526,7 +24526,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G833" t="n">
-        <v>1.67226755619049</v>
+        <v>1.67226767539978</v>
       </c>
       <c r="H833" t="n">
         <v>47937</v>
@@ -24584,7 +24584,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G835" t="n">
-        <v>1.60975277423859</v>
+        <v>1.60975289344788</v>
       </c>
       <c r="H835" t="n">
         <v>57779</v>
@@ -24642,7 +24642,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G837" t="n">
-        <v>1.67226755619049</v>
+        <v>1.67226767539978</v>
       </c>
       <c r="H837" t="n">
         <v>57119</v>
@@ -24671,7 +24671,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G838" t="n">
-        <v>1.67226755619049</v>
+        <v>1.67226767539978</v>
       </c>
       <c r="H838" t="n">
         <v>46771</v>
@@ -24816,7 +24816,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G843" t="n">
-        <v>1.57849538326263</v>
+        <v>1.57849550247192</v>
       </c>
       <c r="H843" t="n">
         <v>5516</v>
@@ -24845,7 +24845,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G844" t="n">
-        <v>1.60975277423859</v>
+        <v>1.60975289344788</v>
       </c>
       <c r="H844" t="n">
         <v>39333</v>
@@ -24903,7 +24903,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G846" t="n">
-        <v>1.60975277423859</v>
+        <v>1.60975289344788</v>
       </c>
       <c r="H846" t="n">
         <v>9208</v>
@@ -24961,7 +24961,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G848" t="n">
-        <v>1.60975277423859</v>
+        <v>1.60975289344788</v>
       </c>
       <c r="H848" t="n">
         <v>10001</v>
@@ -25048,7 +25048,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G851" t="n">
-        <v>1.57849538326263</v>
+        <v>1.57849550247192</v>
       </c>
       <c r="H851" t="n">
         <v>3006</v>
@@ -25077,7 +25077,7 @@
         <v>2</v>
       </c>
       <c r="G852" t="n">
-        <v>1.56286692619324</v>
+        <v>1.56286680698395</v>
       </c>
       <c r="H852" t="n">
         <v>14569</v>
@@ -25106,7 +25106,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G853" t="n">
-        <v>1.53160953521729</v>
+        <v>1.531609416008</v>
       </c>
       <c r="H853" t="n">
         <v>9826</v>
@@ -25164,7 +25164,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G855" t="n">
-        <v>1.53160953521729</v>
+        <v>1.531609416008</v>
       </c>
       <c r="H855" t="n">
         <v>30431</v>
@@ -25193,7 +25193,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G856" t="n">
-        <v>1.54723811149597</v>
+        <v>1.54723823070526</v>
       </c>
       <c r="H856" t="n">
         <v>6091</v>
@@ -25222,7 +25222,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G857" t="n">
-        <v>1.53160953521729</v>
+        <v>1.531609416008</v>
       </c>
       <c r="H857" t="n">
         <v>8665</v>
@@ -25280,7 +25280,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G859" t="n">
-        <v>1.57849538326263</v>
+        <v>1.57849550247192</v>
       </c>
       <c r="H859" t="n">
         <v>7873</v>
@@ -25309,7 +25309,7 @@
         <v>2</v>
       </c>
       <c r="G860" t="n">
-        <v>1.56286692619324</v>
+        <v>1.56286680698395</v>
       </c>
       <c r="H860" t="n">
         <v>500</v>
@@ -25338,7 +25338,7 @@
         <v>2</v>
       </c>
       <c r="G861" t="n">
-        <v>1.56286692619324</v>
+        <v>1.56286680698395</v>
       </c>
       <c r="H861" t="n">
         <v>0</v>
@@ -25454,7 +25454,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G865" t="n">
-        <v>1.50035214424133</v>
+        <v>1.50035226345062</v>
       </c>
       <c r="H865" t="n">
         <v>6903</v>
@@ -25483,7 +25483,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G866" t="n">
-        <v>1.50035214424133</v>
+        <v>1.50035226345062</v>
       </c>
       <c r="H866" t="n">
         <v>8355</v>
@@ -25512,7 +25512,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G867" t="n">
-        <v>1.53160953521729</v>
+        <v>1.531609416008</v>
       </c>
       <c r="H867" t="n">
         <v>3500</v>
@@ -25541,7 +25541,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G868" t="n">
-        <v>1.46909487247467</v>
+        <v>1.46909475326538</v>
       </c>
       <c r="H868" t="n">
         <v>28560</v>
@@ -25570,7 +25570,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G869" t="n">
-        <v>1.4534660577774</v>
+        <v>1.45346617698669</v>
       </c>
       <c r="H869" t="n">
         <v>670</v>
@@ -25599,7 +25599,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G870" t="n">
-        <v>1.46909487247467</v>
+        <v>1.46909475326538</v>
       </c>
       <c r="H870" t="n">
         <v>3044</v>
@@ -25628,7 +25628,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G871" t="n">
-        <v>1.50035214424133</v>
+        <v>1.50035226345062</v>
       </c>
       <c r="H871" t="n">
         <v>1918</v>
@@ -25657,7 +25657,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G872" t="n">
-        <v>1.50035214424133</v>
+        <v>1.50035226345062</v>
       </c>
       <c r="H872" t="n">
         <v>0</v>
@@ -25686,7 +25686,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G873" t="n">
-        <v>1.46909487247467</v>
+        <v>1.46909475326538</v>
       </c>
       <c r="H873" t="n">
         <v>710</v>
@@ -25744,7 +25744,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G875" t="n">
-        <v>1.4534660577774</v>
+        <v>1.45346617698669</v>
       </c>
       <c r="H875" t="n">
         <v>7508</v>
@@ -25773,7 +25773,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G876" t="n">
-        <v>1.4534660577774</v>
+        <v>1.45346617698669</v>
       </c>
       <c r="H876" t="n">
         <v>800</v>
@@ -25831,7 +25831,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G878" t="n">
-        <v>1.53160953521729</v>
+        <v>1.531609416008</v>
       </c>
       <c r="H878" t="n">
         <v>2050</v>
@@ -25889,7 +25889,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G880" t="n">
-        <v>1.46909487247467</v>
+        <v>1.46909475326538</v>
       </c>
       <c r="H880" t="n">
         <v>22334</v>
@@ -25918,7 +25918,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G881" t="n">
-        <v>1.4534660577774</v>
+        <v>1.45346617698669</v>
       </c>
       <c r="H881" t="n">
         <v>880</v>
@@ -25947,7 +25947,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G882" t="n">
-        <v>1.43783748149872</v>
+        <v>1.43783760070801</v>
       </c>
       <c r="H882" t="n">
         <v>3065</v>
@@ -25976,7 +25976,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G883" t="n">
-        <v>1.4534660577774</v>
+        <v>1.45346617698669</v>
       </c>
       <c r="H883" t="n">
         <v>12670</v>
@@ -26005,7 +26005,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G884" t="n">
-        <v>1.4534660577774</v>
+        <v>1.45346617698669</v>
       </c>
       <c r="H884" t="n">
         <v>4516</v>
@@ -26034,7 +26034,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G885" t="n">
-        <v>1.43783748149872</v>
+        <v>1.43783760070801</v>
       </c>
       <c r="H885" t="n">
         <v>29</v>
@@ -26063,7 +26063,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G886" t="n">
-        <v>1.46909487247467</v>
+        <v>1.46909475326538</v>
       </c>
       <c r="H886" t="n">
         <v>4151</v>
@@ -26237,7 +26237,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G892" t="n">
-        <v>1.53160953521729</v>
+        <v>1.531609416008</v>
       </c>
       <c r="H892" t="n">
         <v>6177</v>
@@ -26324,7 +26324,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G895" t="n">
-        <v>1.53160953521729</v>
+        <v>1.531609416008</v>
       </c>
       <c r="H895" t="n">
         <v>4132</v>
@@ -26353,7 +26353,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G896" t="n">
-        <v>1.53160953521729</v>
+        <v>1.531609416008</v>
       </c>
       <c r="H896" t="n">
         <v>15658</v>
@@ -26382,7 +26382,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G897" t="n">
-        <v>1.54723811149597</v>
+        <v>1.54723823070526</v>
       </c>
       <c r="H897" t="n">
         <v>12400</v>
@@ -26411,7 +26411,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G898" t="n">
-        <v>1.50035214424133</v>
+        <v>1.50035226345062</v>
       </c>
       <c r="H898" t="n">
         <v>9001</v>
@@ -26440,7 +26440,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G899" t="n">
-        <v>1.50035214424133</v>
+        <v>1.50035226345062</v>
       </c>
       <c r="H899" t="n">
         <v>5729</v>
@@ -26469,7 +26469,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G900" t="n">
-        <v>1.50035214424133</v>
+        <v>1.50035226345062</v>
       </c>
       <c r="H900" t="n">
         <v>4094</v>
@@ -26498,7 +26498,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G901" t="n">
-        <v>1.54723811149597</v>
+        <v>1.54723823070526</v>
       </c>
       <c r="H901" t="n">
         <v>5238</v>
@@ -26585,7 +26585,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G904" t="n">
-        <v>1.53160953521729</v>
+        <v>1.531609416008</v>
       </c>
       <c r="H904" t="n">
         <v>2250</v>
@@ -26614,7 +26614,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G905" t="n">
-        <v>1.53160953521729</v>
+        <v>1.531609416008</v>
       </c>
       <c r="H905" t="n">
         <v>3080</v>
@@ -26643,7 +26643,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G906" t="n">
-        <v>1.50035214424133</v>
+        <v>1.50035226345062</v>
       </c>
       <c r="H906" t="n">
         <v>3380</v>
@@ -26672,7 +26672,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G907" t="n">
-        <v>1.50035214424133</v>
+        <v>1.50035226345062</v>
       </c>
       <c r="H907" t="n">
         <v>17682</v>
@@ -26759,7 +26759,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G910" t="n">
-        <v>1.50035214424133</v>
+        <v>1.50035226345062</v>
       </c>
       <c r="H910" t="n">
         <v>2535</v>
@@ -26846,7 +26846,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G913" t="n">
-        <v>1.50035214424133</v>
+        <v>1.50035226345062</v>
       </c>
       <c r="H913" t="n">
         <v>1205</v>
@@ -26933,7 +26933,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G916" t="n">
-        <v>1.50035214424133</v>
+        <v>1.50035226345062</v>
       </c>
       <c r="H916" t="n">
         <v>1650</v>
@@ -26962,7 +26962,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G917" t="n">
-        <v>1.50035214424133</v>
+        <v>1.50035226345062</v>
       </c>
       <c r="H917" t="n">
         <v>8100</v>
@@ -26991,7 +26991,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G918" t="n">
-        <v>1.46909487247467</v>
+        <v>1.46909475326538</v>
       </c>
       <c r="H918" t="n">
         <v>9855</v>
@@ -27020,7 +27020,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G919" t="n">
-        <v>1.4534660577774</v>
+        <v>1.45346617698669</v>
       </c>
       <c r="H919" t="n">
         <v>1440</v>
@@ -27049,7 +27049,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G920" t="n">
-        <v>1.4534660577774</v>
+        <v>1.45346617698669</v>
       </c>
       <c r="H920" t="n">
         <v>1744</v>
@@ -27107,7 +27107,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G922" t="n">
-        <v>1.46909487247467</v>
+        <v>1.46909475326538</v>
       </c>
       <c r="H922" t="n">
         <v>577</v>
@@ -27136,7 +27136,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G923" t="n">
-        <v>1.46909487247467</v>
+        <v>1.46909475326538</v>
       </c>
       <c r="H923" t="n">
         <v>1678</v>
@@ -27165,7 +27165,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G924" t="n">
-        <v>1.4534660577774</v>
+        <v>1.45346617698669</v>
       </c>
       <c r="H924" t="n">
         <v>2225</v>
@@ -27223,7 +27223,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G926" t="n">
-        <v>1.50035214424133</v>
+        <v>1.50035226345062</v>
       </c>
       <c r="H926" t="n">
         <v>3414</v>
@@ -27252,7 +27252,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G927" t="n">
-        <v>1.50035214424133</v>
+        <v>1.50035226345062</v>
       </c>
       <c r="H927" t="n">
         <v>60</v>
@@ -27281,7 +27281,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G928" t="n">
-        <v>1.4534660577774</v>
+        <v>1.45346617698669</v>
       </c>
       <c r="H928" t="n">
         <v>750</v>
@@ -27310,7 +27310,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G929" t="n">
-        <v>1.4534660577774</v>
+        <v>1.45346617698669</v>
       </c>
       <c r="H929" t="n">
         <v>800</v>
@@ -27397,7 +27397,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G932" t="n">
-        <v>1.46909487247467</v>
+        <v>1.46909475326538</v>
       </c>
       <c r="H932" t="n">
         <v>7581</v>
@@ -27426,7 +27426,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G933" t="n">
-        <v>1.50035214424133</v>
+        <v>1.50035226345062</v>
       </c>
       <c r="H933" t="n">
         <v>10800</v>
@@ -27455,7 +27455,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G934" t="n">
-        <v>1.46909487247467</v>
+        <v>1.46909475326538</v>
       </c>
       <c r="H934" t="n">
         <v>4422</v>
@@ -27629,7 +27629,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G940" t="n">
-        <v>1.50035214424133</v>
+        <v>1.50035226345062</v>
       </c>
       <c r="H940" t="n">
         <v>3395</v>
@@ -27658,7 +27658,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G941" t="n">
-        <v>1.53160953521729</v>
+        <v>1.531609416008</v>
       </c>
       <c r="H941" t="n">
         <v>62485</v>
@@ -27890,7 +27890,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G949" t="n">
-        <v>1.50035214424133</v>
+        <v>1.50035226345062</v>
       </c>
       <c r="H949" t="n">
         <v>2380</v>
@@ -27919,7 +27919,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G950" t="n">
-        <v>1.50035214424133</v>
+        <v>1.50035226345062</v>
       </c>
       <c r="H950" t="n">
         <v>1118</v>
@@ -27948,7 +27948,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G951" t="n">
-        <v>1.50035214424133</v>
+        <v>1.50035226345062</v>
       </c>
       <c r="H951" t="n">
         <v>2270</v>
@@ -27977,7 +27977,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G952" t="n">
-        <v>1.50035214424133</v>
+        <v>1.50035226345062</v>
       </c>
       <c r="H952" t="n">
         <v>3602</v>
@@ -28006,7 +28006,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G953" t="n">
-        <v>1.50035214424133</v>
+        <v>1.50035226345062</v>
       </c>
       <c r="H953" t="n">
         <v>4131</v>
@@ -28035,7 +28035,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G954" t="n">
-        <v>1.50035214424133</v>
+        <v>1.50035226345062</v>
       </c>
       <c r="H954" t="n">
         <v>7140</v>
@@ -28093,7 +28093,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G956" t="n">
-        <v>1.46909487247467</v>
+        <v>1.46909475326538</v>
       </c>
       <c r="H956" t="n">
         <v>14201</v>
@@ -28122,7 +28122,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G957" t="n">
-        <v>1.46909487247467</v>
+        <v>1.46909475326538</v>
       </c>
       <c r="H957" t="n">
         <v>24615</v>
@@ -28151,7 +28151,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G958" t="n">
-        <v>1.4534660577774</v>
+        <v>1.45346617698669</v>
       </c>
       <c r="H958" t="n">
         <v>5750</v>
@@ -28209,7 +28209,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G960" t="n">
-        <v>1.46909487247467</v>
+        <v>1.46909475326538</v>
       </c>
       <c r="H960" t="n">
         <v>61673</v>
@@ -28238,7 +28238,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G961" t="n">
-        <v>1.46909487247467</v>
+        <v>1.46909475326538</v>
       </c>
       <c r="H961" t="n">
         <v>5222</v>
@@ -28267,7 +28267,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G962" t="n">
-        <v>1.4534660577774</v>
+        <v>1.45346617698669</v>
       </c>
       <c r="H962" t="n">
         <v>10260</v>
@@ -28383,7 +28383,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G966" t="n">
-        <v>1.46909487247467</v>
+        <v>1.46909475326538</v>
       </c>
       <c r="H966" t="n">
         <v>10446</v>
@@ -28412,7 +28412,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G967" t="n">
-        <v>1.46909487247467</v>
+        <v>1.46909475326538</v>
       </c>
       <c r="H967" t="n">
         <v>320</v>
@@ -28441,7 +28441,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G968" t="n">
-        <v>1.46909487247467</v>
+        <v>1.46909475326538</v>
       </c>
       <c r="H968" t="n">
         <v>3588</v>
@@ -28470,7 +28470,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G969" t="n">
-        <v>1.43783748149872</v>
+        <v>1.43783760070801</v>
       </c>
       <c r="H969" t="n">
         <v>21430</v>
@@ -28499,7 +28499,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G970" t="n">
-        <v>1.43783748149872</v>
+        <v>1.43783760070801</v>
       </c>
       <c r="H970" t="n">
         <v>484</v>
@@ -28528,7 +28528,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G971" t="n">
-        <v>1.43783748149872</v>
+        <v>1.43783760070801</v>
       </c>
       <c r="H971" t="n">
         <v>1075</v>
@@ -28557,7 +28557,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G972" t="n">
-        <v>1.43783748149872</v>
+        <v>1.43783760070801</v>
       </c>
       <c r="H972" t="n">
         <v>500</v>
@@ -28615,7 +28615,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G974" t="n">
-        <v>1.4534660577774</v>
+        <v>1.45346617698669</v>
       </c>
       <c r="H974" t="n">
         <v>949</v>
@@ -28644,7 +28644,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G975" t="n">
-        <v>1.43783748149872</v>
+        <v>1.43783760070801</v>
       </c>
       <c r="H975" t="n">
         <v>2000</v>
@@ -28731,7 +28731,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G978" t="n">
-        <v>1.43783748149872</v>
+        <v>1.43783760070801</v>
       </c>
       <c r="H978" t="n">
         <v>4265</v>
@@ -28760,7 +28760,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G979" t="n">
-        <v>1.4534660577774</v>
+        <v>1.45346617698669</v>
       </c>
       <c r="H979" t="n">
         <v>16332</v>
@@ -28789,7 +28789,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G980" t="n">
-        <v>1.43783748149872</v>
+        <v>1.43783760070801</v>
       </c>
       <c r="H980" t="n">
         <v>560</v>
@@ -28818,7 +28818,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G981" t="n">
-        <v>1.43783748149872</v>
+        <v>1.43783760070801</v>
       </c>
       <c r="H981" t="n">
         <v>3315</v>
@@ -28847,7 +28847,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G982" t="n">
-        <v>1.4534660577774</v>
+        <v>1.45346617698669</v>
       </c>
       <c r="H982" t="n">
         <v>130</v>
@@ -28876,7 +28876,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G983" t="n">
-        <v>1.4534660577774</v>
+        <v>1.45346617698669</v>
       </c>
       <c r="H983" t="n">
         <v>51</v>
@@ -29021,7 +29021,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G988" t="n">
-        <v>1.43783748149872</v>
+        <v>1.43783760070801</v>
       </c>
       <c r="H988" t="n">
         <v>3235</v>
@@ -29079,7 +29079,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G990" t="n">
-        <v>1.43783748149872</v>
+        <v>1.43783760070801</v>
       </c>
       <c r="H990" t="n">
         <v>377</v>
@@ -29108,7 +29108,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G991" t="n">
-        <v>1.43783748149872</v>
+        <v>1.43783760070801</v>
       </c>
       <c r="H991" t="n">
         <v>1621</v>
@@ -29137,7 +29137,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G992" t="n">
-        <v>1.43783748149872</v>
+        <v>1.43783760070801</v>
       </c>
       <c r="H992" t="n">
         <v>4633</v>
@@ -29224,7 +29224,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G995" t="n">
-        <v>1.39095139503479</v>
+        <v>1.39095151424408</v>
       </c>
       <c r="H995" t="n">
         <v>4445</v>
@@ -29427,7 +29427,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G1002" t="n">
-        <v>1.43783748149872</v>
+        <v>1.43783760070801</v>
       </c>
       <c r="H1002" t="n">
         <v>29959</v>
@@ -29456,7 +29456,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1003" t="n">
-        <v>1.68789613246918</v>
+        <v>1.68789625167847</v>
       </c>
       <c r="H1003" t="n">
         <v>363297</v>
@@ -29485,7 +29485,7 @@
         <v>2</v>
       </c>
       <c r="G1004" t="n">
-        <v>1.56286692619324</v>
+        <v>1.56286680698395</v>
       </c>
       <c r="H1004" t="n">
         <v>526368</v>
@@ -29572,7 +29572,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G1007" t="n">
-        <v>1.46909487247467</v>
+        <v>1.46909475326538</v>
       </c>
       <c r="H1007" t="n">
         <v>168703</v>
@@ -29630,7 +29630,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G1009" t="n">
-        <v>1.4534660577774</v>
+        <v>1.45346617698669</v>
       </c>
       <c r="H1009" t="n">
         <v>16050</v>
@@ -29688,7 +29688,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G1011" t="n">
-        <v>1.4534660577774</v>
+        <v>1.45346617698669</v>
       </c>
       <c r="H1011" t="n">
         <v>39708</v>
@@ -29717,7 +29717,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G1012" t="n">
-        <v>1.43783748149872</v>
+        <v>1.43783760070801</v>
       </c>
       <c r="H1012" t="n">
         <v>26843</v>
@@ -29746,7 +29746,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G1013" t="n">
-        <v>1.43783748149872</v>
+        <v>1.43783760070801</v>
       </c>
       <c r="H1013" t="n">
         <v>8510</v>
@@ -29775,7 +29775,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G1014" t="n">
-        <v>1.46909487247467</v>
+        <v>1.46909475326538</v>
       </c>
       <c r="H1014" t="n">
         <v>11951</v>
@@ -29862,7 +29862,7 @@
         <v>1.80480003356934</v>
       </c>
       <c r="G1017" t="n">
-        <v>1.41033113002777</v>
+        <v>1.41033101081848</v>
       </c>
       <c r="H1017" t="n">
         <v>6419</v>
@@ -29891,7 +29891,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G1018" t="n">
-        <v>1.35969412326813</v>
+        <v>1.35969400405884</v>
       </c>
       <c r="H1018" t="n">
         <v>21467</v>
@@ -29920,7 +29920,7 @@
         <v>1.76600003242493</v>
       </c>
       <c r="G1019" t="n">
-        <v>1.38001132011414</v>
+        <v>1.38001143932343</v>
       </c>
       <c r="H1019" t="n">
         <v>61548</v>
@@ -29978,7 +29978,7 @@
         <v>1.77359998226166</v>
       </c>
       <c r="G1021" t="n">
-        <v>1.38595020771027</v>
+        <v>1.38595032691956</v>
       </c>
       <c r="H1021" t="n">
         <v>10862</v>
@@ -30007,7 +30007,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G1022" t="n">
-        <v>1.43002307415009</v>
+        <v>1.43002319335938</v>
       </c>
       <c r="H1022" t="n">
         <v>55375</v>
@@ -30036,7 +30036,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G1023" t="n">
-        <v>1.4143944978714</v>
+        <v>1.41439437866211</v>
       </c>
       <c r="H1023" t="n">
         <v>10822</v>
@@ -30210,7 +30210,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G1029" t="n">
-        <v>1.34406566619873</v>
+        <v>1.34406542778015</v>
       </c>
       <c r="H1029" t="n">
         <v>22344</v>
@@ -30297,7 +30297,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G1032" t="n">
-        <v>1.35187995433807</v>
+        <v>1.35187983512878</v>
       </c>
       <c r="H1032" t="n">
         <v>850</v>
@@ -30384,7 +30384,7 @@
         <v>1.68099999427795</v>
       </c>
       <c r="G1035" t="n">
-        <v>1.31358957290649</v>
+        <v>1.3135894536972</v>
       </c>
       <c r="H1035" t="n">
         <v>15612</v>
@@ -30413,7 +30413,7 @@
         <v>1.66919994354248</v>
       </c>
       <c r="G1036" t="n">
-        <v>1.30436849594116</v>
+        <v>1.30436861515045</v>
       </c>
       <c r="H1036" t="n">
         <v>37285</v>
@@ -30442,7 +30442,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G1037" t="n">
-        <v>1.28155088424683</v>
+        <v>1.28155076503754</v>
       </c>
       <c r="H1037" t="n">
         <v>4690</v>
@@ -30500,7 +30500,7 @@
         <v>1.57840001583099</v>
       </c>
       <c r="G1039" t="n">
-        <v>1.23341453075409</v>
+        <v>1.2334144115448</v>
       </c>
       <c r="H1039" t="n">
         <v>13283</v>
@@ -30558,7 +30558,7 @@
         <v>1.57720005512238</v>
       </c>
       <c r="G1041" t="n">
-        <v>1.23247683048248</v>
+        <v>1.23247671127319</v>
       </c>
       <c r="H1041" t="n">
         <v>45218</v>
@@ -30674,7 +30674,7 @@
         <v>1.62979996204376</v>
       </c>
       <c r="G1045" t="n">
-        <v>1.27358019351959</v>
+        <v>1.2735800743103</v>
       </c>
       <c r="H1045" t="n">
         <v>4325</v>
@@ -30703,7 +30703,7 @@
         <v>1.63779997825623</v>
       </c>
       <c r="G1046" t="n">
-        <v>1.27983152866364</v>
+        <v>1.27983164787292</v>
       </c>
       <c r="H1046" t="n">
         <v>22878</v>
@@ -30732,7 +30732,7 @@
         <v>1.66260004043579</v>
       </c>
       <c r="G1047" t="n">
-        <v>1.29921126365662</v>
+        <v>1.29921114444733</v>
       </c>
       <c r="H1047" t="n">
         <v>23626</v>
@@ -30819,7 +30819,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1050" t="n">
-        <v>1.30499374866486</v>
+        <v>1.30499386787415</v>
       </c>
       <c r="H1050" t="n">
         <v>5237</v>
@@ -30877,7 +30877,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1052" t="n">
-        <v>1.30499374866486</v>
+        <v>1.30499386787415</v>
       </c>
       <c r="H1052" t="n">
         <v>3328</v>
@@ -30964,7 +30964,7 @@
         <v>1.61479997634888</v>
       </c>
       <c r="G1055" t="n">
-        <v>1.26185858249664</v>
+        <v>1.26185870170593</v>
       </c>
       <c r="H1055" t="n">
         <v>3537</v>
@@ -31051,7 +31051,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G1058" t="n">
-        <v>1.17996430397034</v>
+        <v>1.17996442317963</v>
       </c>
       <c r="H1058" t="n">
         <v>26123</v>
@@ -31080,7 +31080,7 @@
         <v>1.55980002880096</v>
       </c>
       <c r="G1059" t="n">
-        <v>1.21887993812561</v>
+        <v>1.21887981891632</v>
       </c>
       <c r="H1059" t="n">
         <v>21083</v>
@@ -31109,7 +31109,7 @@
         <v>1.5</v>
       </c>
       <c r="G1060" t="n">
-        <v>1.17215001583099</v>
+        <v>1.17215013504028</v>
       </c>
       <c r="H1060" t="n">
         <v>1635</v>
@@ -31138,7 +31138,7 @@
         <v>1.49779999256134</v>
       </c>
       <c r="G1061" t="n">
-        <v>1.17043113708496</v>
+        <v>1.17043089866638</v>
       </c>
       <c r="H1061" t="n">
         <v>16113</v>
@@ -31196,7 +31196,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G1063" t="n">
-        <v>0.883019685745239</v>
+        <v>0.883019745349884</v>
       </c>
       <c r="H1063" t="n">
         <v>14800</v>
@@ -31225,7 +31225,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G1064" t="n">
-        <v>0.883019685745239</v>
+        <v>0.883019745349884</v>
       </c>
       <c r="H1064" t="n">
         <v>10076</v>
@@ -31254,7 +31254,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G1065" t="n">
-        <v>0.867391109466553</v>
+        <v>0.867391049861908</v>
       </c>
       <c r="H1065" t="n">
         <v>9626</v>
@@ -31283,7 +31283,7 @@
         <v>0.939999997615814</v>
       </c>
       <c r="G1066" t="n">
-        <v>0.734547436237335</v>
+        <v>0.73454737663269</v>
       </c>
       <c r="H1066" t="n">
         <v>21386</v>
@@ -31312,7 +31312,7 @@
         <v>0.997900009155273</v>
       </c>
       <c r="G1067" t="n">
-        <v>0.779792428016663</v>
+        <v>0.779792487621307</v>
       </c>
       <c r="H1067" t="n">
         <v>46633</v>
@@ -31341,7 +31341,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G1068" t="n">
-        <v>0.773619055747986</v>
+        <v>0.773619115352631</v>
       </c>
       <c r="H1068" t="n">
         <v>15083</v>
@@ -31370,7 +31370,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G1069" t="n">
-        <v>0.773619055747986</v>
+        <v>0.773619115352631</v>
       </c>
       <c r="H1069" t="n">
         <v>7200</v>
@@ -31399,7 +31399,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G1070" t="n">
-        <v>0.773619055747986</v>
+        <v>0.773619115352631</v>
       </c>
       <c r="H1070" t="n">
         <v>1500</v>
@@ -31428,7 +31428,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G1071" t="n">
-        <v>0.789247691631317</v>
+        <v>0.789247751235962</v>
       </c>
       <c r="H1071" t="n">
         <v>4000</v>
@@ -31457,7 +31457,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G1072" t="n">
-        <v>0.859576821327209</v>
+        <v>0.859576761722565</v>
       </c>
       <c r="H1072" t="n">
         <v>6459</v>
@@ -31486,7 +31486,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G1073" t="n">
-        <v>0.968977391719818</v>
+        <v>0.968977510929108</v>
       </c>
       <c r="H1073" t="n">
         <v>6985</v>
@@ -31544,7 +31544,7 @@
         <v>1.54499995708466</v>
       </c>
       <c r="G1075" t="n">
-        <v>1.20731461048126</v>
+        <v>1.20731449127197</v>
       </c>
       <c r="H1075" t="n">
         <v>70566</v>
@@ -31602,7 +31602,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G1077" t="n">
-        <v>1.24247896671295</v>
+        <v>1.24247920513153</v>
       </c>
       <c r="H1077" t="n">
         <v>15463</v>
@@ -31718,7 +31718,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G1081" t="n">
-        <v>1.21122181415558</v>
+        <v>1.21122169494629</v>
       </c>
       <c r="H1081" t="n">
         <v>11021</v>
@@ -31805,7 +31805,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G1084" t="n">
-        <v>1.25810790061951</v>
+        <v>1.25810778141022</v>
       </c>
       <c r="H1084" t="n">
         <v>29539</v>
@@ -31892,7 +31892,7 @@
         <v>1.52119994163513</v>
       </c>
       <c r="G1087" t="n">
-        <v>1.18871641159058</v>
+        <v>1.18871653079987</v>
       </c>
       <c r="H1087" t="n">
         <v>999</v>
@@ -31979,7 +31979,7 @@
         <v>1.56959998607635</v>
       </c>
       <c r="G1090" t="n">
-        <v>1.22653794288635</v>
+        <v>1.22653806209564</v>
       </c>
       <c r="H1090" t="n">
         <v>15691</v>
@@ -32008,7 +32008,7 @@
         <v>1.53519999980927</v>
       </c>
       <c r="G1091" t="n">
-        <v>1.19965660572052</v>
+        <v>1.19965648651123</v>
       </c>
       <c r="H1091" t="n">
         <v>7726</v>
@@ -32037,7 +32037,7 @@
         <v>1.51059997081757</v>
       </c>
       <c r="G1092" t="n">
-        <v>1.18043327331543</v>
+        <v>1.18043339252472</v>
       </c>
       <c r="H1092" t="n">
         <v>10176</v>
@@ -32066,7 +32066,7 @@
         <v>1.53840005397797</v>
       </c>
       <c r="G1093" t="n">
-        <v>1.20215702056885</v>
+        <v>1.20215725898743</v>
       </c>
       <c r="H1093" t="n">
         <v>6653</v>
@@ -32095,7 +32095,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G1094" t="n">
-        <v>1.14870715141296</v>
+        <v>1.14870703220367</v>
       </c>
       <c r="H1094" t="n">
         <v>23185</v>
@@ -32124,7 +32124,7 @@
         <v>1.42999994754791</v>
       </c>
       <c r="G1095" t="n">
-        <v>1.11744964122772</v>
+        <v>1.11744976043701</v>
       </c>
       <c r="H1095" t="n">
         <v>6692</v>
@@ -32153,7 +32153,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G1096" t="n">
-        <v>1.08619236946106</v>
+        <v>1.08619248867035</v>
       </c>
       <c r="H1096" t="n">
         <v>36445</v>
@@ -32182,7 +32182,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G1097" t="n">
-        <v>1.05493521690369</v>
+        <v>1.0549350976944</v>
       </c>
       <c r="H1097" t="n">
         <v>24618</v>
@@ -32211,7 +32211,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G1098" t="n">
-        <v>1.05493521690369</v>
+        <v>1.0549350976944</v>
       </c>
       <c r="H1098" t="n">
         <v>0</v>
@@ -32298,7 +32298,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G1101" t="n">
-        <v>1.06274950504303</v>
+        <v>1.06274938583374</v>
       </c>
       <c r="H1101" t="n">
         <v>17633</v>
@@ -32327,7 +32327,7 @@
         <v>1.44400000572205</v>
       </c>
       <c r="G1102" t="n">
-        <v>1.12838971614838</v>
+        <v>1.12838983535767</v>
       </c>
       <c r="H1102" t="n">
         <v>44823</v>
@@ -32443,7 +32443,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1106" t="n">
-        <v>1.04712069034576</v>
+        <v>1.04712080955505</v>
       </c>
       <c r="H1106" t="n">
         <v>11729</v>
@@ -32501,7 +32501,7 @@
         <v>1.30019998550415</v>
       </c>
       <c r="G1108" t="n">
-        <v>1.01601982116699</v>
+        <v>1.0160197019577</v>
       </c>
       <c r="H1108" t="n">
         <v>1305</v>
@@ -32559,7 +32559,7 @@
         <v>1.25279998779297</v>
       </c>
       <c r="G1110" t="n">
-        <v>0.978979766368866</v>
+        <v>0.978979706764221</v>
       </c>
       <c r="H1110" t="n">
         <v>24524</v>
@@ -32646,7 +32646,7 @@
         <v>1.23800003528595</v>
       </c>
       <c r="G1113" t="n">
-        <v>0.967414617538452</v>
+        <v>0.967414557933807</v>
       </c>
       <c r="H1113" t="n">
         <v>18476</v>
@@ -32704,7 +32704,7 @@
         <v>1.25</v>
       </c>
       <c r="G1115" t="n">
-        <v>0.976791799068451</v>
+        <v>0.976791739463806</v>
       </c>
       <c r="H1115" t="n">
         <v>34094</v>
@@ -32849,7 +32849,7 @@
         <v>1.2791999578476</v>
       </c>
       <c r="G1120" t="n">
-        <v>0.999609589576721</v>
+        <v>0.999609649181366</v>
       </c>
       <c r="H1120" t="n">
         <v>25760</v>
@@ -32878,7 +32878,7 @@
         <v>1.2771999835968</v>
       </c>
       <c r="G1121" t="n">
-        <v>0.998046696186066</v>
+        <v>0.998046636581421</v>
       </c>
       <c r="H1121" t="n">
         <v>64712</v>
@@ -32936,7 +32936,7 @@
         <v>1.31359994411469</v>
       </c>
       <c r="G1123" t="n">
-        <v>1.02649080753326</v>
+        <v>1.02649092674255</v>
       </c>
       <c r="H1123" t="n">
         <v>10857</v>
@@ -33110,7 +33110,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G1129" t="n">
-        <v>1.03149199485779</v>
+        <v>1.03149211406708</v>
       </c>
       <c r="H1129" t="n">
         <v>23471</v>
@@ -33139,7 +33139,7 @@
         <v>1.29579997062683</v>
       </c>
       <c r="G1130" t="n">
-        <v>1.01258134841919</v>
+        <v>1.01258146762848</v>
       </c>
       <c r="H1130" t="n">
         <v>34473</v>
@@ -33226,7 +33226,7 @@
         <v>1.29820001125336</v>
       </c>
       <c r="G1133" t="n">
-        <v>1.01445698738098</v>
+        <v>1.01445686817169</v>
       </c>
       <c r="H1133" t="n">
         <v>4011</v>
@@ -33255,7 +33255,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1134" t="n">
-        <v>1.04712069034576</v>
+        <v>1.04712080955505</v>
       </c>
       <c r="H1134" t="n">
         <v>6000</v>
@@ -33284,7 +33284,7 @@
         <v>1.2960000038147</v>
       </c>
       <c r="G1135" t="n">
-        <v>1.01273763179779</v>
+        <v>1.01273787021637</v>
       </c>
       <c r="H1135" t="n">
         <v>2329</v>
@@ -33313,7 +33313,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G1136" t="n">
-        <v>1.03149199485779</v>
+        <v>1.03149211406708</v>
       </c>
       <c r="H1136" t="n">
         <v>3100</v>
@@ -33487,7 +33487,7 @@
         <v>1.29200005531311</v>
       </c>
       <c r="G1142" t="n">
-        <v>1.00961208343506</v>
+        <v>1.00961196422577</v>
       </c>
       <c r="H1142" t="n">
         <v>1000</v>
@@ -33516,7 +33516,7 @@
         <v>1.30900001525879</v>
       </c>
       <c r="G1143" t="n">
-        <v>1.02289628982544</v>
+        <v>1.02289640903473</v>
       </c>
       <c r="H1143" t="n">
         <v>1000</v>
@@ -33545,7 +33545,7 @@
         <v>1.30499994754791</v>
       </c>
       <c r="G1144" t="n">
-        <v>1.01977074146271</v>
+        <v>1.01977050304413</v>
       </c>
       <c r="H1144" t="n">
         <v>3677</v>
@@ -33632,7 +33632,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1147" t="n">
-        <v>0.992420375347137</v>
+        <v>0.992420315742493</v>
       </c>
       <c r="H1147" t="n">
         <v>5704</v>
@@ -33690,7 +33690,7 @@
         <v>1.26240003108978</v>
       </c>
       <c r="G1149" t="n">
-        <v>0.986481547355652</v>
+        <v>0.986481666564941</v>
       </c>
       <c r="H1149" t="n">
         <v>8000</v>
@@ -33748,7 +33748,7 @@
         <v>1.29299998283386</v>
       </c>
       <c r="G1151" t="n">
-        <v>1.01039338111877</v>
+        <v>1.01039350032806</v>
       </c>
       <c r="H1151" t="n">
         <v>4302</v>
@@ -33777,7 +33777,7 @@
         <v>1.29180002212524</v>
       </c>
       <c r="G1152" t="n">
-        <v>1.00945568084717</v>
+        <v>1.00945580005646</v>
       </c>
       <c r="H1152" t="n">
         <v>8200</v>
@@ -33806,7 +33806,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1153" t="n">
-        <v>0.992420375347137</v>
+        <v>0.992420315742493</v>
       </c>
       <c r="H1153" t="n">
         <v>2410</v>
@@ -33835,7 +33835,7 @@
         <v>1.25440001487732</v>
       </c>
       <c r="G1154" t="n">
-        <v>0.980230212211609</v>
+        <v>0.980230093002319</v>
       </c>
       <c r="H1154" t="n">
         <v>5500</v>
@@ -33864,7 +33864,7 @@
         <v>1.28880000114441</v>
       </c>
       <c r="G1155" t="n">
-        <v>1.00711131095886</v>
+        <v>1.00711143016815</v>
       </c>
       <c r="H1155" t="n">
         <v>5122</v>
@@ -33893,7 +33893,7 @@
         <v>1.26199996471405</v>
       </c>
       <c r="G1156" t="n">
-        <v>0.98616886138916</v>
+        <v>0.98616898059845</v>
       </c>
       <c r="H1156" t="n">
         <v>9776</v>
@@ -33922,7 +33922,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G1157" t="n">
-        <v>1.02367770671844</v>
+        <v>1.02367758750916</v>
       </c>
       <c r="H1157" t="n">
         <v>40638</v>
@@ -33951,7 +33951,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G1158" t="n">
-        <v>1.03149199485779</v>
+        <v>1.03149211406708</v>
       </c>
       <c r="H1158" t="n">
         <v>25837</v>
@@ -33980,7 +33980,7 @@
         <v>1.29499995708466</v>
       </c>
       <c r="G1159" t="n">
-        <v>1.01195621490479</v>
+        <v>1.01195633411407</v>
       </c>
       <c r="H1159" t="n">
         <v>21359</v>
@@ -34038,7 +34038,7 @@
         <v>1.28939998149872</v>
       </c>
       <c r="G1161" t="n">
-        <v>1.00758016109467</v>
+        <v>1.00758039951324</v>
       </c>
       <c r="H1161" t="n">
         <v>160</v>
@@ -34067,7 +34067,7 @@
         <v>1.29980003833771</v>
       </c>
       <c r="G1162" t="n">
-        <v>1.01570701599121</v>
+        <v>1.0157071352005</v>
       </c>
       <c r="H1162" t="n">
         <v>16940</v>
@@ -34096,7 +34096,7 @@
         <v>1.23080003261566</v>
       </c>
       <c r="G1163" t="n">
-        <v>0.961788237094879</v>
+        <v>0.961788177490234</v>
       </c>
       <c r="H1163" t="n">
         <v>35956</v>
@@ -34125,7 +34125,7 @@
         <v>1.23099994659424</v>
       </c>
       <c r="G1164" t="n">
-        <v>0.961944460868835</v>
+        <v>0.96194452047348</v>
       </c>
       <c r="H1164" t="n">
         <v>10525</v>
@@ -34154,7 +34154,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1165" t="n">
-        <v>0.992420375347137</v>
+        <v>0.992420315742493</v>
       </c>
       <c r="H1165" t="n">
         <v>10014</v>
@@ -34183,7 +34183,7 @@
         <v>1.27900004386902</v>
       </c>
       <c r="G1166" t="n">
-        <v>0.99945342540741</v>
+        <v>0.999453246593475</v>
       </c>
       <c r="H1166" t="n">
         <v>19032</v>
@@ -34212,7 +34212,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1167" t="n">
-        <v>0.992420375347137</v>
+        <v>0.992420315742493</v>
       </c>
       <c r="H1167" t="n">
         <v>18852</v>
@@ -34241,7 +34241,7 @@
         <v>1.22819995880127</v>
       </c>
       <c r="G1168" t="n">
-        <v>0.95975649356842</v>
+        <v>0.959756553173065</v>
       </c>
       <c r="H1168" t="n">
         <v>10446</v>
@@ -34270,7 +34270,7 @@
         <v>1.25</v>
       </c>
       <c r="G1169" t="n">
-        <v>0.976791799068451</v>
+        <v>0.976791739463806</v>
       </c>
       <c r="H1169" t="n">
         <v>7000</v>
@@ -34299,7 +34299,7 @@
         <v>1.25</v>
       </c>
       <c r="G1170" t="n">
-        <v>0.976791799068451</v>
+        <v>0.976791739463806</v>
       </c>
       <c r="H1170" t="n">
         <v>0</v>
@@ -34328,7 +34328,7 @@
         <v>1.24339997768402</v>
       </c>
       <c r="G1171" t="n">
-        <v>0.971634328365326</v>
+        <v>0.971634268760681</v>
       </c>
       <c r="H1171" t="n">
         <v>4563</v>
@@ -34357,7 +34357,7 @@
         <v>1.22060000896454</v>
       </c>
       <c r="G1172" t="n">
-        <v>0.953817665576935</v>
+        <v>0.95381760597229</v>
       </c>
       <c r="H1172" t="n">
         <v>2356</v>
@@ -34386,7 +34386,7 @@
         <v>1.22060000896454</v>
       </c>
       <c r="G1173" t="n">
-        <v>0.953817665576935</v>
+        <v>0.95381760597229</v>
       </c>
       <c r="H1173" t="n">
         <v>0</v>
@@ -34444,7 +34444,7 @@
         <v>1.22200000286102</v>
       </c>
       <c r="G1175" t="n">
-        <v>0.954911708831787</v>
+        <v>0.954911649227142</v>
       </c>
       <c r="H1175" t="n">
         <v>800</v>
@@ -34502,7 +34502,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1177" t="n">
-        <v>0.953348815441132</v>
+        <v>0.953348696231842</v>
       </c>
       <c r="H1177" t="n">
         <v>1300</v>
@@ -34531,7 +34531,7 @@
         <v>1.23479998111725</v>
       </c>
       <c r="G1178" t="n">
-        <v>0.964913904666901</v>
+        <v>0.96491402387619</v>
       </c>
       <c r="H1178" t="n">
         <v>5677</v>
@@ -34560,7 +34560,7 @@
         <v>1.21700000762939</v>
       </c>
       <c r="G1179" t="n">
-        <v>0.951004326343536</v>
+        <v>0.951004505157471</v>
       </c>
       <c r="H1179" t="n">
         <v>1896</v>
@@ -34618,7 +34618,7 @@
         <v>1.23580002784729</v>
       </c>
       <c r="G1181" t="n">
-        <v>0.965695381164551</v>
+        <v>0.965695440769196</v>
       </c>
       <c r="H1181" t="n">
         <v>2300</v>
@@ -34647,7 +34647,7 @@
         <v>1.24399995803833</v>
       </c>
       <c r="G1182" t="n">
-        <v>0.972103178501129</v>
+        <v>0.97210305929184</v>
       </c>
       <c r="H1182" t="n">
         <v>2300</v>
@@ -34676,7 +34676,7 @@
         <v>1.24399995803833</v>
       </c>
       <c r="G1183" t="n">
-        <v>0.972103178501129</v>
+        <v>0.97210305929184</v>
       </c>
       <c r="H1183" t="n">
         <v>1000</v>
@@ -34763,7 +34763,7 @@
         <v>1.20899999141693</v>
       </c>
       <c r="G1186" t="n">
-        <v>0.944752991199493</v>
+        <v>0.944753050804138</v>
       </c>
       <c r="H1186" t="n">
         <v>8300</v>
@@ -34792,7 +34792,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1187" t="n">
-        <v>0.953348815441132</v>
+        <v>0.953348696231842</v>
       </c>
       <c r="H1187" t="n">
         <v>9105</v>
@@ -34821,7 +34821,7 @@
         <v>1.20019996166229</v>
       </c>
       <c r="G1188" t="n">
-        <v>0.937876462936401</v>
+        <v>0.937876403331757</v>
       </c>
       <c r="H1188" t="n">
         <v>10090</v>
@@ -34879,7 +34879,7 @@
         <v>1.26979994773865</v>
       </c>
       <c r="G1190" t="n">
-        <v>0.992264151573181</v>
+        <v>0.992264211177826</v>
       </c>
       <c r="H1190" t="n">
         <v>2250</v>
@@ -34995,7 +34995,7 @@
         <v>1.22800004482269</v>
       </c>
       <c r="G1194" t="n">
-        <v>0.959600269794464</v>
+        <v>0.959600210189819</v>
       </c>
       <c r="H1194" t="n">
         <v>24707</v>
@@ -35024,7 +35024,7 @@
         <v>1.24279999732971</v>
       </c>
       <c r="G1195" t="n">
-        <v>0.971165359020233</v>
+        <v>0.971165478229523</v>
       </c>
       <c r="H1195" t="n">
         <v>23798</v>
@@ -35082,7 +35082,7 @@
         <v>1.24399995803833</v>
       </c>
       <c r="G1197" t="n">
-        <v>0.972103178501129</v>
+        <v>0.97210305929184</v>
       </c>
       <c r="H1197" t="n">
         <v>28501</v>
@@ -35111,7 +35111,7 @@
         <v>1.23979997634888</v>
       </c>
       <c r="G1198" t="n">
-        <v>0.968821167945862</v>
+        <v>0.968821108341217</v>
       </c>
       <c r="H1198" t="n">
         <v>8654</v>
@@ -35140,7 +35140,7 @@
         <v>1.23979997634888</v>
       </c>
       <c r="G1199" t="n">
-        <v>0.968821167945862</v>
+        <v>0.968821108341217</v>
       </c>
       <c r="H1199" t="n">
         <v>11918</v>
@@ -35169,7 +35169,7 @@
         <v>1.19120001792908</v>
       </c>
       <c r="G1200" t="n">
-        <v>0.930843353271484</v>
+        <v>0.930843532085419</v>
       </c>
       <c r="H1200" t="n">
         <v>13624</v>
@@ -35198,7 +35198,7 @@
         <v>1.19120001792908</v>
       </c>
       <c r="G1201" t="n">
-        <v>0.930843353271484</v>
+        <v>0.930843532085419</v>
       </c>
       <c r="H1201" t="n">
         <v>0</v>
@@ -35227,7 +35227,7 @@
         <v>1.22940003871918</v>
       </c>
       <c r="G1202" t="n">
-        <v>0.960694193840027</v>
+        <v>0.960694253444672</v>
       </c>
       <c r="H1202" t="n">
         <v>930</v>
@@ -35256,7 +35256,7 @@
         <v>1.19140005111694</v>
       </c>
       <c r="G1203" t="n">
-        <v>0.93099981546402</v>
+        <v>0.930999755859375</v>
       </c>
       <c r="H1203" t="n">
         <v>520</v>
@@ -35372,7 +35372,7 @@
         <v>1.21119999885559</v>
       </c>
       <c r="G1207" t="n">
-        <v>0.94647216796875</v>
+        <v>0.946472227573395</v>
       </c>
       <c r="H1207" t="n">
         <v>11015</v>
@@ -35459,7 +35459,7 @@
         <v>1.19900000095367</v>
       </c>
       <c r="G1210" t="n">
-        <v>0.93693870306015</v>
+        <v>0.936938643455505</v>
       </c>
       <c r="H1210" t="n">
         <v>3</v>
@@ -35488,7 +35488,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G1211" t="n">
-        <v>0.968977391719818</v>
+        <v>0.968977510929108</v>
       </c>
       <c r="H1211" t="n">
         <v>39741</v>
@@ -35517,7 +35517,7 @@
         <v>1.20060002803802</v>
       </c>
       <c r="G1212" t="n">
-        <v>0.938188910484314</v>
+        <v>0.938188970088959</v>
       </c>
       <c r="H1212" t="n">
         <v>13237</v>
@@ -35575,7 +35575,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G1214" t="n">
-        <v>1.02367770671844</v>
+        <v>1.02367758750916</v>
       </c>
       <c r="H1214" t="n">
         <v>84862</v>
@@ -35604,7 +35604,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1215" t="n">
-        <v>0.984606087207794</v>
+        <v>0.984605967998505</v>
       </c>
       <c r="H1215" t="n">
         <v>32688</v>
@@ -35633,7 +35633,7 @@
         <v>1.26579999923706</v>
       </c>
       <c r="G1216" t="n">
-        <v>0.98913836479187</v>
+        <v>0.989138424396515</v>
       </c>
       <c r="H1216" t="n">
         <v>35063</v>
@@ -35662,7 +35662,7 @@
         <v>1.26540005207062</v>
       </c>
       <c r="G1217" t="n">
-        <v>0.988825917243958</v>
+        <v>0.988825857639313</v>
       </c>
       <c r="H1217" t="n">
         <v>20941</v>
@@ -35778,7 +35778,7 @@
         <v>1.25539994239807</v>
       </c>
       <c r="G1221" t="n">
-        <v>0.981011629104614</v>
+        <v>0.981011390686035</v>
       </c>
       <c r="H1221" t="n">
         <v>4670</v>
@@ -35807,7 +35807,7 @@
         <v>1.22599995136261</v>
       </c>
       <c r="G1222" t="n">
-        <v>0.958037376403809</v>
+        <v>0.958037316799164</v>
       </c>
       <c r="H1222" t="n">
         <v>119</v>
@@ -35836,7 +35836,7 @@
         <v>1.22599995136261</v>
       </c>
       <c r="G1223" t="n">
-        <v>0.958037376403809</v>
+        <v>0.958037316799164</v>
       </c>
       <c r="H1223" t="n">
         <v>0</v>
@@ -35865,7 +35865,7 @@
         <v>1.22599995136261</v>
       </c>
       <c r="G1224" t="n">
-        <v>0.958037376403809</v>
+        <v>0.958037316799164</v>
       </c>
       <c r="H1224" t="n">
         <v>0</v>
@@ -35923,7 +35923,7 @@
         <v>1.25</v>
       </c>
       <c r="G1226" t="n">
-        <v>0.976791799068451</v>
+        <v>0.976791739463806</v>
       </c>
       <c r="H1226" t="n">
         <v>370</v>
@@ -35952,7 +35952,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1227" t="n">
-        <v>0.937720119953156</v>
+        <v>0.9377201795578</v>
       </c>
       <c r="H1227" t="n">
         <v>6525</v>
@@ -36010,7 +36010,7 @@
         <v>1.192999958992</v>
       </c>
       <c r="G1229" t="n">
-        <v>0.932249963283539</v>
+        <v>0.932250022888184</v>
       </c>
       <c r="H1229" t="n">
         <v>712</v>
@@ -36039,7 +36039,7 @@
         <v>1.18219995498657</v>
       </c>
       <c r="G1230" t="n">
-        <v>0.923810482025146</v>
+        <v>0.923810541629791</v>
       </c>
       <c r="H1230" t="n">
         <v>425</v>
@@ -36068,7 +36068,7 @@
         <v>1.18219995498657</v>
       </c>
       <c r="G1231" t="n">
-        <v>0.923810482025146</v>
+        <v>0.923810541629791</v>
       </c>
       <c r="H1231" t="n">
         <v>0</v>
@@ -36097,7 +36097,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G1232" t="n">
-        <v>0.961163103580475</v>
+        <v>0.96116316318512</v>
       </c>
       <c r="H1232" t="n">
         <v>6056</v>
@@ -36126,7 +36126,7 @@
         <v>1.19159996509552</v>
       </c>
       <c r="G1233" t="n">
-        <v>0.931156039237976</v>
+        <v>0.931155920028687</v>
       </c>
       <c r="H1233" t="n">
         <v>510</v>
@@ -36155,7 +36155,7 @@
         <v>1.19099998474121</v>
       </c>
       <c r="G1234" t="n">
-        <v>0.930687189102173</v>
+        <v>0.930687129497528</v>
       </c>
       <c r="H1234" t="n">
         <v>2006</v>
@@ -36184,7 +36184,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G1235" t="n">
-        <v>0.961163103580475</v>
+        <v>0.96116316318512</v>
       </c>
       <c r="H1235" t="n">
         <v>16103</v>
@@ -36213,7 +36213,7 @@
         <v>1.19799995422363</v>
       </c>
       <c r="G1236" t="n">
-        <v>0.936157166957855</v>
+        <v>0.9361572265625</v>
       </c>
       <c r="H1236" t="n">
         <v>37918</v>
@@ -36242,7 +36242,7 @@
         <v>1.23800003528595</v>
       </c>
       <c r="G1237" t="n">
-        <v>0.967414617538452</v>
+        <v>0.967414557933807</v>
       </c>
       <c r="H1237" t="n">
         <v>7311</v>
@@ -36271,7 +36271,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1238" t="n">
-        <v>0.953348815441132</v>
+        <v>0.953348696231842</v>
       </c>
       <c r="H1238" t="n">
         <v>3720</v>
@@ -36300,7 +36300,7 @@
         <v>1.26800000667572</v>
       </c>
       <c r="G1239" t="n">
-        <v>0.990857541561127</v>
+        <v>0.990857660770416</v>
       </c>
       <c r="H1239" t="n">
         <v>129144</v>
@@ -36329,7 +36329,7 @@
         <v>1.3095999956131</v>
       </c>
       <c r="G1240" t="n">
-        <v>1.02336513996124</v>
+        <v>1.02336525917053</v>
       </c>
       <c r="H1240" t="n">
         <v>78316</v>
@@ -36445,7 +36445,7 @@
         <v>1.26639997959137</v>
       </c>
       <c r="G1244" t="n">
-        <v>0.989607334136963</v>
+        <v>0.989607214927673</v>
       </c>
       <c r="H1244" t="n">
         <v>32132</v>
@@ -36503,7 +36503,7 @@
         <v>1.46099996566772</v>
       </c>
       <c r="G1246" t="n">
-        <v>1.14167416095734</v>
+        <v>1.14167428016663</v>
       </c>
       <c r="H1246" t="n">
         <v>196814</v>
@@ -36532,7 +36532,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G1247" t="n">
-        <v>1.24247896671295</v>
+        <v>1.24247920513153</v>
       </c>
       <c r="H1247" t="n">
         <v>197270</v>
@@ -36561,7 +36561,7 @@
         <v>1.61300003528595</v>
       </c>
       <c r="G1248" t="n">
-        <v>1.26045227050781</v>
+        <v>1.26045215129852</v>
       </c>
       <c r="H1248" t="n">
         <v>112579</v>
@@ -36590,7 +36590,7 @@
         <v>1.59200000762939</v>
       </c>
       <c r="G1249" t="n">
-        <v>1.24404191970825</v>
+        <v>1.24404203891754</v>
       </c>
       <c r="H1249" t="n">
         <v>77714</v>
@@ -36648,7 +36648,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G1251" t="n">
-        <v>1.3128080368042</v>
+        <v>1.31280815601349</v>
       </c>
       <c r="H1251" t="n">
         <v>57237</v>
@@ -36706,7 +36706,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G1253" t="n">
-        <v>1.3128080368042</v>
+        <v>1.31280815601349</v>
       </c>
       <c r="H1253" t="n">
         <v>6137</v>
@@ -36735,7 +36735,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1254" t="n">
-        <v>1.30499374866486</v>
+        <v>1.30499386787415</v>
       </c>
       <c r="H1254" t="n">
         <v>28012</v>
@@ -36764,7 +36764,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G1255" t="n">
-        <v>1.3128080368042</v>
+        <v>1.31280815601349</v>
       </c>
       <c r="H1255" t="n">
         <v>9259</v>
@@ -36793,7 +36793,7 @@
         <v>1.72060000896454</v>
       </c>
       <c r="G1256" t="n">
-        <v>1.34453427791595</v>
+        <v>1.34453439712524</v>
       </c>
       <c r="H1256" t="n">
         <v>88356</v>
@@ -36822,7 +36822,7 @@
         <v>1.72500002384186</v>
       </c>
       <c r="G1257" t="n">
-        <v>1.34797263145447</v>
+        <v>1.34797275066376</v>
       </c>
       <c r="H1257" t="n">
         <v>18428</v>
@@ -36851,7 +36851,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G1258" t="n">
-        <v>1.4143944978714</v>
+        <v>1.41439437866211</v>
       </c>
       <c r="H1258" t="n">
         <v>159971</v>
@@ -36938,7 +36938,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G1261" t="n">
-        <v>1.34406566619873</v>
+        <v>1.34406542778015</v>
       </c>
       <c r="H1261" t="n">
         <v>16020</v>
@@ -36996,7 +36996,7 @@
         <v>1.7208000421524</v>
       </c>
       <c r="G1263" t="n">
-        <v>1.34469056129456</v>
+        <v>1.34469068050385</v>
       </c>
       <c r="H1263" t="n">
         <v>7468</v>
@@ -37025,7 +37025,7 @@
         <v>1.71019995212555</v>
       </c>
       <c r="G1264" t="n">
-        <v>1.33640730381012</v>
+        <v>1.33640742301941</v>
       </c>
       <c r="H1264" t="n">
         <v>18672</v>
@@ -37054,7 +37054,7 @@
         <v>1.67920005321503</v>
       </c>
       <c r="G1265" t="n">
-        <v>1.31218290328979</v>
+        <v>1.31218302249908</v>
       </c>
       <c r="H1265" t="n">
         <v>92610</v>
@@ -37083,7 +37083,7 @@
         <v>1.72940003871918</v>
       </c>
       <c r="G1266" t="n">
-        <v>1.35141098499298</v>
+        <v>1.35141086578369</v>
       </c>
       <c r="H1266" t="n">
         <v>28267</v>
@@ -37112,7 +37112,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G1267" t="n">
-        <v>1.39095139503479</v>
+        <v>1.39095151424408</v>
       </c>
       <c r="H1267" t="n">
         <v>141202</v>
@@ -37141,7 +37141,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G1268" t="n">
-        <v>1.45658135414124</v>
+        <v>1.45658147335052</v>
       </c>
       <c r="H1268" t="n">
         <v>42786</v>
@@ -37199,7 +37199,7 @@
         <v>1.73800003528595</v>
       </c>
       <c r="G1270" t="n">
-        <v>1.45490717887878</v>
+        <v>1.45490705966949</v>
       </c>
       <c r="H1270" t="n">
         <v>14911</v>
@@ -37228,7 +37228,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G1271" t="n">
-        <v>1.45658135414124</v>
+        <v>1.45658147335052</v>
       </c>
       <c r="H1271" t="n">
         <v>53971</v>
@@ -37257,7 +37257,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G1272" t="n">
-        <v>1.43983900547028</v>
+        <v>1.43983912467957</v>
       </c>
       <c r="H1272" t="n">
         <v>16994</v>
@@ -37286,7 +37286,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G1273" t="n">
-        <v>1.43983900547028</v>
+        <v>1.43983912467957</v>
       </c>
       <c r="H1273" t="n">
         <v>0</v>
@@ -37344,7 +37344,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G1275" t="n">
-        <v>1.43983900547028</v>
+        <v>1.43983912467957</v>
       </c>
       <c r="H1275" t="n">
         <v>57560</v>
@@ -37518,7 +37518,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G1281" t="n">
-        <v>1.37286972999573</v>
+        <v>1.37286984920502</v>
       </c>
       <c r="H1281" t="n">
         <v>16602</v>
@@ -37605,7 +37605,7 @@
         <v>1.66939997673035</v>
       </c>
       <c r="G1284" t="n">
-        <v>1.39748096466064</v>
+        <v>1.39748084545135</v>
       </c>
       <c r="H1284" t="n">
         <v>12668</v>
@@ -37634,7 +37634,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G1285" t="n">
-        <v>1.37286972999573</v>
+        <v>1.37286984920502</v>
       </c>
       <c r="H1285" t="n">
         <v>21352</v>
@@ -37721,7 +37721,7 @@
         <v>1.60199999809265</v>
       </c>
       <c r="G1288" t="n">
-        <v>1.34105932712555</v>
+        <v>1.34105944633484</v>
       </c>
       <c r="H1288" t="n">
         <v>26307</v>
@@ -37779,7 +37779,7 @@
         <v>1.64820003509521</v>
       </c>
       <c r="G1290" t="n">
-        <v>1.37973427772522</v>
+        <v>1.37973415851593</v>
       </c>
       <c r="H1290" t="n">
         <v>301</v>
@@ -37837,7 +37837,7 @@
         <v>1.60599994659424</v>
       </c>
       <c r="G1292" t="n">
-        <v>1.34440791606903</v>
+        <v>1.34440779685974</v>
       </c>
       <c r="H1292" t="n">
         <v>20464</v>
@@ -37866,7 +37866,7 @@
         <v>1.60199999809265</v>
       </c>
       <c r="G1293" t="n">
-        <v>1.34105932712555</v>
+        <v>1.34105944633484</v>
       </c>
       <c r="H1293" t="n">
         <v>1484</v>
@@ -38011,7 +38011,7 @@
         <v>1.75419998168945</v>
       </c>
       <c r="G1298" t="n">
-        <v>1.46846842765808</v>
+        <v>1.46846830844879</v>
       </c>
       <c r="H1298" t="n">
         <v>40624</v>
@@ -38127,7 +38127,7 @@
         <v>1.7688000202179</v>
       </c>
       <c r="G1302" t="n">
-        <v>1.48069036006927</v>
+        <v>1.48069024085999</v>
       </c>
       <c r="H1302" t="n">
         <v>40491</v>
@@ -38185,7 +38185,7 @@
         <v>1.74399995803833</v>
       </c>
       <c r="G1304" t="n">
-        <v>1.45992982387543</v>
+        <v>1.45992970466614</v>
       </c>
       <c r="H1304" t="n">
         <v>70208</v>
@@ -38591,7 +38591,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G1318" t="n">
-        <v>1.62400460243225</v>
+        <v>1.62400448322296</v>
       </c>
       <c r="H1318" t="n">
         <v>11052</v>
@@ -38620,7 +38620,7 @@
         <v>1.97979998588562</v>
       </c>
       <c r="G1319" t="n">
-        <v>1.65732181072235</v>
+        <v>1.65732169151306</v>
       </c>
       <c r="H1319" t="n">
         <v>18867</v>
@@ -38649,7 +38649,7 @@
         <v>1.97780001163483</v>
       </c>
       <c r="G1320" t="n">
-        <v>1.65564739704132</v>
+        <v>1.65564751625061</v>
       </c>
       <c r="H1320" t="n">
         <v>14303</v>
@@ -38678,7 +38678,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G1321" t="n">
-        <v>1.65748918056488</v>
+        <v>1.65748906135559</v>
       </c>
       <c r="H1321" t="n">
         <v>17248</v>
@@ -38765,7 +38765,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G1324" t="n">
-        <v>1.61563324928284</v>
+        <v>1.61563336849213</v>
       </c>
       <c r="H1324" t="n">
         <v>11644</v>
@@ -38794,7 +38794,7 @@
         <v>1.92120003700256</v>
       </c>
       <c r="G1325" t="n">
-        <v>1.60826683044434</v>
+        <v>1.60826671123505</v>
       </c>
       <c r="H1325" t="n">
         <v>17616</v>
@@ -38852,7 +38852,7 @@
         <v>1.95239996910095</v>
       </c>
       <c r="G1327" t="n">
-        <v>1.63438475131989</v>
+        <v>1.6343846321106</v>
       </c>
       <c r="H1327" t="n">
         <v>11152</v>
@@ -38881,7 +38881,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G1328" t="n">
-        <v>1.64074695110321</v>
+        <v>1.64074683189392</v>
       </c>
       <c r="H1328" t="n">
         <v>20785</v>
@@ -38910,7 +38910,7 @@
         <v>1.95959997177124</v>
       </c>
       <c r="G1329" t="n">
-        <v>1.64041197299957</v>
+        <v>1.64041185379028</v>
       </c>
       <c r="H1329" t="n">
         <v>3100</v>
@@ -38939,7 +38939,7 @@
         <v>1.91499996185303</v>
       </c>
       <c r="G1330" t="n">
-        <v>1.60307669639587</v>
+        <v>1.60307657718658</v>
       </c>
       <c r="H1330" t="n">
         <v>7584</v>
@@ -38968,7 +38968,7 @@
         <v>1.91620004177094</v>
       </c>
       <c r="G1331" t="n">
-        <v>1.60408115386963</v>
+        <v>1.60408127307892</v>
       </c>
       <c r="H1331" t="n">
         <v>3423</v>
@@ -38997,7 +38997,7 @@
         <v>1.95860004425049</v>
       </c>
       <c r="G1332" t="n">
-        <v>1.63957500457764</v>
+        <v>1.63957488536835</v>
       </c>
       <c r="H1332" t="n">
         <v>6470</v>
@@ -39113,7 +39113,7 @@
         <v>1.91499996185303</v>
       </c>
       <c r="G1336" t="n">
-        <v>1.60307669639587</v>
+        <v>1.60307657718658</v>
       </c>
       <c r="H1336" t="n">
         <v>4148</v>
@@ -39142,7 +39142,7 @@
         <v>1.91499996185303</v>
       </c>
       <c r="G1337" t="n">
-        <v>1.60307669639587</v>
+        <v>1.60307657718658</v>
       </c>
       <c r="H1337" t="n">
         <v>6260</v>
@@ -39200,7 +39200,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G1339" t="n">
-        <v>1.60726237297058</v>
+        <v>1.60726225376129</v>
       </c>
       <c r="H1339" t="n">
         <v>1005</v>
@@ -39229,7 +39229,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G1340" t="n">
-        <v>1.60726237297058</v>
+        <v>1.60726225376129</v>
       </c>
       <c r="H1340" t="n">
         <v>120</v>
@@ -39258,7 +39258,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G1341" t="n">
-        <v>1.60726237297058</v>
+        <v>1.60726225376129</v>
       </c>
       <c r="H1341" t="n">
         <v>20929</v>
@@ -39287,7 +39287,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G1342" t="n">
-        <v>1.61563324928284</v>
+        <v>1.61563336849213</v>
       </c>
       <c r="H1342" t="n">
         <v>4847</v>
@@ -39316,7 +39316,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G1343" t="n">
-        <v>1.60726237297058</v>
+        <v>1.60726225376129</v>
       </c>
       <c r="H1343" t="n">
         <v>14161</v>
@@ -39374,7 +39374,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G1345" t="n">
-        <v>1.65748918056488</v>
+        <v>1.65748906135559</v>
       </c>
       <c r="H1345" t="n">
         <v>50151</v>
@@ -39403,7 +39403,7 @@
         <v>2</v>
       </c>
       <c r="G1346" t="n">
-        <v>1.67423152923584</v>
+        <v>1.67423141002655</v>
       </c>
       <c r="H1346" t="n">
         <v>26218</v>
@@ -39461,7 +39461,7 @@
         <v>2</v>
       </c>
       <c r="G1348" t="n">
-        <v>1.67423152923584</v>
+        <v>1.67423141002655</v>
       </c>
       <c r="H1348" t="n">
         <v>32590</v>
@@ -39490,7 +39490,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G1349" t="n">
-        <v>1.65748918056488</v>
+        <v>1.65748906135559</v>
       </c>
       <c r="H1349" t="n">
         <v>45371</v>
@@ -39519,7 +39519,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G1350" t="n">
-        <v>1.60726237297058</v>
+        <v>1.60726225376129</v>
       </c>
       <c r="H1350" t="n">
         <v>120787</v>
@@ -39548,7 +39548,7 @@
         <v>1.91499996185303</v>
       </c>
       <c r="G1351" t="n">
-        <v>1.60307669639587</v>
+        <v>1.60307657718658</v>
       </c>
       <c r="H1351" t="n">
         <v>33983</v>
@@ -39635,7 +39635,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G1354" t="n">
-        <v>1.59051990509033</v>
+        <v>1.59051978588104</v>
       </c>
       <c r="H1354" t="n">
         <v>15319</v>
@@ -39722,7 +39722,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G1357" t="n">
-        <v>1.55703544616699</v>
+        <v>1.5570353269577</v>
       </c>
       <c r="H1357" t="n">
         <v>10646</v>
@@ -39751,7 +39751,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G1358" t="n">
-        <v>1.54866421222687</v>
+        <v>1.54866409301758</v>
       </c>
       <c r="H1358" t="n">
         <v>9250</v>
@@ -39809,7 +39809,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G1360" t="n">
-        <v>1.59051990509033</v>
+        <v>1.59051978588104</v>
       </c>
       <c r="H1360" t="n">
         <v>13059</v>
@@ -39838,7 +39838,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G1361" t="n">
-        <v>1.60726237297058</v>
+        <v>1.60726225376129</v>
       </c>
       <c r="H1361" t="n">
         <v>16896</v>
@@ -39867,7 +39867,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G1362" t="n">
-        <v>1.59051990509033</v>
+        <v>1.59051978588104</v>
       </c>
       <c r="H1362" t="n">
         <v>7070</v>
@@ -39925,7 +39925,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G1364" t="n">
-        <v>1.59051990509033</v>
+        <v>1.59051978588104</v>
       </c>
       <c r="H1364" t="n">
         <v>4035</v>
@@ -39954,7 +39954,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G1365" t="n">
-        <v>1.59051990509033</v>
+        <v>1.59051978588104</v>
       </c>
       <c r="H1365" t="n">
         <v>1022</v>
@@ -40041,7 +40041,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G1368" t="n">
-        <v>1.59051990509033</v>
+        <v>1.59051978588104</v>
       </c>
       <c r="H1368" t="n">
         <v>25050</v>
@@ -40070,7 +40070,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G1369" t="n">
-        <v>1.55703544616699</v>
+        <v>1.5570353269577</v>
       </c>
       <c r="H1369" t="n">
         <v>6264</v>
@@ -40128,7 +40128,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G1371" t="n">
-        <v>1.55703544616699</v>
+        <v>1.5570353269577</v>
       </c>
       <c r="H1371" t="n">
         <v>5678</v>
@@ -40244,7 +40244,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G1375" t="n">
-        <v>1.55703544616699</v>
+        <v>1.5570353269577</v>
       </c>
       <c r="H1375" t="n">
         <v>5724</v>
@@ -40273,7 +40273,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G1376" t="n">
-        <v>1.54866421222687</v>
+        <v>1.54866409301758</v>
       </c>
       <c r="H1376" t="n">
         <v>13711</v>
@@ -40302,7 +40302,7 @@
         <v>1.86500000953674</v>
       </c>
       <c r="G1377" t="n">
-        <v>1.56122088432312</v>
+        <v>1.56122076511383</v>
       </c>
       <c r="H1377" t="n">
         <v>24781</v>
@@ -40360,7 +40360,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G1379" t="n">
-        <v>1.89188170433044</v>
+        <v>1.89188158512115</v>
       </c>
       <c r="H1379" t="n">
         <v>317280</v>
@@ -40389,7 +40389,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1380" t="n">
-        <v>1.80817008018494</v>
+        <v>1.80816996097565</v>
       </c>
       <c r="H1380" t="n">
         <v>114976</v>
@@ -40418,7 +40418,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G1381" t="n">
-        <v>1.90862381458282</v>
+        <v>1.90862393379211</v>
       </c>
       <c r="H1381" t="n">
         <v>118880</v>
@@ -40447,7 +40447,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G1382" t="n">
-        <v>1.85839688777924</v>
+        <v>1.85839676856995</v>
       </c>
       <c r="H1382" t="n">
         <v>28667</v>
@@ -40476,7 +40476,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G1383" t="n">
-        <v>1.8751392364502</v>
+        <v>1.87513911724091</v>
       </c>
       <c r="H1383" t="n">
         <v>52913</v>
@@ -40534,7 +40534,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G1385" t="n">
-        <v>1.85839688777924</v>
+        <v>1.85839676856995</v>
       </c>
       <c r="H1385" t="n">
         <v>27190</v>
@@ -40563,7 +40563,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G1386" t="n">
-        <v>1.85839688777924</v>
+        <v>1.85839676856995</v>
       </c>
       <c r="H1386" t="n">
         <v>24834</v>
@@ -40592,7 +40592,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G1387" t="n">
-        <v>1.84165489673615</v>
+        <v>1.84165477752686</v>
       </c>
       <c r="H1387" t="n">
         <v>33572</v>
@@ -40621,7 +40621,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G1388" t="n">
-        <v>1.81654119491577</v>
+        <v>1.81654131412506</v>
       </c>
       <c r="H1388" t="n">
         <v>31320</v>
@@ -40708,7 +40708,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1391" t="n">
-        <v>1.80817008018494</v>
+        <v>1.80816996097565</v>
       </c>
       <c r="H1391" t="n">
         <v>20155</v>
@@ -40737,7 +40737,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G1392" t="n">
-        <v>1.7663140296936</v>
+        <v>1.76631414890289</v>
       </c>
       <c r="H1392" t="n">
         <v>3519</v>
@@ -40766,7 +40766,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1393" t="n">
-        <v>1.80817008018494</v>
+        <v>1.80816996097565</v>
       </c>
       <c r="H1393" t="n">
         <v>10650</v>
@@ -40824,7 +40824,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G1395" t="n">
-        <v>1.79142785072327</v>
+        <v>1.79142773151398</v>
       </c>
       <c r="H1395" t="n">
         <v>9872</v>
@@ -40911,7 +40911,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G1398" t="n">
-        <v>1.7663140296936</v>
+        <v>1.76631414890289</v>
       </c>
       <c r="H1398" t="n">
         <v>4485</v>
@@ -40969,7 +40969,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G1400" t="n">
-        <v>1.7412006855011</v>
+        <v>1.74120056629181</v>
       </c>
       <c r="H1400" t="n">
         <v>5207</v>
@@ -40998,7 +40998,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G1401" t="n">
-        <v>1.7412006855011</v>
+        <v>1.74120056629181</v>
       </c>
       <c r="H1401" t="n">
         <v>0</v>
@@ -41143,7 +41143,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G1406" t="n">
-        <v>1.72445845603943</v>
+        <v>1.72445833683014</v>
       </c>
       <c r="H1406" t="n">
         <v>6390</v>
@@ -41201,7 +41201,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G1408" t="n">
-        <v>1.70771610736847</v>
+        <v>1.70771598815918</v>
       </c>
       <c r="H1408" t="n">
         <v>1758</v>
@@ -41288,7 +41288,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G1411" t="n">
-        <v>1.70771610736847</v>
+        <v>1.70771598815918</v>
       </c>
       <c r="H1411" t="n">
         <v>36540</v>
@@ -41346,7 +41346,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G1413" t="n">
-        <v>1.72445845603943</v>
+        <v>1.72445833683014</v>
       </c>
       <c r="H1413" t="n">
         <v>5487</v>
@@ -41433,7 +41433,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G1416" t="n">
-        <v>1.65748918056488</v>
+        <v>1.65748906135559</v>
       </c>
       <c r="H1416" t="n">
         <v>5</v>
@@ -41491,7 +41491,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G1418" t="n">
-        <v>1.72445845603943</v>
+        <v>1.72445833683014</v>
       </c>
       <c r="H1418" t="n">
         <v>23048</v>
@@ -41520,7 +41520,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G1419" t="n">
-        <v>1.77468538284302</v>
+        <v>1.77468526363373</v>
       </c>
       <c r="H1419" t="n">
         <v>15638</v>
@@ -41578,7 +41578,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1421" t="n">
-        <v>1.80817008018494</v>
+        <v>1.80816996097565</v>
       </c>
       <c r="H1421" t="n">
         <v>41767</v>
@@ -41636,7 +41636,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G1423" t="n">
-        <v>1.81654119491577</v>
+        <v>1.81654131412506</v>
       </c>
       <c r="H1423" t="n">
         <v>8578</v>
@@ -41665,7 +41665,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G1424" t="n">
-        <v>1.81654119491577</v>
+        <v>1.81654131412506</v>
       </c>
       <c r="H1424" t="n">
         <v>6559</v>
@@ -41694,7 +41694,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G1425" t="n">
-        <v>1.81654119491577</v>
+        <v>1.81654131412506</v>
       </c>
       <c r="H1425" t="n">
         <v>28383</v>
@@ -41723,7 +41723,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G1426" t="n">
-        <v>1.83328354358673</v>
+        <v>1.83328366279602</v>
       </c>
       <c r="H1426" t="n">
         <v>5861</v>
@@ -41752,7 +41752,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G1427" t="n">
-        <v>1.85839688777924</v>
+        <v>1.85839676856995</v>
       </c>
       <c r="H1427" t="n">
         <v>8698</v>
@@ -41781,7 +41781,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G1428" t="n">
-        <v>1.85839688777924</v>
+        <v>1.85839676856995</v>
       </c>
       <c r="H1428" t="n">
         <v>2382</v>
@@ -41810,7 +41810,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G1429" t="n">
-        <v>1.85839688777924</v>
+        <v>1.85839676856995</v>
       </c>
       <c r="H1429" t="n">
         <v>1386</v>
@@ -41839,7 +41839,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G1430" t="n">
-        <v>1.83328354358673</v>
+        <v>1.83328366279602</v>
       </c>
       <c r="H1430" t="n">
         <v>2450</v>
@@ -41868,7 +41868,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G1431" t="n">
-        <v>1.84165489673615</v>
+        <v>1.84165477752686</v>
       </c>
       <c r="H1431" t="n">
         <v>8624</v>
@@ -41926,7 +41926,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G1433" t="n">
-        <v>1.79142785072327</v>
+        <v>1.79142773151398</v>
       </c>
       <c r="H1433" t="n">
         <v>12195</v>
@@ -41955,7 +41955,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G1434" t="n">
-        <v>1.81654119491577</v>
+        <v>1.81654131412506</v>
       </c>
       <c r="H1434" t="n">
         <v>22886</v>
@@ -41984,7 +41984,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G1435" t="n">
-        <v>1.85839688777924</v>
+        <v>1.85839676856995</v>
       </c>
       <c r="H1435" t="n">
         <v>10508</v>
@@ -42013,7 +42013,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G1436" t="n">
-        <v>1.85839688777924</v>
+        <v>1.85839676856995</v>
       </c>
       <c r="H1436" t="n">
         <v>5310</v>
@@ -42042,7 +42042,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G1437" t="n">
-        <v>1.8500257730484</v>
+        <v>1.85002565383911</v>
       </c>
       <c r="H1437" t="n">
         <v>2124</v>
@@ -42129,7 +42129,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G1440" t="n">
-        <v>1.81654119491577</v>
+        <v>1.81654131412506</v>
       </c>
       <c r="H1440" t="n">
         <v>13224</v>
@@ -42187,7 +42187,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1442" t="n">
-        <v>1.80817008018494</v>
+        <v>1.80816996097565</v>
       </c>
       <c r="H1442" t="n">
         <v>3900</v>
@@ -42216,7 +42216,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G1443" t="n">
-        <v>1.83328354358673</v>
+        <v>1.83328366279602</v>
       </c>
       <c r="H1443" t="n">
         <v>7310</v>
@@ -42245,7 +42245,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G1444" t="n">
-        <v>1.83328354358673</v>
+        <v>1.83328366279602</v>
       </c>
       <c r="H1444" t="n">
         <v>0</v>
@@ -42332,7 +42332,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G1447" t="n">
-        <v>1.79142785072327</v>
+        <v>1.79142773151398</v>
       </c>
       <c r="H1447" t="n">
         <v>1801</v>
@@ -42361,7 +42361,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G1448" t="n">
-        <v>1.7663140296936</v>
+        <v>1.76631414890289</v>
       </c>
       <c r="H1448" t="n">
         <v>6157</v>
@@ -42506,7 +42506,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G1453" t="n">
-        <v>1.77468538284302</v>
+        <v>1.77468526363373</v>
       </c>
       <c r="H1453" t="n">
         <v>5250</v>
@@ -42564,7 +42564,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G1455" t="n">
-        <v>1.79142785072327</v>
+        <v>1.79142773151398</v>
       </c>
       <c r="H1455" t="n">
         <v>8648</v>
@@ -42593,7 +42593,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G1456" t="n">
-        <v>1.83328354358673</v>
+        <v>1.83328366279602</v>
       </c>
       <c r="H1456" t="n">
         <v>33296</v>
@@ -42622,7 +42622,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G1457" t="n">
-        <v>1.84165489673615</v>
+        <v>1.84165477752686</v>
       </c>
       <c r="H1457" t="n">
         <v>31486</v>
@@ -42680,7 +42680,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G1459" t="n">
-        <v>1.8751392364502</v>
+        <v>1.87513911724091</v>
       </c>
       <c r="H1459" t="n">
         <v>10775</v>
@@ -42709,7 +42709,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G1460" t="n">
-        <v>1.8751392364502</v>
+        <v>1.87513911724091</v>
       </c>
       <c r="H1460" t="n">
         <v>12250</v>
@@ -42767,7 +42767,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G1462" t="n">
-        <v>2.1932430267334</v>
+        <v>2.19324278831482</v>
       </c>
       <c r="H1462" t="n">
         <v>497101</v>
@@ -42796,7 +42796,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G1463" t="n">
-        <v>2.20161461830139</v>
+        <v>2.20161437988281</v>
       </c>
       <c r="H1463" t="n">
         <v>261129</v>
@@ -42854,7 +42854,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G1465" t="n">
-        <v>2.16812992095947</v>
+        <v>2.16812968254089</v>
       </c>
       <c r="H1465" t="n">
         <v>38675</v>
@@ -42912,7 +42912,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G1467" t="n">
-        <v>2.07604694366455</v>
+        <v>2.07604718208313</v>
       </c>
       <c r="H1467" t="n">
         <v>8318</v>
@@ -42970,7 +42970,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G1469" t="n">
-        <v>2.07604694366455</v>
+        <v>2.07604718208313</v>
       </c>
       <c r="H1469" t="n">
         <v>10761</v>
@@ -42999,7 +42999,7 @@
         <v>2.5</v>
       </c>
       <c r="G1470" t="n">
-        <v>2.0927894115448</v>
+        <v>2.09278917312622</v>
       </c>
       <c r="H1470" t="n">
         <v>17544</v>
@@ -43028,7 +43028,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G1471" t="n">
-        <v>2.04256248474121</v>
+        <v>2.04256224632263</v>
       </c>
       <c r="H1471" t="n">
         <v>4161</v>
@@ -43057,7 +43057,7 @@
         <v>2.5</v>
       </c>
       <c r="G1472" t="n">
-        <v>2.0927894115448</v>
+        <v>2.09278917312622</v>
       </c>
       <c r="H1472" t="n">
         <v>16513</v>
@@ -43144,7 +43144,7 @@
         <v>2.5</v>
       </c>
       <c r="G1475" t="n">
-        <v>2.0927894115448</v>
+        <v>2.09278917312622</v>
       </c>
       <c r="H1475" t="n">
         <v>1995</v>
@@ -43231,7 +43231,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G1478" t="n">
-        <v>2.20161461830139</v>
+        <v>2.20161437988281</v>
       </c>
       <c r="H1478" t="n">
         <v>8945</v>
@@ -43347,7 +43347,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G1482" t="n">
-        <v>2.1932430267334</v>
+        <v>2.19324278831482</v>
       </c>
       <c r="H1482" t="n">
         <v>2227</v>
@@ -43376,7 +43376,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G1483" t="n">
-        <v>2.15975880622864</v>
+        <v>2.15975856781006</v>
       </c>
       <c r="H1483" t="n">
         <v>11553</v>
@@ -43521,7 +43521,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G1488" t="n">
-        <v>2.16812992095947</v>
+        <v>2.16812968254089</v>
       </c>
       <c r="H1488" t="n">
         <v>17680</v>
@@ -43637,7 +43637,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G1492" t="n">
-        <v>2.15138721466064</v>
+        <v>2.15138745307922</v>
       </c>
       <c r="H1492" t="n">
         <v>4814</v>
@@ -43695,7 +43695,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G1494" t="n">
-        <v>2.2518413066864</v>
+        <v>2.25184154510498</v>
       </c>
       <c r="H1494" t="n">
         <v>89679</v>
@@ -43811,7 +43811,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G1498" t="n">
-        <v>2.21835660934448</v>
+        <v>2.21835684776306</v>
       </c>
       <c r="H1498" t="n">
         <v>26546</v>
@@ -43840,7 +43840,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G1499" t="n">
-        <v>2.21835660934448</v>
+        <v>2.21835684776306</v>
       </c>
       <c r="H1499" t="n">
         <v>2484</v>
@@ -43898,7 +43898,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G1501" t="n">
-        <v>2.2518413066864</v>
+        <v>2.25184154510498</v>
       </c>
       <c r="H1501" t="n">
         <v>65037</v>
@@ -43956,7 +43956,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G1503" t="n">
-        <v>2.2518413066864</v>
+        <v>2.25184154510498</v>
       </c>
       <c r="H1503" t="n">
         <v>18385</v>
@@ -43985,7 +43985,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G1504" t="n">
-        <v>2.24347019195557</v>
+        <v>2.24347043037415</v>
       </c>
       <c r="H1504" t="n">
         <v>44721</v>
@@ -44014,7 +44014,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G1505" t="n">
-        <v>2.21835660934448</v>
+        <v>2.21835684776306</v>
       </c>
       <c r="H1505" t="n">
         <v>7243</v>
@@ -44188,7 +44188,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G1511" t="n">
-        <v>2.21835660934448</v>
+        <v>2.21835684776306</v>
       </c>
       <c r="H1511" t="n">
         <v>8611</v>
@@ -44217,7 +44217,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G1512" t="n">
-        <v>2.2518413066864</v>
+        <v>2.25184154510498</v>
       </c>
       <c r="H1512" t="n">
         <v>1609</v>
@@ -44246,7 +44246,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G1513" t="n">
-        <v>2.2518413066864</v>
+        <v>2.25184154510498</v>
       </c>
       <c r="H1513" t="n">
         <v>10947</v>
@@ -44362,7 +44362,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G1517" t="n">
-        <v>2.5448317527771</v>
+        <v>2.54483199119568</v>
       </c>
       <c r="H1517" t="n">
         <v>82221</v>
@@ -44449,7 +44449,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G1520" t="n">
-        <v>2.67039942741394</v>
+        <v>2.67039918899536</v>
       </c>
       <c r="H1520" t="n">
         <v>70441</v>
@@ -44478,7 +44478,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G1521" t="n">
-        <v>2.71225476264954</v>
+        <v>2.71225500106812</v>
       </c>
       <c r="H1521" t="n">
         <v>58192</v>
@@ -44507,7 +44507,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G1522" t="n">
-        <v>2.6787703037262</v>
+        <v>2.67877054214478</v>
       </c>
       <c r="H1522" t="n">
         <v>13797</v>
@@ -44536,7 +44536,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G1523" t="n">
-        <v>2.75411081314087</v>
+        <v>2.75411057472229</v>
       </c>
       <c r="H1523" t="n">
         <v>36741</v>
@@ -44623,7 +44623,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G1526" t="n">
-        <v>3.20615339279175</v>
+        <v>3.20615315437317</v>
       </c>
       <c r="H1526" t="n">
         <v>73041</v>
@@ -44710,7 +44710,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G1529" t="n">
-        <v>3.0303590297699</v>
+        <v>3.03035879135132</v>
       </c>
       <c r="H1529" t="n">
         <v>25973</v>
@@ -44739,7 +44739,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1530" t="n">
-        <v>3.01361680030823</v>
+        <v>3.01361656188965</v>
       </c>
       <c r="H1530" t="n">
         <v>13796</v>
@@ -44855,7 +44855,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G1534" t="n">
-        <v>2.87967801094055</v>
+        <v>2.87967824935913</v>
       </c>
       <c r="H1534" t="n">
         <v>5863</v>
@@ -44971,7 +44971,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1538" t="n">
-        <v>2.84619331359863</v>
+        <v>2.84619379043579</v>
       </c>
       <c r="H1538" t="n">
         <v>13330</v>
@@ -45029,7 +45029,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G1540" t="n">
-        <v>2.78759551048279</v>
+        <v>2.78759527206421</v>
       </c>
       <c r="H1540" t="n">
         <v>21833</v>
@@ -45058,7 +45058,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1541" t="n">
-        <v>2.80433750152588</v>
+        <v>2.80433773994446</v>
       </c>
       <c r="H1541" t="n">
         <v>9323</v>
@@ -45145,7 +45145,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G1544" t="n">
-        <v>2.97176098823547</v>
+        <v>2.97176074981689</v>
       </c>
       <c r="H1544" t="n">
         <v>25906</v>
@@ -45232,7 +45232,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G1547" t="n">
-        <v>3.04710125923157</v>
+        <v>3.04710149765015</v>
       </c>
       <c r="H1547" t="n">
         <v>27597</v>
@@ -45261,7 +45261,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G1548" t="n">
-        <v>3.12244176864624</v>
+        <v>3.12244153022766</v>
       </c>
       <c r="H1548" t="n">
         <v>31587</v>
@@ -45290,7 +45290,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G1549" t="n">
-        <v>3.18941068649292</v>
+        <v>3.1894109249115</v>
       </c>
       <c r="H1549" t="n">
         <v>55680</v>
@@ -45493,7 +45493,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G1556" t="n">
-        <v>3.2180643081665</v>
+        <v>3.21806406974792</v>
       </c>
       <c r="H1556" t="n">
         <v>26348</v>
@@ -45522,7 +45522,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G1557" t="n">
-        <v>3.1576714515686</v>
+        <v>3.15767168998718</v>
       </c>
       <c r="H1557" t="n">
         <v>14643</v>
@@ -45725,7 +45725,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1564" t="n">
-        <v>3.10590648651123</v>
+        <v>3.10590624809265</v>
       </c>
       <c r="H1564" t="n">
         <v>5841</v>
@@ -45783,7 +45783,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G1566" t="n">
-        <v>2.97649359703064</v>
+        <v>2.97649383544922</v>
       </c>
       <c r="H1566" t="n">
         <v>27030</v>
@@ -46015,7 +46015,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G1574" t="n">
-        <v>2.66590285301208</v>
+        <v>2.66590309143066</v>
       </c>
       <c r="H1574" t="n">
         <v>33185</v>
@@ -46044,7 +46044,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G1575" t="n">
-        <v>2.62276530265808</v>
+        <v>2.62276554107666</v>
       </c>
       <c r="H1575" t="n">
         <v>16919</v>
@@ -46218,7 +46218,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G1581" t="n">
-        <v>3.00237607955933</v>
+        <v>3.00237631797791</v>
       </c>
       <c r="H1581" t="n">
         <v>7369</v>
@@ -46247,7 +46247,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G1582" t="n">
-        <v>2.96786594390869</v>
+        <v>2.96786618232727</v>
       </c>
       <c r="H1582" t="n">
         <v>9819</v>
@@ -46421,7 +46421,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G1588" t="n">
-        <v>3.00237607955933</v>
+        <v>3.00237631797791</v>
       </c>
       <c r="H1588" t="n">
         <v>8197</v>
@@ -46595,7 +46595,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1594" t="n">
-        <v>2.93335604667664</v>
+        <v>2.93335628509521</v>
       </c>
       <c r="H1594" t="n">
         <v>1217</v>
@@ -46624,7 +46624,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1595" t="n">
-        <v>2.93335604667664</v>
+        <v>2.93335628509521</v>
       </c>
       <c r="H1595" t="n">
         <v>2971</v>
@@ -46711,7 +46711,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1598" t="n">
-        <v>2.93335604667664</v>
+        <v>2.93335628509521</v>
       </c>
       <c r="H1598" t="n">
         <v>2090</v>
@@ -46798,7 +46798,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1601" t="n">
-        <v>2.93335604667664</v>
+        <v>2.93335628509521</v>
       </c>
       <c r="H1601" t="n">
         <v>1039</v>
@@ -46827,7 +46827,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G1602" t="n">
-        <v>2.95061135292053</v>
+        <v>2.95061111450195</v>
       </c>
       <c r="H1602" t="n">
         <v>3240</v>
@@ -47001,7 +47001,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G1608" t="n">
-        <v>2.95061135292053</v>
+        <v>2.95061111450195</v>
       </c>
       <c r="H1608" t="n">
         <v>24178</v>
@@ -47059,7 +47059,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G1610" t="n">
-        <v>3.19792723655701</v>
+        <v>3.19792699813843</v>
       </c>
       <c r="H1610" t="n">
         <v>18822</v>
@@ -47088,7 +47088,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1611" t="n">
-        <v>3.05004620552063</v>
+        <v>3.05004596710205</v>
       </c>
       <c r="H1611" t="n">
         <v>18282</v>
@@ -47117,7 +47117,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1612" t="n">
-        <v>3.05004620552063</v>
+        <v>3.05004596710205</v>
       </c>
       <c r="H1612" t="n">
         <v>6535</v>
@@ -47146,7 +47146,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1613" t="n">
-        <v>3.05004620552063</v>
+        <v>3.05004596710205</v>
       </c>
       <c r="H1613" t="n">
         <v>6560</v>
@@ -47204,7 +47204,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G1615" t="n">
-        <v>2.98534822463989</v>
+        <v>2.98534798622131</v>
       </c>
       <c r="H1615" t="n">
         <v>5371</v>
@@ -47262,7 +47262,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G1617" t="n">
-        <v>3.01307582855225</v>
+        <v>3.01307559013367</v>
       </c>
       <c r="H1617" t="n">
         <v>1877</v>
@@ -47320,7 +47320,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G1619" t="n">
-        <v>3.06853103637695</v>
+        <v>3.06853127479553</v>
       </c>
       <c r="H1619" t="n">
         <v>5319</v>
@@ -47378,7 +47378,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G1621" t="n">
-        <v>2.93913531303406</v>
+        <v>2.93913555145264</v>
       </c>
       <c r="H1621" t="n">
         <v>7441</v>
@@ -47407,7 +47407,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G1622" t="n">
-        <v>3.06853103637695</v>
+        <v>3.06853127479553</v>
       </c>
       <c r="H1622" t="n">
         <v>9571</v>
@@ -47494,7 +47494,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G1625" t="n">
-        <v>3.01307582855225</v>
+        <v>3.01307559013367</v>
       </c>
       <c r="H1625" t="n">
         <v>720</v>
@@ -47523,7 +47523,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G1626" t="n">
-        <v>3.01307582855225</v>
+        <v>3.01307559013367</v>
       </c>
       <c r="H1626" t="n">
         <v>0</v>
@@ -47552,7 +47552,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G1627" t="n">
-        <v>2.98534822463989</v>
+        <v>2.98534798622131</v>
       </c>
       <c r="H1627" t="n">
         <v>2900</v>
@@ -47697,7 +47697,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G1632" t="n">
-        <v>2.93913531303406</v>
+        <v>2.93913555145264</v>
       </c>
       <c r="H1632" t="n">
         <v>2221</v>
@@ -47813,7 +47813,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G1636" t="n">
-        <v>2.88367962837219</v>
+        <v>2.88367986679077</v>
       </c>
       <c r="H1636" t="n">
         <v>4351</v>
@@ -48074,7 +48074,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G1645" t="n">
-        <v>2.44927954673767</v>
+        <v>2.44927930831909</v>
       </c>
       <c r="H1645" t="n">
         <v>4242</v>
@@ -48364,7 +48364,7 @@
         <v>2.75</v>
       </c>
       <c r="G1655" t="n">
-        <v>2.54170489311218</v>
+        <v>2.54170513153076</v>
       </c>
       <c r="H1655" t="n">
         <v>4443</v>
@@ -48422,7 +48422,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G1657" t="n">
-        <v>2.66185855865479</v>
+        <v>2.66185832023621</v>
       </c>
       <c r="H1657" t="n">
         <v>1365</v>
@@ -48538,7 +48538,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G1661" t="n">
-        <v>2.51397728919983</v>
+        <v>2.51397752761841</v>
       </c>
       <c r="H1661" t="n">
         <v>2782</v>
@@ -48596,7 +48596,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G1663" t="n">
-        <v>2.53246235847473</v>
+        <v>2.53246259689331</v>
       </c>
       <c r="H1663" t="n">
         <v>37694</v>
@@ -48625,7 +48625,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G1664" t="n">
-        <v>2.48624992370605</v>
+        <v>2.48624968528748</v>
       </c>
       <c r="H1664" t="n">
         <v>1765</v>
@@ -48712,7 +48712,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G1667" t="n">
-        <v>2.51397728919983</v>
+        <v>2.51397752761841</v>
       </c>
       <c r="H1667" t="n">
         <v>22439</v>
@@ -48741,7 +48741,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G1668" t="n">
-        <v>2.44927954673767</v>
+        <v>2.44927930831909</v>
       </c>
       <c r="H1668" t="n">
         <v>12455</v>
@@ -48857,7 +48857,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G1672" t="n">
-        <v>2.42155170440674</v>
+        <v>2.42155146598816</v>
       </c>
       <c r="H1672" t="n">
         <v>3460</v>
@@ -49147,7 +49147,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G1682" t="n">
-        <v>2.40306639671326</v>
+        <v>2.40306663513184</v>
       </c>
       <c r="H1682" t="n">
         <v>1410</v>
@@ -49495,7 +49495,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G1694" t="n">
-        <v>2.27367091178894</v>
+        <v>2.27367067337036</v>
       </c>
       <c r="H1694" t="n">
         <v>3905</v>
@@ -49611,7 +49611,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G1698" t="n">
-        <v>2.27367091178894</v>
+        <v>2.27367067337036</v>
       </c>
       <c r="H1698" t="n">
         <v>19</v>
@@ -49640,7 +49640,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G1699" t="n">
-        <v>2.26442813873291</v>
+        <v>2.26442837715149</v>
       </c>
       <c r="H1699" t="n">
         <v>580</v>
@@ -49669,7 +49669,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G1700" t="n">
-        <v>2.23670053482056</v>
+        <v>2.23670029640198</v>
       </c>
       <c r="H1700" t="n">
         <v>450</v>
@@ -49814,7 +49814,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G1705" t="n">
-        <v>2.2089729309082</v>
+        <v>2.20897269248962</v>
       </c>
       <c r="H1705" t="n">
         <v>1386</v>
@@ -49872,7 +49872,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G1707" t="n">
-        <v>2.26442813873291</v>
+        <v>2.26442837715149</v>
       </c>
       <c r="H1707" t="n">
         <v>190</v>
@@ -49901,7 +49901,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G1708" t="n">
-        <v>2.26442813873291</v>
+        <v>2.26442837715149</v>
       </c>
       <c r="H1708" t="n">
         <v>0</v>
@@ -49959,7 +49959,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G1710" t="n">
-        <v>2.28291344642639</v>
+        <v>2.28291320800781</v>
       </c>
       <c r="H1710" t="n">
         <v>900</v>
@@ -49988,7 +49988,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G1711" t="n">
-        <v>2.28291344642639</v>
+        <v>2.28291320800781</v>
       </c>
       <c r="H1711" t="n">
         <v>0</v>
@@ -50104,7 +50104,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G1715" t="n">
-        <v>2.23670053482056</v>
+        <v>2.23670029640198</v>
       </c>
       <c r="H1715" t="n">
         <v>11340</v>
@@ -50133,7 +50133,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G1716" t="n">
-        <v>2.28291344642639</v>
+        <v>2.28291320800781</v>
       </c>
       <c r="H1716" t="n">
         <v>8732</v>
@@ -50278,7 +50278,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G1721" t="n">
-        <v>2.07033443450928</v>
+        <v>2.0703341960907</v>
       </c>
       <c r="H1721" t="n">
         <v>201</v>
@@ -50336,7 +50336,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G1723" t="n">
-        <v>2.19048738479614</v>
+        <v>2.19048762321472</v>
       </c>
       <c r="H1723" t="n">
         <v>7034</v>
@@ -50423,7 +50423,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G1726" t="n">
-        <v>2.06109189987183</v>
+        <v>2.06109166145325</v>
       </c>
       <c r="H1726" t="n">
         <v>7464</v>
@@ -50684,7 +50684,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G1735" t="n">
-        <v>2.0518491268158</v>
+        <v>2.05184936523438</v>
       </c>
       <c r="H1735" t="n">
         <v>601</v>
@@ -50742,7 +50742,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1737" t="n">
-        <v>1.99639391899109</v>
+        <v>1.99639403820038</v>
       </c>
       <c r="H1737" t="n">
         <v>7242</v>
@@ -50945,7 +50945,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G1744" t="n">
-        <v>2.07033443450928</v>
+        <v>2.0703341960907</v>
       </c>
       <c r="H1744" t="n">
         <v>2600</v>
@@ -51032,7 +51032,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G1747" t="n">
-        <v>2.06109189987183</v>
+        <v>2.06109166145325</v>
       </c>
       <c r="H1747" t="n">
         <v>2976</v>
@@ -51148,7 +51148,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G1751" t="n">
-        <v>2.23670053482056</v>
+        <v>2.23670029640198</v>
       </c>
       <c r="H1751" t="n">
         <v>2433</v>
@@ -51293,7 +51293,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G1756" t="n">
-        <v>2.19048738479614</v>
+        <v>2.19048762321472</v>
       </c>
       <c r="H1756" t="n">
         <v>8634</v>
@@ -51322,7 +51322,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G1757" t="n">
-        <v>2.27367091178894</v>
+        <v>2.27367067337036</v>
       </c>
       <c r="H1757" t="n">
         <v>7714</v>
@@ -51351,7 +51351,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G1758" t="n">
-        <v>2.53246235847473</v>
+        <v>2.53246259689331</v>
       </c>
       <c r="H1758" t="n">
         <v>20349</v>
@@ -51467,7 +51467,7 @@
         <v>2.75</v>
       </c>
       <c r="G1762" t="n">
-        <v>2.54170489311218</v>
+        <v>2.54170513153076</v>
       </c>
       <c r="H1762" t="n">
         <v>6937</v>
@@ -51699,7 +51699,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G1770" t="n">
-        <v>2.51397728919983</v>
+        <v>2.51397752761841</v>
       </c>
       <c r="H1770" t="n">
         <v>9906</v>
@@ -51786,7 +51786,7 @@
         <v>2.75</v>
       </c>
       <c r="G1773" t="n">
-        <v>2.54170489311218</v>
+        <v>2.54170513153076</v>
       </c>
       <c r="H1773" t="n">
         <v>13690</v>
@@ -51844,7 +51844,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G1775" t="n">
-        <v>2.53246235847473</v>
+        <v>2.53246259689331</v>
       </c>
       <c r="H1775" t="n">
         <v>10845</v>
@@ -51873,7 +51873,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G1776" t="n">
-        <v>2.53246235847473</v>
+        <v>2.53246259689331</v>
       </c>
       <c r="H1776" t="n">
         <v>3910</v>
@@ -51902,7 +51902,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G1777" t="n">
-        <v>2.51397728919983</v>
+        <v>2.51397752761841</v>
       </c>
       <c r="H1777" t="n">
         <v>18536</v>
@@ -79951,6 +79951,64 @@
         <v>1100</v>
       </c>
       <c r="I2744" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2745">
+      <c r="A2745" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2745" s="1" t="n">
+        <v>46314.2916666667</v>
+      </c>
+      <c r="C2745" t="n">
+        <v>0.419999986886978</v>
+      </c>
+      <c r="D2745" t="n">
+        <v>0.428000003099442</v>
+      </c>
+      <c r="E2745" t="n">
+        <v>0.418000012636185</v>
+      </c>
+      <c r="F2745" t="n">
+        <v>0.428000003099442</v>
+      </c>
+      <c r="G2745" t="n">
+        <v>0.428000003099442</v>
+      </c>
+      <c r="H2745" t="n">
+        <v>5687</v>
+      </c>
+      <c r="I2745" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2746">
+      <c r="A2746" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2746" s="1" t="n">
+        <v>46315.2916666667</v>
+      </c>
+      <c r="C2746" t="n">
+        <v>0.419999986886978</v>
+      </c>
+      <c r="D2746" t="n">
+        <v>0.428000003099442</v>
+      </c>
+      <c r="E2746" t="n">
+        <v>0.418000012636185</v>
+      </c>
+      <c r="F2746" t="n">
+        <v>0.389999985694885</v>
+      </c>
+      <c r="G2746" t="n">
+        <v>0.389999985694885</v>
+      </c>
+      <c r="H2746" t="n">
+        <v>2466</v>
+      </c>
+      <c r="I2746" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ZUC.MI.xlsx
+++ b/data/ZUC.MI.xlsx
@@ -427,7 +427,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G2" t="n">
-        <v>3.01633286476135</v>
+        <v>3.01633310317993</v>
       </c>
       <c r="H2" t="n">
         <v>42345</v>
@@ -543,7 +543,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G6" t="n">
-        <v>2.96944689750671</v>
+        <v>2.96944713592529</v>
       </c>
       <c r="H6" t="n">
         <v>40605</v>
@@ -572,7 +572,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G7" t="n">
-        <v>2.84441781044006</v>
+        <v>2.84441757202148</v>
       </c>
       <c r="H7" t="n">
         <v>15987</v>
@@ -688,7 +688,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G11" t="n">
-        <v>2.77408838272095</v>
+        <v>2.77408862113953</v>
       </c>
       <c r="H11" t="n">
         <v>14530</v>
@@ -746,7 +746,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G13" t="n">
-        <v>2.5084011554718</v>
+        <v>2.50840139389038</v>
       </c>
       <c r="H13" t="n">
         <v>22831</v>
@@ -775,7 +775,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G14" t="n">
-        <v>2.39900040626526</v>
+        <v>2.39900064468384</v>
       </c>
       <c r="H14" t="n">
         <v>17223</v>
@@ -862,7 +862,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G17" t="n">
-        <v>2.41462898254395</v>
+        <v>2.41462922096252</v>
       </c>
       <c r="H17" t="n">
         <v>14217</v>
@@ -891,7 +891,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G18" t="n">
-        <v>2.41462898254395</v>
+        <v>2.41462922096252</v>
       </c>
       <c r="H18" t="n">
         <v>18543</v>
@@ -949,7 +949,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G20" t="n">
-        <v>2.29741406440735</v>
+        <v>2.29741430282593</v>
       </c>
       <c r="H20" t="n">
         <v>9023</v>
@@ -978,7 +978,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G21" t="n">
-        <v>2.3286714553833</v>
+        <v>2.32867169380188</v>
       </c>
       <c r="H21" t="n">
         <v>6070</v>
@@ -1007,7 +1007,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G22" t="n">
-        <v>2.30522871017456</v>
+        <v>2.30522847175598</v>
       </c>
       <c r="H22" t="n">
         <v>7688</v>
@@ -1036,7 +1036,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G23" t="n">
-        <v>2.29741406440735</v>
+        <v>2.29741430282593</v>
       </c>
       <c r="H23" t="n">
         <v>6069</v>
@@ -1094,7 +1094,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G25" t="n">
-        <v>1.78948259353638</v>
+        <v>1.7894823551178</v>
       </c>
       <c r="H25" t="n">
         <v>29015</v>
@@ -1210,7 +1210,7 @@
         <v>1</v>
       </c>
       <c r="G29" t="n">
-        <v>0.781433403491974</v>
+        <v>0.781433463096619</v>
       </c>
       <c r="H29" t="n">
         <v>16056</v>
@@ -1326,7 +1326,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G33" t="n">
-        <v>1.99265515804291</v>
+        <v>1.99265503883362</v>
       </c>
       <c r="H33" t="n">
         <v>23570</v>
@@ -1558,7 +1558,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G41" t="n">
-        <v>2.51621556282043</v>
+        <v>2.51621580123901</v>
       </c>
       <c r="H41" t="n">
         <v>12434</v>
@@ -1587,7 +1587,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G42" t="n">
-        <v>2.45370078086853</v>
+        <v>2.45370101928711</v>
       </c>
       <c r="H42" t="n">
         <v>6497</v>
@@ -1616,7 +1616,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G43" t="n">
-        <v>2.43025803565979</v>
+        <v>2.43025779724121</v>
       </c>
       <c r="H43" t="n">
         <v>31886</v>
@@ -1645,7 +1645,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G44" t="n">
-        <v>2.48495841026306</v>
+        <v>2.48495817184448</v>
       </c>
       <c r="H44" t="n">
         <v>10570</v>
@@ -1674,7 +1674,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G45" t="n">
-        <v>2.77408838272095</v>
+        <v>2.77408862113953</v>
       </c>
       <c r="H45" t="n">
         <v>276654</v>
@@ -1761,7 +1761,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G48" t="n">
-        <v>2.52402997016907</v>
+        <v>2.52403020858765</v>
       </c>
       <c r="H48" t="n">
         <v>14408</v>
@@ -1935,7 +1935,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G54" t="n">
-        <v>2.43025803565979</v>
+        <v>2.43025779724121</v>
       </c>
       <c r="H54" t="n">
         <v>6029</v>
@@ -1993,7 +1993,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G56" t="n">
-        <v>2.41462898254395</v>
+        <v>2.41462922096252</v>
       </c>
       <c r="H56" t="n">
         <v>6905</v>
@@ -2051,7 +2051,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G58" t="n">
-        <v>2.27397131919861</v>
+        <v>2.27397108078003</v>
       </c>
       <c r="H58" t="n">
         <v>5139</v>
@@ -2080,7 +2080,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G59" t="n">
-        <v>2.22708535194397</v>
+        <v>2.22708511352539</v>
       </c>
       <c r="H59" t="n">
         <v>10942</v>
@@ -2138,7 +2138,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G61" t="n">
-        <v>2.08642745018005</v>
+        <v>2.08642721176147</v>
       </c>
       <c r="H61" t="n">
         <v>24791</v>
@@ -2167,7 +2167,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G62" t="n">
-        <v>2.05516982078552</v>
+        <v>2.0551700592041</v>
       </c>
       <c r="H62" t="n">
         <v>7073</v>
@@ -2341,7 +2341,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G68" t="n">
-        <v>1.86762595176697</v>
+        <v>1.86762583255768</v>
       </c>
       <c r="H68" t="n">
         <v>5688</v>
@@ -2370,7 +2370,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G69" t="n">
-        <v>1.83636844158173</v>
+        <v>1.83636856079102</v>
       </c>
       <c r="H69" t="n">
         <v>7190</v>
@@ -2399,7 +2399,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G70" t="n">
-        <v>1.82073962688446</v>
+        <v>1.82073986530304</v>
       </c>
       <c r="H70" t="n">
         <v>19067</v>
@@ -2428,7 +2428,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G71" t="n">
-        <v>1.81292533874512</v>
+        <v>1.8129255771637</v>
       </c>
       <c r="H71" t="n">
         <v>7528</v>
@@ -2457,7 +2457,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G72" t="n">
-        <v>1.80511105060577</v>
+        <v>1.80511116981506</v>
       </c>
       <c r="H72" t="n">
         <v>6071</v>
@@ -2602,7 +2602,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G77" t="n">
-        <v>1.80511105060577</v>
+        <v>1.80511116981506</v>
       </c>
       <c r="H77" t="n">
         <v>15224</v>
@@ -2631,7 +2631,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G78" t="n">
-        <v>1.7738538980484</v>
+        <v>1.77385377883911</v>
       </c>
       <c r="H78" t="n">
         <v>12767</v>
@@ -2660,7 +2660,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G79" t="n">
-        <v>1.7504106760025</v>
+        <v>1.75041091442108</v>
       </c>
       <c r="H79" t="n">
         <v>18881</v>
@@ -2689,7 +2689,7 @@
         <v>2.25</v>
       </c>
       <c r="G80" t="n">
-        <v>1.75822532176971</v>
+        <v>1.75822520256042</v>
       </c>
       <c r="H80" t="n">
         <v>4825</v>
@@ -2718,7 +2718,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G81" t="n">
-        <v>1.7504106760025</v>
+        <v>1.75041091442108</v>
       </c>
       <c r="H81" t="n">
         <v>11995</v>
@@ -2747,7 +2747,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G82" t="n">
-        <v>1.85981166362762</v>
+        <v>1.85981178283691</v>
       </c>
       <c r="H82" t="n">
         <v>17718</v>
@@ -2776,7 +2776,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G83" t="n">
-        <v>1.85981166362762</v>
+        <v>1.85981178283691</v>
       </c>
       <c r="H83" t="n">
         <v>1959</v>
@@ -2805,7 +2805,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G84" t="n">
-        <v>1.85981166362762</v>
+        <v>1.85981178283691</v>
       </c>
       <c r="H84" t="n">
         <v>1535</v>
@@ -2834,7 +2834,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G85" t="n">
-        <v>1.83636844158173</v>
+        <v>1.83636856079102</v>
       </c>
       <c r="H85" t="n">
         <v>1560</v>
@@ -2863,7 +2863,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G86" t="n">
-        <v>1.78166818618774</v>
+        <v>1.78166806697845</v>
       </c>
       <c r="H86" t="n">
         <v>2070</v>
@@ -2892,7 +2892,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G87" t="n">
-        <v>1.73478209972382</v>
+        <v>1.7347823381424</v>
       </c>
       <c r="H87" t="n">
         <v>11269</v>
@@ -2921,7 +2921,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G88" t="n">
-        <v>1.73478209972382</v>
+        <v>1.7347823381424</v>
       </c>
       <c r="H88" t="n">
         <v>9381</v>
@@ -2950,7 +2950,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G89" t="n">
-        <v>1.78948259353638</v>
+        <v>1.7894823551178</v>
       </c>
       <c r="H89" t="n">
         <v>13120</v>
@@ -2979,7 +2979,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G90" t="n">
-        <v>1.70352494716644</v>
+        <v>1.70352482795715</v>
       </c>
       <c r="H90" t="n">
         <v>5489</v>
@@ -3066,7 +3066,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G93" t="n">
-        <v>1.70352494716644</v>
+        <v>1.70352482795715</v>
       </c>
       <c r="H93" t="n">
         <v>5250</v>
@@ -3095,7 +3095,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G94" t="n">
-        <v>1.6957106590271</v>
+        <v>1.69571042060852</v>
       </c>
       <c r="H94" t="n">
         <v>7592</v>
@@ -3240,7 +3240,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G99" t="n">
-        <v>2.26615715026855</v>
+        <v>2.26615691184998</v>
       </c>
       <c r="H99" t="n">
         <v>221937</v>
@@ -3269,7 +3269,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G100" t="n">
-        <v>2.08642745018005</v>
+        <v>2.08642721176147</v>
       </c>
       <c r="H100" t="n">
         <v>131201</v>
@@ -3356,7 +3356,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G103" t="n">
-        <v>2.00046968460083</v>
+        <v>2.00046944618225</v>
       </c>
       <c r="H103" t="n">
         <v>59949</v>
@@ -3385,7 +3385,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G104" t="n">
-        <v>1.93795502185822</v>
+        <v>1.93795490264893</v>
       </c>
       <c r="H104" t="n">
         <v>28640</v>
@@ -3414,7 +3414,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G105" t="n">
-        <v>1.88325440883636</v>
+        <v>1.88325452804565</v>
       </c>
       <c r="H105" t="n">
         <v>30798</v>
@@ -3443,7 +3443,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G106" t="n">
-        <v>1.8285539150238</v>
+        <v>1.82855415344238</v>
       </c>
       <c r="H106" t="n">
         <v>48556</v>
@@ -3472,7 +3472,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G107" t="n">
-        <v>1.74259638786316</v>
+        <v>1.74259650707245</v>
       </c>
       <c r="H107" t="n">
         <v>29505</v>
@@ -3588,7 +3588,7 @@
         <v>2.25</v>
       </c>
       <c r="G111" t="n">
-        <v>1.75822532176971</v>
+        <v>1.75822520256042</v>
       </c>
       <c r="H111" t="n">
         <v>12997</v>
@@ -3617,7 +3617,7 @@
         <v>2.25</v>
       </c>
       <c r="G112" t="n">
-        <v>1.75822532176971</v>
+        <v>1.75822520256042</v>
       </c>
       <c r="H112" t="n">
         <v>6892</v>
@@ -3646,7 +3646,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G113" t="n">
-        <v>1.6957106590271</v>
+        <v>1.69571042060852</v>
       </c>
       <c r="H113" t="n">
         <v>7676</v>
@@ -4139,7 +4139,7 @@
         <v>2.25</v>
       </c>
       <c r="G130" t="n">
-        <v>1.75822532176971</v>
+        <v>1.75822520256042</v>
       </c>
       <c r="H130" t="n">
         <v>83797</v>
@@ -4255,7 +4255,7 @@
         <v>1.75</v>
       </c>
       <c r="G134" t="n">
-        <v>1.36750853061676</v>
+        <v>1.36750841140747</v>
       </c>
       <c r="H134" t="n">
         <v>31791</v>
@@ -4342,7 +4342,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G137" t="n">
-        <v>1.42220890522003</v>
+        <v>1.42220878601074</v>
       </c>
       <c r="H137" t="n">
         <v>10331</v>
@@ -4400,7 +4400,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G139" t="n">
-        <v>1.46128046512604</v>
+        <v>1.46128058433533</v>
       </c>
       <c r="H139" t="n">
         <v>173037</v>
@@ -4458,7 +4458,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G141" t="n">
-        <v>1.47690916061401</v>
+        <v>1.47690904140472</v>
       </c>
       <c r="H141" t="n">
         <v>16351</v>
@@ -4516,7 +4516,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G143" t="n">
-        <v>1.42220890522003</v>
+        <v>1.42220878601074</v>
       </c>
       <c r="H143" t="n">
         <v>15680</v>
@@ -4574,7 +4574,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G145" t="n">
-        <v>1.45346617698669</v>
+        <v>1.4534660577774</v>
       </c>
       <c r="H145" t="n">
         <v>20080</v>
@@ -4603,7 +4603,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G146" t="n">
-        <v>1.43002319335938</v>
+        <v>1.43002307415009</v>
       </c>
       <c r="H146" t="n">
         <v>5668</v>
@@ -4661,7 +4661,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G148" t="n">
-        <v>1.43002319335938</v>
+        <v>1.43002307415009</v>
       </c>
       <c r="H148" t="n">
         <v>3047</v>
@@ -4719,7 +4719,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G150" t="n">
-        <v>1.43002319335938</v>
+        <v>1.43002307415009</v>
       </c>
       <c r="H150" t="n">
         <v>3668</v>
@@ -4748,7 +4748,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G151" t="n">
-        <v>1.43002319335938</v>
+        <v>1.43002307415009</v>
       </c>
       <c r="H151" t="n">
         <v>20454</v>
@@ -4806,7 +4806,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G153" t="n">
-        <v>1.42220890522003</v>
+        <v>1.42220878601074</v>
       </c>
       <c r="H153" t="n">
         <v>9667</v>
@@ -4864,7 +4864,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G155" t="n">
-        <v>1.50035226345062</v>
+        <v>1.50035214424133</v>
       </c>
       <c r="H155" t="n">
         <v>11333</v>
@@ -4922,7 +4922,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G157" t="n">
-        <v>1.50816643238068</v>
+        <v>1.50816655158997</v>
       </c>
       <c r="H157" t="n">
         <v>300</v>
@@ -4951,7 +4951,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G158" t="n">
-        <v>1.50035226345062</v>
+        <v>1.50035214424133</v>
       </c>
       <c r="H158" t="n">
         <v>230</v>
@@ -4980,7 +4980,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G159" t="n">
-        <v>1.48472344875336</v>
+        <v>1.48472356796265</v>
       </c>
       <c r="H159" t="n">
         <v>1540</v>
@@ -5009,7 +5009,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G160" t="n">
-        <v>1.46128046512604</v>
+        <v>1.46128058433533</v>
       </c>
       <c r="H160" t="n">
         <v>3965</v>
@@ -5038,7 +5038,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G161" t="n">
-        <v>1.47690916061401</v>
+        <v>1.47690904140472</v>
       </c>
       <c r="H161" t="n">
         <v>4796</v>
@@ -5067,7 +5067,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G162" t="n">
-        <v>1.46128046512604</v>
+        <v>1.46128058433533</v>
       </c>
       <c r="H162" t="n">
         <v>1540</v>
@@ -5154,7 +5154,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G165" t="n">
-        <v>1.45346617698669</v>
+        <v>1.4534660577774</v>
       </c>
       <c r="H165" t="n">
         <v>815</v>
@@ -5270,7 +5270,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G169" t="n">
-        <v>1.47690916061401</v>
+        <v>1.47690904140472</v>
       </c>
       <c r="H169" t="n">
         <v>12338</v>
@@ -5299,7 +5299,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G170" t="n">
-        <v>1.48472344875336</v>
+        <v>1.48472356796265</v>
       </c>
       <c r="H170" t="n">
         <v>6190</v>
@@ -5328,7 +5328,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G171" t="n">
-        <v>1.47690916061401</v>
+        <v>1.47690904140472</v>
       </c>
       <c r="H171" t="n">
         <v>7601</v>
@@ -5357,7 +5357,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G172" t="n">
-        <v>1.47690916061401</v>
+        <v>1.47690904140472</v>
       </c>
       <c r="H172" t="n">
         <v>2406</v>
@@ -5386,7 +5386,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G173" t="n">
-        <v>1.46128046512604</v>
+        <v>1.46128058433533</v>
       </c>
       <c r="H173" t="n">
         <v>902</v>
@@ -5473,7 +5473,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G176" t="n">
-        <v>1.46128046512604</v>
+        <v>1.46128058433533</v>
       </c>
       <c r="H176" t="n">
         <v>13742</v>
@@ -5502,7 +5502,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G177" t="n">
-        <v>1.52379524707794</v>
+        <v>1.52379512786865</v>
       </c>
       <c r="H177" t="n">
         <v>51119</v>
@@ -5560,7 +5560,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G179" t="n">
-        <v>1.48472344875336</v>
+        <v>1.48472356796265</v>
       </c>
       <c r="H179" t="n">
         <v>7463</v>
@@ -5647,7 +5647,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G182" t="n">
-        <v>1.47690916061401</v>
+        <v>1.47690904140472</v>
       </c>
       <c r="H182" t="n">
         <v>1510</v>
@@ -5705,7 +5705,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G184" t="n">
-        <v>1.45346617698669</v>
+        <v>1.4534660577774</v>
       </c>
       <c r="H184" t="n">
         <v>3021</v>
@@ -5734,7 +5734,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G185" t="n">
-        <v>1.43783760070801</v>
+        <v>1.43783748149872</v>
       </c>
       <c r="H185" t="n">
         <v>3980</v>
@@ -5850,7 +5850,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G189" t="n">
-        <v>1.62538146972656</v>
+        <v>1.62538135051727</v>
       </c>
       <c r="H189" t="n">
         <v>39826</v>
@@ -5879,7 +5879,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G190" t="n">
-        <v>1.52379524707794</v>
+        <v>1.52379512786865</v>
       </c>
       <c r="H190" t="n">
         <v>29552</v>
@@ -5908,7 +5908,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G191" t="n">
-        <v>1.52379524707794</v>
+        <v>1.52379512786865</v>
       </c>
       <c r="H191" t="n">
         <v>10729</v>
@@ -5937,7 +5937,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G192" t="n">
-        <v>1.48472344875336</v>
+        <v>1.48472356796265</v>
       </c>
       <c r="H192" t="n">
         <v>13618</v>
@@ -5966,7 +5966,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G193" t="n">
-        <v>1.48472344875336</v>
+        <v>1.48472356796265</v>
       </c>
       <c r="H193" t="n">
         <v>14381</v>
@@ -5995,7 +5995,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G194" t="n">
-        <v>1.48472344875336</v>
+        <v>1.48472356796265</v>
       </c>
       <c r="H194" t="n">
         <v>4773</v>
@@ -6053,7 +6053,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G196" t="n">
-        <v>1.48472344875336</v>
+        <v>1.48472356796265</v>
       </c>
       <c r="H196" t="n">
         <v>4429</v>
@@ -6082,7 +6082,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G197" t="n">
-        <v>1.48472344875336</v>
+        <v>1.48472356796265</v>
       </c>
       <c r="H197" t="n">
         <v>7415</v>
@@ -6140,7 +6140,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G199" t="n">
-        <v>1.48472344875336</v>
+        <v>1.48472356796265</v>
       </c>
       <c r="H199" t="n">
         <v>11625</v>
@@ -6169,7 +6169,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G200" t="n">
-        <v>1.48472344875336</v>
+        <v>1.48472356796265</v>
       </c>
       <c r="H200" t="n">
         <v>750</v>
@@ -6198,7 +6198,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G201" t="n">
-        <v>1.48472344875336</v>
+        <v>1.48472356796265</v>
       </c>
       <c r="H201" t="n">
         <v>1501</v>
@@ -6227,7 +6227,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G202" t="n">
-        <v>1.47690916061401</v>
+        <v>1.47690904140472</v>
       </c>
       <c r="H202" t="n">
         <v>7610</v>
@@ -6256,7 +6256,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G203" t="n">
-        <v>1.48472344875336</v>
+        <v>1.48472356796265</v>
       </c>
       <c r="H203" t="n">
         <v>5280</v>
@@ -6285,7 +6285,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G204" t="n">
-        <v>1.531609416008</v>
+        <v>1.53160965442657</v>
       </c>
       <c r="H204" t="n">
         <v>8646</v>
@@ -6314,7 +6314,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G205" t="n">
-        <v>1.50816643238068</v>
+        <v>1.50816655158997</v>
       </c>
       <c r="H205" t="n">
         <v>23070</v>
@@ -6343,7 +6343,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G206" t="n">
-        <v>1.48472344875336</v>
+        <v>1.48472356796265</v>
       </c>
       <c r="H206" t="n">
         <v>7790</v>
@@ -6372,7 +6372,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G207" t="n">
-        <v>1.48472344875336</v>
+        <v>1.48472356796265</v>
       </c>
       <c r="H207" t="n">
         <v>5950</v>
@@ -6459,7 +6459,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G210" t="n">
-        <v>1.52379524707794</v>
+        <v>1.52379512786865</v>
       </c>
       <c r="H210" t="n">
         <v>3092</v>
@@ -6546,7 +6546,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G213" t="n">
-        <v>1.5550525188446</v>
+        <v>1.55505263805389</v>
       </c>
       <c r="H213" t="n">
         <v>7649</v>
@@ -6604,7 +6604,7 @@
         <v>2</v>
       </c>
       <c r="G215" t="n">
-        <v>1.56286680698395</v>
+        <v>1.56286692619324</v>
       </c>
       <c r="H215" t="n">
         <v>7270</v>
@@ -6633,7 +6633,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G216" t="n">
-        <v>1.50816643238068</v>
+        <v>1.50816655158997</v>
       </c>
       <c r="H216" t="n">
         <v>15002</v>
@@ -6662,7 +6662,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G217" t="n">
-        <v>1.52379524707794</v>
+        <v>1.52379512786865</v>
       </c>
       <c r="H217" t="n">
         <v>9361</v>
@@ -6720,7 +6720,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G219" t="n">
-        <v>1.531609416008</v>
+        <v>1.53160965442657</v>
       </c>
       <c r="H219" t="n">
         <v>16116</v>
@@ -6778,7 +6778,7 @@
         <v>2</v>
       </c>
       <c r="G221" t="n">
-        <v>1.56286680698395</v>
+        <v>1.56286692619324</v>
       </c>
       <c r="H221" t="n">
         <v>25291</v>
@@ -6807,7 +6807,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G222" t="n">
-        <v>1.61756718158722</v>
+        <v>1.61756706237793</v>
       </c>
       <c r="H222" t="n">
         <v>33429</v>
@@ -6865,7 +6865,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G224" t="n">
-        <v>1.5550525188446</v>
+        <v>1.55505263805389</v>
       </c>
       <c r="H224" t="n">
         <v>22722</v>
@@ -6923,7 +6923,7 @@
         <v>2</v>
       </c>
       <c r="G226" t="n">
-        <v>1.56286680698395</v>
+        <v>1.56286692619324</v>
       </c>
       <c r="H226" t="n">
         <v>13694</v>
@@ -7068,7 +7068,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G231" t="n">
-        <v>1.48472344875336</v>
+        <v>1.48472356796265</v>
       </c>
       <c r="H231" t="n">
         <v>2054</v>
@@ -7126,7 +7126,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G233" t="n">
-        <v>1.52379524707794</v>
+        <v>1.52379512786865</v>
       </c>
       <c r="H233" t="n">
         <v>6905</v>
@@ -7184,7 +7184,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G235" t="n">
-        <v>1.43002319335938</v>
+        <v>1.43002307415009</v>
       </c>
       <c r="H235" t="n">
         <v>7002</v>
@@ -7213,7 +7213,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G236" t="n">
-        <v>1.46128046512604</v>
+        <v>1.46128058433533</v>
       </c>
       <c r="H236" t="n">
         <v>2358</v>
@@ -7242,7 +7242,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G237" t="n">
-        <v>1.47690916061401</v>
+        <v>1.47690904140472</v>
       </c>
       <c r="H237" t="n">
         <v>3415</v>
@@ -7271,7 +7271,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G238" t="n">
-        <v>1.43783760070801</v>
+        <v>1.43783748149872</v>
       </c>
       <c r="H238" t="n">
         <v>1692</v>
@@ -7358,7 +7358,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G241" t="n">
-        <v>1.52379524707794</v>
+        <v>1.52379512786865</v>
       </c>
       <c r="H241" t="n">
         <v>5500</v>
@@ -7387,7 +7387,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G242" t="n">
-        <v>1.52379524707794</v>
+        <v>1.52379512786865</v>
       </c>
       <c r="H242" t="n">
         <v>6897</v>
@@ -7416,7 +7416,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G243" t="n">
-        <v>1.50035226345062</v>
+        <v>1.50035214424133</v>
       </c>
       <c r="H243" t="n">
         <v>2774</v>
@@ -7445,7 +7445,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G244" t="n">
-        <v>1.50035226345062</v>
+        <v>1.50035214424133</v>
       </c>
       <c r="H244" t="n">
         <v>2142</v>
@@ -7503,7 +7503,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G246" t="n">
-        <v>1.50035226345062</v>
+        <v>1.50035214424133</v>
       </c>
       <c r="H246" t="n">
         <v>6837</v>
@@ -7532,7 +7532,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G247" t="n">
-        <v>1.50035226345062</v>
+        <v>1.50035214424133</v>
       </c>
       <c r="H247" t="n">
         <v>9596</v>
@@ -7561,7 +7561,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G248" t="n">
-        <v>1.50035226345062</v>
+        <v>1.50035214424133</v>
       </c>
       <c r="H248" t="n">
         <v>3796</v>
@@ -7619,7 +7619,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G250" t="n">
-        <v>1.50035226345062</v>
+        <v>1.50035214424133</v>
       </c>
       <c r="H250" t="n">
         <v>16130</v>
@@ -7648,7 +7648,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G251" t="n">
-        <v>1.50816643238068</v>
+        <v>1.50816655158997</v>
       </c>
       <c r="H251" t="n">
         <v>4699</v>
@@ -7706,7 +7706,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G253" t="n">
-        <v>1.47690916061401</v>
+        <v>1.47690904140472</v>
       </c>
       <c r="H253" t="n">
         <v>5630</v>
@@ -7735,7 +7735,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G254" t="n">
-        <v>1.50035226345062</v>
+        <v>1.50035214424133</v>
       </c>
       <c r="H254" t="n">
         <v>10860</v>
@@ -7851,7 +7851,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G258" t="n">
-        <v>1.83636844158173</v>
+        <v>1.83636856079102</v>
       </c>
       <c r="H258" t="n">
         <v>125566</v>
@@ -7880,7 +7880,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G259" t="n">
-        <v>1.7738538980484</v>
+        <v>1.77385377883911</v>
       </c>
       <c r="H259" t="n">
         <v>144770</v>
@@ -7909,7 +7909,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G260" t="n">
-        <v>1.76603949069977</v>
+        <v>1.76603937149048</v>
       </c>
       <c r="H260" t="n">
         <v>45306</v>
@@ -7938,7 +7938,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G261" t="n">
-        <v>1.73478209972382</v>
+        <v>1.7347823381424</v>
       </c>
       <c r="H261" t="n">
         <v>35690</v>
@@ -7967,7 +7967,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G262" t="n">
-        <v>1.72696781158447</v>
+        <v>1.72696793079376</v>
       </c>
       <c r="H262" t="n">
         <v>17933</v>
@@ -7996,7 +7996,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G263" t="n">
-        <v>1.67226767539978</v>
+        <v>1.67226755619049</v>
       </c>
       <c r="H263" t="n">
         <v>45589</v>
@@ -8112,7 +8112,7 @@
         <v>2.25</v>
       </c>
       <c r="G267" t="n">
-        <v>1.75822532176971</v>
+        <v>1.75822520256042</v>
       </c>
       <c r="H267" t="n">
         <v>48617</v>
@@ -8228,7 +8228,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G271" t="n">
-        <v>1.79729688167572</v>
+        <v>1.79729664325714</v>
       </c>
       <c r="H271" t="n">
         <v>110444</v>
@@ -8315,7 +8315,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G274" t="n">
-        <v>2.78190302848816</v>
+        <v>2.78190279006958</v>
       </c>
       <c r="H274" t="n">
         <v>248750</v>
@@ -8431,7 +8431,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G278" t="n">
-        <v>2.36774301528931</v>
+        <v>2.36774325370789</v>
       </c>
       <c r="H278" t="n">
         <v>155933</v>
@@ -8460,7 +8460,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G279" t="n">
-        <v>2.32085752487183</v>
+        <v>2.32085728645325</v>
       </c>
       <c r="H279" t="n">
         <v>23589</v>
@@ -8489,7 +8489,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G280" t="n">
-        <v>2.36774301528931</v>
+        <v>2.36774325370789</v>
       </c>
       <c r="H280" t="n">
         <v>42641</v>
@@ -8518,7 +8518,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G281" t="n">
-        <v>2.26615715026855</v>
+        <v>2.26615691184998</v>
       </c>
       <c r="H281" t="n">
         <v>36137</v>
@@ -8547,7 +8547,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G282" t="n">
-        <v>2.66468811035156</v>
+        <v>2.66468787193298</v>
       </c>
       <c r="H282" t="n">
         <v>180543</v>
@@ -8576,7 +8576,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G283" t="n">
-        <v>2.48495841026306</v>
+        <v>2.48495817184448</v>
       </c>
       <c r="H283" t="n">
         <v>174485</v>
@@ -8605,7 +8605,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G284" t="n">
-        <v>2.41462898254395</v>
+        <v>2.41462922096252</v>
       </c>
       <c r="H284" t="n">
         <v>141085</v>
@@ -8634,7 +8634,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G285" t="n">
-        <v>2.41462898254395</v>
+        <v>2.41462922096252</v>
       </c>
       <c r="H285" t="n">
         <v>32999</v>
@@ -8750,7 +8750,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G289" t="n">
-        <v>2.5084011554718</v>
+        <v>2.50840139389038</v>
       </c>
       <c r="H289" t="n">
         <v>75755</v>
@@ -8779,7 +8779,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G290" t="n">
-        <v>2.48495841026306</v>
+        <v>2.48495817184448</v>
       </c>
       <c r="H290" t="n">
         <v>43039</v>
@@ -8808,7 +8808,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G291" t="n">
-        <v>2.45370078086853</v>
+        <v>2.45370101928711</v>
       </c>
       <c r="H291" t="n">
         <v>62585</v>
@@ -8866,7 +8866,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G293" t="n">
-        <v>2.30522871017456</v>
+        <v>2.30522847175598</v>
       </c>
       <c r="H293" t="n">
         <v>63123</v>
@@ -8924,7 +8924,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G295" t="n">
-        <v>2.21145629882812</v>
+        <v>2.2114565372467</v>
       </c>
       <c r="H295" t="n">
         <v>127250</v>
@@ -8953,7 +8953,7 @@
         <v>2.75</v>
       </c>
       <c r="G296" t="n">
-        <v>2.14894199371338</v>
+        <v>2.1489417552948</v>
       </c>
       <c r="H296" t="n">
         <v>145249</v>
@@ -8982,7 +8982,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G297" t="n">
-        <v>2.07861280441284</v>
+        <v>2.07861256599426</v>
       </c>
       <c r="H297" t="n">
         <v>57099</v>
@@ -9040,7 +9040,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G299" t="n">
-        <v>2.18801355361938</v>
+        <v>2.18801331520081</v>
       </c>
       <c r="H299" t="n">
         <v>145545</v>
@@ -9127,7 +9127,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G302" t="n">
-        <v>2.10987019538879</v>
+        <v>2.10987043380737</v>
       </c>
       <c r="H302" t="n">
         <v>17255</v>
@@ -9185,7 +9185,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G304" t="n">
-        <v>2.08642745018005</v>
+        <v>2.08642721176147</v>
       </c>
       <c r="H304" t="n">
         <v>19530</v>
@@ -9214,7 +9214,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G305" t="n">
-        <v>2.08642745018005</v>
+        <v>2.08642721176147</v>
       </c>
       <c r="H305" t="n">
         <v>13542</v>
@@ -9243,7 +9243,7 @@
         <v>2.75</v>
       </c>
       <c r="G306" t="n">
-        <v>2.14894199371338</v>
+        <v>2.1489417552948</v>
       </c>
       <c r="H306" t="n">
         <v>29862</v>
@@ -9301,7 +9301,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G308" t="n">
-        <v>2.18801355361938</v>
+        <v>2.18801331520081</v>
       </c>
       <c r="H308" t="n">
         <v>36108</v>
@@ -9388,7 +9388,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G311" t="n">
-        <v>2.13331294059753</v>
+        <v>2.13331317901611</v>
       </c>
       <c r="H311" t="n">
         <v>20423</v>
@@ -9417,7 +9417,7 @@
         <v>2.75</v>
       </c>
       <c r="G312" t="n">
-        <v>2.14894199371338</v>
+        <v>2.1489417552948</v>
       </c>
       <c r="H312" t="n">
         <v>12417</v>
@@ -9475,7 +9475,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G314" t="n">
-        <v>2.19582796096802</v>
+        <v>2.19582772254944</v>
       </c>
       <c r="H314" t="n">
         <v>90558</v>
@@ -9504,7 +9504,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G315" t="n">
-        <v>2.21145629882812</v>
+        <v>2.2114565372467</v>
       </c>
       <c r="H315" t="n">
         <v>24918</v>
@@ -9620,7 +9620,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G319" t="n">
-        <v>2.43025803565979</v>
+        <v>2.43025779724121</v>
       </c>
       <c r="H319" t="n">
         <v>373672</v>
@@ -9707,7 +9707,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G322" t="n">
-        <v>2.32085752487183</v>
+        <v>2.32085728645325</v>
       </c>
       <c r="H322" t="n">
         <v>120703</v>
@@ -9736,7 +9736,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G323" t="n">
-        <v>2.26615715026855</v>
+        <v>2.26615691184998</v>
       </c>
       <c r="H323" t="n">
         <v>66785</v>
@@ -9794,7 +9794,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G325" t="n">
-        <v>2.36774301528931</v>
+        <v>2.36774325370789</v>
       </c>
       <c r="H325" t="n">
         <v>123555</v>
@@ -9823,7 +9823,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G326" t="n">
-        <v>2.3286714553833</v>
+        <v>2.32867169380188</v>
       </c>
       <c r="H326" t="n">
         <v>34122</v>
@@ -9881,7 +9881,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G328" t="n">
-        <v>2.27397131919861</v>
+        <v>2.27397108078003</v>
       </c>
       <c r="H328" t="n">
         <v>24472</v>
@@ -9910,7 +9910,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G329" t="n">
-        <v>2.27397131919861</v>
+        <v>2.27397108078003</v>
       </c>
       <c r="H329" t="n">
         <v>19303</v>
@@ -9939,7 +9939,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G330" t="n">
-        <v>2.26615715026855</v>
+        <v>2.26615691184998</v>
       </c>
       <c r="H330" t="n">
         <v>9551</v>
@@ -9968,7 +9968,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G331" t="n">
-        <v>2.27397131919861</v>
+        <v>2.27397108078003</v>
       </c>
       <c r="H331" t="n">
         <v>11915</v>
@@ -9997,7 +9997,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G332" t="n">
-        <v>2.19582796096802</v>
+        <v>2.19582772254944</v>
       </c>
       <c r="H332" t="n">
         <v>23745</v>
@@ -10026,7 +10026,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G333" t="n">
-        <v>2.25834274291992</v>
+        <v>2.25834250450134</v>
       </c>
       <c r="H333" t="n">
         <v>41046</v>
@@ -10055,7 +10055,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G334" t="n">
-        <v>2.30522871017456</v>
+        <v>2.30522847175598</v>
       </c>
       <c r="H334" t="n">
         <v>27597</v>
@@ -10084,7 +10084,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G335" t="n">
-        <v>2.29741406440735</v>
+        <v>2.29741430282593</v>
       </c>
       <c r="H335" t="n">
         <v>14756</v>
@@ -10113,7 +10113,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G336" t="n">
-        <v>2.36774301528931</v>
+        <v>2.36774325370789</v>
       </c>
       <c r="H336" t="n">
         <v>60523</v>
@@ -10142,7 +10142,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G337" t="n">
-        <v>2.30522871017456</v>
+        <v>2.30522847175598</v>
       </c>
       <c r="H337" t="n">
         <v>70691</v>
@@ -10200,7 +10200,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G339" t="n">
-        <v>2.3286714553833</v>
+        <v>2.32867169380188</v>
       </c>
       <c r="H339" t="n">
         <v>58353</v>
@@ -10229,7 +10229,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G340" t="n">
-        <v>2.26615715026855</v>
+        <v>2.26615691184998</v>
       </c>
       <c r="H340" t="n">
         <v>69321</v>
@@ -10258,7 +10258,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G341" t="n">
-        <v>2.25834274291992</v>
+        <v>2.25834250450134</v>
       </c>
       <c r="H341" t="n">
         <v>19671</v>
@@ -10287,7 +10287,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G342" t="n">
-        <v>2.25834274291992</v>
+        <v>2.25834250450134</v>
       </c>
       <c r="H342" t="n">
         <v>9250</v>
@@ -10316,7 +10316,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G343" t="n">
-        <v>2.29741406440735</v>
+        <v>2.29741430282593</v>
       </c>
       <c r="H343" t="n">
         <v>68674</v>
@@ -10345,7 +10345,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G344" t="n">
-        <v>2.5084011554718</v>
+        <v>2.50840139389038</v>
       </c>
       <c r="H344" t="n">
         <v>306118</v>
@@ -10403,7 +10403,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G346" t="n">
-        <v>2.39900040626526</v>
+        <v>2.39900064468384</v>
       </c>
       <c r="H346" t="n">
         <v>45418</v>
@@ -10432,7 +10432,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G347" t="n">
-        <v>2.41462898254395</v>
+        <v>2.41462922096252</v>
       </c>
       <c r="H347" t="n">
         <v>25889</v>
@@ -10519,7 +10519,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G350" t="n">
-        <v>2.33648586273193</v>
+        <v>2.33648610115051</v>
       </c>
       <c r="H350" t="n">
         <v>30279</v>
@@ -10548,7 +10548,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G351" t="n">
-        <v>2.30522871017456</v>
+        <v>2.30522847175598</v>
       </c>
       <c r="H351" t="n">
         <v>10524</v>
@@ -10577,7 +10577,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G352" t="n">
-        <v>2.25834274291992</v>
+        <v>2.25834250450134</v>
       </c>
       <c r="H352" t="n">
         <v>34161</v>
@@ -10606,7 +10606,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G353" t="n">
-        <v>2.26615715026855</v>
+        <v>2.26615691184998</v>
       </c>
       <c r="H353" t="n">
         <v>11227</v>
@@ -10635,7 +10635,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G354" t="n">
-        <v>2.27397131919861</v>
+        <v>2.27397108078003</v>
       </c>
       <c r="H354" t="n">
         <v>5260</v>
@@ -10664,7 +10664,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G355" t="n">
-        <v>2.30522871017456</v>
+        <v>2.30522847175598</v>
       </c>
       <c r="H355" t="n">
         <v>6469</v>
@@ -10722,7 +10722,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G357" t="n">
-        <v>2.3286714553833</v>
+        <v>2.32867169380188</v>
       </c>
       <c r="H357" t="n">
         <v>14916</v>
@@ -10780,7 +10780,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G359" t="n">
-        <v>2.30522871017456</v>
+        <v>2.30522847175598</v>
       </c>
       <c r="H359" t="n">
         <v>21418</v>
@@ -10838,7 +10838,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G361" t="n">
-        <v>2.30522871017456</v>
+        <v>2.30522847175598</v>
       </c>
       <c r="H361" t="n">
         <v>12853</v>
@@ -10867,7 +10867,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G362" t="n">
-        <v>2.39900040626526</v>
+        <v>2.39900064468384</v>
       </c>
       <c r="H362" t="n">
         <v>53897</v>
@@ -10896,7 +10896,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G363" t="n">
-        <v>2.29741406440735</v>
+        <v>2.29741430282593</v>
       </c>
       <c r="H363" t="n">
         <v>67201</v>
@@ -10954,7 +10954,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G365" t="n">
-        <v>2.19582796096802</v>
+        <v>2.19582772254944</v>
       </c>
       <c r="H365" t="n">
         <v>66685</v>
@@ -10983,7 +10983,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G366" t="n">
-        <v>2.19582796096802</v>
+        <v>2.19582772254944</v>
       </c>
       <c r="H366" t="n">
         <v>21330</v>
@@ -11012,7 +11012,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G367" t="n">
-        <v>2.22708535194397</v>
+        <v>2.22708511352539</v>
       </c>
       <c r="H367" t="n">
         <v>8955</v>
@@ -11041,7 +11041,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G368" t="n">
-        <v>2.22708535194397</v>
+        <v>2.22708511352539</v>
       </c>
       <c r="H368" t="n">
         <v>5899</v>
@@ -11070,7 +11070,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G369" t="n">
-        <v>2.19582796096802</v>
+        <v>2.19582772254944</v>
       </c>
       <c r="H369" t="n">
         <v>25375</v>
@@ -11099,7 +11099,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G370" t="n">
-        <v>2.19582796096802</v>
+        <v>2.19582772254944</v>
       </c>
       <c r="H370" t="n">
         <v>2922</v>
@@ -11157,7 +11157,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G372" t="n">
-        <v>2.22708535194397</v>
+        <v>2.22708511352539</v>
       </c>
       <c r="H372" t="n">
         <v>12004</v>
@@ -11215,7 +11215,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G374" t="n">
-        <v>2.21145629882812</v>
+        <v>2.2114565372467</v>
       </c>
       <c r="H374" t="n">
         <v>1201</v>
@@ -11273,7 +11273,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G376" t="n">
-        <v>2.18801355361938</v>
+        <v>2.18801331520081</v>
       </c>
       <c r="H376" t="n">
         <v>4715</v>
@@ -11302,7 +11302,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G377" t="n">
-        <v>2.22708535194397</v>
+        <v>2.22708511352539</v>
       </c>
       <c r="H377" t="n">
         <v>4658</v>
@@ -11360,7 +11360,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G379" t="n">
-        <v>2.22708535194397</v>
+        <v>2.22708511352539</v>
       </c>
       <c r="H379" t="n">
         <v>7003</v>
@@ -11447,7 +11447,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G382" t="n">
-        <v>2.21145629882812</v>
+        <v>2.2114565372467</v>
       </c>
       <c r="H382" t="n">
         <v>7415</v>
@@ -11476,7 +11476,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G383" t="n">
-        <v>2.25834274291992</v>
+        <v>2.25834250450134</v>
       </c>
       <c r="H383" t="n">
         <v>38535</v>
@@ -11505,7 +11505,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G384" t="n">
-        <v>2.23489952087402</v>
+        <v>2.23489928245544</v>
       </c>
       <c r="H384" t="n">
         <v>7914</v>
@@ -11534,7 +11534,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G385" t="n">
-        <v>2.23489952087402</v>
+        <v>2.23489928245544</v>
       </c>
       <c r="H385" t="n">
         <v>2794</v>
@@ -11563,7 +11563,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G386" t="n">
-        <v>2.25834274291992</v>
+        <v>2.25834250450134</v>
       </c>
       <c r="H386" t="n">
         <v>100</v>
@@ -11621,7 +11621,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G388" t="n">
-        <v>2.22708535194397</v>
+        <v>2.22708511352539</v>
       </c>
       <c r="H388" t="n">
         <v>100</v>
@@ -11650,7 +11650,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G389" t="n">
-        <v>2.18019938468933</v>
+        <v>2.18019914627075</v>
       </c>
       <c r="H389" t="n">
         <v>20929</v>
@@ -11679,7 +11679,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G390" t="n">
-        <v>2.19582796096802</v>
+        <v>2.19582772254944</v>
       </c>
       <c r="H390" t="n">
         <v>6870</v>
@@ -11708,7 +11708,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G391" t="n">
-        <v>2.23489952087402</v>
+        <v>2.23489928245544</v>
       </c>
       <c r="H391" t="n">
         <v>13073</v>
@@ -11737,7 +11737,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G392" t="n">
-        <v>2.22708535194397</v>
+        <v>2.22708511352539</v>
       </c>
       <c r="H392" t="n">
         <v>4464</v>
@@ -11824,7 +11824,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G395" t="n">
-        <v>2.26615715026855</v>
+        <v>2.26615691184998</v>
       </c>
       <c r="H395" t="n">
         <v>27151</v>
@@ -11853,7 +11853,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G396" t="n">
-        <v>2.22708535194397</v>
+        <v>2.22708511352539</v>
       </c>
       <c r="H396" t="n">
         <v>21203</v>
@@ -11882,7 +11882,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G397" t="n">
-        <v>2.21145629882812</v>
+        <v>2.2114565372467</v>
       </c>
       <c r="H397" t="n">
         <v>14364</v>
@@ -11911,7 +11911,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G398" t="n">
-        <v>2.23489952087402</v>
+        <v>2.23489928245544</v>
       </c>
       <c r="H398" t="n">
         <v>19480</v>
@@ -11940,7 +11940,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G399" t="n">
-        <v>2.25834274291992</v>
+        <v>2.25834250450134</v>
       </c>
       <c r="H399" t="n">
         <v>9326</v>
@@ -11998,7 +11998,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G401" t="n">
-        <v>2.27397131919861</v>
+        <v>2.27397108078003</v>
       </c>
       <c r="H401" t="n">
         <v>8887</v>
@@ -12027,7 +12027,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G402" t="n">
-        <v>2.28178572654724</v>
+        <v>2.28178548812866</v>
       </c>
       <c r="H402" t="n">
         <v>11823</v>
@@ -12085,7 +12085,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G404" t="n">
-        <v>2.28178572654724</v>
+        <v>2.28178548812866</v>
       </c>
       <c r="H404" t="n">
         <v>4961</v>
@@ -12114,7 +12114,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G405" t="n">
-        <v>2.26615715026855</v>
+        <v>2.26615691184998</v>
       </c>
       <c r="H405" t="n">
         <v>3645</v>
@@ -12172,7 +12172,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G407" t="n">
-        <v>2.26615715026855</v>
+        <v>2.26615691184998</v>
       </c>
       <c r="H407" t="n">
         <v>13225</v>
@@ -12259,7 +12259,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G410" t="n">
-        <v>2.27397131919861</v>
+        <v>2.27397108078003</v>
       </c>
       <c r="H410" t="n">
         <v>12237</v>
@@ -12288,7 +12288,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G411" t="n">
-        <v>2.26615715026855</v>
+        <v>2.26615691184998</v>
       </c>
       <c r="H411" t="n">
         <v>4008</v>
@@ -12375,7 +12375,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G414" t="n">
-        <v>2.22708535194397</v>
+        <v>2.22708511352539</v>
       </c>
       <c r="H414" t="n">
         <v>16306</v>
@@ -12404,7 +12404,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G415" t="n">
-        <v>2.22708535194397</v>
+        <v>2.22708511352539</v>
       </c>
       <c r="H415" t="n">
         <v>4789</v>
@@ -12462,7 +12462,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G417" t="n">
-        <v>2.25834274291992</v>
+        <v>2.25834250450134</v>
       </c>
       <c r="H417" t="n">
         <v>1700</v>
@@ -12491,7 +12491,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G418" t="n">
-        <v>2.27397131919861</v>
+        <v>2.27397108078003</v>
       </c>
       <c r="H418" t="n">
         <v>7095</v>
@@ -12636,7 +12636,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G423" t="n">
-        <v>2.25834274291992</v>
+        <v>2.25834250450134</v>
       </c>
       <c r="H423" t="n">
         <v>19254</v>
@@ -12665,7 +12665,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G424" t="n">
-        <v>2.25834274291992</v>
+        <v>2.25834250450134</v>
       </c>
       <c r="H424" t="n">
         <v>2892</v>
@@ -12781,7 +12781,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G428" t="n">
-        <v>2.28178572654724</v>
+        <v>2.28178548812866</v>
       </c>
       <c r="H428" t="n">
         <v>8669</v>
@@ -12810,7 +12810,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G429" t="n">
-        <v>2.27397131919861</v>
+        <v>2.27397108078003</v>
       </c>
       <c r="H429" t="n">
         <v>3175</v>
@@ -12839,7 +12839,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G430" t="n">
-        <v>2.26615715026855</v>
+        <v>2.26615691184998</v>
       </c>
       <c r="H430" t="n">
         <v>3551</v>
@@ -12868,7 +12868,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G431" t="n">
-        <v>2.27397131919861</v>
+        <v>2.27397108078003</v>
       </c>
       <c r="H431" t="n">
         <v>5595</v>
@@ -12955,7 +12955,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G434" t="n">
-        <v>2.30522871017456</v>
+        <v>2.30522847175598</v>
       </c>
       <c r="H434" t="n">
         <v>3559</v>
@@ -13013,7 +13013,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G436" t="n">
-        <v>2.28178572654724</v>
+        <v>2.28178548812866</v>
       </c>
       <c r="H436" t="n">
         <v>3312</v>
@@ -13042,7 +13042,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G437" t="n">
-        <v>2.27397131919861</v>
+        <v>2.27397108078003</v>
       </c>
       <c r="H437" t="n">
         <v>4699</v>
@@ -13071,7 +13071,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G438" t="n">
-        <v>2.28178572654724</v>
+        <v>2.28178548812866</v>
       </c>
       <c r="H438" t="n">
         <v>17639</v>
@@ -13100,7 +13100,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G439" t="n">
-        <v>2.30522871017456</v>
+        <v>2.30522847175598</v>
       </c>
       <c r="H439" t="n">
         <v>7059</v>
@@ -13129,7 +13129,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G440" t="n">
-        <v>2.29741406440735</v>
+        <v>2.29741430282593</v>
       </c>
       <c r="H440" t="n">
         <v>7441</v>
@@ -13187,7 +13187,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G442" t="n">
-        <v>2.33648586273193</v>
+        <v>2.33648610115051</v>
       </c>
       <c r="H442" t="n">
         <v>35567</v>
@@ -13245,7 +13245,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G444" t="n">
-        <v>2.42244338989258</v>
+        <v>2.42244362831116</v>
       </c>
       <c r="H444" t="n">
         <v>158865</v>
@@ -13274,7 +13274,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G445" t="n">
-        <v>2.32085752487183</v>
+        <v>2.32085728645325</v>
       </c>
       <c r="H445" t="n">
         <v>109510</v>
@@ -13303,7 +13303,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G446" t="n">
-        <v>2.3286714553833</v>
+        <v>2.32867169380188</v>
       </c>
       <c r="H446" t="n">
         <v>38929</v>
@@ -13361,7 +13361,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G448" t="n">
-        <v>2.29741406440735</v>
+        <v>2.29741430282593</v>
       </c>
       <c r="H448" t="n">
         <v>19867</v>
@@ -13448,7 +13448,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G451" t="n">
-        <v>2.28178572654724</v>
+        <v>2.28178548812866</v>
       </c>
       <c r="H451" t="n">
         <v>11688</v>
@@ -13477,7 +13477,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G452" t="n">
-        <v>2.27397131919861</v>
+        <v>2.27397108078003</v>
       </c>
       <c r="H452" t="n">
         <v>4236</v>
@@ -13506,7 +13506,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G453" t="n">
-        <v>2.25834274291992</v>
+        <v>2.25834250450134</v>
       </c>
       <c r="H453" t="n">
         <v>12264</v>
@@ -13535,7 +13535,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G454" t="n">
-        <v>2.25834274291992</v>
+        <v>2.25834250450134</v>
       </c>
       <c r="H454" t="n">
         <v>3217</v>
@@ -13593,7 +13593,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G456" t="n">
-        <v>2.27397131919861</v>
+        <v>2.27397108078003</v>
       </c>
       <c r="H456" t="n">
         <v>23276</v>
@@ -13622,7 +13622,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G457" t="n">
-        <v>2.26615715026855</v>
+        <v>2.26615691184998</v>
       </c>
       <c r="H457" t="n">
         <v>12905</v>
@@ -13651,7 +13651,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G458" t="n">
-        <v>2.26615715026855</v>
+        <v>2.26615691184998</v>
       </c>
       <c r="H458" t="n">
         <v>5857</v>
@@ -13680,7 +13680,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G459" t="n">
-        <v>2.27397131919861</v>
+        <v>2.27397108078003</v>
       </c>
       <c r="H459" t="n">
         <v>4372</v>
@@ -13709,7 +13709,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G460" t="n">
-        <v>2.26615715026855</v>
+        <v>2.26615691184998</v>
       </c>
       <c r="H460" t="n">
         <v>5248</v>
@@ -13738,7 +13738,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G461" t="n">
-        <v>2.27397131919861</v>
+        <v>2.27397108078003</v>
       </c>
       <c r="H461" t="n">
         <v>2391</v>
@@ -13767,7 +13767,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G462" t="n">
-        <v>2.25834274291992</v>
+        <v>2.25834250450134</v>
       </c>
       <c r="H462" t="n">
         <v>11311</v>
@@ -13796,7 +13796,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G463" t="n">
-        <v>2.27397131919861</v>
+        <v>2.27397108078003</v>
       </c>
       <c r="H463" t="n">
         <v>891</v>
@@ -13825,7 +13825,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G464" t="n">
-        <v>2.25834274291992</v>
+        <v>2.25834250450134</v>
       </c>
       <c r="H464" t="n">
         <v>893</v>
@@ -14028,7 +14028,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G471" t="n">
-        <v>2.25834274291992</v>
+        <v>2.25834250450134</v>
       </c>
       <c r="H471" t="n">
         <v>5598</v>
@@ -14086,7 +14086,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G473" t="n">
-        <v>2.25834274291992</v>
+        <v>2.25834250450134</v>
       </c>
       <c r="H473" t="n">
         <v>2692</v>
@@ -14115,7 +14115,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G474" t="n">
-        <v>2.28178572654724</v>
+        <v>2.28178548812866</v>
       </c>
       <c r="H474" t="n">
         <v>36315</v>
@@ -14144,7 +14144,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G475" t="n">
-        <v>2.26615715026855</v>
+        <v>2.26615691184998</v>
       </c>
       <c r="H475" t="n">
         <v>6319</v>
@@ -14173,7 +14173,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G476" t="n">
-        <v>2.26615715026855</v>
+        <v>2.26615691184998</v>
       </c>
       <c r="H476" t="n">
         <v>11654</v>
@@ -14202,7 +14202,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G477" t="n">
-        <v>2.26615715026855</v>
+        <v>2.26615691184998</v>
       </c>
       <c r="H477" t="n">
         <v>9741</v>
@@ -14289,7 +14289,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G480" t="n">
-        <v>2.18801355361938</v>
+        <v>2.18801331520081</v>
       </c>
       <c r="H480" t="n">
         <v>127127</v>
@@ -14347,7 +14347,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G482" t="n">
-        <v>2.05516982078552</v>
+        <v>2.0551700592041</v>
       </c>
       <c r="H482" t="n">
         <v>33954</v>
@@ -14376,7 +14376,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G483" t="n">
-        <v>2.05516982078552</v>
+        <v>2.0551700592041</v>
       </c>
       <c r="H483" t="n">
         <v>1310</v>
@@ -14434,7 +14434,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G485" t="n">
-        <v>2.04735517501831</v>
+        <v>2.04735541343689</v>
       </c>
       <c r="H485" t="n">
         <v>5465</v>
@@ -14492,7 +14492,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G487" t="n">
-        <v>2.05516982078552</v>
+        <v>2.0551700592041</v>
       </c>
       <c r="H487" t="n">
         <v>7884</v>
@@ -14521,7 +14521,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G488" t="n">
-        <v>2.09424161911011</v>
+        <v>2.09424138069153</v>
       </c>
       <c r="H488" t="n">
         <v>6344</v>
@@ -14579,7 +14579,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G490" t="n">
-        <v>2.03954100608826</v>
+        <v>2.03954124450684</v>
       </c>
       <c r="H490" t="n">
         <v>11032</v>
@@ -14608,7 +14608,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G491" t="n">
-        <v>2.05516982078552</v>
+        <v>2.0551700592041</v>
       </c>
       <c r="H491" t="n">
         <v>4461</v>
@@ -14637,7 +14637,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G492" t="n">
-        <v>1.99265515804291</v>
+        <v>1.99265503883362</v>
       </c>
       <c r="H492" t="n">
         <v>39507</v>
@@ -14695,7 +14695,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G494" t="n">
-        <v>2.02391266822815</v>
+        <v>2.02391242980957</v>
       </c>
       <c r="H494" t="n">
         <v>4454</v>
@@ -14724,7 +14724,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G495" t="n">
-        <v>2.02391266822815</v>
+        <v>2.02391242980957</v>
       </c>
       <c r="H495" t="n">
         <v>1453</v>
@@ -14782,7 +14782,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G497" t="n">
-        <v>1.99265515804291</v>
+        <v>1.99265503883362</v>
       </c>
       <c r="H497" t="n">
         <v>2512</v>
@@ -14811,7 +14811,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G498" t="n">
-        <v>2.00046968460083</v>
+        <v>2.00046944618225</v>
       </c>
       <c r="H498" t="n">
         <v>8797</v>
@@ -14840,7 +14840,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G499" t="n">
-        <v>2.00046968460083</v>
+        <v>2.00046944618225</v>
       </c>
       <c r="H499" t="n">
         <v>746</v>
@@ -14927,7 +14927,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G502" t="n">
-        <v>2.00046968460083</v>
+        <v>2.00046944618225</v>
       </c>
       <c r="H502" t="n">
         <v>6182</v>
@@ -14985,7 +14985,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G504" t="n">
-        <v>1.99265515804291</v>
+        <v>1.99265503883362</v>
       </c>
       <c r="H504" t="n">
         <v>3080</v>
@@ -15014,7 +15014,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G505" t="n">
-        <v>2.00046968460083</v>
+        <v>2.00046944618225</v>
       </c>
       <c r="H505" t="n">
         <v>350</v>
@@ -15130,7 +15130,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G509" t="n">
-        <v>2.00046968460083</v>
+        <v>2.00046944618225</v>
       </c>
       <c r="H509" t="n">
         <v>1703</v>
@@ -15188,7 +15188,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G511" t="n">
-        <v>2.00046968460083</v>
+        <v>2.00046944618225</v>
       </c>
       <c r="H511" t="n">
         <v>1228</v>
@@ -15217,7 +15217,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G512" t="n">
-        <v>2.00046968460083</v>
+        <v>2.00046944618225</v>
       </c>
       <c r="H512" t="n">
         <v>3230</v>
@@ -15391,7 +15391,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G518" t="n">
-        <v>2.09424161911011</v>
+        <v>2.09424138069153</v>
       </c>
       <c r="H518" t="n">
         <v>112388</v>
@@ -15420,7 +15420,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G519" t="n">
-        <v>2.08642745018005</v>
+        <v>2.08642721176147</v>
       </c>
       <c r="H519" t="n">
         <v>11274</v>
@@ -15449,7 +15449,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G520" t="n">
-        <v>2.07861280441284</v>
+        <v>2.07861256599426</v>
       </c>
       <c r="H520" t="n">
         <v>10226</v>
@@ -15507,7 +15507,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G522" t="n">
-        <v>2.05516982078552</v>
+        <v>2.0551700592041</v>
       </c>
       <c r="H522" t="n">
         <v>2500</v>
@@ -15536,7 +15536,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G523" t="n">
-        <v>2.08642745018005</v>
+        <v>2.08642721176147</v>
       </c>
       <c r="H523" t="n">
         <v>9758</v>
@@ -15594,7 +15594,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G525" t="n">
-        <v>2.05516982078552</v>
+        <v>2.0551700592041</v>
       </c>
       <c r="H525" t="n">
         <v>14380</v>
@@ -15623,7 +15623,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G526" t="n">
-        <v>2.04735517501831</v>
+        <v>2.04735541343689</v>
       </c>
       <c r="H526" t="n">
         <v>13140</v>
@@ -15652,7 +15652,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G527" t="n">
-        <v>2.04735517501831</v>
+        <v>2.04735541343689</v>
       </c>
       <c r="H527" t="n">
         <v>1930</v>
@@ -15681,7 +15681,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G528" t="n">
-        <v>2.05516982078552</v>
+        <v>2.0551700592041</v>
       </c>
       <c r="H528" t="n">
         <v>4970</v>
@@ -15710,7 +15710,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G529" t="n">
-        <v>2.04735517501831</v>
+        <v>2.04735541343689</v>
       </c>
       <c r="H529" t="n">
         <v>6486</v>
@@ -15739,7 +15739,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G530" t="n">
-        <v>2.08642745018005</v>
+        <v>2.08642721176147</v>
       </c>
       <c r="H530" t="n">
         <v>11459</v>
@@ -15768,7 +15768,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G531" t="n">
-        <v>2.07861280441284</v>
+        <v>2.07861256599426</v>
       </c>
       <c r="H531" t="n">
         <v>7675</v>
@@ -15797,7 +15797,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G532" t="n">
-        <v>2.03954100608826</v>
+        <v>2.03954124450684</v>
       </c>
       <c r="H532" t="n">
         <v>7408</v>
@@ -15826,7 +15826,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G533" t="n">
-        <v>2.03954100608826</v>
+        <v>2.03954124450684</v>
       </c>
       <c r="H533" t="n">
         <v>1950</v>
@@ -15913,7 +15913,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G536" t="n">
-        <v>2.00046968460083</v>
+        <v>2.00046944618225</v>
       </c>
       <c r="H536" t="n">
         <v>1180</v>
@@ -15942,7 +15942,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G537" t="n">
-        <v>2.00046968460083</v>
+        <v>2.00046944618225</v>
       </c>
       <c r="H537" t="n">
         <v>13992</v>
@@ -15971,7 +15971,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G538" t="n">
-        <v>2.00046968460083</v>
+        <v>2.00046944618225</v>
       </c>
       <c r="H538" t="n">
         <v>2472</v>
@@ -16000,7 +16000,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G539" t="n">
-        <v>1.98484063148499</v>
+        <v>1.98484098911285</v>
       </c>
       <c r="H539" t="n">
         <v>4051</v>
@@ -16029,7 +16029,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G540" t="n">
-        <v>1.97702646255493</v>
+        <v>1.97702634334564</v>
       </c>
       <c r="H540" t="n">
         <v>1849</v>
@@ -16116,7 +16116,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G543" t="n">
-        <v>1.92232632637024</v>
+        <v>1.92232620716095</v>
       </c>
       <c r="H543" t="n">
         <v>2000</v>
@@ -16174,7 +16174,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G545" t="n">
-        <v>1.98484063148499</v>
+        <v>1.98484098911285</v>
       </c>
       <c r="H545" t="n">
         <v>7157</v>
@@ -16232,7 +16232,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G547" t="n">
-        <v>1.96921193599701</v>
+        <v>1.96921217441559</v>
       </c>
       <c r="H547" t="n">
         <v>4409</v>
@@ -16261,7 +16261,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G548" t="n">
-        <v>1.96921193599701</v>
+        <v>1.96921217441559</v>
       </c>
       <c r="H548" t="n">
         <v>2935</v>
@@ -16290,7 +16290,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G549" t="n">
-        <v>1.93795502185822</v>
+        <v>1.93795490264893</v>
       </c>
       <c r="H549" t="n">
         <v>78</v>
@@ -16319,7 +16319,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G550" t="n">
-        <v>2.04735517501831</v>
+        <v>2.04735541343689</v>
       </c>
       <c r="H550" t="n">
         <v>12782</v>
@@ -16377,7 +16377,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G552" t="n">
-        <v>2.02391266822815</v>
+        <v>2.02391242980957</v>
       </c>
       <c r="H552" t="n">
         <v>3342</v>
@@ -16493,7 +16493,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G556" t="n">
-        <v>1.86762595176697</v>
+        <v>1.86762583255768</v>
       </c>
       <c r="H556" t="n">
         <v>3914</v>
@@ -16551,7 +16551,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G558" t="n">
-        <v>1.88325440883636</v>
+        <v>1.88325452804565</v>
       </c>
       <c r="H558" t="n">
         <v>7999</v>
@@ -16609,7 +16609,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G560" t="n">
-        <v>1.89888322353363</v>
+        <v>1.89888334274292</v>
       </c>
       <c r="H560" t="n">
         <v>4094</v>
@@ -16638,7 +16638,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G561" t="n">
-        <v>1.89888322353363</v>
+        <v>1.89888334274292</v>
       </c>
       <c r="H561" t="n">
         <v>2899</v>
@@ -16667,7 +16667,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G562" t="n">
-        <v>1.88325440883636</v>
+        <v>1.88325452804565</v>
       </c>
       <c r="H562" t="n">
         <v>12511</v>
@@ -16696,7 +16696,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G563" t="n">
-        <v>1.90669739246368</v>
+        <v>1.90669775009155</v>
       </c>
       <c r="H563" t="n">
         <v>3670</v>
@@ -16725,7 +16725,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G564" t="n">
-        <v>1.90669739246368</v>
+        <v>1.90669775009155</v>
       </c>
       <c r="H564" t="n">
         <v>290</v>
@@ -16841,7 +16841,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G568" t="n">
-        <v>1.86762595176697</v>
+        <v>1.86762583255768</v>
       </c>
       <c r="H568" t="n">
         <v>5620</v>
@@ -16899,7 +16899,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G570" t="n">
-        <v>1.92232632637024</v>
+        <v>1.92232620716095</v>
       </c>
       <c r="H570" t="n">
         <v>34637</v>
@@ -16928,7 +16928,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G571" t="n">
-        <v>2.00046968460083</v>
+        <v>2.00046944618225</v>
       </c>
       <c r="H571" t="n">
         <v>25947</v>
@@ -17015,7 +17015,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G574" t="n">
-        <v>2.03954100608826</v>
+        <v>2.03954124450684</v>
       </c>
       <c r="H574" t="n">
         <v>1270</v>
@@ -17131,7 +17131,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G578" t="n">
-        <v>2.05516982078552</v>
+        <v>2.0551700592041</v>
       </c>
       <c r="H578" t="n">
         <v>3757</v>
@@ -17160,7 +17160,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G579" t="n">
-        <v>2.03954100608826</v>
+        <v>2.03954124450684</v>
       </c>
       <c r="H579" t="n">
         <v>4138</v>
@@ -17189,7 +17189,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G580" t="n">
-        <v>2.04735517501831</v>
+        <v>2.04735541343689</v>
       </c>
       <c r="H580" t="n">
         <v>2057</v>
@@ -17247,7 +17247,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G582" t="n">
-        <v>1.98484063148499</v>
+        <v>1.98484098911285</v>
       </c>
       <c r="H582" t="n">
         <v>5772</v>
@@ -17276,7 +17276,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G583" t="n">
-        <v>1.98484063148499</v>
+        <v>1.98484098911285</v>
       </c>
       <c r="H583" t="n">
         <v>817</v>
@@ -17305,7 +17305,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G584" t="n">
-        <v>1.96139800548553</v>
+        <v>1.96139788627625</v>
       </c>
       <c r="H584" t="n">
         <v>534</v>
@@ -17334,7 +17334,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G585" t="n">
-        <v>1.97702646255493</v>
+        <v>1.97702634334564</v>
       </c>
       <c r="H585" t="n">
         <v>2222</v>
@@ -17363,7 +17363,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G586" t="n">
-        <v>2.02391266822815</v>
+        <v>2.02391242980957</v>
       </c>
       <c r="H586" t="n">
         <v>4748</v>
@@ -17421,7 +17421,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G588" t="n">
-        <v>1.96921193599701</v>
+        <v>1.96921217441559</v>
       </c>
       <c r="H588" t="n">
         <v>1223</v>
@@ -17450,7 +17450,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G589" t="n">
-        <v>1.97702646255493</v>
+        <v>1.97702634334564</v>
       </c>
       <c r="H589" t="n">
         <v>1767</v>
@@ -17508,7 +17508,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G591" t="n">
-        <v>1.93795502185822</v>
+        <v>1.93795490264893</v>
       </c>
       <c r="H591" t="n">
         <v>11871</v>
@@ -17537,7 +17537,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G592" t="n">
-        <v>1.96921193599701</v>
+        <v>1.96921217441559</v>
       </c>
       <c r="H592" t="n">
         <v>100</v>
@@ -17566,7 +17566,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G593" t="n">
-        <v>1.89888322353363</v>
+        <v>1.89888334274292</v>
       </c>
       <c r="H593" t="n">
         <v>219</v>
@@ -17595,7 +17595,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G594" t="n">
-        <v>1.96921193599701</v>
+        <v>1.96921217441559</v>
       </c>
       <c r="H594" t="n">
         <v>28</v>
@@ -17653,7 +17653,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G596" t="n">
-        <v>1.93014073371887</v>
+        <v>1.93014061450958</v>
       </c>
       <c r="H596" t="n">
         <v>321</v>
@@ -17682,7 +17682,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G597" t="n">
-        <v>1.93014073371887</v>
+        <v>1.93014061450958</v>
       </c>
       <c r="H597" t="n">
         <v>1300</v>
@@ -17711,7 +17711,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G598" t="n">
-        <v>1.93795502185822</v>
+        <v>1.93795490264893</v>
       </c>
       <c r="H598" t="n">
         <v>301</v>
@@ -17885,7 +17885,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G604" t="n">
-        <v>1.93795502185822</v>
+        <v>1.93795490264893</v>
       </c>
       <c r="H604" t="n">
         <v>100</v>
@@ -18030,7 +18030,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G609" t="n">
-        <v>1.85199725627899</v>
+        <v>1.8519971370697</v>
       </c>
       <c r="H609" t="n">
         <v>700</v>
@@ -18117,7 +18117,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G612" t="n">
-        <v>1.85981166362762</v>
+        <v>1.85981178283691</v>
       </c>
       <c r="H612" t="n">
         <v>992</v>
@@ -18146,7 +18146,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G613" t="n">
-        <v>1.78166818618774</v>
+        <v>1.78166806697845</v>
       </c>
       <c r="H613" t="n">
         <v>2844</v>
@@ -18175,7 +18175,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G614" t="n">
-        <v>1.79729688167572</v>
+        <v>1.79729664325714</v>
       </c>
       <c r="H614" t="n">
         <v>10850</v>
@@ -18204,7 +18204,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G615" t="n">
-        <v>1.88325440883636</v>
+        <v>1.88325452804565</v>
       </c>
       <c r="H615" t="n">
         <v>100</v>
@@ -18233,7 +18233,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G616" t="n">
-        <v>1.88325440883636</v>
+        <v>1.88325452804565</v>
       </c>
       <c r="H616" t="n">
         <v>0</v>
@@ -18349,7 +18349,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G620" t="n">
-        <v>1.82073962688446</v>
+        <v>1.82073986530304</v>
       </c>
       <c r="H620" t="n">
         <v>2510</v>
@@ -18378,7 +18378,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G621" t="n">
-        <v>1.86762595176697</v>
+        <v>1.86762583255768</v>
       </c>
       <c r="H621" t="n">
         <v>16907</v>
@@ -18436,7 +18436,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G623" t="n">
-        <v>1.92232632637024</v>
+        <v>1.92232620716095</v>
       </c>
       <c r="H623" t="n">
         <v>678</v>
@@ -18465,7 +18465,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G624" t="n">
-        <v>1.86762595176697</v>
+        <v>1.86762583255768</v>
       </c>
       <c r="H624" t="n">
         <v>5391</v>
@@ -18523,7 +18523,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G626" t="n">
-        <v>1.86762595176697</v>
+        <v>1.86762583255768</v>
       </c>
       <c r="H626" t="n">
         <v>4224</v>
@@ -18552,7 +18552,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G627" t="n">
-        <v>1.82073962688446</v>
+        <v>1.82073986530304</v>
       </c>
       <c r="H627" t="n">
         <v>5337</v>
@@ -18581,7 +18581,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G628" t="n">
-        <v>1.85199725627899</v>
+        <v>1.8519971370697</v>
       </c>
       <c r="H628" t="n">
         <v>767</v>
@@ -18610,7 +18610,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G629" t="n">
-        <v>1.83636844158173</v>
+        <v>1.83636856079102</v>
       </c>
       <c r="H629" t="n">
         <v>2700</v>
@@ -18668,7 +18668,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G631" t="n">
-        <v>1.79729688167572</v>
+        <v>1.79729664325714</v>
       </c>
       <c r="H631" t="n">
         <v>1387</v>
@@ -18697,7 +18697,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G632" t="n">
-        <v>1.76603949069977</v>
+        <v>1.76603937149048</v>
       </c>
       <c r="H632" t="n">
         <v>2150</v>
@@ -18726,7 +18726,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G633" t="n">
-        <v>1.76603949069977</v>
+        <v>1.76603937149048</v>
       </c>
       <c r="H633" t="n">
         <v>0</v>
@@ -18755,7 +18755,7 @@
         <v>2.25</v>
       </c>
       <c r="G634" t="n">
-        <v>1.75822532176971</v>
+        <v>1.75822520256042</v>
       </c>
       <c r="H634" t="n">
         <v>3308</v>
@@ -18784,7 +18784,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G635" t="n">
-        <v>1.72696781158447</v>
+        <v>1.72696793079376</v>
       </c>
       <c r="H635" t="n">
         <v>2340</v>
@@ -18813,7 +18813,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G636" t="n">
-        <v>1.7504106760025</v>
+        <v>1.75041091442108</v>
       </c>
       <c r="H636" t="n">
         <v>116</v>
@@ -18842,7 +18842,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G637" t="n">
-        <v>1.78166818618774</v>
+        <v>1.78166806697845</v>
       </c>
       <c r="H637" t="n">
         <v>4216</v>
@@ -18871,7 +18871,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G638" t="n">
-        <v>1.82073962688446</v>
+        <v>1.82073986530304</v>
       </c>
       <c r="H638" t="n">
         <v>1300</v>
@@ -18900,7 +18900,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G639" t="n">
-        <v>1.73478209972382</v>
+        <v>1.7347823381424</v>
       </c>
       <c r="H639" t="n">
         <v>17652</v>
@@ -18987,7 +18987,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G642" t="n">
-        <v>1.7504106760025</v>
+        <v>1.75041091442108</v>
       </c>
       <c r="H642" t="n">
         <v>870</v>
@@ -19045,7 +19045,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G644" t="n">
-        <v>1.74259638786316</v>
+        <v>1.74259650707245</v>
       </c>
       <c r="H644" t="n">
         <v>1986</v>
@@ -19190,7 +19190,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G649" t="n">
-        <v>1.70352494716644</v>
+        <v>1.70352482795715</v>
       </c>
       <c r="H649" t="n">
         <v>1910</v>
@@ -19248,7 +19248,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G651" t="n">
-        <v>1.68008184432983</v>
+        <v>1.68008196353912</v>
       </c>
       <c r="H651" t="n">
         <v>2312</v>
@@ -19277,7 +19277,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G652" t="n">
-        <v>1.68008184432983</v>
+        <v>1.68008196353912</v>
       </c>
       <c r="H652" t="n">
         <v>3142</v>
@@ -19364,7 +19364,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G655" t="n">
-        <v>1.61756718158722</v>
+        <v>1.61756706237793</v>
       </c>
       <c r="H655" t="n">
         <v>2957</v>
@@ -19393,7 +19393,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G656" t="n">
-        <v>1.61756718158722</v>
+        <v>1.61756706237793</v>
       </c>
       <c r="H656" t="n">
         <v>4076</v>
@@ -19422,7 +19422,7 @@
         <v>2</v>
       </c>
       <c r="G657" t="n">
-        <v>1.56286680698395</v>
+        <v>1.56286692619324</v>
       </c>
       <c r="H657" t="n">
         <v>7242</v>
@@ -19596,7 +19596,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G663" t="n">
-        <v>1.48472344875336</v>
+        <v>1.48472356796265</v>
       </c>
       <c r="H663" t="n">
         <v>210</v>
@@ -19625,7 +19625,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G664" t="n">
-        <v>1.5550525188446</v>
+        <v>1.55505263805389</v>
       </c>
       <c r="H664" t="n">
         <v>7681</v>
@@ -19683,7 +19683,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G666" t="n">
-        <v>1.92232632637024</v>
+        <v>1.92232620716095</v>
       </c>
       <c r="H666" t="n">
         <v>446846</v>
@@ -19741,7 +19741,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G668" t="n">
-        <v>1.88325440883636</v>
+        <v>1.88325452804565</v>
       </c>
       <c r="H668" t="n">
         <v>20273</v>
@@ -19770,7 +19770,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G669" t="n">
-        <v>1.92232632637024</v>
+        <v>1.92232620716095</v>
       </c>
       <c r="H669" t="n">
         <v>32286</v>
@@ -19799,7 +19799,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G670" t="n">
-        <v>1.99265515804291</v>
+        <v>1.99265503883362</v>
       </c>
       <c r="H670" t="n">
         <v>78330</v>
@@ -19828,7 +19828,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G671" t="n">
-        <v>1.93014073371887</v>
+        <v>1.93014061450958</v>
       </c>
       <c r="H671" t="n">
         <v>41175</v>
@@ -19857,7 +19857,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G672" t="n">
-        <v>1.89888322353363</v>
+        <v>1.89888334274292</v>
       </c>
       <c r="H672" t="n">
         <v>10847</v>
@@ -19886,7 +19886,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G673" t="n">
-        <v>1.92232632637024</v>
+        <v>1.92232620716095</v>
       </c>
       <c r="H673" t="n">
         <v>37391</v>
@@ -19915,7 +19915,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G674" t="n">
-        <v>1.97702646255493</v>
+        <v>1.97702634334564</v>
       </c>
       <c r="H674" t="n">
         <v>10462</v>
@@ -20002,7 +20002,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G677" t="n">
-        <v>1.88325440883636</v>
+        <v>1.88325452804565</v>
       </c>
       <c r="H677" t="n">
         <v>24276</v>
@@ -20031,7 +20031,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G678" t="n">
-        <v>1.8285539150238</v>
+        <v>1.82855415344238</v>
       </c>
       <c r="H678" t="n">
         <v>7847</v>
@@ -20060,7 +20060,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G679" t="n">
-        <v>1.85981166362762</v>
+        <v>1.85981178283691</v>
       </c>
       <c r="H679" t="n">
         <v>1203</v>
@@ -20089,7 +20089,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G680" t="n">
-        <v>1.8285539150238</v>
+        <v>1.82855415344238</v>
       </c>
       <c r="H680" t="n">
         <v>4199</v>
@@ -20118,7 +20118,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G681" t="n">
-        <v>1.76603949069977</v>
+        <v>1.76603937149048</v>
       </c>
       <c r="H681" t="n">
         <v>6126</v>
@@ -20147,7 +20147,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G682" t="n">
-        <v>1.70352494716644</v>
+        <v>1.70352482795715</v>
       </c>
       <c r="H682" t="n">
         <v>21460</v>
@@ -20205,7 +20205,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G684" t="n">
-        <v>1.82073962688446</v>
+        <v>1.82073986530304</v>
       </c>
       <c r="H684" t="n">
         <v>79297</v>
@@ -20234,7 +20234,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G685" t="n">
-        <v>1.76603949069977</v>
+        <v>1.76603937149048</v>
       </c>
       <c r="H685" t="n">
         <v>13837</v>
@@ -20263,7 +20263,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G686" t="n">
-        <v>1.78166818618774</v>
+        <v>1.78166806697845</v>
       </c>
       <c r="H686" t="n">
         <v>16568</v>
@@ -20292,7 +20292,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G687" t="n">
-        <v>1.76603949069977</v>
+        <v>1.76603937149048</v>
       </c>
       <c r="H687" t="n">
         <v>11052</v>
@@ -20321,7 +20321,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G688" t="n">
-        <v>1.76603949069977</v>
+        <v>1.76603937149048</v>
       </c>
       <c r="H688" t="n">
         <v>8342</v>
@@ -20350,7 +20350,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G689" t="n">
-        <v>1.78166818618774</v>
+        <v>1.78166806697845</v>
       </c>
       <c r="H689" t="n">
         <v>4504</v>
@@ -20379,7 +20379,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G690" t="n">
-        <v>1.7504106760025</v>
+        <v>1.75041091442108</v>
       </c>
       <c r="H690" t="n">
         <v>2392</v>
@@ -20437,7 +20437,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G692" t="n">
-        <v>1.70352494716644</v>
+        <v>1.70352482795715</v>
       </c>
       <c r="H692" t="n">
         <v>29415</v>
@@ -20553,7 +20553,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G696" t="n">
-        <v>1.67226767539978</v>
+        <v>1.67226755619049</v>
       </c>
       <c r="H696" t="n">
         <v>11489</v>
@@ -20582,7 +20582,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G697" t="n">
-        <v>1.68008184432983</v>
+        <v>1.68008196353912</v>
       </c>
       <c r="H697" t="n">
         <v>5973</v>
@@ -20611,7 +20611,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G698" t="n">
-        <v>1.68008184432983</v>
+        <v>1.68008196353912</v>
       </c>
       <c r="H698" t="n">
         <v>6783</v>
@@ -20640,7 +20640,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G699" t="n">
-        <v>1.74259638786316</v>
+        <v>1.74259650707245</v>
       </c>
       <c r="H699" t="n">
         <v>125437</v>
@@ -20669,7 +20669,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G700" t="n">
-        <v>1.78166818618774</v>
+        <v>1.78166806697845</v>
       </c>
       <c r="H700" t="n">
         <v>16469</v>
@@ -20698,7 +20698,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G701" t="n">
-        <v>1.70352494716644</v>
+        <v>1.70352482795715</v>
       </c>
       <c r="H701" t="n">
         <v>20038</v>
@@ -20727,7 +20727,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G702" t="n">
-        <v>1.6957106590271</v>
+        <v>1.69571042060852</v>
       </c>
       <c r="H702" t="n">
         <v>42863</v>
@@ -20814,7 +20814,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G705" t="n">
-        <v>1.6957106590271</v>
+        <v>1.69571042060852</v>
       </c>
       <c r="H705" t="n">
         <v>9685</v>
@@ -20872,7 +20872,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G707" t="n">
-        <v>1.62538146972656</v>
+        <v>1.62538135051727</v>
       </c>
       <c r="H707" t="n">
         <v>2029</v>
@@ -20988,7 +20988,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G711" t="n">
-        <v>1.68008184432983</v>
+        <v>1.68008196353912</v>
       </c>
       <c r="H711" t="n">
         <v>1343</v>
@@ -21017,7 +21017,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G712" t="n">
-        <v>1.68008184432983</v>
+        <v>1.68008196353912</v>
       </c>
       <c r="H712" t="n">
         <v>1105</v>
@@ -21104,7 +21104,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G715" t="n">
-        <v>1.61756718158722</v>
+        <v>1.61756706237793</v>
       </c>
       <c r="H715" t="n">
         <v>5893</v>
@@ -21133,7 +21133,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G716" t="n">
-        <v>1.61756718158722</v>
+        <v>1.61756706237793</v>
       </c>
       <c r="H716" t="n">
         <v>15324</v>
@@ -21191,7 +21191,7 @@
         <v>2</v>
       </c>
       <c r="G718" t="n">
-        <v>1.56286680698395</v>
+        <v>1.56286692619324</v>
       </c>
       <c r="H718" t="n">
         <v>6637</v>
@@ -21307,7 +21307,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G722" t="n">
-        <v>1.61756718158722</v>
+        <v>1.61756706237793</v>
       </c>
       <c r="H722" t="n">
         <v>3905</v>
@@ -21655,7 +21655,7 @@
         <v>2</v>
       </c>
       <c r="G734" t="n">
-        <v>1.56286680698395</v>
+        <v>1.56286692619324</v>
       </c>
       <c r="H734" t="n">
         <v>1000</v>
@@ -21684,7 +21684,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G735" t="n">
-        <v>1.5550525188446</v>
+        <v>1.55505263805389</v>
       </c>
       <c r="H735" t="n">
         <v>5470</v>
@@ -21713,7 +21713,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G736" t="n">
-        <v>1.531609416008</v>
+        <v>1.53160965442657</v>
       </c>
       <c r="H736" t="n">
         <v>1180</v>
@@ -21742,7 +21742,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G737" t="n">
-        <v>1.50816643238068</v>
+        <v>1.50816655158997</v>
       </c>
       <c r="H737" t="n">
         <v>2610</v>
@@ -21771,7 +21771,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G738" t="n">
-        <v>1.50035226345062</v>
+        <v>1.50035214424133</v>
       </c>
       <c r="H738" t="n">
         <v>3783</v>
@@ -21829,7 +21829,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G740" t="n">
-        <v>1.531609416008</v>
+        <v>1.53160965442657</v>
       </c>
       <c r="H740" t="n">
         <v>1201</v>
@@ -21858,7 +21858,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G741" t="n">
-        <v>1.50035226345062</v>
+        <v>1.50035214424133</v>
       </c>
       <c r="H741" t="n">
         <v>1657</v>
@@ -21887,7 +21887,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G742" t="n">
-        <v>1.50816643238068</v>
+        <v>1.50816655158997</v>
       </c>
       <c r="H742" t="n">
         <v>8117</v>
@@ -21945,7 +21945,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G744" t="n">
-        <v>1.62538146972656</v>
+        <v>1.62538135051727</v>
       </c>
       <c r="H744" t="n">
         <v>19613</v>
@@ -22177,7 +22177,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G752" t="n">
-        <v>1.52379524707794</v>
+        <v>1.52379512786865</v>
       </c>
       <c r="H752" t="n">
         <v>2112</v>
@@ -22206,7 +22206,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G753" t="n">
-        <v>1.52379524707794</v>
+        <v>1.52379512786865</v>
       </c>
       <c r="H753" t="n">
         <v>2730</v>
@@ -22235,7 +22235,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G754" t="n">
-        <v>1.52379524707794</v>
+        <v>1.52379512786865</v>
       </c>
       <c r="H754" t="n">
         <v>116</v>
@@ -22264,7 +22264,7 @@
         <v>2</v>
       </c>
       <c r="G755" t="n">
-        <v>1.56286680698395</v>
+        <v>1.56286692619324</v>
       </c>
       <c r="H755" t="n">
         <v>4200</v>
@@ -22322,7 +22322,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G757" t="n">
-        <v>1.50816643238068</v>
+        <v>1.50816655158997</v>
       </c>
       <c r="H757" t="n">
         <v>390</v>
@@ -22351,7 +22351,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G758" t="n">
-        <v>1.48472344875336</v>
+        <v>1.48472356796265</v>
       </c>
       <c r="H758" t="n">
         <v>3743</v>
@@ -22380,7 +22380,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G759" t="n">
-        <v>1.48472344875336</v>
+        <v>1.48472356796265</v>
       </c>
       <c r="H759" t="n">
         <v>4807</v>
@@ -22467,7 +22467,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G762" t="n">
-        <v>1.47690916061401</v>
+        <v>1.47690904140472</v>
       </c>
       <c r="H762" t="n">
         <v>4134</v>
@@ -22525,7 +22525,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G764" t="n">
-        <v>1.50816643238068</v>
+        <v>1.50816655158997</v>
       </c>
       <c r="H764" t="n">
         <v>2240</v>
@@ -22554,7 +22554,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G765" t="n">
-        <v>1.74259638786316</v>
+        <v>1.74259650707245</v>
       </c>
       <c r="H765" t="n">
         <v>62191</v>
@@ -22583,7 +22583,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G766" t="n">
-        <v>1.5550525188446</v>
+        <v>1.55505263805389</v>
       </c>
       <c r="H766" t="n">
         <v>117476</v>
@@ -22641,7 +22641,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G768" t="n">
-        <v>1.5550525188446</v>
+        <v>1.55505263805389</v>
       </c>
       <c r="H768" t="n">
         <v>5714</v>
@@ -22786,7 +22786,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G773" t="n">
-        <v>1.5550525188446</v>
+        <v>1.55505263805389</v>
       </c>
       <c r="H773" t="n">
         <v>8089</v>
@@ -22844,7 +22844,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G775" t="n">
-        <v>1.5550525188446</v>
+        <v>1.55505263805389</v>
       </c>
       <c r="H775" t="n">
         <v>2807</v>
@@ -22873,7 +22873,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G776" t="n">
-        <v>1.531609416008</v>
+        <v>1.53160965442657</v>
       </c>
       <c r="H776" t="n">
         <v>5415</v>
@@ -22960,7 +22960,7 @@
         <v>2</v>
       </c>
       <c r="G779" t="n">
-        <v>1.56286680698395</v>
+        <v>1.56286692619324</v>
       </c>
       <c r="H779" t="n">
         <v>770</v>
@@ -22989,7 +22989,7 @@
         <v>2</v>
       </c>
       <c r="G780" t="n">
-        <v>1.56286680698395</v>
+        <v>1.56286692619324</v>
       </c>
       <c r="H780" t="n">
         <v>1385</v>
@@ -23018,7 +23018,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G781" t="n">
-        <v>1.5550525188446</v>
+        <v>1.55505263805389</v>
       </c>
       <c r="H781" t="n">
         <v>1090</v>
@@ -23047,7 +23047,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G782" t="n">
-        <v>1.531609416008</v>
+        <v>1.53160965442657</v>
       </c>
       <c r="H782" t="n">
         <v>5650</v>
@@ -23076,7 +23076,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G783" t="n">
-        <v>1.531609416008</v>
+        <v>1.53160965442657</v>
       </c>
       <c r="H783" t="n">
         <v>9208</v>
@@ -23105,7 +23105,7 @@
         <v>2</v>
       </c>
       <c r="G784" t="n">
-        <v>1.56286680698395</v>
+        <v>1.56286692619324</v>
       </c>
       <c r="H784" t="n">
         <v>1630</v>
@@ -23134,7 +23134,7 @@
         <v>2</v>
       </c>
       <c r="G785" t="n">
-        <v>1.56286680698395</v>
+        <v>1.56286692619324</v>
       </c>
       <c r="H785" t="n">
         <v>3493</v>
@@ -23163,7 +23163,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G786" t="n">
-        <v>1.5550525188446</v>
+        <v>1.55505263805389</v>
       </c>
       <c r="H786" t="n">
         <v>3597</v>
@@ -23192,7 +23192,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G787" t="n">
-        <v>1.5550525188446</v>
+        <v>1.55505263805389</v>
       </c>
       <c r="H787" t="n">
         <v>375</v>
@@ -23221,7 +23221,7 @@
         <v>2</v>
       </c>
       <c r="G788" t="n">
-        <v>1.56286680698395</v>
+        <v>1.56286692619324</v>
       </c>
       <c r="H788" t="n">
         <v>400</v>
@@ -23250,7 +23250,7 @@
         <v>2</v>
       </c>
       <c r="G789" t="n">
-        <v>1.56286680698395</v>
+        <v>1.56286692619324</v>
       </c>
       <c r="H789" t="n">
         <v>540</v>
@@ -23279,7 +23279,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G790" t="n">
-        <v>1.5550525188446</v>
+        <v>1.55505263805389</v>
       </c>
       <c r="H790" t="n">
         <v>935</v>
@@ -23308,7 +23308,7 @@
         <v>2</v>
       </c>
       <c r="G791" t="n">
-        <v>1.56286680698395</v>
+        <v>1.56286692619324</v>
       </c>
       <c r="H791" t="n">
         <v>88</v>
@@ -23424,7 +23424,7 @@
         <v>2</v>
       </c>
       <c r="G795" t="n">
-        <v>1.56286680698395</v>
+        <v>1.56286692619324</v>
       </c>
       <c r="H795" t="n">
         <v>8735</v>
@@ -23453,7 +23453,7 @@
         <v>2</v>
       </c>
       <c r="G796" t="n">
-        <v>1.56286680698395</v>
+        <v>1.56286692619324</v>
       </c>
       <c r="H796" t="n">
         <v>8350</v>
@@ -23627,7 +23627,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G802" t="n">
-        <v>1.5550525188446</v>
+        <v>1.55505263805389</v>
       </c>
       <c r="H802" t="n">
         <v>11782</v>
@@ -23685,7 +23685,7 @@
         <v>2</v>
       </c>
       <c r="G804" t="n">
-        <v>1.56286680698395</v>
+        <v>1.56286692619324</v>
       </c>
       <c r="H804" t="n">
         <v>715</v>
@@ -23830,7 +23830,7 @@
         <v>2</v>
       </c>
       <c r="G809" t="n">
-        <v>1.56286680698395</v>
+        <v>1.56286692619324</v>
       </c>
       <c r="H809" t="n">
         <v>100</v>
@@ -23859,7 +23859,7 @@
         <v>2</v>
       </c>
       <c r="G810" t="n">
-        <v>1.56286680698395</v>
+        <v>1.56286692619324</v>
       </c>
       <c r="H810" t="n">
         <v>2902</v>
@@ -23888,7 +23888,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G811" t="n">
-        <v>1.5550525188446</v>
+        <v>1.55505263805389</v>
       </c>
       <c r="H811" t="n">
         <v>1500</v>
@@ -23917,7 +23917,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G812" t="n">
-        <v>1.5550525188446</v>
+        <v>1.55505263805389</v>
       </c>
       <c r="H812" t="n">
         <v>3468</v>
@@ -23946,7 +23946,7 @@
         <v>2</v>
       </c>
       <c r="G813" t="n">
-        <v>1.56286680698395</v>
+        <v>1.56286692619324</v>
       </c>
       <c r="H813" t="n">
         <v>3779</v>
@@ -24004,7 +24004,7 @@
         <v>2</v>
       </c>
       <c r="G815" t="n">
-        <v>1.56286680698395</v>
+        <v>1.56286692619324</v>
       </c>
       <c r="H815" t="n">
         <v>4107</v>
@@ -24033,7 +24033,7 @@
         <v>2</v>
       </c>
       <c r="G816" t="n">
-        <v>1.56286680698395</v>
+        <v>1.56286692619324</v>
       </c>
       <c r="H816" t="n">
         <v>8835</v>
@@ -24062,7 +24062,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G817" t="n">
-        <v>1.68008184432983</v>
+        <v>1.68008196353912</v>
       </c>
       <c r="H817" t="n">
         <v>78580</v>
@@ -24178,7 +24178,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G821" t="n">
-        <v>1.62538146972656</v>
+        <v>1.62538135051727</v>
       </c>
       <c r="H821" t="n">
         <v>2898</v>
@@ -24207,7 +24207,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G822" t="n">
-        <v>1.61756718158722</v>
+        <v>1.61756706237793</v>
       </c>
       <c r="H822" t="n">
         <v>271</v>
@@ -24352,7 +24352,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G827" t="n">
-        <v>1.62538146972656</v>
+        <v>1.62538135051727</v>
       </c>
       <c r="H827" t="n">
         <v>17597</v>
@@ -24410,7 +24410,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G829" t="n">
-        <v>1.73478209972382</v>
+        <v>1.7347823381424</v>
       </c>
       <c r="H829" t="n">
         <v>220051</v>
@@ -24439,7 +24439,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G830" t="n">
-        <v>1.67226767539978</v>
+        <v>1.67226755619049</v>
       </c>
       <c r="H830" t="n">
         <v>111394</v>
@@ -24526,7 +24526,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G833" t="n">
-        <v>1.67226767539978</v>
+        <v>1.67226755619049</v>
       </c>
       <c r="H833" t="n">
         <v>47937</v>
@@ -24613,7 +24613,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G836" t="n">
-        <v>1.62538146972656</v>
+        <v>1.62538135051727</v>
       </c>
       <c r="H836" t="n">
         <v>52160</v>
@@ -24642,7 +24642,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G837" t="n">
-        <v>1.67226767539978</v>
+        <v>1.67226755619049</v>
       </c>
       <c r="H837" t="n">
         <v>57119</v>
@@ -24671,7 +24671,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G838" t="n">
-        <v>1.67226767539978</v>
+        <v>1.67226755619049</v>
       </c>
       <c r="H838" t="n">
         <v>46771</v>
@@ -24874,7 +24874,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G845" t="n">
-        <v>1.62538146972656</v>
+        <v>1.62538135051727</v>
       </c>
       <c r="H845" t="n">
         <v>14102</v>
@@ -24932,7 +24932,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G847" t="n">
-        <v>1.62538146972656</v>
+        <v>1.62538135051727</v>
       </c>
       <c r="H847" t="n">
         <v>14870</v>
@@ -25077,7 +25077,7 @@
         <v>2</v>
       </c>
       <c r="G852" t="n">
-        <v>1.56286680698395</v>
+        <v>1.56286692619324</v>
       </c>
       <c r="H852" t="n">
         <v>14569</v>
@@ -25106,7 +25106,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G853" t="n">
-        <v>1.531609416008</v>
+        <v>1.53160965442657</v>
       </c>
       <c r="H853" t="n">
         <v>9826</v>
@@ -25164,7 +25164,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G855" t="n">
-        <v>1.531609416008</v>
+        <v>1.53160965442657</v>
       </c>
       <c r="H855" t="n">
         <v>30431</v>
@@ -25222,7 +25222,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G857" t="n">
-        <v>1.531609416008</v>
+        <v>1.53160965442657</v>
       </c>
       <c r="H857" t="n">
         <v>8665</v>
@@ -25309,7 +25309,7 @@
         <v>2</v>
       </c>
       <c r="G860" t="n">
-        <v>1.56286680698395</v>
+        <v>1.56286692619324</v>
       </c>
       <c r="H860" t="n">
         <v>500</v>
@@ -25338,7 +25338,7 @@
         <v>2</v>
       </c>
       <c r="G861" t="n">
-        <v>1.56286680698395</v>
+        <v>1.56286692619324</v>
       </c>
       <c r="H861" t="n">
         <v>0</v>
@@ -25454,7 +25454,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G865" t="n">
-        <v>1.50035226345062</v>
+        <v>1.50035214424133</v>
       </c>
       <c r="H865" t="n">
         <v>6903</v>
@@ -25483,7 +25483,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G866" t="n">
-        <v>1.50035226345062</v>
+        <v>1.50035214424133</v>
       </c>
       <c r="H866" t="n">
         <v>8355</v>
@@ -25512,7 +25512,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G867" t="n">
-        <v>1.531609416008</v>
+        <v>1.53160965442657</v>
       </c>
       <c r="H867" t="n">
         <v>3500</v>
@@ -25570,7 +25570,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G869" t="n">
-        <v>1.45346617698669</v>
+        <v>1.4534660577774</v>
       </c>
       <c r="H869" t="n">
         <v>670</v>
@@ -25628,7 +25628,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G871" t="n">
-        <v>1.50035226345062</v>
+        <v>1.50035214424133</v>
       </c>
       <c r="H871" t="n">
         <v>1918</v>
@@ -25657,7 +25657,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G872" t="n">
-        <v>1.50035226345062</v>
+        <v>1.50035214424133</v>
       </c>
       <c r="H872" t="n">
         <v>0</v>
@@ -25715,7 +25715,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G874" t="n">
-        <v>1.48472344875336</v>
+        <v>1.48472356796265</v>
       </c>
       <c r="H874" t="n">
         <v>750</v>
@@ -25744,7 +25744,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G875" t="n">
-        <v>1.45346617698669</v>
+        <v>1.4534660577774</v>
       </c>
       <c r="H875" t="n">
         <v>7508</v>
@@ -25773,7 +25773,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G876" t="n">
-        <v>1.45346617698669</v>
+        <v>1.4534660577774</v>
       </c>
       <c r="H876" t="n">
         <v>800</v>
@@ -25831,7 +25831,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G878" t="n">
-        <v>1.531609416008</v>
+        <v>1.53160965442657</v>
       </c>
       <c r="H878" t="n">
         <v>2050</v>
@@ -25860,7 +25860,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G879" t="n">
-        <v>1.48472344875336</v>
+        <v>1.48472356796265</v>
       </c>
       <c r="H879" t="n">
         <v>2150</v>
@@ -25918,7 +25918,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G881" t="n">
-        <v>1.45346617698669</v>
+        <v>1.4534660577774</v>
       </c>
       <c r="H881" t="n">
         <v>880</v>
@@ -25947,7 +25947,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G882" t="n">
-        <v>1.43783760070801</v>
+        <v>1.43783748149872</v>
       </c>
       <c r="H882" t="n">
         <v>3065</v>
@@ -25976,7 +25976,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G883" t="n">
-        <v>1.45346617698669</v>
+        <v>1.4534660577774</v>
       </c>
       <c r="H883" t="n">
         <v>12670</v>
@@ -26005,7 +26005,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G884" t="n">
-        <v>1.45346617698669</v>
+        <v>1.4534660577774</v>
       </c>
       <c r="H884" t="n">
         <v>4516</v>
@@ -26034,7 +26034,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G885" t="n">
-        <v>1.43783760070801</v>
+        <v>1.43783748149872</v>
       </c>
       <c r="H885" t="n">
         <v>29</v>
@@ -26092,7 +26092,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G887" t="n">
-        <v>1.48472344875336</v>
+        <v>1.48472356796265</v>
       </c>
       <c r="H887" t="n">
         <v>341707</v>
@@ -26121,7 +26121,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G888" t="n">
-        <v>1.48472344875336</v>
+        <v>1.48472356796265</v>
       </c>
       <c r="H888" t="n">
         <v>16005</v>
@@ -26237,7 +26237,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G892" t="n">
-        <v>1.531609416008</v>
+        <v>1.53160965442657</v>
       </c>
       <c r="H892" t="n">
         <v>6177</v>
@@ -26295,7 +26295,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G894" t="n">
-        <v>1.48472344875336</v>
+        <v>1.48472356796265</v>
       </c>
       <c r="H894" t="n">
         <v>20473</v>
@@ -26324,7 +26324,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G895" t="n">
-        <v>1.531609416008</v>
+        <v>1.53160965442657</v>
       </c>
       <c r="H895" t="n">
         <v>4132</v>
@@ -26353,7 +26353,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G896" t="n">
-        <v>1.531609416008</v>
+        <v>1.53160965442657</v>
       </c>
       <c r="H896" t="n">
         <v>15658</v>
@@ -26411,7 +26411,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G898" t="n">
-        <v>1.50035226345062</v>
+        <v>1.50035214424133</v>
       </c>
       <c r="H898" t="n">
         <v>9001</v>
@@ -26440,7 +26440,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G899" t="n">
-        <v>1.50035226345062</v>
+        <v>1.50035214424133</v>
       </c>
       <c r="H899" t="n">
         <v>5729</v>
@@ -26469,7 +26469,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G900" t="n">
-        <v>1.50035226345062</v>
+        <v>1.50035214424133</v>
       </c>
       <c r="H900" t="n">
         <v>4094</v>
@@ -26585,7 +26585,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G904" t="n">
-        <v>1.531609416008</v>
+        <v>1.53160965442657</v>
       </c>
       <c r="H904" t="n">
         <v>2250</v>
@@ -26614,7 +26614,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G905" t="n">
-        <v>1.531609416008</v>
+        <v>1.53160965442657</v>
       </c>
       <c r="H905" t="n">
         <v>3080</v>
@@ -26643,7 +26643,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G906" t="n">
-        <v>1.50035226345062</v>
+        <v>1.50035214424133</v>
       </c>
       <c r="H906" t="n">
         <v>3380</v>
@@ -26672,7 +26672,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G907" t="n">
-        <v>1.50035226345062</v>
+        <v>1.50035214424133</v>
       </c>
       <c r="H907" t="n">
         <v>17682</v>
@@ -26759,7 +26759,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G910" t="n">
-        <v>1.50035226345062</v>
+        <v>1.50035214424133</v>
       </c>
       <c r="H910" t="n">
         <v>2535</v>
@@ -26788,7 +26788,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G911" t="n">
-        <v>1.48472344875336</v>
+        <v>1.48472356796265</v>
       </c>
       <c r="H911" t="n">
         <v>50</v>
@@ -26846,7 +26846,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G913" t="n">
-        <v>1.50035226345062</v>
+        <v>1.50035214424133</v>
       </c>
       <c r="H913" t="n">
         <v>1205</v>
@@ -26933,7 +26933,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G916" t="n">
-        <v>1.50035226345062</v>
+        <v>1.50035214424133</v>
       </c>
       <c r="H916" t="n">
         <v>1650</v>
@@ -26962,7 +26962,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G917" t="n">
-        <v>1.50035226345062</v>
+        <v>1.50035214424133</v>
       </c>
       <c r="H917" t="n">
         <v>8100</v>
@@ -27020,7 +27020,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G919" t="n">
-        <v>1.45346617698669</v>
+        <v>1.4534660577774</v>
       </c>
       <c r="H919" t="n">
         <v>1440</v>
@@ -27049,7 +27049,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G920" t="n">
-        <v>1.45346617698669</v>
+        <v>1.4534660577774</v>
       </c>
       <c r="H920" t="n">
         <v>1744</v>
@@ -27078,7 +27078,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G921" t="n">
-        <v>1.48472344875336</v>
+        <v>1.48472356796265</v>
       </c>
       <c r="H921" t="n">
         <v>1357</v>
@@ -27165,7 +27165,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G924" t="n">
-        <v>1.45346617698669</v>
+        <v>1.4534660577774</v>
       </c>
       <c r="H924" t="n">
         <v>2225</v>
@@ -27194,7 +27194,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G925" t="n">
-        <v>1.48472344875336</v>
+        <v>1.48472356796265</v>
       </c>
       <c r="H925" t="n">
         <v>10370</v>
@@ -27223,7 +27223,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G926" t="n">
-        <v>1.50035226345062</v>
+        <v>1.50035214424133</v>
       </c>
       <c r="H926" t="n">
         <v>3414</v>
@@ -27252,7 +27252,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G927" t="n">
-        <v>1.50035226345062</v>
+        <v>1.50035214424133</v>
       </c>
       <c r="H927" t="n">
         <v>60</v>
@@ -27281,7 +27281,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G928" t="n">
-        <v>1.45346617698669</v>
+        <v>1.4534660577774</v>
       </c>
       <c r="H928" t="n">
         <v>750</v>
@@ -27310,7 +27310,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G929" t="n">
-        <v>1.45346617698669</v>
+        <v>1.4534660577774</v>
       </c>
       <c r="H929" t="n">
         <v>800</v>
@@ -27339,7 +27339,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G930" t="n">
-        <v>1.48472344875336</v>
+        <v>1.48472356796265</v>
       </c>
       <c r="H930" t="n">
         <v>4310</v>
@@ -27368,7 +27368,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G931" t="n">
-        <v>1.48472344875336</v>
+        <v>1.48472356796265</v>
       </c>
       <c r="H931" t="n">
         <v>634</v>
@@ -27426,7 +27426,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G933" t="n">
-        <v>1.50035226345062</v>
+        <v>1.50035214424133</v>
       </c>
       <c r="H933" t="n">
         <v>10800</v>
@@ -27629,7 +27629,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G940" t="n">
-        <v>1.50035226345062</v>
+        <v>1.50035214424133</v>
       </c>
       <c r="H940" t="n">
         <v>3395</v>
@@ -27658,7 +27658,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G941" t="n">
-        <v>1.531609416008</v>
+        <v>1.53160965442657</v>
       </c>
       <c r="H941" t="n">
         <v>62485</v>
@@ -27687,7 +27687,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G942" t="n">
-        <v>1.48472344875336</v>
+        <v>1.48472356796265</v>
       </c>
       <c r="H942" t="n">
         <v>10270</v>
@@ -27832,7 +27832,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G947" t="n">
-        <v>1.48472344875336</v>
+        <v>1.48472356796265</v>
       </c>
       <c r="H947" t="n">
         <v>7679</v>
@@ -27890,7 +27890,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G949" t="n">
-        <v>1.50035226345062</v>
+        <v>1.50035214424133</v>
       </c>
       <c r="H949" t="n">
         <v>2380</v>
@@ -27919,7 +27919,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G950" t="n">
-        <v>1.50035226345062</v>
+        <v>1.50035214424133</v>
       </c>
       <c r="H950" t="n">
         <v>1118</v>
@@ -27948,7 +27948,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G951" t="n">
-        <v>1.50035226345062</v>
+        <v>1.50035214424133</v>
       </c>
       <c r="H951" t="n">
         <v>2270</v>
@@ -27977,7 +27977,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G952" t="n">
-        <v>1.50035226345062</v>
+        <v>1.50035214424133</v>
       </c>
       <c r="H952" t="n">
         <v>3602</v>
@@ -28006,7 +28006,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G953" t="n">
-        <v>1.50035226345062</v>
+        <v>1.50035214424133</v>
       </c>
       <c r="H953" t="n">
         <v>4131</v>
@@ -28035,7 +28035,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G954" t="n">
-        <v>1.50035226345062</v>
+        <v>1.50035214424133</v>
       </c>
       <c r="H954" t="n">
         <v>7140</v>
@@ -28064,7 +28064,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G955" t="n">
-        <v>1.48472344875336</v>
+        <v>1.48472356796265</v>
       </c>
       <c r="H955" t="n">
         <v>8758</v>
@@ -28151,7 +28151,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G958" t="n">
-        <v>1.45346617698669</v>
+        <v>1.4534660577774</v>
       </c>
       <c r="H958" t="n">
         <v>5750</v>
@@ -28267,7 +28267,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G962" t="n">
-        <v>1.45346617698669</v>
+        <v>1.4534660577774</v>
       </c>
       <c r="H962" t="n">
         <v>10260</v>
@@ -28296,7 +28296,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G963" t="n">
-        <v>1.48472344875336</v>
+        <v>1.48472356796265</v>
       </c>
       <c r="H963" t="n">
         <v>9765</v>
@@ -28325,7 +28325,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G964" t="n">
-        <v>1.48472344875336</v>
+        <v>1.48472356796265</v>
       </c>
       <c r="H964" t="n">
         <v>11563</v>
@@ -28354,7 +28354,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G965" t="n">
-        <v>1.48472344875336</v>
+        <v>1.48472356796265</v>
       </c>
       <c r="H965" t="n">
         <v>4432</v>
@@ -28470,7 +28470,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G969" t="n">
-        <v>1.43783760070801</v>
+        <v>1.43783748149872</v>
       </c>
       <c r="H969" t="n">
         <v>21430</v>
@@ -28499,7 +28499,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G970" t="n">
-        <v>1.43783760070801</v>
+        <v>1.43783748149872</v>
       </c>
       <c r="H970" t="n">
         <v>484</v>
@@ -28528,7 +28528,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G971" t="n">
-        <v>1.43783760070801</v>
+        <v>1.43783748149872</v>
       </c>
       <c r="H971" t="n">
         <v>1075</v>
@@ -28557,7 +28557,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G972" t="n">
-        <v>1.43783760070801</v>
+        <v>1.43783748149872</v>
       </c>
       <c r="H972" t="n">
         <v>500</v>
@@ -28586,7 +28586,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G973" t="n">
-        <v>1.42220890522003</v>
+        <v>1.42220878601074</v>
       </c>
       <c r="H973" t="n">
         <v>30</v>
@@ -28615,7 +28615,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G974" t="n">
-        <v>1.45346617698669</v>
+        <v>1.4534660577774</v>
       </c>
       <c r="H974" t="n">
         <v>949</v>
@@ -28644,7 +28644,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G975" t="n">
-        <v>1.43783760070801</v>
+        <v>1.43783748149872</v>
       </c>
       <c r="H975" t="n">
         <v>2000</v>
@@ -28673,7 +28673,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G976" t="n">
-        <v>1.42220890522003</v>
+        <v>1.42220878601074</v>
       </c>
       <c r="H976" t="n">
         <v>8943</v>
@@ -28702,7 +28702,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G977" t="n">
-        <v>1.42220890522003</v>
+        <v>1.42220878601074</v>
       </c>
       <c r="H977" t="n">
         <v>2955</v>
@@ -28731,7 +28731,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G978" t="n">
-        <v>1.43783760070801</v>
+        <v>1.43783748149872</v>
       </c>
       <c r="H978" t="n">
         <v>4265</v>
@@ -28760,7 +28760,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G979" t="n">
-        <v>1.45346617698669</v>
+        <v>1.4534660577774</v>
       </c>
       <c r="H979" t="n">
         <v>16332</v>
@@ -28789,7 +28789,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G980" t="n">
-        <v>1.43783760070801</v>
+        <v>1.43783748149872</v>
       </c>
       <c r="H980" t="n">
         <v>560</v>
@@ -28818,7 +28818,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G981" t="n">
-        <v>1.43783760070801</v>
+        <v>1.43783748149872</v>
       </c>
       <c r="H981" t="n">
         <v>3315</v>
@@ -28847,7 +28847,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G982" t="n">
-        <v>1.45346617698669</v>
+        <v>1.4534660577774</v>
       </c>
       <c r="H982" t="n">
         <v>130</v>
@@ -28876,7 +28876,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G983" t="n">
-        <v>1.45346617698669</v>
+        <v>1.4534660577774</v>
       </c>
       <c r="H983" t="n">
         <v>51</v>
@@ -28905,7 +28905,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G984" t="n">
-        <v>1.42220890522003</v>
+        <v>1.42220878601074</v>
       </c>
       <c r="H984" t="n">
         <v>2400</v>
@@ -28934,7 +28934,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G985" t="n">
-        <v>1.42220890522003</v>
+        <v>1.42220878601074</v>
       </c>
       <c r="H985" t="n">
         <v>7856</v>
@@ -28963,7 +28963,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G986" t="n">
-        <v>1.42220890522003</v>
+        <v>1.42220878601074</v>
       </c>
       <c r="H986" t="n">
         <v>28690</v>
@@ -29021,7 +29021,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G988" t="n">
-        <v>1.43783760070801</v>
+        <v>1.43783748149872</v>
       </c>
       <c r="H988" t="n">
         <v>3235</v>
@@ -29079,7 +29079,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G990" t="n">
-        <v>1.43783760070801</v>
+        <v>1.43783748149872</v>
       </c>
       <c r="H990" t="n">
         <v>377</v>
@@ -29108,7 +29108,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G991" t="n">
-        <v>1.43783760070801</v>
+        <v>1.43783748149872</v>
       </c>
       <c r="H991" t="n">
         <v>1621</v>
@@ -29137,7 +29137,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G992" t="n">
-        <v>1.43783760070801</v>
+        <v>1.43783748149872</v>
       </c>
       <c r="H992" t="n">
         <v>4633</v>
@@ -29166,7 +29166,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G993" t="n">
-        <v>1.42220890522003</v>
+        <v>1.42220878601074</v>
       </c>
       <c r="H993" t="n">
         <v>2550</v>
@@ -29195,7 +29195,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G994" t="n">
-        <v>1.42220890522003</v>
+        <v>1.42220878601074</v>
       </c>
       <c r="H994" t="n">
         <v>2459</v>
@@ -29224,7 +29224,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G995" t="n">
-        <v>1.39095151424408</v>
+        <v>1.39095139503479</v>
       </c>
       <c r="H995" t="n">
         <v>4445</v>
@@ -29253,7 +29253,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G996" t="n">
-        <v>1.42220890522003</v>
+        <v>1.42220878601074</v>
       </c>
       <c r="H996" t="n">
         <v>739</v>
@@ -29340,7 +29340,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G999" t="n">
-        <v>1.3753228187561</v>
+        <v>1.37532269954681</v>
       </c>
       <c r="H999" t="n">
         <v>5008</v>
@@ -29398,7 +29398,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G1001" t="n">
-        <v>1.3753228187561</v>
+        <v>1.37532269954681</v>
       </c>
       <c r="H1001" t="n">
         <v>3675</v>
@@ -29427,7 +29427,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G1002" t="n">
-        <v>1.43783760070801</v>
+        <v>1.43783748149872</v>
       </c>
       <c r="H1002" t="n">
         <v>29959</v>
@@ -29485,7 +29485,7 @@
         <v>2</v>
       </c>
       <c r="G1004" t="n">
-        <v>1.56286680698395</v>
+        <v>1.56286692619324</v>
       </c>
       <c r="H1004" t="n">
         <v>526368</v>
@@ -29514,7 +29514,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G1005" t="n">
-        <v>1.48472344875336</v>
+        <v>1.48472356796265</v>
       </c>
       <c r="H1005" t="n">
         <v>203908</v>
@@ -29601,7 +29601,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G1008" t="n">
-        <v>1.42220890522003</v>
+        <v>1.42220878601074</v>
       </c>
       <c r="H1008" t="n">
         <v>24714</v>
@@ -29630,7 +29630,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G1009" t="n">
-        <v>1.45346617698669</v>
+        <v>1.4534660577774</v>
       </c>
       <c r="H1009" t="n">
         <v>16050</v>
@@ -29688,7 +29688,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G1011" t="n">
-        <v>1.45346617698669</v>
+        <v>1.4534660577774</v>
       </c>
       <c r="H1011" t="n">
         <v>39708</v>
@@ -29717,7 +29717,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G1012" t="n">
-        <v>1.43783760070801</v>
+        <v>1.43783748149872</v>
       </c>
       <c r="H1012" t="n">
         <v>26843</v>
@@ -29746,7 +29746,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G1013" t="n">
-        <v>1.43783760070801</v>
+        <v>1.43783748149872</v>
       </c>
       <c r="H1013" t="n">
         <v>8510</v>
@@ -29804,7 +29804,7 @@
         <v>1.86940002441406</v>
       </c>
       <c r="G1015" t="n">
-        <v>1.46081161499023</v>
+        <v>1.46081173419952</v>
       </c>
       <c r="H1015" t="n">
         <v>31731</v>
@@ -29862,7 +29862,7 @@
         <v>1.80480003356934</v>
       </c>
       <c r="G1017" t="n">
-        <v>1.41033101081848</v>
+        <v>1.41033113002777</v>
       </c>
       <c r="H1017" t="n">
         <v>6419</v>
@@ -29891,7 +29891,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G1018" t="n">
-        <v>1.35969400405884</v>
+        <v>1.35969424247742</v>
       </c>
       <c r="H1018" t="n">
         <v>21467</v>
@@ -29949,7 +29949,7 @@
         <v>1.81679999828339</v>
       </c>
       <c r="G1020" t="n">
-        <v>1.41970825195312</v>
+        <v>1.41970813274384</v>
       </c>
       <c r="H1020" t="n">
         <v>54639</v>
@@ -29978,7 +29978,7 @@
         <v>1.77359998226166</v>
       </c>
       <c r="G1021" t="n">
-        <v>1.38595032691956</v>
+        <v>1.38595020771027</v>
       </c>
       <c r="H1021" t="n">
         <v>10862</v>
@@ -30007,7 +30007,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G1022" t="n">
-        <v>1.43002319335938</v>
+        <v>1.43002307415009</v>
       </c>
       <c r="H1022" t="n">
         <v>55375</v>
@@ -30065,7 +30065,7 @@
         <v>1.81959998607635</v>
       </c>
       <c r="G1024" t="n">
-        <v>1.42189621925354</v>
+        <v>1.42189610004425</v>
       </c>
       <c r="H1024" t="n">
         <v>67133</v>
@@ -30123,7 +30123,7 @@
         <v>1.74119997024536</v>
       </c>
       <c r="G1026" t="n">
-        <v>1.36063182353973</v>
+        <v>1.36063170433044</v>
       </c>
       <c r="H1026" t="n">
         <v>42274</v>
@@ -30181,7 +30181,7 @@
         <v>1.70500004291534</v>
       </c>
       <c r="G1028" t="n">
-        <v>1.33234405517578</v>
+        <v>1.33234393596649</v>
       </c>
       <c r="H1028" t="n">
         <v>21254</v>
@@ -30210,7 +30210,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G1029" t="n">
-        <v>1.34406542778015</v>
+        <v>1.34406554698944</v>
       </c>
       <c r="H1029" t="n">
         <v>22344</v>
@@ -30239,7 +30239,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G1030" t="n">
-        <v>1.33625113964081</v>
+        <v>1.3362512588501</v>
       </c>
       <c r="H1030" t="n">
         <v>3600</v>
@@ -30355,7 +30355,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G1034" t="n">
-        <v>1.33625113964081</v>
+        <v>1.3362512588501</v>
       </c>
       <c r="H1034" t="n">
         <v>4038</v>
@@ -30384,7 +30384,7 @@
         <v>1.68099999427795</v>
       </c>
       <c r="G1035" t="n">
-        <v>1.3135894536972</v>
+        <v>1.31358957290649</v>
       </c>
       <c r="H1035" t="n">
         <v>15612</v>
@@ -30500,7 +30500,7 @@
         <v>1.57840001583099</v>
       </c>
       <c r="G1039" t="n">
-        <v>1.2334144115448</v>
+        <v>1.23341453075409</v>
       </c>
       <c r="H1039" t="n">
         <v>13283</v>
@@ -30558,7 +30558,7 @@
         <v>1.57720005512238</v>
       </c>
       <c r="G1041" t="n">
-        <v>1.23247671127319</v>
+        <v>1.23247683048248</v>
       </c>
       <c r="H1041" t="n">
         <v>45218</v>
@@ -30587,7 +30587,7 @@
         <v>1.60580003261566</v>
       </c>
       <c r="G1042" t="n">
-        <v>1.25482583045959</v>
+        <v>1.25482571125031</v>
       </c>
       <c r="H1042" t="n">
         <v>57252</v>
@@ -30819,7 +30819,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1050" t="n">
-        <v>1.30499386787415</v>
+        <v>1.30499374866486</v>
       </c>
       <c r="H1050" t="n">
         <v>5237</v>
@@ -30877,7 +30877,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1052" t="n">
-        <v>1.30499386787415</v>
+        <v>1.30499374866486</v>
       </c>
       <c r="H1052" t="n">
         <v>3328</v>
@@ -30964,7 +30964,7 @@
         <v>1.61479997634888</v>
       </c>
       <c r="G1055" t="n">
-        <v>1.26185870170593</v>
+        <v>1.26185858249664</v>
       </c>
       <c r="H1055" t="n">
         <v>3537</v>
@@ -31080,7 +31080,7 @@
         <v>1.55980002880096</v>
       </c>
       <c r="G1059" t="n">
-        <v>1.21887981891632</v>
+        <v>1.21887993812561</v>
       </c>
       <c r="H1059" t="n">
         <v>21083</v>
@@ -31138,7 +31138,7 @@
         <v>1.49779999256134</v>
       </c>
       <c r="G1061" t="n">
-        <v>1.17043089866638</v>
+        <v>1.17043101787567</v>
       </c>
       <c r="H1061" t="n">
         <v>16113</v>
@@ -31196,7 +31196,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G1063" t="n">
-        <v>0.883019745349884</v>
+        <v>0.883019685745239</v>
       </c>
       <c r="H1063" t="n">
         <v>14800</v>
@@ -31225,7 +31225,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G1064" t="n">
-        <v>0.883019745349884</v>
+        <v>0.883019685745239</v>
       </c>
       <c r="H1064" t="n">
         <v>10076</v>
@@ -31254,7 +31254,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G1065" t="n">
-        <v>0.867391049861908</v>
+        <v>0.867391169071198</v>
       </c>
       <c r="H1065" t="n">
         <v>9626</v>
@@ -31312,7 +31312,7 @@
         <v>0.997900009155273</v>
       </c>
       <c r="G1067" t="n">
-        <v>0.779792487621307</v>
+        <v>0.779792428016663</v>
       </c>
       <c r="H1067" t="n">
         <v>46633</v>
@@ -31486,7 +31486,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G1073" t="n">
-        <v>0.968977510929108</v>
+        <v>0.968977451324463</v>
       </c>
       <c r="H1073" t="n">
         <v>6985</v>
@@ -31515,7 +31515,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G1074" t="n">
-        <v>1.09400677680969</v>
+        <v>1.0940066576004</v>
       </c>
       <c r="H1074" t="n">
         <v>7710</v>
@@ -31544,7 +31544,7 @@
         <v>1.54499995708466</v>
       </c>
       <c r="G1075" t="n">
-        <v>1.20731449127197</v>
+        <v>1.20731461048126</v>
       </c>
       <c r="H1075" t="n">
         <v>70566</v>
@@ -31602,7 +31602,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G1077" t="n">
-        <v>1.24247920513153</v>
+        <v>1.24247908592224</v>
       </c>
       <c r="H1077" t="n">
         <v>15463</v>
@@ -31631,7 +31631,7 @@
         <v>1.61500000953674</v>
       </c>
       <c r="G1078" t="n">
-        <v>1.26201498508453</v>
+        <v>1.26201510429382</v>
       </c>
       <c r="H1078" t="n">
         <v>5525</v>
@@ -31718,7 +31718,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G1081" t="n">
-        <v>1.21122169494629</v>
+        <v>1.21122181415558</v>
       </c>
       <c r="H1081" t="n">
         <v>11021</v>
@@ -31805,7 +31805,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G1084" t="n">
-        <v>1.25810778141022</v>
+        <v>1.25810790061951</v>
       </c>
       <c r="H1084" t="n">
         <v>29539</v>
@@ -31892,7 +31892,7 @@
         <v>1.52119994163513</v>
       </c>
       <c r="G1087" t="n">
-        <v>1.18871653079987</v>
+        <v>1.18871641159058</v>
       </c>
       <c r="H1087" t="n">
         <v>999</v>
@@ -31979,7 +31979,7 @@
         <v>1.56959998607635</v>
       </c>
       <c r="G1090" t="n">
-        <v>1.22653806209564</v>
+        <v>1.22653794288635</v>
       </c>
       <c r="H1090" t="n">
         <v>15691</v>
@@ -32008,7 +32008,7 @@
         <v>1.53519999980927</v>
       </c>
       <c r="G1091" t="n">
-        <v>1.19965648651123</v>
+        <v>1.19965660572052</v>
       </c>
       <c r="H1091" t="n">
         <v>7726</v>
@@ -32037,7 +32037,7 @@
         <v>1.51059997081757</v>
       </c>
       <c r="G1092" t="n">
-        <v>1.18043339252472</v>
+        <v>1.18043327331543</v>
       </c>
       <c r="H1092" t="n">
         <v>10176</v>
@@ -32066,7 +32066,7 @@
         <v>1.53840005397797</v>
       </c>
       <c r="G1093" t="n">
-        <v>1.20215725898743</v>
+        <v>1.20215713977814</v>
       </c>
       <c r="H1093" t="n">
         <v>6653</v>
@@ -32095,7 +32095,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G1094" t="n">
-        <v>1.14870703220367</v>
+        <v>1.14870715141296</v>
       </c>
       <c r="H1094" t="n">
         <v>23185</v>
@@ -32124,7 +32124,7 @@
         <v>1.42999994754791</v>
       </c>
       <c r="G1095" t="n">
-        <v>1.11744976043701</v>
+        <v>1.11744964122772</v>
       </c>
       <c r="H1095" t="n">
         <v>6692</v>
@@ -32153,7 +32153,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G1096" t="n">
-        <v>1.08619248867035</v>
+        <v>1.08619236946106</v>
       </c>
       <c r="H1096" t="n">
         <v>36445</v>
@@ -32182,7 +32182,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G1097" t="n">
-        <v>1.0549350976944</v>
+        <v>1.05493521690369</v>
       </c>
       <c r="H1097" t="n">
         <v>24618</v>
@@ -32211,7 +32211,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G1098" t="n">
-        <v>1.0549350976944</v>
+        <v>1.05493521690369</v>
       </c>
       <c r="H1098" t="n">
         <v>0</v>
@@ -32298,7 +32298,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G1101" t="n">
-        <v>1.06274938583374</v>
+        <v>1.06274950504303</v>
       </c>
       <c r="H1101" t="n">
         <v>17633</v>
@@ -32327,7 +32327,7 @@
         <v>1.44400000572205</v>
       </c>
       <c r="G1102" t="n">
-        <v>1.12838983535767</v>
+        <v>1.12838995456696</v>
       </c>
       <c r="H1102" t="n">
         <v>44823</v>
@@ -32385,7 +32385,7 @@
         <v>1.37020003795624</v>
       </c>
       <c r="G1104" t="n">
-        <v>1.07072007656097</v>
+        <v>1.07072019577026</v>
       </c>
       <c r="H1104" t="n">
         <v>5553</v>
@@ -32443,7 +32443,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1106" t="n">
-        <v>1.04712080955505</v>
+        <v>1.04712069034576</v>
       </c>
       <c r="H1106" t="n">
         <v>11729</v>
@@ -32559,7 +32559,7 @@
         <v>1.25279998779297</v>
       </c>
       <c r="G1110" t="n">
-        <v>0.978979706764221</v>
+        <v>0.978979825973511</v>
       </c>
       <c r="H1110" t="n">
         <v>24524</v>
@@ -32617,7 +32617,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1112" t="n">
-        <v>1.00023484230042</v>
+        <v>1.00023472309113</v>
       </c>
       <c r="H1112" t="n">
         <v>12512</v>
@@ -32646,7 +32646,7 @@
         <v>1.23800003528595</v>
       </c>
       <c r="G1113" t="n">
-        <v>0.967414557933807</v>
+        <v>0.967414498329163</v>
       </c>
       <c r="H1113" t="n">
         <v>18476</v>
@@ -32675,7 +32675,7 @@
         <v>1.23039996623993</v>
       </c>
       <c r="G1114" t="n">
-        <v>0.961475670337677</v>
+        <v>0.961475729942322</v>
       </c>
       <c r="H1114" t="n">
         <v>12655</v>
@@ -32733,7 +32733,7 @@
         <v>1.29779994487762</v>
       </c>
       <c r="G1116" t="n">
-        <v>1.0141441822052</v>
+        <v>1.01414406299591</v>
       </c>
       <c r="H1116" t="n">
         <v>37261</v>
@@ -32878,7 +32878,7 @@
         <v>1.2771999835968</v>
       </c>
       <c r="G1121" t="n">
-        <v>0.998046636581421</v>
+        <v>0.99804675579071</v>
       </c>
       <c r="H1121" t="n">
         <v>64712</v>
@@ -32907,7 +32907,7 @@
         <v>1.33940005302429</v>
       </c>
       <c r="G1122" t="n">
-        <v>1.04665195941925</v>
+        <v>1.04665184020996</v>
       </c>
       <c r="H1122" t="n">
         <v>68249</v>
@@ -33052,7 +33052,7 @@
         <v>1.37399995326996</v>
       </c>
       <c r="G1127" t="n">
-        <v>1.07368946075439</v>
+        <v>1.0736893415451</v>
       </c>
       <c r="H1127" t="n">
         <v>9812</v>
@@ -33081,7 +33081,7 @@
         <v>1.34979999065399</v>
       </c>
       <c r="G1128" t="n">
-        <v>1.05477893352509</v>
+        <v>1.0547788143158</v>
       </c>
       <c r="H1128" t="n">
         <v>30907</v>
@@ -33139,7 +33139,7 @@
         <v>1.29579997062683</v>
       </c>
       <c r="G1130" t="n">
-        <v>1.01258146762848</v>
+        <v>1.01258134841919</v>
       </c>
       <c r="H1130" t="n">
         <v>34473</v>
@@ -33255,7 +33255,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1134" t="n">
-        <v>1.04712080955505</v>
+        <v>1.04712069034576</v>
       </c>
       <c r="H1134" t="n">
         <v>6000</v>
@@ -33284,7 +33284,7 @@
         <v>1.2960000038147</v>
       </c>
       <c r="G1135" t="n">
-        <v>1.01273787021637</v>
+        <v>1.01273775100708</v>
       </c>
       <c r="H1135" t="n">
         <v>2329</v>
@@ -33400,7 +33400,7 @@
         <v>1.29779994487762</v>
       </c>
       <c r="G1139" t="n">
-        <v>1.0141441822052</v>
+        <v>1.01414406299591</v>
       </c>
       <c r="H1139" t="n">
         <v>8928</v>
@@ -33429,7 +33429,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1140" t="n">
-        <v>1.03930640220642</v>
+        <v>1.03930628299713</v>
       </c>
       <c r="H1140" t="n">
         <v>4250</v>
@@ -33487,7 +33487,7 @@
         <v>1.29200005531311</v>
       </c>
       <c r="G1142" t="n">
-        <v>1.00961196422577</v>
+        <v>1.00961208343506</v>
       </c>
       <c r="H1142" t="n">
         <v>1000</v>
@@ -33516,7 +33516,7 @@
         <v>1.30900001525879</v>
       </c>
       <c r="G1143" t="n">
-        <v>1.02289640903473</v>
+        <v>1.02289628982544</v>
       </c>
       <c r="H1143" t="n">
         <v>1000</v>
@@ -33545,7 +33545,7 @@
         <v>1.30499994754791</v>
       </c>
       <c r="G1144" t="n">
-        <v>1.01977050304413</v>
+        <v>1.01977062225342</v>
       </c>
       <c r="H1144" t="n">
         <v>3677</v>
@@ -33632,7 +33632,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1147" t="n">
-        <v>0.992420315742493</v>
+        <v>0.992420494556427</v>
       </c>
       <c r="H1147" t="n">
         <v>5704</v>
@@ -33661,7 +33661,7 @@
         <v>1.26499998569489</v>
       </c>
       <c r="G1148" t="n">
-        <v>0.988513231277466</v>
+        <v>0.988513171672821</v>
       </c>
       <c r="H1148" t="n">
         <v>1022</v>
@@ -33690,7 +33690,7 @@
         <v>1.26240003108978</v>
       </c>
       <c r="G1149" t="n">
-        <v>0.986481666564941</v>
+        <v>0.986481547355652</v>
       </c>
       <c r="H1149" t="n">
         <v>8000</v>
@@ -33719,7 +33719,7 @@
         <v>1.29779994487762</v>
       </c>
       <c r="G1150" t="n">
-        <v>1.0141441822052</v>
+        <v>1.01414406299591</v>
       </c>
       <c r="H1150" t="n">
         <v>16478</v>
@@ -33748,7 +33748,7 @@
         <v>1.29299998283386</v>
       </c>
       <c r="G1151" t="n">
-        <v>1.01039350032806</v>
+        <v>1.01039338111877</v>
       </c>
       <c r="H1151" t="n">
         <v>4302</v>
@@ -33777,7 +33777,7 @@
         <v>1.29180002212524</v>
       </c>
       <c r="G1152" t="n">
-        <v>1.00945580005646</v>
+        <v>1.00945568084717</v>
       </c>
       <c r="H1152" t="n">
         <v>8200</v>
@@ -33806,7 +33806,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1153" t="n">
-        <v>0.992420315742493</v>
+        <v>0.992420494556427</v>
       </c>
       <c r="H1153" t="n">
         <v>2410</v>
@@ -33922,7 +33922,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G1157" t="n">
-        <v>1.02367758750916</v>
+        <v>1.02367770671844</v>
       </c>
       <c r="H1157" t="n">
         <v>40638</v>
@@ -33980,7 +33980,7 @@
         <v>1.29499995708466</v>
       </c>
       <c r="G1159" t="n">
-        <v>1.01195633411407</v>
+        <v>1.01195621490479</v>
       </c>
       <c r="H1159" t="n">
         <v>21359</v>
@@ -34038,7 +34038,7 @@
         <v>1.28939998149872</v>
       </c>
       <c r="G1161" t="n">
-        <v>1.00758039951324</v>
+        <v>1.00758016109467</v>
       </c>
       <c r="H1161" t="n">
         <v>160</v>
@@ -34067,7 +34067,7 @@
         <v>1.29980003833771</v>
       </c>
       <c r="G1162" t="n">
-        <v>1.0157071352005</v>
+        <v>1.01570725440979</v>
       </c>
       <c r="H1162" t="n">
         <v>16940</v>
@@ -34154,7 +34154,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1165" t="n">
-        <v>0.992420315742493</v>
+        <v>0.992420494556427</v>
       </c>
       <c r="H1165" t="n">
         <v>10014</v>
@@ -34183,7 +34183,7 @@
         <v>1.27900004386902</v>
       </c>
       <c r="G1166" t="n">
-        <v>0.999453246593475</v>
+        <v>0.99945330619812</v>
       </c>
       <c r="H1166" t="n">
         <v>19032</v>
@@ -34212,7 +34212,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1167" t="n">
-        <v>0.992420315742493</v>
+        <v>0.992420494556427</v>
       </c>
       <c r="H1167" t="n">
         <v>18852</v>
@@ -34241,7 +34241,7 @@
         <v>1.22819995880127</v>
       </c>
       <c r="G1168" t="n">
-        <v>0.959756553173065</v>
+        <v>0.95975649356842</v>
       </c>
       <c r="H1168" t="n">
         <v>10446</v>
@@ -34357,7 +34357,7 @@
         <v>1.22060000896454</v>
       </c>
       <c r="G1172" t="n">
-        <v>0.95381760597229</v>
+        <v>0.95381772518158</v>
       </c>
       <c r="H1172" t="n">
         <v>2356</v>
@@ -34386,7 +34386,7 @@
         <v>1.22060000896454</v>
       </c>
       <c r="G1173" t="n">
-        <v>0.95381760597229</v>
+        <v>0.95381772518158</v>
       </c>
       <c r="H1173" t="n">
         <v>0</v>
@@ -34444,7 +34444,7 @@
         <v>1.22200000286102</v>
       </c>
       <c r="G1175" t="n">
-        <v>0.954911649227142</v>
+        <v>0.954911589622498</v>
       </c>
       <c r="H1175" t="n">
         <v>800</v>
@@ -34473,7 +34473,7 @@
         <v>1.22019994258881</v>
       </c>
       <c r="G1176" t="n">
-        <v>0.953505039215088</v>
+        <v>0.953504979610443</v>
       </c>
       <c r="H1176" t="n">
         <v>1000</v>
@@ -34502,7 +34502,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1177" t="n">
-        <v>0.953348696231842</v>
+        <v>0.953348875045776</v>
       </c>
       <c r="H1177" t="n">
         <v>1300</v>
@@ -34531,7 +34531,7 @@
         <v>1.23479998111725</v>
       </c>
       <c r="G1178" t="n">
-        <v>0.96491402387619</v>
+        <v>0.964913964271545</v>
       </c>
       <c r="H1178" t="n">
         <v>5677</v>
@@ -34560,7 +34560,7 @@
         <v>1.21700000762939</v>
       </c>
       <c r="G1179" t="n">
-        <v>0.951004505157471</v>
+        <v>0.951004445552826</v>
       </c>
       <c r="H1179" t="n">
         <v>1896</v>
@@ -34589,7 +34589,7 @@
         <v>1.19500005245209</v>
       </c>
       <c r="G1180" t="n">
-        <v>0.933812975883484</v>
+        <v>0.933812916278839</v>
       </c>
       <c r="H1180" t="n">
         <v>1588</v>
@@ -34618,7 +34618,7 @@
         <v>1.23580002784729</v>
       </c>
       <c r="G1181" t="n">
-        <v>0.965695440769196</v>
+        <v>0.965695381164551</v>
       </c>
       <c r="H1181" t="n">
         <v>2300</v>
@@ -34647,7 +34647,7 @@
         <v>1.24399995803833</v>
       </c>
       <c r="G1182" t="n">
-        <v>0.97210305929184</v>
+        <v>0.972103118896484</v>
       </c>
       <c r="H1182" t="n">
         <v>2300</v>
@@ -34676,7 +34676,7 @@
         <v>1.24399995803833</v>
       </c>
       <c r="G1183" t="n">
-        <v>0.97210305929184</v>
+        <v>0.972103118896484</v>
       </c>
       <c r="H1183" t="n">
         <v>1000</v>
@@ -34734,7 +34734,7 @@
         <v>1.20500004291534</v>
       </c>
       <c r="G1185" t="n">
-        <v>0.941627204418182</v>
+        <v>0.941627264022827</v>
       </c>
       <c r="H1185" t="n">
         <v>6534</v>
@@ -34763,7 +34763,7 @@
         <v>1.20899999141693</v>
       </c>
       <c r="G1186" t="n">
-        <v>0.944753050804138</v>
+        <v>0.944752931594849</v>
       </c>
       <c r="H1186" t="n">
         <v>8300</v>
@@ -34792,7 +34792,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1187" t="n">
-        <v>0.953348696231842</v>
+        <v>0.953348875045776</v>
       </c>
       <c r="H1187" t="n">
         <v>9105</v>
@@ -34821,7 +34821,7 @@
         <v>1.20019996166229</v>
       </c>
       <c r="G1188" t="n">
-        <v>0.937876403331757</v>
+        <v>0.937876343727112</v>
       </c>
       <c r="H1188" t="n">
         <v>10090</v>
@@ -34850,7 +34850,7 @@
         <v>1.22019994258881</v>
       </c>
       <c r="G1189" t="n">
-        <v>0.953505039215088</v>
+        <v>0.953504979610443</v>
       </c>
       <c r="H1189" t="n">
         <v>7534</v>
@@ -34879,7 +34879,7 @@
         <v>1.26979994773865</v>
       </c>
       <c r="G1190" t="n">
-        <v>0.992264211177826</v>
+        <v>0.992264091968536</v>
       </c>
       <c r="H1190" t="n">
         <v>2250</v>
@@ -34908,7 +34908,7 @@
         <v>1.23959994316101</v>
       </c>
       <c r="G1191" t="n">
-        <v>0.968664824962616</v>
+        <v>0.968664884567261</v>
       </c>
       <c r="H1191" t="n">
         <v>1101</v>
@@ -34966,7 +34966,7 @@
         <v>1.21319997310638</v>
       </c>
       <c r="G1193" t="n">
-        <v>0.948034942150116</v>
+        <v>0.948035001754761</v>
       </c>
       <c r="H1193" t="n">
         <v>5835</v>
@@ -35024,7 +35024,7 @@
         <v>1.24279999732971</v>
       </c>
       <c r="G1195" t="n">
-        <v>0.971165478229523</v>
+        <v>0.971165418624878</v>
       </c>
       <c r="H1195" t="n">
         <v>23798</v>
@@ -35053,7 +35053,7 @@
         <v>1.24199998378754</v>
       </c>
       <c r="G1196" t="n">
-        <v>0.970540285110474</v>
+        <v>0.970540344715118</v>
       </c>
       <c r="H1196" t="n">
         <v>22960</v>
@@ -35082,7 +35082,7 @@
         <v>1.24399995803833</v>
       </c>
       <c r="G1197" t="n">
-        <v>0.97210305929184</v>
+        <v>0.972103118896484</v>
       </c>
       <c r="H1197" t="n">
         <v>28501</v>
@@ -35169,7 +35169,7 @@
         <v>1.19120001792908</v>
       </c>
       <c r="G1200" t="n">
-        <v>0.930843532085419</v>
+        <v>0.930843353271484</v>
       </c>
       <c r="H1200" t="n">
         <v>13624</v>
@@ -35198,7 +35198,7 @@
         <v>1.19120001792908</v>
       </c>
       <c r="G1201" t="n">
-        <v>0.930843532085419</v>
+        <v>0.930843353271484</v>
       </c>
       <c r="H1201" t="n">
         <v>0</v>
@@ -35227,7 +35227,7 @@
         <v>1.22940003871918</v>
       </c>
       <c r="G1202" t="n">
-        <v>0.960694253444672</v>
+        <v>0.960694134235382</v>
       </c>
       <c r="H1202" t="n">
         <v>930</v>
@@ -35256,7 +35256,7 @@
         <v>1.19140005111694</v>
       </c>
       <c r="G1203" t="n">
-        <v>0.930999755859375</v>
+        <v>0.93099981546402</v>
       </c>
       <c r="H1203" t="n">
         <v>520</v>
@@ -35285,7 +35285,7 @@
         <v>1.22979998588562</v>
       </c>
       <c r="G1204" t="n">
-        <v>0.961006760597229</v>
+        <v>0.961006641387939</v>
       </c>
       <c r="H1204" t="n">
         <v>4250</v>
@@ -35314,7 +35314,7 @@
         <v>1.24199998378754</v>
       </c>
       <c r="G1205" t="n">
-        <v>0.970540285110474</v>
+        <v>0.970540344715118</v>
       </c>
       <c r="H1205" t="n">
         <v>5811</v>
@@ -35372,7 +35372,7 @@
         <v>1.21119999885559</v>
       </c>
       <c r="G1207" t="n">
-        <v>0.946472227573395</v>
+        <v>0.94647216796875</v>
       </c>
       <c r="H1207" t="n">
         <v>11015</v>
@@ -35401,7 +35401,7 @@
         <v>1.19500005245209</v>
       </c>
       <c r="G1208" t="n">
-        <v>0.933812975883484</v>
+        <v>0.933812916278839</v>
       </c>
       <c r="H1208" t="n">
         <v>1086</v>
@@ -35430,7 +35430,7 @@
         <v>1.19500005245209</v>
       </c>
       <c r="G1209" t="n">
-        <v>0.933812975883484</v>
+        <v>0.933812916278839</v>
       </c>
       <c r="H1209" t="n">
         <v>7175</v>
@@ -35488,7 +35488,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G1211" t="n">
-        <v>0.968977510929108</v>
+        <v>0.968977451324463</v>
       </c>
       <c r="H1211" t="n">
         <v>39741</v>
@@ -35575,7 +35575,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G1214" t="n">
-        <v>1.02367758750916</v>
+        <v>1.02367770671844</v>
       </c>
       <c r="H1214" t="n">
         <v>84862</v>
@@ -35604,7 +35604,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1215" t="n">
-        <v>0.984605967998505</v>
+        <v>0.984606087207794</v>
       </c>
       <c r="H1215" t="n">
         <v>32688</v>
@@ -35633,7 +35633,7 @@
         <v>1.26579999923706</v>
       </c>
       <c r="G1216" t="n">
-        <v>0.989138424396515</v>
+        <v>0.98913836479187</v>
       </c>
       <c r="H1216" t="n">
         <v>35063</v>
@@ -35778,7 +35778,7 @@
         <v>1.25539994239807</v>
       </c>
       <c r="G1221" t="n">
-        <v>0.981011390686035</v>
+        <v>0.981011509895325</v>
       </c>
       <c r="H1221" t="n">
         <v>4670</v>
@@ -35807,7 +35807,7 @@
         <v>1.22599995136261</v>
       </c>
       <c r="G1222" t="n">
-        <v>0.958037316799164</v>
+        <v>0.958037495613098</v>
       </c>
       <c r="H1222" t="n">
         <v>119</v>
@@ -35836,7 +35836,7 @@
         <v>1.22599995136261</v>
       </c>
       <c r="G1223" t="n">
-        <v>0.958037316799164</v>
+        <v>0.958037495613098</v>
       </c>
       <c r="H1223" t="n">
         <v>0</v>
@@ -35865,7 +35865,7 @@
         <v>1.22599995136261</v>
       </c>
       <c r="G1224" t="n">
-        <v>0.958037316799164</v>
+        <v>0.958037495613098</v>
       </c>
       <c r="H1224" t="n">
         <v>0</v>
@@ -35894,7 +35894,7 @@
         <v>1.23039996623993</v>
       </c>
       <c r="G1225" t="n">
-        <v>0.961475670337677</v>
+        <v>0.961475729942322</v>
       </c>
       <c r="H1225" t="n">
         <v>3067</v>
@@ -35981,7 +35981,7 @@
         <v>1.17519998550415</v>
       </c>
       <c r="G1228" t="n">
-        <v>0.918340504169464</v>
+        <v>0.918340563774109</v>
       </c>
       <c r="H1228" t="n">
         <v>8221</v>
@@ -36010,7 +36010,7 @@
         <v>1.192999958992</v>
       </c>
       <c r="G1229" t="n">
-        <v>0.932250022888184</v>
+        <v>0.932249963283539</v>
       </c>
       <c r="H1229" t="n">
         <v>712</v>
@@ -36039,7 +36039,7 @@
         <v>1.18219995498657</v>
       </c>
       <c r="G1230" t="n">
-        <v>0.923810541629791</v>
+        <v>0.923810482025146</v>
       </c>
       <c r="H1230" t="n">
         <v>425</v>
@@ -36068,7 +36068,7 @@
         <v>1.18219995498657</v>
       </c>
       <c r="G1231" t="n">
-        <v>0.923810541629791</v>
+        <v>0.923810482025146</v>
       </c>
       <c r="H1231" t="n">
         <v>0</v>
@@ -36097,7 +36097,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G1232" t="n">
-        <v>0.96116316318512</v>
+        <v>0.961163103580475</v>
       </c>
       <c r="H1232" t="n">
         <v>6056</v>
@@ -36126,7 +36126,7 @@
         <v>1.19159996509552</v>
       </c>
       <c r="G1233" t="n">
-        <v>0.931155920028687</v>
+        <v>0.931155979633331</v>
       </c>
       <c r="H1233" t="n">
         <v>510</v>
@@ -36155,7 +36155,7 @@
         <v>1.19099998474121</v>
       </c>
       <c r="G1234" t="n">
-        <v>0.930687129497528</v>
+        <v>0.930687248706818</v>
       </c>
       <c r="H1234" t="n">
         <v>2006</v>
@@ -36184,7 +36184,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G1235" t="n">
-        <v>0.96116316318512</v>
+        <v>0.961163103580475</v>
       </c>
       <c r="H1235" t="n">
         <v>16103</v>
@@ -36213,7 +36213,7 @@
         <v>1.19799995422363</v>
       </c>
       <c r="G1236" t="n">
-        <v>0.9361572265625</v>
+        <v>0.93615710735321</v>
       </c>
       <c r="H1236" t="n">
         <v>37918</v>
@@ -36242,7 +36242,7 @@
         <v>1.23800003528595</v>
       </c>
       <c r="G1237" t="n">
-        <v>0.967414557933807</v>
+        <v>0.967414498329163</v>
       </c>
       <c r="H1237" t="n">
         <v>7311</v>
@@ -36271,7 +36271,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1238" t="n">
-        <v>0.953348696231842</v>
+        <v>0.953348875045776</v>
       </c>
       <c r="H1238" t="n">
         <v>3720</v>
@@ -36300,7 +36300,7 @@
         <v>1.26800000667572</v>
       </c>
       <c r="G1239" t="n">
-        <v>0.990857660770416</v>
+        <v>0.990857481956482</v>
       </c>
       <c r="H1239" t="n">
         <v>129144</v>
@@ -36358,7 +36358,7 @@
         <v>1.27320003509521</v>
       </c>
       <c r="G1241" t="n">
-        <v>0.994921088218689</v>
+        <v>0.994921028614044</v>
       </c>
       <c r="H1241" t="n">
         <v>41792</v>
@@ -36387,7 +36387,7 @@
         <v>1.27320003509521</v>
       </c>
       <c r="G1242" t="n">
-        <v>0.994921088218689</v>
+        <v>0.994921028614044</v>
       </c>
       <c r="H1242" t="n">
         <v>13700</v>
@@ -36416,7 +36416,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1243" t="n">
-        <v>1.00023484230042</v>
+        <v>1.00023472309113</v>
       </c>
       <c r="H1243" t="n">
         <v>7071</v>
@@ -36445,7 +36445,7 @@
         <v>1.26639997959137</v>
       </c>
       <c r="G1244" t="n">
-        <v>0.989607214927673</v>
+        <v>0.989607334136963</v>
       </c>
       <c r="H1244" t="n">
         <v>32132</v>
@@ -36503,7 +36503,7 @@
         <v>1.46099996566772</v>
       </c>
       <c r="G1246" t="n">
-        <v>1.14167428016663</v>
+        <v>1.14167416095734</v>
       </c>
       <c r="H1246" t="n">
         <v>196814</v>
@@ -36532,7 +36532,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G1247" t="n">
-        <v>1.24247920513153</v>
+        <v>1.24247908592224</v>
       </c>
       <c r="H1247" t="n">
         <v>197270</v>
@@ -36561,7 +36561,7 @@
         <v>1.61300003528595</v>
       </c>
       <c r="G1248" t="n">
-        <v>1.26045215129852</v>
+        <v>1.26045203208923</v>
       </c>
       <c r="H1248" t="n">
         <v>112579</v>
@@ -36590,7 +36590,7 @@
         <v>1.59200000762939</v>
       </c>
       <c r="G1249" t="n">
-        <v>1.24404203891754</v>
+        <v>1.24404191970825</v>
       </c>
       <c r="H1249" t="n">
         <v>77714</v>
@@ -36619,7 +36619,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G1250" t="n">
-        <v>1.33625113964081</v>
+        <v>1.3362512588501</v>
       </c>
       <c r="H1250" t="n">
         <v>95910</v>
@@ -36735,7 +36735,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1254" t="n">
-        <v>1.30499386787415</v>
+        <v>1.30499374866486</v>
       </c>
       <c r="H1254" t="n">
         <v>28012</v>
@@ -36822,7 +36822,7 @@
         <v>1.72500002384186</v>
       </c>
       <c r="G1257" t="n">
-        <v>1.34797275066376</v>
+        <v>1.34797263145447</v>
       </c>
       <c r="H1257" t="n">
         <v>18428</v>
@@ -36909,7 +36909,7 @@
         <v>1.71200001239777</v>
       </c>
       <c r="G1260" t="n">
-        <v>1.33781397342682</v>
+        <v>1.33781409263611</v>
       </c>
       <c r="H1260" t="n">
         <v>36578</v>
@@ -36938,7 +36938,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G1261" t="n">
-        <v>1.34406542778015</v>
+        <v>1.34406554698944</v>
       </c>
       <c r="H1261" t="n">
         <v>16020</v>
@@ -36967,7 +36967,7 @@
         <v>1.74119997024536</v>
       </c>
       <c r="G1262" t="n">
-        <v>1.36063182353973</v>
+        <v>1.36063170433044</v>
       </c>
       <c r="H1262" t="n">
         <v>7273</v>
@@ -37112,7 +37112,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G1267" t="n">
-        <v>1.39095151424408</v>
+        <v>1.39095139503479</v>
       </c>
       <c r="H1267" t="n">
         <v>141202</v>
@@ -37170,7 +37170,7 @@
         <v>1.74979996681213</v>
       </c>
       <c r="G1269" t="n">
-        <v>1.46478521823883</v>
+        <v>1.46478509902954</v>
       </c>
       <c r="H1269" t="n">
         <v>33596</v>
@@ -37257,7 +37257,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G1272" t="n">
-        <v>1.43983912467957</v>
+        <v>1.43983900547028</v>
       </c>
       <c r="H1272" t="n">
         <v>16994</v>
@@ -37286,7 +37286,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G1273" t="n">
-        <v>1.43983912467957</v>
+        <v>1.43983900547028</v>
       </c>
       <c r="H1273" t="n">
         <v>0</v>
@@ -37344,7 +37344,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G1275" t="n">
-        <v>1.43983912467957</v>
+        <v>1.43983900547028</v>
       </c>
       <c r="H1275" t="n">
         <v>57560</v>
@@ -37489,7 +37489,7 @@
         <v>1.66600000858307</v>
       </c>
       <c r="G1280" t="n">
-        <v>1.39463484287262</v>
+        <v>1.39463472366333</v>
       </c>
       <c r="H1280" t="n">
         <v>32262</v>
@@ -37518,7 +37518,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G1281" t="n">
-        <v>1.37286984920502</v>
+        <v>1.37286972999573</v>
       </c>
       <c r="H1281" t="n">
         <v>16602</v>
@@ -37576,7 +37576,7 @@
         <v>1.64800000190735</v>
       </c>
       <c r="G1283" t="n">
-        <v>1.37956666946411</v>
+        <v>1.3795667886734</v>
       </c>
       <c r="H1283" t="n">
         <v>12860</v>
@@ -37634,7 +37634,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G1285" t="n">
-        <v>1.37286984920502</v>
+        <v>1.37286972999573</v>
       </c>
       <c r="H1285" t="n">
         <v>21352</v>
@@ -37663,7 +37663,7 @@
         <v>1.60060000419617</v>
       </c>
       <c r="G1286" t="n">
-        <v>1.33988749980927</v>
+        <v>1.33988738059998</v>
       </c>
       <c r="H1286" t="n">
         <v>27968</v>
@@ -37721,7 +37721,7 @@
         <v>1.60199999809265</v>
       </c>
       <c r="G1288" t="n">
-        <v>1.34105944633484</v>
+        <v>1.34105932712555</v>
       </c>
       <c r="H1288" t="n">
         <v>26307</v>
@@ -37837,7 +37837,7 @@
         <v>1.60599994659424</v>
       </c>
       <c r="G1292" t="n">
-        <v>1.34440779685974</v>
+        <v>1.34440791606903</v>
       </c>
       <c r="H1292" t="n">
         <v>20464</v>
@@ -37866,7 +37866,7 @@
         <v>1.60199999809265</v>
       </c>
       <c r="G1293" t="n">
-        <v>1.34105944633484</v>
+        <v>1.34105932712555</v>
       </c>
       <c r="H1293" t="n">
         <v>1484</v>
@@ -37953,7 +37953,7 @@
         <v>1.71039998531342</v>
       </c>
       <c r="G1296" t="n">
-        <v>1.4318026304245</v>
+        <v>1.43180274963379</v>
       </c>
       <c r="H1296" t="n">
         <v>100876</v>
@@ -37982,7 +37982,7 @@
         <v>1.77799999713898</v>
       </c>
       <c r="G1297" t="n">
-        <v>1.48839175701141</v>
+        <v>1.4883918762207</v>
       </c>
       <c r="H1297" t="n">
         <v>90989</v>
@@ -38011,7 +38011,7 @@
         <v>1.75419998168945</v>
       </c>
       <c r="G1298" t="n">
-        <v>1.46846830844879</v>
+        <v>1.46846842765808</v>
       </c>
       <c r="H1298" t="n">
         <v>40624</v>
@@ -38069,7 +38069,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G1300" t="n">
-        <v>1.49006605148315</v>
+        <v>1.49006593227386</v>
       </c>
       <c r="H1300" t="n">
         <v>15871</v>
@@ -38127,7 +38127,7 @@
         <v>1.7688000202179</v>
       </c>
       <c r="G1302" t="n">
-        <v>1.48069024085999</v>
+        <v>1.48069036006927</v>
       </c>
       <c r="H1302" t="n">
         <v>40491</v>
@@ -38185,7 +38185,7 @@
         <v>1.74399995803833</v>
       </c>
       <c r="G1304" t="n">
-        <v>1.45992970466614</v>
+        <v>1.45992982387543</v>
       </c>
       <c r="H1304" t="n">
         <v>70208</v>
@@ -38214,7 +38214,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G1305" t="n">
-        <v>1.56540644168854</v>
+        <v>1.56540656089783</v>
       </c>
       <c r="H1305" t="n">
         <v>90063</v>
@@ -38243,7 +38243,7 @@
         <v>1.83259999752045</v>
       </c>
       <c r="G1306" t="n">
-        <v>1.53409826755524</v>
+        <v>1.53409838676453</v>
       </c>
       <c r="H1306" t="n">
         <v>15504</v>
@@ -38330,7 +38330,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G1309" t="n">
-        <v>1.56540644168854</v>
+        <v>1.56540656089783</v>
       </c>
       <c r="H1309" t="n">
         <v>5381</v>
@@ -38359,7 +38359,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G1310" t="n">
-        <v>1.56540644168854</v>
+        <v>1.56540656089783</v>
       </c>
       <c r="H1310" t="n">
         <v>6800</v>
@@ -38388,7 +38388,7 @@
         <v>1.87479996681213</v>
       </c>
       <c r="G1311" t="n">
-        <v>1.56942451000214</v>
+        <v>1.56942462921143</v>
       </c>
       <c r="H1311" t="n">
         <v>5785</v>
@@ -38504,7 +38504,7 @@
         <v>1.84019994735718</v>
       </c>
       <c r="G1315" t="n">
-        <v>1.54046034812927</v>
+        <v>1.54046046733856</v>
       </c>
       <c r="H1315" t="n">
         <v>5051</v>
@@ -38591,7 +38591,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G1318" t="n">
-        <v>1.62400448322296</v>
+        <v>1.62400460243225</v>
       </c>
       <c r="H1318" t="n">
         <v>11052</v>
@@ -38678,7 +38678,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G1321" t="n">
-        <v>1.65748906135559</v>
+        <v>1.65748918056488</v>
       </c>
       <c r="H1321" t="n">
         <v>17248</v>
@@ -38765,7 +38765,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G1324" t="n">
-        <v>1.61563336849213</v>
+        <v>1.61563324928284</v>
       </c>
       <c r="H1324" t="n">
         <v>11644</v>
@@ -38794,7 +38794,7 @@
         <v>1.92120003700256</v>
       </c>
       <c r="G1325" t="n">
-        <v>1.60826671123505</v>
+        <v>1.60826683044434</v>
       </c>
       <c r="H1325" t="n">
         <v>17616</v>
@@ -38823,7 +38823,7 @@
         <v>1.94700002670288</v>
       </c>
       <c r="G1326" t="n">
-        <v>1.62986433506012</v>
+        <v>1.62986445426941</v>
       </c>
       <c r="H1326" t="n">
         <v>33486</v>
@@ -38852,7 +38852,7 @@
         <v>1.95239996910095</v>
       </c>
       <c r="G1327" t="n">
-        <v>1.6343846321106</v>
+        <v>1.63438475131989</v>
       </c>
       <c r="H1327" t="n">
         <v>11152</v>
@@ -38881,7 +38881,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G1328" t="n">
-        <v>1.64074683189392</v>
+        <v>1.64074695110321</v>
       </c>
       <c r="H1328" t="n">
         <v>20785</v>
@@ -38910,7 +38910,7 @@
         <v>1.95959997177124</v>
       </c>
       <c r="G1329" t="n">
-        <v>1.64041185379028</v>
+        <v>1.64041197299957</v>
       </c>
       <c r="H1329" t="n">
         <v>3100</v>
@@ -38939,7 +38939,7 @@
         <v>1.91499996185303</v>
       </c>
       <c r="G1330" t="n">
-        <v>1.60307657718658</v>
+        <v>1.60307669639587</v>
       </c>
       <c r="H1330" t="n">
         <v>7584</v>
@@ -38968,7 +38968,7 @@
         <v>1.91620004177094</v>
       </c>
       <c r="G1331" t="n">
-        <v>1.60408127307892</v>
+        <v>1.60408115386963</v>
       </c>
       <c r="H1331" t="n">
         <v>3423</v>
@@ -39113,7 +39113,7 @@
         <v>1.91499996185303</v>
       </c>
       <c r="G1336" t="n">
-        <v>1.60307657718658</v>
+        <v>1.60307669639587</v>
       </c>
       <c r="H1336" t="n">
         <v>4148</v>
@@ -39142,7 +39142,7 @@
         <v>1.91499996185303</v>
       </c>
       <c r="G1337" t="n">
-        <v>1.60307657718658</v>
+        <v>1.60307669639587</v>
       </c>
       <c r="H1337" t="n">
         <v>6260</v>
@@ -39200,7 +39200,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G1339" t="n">
-        <v>1.60726225376129</v>
+        <v>1.607262134552</v>
       </c>
       <c r="H1339" t="n">
         <v>1005</v>
@@ -39229,7 +39229,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G1340" t="n">
-        <v>1.60726225376129</v>
+        <v>1.607262134552</v>
       </c>
       <c r="H1340" t="n">
         <v>120</v>
@@ -39258,7 +39258,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G1341" t="n">
-        <v>1.60726225376129</v>
+        <v>1.607262134552</v>
       </c>
       <c r="H1341" t="n">
         <v>20929</v>
@@ -39287,7 +39287,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G1342" t="n">
-        <v>1.61563336849213</v>
+        <v>1.61563324928284</v>
       </c>
       <c r="H1342" t="n">
         <v>4847</v>
@@ -39316,7 +39316,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G1343" t="n">
-        <v>1.60726225376129</v>
+        <v>1.607262134552</v>
       </c>
       <c r="H1343" t="n">
         <v>14161</v>
@@ -39374,7 +39374,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G1345" t="n">
-        <v>1.65748906135559</v>
+        <v>1.65748918056488</v>
       </c>
       <c r="H1345" t="n">
         <v>50151</v>
@@ -39490,7 +39490,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G1349" t="n">
-        <v>1.65748906135559</v>
+        <v>1.65748918056488</v>
       </c>
       <c r="H1349" t="n">
         <v>45371</v>
@@ -39519,7 +39519,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G1350" t="n">
-        <v>1.60726225376129</v>
+        <v>1.607262134552</v>
       </c>
       <c r="H1350" t="n">
         <v>120787</v>
@@ -39548,7 +39548,7 @@
         <v>1.91499996185303</v>
       </c>
       <c r="G1351" t="n">
-        <v>1.60307657718658</v>
+        <v>1.60307669639587</v>
       </c>
       <c r="H1351" t="n">
         <v>33983</v>
@@ -39635,7 +39635,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G1354" t="n">
-        <v>1.59051978588104</v>
+        <v>1.59051990509033</v>
       </c>
       <c r="H1354" t="n">
         <v>15319</v>
@@ -39780,7 +39780,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G1359" t="n">
-        <v>1.56540644168854</v>
+        <v>1.56540656089783</v>
       </c>
       <c r="H1359" t="n">
         <v>4850</v>
@@ -39809,7 +39809,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G1360" t="n">
-        <v>1.59051978588104</v>
+        <v>1.59051990509033</v>
       </c>
       <c r="H1360" t="n">
         <v>13059</v>
@@ -39838,7 +39838,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G1361" t="n">
-        <v>1.60726225376129</v>
+        <v>1.607262134552</v>
       </c>
       <c r="H1361" t="n">
         <v>16896</v>
@@ -39867,7 +39867,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G1362" t="n">
-        <v>1.59051978588104</v>
+        <v>1.59051990509033</v>
       </c>
       <c r="H1362" t="n">
         <v>7070</v>
@@ -39925,7 +39925,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G1364" t="n">
-        <v>1.59051978588104</v>
+        <v>1.59051990509033</v>
       </c>
       <c r="H1364" t="n">
         <v>4035</v>
@@ -39954,7 +39954,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G1365" t="n">
-        <v>1.59051978588104</v>
+        <v>1.59051990509033</v>
       </c>
       <c r="H1365" t="n">
         <v>1022</v>
@@ -40041,7 +40041,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G1368" t="n">
-        <v>1.59051978588104</v>
+        <v>1.59051990509033</v>
       </c>
       <c r="H1368" t="n">
         <v>25050</v>
@@ -40186,7 +40186,7 @@
         <v>1.83500003814697</v>
       </c>
       <c r="G1373" t="n">
-        <v>1.53610742092133</v>
+        <v>1.53610730171204</v>
       </c>
       <c r="H1373" t="n">
         <v>6413</v>
@@ -40389,7 +40389,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1380" t="n">
-        <v>1.80816996097565</v>
+        <v>1.80817008018494</v>
       </c>
       <c r="H1380" t="n">
         <v>114976</v>
@@ -40418,7 +40418,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G1381" t="n">
-        <v>1.90862393379211</v>
+        <v>1.90862369537354</v>
       </c>
       <c r="H1381" t="n">
         <v>118880</v>
@@ -40476,7 +40476,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G1383" t="n">
-        <v>1.87513911724091</v>
+        <v>1.87513935565948</v>
       </c>
       <c r="H1383" t="n">
         <v>52913</v>
@@ -40592,7 +40592,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G1387" t="n">
-        <v>1.84165477752686</v>
+        <v>1.84165465831757</v>
       </c>
       <c r="H1387" t="n">
         <v>33572</v>
@@ -40708,7 +40708,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1391" t="n">
-        <v>1.80816996097565</v>
+        <v>1.80817008018494</v>
       </c>
       <c r="H1391" t="n">
         <v>20155</v>
@@ -40737,7 +40737,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G1392" t="n">
-        <v>1.76631414890289</v>
+        <v>1.7663140296936</v>
       </c>
       <c r="H1392" t="n">
         <v>3519</v>
@@ -40766,7 +40766,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1393" t="n">
-        <v>1.80816996097565</v>
+        <v>1.80817008018494</v>
       </c>
       <c r="H1393" t="n">
         <v>10650</v>
@@ -40853,7 +40853,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1396" t="n">
-        <v>1.75794291496277</v>
+        <v>1.75794303417206</v>
       </c>
       <c r="H1396" t="n">
         <v>11946</v>
@@ -40882,7 +40882,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1397" t="n">
-        <v>1.75794291496277</v>
+        <v>1.75794303417206</v>
       </c>
       <c r="H1397" t="n">
         <v>17267</v>
@@ -40911,7 +40911,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G1398" t="n">
-        <v>1.76631414890289</v>
+        <v>1.7663140296936</v>
       </c>
       <c r="H1398" t="n">
         <v>4485</v>
@@ -40940,7 +40940,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1399" t="n">
-        <v>1.75794291496277</v>
+        <v>1.75794303417206</v>
       </c>
       <c r="H1399" t="n">
         <v>13274</v>
@@ -41027,7 +41027,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G1402" t="n">
-        <v>1.7160872220993</v>
+        <v>1.71608710289001</v>
       </c>
       <c r="H1402" t="n">
         <v>33165</v>
@@ -41114,7 +41114,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G1405" t="n">
-        <v>1.74957180023193</v>
+        <v>1.74957191944122</v>
       </c>
       <c r="H1405" t="n">
         <v>6593</v>
@@ -41172,7 +41172,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G1407" t="n">
-        <v>1.7160872220993</v>
+        <v>1.71608710289001</v>
       </c>
       <c r="H1407" t="n">
         <v>5350</v>
@@ -41259,7 +41259,7 @@
         <v>1.9650000333786</v>
       </c>
       <c r="G1410" t="n">
-        <v>1.64493238925934</v>
+        <v>1.64493250846863</v>
       </c>
       <c r="H1410" t="n">
         <v>8674</v>
@@ -41433,7 +41433,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G1416" t="n">
-        <v>1.65748906135559</v>
+        <v>1.65748918056488</v>
       </c>
       <c r="H1416" t="n">
         <v>5</v>
@@ -41578,7 +41578,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1421" t="n">
-        <v>1.80816996097565</v>
+        <v>1.80817008018494</v>
       </c>
       <c r="H1421" t="n">
         <v>41767</v>
@@ -41723,7 +41723,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G1426" t="n">
-        <v>1.83328366279602</v>
+        <v>1.83328354358673</v>
       </c>
       <c r="H1426" t="n">
         <v>5861</v>
@@ -41839,7 +41839,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G1430" t="n">
-        <v>1.83328366279602</v>
+        <v>1.83328354358673</v>
       </c>
       <c r="H1430" t="n">
         <v>2450</v>
@@ -41868,7 +41868,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G1431" t="n">
-        <v>1.84165477752686</v>
+        <v>1.84165465831757</v>
       </c>
       <c r="H1431" t="n">
         <v>8624</v>
@@ -42042,7 +42042,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G1437" t="n">
-        <v>1.85002565383911</v>
+        <v>1.8500257730484</v>
       </c>
       <c r="H1437" t="n">
         <v>2124</v>
@@ -42187,7 +42187,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1442" t="n">
-        <v>1.80816996097565</v>
+        <v>1.80817008018494</v>
       </c>
       <c r="H1442" t="n">
         <v>3900</v>
@@ -42216,7 +42216,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G1443" t="n">
-        <v>1.83328366279602</v>
+        <v>1.83328354358673</v>
       </c>
       <c r="H1443" t="n">
         <v>7310</v>
@@ -42245,7 +42245,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G1444" t="n">
-        <v>1.83328366279602</v>
+        <v>1.83328354358673</v>
       </c>
       <c r="H1444" t="n">
         <v>0</v>
@@ -42361,7 +42361,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G1448" t="n">
-        <v>1.76631414890289</v>
+        <v>1.7663140296936</v>
       </c>
       <c r="H1448" t="n">
         <v>6157</v>
@@ -42535,7 +42535,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1454" t="n">
-        <v>1.75794291496277</v>
+        <v>1.75794303417206</v>
       </c>
       <c r="H1454" t="n">
         <v>10200</v>
@@ -42593,7 +42593,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G1456" t="n">
-        <v>1.83328366279602</v>
+        <v>1.83328354358673</v>
       </c>
       <c r="H1456" t="n">
         <v>33296</v>
@@ -42622,7 +42622,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G1457" t="n">
-        <v>1.84165477752686</v>
+        <v>1.84165465831757</v>
       </c>
       <c r="H1457" t="n">
         <v>31486</v>
@@ -42651,7 +42651,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G1458" t="n">
-        <v>1.86676800251007</v>
+        <v>1.86676812171936</v>
       </c>
       <c r="H1458" t="n">
         <v>13297</v>
@@ -42680,7 +42680,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G1459" t="n">
-        <v>1.87513911724091</v>
+        <v>1.87513935565948</v>
       </c>
       <c r="H1459" t="n">
         <v>10775</v>
@@ -42709,7 +42709,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G1460" t="n">
-        <v>1.87513911724091</v>
+        <v>1.87513935565948</v>
       </c>
       <c r="H1460" t="n">
         <v>12250</v>
@@ -42767,7 +42767,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G1462" t="n">
-        <v>2.19324278831482</v>
+        <v>2.1932430267334</v>
       </c>
       <c r="H1462" t="n">
         <v>497101</v>
@@ -42854,7 +42854,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G1465" t="n">
-        <v>2.16812968254089</v>
+        <v>2.16812992095947</v>
       </c>
       <c r="H1465" t="n">
         <v>38675</v>
@@ -42999,7 +42999,7 @@
         <v>2.5</v>
       </c>
       <c r="G1470" t="n">
-        <v>2.09278917312622</v>
+        <v>2.0927894115448</v>
       </c>
       <c r="H1470" t="n">
         <v>17544</v>
@@ -43057,7 +43057,7 @@
         <v>2.5</v>
       </c>
       <c r="G1472" t="n">
-        <v>2.09278917312622</v>
+        <v>2.0927894115448</v>
       </c>
       <c r="H1472" t="n">
         <v>16513</v>
@@ -43115,7 +43115,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G1474" t="n">
-        <v>2.10953140258789</v>
+        <v>2.10953164100647</v>
       </c>
       <c r="H1474" t="n">
         <v>11143</v>
@@ -43144,7 +43144,7 @@
         <v>2.5</v>
       </c>
       <c r="G1475" t="n">
-        <v>2.09278917312622</v>
+        <v>2.0927894115448</v>
       </c>
       <c r="H1475" t="n">
         <v>1995</v>
@@ -43289,7 +43289,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G1480" t="n">
-        <v>2.20998549461365</v>
+        <v>2.20998573303223</v>
       </c>
       <c r="H1480" t="n">
         <v>16620</v>
@@ -43318,7 +43318,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G1481" t="n">
-        <v>2.20998549461365</v>
+        <v>2.20998573303223</v>
       </c>
       <c r="H1481" t="n">
         <v>3620</v>
@@ -43347,7 +43347,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G1482" t="n">
-        <v>2.19324278831482</v>
+        <v>2.1932430267334</v>
       </c>
       <c r="H1482" t="n">
         <v>2227</v>
@@ -43521,7 +43521,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G1488" t="n">
-        <v>2.16812968254089</v>
+        <v>2.16812992095947</v>
       </c>
       <c r="H1488" t="n">
         <v>17680</v>
@@ -43637,7 +43637,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G1492" t="n">
-        <v>2.15138745307922</v>
+        <v>2.15138721466064</v>
       </c>
       <c r="H1492" t="n">
         <v>4814</v>
@@ -43666,7 +43666,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G1493" t="n">
-        <v>2.28532600402832</v>
+        <v>2.28532576560974</v>
       </c>
       <c r="H1493" t="n">
         <v>72360</v>
@@ -43724,7 +43724,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G1495" t="n">
-        <v>2.26021242141724</v>
+        <v>2.26021265983582</v>
       </c>
       <c r="H1495" t="n">
         <v>31872</v>
@@ -43811,7 +43811,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G1498" t="n">
-        <v>2.21835684776306</v>
+        <v>2.21835660934448</v>
       </c>
       <c r="H1498" t="n">
         <v>26546</v>
@@ -43840,7 +43840,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G1499" t="n">
-        <v>2.21835684776306</v>
+        <v>2.21835660934448</v>
       </c>
       <c r="H1499" t="n">
         <v>2484</v>
@@ -43985,7 +43985,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G1504" t="n">
-        <v>2.24347043037415</v>
+        <v>2.24347019195557</v>
       </c>
       <c r="H1504" t="n">
         <v>44721</v>
@@ -44014,7 +44014,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G1505" t="n">
-        <v>2.21835684776306</v>
+        <v>2.21835660934448</v>
       </c>
       <c r="H1505" t="n">
         <v>7243</v>
@@ -44101,7 +44101,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G1508" t="n">
-        <v>2.26021242141724</v>
+        <v>2.26021265983582</v>
       </c>
       <c r="H1508" t="n">
         <v>11295</v>
@@ -44159,7 +44159,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G1510" t="n">
-        <v>2.26021242141724</v>
+        <v>2.26021265983582</v>
       </c>
       <c r="H1510" t="n">
         <v>3332</v>
@@ -44188,7 +44188,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G1511" t="n">
-        <v>2.21835684776306</v>
+        <v>2.21835660934448</v>
       </c>
       <c r="H1511" t="n">
         <v>8611</v>
@@ -44333,7 +44333,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G1516" t="n">
-        <v>2.26021242141724</v>
+        <v>2.26021265983582</v>
       </c>
       <c r="H1516" t="n">
         <v>39885</v>
@@ -44362,7 +44362,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G1517" t="n">
-        <v>2.54483199119568</v>
+        <v>2.5448317527771</v>
       </c>
       <c r="H1517" t="n">
         <v>82221</v>
@@ -44391,7 +44391,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G1518" t="n">
-        <v>2.62017226219177</v>
+        <v>2.62017250061035</v>
       </c>
       <c r="H1518" t="n">
         <v>151266</v>
@@ -44420,7 +44420,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G1519" t="n">
-        <v>2.59505867958069</v>
+        <v>2.59505891799927</v>
       </c>
       <c r="H1519" t="n">
         <v>110398</v>
@@ -44536,7 +44536,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G1523" t="n">
-        <v>2.75411057472229</v>
+        <v>2.75411081314087</v>
       </c>
       <c r="H1523" t="n">
         <v>36741</v>
@@ -44623,7 +44623,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G1526" t="n">
-        <v>3.20615315437317</v>
+        <v>3.20615339279175</v>
       </c>
       <c r="H1526" t="n">
         <v>73041</v>
@@ -44797,7 +44797,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G1532" t="n">
-        <v>2.95501852035522</v>
+        <v>2.9550187587738</v>
       </c>
       <c r="H1532" t="n">
         <v>14573</v>
@@ -44855,7 +44855,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G1534" t="n">
-        <v>2.87967824935913</v>
+        <v>2.87967801094055</v>
       </c>
       <c r="H1534" t="n">
         <v>5863</v>
@@ -44971,7 +44971,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1538" t="n">
-        <v>2.84619379043579</v>
+        <v>2.84619331359863</v>
       </c>
       <c r="H1538" t="n">
         <v>13330</v>
@@ -45058,7 +45058,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1541" t="n">
-        <v>2.80433773994446</v>
+        <v>2.80433750152588</v>
       </c>
       <c r="H1541" t="n">
         <v>9323</v>
@@ -45348,7 +45348,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G1551" t="n">
-        <v>3.22289538383484</v>
+        <v>3.22289562225342</v>
       </c>
       <c r="H1551" t="n">
         <v>94238</v>
@@ -79991,13 +79991,13 @@
         <v>46315.2916666667</v>
       </c>
       <c r="C2746" t="n">
-        <v>0.419999986886978</v>
+        <v>0.389999985694885</v>
       </c>
       <c r="D2746" t="n">
-        <v>0.428000003099442</v>
+        <v>0.389999985694885</v>
       </c>
       <c r="E2746" t="n">
-        <v>0.418000012636185</v>
+        <v>0.389999985694885</v>
       </c>
       <c r="F2746" t="n">
         <v>0.389999985694885</v>
@@ -80009,6 +80009,35 @@
         <v>2466</v>
       </c>
       <c r="I2746" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2747">
+      <c r="A2747" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2747" s="1" t="n">
+        <v>46316.2916666667</v>
+      </c>
+      <c r="C2747" t="n">
+        <v>0.389999985694885</v>
+      </c>
+      <c r="D2747" t="n">
+        <v>0.407999992370605</v>
+      </c>
+      <c r="E2747" t="n">
+        <v>0.389999985694885</v>
+      </c>
+      <c r="F2747" t="n">
+        <v>0.407999992370605</v>
+      </c>
+      <c r="G2747" t="n">
+        <v>0.407999992370605</v>
+      </c>
+      <c r="H2747" t="n">
+        <v>3115</v>
+      </c>
+      <c r="I2747" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ZUC.MI.xlsx
+++ b/data/ZUC.MI.xlsx
@@ -427,7 +427,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G2" t="n">
-        <v>3.01633310317993</v>
+        <v>3.01633286476135</v>
       </c>
       <c r="H2" t="n">
         <v>42345</v>
@@ -456,7 +456,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G3" t="n">
-        <v>3.07884788513184</v>
+        <v>3.07884764671326</v>
       </c>
       <c r="H3" t="n">
         <v>28114</v>
@@ -485,7 +485,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G4" t="n">
-        <v>2.96163272857666</v>
+        <v>2.96163249015808</v>
       </c>
       <c r="H4" t="n">
         <v>12680</v>
@@ -572,7 +572,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G7" t="n">
-        <v>2.84441757202148</v>
+        <v>2.84441781044006</v>
       </c>
       <c r="H7" t="n">
         <v>15987</v>
@@ -688,7 +688,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G11" t="n">
-        <v>2.77408862113953</v>
+        <v>2.77408885955811</v>
       </c>
       <c r="H11" t="n">
         <v>14530</v>
@@ -717,7 +717,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G12" t="n">
-        <v>2.62561631202698</v>
+        <v>2.6256160736084</v>
       </c>
       <c r="H12" t="n">
         <v>16207</v>
@@ -746,7 +746,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G13" t="n">
-        <v>2.50840139389038</v>
+        <v>2.5084011554718</v>
       </c>
       <c r="H13" t="n">
         <v>22831</v>
@@ -833,7 +833,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G16" t="n">
-        <v>2.39118623733521</v>
+        <v>2.39118647575378</v>
       </c>
       <c r="H16" t="n">
         <v>21477</v>
@@ -978,7 +978,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G21" t="n">
-        <v>2.32867169380188</v>
+        <v>2.3286714553833</v>
       </c>
       <c r="H21" t="n">
         <v>6070</v>
@@ -1094,7 +1094,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G25" t="n">
-        <v>1.7894823551178</v>
+        <v>1.78948271274567</v>
       </c>
       <c r="H25" t="n">
         <v>29015</v>
@@ -1326,7 +1326,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G33" t="n">
-        <v>1.99265503883362</v>
+        <v>1.99265539646149</v>
       </c>
       <c r="H33" t="n">
         <v>23570</v>
@@ -1500,7 +1500,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G39" t="n">
-        <v>2.44588661193848</v>
+        <v>2.44588685035706</v>
       </c>
       <c r="H39" t="n">
         <v>23320</v>
@@ -1558,7 +1558,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G41" t="n">
-        <v>2.51621580123901</v>
+        <v>2.51621556282043</v>
       </c>
       <c r="H41" t="n">
         <v>12434</v>
@@ -1674,7 +1674,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G45" t="n">
-        <v>2.77408862113953</v>
+        <v>2.77408885955811</v>
       </c>
       <c r="H45" t="n">
         <v>276654</v>
@@ -1761,7 +1761,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G48" t="n">
-        <v>2.52403020858765</v>
+        <v>2.52402997016907</v>
       </c>
       <c r="H48" t="n">
         <v>14408</v>
@@ -2022,7 +2022,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G57" t="n">
-        <v>2.3521146774292</v>
+        <v>2.35211443901062</v>
       </c>
       <c r="H57" t="n">
         <v>7619</v>
@@ -2051,7 +2051,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G58" t="n">
-        <v>2.27397108078003</v>
+        <v>2.27397131919861</v>
       </c>
       <c r="H58" t="n">
         <v>5139</v>
@@ -2080,7 +2080,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G59" t="n">
-        <v>2.22708511352539</v>
+        <v>2.22708487510681</v>
       </c>
       <c r="H59" t="n">
         <v>10942</v>
@@ -2138,7 +2138,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G61" t="n">
-        <v>2.08642721176147</v>
+        <v>2.08642745018005</v>
       </c>
       <c r="H61" t="n">
         <v>24791</v>
@@ -2196,7 +2196,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G63" t="n">
-        <v>2.07079863548279</v>
+        <v>2.07079887390137</v>
       </c>
       <c r="H63" t="n">
         <v>3910</v>
@@ -2254,7 +2254,7 @@
         <v>2.5</v>
       </c>
       <c r="G65" t="n">
-        <v>1.95358347892761</v>
+        <v>1.95358335971832</v>
       </c>
       <c r="H65" t="n">
         <v>4420</v>
@@ -2283,7 +2283,7 @@
         <v>2.5</v>
       </c>
       <c r="G66" t="n">
-        <v>1.95358347892761</v>
+        <v>1.95358335971832</v>
       </c>
       <c r="H66" t="n">
         <v>8536</v>
@@ -2312,7 +2312,7 @@
         <v>2.5</v>
       </c>
       <c r="G67" t="n">
-        <v>1.95358347892761</v>
+        <v>1.95358335971832</v>
       </c>
       <c r="H67" t="n">
         <v>400</v>
@@ -2341,7 +2341,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G68" t="n">
-        <v>1.86762583255768</v>
+        <v>1.86762571334839</v>
       </c>
       <c r="H68" t="n">
         <v>5688</v>
@@ -2370,7 +2370,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G69" t="n">
-        <v>1.83636856079102</v>
+        <v>1.83636832237244</v>
       </c>
       <c r="H69" t="n">
         <v>7190</v>
@@ -2399,7 +2399,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G70" t="n">
-        <v>1.82073986530304</v>
+        <v>1.82073962688446</v>
       </c>
       <c r="H70" t="n">
         <v>19067</v>
@@ -2428,7 +2428,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G71" t="n">
-        <v>1.8129255771637</v>
+        <v>1.81292545795441</v>
       </c>
       <c r="H71" t="n">
         <v>7528</v>
@@ -2457,7 +2457,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G72" t="n">
-        <v>1.80511116981506</v>
+        <v>1.80511128902435</v>
       </c>
       <c r="H72" t="n">
         <v>6071</v>
@@ -2486,7 +2486,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G73" t="n">
-        <v>1.94576930999756</v>
+        <v>1.94576907157898</v>
       </c>
       <c r="H73" t="n">
         <v>30047</v>
@@ -2515,7 +2515,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G74" t="n">
-        <v>1.9145120382309</v>
+        <v>1.91451179981232</v>
       </c>
       <c r="H74" t="n">
         <v>27553</v>
@@ -2544,7 +2544,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G75" t="n">
-        <v>1.84418284893036</v>
+        <v>1.84418261051178</v>
       </c>
       <c r="H75" t="n">
         <v>12321</v>
@@ -2573,7 +2573,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G76" t="n">
-        <v>1.8754403591156</v>
+        <v>1.87544012069702</v>
       </c>
       <c r="H76" t="n">
         <v>16625</v>
@@ -2602,7 +2602,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G77" t="n">
-        <v>1.80511116981506</v>
+        <v>1.80511128902435</v>
       </c>
       <c r="H77" t="n">
         <v>15224</v>
@@ -2631,7 +2631,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G78" t="n">
-        <v>1.77385377883911</v>
+        <v>1.7738538980484</v>
       </c>
       <c r="H78" t="n">
         <v>12767</v>
@@ -2660,7 +2660,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G79" t="n">
-        <v>1.75041091442108</v>
+        <v>1.75041079521179</v>
       </c>
       <c r="H79" t="n">
         <v>18881</v>
@@ -2718,7 +2718,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G81" t="n">
-        <v>1.75041091442108</v>
+        <v>1.75041079521179</v>
       </c>
       <c r="H81" t="n">
         <v>11995</v>
@@ -2747,7 +2747,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G82" t="n">
-        <v>1.85981178283691</v>
+        <v>1.85981154441833</v>
       </c>
       <c r="H82" t="n">
         <v>17718</v>
@@ -2776,7 +2776,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G83" t="n">
-        <v>1.85981178283691</v>
+        <v>1.85981154441833</v>
       </c>
       <c r="H83" t="n">
         <v>1959</v>
@@ -2805,7 +2805,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G84" t="n">
-        <v>1.85981178283691</v>
+        <v>1.85981154441833</v>
       </c>
       <c r="H84" t="n">
         <v>1535</v>
@@ -2834,7 +2834,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G85" t="n">
-        <v>1.83636856079102</v>
+        <v>1.83636832237244</v>
       </c>
       <c r="H85" t="n">
         <v>1560</v>
@@ -2863,7 +2863,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G86" t="n">
-        <v>1.78166806697845</v>
+        <v>1.78166830539703</v>
       </c>
       <c r="H86" t="n">
         <v>2070</v>
@@ -2892,7 +2892,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G87" t="n">
-        <v>1.7347823381424</v>
+        <v>1.73478221893311</v>
       </c>
       <c r="H87" t="n">
         <v>11269</v>
@@ -2921,7 +2921,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G88" t="n">
-        <v>1.7347823381424</v>
+        <v>1.73478221893311</v>
       </c>
       <c r="H88" t="n">
         <v>9381</v>
@@ -2950,7 +2950,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G89" t="n">
-        <v>1.7894823551178</v>
+        <v>1.78948271274567</v>
       </c>
       <c r="H89" t="n">
         <v>13120</v>
@@ -2979,7 +2979,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G90" t="n">
-        <v>1.70352482795715</v>
+        <v>1.70352494716644</v>
       </c>
       <c r="H90" t="n">
         <v>5489</v>
@@ -3037,7 +3037,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G92" t="n">
-        <v>1.63319575786591</v>
+        <v>1.6331958770752</v>
       </c>
       <c r="H92" t="n">
         <v>15187</v>
@@ -3066,7 +3066,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G93" t="n">
-        <v>1.70352482795715</v>
+        <v>1.70352494716644</v>
       </c>
       <c r="H93" t="n">
         <v>5250</v>
@@ -3095,7 +3095,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G94" t="n">
-        <v>1.69571042060852</v>
+        <v>1.69571053981781</v>
       </c>
       <c r="H94" t="n">
         <v>7592</v>
@@ -3153,7 +3153,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G96" t="n">
-        <v>1.64882433414459</v>
+        <v>1.64882445335388</v>
       </c>
       <c r="H96" t="n">
         <v>2615</v>
@@ -3269,7 +3269,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G100" t="n">
-        <v>2.08642721176147</v>
+        <v>2.08642745018005</v>
       </c>
       <c r="H100" t="n">
         <v>131201</v>
@@ -3443,7 +3443,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G106" t="n">
-        <v>1.82855415344238</v>
+        <v>1.8285539150238</v>
       </c>
       <c r="H106" t="n">
         <v>48556</v>
@@ -3472,7 +3472,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G107" t="n">
-        <v>1.74259650707245</v>
+        <v>1.74259638786316</v>
       </c>
       <c r="H107" t="n">
         <v>29505</v>
@@ -3646,7 +3646,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G113" t="n">
-        <v>1.69571042060852</v>
+        <v>1.69571053981781</v>
       </c>
       <c r="H113" t="n">
         <v>7676</v>
@@ -3675,7 +3675,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G114" t="n">
-        <v>1.64882433414459</v>
+        <v>1.64882445335388</v>
       </c>
       <c r="H114" t="n">
         <v>16400</v>
@@ -3704,7 +3704,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G115" t="n">
-        <v>1.58630979061127</v>
+        <v>1.58630967140198</v>
       </c>
       <c r="H115" t="n">
         <v>15973</v>
@@ -3733,7 +3733,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G116" t="n">
-        <v>1.60193848609924</v>
+        <v>1.60193836688995</v>
       </c>
       <c r="H116" t="n">
         <v>15987</v>
@@ -3762,7 +3762,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G117" t="n">
-        <v>1.57068109512329</v>
+        <v>1.57068121433258</v>
       </c>
       <c r="H117" t="n">
         <v>1475</v>
@@ -3791,7 +3791,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G118" t="n">
-        <v>1.54723823070526</v>
+        <v>1.54723811149597</v>
       </c>
       <c r="H118" t="n">
         <v>2966</v>
@@ -4168,7 +4168,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G131" t="n">
-        <v>1.57068109512329</v>
+        <v>1.57068121433258</v>
       </c>
       <c r="H131" t="n">
         <v>61460</v>
@@ -4197,7 +4197,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G132" t="n">
-        <v>1.32843685150146</v>
+        <v>1.32843673229218</v>
       </c>
       <c r="H132" t="n">
         <v>54470</v>
@@ -4313,7 +4313,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G136" t="n">
-        <v>1.41439437866211</v>
+        <v>1.4143944978714</v>
       </c>
       <c r="H136" t="n">
         <v>17202</v>
@@ -4342,7 +4342,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G137" t="n">
-        <v>1.42220878601074</v>
+        <v>1.42220890522003</v>
       </c>
       <c r="H137" t="n">
         <v>10331</v>
@@ -4371,7 +4371,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G138" t="n">
-        <v>1.41439437866211</v>
+        <v>1.4143944978714</v>
       </c>
       <c r="H138" t="n">
         <v>9467</v>
@@ -4400,7 +4400,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G139" t="n">
-        <v>1.46128058433533</v>
+        <v>1.46128046512604</v>
       </c>
       <c r="H139" t="n">
         <v>173037</v>
@@ -4429,7 +4429,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G140" t="n">
-        <v>1.41439437866211</v>
+        <v>1.4143944978714</v>
       </c>
       <c r="H140" t="n">
         <v>22023</v>
@@ -4458,7 +4458,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G141" t="n">
-        <v>1.47690904140472</v>
+        <v>1.47690916061401</v>
       </c>
       <c r="H141" t="n">
         <v>16351</v>
@@ -4516,7 +4516,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G143" t="n">
-        <v>1.42220878601074</v>
+        <v>1.42220890522003</v>
       </c>
       <c r="H143" t="n">
         <v>15680</v>
@@ -4574,7 +4574,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G145" t="n">
-        <v>1.4534660577774</v>
+        <v>1.45346617698669</v>
       </c>
       <c r="H145" t="n">
         <v>20080</v>
@@ -4806,7 +4806,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G153" t="n">
-        <v>1.42220878601074</v>
+        <v>1.42220890522003</v>
       </c>
       <c r="H153" t="n">
         <v>9667</v>
@@ -4864,7 +4864,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G155" t="n">
-        <v>1.50035214424133</v>
+        <v>1.50035226345062</v>
       </c>
       <c r="H155" t="n">
         <v>11333</v>
@@ -4893,7 +4893,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G156" t="n">
-        <v>1.49253785610199</v>
+        <v>1.49253797531128</v>
       </c>
       <c r="H156" t="n">
         <v>5721</v>
@@ -4922,7 +4922,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G157" t="n">
-        <v>1.50816655158997</v>
+        <v>1.50816643238068</v>
       </c>
       <c r="H157" t="n">
         <v>300</v>
@@ -4951,7 +4951,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G158" t="n">
-        <v>1.50035214424133</v>
+        <v>1.50035226345062</v>
       </c>
       <c r="H158" t="n">
         <v>230</v>
@@ -5009,7 +5009,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G160" t="n">
-        <v>1.46128058433533</v>
+        <v>1.46128046512604</v>
       </c>
       <c r="H160" t="n">
         <v>3965</v>
@@ -5038,7 +5038,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G161" t="n">
-        <v>1.47690904140472</v>
+        <v>1.47690916061401</v>
       </c>
       <c r="H161" t="n">
         <v>4796</v>
@@ -5067,7 +5067,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G162" t="n">
-        <v>1.46128058433533</v>
+        <v>1.46128046512604</v>
       </c>
       <c r="H162" t="n">
         <v>1540</v>
@@ -5154,7 +5154,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G165" t="n">
-        <v>1.4534660577774</v>
+        <v>1.45346617698669</v>
       </c>
       <c r="H165" t="n">
         <v>815</v>
@@ -5270,7 +5270,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G169" t="n">
-        <v>1.47690904140472</v>
+        <v>1.47690916061401</v>
       </c>
       <c r="H169" t="n">
         <v>12338</v>
@@ -5328,7 +5328,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G171" t="n">
-        <v>1.47690904140472</v>
+        <v>1.47690916061401</v>
       </c>
       <c r="H171" t="n">
         <v>7601</v>
@@ -5357,7 +5357,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G172" t="n">
-        <v>1.47690904140472</v>
+        <v>1.47690916061401</v>
       </c>
       <c r="H172" t="n">
         <v>2406</v>
@@ -5386,7 +5386,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G173" t="n">
-        <v>1.46128058433533</v>
+        <v>1.46128046512604</v>
       </c>
       <c r="H173" t="n">
         <v>902</v>
@@ -5415,7 +5415,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G174" t="n">
-        <v>1.54723823070526</v>
+        <v>1.54723811149597</v>
       </c>
       <c r="H174" t="n">
         <v>47810</v>
@@ -5444,7 +5444,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G175" t="n">
-        <v>1.49253785610199</v>
+        <v>1.49253797531128</v>
       </c>
       <c r="H175" t="n">
         <v>8883</v>
@@ -5473,7 +5473,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G176" t="n">
-        <v>1.46128058433533</v>
+        <v>1.46128046512604</v>
       </c>
       <c r="H176" t="n">
         <v>13742</v>
@@ -5531,7 +5531,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G178" t="n">
-        <v>1.49253785610199</v>
+        <v>1.49253797531128</v>
       </c>
       <c r="H178" t="n">
         <v>7365</v>
@@ -5647,7 +5647,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G182" t="n">
-        <v>1.47690904140472</v>
+        <v>1.47690916061401</v>
       </c>
       <c r="H182" t="n">
         <v>1510</v>
@@ -5676,7 +5676,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G183" t="n">
-        <v>1.41439437866211</v>
+        <v>1.4143944978714</v>
       </c>
       <c r="H183" t="n">
         <v>13615</v>
@@ -5705,7 +5705,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G184" t="n">
-        <v>1.4534660577774</v>
+        <v>1.45346617698669</v>
       </c>
       <c r="H184" t="n">
         <v>3021</v>
@@ -5792,7 +5792,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G187" t="n">
-        <v>1.60975289344788</v>
+        <v>1.6097526550293</v>
       </c>
       <c r="H187" t="n">
         <v>206627</v>
@@ -5850,7 +5850,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G189" t="n">
-        <v>1.62538135051727</v>
+        <v>1.62538146972656</v>
       </c>
       <c r="H189" t="n">
         <v>39826</v>
@@ -6227,7 +6227,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G202" t="n">
-        <v>1.47690904140472</v>
+        <v>1.47690916061401</v>
       </c>
       <c r="H202" t="n">
         <v>7610</v>
@@ -6285,7 +6285,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G204" t="n">
-        <v>1.53160965442657</v>
+        <v>1.531609416008</v>
       </c>
       <c r="H204" t="n">
         <v>8646</v>
@@ -6314,7 +6314,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G205" t="n">
-        <v>1.50816655158997</v>
+        <v>1.50816643238068</v>
       </c>
       <c r="H205" t="n">
         <v>23070</v>
@@ -6401,7 +6401,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G208" t="n">
-        <v>1.54723823070526</v>
+        <v>1.54723811149597</v>
       </c>
       <c r="H208" t="n">
         <v>30696</v>
@@ -6430,7 +6430,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G209" t="n">
-        <v>1.54723823070526</v>
+        <v>1.54723811149597</v>
       </c>
       <c r="H209" t="n">
         <v>5243</v>
@@ -6488,7 +6488,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G211" t="n">
-        <v>1.53942394256592</v>
+        <v>1.53942382335663</v>
       </c>
       <c r="H211" t="n">
         <v>2400</v>
@@ -6517,7 +6517,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G212" t="n">
-        <v>1.54723823070526</v>
+        <v>1.54723811149597</v>
       </c>
       <c r="H212" t="n">
         <v>600</v>
@@ -6546,7 +6546,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G213" t="n">
-        <v>1.55505263805389</v>
+        <v>1.5550525188446</v>
       </c>
       <c r="H213" t="n">
         <v>7649</v>
@@ -6575,7 +6575,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G214" t="n">
-        <v>1.57068109512329</v>
+        <v>1.57068121433258</v>
       </c>
       <c r="H214" t="n">
         <v>101975</v>
@@ -6633,7 +6633,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G216" t="n">
-        <v>1.50816655158997</v>
+        <v>1.50816643238068</v>
       </c>
       <c r="H216" t="n">
         <v>15002</v>
@@ -6720,7 +6720,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G219" t="n">
-        <v>1.53160965442657</v>
+        <v>1.531609416008</v>
       </c>
       <c r="H219" t="n">
         <v>16116</v>
@@ -6807,7 +6807,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G222" t="n">
-        <v>1.61756706237793</v>
+        <v>1.61756694316864</v>
       </c>
       <c r="H222" t="n">
         <v>33429</v>
@@ -6865,7 +6865,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G224" t="n">
-        <v>1.55505263805389</v>
+        <v>1.5550525188446</v>
       </c>
       <c r="H224" t="n">
         <v>22722</v>
@@ -6894,7 +6894,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G225" t="n">
-        <v>1.58630979061127</v>
+        <v>1.58630967140198</v>
       </c>
       <c r="H225" t="n">
         <v>24397</v>
@@ -6952,7 +6952,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G227" t="n">
-        <v>1.53942394256592</v>
+        <v>1.53942382335663</v>
       </c>
       <c r="H227" t="n">
         <v>13085</v>
@@ -6981,7 +6981,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G228" t="n">
-        <v>1.53942394256592</v>
+        <v>1.53942382335663</v>
       </c>
       <c r="H228" t="n">
         <v>7625</v>
@@ -7039,7 +7039,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G230" t="n">
-        <v>1.49253785610199</v>
+        <v>1.49253797531128</v>
       </c>
       <c r="H230" t="n">
         <v>3975</v>
@@ -7155,7 +7155,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G234" t="n">
-        <v>1.41439437866211</v>
+        <v>1.4143944978714</v>
       </c>
       <c r="H234" t="n">
         <v>15984</v>
@@ -7213,7 +7213,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G236" t="n">
-        <v>1.46128058433533</v>
+        <v>1.46128046512604</v>
       </c>
       <c r="H236" t="n">
         <v>2358</v>
@@ -7242,7 +7242,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G237" t="n">
-        <v>1.47690904140472</v>
+        <v>1.47690916061401</v>
       </c>
       <c r="H237" t="n">
         <v>3415</v>
@@ -7416,7 +7416,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G243" t="n">
-        <v>1.50035214424133</v>
+        <v>1.50035226345062</v>
       </c>
       <c r="H243" t="n">
         <v>2774</v>
@@ -7445,7 +7445,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G244" t="n">
-        <v>1.50035214424133</v>
+        <v>1.50035226345062</v>
       </c>
       <c r="H244" t="n">
         <v>2142</v>
@@ -7474,7 +7474,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G245" t="n">
-        <v>1.49253785610199</v>
+        <v>1.49253797531128</v>
       </c>
       <c r="H245" t="n">
         <v>6756</v>
@@ -7503,7 +7503,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G246" t="n">
-        <v>1.50035214424133</v>
+        <v>1.50035226345062</v>
       </c>
       <c r="H246" t="n">
         <v>6837</v>
@@ -7532,7 +7532,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G247" t="n">
-        <v>1.50035214424133</v>
+        <v>1.50035226345062</v>
       </c>
       <c r="H247" t="n">
         <v>9596</v>
@@ -7561,7 +7561,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G248" t="n">
-        <v>1.50035214424133</v>
+        <v>1.50035226345062</v>
       </c>
       <c r="H248" t="n">
         <v>3796</v>
@@ -7619,7 +7619,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G250" t="n">
-        <v>1.50035214424133</v>
+        <v>1.50035226345062</v>
       </c>
       <c r="H250" t="n">
         <v>16130</v>
@@ -7648,7 +7648,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G251" t="n">
-        <v>1.50816655158997</v>
+        <v>1.50816643238068</v>
       </c>
       <c r="H251" t="n">
         <v>4699</v>
@@ -7677,7 +7677,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G252" t="n">
-        <v>1.49253785610199</v>
+        <v>1.49253797531128</v>
       </c>
       <c r="H252" t="n">
         <v>8020</v>
@@ -7706,7 +7706,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G253" t="n">
-        <v>1.47690904140472</v>
+        <v>1.47690916061401</v>
       </c>
       <c r="H253" t="n">
         <v>5630</v>
@@ -7735,7 +7735,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G254" t="n">
-        <v>1.50035214424133</v>
+        <v>1.50035226345062</v>
       </c>
       <c r="H254" t="n">
         <v>10860</v>
@@ -7764,7 +7764,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G255" t="n">
-        <v>1.49253785610199</v>
+        <v>1.49253797531128</v>
       </c>
       <c r="H255" t="n">
         <v>45713</v>
@@ -7793,7 +7793,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G256" t="n">
-        <v>1.53942394256592</v>
+        <v>1.53942382335663</v>
       </c>
       <c r="H256" t="n">
         <v>12280</v>
@@ -7822,7 +7822,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G257" t="n">
-        <v>1.54723823070526</v>
+        <v>1.54723811149597</v>
       </c>
       <c r="H257" t="n">
         <v>41048</v>
@@ -7851,7 +7851,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G258" t="n">
-        <v>1.83636856079102</v>
+        <v>1.83636832237244</v>
       </c>
       <c r="H258" t="n">
         <v>125566</v>
@@ -7880,7 +7880,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G259" t="n">
-        <v>1.77385377883911</v>
+        <v>1.7738538980484</v>
       </c>
       <c r="H259" t="n">
         <v>144770</v>
@@ -7909,7 +7909,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G260" t="n">
-        <v>1.76603937149048</v>
+        <v>1.76603960990906</v>
       </c>
       <c r="H260" t="n">
         <v>45306</v>
@@ -7938,7 +7938,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G261" t="n">
-        <v>1.7347823381424</v>
+        <v>1.73478221893311</v>
       </c>
       <c r="H261" t="n">
         <v>35690</v>
@@ -7967,7 +7967,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G262" t="n">
-        <v>1.72696793079376</v>
+        <v>1.72696805000305</v>
       </c>
       <c r="H262" t="n">
         <v>17933</v>
@@ -8025,7 +8025,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G264" t="n">
-        <v>1.64882433414459</v>
+        <v>1.64882445335388</v>
       </c>
       <c r="H264" t="n">
         <v>11388</v>
@@ -8054,7 +8054,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G265" t="n">
-        <v>1.63319575786591</v>
+        <v>1.6331958770752</v>
       </c>
       <c r="H265" t="n">
         <v>33628</v>
@@ -8083,7 +8083,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G266" t="n">
-        <v>1.60193848609924</v>
+        <v>1.60193836688995</v>
       </c>
       <c r="H266" t="n">
         <v>12204</v>
@@ -8228,7 +8228,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G271" t="n">
-        <v>1.79729664325714</v>
+        <v>1.79729688167572</v>
       </c>
       <c r="H271" t="n">
         <v>110444</v>
@@ -8315,7 +8315,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G274" t="n">
-        <v>2.78190279006958</v>
+        <v>2.78190302848816</v>
       </c>
       <c r="H274" t="n">
         <v>248750</v>
@@ -8750,7 +8750,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G289" t="n">
-        <v>2.50840139389038</v>
+        <v>2.5084011554718</v>
       </c>
       <c r="H289" t="n">
         <v>75755</v>
@@ -8837,7 +8837,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G292" t="n">
-        <v>2.3521146774292</v>
+        <v>2.35211443901062</v>
       </c>
       <c r="H292" t="n">
         <v>52504</v>
@@ -8924,7 +8924,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G295" t="n">
-        <v>2.2114565372467</v>
+        <v>2.21145629882812</v>
       </c>
       <c r="H295" t="n">
         <v>127250</v>
@@ -8953,7 +8953,7 @@
         <v>2.75</v>
       </c>
       <c r="G296" t="n">
-        <v>2.1489417552948</v>
+        <v>2.14894199371338</v>
       </c>
       <c r="H296" t="n">
         <v>145249</v>
@@ -8982,7 +8982,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G297" t="n">
-        <v>2.07861256599426</v>
+        <v>2.07861304283142</v>
       </c>
       <c r="H297" t="n">
         <v>57099</v>
@@ -9040,7 +9040,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G299" t="n">
-        <v>2.18801331520081</v>
+        <v>2.18801355361938</v>
       </c>
       <c r="H299" t="n">
         <v>145545</v>
@@ -9098,7 +9098,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G301" t="n">
-        <v>2.11768460273743</v>
+        <v>2.11768484115601</v>
       </c>
       <c r="H301" t="n">
         <v>31779</v>
@@ -9185,7 +9185,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G304" t="n">
-        <v>2.08642721176147</v>
+        <v>2.08642745018005</v>
       </c>
       <c r="H304" t="n">
         <v>19530</v>
@@ -9214,7 +9214,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G305" t="n">
-        <v>2.08642721176147</v>
+        <v>2.08642745018005</v>
       </c>
       <c r="H305" t="n">
         <v>13542</v>
@@ -9243,7 +9243,7 @@
         <v>2.75</v>
       </c>
       <c r="G306" t="n">
-        <v>2.1489417552948</v>
+        <v>2.14894199371338</v>
       </c>
       <c r="H306" t="n">
         <v>29862</v>
@@ -9272,7 +9272,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G307" t="n">
-        <v>2.11768460273743</v>
+        <v>2.11768484115601</v>
       </c>
       <c r="H307" t="n">
         <v>94727</v>
@@ -9301,7 +9301,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G308" t="n">
-        <v>2.18801331520081</v>
+        <v>2.18801355361938</v>
       </c>
       <c r="H308" t="n">
         <v>36108</v>
@@ -9359,7 +9359,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G310" t="n">
-        <v>2.11768460273743</v>
+        <v>2.11768484115601</v>
       </c>
       <c r="H310" t="n">
         <v>7325</v>
@@ -9388,7 +9388,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G311" t="n">
-        <v>2.13331317901611</v>
+        <v>2.13331341743469</v>
       </c>
       <c r="H311" t="n">
         <v>20423</v>
@@ -9417,7 +9417,7 @@
         <v>2.75</v>
       </c>
       <c r="G312" t="n">
-        <v>2.1489417552948</v>
+        <v>2.14894199371338</v>
       </c>
       <c r="H312" t="n">
         <v>12417</v>
@@ -9446,7 +9446,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G313" t="n">
-        <v>2.14112758636475</v>
+        <v>2.14112782478333</v>
       </c>
       <c r="H313" t="n">
         <v>5822</v>
@@ -9475,7 +9475,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G314" t="n">
-        <v>2.19582772254944</v>
+        <v>2.19582796096802</v>
       </c>
       <c r="H314" t="n">
         <v>90558</v>
@@ -9504,7 +9504,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G315" t="n">
-        <v>2.2114565372467</v>
+        <v>2.21145629882812</v>
       </c>
       <c r="H315" t="n">
         <v>24918</v>
@@ -9591,7 +9591,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G318" t="n">
-        <v>2.65687370300293</v>
+        <v>2.65687346458435</v>
       </c>
       <c r="H318" t="n">
         <v>288982</v>
@@ -9649,7 +9649,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G320" t="n">
-        <v>2.3521146774292</v>
+        <v>2.35211443901062</v>
       </c>
       <c r="H320" t="n">
         <v>104790</v>
@@ -9823,7 +9823,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G326" t="n">
-        <v>2.32867169380188</v>
+        <v>2.3286714553833</v>
       </c>
       <c r="H326" t="n">
         <v>34122</v>
@@ -9881,7 +9881,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G328" t="n">
-        <v>2.27397108078003</v>
+        <v>2.27397131919861</v>
       </c>
       <c r="H328" t="n">
         <v>24472</v>
@@ -9910,7 +9910,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G329" t="n">
-        <v>2.27397108078003</v>
+        <v>2.27397131919861</v>
       </c>
       <c r="H329" t="n">
         <v>19303</v>
@@ -9968,7 +9968,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G331" t="n">
-        <v>2.27397108078003</v>
+        <v>2.27397131919861</v>
       </c>
       <c r="H331" t="n">
         <v>11915</v>
@@ -9997,7 +9997,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G332" t="n">
-        <v>2.19582772254944</v>
+        <v>2.19582796096802</v>
       </c>
       <c r="H332" t="n">
         <v>23745</v>
@@ -10200,7 +10200,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G339" t="n">
-        <v>2.32867169380188</v>
+        <v>2.3286714553833</v>
       </c>
       <c r="H339" t="n">
         <v>58353</v>
@@ -10345,7 +10345,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G344" t="n">
-        <v>2.50840139389038</v>
+        <v>2.5084011554718</v>
       </c>
       <c r="H344" t="n">
         <v>306118</v>
@@ -10374,7 +10374,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G345" t="n">
-        <v>2.40681505203247</v>
+        <v>2.40681481361389</v>
       </c>
       <c r="H345" t="n">
         <v>126337</v>
@@ -10461,7 +10461,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G348" t="n">
-        <v>2.3521146774292</v>
+        <v>2.35211443901062</v>
       </c>
       <c r="H348" t="n">
         <v>139966</v>
@@ -10490,7 +10490,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G349" t="n">
-        <v>2.28959965705872</v>
+        <v>2.28959989547729</v>
       </c>
       <c r="H349" t="n">
         <v>69457</v>
@@ -10519,7 +10519,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G350" t="n">
-        <v>2.33648610115051</v>
+        <v>2.33648586273193</v>
       </c>
       <c r="H350" t="n">
         <v>30279</v>
@@ -10635,7 +10635,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G354" t="n">
-        <v>2.27397108078003</v>
+        <v>2.27397131919861</v>
       </c>
       <c r="H354" t="n">
         <v>5260</v>
@@ -10722,7 +10722,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G357" t="n">
-        <v>2.32867169380188</v>
+        <v>2.3286714553833</v>
       </c>
       <c r="H357" t="n">
         <v>14916</v>
@@ -10925,7 +10925,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G364" t="n">
-        <v>2.28959965705872</v>
+        <v>2.28959989547729</v>
       </c>
       <c r="H364" t="n">
         <v>9629</v>
@@ -10954,7 +10954,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G365" t="n">
-        <v>2.19582772254944</v>
+        <v>2.19582796096802</v>
       </c>
       <c r="H365" t="n">
         <v>66685</v>
@@ -10983,7 +10983,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G366" t="n">
-        <v>2.19582772254944</v>
+        <v>2.19582796096802</v>
       </c>
       <c r="H366" t="n">
         <v>21330</v>
@@ -11012,7 +11012,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G367" t="n">
-        <v>2.22708511352539</v>
+        <v>2.22708487510681</v>
       </c>
       <c r="H367" t="n">
         <v>8955</v>
@@ -11041,7 +11041,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G368" t="n">
-        <v>2.22708511352539</v>
+        <v>2.22708487510681</v>
       </c>
       <c r="H368" t="n">
         <v>5899</v>
@@ -11070,7 +11070,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G369" t="n">
-        <v>2.19582772254944</v>
+        <v>2.19582796096802</v>
       </c>
       <c r="H369" t="n">
         <v>25375</v>
@@ -11099,7 +11099,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G370" t="n">
-        <v>2.19582772254944</v>
+        <v>2.19582796096802</v>
       </c>
       <c r="H370" t="n">
         <v>2922</v>
@@ -11157,7 +11157,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G372" t="n">
-        <v>2.22708511352539</v>
+        <v>2.22708487510681</v>
       </c>
       <c r="H372" t="n">
         <v>12004</v>
@@ -11215,7 +11215,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G374" t="n">
-        <v>2.2114565372467</v>
+        <v>2.21145629882812</v>
       </c>
       <c r="H374" t="n">
         <v>1201</v>
@@ -11273,7 +11273,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G376" t="n">
-        <v>2.18801331520081</v>
+        <v>2.18801355361938</v>
       </c>
       <c r="H376" t="n">
         <v>4715</v>
@@ -11302,7 +11302,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G377" t="n">
-        <v>2.22708511352539</v>
+        <v>2.22708487510681</v>
       </c>
       <c r="H377" t="n">
         <v>4658</v>
@@ -11360,7 +11360,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G379" t="n">
-        <v>2.22708511352539</v>
+        <v>2.22708487510681</v>
       </c>
       <c r="H379" t="n">
         <v>7003</v>
@@ -11447,7 +11447,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G382" t="n">
-        <v>2.2114565372467</v>
+        <v>2.21145629882812</v>
       </c>
       <c r="H382" t="n">
         <v>7415</v>
@@ -11621,7 +11621,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G388" t="n">
-        <v>2.22708511352539</v>
+        <v>2.22708487510681</v>
       </c>
       <c r="H388" t="n">
         <v>100</v>
@@ -11679,7 +11679,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G390" t="n">
-        <v>2.19582772254944</v>
+        <v>2.19582796096802</v>
       </c>
       <c r="H390" t="n">
         <v>6870</v>
@@ -11737,7 +11737,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G392" t="n">
-        <v>2.22708511352539</v>
+        <v>2.22708487510681</v>
       </c>
       <c r="H392" t="n">
         <v>4464</v>
@@ -11766,7 +11766,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G393" t="n">
-        <v>2.28959965705872</v>
+        <v>2.28959989547729</v>
       </c>
       <c r="H393" t="n">
         <v>490568</v>
@@ -11795,7 +11795,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G394" t="n">
-        <v>2.25052833557129</v>
+        <v>2.25052809715271</v>
       </c>
       <c r="H394" t="n">
         <v>49928</v>
@@ -11853,7 +11853,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G396" t="n">
-        <v>2.22708511352539</v>
+        <v>2.22708487510681</v>
       </c>
       <c r="H396" t="n">
         <v>21203</v>
@@ -11882,7 +11882,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G397" t="n">
-        <v>2.2114565372467</v>
+        <v>2.21145629882812</v>
       </c>
       <c r="H397" t="n">
         <v>14364</v>
@@ -11969,7 +11969,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G400" t="n">
-        <v>2.25052833557129</v>
+        <v>2.25052809715271</v>
       </c>
       <c r="H400" t="n">
         <v>125043</v>
@@ -11998,7 +11998,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G401" t="n">
-        <v>2.27397108078003</v>
+        <v>2.27397131919861</v>
       </c>
       <c r="H401" t="n">
         <v>8887</v>
@@ -12056,7 +12056,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G403" t="n">
-        <v>2.28959965705872</v>
+        <v>2.28959989547729</v>
       </c>
       <c r="H403" t="n">
         <v>3440</v>
@@ -12201,7 +12201,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G408" t="n">
-        <v>2.28959965705872</v>
+        <v>2.28959989547729</v>
       </c>
       <c r="H408" t="n">
         <v>16796</v>
@@ -12230,7 +12230,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G409" t="n">
-        <v>2.25052833557129</v>
+        <v>2.25052809715271</v>
       </c>
       <c r="H409" t="n">
         <v>3826</v>
@@ -12259,7 +12259,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G410" t="n">
-        <v>2.27397108078003</v>
+        <v>2.27397131919861</v>
       </c>
       <c r="H410" t="n">
         <v>12237</v>
@@ -12317,7 +12317,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G412" t="n">
-        <v>2.25052833557129</v>
+        <v>2.25052809715271</v>
       </c>
       <c r="H412" t="n">
         <v>13597</v>
@@ -12375,7 +12375,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G414" t="n">
-        <v>2.22708511352539</v>
+        <v>2.22708487510681</v>
       </c>
       <c r="H414" t="n">
         <v>16306</v>
@@ -12404,7 +12404,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G415" t="n">
-        <v>2.22708511352539</v>
+        <v>2.22708487510681</v>
       </c>
       <c r="H415" t="n">
         <v>4789</v>
@@ -12433,7 +12433,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G416" t="n">
-        <v>2.25052833557129</v>
+        <v>2.25052809715271</v>
       </c>
       <c r="H416" t="n">
         <v>4039</v>
@@ -12491,7 +12491,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G418" t="n">
-        <v>2.27397108078003</v>
+        <v>2.27397131919861</v>
       </c>
       <c r="H418" t="n">
         <v>7095</v>
@@ -12520,7 +12520,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G419" t="n">
-        <v>2.25052833557129</v>
+        <v>2.25052809715271</v>
       </c>
       <c r="H419" t="n">
         <v>6100</v>
@@ -12578,7 +12578,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G421" t="n">
-        <v>2.25052833557129</v>
+        <v>2.25052809715271</v>
       </c>
       <c r="H421" t="n">
         <v>5308</v>
@@ -12607,7 +12607,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G422" t="n">
-        <v>2.25052833557129</v>
+        <v>2.25052809715271</v>
       </c>
       <c r="H422" t="n">
         <v>13271</v>
@@ -12723,7 +12723,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G426" t="n">
-        <v>2.28959965705872</v>
+        <v>2.28959989547729</v>
       </c>
       <c r="H426" t="n">
         <v>16488</v>
@@ -12752,7 +12752,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G427" t="n">
-        <v>2.28959965705872</v>
+        <v>2.28959989547729</v>
       </c>
       <c r="H427" t="n">
         <v>33109</v>
@@ -12810,7 +12810,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G429" t="n">
-        <v>2.27397108078003</v>
+        <v>2.27397131919861</v>
       </c>
       <c r="H429" t="n">
         <v>3175</v>
@@ -12868,7 +12868,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G431" t="n">
-        <v>2.27397108078003</v>
+        <v>2.27397131919861</v>
       </c>
       <c r="H431" t="n">
         <v>5595</v>
@@ -12897,7 +12897,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G432" t="n">
-        <v>2.28959965705872</v>
+        <v>2.28959989547729</v>
       </c>
       <c r="H432" t="n">
         <v>7635</v>
@@ -12926,7 +12926,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G433" t="n">
-        <v>2.28959965705872</v>
+        <v>2.28959989547729</v>
       </c>
       <c r="H433" t="n">
         <v>12703</v>
@@ -12984,7 +12984,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G435" t="n">
-        <v>2.28959965705872</v>
+        <v>2.28959989547729</v>
       </c>
       <c r="H435" t="n">
         <v>6499</v>
@@ -13042,7 +13042,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G437" t="n">
-        <v>2.27397108078003</v>
+        <v>2.27397131919861</v>
       </c>
       <c r="H437" t="n">
         <v>4699</v>
@@ -13187,7 +13187,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G442" t="n">
-        <v>2.33648610115051</v>
+        <v>2.33648586273193</v>
       </c>
       <c r="H442" t="n">
         <v>35567</v>
@@ -13303,7 +13303,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G446" t="n">
-        <v>2.32867169380188</v>
+        <v>2.3286714553833</v>
       </c>
       <c r="H446" t="n">
         <v>38929</v>
@@ -13332,7 +13332,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G447" t="n">
-        <v>2.28959965705872</v>
+        <v>2.28959989547729</v>
       </c>
       <c r="H447" t="n">
         <v>18719</v>
@@ -13419,7 +13419,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G450" t="n">
-        <v>2.28959965705872</v>
+        <v>2.28959989547729</v>
       </c>
       <c r="H450" t="n">
         <v>5156</v>
@@ -13477,7 +13477,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G452" t="n">
-        <v>2.27397108078003</v>
+        <v>2.27397131919861</v>
       </c>
       <c r="H452" t="n">
         <v>4236</v>
@@ -13564,7 +13564,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G455" t="n">
-        <v>2.25052833557129</v>
+        <v>2.25052809715271</v>
       </c>
       <c r="H455" t="n">
         <v>4720</v>
@@ -13593,7 +13593,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G456" t="n">
-        <v>2.27397108078003</v>
+        <v>2.27397131919861</v>
       </c>
       <c r="H456" t="n">
         <v>23276</v>
@@ -13680,7 +13680,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G459" t="n">
-        <v>2.27397108078003</v>
+        <v>2.27397131919861</v>
       </c>
       <c r="H459" t="n">
         <v>4372</v>
@@ -13738,7 +13738,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G461" t="n">
-        <v>2.27397108078003</v>
+        <v>2.27397131919861</v>
       </c>
       <c r="H461" t="n">
         <v>2391</v>
@@ -13796,7 +13796,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G463" t="n">
-        <v>2.27397108078003</v>
+        <v>2.27397131919861</v>
       </c>
       <c r="H463" t="n">
         <v>891</v>
@@ -13854,7 +13854,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G465" t="n">
-        <v>2.25052833557129</v>
+        <v>2.25052809715271</v>
       </c>
       <c r="H465" t="n">
         <v>7854</v>
@@ -13912,7 +13912,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G467" t="n">
-        <v>2.25052833557129</v>
+        <v>2.25052809715271</v>
       </c>
       <c r="H467" t="n">
         <v>6429</v>
@@ -13999,7 +13999,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G470" t="n">
-        <v>2.25052833557129</v>
+        <v>2.25052809715271</v>
       </c>
       <c r="H470" t="n">
         <v>4682</v>
@@ -14231,7 +14231,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G478" t="n">
-        <v>2.25052833557129</v>
+        <v>2.25052809715271</v>
       </c>
       <c r="H478" t="n">
         <v>13054</v>
@@ -14289,7 +14289,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G480" t="n">
-        <v>2.18801331520081</v>
+        <v>2.18801355361938</v>
       </c>
       <c r="H480" t="n">
         <v>127127</v>
@@ -14318,7 +14318,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G481" t="n">
-        <v>2.11768460273743</v>
+        <v>2.11768484115601</v>
       </c>
       <c r="H481" t="n">
         <v>18942</v>
@@ -14405,7 +14405,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G484" t="n">
-        <v>2.06298422813416</v>
+        <v>2.06298446655273</v>
       </c>
       <c r="H484" t="n">
         <v>4500</v>
@@ -14463,7 +14463,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G486" t="n">
-        <v>2.07079863548279</v>
+        <v>2.07079887390137</v>
       </c>
       <c r="H486" t="n">
         <v>9534</v>
@@ -14521,7 +14521,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G488" t="n">
-        <v>2.09424138069153</v>
+        <v>2.09424161911011</v>
       </c>
       <c r="H488" t="n">
         <v>6344</v>
@@ -14637,7 +14637,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G492" t="n">
-        <v>1.99265503883362</v>
+        <v>1.99265539646149</v>
       </c>
       <c r="H492" t="n">
         <v>39507</v>
@@ -14782,7 +14782,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G497" t="n">
-        <v>1.99265503883362</v>
+        <v>1.99265539646149</v>
       </c>
       <c r="H497" t="n">
         <v>2512</v>
@@ -14985,7 +14985,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G504" t="n">
-        <v>1.99265503883362</v>
+        <v>1.99265539646149</v>
       </c>
       <c r="H504" t="n">
         <v>3080</v>
@@ -15391,7 +15391,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G518" t="n">
-        <v>2.09424138069153</v>
+        <v>2.09424161911011</v>
       </c>
       <c r="H518" t="n">
         <v>112388</v>
@@ -15420,7 +15420,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G519" t="n">
-        <v>2.08642721176147</v>
+        <v>2.08642745018005</v>
       </c>
       <c r="H519" t="n">
         <v>11274</v>
@@ -15449,7 +15449,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G520" t="n">
-        <v>2.07861256599426</v>
+        <v>2.07861304283142</v>
       </c>
       <c r="H520" t="n">
         <v>10226</v>
@@ -15478,7 +15478,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G521" t="n">
-        <v>2.06298422813416</v>
+        <v>2.06298446655273</v>
       </c>
       <c r="H521" t="n">
         <v>14270</v>
@@ -15536,7 +15536,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G523" t="n">
-        <v>2.08642721176147</v>
+        <v>2.08642745018005</v>
       </c>
       <c r="H523" t="n">
         <v>9758</v>
@@ -15739,7 +15739,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G530" t="n">
-        <v>2.08642721176147</v>
+        <v>2.08642745018005</v>
       </c>
       <c r="H530" t="n">
         <v>11459</v>
@@ -15768,7 +15768,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G531" t="n">
-        <v>2.07861256599426</v>
+        <v>2.07861304283142</v>
       </c>
       <c r="H531" t="n">
         <v>7675</v>
@@ -16000,7 +16000,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G539" t="n">
-        <v>1.98484098911285</v>
+        <v>1.98484075069427</v>
       </c>
       <c r="H539" t="n">
         <v>4051</v>
@@ -16029,7 +16029,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G540" t="n">
-        <v>1.97702634334564</v>
+        <v>1.97702646255493</v>
       </c>
       <c r="H540" t="n">
         <v>1849</v>
@@ -16058,7 +16058,7 @@
         <v>2.5</v>
       </c>
       <c r="G541" t="n">
-        <v>1.95358347892761</v>
+        <v>1.95358335971832</v>
       </c>
       <c r="H541" t="n">
         <v>1628</v>
@@ -16116,7 +16116,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G543" t="n">
-        <v>1.92232620716095</v>
+        <v>1.92232608795166</v>
       </c>
       <c r="H543" t="n">
         <v>2000</v>
@@ -16174,7 +16174,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G545" t="n">
-        <v>1.98484098911285</v>
+        <v>1.98484075069427</v>
       </c>
       <c r="H545" t="n">
         <v>7157</v>
@@ -16203,7 +16203,7 @@
         <v>2.5</v>
       </c>
       <c r="G546" t="n">
-        <v>1.95358347892761</v>
+        <v>1.95358335971832</v>
       </c>
       <c r="H546" t="n">
         <v>13540</v>
@@ -16435,7 +16435,7 @@
         <v>2.5</v>
       </c>
       <c r="G554" t="n">
-        <v>1.95358347892761</v>
+        <v>1.95358335971832</v>
       </c>
       <c r="H554" t="n">
         <v>801</v>
@@ -16464,7 +16464,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G555" t="n">
-        <v>1.8754403591156</v>
+        <v>1.87544012069702</v>
       </c>
       <c r="H555" t="n">
         <v>11021</v>
@@ -16493,7 +16493,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G556" t="n">
-        <v>1.86762583255768</v>
+        <v>1.86762571334839</v>
       </c>
       <c r="H556" t="n">
         <v>3914</v>
@@ -16522,7 +16522,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G557" t="n">
-        <v>1.8754403591156</v>
+        <v>1.87544012069702</v>
       </c>
       <c r="H557" t="n">
         <v>9292</v>
@@ -16580,7 +16580,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G559" t="n">
-        <v>1.8754403591156</v>
+        <v>1.87544012069702</v>
       </c>
       <c r="H559" t="n">
         <v>2957</v>
@@ -16609,7 +16609,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G560" t="n">
-        <v>1.89888334274292</v>
+        <v>1.89888298511505</v>
       </c>
       <c r="H560" t="n">
         <v>4094</v>
@@ -16638,7 +16638,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G561" t="n">
-        <v>1.89888334274292</v>
+        <v>1.89888298511505</v>
       </c>
       <c r="H561" t="n">
         <v>2899</v>
@@ -16696,7 +16696,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G563" t="n">
-        <v>1.90669775009155</v>
+        <v>1.90669739246368</v>
       </c>
       <c r="H563" t="n">
         <v>3670</v>
@@ -16725,7 +16725,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G564" t="n">
-        <v>1.90669775009155</v>
+        <v>1.90669739246368</v>
       </c>
       <c r="H564" t="n">
         <v>290</v>
@@ -16754,7 +16754,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G565" t="n">
-        <v>1.9145120382309</v>
+        <v>1.91451179981232</v>
       </c>
       <c r="H565" t="n">
         <v>930</v>
@@ -16783,7 +16783,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G566" t="n">
-        <v>1.8754403591156</v>
+        <v>1.87544012069702</v>
       </c>
       <c r="H566" t="n">
         <v>3211</v>
@@ -16812,7 +16812,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G567" t="n">
-        <v>1.8754403591156</v>
+        <v>1.87544012069702</v>
       </c>
       <c r="H567" t="n">
         <v>2215</v>
@@ -16841,7 +16841,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G568" t="n">
-        <v>1.86762583255768</v>
+        <v>1.86762571334839</v>
       </c>
       <c r="H568" t="n">
         <v>5620</v>
@@ -16870,7 +16870,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G569" t="n">
-        <v>1.84418284893036</v>
+        <v>1.84418261051178</v>
       </c>
       <c r="H569" t="n">
         <v>2584</v>
@@ -16899,7 +16899,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G570" t="n">
-        <v>1.92232620716095</v>
+        <v>1.92232608795166</v>
       </c>
       <c r="H570" t="n">
         <v>34637</v>
@@ -17102,7 +17102,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G577" t="n">
-        <v>2.06298422813416</v>
+        <v>2.06298446655273</v>
       </c>
       <c r="H577" t="n">
         <v>25388</v>
@@ -17247,7 +17247,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G582" t="n">
-        <v>1.98484098911285</v>
+        <v>1.98484075069427</v>
       </c>
       <c r="H582" t="n">
         <v>5772</v>
@@ -17276,7 +17276,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G583" t="n">
-        <v>1.98484098911285</v>
+        <v>1.98484075069427</v>
       </c>
       <c r="H583" t="n">
         <v>817</v>
@@ -17334,7 +17334,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G585" t="n">
-        <v>1.97702634334564</v>
+        <v>1.97702646255493</v>
       </c>
       <c r="H585" t="n">
         <v>2222</v>
@@ -17450,7 +17450,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G589" t="n">
-        <v>1.97702634334564</v>
+        <v>1.97702646255493</v>
       </c>
       <c r="H589" t="n">
         <v>1767</v>
@@ -17479,7 +17479,7 @@
         <v>2.5</v>
       </c>
       <c r="G590" t="n">
-        <v>1.95358347892761</v>
+        <v>1.95358335971832</v>
       </c>
       <c r="H590" t="n">
         <v>6559</v>
@@ -17566,7 +17566,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G593" t="n">
-        <v>1.89888334274292</v>
+        <v>1.89888298511505</v>
       </c>
       <c r="H593" t="n">
         <v>219</v>
@@ -17624,7 +17624,7 @@
         <v>2.5</v>
       </c>
       <c r="G595" t="n">
-        <v>1.95358347892761</v>
+        <v>1.95358335971832</v>
       </c>
       <c r="H595" t="n">
         <v>2570</v>
@@ -17653,7 +17653,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G596" t="n">
-        <v>1.93014061450958</v>
+        <v>1.93014049530029</v>
       </c>
       <c r="H596" t="n">
         <v>321</v>
@@ -17682,7 +17682,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G597" t="n">
-        <v>1.93014061450958</v>
+        <v>1.93014049530029</v>
       </c>
       <c r="H597" t="n">
         <v>1300</v>
@@ -17740,7 +17740,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G599" t="n">
-        <v>1.9145120382309</v>
+        <v>1.91451179981232</v>
       </c>
       <c r="H599" t="n">
         <v>16585</v>
@@ -17769,7 +17769,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G600" t="n">
-        <v>1.94576930999756</v>
+        <v>1.94576907157898</v>
       </c>
       <c r="H600" t="n">
         <v>1103</v>
@@ -17798,7 +17798,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G601" t="n">
-        <v>1.94576930999756</v>
+        <v>1.94576907157898</v>
       </c>
       <c r="H601" t="n">
         <v>200</v>
@@ -17856,7 +17856,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G603" t="n">
-        <v>1.94576930999756</v>
+        <v>1.94576907157898</v>
       </c>
       <c r="H603" t="n">
         <v>7397</v>
@@ -17943,7 +17943,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G606" t="n">
-        <v>1.8754403591156</v>
+        <v>1.87544012069702</v>
       </c>
       <c r="H606" t="n">
         <v>311</v>
@@ -17972,7 +17972,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G607" t="n">
-        <v>1.8754403591156</v>
+        <v>1.87544012069702</v>
       </c>
       <c r="H607" t="n">
         <v>1604</v>
@@ -18001,7 +18001,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G608" t="n">
-        <v>1.8754403591156</v>
+        <v>1.87544012069702</v>
       </c>
       <c r="H608" t="n">
         <v>5380</v>
@@ -18030,7 +18030,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G609" t="n">
-        <v>1.8519971370697</v>
+        <v>1.85199689865112</v>
       </c>
       <c r="H609" t="n">
         <v>700</v>
@@ -18059,7 +18059,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G610" t="n">
-        <v>1.84418284893036</v>
+        <v>1.84418261051178</v>
       </c>
       <c r="H610" t="n">
         <v>4036</v>
@@ -18088,7 +18088,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G611" t="n">
-        <v>1.84418284893036</v>
+        <v>1.84418261051178</v>
       </c>
       <c r="H611" t="n">
         <v>937</v>
@@ -18117,7 +18117,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G612" t="n">
-        <v>1.85981178283691</v>
+        <v>1.85981154441833</v>
       </c>
       <c r="H612" t="n">
         <v>992</v>
@@ -18146,7 +18146,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G613" t="n">
-        <v>1.78166806697845</v>
+        <v>1.78166830539703</v>
       </c>
       <c r="H613" t="n">
         <v>2844</v>
@@ -18175,7 +18175,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G614" t="n">
-        <v>1.79729664325714</v>
+        <v>1.79729688167572</v>
       </c>
       <c r="H614" t="n">
         <v>10850</v>
@@ -18262,7 +18262,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G617" t="n">
-        <v>1.8754403591156</v>
+        <v>1.87544012069702</v>
       </c>
       <c r="H617" t="n">
         <v>1865</v>
@@ -18291,7 +18291,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G618" t="n">
-        <v>1.84418284893036</v>
+        <v>1.84418261051178</v>
       </c>
       <c r="H618" t="n">
         <v>2111</v>
@@ -18349,7 +18349,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G620" t="n">
-        <v>1.82073986530304</v>
+        <v>1.82073962688446</v>
       </c>
       <c r="H620" t="n">
         <v>2510</v>
@@ -18378,7 +18378,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G621" t="n">
-        <v>1.86762583255768</v>
+        <v>1.86762571334839</v>
       </c>
       <c r="H621" t="n">
         <v>16907</v>
@@ -18407,7 +18407,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G622" t="n">
-        <v>1.84418284893036</v>
+        <v>1.84418261051178</v>
       </c>
       <c r="H622" t="n">
         <v>1654</v>
@@ -18436,7 +18436,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G623" t="n">
-        <v>1.92232620716095</v>
+        <v>1.92232608795166</v>
       </c>
       <c r="H623" t="n">
         <v>678</v>
@@ -18465,7 +18465,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G624" t="n">
-        <v>1.86762583255768</v>
+        <v>1.86762571334839</v>
       </c>
       <c r="H624" t="n">
         <v>5391</v>
@@ -18494,7 +18494,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G625" t="n">
-        <v>1.9145120382309</v>
+        <v>1.91451179981232</v>
       </c>
       <c r="H625" t="n">
         <v>1010</v>
@@ -18523,7 +18523,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G626" t="n">
-        <v>1.86762583255768</v>
+        <v>1.86762571334839</v>
       </c>
       <c r="H626" t="n">
         <v>4224</v>
@@ -18552,7 +18552,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G627" t="n">
-        <v>1.82073986530304</v>
+        <v>1.82073962688446</v>
       </c>
       <c r="H627" t="n">
         <v>5337</v>
@@ -18581,7 +18581,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G628" t="n">
-        <v>1.8519971370697</v>
+        <v>1.85199689865112</v>
       </c>
       <c r="H628" t="n">
         <v>767</v>
@@ -18610,7 +18610,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G629" t="n">
-        <v>1.83636856079102</v>
+        <v>1.83636832237244</v>
       </c>
       <c r="H629" t="n">
         <v>2700</v>
@@ -18639,7 +18639,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G630" t="n">
-        <v>1.84418284893036</v>
+        <v>1.84418261051178</v>
       </c>
       <c r="H630" t="n">
         <v>470</v>
@@ -18668,7 +18668,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G631" t="n">
-        <v>1.79729664325714</v>
+        <v>1.79729688167572</v>
       </c>
       <c r="H631" t="n">
         <v>1387</v>
@@ -18697,7 +18697,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G632" t="n">
-        <v>1.76603937149048</v>
+        <v>1.76603960990906</v>
       </c>
       <c r="H632" t="n">
         <v>2150</v>
@@ -18726,7 +18726,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G633" t="n">
-        <v>1.76603937149048</v>
+        <v>1.76603960990906</v>
       </c>
       <c r="H633" t="n">
         <v>0</v>
@@ -18784,7 +18784,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G635" t="n">
-        <v>1.72696793079376</v>
+        <v>1.72696805000305</v>
       </c>
       <c r="H635" t="n">
         <v>2340</v>
@@ -18813,7 +18813,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G636" t="n">
-        <v>1.75041091442108</v>
+        <v>1.75041079521179</v>
       </c>
       <c r="H636" t="n">
         <v>116</v>
@@ -18842,7 +18842,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G637" t="n">
-        <v>1.78166806697845</v>
+        <v>1.78166830539703</v>
       </c>
       <c r="H637" t="n">
         <v>4216</v>
@@ -18871,7 +18871,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G638" t="n">
-        <v>1.82073986530304</v>
+        <v>1.82073962688446</v>
       </c>
       <c r="H638" t="n">
         <v>1300</v>
@@ -18900,7 +18900,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G639" t="n">
-        <v>1.7347823381424</v>
+        <v>1.73478221893311</v>
       </c>
       <c r="H639" t="n">
         <v>17652</v>
@@ -18987,7 +18987,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G642" t="n">
-        <v>1.75041091442108</v>
+        <v>1.75041079521179</v>
       </c>
       <c r="H642" t="n">
         <v>870</v>
@@ -19045,7 +19045,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G644" t="n">
-        <v>1.74259650707245</v>
+        <v>1.74259638786316</v>
       </c>
       <c r="H644" t="n">
         <v>1986</v>
@@ -19190,7 +19190,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G649" t="n">
-        <v>1.70352482795715</v>
+        <v>1.70352494716644</v>
       </c>
       <c r="H649" t="n">
         <v>1910</v>
@@ -19364,7 +19364,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G655" t="n">
-        <v>1.61756706237793</v>
+        <v>1.61756694316864</v>
       </c>
       <c r="H655" t="n">
         <v>2957</v>
@@ -19393,7 +19393,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G656" t="n">
-        <v>1.61756706237793</v>
+        <v>1.61756694316864</v>
       </c>
       <c r="H656" t="n">
         <v>4076</v>
@@ -19480,7 +19480,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G659" t="n">
-        <v>1.60193848609924</v>
+        <v>1.60193836688995</v>
       </c>
       <c r="H659" t="n">
         <v>9353</v>
@@ -19538,7 +19538,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G661" t="n">
-        <v>1.60193848609924</v>
+        <v>1.60193836688995</v>
       </c>
       <c r="H661" t="n">
         <v>790</v>
@@ -19567,7 +19567,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G662" t="n">
-        <v>1.60975289344788</v>
+        <v>1.6097526550293</v>
       </c>
       <c r="H662" t="n">
         <v>1581</v>
@@ -19625,7 +19625,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G664" t="n">
-        <v>1.55505263805389</v>
+        <v>1.5550525188446</v>
       </c>
       <c r="H664" t="n">
         <v>7681</v>
@@ -19654,7 +19654,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G665" t="n">
-        <v>2.06298422813416</v>
+        <v>2.06298446655273</v>
       </c>
       <c r="H665" t="n">
         <v>130384</v>
@@ -19683,7 +19683,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G666" t="n">
-        <v>1.92232620716095</v>
+        <v>1.92232608795166</v>
       </c>
       <c r="H666" t="n">
         <v>446846</v>
@@ -19770,7 +19770,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G669" t="n">
-        <v>1.92232620716095</v>
+        <v>1.92232608795166</v>
       </c>
       <c r="H669" t="n">
         <v>32286</v>
@@ -19799,7 +19799,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G670" t="n">
-        <v>1.99265503883362</v>
+        <v>1.99265539646149</v>
       </c>
       <c r="H670" t="n">
         <v>78330</v>
@@ -19828,7 +19828,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G671" t="n">
-        <v>1.93014061450958</v>
+        <v>1.93014049530029</v>
       </c>
       <c r="H671" t="n">
         <v>41175</v>
@@ -19857,7 +19857,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G672" t="n">
-        <v>1.89888334274292</v>
+        <v>1.89888298511505</v>
       </c>
       <c r="H672" t="n">
         <v>10847</v>
@@ -19886,7 +19886,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G673" t="n">
-        <v>1.92232620716095</v>
+        <v>1.92232608795166</v>
       </c>
       <c r="H673" t="n">
         <v>37391</v>
@@ -19915,7 +19915,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G674" t="n">
-        <v>1.97702634334564</v>
+        <v>1.97702646255493</v>
       </c>
       <c r="H674" t="n">
         <v>10462</v>
@@ -19973,7 +19973,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G676" t="n">
-        <v>1.9145120382309</v>
+        <v>1.91451179981232</v>
       </c>
       <c r="H676" t="n">
         <v>18044</v>
@@ -20031,7 +20031,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G678" t="n">
-        <v>1.82855415344238</v>
+        <v>1.8285539150238</v>
       </c>
       <c r="H678" t="n">
         <v>7847</v>
@@ -20060,7 +20060,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G679" t="n">
-        <v>1.85981178283691</v>
+        <v>1.85981154441833</v>
       </c>
       <c r="H679" t="n">
         <v>1203</v>
@@ -20089,7 +20089,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G680" t="n">
-        <v>1.82855415344238</v>
+        <v>1.8285539150238</v>
       </c>
       <c r="H680" t="n">
         <v>4199</v>
@@ -20118,7 +20118,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G681" t="n">
-        <v>1.76603937149048</v>
+        <v>1.76603960990906</v>
       </c>
       <c r="H681" t="n">
         <v>6126</v>
@@ -20147,7 +20147,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G682" t="n">
-        <v>1.70352482795715</v>
+        <v>1.70352494716644</v>
       </c>
       <c r="H682" t="n">
         <v>21460</v>
@@ -20176,7 +20176,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G683" t="n">
-        <v>1.9145120382309</v>
+        <v>1.91451179981232</v>
       </c>
       <c r="H683" t="n">
         <v>82840</v>
@@ -20205,7 +20205,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G684" t="n">
-        <v>1.82073986530304</v>
+        <v>1.82073962688446</v>
       </c>
       <c r="H684" t="n">
         <v>79297</v>
@@ -20234,7 +20234,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G685" t="n">
-        <v>1.76603937149048</v>
+        <v>1.76603960990906</v>
       </c>
       <c r="H685" t="n">
         <v>13837</v>
@@ -20263,7 +20263,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G686" t="n">
-        <v>1.78166806697845</v>
+        <v>1.78166830539703</v>
       </c>
       <c r="H686" t="n">
         <v>16568</v>
@@ -20292,7 +20292,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G687" t="n">
-        <v>1.76603937149048</v>
+        <v>1.76603960990906</v>
       </c>
       <c r="H687" t="n">
         <v>11052</v>
@@ -20321,7 +20321,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G688" t="n">
-        <v>1.76603937149048</v>
+        <v>1.76603960990906</v>
       </c>
       <c r="H688" t="n">
         <v>8342</v>
@@ -20350,7 +20350,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G689" t="n">
-        <v>1.78166806697845</v>
+        <v>1.78166830539703</v>
       </c>
       <c r="H689" t="n">
         <v>4504</v>
@@ -20379,7 +20379,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G690" t="n">
-        <v>1.75041091442108</v>
+        <v>1.75041079521179</v>
       </c>
       <c r="H690" t="n">
         <v>2392</v>
@@ -20437,7 +20437,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G692" t="n">
-        <v>1.70352482795715</v>
+        <v>1.70352494716644</v>
       </c>
       <c r="H692" t="n">
         <v>29415</v>
@@ -20524,7 +20524,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G695" t="n">
-        <v>1.64882433414459</v>
+        <v>1.64882445335388</v>
       </c>
       <c r="H695" t="n">
         <v>5710</v>
@@ -20640,7 +20640,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G699" t="n">
-        <v>1.74259650707245</v>
+        <v>1.74259638786316</v>
       </c>
       <c r="H699" t="n">
         <v>125437</v>
@@ -20669,7 +20669,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G700" t="n">
-        <v>1.78166806697845</v>
+        <v>1.78166830539703</v>
       </c>
       <c r="H700" t="n">
         <v>16469</v>
@@ -20698,7 +20698,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G701" t="n">
-        <v>1.70352482795715</v>
+        <v>1.70352494716644</v>
       </c>
       <c r="H701" t="n">
         <v>20038</v>
@@ -20727,7 +20727,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G702" t="n">
-        <v>1.69571042060852</v>
+        <v>1.69571053981781</v>
       </c>
       <c r="H702" t="n">
         <v>42863</v>
@@ -20756,7 +20756,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G703" t="n">
-        <v>1.64882433414459</v>
+        <v>1.64882445335388</v>
       </c>
       <c r="H703" t="n">
         <v>2626</v>
@@ -20814,7 +20814,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G705" t="n">
-        <v>1.69571042060852</v>
+        <v>1.69571053981781</v>
       </c>
       <c r="H705" t="n">
         <v>9685</v>
@@ -20872,7 +20872,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G707" t="n">
-        <v>1.62538135051727</v>
+        <v>1.62538146972656</v>
       </c>
       <c r="H707" t="n">
         <v>2029</v>
@@ -20959,7 +20959,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G710" t="n">
-        <v>1.63319575786591</v>
+        <v>1.6331958770752</v>
       </c>
       <c r="H710" t="n">
         <v>5696</v>
@@ -21046,7 +21046,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G713" t="n">
-        <v>1.63319575786591</v>
+        <v>1.6331958770752</v>
       </c>
       <c r="H713" t="n">
         <v>1527</v>
@@ -21104,7 +21104,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G715" t="n">
-        <v>1.61756706237793</v>
+        <v>1.61756694316864</v>
       </c>
       <c r="H715" t="n">
         <v>5893</v>
@@ -21133,7 +21133,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G716" t="n">
-        <v>1.61756706237793</v>
+        <v>1.61756694316864</v>
       </c>
       <c r="H716" t="n">
         <v>15324</v>
@@ -21162,7 +21162,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G717" t="n">
-        <v>1.58630979061127</v>
+        <v>1.58630967140198</v>
       </c>
       <c r="H717" t="n">
         <v>4983</v>
@@ -21220,7 +21220,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G719" t="n">
-        <v>1.54723823070526</v>
+        <v>1.54723811149597</v>
       </c>
       <c r="H719" t="n">
         <v>9044</v>
@@ -21249,7 +21249,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G720" t="n">
-        <v>1.57068109512329</v>
+        <v>1.57068121433258</v>
       </c>
       <c r="H720" t="n">
         <v>7076</v>
@@ -21278,7 +21278,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G721" t="n">
-        <v>1.54723823070526</v>
+        <v>1.54723811149597</v>
       </c>
       <c r="H721" t="n">
         <v>4279</v>
@@ -21307,7 +21307,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G722" t="n">
-        <v>1.61756706237793</v>
+        <v>1.61756694316864</v>
       </c>
       <c r="H722" t="n">
         <v>3905</v>
@@ -21336,7 +21336,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G723" t="n">
-        <v>1.60193848609924</v>
+        <v>1.60193836688995</v>
       </c>
       <c r="H723" t="n">
         <v>33</v>
@@ -21365,7 +21365,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G724" t="n">
-        <v>1.60193848609924</v>
+        <v>1.60193836688995</v>
       </c>
       <c r="H724" t="n">
         <v>1593</v>
@@ -21394,7 +21394,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G725" t="n">
-        <v>1.60193848609924</v>
+        <v>1.60193836688995</v>
       </c>
       <c r="H725" t="n">
         <v>772</v>
@@ -21423,7 +21423,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G726" t="n">
-        <v>1.60193848609924</v>
+        <v>1.60193836688995</v>
       </c>
       <c r="H726" t="n">
         <v>1638</v>
@@ -21452,7 +21452,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G727" t="n">
-        <v>1.60193848609924</v>
+        <v>1.60193836688995</v>
       </c>
       <c r="H727" t="n">
         <v>0</v>
@@ -21510,7 +21510,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G729" t="n">
-        <v>1.57068109512329</v>
+        <v>1.57068121433258</v>
       </c>
       <c r="H729" t="n">
         <v>530</v>
@@ -21539,7 +21539,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G730" t="n">
-        <v>1.57068109512329</v>
+        <v>1.57068121433258</v>
       </c>
       <c r="H730" t="n">
         <v>1325</v>
@@ -21568,7 +21568,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G731" t="n">
-        <v>1.54723823070526</v>
+        <v>1.54723811149597</v>
       </c>
       <c r="H731" t="n">
         <v>2640</v>
@@ -21597,7 +21597,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G732" t="n">
-        <v>1.60193848609924</v>
+        <v>1.60193836688995</v>
       </c>
       <c r="H732" t="n">
         <v>686</v>
@@ -21626,7 +21626,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G733" t="n">
-        <v>1.54723823070526</v>
+        <v>1.54723811149597</v>
       </c>
       <c r="H733" t="n">
         <v>10612</v>
@@ -21684,7 +21684,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G735" t="n">
-        <v>1.55505263805389</v>
+        <v>1.5550525188446</v>
       </c>
       <c r="H735" t="n">
         <v>5470</v>
@@ -21713,7 +21713,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G736" t="n">
-        <v>1.53160965442657</v>
+        <v>1.531609416008</v>
       </c>
       <c r="H736" t="n">
         <v>1180</v>
@@ -21742,7 +21742,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G737" t="n">
-        <v>1.50816655158997</v>
+        <v>1.50816643238068</v>
       </c>
       <c r="H737" t="n">
         <v>2610</v>
@@ -21771,7 +21771,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G738" t="n">
-        <v>1.50035214424133</v>
+        <v>1.50035226345062</v>
       </c>
       <c r="H738" t="n">
         <v>3783</v>
@@ -21800,7 +21800,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G739" t="n">
-        <v>1.49253785610199</v>
+        <v>1.49253797531128</v>
       </c>
       <c r="H739" t="n">
         <v>1588</v>
@@ -21829,7 +21829,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G740" t="n">
-        <v>1.53160965442657</v>
+        <v>1.531609416008</v>
       </c>
       <c r="H740" t="n">
         <v>1201</v>
@@ -21858,7 +21858,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G741" t="n">
-        <v>1.50035214424133</v>
+        <v>1.50035226345062</v>
       </c>
       <c r="H741" t="n">
         <v>1657</v>
@@ -21887,7 +21887,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G742" t="n">
-        <v>1.50816655158997</v>
+        <v>1.50816643238068</v>
       </c>
       <c r="H742" t="n">
         <v>8117</v>
@@ -21916,7 +21916,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G743" t="n">
-        <v>1.60975289344788</v>
+        <v>1.6097526550293</v>
       </c>
       <c r="H743" t="n">
         <v>83441</v>
@@ -21945,7 +21945,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G744" t="n">
-        <v>1.62538135051727</v>
+        <v>1.62538146972656</v>
       </c>
       <c r="H744" t="n">
         <v>19613</v>
@@ -21974,7 +21974,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G745" t="n">
-        <v>1.54723823070526</v>
+        <v>1.54723811149597</v>
       </c>
       <c r="H745" t="n">
         <v>6604</v>
@@ -22032,7 +22032,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G747" t="n">
-        <v>1.58630979061127</v>
+        <v>1.58630967140198</v>
       </c>
       <c r="H747" t="n">
         <v>1818</v>
@@ -22061,7 +22061,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G748" t="n">
-        <v>1.58630979061127</v>
+        <v>1.58630967140198</v>
       </c>
       <c r="H748" t="n">
         <v>5636</v>
@@ -22090,7 +22090,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G749" t="n">
-        <v>1.58630979061127</v>
+        <v>1.58630967140198</v>
       </c>
       <c r="H749" t="n">
         <v>4728</v>
@@ -22293,7 +22293,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G756" t="n">
-        <v>1.53942394256592</v>
+        <v>1.53942382335663</v>
       </c>
       <c r="H756" t="n">
         <v>2030</v>
@@ -22322,7 +22322,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G757" t="n">
-        <v>1.50816655158997</v>
+        <v>1.50816643238068</v>
       </c>
       <c r="H757" t="n">
         <v>390</v>
@@ -22409,7 +22409,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G760" t="n">
-        <v>1.57068109512329</v>
+        <v>1.57068121433258</v>
       </c>
       <c r="H760" t="n">
         <v>3200</v>
@@ -22438,7 +22438,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G761" t="n">
-        <v>1.49253785610199</v>
+        <v>1.49253797531128</v>
       </c>
       <c r="H761" t="n">
         <v>6174</v>
@@ -22467,7 +22467,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G762" t="n">
-        <v>1.47690904140472</v>
+        <v>1.47690916061401</v>
       </c>
       <c r="H762" t="n">
         <v>4134</v>
@@ -22525,7 +22525,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G764" t="n">
-        <v>1.50816655158997</v>
+        <v>1.50816643238068</v>
       </c>
       <c r="H764" t="n">
         <v>2240</v>
@@ -22554,7 +22554,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G765" t="n">
-        <v>1.74259650707245</v>
+        <v>1.74259638786316</v>
       </c>
       <c r="H765" t="n">
         <v>62191</v>
@@ -22583,7 +22583,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G766" t="n">
-        <v>1.55505263805389</v>
+        <v>1.5550525188446</v>
       </c>
       <c r="H766" t="n">
         <v>117476</v>
@@ -22612,7 +22612,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G767" t="n">
-        <v>1.58630979061127</v>
+        <v>1.58630967140198</v>
       </c>
       <c r="H767" t="n">
         <v>8040</v>
@@ -22641,7 +22641,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G768" t="n">
-        <v>1.55505263805389</v>
+        <v>1.5550525188446</v>
       </c>
       <c r="H768" t="n">
         <v>5714</v>
@@ -22670,7 +22670,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G769" t="n">
-        <v>1.58630979061127</v>
+        <v>1.58630967140198</v>
       </c>
       <c r="H769" t="n">
         <v>1450</v>
@@ -22699,7 +22699,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G770" t="n">
-        <v>1.58630979061127</v>
+        <v>1.58630967140198</v>
       </c>
       <c r="H770" t="n">
         <v>1250</v>
@@ -22728,7 +22728,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G771" t="n">
-        <v>1.58630979061127</v>
+        <v>1.58630967140198</v>
       </c>
       <c r="H771" t="n">
         <v>505</v>
@@ -22757,7 +22757,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G772" t="n">
-        <v>1.58630979061127</v>
+        <v>1.58630967140198</v>
       </c>
       <c r="H772" t="n">
         <v>0</v>
@@ -22786,7 +22786,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G773" t="n">
-        <v>1.55505263805389</v>
+        <v>1.5550525188446</v>
       </c>
       <c r="H773" t="n">
         <v>8089</v>
@@ -22844,7 +22844,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G775" t="n">
-        <v>1.55505263805389</v>
+        <v>1.5550525188446</v>
       </c>
       <c r="H775" t="n">
         <v>2807</v>
@@ -22873,7 +22873,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G776" t="n">
-        <v>1.53160965442657</v>
+        <v>1.531609416008</v>
       </c>
       <c r="H776" t="n">
         <v>5415</v>
@@ -22902,7 +22902,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G777" t="n">
-        <v>1.53942394256592</v>
+        <v>1.53942382335663</v>
       </c>
       <c r="H777" t="n">
         <v>6542</v>
@@ -22931,7 +22931,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G778" t="n">
-        <v>1.53942394256592</v>
+        <v>1.53942382335663</v>
       </c>
       <c r="H778" t="n">
         <v>8387</v>
@@ -23018,7 +23018,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G781" t="n">
-        <v>1.55505263805389</v>
+        <v>1.5550525188446</v>
       </c>
       <c r="H781" t="n">
         <v>1090</v>
@@ -23047,7 +23047,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G782" t="n">
-        <v>1.53160965442657</v>
+        <v>1.531609416008</v>
       </c>
       <c r="H782" t="n">
         <v>5650</v>
@@ -23076,7 +23076,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G783" t="n">
-        <v>1.53160965442657</v>
+        <v>1.531609416008</v>
       </c>
       <c r="H783" t="n">
         <v>9208</v>
@@ -23163,7 +23163,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G786" t="n">
-        <v>1.55505263805389</v>
+        <v>1.5550525188446</v>
       </c>
       <c r="H786" t="n">
         <v>3597</v>
@@ -23192,7 +23192,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G787" t="n">
-        <v>1.55505263805389</v>
+        <v>1.5550525188446</v>
       </c>
       <c r="H787" t="n">
         <v>375</v>
@@ -23279,7 +23279,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G790" t="n">
-        <v>1.55505263805389</v>
+        <v>1.5550525188446</v>
       </c>
       <c r="H790" t="n">
         <v>935</v>
@@ -23337,7 +23337,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G792" t="n">
-        <v>1.54723823070526</v>
+        <v>1.54723811149597</v>
       </c>
       <c r="H792" t="n">
         <v>3760</v>
@@ -23366,7 +23366,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G793" t="n">
-        <v>1.54723823070526</v>
+        <v>1.54723811149597</v>
       </c>
       <c r="H793" t="n">
         <v>1646</v>
@@ -23395,7 +23395,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G794" t="n">
-        <v>1.54723823070526</v>
+        <v>1.54723811149597</v>
       </c>
       <c r="H794" t="n">
         <v>3700</v>
@@ -23482,7 +23482,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G797" t="n">
-        <v>1.57068109512329</v>
+        <v>1.57068121433258</v>
       </c>
       <c r="H797" t="n">
         <v>8209</v>
@@ -23569,7 +23569,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G800" t="n">
-        <v>1.53942394256592</v>
+        <v>1.53942382335663</v>
       </c>
       <c r="H800" t="n">
         <v>7026</v>
@@ -23598,7 +23598,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G801" t="n">
-        <v>1.54723823070526</v>
+        <v>1.54723811149597</v>
       </c>
       <c r="H801" t="n">
         <v>4800</v>
@@ -23627,7 +23627,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G802" t="n">
-        <v>1.55505263805389</v>
+        <v>1.5550525188446</v>
       </c>
       <c r="H802" t="n">
         <v>11782</v>
@@ -23656,7 +23656,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G803" t="n">
-        <v>1.58630979061127</v>
+        <v>1.58630967140198</v>
       </c>
       <c r="H803" t="n">
         <v>3550</v>
@@ -23743,7 +23743,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G806" t="n">
-        <v>1.58630979061127</v>
+        <v>1.58630967140198</v>
       </c>
       <c r="H806" t="n">
         <v>9021</v>
@@ -23772,7 +23772,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G807" t="n">
-        <v>1.60975289344788</v>
+        <v>1.6097526550293</v>
       </c>
       <c r="H807" t="n">
         <v>6800</v>
@@ -23801,7 +23801,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G808" t="n">
-        <v>1.58630979061127</v>
+        <v>1.58630967140198</v>
       </c>
       <c r="H808" t="n">
         <v>6622</v>
@@ -23888,7 +23888,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G811" t="n">
-        <v>1.55505263805389</v>
+        <v>1.5550525188446</v>
       </c>
       <c r="H811" t="n">
         <v>1500</v>
@@ -23917,7 +23917,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G812" t="n">
-        <v>1.55505263805389</v>
+        <v>1.5550525188446</v>
       </c>
       <c r="H812" t="n">
         <v>3468</v>
@@ -23975,7 +23975,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G814" t="n">
-        <v>1.57068109512329</v>
+        <v>1.57068121433258</v>
       </c>
       <c r="H814" t="n">
         <v>19292</v>
@@ -24091,7 +24091,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G818" t="n">
-        <v>1.60975289344788</v>
+        <v>1.6097526550293</v>
       </c>
       <c r="H818" t="n">
         <v>32403</v>
@@ -24120,7 +24120,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G819" t="n">
-        <v>1.58630979061127</v>
+        <v>1.58630967140198</v>
       </c>
       <c r="H819" t="n">
         <v>15326</v>
@@ -24178,7 +24178,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G821" t="n">
-        <v>1.62538135051727</v>
+        <v>1.62538146972656</v>
       </c>
       <c r="H821" t="n">
         <v>2898</v>
@@ -24207,7 +24207,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G822" t="n">
-        <v>1.61756706237793</v>
+        <v>1.61756694316864</v>
       </c>
       <c r="H822" t="n">
         <v>271</v>
@@ -24294,7 +24294,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G825" t="n">
-        <v>1.58630979061127</v>
+        <v>1.58630967140198</v>
       </c>
       <c r="H825" t="n">
         <v>1500</v>
@@ -24352,7 +24352,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G827" t="n">
-        <v>1.62538135051727</v>
+        <v>1.62538146972656</v>
       </c>
       <c r="H827" t="n">
         <v>17597</v>
@@ -24410,7 +24410,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G829" t="n">
-        <v>1.7347823381424</v>
+        <v>1.73478221893311</v>
       </c>
       <c r="H829" t="n">
         <v>220051</v>
@@ -24468,7 +24468,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G831" t="n">
-        <v>1.65663874149323</v>
+        <v>1.65663886070251</v>
       </c>
       <c r="H831" t="n">
         <v>34511</v>
@@ -24497,7 +24497,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G832" t="n">
-        <v>1.65663874149323</v>
+        <v>1.65663886070251</v>
       </c>
       <c r="H832" t="n">
         <v>51170</v>
@@ -24584,7 +24584,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G835" t="n">
-        <v>1.60975289344788</v>
+        <v>1.6097526550293</v>
       </c>
       <c r="H835" t="n">
         <v>57779</v>
@@ -24613,7 +24613,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G836" t="n">
-        <v>1.62538135051727</v>
+        <v>1.62538146972656</v>
       </c>
       <c r="H836" t="n">
         <v>52160</v>
@@ -24845,7 +24845,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G844" t="n">
-        <v>1.60975289344788</v>
+        <v>1.6097526550293</v>
       </c>
       <c r="H844" t="n">
         <v>39333</v>
@@ -24874,7 +24874,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G845" t="n">
-        <v>1.62538135051727</v>
+        <v>1.62538146972656</v>
       </c>
       <c r="H845" t="n">
         <v>14102</v>
@@ -24903,7 +24903,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G846" t="n">
-        <v>1.60975289344788</v>
+        <v>1.6097526550293</v>
       </c>
       <c r="H846" t="n">
         <v>9208</v>
@@ -24932,7 +24932,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G847" t="n">
-        <v>1.62538135051727</v>
+        <v>1.62538146972656</v>
       </c>
       <c r="H847" t="n">
         <v>14870</v>
@@ -24961,7 +24961,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G848" t="n">
-        <v>1.60975289344788</v>
+        <v>1.6097526550293</v>
       </c>
       <c r="H848" t="n">
         <v>10001</v>
@@ -25106,7 +25106,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G853" t="n">
-        <v>1.53160965442657</v>
+        <v>1.531609416008</v>
       </c>
       <c r="H853" t="n">
         <v>9826</v>
@@ -25164,7 +25164,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G855" t="n">
-        <v>1.53160965442657</v>
+        <v>1.531609416008</v>
       </c>
       <c r="H855" t="n">
         <v>30431</v>
@@ -25193,7 +25193,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G856" t="n">
-        <v>1.54723823070526</v>
+        <v>1.54723811149597</v>
       </c>
       <c r="H856" t="n">
         <v>6091</v>
@@ -25222,7 +25222,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G857" t="n">
-        <v>1.53160965442657</v>
+        <v>1.531609416008</v>
       </c>
       <c r="H857" t="n">
         <v>8665</v>
@@ -25454,7 +25454,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G865" t="n">
-        <v>1.50035214424133</v>
+        <v>1.50035226345062</v>
       </c>
       <c r="H865" t="n">
         <v>6903</v>
@@ -25483,7 +25483,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G866" t="n">
-        <v>1.50035214424133</v>
+        <v>1.50035226345062</v>
       </c>
       <c r="H866" t="n">
         <v>8355</v>
@@ -25512,7 +25512,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G867" t="n">
-        <v>1.53160965442657</v>
+        <v>1.531609416008</v>
       </c>
       <c r="H867" t="n">
         <v>3500</v>
@@ -25570,7 +25570,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G869" t="n">
-        <v>1.4534660577774</v>
+        <v>1.45346617698669</v>
       </c>
       <c r="H869" t="n">
         <v>670</v>
@@ -25628,7 +25628,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G871" t="n">
-        <v>1.50035214424133</v>
+        <v>1.50035226345062</v>
       </c>
       <c r="H871" t="n">
         <v>1918</v>
@@ -25657,7 +25657,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G872" t="n">
-        <v>1.50035214424133</v>
+        <v>1.50035226345062</v>
       </c>
       <c r="H872" t="n">
         <v>0</v>
@@ -25744,7 +25744,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G875" t="n">
-        <v>1.4534660577774</v>
+        <v>1.45346617698669</v>
       </c>
       <c r="H875" t="n">
         <v>7508</v>
@@ -25773,7 +25773,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G876" t="n">
-        <v>1.4534660577774</v>
+        <v>1.45346617698669</v>
       </c>
       <c r="H876" t="n">
         <v>800</v>
@@ -25831,7 +25831,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G878" t="n">
-        <v>1.53160965442657</v>
+        <v>1.531609416008</v>
       </c>
       <c r="H878" t="n">
         <v>2050</v>
@@ -25918,7 +25918,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G881" t="n">
-        <v>1.4534660577774</v>
+        <v>1.45346617698669</v>
       </c>
       <c r="H881" t="n">
         <v>880</v>
@@ -25976,7 +25976,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G883" t="n">
-        <v>1.4534660577774</v>
+        <v>1.45346617698669</v>
       </c>
       <c r="H883" t="n">
         <v>12670</v>
@@ -26005,7 +26005,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G884" t="n">
-        <v>1.4534660577774</v>
+        <v>1.45346617698669</v>
       </c>
       <c r="H884" t="n">
         <v>4516</v>
@@ -26237,7 +26237,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G892" t="n">
-        <v>1.53160965442657</v>
+        <v>1.531609416008</v>
       </c>
       <c r="H892" t="n">
         <v>6177</v>
@@ -26324,7 +26324,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G895" t="n">
-        <v>1.53160965442657</v>
+        <v>1.531609416008</v>
       </c>
       <c r="H895" t="n">
         <v>4132</v>
@@ -26353,7 +26353,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G896" t="n">
-        <v>1.53160965442657</v>
+        <v>1.531609416008</v>
       </c>
       <c r="H896" t="n">
         <v>15658</v>
@@ -26382,7 +26382,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G897" t="n">
-        <v>1.54723823070526</v>
+        <v>1.54723811149597</v>
       </c>
       <c r="H897" t="n">
         <v>12400</v>
@@ -26411,7 +26411,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G898" t="n">
-        <v>1.50035214424133</v>
+        <v>1.50035226345062</v>
       </c>
       <c r="H898" t="n">
         <v>9001</v>
@@ -26440,7 +26440,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G899" t="n">
-        <v>1.50035214424133</v>
+        <v>1.50035226345062</v>
       </c>
       <c r="H899" t="n">
         <v>5729</v>
@@ -26469,7 +26469,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G900" t="n">
-        <v>1.50035214424133</v>
+        <v>1.50035226345062</v>
       </c>
       <c r="H900" t="n">
         <v>4094</v>
@@ -26498,7 +26498,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G901" t="n">
-        <v>1.54723823070526</v>
+        <v>1.54723811149597</v>
       </c>
       <c r="H901" t="n">
         <v>5238</v>
@@ -26585,7 +26585,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G904" t="n">
-        <v>1.53160965442657</v>
+        <v>1.531609416008</v>
       </c>
       <c r="H904" t="n">
         <v>2250</v>
@@ -26614,7 +26614,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G905" t="n">
-        <v>1.53160965442657</v>
+        <v>1.531609416008</v>
       </c>
       <c r="H905" t="n">
         <v>3080</v>
@@ -26643,7 +26643,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G906" t="n">
-        <v>1.50035214424133</v>
+        <v>1.50035226345062</v>
       </c>
       <c r="H906" t="n">
         <v>3380</v>
@@ -26672,7 +26672,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G907" t="n">
-        <v>1.50035214424133</v>
+        <v>1.50035226345062</v>
       </c>
       <c r="H907" t="n">
         <v>17682</v>
@@ -26759,7 +26759,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G910" t="n">
-        <v>1.50035214424133</v>
+        <v>1.50035226345062</v>
       </c>
       <c r="H910" t="n">
         <v>2535</v>
@@ -26846,7 +26846,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G913" t="n">
-        <v>1.50035214424133</v>
+        <v>1.50035226345062</v>
       </c>
       <c r="H913" t="n">
         <v>1205</v>
@@ -26933,7 +26933,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G916" t="n">
-        <v>1.50035214424133</v>
+        <v>1.50035226345062</v>
       </c>
       <c r="H916" t="n">
         <v>1650</v>
@@ -26962,7 +26962,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G917" t="n">
-        <v>1.50035214424133</v>
+        <v>1.50035226345062</v>
       </c>
       <c r="H917" t="n">
         <v>8100</v>
@@ -27020,7 +27020,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G919" t="n">
-        <v>1.4534660577774</v>
+        <v>1.45346617698669</v>
       </c>
       <c r="H919" t="n">
         <v>1440</v>
@@ -27049,7 +27049,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G920" t="n">
-        <v>1.4534660577774</v>
+        <v>1.45346617698669</v>
       </c>
       <c r="H920" t="n">
         <v>1744</v>
@@ -27165,7 +27165,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G924" t="n">
-        <v>1.4534660577774</v>
+        <v>1.45346617698669</v>
       </c>
       <c r="H924" t="n">
         <v>2225</v>
@@ -27223,7 +27223,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G926" t="n">
-        <v>1.50035214424133</v>
+        <v>1.50035226345062</v>
       </c>
       <c r="H926" t="n">
         <v>3414</v>
@@ -27252,7 +27252,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G927" t="n">
-        <v>1.50035214424133</v>
+        <v>1.50035226345062</v>
       </c>
       <c r="H927" t="n">
         <v>60</v>
@@ -27281,7 +27281,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G928" t="n">
-        <v>1.4534660577774</v>
+        <v>1.45346617698669</v>
       </c>
       <c r="H928" t="n">
         <v>750</v>
@@ -27310,7 +27310,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G929" t="n">
-        <v>1.4534660577774</v>
+        <v>1.45346617698669</v>
       </c>
       <c r="H929" t="n">
         <v>800</v>
@@ -27426,7 +27426,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G933" t="n">
-        <v>1.50035214424133</v>
+        <v>1.50035226345062</v>
       </c>
       <c r="H933" t="n">
         <v>10800</v>
@@ -27629,7 +27629,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G940" t="n">
-        <v>1.50035214424133</v>
+        <v>1.50035226345062</v>
       </c>
       <c r="H940" t="n">
         <v>3395</v>
@@ -27658,7 +27658,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G941" t="n">
-        <v>1.53160965442657</v>
+        <v>1.531609416008</v>
       </c>
       <c r="H941" t="n">
         <v>62485</v>
@@ -27890,7 +27890,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G949" t="n">
-        <v>1.50035214424133</v>
+        <v>1.50035226345062</v>
       </c>
       <c r="H949" t="n">
         <v>2380</v>
@@ -27919,7 +27919,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G950" t="n">
-        <v>1.50035214424133</v>
+        <v>1.50035226345062</v>
       </c>
       <c r="H950" t="n">
         <v>1118</v>
@@ -27948,7 +27948,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G951" t="n">
-        <v>1.50035214424133</v>
+        <v>1.50035226345062</v>
       </c>
       <c r="H951" t="n">
         <v>2270</v>
@@ -27977,7 +27977,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G952" t="n">
-        <v>1.50035214424133</v>
+        <v>1.50035226345062</v>
       </c>
       <c r="H952" t="n">
         <v>3602</v>
@@ -28006,7 +28006,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G953" t="n">
-        <v>1.50035214424133</v>
+        <v>1.50035226345062</v>
       </c>
       <c r="H953" t="n">
         <v>4131</v>
@@ -28035,7 +28035,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G954" t="n">
-        <v>1.50035214424133</v>
+        <v>1.50035226345062</v>
       </c>
       <c r="H954" t="n">
         <v>7140</v>
@@ -28151,7 +28151,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G958" t="n">
-        <v>1.4534660577774</v>
+        <v>1.45346617698669</v>
       </c>
       <c r="H958" t="n">
         <v>5750</v>
@@ -28267,7 +28267,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G962" t="n">
-        <v>1.4534660577774</v>
+        <v>1.45346617698669</v>
       </c>
       <c r="H962" t="n">
         <v>10260</v>
@@ -28586,7 +28586,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G973" t="n">
-        <v>1.42220878601074</v>
+        <v>1.42220890522003</v>
       </c>
       <c r="H973" t="n">
         <v>30</v>
@@ -28615,7 +28615,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G974" t="n">
-        <v>1.4534660577774</v>
+        <v>1.45346617698669</v>
       </c>
       <c r="H974" t="n">
         <v>949</v>
@@ -28673,7 +28673,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G976" t="n">
-        <v>1.42220878601074</v>
+        <v>1.42220890522003</v>
       </c>
       <c r="H976" t="n">
         <v>8943</v>
@@ -28702,7 +28702,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G977" t="n">
-        <v>1.42220878601074</v>
+        <v>1.42220890522003</v>
       </c>
       <c r="H977" t="n">
         <v>2955</v>
@@ -28760,7 +28760,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G979" t="n">
-        <v>1.4534660577774</v>
+        <v>1.45346617698669</v>
       </c>
       <c r="H979" t="n">
         <v>16332</v>
@@ -28847,7 +28847,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G982" t="n">
-        <v>1.4534660577774</v>
+        <v>1.45346617698669</v>
       </c>
       <c r="H982" t="n">
         <v>130</v>
@@ -28876,7 +28876,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G983" t="n">
-        <v>1.4534660577774</v>
+        <v>1.45346617698669</v>
       </c>
       <c r="H983" t="n">
         <v>51</v>
@@ -28905,7 +28905,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G984" t="n">
-        <v>1.42220878601074</v>
+        <v>1.42220890522003</v>
       </c>
       <c r="H984" t="n">
         <v>2400</v>
@@ -28934,7 +28934,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G985" t="n">
-        <v>1.42220878601074</v>
+        <v>1.42220890522003</v>
       </c>
       <c r="H985" t="n">
         <v>7856</v>
@@ -28963,7 +28963,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G986" t="n">
-        <v>1.42220878601074</v>
+        <v>1.42220890522003</v>
       </c>
       <c r="H986" t="n">
         <v>28690</v>
@@ -29166,7 +29166,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G993" t="n">
-        <v>1.42220878601074</v>
+        <v>1.42220890522003</v>
       </c>
       <c r="H993" t="n">
         <v>2550</v>
@@ -29195,7 +29195,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G994" t="n">
-        <v>1.42220878601074</v>
+        <v>1.42220890522003</v>
       </c>
       <c r="H994" t="n">
         <v>2459</v>
@@ -29224,7 +29224,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G995" t="n">
-        <v>1.39095139503479</v>
+        <v>1.39095151424408</v>
       </c>
       <c r="H995" t="n">
         <v>4445</v>
@@ -29253,7 +29253,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G996" t="n">
-        <v>1.42220878601074</v>
+        <v>1.42220890522003</v>
       </c>
       <c r="H996" t="n">
         <v>739</v>
@@ -29340,7 +29340,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G999" t="n">
-        <v>1.37532269954681</v>
+        <v>1.3753228187561</v>
       </c>
       <c r="H999" t="n">
         <v>5008</v>
@@ -29398,7 +29398,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G1001" t="n">
-        <v>1.37532269954681</v>
+        <v>1.3753228187561</v>
       </c>
       <c r="H1001" t="n">
         <v>3675</v>
@@ -29601,7 +29601,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G1008" t="n">
-        <v>1.42220878601074</v>
+        <v>1.42220890522003</v>
       </c>
       <c r="H1008" t="n">
         <v>24714</v>
@@ -29630,7 +29630,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G1009" t="n">
-        <v>1.4534660577774</v>
+        <v>1.45346617698669</v>
       </c>
       <c r="H1009" t="n">
         <v>16050</v>
@@ -29688,7 +29688,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G1011" t="n">
-        <v>1.4534660577774</v>
+        <v>1.45346617698669</v>
       </c>
       <c r="H1011" t="n">
         <v>39708</v>
@@ -29804,7 +29804,7 @@
         <v>1.86940002441406</v>
       </c>
       <c r="G1015" t="n">
-        <v>1.46081173419952</v>
+        <v>1.46081161499023</v>
       </c>
       <c r="H1015" t="n">
         <v>31731</v>
@@ -29891,7 +29891,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G1018" t="n">
-        <v>1.35969424247742</v>
+        <v>1.35969412326813</v>
       </c>
       <c r="H1018" t="n">
         <v>21467</v>
@@ -29949,7 +29949,7 @@
         <v>1.81679999828339</v>
       </c>
       <c r="G1020" t="n">
-        <v>1.41970813274384</v>
+        <v>1.41970825195312</v>
       </c>
       <c r="H1020" t="n">
         <v>54639</v>
@@ -30036,7 +30036,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G1023" t="n">
-        <v>1.41439437866211</v>
+        <v>1.4143944978714</v>
       </c>
       <c r="H1023" t="n">
         <v>10822</v>
@@ -30065,7 +30065,7 @@
         <v>1.81959998607635</v>
       </c>
       <c r="G1024" t="n">
-        <v>1.42189610004425</v>
+        <v>1.42189621925354</v>
       </c>
       <c r="H1024" t="n">
         <v>67133</v>
@@ -30123,7 +30123,7 @@
         <v>1.74119997024536</v>
       </c>
       <c r="G1026" t="n">
-        <v>1.36063170433044</v>
+        <v>1.36063182353973</v>
       </c>
       <c r="H1026" t="n">
         <v>42274</v>
@@ -30239,7 +30239,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G1030" t="n">
-        <v>1.3362512588501</v>
+        <v>1.33625113964081</v>
       </c>
       <c r="H1030" t="n">
         <v>3600</v>
@@ -30268,7 +30268,7 @@
         <v>1.73239994049072</v>
       </c>
       <c r="G1031" t="n">
-        <v>1.353755235672</v>
+        <v>1.35375511646271</v>
       </c>
       <c r="H1031" t="n">
         <v>8694</v>
@@ -30326,7 +30326,7 @@
         <v>1.70099997520447</v>
       </c>
       <c r="G1033" t="n">
-        <v>1.32921826839447</v>
+        <v>1.32921814918518</v>
       </c>
       <c r="H1033" t="n">
         <v>15378</v>
@@ -30355,7 +30355,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G1034" t="n">
-        <v>1.3362512588501</v>
+        <v>1.33625113964081</v>
       </c>
       <c r="H1034" t="n">
         <v>4038</v>
@@ -30413,7 +30413,7 @@
         <v>1.66919994354248</v>
       </c>
       <c r="G1036" t="n">
-        <v>1.30436861515045</v>
+        <v>1.30436873435974</v>
       </c>
       <c r="H1036" t="n">
         <v>37285</v>
@@ -30529,7 +30529,7 @@
         <v>1.52020001411438</v>
       </c>
       <c r="G1040" t="n">
-        <v>1.18793499469757</v>
+        <v>1.18793511390686</v>
       </c>
       <c r="H1040" t="n">
         <v>32531</v>
@@ -30587,7 +30587,7 @@
         <v>1.60580003261566</v>
       </c>
       <c r="G1042" t="n">
-        <v>1.25482571125031</v>
+        <v>1.25482594966888</v>
       </c>
       <c r="H1042" t="n">
         <v>57252</v>
@@ -30645,7 +30645,7 @@
         <v>1.63900005817413</v>
       </c>
       <c r="G1044" t="n">
-        <v>1.28076946735382</v>
+        <v>1.28076934814453</v>
       </c>
       <c r="H1044" t="n">
         <v>37874</v>
@@ -30674,7 +30674,7 @@
         <v>1.62979996204376</v>
       </c>
       <c r="G1045" t="n">
-        <v>1.2735800743103</v>
+        <v>1.27358019351959</v>
       </c>
       <c r="H1045" t="n">
         <v>4325</v>
@@ -30703,7 +30703,7 @@
         <v>1.63779997825623</v>
       </c>
       <c r="G1046" t="n">
-        <v>1.27983164787292</v>
+        <v>1.27983176708221</v>
       </c>
       <c r="H1046" t="n">
         <v>22878</v>
@@ -30732,7 +30732,7 @@
         <v>1.66260004043579</v>
       </c>
       <c r="G1047" t="n">
-        <v>1.29921114444733</v>
+        <v>1.29921126365662</v>
       </c>
       <c r="H1047" t="n">
         <v>23626</v>
@@ -30761,7 +30761,7 @@
         <v>1.68579995632172</v>
       </c>
       <c r="G1048" t="n">
-        <v>1.31734049320221</v>
+        <v>1.31734037399292</v>
       </c>
       <c r="H1048" t="n">
         <v>10382</v>
@@ -30964,7 +30964,7 @@
         <v>1.61479997634888</v>
       </c>
       <c r="G1055" t="n">
-        <v>1.26185858249664</v>
+        <v>1.26185870170593</v>
       </c>
       <c r="H1055" t="n">
         <v>3537</v>
@@ -30993,7 +30993,7 @@
         <v>1.54159998893738</v>
       </c>
       <c r="G1056" t="n">
-        <v>1.20465779304504</v>
+        <v>1.20465767383575</v>
       </c>
       <c r="H1056" t="n">
         <v>6735</v>
@@ -31022,7 +31022,7 @@
         <v>1.58980000019073</v>
       </c>
       <c r="G1057" t="n">
-        <v>1.24232292175293</v>
+        <v>1.24232280254364</v>
       </c>
       <c r="H1057" t="n">
         <v>20662</v>
@@ -31138,7 +31138,7 @@
         <v>1.49779999256134</v>
       </c>
       <c r="G1061" t="n">
-        <v>1.17043101787567</v>
+        <v>1.17043089866638</v>
       </c>
       <c r="H1061" t="n">
         <v>16113</v>
@@ -31167,7 +31167,7 @@
         <v>1.35800004005432</v>
       </c>
       <c r="G1062" t="n">
-        <v>1.06118667125702</v>
+        <v>1.06118655204773</v>
       </c>
       <c r="H1062" t="n">
         <v>18498</v>
@@ -31196,7 +31196,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G1063" t="n">
-        <v>0.883019685745239</v>
+        <v>0.883019804954529</v>
       </c>
       <c r="H1063" t="n">
         <v>14800</v>
@@ -31225,7 +31225,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G1064" t="n">
-        <v>0.883019685745239</v>
+        <v>0.883019804954529</v>
       </c>
       <c r="H1064" t="n">
         <v>10076</v>
@@ -31254,7 +31254,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G1065" t="n">
-        <v>0.867391169071198</v>
+        <v>0.867391109466553</v>
       </c>
       <c r="H1065" t="n">
         <v>9626</v>
@@ -31341,7 +31341,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G1068" t="n">
-        <v>0.773619115352631</v>
+        <v>0.773619055747986</v>
       </c>
       <c r="H1068" t="n">
         <v>15083</v>
@@ -31370,7 +31370,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G1069" t="n">
-        <v>0.773619115352631</v>
+        <v>0.773619055747986</v>
       </c>
       <c r="H1069" t="n">
         <v>7200</v>
@@ -31399,7 +31399,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G1070" t="n">
-        <v>0.773619115352631</v>
+        <v>0.773619055747986</v>
       </c>
       <c r="H1070" t="n">
         <v>1500</v>
@@ -31515,7 +31515,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G1074" t="n">
-        <v>1.0940066576004</v>
+        <v>1.09400677680969</v>
       </c>
       <c r="H1074" t="n">
         <v>7710</v>
@@ -31631,7 +31631,7 @@
         <v>1.61500000953674</v>
       </c>
       <c r="G1078" t="n">
-        <v>1.26201510429382</v>
+        <v>1.26201498508453</v>
       </c>
       <c r="H1078" t="n">
         <v>5525</v>
@@ -31776,7 +31776,7 @@
         <v>1.58800005912781</v>
       </c>
       <c r="G1083" t="n">
-        <v>1.24091625213623</v>
+        <v>1.24091649055481</v>
       </c>
       <c r="H1083" t="n">
         <v>22509</v>
@@ -31805,7 +31805,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G1084" t="n">
-        <v>1.25810790061951</v>
+        <v>1.25810778141022</v>
       </c>
       <c r="H1084" t="n">
         <v>29539</v>
@@ -31892,7 +31892,7 @@
         <v>1.52119994163513</v>
       </c>
       <c r="G1087" t="n">
-        <v>1.18871641159058</v>
+        <v>1.18871629238129</v>
       </c>
       <c r="H1087" t="n">
         <v>999</v>
@@ -31921,7 +31921,7 @@
         <v>1.52999997138977</v>
       </c>
       <c r="G1088" t="n">
-        <v>1.1955931186676</v>
+        <v>1.19559323787689</v>
       </c>
       <c r="H1088" t="n">
         <v>8558</v>
@@ -31979,7 +31979,7 @@
         <v>1.56959998607635</v>
       </c>
       <c r="G1090" t="n">
-        <v>1.22653794288635</v>
+        <v>1.22653782367706</v>
       </c>
       <c r="H1090" t="n">
         <v>15691</v>
@@ -32008,7 +32008,7 @@
         <v>1.53519999980927</v>
       </c>
       <c r="G1091" t="n">
-        <v>1.19965660572052</v>
+        <v>1.19965672492981</v>
       </c>
       <c r="H1091" t="n">
         <v>7726</v>
@@ -32037,7 +32037,7 @@
         <v>1.51059997081757</v>
       </c>
       <c r="G1092" t="n">
-        <v>1.18043327331543</v>
+        <v>1.18043339252472</v>
       </c>
       <c r="H1092" t="n">
         <v>10176</v>
@@ -32153,7 +32153,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G1096" t="n">
-        <v>1.08619236946106</v>
+        <v>1.08619248867035</v>
       </c>
       <c r="H1096" t="n">
         <v>36445</v>
@@ -32327,7 +32327,7 @@
         <v>1.44400000572205</v>
       </c>
       <c r="G1102" t="n">
-        <v>1.12838995456696</v>
+        <v>1.12838983535767</v>
       </c>
       <c r="H1102" t="n">
         <v>44823</v>
@@ -32385,7 +32385,7 @@
         <v>1.37020003795624</v>
       </c>
       <c r="G1104" t="n">
-        <v>1.07072019577026</v>
+        <v>1.07072007656097</v>
       </c>
       <c r="H1104" t="n">
         <v>5553</v>
@@ -32443,7 +32443,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1106" t="n">
-        <v>1.04712069034576</v>
+        <v>1.04712080955505</v>
       </c>
       <c r="H1106" t="n">
         <v>11729</v>
@@ -32559,7 +32559,7 @@
         <v>1.25279998779297</v>
       </c>
       <c r="G1110" t="n">
-        <v>0.978979825973511</v>
+        <v>0.978979647159576</v>
       </c>
       <c r="H1110" t="n">
         <v>24524</v>
@@ -32588,7 +32588,7 @@
         <v>1.24500000476837</v>
       </c>
       <c r="G1111" t="n">
-        <v>0.972884654998779</v>
+        <v>0.97288453578949</v>
       </c>
       <c r="H1111" t="n">
         <v>16126</v>
@@ -32646,7 +32646,7 @@
         <v>1.23800003528595</v>
       </c>
       <c r="G1113" t="n">
-        <v>0.967414498329163</v>
+        <v>0.967414557933807</v>
       </c>
       <c r="H1113" t="n">
         <v>18476</v>
@@ -32704,7 +32704,7 @@
         <v>1.25</v>
       </c>
       <c r="G1115" t="n">
-        <v>0.976791739463806</v>
+        <v>0.976791679859161</v>
       </c>
       <c r="H1115" t="n">
         <v>34094</v>
@@ -32733,7 +32733,7 @@
         <v>1.29779994487762</v>
       </c>
       <c r="G1116" t="n">
-        <v>1.01414406299591</v>
+        <v>1.0141441822052</v>
       </c>
       <c r="H1116" t="n">
         <v>37261</v>
@@ -32849,7 +32849,7 @@
         <v>1.2791999578476</v>
       </c>
       <c r="G1120" t="n">
-        <v>0.999609649181366</v>
+        <v>0.999609589576721</v>
       </c>
       <c r="H1120" t="n">
         <v>25760</v>
@@ -32878,7 +32878,7 @@
         <v>1.2771999835968</v>
       </c>
       <c r="G1121" t="n">
-        <v>0.99804675579071</v>
+        <v>0.998046696186066</v>
       </c>
       <c r="H1121" t="n">
         <v>64712</v>
@@ -32907,7 +32907,7 @@
         <v>1.33940005302429</v>
       </c>
       <c r="G1122" t="n">
-        <v>1.04665184020996</v>
+        <v>1.04665207862854</v>
       </c>
       <c r="H1122" t="n">
         <v>68249</v>
@@ -33023,7 +33023,7 @@
         <v>1.35979998111725</v>
       </c>
       <c r="G1126" t="n">
-        <v>1.06259310245514</v>
+        <v>1.06259322166443</v>
       </c>
       <c r="H1126" t="n">
         <v>19347</v>
@@ -33052,7 +33052,7 @@
         <v>1.37399995326996</v>
       </c>
       <c r="G1127" t="n">
-        <v>1.0736893415451</v>
+        <v>1.07368957996368</v>
       </c>
       <c r="H1127" t="n">
         <v>9812</v>
@@ -33081,7 +33081,7 @@
         <v>1.34979999065399</v>
       </c>
       <c r="G1128" t="n">
-        <v>1.0547788143158</v>
+        <v>1.05477893352509</v>
       </c>
       <c r="H1128" t="n">
         <v>30907</v>
@@ -33110,7 +33110,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G1129" t="n">
-        <v>1.03149211406708</v>
+        <v>1.03149223327637</v>
       </c>
       <c r="H1129" t="n">
         <v>23471</v>
@@ -33197,7 +33197,7 @@
         <v>1.32280004024506</v>
       </c>
       <c r="G1132" t="n">
-        <v>1.03368020057678</v>
+        <v>1.03368008136749</v>
       </c>
       <c r="H1132" t="n">
         <v>4792</v>
@@ -33255,7 +33255,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1134" t="n">
-        <v>1.04712069034576</v>
+        <v>1.04712080955505</v>
       </c>
       <c r="H1134" t="n">
         <v>6000</v>
@@ -33284,7 +33284,7 @@
         <v>1.2960000038147</v>
       </c>
       <c r="G1135" t="n">
-        <v>1.01273775100708</v>
+        <v>1.01273763179779</v>
       </c>
       <c r="H1135" t="n">
         <v>2329</v>
@@ -33313,7 +33313,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G1136" t="n">
-        <v>1.03149211406708</v>
+        <v>1.03149223327637</v>
       </c>
       <c r="H1136" t="n">
         <v>3100</v>
@@ -33400,7 +33400,7 @@
         <v>1.29779994487762</v>
       </c>
       <c r="G1139" t="n">
-        <v>1.01414406299591</v>
+        <v>1.0141441822052</v>
       </c>
       <c r="H1139" t="n">
         <v>8928</v>
@@ -33429,7 +33429,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1140" t="n">
-        <v>1.03930628299713</v>
+        <v>1.03930652141571</v>
       </c>
       <c r="H1140" t="n">
         <v>4250</v>
@@ -33487,7 +33487,7 @@
         <v>1.29200005531311</v>
       </c>
       <c r="G1142" t="n">
-        <v>1.00961208343506</v>
+        <v>1.00961196422577</v>
       </c>
       <c r="H1142" t="n">
         <v>1000</v>
@@ -33574,7 +33574,7 @@
         <v>1.28260004520416</v>
       </c>
       <c r="G1145" t="n">
-        <v>1.00226652622223</v>
+        <v>1.00226640701294</v>
       </c>
       <c r="H1145" t="n">
         <v>44531</v>
@@ -33603,7 +33603,7 @@
         <v>1.3257999420166</v>
       </c>
       <c r="G1146" t="n">
-        <v>1.03602433204651</v>
+        <v>1.0360244512558</v>
       </c>
       <c r="H1146" t="n">
         <v>10539</v>
@@ -33632,7 +33632,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1147" t="n">
-        <v>0.992420494556427</v>
+        <v>0.992420375347137</v>
       </c>
       <c r="H1147" t="n">
         <v>5704</v>
@@ -33661,7 +33661,7 @@
         <v>1.26499998569489</v>
       </c>
       <c r="G1148" t="n">
-        <v>0.988513171672821</v>
+        <v>0.988513231277466</v>
       </c>
       <c r="H1148" t="n">
         <v>1022</v>
@@ -33690,7 +33690,7 @@
         <v>1.26240003108978</v>
       </c>
       <c r="G1149" t="n">
-        <v>0.986481547355652</v>
+        <v>0.986481666564941</v>
       </c>
       <c r="H1149" t="n">
         <v>8000</v>
@@ -33719,7 +33719,7 @@
         <v>1.29779994487762</v>
       </c>
       <c r="G1150" t="n">
-        <v>1.01414406299591</v>
+        <v>1.0141441822052</v>
       </c>
       <c r="H1150" t="n">
         <v>16478</v>
@@ -33806,7 +33806,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1153" t="n">
-        <v>0.992420494556427</v>
+        <v>0.992420375347137</v>
       </c>
       <c r="H1153" t="n">
         <v>2410</v>
@@ -33835,7 +33835,7 @@
         <v>1.25440001487732</v>
       </c>
       <c r="G1154" t="n">
-        <v>0.980230093002319</v>
+        <v>0.980230033397675</v>
       </c>
       <c r="H1154" t="n">
         <v>5500</v>
@@ -33893,7 +33893,7 @@
         <v>1.26199996471405</v>
       </c>
       <c r="G1156" t="n">
-        <v>0.98616898059845</v>
+        <v>0.98616886138916</v>
       </c>
       <c r="H1156" t="n">
         <v>9776</v>
@@ -33951,7 +33951,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G1158" t="n">
-        <v>1.03149211406708</v>
+        <v>1.03149223327637</v>
       </c>
       <c r="H1158" t="n">
         <v>25837</v>
@@ -34067,7 +34067,7 @@
         <v>1.29980003833771</v>
       </c>
       <c r="G1162" t="n">
-        <v>1.01570725440979</v>
+        <v>1.0157071352005</v>
       </c>
       <c r="H1162" t="n">
         <v>16940</v>
@@ -34096,7 +34096,7 @@
         <v>1.23080003261566</v>
       </c>
       <c r="G1163" t="n">
-        <v>0.961788177490234</v>
+        <v>0.961788296699524</v>
       </c>
       <c r="H1163" t="n">
         <v>35956</v>
@@ -34154,7 +34154,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1165" t="n">
-        <v>0.992420494556427</v>
+        <v>0.992420375347137</v>
       </c>
       <c r="H1165" t="n">
         <v>10014</v>
@@ -34183,7 +34183,7 @@
         <v>1.27900004386902</v>
       </c>
       <c r="G1166" t="n">
-        <v>0.99945330619812</v>
+        <v>0.99945342540741</v>
       </c>
       <c r="H1166" t="n">
         <v>19032</v>
@@ -34212,7 +34212,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1167" t="n">
-        <v>0.992420494556427</v>
+        <v>0.992420375347137</v>
       </c>
       <c r="H1167" t="n">
         <v>18852</v>
@@ -34270,7 +34270,7 @@
         <v>1.25</v>
       </c>
       <c r="G1169" t="n">
-        <v>0.976791739463806</v>
+        <v>0.976791679859161</v>
       </c>
       <c r="H1169" t="n">
         <v>7000</v>
@@ -34299,7 +34299,7 @@
         <v>1.25</v>
       </c>
       <c r="G1170" t="n">
-        <v>0.976791739463806</v>
+        <v>0.976791679859161</v>
       </c>
       <c r="H1170" t="n">
         <v>0</v>
@@ -34328,7 +34328,7 @@
         <v>1.24339997768402</v>
       </c>
       <c r="G1171" t="n">
-        <v>0.971634268760681</v>
+        <v>0.971634209156036</v>
       </c>
       <c r="H1171" t="n">
         <v>4563</v>
@@ -34357,7 +34357,7 @@
         <v>1.22060000896454</v>
       </c>
       <c r="G1172" t="n">
-        <v>0.95381772518158</v>
+        <v>0.953817546367645</v>
       </c>
       <c r="H1172" t="n">
         <v>2356</v>
@@ -34386,7 +34386,7 @@
         <v>1.22060000896454</v>
       </c>
       <c r="G1173" t="n">
-        <v>0.95381772518158</v>
+        <v>0.953817546367645</v>
       </c>
       <c r="H1173" t="n">
         <v>0</v>
@@ -34415,7 +34415,7 @@
         <v>1.24979996681213</v>
       </c>
       <c r="G1174" t="n">
-        <v>0.97663551568985</v>
+        <v>0.97663539648056</v>
       </c>
       <c r="H1174" t="n">
         <v>1000</v>
@@ -34444,7 +34444,7 @@
         <v>1.22200000286102</v>
       </c>
       <c r="G1175" t="n">
-        <v>0.954911589622498</v>
+        <v>0.954911530017853</v>
       </c>
       <c r="H1175" t="n">
         <v>800</v>
@@ -34502,7 +34502,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1177" t="n">
-        <v>0.953348875045776</v>
+        <v>0.953348696231842</v>
       </c>
       <c r="H1177" t="n">
         <v>1300</v>
@@ -34531,7 +34531,7 @@
         <v>1.23479998111725</v>
       </c>
       <c r="G1178" t="n">
-        <v>0.964913964271545</v>
+        <v>0.964913904666901</v>
       </c>
       <c r="H1178" t="n">
         <v>5677</v>
@@ -34589,7 +34589,7 @@
         <v>1.19500005245209</v>
       </c>
       <c r="G1180" t="n">
-        <v>0.933812916278839</v>
+        <v>0.933812856674194</v>
       </c>
       <c r="H1180" t="n">
         <v>1588</v>
@@ -34618,7 +34618,7 @@
         <v>1.23580002784729</v>
       </c>
       <c r="G1181" t="n">
-        <v>0.965695381164551</v>
+        <v>0.96569550037384</v>
       </c>
       <c r="H1181" t="n">
         <v>2300</v>
@@ -34647,7 +34647,7 @@
         <v>1.24399995803833</v>
       </c>
       <c r="G1182" t="n">
-        <v>0.972103118896484</v>
+        <v>0.972103238105774</v>
       </c>
       <c r="H1182" t="n">
         <v>2300</v>
@@ -34676,7 +34676,7 @@
         <v>1.24399995803833</v>
       </c>
       <c r="G1183" t="n">
-        <v>0.972103118896484</v>
+        <v>0.972103238105774</v>
       </c>
       <c r="H1183" t="n">
         <v>1000</v>
@@ -34763,7 +34763,7 @@
         <v>1.20899999141693</v>
       </c>
       <c r="G1186" t="n">
-        <v>0.944752931594849</v>
+        <v>0.944753050804138</v>
       </c>
       <c r="H1186" t="n">
         <v>8300</v>
@@ -34792,7 +34792,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1187" t="n">
-        <v>0.953348875045776</v>
+        <v>0.953348696231842</v>
       </c>
       <c r="H1187" t="n">
         <v>9105</v>
@@ -34821,7 +34821,7 @@
         <v>1.20019996166229</v>
       </c>
       <c r="G1188" t="n">
-        <v>0.937876343727112</v>
+        <v>0.937876284122467</v>
       </c>
       <c r="H1188" t="n">
         <v>10090</v>
@@ -34879,7 +34879,7 @@
         <v>1.26979994773865</v>
       </c>
       <c r="G1190" t="n">
-        <v>0.992264091968536</v>
+        <v>0.992264151573181</v>
       </c>
       <c r="H1190" t="n">
         <v>2250</v>
@@ -34908,7 +34908,7 @@
         <v>1.23959994316101</v>
       </c>
       <c r="G1191" t="n">
-        <v>0.968664884567261</v>
+        <v>0.968664765357971</v>
       </c>
       <c r="H1191" t="n">
         <v>1101</v>
@@ -34937,7 +34937,7 @@
         <v>1.24979996681213</v>
       </c>
       <c r="G1192" t="n">
-        <v>0.97663551568985</v>
+        <v>0.97663539648056</v>
       </c>
       <c r="H1192" t="n">
         <v>7471</v>
@@ -34966,7 +34966,7 @@
         <v>1.21319997310638</v>
       </c>
       <c r="G1193" t="n">
-        <v>0.948035001754761</v>
+        <v>0.948034942150116</v>
       </c>
       <c r="H1193" t="n">
         <v>5835</v>
@@ -34995,7 +34995,7 @@
         <v>1.22800004482269</v>
       </c>
       <c r="G1194" t="n">
-        <v>0.959600210189819</v>
+        <v>0.959600269794464</v>
       </c>
       <c r="H1194" t="n">
         <v>24707</v>
@@ -35024,7 +35024,7 @@
         <v>1.24279999732971</v>
       </c>
       <c r="G1195" t="n">
-        <v>0.971165418624878</v>
+        <v>0.971165359020233</v>
       </c>
       <c r="H1195" t="n">
         <v>23798</v>
@@ -35053,7 +35053,7 @@
         <v>1.24199998378754</v>
       </c>
       <c r="G1196" t="n">
-        <v>0.970540344715118</v>
+        <v>0.970540285110474</v>
       </c>
       <c r="H1196" t="n">
         <v>22960</v>
@@ -35082,7 +35082,7 @@
         <v>1.24399995803833</v>
       </c>
       <c r="G1197" t="n">
-        <v>0.972103118896484</v>
+        <v>0.972103238105774</v>
       </c>
       <c r="H1197" t="n">
         <v>28501</v>
@@ -35169,7 +35169,7 @@
         <v>1.19120001792908</v>
       </c>
       <c r="G1200" t="n">
-        <v>0.930843353271484</v>
+        <v>0.930843591690063</v>
       </c>
       <c r="H1200" t="n">
         <v>13624</v>
@@ -35198,7 +35198,7 @@
         <v>1.19120001792908</v>
       </c>
       <c r="G1201" t="n">
-        <v>0.930843353271484</v>
+        <v>0.930843591690063</v>
       </c>
       <c r="H1201" t="n">
         <v>0</v>
@@ -35227,7 +35227,7 @@
         <v>1.22940003871918</v>
       </c>
       <c r="G1202" t="n">
-        <v>0.960694134235382</v>
+        <v>0.960694313049316</v>
       </c>
       <c r="H1202" t="n">
         <v>930</v>
@@ -35256,7 +35256,7 @@
         <v>1.19140005111694</v>
       </c>
       <c r="G1203" t="n">
-        <v>0.93099981546402</v>
+        <v>0.930999875068665</v>
       </c>
       <c r="H1203" t="n">
         <v>520</v>
@@ -35285,7 +35285,7 @@
         <v>1.22979998588562</v>
       </c>
       <c r="G1204" t="n">
-        <v>0.961006641387939</v>
+        <v>0.961006820201874</v>
       </c>
       <c r="H1204" t="n">
         <v>4250</v>
@@ -35314,7 +35314,7 @@
         <v>1.24199998378754</v>
       </c>
       <c r="G1205" t="n">
-        <v>0.970540344715118</v>
+        <v>0.970540285110474</v>
       </c>
       <c r="H1205" t="n">
         <v>5811</v>
@@ -35401,7 +35401,7 @@
         <v>1.19500005245209</v>
       </c>
       <c r="G1208" t="n">
-        <v>0.933812916278839</v>
+        <v>0.933812856674194</v>
       </c>
       <c r="H1208" t="n">
         <v>1086</v>
@@ -35430,7 +35430,7 @@
         <v>1.19500005245209</v>
       </c>
       <c r="G1209" t="n">
-        <v>0.933812916278839</v>
+        <v>0.933812856674194</v>
       </c>
       <c r="H1209" t="n">
         <v>7175</v>
@@ -35459,7 +35459,7 @@
         <v>1.19900000095367</v>
       </c>
       <c r="G1210" t="n">
-        <v>0.936938643455505</v>
+        <v>0.93693870306015</v>
       </c>
       <c r="H1210" t="n">
         <v>3</v>
@@ -35633,7 +35633,7 @@
         <v>1.26579999923706</v>
       </c>
       <c r="G1216" t="n">
-        <v>0.98913836479187</v>
+        <v>0.98913848400116</v>
       </c>
       <c r="H1216" t="n">
         <v>35063</v>
@@ -35662,7 +35662,7 @@
         <v>1.26540005207062</v>
       </c>
       <c r="G1217" t="n">
-        <v>0.988825857639313</v>
+        <v>0.988825917243958</v>
       </c>
       <c r="H1217" t="n">
         <v>20941</v>
@@ -35691,7 +35691,7 @@
         <v>1.24020004272461</v>
       </c>
       <c r="G1218" t="n">
-        <v>0.969133734703064</v>
+        <v>0.969133794307709</v>
       </c>
       <c r="H1218" t="n">
         <v>4530</v>
@@ -35807,7 +35807,7 @@
         <v>1.22599995136261</v>
       </c>
       <c r="G1222" t="n">
-        <v>0.958037495613098</v>
+        <v>0.958037316799164</v>
       </c>
       <c r="H1222" t="n">
         <v>119</v>
@@ -35836,7 +35836,7 @@
         <v>1.22599995136261</v>
       </c>
       <c r="G1223" t="n">
-        <v>0.958037495613098</v>
+        <v>0.958037316799164</v>
       </c>
       <c r="H1223" t="n">
         <v>0</v>
@@ -35865,7 +35865,7 @@
         <v>1.22599995136261</v>
       </c>
       <c r="G1224" t="n">
-        <v>0.958037495613098</v>
+        <v>0.958037316799164</v>
       </c>
       <c r="H1224" t="n">
         <v>0</v>
@@ -35923,7 +35923,7 @@
         <v>1.25</v>
       </c>
       <c r="G1226" t="n">
-        <v>0.976791739463806</v>
+        <v>0.976791679859161</v>
       </c>
       <c r="H1226" t="n">
         <v>370</v>
@@ -35952,7 +35952,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1227" t="n">
-        <v>0.9377201795578</v>
+        <v>0.937720060348511</v>
       </c>
       <c r="H1227" t="n">
         <v>6525</v>
@@ -35981,7 +35981,7 @@
         <v>1.17519998550415</v>
       </c>
       <c r="G1228" t="n">
-        <v>0.918340563774109</v>
+        <v>0.918340504169464</v>
       </c>
       <c r="H1228" t="n">
         <v>8221</v>
@@ -36010,7 +36010,7 @@
         <v>1.192999958992</v>
       </c>
       <c r="G1229" t="n">
-        <v>0.932249963283539</v>
+        <v>0.932250022888184</v>
       </c>
       <c r="H1229" t="n">
         <v>712</v>
@@ -36097,7 +36097,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G1232" t="n">
-        <v>0.961163103580475</v>
+        <v>0.96116304397583</v>
       </c>
       <c r="H1232" t="n">
         <v>6056</v>
@@ -36184,7 +36184,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G1235" t="n">
-        <v>0.961163103580475</v>
+        <v>0.96116304397583</v>
       </c>
       <c r="H1235" t="n">
         <v>16103</v>
@@ -36213,7 +36213,7 @@
         <v>1.19799995422363</v>
       </c>
       <c r="G1236" t="n">
-        <v>0.93615710735321</v>
+        <v>0.9361572265625</v>
       </c>
       <c r="H1236" t="n">
         <v>37918</v>
@@ -36242,7 +36242,7 @@
         <v>1.23800003528595</v>
       </c>
       <c r="G1237" t="n">
-        <v>0.967414498329163</v>
+        <v>0.967414557933807</v>
       </c>
       <c r="H1237" t="n">
         <v>7311</v>
@@ -36271,7 +36271,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1238" t="n">
-        <v>0.953348875045776</v>
+        <v>0.953348696231842</v>
       </c>
       <c r="H1238" t="n">
         <v>3720</v>
@@ -36300,7 +36300,7 @@
         <v>1.26800000667572</v>
       </c>
       <c r="G1239" t="n">
-        <v>0.990857481956482</v>
+        <v>0.990857541561127</v>
       </c>
       <c r="H1239" t="n">
         <v>129144</v>
@@ -36329,7 +36329,7 @@
         <v>1.3095999956131</v>
       </c>
       <c r="G1240" t="n">
-        <v>1.02336525917053</v>
+        <v>1.02336513996124</v>
       </c>
       <c r="H1240" t="n">
         <v>78316</v>
@@ -36358,7 +36358,7 @@
         <v>1.27320003509521</v>
       </c>
       <c r="G1241" t="n">
-        <v>0.994921028614044</v>
+        <v>0.994921088218689</v>
       </c>
       <c r="H1241" t="n">
         <v>41792</v>
@@ -36387,7 +36387,7 @@
         <v>1.27320003509521</v>
       </c>
       <c r="G1242" t="n">
-        <v>0.994921028614044</v>
+        <v>0.994921088218689</v>
       </c>
       <c r="H1242" t="n">
         <v>13700</v>
@@ -36445,7 +36445,7 @@
         <v>1.26639997959137</v>
       </c>
       <c r="G1244" t="n">
-        <v>0.989607334136963</v>
+        <v>0.989607214927673</v>
       </c>
       <c r="H1244" t="n">
         <v>32132</v>
@@ -36474,7 +36474,7 @@
         <v>1.32840001583099</v>
       </c>
       <c r="G1245" t="n">
-        <v>1.03805613517761</v>
+        <v>1.0380562543869</v>
       </c>
       <c r="H1245" t="n">
         <v>67169</v>
@@ -36561,7 +36561,7 @@
         <v>1.61300003528595</v>
       </c>
       <c r="G1248" t="n">
-        <v>1.26045203208923</v>
+        <v>1.26045215129852</v>
       </c>
       <c r="H1248" t="n">
         <v>112579</v>
@@ -36590,7 +36590,7 @@
         <v>1.59200000762939</v>
       </c>
       <c r="G1249" t="n">
-        <v>1.24404191970825</v>
+        <v>1.24404203891754</v>
       </c>
       <c r="H1249" t="n">
         <v>77714</v>
@@ -36619,7 +36619,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G1250" t="n">
-        <v>1.3362512588501</v>
+        <v>1.33625113964081</v>
       </c>
       <c r="H1250" t="n">
         <v>95910</v>
@@ -36648,7 +36648,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G1251" t="n">
-        <v>1.31280815601349</v>
+        <v>1.3128080368042</v>
       </c>
       <c r="H1251" t="n">
         <v>57237</v>
@@ -36706,7 +36706,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G1253" t="n">
-        <v>1.31280815601349</v>
+        <v>1.3128080368042</v>
       </c>
       <c r="H1253" t="n">
         <v>6137</v>
@@ -36764,7 +36764,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G1255" t="n">
-        <v>1.31280815601349</v>
+        <v>1.3128080368042</v>
       </c>
       <c r="H1255" t="n">
         <v>9259</v>
@@ -36793,7 +36793,7 @@
         <v>1.72060000896454</v>
       </c>
       <c r="G1256" t="n">
-        <v>1.34453439712524</v>
+        <v>1.34453427791595</v>
       </c>
       <c r="H1256" t="n">
         <v>88356</v>
@@ -36851,7 +36851,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G1258" t="n">
-        <v>1.41439437866211</v>
+        <v>1.4143944978714</v>
       </c>
       <c r="H1258" t="n">
         <v>159971</v>
@@ -36880,7 +36880,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G1259" t="n">
-        <v>1.32843685150146</v>
+        <v>1.32843673229218</v>
       </c>
       <c r="H1259" t="n">
         <v>147479</v>
@@ -36967,7 +36967,7 @@
         <v>1.74119997024536</v>
       </c>
       <c r="G1262" t="n">
-        <v>1.36063170433044</v>
+        <v>1.36063182353973</v>
       </c>
       <c r="H1262" t="n">
         <v>7273</v>
@@ -36996,7 +36996,7 @@
         <v>1.7208000421524</v>
       </c>
       <c r="G1263" t="n">
-        <v>1.34469068050385</v>
+        <v>1.34469056129456</v>
       </c>
       <c r="H1263" t="n">
         <v>7468</v>
@@ -37025,7 +37025,7 @@
         <v>1.71019995212555</v>
       </c>
       <c r="G1264" t="n">
-        <v>1.33640742301941</v>
+        <v>1.33640730381012</v>
       </c>
       <c r="H1264" t="n">
         <v>18672</v>
@@ -37083,7 +37083,7 @@
         <v>1.72940003871918</v>
       </c>
       <c r="G1266" t="n">
-        <v>1.35141086578369</v>
+        <v>1.35141098499298</v>
       </c>
       <c r="H1266" t="n">
         <v>28267</v>
@@ -37112,7 +37112,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G1267" t="n">
-        <v>1.39095139503479</v>
+        <v>1.39095151424408</v>
       </c>
       <c r="H1267" t="n">
         <v>141202</v>
@@ -37170,7 +37170,7 @@
         <v>1.74979996681213</v>
       </c>
       <c r="G1269" t="n">
-        <v>1.46478509902954</v>
+        <v>1.46478521823883</v>
       </c>
       <c r="H1269" t="n">
         <v>33596</v>
@@ -37199,7 +37199,7 @@
         <v>1.73800003528595</v>
       </c>
       <c r="G1270" t="n">
-        <v>1.45490705966949</v>
+        <v>1.45490729808807</v>
       </c>
       <c r="H1270" t="n">
         <v>14911</v>
@@ -37489,7 +37489,7 @@
         <v>1.66600000858307</v>
       </c>
       <c r="G1280" t="n">
-        <v>1.39463472366333</v>
+        <v>1.39463484287262</v>
       </c>
       <c r="H1280" t="n">
         <v>32262</v>
@@ -37605,7 +37605,7 @@
         <v>1.66939997673035</v>
       </c>
       <c r="G1284" t="n">
-        <v>1.39748084545135</v>
+        <v>1.39748108386993</v>
       </c>
       <c r="H1284" t="n">
         <v>12668</v>
@@ -37692,7 +37692,7 @@
         <v>1.6088000535965</v>
       </c>
       <c r="G1287" t="n">
-        <v>1.34675180912018</v>
+        <v>1.34675192832947</v>
       </c>
       <c r="H1287" t="n">
         <v>15942</v>
@@ -37750,7 +37750,7 @@
         <v>1.62999999523163</v>
       </c>
       <c r="G1289" t="n">
-        <v>1.36449861526489</v>
+        <v>1.36449873447418</v>
       </c>
       <c r="H1289" t="n">
         <v>57500</v>
@@ -37837,7 +37837,7 @@
         <v>1.60599994659424</v>
       </c>
       <c r="G1292" t="n">
-        <v>1.34440791606903</v>
+        <v>1.34440779685974</v>
       </c>
       <c r="H1292" t="n">
         <v>20464</v>
@@ -37924,7 +37924,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G1295" t="n">
-        <v>1.40635442733765</v>
+        <v>1.40635454654694</v>
       </c>
       <c r="H1295" t="n">
         <v>92320</v>
@@ -38011,7 +38011,7 @@
         <v>1.75419998168945</v>
       </c>
       <c r="G1298" t="n">
-        <v>1.46846842765808</v>
+        <v>1.46846830844879</v>
       </c>
       <c r="H1298" t="n">
         <v>40624</v>
@@ -38069,7 +38069,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G1300" t="n">
-        <v>1.49006593227386</v>
+        <v>1.49006605148315</v>
       </c>
       <c r="H1300" t="n">
         <v>15871</v>
@@ -38098,7 +38098,7 @@
         <v>1.80540001392365</v>
       </c>
       <c r="G1301" t="n">
-        <v>1.51132881641388</v>
+        <v>1.51132869720459</v>
       </c>
       <c r="H1301" t="n">
         <v>61944</v>
@@ -38214,7 +38214,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G1305" t="n">
-        <v>1.56540656089783</v>
+        <v>1.56540632247925</v>
       </c>
       <c r="H1305" t="n">
         <v>90063</v>
@@ -38243,7 +38243,7 @@
         <v>1.83259999752045</v>
       </c>
       <c r="G1306" t="n">
-        <v>1.53409838676453</v>
+        <v>1.53409814834595</v>
       </c>
       <c r="H1306" t="n">
         <v>15504</v>
@@ -38272,7 +38272,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G1307" t="n">
-        <v>1.57377755641937</v>
+        <v>1.57377743721008</v>
       </c>
       <c r="H1307" t="n">
         <v>25764</v>
@@ -38301,7 +38301,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G1308" t="n">
-        <v>1.57377755641937</v>
+        <v>1.57377743721008</v>
       </c>
       <c r="H1308" t="n">
         <v>6508</v>
@@ -38330,7 +38330,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G1309" t="n">
-        <v>1.56540656089783</v>
+        <v>1.56540632247925</v>
       </c>
       <c r="H1309" t="n">
         <v>5381</v>
@@ -38359,7 +38359,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G1310" t="n">
-        <v>1.56540656089783</v>
+        <v>1.56540632247925</v>
       </c>
       <c r="H1310" t="n">
         <v>6800</v>
@@ -38446,7 +38446,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G1313" t="n">
-        <v>1.57377755641937</v>
+        <v>1.57377743721008</v>
       </c>
       <c r="H1313" t="n">
         <v>4995</v>
@@ -38504,7 +38504,7 @@
         <v>1.84019994735718</v>
       </c>
       <c r="G1315" t="n">
-        <v>1.54046046733856</v>
+        <v>1.54046034812927</v>
       </c>
       <c r="H1315" t="n">
         <v>5051</v>
@@ -38533,7 +38533,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G1316" t="n">
-        <v>1.57377755641937</v>
+        <v>1.57377743721008</v>
       </c>
       <c r="H1316" t="n">
         <v>16667</v>
@@ -38881,7 +38881,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G1328" t="n">
-        <v>1.64074695110321</v>
+        <v>1.64074683189392</v>
       </c>
       <c r="H1328" t="n">
         <v>20785</v>
@@ -38939,7 +38939,7 @@
         <v>1.91499996185303</v>
       </c>
       <c r="G1330" t="n">
-        <v>1.60307669639587</v>
+        <v>1.60307657718658</v>
       </c>
       <c r="H1330" t="n">
         <v>7584</v>
@@ -39113,7 +39113,7 @@
         <v>1.91499996185303</v>
       </c>
       <c r="G1336" t="n">
-        <v>1.60307669639587</v>
+        <v>1.60307657718658</v>
       </c>
       <c r="H1336" t="n">
         <v>4148</v>
@@ -39142,7 +39142,7 @@
         <v>1.91499996185303</v>
       </c>
       <c r="G1337" t="n">
-        <v>1.60307669639587</v>
+        <v>1.60307657718658</v>
       </c>
       <c r="H1337" t="n">
         <v>6260</v>
@@ -39200,7 +39200,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G1339" t="n">
-        <v>1.607262134552</v>
+        <v>1.60726225376129</v>
       </c>
       <c r="H1339" t="n">
         <v>1005</v>
@@ -39229,7 +39229,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G1340" t="n">
-        <v>1.607262134552</v>
+        <v>1.60726225376129</v>
       </c>
       <c r="H1340" t="n">
         <v>120</v>
@@ -39258,7 +39258,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G1341" t="n">
-        <v>1.607262134552</v>
+        <v>1.60726225376129</v>
       </c>
       <c r="H1341" t="n">
         <v>20929</v>
@@ -39316,7 +39316,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G1343" t="n">
-        <v>1.607262134552</v>
+        <v>1.60726225376129</v>
       </c>
       <c r="H1343" t="n">
         <v>14161</v>
@@ -39519,7 +39519,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G1350" t="n">
-        <v>1.607262134552</v>
+        <v>1.60726225376129</v>
       </c>
       <c r="H1350" t="n">
         <v>120787</v>
@@ -39548,7 +39548,7 @@
         <v>1.91499996185303</v>
       </c>
       <c r="G1351" t="n">
-        <v>1.60307669639587</v>
+        <v>1.60307657718658</v>
       </c>
       <c r="H1351" t="n">
         <v>33983</v>
@@ -39577,7 +39577,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G1352" t="n">
-        <v>1.59889101982117</v>
+        <v>1.59889113903046</v>
       </c>
       <c r="H1352" t="n">
         <v>23824</v>
@@ -39606,7 +39606,7 @@
         <v>1.85500001907349</v>
       </c>
       <c r="G1353" t="n">
-        <v>1.55284976959229</v>
+        <v>1.552849650383</v>
       </c>
       <c r="H1353" t="n">
         <v>21990</v>
@@ -39635,7 +39635,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G1354" t="n">
-        <v>1.59051990509033</v>
+        <v>1.59051978588104</v>
       </c>
       <c r="H1354" t="n">
         <v>15319</v>
@@ -39693,7 +39693,7 @@
         <v>1.88499999046326</v>
       </c>
       <c r="G1356" t="n">
-        <v>1.57796311378479</v>
+        <v>1.57796323299408</v>
       </c>
       <c r="H1356" t="n">
         <v>10700</v>
@@ -39722,7 +39722,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G1357" t="n">
-        <v>1.5570353269577</v>
+        <v>1.55703544616699</v>
       </c>
       <c r="H1357" t="n">
         <v>10646</v>
@@ -39780,7 +39780,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G1359" t="n">
-        <v>1.56540656089783</v>
+        <v>1.56540632247925</v>
       </c>
       <c r="H1359" t="n">
         <v>4850</v>
@@ -39809,7 +39809,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G1360" t="n">
-        <v>1.59051990509033</v>
+        <v>1.59051978588104</v>
       </c>
       <c r="H1360" t="n">
         <v>13059</v>
@@ -39838,7 +39838,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G1361" t="n">
-        <v>1.607262134552</v>
+        <v>1.60726225376129</v>
       </c>
       <c r="H1361" t="n">
         <v>16896</v>
@@ -39867,7 +39867,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G1362" t="n">
-        <v>1.59051990509033</v>
+        <v>1.59051978588104</v>
       </c>
       <c r="H1362" t="n">
         <v>7070</v>
@@ -39896,7 +39896,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G1363" t="n">
-        <v>1.58214867115021</v>
+        <v>1.5821487903595</v>
       </c>
       <c r="H1363" t="n">
         <v>20795</v>
@@ -39925,7 +39925,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G1364" t="n">
-        <v>1.59051990509033</v>
+        <v>1.59051978588104</v>
       </c>
       <c r="H1364" t="n">
         <v>4035</v>
@@ -39954,7 +39954,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G1365" t="n">
-        <v>1.59051990509033</v>
+        <v>1.59051978588104</v>
       </c>
       <c r="H1365" t="n">
         <v>1022</v>
@@ -39983,7 +39983,7 @@
         <v>1.85500001907349</v>
       </c>
       <c r="G1366" t="n">
-        <v>1.55284976959229</v>
+        <v>1.552849650383</v>
       </c>
       <c r="H1366" t="n">
         <v>32969</v>
@@ -40041,7 +40041,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G1368" t="n">
-        <v>1.59051990509033</v>
+        <v>1.59051978588104</v>
       </c>
       <c r="H1368" t="n">
         <v>25050</v>
@@ -40070,7 +40070,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G1369" t="n">
-        <v>1.5570353269577</v>
+        <v>1.55703544616699</v>
       </c>
       <c r="H1369" t="n">
         <v>6264</v>
@@ -40128,7 +40128,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G1371" t="n">
-        <v>1.5570353269577</v>
+        <v>1.55703544616699</v>
       </c>
       <c r="H1371" t="n">
         <v>5678</v>
@@ -40186,7 +40186,7 @@
         <v>1.83500003814697</v>
       </c>
       <c r="G1373" t="n">
-        <v>1.53610730171204</v>
+        <v>1.53610754013062</v>
       </c>
       <c r="H1373" t="n">
         <v>6413</v>
@@ -40244,7 +40244,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G1375" t="n">
-        <v>1.5570353269577</v>
+        <v>1.55703544616699</v>
       </c>
       <c r="H1375" t="n">
         <v>5724</v>
@@ -40302,7 +40302,7 @@
         <v>1.86500000953674</v>
       </c>
       <c r="G1377" t="n">
-        <v>1.56122076511383</v>
+        <v>1.56122088432312</v>
       </c>
       <c r="H1377" t="n">
         <v>24781</v>
@@ -40331,7 +40331,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G1378" t="n">
-        <v>1.8249124288559</v>
+        <v>1.82491230964661</v>
       </c>
       <c r="H1378" t="n">
         <v>490339</v>
@@ -40418,7 +40418,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G1381" t="n">
-        <v>1.90862369537354</v>
+        <v>1.90862381458282</v>
       </c>
       <c r="H1381" t="n">
         <v>118880</v>
@@ -40447,7 +40447,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G1382" t="n">
-        <v>1.85839676856995</v>
+        <v>1.85839700698853</v>
       </c>
       <c r="H1382" t="n">
         <v>28667</v>
@@ -40505,7 +40505,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G1384" t="n">
-        <v>1.90025281906128</v>
+        <v>1.90025269985199</v>
       </c>
       <c r="H1384" t="n">
         <v>25190</v>
@@ -40534,7 +40534,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G1385" t="n">
-        <v>1.85839676856995</v>
+        <v>1.85839700698853</v>
       </c>
       <c r="H1385" t="n">
         <v>27190</v>
@@ -40563,7 +40563,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G1386" t="n">
-        <v>1.85839676856995</v>
+        <v>1.85839700698853</v>
       </c>
       <c r="H1386" t="n">
         <v>24834</v>
@@ -40621,7 +40621,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G1388" t="n">
-        <v>1.81654131412506</v>
+        <v>1.81654119491577</v>
       </c>
       <c r="H1388" t="n">
         <v>31320</v>
@@ -40650,7 +40650,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G1389" t="n">
-        <v>1.78305661678314</v>
+        <v>1.78305649757385</v>
       </c>
       <c r="H1389" t="n">
         <v>7396</v>
@@ -40679,7 +40679,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G1390" t="n">
-        <v>1.8249124288559</v>
+        <v>1.82491230964661</v>
       </c>
       <c r="H1390" t="n">
         <v>20518</v>
@@ -40795,7 +40795,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G1394" t="n">
-        <v>1.78305661678314</v>
+        <v>1.78305649757385</v>
       </c>
       <c r="H1394" t="n">
         <v>6872</v>
@@ -40824,7 +40824,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G1395" t="n">
-        <v>1.79142773151398</v>
+        <v>1.79142785072327</v>
       </c>
       <c r="H1395" t="n">
         <v>9872</v>
@@ -40853,7 +40853,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1396" t="n">
-        <v>1.75794303417206</v>
+        <v>1.75794279575348</v>
       </c>
       <c r="H1396" t="n">
         <v>11946</v>
@@ -40882,7 +40882,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1397" t="n">
-        <v>1.75794303417206</v>
+        <v>1.75794279575348</v>
       </c>
       <c r="H1397" t="n">
         <v>17267</v>
@@ -40940,7 +40940,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1399" t="n">
-        <v>1.75794303417206</v>
+        <v>1.75794279575348</v>
       </c>
       <c r="H1399" t="n">
         <v>13274</v>
@@ -40969,7 +40969,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G1400" t="n">
-        <v>1.74120056629181</v>
+        <v>1.7412006855011</v>
       </c>
       <c r="H1400" t="n">
         <v>5207</v>
@@ -40998,7 +40998,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G1401" t="n">
-        <v>1.74120056629181</v>
+        <v>1.7412006855011</v>
       </c>
       <c r="H1401" t="n">
         <v>0</v>
@@ -41027,7 +41027,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G1402" t="n">
-        <v>1.71608710289001</v>
+        <v>1.7160872220993</v>
       </c>
       <c r="H1402" t="n">
         <v>33165</v>
@@ -41056,7 +41056,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G1403" t="n">
-        <v>1.73282957077026</v>
+        <v>1.73282945156097</v>
       </c>
       <c r="H1403" t="n">
         <v>1076</v>
@@ -41172,7 +41172,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G1407" t="n">
-        <v>1.71608710289001</v>
+        <v>1.7160872220993</v>
       </c>
       <c r="H1407" t="n">
         <v>5350</v>
@@ -41201,7 +41201,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G1408" t="n">
-        <v>1.70771598815918</v>
+        <v>1.70771610736847</v>
       </c>
       <c r="H1408" t="n">
         <v>1758</v>
@@ -41259,7 +41259,7 @@
         <v>1.9650000333786</v>
       </c>
       <c r="G1410" t="n">
-        <v>1.64493250846863</v>
+        <v>1.64493238925934</v>
       </c>
       <c r="H1410" t="n">
         <v>8674</v>
@@ -41288,7 +41288,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G1411" t="n">
-        <v>1.70771598815918</v>
+        <v>1.70771610736847</v>
       </c>
       <c r="H1411" t="n">
         <v>36540</v>
@@ -41317,7 +41317,7 @@
         <v>1.98500001430511</v>
       </c>
       <c r="G1412" t="n">
-        <v>1.6616747379303</v>
+        <v>1.66167485713959</v>
       </c>
       <c r="H1412" t="n">
         <v>10099</v>
@@ -41404,7 +41404,7 @@
         <v>1.99500000476837</v>
       </c>
       <c r="G1415" t="n">
-        <v>1.67004597187042</v>
+        <v>1.67004585266113</v>
       </c>
       <c r="H1415" t="n">
         <v>1050</v>
@@ -41549,7 +41549,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G1420" t="n">
-        <v>1.73282957077026</v>
+        <v>1.73282945156097</v>
       </c>
       <c r="H1420" t="n">
         <v>15659</v>
@@ -41636,7 +41636,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G1423" t="n">
-        <v>1.81654131412506</v>
+        <v>1.81654119491577</v>
       </c>
       <c r="H1423" t="n">
         <v>8578</v>
@@ -41665,7 +41665,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G1424" t="n">
-        <v>1.81654131412506</v>
+        <v>1.81654119491577</v>
       </c>
       <c r="H1424" t="n">
         <v>6559</v>
@@ -41694,7 +41694,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G1425" t="n">
-        <v>1.81654131412506</v>
+        <v>1.81654119491577</v>
       </c>
       <c r="H1425" t="n">
         <v>28383</v>
@@ -41723,7 +41723,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G1426" t="n">
-        <v>1.83328354358673</v>
+        <v>1.83328366279602</v>
       </c>
       <c r="H1426" t="n">
         <v>5861</v>
@@ -41752,7 +41752,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G1427" t="n">
-        <v>1.85839676856995</v>
+        <v>1.85839700698853</v>
       </c>
       <c r="H1427" t="n">
         <v>8698</v>
@@ -41781,7 +41781,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G1428" t="n">
-        <v>1.85839676856995</v>
+        <v>1.85839700698853</v>
       </c>
       <c r="H1428" t="n">
         <v>2382</v>
@@ -41810,7 +41810,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G1429" t="n">
-        <v>1.85839676856995</v>
+        <v>1.85839700698853</v>
       </c>
       <c r="H1429" t="n">
         <v>1386</v>
@@ -41839,7 +41839,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G1430" t="n">
-        <v>1.83328354358673</v>
+        <v>1.83328366279602</v>
       </c>
       <c r="H1430" t="n">
         <v>2450</v>
@@ -41897,7 +41897,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G1432" t="n">
-        <v>1.78305661678314</v>
+        <v>1.78305649757385</v>
       </c>
       <c r="H1432" t="n">
         <v>23425</v>
@@ -41926,7 +41926,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G1433" t="n">
-        <v>1.79142773151398</v>
+        <v>1.79142785072327</v>
       </c>
       <c r="H1433" t="n">
         <v>12195</v>
@@ -41955,7 +41955,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G1434" t="n">
-        <v>1.81654131412506</v>
+        <v>1.81654119491577</v>
       </c>
       <c r="H1434" t="n">
         <v>22886</v>
@@ -41984,7 +41984,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G1435" t="n">
-        <v>1.85839676856995</v>
+        <v>1.85839700698853</v>
       </c>
       <c r="H1435" t="n">
         <v>10508</v>
@@ -42013,7 +42013,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G1436" t="n">
-        <v>1.85839676856995</v>
+        <v>1.85839700698853</v>
       </c>
       <c r="H1436" t="n">
         <v>5310</v>
@@ -42071,7 +42071,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G1438" t="n">
-        <v>1.8249124288559</v>
+        <v>1.82491230964661</v>
       </c>
       <c r="H1438" t="n">
         <v>4934</v>
@@ -42129,7 +42129,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G1440" t="n">
-        <v>1.81654131412506</v>
+        <v>1.81654119491577</v>
       </c>
       <c r="H1440" t="n">
         <v>13224</v>
@@ -42158,7 +42158,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G1441" t="n">
-        <v>1.8249124288559</v>
+        <v>1.82491230964661</v>
       </c>
       <c r="H1441" t="n">
         <v>2753</v>
@@ -42216,7 +42216,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G1443" t="n">
-        <v>1.83328354358673</v>
+        <v>1.83328366279602</v>
       </c>
       <c r="H1443" t="n">
         <v>7310</v>
@@ -42245,7 +42245,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G1444" t="n">
-        <v>1.83328354358673</v>
+        <v>1.83328366279602</v>
       </c>
       <c r="H1444" t="n">
         <v>0</v>
@@ -42332,7 +42332,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G1447" t="n">
-        <v>1.79142773151398</v>
+        <v>1.79142785072327</v>
       </c>
       <c r="H1447" t="n">
         <v>1801</v>
@@ -42419,7 +42419,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G1450" t="n">
-        <v>1.78305661678314</v>
+        <v>1.78305649757385</v>
       </c>
       <c r="H1450" t="n">
         <v>39</v>
@@ -42535,7 +42535,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1454" t="n">
-        <v>1.75794303417206</v>
+        <v>1.75794279575348</v>
       </c>
       <c r="H1454" t="n">
         <v>10200</v>
@@ -42564,7 +42564,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G1455" t="n">
-        <v>1.79142773151398</v>
+        <v>1.79142785072327</v>
       </c>
       <c r="H1455" t="n">
         <v>8648</v>
@@ -42593,7 +42593,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G1456" t="n">
-        <v>1.83328354358673</v>
+        <v>1.83328366279602</v>
       </c>
       <c r="H1456" t="n">
         <v>33296</v>
@@ -42651,7 +42651,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G1458" t="n">
-        <v>1.86676812171936</v>
+        <v>1.86676800251007</v>
       </c>
       <c r="H1458" t="n">
         <v>13297</v>
@@ -42738,7 +42738,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G1461" t="n">
-        <v>1.90025281906128</v>
+        <v>1.90025269985199</v>
       </c>
       <c r="H1461" t="n">
         <v>22939</v>
@@ -42854,7 +42854,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G1465" t="n">
-        <v>2.16812992095947</v>
+        <v>2.16812968254089</v>
       </c>
       <c r="H1465" t="n">
         <v>38675</v>
@@ -42912,7 +42912,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G1467" t="n">
-        <v>2.07604718208313</v>
+        <v>2.07604694366455</v>
       </c>
       <c r="H1467" t="n">
         <v>8318</v>
@@ -42941,7 +42941,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G1468" t="n">
-        <v>2.01744890213013</v>
+        <v>2.01744914054871</v>
       </c>
       <c r="H1468" t="n">
         <v>9087</v>
@@ -42970,7 +42970,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G1469" t="n">
-        <v>2.07604718208313</v>
+        <v>2.07604694366455</v>
       </c>
       <c r="H1469" t="n">
         <v>10761</v>
@@ -43028,7 +43028,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G1471" t="n">
-        <v>2.04256224632263</v>
+        <v>2.04256248474121</v>
       </c>
       <c r="H1471" t="n">
         <v>4161</v>
@@ -43086,7 +43086,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G1473" t="n">
-        <v>2.13464498519897</v>
+        <v>2.13464522361755</v>
       </c>
       <c r="H1473" t="n">
         <v>33269</v>
@@ -43521,7 +43521,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G1488" t="n">
-        <v>2.16812992095947</v>
+        <v>2.16812968254089</v>
       </c>
       <c r="H1488" t="n">
         <v>17680</v>
@@ -43608,7 +43608,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G1491" t="n">
-        <v>2.13464498519897</v>
+        <v>2.13464522361755</v>
       </c>
       <c r="H1491" t="n">
         <v>11546</v>
@@ -43666,7 +43666,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G1493" t="n">
-        <v>2.28532576560974</v>
+        <v>2.28532600402832</v>
       </c>
       <c r="H1493" t="n">
         <v>72360</v>
@@ -43695,7 +43695,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G1494" t="n">
-        <v>2.25184154510498</v>
+        <v>2.2518413066864</v>
       </c>
       <c r="H1494" t="n">
         <v>89679</v>
@@ -43724,7 +43724,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G1495" t="n">
-        <v>2.26021265983582</v>
+        <v>2.26021242141724</v>
       </c>
       <c r="H1495" t="n">
         <v>31872</v>
@@ -43811,7 +43811,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G1498" t="n">
-        <v>2.21835660934448</v>
+        <v>2.21835684776306</v>
       </c>
       <c r="H1498" t="n">
         <v>26546</v>
@@ -43840,7 +43840,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G1499" t="n">
-        <v>2.21835660934448</v>
+        <v>2.21835684776306</v>
       </c>
       <c r="H1499" t="n">
         <v>2484</v>
@@ -43898,7 +43898,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G1501" t="n">
-        <v>2.25184154510498</v>
+        <v>2.2518413066864</v>
       </c>
       <c r="H1501" t="n">
         <v>65037</v>
@@ -43956,7 +43956,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G1503" t="n">
-        <v>2.25184154510498</v>
+        <v>2.2518413066864</v>
       </c>
       <c r="H1503" t="n">
         <v>18385</v>
@@ -43985,7 +43985,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G1504" t="n">
-        <v>2.24347019195557</v>
+        <v>2.24347043037415</v>
       </c>
       <c r="H1504" t="n">
         <v>44721</v>
@@ -44014,7 +44014,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G1505" t="n">
-        <v>2.21835660934448</v>
+        <v>2.21835684776306</v>
       </c>
       <c r="H1505" t="n">
         <v>7243</v>
@@ -44101,7 +44101,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G1508" t="n">
-        <v>2.26021265983582</v>
+        <v>2.26021242141724</v>
       </c>
       <c r="H1508" t="n">
         <v>11295</v>
@@ -44159,7 +44159,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G1510" t="n">
-        <v>2.26021265983582</v>
+        <v>2.26021242141724</v>
       </c>
       <c r="H1510" t="n">
         <v>3332</v>
@@ -44188,7 +44188,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G1511" t="n">
-        <v>2.21835660934448</v>
+        <v>2.21835684776306</v>
       </c>
       <c r="H1511" t="n">
         <v>8611</v>
@@ -44217,7 +44217,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G1512" t="n">
-        <v>2.25184154510498</v>
+        <v>2.2518413066864</v>
       </c>
       <c r="H1512" t="n">
         <v>1609</v>
@@ -44246,7 +44246,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G1513" t="n">
-        <v>2.25184154510498</v>
+        <v>2.2518413066864</v>
       </c>
       <c r="H1513" t="n">
         <v>10947</v>
@@ -44333,7 +44333,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G1516" t="n">
-        <v>2.26021265983582</v>
+        <v>2.26021242141724</v>
       </c>
       <c r="H1516" t="n">
         <v>39885</v>
@@ -44362,7 +44362,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G1517" t="n">
-        <v>2.5448317527771</v>
+        <v>2.54483199119568</v>
       </c>
       <c r="H1517" t="n">
         <v>82221</v>
@@ -44391,7 +44391,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G1518" t="n">
-        <v>2.62017250061035</v>
+        <v>2.62017226219177</v>
       </c>
       <c r="H1518" t="n">
         <v>151266</v>
@@ -44623,7 +44623,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G1526" t="n">
-        <v>3.20615339279175</v>
+        <v>3.20615315437317</v>
       </c>
       <c r="H1526" t="n">
         <v>73041</v>
@@ -44652,7 +44652,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G1527" t="n">
-        <v>3.10569953918457</v>
+        <v>3.10569930076599</v>
       </c>
       <c r="H1527" t="n">
         <v>40326</v>
@@ -44710,7 +44710,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G1529" t="n">
-        <v>3.03035879135132</v>
+        <v>3.0303590297699</v>
       </c>
       <c r="H1529" t="n">
         <v>25973</v>
@@ -44797,7 +44797,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G1532" t="n">
-        <v>2.9550187587738</v>
+        <v>2.95501852035522</v>
       </c>
       <c r="H1532" t="n">
         <v>14573</v>
@@ -44884,7 +44884,7 @@
         <v>3.5</v>
       </c>
       <c r="G1535" t="n">
-        <v>2.92990517616272</v>
+        <v>2.92990493774414</v>
       </c>
       <c r="H1535" t="n">
         <v>5651</v>
@@ -44913,7 +44913,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G1536" t="n">
-        <v>2.8964204788208</v>
+        <v>2.89642071723938</v>
       </c>
       <c r="H1536" t="n">
         <v>9495</v>
@@ -45029,7 +45029,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G1540" t="n">
-        <v>2.78759527206421</v>
+        <v>2.78759551048279</v>
       </c>
       <c r="H1540" t="n">
         <v>21833</v>
@@ -45087,7 +45087,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G1542" t="n">
-        <v>2.8964204788208</v>
+        <v>2.89642071723938</v>
       </c>
       <c r="H1542" t="n">
         <v>56699</v>
@@ -45174,7 +45174,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G1545" t="n">
-        <v>3.03873038291931</v>
+        <v>3.03873014450073</v>
       </c>
       <c r="H1545" t="n">
         <v>46478</v>
@@ -45232,7 +45232,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G1547" t="n">
-        <v>3.04710149765015</v>
+        <v>3.04710125923157</v>
       </c>
       <c r="H1547" t="n">
         <v>27597</v>
@@ -45261,7 +45261,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G1548" t="n">
-        <v>3.12244153022766</v>
+        <v>3.12244176864624</v>
       </c>
       <c r="H1548" t="n">
         <v>31587</v>
@@ -45290,7 +45290,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G1549" t="n">
-        <v>3.1894109249115</v>
+        <v>3.18941068649292</v>
       </c>
       <c r="H1549" t="n">
         <v>55680</v>
@@ -45493,7 +45493,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G1556" t="n">
-        <v>3.21806406974792</v>
+        <v>3.2180643081665</v>
       </c>
       <c r="H1556" t="n">
         <v>26348</v>
@@ -45522,7 +45522,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G1557" t="n">
-        <v>3.15767168998718</v>
+        <v>3.1576714515686</v>
       </c>
       <c r="H1557" t="n">
         <v>14643</v>
@@ -45725,7 +45725,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1564" t="n">
-        <v>3.10590624809265</v>
+        <v>3.10590648651123</v>
       </c>
       <c r="H1564" t="n">
         <v>5841</v>
@@ -45783,7 +45783,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G1566" t="n">
-        <v>2.97649383544922</v>
+        <v>2.97649359703064</v>
       </c>
       <c r="H1566" t="n">
         <v>27030</v>
@@ -46015,7 +46015,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G1574" t="n">
-        <v>2.66590309143066</v>
+        <v>2.66590285301208</v>
       </c>
       <c r="H1574" t="n">
         <v>33185</v>
@@ -46044,7 +46044,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G1575" t="n">
-        <v>2.62276554107666</v>
+        <v>2.62276530265808</v>
       </c>
       <c r="H1575" t="n">
         <v>16919</v>
@@ -46218,7 +46218,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G1581" t="n">
-        <v>3.00237631797791</v>
+        <v>3.00237607955933</v>
       </c>
       <c r="H1581" t="n">
         <v>7369</v>
@@ -46247,7 +46247,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G1582" t="n">
-        <v>2.96786618232727</v>
+        <v>2.96786594390869</v>
       </c>
       <c r="H1582" t="n">
         <v>9819</v>
@@ -46421,7 +46421,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G1588" t="n">
-        <v>3.00237631797791</v>
+        <v>3.00237607955933</v>
       </c>
       <c r="H1588" t="n">
         <v>8197</v>
@@ -46595,7 +46595,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1594" t="n">
-        <v>2.93335628509521</v>
+        <v>2.93335604667664</v>
       </c>
       <c r="H1594" t="n">
         <v>1217</v>
@@ -46624,7 +46624,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1595" t="n">
-        <v>2.93335628509521</v>
+        <v>2.93335604667664</v>
       </c>
       <c r="H1595" t="n">
         <v>2971</v>
@@ -46711,7 +46711,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1598" t="n">
-        <v>2.93335628509521</v>
+        <v>2.93335604667664</v>
       </c>
       <c r="H1598" t="n">
         <v>2090</v>
@@ -46798,7 +46798,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1601" t="n">
-        <v>2.93335628509521</v>
+        <v>2.93335604667664</v>
       </c>
       <c r="H1601" t="n">
         <v>1039</v>
@@ -46827,7 +46827,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G1602" t="n">
-        <v>2.95061111450195</v>
+        <v>2.95061135292053</v>
       </c>
       <c r="H1602" t="n">
         <v>3240</v>
@@ -47001,7 +47001,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G1608" t="n">
-        <v>2.95061111450195</v>
+        <v>2.95061135292053</v>
       </c>
       <c r="H1608" t="n">
         <v>24178</v>
@@ -47059,7 +47059,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G1610" t="n">
-        <v>3.19792699813843</v>
+        <v>3.19792723655701</v>
       </c>
       <c r="H1610" t="n">
         <v>18822</v>
@@ -47088,7 +47088,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1611" t="n">
-        <v>3.05004596710205</v>
+        <v>3.05004620552063</v>
       </c>
       <c r="H1611" t="n">
         <v>18282</v>
@@ -47117,7 +47117,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1612" t="n">
-        <v>3.05004596710205</v>
+        <v>3.05004620552063</v>
       </c>
       <c r="H1612" t="n">
         <v>6535</v>
@@ -47146,7 +47146,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1613" t="n">
-        <v>3.05004596710205</v>
+        <v>3.05004620552063</v>
       </c>
       <c r="H1613" t="n">
         <v>6560</v>
@@ -47204,7 +47204,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G1615" t="n">
-        <v>2.98534798622131</v>
+        <v>2.98534822463989</v>
       </c>
       <c r="H1615" t="n">
         <v>5371</v>
@@ -47262,7 +47262,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G1617" t="n">
-        <v>3.01307559013367</v>
+        <v>3.01307582855225</v>
       </c>
       <c r="H1617" t="n">
         <v>1877</v>
@@ -47320,7 +47320,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G1619" t="n">
-        <v>3.06853127479553</v>
+        <v>3.06853103637695</v>
       </c>
       <c r="H1619" t="n">
         <v>5319</v>
@@ -47378,7 +47378,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G1621" t="n">
-        <v>2.93913555145264</v>
+        <v>2.93913531303406</v>
       </c>
       <c r="H1621" t="n">
         <v>7441</v>
@@ -47407,7 +47407,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G1622" t="n">
-        <v>3.06853127479553</v>
+        <v>3.06853103637695</v>
       </c>
       <c r="H1622" t="n">
         <v>9571</v>
@@ -47494,7 +47494,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G1625" t="n">
-        <v>3.01307559013367</v>
+        <v>3.01307582855225</v>
       </c>
       <c r="H1625" t="n">
         <v>720</v>
@@ -47523,7 +47523,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G1626" t="n">
-        <v>3.01307559013367</v>
+        <v>3.01307582855225</v>
       </c>
       <c r="H1626" t="n">
         <v>0</v>
@@ -47552,7 +47552,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G1627" t="n">
-        <v>2.98534798622131</v>
+        <v>2.98534822463989</v>
       </c>
       <c r="H1627" t="n">
         <v>2900</v>
@@ -47697,7 +47697,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G1632" t="n">
-        <v>2.93913555145264</v>
+        <v>2.93913531303406</v>
       </c>
       <c r="H1632" t="n">
         <v>2221</v>
@@ -47813,7 +47813,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G1636" t="n">
-        <v>2.88367986679077</v>
+        <v>2.88367962837219</v>
       </c>
       <c r="H1636" t="n">
         <v>4351</v>
@@ -48074,7 +48074,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G1645" t="n">
-        <v>2.44927930831909</v>
+        <v>2.44927954673767</v>
       </c>
       <c r="H1645" t="n">
         <v>4242</v>
@@ -48364,7 +48364,7 @@
         <v>2.75</v>
       </c>
       <c r="G1655" t="n">
-        <v>2.54170513153076</v>
+        <v>2.54170489311218</v>
       </c>
       <c r="H1655" t="n">
         <v>4443</v>
@@ -48422,7 +48422,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G1657" t="n">
-        <v>2.66185832023621</v>
+        <v>2.66185855865479</v>
       </c>
       <c r="H1657" t="n">
         <v>1365</v>
@@ -48538,7 +48538,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G1661" t="n">
-        <v>2.51397752761841</v>
+        <v>2.51397728919983</v>
       </c>
       <c r="H1661" t="n">
         <v>2782</v>
@@ -48596,7 +48596,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G1663" t="n">
-        <v>2.53246259689331</v>
+        <v>2.53246235847473</v>
       </c>
       <c r="H1663" t="n">
         <v>37694</v>
@@ -48625,7 +48625,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G1664" t="n">
-        <v>2.48624968528748</v>
+        <v>2.48624992370605</v>
       </c>
       <c r="H1664" t="n">
         <v>1765</v>
@@ -48712,7 +48712,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G1667" t="n">
-        <v>2.51397752761841</v>
+        <v>2.51397728919983</v>
       </c>
       <c r="H1667" t="n">
         <v>22439</v>
@@ -48741,7 +48741,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G1668" t="n">
-        <v>2.44927930831909</v>
+        <v>2.44927954673767</v>
       </c>
       <c r="H1668" t="n">
         <v>12455</v>
@@ -48857,7 +48857,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G1672" t="n">
-        <v>2.42155146598816</v>
+        <v>2.42155170440674</v>
       </c>
       <c r="H1672" t="n">
         <v>3460</v>
@@ -49147,7 +49147,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G1682" t="n">
-        <v>2.40306663513184</v>
+        <v>2.40306639671326</v>
       </c>
       <c r="H1682" t="n">
         <v>1410</v>
@@ -49495,7 +49495,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G1694" t="n">
-        <v>2.27367067337036</v>
+        <v>2.27367091178894</v>
       </c>
       <c r="H1694" t="n">
         <v>3905</v>
@@ -49611,7 +49611,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G1698" t="n">
-        <v>2.27367067337036</v>
+        <v>2.27367091178894</v>
       </c>
       <c r="H1698" t="n">
         <v>19</v>
@@ -49640,7 +49640,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G1699" t="n">
-        <v>2.26442837715149</v>
+        <v>2.26442813873291</v>
       </c>
       <c r="H1699" t="n">
         <v>580</v>
@@ -49669,7 +49669,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G1700" t="n">
-        <v>2.23670029640198</v>
+        <v>2.23670053482056</v>
       </c>
       <c r="H1700" t="n">
         <v>450</v>
@@ -49814,7 +49814,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G1705" t="n">
-        <v>2.20897269248962</v>
+        <v>2.2089729309082</v>
       </c>
       <c r="H1705" t="n">
         <v>1386</v>
@@ -49872,7 +49872,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G1707" t="n">
-        <v>2.26442837715149</v>
+        <v>2.26442813873291</v>
       </c>
       <c r="H1707" t="n">
         <v>190</v>
@@ -49901,7 +49901,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G1708" t="n">
-        <v>2.26442837715149</v>
+        <v>2.26442813873291</v>
       </c>
       <c r="H1708" t="n">
         <v>0</v>
@@ -49959,7 +49959,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G1710" t="n">
-        <v>2.28291320800781</v>
+        <v>2.28291344642639</v>
       </c>
       <c r="H1710" t="n">
         <v>900</v>
@@ -49988,7 +49988,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G1711" t="n">
-        <v>2.28291320800781</v>
+        <v>2.28291344642639</v>
       </c>
       <c r="H1711" t="n">
         <v>0</v>
@@ -50104,7 +50104,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G1715" t="n">
-        <v>2.23670029640198</v>
+        <v>2.23670053482056</v>
       </c>
       <c r="H1715" t="n">
         <v>11340</v>
@@ -50133,7 +50133,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G1716" t="n">
-        <v>2.28291320800781</v>
+        <v>2.28291344642639</v>
       </c>
       <c r="H1716" t="n">
         <v>8732</v>
@@ -50278,7 +50278,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G1721" t="n">
-        <v>2.0703341960907</v>
+        <v>2.07033443450928</v>
       </c>
       <c r="H1721" t="n">
         <v>201</v>
@@ -50336,7 +50336,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G1723" t="n">
-        <v>2.19048762321472</v>
+        <v>2.19048738479614</v>
       </c>
       <c r="H1723" t="n">
         <v>7034</v>
@@ -50423,7 +50423,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G1726" t="n">
-        <v>2.06109166145325</v>
+        <v>2.06109189987183</v>
       </c>
       <c r="H1726" t="n">
         <v>7464</v>
@@ -50684,7 +50684,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G1735" t="n">
-        <v>2.05184936523438</v>
+        <v>2.0518491268158</v>
       </c>
       <c r="H1735" t="n">
         <v>601</v>
@@ -50742,7 +50742,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1737" t="n">
-        <v>1.99639403820038</v>
+        <v>1.99639391899109</v>
       </c>
       <c r="H1737" t="n">
         <v>7242</v>
@@ -50945,7 +50945,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G1744" t="n">
-        <v>2.0703341960907</v>
+        <v>2.07033443450928</v>
       </c>
       <c r="H1744" t="n">
         <v>2600</v>
@@ -51032,7 +51032,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G1747" t="n">
-        <v>2.06109166145325</v>
+        <v>2.06109189987183</v>
       </c>
       <c r="H1747" t="n">
         <v>2976</v>
@@ -51148,7 +51148,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G1751" t="n">
-        <v>2.23670029640198</v>
+        <v>2.23670053482056</v>
       </c>
       <c r="H1751" t="n">
         <v>2433</v>
@@ -51293,7 +51293,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G1756" t="n">
-        <v>2.19048762321472</v>
+        <v>2.19048738479614</v>
       </c>
       <c r="H1756" t="n">
         <v>8634</v>
@@ -51322,7 +51322,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G1757" t="n">
-        <v>2.27367067337036</v>
+        <v>2.27367091178894</v>
       </c>
       <c r="H1757" t="n">
         <v>7714</v>
@@ -51351,7 +51351,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G1758" t="n">
-        <v>2.53246259689331</v>
+        <v>2.53246235847473</v>
       </c>
       <c r="H1758" t="n">
         <v>20349</v>
@@ -51467,7 +51467,7 @@
         <v>2.75</v>
       </c>
       <c r="G1762" t="n">
-        <v>2.54170513153076</v>
+        <v>2.54170489311218</v>
       </c>
       <c r="H1762" t="n">
         <v>6937</v>
@@ -51699,7 +51699,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G1770" t="n">
-        <v>2.51397752761841</v>
+        <v>2.51397728919983</v>
       </c>
       <c r="H1770" t="n">
         <v>9906</v>
@@ -51786,7 +51786,7 @@
         <v>2.75</v>
       </c>
       <c r="G1773" t="n">
-        <v>2.54170513153076</v>
+        <v>2.54170489311218</v>
       </c>
       <c r="H1773" t="n">
         <v>13690</v>
@@ -51844,7 +51844,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G1775" t="n">
-        <v>2.53246259689331</v>
+        <v>2.53246235847473</v>
       </c>
       <c r="H1775" t="n">
         <v>10845</v>
@@ -51873,7 +51873,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G1776" t="n">
-        <v>2.53246259689331</v>
+        <v>2.53246235847473</v>
       </c>
       <c r="H1776" t="n">
         <v>3910</v>
@@ -51902,7 +51902,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G1777" t="n">
-        <v>2.51397752761841</v>
+        <v>2.51397728919983</v>
       </c>
       <c r="H1777" t="n">
         <v>18536</v>
@@ -80038,6 +80038,35 @@
         <v>3115</v>
       </c>
       <c r="I2747" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2748">
+      <c r="A2748" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2748" s="1" t="n">
+        <v>46317.2916666667</v>
+      </c>
+      <c r="C2748" t="n">
+        <v>0.389999985694885</v>
+      </c>
+      <c r="D2748" t="n">
+        <v>0.389999985694885</v>
+      </c>
+      <c r="E2748" t="n">
+        <v>0.379999995231628</v>
+      </c>
+      <c r="F2748" t="n">
+        <v>0.379999995231628</v>
+      </c>
+      <c r="G2748" t="n">
+        <v>0.379999995231628</v>
+      </c>
+      <c r="H2748" t="n">
+        <v>4509</v>
+      </c>
+      <c r="I2748" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ZUC.MI.xlsx
+++ b/data/ZUC.MI.xlsx
@@ -427,7 +427,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G2" t="n">
-        <v>3.01633286476135</v>
+        <v>3.01633310317993</v>
       </c>
       <c r="H2" t="n">
         <v>42345</v>
@@ -572,7 +572,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G7" t="n">
-        <v>2.84441781044006</v>
+        <v>2.84441757202148</v>
       </c>
       <c r="H7" t="n">
         <v>15987</v>
@@ -659,7 +659,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G10" t="n">
-        <v>2.89130353927612</v>
+        <v>2.8913037776947</v>
       </c>
       <c r="H10" t="n">
         <v>21901</v>
@@ -688,7 +688,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G11" t="n">
-        <v>2.77408885955811</v>
+        <v>2.77408862113953</v>
       </c>
       <c r="H11" t="n">
         <v>14530</v>
@@ -717,7 +717,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G12" t="n">
-        <v>2.6256160736084</v>
+        <v>2.62561631202698</v>
       </c>
       <c r="H12" t="n">
         <v>16207</v>
@@ -746,7 +746,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G13" t="n">
-        <v>2.5084011554718</v>
+        <v>2.50840163230896</v>
       </c>
       <c r="H13" t="n">
         <v>22831</v>
@@ -833,7 +833,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G16" t="n">
-        <v>2.39118647575378</v>
+        <v>2.39118623733521</v>
       </c>
       <c r="H16" t="n">
         <v>21477</v>
@@ -862,7 +862,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G17" t="n">
-        <v>2.41462922096252</v>
+        <v>2.4146294593811</v>
       </c>
       <c r="H17" t="n">
         <v>14217</v>
@@ -891,7 +891,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G18" t="n">
-        <v>2.41462922096252</v>
+        <v>2.4146294593811</v>
       </c>
       <c r="H18" t="n">
         <v>18543</v>
@@ -1007,7 +1007,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G22" t="n">
-        <v>2.30522847175598</v>
+        <v>2.30522871017456</v>
       </c>
       <c r="H22" t="n">
         <v>7688</v>
@@ -1065,7 +1065,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G24" t="n">
-        <v>2.16457033157349</v>
+        <v>2.16457056999207</v>
       </c>
       <c r="H24" t="n">
         <v>15034</v>
@@ -1094,7 +1094,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G25" t="n">
-        <v>1.78948271274567</v>
+        <v>1.78948247432709</v>
       </c>
       <c r="H25" t="n">
         <v>29015</v>
@@ -1123,7 +1123,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G26" t="n">
-        <v>1.44565176963806</v>
+        <v>1.44565188884735</v>
       </c>
       <c r="H26" t="n">
         <v>34743</v>
@@ -1181,7 +1181,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G28" t="n">
-        <v>0.625146746635437</v>
+        <v>0.625146806240082</v>
       </c>
       <c r="H28" t="n">
         <v>17146</v>
@@ -1297,7 +1297,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G32" t="n">
-        <v>1.64101004600525</v>
+        <v>1.64101016521454</v>
       </c>
       <c r="H32" t="n">
         <v>80086</v>
@@ -1326,7 +1326,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G33" t="n">
-        <v>1.99265539646149</v>
+        <v>1.99265480041504</v>
       </c>
       <c r="H33" t="n">
         <v>23570</v>
@@ -1384,7 +1384,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G35" t="n">
-        <v>2.50058698654175</v>
+        <v>2.50058722496033</v>
       </c>
       <c r="H35" t="n">
         <v>58798</v>
@@ -1500,7 +1500,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G39" t="n">
-        <v>2.44588685035706</v>
+        <v>2.44588661193848</v>
       </c>
       <c r="H39" t="n">
         <v>23320</v>
@@ -1558,7 +1558,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G41" t="n">
-        <v>2.51621556282043</v>
+        <v>2.51621580123901</v>
       </c>
       <c r="H41" t="n">
         <v>12434</v>
@@ -1645,7 +1645,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G44" t="n">
-        <v>2.48495817184448</v>
+        <v>2.48495841026306</v>
       </c>
       <c r="H44" t="n">
         <v>10570</v>
@@ -1674,7 +1674,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G45" t="n">
-        <v>2.77408885955811</v>
+        <v>2.77408862113953</v>
       </c>
       <c r="H45" t="n">
         <v>276654</v>
@@ -1732,7 +1732,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G47" t="n">
-        <v>2.50058698654175</v>
+        <v>2.50058722496033</v>
       </c>
       <c r="H47" t="n">
         <v>39352</v>
@@ -1761,7 +1761,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G48" t="n">
-        <v>2.52402997016907</v>
+        <v>2.52403020858765</v>
       </c>
       <c r="H48" t="n">
         <v>14408</v>
@@ -1877,7 +1877,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G52" t="n">
-        <v>2.50058698654175</v>
+        <v>2.50058722496033</v>
       </c>
       <c r="H52" t="n">
         <v>6390</v>
@@ -1993,7 +1993,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G56" t="n">
-        <v>2.41462922096252</v>
+        <v>2.4146294593811</v>
       </c>
       <c r="H56" t="n">
         <v>6905</v>
@@ -2080,7 +2080,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G59" t="n">
-        <v>2.22708487510681</v>
+        <v>2.22708511352539</v>
       </c>
       <c r="H59" t="n">
         <v>10942</v>
@@ -2138,7 +2138,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G61" t="n">
-        <v>2.08642745018005</v>
+        <v>2.0864269733429</v>
       </c>
       <c r="H61" t="n">
         <v>24791</v>
@@ -2196,7 +2196,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G63" t="n">
-        <v>2.07079887390137</v>
+        <v>2.07079863548279</v>
       </c>
       <c r="H63" t="n">
         <v>3910</v>
@@ -2254,7 +2254,7 @@
         <v>2.5</v>
       </c>
       <c r="G65" t="n">
-        <v>1.95358335971832</v>
+        <v>1.95358347892761</v>
       </c>
       <c r="H65" t="n">
         <v>4420</v>
@@ -2283,7 +2283,7 @@
         <v>2.5</v>
       </c>
       <c r="G66" t="n">
-        <v>1.95358335971832</v>
+        <v>1.95358347892761</v>
       </c>
       <c r="H66" t="n">
         <v>8536</v>
@@ -2312,7 +2312,7 @@
         <v>2.5</v>
       </c>
       <c r="G67" t="n">
-        <v>1.95358335971832</v>
+        <v>1.95358347892761</v>
       </c>
       <c r="H67" t="n">
         <v>400</v>
@@ -2370,7 +2370,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G69" t="n">
-        <v>1.83636832237244</v>
+        <v>1.83636844158173</v>
       </c>
       <c r="H69" t="n">
         <v>7190</v>
@@ -2399,7 +2399,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G70" t="n">
-        <v>1.82073962688446</v>
+        <v>1.82073986530304</v>
       </c>
       <c r="H70" t="n">
         <v>19067</v>
@@ -2428,7 +2428,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G71" t="n">
-        <v>1.81292545795441</v>
+        <v>1.8129255771637</v>
       </c>
       <c r="H71" t="n">
         <v>7528</v>
@@ -2457,7 +2457,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G72" t="n">
-        <v>1.80511128902435</v>
+        <v>1.80511105060577</v>
       </c>
       <c r="H72" t="n">
         <v>6071</v>
@@ -2544,7 +2544,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G75" t="n">
-        <v>1.84418261051178</v>
+        <v>1.84418272972107</v>
       </c>
       <c r="H75" t="n">
         <v>12321</v>
@@ -2602,7 +2602,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G77" t="n">
-        <v>1.80511128902435</v>
+        <v>1.80511105060577</v>
       </c>
       <c r="H77" t="n">
         <v>15224</v>
@@ -2689,7 +2689,7 @@
         <v>2.25</v>
       </c>
       <c r="G80" t="n">
-        <v>1.75822520256042</v>
+        <v>1.75822532176971</v>
       </c>
       <c r="H80" t="n">
         <v>4825</v>
@@ -2747,7 +2747,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G82" t="n">
-        <v>1.85981154441833</v>
+        <v>1.85981166362762</v>
       </c>
       <c r="H82" t="n">
         <v>17718</v>
@@ -2776,7 +2776,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G83" t="n">
-        <v>1.85981154441833</v>
+        <v>1.85981166362762</v>
       </c>
       <c r="H83" t="n">
         <v>1959</v>
@@ -2805,7 +2805,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G84" t="n">
-        <v>1.85981154441833</v>
+        <v>1.85981166362762</v>
       </c>
       <c r="H84" t="n">
         <v>1535</v>
@@ -2834,7 +2834,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G85" t="n">
-        <v>1.83636832237244</v>
+        <v>1.83636844158173</v>
       </c>
       <c r="H85" t="n">
         <v>1560</v>
@@ -2863,7 +2863,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G86" t="n">
-        <v>1.78166830539703</v>
+        <v>1.78166818618774</v>
       </c>
       <c r="H86" t="n">
         <v>2070</v>
@@ -2950,7 +2950,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G89" t="n">
-        <v>1.78948271274567</v>
+        <v>1.78948247432709</v>
       </c>
       <c r="H89" t="n">
         <v>13120</v>
@@ -2979,7 +2979,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G90" t="n">
-        <v>1.70352494716644</v>
+        <v>1.70352470874786</v>
       </c>
       <c r="H90" t="n">
         <v>5489</v>
@@ -3037,7 +3037,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G92" t="n">
-        <v>1.6331958770752</v>
+        <v>1.63319575786591</v>
       </c>
       <c r="H92" t="n">
         <v>15187</v>
@@ -3066,7 +3066,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G93" t="n">
-        <v>1.70352494716644</v>
+        <v>1.70352470874786</v>
       </c>
       <c r="H93" t="n">
         <v>5250</v>
@@ -3095,7 +3095,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G94" t="n">
-        <v>1.69571053981781</v>
+        <v>1.69571042060852</v>
       </c>
       <c r="H94" t="n">
         <v>7592</v>
@@ -3211,7 +3211,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G98" t="n">
-        <v>2.21927070617676</v>
+        <v>2.21927094459534</v>
       </c>
       <c r="H98" t="n">
         <v>189197</v>
@@ -3240,7 +3240,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G99" t="n">
-        <v>2.26615691184998</v>
+        <v>2.26615715026855</v>
       </c>
       <c r="H99" t="n">
         <v>221937</v>
@@ -3269,7 +3269,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G100" t="n">
-        <v>2.08642745018005</v>
+        <v>2.0864269733429</v>
       </c>
       <c r="H100" t="n">
         <v>131201</v>
@@ -3385,7 +3385,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G104" t="n">
-        <v>1.93795490264893</v>
+        <v>1.93795478343964</v>
       </c>
       <c r="H104" t="n">
         <v>28640</v>
@@ -3414,7 +3414,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G105" t="n">
-        <v>1.88325452804565</v>
+        <v>1.88325476646423</v>
       </c>
       <c r="H105" t="n">
         <v>30798</v>
@@ -3443,7 +3443,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G106" t="n">
-        <v>1.8285539150238</v>
+        <v>1.82855415344238</v>
       </c>
       <c r="H106" t="n">
         <v>48556</v>
@@ -3588,7 +3588,7 @@
         <v>2.25</v>
       </c>
       <c r="G111" t="n">
-        <v>1.75822520256042</v>
+        <v>1.75822532176971</v>
       </c>
       <c r="H111" t="n">
         <v>12997</v>
@@ -3617,7 +3617,7 @@
         <v>2.25</v>
       </c>
       <c r="G112" t="n">
-        <v>1.75822520256042</v>
+        <v>1.75822532176971</v>
       </c>
       <c r="H112" t="n">
         <v>6892</v>
@@ -3646,7 +3646,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G113" t="n">
-        <v>1.69571053981781</v>
+        <v>1.69571042060852</v>
       </c>
       <c r="H113" t="n">
         <v>7676</v>
@@ -3704,7 +3704,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G115" t="n">
-        <v>1.58630967140198</v>
+        <v>1.58630979061127</v>
       </c>
       <c r="H115" t="n">
         <v>15973</v>
@@ -3733,7 +3733,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G116" t="n">
-        <v>1.60193836688995</v>
+        <v>1.60193848609924</v>
       </c>
       <c r="H116" t="n">
         <v>15987</v>
@@ -3762,7 +3762,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G117" t="n">
-        <v>1.57068121433258</v>
+        <v>1.57068109512329</v>
       </c>
       <c r="H117" t="n">
         <v>1475</v>
@@ -3791,7 +3791,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G118" t="n">
-        <v>1.54723811149597</v>
+        <v>1.54723823070526</v>
       </c>
       <c r="H118" t="n">
         <v>2966</v>
@@ -3820,7 +3820,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G119" t="n">
-        <v>1.64101004600525</v>
+        <v>1.64101016521454</v>
       </c>
       <c r="H119" t="n">
         <v>7103</v>
@@ -4023,7 +4023,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G126" t="n">
-        <v>1.44565176963806</v>
+        <v>1.44565188884735</v>
       </c>
       <c r="H126" t="n">
         <v>4514</v>
@@ -4052,7 +4052,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G127" t="n">
-        <v>1.44565176963806</v>
+        <v>1.44565188884735</v>
       </c>
       <c r="H127" t="n">
         <v>0</v>
@@ -4139,7 +4139,7 @@
         <v>2.25</v>
       </c>
       <c r="G130" t="n">
-        <v>1.75822520256042</v>
+        <v>1.75822532176971</v>
       </c>
       <c r="H130" t="n">
         <v>83797</v>
@@ -4168,7 +4168,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G131" t="n">
-        <v>1.57068121433258</v>
+        <v>1.57068109512329</v>
       </c>
       <c r="H131" t="n">
         <v>61460</v>
@@ -4197,7 +4197,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G132" t="n">
-        <v>1.32843673229218</v>
+        <v>1.32843685150146</v>
       </c>
       <c r="H132" t="n">
         <v>54470</v>
@@ -4313,7 +4313,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G136" t="n">
-        <v>1.4143944978714</v>
+        <v>1.41439437866211</v>
       </c>
       <c r="H136" t="n">
         <v>17202</v>
@@ -4342,7 +4342,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G137" t="n">
-        <v>1.42220890522003</v>
+        <v>1.42220878601074</v>
       </c>
       <c r="H137" t="n">
         <v>10331</v>
@@ -4371,7 +4371,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G138" t="n">
-        <v>1.4143944978714</v>
+        <v>1.41439437866211</v>
       </c>
       <c r="H138" t="n">
         <v>9467</v>
@@ -4400,7 +4400,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G139" t="n">
-        <v>1.46128046512604</v>
+        <v>1.46128058433533</v>
       </c>
       <c r="H139" t="n">
         <v>173037</v>
@@ -4429,7 +4429,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G140" t="n">
-        <v>1.4143944978714</v>
+        <v>1.41439437866211</v>
       </c>
       <c r="H140" t="n">
         <v>22023</v>
@@ -4458,7 +4458,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G141" t="n">
-        <v>1.47690916061401</v>
+        <v>1.47690904140472</v>
       </c>
       <c r="H141" t="n">
         <v>16351</v>
@@ -4516,7 +4516,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G143" t="n">
-        <v>1.42220890522003</v>
+        <v>1.42220878601074</v>
       </c>
       <c r="H143" t="n">
         <v>15680</v>
@@ -4603,7 +4603,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G146" t="n">
-        <v>1.43002307415009</v>
+        <v>1.43002319335938</v>
       </c>
       <c r="H146" t="n">
         <v>5668</v>
@@ -4632,7 +4632,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G147" t="n">
-        <v>1.44565176963806</v>
+        <v>1.44565188884735</v>
       </c>
       <c r="H147" t="n">
         <v>3897</v>
@@ -4661,7 +4661,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G148" t="n">
-        <v>1.43002307415009</v>
+        <v>1.43002319335938</v>
       </c>
       <c r="H148" t="n">
         <v>3047</v>
@@ -4719,7 +4719,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G150" t="n">
-        <v>1.43002307415009</v>
+        <v>1.43002319335938</v>
       </c>
       <c r="H150" t="n">
         <v>3668</v>
@@ -4748,7 +4748,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G151" t="n">
-        <v>1.43002307415009</v>
+        <v>1.43002319335938</v>
       </c>
       <c r="H151" t="n">
         <v>20454</v>
@@ -4777,7 +4777,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G152" t="n">
-        <v>1.44565176963806</v>
+        <v>1.44565188884735</v>
       </c>
       <c r="H152" t="n">
         <v>3895</v>
@@ -4806,7 +4806,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G153" t="n">
-        <v>1.42220890522003</v>
+        <v>1.42220878601074</v>
       </c>
       <c r="H153" t="n">
         <v>9667</v>
@@ -4864,7 +4864,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G155" t="n">
-        <v>1.50035226345062</v>
+        <v>1.50035214424133</v>
       </c>
       <c r="H155" t="n">
         <v>11333</v>
@@ -4893,7 +4893,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G156" t="n">
-        <v>1.49253797531128</v>
+        <v>1.49253785610199</v>
       </c>
       <c r="H156" t="n">
         <v>5721</v>
@@ -4922,7 +4922,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G157" t="n">
-        <v>1.50816643238068</v>
+        <v>1.50816655158997</v>
       </c>
       <c r="H157" t="n">
         <v>300</v>
@@ -4951,7 +4951,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G158" t="n">
-        <v>1.50035226345062</v>
+        <v>1.50035214424133</v>
       </c>
       <c r="H158" t="n">
         <v>230</v>
@@ -5009,7 +5009,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G160" t="n">
-        <v>1.46128046512604</v>
+        <v>1.46128058433533</v>
       </c>
       <c r="H160" t="n">
         <v>3965</v>
@@ -5038,7 +5038,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G161" t="n">
-        <v>1.47690916061401</v>
+        <v>1.47690904140472</v>
       </c>
       <c r="H161" t="n">
         <v>4796</v>
@@ -5067,7 +5067,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G162" t="n">
-        <v>1.46128046512604</v>
+        <v>1.46128058433533</v>
       </c>
       <c r="H162" t="n">
         <v>1540</v>
@@ -5125,7 +5125,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G164" t="n">
-        <v>1.44565176963806</v>
+        <v>1.44565188884735</v>
       </c>
       <c r="H164" t="n">
         <v>2612</v>
@@ -5270,7 +5270,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G169" t="n">
-        <v>1.47690916061401</v>
+        <v>1.47690904140472</v>
       </c>
       <c r="H169" t="n">
         <v>12338</v>
@@ -5328,7 +5328,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G171" t="n">
-        <v>1.47690916061401</v>
+        <v>1.47690904140472</v>
       </c>
       <c r="H171" t="n">
         <v>7601</v>
@@ -5357,7 +5357,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G172" t="n">
-        <v>1.47690916061401</v>
+        <v>1.47690904140472</v>
       </c>
       <c r="H172" t="n">
         <v>2406</v>
@@ -5386,7 +5386,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G173" t="n">
-        <v>1.46128046512604</v>
+        <v>1.46128058433533</v>
       </c>
       <c r="H173" t="n">
         <v>902</v>
@@ -5415,7 +5415,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G174" t="n">
-        <v>1.54723811149597</v>
+        <v>1.54723823070526</v>
       </c>
       <c r="H174" t="n">
         <v>47810</v>
@@ -5444,7 +5444,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G175" t="n">
-        <v>1.49253797531128</v>
+        <v>1.49253785610199</v>
       </c>
       <c r="H175" t="n">
         <v>8883</v>
@@ -5473,7 +5473,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G176" t="n">
-        <v>1.46128046512604</v>
+        <v>1.46128058433533</v>
       </c>
       <c r="H176" t="n">
         <v>13742</v>
@@ -5531,7 +5531,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G178" t="n">
-        <v>1.49253797531128</v>
+        <v>1.49253785610199</v>
       </c>
       <c r="H178" t="n">
         <v>7365</v>
@@ -5647,7 +5647,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G182" t="n">
-        <v>1.47690916061401</v>
+        <v>1.47690904140472</v>
       </c>
       <c r="H182" t="n">
         <v>1510</v>
@@ -5676,7 +5676,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G183" t="n">
-        <v>1.4143944978714</v>
+        <v>1.41439437866211</v>
       </c>
       <c r="H183" t="n">
         <v>13615</v>
@@ -5763,7 +5763,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G186" t="n">
-        <v>1.44565176963806</v>
+        <v>1.44565188884735</v>
       </c>
       <c r="H186" t="n">
         <v>5051</v>
@@ -5792,7 +5792,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G187" t="n">
-        <v>1.6097526550293</v>
+        <v>1.60975289344788</v>
       </c>
       <c r="H187" t="n">
         <v>206627</v>
@@ -6227,7 +6227,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G202" t="n">
-        <v>1.47690916061401</v>
+        <v>1.47690904140472</v>
       </c>
       <c r="H202" t="n">
         <v>7610</v>
@@ -6285,7 +6285,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G204" t="n">
-        <v>1.531609416008</v>
+        <v>1.53160953521729</v>
       </c>
       <c r="H204" t="n">
         <v>8646</v>
@@ -6314,7 +6314,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G205" t="n">
-        <v>1.50816643238068</v>
+        <v>1.50816655158997</v>
       </c>
       <c r="H205" t="n">
         <v>23070</v>
@@ -6401,7 +6401,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G208" t="n">
-        <v>1.54723811149597</v>
+        <v>1.54723823070526</v>
       </c>
       <c r="H208" t="n">
         <v>30696</v>
@@ -6430,7 +6430,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G209" t="n">
-        <v>1.54723811149597</v>
+        <v>1.54723823070526</v>
       </c>
       <c r="H209" t="n">
         <v>5243</v>
@@ -6517,7 +6517,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G212" t="n">
-        <v>1.54723811149597</v>
+        <v>1.54723823070526</v>
       </c>
       <c r="H212" t="n">
         <v>600</v>
@@ -6546,7 +6546,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G213" t="n">
-        <v>1.5550525188446</v>
+        <v>1.55505263805389</v>
       </c>
       <c r="H213" t="n">
         <v>7649</v>
@@ -6575,7 +6575,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G214" t="n">
-        <v>1.57068121433258</v>
+        <v>1.57068109512329</v>
       </c>
       <c r="H214" t="n">
         <v>101975</v>
@@ -6633,7 +6633,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G216" t="n">
-        <v>1.50816643238068</v>
+        <v>1.50816655158997</v>
       </c>
       <c r="H216" t="n">
         <v>15002</v>
@@ -6720,7 +6720,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G219" t="n">
-        <v>1.531609416008</v>
+        <v>1.53160953521729</v>
       </c>
       <c r="H219" t="n">
         <v>16116</v>
@@ -6807,7 +6807,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G222" t="n">
-        <v>1.61756694316864</v>
+        <v>1.61756718158722</v>
       </c>
       <c r="H222" t="n">
         <v>33429</v>
@@ -6865,7 +6865,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G224" t="n">
-        <v>1.5550525188446</v>
+        <v>1.55505263805389</v>
       </c>
       <c r="H224" t="n">
         <v>22722</v>
@@ -6894,7 +6894,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G225" t="n">
-        <v>1.58630967140198</v>
+        <v>1.58630979061127</v>
       </c>
       <c r="H225" t="n">
         <v>24397</v>
@@ -7039,7 +7039,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G230" t="n">
-        <v>1.49253797531128</v>
+        <v>1.49253785610199</v>
       </c>
       <c r="H230" t="n">
         <v>3975</v>
@@ -7155,7 +7155,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G234" t="n">
-        <v>1.4143944978714</v>
+        <v>1.41439437866211</v>
       </c>
       <c r="H234" t="n">
         <v>15984</v>
@@ -7184,7 +7184,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G235" t="n">
-        <v>1.43002307415009</v>
+        <v>1.43002319335938</v>
       </c>
       <c r="H235" t="n">
         <v>7002</v>
@@ -7213,7 +7213,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G236" t="n">
-        <v>1.46128046512604</v>
+        <v>1.46128058433533</v>
       </c>
       <c r="H236" t="n">
         <v>2358</v>
@@ -7242,7 +7242,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G237" t="n">
-        <v>1.47690916061401</v>
+        <v>1.47690904140472</v>
       </c>
       <c r="H237" t="n">
         <v>3415</v>
@@ -7416,7 +7416,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G243" t="n">
-        <v>1.50035226345062</v>
+        <v>1.50035214424133</v>
       </c>
       <c r="H243" t="n">
         <v>2774</v>
@@ -7445,7 +7445,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G244" t="n">
-        <v>1.50035226345062</v>
+        <v>1.50035214424133</v>
       </c>
       <c r="H244" t="n">
         <v>2142</v>
@@ -7474,7 +7474,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G245" t="n">
-        <v>1.49253797531128</v>
+        <v>1.49253785610199</v>
       </c>
       <c r="H245" t="n">
         <v>6756</v>
@@ -7503,7 +7503,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G246" t="n">
-        <v>1.50035226345062</v>
+        <v>1.50035214424133</v>
       </c>
       <c r="H246" t="n">
         <v>6837</v>
@@ -7532,7 +7532,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G247" t="n">
-        <v>1.50035226345062</v>
+        <v>1.50035214424133</v>
       </c>
       <c r="H247" t="n">
         <v>9596</v>
@@ -7561,7 +7561,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G248" t="n">
-        <v>1.50035226345062</v>
+        <v>1.50035214424133</v>
       </c>
       <c r="H248" t="n">
         <v>3796</v>
@@ -7619,7 +7619,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G250" t="n">
-        <v>1.50035226345062</v>
+        <v>1.50035214424133</v>
       </c>
       <c r="H250" t="n">
         <v>16130</v>
@@ -7648,7 +7648,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G251" t="n">
-        <v>1.50816643238068</v>
+        <v>1.50816655158997</v>
       </c>
       <c r="H251" t="n">
         <v>4699</v>
@@ -7677,7 +7677,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G252" t="n">
-        <v>1.49253797531128</v>
+        <v>1.49253785610199</v>
       </c>
       <c r="H252" t="n">
         <v>8020</v>
@@ -7706,7 +7706,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G253" t="n">
-        <v>1.47690916061401</v>
+        <v>1.47690904140472</v>
       </c>
       <c r="H253" t="n">
         <v>5630</v>
@@ -7735,7 +7735,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G254" t="n">
-        <v>1.50035226345062</v>
+        <v>1.50035214424133</v>
       </c>
       <c r="H254" t="n">
         <v>10860</v>
@@ -7764,7 +7764,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G255" t="n">
-        <v>1.49253797531128</v>
+        <v>1.49253785610199</v>
       </c>
       <c r="H255" t="n">
         <v>45713</v>
@@ -7822,7 +7822,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G257" t="n">
-        <v>1.54723811149597</v>
+        <v>1.54723823070526</v>
       </c>
       <c r="H257" t="n">
         <v>41048</v>
@@ -7851,7 +7851,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G258" t="n">
-        <v>1.83636832237244</v>
+        <v>1.83636844158173</v>
       </c>
       <c r="H258" t="n">
         <v>125566</v>
@@ -7909,7 +7909,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G260" t="n">
-        <v>1.76603960990906</v>
+        <v>1.76603949069977</v>
       </c>
       <c r="H260" t="n">
         <v>45306</v>
@@ -7967,7 +7967,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G262" t="n">
-        <v>1.72696805000305</v>
+        <v>1.72696781158447</v>
       </c>
       <c r="H262" t="n">
         <v>17933</v>
@@ -8054,7 +8054,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G265" t="n">
-        <v>1.6331958770752</v>
+        <v>1.63319575786591</v>
       </c>
       <c r="H265" t="n">
         <v>33628</v>
@@ -8083,7 +8083,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G266" t="n">
-        <v>1.60193836688995</v>
+        <v>1.60193848609924</v>
       </c>
       <c r="H266" t="n">
         <v>12204</v>
@@ -8112,7 +8112,7 @@
         <v>2.25</v>
       </c>
       <c r="G267" t="n">
-        <v>1.75822520256042</v>
+        <v>1.75822532176971</v>
       </c>
       <c r="H267" t="n">
         <v>48617</v>
@@ -8199,7 +8199,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G270" t="n">
-        <v>1.64101004600525</v>
+        <v>1.64101016521454</v>
       </c>
       <c r="H270" t="n">
         <v>10671</v>
@@ -8228,7 +8228,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G271" t="n">
-        <v>1.79729688167572</v>
+        <v>1.79729676246643</v>
       </c>
       <c r="H271" t="n">
         <v>110444</v>
@@ -8315,7 +8315,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G274" t="n">
-        <v>2.78190302848816</v>
+        <v>2.781902551651</v>
       </c>
       <c r="H274" t="n">
         <v>248750</v>
@@ -8402,7 +8402,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G277" t="n">
-        <v>2.31304287910461</v>
+        <v>2.31304311752319</v>
       </c>
       <c r="H277" t="n">
         <v>178115</v>
@@ -8431,7 +8431,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G278" t="n">
-        <v>2.36774325370789</v>
+        <v>2.36774349212646</v>
       </c>
       <c r="H278" t="n">
         <v>155933</v>
@@ -8460,7 +8460,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G279" t="n">
-        <v>2.32085728645325</v>
+        <v>2.32085752487183</v>
       </c>
       <c r="H279" t="n">
         <v>23589</v>
@@ -8489,7 +8489,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G280" t="n">
-        <v>2.36774325370789</v>
+        <v>2.36774349212646</v>
       </c>
       <c r="H280" t="n">
         <v>42641</v>
@@ -8518,7 +8518,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G281" t="n">
-        <v>2.26615691184998</v>
+        <v>2.26615715026855</v>
       </c>
       <c r="H281" t="n">
         <v>36137</v>
@@ -8576,7 +8576,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G283" t="n">
-        <v>2.48495817184448</v>
+        <v>2.48495841026306</v>
       </c>
       <c r="H283" t="n">
         <v>174485</v>
@@ -8605,7 +8605,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G284" t="n">
-        <v>2.41462922096252</v>
+        <v>2.4146294593811</v>
       </c>
       <c r="H284" t="n">
         <v>141085</v>
@@ -8634,7 +8634,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G285" t="n">
-        <v>2.41462922096252</v>
+        <v>2.4146294593811</v>
       </c>
       <c r="H285" t="n">
         <v>32999</v>
@@ -8750,7 +8750,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G289" t="n">
-        <v>2.5084011554718</v>
+        <v>2.50840163230896</v>
       </c>
       <c r="H289" t="n">
         <v>75755</v>
@@ -8779,7 +8779,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G290" t="n">
-        <v>2.48495817184448</v>
+        <v>2.48495841026306</v>
       </c>
       <c r="H290" t="n">
         <v>43039</v>
@@ -8866,7 +8866,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G293" t="n">
-        <v>2.30522847175598</v>
+        <v>2.30522871017456</v>
       </c>
       <c r="H293" t="n">
         <v>63123</v>
@@ -8895,7 +8895,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G294" t="n">
-        <v>2.21927070617676</v>
+        <v>2.21927094459534</v>
       </c>
       <c r="H294" t="n">
         <v>88001</v>
@@ -8924,7 +8924,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G295" t="n">
-        <v>2.21145629882812</v>
+        <v>2.2114565372467</v>
       </c>
       <c r="H295" t="n">
         <v>127250</v>
@@ -8982,7 +8982,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G297" t="n">
-        <v>2.07861304283142</v>
+        <v>2.07861280441284</v>
       </c>
       <c r="H297" t="n">
         <v>57099</v>
@@ -9040,7 +9040,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G299" t="n">
-        <v>2.18801355361938</v>
+        <v>2.18801331520081</v>
       </c>
       <c r="H299" t="n">
         <v>145545</v>
@@ -9069,7 +9069,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G300" t="n">
-        <v>2.16457033157349</v>
+        <v>2.16457056999207</v>
       </c>
       <c r="H300" t="n">
         <v>48238</v>
@@ -9098,7 +9098,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G301" t="n">
-        <v>2.11768484115601</v>
+        <v>2.11768460273743</v>
       </c>
       <c r="H301" t="n">
         <v>31779</v>
@@ -9127,7 +9127,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G302" t="n">
-        <v>2.10987043380737</v>
+        <v>2.10987019538879</v>
       </c>
       <c r="H302" t="n">
         <v>17255</v>
@@ -9185,7 +9185,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G304" t="n">
-        <v>2.08642745018005</v>
+        <v>2.0864269733429</v>
       </c>
       <c r="H304" t="n">
         <v>19530</v>
@@ -9214,7 +9214,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G305" t="n">
-        <v>2.08642745018005</v>
+        <v>2.0864269733429</v>
       </c>
       <c r="H305" t="n">
         <v>13542</v>
@@ -9272,7 +9272,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G307" t="n">
-        <v>2.11768484115601</v>
+        <v>2.11768460273743</v>
       </c>
       <c r="H307" t="n">
         <v>94727</v>
@@ -9301,7 +9301,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G308" t="n">
-        <v>2.18801355361938</v>
+        <v>2.18801331520081</v>
       </c>
       <c r="H308" t="n">
         <v>36108</v>
@@ -9330,7 +9330,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G309" t="n">
-        <v>2.16457033157349</v>
+        <v>2.16457056999207</v>
       </c>
       <c r="H309" t="n">
         <v>14321</v>
@@ -9359,7 +9359,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G310" t="n">
-        <v>2.11768484115601</v>
+        <v>2.11768460273743</v>
       </c>
       <c r="H310" t="n">
         <v>7325</v>
@@ -9388,7 +9388,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G311" t="n">
-        <v>2.13331341743469</v>
+        <v>2.13331317901611</v>
       </c>
       <c r="H311" t="n">
         <v>20423</v>
@@ -9446,7 +9446,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G313" t="n">
-        <v>2.14112782478333</v>
+        <v>2.14112758636475</v>
       </c>
       <c r="H313" t="n">
         <v>5822</v>
@@ -9475,7 +9475,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G314" t="n">
-        <v>2.19582796096802</v>
+        <v>2.19582772254944</v>
       </c>
       <c r="H314" t="n">
         <v>90558</v>
@@ -9504,7 +9504,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G315" t="n">
-        <v>2.21145629882812</v>
+        <v>2.2114565372467</v>
       </c>
       <c r="H315" t="n">
         <v>24918</v>
@@ -9533,7 +9533,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G316" t="n">
-        <v>2.31304287910461</v>
+        <v>2.31304311752319</v>
       </c>
       <c r="H316" t="n">
         <v>166647</v>
@@ -9591,7 +9591,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G318" t="n">
-        <v>2.65687346458435</v>
+        <v>2.65687370300293</v>
       </c>
       <c r="H318" t="n">
         <v>288982</v>
@@ -9707,7 +9707,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G322" t="n">
-        <v>2.32085728645325</v>
+        <v>2.32085752487183</v>
       </c>
       <c r="H322" t="n">
         <v>120703</v>
@@ -9736,7 +9736,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G323" t="n">
-        <v>2.26615691184998</v>
+        <v>2.26615715026855</v>
       </c>
       <c r="H323" t="n">
         <v>66785</v>
@@ -9765,7 +9765,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G324" t="n">
-        <v>2.24271368980408</v>
+        <v>2.24271392822266</v>
       </c>
       <c r="H324" t="n">
         <v>19757</v>
@@ -9794,7 +9794,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G325" t="n">
-        <v>2.36774325370789</v>
+        <v>2.36774349212646</v>
       </c>
       <c r="H325" t="n">
         <v>123555</v>
@@ -9852,7 +9852,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G327" t="n">
-        <v>2.31304287910461</v>
+        <v>2.31304311752319</v>
       </c>
       <c r="H327" t="n">
         <v>15378</v>
@@ -9939,7 +9939,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G330" t="n">
-        <v>2.26615691184998</v>
+        <v>2.26615715026855</v>
       </c>
       <c r="H330" t="n">
         <v>9551</v>
@@ -9997,7 +9997,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G332" t="n">
-        <v>2.19582796096802</v>
+        <v>2.19582772254944</v>
       </c>
       <c r="H332" t="n">
         <v>23745</v>
@@ -10026,7 +10026,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G333" t="n">
-        <v>2.25834250450134</v>
+        <v>2.25834274291992</v>
       </c>
       <c r="H333" t="n">
         <v>41046</v>
@@ -10055,7 +10055,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G334" t="n">
-        <v>2.30522847175598</v>
+        <v>2.30522871017456</v>
       </c>
       <c r="H334" t="n">
         <v>27597</v>
@@ -10113,7 +10113,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G336" t="n">
-        <v>2.36774325370789</v>
+        <v>2.36774349212646</v>
       </c>
       <c r="H336" t="n">
         <v>60523</v>
@@ -10142,7 +10142,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G337" t="n">
-        <v>2.30522847175598</v>
+        <v>2.30522871017456</v>
       </c>
       <c r="H337" t="n">
         <v>70691</v>
@@ -10171,7 +10171,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G338" t="n">
-        <v>2.31304287910461</v>
+        <v>2.31304311752319</v>
       </c>
       <c r="H338" t="n">
         <v>35872</v>
@@ -10229,7 +10229,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G340" t="n">
-        <v>2.26615691184998</v>
+        <v>2.26615715026855</v>
       </c>
       <c r="H340" t="n">
         <v>69321</v>
@@ -10258,7 +10258,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G341" t="n">
-        <v>2.25834250450134</v>
+        <v>2.25834274291992</v>
       </c>
       <c r="H341" t="n">
         <v>19671</v>
@@ -10287,7 +10287,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G342" t="n">
-        <v>2.25834250450134</v>
+        <v>2.25834274291992</v>
       </c>
       <c r="H342" t="n">
         <v>9250</v>
@@ -10345,7 +10345,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G344" t="n">
-        <v>2.5084011554718</v>
+        <v>2.50840163230896</v>
       </c>
       <c r="H344" t="n">
         <v>306118</v>
@@ -10374,7 +10374,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G345" t="n">
-        <v>2.40681481361389</v>
+        <v>2.40681505203247</v>
       </c>
       <c r="H345" t="n">
         <v>126337</v>
@@ -10432,7 +10432,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G347" t="n">
-        <v>2.41462922096252</v>
+        <v>2.4146294593811</v>
       </c>
       <c r="H347" t="n">
         <v>25889</v>
@@ -10548,7 +10548,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G351" t="n">
-        <v>2.30522847175598</v>
+        <v>2.30522871017456</v>
       </c>
       <c r="H351" t="n">
         <v>10524</v>
@@ -10577,7 +10577,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G352" t="n">
-        <v>2.25834250450134</v>
+        <v>2.25834274291992</v>
       </c>
       <c r="H352" t="n">
         <v>34161</v>
@@ -10606,7 +10606,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G353" t="n">
-        <v>2.26615691184998</v>
+        <v>2.26615715026855</v>
       </c>
       <c r="H353" t="n">
         <v>11227</v>
@@ -10664,7 +10664,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G355" t="n">
-        <v>2.30522847175598</v>
+        <v>2.30522871017456</v>
       </c>
       <c r="H355" t="n">
         <v>6469</v>
@@ -10693,7 +10693,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G356" t="n">
-        <v>2.35992884635925</v>
+        <v>2.35992908477783</v>
       </c>
       <c r="H356" t="n">
         <v>37071</v>
@@ -10780,7 +10780,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G359" t="n">
-        <v>2.30522847175598</v>
+        <v>2.30522871017456</v>
       </c>
       <c r="H359" t="n">
         <v>21418</v>
@@ -10809,7 +10809,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G360" t="n">
-        <v>2.31304287910461</v>
+        <v>2.31304311752319</v>
       </c>
       <c r="H360" t="n">
         <v>6391</v>
@@ -10838,7 +10838,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G361" t="n">
-        <v>2.30522847175598</v>
+        <v>2.30522871017456</v>
       </c>
       <c r="H361" t="n">
         <v>12853</v>
@@ -10954,7 +10954,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G365" t="n">
-        <v>2.19582796096802</v>
+        <v>2.19582772254944</v>
       </c>
       <c r="H365" t="n">
         <v>66685</v>
@@ -10983,7 +10983,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G366" t="n">
-        <v>2.19582796096802</v>
+        <v>2.19582772254944</v>
       </c>
       <c r="H366" t="n">
         <v>21330</v>
@@ -11012,7 +11012,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G367" t="n">
-        <v>2.22708487510681</v>
+        <v>2.22708511352539</v>
       </c>
       <c r="H367" t="n">
         <v>8955</v>
@@ -11041,7 +11041,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G368" t="n">
-        <v>2.22708487510681</v>
+        <v>2.22708511352539</v>
       </c>
       <c r="H368" t="n">
         <v>5899</v>
@@ -11070,7 +11070,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G369" t="n">
-        <v>2.19582796096802</v>
+        <v>2.19582772254944</v>
       </c>
       <c r="H369" t="n">
         <v>25375</v>
@@ -11099,7 +11099,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G370" t="n">
-        <v>2.19582796096802</v>
+        <v>2.19582772254944</v>
       </c>
       <c r="H370" t="n">
         <v>2922</v>
@@ -11157,7 +11157,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G372" t="n">
-        <v>2.22708487510681</v>
+        <v>2.22708511352539</v>
       </c>
       <c r="H372" t="n">
         <v>12004</v>
@@ -11215,7 +11215,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G374" t="n">
-        <v>2.21145629882812</v>
+        <v>2.2114565372467</v>
       </c>
       <c r="H374" t="n">
         <v>1201</v>
@@ -11273,7 +11273,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G376" t="n">
-        <v>2.18801355361938</v>
+        <v>2.18801331520081</v>
       </c>
       <c r="H376" t="n">
         <v>4715</v>
@@ -11302,7 +11302,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G377" t="n">
-        <v>2.22708487510681</v>
+        <v>2.22708511352539</v>
       </c>
       <c r="H377" t="n">
         <v>4658</v>
@@ -11331,7 +11331,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G378" t="n">
-        <v>2.21927070617676</v>
+        <v>2.21927094459534</v>
       </c>
       <c r="H378" t="n">
         <v>6809</v>
@@ -11360,7 +11360,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G379" t="n">
-        <v>2.22708487510681</v>
+        <v>2.22708511352539</v>
       </c>
       <c r="H379" t="n">
         <v>7003</v>
@@ -11418,7 +11418,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G381" t="n">
-        <v>2.21927070617676</v>
+        <v>2.21927094459534</v>
       </c>
       <c r="H381" t="n">
         <v>34021</v>
@@ -11447,7 +11447,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G382" t="n">
-        <v>2.21145629882812</v>
+        <v>2.2114565372467</v>
       </c>
       <c r="H382" t="n">
         <v>7415</v>
@@ -11476,7 +11476,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G383" t="n">
-        <v>2.25834250450134</v>
+        <v>2.25834274291992</v>
       </c>
       <c r="H383" t="n">
         <v>38535</v>
@@ -11563,7 +11563,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G386" t="n">
-        <v>2.25834250450134</v>
+        <v>2.25834274291992</v>
       </c>
       <c r="H386" t="n">
         <v>100</v>
@@ -11592,7 +11592,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G387" t="n">
-        <v>2.24271368980408</v>
+        <v>2.24271392822266</v>
       </c>
       <c r="H387" t="n">
         <v>6947</v>
@@ -11621,7 +11621,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G388" t="n">
-        <v>2.22708487510681</v>
+        <v>2.22708511352539</v>
       </c>
       <c r="H388" t="n">
         <v>100</v>
@@ -11650,7 +11650,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G389" t="n">
-        <v>2.18019914627075</v>
+        <v>2.18019890785217</v>
       </c>
       <c r="H389" t="n">
         <v>20929</v>
@@ -11679,7 +11679,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G390" t="n">
-        <v>2.19582796096802</v>
+        <v>2.19582772254944</v>
       </c>
       <c r="H390" t="n">
         <v>6870</v>
@@ -11737,7 +11737,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G392" t="n">
-        <v>2.22708487510681</v>
+        <v>2.22708511352539</v>
       </c>
       <c r="H392" t="n">
         <v>4464</v>
@@ -11795,7 +11795,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G394" t="n">
-        <v>2.25052809715271</v>
+        <v>2.25052833557129</v>
       </c>
       <c r="H394" t="n">
         <v>49928</v>
@@ -11824,7 +11824,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G395" t="n">
-        <v>2.26615691184998</v>
+        <v>2.26615715026855</v>
       </c>
       <c r="H395" t="n">
         <v>27151</v>
@@ -11853,7 +11853,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G396" t="n">
-        <v>2.22708487510681</v>
+        <v>2.22708511352539</v>
       </c>
       <c r="H396" t="n">
         <v>21203</v>
@@ -11882,7 +11882,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G397" t="n">
-        <v>2.21145629882812</v>
+        <v>2.2114565372467</v>
       </c>
       <c r="H397" t="n">
         <v>14364</v>
@@ -11940,7 +11940,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G399" t="n">
-        <v>2.25834250450134</v>
+        <v>2.25834274291992</v>
       </c>
       <c r="H399" t="n">
         <v>9326</v>
@@ -11969,7 +11969,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G400" t="n">
-        <v>2.25052809715271</v>
+        <v>2.25052833557129</v>
       </c>
       <c r="H400" t="n">
         <v>125043</v>
@@ -12114,7 +12114,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G405" t="n">
-        <v>2.26615691184998</v>
+        <v>2.26615715026855</v>
       </c>
       <c r="H405" t="n">
         <v>3645</v>
@@ -12143,7 +12143,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G406" t="n">
-        <v>2.24271368980408</v>
+        <v>2.24271392822266</v>
       </c>
       <c r="H406" t="n">
         <v>10421</v>
@@ -12172,7 +12172,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G407" t="n">
-        <v>2.26615691184998</v>
+        <v>2.26615715026855</v>
       </c>
       <c r="H407" t="n">
         <v>13225</v>
@@ -12230,7 +12230,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G409" t="n">
-        <v>2.25052809715271</v>
+        <v>2.25052833557129</v>
       </c>
       <c r="H409" t="n">
         <v>3826</v>
@@ -12288,7 +12288,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G411" t="n">
-        <v>2.26615691184998</v>
+        <v>2.26615715026855</v>
       </c>
       <c r="H411" t="n">
         <v>4008</v>
@@ -12317,7 +12317,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G412" t="n">
-        <v>2.25052809715271</v>
+        <v>2.25052833557129</v>
       </c>
       <c r="H412" t="n">
         <v>13597</v>
@@ -12346,7 +12346,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G413" t="n">
-        <v>2.24271368980408</v>
+        <v>2.24271392822266</v>
       </c>
       <c r="H413" t="n">
         <v>8588</v>
@@ -12375,7 +12375,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G414" t="n">
-        <v>2.22708487510681</v>
+        <v>2.22708511352539</v>
       </c>
       <c r="H414" t="n">
         <v>16306</v>
@@ -12404,7 +12404,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G415" t="n">
-        <v>2.22708487510681</v>
+        <v>2.22708511352539</v>
       </c>
       <c r="H415" t="n">
         <v>4789</v>
@@ -12433,7 +12433,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G416" t="n">
-        <v>2.25052809715271</v>
+        <v>2.25052833557129</v>
       </c>
       <c r="H416" t="n">
         <v>4039</v>
@@ -12462,7 +12462,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G417" t="n">
-        <v>2.25834250450134</v>
+        <v>2.25834274291992</v>
       </c>
       <c r="H417" t="n">
         <v>1700</v>
@@ -12520,7 +12520,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G419" t="n">
-        <v>2.25052809715271</v>
+        <v>2.25052833557129</v>
       </c>
       <c r="H419" t="n">
         <v>6100</v>
@@ -12549,7 +12549,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G420" t="n">
-        <v>2.24271368980408</v>
+        <v>2.24271392822266</v>
       </c>
       <c r="H420" t="n">
         <v>4693</v>
@@ -12578,7 +12578,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G421" t="n">
-        <v>2.25052809715271</v>
+        <v>2.25052833557129</v>
       </c>
       <c r="H421" t="n">
         <v>5308</v>
@@ -12607,7 +12607,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G422" t="n">
-        <v>2.25052809715271</v>
+        <v>2.25052833557129</v>
       </c>
       <c r="H422" t="n">
         <v>13271</v>
@@ -12636,7 +12636,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G423" t="n">
-        <v>2.25834250450134</v>
+        <v>2.25834274291992</v>
       </c>
       <c r="H423" t="n">
         <v>19254</v>
@@ -12665,7 +12665,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G424" t="n">
-        <v>2.25834250450134</v>
+        <v>2.25834274291992</v>
       </c>
       <c r="H424" t="n">
         <v>2892</v>
@@ -12694,7 +12694,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G425" t="n">
-        <v>2.24271368980408</v>
+        <v>2.24271392822266</v>
       </c>
       <c r="H425" t="n">
         <v>22550</v>
@@ -12839,7 +12839,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G430" t="n">
-        <v>2.26615691184998</v>
+        <v>2.26615715026855</v>
       </c>
       <c r="H430" t="n">
         <v>3551</v>
@@ -12955,7 +12955,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G434" t="n">
-        <v>2.30522847175598</v>
+        <v>2.30522871017456</v>
       </c>
       <c r="H434" t="n">
         <v>3559</v>
@@ -13100,7 +13100,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G439" t="n">
-        <v>2.30522847175598</v>
+        <v>2.30522871017456</v>
       </c>
       <c r="H439" t="n">
         <v>7059</v>
@@ -13216,7 +13216,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G443" t="n">
-        <v>2.35992884635925</v>
+        <v>2.35992908477783</v>
       </c>
       <c r="H443" t="n">
         <v>25888</v>
@@ -13274,7 +13274,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G445" t="n">
-        <v>2.32085728645325</v>
+        <v>2.32085752487183</v>
       </c>
       <c r="H445" t="n">
         <v>109510</v>
@@ -13390,7 +13390,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G449" t="n">
-        <v>2.31304287910461</v>
+        <v>2.31304311752319</v>
       </c>
       <c r="H449" t="n">
         <v>8698</v>
@@ -13506,7 +13506,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G453" t="n">
-        <v>2.25834250450134</v>
+        <v>2.25834274291992</v>
       </c>
       <c r="H453" t="n">
         <v>12264</v>
@@ -13535,7 +13535,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G454" t="n">
-        <v>2.25834250450134</v>
+        <v>2.25834274291992</v>
       </c>
       <c r="H454" t="n">
         <v>3217</v>
@@ -13564,7 +13564,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G455" t="n">
-        <v>2.25052809715271</v>
+        <v>2.25052833557129</v>
       </c>
       <c r="H455" t="n">
         <v>4720</v>
@@ -13622,7 +13622,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G457" t="n">
-        <v>2.26615691184998</v>
+        <v>2.26615715026855</v>
       </c>
       <c r="H457" t="n">
         <v>12905</v>
@@ -13651,7 +13651,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G458" t="n">
-        <v>2.26615691184998</v>
+        <v>2.26615715026855</v>
       </c>
       <c r="H458" t="n">
         <v>5857</v>
@@ -13709,7 +13709,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G460" t="n">
-        <v>2.26615691184998</v>
+        <v>2.26615715026855</v>
       </c>
       <c r="H460" t="n">
         <v>5248</v>
@@ -13767,7 +13767,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G462" t="n">
-        <v>2.25834250450134</v>
+        <v>2.25834274291992</v>
       </c>
       <c r="H462" t="n">
         <v>11311</v>
@@ -13825,7 +13825,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G464" t="n">
-        <v>2.25834250450134</v>
+        <v>2.25834274291992</v>
       </c>
       <c r="H464" t="n">
         <v>893</v>
@@ -13854,7 +13854,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G465" t="n">
-        <v>2.25052809715271</v>
+        <v>2.25052833557129</v>
       </c>
       <c r="H465" t="n">
         <v>7854</v>
@@ -13883,7 +13883,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G466" t="n">
-        <v>2.24271368980408</v>
+        <v>2.24271392822266</v>
       </c>
       <c r="H466" t="n">
         <v>8835</v>
@@ -13912,7 +13912,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G467" t="n">
-        <v>2.25052809715271</v>
+        <v>2.25052833557129</v>
       </c>
       <c r="H467" t="n">
         <v>6429</v>
@@ -13941,7 +13941,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G468" t="n">
-        <v>2.24271368980408</v>
+        <v>2.24271392822266</v>
       </c>
       <c r="H468" t="n">
         <v>4382</v>
@@ -13970,7 +13970,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G469" t="n">
-        <v>2.24271368980408</v>
+        <v>2.24271392822266</v>
       </c>
       <c r="H469" t="n">
         <v>5207</v>
@@ -13999,7 +13999,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G470" t="n">
-        <v>2.25052809715271</v>
+        <v>2.25052833557129</v>
       </c>
       <c r="H470" t="n">
         <v>4682</v>
@@ -14028,7 +14028,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G471" t="n">
-        <v>2.25834250450134</v>
+        <v>2.25834274291992</v>
       </c>
       <c r="H471" t="n">
         <v>5598</v>
@@ -14057,7 +14057,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G472" t="n">
-        <v>2.24271368980408</v>
+        <v>2.24271392822266</v>
       </c>
       <c r="H472" t="n">
         <v>5970</v>
@@ -14086,7 +14086,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G473" t="n">
-        <v>2.25834250450134</v>
+        <v>2.25834274291992</v>
       </c>
       <c r="H473" t="n">
         <v>2692</v>
@@ -14144,7 +14144,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G475" t="n">
-        <v>2.26615691184998</v>
+        <v>2.26615715026855</v>
       </c>
       <c r="H475" t="n">
         <v>6319</v>
@@ -14173,7 +14173,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G476" t="n">
-        <v>2.26615691184998</v>
+        <v>2.26615715026855</v>
       </c>
       <c r="H476" t="n">
         <v>11654</v>
@@ -14202,7 +14202,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G477" t="n">
-        <v>2.26615691184998</v>
+        <v>2.26615715026855</v>
       </c>
       <c r="H477" t="n">
         <v>9741</v>
@@ -14231,7 +14231,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G478" t="n">
-        <v>2.25052809715271</v>
+        <v>2.25052833557129</v>
       </c>
       <c r="H478" t="n">
         <v>13054</v>
@@ -14260,7 +14260,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G479" t="n">
-        <v>2.21927070617676</v>
+        <v>2.21927094459534</v>
       </c>
       <c r="H479" t="n">
         <v>14483</v>
@@ -14289,7 +14289,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G480" t="n">
-        <v>2.18801355361938</v>
+        <v>2.18801331520081</v>
       </c>
       <c r="H480" t="n">
         <v>127127</v>
@@ -14318,7 +14318,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G481" t="n">
-        <v>2.11768484115601</v>
+        <v>2.11768460273743</v>
       </c>
       <c r="H481" t="n">
         <v>18942</v>
@@ -14405,7 +14405,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G484" t="n">
-        <v>2.06298446655273</v>
+        <v>2.06298422813416</v>
       </c>
       <c r="H484" t="n">
         <v>4500</v>
@@ -14463,7 +14463,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G486" t="n">
-        <v>2.07079887390137</v>
+        <v>2.07079863548279</v>
       </c>
       <c r="H486" t="n">
         <v>9534</v>
@@ -14521,7 +14521,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G488" t="n">
-        <v>2.09424161911011</v>
+        <v>2.09424138069153</v>
       </c>
       <c r="H488" t="n">
         <v>6344</v>
@@ -14579,7 +14579,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G490" t="n">
-        <v>2.03954124450684</v>
+        <v>2.03954100608826</v>
       </c>
       <c r="H490" t="n">
         <v>11032</v>
@@ -14637,7 +14637,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G492" t="n">
-        <v>1.99265539646149</v>
+        <v>1.99265480041504</v>
       </c>
       <c r="H492" t="n">
         <v>39507</v>
@@ -14695,7 +14695,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G494" t="n">
-        <v>2.02391242980957</v>
+        <v>2.02391266822815</v>
       </c>
       <c r="H494" t="n">
         <v>4454</v>
@@ -14724,7 +14724,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G495" t="n">
-        <v>2.02391242980957</v>
+        <v>2.02391266822815</v>
       </c>
       <c r="H495" t="n">
         <v>1453</v>
@@ -14782,7 +14782,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G497" t="n">
-        <v>1.99265539646149</v>
+        <v>1.99265480041504</v>
       </c>
       <c r="H497" t="n">
         <v>2512</v>
@@ -14985,7 +14985,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G504" t="n">
-        <v>1.99265539646149</v>
+        <v>1.99265480041504</v>
       </c>
       <c r="H504" t="n">
         <v>3080</v>
@@ -15391,7 +15391,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G518" t="n">
-        <v>2.09424161911011</v>
+        <v>2.09424138069153</v>
       </c>
       <c r="H518" t="n">
         <v>112388</v>
@@ -15420,7 +15420,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G519" t="n">
-        <v>2.08642745018005</v>
+        <v>2.0864269733429</v>
       </c>
       <c r="H519" t="n">
         <v>11274</v>
@@ -15449,7 +15449,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G520" t="n">
-        <v>2.07861304283142</v>
+        <v>2.07861280441284</v>
       </c>
       <c r="H520" t="n">
         <v>10226</v>
@@ -15478,7 +15478,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G521" t="n">
-        <v>2.06298446655273</v>
+        <v>2.06298422813416</v>
       </c>
       <c r="H521" t="n">
         <v>14270</v>
@@ -15536,7 +15536,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G523" t="n">
-        <v>2.08642745018005</v>
+        <v>2.0864269733429</v>
       </c>
       <c r="H523" t="n">
         <v>9758</v>
@@ -15739,7 +15739,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G530" t="n">
-        <v>2.08642745018005</v>
+        <v>2.0864269733429</v>
       </c>
       <c r="H530" t="n">
         <v>11459</v>
@@ -15768,7 +15768,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G531" t="n">
-        <v>2.07861304283142</v>
+        <v>2.07861280441284</v>
       </c>
       <c r="H531" t="n">
         <v>7675</v>
@@ -15797,7 +15797,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G532" t="n">
-        <v>2.03954124450684</v>
+        <v>2.03954100608826</v>
       </c>
       <c r="H532" t="n">
         <v>7408</v>
@@ -15826,7 +15826,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G533" t="n">
-        <v>2.03954124450684</v>
+        <v>2.03954100608826</v>
       </c>
       <c r="H533" t="n">
         <v>1950</v>
@@ -16029,7 +16029,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G540" t="n">
-        <v>1.97702646255493</v>
+        <v>1.97702634334564</v>
       </c>
       <c r="H540" t="n">
         <v>1849</v>
@@ -16058,7 +16058,7 @@
         <v>2.5</v>
       </c>
       <c r="G541" t="n">
-        <v>1.95358335971832</v>
+        <v>1.95358347892761</v>
       </c>
       <c r="H541" t="n">
         <v>1628</v>
@@ -16116,7 +16116,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G543" t="n">
-        <v>1.92232608795166</v>
+        <v>1.92232620716095</v>
       </c>
       <c r="H543" t="n">
         <v>2000</v>
@@ -16203,7 +16203,7 @@
         <v>2.5</v>
       </c>
       <c r="G546" t="n">
-        <v>1.95358335971832</v>
+        <v>1.95358347892761</v>
       </c>
       <c r="H546" t="n">
         <v>13540</v>
@@ -16232,7 +16232,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G547" t="n">
-        <v>1.96921217441559</v>
+        <v>1.96921193599701</v>
       </c>
       <c r="H547" t="n">
         <v>4409</v>
@@ -16261,7 +16261,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G548" t="n">
-        <v>1.96921217441559</v>
+        <v>1.96921193599701</v>
       </c>
       <c r="H548" t="n">
         <v>2935</v>
@@ -16290,7 +16290,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G549" t="n">
-        <v>1.93795490264893</v>
+        <v>1.93795478343964</v>
       </c>
       <c r="H549" t="n">
         <v>78</v>
@@ -16377,7 +16377,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G552" t="n">
-        <v>2.02391242980957</v>
+        <v>2.02391266822815</v>
       </c>
       <c r="H552" t="n">
         <v>3342</v>
@@ -16435,7 +16435,7 @@
         <v>2.5</v>
       </c>
       <c r="G554" t="n">
-        <v>1.95358335971832</v>
+        <v>1.95358347892761</v>
       </c>
       <c r="H554" t="n">
         <v>801</v>
@@ -16551,7 +16551,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G558" t="n">
-        <v>1.88325452804565</v>
+        <v>1.88325476646423</v>
       </c>
       <c r="H558" t="n">
         <v>7999</v>
@@ -16609,7 +16609,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G560" t="n">
-        <v>1.89888298511505</v>
+        <v>1.89888322353363</v>
       </c>
       <c r="H560" t="n">
         <v>4094</v>
@@ -16638,7 +16638,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G561" t="n">
-        <v>1.89888298511505</v>
+        <v>1.89888322353363</v>
       </c>
       <c r="H561" t="n">
         <v>2899</v>
@@ -16667,7 +16667,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G562" t="n">
-        <v>1.88325452804565</v>
+        <v>1.88325476646423</v>
       </c>
       <c r="H562" t="n">
         <v>12511</v>
@@ -16696,7 +16696,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G563" t="n">
-        <v>1.90669739246368</v>
+        <v>1.90669775009155</v>
       </c>
       <c r="H563" t="n">
         <v>3670</v>
@@ -16725,7 +16725,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G564" t="n">
-        <v>1.90669739246368</v>
+        <v>1.90669775009155</v>
       </c>
       <c r="H564" t="n">
         <v>290</v>
@@ -16870,7 +16870,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G569" t="n">
-        <v>1.84418261051178</v>
+        <v>1.84418272972107</v>
       </c>
       <c r="H569" t="n">
         <v>2584</v>
@@ -16899,7 +16899,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G570" t="n">
-        <v>1.92232608795166</v>
+        <v>1.92232620716095</v>
       </c>
       <c r="H570" t="n">
         <v>34637</v>
@@ -17015,7 +17015,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G574" t="n">
-        <v>2.03954124450684</v>
+        <v>2.03954100608826</v>
       </c>
       <c r="H574" t="n">
         <v>1270</v>
@@ -17102,7 +17102,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G577" t="n">
-        <v>2.06298446655273</v>
+        <v>2.06298422813416</v>
       </c>
       <c r="H577" t="n">
         <v>25388</v>
@@ -17160,7 +17160,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G579" t="n">
-        <v>2.03954124450684</v>
+        <v>2.03954100608826</v>
       </c>
       <c r="H579" t="n">
         <v>4138</v>
@@ -17334,7 +17334,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G585" t="n">
-        <v>1.97702646255493</v>
+        <v>1.97702634334564</v>
       </c>
       <c r="H585" t="n">
         <v>2222</v>
@@ -17363,7 +17363,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G586" t="n">
-        <v>2.02391242980957</v>
+        <v>2.02391266822815</v>
       </c>
       <c r="H586" t="n">
         <v>4748</v>
@@ -17421,7 +17421,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G588" t="n">
-        <v>1.96921217441559</v>
+        <v>1.96921193599701</v>
       </c>
       <c r="H588" t="n">
         <v>1223</v>
@@ -17450,7 +17450,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G589" t="n">
-        <v>1.97702646255493</v>
+        <v>1.97702634334564</v>
       </c>
       <c r="H589" t="n">
         <v>1767</v>
@@ -17479,7 +17479,7 @@
         <v>2.5</v>
       </c>
       <c r="G590" t="n">
-        <v>1.95358335971832</v>
+        <v>1.95358347892761</v>
       </c>
       <c r="H590" t="n">
         <v>6559</v>
@@ -17508,7 +17508,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G591" t="n">
-        <v>1.93795490264893</v>
+        <v>1.93795478343964</v>
       </c>
       <c r="H591" t="n">
         <v>11871</v>
@@ -17537,7 +17537,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G592" t="n">
-        <v>1.96921217441559</v>
+        <v>1.96921193599701</v>
       </c>
       <c r="H592" t="n">
         <v>100</v>
@@ -17566,7 +17566,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G593" t="n">
-        <v>1.89888298511505</v>
+        <v>1.89888322353363</v>
       </c>
       <c r="H593" t="n">
         <v>219</v>
@@ -17595,7 +17595,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G594" t="n">
-        <v>1.96921217441559</v>
+        <v>1.96921193599701</v>
       </c>
       <c r="H594" t="n">
         <v>28</v>
@@ -17624,7 +17624,7 @@
         <v>2.5</v>
       </c>
       <c r="G595" t="n">
-        <v>1.95358335971832</v>
+        <v>1.95358347892761</v>
       </c>
       <c r="H595" t="n">
         <v>2570</v>
@@ -17653,7 +17653,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G596" t="n">
-        <v>1.93014049530029</v>
+        <v>1.93014061450958</v>
       </c>
       <c r="H596" t="n">
         <v>321</v>
@@ -17682,7 +17682,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G597" t="n">
-        <v>1.93014049530029</v>
+        <v>1.93014061450958</v>
       </c>
       <c r="H597" t="n">
         <v>1300</v>
@@ -17711,7 +17711,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G598" t="n">
-        <v>1.93795490264893</v>
+        <v>1.93795478343964</v>
       </c>
       <c r="H598" t="n">
         <v>301</v>
@@ -17885,7 +17885,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G604" t="n">
-        <v>1.93795490264893</v>
+        <v>1.93795478343964</v>
       </c>
       <c r="H604" t="n">
         <v>100</v>
@@ -18030,7 +18030,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G609" t="n">
-        <v>1.85199689865112</v>
+        <v>1.85199701786041</v>
       </c>
       <c r="H609" t="n">
         <v>700</v>
@@ -18059,7 +18059,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G610" t="n">
-        <v>1.84418261051178</v>
+        <v>1.84418272972107</v>
       </c>
       <c r="H610" t="n">
         <v>4036</v>
@@ -18088,7 +18088,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G611" t="n">
-        <v>1.84418261051178</v>
+        <v>1.84418272972107</v>
       </c>
       <c r="H611" t="n">
         <v>937</v>
@@ -18117,7 +18117,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G612" t="n">
-        <v>1.85981154441833</v>
+        <v>1.85981166362762</v>
       </c>
       <c r="H612" t="n">
         <v>992</v>
@@ -18146,7 +18146,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G613" t="n">
-        <v>1.78166830539703</v>
+        <v>1.78166818618774</v>
       </c>
       <c r="H613" t="n">
         <v>2844</v>
@@ -18175,7 +18175,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G614" t="n">
-        <v>1.79729688167572</v>
+        <v>1.79729676246643</v>
       </c>
       <c r="H614" t="n">
         <v>10850</v>
@@ -18204,7 +18204,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G615" t="n">
-        <v>1.88325452804565</v>
+        <v>1.88325476646423</v>
       </c>
       <c r="H615" t="n">
         <v>100</v>
@@ -18233,7 +18233,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G616" t="n">
-        <v>1.88325452804565</v>
+        <v>1.88325476646423</v>
       </c>
       <c r="H616" t="n">
         <v>0</v>
@@ -18291,7 +18291,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G618" t="n">
-        <v>1.84418261051178</v>
+        <v>1.84418272972107</v>
       </c>
       <c r="H618" t="n">
         <v>2111</v>
@@ -18349,7 +18349,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G620" t="n">
-        <v>1.82073962688446</v>
+        <v>1.82073986530304</v>
       </c>
       <c r="H620" t="n">
         <v>2510</v>
@@ -18407,7 +18407,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G622" t="n">
-        <v>1.84418261051178</v>
+        <v>1.84418272972107</v>
       </c>
       <c r="H622" t="n">
         <v>1654</v>
@@ -18436,7 +18436,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G623" t="n">
-        <v>1.92232608795166</v>
+        <v>1.92232620716095</v>
       </c>
       <c r="H623" t="n">
         <v>678</v>
@@ -18552,7 +18552,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G627" t="n">
-        <v>1.82073962688446</v>
+        <v>1.82073986530304</v>
       </c>
       <c r="H627" t="n">
         <v>5337</v>
@@ -18581,7 +18581,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G628" t="n">
-        <v>1.85199689865112</v>
+        <v>1.85199701786041</v>
       </c>
       <c r="H628" t="n">
         <v>767</v>
@@ -18610,7 +18610,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G629" t="n">
-        <v>1.83636832237244</v>
+        <v>1.83636844158173</v>
       </c>
       <c r="H629" t="n">
         <v>2700</v>
@@ -18639,7 +18639,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G630" t="n">
-        <v>1.84418261051178</v>
+        <v>1.84418272972107</v>
       </c>
       <c r="H630" t="n">
         <v>470</v>
@@ -18668,7 +18668,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G631" t="n">
-        <v>1.79729688167572</v>
+        <v>1.79729676246643</v>
       </c>
       <c r="H631" t="n">
         <v>1387</v>
@@ -18697,7 +18697,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G632" t="n">
-        <v>1.76603960990906</v>
+        <v>1.76603949069977</v>
       </c>
       <c r="H632" t="n">
         <v>2150</v>
@@ -18726,7 +18726,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G633" t="n">
-        <v>1.76603960990906</v>
+        <v>1.76603949069977</v>
       </c>
       <c r="H633" t="n">
         <v>0</v>
@@ -18755,7 +18755,7 @@
         <v>2.25</v>
       </c>
       <c r="G634" t="n">
-        <v>1.75822520256042</v>
+        <v>1.75822532176971</v>
       </c>
       <c r="H634" t="n">
         <v>3308</v>
@@ -18784,7 +18784,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G635" t="n">
-        <v>1.72696805000305</v>
+        <v>1.72696781158447</v>
       </c>
       <c r="H635" t="n">
         <v>2340</v>
@@ -18842,7 +18842,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G637" t="n">
-        <v>1.78166830539703</v>
+        <v>1.78166818618774</v>
       </c>
       <c r="H637" t="n">
         <v>4216</v>
@@ -18871,7 +18871,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G638" t="n">
-        <v>1.82073962688446</v>
+        <v>1.82073986530304</v>
       </c>
       <c r="H638" t="n">
         <v>1300</v>
@@ -19190,7 +19190,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G649" t="n">
-        <v>1.70352494716644</v>
+        <v>1.70352470874786</v>
       </c>
       <c r="H649" t="n">
         <v>1910</v>
@@ -19248,7 +19248,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G651" t="n">
-        <v>1.68008196353912</v>
+        <v>1.68008184432983</v>
       </c>
       <c r="H651" t="n">
         <v>2312</v>
@@ -19277,7 +19277,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G652" t="n">
-        <v>1.68008196353912</v>
+        <v>1.68008184432983</v>
       </c>
       <c r="H652" t="n">
         <v>3142</v>
@@ -19364,7 +19364,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G655" t="n">
-        <v>1.61756694316864</v>
+        <v>1.61756718158722</v>
       </c>
       <c r="H655" t="n">
         <v>2957</v>
@@ -19393,7 +19393,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G656" t="n">
-        <v>1.61756694316864</v>
+        <v>1.61756718158722</v>
       </c>
       <c r="H656" t="n">
         <v>4076</v>
@@ -19451,7 +19451,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G658" t="n">
-        <v>1.59412407875061</v>
+        <v>1.5941241979599</v>
       </c>
       <c r="H658" t="n">
         <v>5786</v>
@@ -19480,7 +19480,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G659" t="n">
-        <v>1.60193836688995</v>
+        <v>1.60193848609924</v>
       </c>
       <c r="H659" t="n">
         <v>9353</v>
@@ -19509,7 +19509,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G660" t="n">
-        <v>1.64101004600525</v>
+        <v>1.64101016521454</v>
       </c>
       <c r="H660" t="n">
         <v>2150</v>
@@ -19538,7 +19538,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G661" t="n">
-        <v>1.60193836688995</v>
+        <v>1.60193848609924</v>
       </c>
       <c r="H661" t="n">
         <v>790</v>
@@ -19567,7 +19567,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G662" t="n">
-        <v>1.6097526550293</v>
+        <v>1.60975289344788</v>
       </c>
       <c r="H662" t="n">
         <v>1581</v>
@@ -19625,7 +19625,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G664" t="n">
-        <v>1.5550525188446</v>
+        <v>1.55505263805389</v>
       </c>
       <c r="H664" t="n">
         <v>7681</v>
@@ -19654,7 +19654,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G665" t="n">
-        <v>2.06298446655273</v>
+        <v>2.06298422813416</v>
       </c>
       <c r="H665" t="n">
         <v>130384</v>
@@ -19683,7 +19683,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G666" t="n">
-        <v>1.92232608795166</v>
+        <v>1.92232620716095</v>
       </c>
       <c r="H666" t="n">
         <v>446846</v>
@@ -19741,7 +19741,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G668" t="n">
-        <v>1.88325452804565</v>
+        <v>1.88325476646423</v>
       </c>
       <c r="H668" t="n">
         <v>20273</v>
@@ -19770,7 +19770,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G669" t="n">
-        <v>1.92232608795166</v>
+        <v>1.92232620716095</v>
       </c>
       <c r="H669" t="n">
         <v>32286</v>
@@ -19799,7 +19799,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G670" t="n">
-        <v>1.99265539646149</v>
+        <v>1.99265480041504</v>
       </c>
       <c r="H670" t="n">
         <v>78330</v>
@@ -19828,7 +19828,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G671" t="n">
-        <v>1.93014049530029</v>
+        <v>1.93014061450958</v>
       </c>
       <c r="H671" t="n">
         <v>41175</v>
@@ -19857,7 +19857,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G672" t="n">
-        <v>1.89888298511505</v>
+        <v>1.89888322353363</v>
       </c>
       <c r="H672" t="n">
         <v>10847</v>
@@ -19886,7 +19886,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G673" t="n">
-        <v>1.92232608795166</v>
+        <v>1.92232620716095</v>
       </c>
       <c r="H673" t="n">
         <v>37391</v>
@@ -19915,7 +19915,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G674" t="n">
-        <v>1.97702646255493</v>
+        <v>1.97702634334564</v>
       </c>
       <c r="H674" t="n">
         <v>10462</v>
@@ -20002,7 +20002,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G677" t="n">
-        <v>1.88325452804565</v>
+        <v>1.88325476646423</v>
       </c>
       <c r="H677" t="n">
         <v>24276</v>
@@ -20031,7 +20031,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G678" t="n">
-        <v>1.8285539150238</v>
+        <v>1.82855415344238</v>
       </c>
       <c r="H678" t="n">
         <v>7847</v>
@@ -20060,7 +20060,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G679" t="n">
-        <v>1.85981154441833</v>
+        <v>1.85981166362762</v>
       </c>
       <c r="H679" t="n">
         <v>1203</v>
@@ -20089,7 +20089,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G680" t="n">
-        <v>1.8285539150238</v>
+        <v>1.82855415344238</v>
       </c>
       <c r="H680" t="n">
         <v>4199</v>
@@ -20118,7 +20118,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G681" t="n">
-        <v>1.76603960990906</v>
+        <v>1.76603949069977</v>
       </c>
       <c r="H681" t="n">
         <v>6126</v>
@@ -20147,7 +20147,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G682" t="n">
-        <v>1.70352494716644</v>
+        <v>1.70352470874786</v>
       </c>
       <c r="H682" t="n">
         <v>21460</v>
@@ -20205,7 +20205,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G684" t="n">
-        <v>1.82073962688446</v>
+        <v>1.82073986530304</v>
       </c>
       <c r="H684" t="n">
         <v>79297</v>
@@ -20234,7 +20234,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G685" t="n">
-        <v>1.76603960990906</v>
+        <v>1.76603949069977</v>
       </c>
       <c r="H685" t="n">
         <v>13837</v>
@@ -20263,7 +20263,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G686" t="n">
-        <v>1.78166830539703</v>
+        <v>1.78166818618774</v>
       </c>
       <c r="H686" t="n">
         <v>16568</v>
@@ -20292,7 +20292,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G687" t="n">
-        <v>1.76603960990906</v>
+        <v>1.76603949069977</v>
       </c>
       <c r="H687" t="n">
         <v>11052</v>
@@ -20321,7 +20321,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G688" t="n">
-        <v>1.76603960990906</v>
+        <v>1.76603949069977</v>
       </c>
       <c r="H688" t="n">
         <v>8342</v>
@@ -20350,7 +20350,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G689" t="n">
-        <v>1.78166830539703</v>
+        <v>1.78166818618774</v>
       </c>
       <c r="H689" t="n">
         <v>4504</v>
@@ -20437,7 +20437,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G692" t="n">
-        <v>1.70352494716644</v>
+        <v>1.70352470874786</v>
       </c>
       <c r="H692" t="n">
         <v>29415</v>
@@ -20582,7 +20582,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G697" t="n">
-        <v>1.68008196353912</v>
+        <v>1.68008184432983</v>
       </c>
       <c r="H697" t="n">
         <v>5973</v>
@@ -20611,7 +20611,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G698" t="n">
-        <v>1.68008196353912</v>
+        <v>1.68008184432983</v>
       </c>
       <c r="H698" t="n">
         <v>6783</v>
@@ -20669,7 +20669,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G700" t="n">
-        <v>1.78166830539703</v>
+        <v>1.78166818618774</v>
       </c>
       <c r="H700" t="n">
         <v>16469</v>
@@ -20698,7 +20698,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G701" t="n">
-        <v>1.70352494716644</v>
+        <v>1.70352470874786</v>
       </c>
       <c r="H701" t="n">
         <v>20038</v>
@@ -20727,7 +20727,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G702" t="n">
-        <v>1.69571053981781</v>
+        <v>1.69571042060852</v>
       </c>
       <c r="H702" t="n">
         <v>42863</v>
@@ -20814,7 +20814,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G705" t="n">
-        <v>1.69571053981781</v>
+        <v>1.69571042060852</v>
       </c>
       <c r="H705" t="n">
         <v>9685</v>
@@ -20901,7 +20901,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G708" t="n">
-        <v>1.64101004600525</v>
+        <v>1.64101016521454</v>
       </c>
       <c r="H708" t="n">
         <v>1684</v>
@@ -20959,7 +20959,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G710" t="n">
-        <v>1.6331958770752</v>
+        <v>1.63319575786591</v>
       </c>
       <c r="H710" t="n">
         <v>5696</v>
@@ -20988,7 +20988,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G711" t="n">
-        <v>1.68008196353912</v>
+        <v>1.68008184432983</v>
       </c>
       <c r="H711" t="n">
         <v>1343</v>
@@ -21017,7 +21017,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G712" t="n">
-        <v>1.68008196353912</v>
+        <v>1.68008184432983</v>
       </c>
       <c r="H712" t="n">
         <v>1105</v>
@@ -21046,7 +21046,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G713" t="n">
-        <v>1.6331958770752</v>
+        <v>1.63319575786591</v>
       </c>
       <c r="H713" t="n">
         <v>1527</v>
@@ -21075,7 +21075,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G714" t="n">
-        <v>1.64101004600525</v>
+        <v>1.64101016521454</v>
       </c>
       <c r="H714" t="n">
         <v>318</v>
@@ -21104,7 +21104,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G715" t="n">
-        <v>1.61756694316864</v>
+        <v>1.61756718158722</v>
       </c>
       <c r="H715" t="n">
         <v>5893</v>
@@ -21133,7 +21133,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G716" t="n">
-        <v>1.61756694316864</v>
+        <v>1.61756718158722</v>
       </c>
       <c r="H716" t="n">
         <v>15324</v>
@@ -21162,7 +21162,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G717" t="n">
-        <v>1.58630967140198</v>
+        <v>1.58630979061127</v>
       </c>
       <c r="H717" t="n">
         <v>4983</v>
@@ -21220,7 +21220,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G719" t="n">
-        <v>1.54723811149597</v>
+        <v>1.54723823070526</v>
       </c>
       <c r="H719" t="n">
         <v>9044</v>
@@ -21249,7 +21249,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G720" t="n">
-        <v>1.57068121433258</v>
+        <v>1.57068109512329</v>
       </c>
       <c r="H720" t="n">
         <v>7076</v>
@@ -21278,7 +21278,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G721" t="n">
-        <v>1.54723811149597</v>
+        <v>1.54723823070526</v>
       </c>
       <c r="H721" t="n">
         <v>4279</v>
@@ -21307,7 +21307,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G722" t="n">
-        <v>1.61756694316864</v>
+        <v>1.61756718158722</v>
       </c>
       <c r="H722" t="n">
         <v>3905</v>
@@ -21336,7 +21336,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G723" t="n">
-        <v>1.60193836688995</v>
+        <v>1.60193848609924</v>
       </c>
       <c r="H723" t="n">
         <v>33</v>
@@ -21365,7 +21365,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G724" t="n">
-        <v>1.60193836688995</v>
+        <v>1.60193848609924</v>
       </c>
       <c r="H724" t="n">
         <v>1593</v>
@@ -21394,7 +21394,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G725" t="n">
-        <v>1.60193836688995</v>
+        <v>1.60193848609924</v>
       </c>
       <c r="H725" t="n">
         <v>772</v>
@@ -21423,7 +21423,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G726" t="n">
-        <v>1.60193836688995</v>
+        <v>1.60193848609924</v>
       </c>
       <c r="H726" t="n">
         <v>1638</v>
@@ -21452,7 +21452,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G727" t="n">
-        <v>1.60193836688995</v>
+        <v>1.60193848609924</v>
       </c>
       <c r="H727" t="n">
         <v>0</v>
@@ -21481,7 +21481,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G728" t="n">
-        <v>1.59412407875061</v>
+        <v>1.5941241979599</v>
       </c>
       <c r="H728" t="n">
         <v>2500</v>
@@ -21510,7 +21510,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G729" t="n">
-        <v>1.57068121433258</v>
+        <v>1.57068109512329</v>
       </c>
       <c r="H729" t="n">
         <v>530</v>
@@ -21539,7 +21539,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G730" t="n">
-        <v>1.57068121433258</v>
+        <v>1.57068109512329</v>
       </c>
       <c r="H730" t="n">
         <v>1325</v>
@@ -21568,7 +21568,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G731" t="n">
-        <v>1.54723811149597</v>
+        <v>1.54723823070526</v>
       </c>
       <c r="H731" t="n">
         <v>2640</v>
@@ -21597,7 +21597,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G732" t="n">
-        <v>1.60193836688995</v>
+        <v>1.60193848609924</v>
       </c>
       <c r="H732" t="n">
         <v>686</v>
@@ -21626,7 +21626,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G733" t="n">
-        <v>1.54723811149597</v>
+        <v>1.54723823070526</v>
       </c>
       <c r="H733" t="n">
         <v>10612</v>
@@ -21684,7 +21684,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G735" t="n">
-        <v>1.5550525188446</v>
+        <v>1.55505263805389</v>
       </c>
       <c r="H735" t="n">
         <v>5470</v>
@@ -21713,7 +21713,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G736" t="n">
-        <v>1.531609416008</v>
+        <v>1.53160953521729</v>
       </c>
       <c r="H736" t="n">
         <v>1180</v>
@@ -21742,7 +21742,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G737" t="n">
-        <v>1.50816643238068</v>
+        <v>1.50816655158997</v>
       </c>
       <c r="H737" t="n">
         <v>2610</v>
@@ -21771,7 +21771,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G738" t="n">
-        <v>1.50035226345062</v>
+        <v>1.50035214424133</v>
       </c>
       <c r="H738" t="n">
         <v>3783</v>
@@ -21800,7 +21800,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G739" t="n">
-        <v>1.49253797531128</v>
+        <v>1.49253785610199</v>
       </c>
       <c r="H739" t="n">
         <v>1588</v>
@@ -21829,7 +21829,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G740" t="n">
-        <v>1.531609416008</v>
+        <v>1.53160953521729</v>
       </c>
       <c r="H740" t="n">
         <v>1201</v>
@@ -21858,7 +21858,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G741" t="n">
-        <v>1.50035226345062</v>
+        <v>1.50035214424133</v>
       </c>
       <c r="H741" t="n">
         <v>1657</v>
@@ -21887,7 +21887,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G742" t="n">
-        <v>1.50816643238068</v>
+        <v>1.50816655158997</v>
       </c>
       <c r="H742" t="n">
         <v>8117</v>
@@ -21916,7 +21916,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G743" t="n">
-        <v>1.6097526550293</v>
+        <v>1.60975289344788</v>
       </c>
       <c r="H743" t="n">
         <v>83441</v>
@@ -21974,7 +21974,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G745" t="n">
-        <v>1.54723811149597</v>
+        <v>1.54723823070526</v>
       </c>
       <c r="H745" t="n">
         <v>6604</v>
@@ -22003,7 +22003,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G746" t="n">
-        <v>1.59412407875061</v>
+        <v>1.5941241979599</v>
       </c>
       <c r="H746" t="n">
         <v>4010</v>
@@ -22032,7 +22032,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G747" t="n">
-        <v>1.58630967140198</v>
+        <v>1.58630979061127</v>
       </c>
       <c r="H747" t="n">
         <v>1818</v>
@@ -22061,7 +22061,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G748" t="n">
-        <v>1.58630967140198</v>
+        <v>1.58630979061127</v>
       </c>
       <c r="H748" t="n">
         <v>5636</v>
@@ -22090,7 +22090,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G749" t="n">
-        <v>1.58630967140198</v>
+        <v>1.58630979061127</v>
       </c>
       <c r="H749" t="n">
         <v>4728</v>
@@ -22322,7 +22322,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G757" t="n">
-        <v>1.50816643238068</v>
+        <v>1.50816655158997</v>
       </c>
       <c r="H757" t="n">
         <v>390</v>
@@ -22409,7 +22409,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G760" t="n">
-        <v>1.57068121433258</v>
+        <v>1.57068109512329</v>
       </c>
       <c r="H760" t="n">
         <v>3200</v>
@@ -22438,7 +22438,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G761" t="n">
-        <v>1.49253797531128</v>
+        <v>1.49253785610199</v>
       </c>
       <c r="H761" t="n">
         <v>6174</v>
@@ -22467,7 +22467,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G762" t="n">
-        <v>1.47690916061401</v>
+        <v>1.47690904140472</v>
       </c>
       <c r="H762" t="n">
         <v>4134</v>
@@ -22525,7 +22525,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G764" t="n">
-        <v>1.50816643238068</v>
+        <v>1.50816655158997</v>
       </c>
       <c r="H764" t="n">
         <v>2240</v>
@@ -22583,7 +22583,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G766" t="n">
-        <v>1.5550525188446</v>
+        <v>1.55505263805389</v>
       </c>
       <c r="H766" t="n">
         <v>117476</v>
@@ -22612,7 +22612,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G767" t="n">
-        <v>1.58630967140198</v>
+        <v>1.58630979061127</v>
       </c>
       <c r="H767" t="n">
         <v>8040</v>
@@ -22641,7 +22641,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G768" t="n">
-        <v>1.5550525188446</v>
+        <v>1.55505263805389</v>
       </c>
       <c r="H768" t="n">
         <v>5714</v>
@@ -22670,7 +22670,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G769" t="n">
-        <v>1.58630967140198</v>
+        <v>1.58630979061127</v>
       </c>
       <c r="H769" t="n">
         <v>1450</v>
@@ -22699,7 +22699,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G770" t="n">
-        <v>1.58630967140198</v>
+        <v>1.58630979061127</v>
       </c>
       <c r="H770" t="n">
         <v>1250</v>
@@ -22728,7 +22728,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G771" t="n">
-        <v>1.58630967140198</v>
+        <v>1.58630979061127</v>
       </c>
       <c r="H771" t="n">
         <v>505</v>
@@ -22757,7 +22757,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G772" t="n">
-        <v>1.58630967140198</v>
+        <v>1.58630979061127</v>
       </c>
       <c r="H772" t="n">
         <v>0</v>
@@ -22786,7 +22786,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G773" t="n">
-        <v>1.5550525188446</v>
+        <v>1.55505263805389</v>
       </c>
       <c r="H773" t="n">
         <v>8089</v>
@@ -22844,7 +22844,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G775" t="n">
-        <v>1.5550525188446</v>
+        <v>1.55505263805389</v>
       </c>
       <c r="H775" t="n">
         <v>2807</v>
@@ -22873,7 +22873,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G776" t="n">
-        <v>1.531609416008</v>
+        <v>1.53160953521729</v>
       </c>
       <c r="H776" t="n">
         <v>5415</v>
@@ -23018,7 +23018,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G781" t="n">
-        <v>1.5550525188446</v>
+        <v>1.55505263805389</v>
       </c>
       <c r="H781" t="n">
         <v>1090</v>
@@ -23047,7 +23047,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G782" t="n">
-        <v>1.531609416008</v>
+        <v>1.53160953521729</v>
       </c>
       <c r="H782" t="n">
         <v>5650</v>
@@ -23076,7 +23076,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G783" t="n">
-        <v>1.531609416008</v>
+        <v>1.53160953521729</v>
       </c>
       <c r="H783" t="n">
         <v>9208</v>
@@ -23163,7 +23163,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G786" t="n">
-        <v>1.5550525188446</v>
+        <v>1.55505263805389</v>
       </c>
       <c r="H786" t="n">
         <v>3597</v>
@@ -23192,7 +23192,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G787" t="n">
-        <v>1.5550525188446</v>
+        <v>1.55505263805389</v>
       </c>
       <c r="H787" t="n">
         <v>375</v>
@@ -23279,7 +23279,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G790" t="n">
-        <v>1.5550525188446</v>
+        <v>1.55505263805389</v>
       </c>
       <c r="H790" t="n">
         <v>935</v>
@@ -23337,7 +23337,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G792" t="n">
-        <v>1.54723811149597</v>
+        <v>1.54723823070526</v>
       </c>
       <c r="H792" t="n">
         <v>3760</v>
@@ -23366,7 +23366,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G793" t="n">
-        <v>1.54723811149597</v>
+        <v>1.54723823070526</v>
       </c>
       <c r="H793" t="n">
         <v>1646</v>
@@ -23395,7 +23395,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G794" t="n">
-        <v>1.54723811149597</v>
+        <v>1.54723823070526</v>
       </c>
       <c r="H794" t="n">
         <v>3700</v>
@@ -23482,7 +23482,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G797" t="n">
-        <v>1.57068121433258</v>
+        <v>1.57068109512329</v>
       </c>
       <c r="H797" t="n">
         <v>8209</v>
@@ -23540,7 +23540,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G799" t="n">
-        <v>1.59412407875061</v>
+        <v>1.5941241979599</v>
       </c>
       <c r="H799" t="n">
         <v>10202</v>
@@ -23598,7 +23598,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G801" t="n">
-        <v>1.54723811149597</v>
+        <v>1.54723823070526</v>
       </c>
       <c r="H801" t="n">
         <v>4800</v>
@@ -23627,7 +23627,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G802" t="n">
-        <v>1.5550525188446</v>
+        <v>1.55505263805389</v>
       </c>
       <c r="H802" t="n">
         <v>11782</v>
@@ -23656,7 +23656,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G803" t="n">
-        <v>1.58630967140198</v>
+        <v>1.58630979061127</v>
       </c>
       <c r="H803" t="n">
         <v>3550</v>
@@ -23714,7 +23714,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G805" t="n">
-        <v>1.59412407875061</v>
+        <v>1.5941241979599</v>
       </c>
       <c r="H805" t="n">
         <v>4829</v>
@@ -23743,7 +23743,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G806" t="n">
-        <v>1.58630967140198</v>
+        <v>1.58630979061127</v>
       </c>
       <c r="H806" t="n">
         <v>9021</v>
@@ -23772,7 +23772,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G807" t="n">
-        <v>1.6097526550293</v>
+        <v>1.60975289344788</v>
       </c>
       <c r="H807" t="n">
         <v>6800</v>
@@ -23801,7 +23801,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G808" t="n">
-        <v>1.58630967140198</v>
+        <v>1.58630979061127</v>
       </c>
       <c r="H808" t="n">
         <v>6622</v>
@@ -23888,7 +23888,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G811" t="n">
-        <v>1.5550525188446</v>
+        <v>1.55505263805389</v>
       </c>
       <c r="H811" t="n">
         <v>1500</v>
@@ -23917,7 +23917,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G812" t="n">
-        <v>1.5550525188446</v>
+        <v>1.55505263805389</v>
       </c>
       <c r="H812" t="n">
         <v>3468</v>
@@ -23975,7 +23975,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G814" t="n">
-        <v>1.57068121433258</v>
+        <v>1.57068109512329</v>
       </c>
       <c r="H814" t="n">
         <v>19292</v>
@@ -24062,7 +24062,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G817" t="n">
-        <v>1.68008196353912</v>
+        <v>1.68008184432983</v>
       </c>
       <c r="H817" t="n">
         <v>78580</v>
@@ -24091,7 +24091,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G818" t="n">
-        <v>1.6097526550293</v>
+        <v>1.60975289344788</v>
       </c>
       <c r="H818" t="n">
         <v>32403</v>
@@ -24120,7 +24120,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G819" t="n">
-        <v>1.58630967140198</v>
+        <v>1.58630979061127</v>
       </c>
       <c r="H819" t="n">
         <v>15326</v>
@@ -24149,7 +24149,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G820" t="n">
-        <v>1.64101004600525</v>
+        <v>1.64101016521454</v>
       </c>
       <c r="H820" t="n">
         <v>7169</v>
@@ -24207,7 +24207,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G822" t="n">
-        <v>1.61756694316864</v>
+        <v>1.61756718158722</v>
       </c>
       <c r="H822" t="n">
         <v>271</v>
@@ -24294,7 +24294,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G825" t="n">
-        <v>1.58630967140198</v>
+        <v>1.58630979061127</v>
       </c>
       <c r="H825" t="n">
         <v>1500</v>
@@ -24323,7 +24323,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G826" t="n">
-        <v>1.59412407875061</v>
+        <v>1.5941241979599</v>
       </c>
       <c r="H826" t="n">
         <v>4684</v>
@@ -24468,7 +24468,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G831" t="n">
-        <v>1.65663886070251</v>
+        <v>1.65663874149323</v>
       </c>
       <c r="H831" t="n">
         <v>34511</v>
@@ -24497,7 +24497,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G832" t="n">
-        <v>1.65663886070251</v>
+        <v>1.65663874149323</v>
       </c>
       <c r="H832" t="n">
         <v>51170</v>
@@ -24555,7 +24555,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G834" t="n">
-        <v>1.64101004600525</v>
+        <v>1.64101016521454</v>
       </c>
       <c r="H834" t="n">
         <v>9584</v>
@@ -24584,7 +24584,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G835" t="n">
-        <v>1.6097526550293</v>
+        <v>1.60975289344788</v>
       </c>
       <c r="H835" t="n">
         <v>57779</v>
@@ -24700,7 +24700,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G839" t="n">
-        <v>1.64101004600525</v>
+        <v>1.64101016521454</v>
       </c>
       <c r="H839" t="n">
         <v>10970</v>
@@ -24729,7 +24729,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G840" t="n">
-        <v>1.59412407875061</v>
+        <v>1.5941241979599</v>
       </c>
       <c r="H840" t="n">
         <v>22366</v>
@@ -24758,7 +24758,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G841" t="n">
-        <v>1.64101004600525</v>
+        <v>1.64101016521454</v>
       </c>
       <c r="H841" t="n">
         <v>17557</v>
@@ -24787,7 +24787,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G842" t="n">
-        <v>1.59412407875061</v>
+        <v>1.5941241979599</v>
       </c>
       <c r="H842" t="n">
         <v>34014</v>
@@ -24845,7 +24845,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G844" t="n">
-        <v>1.6097526550293</v>
+        <v>1.60975289344788</v>
       </c>
       <c r="H844" t="n">
         <v>39333</v>
@@ -24903,7 +24903,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G846" t="n">
-        <v>1.6097526550293</v>
+        <v>1.60975289344788</v>
       </c>
       <c r="H846" t="n">
         <v>9208</v>
@@ -24961,7 +24961,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G848" t="n">
-        <v>1.6097526550293</v>
+        <v>1.60975289344788</v>
       </c>
       <c r="H848" t="n">
         <v>10001</v>
@@ -24990,7 +24990,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G849" t="n">
-        <v>1.59412407875061</v>
+        <v>1.5941241979599</v>
       </c>
       <c r="H849" t="n">
         <v>8778</v>
@@ -25019,7 +25019,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G850" t="n">
-        <v>1.59412407875061</v>
+        <v>1.5941241979599</v>
       </c>
       <c r="H850" t="n">
         <v>1999</v>
@@ -25106,7 +25106,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G853" t="n">
-        <v>1.531609416008</v>
+        <v>1.53160953521729</v>
       </c>
       <c r="H853" t="n">
         <v>9826</v>
@@ -25135,7 +25135,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G854" t="n">
-        <v>1.59412407875061</v>
+        <v>1.5941241979599</v>
       </c>
       <c r="H854" t="n">
         <v>10243</v>
@@ -25164,7 +25164,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G855" t="n">
-        <v>1.531609416008</v>
+        <v>1.53160953521729</v>
       </c>
       <c r="H855" t="n">
         <v>30431</v>
@@ -25193,7 +25193,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G856" t="n">
-        <v>1.54723811149597</v>
+        <v>1.54723823070526</v>
       </c>
       <c r="H856" t="n">
         <v>6091</v>
@@ -25222,7 +25222,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G857" t="n">
-        <v>1.531609416008</v>
+        <v>1.53160953521729</v>
       </c>
       <c r="H857" t="n">
         <v>8665</v>
@@ -25454,7 +25454,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G865" t="n">
-        <v>1.50035226345062</v>
+        <v>1.50035214424133</v>
       </c>
       <c r="H865" t="n">
         <v>6903</v>
@@ -25483,7 +25483,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G866" t="n">
-        <v>1.50035226345062</v>
+        <v>1.50035214424133</v>
       </c>
       <c r="H866" t="n">
         <v>8355</v>
@@ -25512,7 +25512,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G867" t="n">
-        <v>1.531609416008</v>
+        <v>1.53160953521729</v>
       </c>
       <c r="H867" t="n">
         <v>3500</v>
@@ -25628,7 +25628,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G871" t="n">
-        <v>1.50035226345062</v>
+        <v>1.50035214424133</v>
       </c>
       <c r="H871" t="n">
         <v>1918</v>
@@ -25657,7 +25657,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G872" t="n">
-        <v>1.50035226345062</v>
+        <v>1.50035214424133</v>
       </c>
       <c r="H872" t="n">
         <v>0</v>
@@ -25831,7 +25831,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G878" t="n">
-        <v>1.531609416008</v>
+        <v>1.53160953521729</v>
       </c>
       <c r="H878" t="n">
         <v>2050</v>
@@ -26237,7 +26237,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G892" t="n">
-        <v>1.531609416008</v>
+        <v>1.53160953521729</v>
       </c>
       <c r="H892" t="n">
         <v>6177</v>
@@ -26324,7 +26324,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G895" t="n">
-        <v>1.531609416008</v>
+        <v>1.53160953521729</v>
       </c>
       <c r="H895" t="n">
         <v>4132</v>
@@ -26353,7 +26353,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G896" t="n">
-        <v>1.531609416008</v>
+        <v>1.53160953521729</v>
       </c>
       <c r="H896" t="n">
         <v>15658</v>
@@ -26382,7 +26382,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G897" t="n">
-        <v>1.54723811149597</v>
+        <v>1.54723823070526</v>
       </c>
       <c r="H897" t="n">
         <v>12400</v>
@@ -26411,7 +26411,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G898" t="n">
-        <v>1.50035226345062</v>
+        <v>1.50035214424133</v>
       </c>
       <c r="H898" t="n">
         <v>9001</v>
@@ -26440,7 +26440,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G899" t="n">
-        <v>1.50035226345062</v>
+        <v>1.50035214424133</v>
       </c>
       <c r="H899" t="n">
         <v>5729</v>
@@ -26469,7 +26469,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G900" t="n">
-        <v>1.50035226345062</v>
+        <v>1.50035214424133</v>
       </c>
       <c r="H900" t="n">
         <v>4094</v>
@@ -26498,7 +26498,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G901" t="n">
-        <v>1.54723811149597</v>
+        <v>1.54723823070526</v>
       </c>
       <c r="H901" t="n">
         <v>5238</v>
@@ -26585,7 +26585,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G904" t="n">
-        <v>1.531609416008</v>
+        <v>1.53160953521729</v>
       </c>
       <c r="H904" t="n">
         <v>2250</v>
@@ -26614,7 +26614,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G905" t="n">
-        <v>1.531609416008</v>
+        <v>1.53160953521729</v>
       </c>
       <c r="H905" t="n">
         <v>3080</v>
@@ -26643,7 +26643,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G906" t="n">
-        <v>1.50035226345062</v>
+        <v>1.50035214424133</v>
       </c>
       <c r="H906" t="n">
         <v>3380</v>
@@ -26672,7 +26672,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G907" t="n">
-        <v>1.50035226345062</v>
+        <v>1.50035214424133</v>
       </c>
       <c r="H907" t="n">
         <v>17682</v>
@@ -26759,7 +26759,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G910" t="n">
-        <v>1.50035226345062</v>
+        <v>1.50035214424133</v>
       </c>
       <c r="H910" t="n">
         <v>2535</v>
@@ -26846,7 +26846,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G913" t="n">
-        <v>1.50035226345062</v>
+        <v>1.50035214424133</v>
       </c>
       <c r="H913" t="n">
         <v>1205</v>
@@ -26933,7 +26933,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G916" t="n">
-        <v>1.50035226345062</v>
+        <v>1.50035214424133</v>
       </c>
       <c r="H916" t="n">
         <v>1650</v>
@@ -26962,7 +26962,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G917" t="n">
-        <v>1.50035226345062</v>
+        <v>1.50035214424133</v>
       </c>
       <c r="H917" t="n">
         <v>8100</v>
@@ -27223,7 +27223,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G926" t="n">
-        <v>1.50035226345062</v>
+        <v>1.50035214424133</v>
       </c>
       <c r="H926" t="n">
         <v>3414</v>
@@ -27252,7 +27252,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G927" t="n">
-        <v>1.50035226345062</v>
+        <v>1.50035214424133</v>
       </c>
       <c r="H927" t="n">
         <v>60</v>
@@ -27426,7 +27426,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G933" t="n">
-        <v>1.50035226345062</v>
+        <v>1.50035214424133</v>
       </c>
       <c r="H933" t="n">
         <v>10800</v>
@@ -27629,7 +27629,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G940" t="n">
-        <v>1.50035226345062</v>
+        <v>1.50035214424133</v>
       </c>
       <c r="H940" t="n">
         <v>3395</v>
@@ -27658,7 +27658,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G941" t="n">
-        <v>1.531609416008</v>
+        <v>1.53160953521729</v>
       </c>
       <c r="H941" t="n">
         <v>62485</v>
@@ -27890,7 +27890,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G949" t="n">
-        <v>1.50035226345062</v>
+        <v>1.50035214424133</v>
       </c>
       <c r="H949" t="n">
         <v>2380</v>
@@ -27919,7 +27919,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G950" t="n">
-        <v>1.50035226345062</v>
+        <v>1.50035214424133</v>
       </c>
       <c r="H950" t="n">
         <v>1118</v>
@@ -27948,7 +27948,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G951" t="n">
-        <v>1.50035226345062</v>
+        <v>1.50035214424133</v>
       </c>
       <c r="H951" t="n">
         <v>2270</v>
@@ -27977,7 +27977,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G952" t="n">
-        <v>1.50035226345062</v>
+        <v>1.50035214424133</v>
       </c>
       <c r="H952" t="n">
         <v>3602</v>
@@ -28006,7 +28006,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G953" t="n">
-        <v>1.50035226345062</v>
+        <v>1.50035214424133</v>
       </c>
       <c r="H953" t="n">
         <v>4131</v>
@@ -28035,7 +28035,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G954" t="n">
-        <v>1.50035226345062</v>
+        <v>1.50035214424133</v>
       </c>
       <c r="H954" t="n">
         <v>7140</v>
@@ -28586,7 +28586,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G973" t="n">
-        <v>1.42220890522003</v>
+        <v>1.42220878601074</v>
       </c>
       <c r="H973" t="n">
         <v>30</v>
@@ -28673,7 +28673,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G976" t="n">
-        <v>1.42220890522003</v>
+        <v>1.42220878601074</v>
       </c>
       <c r="H976" t="n">
         <v>8943</v>
@@ -28702,7 +28702,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G977" t="n">
-        <v>1.42220890522003</v>
+        <v>1.42220878601074</v>
       </c>
       <c r="H977" t="n">
         <v>2955</v>
@@ -28905,7 +28905,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G984" t="n">
-        <v>1.42220890522003</v>
+        <v>1.42220878601074</v>
       </c>
       <c r="H984" t="n">
         <v>2400</v>
@@ -28934,7 +28934,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G985" t="n">
-        <v>1.42220890522003</v>
+        <v>1.42220878601074</v>
       </c>
       <c r="H985" t="n">
         <v>7856</v>
@@ -28963,7 +28963,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G986" t="n">
-        <v>1.42220890522003</v>
+        <v>1.42220878601074</v>
       </c>
       <c r="H986" t="n">
         <v>28690</v>
@@ -29166,7 +29166,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G993" t="n">
-        <v>1.42220890522003</v>
+        <v>1.42220878601074</v>
       </c>
       <c r="H993" t="n">
         <v>2550</v>
@@ -29195,7 +29195,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G994" t="n">
-        <v>1.42220890522003</v>
+        <v>1.42220878601074</v>
       </c>
       <c r="H994" t="n">
         <v>2459</v>
@@ -29224,7 +29224,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G995" t="n">
-        <v>1.39095151424408</v>
+        <v>1.3909512758255</v>
       </c>
       <c r="H995" t="n">
         <v>4445</v>
@@ -29253,7 +29253,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G996" t="n">
-        <v>1.42220890522003</v>
+        <v>1.42220878601074</v>
       </c>
       <c r="H996" t="n">
         <v>739</v>
@@ -29601,7 +29601,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G1008" t="n">
-        <v>1.42220890522003</v>
+        <v>1.42220878601074</v>
       </c>
       <c r="H1008" t="n">
         <v>24714</v>
@@ -29804,7 +29804,7 @@
         <v>1.86940002441406</v>
       </c>
       <c r="G1015" t="n">
-        <v>1.46081161499023</v>
+        <v>1.46081173419952</v>
       </c>
       <c r="H1015" t="n">
         <v>31731</v>
@@ -29833,7 +29833,7 @@
         <v>1.84019994735718</v>
       </c>
       <c r="G1016" t="n">
-        <v>1.43799376487732</v>
+        <v>1.43799364566803</v>
       </c>
       <c r="H1016" t="n">
         <v>22250</v>
@@ -29862,7 +29862,7 @@
         <v>1.80480003356934</v>
       </c>
       <c r="G1017" t="n">
-        <v>1.41033113002777</v>
+        <v>1.41033101081848</v>
       </c>
       <c r="H1017" t="n">
         <v>6419</v>
@@ -29978,7 +29978,7 @@
         <v>1.77359998226166</v>
       </c>
       <c r="G1021" t="n">
-        <v>1.38595020771027</v>
+        <v>1.38595032691956</v>
       </c>
       <c r="H1021" t="n">
         <v>10862</v>
@@ -30007,7 +30007,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G1022" t="n">
-        <v>1.43002307415009</v>
+        <v>1.43002319335938</v>
       </c>
       <c r="H1022" t="n">
         <v>55375</v>
@@ -30036,7 +30036,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G1023" t="n">
-        <v>1.4143944978714</v>
+        <v>1.41439437866211</v>
       </c>
       <c r="H1023" t="n">
         <v>10822</v>
@@ -30152,7 +30152,7 @@
         <v>1.74600005149841</v>
       </c>
       <c r="G1027" t="n">
-        <v>1.36438274383545</v>
+        <v>1.36438286304474</v>
       </c>
       <c r="H1027" t="n">
         <v>3497</v>
@@ -30210,7 +30210,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G1029" t="n">
-        <v>1.34406554698944</v>
+        <v>1.34406542778015</v>
       </c>
       <c r="H1029" t="n">
         <v>22344</v>
@@ -30268,7 +30268,7 @@
         <v>1.73239994049072</v>
       </c>
       <c r="G1031" t="n">
-        <v>1.35375511646271</v>
+        <v>1.35375535488129</v>
       </c>
       <c r="H1031" t="n">
         <v>8694</v>
@@ -30384,7 +30384,7 @@
         <v>1.68099999427795</v>
       </c>
       <c r="G1035" t="n">
-        <v>1.31358957290649</v>
+        <v>1.31358969211578</v>
       </c>
       <c r="H1035" t="n">
         <v>15612</v>
@@ -30413,7 +30413,7 @@
         <v>1.66919994354248</v>
       </c>
       <c r="G1036" t="n">
-        <v>1.30436873435974</v>
+        <v>1.30436861515045</v>
       </c>
       <c r="H1036" t="n">
         <v>37285</v>
@@ -30471,7 +30471,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1038" t="n">
-        <v>1.25029349327087</v>
+        <v>1.25029361248016</v>
       </c>
       <c r="H1038" t="n">
         <v>7984</v>
@@ -30500,7 +30500,7 @@
         <v>1.57840001583099</v>
       </c>
       <c r="G1039" t="n">
-        <v>1.23341453075409</v>
+        <v>1.23341464996338</v>
       </c>
       <c r="H1039" t="n">
         <v>13283</v>
@@ -30587,7 +30587,7 @@
         <v>1.60580003261566</v>
       </c>
       <c r="G1042" t="n">
-        <v>1.25482594966888</v>
+        <v>1.25482571125031</v>
       </c>
       <c r="H1042" t="n">
         <v>57252</v>
@@ -30645,7 +30645,7 @@
         <v>1.63900005817413</v>
       </c>
       <c r="G1044" t="n">
-        <v>1.28076934814453</v>
+        <v>1.28076946735382</v>
       </c>
       <c r="H1044" t="n">
         <v>37874</v>
@@ -30703,7 +30703,7 @@
         <v>1.63779997825623</v>
       </c>
       <c r="G1046" t="n">
-        <v>1.27983176708221</v>
+        <v>1.27983164787292</v>
       </c>
       <c r="H1046" t="n">
         <v>22878</v>
@@ -30732,7 +30732,7 @@
         <v>1.66260004043579</v>
       </c>
       <c r="G1047" t="n">
-        <v>1.29921126365662</v>
+        <v>1.29921114444733</v>
       </c>
       <c r="H1047" t="n">
         <v>23626</v>
@@ -30761,7 +30761,7 @@
         <v>1.68579995632172</v>
       </c>
       <c r="G1048" t="n">
-        <v>1.31734037399292</v>
+        <v>1.31734049320221</v>
       </c>
       <c r="H1048" t="n">
         <v>10382</v>
@@ -30819,7 +30819,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1050" t="n">
-        <v>1.30499374866486</v>
+        <v>1.30499386787415</v>
       </c>
       <c r="H1050" t="n">
         <v>5237</v>
@@ -30877,7 +30877,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1052" t="n">
-        <v>1.30499374866486</v>
+        <v>1.30499386787415</v>
       </c>
       <c r="H1052" t="n">
         <v>3328</v>
@@ -30964,7 +30964,7 @@
         <v>1.61479997634888</v>
       </c>
       <c r="G1055" t="n">
-        <v>1.26185870170593</v>
+        <v>1.26185858249664</v>
       </c>
       <c r="H1055" t="n">
         <v>3537</v>
@@ -30993,7 +30993,7 @@
         <v>1.54159998893738</v>
       </c>
       <c r="G1056" t="n">
-        <v>1.20465767383575</v>
+        <v>1.20465779304504</v>
       </c>
       <c r="H1056" t="n">
         <v>6735</v>
@@ -31022,7 +31022,7 @@
         <v>1.58980000019073</v>
       </c>
       <c r="G1057" t="n">
-        <v>1.24232280254364</v>
+        <v>1.24232292175293</v>
       </c>
       <c r="H1057" t="n">
         <v>20662</v>
@@ -31051,7 +31051,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G1058" t="n">
-        <v>1.17996442317963</v>
+        <v>1.17996454238892</v>
       </c>
       <c r="H1058" t="n">
         <v>26123</v>
@@ -31080,7 +31080,7 @@
         <v>1.55980002880096</v>
       </c>
       <c r="G1059" t="n">
-        <v>1.21887993812561</v>
+        <v>1.2188800573349</v>
       </c>
       <c r="H1059" t="n">
         <v>21083</v>
@@ -31196,7 +31196,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G1063" t="n">
-        <v>0.883019804954529</v>
+        <v>0.883019745349884</v>
       </c>
       <c r="H1063" t="n">
         <v>14800</v>
@@ -31225,7 +31225,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G1064" t="n">
-        <v>0.883019804954529</v>
+        <v>0.883019745349884</v>
       </c>
       <c r="H1064" t="n">
         <v>10076</v>
@@ -31341,7 +31341,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G1068" t="n">
-        <v>0.773619055747986</v>
+        <v>0.773619115352631</v>
       </c>
       <c r="H1068" t="n">
         <v>15083</v>
@@ -31370,7 +31370,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G1069" t="n">
-        <v>0.773619055747986</v>
+        <v>0.773619115352631</v>
       </c>
       <c r="H1069" t="n">
         <v>7200</v>
@@ -31399,7 +31399,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G1070" t="n">
-        <v>0.773619055747986</v>
+        <v>0.773619115352631</v>
       </c>
       <c r="H1070" t="n">
         <v>1500</v>
@@ -31486,7 +31486,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G1073" t="n">
-        <v>0.968977451324463</v>
+        <v>0.968977391719818</v>
       </c>
       <c r="H1073" t="n">
         <v>6985</v>
@@ -31515,7 +31515,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G1074" t="n">
-        <v>1.09400677680969</v>
+        <v>1.0940066576004</v>
       </c>
       <c r="H1074" t="n">
         <v>7710</v>
@@ -31544,7 +31544,7 @@
         <v>1.54499995708466</v>
       </c>
       <c r="G1075" t="n">
-        <v>1.20731461048126</v>
+        <v>1.20731472969055</v>
       </c>
       <c r="H1075" t="n">
         <v>70566</v>
@@ -31573,7 +31573,7 @@
         <v>1.5958000421524</v>
       </c>
       <c r="G1076" t="n">
-        <v>1.24701154232025</v>
+        <v>1.24701142311096</v>
       </c>
       <c r="H1076" t="n">
         <v>28795</v>
@@ -31602,7 +31602,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G1077" t="n">
-        <v>1.24247908592224</v>
+        <v>1.24247920513153</v>
       </c>
       <c r="H1077" t="n">
         <v>15463</v>
@@ -31631,7 +31631,7 @@
         <v>1.61500000953674</v>
       </c>
       <c r="G1078" t="n">
-        <v>1.26201498508453</v>
+        <v>1.26201510429382</v>
       </c>
       <c r="H1078" t="n">
         <v>5525</v>
@@ -31660,7 +31660,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1079" t="n">
-        <v>1.25029349327087</v>
+        <v>1.25029361248016</v>
       </c>
       <c r="H1079" t="n">
         <v>7119</v>
@@ -31776,7 +31776,7 @@
         <v>1.58800005912781</v>
       </c>
       <c r="G1083" t="n">
-        <v>1.24091649055481</v>
+        <v>1.24091625213623</v>
       </c>
       <c r="H1083" t="n">
         <v>22509</v>
@@ -31805,7 +31805,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G1084" t="n">
-        <v>1.25810778141022</v>
+        <v>1.25810790061951</v>
       </c>
       <c r="H1084" t="n">
         <v>29539</v>
@@ -31892,7 +31892,7 @@
         <v>1.52119994163513</v>
       </c>
       <c r="G1087" t="n">
-        <v>1.18871629238129</v>
+        <v>1.18871641159058</v>
       </c>
       <c r="H1087" t="n">
         <v>999</v>
@@ -31921,7 +31921,7 @@
         <v>1.52999997138977</v>
       </c>
       <c r="G1088" t="n">
-        <v>1.19559323787689</v>
+        <v>1.1955931186676</v>
       </c>
       <c r="H1088" t="n">
         <v>8558</v>
@@ -32008,7 +32008,7 @@
         <v>1.53519999980927</v>
       </c>
       <c r="G1091" t="n">
-        <v>1.19965672492981</v>
+        <v>1.19965660572052</v>
       </c>
       <c r="H1091" t="n">
         <v>7726</v>
@@ -32037,7 +32037,7 @@
         <v>1.51059997081757</v>
       </c>
       <c r="G1092" t="n">
-        <v>1.18043339252472</v>
+        <v>1.18043327331543</v>
       </c>
       <c r="H1092" t="n">
         <v>10176</v>
@@ -32182,7 +32182,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G1097" t="n">
-        <v>1.05493521690369</v>
+        <v>1.0549350976944</v>
       </c>
       <c r="H1097" t="n">
         <v>24618</v>
@@ -32211,7 +32211,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G1098" t="n">
-        <v>1.05493521690369</v>
+        <v>1.0549350976944</v>
       </c>
       <c r="H1098" t="n">
         <v>0</v>
@@ -32240,7 +32240,7 @@
         <v>1.42980003356934</v>
       </c>
       <c r="G1099" t="n">
-        <v>1.1172935962677</v>
+        <v>1.11729347705841</v>
       </c>
       <c r="H1099" t="n">
         <v>10201</v>
@@ -32269,7 +32269,7 @@
         <v>1.42980003356934</v>
       </c>
       <c r="G1100" t="n">
-        <v>1.1172935962677</v>
+        <v>1.11729347705841</v>
       </c>
       <c r="H1100" t="n">
         <v>0</v>
@@ -32443,7 +32443,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1106" t="n">
-        <v>1.04712080955505</v>
+        <v>1.04712069034576</v>
       </c>
       <c r="H1106" t="n">
         <v>11729</v>
@@ -32472,7 +32472,7 @@
         <v>1.34080004692078</v>
       </c>
       <c r="G1107" t="n">
-        <v>1.04774594306946</v>
+        <v>1.04774606227875</v>
       </c>
       <c r="H1107" t="n">
         <v>27019</v>
@@ -32559,7 +32559,7 @@
         <v>1.25279998779297</v>
       </c>
       <c r="G1110" t="n">
-        <v>0.978979647159576</v>
+        <v>0.978979825973511</v>
       </c>
       <c r="H1110" t="n">
         <v>24524</v>
@@ -32646,7 +32646,7 @@
         <v>1.23800003528595</v>
       </c>
       <c r="G1113" t="n">
-        <v>0.967414557933807</v>
+        <v>0.967414736747742</v>
       </c>
       <c r="H1113" t="n">
         <v>18476</v>
@@ -32704,7 +32704,7 @@
         <v>1.25</v>
       </c>
       <c r="G1115" t="n">
-        <v>0.976791679859161</v>
+        <v>0.976791739463806</v>
       </c>
       <c r="H1115" t="n">
         <v>34094</v>
@@ -32791,7 +32791,7 @@
         <v>1.31719994544983</v>
       </c>
       <c r="G1118" t="n">
-        <v>1.02930402755737</v>
+        <v>1.02930414676666</v>
       </c>
       <c r="H1118" t="n">
         <v>20471</v>
@@ -32849,7 +32849,7 @@
         <v>1.2791999578476</v>
       </c>
       <c r="G1120" t="n">
-        <v>0.999609589576721</v>
+        <v>0.999609649181366</v>
       </c>
       <c r="H1120" t="n">
         <v>25760</v>
@@ -32878,7 +32878,7 @@
         <v>1.2771999835968</v>
       </c>
       <c r="G1121" t="n">
-        <v>0.998046696186066</v>
+        <v>0.99804675579071</v>
       </c>
       <c r="H1121" t="n">
         <v>64712</v>
@@ -32907,7 +32907,7 @@
         <v>1.33940005302429</v>
       </c>
       <c r="G1122" t="n">
-        <v>1.04665207862854</v>
+        <v>1.04665184020996</v>
       </c>
       <c r="H1122" t="n">
         <v>68249</v>
@@ -32965,7 +32965,7 @@
         <v>1.31900000572205</v>
       </c>
       <c r="G1124" t="n">
-        <v>1.03071069717407</v>
+        <v>1.03071081638336</v>
       </c>
       <c r="H1124" t="n">
         <v>11224</v>
@@ -33023,7 +33023,7 @@
         <v>1.35979998111725</v>
       </c>
       <c r="G1126" t="n">
-        <v>1.06259322166443</v>
+        <v>1.06259310245514</v>
       </c>
       <c r="H1126" t="n">
         <v>19347</v>
@@ -33081,7 +33081,7 @@
         <v>1.34979999065399</v>
       </c>
       <c r="G1128" t="n">
-        <v>1.05477893352509</v>
+        <v>1.05477869510651</v>
       </c>
       <c r="H1128" t="n">
         <v>30907</v>
@@ -33110,7 +33110,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G1129" t="n">
-        <v>1.03149223327637</v>
+        <v>1.03149211406708</v>
       </c>
       <c r="H1129" t="n">
         <v>23471</v>
@@ -33139,7 +33139,7 @@
         <v>1.29579997062683</v>
       </c>
       <c r="G1130" t="n">
-        <v>1.01258134841919</v>
+        <v>1.01258146762848</v>
       </c>
       <c r="H1130" t="n">
         <v>34473</v>
@@ -33255,7 +33255,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1134" t="n">
-        <v>1.04712080955505</v>
+        <v>1.04712069034576</v>
       </c>
       <c r="H1134" t="n">
         <v>6000</v>
@@ -33284,7 +33284,7 @@
         <v>1.2960000038147</v>
       </c>
       <c r="G1135" t="n">
-        <v>1.01273763179779</v>
+        <v>1.01273787021637</v>
       </c>
       <c r="H1135" t="n">
         <v>2329</v>
@@ -33313,7 +33313,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G1136" t="n">
-        <v>1.03149223327637</v>
+        <v>1.03149211406708</v>
       </c>
       <c r="H1136" t="n">
         <v>3100</v>
@@ -33429,7 +33429,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1140" t="n">
-        <v>1.03930652141571</v>
+        <v>1.03930640220642</v>
       </c>
       <c r="H1140" t="n">
         <v>4250</v>
@@ -33487,7 +33487,7 @@
         <v>1.29200005531311</v>
       </c>
       <c r="G1142" t="n">
-        <v>1.00961196422577</v>
+        <v>1.00961208343506</v>
       </c>
       <c r="H1142" t="n">
         <v>1000</v>
@@ -33516,7 +33516,7 @@
         <v>1.30900001525879</v>
       </c>
       <c r="G1143" t="n">
-        <v>1.02289628982544</v>
+        <v>1.02289640903473</v>
       </c>
       <c r="H1143" t="n">
         <v>1000</v>
@@ -33545,7 +33545,7 @@
         <v>1.30499994754791</v>
       </c>
       <c r="G1144" t="n">
-        <v>1.01977062225342</v>
+        <v>1.01977050304413</v>
       </c>
       <c r="H1144" t="n">
         <v>3677</v>
@@ -33574,7 +33574,7 @@
         <v>1.28260004520416</v>
       </c>
       <c r="G1145" t="n">
-        <v>1.00226640701294</v>
+        <v>1.00226652622223</v>
       </c>
       <c r="H1145" t="n">
         <v>44531</v>
@@ -33661,7 +33661,7 @@
         <v>1.26499998569489</v>
       </c>
       <c r="G1148" t="n">
-        <v>0.988513231277466</v>
+        <v>0.988513171672821</v>
       </c>
       <c r="H1148" t="n">
         <v>1022</v>
@@ -33690,7 +33690,7 @@
         <v>1.26240003108978</v>
       </c>
       <c r="G1149" t="n">
-        <v>0.986481666564941</v>
+        <v>0.986481547355652</v>
       </c>
       <c r="H1149" t="n">
         <v>8000</v>
@@ -33748,7 +33748,7 @@
         <v>1.29299998283386</v>
       </c>
       <c r="G1151" t="n">
-        <v>1.01039338111877</v>
+        <v>1.01039326190948</v>
       </c>
       <c r="H1151" t="n">
         <v>4302</v>
@@ -33835,7 +33835,7 @@
         <v>1.25440001487732</v>
       </c>
       <c r="G1154" t="n">
-        <v>0.980230033397675</v>
+        <v>0.980230212211609</v>
       </c>
       <c r="H1154" t="n">
         <v>5500</v>
@@ -33893,7 +33893,7 @@
         <v>1.26199996471405</v>
       </c>
       <c r="G1156" t="n">
-        <v>0.98616886138916</v>
+        <v>0.98616898059845</v>
       </c>
       <c r="H1156" t="n">
         <v>9776</v>
@@ -33951,7 +33951,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G1158" t="n">
-        <v>1.03149223327637</v>
+        <v>1.03149211406708</v>
       </c>
       <c r="H1158" t="n">
         <v>25837</v>
@@ -33980,7 +33980,7 @@
         <v>1.29499995708466</v>
       </c>
       <c r="G1159" t="n">
-        <v>1.01195621490479</v>
+        <v>1.01195633411407</v>
       </c>
       <c r="H1159" t="n">
         <v>21359</v>
@@ -34183,7 +34183,7 @@
         <v>1.27900004386902</v>
       </c>
       <c r="G1166" t="n">
-        <v>0.99945342540741</v>
+        <v>0.99945330619812</v>
       </c>
       <c r="H1166" t="n">
         <v>19032</v>
@@ -34270,7 +34270,7 @@
         <v>1.25</v>
       </c>
       <c r="G1169" t="n">
-        <v>0.976791679859161</v>
+        <v>0.976791739463806</v>
       </c>
       <c r="H1169" t="n">
         <v>7000</v>
@@ -34299,7 +34299,7 @@
         <v>1.25</v>
       </c>
       <c r="G1170" t="n">
-        <v>0.976791679859161</v>
+        <v>0.976791739463806</v>
       </c>
       <c r="H1170" t="n">
         <v>0</v>
@@ -34328,7 +34328,7 @@
         <v>1.24339997768402</v>
       </c>
       <c r="G1171" t="n">
-        <v>0.971634209156036</v>
+        <v>0.971634387969971</v>
       </c>
       <c r="H1171" t="n">
         <v>4563</v>
@@ -34357,7 +34357,7 @@
         <v>1.22060000896454</v>
       </c>
       <c r="G1172" t="n">
-        <v>0.953817546367645</v>
+        <v>0.95381772518158</v>
       </c>
       <c r="H1172" t="n">
         <v>2356</v>
@@ -34386,7 +34386,7 @@
         <v>1.22060000896454</v>
       </c>
       <c r="G1173" t="n">
-        <v>0.953817546367645</v>
+        <v>0.95381772518158</v>
       </c>
       <c r="H1173" t="n">
         <v>0</v>
@@ -34415,7 +34415,7 @@
         <v>1.24979996681213</v>
       </c>
       <c r="G1174" t="n">
-        <v>0.97663539648056</v>
+        <v>0.97663551568985</v>
       </c>
       <c r="H1174" t="n">
         <v>1000</v>
@@ -34444,7 +34444,7 @@
         <v>1.22200000286102</v>
       </c>
       <c r="G1175" t="n">
-        <v>0.954911530017853</v>
+        <v>0.954911589622498</v>
       </c>
       <c r="H1175" t="n">
         <v>800</v>
@@ -34502,7 +34502,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1177" t="n">
-        <v>0.953348696231842</v>
+        <v>0.953348875045776</v>
       </c>
       <c r="H1177" t="n">
         <v>1300</v>
@@ -34531,7 +34531,7 @@
         <v>1.23479998111725</v>
       </c>
       <c r="G1178" t="n">
-        <v>0.964913904666901</v>
+        <v>0.964913964271545</v>
       </c>
       <c r="H1178" t="n">
         <v>5677</v>
@@ -34647,7 +34647,7 @@
         <v>1.24399995803833</v>
       </c>
       <c r="G1182" t="n">
-        <v>0.972103238105774</v>
+        <v>0.972103118896484</v>
       </c>
       <c r="H1182" t="n">
         <v>2300</v>
@@ -34676,7 +34676,7 @@
         <v>1.24399995803833</v>
       </c>
       <c r="G1183" t="n">
-        <v>0.972103238105774</v>
+        <v>0.972103118896484</v>
       </c>
       <c r="H1183" t="n">
         <v>1000</v>
@@ -34734,7 +34734,7 @@
         <v>1.20500004291534</v>
       </c>
       <c r="G1185" t="n">
-        <v>0.941627264022827</v>
+        <v>0.941627383232117</v>
       </c>
       <c r="H1185" t="n">
         <v>6534</v>
@@ -34763,7 +34763,7 @@
         <v>1.20899999141693</v>
       </c>
       <c r="G1186" t="n">
-        <v>0.944753050804138</v>
+        <v>0.944752931594849</v>
       </c>
       <c r="H1186" t="n">
         <v>8300</v>
@@ -34792,7 +34792,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1187" t="n">
-        <v>0.953348696231842</v>
+        <v>0.953348875045776</v>
       </c>
       <c r="H1187" t="n">
         <v>9105</v>
@@ -34821,7 +34821,7 @@
         <v>1.20019996166229</v>
       </c>
       <c r="G1188" t="n">
-        <v>0.937876284122467</v>
+        <v>0.937876403331757</v>
       </c>
       <c r="H1188" t="n">
         <v>10090</v>
@@ -34879,7 +34879,7 @@
         <v>1.26979994773865</v>
       </c>
       <c r="G1190" t="n">
-        <v>0.992264151573181</v>
+        <v>0.992264091968536</v>
       </c>
       <c r="H1190" t="n">
         <v>2250</v>
@@ -34908,7 +34908,7 @@
         <v>1.23959994316101</v>
       </c>
       <c r="G1191" t="n">
-        <v>0.968664765357971</v>
+        <v>0.968664884567261</v>
       </c>
       <c r="H1191" t="n">
         <v>1101</v>
@@ -34937,7 +34937,7 @@
         <v>1.24979996681213</v>
       </c>
       <c r="G1192" t="n">
-        <v>0.97663539648056</v>
+        <v>0.97663551568985</v>
       </c>
       <c r="H1192" t="n">
         <v>7471</v>
@@ -34966,7 +34966,7 @@
         <v>1.21319997310638</v>
       </c>
       <c r="G1193" t="n">
-        <v>0.948034942150116</v>
+        <v>0.94803512096405</v>
       </c>
       <c r="H1193" t="n">
         <v>5835</v>
@@ -34995,7 +34995,7 @@
         <v>1.22800004482269</v>
       </c>
       <c r="G1194" t="n">
-        <v>0.959600269794464</v>
+        <v>0.959600329399109</v>
       </c>
       <c r="H1194" t="n">
         <v>24707</v>
@@ -35024,7 +35024,7 @@
         <v>1.24279999732971</v>
       </c>
       <c r="G1195" t="n">
-        <v>0.971165359020233</v>
+        <v>0.971165418624878</v>
       </c>
       <c r="H1195" t="n">
         <v>23798</v>
@@ -35053,7 +35053,7 @@
         <v>1.24199998378754</v>
       </c>
       <c r="G1196" t="n">
-        <v>0.970540285110474</v>
+        <v>0.970540225505829</v>
       </c>
       <c r="H1196" t="n">
         <v>22960</v>
@@ -35082,7 +35082,7 @@
         <v>1.24399995803833</v>
       </c>
       <c r="G1197" t="n">
-        <v>0.972103238105774</v>
+        <v>0.972103118896484</v>
       </c>
       <c r="H1197" t="n">
         <v>28501</v>
@@ -35169,7 +35169,7 @@
         <v>1.19120001792908</v>
       </c>
       <c r="G1200" t="n">
-        <v>0.930843591690063</v>
+        <v>0.930843353271484</v>
       </c>
       <c r="H1200" t="n">
         <v>13624</v>
@@ -35198,7 +35198,7 @@
         <v>1.19120001792908</v>
       </c>
       <c r="G1201" t="n">
-        <v>0.930843591690063</v>
+        <v>0.930843353271484</v>
       </c>
       <c r="H1201" t="n">
         <v>0</v>
@@ -35227,7 +35227,7 @@
         <v>1.22940003871918</v>
       </c>
       <c r="G1202" t="n">
-        <v>0.960694313049316</v>
+        <v>0.960694253444672</v>
       </c>
       <c r="H1202" t="n">
         <v>930</v>
@@ -35256,7 +35256,7 @@
         <v>1.19140005111694</v>
       </c>
       <c r="G1203" t="n">
-        <v>0.930999875068665</v>
+        <v>0.930999755859375</v>
       </c>
       <c r="H1203" t="n">
         <v>520</v>
@@ -35285,7 +35285,7 @@
         <v>1.22979998588562</v>
       </c>
       <c r="G1204" t="n">
-        <v>0.961006820201874</v>
+        <v>0.961006760597229</v>
       </c>
       <c r="H1204" t="n">
         <v>4250</v>
@@ -35314,7 +35314,7 @@
         <v>1.24199998378754</v>
       </c>
       <c r="G1205" t="n">
-        <v>0.970540285110474</v>
+        <v>0.970540225505829</v>
       </c>
       <c r="H1205" t="n">
         <v>5811</v>
@@ -35343,7 +35343,7 @@
         <v>1.2117999792099</v>
       </c>
       <c r="G1206" t="n">
-        <v>0.946941018104553</v>
+        <v>0.946941077709198</v>
       </c>
       <c r="H1206" t="n">
         <v>27456</v>
@@ -35372,7 +35372,7 @@
         <v>1.21119999885559</v>
       </c>
       <c r="G1207" t="n">
-        <v>0.94647216796875</v>
+        <v>0.946472108364105</v>
       </c>
       <c r="H1207" t="n">
         <v>11015</v>
@@ -35459,7 +35459,7 @@
         <v>1.19900000095367</v>
       </c>
       <c r="G1210" t="n">
-        <v>0.93693870306015</v>
+        <v>0.936938583850861</v>
       </c>
       <c r="H1210" t="n">
         <v>3</v>
@@ -35488,7 +35488,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G1211" t="n">
-        <v>0.968977451324463</v>
+        <v>0.968977391719818</v>
       </c>
       <c r="H1211" t="n">
         <v>39741</v>
@@ -35604,7 +35604,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1215" t="n">
-        <v>0.984606087207794</v>
+        <v>0.984605967998505</v>
       </c>
       <c r="H1215" t="n">
         <v>32688</v>
@@ -35662,7 +35662,7 @@
         <v>1.26540005207062</v>
       </c>
       <c r="G1217" t="n">
-        <v>0.988825917243958</v>
+        <v>0.988825857639313</v>
       </c>
       <c r="H1217" t="n">
         <v>20941</v>
@@ -35691,7 +35691,7 @@
         <v>1.24020004272461</v>
       </c>
       <c r="G1218" t="n">
-        <v>0.969133794307709</v>
+        <v>0.969133615493774</v>
       </c>
       <c r="H1218" t="n">
         <v>4530</v>
@@ -35778,7 +35778,7 @@
         <v>1.25539994239807</v>
       </c>
       <c r="G1221" t="n">
-        <v>0.981011509895325</v>
+        <v>0.981011390686035</v>
       </c>
       <c r="H1221" t="n">
         <v>4670</v>
@@ -35807,7 +35807,7 @@
         <v>1.22599995136261</v>
       </c>
       <c r="G1222" t="n">
-        <v>0.958037316799164</v>
+        <v>0.958037376403809</v>
       </c>
       <c r="H1222" t="n">
         <v>119</v>
@@ -35836,7 +35836,7 @@
         <v>1.22599995136261</v>
       </c>
       <c r="G1223" t="n">
-        <v>0.958037316799164</v>
+        <v>0.958037376403809</v>
       </c>
       <c r="H1223" t="n">
         <v>0</v>
@@ -35865,7 +35865,7 @@
         <v>1.22599995136261</v>
       </c>
       <c r="G1224" t="n">
-        <v>0.958037316799164</v>
+        <v>0.958037376403809</v>
       </c>
       <c r="H1224" t="n">
         <v>0</v>
@@ -35923,7 +35923,7 @@
         <v>1.25</v>
       </c>
       <c r="G1226" t="n">
-        <v>0.976791679859161</v>
+        <v>0.976791739463806</v>
       </c>
       <c r="H1226" t="n">
         <v>370</v>
@@ -35981,7 +35981,7 @@
         <v>1.17519998550415</v>
       </c>
       <c r="G1228" t="n">
-        <v>0.918340504169464</v>
+        <v>0.918340563774109</v>
       </c>
       <c r="H1228" t="n">
         <v>8221</v>
@@ -36097,7 +36097,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G1232" t="n">
-        <v>0.96116304397583</v>
+        <v>0.961163103580475</v>
       </c>
       <c r="H1232" t="n">
         <v>6056</v>
@@ -36155,7 +36155,7 @@
         <v>1.19099998474121</v>
       </c>
       <c r="G1234" t="n">
-        <v>0.930687248706818</v>
+        <v>0.930687189102173</v>
       </c>
       <c r="H1234" t="n">
         <v>2006</v>
@@ -36184,7 +36184,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G1235" t="n">
-        <v>0.96116304397583</v>
+        <v>0.961163103580475</v>
       </c>
       <c r="H1235" t="n">
         <v>16103</v>
@@ -36213,7 +36213,7 @@
         <v>1.19799995422363</v>
       </c>
       <c r="G1236" t="n">
-        <v>0.9361572265625</v>
+        <v>0.936157166957855</v>
       </c>
       <c r="H1236" t="n">
         <v>37918</v>
@@ -36242,7 +36242,7 @@
         <v>1.23800003528595</v>
       </c>
       <c r="G1237" t="n">
-        <v>0.967414557933807</v>
+        <v>0.967414736747742</v>
       </c>
       <c r="H1237" t="n">
         <v>7311</v>
@@ -36271,7 +36271,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1238" t="n">
-        <v>0.953348696231842</v>
+        <v>0.953348875045776</v>
       </c>
       <c r="H1238" t="n">
         <v>3720</v>
@@ -36300,7 +36300,7 @@
         <v>1.26800000667572</v>
       </c>
       <c r="G1239" t="n">
-        <v>0.990857541561127</v>
+        <v>0.990857481956482</v>
       </c>
       <c r="H1239" t="n">
         <v>129144</v>
@@ -36358,7 +36358,7 @@
         <v>1.27320003509521</v>
       </c>
       <c r="G1241" t="n">
-        <v>0.994921088218689</v>
+        <v>0.994921028614044</v>
       </c>
       <c r="H1241" t="n">
         <v>41792</v>
@@ -36387,7 +36387,7 @@
         <v>1.27320003509521</v>
       </c>
       <c r="G1242" t="n">
-        <v>0.994921088218689</v>
+        <v>0.994921028614044</v>
       </c>
       <c r="H1242" t="n">
         <v>13700</v>
@@ -36474,7 +36474,7 @@
         <v>1.32840001583099</v>
       </c>
       <c r="G1245" t="n">
-        <v>1.0380562543869</v>
+        <v>1.03805613517761</v>
       </c>
       <c r="H1245" t="n">
         <v>67169</v>
@@ -36532,7 +36532,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G1247" t="n">
-        <v>1.24247908592224</v>
+        <v>1.24247920513153</v>
       </c>
       <c r="H1247" t="n">
         <v>197270</v>
@@ -36590,7 +36590,7 @@
         <v>1.59200000762939</v>
       </c>
       <c r="G1249" t="n">
-        <v>1.24404203891754</v>
+        <v>1.24404191970825</v>
       </c>
       <c r="H1249" t="n">
         <v>77714</v>
@@ -36648,7 +36648,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G1251" t="n">
-        <v>1.3128080368042</v>
+        <v>1.31280815601349</v>
       </c>
       <c r="H1251" t="n">
         <v>57237</v>
@@ -36706,7 +36706,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G1253" t="n">
-        <v>1.3128080368042</v>
+        <v>1.31280815601349</v>
       </c>
       <c r="H1253" t="n">
         <v>6137</v>
@@ -36735,7 +36735,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1254" t="n">
-        <v>1.30499374866486</v>
+        <v>1.30499386787415</v>
       </c>
       <c r="H1254" t="n">
         <v>28012</v>
@@ -36764,7 +36764,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G1255" t="n">
-        <v>1.3128080368042</v>
+        <v>1.31280815601349</v>
       </c>
       <c r="H1255" t="n">
         <v>9259</v>
@@ -36793,7 +36793,7 @@
         <v>1.72060000896454</v>
       </c>
       <c r="G1256" t="n">
-        <v>1.34453427791595</v>
+        <v>1.34453439712524</v>
       </c>
       <c r="H1256" t="n">
         <v>88356</v>
@@ -36851,7 +36851,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G1258" t="n">
-        <v>1.4143944978714</v>
+        <v>1.41439437866211</v>
       </c>
       <c r="H1258" t="n">
         <v>159971</v>
@@ -36880,7 +36880,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G1259" t="n">
-        <v>1.32843673229218</v>
+        <v>1.32843685150146</v>
       </c>
       <c r="H1259" t="n">
         <v>147479</v>
@@ -36909,7 +36909,7 @@
         <v>1.71200001239777</v>
       </c>
       <c r="G1260" t="n">
-        <v>1.33781409263611</v>
+        <v>1.33781397342682</v>
       </c>
       <c r="H1260" t="n">
         <v>36578</v>
@@ -36938,7 +36938,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G1261" t="n">
-        <v>1.34406554698944</v>
+        <v>1.34406542778015</v>
       </c>
       <c r="H1261" t="n">
         <v>16020</v>
@@ -36996,7 +36996,7 @@
         <v>1.7208000421524</v>
       </c>
       <c r="G1263" t="n">
-        <v>1.34469056129456</v>
+        <v>1.34469068050385</v>
       </c>
       <c r="H1263" t="n">
         <v>7468</v>
@@ -37025,7 +37025,7 @@
         <v>1.71019995212555</v>
       </c>
       <c r="G1264" t="n">
-        <v>1.33640730381012</v>
+        <v>1.33640742301941</v>
       </c>
       <c r="H1264" t="n">
         <v>18672</v>
@@ -37112,7 +37112,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G1267" t="n">
-        <v>1.39095151424408</v>
+        <v>1.3909512758255</v>
       </c>
       <c r="H1267" t="n">
         <v>141202</v>
@@ -37141,7 +37141,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G1268" t="n">
-        <v>1.45658147335052</v>
+        <v>1.45658135414124</v>
       </c>
       <c r="H1268" t="n">
         <v>42786</v>
@@ -37170,7 +37170,7 @@
         <v>1.74979996681213</v>
       </c>
       <c r="G1269" t="n">
-        <v>1.46478521823883</v>
+        <v>1.46478497982025</v>
       </c>
       <c r="H1269" t="n">
         <v>33596</v>
@@ -37199,7 +37199,7 @@
         <v>1.73800003528595</v>
       </c>
       <c r="G1270" t="n">
-        <v>1.45490729808807</v>
+        <v>1.45490717887878</v>
       </c>
       <c r="H1270" t="n">
         <v>14911</v>
@@ -37228,7 +37228,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G1271" t="n">
-        <v>1.45658147335052</v>
+        <v>1.45658135414124</v>
       </c>
       <c r="H1271" t="n">
         <v>53971</v>
@@ -37257,7 +37257,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G1272" t="n">
-        <v>1.43983900547028</v>
+        <v>1.43983912467957</v>
       </c>
       <c r="H1272" t="n">
         <v>16994</v>
@@ -37286,7 +37286,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G1273" t="n">
-        <v>1.43983900547028</v>
+        <v>1.43983912467957</v>
       </c>
       <c r="H1273" t="n">
         <v>0</v>
@@ -37315,7 +37315,7 @@
         <v>1.69459998607635</v>
       </c>
       <c r="G1274" t="n">
-        <v>1.41857624053955</v>
+        <v>1.41857635974884</v>
       </c>
       <c r="H1274" t="n">
         <v>82713</v>
@@ -37344,7 +37344,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G1275" t="n">
-        <v>1.43983900547028</v>
+        <v>1.43983912467957</v>
       </c>
       <c r="H1275" t="n">
         <v>57560</v>
@@ -37489,7 +37489,7 @@
         <v>1.66600000858307</v>
       </c>
       <c r="G1280" t="n">
-        <v>1.39463484287262</v>
+        <v>1.39463472366333</v>
       </c>
       <c r="H1280" t="n">
         <v>32262</v>
@@ -37576,7 +37576,7 @@
         <v>1.64800000190735</v>
       </c>
       <c r="G1283" t="n">
-        <v>1.3795667886734</v>
+        <v>1.37956666946411</v>
       </c>
       <c r="H1283" t="n">
         <v>12860</v>
@@ -37605,7 +37605,7 @@
         <v>1.66939997673035</v>
       </c>
       <c r="G1284" t="n">
-        <v>1.39748108386993</v>
+        <v>1.39748084545135</v>
       </c>
       <c r="H1284" t="n">
         <v>12668</v>
@@ -37663,7 +37663,7 @@
         <v>1.60060000419617</v>
       </c>
       <c r="G1286" t="n">
-        <v>1.33988738059998</v>
+        <v>1.33988749980927</v>
       </c>
       <c r="H1286" t="n">
         <v>27968</v>
@@ -37692,7 +37692,7 @@
         <v>1.6088000535965</v>
       </c>
       <c r="G1287" t="n">
-        <v>1.34675192832947</v>
+        <v>1.34675180912018</v>
       </c>
       <c r="H1287" t="n">
         <v>15942</v>
@@ -37750,7 +37750,7 @@
         <v>1.62999999523163</v>
       </c>
       <c r="G1289" t="n">
-        <v>1.36449873447418</v>
+        <v>1.3644984960556</v>
       </c>
       <c r="H1289" t="n">
         <v>57500</v>
@@ -37779,7 +37779,7 @@
         <v>1.64820003509521</v>
       </c>
       <c r="G1290" t="n">
-        <v>1.37973415851593</v>
+        <v>1.37973403930664</v>
       </c>
       <c r="H1290" t="n">
         <v>301</v>
@@ -37924,7 +37924,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G1295" t="n">
-        <v>1.40635454654694</v>
+        <v>1.40635442733765</v>
       </c>
       <c r="H1295" t="n">
         <v>92320</v>
@@ -37953,7 +37953,7 @@
         <v>1.71039998531342</v>
       </c>
       <c r="G1296" t="n">
-        <v>1.43180274963379</v>
+        <v>1.4318026304245</v>
       </c>
       <c r="H1296" t="n">
         <v>100876</v>
@@ -37982,7 +37982,7 @@
         <v>1.77799999713898</v>
       </c>
       <c r="G1297" t="n">
-        <v>1.4883918762207</v>
+        <v>1.48839175701141</v>
       </c>
       <c r="H1297" t="n">
         <v>90989</v>
@@ -38011,7 +38011,7 @@
         <v>1.75419998168945</v>
       </c>
       <c r="G1298" t="n">
-        <v>1.46846830844879</v>
+        <v>1.46846842765808</v>
       </c>
       <c r="H1298" t="n">
         <v>40624</v>
@@ -38069,7 +38069,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G1300" t="n">
-        <v>1.49006605148315</v>
+        <v>1.49006593227386</v>
       </c>
       <c r="H1300" t="n">
         <v>15871</v>
@@ -38098,7 +38098,7 @@
         <v>1.80540001392365</v>
       </c>
       <c r="G1301" t="n">
-        <v>1.51132869720459</v>
+        <v>1.51132881641388</v>
       </c>
       <c r="H1301" t="n">
         <v>61944</v>
@@ -38214,7 +38214,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G1305" t="n">
-        <v>1.56540632247925</v>
+        <v>1.56540644168854</v>
       </c>
       <c r="H1305" t="n">
         <v>90063</v>
@@ -38243,7 +38243,7 @@
         <v>1.83259999752045</v>
       </c>
       <c r="G1306" t="n">
-        <v>1.53409814834595</v>
+        <v>1.53409826755524</v>
       </c>
       <c r="H1306" t="n">
         <v>15504</v>
@@ -38272,7 +38272,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G1307" t="n">
-        <v>1.57377743721008</v>
+        <v>1.57377755641937</v>
       </c>
       <c r="H1307" t="n">
         <v>25764</v>
@@ -38301,7 +38301,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G1308" t="n">
-        <v>1.57377743721008</v>
+        <v>1.57377755641937</v>
       </c>
       <c r="H1308" t="n">
         <v>6508</v>
@@ -38330,7 +38330,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G1309" t="n">
-        <v>1.56540632247925</v>
+        <v>1.56540644168854</v>
       </c>
       <c r="H1309" t="n">
         <v>5381</v>
@@ -38359,7 +38359,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G1310" t="n">
-        <v>1.56540632247925</v>
+        <v>1.56540644168854</v>
       </c>
       <c r="H1310" t="n">
         <v>6800</v>
@@ -38388,7 +38388,7 @@
         <v>1.87479996681213</v>
       </c>
       <c r="G1311" t="n">
-        <v>1.56942462921143</v>
+        <v>1.56942451000214</v>
       </c>
       <c r="H1311" t="n">
         <v>5785</v>
@@ -38417,7 +38417,7 @@
         <v>1.88979995250702</v>
       </c>
       <c r="G1312" t="n">
-        <v>1.58198130130768</v>
+        <v>1.58198118209839</v>
       </c>
       <c r="H1312" t="n">
         <v>7026</v>
@@ -38446,7 +38446,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G1313" t="n">
-        <v>1.57377743721008</v>
+        <v>1.57377755641937</v>
       </c>
       <c r="H1313" t="n">
         <v>4995</v>
@@ -38533,7 +38533,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G1316" t="n">
-        <v>1.57377743721008</v>
+        <v>1.57377755641937</v>
       </c>
       <c r="H1316" t="n">
         <v>16667</v>
@@ -38562,7 +38562,7 @@
         <v>1.9423999786377</v>
       </c>
       <c r="G1317" t="n">
-        <v>1.62601351737976</v>
+        <v>1.62601363658905</v>
       </c>
       <c r="H1317" t="n">
         <v>154605</v>
@@ -38620,7 +38620,7 @@
         <v>1.97979998588562</v>
       </c>
       <c r="G1319" t="n">
-        <v>1.65732169151306</v>
+        <v>1.65732181072235</v>
       </c>
       <c r="H1319" t="n">
         <v>18867</v>
@@ -38765,7 +38765,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G1324" t="n">
-        <v>1.61563324928284</v>
+        <v>1.61563336849213</v>
       </c>
       <c r="H1324" t="n">
         <v>11644</v>
@@ -38823,7 +38823,7 @@
         <v>1.94700002670288</v>
       </c>
       <c r="G1326" t="n">
-        <v>1.62986445426941</v>
+        <v>1.62986433506012</v>
       </c>
       <c r="H1326" t="n">
         <v>33486</v>
@@ -39171,7 +39171,7 @@
         <v>1.93499994277954</v>
       </c>
       <c r="G1338" t="n">
-        <v>1.61981892585754</v>
+        <v>1.61981904506683</v>
       </c>
       <c r="H1338" t="n">
         <v>12311</v>
@@ -39200,7 +39200,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G1339" t="n">
-        <v>1.60726225376129</v>
+        <v>1.607262134552</v>
       </c>
       <c r="H1339" t="n">
         <v>1005</v>
@@ -39229,7 +39229,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G1340" t="n">
-        <v>1.60726225376129</v>
+        <v>1.607262134552</v>
       </c>
       <c r="H1340" t="n">
         <v>120</v>
@@ -39258,7 +39258,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G1341" t="n">
-        <v>1.60726225376129</v>
+        <v>1.607262134552</v>
       </c>
       <c r="H1341" t="n">
         <v>20929</v>
@@ -39287,7 +39287,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G1342" t="n">
-        <v>1.61563324928284</v>
+        <v>1.61563336849213</v>
       </c>
       <c r="H1342" t="n">
         <v>4847</v>
@@ -39316,7 +39316,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G1343" t="n">
-        <v>1.60726225376129</v>
+        <v>1.607262134552</v>
       </c>
       <c r="H1343" t="n">
         <v>14161</v>
@@ -39345,7 +39345,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G1344" t="n">
-        <v>1.6909738779068</v>
+        <v>1.69097375869751</v>
       </c>
       <c r="H1344" t="n">
         <v>155728</v>
@@ -39432,7 +39432,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G1347" t="n">
-        <v>1.6909738779068</v>
+        <v>1.69097375869751</v>
       </c>
       <c r="H1347" t="n">
         <v>31082</v>
@@ -39519,7 +39519,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G1350" t="n">
-        <v>1.60726225376129</v>
+        <v>1.607262134552</v>
       </c>
       <c r="H1350" t="n">
         <v>120787</v>
@@ -39577,7 +39577,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G1352" t="n">
-        <v>1.59889113903046</v>
+        <v>1.59889101982117</v>
       </c>
       <c r="H1352" t="n">
         <v>23824</v>
@@ -39635,7 +39635,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G1354" t="n">
-        <v>1.59051978588104</v>
+        <v>1.59051990509033</v>
       </c>
       <c r="H1354" t="n">
         <v>15319</v>
@@ -39693,7 +39693,7 @@
         <v>1.88499999046326</v>
       </c>
       <c r="G1356" t="n">
-        <v>1.57796323299408</v>
+        <v>1.57796311378479</v>
       </c>
       <c r="H1356" t="n">
         <v>10700</v>
@@ -39722,7 +39722,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G1357" t="n">
-        <v>1.55703544616699</v>
+        <v>1.55703520774841</v>
       </c>
       <c r="H1357" t="n">
         <v>10646</v>
@@ -39780,7 +39780,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G1359" t="n">
-        <v>1.56540632247925</v>
+        <v>1.56540644168854</v>
       </c>
       <c r="H1359" t="n">
         <v>4850</v>
@@ -39809,7 +39809,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G1360" t="n">
-        <v>1.59051978588104</v>
+        <v>1.59051990509033</v>
       </c>
       <c r="H1360" t="n">
         <v>13059</v>
@@ -39838,7 +39838,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G1361" t="n">
-        <v>1.60726225376129</v>
+        <v>1.607262134552</v>
       </c>
       <c r="H1361" t="n">
         <v>16896</v>
@@ -39867,7 +39867,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G1362" t="n">
-        <v>1.59051978588104</v>
+        <v>1.59051990509033</v>
       </c>
       <c r="H1362" t="n">
         <v>7070</v>
@@ -39896,7 +39896,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G1363" t="n">
-        <v>1.5821487903595</v>
+        <v>1.58214867115021</v>
       </c>
       <c r="H1363" t="n">
         <v>20795</v>
@@ -39925,7 +39925,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G1364" t="n">
-        <v>1.59051978588104</v>
+        <v>1.59051990509033</v>
       </c>
       <c r="H1364" t="n">
         <v>4035</v>
@@ -39954,7 +39954,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G1365" t="n">
-        <v>1.59051978588104</v>
+        <v>1.59051990509033</v>
       </c>
       <c r="H1365" t="n">
         <v>1022</v>
@@ -40041,7 +40041,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G1368" t="n">
-        <v>1.59051978588104</v>
+        <v>1.59051990509033</v>
       </c>
       <c r="H1368" t="n">
         <v>25050</v>
@@ -40070,7 +40070,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G1369" t="n">
-        <v>1.55703544616699</v>
+        <v>1.55703520774841</v>
       </c>
       <c r="H1369" t="n">
         <v>6264</v>
@@ -40128,7 +40128,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G1371" t="n">
-        <v>1.55703544616699</v>
+        <v>1.55703520774841</v>
       </c>
       <c r="H1371" t="n">
         <v>5678</v>
@@ -40186,7 +40186,7 @@
         <v>1.83500003814697</v>
       </c>
       <c r="G1373" t="n">
-        <v>1.53610754013062</v>
+        <v>1.53610742092133</v>
       </c>
       <c r="H1373" t="n">
         <v>6413</v>
@@ -40244,7 +40244,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G1375" t="n">
-        <v>1.55703544616699</v>
+        <v>1.55703520774841</v>
       </c>
       <c r="H1375" t="n">
         <v>5724</v>
@@ -40302,7 +40302,7 @@
         <v>1.86500000953674</v>
       </c>
       <c r="G1377" t="n">
-        <v>1.56122088432312</v>
+        <v>1.56122076511383</v>
       </c>
       <c r="H1377" t="n">
         <v>24781</v>
@@ -40360,7 +40360,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G1379" t="n">
-        <v>1.89188158512115</v>
+        <v>1.89188170433044</v>
       </c>
       <c r="H1379" t="n">
         <v>317280</v>
@@ -40389,7 +40389,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1380" t="n">
-        <v>1.80817008018494</v>
+        <v>1.80817019939423</v>
       </c>
       <c r="H1380" t="n">
         <v>114976</v>
@@ -40418,7 +40418,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G1381" t="n">
-        <v>1.90862381458282</v>
+        <v>1.90862393379211</v>
       </c>
       <c r="H1381" t="n">
         <v>118880</v>
@@ -40476,7 +40476,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G1383" t="n">
-        <v>1.87513935565948</v>
+        <v>1.87513911724091</v>
       </c>
       <c r="H1383" t="n">
         <v>52913</v>
@@ -40505,7 +40505,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G1384" t="n">
-        <v>1.90025269985199</v>
+        <v>1.9002525806427</v>
       </c>
       <c r="H1384" t="n">
         <v>25190</v>
@@ -40708,7 +40708,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1391" t="n">
-        <v>1.80817008018494</v>
+        <v>1.80817019939423</v>
       </c>
       <c r="H1391" t="n">
         <v>20155</v>
@@ -40737,7 +40737,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G1392" t="n">
-        <v>1.7663140296936</v>
+        <v>1.76631414890289</v>
       </c>
       <c r="H1392" t="n">
         <v>3519</v>
@@ -40766,7 +40766,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1393" t="n">
-        <v>1.80817008018494</v>
+        <v>1.80817019939423</v>
       </c>
       <c r="H1393" t="n">
         <v>10650</v>
@@ -40824,7 +40824,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G1395" t="n">
-        <v>1.79142785072327</v>
+        <v>1.79142773151398</v>
       </c>
       <c r="H1395" t="n">
         <v>9872</v>
@@ -40911,7 +40911,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G1398" t="n">
-        <v>1.7663140296936</v>
+        <v>1.76631414890289</v>
       </c>
       <c r="H1398" t="n">
         <v>4485</v>
@@ -41114,7 +41114,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G1405" t="n">
-        <v>1.74957191944122</v>
+        <v>1.74957180023193</v>
       </c>
       <c r="H1405" t="n">
         <v>6593</v>
@@ -41317,7 +41317,7 @@
         <v>1.98500001430511</v>
       </c>
       <c r="G1412" t="n">
-        <v>1.66167485713959</v>
+        <v>1.6616747379303</v>
       </c>
       <c r="H1412" t="n">
         <v>10099</v>
@@ -41462,7 +41462,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G1417" t="n">
-        <v>1.6909738779068</v>
+        <v>1.69097375869751</v>
       </c>
       <c r="H1417" t="n">
         <v>5747</v>
@@ -41578,7 +41578,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1421" t="n">
-        <v>1.80817008018494</v>
+        <v>1.80817019939423</v>
       </c>
       <c r="H1421" t="n">
         <v>41767</v>
@@ -41723,7 +41723,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G1426" t="n">
-        <v>1.83328366279602</v>
+        <v>1.83328354358673</v>
       </c>
       <c r="H1426" t="n">
         <v>5861</v>
@@ -41839,7 +41839,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G1430" t="n">
-        <v>1.83328366279602</v>
+        <v>1.83328354358673</v>
       </c>
       <c r="H1430" t="n">
         <v>2450</v>
@@ -41926,7 +41926,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G1433" t="n">
-        <v>1.79142785072327</v>
+        <v>1.79142773151398</v>
       </c>
       <c r="H1433" t="n">
         <v>12195</v>
@@ -42042,7 +42042,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G1437" t="n">
-        <v>1.8500257730484</v>
+        <v>1.85002565383911</v>
       </c>
       <c r="H1437" t="n">
         <v>2124</v>
@@ -42187,7 +42187,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1442" t="n">
-        <v>1.80817008018494</v>
+        <v>1.80817019939423</v>
       </c>
       <c r="H1442" t="n">
         <v>3900</v>
@@ -42216,7 +42216,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G1443" t="n">
-        <v>1.83328366279602</v>
+        <v>1.83328354358673</v>
       </c>
       <c r="H1443" t="n">
         <v>7310</v>
@@ -42245,7 +42245,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G1444" t="n">
-        <v>1.83328366279602</v>
+        <v>1.83328354358673</v>
       </c>
       <c r="H1444" t="n">
         <v>0</v>
@@ -42332,7 +42332,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G1447" t="n">
-        <v>1.79142785072327</v>
+        <v>1.79142773151398</v>
       </c>
       <c r="H1447" t="n">
         <v>1801</v>
@@ -42361,7 +42361,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G1448" t="n">
-        <v>1.7663140296936</v>
+        <v>1.76631414890289</v>
       </c>
       <c r="H1448" t="n">
         <v>6157</v>
@@ -42564,7 +42564,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G1455" t="n">
-        <v>1.79142785072327</v>
+        <v>1.79142773151398</v>
       </c>
       <c r="H1455" t="n">
         <v>8648</v>
@@ -42593,7 +42593,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G1456" t="n">
-        <v>1.83328366279602</v>
+        <v>1.83328354358673</v>
       </c>
       <c r="H1456" t="n">
         <v>33296</v>
@@ -42651,7 +42651,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G1458" t="n">
-        <v>1.86676800251007</v>
+        <v>1.86676824092865</v>
       </c>
       <c r="H1458" t="n">
         <v>13297</v>
@@ -42680,7 +42680,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G1459" t="n">
-        <v>1.87513935565948</v>
+        <v>1.87513911724091</v>
       </c>
       <c r="H1459" t="n">
         <v>10775</v>
@@ -42709,7 +42709,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G1460" t="n">
-        <v>1.87513935565948</v>
+        <v>1.87513911724091</v>
       </c>
       <c r="H1460" t="n">
         <v>12250</v>
@@ -42738,7 +42738,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G1461" t="n">
-        <v>1.90025269985199</v>
+        <v>1.9002525806427</v>
       </c>
       <c r="H1461" t="n">
         <v>22939</v>
@@ -42767,7 +42767,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G1462" t="n">
-        <v>2.1932430267334</v>
+        <v>2.19324278831482</v>
       </c>
       <c r="H1462" t="n">
         <v>497101</v>
@@ -42796,7 +42796,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G1463" t="n">
-        <v>2.20161437988281</v>
+        <v>2.20161461830139</v>
       </c>
       <c r="H1463" t="n">
         <v>261129</v>
@@ -42854,7 +42854,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G1465" t="n">
-        <v>2.16812968254089</v>
+        <v>2.16812944412231</v>
       </c>
       <c r="H1465" t="n">
         <v>38675</v>
@@ -42912,7 +42912,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G1467" t="n">
-        <v>2.07604694366455</v>
+        <v>2.07604718208313</v>
       </c>
       <c r="H1467" t="n">
         <v>8318</v>
@@ -42970,7 +42970,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G1469" t="n">
-        <v>2.07604694366455</v>
+        <v>2.07604718208313</v>
       </c>
       <c r="H1469" t="n">
         <v>10761</v>
@@ -42999,7 +42999,7 @@
         <v>2.5</v>
       </c>
       <c r="G1470" t="n">
-        <v>2.0927894115448</v>
+        <v>2.09278917312622</v>
       </c>
       <c r="H1470" t="n">
         <v>17544</v>
@@ -43057,7 +43057,7 @@
         <v>2.5</v>
       </c>
       <c r="G1472" t="n">
-        <v>2.0927894115448</v>
+        <v>2.09278917312622</v>
       </c>
       <c r="H1472" t="n">
         <v>16513</v>
@@ -43115,7 +43115,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G1474" t="n">
-        <v>2.10953164100647</v>
+        <v>2.10953187942505</v>
       </c>
       <c r="H1474" t="n">
         <v>11143</v>
@@ -43144,7 +43144,7 @@
         <v>2.5</v>
       </c>
       <c r="G1475" t="n">
-        <v>2.0927894115448</v>
+        <v>2.09278917312622</v>
       </c>
       <c r="H1475" t="n">
         <v>1995</v>
@@ -43202,7 +43202,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G1477" t="n">
-        <v>2.18487215042114</v>
+        <v>2.18487191200256</v>
       </c>
       <c r="H1477" t="n">
         <v>44426</v>
@@ -43231,7 +43231,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G1478" t="n">
-        <v>2.20161437988281</v>
+        <v>2.20161461830139</v>
       </c>
       <c r="H1478" t="n">
         <v>8945</v>
@@ -43347,7 +43347,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G1482" t="n">
-        <v>2.1932430267334</v>
+        <v>2.19324278831482</v>
       </c>
       <c r="H1482" t="n">
         <v>2227</v>
@@ -43405,7 +43405,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G1484" t="n">
-        <v>2.18487215042114</v>
+        <v>2.18487191200256</v>
       </c>
       <c r="H1484" t="n">
         <v>432</v>
@@ -43434,7 +43434,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G1485" t="n">
-        <v>2.18487215042114</v>
+        <v>2.18487191200256</v>
       </c>
       <c r="H1485" t="n">
         <v>5778</v>
@@ -43463,7 +43463,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G1486" t="n">
-        <v>2.18487215042114</v>
+        <v>2.18487191200256</v>
       </c>
       <c r="H1486" t="n">
         <v>5915</v>
@@ -43492,7 +43492,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G1487" t="n">
-        <v>2.18487215042114</v>
+        <v>2.18487191200256</v>
       </c>
       <c r="H1487" t="n">
         <v>4544</v>
@@ -43521,7 +43521,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G1488" t="n">
-        <v>2.16812968254089</v>
+        <v>2.16812944412231</v>
       </c>
       <c r="H1488" t="n">
         <v>17680</v>
@@ -43637,7 +43637,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G1492" t="n">
-        <v>2.15138721466064</v>
+        <v>2.15138745307922</v>
       </c>
       <c r="H1492" t="n">
         <v>4814</v>
@@ -43695,7 +43695,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G1494" t="n">
-        <v>2.2518413066864</v>
+        <v>2.25184154510498</v>
       </c>
       <c r="H1494" t="n">
         <v>89679</v>
@@ -43724,7 +43724,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G1495" t="n">
-        <v>2.26021242141724</v>
+        <v>2.26021265983582</v>
       </c>
       <c r="H1495" t="n">
         <v>31872</v>
@@ -43811,7 +43811,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G1498" t="n">
-        <v>2.21835684776306</v>
+        <v>2.21835660934448</v>
       </c>
       <c r="H1498" t="n">
         <v>26546</v>
@@ -43840,7 +43840,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G1499" t="n">
-        <v>2.21835684776306</v>
+        <v>2.21835660934448</v>
       </c>
       <c r="H1499" t="n">
         <v>2484</v>
@@ -43898,7 +43898,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G1501" t="n">
-        <v>2.2518413066864</v>
+        <v>2.25184154510498</v>
       </c>
       <c r="H1501" t="n">
         <v>65037</v>
@@ -43927,7 +43927,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G1502" t="n">
-        <v>2.27695465087891</v>
+        <v>2.27695488929749</v>
       </c>
       <c r="H1502" t="n">
         <v>6864</v>
@@ -43956,7 +43956,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G1503" t="n">
-        <v>2.2518413066864</v>
+        <v>2.25184154510498</v>
       </c>
       <c r="H1503" t="n">
         <v>18385</v>
@@ -43985,7 +43985,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G1504" t="n">
-        <v>2.24347043037415</v>
+        <v>2.24346995353699</v>
       </c>
       <c r="H1504" t="n">
         <v>44721</v>
@@ -44014,7 +44014,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G1505" t="n">
-        <v>2.21835684776306</v>
+        <v>2.21835660934448</v>
       </c>
       <c r="H1505" t="n">
         <v>7243</v>
@@ -44043,7 +44043,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G1506" t="n">
-        <v>2.26858377456665</v>
+        <v>2.26858353614807</v>
       </c>
       <c r="H1506" t="n">
         <v>24102</v>
@@ -44072,7 +44072,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G1507" t="n">
-        <v>2.26858377456665</v>
+        <v>2.26858353614807</v>
       </c>
       <c r="H1507" t="n">
         <v>15920</v>
@@ -44101,7 +44101,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G1508" t="n">
-        <v>2.26021242141724</v>
+        <v>2.26021265983582</v>
       </c>
       <c r="H1508" t="n">
         <v>11295</v>
@@ -44130,7 +44130,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G1509" t="n">
-        <v>2.26858377456665</v>
+        <v>2.26858353614807</v>
       </c>
       <c r="H1509" t="n">
         <v>27905</v>
@@ -44159,7 +44159,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G1510" t="n">
-        <v>2.26021242141724</v>
+        <v>2.26021265983582</v>
       </c>
       <c r="H1510" t="n">
         <v>3332</v>
@@ -44188,7 +44188,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G1511" t="n">
-        <v>2.21835684776306</v>
+        <v>2.21835660934448</v>
       </c>
       <c r="H1511" t="n">
         <v>8611</v>
@@ -44217,7 +44217,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G1512" t="n">
-        <v>2.2518413066864</v>
+        <v>2.25184154510498</v>
       </c>
       <c r="H1512" t="n">
         <v>1609</v>
@@ -44246,7 +44246,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G1513" t="n">
-        <v>2.2518413066864</v>
+        <v>2.25184154510498</v>
       </c>
       <c r="H1513" t="n">
         <v>10947</v>
@@ -44275,7 +44275,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G1514" t="n">
-        <v>2.26858377456665</v>
+        <v>2.26858353614807</v>
       </c>
       <c r="H1514" t="n">
         <v>9007</v>
@@ -44304,7 +44304,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G1515" t="n">
-        <v>2.26858377456665</v>
+        <v>2.26858353614807</v>
       </c>
       <c r="H1515" t="n">
         <v>22258</v>
@@ -44333,7 +44333,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G1516" t="n">
-        <v>2.26021242141724</v>
+        <v>2.26021265983582</v>
       </c>
       <c r="H1516" t="n">
         <v>39885</v>
@@ -44362,7 +44362,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G1517" t="n">
-        <v>2.54483199119568</v>
+        <v>2.5448317527771</v>
       </c>
       <c r="H1517" t="n">
         <v>82221</v>
@@ -44391,7 +44391,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G1518" t="n">
-        <v>2.62017226219177</v>
+        <v>2.62017250061035</v>
       </c>
       <c r="H1518" t="n">
         <v>151266</v>
@@ -44420,7 +44420,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G1519" t="n">
-        <v>2.59505891799927</v>
+        <v>2.59505867958069</v>
       </c>
       <c r="H1519" t="n">
         <v>110398</v>
@@ -44449,7 +44449,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G1520" t="n">
-        <v>2.67039918899536</v>
+        <v>2.67039942741394</v>
       </c>
       <c r="H1520" t="n">
         <v>70441</v>
@@ -44478,7 +44478,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G1521" t="n">
-        <v>2.71225500106812</v>
+        <v>2.71225523948669</v>
       </c>
       <c r="H1521" t="n">
         <v>58192</v>
@@ -44536,7 +44536,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G1523" t="n">
-        <v>2.75411081314087</v>
+        <v>2.75411057472229</v>
       </c>
       <c r="H1523" t="n">
         <v>36741</v>
@@ -44565,7 +44565,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G1524" t="n">
-        <v>3.23963785171509</v>
+        <v>3.23963809013367</v>
       </c>
       <c r="H1524" t="n">
         <v>106501</v>
@@ -44710,7 +44710,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G1529" t="n">
-        <v>3.0303590297699</v>
+        <v>3.03035879135132</v>
       </c>
       <c r="H1529" t="n">
         <v>25973</v>
@@ -44855,7 +44855,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G1534" t="n">
-        <v>2.87967801094055</v>
+        <v>2.87967824935913</v>
       </c>
       <c r="H1534" t="n">
         <v>5863</v>
@@ -44971,7 +44971,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1538" t="n">
-        <v>2.84619331359863</v>
+        <v>2.84619355201721</v>
       </c>
       <c r="H1538" t="n">
         <v>13330</v>
@@ -45029,7 +45029,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G1540" t="n">
-        <v>2.78759551048279</v>
+        <v>2.78759527206421</v>
       </c>
       <c r="H1540" t="n">
         <v>21833</v>
@@ -45058,7 +45058,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1541" t="n">
-        <v>2.80433750152588</v>
+        <v>2.80433773994446</v>
       </c>
       <c r="H1541" t="n">
         <v>9323</v>
@@ -45174,7 +45174,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G1545" t="n">
-        <v>3.03873014450073</v>
+        <v>3.03873038291931</v>
       </c>
       <c r="H1545" t="n">
         <v>46478</v>
@@ -45232,7 +45232,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G1547" t="n">
-        <v>3.04710125923157</v>
+        <v>3.04710149765015</v>
       </c>
       <c r="H1547" t="n">
         <v>27597</v>
@@ -45261,7 +45261,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G1548" t="n">
-        <v>3.12244176864624</v>
+        <v>3.12244153022766</v>
       </c>
       <c r="H1548" t="n">
         <v>31587</v>
@@ -45290,7 +45290,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G1549" t="n">
-        <v>3.18941068649292</v>
+        <v>3.1894109249115</v>
       </c>
       <c r="H1549" t="n">
         <v>55680</v>
@@ -45493,7 +45493,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G1556" t="n">
-        <v>3.2180643081665</v>
+        <v>3.21806406974792</v>
       </c>
       <c r="H1556" t="n">
         <v>26348</v>
@@ -45522,7 +45522,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G1557" t="n">
-        <v>3.1576714515686</v>
+        <v>3.15767168998718</v>
       </c>
       <c r="H1557" t="n">
         <v>14643</v>
@@ -45725,7 +45725,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1564" t="n">
-        <v>3.10590648651123</v>
+        <v>3.10590624809265</v>
       </c>
       <c r="H1564" t="n">
         <v>5841</v>
@@ -45783,7 +45783,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G1566" t="n">
-        <v>2.97649359703064</v>
+        <v>2.97649383544922</v>
       </c>
       <c r="H1566" t="n">
         <v>27030</v>
@@ -46015,7 +46015,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G1574" t="n">
-        <v>2.66590285301208</v>
+        <v>2.66590309143066</v>
       </c>
       <c r="H1574" t="n">
         <v>33185</v>
@@ -46044,7 +46044,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G1575" t="n">
-        <v>2.62276530265808</v>
+        <v>2.62276554107666</v>
       </c>
       <c r="H1575" t="n">
         <v>16919</v>
@@ -46218,7 +46218,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G1581" t="n">
-        <v>3.00237607955933</v>
+        <v>3.00237631797791</v>
       </c>
       <c r="H1581" t="n">
         <v>7369</v>
@@ -46247,7 +46247,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G1582" t="n">
-        <v>2.96786594390869</v>
+        <v>2.96786618232727</v>
       </c>
       <c r="H1582" t="n">
         <v>9819</v>
@@ -46421,7 +46421,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G1588" t="n">
-        <v>3.00237607955933</v>
+        <v>3.00237631797791</v>
       </c>
       <c r="H1588" t="n">
         <v>8197</v>
@@ -46595,7 +46595,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1594" t="n">
-        <v>2.93335604667664</v>
+        <v>2.93335628509521</v>
       </c>
       <c r="H1594" t="n">
         <v>1217</v>
@@ -46624,7 +46624,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1595" t="n">
-        <v>2.93335604667664</v>
+        <v>2.93335628509521</v>
       </c>
       <c r="H1595" t="n">
         <v>2971</v>
@@ -46711,7 +46711,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1598" t="n">
-        <v>2.93335604667664</v>
+        <v>2.93335628509521</v>
       </c>
       <c r="H1598" t="n">
         <v>2090</v>
@@ -46798,7 +46798,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1601" t="n">
-        <v>2.93335604667664</v>
+        <v>2.93335628509521</v>
       </c>
       <c r="H1601" t="n">
         <v>1039</v>
@@ -46827,7 +46827,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G1602" t="n">
-        <v>2.95061135292053</v>
+        <v>2.95061111450195</v>
       </c>
       <c r="H1602" t="n">
         <v>3240</v>
@@ -47001,7 +47001,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G1608" t="n">
-        <v>2.95061135292053</v>
+        <v>2.95061111450195</v>
       </c>
       <c r="H1608" t="n">
         <v>24178</v>
@@ -47059,7 +47059,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G1610" t="n">
-        <v>3.19792723655701</v>
+        <v>3.19792699813843</v>
       </c>
       <c r="H1610" t="n">
         <v>18822</v>
@@ -47088,7 +47088,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1611" t="n">
-        <v>3.05004620552063</v>
+        <v>3.05004596710205</v>
       </c>
       <c r="H1611" t="n">
         <v>18282</v>
@@ -47117,7 +47117,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1612" t="n">
-        <v>3.05004620552063</v>
+        <v>3.05004596710205</v>
       </c>
       <c r="H1612" t="n">
         <v>6535</v>
@@ -47146,7 +47146,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1613" t="n">
-        <v>3.05004620552063</v>
+        <v>3.05004596710205</v>
       </c>
       <c r="H1613" t="n">
         <v>6560</v>
@@ -47204,7 +47204,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G1615" t="n">
-        <v>2.98534822463989</v>
+        <v>2.98534798622131</v>
       </c>
       <c r="H1615" t="n">
         <v>5371</v>
@@ -47262,7 +47262,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G1617" t="n">
-        <v>3.01307582855225</v>
+        <v>3.01307559013367</v>
       </c>
       <c r="H1617" t="n">
         <v>1877</v>
@@ -47320,7 +47320,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G1619" t="n">
-        <v>3.06853103637695</v>
+        <v>3.06853127479553</v>
       </c>
       <c r="H1619" t="n">
         <v>5319</v>
@@ -47378,7 +47378,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G1621" t="n">
-        <v>2.93913531303406</v>
+        <v>2.93913555145264</v>
       </c>
       <c r="H1621" t="n">
         <v>7441</v>
@@ -47407,7 +47407,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G1622" t="n">
-        <v>3.06853103637695</v>
+        <v>3.06853127479553</v>
       </c>
       <c r="H1622" t="n">
         <v>9571</v>
@@ -47494,7 +47494,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G1625" t="n">
-        <v>3.01307582855225</v>
+        <v>3.01307559013367</v>
       </c>
       <c r="H1625" t="n">
         <v>720</v>
@@ -47523,7 +47523,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G1626" t="n">
-        <v>3.01307582855225</v>
+        <v>3.01307559013367</v>
       </c>
       <c r="H1626" t="n">
         <v>0</v>
@@ -47552,7 +47552,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G1627" t="n">
-        <v>2.98534822463989</v>
+        <v>2.98534798622131</v>
       </c>
       <c r="H1627" t="n">
         <v>2900</v>
@@ -47697,7 +47697,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G1632" t="n">
-        <v>2.93913531303406</v>
+        <v>2.93913555145264</v>
       </c>
       <c r="H1632" t="n">
         <v>2221</v>
@@ -47813,7 +47813,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G1636" t="n">
-        <v>2.88367962837219</v>
+        <v>2.88367986679077</v>
       </c>
       <c r="H1636" t="n">
         <v>4351</v>
@@ -48074,7 +48074,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G1645" t="n">
-        <v>2.44927954673767</v>
+        <v>2.44927930831909</v>
       </c>
       <c r="H1645" t="n">
         <v>4242</v>
@@ -48364,7 +48364,7 @@
         <v>2.75</v>
       </c>
       <c r="G1655" t="n">
-        <v>2.54170489311218</v>
+        <v>2.54170513153076</v>
       </c>
       <c r="H1655" t="n">
         <v>4443</v>
@@ -48422,7 +48422,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G1657" t="n">
-        <v>2.66185855865479</v>
+        <v>2.66185832023621</v>
       </c>
       <c r="H1657" t="n">
         <v>1365</v>
@@ -48538,7 +48538,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G1661" t="n">
-        <v>2.51397728919983</v>
+        <v>2.51397752761841</v>
       </c>
       <c r="H1661" t="n">
         <v>2782</v>
@@ -48596,7 +48596,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G1663" t="n">
-        <v>2.53246235847473</v>
+        <v>2.53246259689331</v>
       </c>
       <c r="H1663" t="n">
         <v>37694</v>
@@ -48625,7 +48625,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G1664" t="n">
-        <v>2.48624992370605</v>
+        <v>2.48624968528748</v>
       </c>
       <c r="H1664" t="n">
         <v>1765</v>
@@ -48712,7 +48712,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G1667" t="n">
-        <v>2.51397728919983</v>
+        <v>2.51397752761841</v>
       </c>
       <c r="H1667" t="n">
         <v>22439</v>
@@ -48741,7 +48741,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G1668" t="n">
-        <v>2.44927954673767</v>
+        <v>2.44927930831909</v>
       </c>
       <c r="H1668" t="n">
         <v>12455</v>
@@ -48857,7 +48857,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G1672" t="n">
-        <v>2.42155170440674</v>
+        <v>2.42155146598816</v>
       </c>
       <c r="H1672" t="n">
         <v>3460</v>
@@ -49147,7 +49147,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G1682" t="n">
-        <v>2.40306639671326</v>
+        <v>2.40306663513184</v>
       </c>
       <c r="H1682" t="n">
         <v>1410</v>
@@ -49495,7 +49495,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G1694" t="n">
-        <v>2.27367091178894</v>
+        <v>2.27367067337036</v>
       </c>
       <c r="H1694" t="n">
         <v>3905</v>
@@ -49611,7 +49611,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G1698" t="n">
-        <v>2.27367091178894</v>
+        <v>2.27367067337036</v>
       </c>
       <c r="H1698" t="n">
         <v>19</v>
@@ -49640,7 +49640,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G1699" t="n">
-        <v>2.26442813873291</v>
+        <v>2.26442837715149</v>
       </c>
       <c r="H1699" t="n">
         <v>580</v>
@@ -49669,7 +49669,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G1700" t="n">
-        <v>2.23670053482056</v>
+        <v>2.23670029640198</v>
       </c>
       <c r="H1700" t="n">
         <v>450</v>
@@ -49814,7 +49814,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G1705" t="n">
-        <v>2.2089729309082</v>
+        <v>2.20897269248962</v>
       </c>
       <c r="H1705" t="n">
         <v>1386</v>
@@ -49872,7 +49872,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G1707" t="n">
-        <v>2.26442813873291</v>
+        <v>2.26442837715149</v>
       </c>
       <c r="H1707" t="n">
         <v>190</v>
@@ -49901,7 +49901,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G1708" t="n">
-        <v>2.26442813873291</v>
+        <v>2.26442837715149</v>
       </c>
       <c r="H1708" t="n">
         <v>0</v>
@@ -49959,7 +49959,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G1710" t="n">
-        <v>2.28291344642639</v>
+        <v>2.28291320800781</v>
       </c>
       <c r="H1710" t="n">
         <v>900</v>
@@ -49988,7 +49988,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G1711" t="n">
-        <v>2.28291344642639</v>
+        <v>2.28291320800781</v>
       </c>
       <c r="H1711" t="n">
         <v>0</v>
@@ -50104,7 +50104,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G1715" t="n">
-        <v>2.23670053482056</v>
+        <v>2.23670029640198</v>
       </c>
       <c r="H1715" t="n">
         <v>11340</v>
@@ -50133,7 +50133,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G1716" t="n">
-        <v>2.28291344642639</v>
+        <v>2.28291320800781</v>
       </c>
       <c r="H1716" t="n">
         <v>8732</v>
@@ -50278,7 +50278,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G1721" t="n">
-        <v>2.07033443450928</v>
+        <v>2.0703341960907</v>
       </c>
       <c r="H1721" t="n">
         <v>201</v>
@@ -50336,7 +50336,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G1723" t="n">
-        <v>2.19048738479614</v>
+        <v>2.19048762321472</v>
       </c>
       <c r="H1723" t="n">
         <v>7034</v>
@@ -50423,7 +50423,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G1726" t="n">
-        <v>2.06109189987183</v>
+        <v>2.06109166145325</v>
       </c>
       <c r="H1726" t="n">
         <v>7464</v>
@@ -50684,7 +50684,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G1735" t="n">
-        <v>2.0518491268158</v>
+        <v>2.05184936523438</v>
       </c>
       <c r="H1735" t="n">
         <v>601</v>
@@ -50742,7 +50742,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1737" t="n">
-        <v>1.99639391899109</v>
+        <v>1.99639403820038</v>
       </c>
       <c r="H1737" t="n">
         <v>7242</v>
@@ -50945,7 +50945,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G1744" t="n">
-        <v>2.07033443450928</v>
+        <v>2.0703341960907</v>
       </c>
       <c r="H1744" t="n">
         <v>2600</v>
@@ -51032,7 +51032,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G1747" t="n">
-        <v>2.06109189987183</v>
+        <v>2.06109166145325</v>
       </c>
       <c r="H1747" t="n">
         <v>2976</v>
@@ -51148,7 +51148,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G1751" t="n">
-        <v>2.23670053482056</v>
+        <v>2.23670029640198</v>
       </c>
       <c r="H1751" t="n">
         <v>2433</v>
@@ -51293,7 +51293,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G1756" t="n">
-        <v>2.19048738479614</v>
+        <v>2.19048762321472</v>
       </c>
       <c r="H1756" t="n">
         <v>8634</v>
@@ -51322,7 +51322,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G1757" t="n">
-        <v>2.27367091178894</v>
+        <v>2.27367067337036</v>
       </c>
       <c r="H1757" t="n">
         <v>7714</v>
@@ -51351,7 +51351,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G1758" t="n">
-        <v>2.53246235847473</v>
+        <v>2.53246259689331</v>
       </c>
       <c r="H1758" t="n">
         <v>20349</v>
@@ -51467,7 +51467,7 @@
         <v>2.75</v>
       </c>
       <c r="G1762" t="n">
-        <v>2.54170489311218</v>
+        <v>2.54170513153076</v>
       </c>
       <c r="H1762" t="n">
         <v>6937</v>
@@ -51699,7 +51699,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G1770" t="n">
-        <v>2.51397728919983</v>
+        <v>2.51397752761841</v>
       </c>
       <c r="H1770" t="n">
         <v>9906</v>
@@ -51786,7 +51786,7 @@
         <v>2.75</v>
       </c>
       <c r="G1773" t="n">
-        <v>2.54170489311218</v>
+        <v>2.54170513153076</v>
       </c>
       <c r="H1773" t="n">
         <v>13690</v>
@@ -51844,7 +51844,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G1775" t="n">
-        <v>2.53246235847473</v>
+        <v>2.53246259689331</v>
       </c>
       <c r="H1775" t="n">
         <v>10845</v>
@@ -51873,7 +51873,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G1776" t="n">
-        <v>2.53246235847473</v>
+        <v>2.53246259689331</v>
       </c>
       <c r="H1776" t="n">
         <v>3910</v>
@@ -51902,7 +51902,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G1777" t="n">
-        <v>2.51397728919983</v>
+        <v>2.51397752761841</v>
       </c>
       <c r="H1777" t="n">
         <v>18536</v>
@@ -80067,6 +80067,35 @@
         <v>4509</v>
       </c>
       <c r="I2748" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2749">
+      <c r="A2749" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2749" s="1" t="n">
+        <v>46318.2916666667</v>
+      </c>
+      <c r="C2749" t="n">
+        <v>0.389999985694885</v>
+      </c>
+      <c r="D2749" t="n">
+        <v>0.398000001907349</v>
+      </c>
+      <c r="E2749" t="n">
+        <v>0.389999985694885</v>
+      </c>
+      <c r="F2749" t="n">
+        <v>0.398000001907349</v>
+      </c>
+      <c r="G2749" t="n">
+        <v>0.398000001907349</v>
+      </c>
+      <c r="H2749" t="n">
+        <v>1001</v>
+      </c>
+      <c r="I2749" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ZUC.MI.xlsx
+++ b/data/ZUC.MI.xlsx
@@ -456,7 +456,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G3" t="n">
-        <v>3.07884764671326</v>
+        <v>3.07884788513184</v>
       </c>
       <c r="H3" t="n">
         <v>28114</v>
@@ -485,7 +485,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G4" t="n">
-        <v>2.96163249015808</v>
+        <v>2.96163272857666</v>
       </c>
       <c r="H4" t="n">
         <v>12680</v>
@@ -543,7 +543,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G6" t="n">
-        <v>2.96944713592529</v>
+        <v>2.96944689750671</v>
       </c>
       <c r="H6" t="n">
         <v>40605</v>
@@ -572,7 +572,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G7" t="n">
-        <v>2.84441757202148</v>
+        <v>2.84441781044006</v>
       </c>
       <c r="H7" t="n">
         <v>15987</v>
@@ -659,7 +659,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G10" t="n">
-        <v>2.8913037776947</v>
+        <v>2.89130353927612</v>
       </c>
       <c r="H10" t="n">
         <v>21901</v>
@@ -688,7 +688,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G11" t="n">
-        <v>2.77408862113953</v>
+        <v>2.77408838272095</v>
       </c>
       <c r="H11" t="n">
         <v>14530</v>
@@ -717,7 +717,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G12" t="n">
-        <v>2.62561631202698</v>
+        <v>2.6256160736084</v>
       </c>
       <c r="H12" t="n">
         <v>16207</v>
@@ -746,7 +746,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G13" t="n">
-        <v>2.50840163230896</v>
+        <v>2.5084011554718</v>
       </c>
       <c r="H13" t="n">
         <v>22831</v>
@@ -775,7 +775,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G14" t="n">
-        <v>2.39900064468384</v>
+        <v>2.39900040626526</v>
       </c>
       <c r="H14" t="n">
         <v>17223</v>
@@ -833,7 +833,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G16" t="n">
-        <v>2.39118623733521</v>
+        <v>2.39118599891663</v>
       </c>
       <c r="H16" t="n">
         <v>21477</v>
@@ -862,7 +862,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G17" t="n">
-        <v>2.4146294593811</v>
+        <v>2.41462922096252</v>
       </c>
       <c r="H17" t="n">
         <v>14217</v>
@@ -891,7 +891,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G18" t="n">
-        <v>2.4146294593811</v>
+        <v>2.41462922096252</v>
       </c>
       <c r="H18" t="n">
         <v>18543</v>
@@ -1007,7 +1007,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G22" t="n">
-        <v>2.30522871017456</v>
+        <v>2.30522847175598</v>
       </c>
       <c r="H22" t="n">
         <v>7688</v>
@@ -1094,7 +1094,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G25" t="n">
-        <v>1.78948247432709</v>
+        <v>1.78948259353638</v>
       </c>
       <c r="H25" t="n">
         <v>29015</v>
@@ -1123,7 +1123,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G26" t="n">
-        <v>1.44565188884735</v>
+        <v>1.44565176963806</v>
       </c>
       <c r="H26" t="n">
         <v>34743</v>
@@ -1181,7 +1181,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G28" t="n">
-        <v>0.625146806240082</v>
+        <v>0.625146746635437</v>
       </c>
       <c r="H28" t="n">
         <v>17146</v>
@@ -1210,7 +1210,7 @@
         <v>1</v>
       </c>
       <c r="G29" t="n">
-        <v>0.781433463096619</v>
+        <v>0.781433403491974</v>
       </c>
       <c r="H29" t="n">
         <v>16056</v>
@@ -1297,7 +1297,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G32" t="n">
-        <v>1.64101016521454</v>
+        <v>1.64101004600525</v>
       </c>
       <c r="H32" t="n">
         <v>80086</v>
@@ -1326,7 +1326,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G33" t="n">
-        <v>1.99265480041504</v>
+        <v>1.99265515804291</v>
       </c>
       <c r="H33" t="n">
         <v>23570</v>
@@ -1384,7 +1384,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G35" t="n">
-        <v>2.50058722496033</v>
+        <v>2.50058698654175</v>
       </c>
       <c r="H35" t="n">
         <v>58798</v>
@@ -1558,7 +1558,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G41" t="n">
-        <v>2.51621580123901</v>
+        <v>2.51621556282043</v>
       </c>
       <c r="H41" t="n">
         <v>12434</v>
@@ -1587,7 +1587,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G42" t="n">
-        <v>2.45370101928711</v>
+        <v>2.45370078086853</v>
       </c>
       <c r="H42" t="n">
         <v>6497</v>
@@ -1645,7 +1645,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G44" t="n">
-        <v>2.48495841026306</v>
+        <v>2.48495817184448</v>
       </c>
       <c r="H44" t="n">
         <v>10570</v>
@@ -1674,7 +1674,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G45" t="n">
-        <v>2.77408862113953</v>
+        <v>2.77408838272095</v>
       </c>
       <c r="H45" t="n">
         <v>276654</v>
@@ -1732,7 +1732,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G47" t="n">
-        <v>2.50058722496033</v>
+        <v>2.50058698654175</v>
       </c>
       <c r="H47" t="n">
         <v>39352</v>
@@ -1761,7 +1761,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G48" t="n">
-        <v>2.52403020858765</v>
+        <v>2.52402973175049</v>
       </c>
       <c r="H48" t="n">
         <v>14408</v>
@@ -1790,7 +1790,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G49" t="n">
-        <v>2.57091593742371</v>
+        <v>2.57091569900513</v>
       </c>
       <c r="H49" t="n">
         <v>6727</v>
@@ -1848,7 +1848,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G51" t="n">
-        <v>2.54747295379639</v>
+        <v>2.54747271537781</v>
       </c>
       <c r="H51" t="n">
         <v>16194</v>
@@ -1877,7 +1877,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G52" t="n">
-        <v>2.50058722496033</v>
+        <v>2.50058698654175</v>
       </c>
       <c r="H52" t="n">
         <v>6390</v>
@@ -1993,7 +1993,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G56" t="n">
-        <v>2.4146294593811</v>
+        <v>2.41462922096252</v>
       </c>
       <c r="H56" t="n">
         <v>6905</v>
@@ -2080,7 +2080,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G59" t="n">
-        <v>2.22708511352539</v>
+        <v>2.22708535194397</v>
       </c>
       <c r="H59" t="n">
         <v>10942</v>
@@ -2109,7 +2109,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G60" t="n">
-        <v>2.15675616264343</v>
+        <v>2.15675640106201</v>
       </c>
       <c r="H60" t="n">
         <v>5903</v>
@@ -2138,7 +2138,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G61" t="n">
-        <v>2.0864269733429</v>
+        <v>2.08642745018005</v>
       </c>
       <c r="H61" t="n">
         <v>24791</v>
@@ -2167,7 +2167,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G62" t="n">
-        <v>2.0551700592041</v>
+        <v>2.05517029762268</v>
       </c>
       <c r="H62" t="n">
         <v>7073</v>
@@ -2196,7 +2196,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G63" t="n">
-        <v>2.07079863548279</v>
+        <v>2.07079839706421</v>
       </c>
       <c r="H63" t="n">
         <v>3910</v>
@@ -2370,7 +2370,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G69" t="n">
-        <v>1.83636844158173</v>
+        <v>1.83636856079102</v>
       </c>
       <c r="H69" t="n">
         <v>7190</v>
@@ -2399,7 +2399,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G70" t="n">
-        <v>1.82073986530304</v>
+        <v>1.82073962688446</v>
       </c>
       <c r="H70" t="n">
         <v>19067</v>
@@ -2428,7 +2428,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G71" t="n">
-        <v>1.8129255771637</v>
+        <v>1.81292545795441</v>
       </c>
       <c r="H71" t="n">
         <v>7528</v>
@@ -2457,7 +2457,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G72" t="n">
-        <v>1.80511105060577</v>
+        <v>1.80511116981506</v>
       </c>
       <c r="H72" t="n">
         <v>6071</v>
@@ -2486,7 +2486,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G73" t="n">
-        <v>1.94576907157898</v>
+        <v>1.94576930999756</v>
       </c>
       <c r="H73" t="n">
         <v>30047</v>
@@ -2515,7 +2515,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G74" t="n">
-        <v>1.91451179981232</v>
+        <v>1.91451215744019</v>
       </c>
       <c r="H74" t="n">
         <v>27553</v>
@@ -2544,7 +2544,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G75" t="n">
-        <v>1.84418272972107</v>
+        <v>1.84418261051178</v>
       </c>
       <c r="H75" t="n">
         <v>12321</v>
@@ -2573,7 +2573,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G76" t="n">
-        <v>1.87544012069702</v>
+        <v>1.87544047832489</v>
       </c>
       <c r="H76" t="n">
         <v>16625</v>
@@ -2602,7 +2602,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G77" t="n">
-        <v>1.80511105060577</v>
+        <v>1.80511116981506</v>
       </c>
       <c r="H77" t="n">
         <v>15224</v>
@@ -2631,7 +2631,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G78" t="n">
-        <v>1.7738538980484</v>
+        <v>1.77385365962982</v>
       </c>
       <c r="H78" t="n">
         <v>12767</v>
@@ -2660,7 +2660,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G79" t="n">
-        <v>1.75041079521179</v>
+        <v>1.7504106760025</v>
       </c>
       <c r="H79" t="n">
         <v>18881</v>
@@ -2689,7 +2689,7 @@
         <v>2.25</v>
       </c>
       <c r="G80" t="n">
-        <v>1.75822532176971</v>
+        <v>1.75822520256042</v>
       </c>
       <c r="H80" t="n">
         <v>4825</v>
@@ -2718,7 +2718,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G81" t="n">
-        <v>1.75041079521179</v>
+        <v>1.7504106760025</v>
       </c>
       <c r="H81" t="n">
         <v>11995</v>
@@ -2747,7 +2747,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G82" t="n">
-        <v>1.85981166362762</v>
+        <v>1.85981178283691</v>
       </c>
       <c r="H82" t="n">
         <v>17718</v>
@@ -2776,7 +2776,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G83" t="n">
-        <v>1.85981166362762</v>
+        <v>1.85981178283691</v>
       </c>
       <c r="H83" t="n">
         <v>1959</v>
@@ -2805,7 +2805,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G84" t="n">
-        <v>1.85981166362762</v>
+        <v>1.85981178283691</v>
       </c>
       <c r="H84" t="n">
         <v>1535</v>
@@ -2834,7 +2834,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G85" t="n">
-        <v>1.83636844158173</v>
+        <v>1.83636856079102</v>
       </c>
       <c r="H85" t="n">
         <v>1560</v>
@@ -2950,7 +2950,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G89" t="n">
-        <v>1.78948247432709</v>
+        <v>1.78948259353638</v>
       </c>
       <c r="H89" t="n">
         <v>13120</v>
@@ -2979,7 +2979,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G90" t="n">
-        <v>1.70352470874786</v>
+        <v>1.70352482795715</v>
       </c>
       <c r="H90" t="n">
         <v>5489</v>
@@ -3066,7 +3066,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G93" t="n">
-        <v>1.70352470874786</v>
+        <v>1.70352482795715</v>
       </c>
       <c r="H93" t="n">
         <v>5250</v>
@@ -3095,7 +3095,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G94" t="n">
-        <v>1.69571042060852</v>
+        <v>1.69571053981781</v>
       </c>
       <c r="H94" t="n">
         <v>7592</v>
@@ -3269,7 +3269,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G100" t="n">
-        <v>2.0864269733429</v>
+        <v>2.08642745018005</v>
       </c>
       <c r="H100" t="n">
         <v>131201</v>
@@ -3385,7 +3385,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G104" t="n">
-        <v>1.93795478343964</v>
+        <v>1.93795502185822</v>
       </c>
       <c r="H104" t="n">
         <v>28640</v>
@@ -3414,7 +3414,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G105" t="n">
-        <v>1.88325476646423</v>
+        <v>1.88325464725494</v>
       </c>
       <c r="H105" t="n">
         <v>30798</v>
@@ -3472,7 +3472,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G107" t="n">
-        <v>1.74259638786316</v>
+        <v>1.74259662628174</v>
       </c>
       <c r="H107" t="n">
         <v>29505</v>
@@ -3588,7 +3588,7 @@
         <v>2.25</v>
       </c>
       <c r="G111" t="n">
-        <v>1.75822532176971</v>
+        <v>1.75822520256042</v>
       </c>
       <c r="H111" t="n">
         <v>12997</v>
@@ -3617,7 +3617,7 @@
         <v>2.25</v>
       </c>
       <c r="G112" t="n">
-        <v>1.75822532176971</v>
+        <v>1.75822520256042</v>
       </c>
       <c r="H112" t="n">
         <v>6892</v>
@@ -3646,7 +3646,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G113" t="n">
-        <v>1.69571042060852</v>
+        <v>1.69571053981781</v>
       </c>
       <c r="H113" t="n">
         <v>7676</v>
@@ -3762,7 +3762,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G117" t="n">
-        <v>1.57068109512329</v>
+        <v>1.57068121433258</v>
       </c>
       <c r="H117" t="n">
         <v>1475</v>
@@ -3791,7 +3791,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G118" t="n">
-        <v>1.54723823070526</v>
+        <v>1.54723811149597</v>
       </c>
       <c r="H118" t="n">
         <v>2966</v>
@@ -3820,7 +3820,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G119" t="n">
-        <v>1.64101016521454</v>
+        <v>1.64101004600525</v>
       </c>
       <c r="H119" t="n">
         <v>7103</v>
@@ -3965,7 +3965,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G124" t="n">
-        <v>1.46909475326538</v>
+        <v>1.46909487247467</v>
       </c>
       <c r="H124" t="n">
         <v>33327</v>
@@ -4023,7 +4023,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G126" t="n">
-        <v>1.44565188884735</v>
+        <v>1.44565176963806</v>
       </c>
       <c r="H126" t="n">
         <v>4514</v>
@@ -4052,7 +4052,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G127" t="n">
-        <v>1.44565188884735</v>
+        <v>1.44565176963806</v>
       </c>
       <c r="H127" t="n">
         <v>0</v>
@@ -4139,7 +4139,7 @@
         <v>2.25</v>
       </c>
       <c r="G130" t="n">
-        <v>1.75822532176971</v>
+        <v>1.75822520256042</v>
       </c>
       <c r="H130" t="n">
         <v>83797</v>
@@ -4168,7 +4168,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G131" t="n">
-        <v>1.57068109512329</v>
+        <v>1.57068121433258</v>
       </c>
       <c r="H131" t="n">
         <v>61460</v>
@@ -4255,7 +4255,7 @@
         <v>1.75</v>
       </c>
       <c r="G134" t="n">
-        <v>1.36750841140747</v>
+        <v>1.36750853061676</v>
       </c>
       <c r="H134" t="n">
         <v>31791</v>
@@ -4342,7 +4342,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G137" t="n">
-        <v>1.42220878601074</v>
+        <v>1.42220890522003</v>
       </c>
       <c r="H137" t="n">
         <v>10331</v>
@@ -4400,7 +4400,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G139" t="n">
-        <v>1.46128058433533</v>
+        <v>1.46128046512604</v>
       </c>
       <c r="H139" t="n">
         <v>173037</v>
@@ -4458,7 +4458,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G141" t="n">
-        <v>1.47690904140472</v>
+        <v>1.47690916061401</v>
       </c>
       <c r="H141" t="n">
         <v>16351</v>
@@ -4487,7 +4487,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G142" t="n">
-        <v>1.46909475326538</v>
+        <v>1.46909487247467</v>
       </c>
       <c r="H142" t="n">
         <v>23001</v>
@@ -4516,7 +4516,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G143" t="n">
-        <v>1.42220878601074</v>
+        <v>1.42220890522003</v>
       </c>
       <c r="H143" t="n">
         <v>15680</v>
@@ -4632,7 +4632,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G147" t="n">
-        <v>1.44565188884735</v>
+        <v>1.44565176963806</v>
       </c>
       <c r="H147" t="n">
         <v>3897</v>
@@ -4777,7 +4777,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G152" t="n">
-        <v>1.44565188884735</v>
+        <v>1.44565176963806</v>
       </c>
       <c r="H152" t="n">
         <v>3895</v>
@@ -4806,7 +4806,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G153" t="n">
-        <v>1.42220878601074</v>
+        <v>1.42220890522003</v>
       </c>
       <c r="H153" t="n">
         <v>9667</v>
@@ -4835,7 +4835,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G154" t="n">
-        <v>1.46909475326538</v>
+        <v>1.46909487247467</v>
       </c>
       <c r="H154" t="n">
         <v>6731</v>
@@ -4980,7 +4980,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G159" t="n">
-        <v>1.48472356796265</v>
+        <v>1.48472344875336</v>
       </c>
       <c r="H159" t="n">
         <v>1540</v>
@@ -5009,7 +5009,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G160" t="n">
-        <v>1.46128058433533</v>
+        <v>1.46128046512604</v>
       </c>
       <c r="H160" t="n">
         <v>3965</v>
@@ -5038,7 +5038,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G161" t="n">
-        <v>1.47690904140472</v>
+        <v>1.47690916061401</v>
       </c>
       <c r="H161" t="n">
         <v>4796</v>
@@ -5067,7 +5067,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G162" t="n">
-        <v>1.46128058433533</v>
+        <v>1.46128046512604</v>
       </c>
       <c r="H162" t="n">
         <v>1540</v>
@@ -5096,7 +5096,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G163" t="n">
-        <v>1.46909475326538</v>
+        <v>1.46909487247467</v>
       </c>
       <c r="H163" t="n">
         <v>3375</v>
@@ -5125,7 +5125,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G164" t="n">
-        <v>1.44565188884735</v>
+        <v>1.44565176963806</v>
       </c>
       <c r="H164" t="n">
         <v>2612</v>
@@ -5183,7 +5183,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G166" t="n">
-        <v>1.46909475326538</v>
+        <v>1.46909487247467</v>
       </c>
       <c r="H166" t="n">
         <v>3815</v>
@@ -5212,7 +5212,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G167" t="n">
-        <v>1.46909475326538</v>
+        <v>1.46909487247467</v>
       </c>
       <c r="H167" t="n">
         <v>100</v>
@@ -5241,7 +5241,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G168" t="n">
-        <v>1.46909475326538</v>
+        <v>1.46909487247467</v>
       </c>
       <c r="H168" t="n">
         <v>600</v>
@@ -5270,7 +5270,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G169" t="n">
-        <v>1.47690904140472</v>
+        <v>1.47690916061401</v>
       </c>
       <c r="H169" t="n">
         <v>12338</v>
@@ -5299,7 +5299,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G170" t="n">
-        <v>1.48472356796265</v>
+        <v>1.48472344875336</v>
       </c>
       <c r="H170" t="n">
         <v>6190</v>
@@ -5328,7 +5328,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G171" t="n">
-        <v>1.47690904140472</v>
+        <v>1.47690916061401</v>
       </c>
       <c r="H171" t="n">
         <v>7601</v>
@@ -5357,7 +5357,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G172" t="n">
-        <v>1.47690904140472</v>
+        <v>1.47690916061401</v>
       </c>
       <c r="H172" t="n">
         <v>2406</v>
@@ -5386,7 +5386,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G173" t="n">
-        <v>1.46128058433533</v>
+        <v>1.46128046512604</v>
       </c>
       <c r="H173" t="n">
         <v>902</v>
@@ -5415,7 +5415,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G174" t="n">
-        <v>1.54723823070526</v>
+        <v>1.54723811149597</v>
       </c>
       <c r="H174" t="n">
         <v>47810</v>
@@ -5473,7 +5473,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G176" t="n">
-        <v>1.46128058433533</v>
+        <v>1.46128046512604</v>
       </c>
       <c r="H176" t="n">
         <v>13742</v>
@@ -5502,7 +5502,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G177" t="n">
-        <v>1.52379512786865</v>
+        <v>1.52379524707794</v>
       </c>
       <c r="H177" t="n">
         <v>51119</v>
@@ -5560,7 +5560,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G179" t="n">
-        <v>1.48472356796265</v>
+        <v>1.48472344875336</v>
       </c>
       <c r="H179" t="n">
         <v>7463</v>
@@ -5647,7 +5647,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G182" t="n">
-        <v>1.47690904140472</v>
+        <v>1.47690916061401</v>
       </c>
       <c r="H182" t="n">
         <v>1510</v>
@@ -5734,7 +5734,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G185" t="n">
-        <v>1.43783748149872</v>
+        <v>1.43783760070801</v>
       </c>
       <c r="H185" t="n">
         <v>3980</v>
@@ -5763,7 +5763,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G186" t="n">
-        <v>1.44565188884735</v>
+        <v>1.44565176963806</v>
       </c>
       <c r="H186" t="n">
         <v>5051</v>
@@ -5821,7 +5821,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G188" t="n">
-        <v>1.66445314884186</v>
+        <v>1.66445302963257</v>
       </c>
       <c r="H188" t="n">
         <v>64466</v>
@@ -5879,7 +5879,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G190" t="n">
-        <v>1.52379512786865</v>
+        <v>1.52379524707794</v>
       </c>
       <c r="H190" t="n">
         <v>29552</v>
@@ -5908,7 +5908,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G191" t="n">
-        <v>1.52379512786865</v>
+        <v>1.52379524707794</v>
       </c>
       <c r="H191" t="n">
         <v>10729</v>
@@ -5937,7 +5937,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G192" t="n">
-        <v>1.48472356796265</v>
+        <v>1.48472344875336</v>
       </c>
       <c r="H192" t="n">
         <v>13618</v>
@@ -5966,7 +5966,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G193" t="n">
-        <v>1.48472356796265</v>
+        <v>1.48472344875336</v>
       </c>
       <c r="H193" t="n">
         <v>14381</v>
@@ -5995,7 +5995,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G194" t="n">
-        <v>1.48472356796265</v>
+        <v>1.48472344875336</v>
       </c>
       <c r="H194" t="n">
         <v>4773</v>
@@ -6053,7 +6053,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G196" t="n">
-        <v>1.48472356796265</v>
+        <v>1.48472344875336</v>
       </c>
       <c r="H196" t="n">
         <v>4429</v>
@@ -6082,7 +6082,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G197" t="n">
-        <v>1.48472356796265</v>
+        <v>1.48472344875336</v>
       </c>
       <c r="H197" t="n">
         <v>7415</v>
@@ -6111,7 +6111,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G198" t="n">
-        <v>1.46909475326538</v>
+        <v>1.46909487247467</v>
       </c>
       <c r="H198" t="n">
         <v>7517</v>
@@ -6140,7 +6140,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G199" t="n">
-        <v>1.48472356796265</v>
+        <v>1.48472344875336</v>
       </c>
       <c r="H199" t="n">
         <v>11625</v>
@@ -6169,7 +6169,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G200" t="n">
-        <v>1.48472356796265</v>
+        <v>1.48472344875336</v>
       </c>
       <c r="H200" t="n">
         <v>750</v>
@@ -6198,7 +6198,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G201" t="n">
-        <v>1.48472356796265</v>
+        <v>1.48472344875336</v>
       </c>
       <c r="H201" t="n">
         <v>1501</v>
@@ -6227,7 +6227,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G202" t="n">
-        <v>1.47690904140472</v>
+        <v>1.47690916061401</v>
       </c>
       <c r="H202" t="n">
         <v>7610</v>
@@ -6256,7 +6256,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G203" t="n">
-        <v>1.48472356796265</v>
+        <v>1.48472344875336</v>
       </c>
       <c r="H203" t="n">
         <v>5280</v>
@@ -6343,7 +6343,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G206" t="n">
-        <v>1.48472356796265</v>
+        <v>1.48472344875336</v>
       </c>
       <c r="H206" t="n">
         <v>7790</v>
@@ -6372,7 +6372,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G207" t="n">
-        <v>1.48472356796265</v>
+        <v>1.48472344875336</v>
       </c>
       <c r="H207" t="n">
         <v>5950</v>
@@ -6401,7 +6401,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G208" t="n">
-        <v>1.54723823070526</v>
+        <v>1.54723811149597</v>
       </c>
       <c r="H208" t="n">
         <v>30696</v>
@@ -6430,7 +6430,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G209" t="n">
-        <v>1.54723823070526</v>
+        <v>1.54723811149597</v>
       </c>
       <c r="H209" t="n">
         <v>5243</v>
@@ -6459,7 +6459,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G210" t="n">
-        <v>1.52379512786865</v>
+        <v>1.52379524707794</v>
       </c>
       <c r="H210" t="n">
         <v>3092</v>
@@ -6488,7 +6488,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G211" t="n">
-        <v>1.53942382335663</v>
+        <v>1.53942394256592</v>
       </c>
       <c r="H211" t="n">
         <v>2400</v>
@@ -6517,7 +6517,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G212" t="n">
-        <v>1.54723823070526</v>
+        <v>1.54723811149597</v>
       </c>
       <c r="H212" t="n">
         <v>600</v>
@@ -6546,7 +6546,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G213" t="n">
-        <v>1.55505263805389</v>
+        <v>1.5550525188446</v>
       </c>
       <c r="H213" t="n">
         <v>7649</v>
@@ -6575,7 +6575,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G214" t="n">
-        <v>1.57068109512329</v>
+        <v>1.57068121433258</v>
       </c>
       <c r="H214" t="n">
         <v>101975</v>
@@ -6604,7 +6604,7 @@
         <v>2</v>
       </c>
       <c r="G215" t="n">
-        <v>1.56286692619324</v>
+        <v>1.56286680698395</v>
       </c>
       <c r="H215" t="n">
         <v>7270</v>
@@ -6662,7 +6662,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G217" t="n">
-        <v>1.52379512786865</v>
+        <v>1.52379524707794</v>
       </c>
       <c r="H217" t="n">
         <v>9361</v>
@@ -6778,7 +6778,7 @@
         <v>2</v>
       </c>
       <c r="G221" t="n">
-        <v>1.56286692619324</v>
+        <v>1.56286680698395</v>
       </c>
       <c r="H221" t="n">
         <v>25291</v>
@@ -6807,7 +6807,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G222" t="n">
-        <v>1.61756718158722</v>
+        <v>1.61756706237793</v>
       </c>
       <c r="H222" t="n">
         <v>33429</v>
@@ -6865,7 +6865,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G224" t="n">
-        <v>1.55505263805389</v>
+        <v>1.5550525188446</v>
       </c>
       <c r="H224" t="n">
         <v>22722</v>
@@ -6923,7 +6923,7 @@
         <v>2</v>
       </c>
       <c r="G226" t="n">
-        <v>1.56286692619324</v>
+        <v>1.56286680698395</v>
       </c>
       <c r="H226" t="n">
         <v>13694</v>
@@ -6952,7 +6952,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G227" t="n">
-        <v>1.53942382335663</v>
+        <v>1.53942394256592</v>
       </c>
       <c r="H227" t="n">
         <v>13085</v>
@@ -6981,7 +6981,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G228" t="n">
-        <v>1.53942382335663</v>
+        <v>1.53942394256592</v>
       </c>
       <c r="H228" t="n">
         <v>7625</v>
@@ -7010,7 +7010,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G229" t="n">
-        <v>1.46909475326538</v>
+        <v>1.46909487247467</v>
       </c>
       <c r="H229" t="n">
         <v>18045</v>
@@ -7068,7 +7068,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G231" t="n">
-        <v>1.48472356796265</v>
+        <v>1.48472344875336</v>
       </c>
       <c r="H231" t="n">
         <v>2054</v>
@@ -7126,7 +7126,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G233" t="n">
-        <v>1.52379512786865</v>
+        <v>1.52379524707794</v>
       </c>
       <c r="H233" t="n">
         <v>6905</v>
@@ -7213,7 +7213,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G236" t="n">
-        <v>1.46128058433533</v>
+        <v>1.46128046512604</v>
       </c>
       <c r="H236" t="n">
         <v>2358</v>
@@ -7242,7 +7242,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G237" t="n">
-        <v>1.47690904140472</v>
+        <v>1.47690916061401</v>
       </c>
       <c r="H237" t="n">
         <v>3415</v>
@@ -7271,7 +7271,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G238" t="n">
-        <v>1.43783748149872</v>
+        <v>1.43783760070801</v>
       </c>
       <c r="H238" t="n">
         <v>1692</v>
@@ -7300,7 +7300,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G239" t="n">
-        <v>1.46909475326538</v>
+        <v>1.46909487247467</v>
       </c>
       <c r="H239" t="n">
         <v>4746</v>
@@ -7358,7 +7358,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G241" t="n">
-        <v>1.52379512786865</v>
+        <v>1.52379524707794</v>
       </c>
       <c r="H241" t="n">
         <v>5500</v>
@@ -7387,7 +7387,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G242" t="n">
-        <v>1.52379512786865</v>
+        <v>1.52379524707794</v>
       </c>
       <c r="H242" t="n">
         <v>6897</v>
@@ -7706,7 +7706,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G253" t="n">
-        <v>1.47690904140472</v>
+        <v>1.47690916061401</v>
       </c>
       <c r="H253" t="n">
         <v>5630</v>
@@ -7793,7 +7793,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G256" t="n">
-        <v>1.53942382335663</v>
+        <v>1.53942394256592</v>
       </c>
       <c r="H256" t="n">
         <v>12280</v>
@@ -7822,7 +7822,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G257" t="n">
-        <v>1.54723823070526</v>
+        <v>1.54723811149597</v>
       </c>
       <c r="H257" t="n">
         <v>41048</v>
@@ -7851,7 +7851,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G258" t="n">
-        <v>1.83636844158173</v>
+        <v>1.83636856079102</v>
       </c>
       <c r="H258" t="n">
         <v>125566</v>
@@ -7880,7 +7880,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G259" t="n">
-        <v>1.7738538980484</v>
+        <v>1.77385365962982</v>
       </c>
       <c r="H259" t="n">
         <v>144770</v>
@@ -7967,7 +7967,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G262" t="n">
-        <v>1.72696781158447</v>
+        <v>1.72696769237518</v>
       </c>
       <c r="H262" t="n">
         <v>17933</v>
@@ -8112,7 +8112,7 @@
         <v>2.25</v>
       </c>
       <c r="G267" t="n">
-        <v>1.75822532176971</v>
+        <v>1.75822520256042</v>
       </c>
       <c r="H267" t="n">
         <v>48617</v>
@@ -8170,7 +8170,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G269" t="n">
-        <v>1.66445314884186</v>
+        <v>1.66445302963257</v>
       </c>
       <c r="H269" t="n">
         <v>20304</v>
@@ -8199,7 +8199,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G270" t="n">
-        <v>1.64101016521454</v>
+        <v>1.64101004600525</v>
       </c>
       <c r="H270" t="n">
         <v>10671</v>
@@ -8228,7 +8228,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G271" t="n">
-        <v>1.79729676246643</v>
+        <v>1.79729664325714</v>
       </c>
       <c r="H271" t="n">
         <v>110444</v>
@@ -8286,7 +8286,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G273" t="n">
-        <v>2.54747295379639</v>
+        <v>2.54747271537781</v>
       </c>
       <c r="H273" t="n">
         <v>419311</v>
@@ -8315,7 +8315,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G274" t="n">
-        <v>2.781902551651</v>
+        <v>2.78190302848816</v>
       </c>
       <c r="H274" t="n">
         <v>248750</v>
@@ -8373,7 +8373,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G276" t="n">
-        <v>2.54747295379639</v>
+        <v>2.54747271537781</v>
       </c>
       <c r="H276" t="n">
         <v>186391</v>
@@ -8402,7 +8402,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G277" t="n">
-        <v>2.31304311752319</v>
+        <v>2.31304264068604</v>
       </c>
       <c r="H277" t="n">
         <v>178115</v>
@@ -8431,7 +8431,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G278" t="n">
-        <v>2.36774349212646</v>
+        <v>2.36774301528931</v>
       </c>
       <c r="H278" t="n">
         <v>155933</v>
@@ -8460,7 +8460,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G279" t="n">
-        <v>2.32085752487183</v>
+        <v>2.32085728645325</v>
       </c>
       <c r="H279" t="n">
         <v>23589</v>
@@ -8489,7 +8489,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G280" t="n">
-        <v>2.36774349212646</v>
+        <v>2.36774301528931</v>
       </c>
       <c r="H280" t="n">
         <v>42641</v>
@@ -8547,7 +8547,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G282" t="n">
-        <v>2.66468787193298</v>
+        <v>2.66468811035156</v>
       </c>
       <c r="H282" t="n">
         <v>180543</v>
@@ -8576,7 +8576,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G283" t="n">
-        <v>2.48495841026306</v>
+        <v>2.48495817184448</v>
       </c>
       <c r="H283" t="n">
         <v>174485</v>
@@ -8605,7 +8605,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G284" t="n">
-        <v>2.4146294593811</v>
+        <v>2.41462922096252</v>
       </c>
       <c r="H284" t="n">
         <v>141085</v>
@@ -8634,7 +8634,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G285" t="n">
-        <v>2.4146294593811</v>
+        <v>2.41462922096252</v>
       </c>
       <c r="H285" t="n">
         <v>32999</v>
@@ -8692,7 +8692,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G287" t="n">
-        <v>2.5318443775177</v>
+        <v>2.53184413909912</v>
       </c>
       <c r="H287" t="n">
         <v>175902</v>
@@ -8750,7 +8750,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G289" t="n">
-        <v>2.50840163230896</v>
+        <v>2.5084011554718</v>
       </c>
       <c r="H289" t="n">
         <v>75755</v>
@@ -8779,7 +8779,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G290" t="n">
-        <v>2.48495841026306</v>
+        <v>2.48495817184448</v>
       </c>
       <c r="H290" t="n">
         <v>43039</v>
@@ -8808,7 +8808,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G291" t="n">
-        <v>2.45370101928711</v>
+        <v>2.45370078086853</v>
       </c>
       <c r="H291" t="n">
         <v>62585</v>
@@ -8866,7 +8866,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G293" t="n">
-        <v>2.30522871017456</v>
+        <v>2.30522847175598</v>
       </c>
       <c r="H293" t="n">
         <v>63123</v>
@@ -8982,7 +8982,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G297" t="n">
-        <v>2.07861280441284</v>
+        <v>2.07861304283142</v>
       </c>
       <c r="H297" t="n">
         <v>57099</v>
@@ -9040,7 +9040,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G299" t="n">
-        <v>2.18801331520081</v>
+        <v>2.18801355361938</v>
       </c>
       <c r="H299" t="n">
         <v>145545</v>
@@ -9185,7 +9185,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G304" t="n">
-        <v>2.0864269733429</v>
+        <v>2.08642745018005</v>
       </c>
       <c r="H304" t="n">
         <v>19530</v>
@@ -9214,7 +9214,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G305" t="n">
-        <v>2.0864269733429</v>
+        <v>2.08642745018005</v>
       </c>
       <c r="H305" t="n">
         <v>13542</v>
@@ -9301,7 +9301,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G308" t="n">
-        <v>2.18801331520081</v>
+        <v>2.18801355361938</v>
       </c>
       <c r="H308" t="n">
         <v>36108</v>
@@ -9446,7 +9446,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G313" t="n">
-        <v>2.14112758636475</v>
+        <v>2.14112782478333</v>
       </c>
       <c r="H313" t="n">
         <v>5822</v>
@@ -9475,7 +9475,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G314" t="n">
-        <v>2.19582772254944</v>
+        <v>2.19582796096802</v>
       </c>
       <c r="H314" t="n">
         <v>90558</v>
@@ -9533,7 +9533,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G316" t="n">
-        <v>2.31304311752319</v>
+        <v>2.31304264068604</v>
       </c>
       <c r="H316" t="n">
         <v>166647</v>
@@ -9707,7 +9707,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G322" t="n">
-        <v>2.32085752487183</v>
+        <v>2.32085728645325</v>
       </c>
       <c r="H322" t="n">
         <v>120703</v>
@@ -9794,7 +9794,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G325" t="n">
-        <v>2.36774349212646</v>
+        <v>2.36774301528931</v>
       </c>
       <c r="H325" t="n">
         <v>123555</v>
@@ -9852,7 +9852,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G327" t="n">
-        <v>2.31304311752319</v>
+        <v>2.31304264068604</v>
       </c>
       <c r="H327" t="n">
         <v>15378</v>
@@ -9997,7 +9997,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G332" t="n">
-        <v>2.19582772254944</v>
+        <v>2.19582796096802</v>
       </c>
       <c r="H332" t="n">
         <v>23745</v>
@@ -10055,7 +10055,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G334" t="n">
-        <v>2.30522871017456</v>
+        <v>2.30522847175598</v>
       </c>
       <c r="H334" t="n">
         <v>27597</v>
@@ -10113,7 +10113,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G336" t="n">
-        <v>2.36774349212646</v>
+        <v>2.36774301528931</v>
       </c>
       <c r="H336" t="n">
         <v>60523</v>
@@ -10142,7 +10142,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G337" t="n">
-        <v>2.30522871017456</v>
+        <v>2.30522847175598</v>
       </c>
       <c r="H337" t="n">
         <v>70691</v>
@@ -10171,7 +10171,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G338" t="n">
-        <v>2.31304311752319</v>
+        <v>2.31304264068604</v>
       </c>
       <c r="H338" t="n">
         <v>35872</v>
@@ -10345,7 +10345,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G344" t="n">
-        <v>2.50840163230896</v>
+        <v>2.5084011554718</v>
       </c>
       <c r="H344" t="n">
         <v>306118</v>
@@ -10374,7 +10374,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G345" t="n">
-        <v>2.40681505203247</v>
+        <v>2.40681481361389</v>
       </c>
       <c r="H345" t="n">
         <v>126337</v>
@@ -10403,7 +10403,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G346" t="n">
-        <v>2.39900064468384</v>
+        <v>2.39900040626526</v>
       </c>
       <c r="H346" t="n">
         <v>45418</v>
@@ -10432,7 +10432,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G347" t="n">
-        <v>2.4146294593811</v>
+        <v>2.41462922096252</v>
       </c>
       <c r="H347" t="n">
         <v>25889</v>
@@ -10490,7 +10490,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G349" t="n">
-        <v>2.28959989547729</v>
+        <v>2.28960013389587</v>
       </c>
       <c r="H349" t="n">
         <v>69457</v>
@@ -10548,7 +10548,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G351" t="n">
-        <v>2.30522871017456</v>
+        <v>2.30522847175598</v>
       </c>
       <c r="H351" t="n">
         <v>10524</v>
@@ -10664,7 +10664,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G355" t="n">
-        <v>2.30522871017456</v>
+        <v>2.30522847175598</v>
       </c>
       <c r="H355" t="n">
         <v>6469</v>
@@ -10693,7 +10693,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G356" t="n">
-        <v>2.35992908477783</v>
+        <v>2.35992884635925</v>
       </c>
       <c r="H356" t="n">
         <v>37071</v>
@@ -10780,7 +10780,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G359" t="n">
-        <v>2.30522871017456</v>
+        <v>2.30522847175598</v>
       </c>
       <c r="H359" t="n">
         <v>21418</v>
@@ -10809,7 +10809,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G360" t="n">
-        <v>2.31304311752319</v>
+        <v>2.31304264068604</v>
       </c>
       <c r="H360" t="n">
         <v>6391</v>
@@ -10838,7 +10838,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G361" t="n">
-        <v>2.30522871017456</v>
+        <v>2.30522847175598</v>
       </c>
       <c r="H361" t="n">
         <v>12853</v>
@@ -10867,7 +10867,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G362" t="n">
-        <v>2.39900064468384</v>
+        <v>2.39900040626526</v>
       </c>
       <c r="H362" t="n">
         <v>53897</v>
@@ -10925,7 +10925,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G364" t="n">
-        <v>2.28959989547729</v>
+        <v>2.28960013389587</v>
       </c>
       <c r="H364" t="n">
         <v>9629</v>
@@ -10954,7 +10954,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G365" t="n">
-        <v>2.19582772254944</v>
+        <v>2.19582796096802</v>
       </c>
       <c r="H365" t="n">
         <v>66685</v>
@@ -10983,7 +10983,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G366" t="n">
-        <v>2.19582772254944</v>
+        <v>2.19582796096802</v>
       </c>
       <c r="H366" t="n">
         <v>21330</v>
@@ -11012,7 +11012,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G367" t="n">
-        <v>2.22708511352539</v>
+        <v>2.22708535194397</v>
       </c>
       <c r="H367" t="n">
         <v>8955</v>
@@ -11041,7 +11041,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G368" t="n">
-        <v>2.22708511352539</v>
+        <v>2.22708535194397</v>
       </c>
       <c r="H368" t="n">
         <v>5899</v>
@@ -11070,7 +11070,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G369" t="n">
-        <v>2.19582772254944</v>
+        <v>2.19582796096802</v>
       </c>
       <c r="H369" t="n">
         <v>25375</v>
@@ -11099,7 +11099,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G370" t="n">
-        <v>2.19582772254944</v>
+        <v>2.19582796096802</v>
       </c>
       <c r="H370" t="n">
         <v>2922</v>
@@ -11128,7 +11128,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G371" t="n">
-        <v>2.20364212989807</v>
+        <v>2.20364236831665</v>
       </c>
       <c r="H371" t="n">
         <v>6831</v>
@@ -11157,7 +11157,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G372" t="n">
-        <v>2.22708511352539</v>
+        <v>2.22708535194397</v>
       </c>
       <c r="H372" t="n">
         <v>12004</v>
@@ -11186,7 +11186,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G373" t="n">
-        <v>2.20364212989807</v>
+        <v>2.20364236831665</v>
       </c>
       <c r="H373" t="n">
         <v>664</v>
@@ -11244,7 +11244,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G375" t="n">
-        <v>2.20364212989807</v>
+        <v>2.20364236831665</v>
       </c>
       <c r="H375" t="n">
         <v>2860</v>
@@ -11273,7 +11273,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G376" t="n">
-        <v>2.18801331520081</v>
+        <v>2.18801355361938</v>
       </c>
       <c r="H376" t="n">
         <v>4715</v>
@@ -11302,7 +11302,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G377" t="n">
-        <v>2.22708511352539</v>
+        <v>2.22708535194397</v>
       </c>
       <c r="H377" t="n">
         <v>4658</v>
@@ -11360,7 +11360,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G379" t="n">
-        <v>2.22708511352539</v>
+        <v>2.22708535194397</v>
       </c>
       <c r="H379" t="n">
         <v>7003</v>
@@ -11389,7 +11389,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G380" t="n">
-        <v>2.20364212989807</v>
+        <v>2.20364236831665</v>
       </c>
       <c r="H380" t="n">
         <v>5030</v>
@@ -11505,7 +11505,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G384" t="n">
-        <v>2.23489928245544</v>
+        <v>2.2348997592926</v>
       </c>
       <c r="H384" t="n">
         <v>7914</v>
@@ -11534,7 +11534,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G385" t="n">
-        <v>2.23489928245544</v>
+        <v>2.2348997592926</v>
       </c>
       <c r="H385" t="n">
         <v>2794</v>
@@ -11621,7 +11621,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G388" t="n">
-        <v>2.22708511352539</v>
+        <v>2.22708535194397</v>
       </c>
       <c r="H388" t="n">
         <v>100</v>
@@ -11650,7 +11650,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G389" t="n">
-        <v>2.18019890785217</v>
+        <v>2.18019938468933</v>
       </c>
       <c r="H389" t="n">
         <v>20929</v>
@@ -11679,7 +11679,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G390" t="n">
-        <v>2.19582772254944</v>
+        <v>2.19582796096802</v>
       </c>
       <c r="H390" t="n">
         <v>6870</v>
@@ -11708,7 +11708,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G391" t="n">
-        <v>2.23489928245544</v>
+        <v>2.2348997592926</v>
       </c>
       <c r="H391" t="n">
         <v>13073</v>
@@ -11737,7 +11737,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G392" t="n">
-        <v>2.22708511352539</v>
+        <v>2.22708535194397</v>
       </c>
       <c r="H392" t="n">
         <v>4464</v>
@@ -11766,7 +11766,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G393" t="n">
-        <v>2.28959989547729</v>
+        <v>2.28960013389587</v>
       </c>
       <c r="H393" t="n">
         <v>490568</v>
@@ -11795,7 +11795,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G394" t="n">
-        <v>2.25052833557129</v>
+        <v>2.25052809715271</v>
       </c>
       <c r="H394" t="n">
         <v>49928</v>
@@ -11853,7 +11853,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G396" t="n">
-        <v>2.22708511352539</v>
+        <v>2.22708535194397</v>
       </c>
       <c r="H396" t="n">
         <v>21203</v>
@@ -11911,7 +11911,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G398" t="n">
-        <v>2.23489928245544</v>
+        <v>2.2348997592926</v>
       </c>
       <c r="H398" t="n">
         <v>19480</v>
@@ -11969,7 +11969,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G400" t="n">
-        <v>2.25052833557129</v>
+        <v>2.25052809715271</v>
       </c>
       <c r="H400" t="n">
         <v>125043</v>
@@ -12056,7 +12056,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G403" t="n">
-        <v>2.28959989547729</v>
+        <v>2.28960013389587</v>
       </c>
       <c r="H403" t="n">
         <v>3440</v>
@@ -12201,7 +12201,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G408" t="n">
-        <v>2.28959989547729</v>
+        <v>2.28960013389587</v>
       </c>
       <c r="H408" t="n">
         <v>16796</v>
@@ -12230,7 +12230,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G409" t="n">
-        <v>2.25052833557129</v>
+        <v>2.25052809715271</v>
       </c>
       <c r="H409" t="n">
         <v>3826</v>
@@ -12317,7 +12317,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G412" t="n">
-        <v>2.25052833557129</v>
+        <v>2.25052809715271</v>
       </c>
       <c r="H412" t="n">
         <v>13597</v>
@@ -12375,7 +12375,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G414" t="n">
-        <v>2.22708511352539</v>
+        <v>2.22708535194397</v>
       </c>
       <c r="H414" t="n">
         <v>16306</v>
@@ -12404,7 +12404,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G415" t="n">
-        <v>2.22708511352539</v>
+        <v>2.22708535194397</v>
       </c>
       <c r="H415" t="n">
         <v>4789</v>
@@ -12433,7 +12433,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G416" t="n">
-        <v>2.25052833557129</v>
+        <v>2.25052809715271</v>
       </c>
       <c r="H416" t="n">
         <v>4039</v>
@@ -12520,7 +12520,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G419" t="n">
-        <v>2.25052833557129</v>
+        <v>2.25052809715271</v>
       </c>
       <c r="H419" t="n">
         <v>6100</v>
@@ -12578,7 +12578,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G421" t="n">
-        <v>2.25052833557129</v>
+        <v>2.25052809715271</v>
       </c>
       <c r="H421" t="n">
         <v>5308</v>
@@ -12607,7 +12607,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G422" t="n">
-        <v>2.25052833557129</v>
+        <v>2.25052809715271</v>
       </c>
       <c r="H422" t="n">
         <v>13271</v>
@@ -12723,7 +12723,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G426" t="n">
-        <v>2.28959989547729</v>
+        <v>2.28960013389587</v>
       </c>
       <c r="H426" t="n">
         <v>16488</v>
@@ -12752,7 +12752,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G427" t="n">
-        <v>2.28959989547729</v>
+        <v>2.28960013389587</v>
       </c>
       <c r="H427" t="n">
         <v>33109</v>
@@ -12897,7 +12897,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G432" t="n">
-        <v>2.28959989547729</v>
+        <v>2.28960013389587</v>
       </c>
       <c r="H432" t="n">
         <v>7635</v>
@@ -12926,7 +12926,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G433" t="n">
-        <v>2.28959989547729</v>
+        <v>2.28960013389587</v>
       </c>
       <c r="H433" t="n">
         <v>12703</v>
@@ -12955,7 +12955,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G434" t="n">
-        <v>2.30522871017456</v>
+        <v>2.30522847175598</v>
       </c>
       <c r="H434" t="n">
         <v>3559</v>
@@ -12984,7 +12984,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G435" t="n">
-        <v>2.28959989547729</v>
+        <v>2.28960013389587</v>
       </c>
       <c r="H435" t="n">
         <v>6499</v>
@@ -13100,7 +13100,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G439" t="n">
-        <v>2.30522871017456</v>
+        <v>2.30522847175598</v>
       </c>
       <c r="H439" t="n">
         <v>7059</v>
@@ -13216,7 +13216,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G443" t="n">
-        <v>2.35992908477783</v>
+        <v>2.35992884635925</v>
       </c>
       <c r="H443" t="n">
         <v>25888</v>
@@ -13245,7 +13245,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G444" t="n">
-        <v>2.42244362831116</v>
+        <v>2.42244338989258</v>
       </c>
       <c r="H444" t="n">
         <v>158865</v>
@@ -13274,7 +13274,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G445" t="n">
-        <v>2.32085752487183</v>
+        <v>2.32085728645325</v>
       </c>
       <c r="H445" t="n">
         <v>109510</v>
@@ -13332,7 +13332,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G447" t="n">
-        <v>2.28959989547729</v>
+        <v>2.28960013389587</v>
       </c>
       <c r="H447" t="n">
         <v>18719</v>
@@ -13390,7 +13390,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G449" t="n">
-        <v>2.31304311752319</v>
+        <v>2.31304264068604</v>
       </c>
       <c r="H449" t="n">
         <v>8698</v>
@@ -13419,7 +13419,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G450" t="n">
-        <v>2.28959989547729</v>
+        <v>2.28960013389587</v>
       </c>
       <c r="H450" t="n">
         <v>5156</v>
@@ -13564,7 +13564,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G455" t="n">
-        <v>2.25052833557129</v>
+        <v>2.25052809715271</v>
       </c>
       <c r="H455" t="n">
         <v>4720</v>
@@ -13854,7 +13854,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G465" t="n">
-        <v>2.25052833557129</v>
+        <v>2.25052809715271</v>
       </c>
       <c r="H465" t="n">
         <v>7854</v>
@@ -13912,7 +13912,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G467" t="n">
-        <v>2.25052833557129</v>
+        <v>2.25052809715271</v>
       </c>
       <c r="H467" t="n">
         <v>6429</v>
@@ -13999,7 +13999,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G470" t="n">
-        <v>2.25052833557129</v>
+        <v>2.25052809715271</v>
       </c>
       <c r="H470" t="n">
         <v>4682</v>
@@ -14231,7 +14231,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G478" t="n">
-        <v>2.25052833557129</v>
+        <v>2.25052809715271</v>
       </c>
       <c r="H478" t="n">
         <v>13054</v>
@@ -14289,7 +14289,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G480" t="n">
-        <v>2.18801331520081</v>
+        <v>2.18801355361938</v>
       </c>
       <c r="H480" t="n">
         <v>127127</v>
@@ -14347,7 +14347,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G482" t="n">
-        <v>2.0551700592041</v>
+        <v>2.05517029762268</v>
       </c>
       <c r="H482" t="n">
         <v>33954</v>
@@ -14376,7 +14376,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G483" t="n">
-        <v>2.0551700592041</v>
+        <v>2.05517029762268</v>
       </c>
       <c r="H483" t="n">
         <v>1310</v>
@@ -14405,7 +14405,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G484" t="n">
-        <v>2.06298422813416</v>
+        <v>2.06298446655273</v>
       </c>
       <c r="H484" t="n">
         <v>4500</v>
@@ -14434,7 +14434,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G485" t="n">
-        <v>2.04735541343689</v>
+        <v>2.04735517501831</v>
       </c>
       <c r="H485" t="n">
         <v>5465</v>
@@ -14463,7 +14463,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G486" t="n">
-        <v>2.07079863548279</v>
+        <v>2.07079839706421</v>
       </c>
       <c r="H486" t="n">
         <v>9534</v>
@@ -14492,7 +14492,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G487" t="n">
-        <v>2.0551700592041</v>
+        <v>2.05517029762268</v>
       </c>
       <c r="H487" t="n">
         <v>7884</v>
@@ -14521,7 +14521,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G488" t="n">
-        <v>2.09424138069153</v>
+        <v>2.09424161911011</v>
       </c>
       <c r="H488" t="n">
         <v>6344</v>
@@ -14579,7 +14579,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G490" t="n">
-        <v>2.03954100608826</v>
+        <v>2.03954124450684</v>
       </c>
       <c r="H490" t="n">
         <v>11032</v>
@@ -14608,7 +14608,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G491" t="n">
-        <v>2.0551700592041</v>
+        <v>2.05517029762268</v>
       </c>
       <c r="H491" t="n">
         <v>4461</v>
@@ -14637,7 +14637,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G492" t="n">
-        <v>1.99265480041504</v>
+        <v>1.99265515804291</v>
       </c>
       <c r="H492" t="n">
         <v>39507</v>
@@ -14695,7 +14695,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G494" t="n">
-        <v>2.02391266822815</v>
+        <v>2.02391242980957</v>
       </c>
       <c r="H494" t="n">
         <v>4454</v>
@@ -14724,7 +14724,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G495" t="n">
-        <v>2.02391266822815</v>
+        <v>2.02391242980957</v>
       </c>
       <c r="H495" t="n">
         <v>1453</v>
@@ -14782,7 +14782,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G497" t="n">
-        <v>1.99265480041504</v>
+        <v>1.99265515804291</v>
       </c>
       <c r="H497" t="n">
         <v>2512</v>
@@ -14985,7 +14985,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G504" t="n">
-        <v>1.99265480041504</v>
+        <v>1.99265515804291</v>
       </c>
       <c r="H504" t="n">
         <v>3080</v>
@@ -15391,7 +15391,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G518" t="n">
-        <v>2.09424138069153</v>
+        <v>2.09424161911011</v>
       </c>
       <c r="H518" t="n">
         <v>112388</v>
@@ -15420,7 +15420,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G519" t="n">
-        <v>2.0864269733429</v>
+        <v>2.08642745018005</v>
       </c>
       <c r="H519" t="n">
         <v>11274</v>
@@ -15449,7 +15449,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G520" t="n">
-        <v>2.07861280441284</v>
+        <v>2.07861304283142</v>
       </c>
       <c r="H520" t="n">
         <v>10226</v>
@@ -15478,7 +15478,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G521" t="n">
-        <v>2.06298422813416</v>
+        <v>2.06298446655273</v>
       </c>
       <c r="H521" t="n">
         <v>14270</v>
@@ -15507,7 +15507,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G522" t="n">
-        <v>2.0551700592041</v>
+        <v>2.05517029762268</v>
       </c>
       <c r="H522" t="n">
         <v>2500</v>
@@ -15536,7 +15536,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G523" t="n">
-        <v>2.0864269733429</v>
+        <v>2.08642745018005</v>
       </c>
       <c r="H523" t="n">
         <v>9758</v>
@@ -15594,7 +15594,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G525" t="n">
-        <v>2.0551700592041</v>
+        <v>2.05517029762268</v>
       </c>
       <c r="H525" t="n">
         <v>14380</v>
@@ -15623,7 +15623,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G526" t="n">
-        <v>2.04735541343689</v>
+        <v>2.04735517501831</v>
       </c>
       <c r="H526" t="n">
         <v>13140</v>
@@ -15652,7 +15652,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G527" t="n">
-        <v>2.04735541343689</v>
+        <v>2.04735517501831</v>
       </c>
       <c r="H527" t="n">
         <v>1930</v>
@@ -15681,7 +15681,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G528" t="n">
-        <v>2.0551700592041</v>
+        <v>2.05517029762268</v>
       </c>
       <c r="H528" t="n">
         <v>4970</v>
@@ -15710,7 +15710,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G529" t="n">
-        <v>2.04735541343689</v>
+        <v>2.04735517501831</v>
       </c>
       <c r="H529" t="n">
         <v>6486</v>
@@ -15739,7 +15739,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G530" t="n">
-        <v>2.0864269733429</v>
+        <v>2.08642745018005</v>
       </c>
       <c r="H530" t="n">
         <v>11459</v>
@@ -15768,7 +15768,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G531" t="n">
-        <v>2.07861280441284</v>
+        <v>2.07861304283142</v>
       </c>
       <c r="H531" t="n">
         <v>7675</v>
@@ -15797,7 +15797,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G532" t="n">
-        <v>2.03954100608826</v>
+        <v>2.03954124450684</v>
       </c>
       <c r="H532" t="n">
         <v>7408</v>
@@ -15826,7 +15826,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G533" t="n">
-        <v>2.03954100608826</v>
+        <v>2.03954124450684</v>
       </c>
       <c r="H533" t="n">
         <v>1950</v>
@@ -16000,7 +16000,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G539" t="n">
-        <v>1.98484075069427</v>
+        <v>1.98484086990356</v>
       </c>
       <c r="H539" t="n">
         <v>4051</v>
@@ -16029,7 +16029,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G540" t="n">
-        <v>1.97702634334564</v>
+        <v>1.97702646255493</v>
       </c>
       <c r="H540" t="n">
         <v>1849</v>
@@ -16087,7 +16087,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G542" t="n">
-        <v>1.891068816185</v>
+        <v>1.89106869697571</v>
       </c>
       <c r="H542" t="n">
         <v>4966</v>
@@ -16116,7 +16116,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G543" t="n">
-        <v>1.92232620716095</v>
+        <v>1.92232632637024</v>
       </c>
       <c r="H543" t="n">
         <v>2000</v>
@@ -16145,7 +16145,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G544" t="n">
-        <v>1.891068816185</v>
+        <v>1.89106869697571</v>
       </c>
       <c r="H544" t="n">
         <v>1977</v>
@@ -16174,7 +16174,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G545" t="n">
-        <v>1.98484075069427</v>
+        <v>1.98484086990356</v>
       </c>
       <c r="H545" t="n">
         <v>7157</v>
@@ -16232,7 +16232,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G547" t="n">
-        <v>1.96921193599701</v>
+        <v>1.96921217441559</v>
       </c>
       <c r="H547" t="n">
         <v>4409</v>
@@ -16261,7 +16261,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G548" t="n">
-        <v>1.96921193599701</v>
+        <v>1.96921217441559</v>
       </c>
       <c r="H548" t="n">
         <v>2935</v>
@@ -16290,7 +16290,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G549" t="n">
-        <v>1.93795478343964</v>
+        <v>1.93795502185822</v>
       </c>
       <c r="H549" t="n">
         <v>78</v>
@@ -16319,7 +16319,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G550" t="n">
-        <v>2.04735541343689</v>
+        <v>2.04735517501831</v>
       </c>
       <c r="H550" t="n">
         <v>12782</v>
@@ -16377,7 +16377,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G552" t="n">
-        <v>2.02391266822815</v>
+        <v>2.02391242980957</v>
       </c>
       <c r="H552" t="n">
         <v>3342</v>
@@ -16464,7 +16464,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G555" t="n">
-        <v>1.87544012069702</v>
+        <v>1.87544047832489</v>
       </c>
       <c r="H555" t="n">
         <v>11021</v>
@@ -16522,7 +16522,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G557" t="n">
-        <v>1.87544012069702</v>
+        <v>1.87544047832489</v>
       </c>
       <c r="H557" t="n">
         <v>9292</v>
@@ -16551,7 +16551,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G558" t="n">
-        <v>1.88325476646423</v>
+        <v>1.88325464725494</v>
       </c>
       <c r="H558" t="n">
         <v>7999</v>
@@ -16580,7 +16580,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G559" t="n">
-        <v>1.87544012069702</v>
+        <v>1.87544047832489</v>
       </c>
       <c r="H559" t="n">
         <v>2957</v>
@@ -16609,7 +16609,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G560" t="n">
-        <v>1.89888322353363</v>
+        <v>1.89888334274292</v>
       </c>
       <c r="H560" t="n">
         <v>4094</v>
@@ -16638,7 +16638,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G561" t="n">
-        <v>1.89888322353363</v>
+        <v>1.89888334274292</v>
       </c>
       <c r="H561" t="n">
         <v>2899</v>
@@ -16667,7 +16667,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G562" t="n">
-        <v>1.88325476646423</v>
+        <v>1.88325464725494</v>
       </c>
       <c r="H562" t="n">
         <v>12511</v>
@@ -16696,7 +16696,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G563" t="n">
-        <v>1.90669775009155</v>
+        <v>1.90669763088226</v>
       </c>
       <c r="H563" t="n">
         <v>3670</v>
@@ -16725,7 +16725,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G564" t="n">
-        <v>1.90669775009155</v>
+        <v>1.90669763088226</v>
       </c>
       <c r="H564" t="n">
         <v>290</v>
@@ -16754,7 +16754,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G565" t="n">
-        <v>1.91451179981232</v>
+        <v>1.91451215744019</v>
       </c>
       <c r="H565" t="n">
         <v>930</v>
@@ -16783,7 +16783,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G566" t="n">
-        <v>1.87544012069702</v>
+        <v>1.87544047832489</v>
       </c>
       <c r="H566" t="n">
         <v>3211</v>
@@ -16812,7 +16812,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G567" t="n">
-        <v>1.87544012069702</v>
+        <v>1.87544047832489</v>
       </c>
       <c r="H567" t="n">
         <v>2215</v>
@@ -16870,7 +16870,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G569" t="n">
-        <v>1.84418272972107</v>
+        <v>1.84418261051178</v>
       </c>
       <c r="H569" t="n">
         <v>2584</v>
@@ -16899,7 +16899,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G570" t="n">
-        <v>1.92232620716095</v>
+        <v>1.92232632637024</v>
       </c>
       <c r="H570" t="n">
         <v>34637</v>
@@ -17015,7 +17015,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G574" t="n">
-        <v>2.03954100608826</v>
+        <v>2.03954124450684</v>
       </c>
       <c r="H574" t="n">
         <v>1270</v>
@@ -17102,7 +17102,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G577" t="n">
-        <v>2.06298422813416</v>
+        <v>2.06298446655273</v>
       </c>
       <c r="H577" t="n">
         <v>25388</v>
@@ -17131,7 +17131,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G578" t="n">
-        <v>2.0551700592041</v>
+        <v>2.05517029762268</v>
       </c>
       <c r="H578" t="n">
         <v>3757</v>
@@ -17160,7 +17160,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G579" t="n">
-        <v>2.03954100608826</v>
+        <v>2.03954124450684</v>
       </c>
       <c r="H579" t="n">
         <v>4138</v>
@@ -17189,7 +17189,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G580" t="n">
-        <v>2.04735541343689</v>
+        <v>2.04735517501831</v>
       </c>
       <c r="H580" t="n">
         <v>2057</v>
@@ -17247,7 +17247,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G582" t="n">
-        <v>1.98484075069427</v>
+        <v>1.98484086990356</v>
       </c>
       <c r="H582" t="n">
         <v>5772</v>
@@ -17276,7 +17276,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G583" t="n">
-        <v>1.98484075069427</v>
+        <v>1.98484086990356</v>
       </c>
       <c r="H583" t="n">
         <v>817</v>
@@ -17305,7 +17305,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G584" t="n">
-        <v>1.96139788627625</v>
+        <v>1.96139800548553</v>
       </c>
       <c r="H584" t="n">
         <v>534</v>
@@ -17334,7 +17334,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G585" t="n">
-        <v>1.97702634334564</v>
+        <v>1.97702646255493</v>
       </c>
       <c r="H585" t="n">
         <v>2222</v>
@@ -17363,7 +17363,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G586" t="n">
-        <v>2.02391266822815</v>
+        <v>2.02391242980957</v>
       </c>
       <c r="H586" t="n">
         <v>4748</v>
@@ -17421,7 +17421,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G588" t="n">
-        <v>1.96921193599701</v>
+        <v>1.96921217441559</v>
       </c>
       <c r="H588" t="n">
         <v>1223</v>
@@ -17450,7 +17450,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G589" t="n">
-        <v>1.97702634334564</v>
+        <v>1.97702646255493</v>
       </c>
       <c r="H589" t="n">
         <v>1767</v>
@@ -17508,7 +17508,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G591" t="n">
-        <v>1.93795478343964</v>
+        <v>1.93795502185822</v>
       </c>
       <c r="H591" t="n">
         <v>11871</v>
@@ -17537,7 +17537,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G592" t="n">
-        <v>1.96921193599701</v>
+        <v>1.96921217441559</v>
       </c>
       <c r="H592" t="n">
         <v>100</v>
@@ -17566,7 +17566,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G593" t="n">
-        <v>1.89888322353363</v>
+        <v>1.89888334274292</v>
       </c>
       <c r="H593" t="n">
         <v>219</v>
@@ -17595,7 +17595,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G594" t="n">
-        <v>1.96921193599701</v>
+        <v>1.96921217441559</v>
       </c>
       <c r="H594" t="n">
         <v>28</v>
@@ -17653,7 +17653,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G596" t="n">
-        <v>1.93014061450958</v>
+        <v>1.930140376091</v>
       </c>
       <c r="H596" t="n">
         <v>321</v>
@@ -17682,7 +17682,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G597" t="n">
-        <v>1.93014061450958</v>
+        <v>1.930140376091</v>
       </c>
       <c r="H597" t="n">
         <v>1300</v>
@@ -17711,7 +17711,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G598" t="n">
-        <v>1.93795478343964</v>
+        <v>1.93795502185822</v>
       </c>
       <c r="H598" t="n">
         <v>301</v>
@@ -17740,7 +17740,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G599" t="n">
-        <v>1.91451179981232</v>
+        <v>1.91451215744019</v>
       </c>
       <c r="H599" t="n">
         <v>16585</v>
@@ -17769,7 +17769,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G600" t="n">
-        <v>1.94576907157898</v>
+        <v>1.94576930999756</v>
       </c>
       <c r="H600" t="n">
         <v>1103</v>
@@ -17798,7 +17798,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G601" t="n">
-        <v>1.94576907157898</v>
+        <v>1.94576930999756</v>
       </c>
       <c r="H601" t="n">
         <v>200</v>
@@ -17827,7 +17827,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G602" t="n">
-        <v>1.891068816185</v>
+        <v>1.89106869697571</v>
       </c>
       <c r="H602" t="n">
         <v>3186</v>
@@ -17856,7 +17856,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G603" t="n">
-        <v>1.94576907157898</v>
+        <v>1.94576930999756</v>
       </c>
       <c r="H603" t="n">
         <v>7397</v>
@@ -17885,7 +17885,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G604" t="n">
-        <v>1.93795478343964</v>
+        <v>1.93795502185822</v>
       </c>
       <c r="H604" t="n">
         <v>100</v>
@@ -17914,7 +17914,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G605" t="n">
-        <v>1.891068816185</v>
+        <v>1.89106869697571</v>
       </c>
       <c r="H605" t="n">
         <v>12977</v>
@@ -17943,7 +17943,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G606" t="n">
-        <v>1.87544012069702</v>
+        <v>1.87544047832489</v>
       </c>
       <c r="H606" t="n">
         <v>311</v>
@@ -17972,7 +17972,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G607" t="n">
-        <v>1.87544012069702</v>
+        <v>1.87544047832489</v>
       </c>
       <c r="H607" t="n">
         <v>1604</v>
@@ -18001,7 +18001,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G608" t="n">
-        <v>1.87544012069702</v>
+        <v>1.87544047832489</v>
       </c>
       <c r="H608" t="n">
         <v>5380</v>
@@ -18059,7 +18059,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G610" t="n">
-        <v>1.84418272972107</v>
+        <v>1.84418261051178</v>
       </c>
       <c r="H610" t="n">
         <v>4036</v>
@@ -18088,7 +18088,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G611" t="n">
-        <v>1.84418272972107</v>
+        <v>1.84418261051178</v>
       </c>
       <c r="H611" t="n">
         <v>937</v>
@@ -18117,7 +18117,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G612" t="n">
-        <v>1.85981166362762</v>
+        <v>1.85981178283691</v>
       </c>
       <c r="H612" t="n">
         <v>992</v>
@@ -18175,7 +18175,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G614" t="n">
-        <v>1.79729676246643</v>
+        <v>1.79729664325714</v>
       </c>
       <c r="H614" t="n">
         <v>10850</v>
@@ -18204,7 +18204,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G615" t="n">
-        <v>1.88325476646423</v>
+        <v>1.88325464725494</v>
       </c>
       <c r="H615" t="n">
         <v>100</v>
@@ -18233,7 +18233,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G616" t="n">
-        <v>1.88325476646423</v>
+        <v>1.88325464725494</v>
       </c>
       <c r="H616" t="n">
         <v>0</v>
@@ -18262,7 +18262,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G617" t="n">
-        <v>1.87544012069702</v>
+        <v>1.87544047832489</v>
       </c>
       <c r="H617" t="n">
         <v>1865</v>
@@ -18291,7 +18291,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G618" t="n">
-        <v>1.84418272972107</v>
+        <v>1.84418261051178</v>
       </c>
       <c r="H618" t="n">
         <v>2111</v>
@@ -18320,7 +18320,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G619" t="n">
-        <v>1.891068816185</v>
+        <v>1.89106869697571</v>
       </c>
       <c r="H619" t="n">
         <v>4395</v>
@@ -18349,7 +18349,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G620" t="n">
-        <v>1.82073986530304</v>
+        <v>1.82073962688446</v>
       </c>
       <c r="H620" t="n">
         <v>2510</v>
@@ -18407,7 +18407,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G622" t="n">
-        <v>1.84418272972107</v>
+        <v>1.84418261051178</v>
       </c>
       <c r="H622" t="n">
         <v>1654</v>
@@ -18436,7 +18436,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G623" t="n">
-        <v>1.92232620716095</v>
+        <v>1.92232632637024</v>
       </c>
       <c r="H623" t="n">
         <v>678</v>
@@ -18494,7 +18494,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G625" t="n">
-        <v>1.91451179981232</v>
+        <v>1.91451215744019</v>
       </c>
       <c r="H625" t="n">
         <v>1010</v>
@@ -18552,7 +18552,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G627" t="n">
-        <v>1.82073986530304</v>
+        <v>1.82073962688446</v>
       </c>
       <c r="H627" t="n">
         <v>5337</v>
@@ -18610,7 +18610,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G629" t="n">
-        <v>1.83636844158173</v>
+        <v>1.83636856079102</v>
       </c>
       <c r="H629" t="n">
         <v>2700</v>
@@ -18639,7 +18639,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G630" t="n">
-        <v>1.84418272972107</v>
+        <v>1.84418261051178</v>
       </c>
       <c r="H630" t="n">
         <v>470</v>
@@ -18668,7 +18668,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G631" t="n">
-        <v>1.79729676246643</v>
+        <v>1.79729664325714</v>
       </c>
       <c r="H631" t="n">
         <v>1387</v>
@@ -18755,7 +18755,7 @@
         <v>2.25</v>
       </c>
       <c r="G634" t="n">
-        <v>1.75822532176971</v>
+        <v>1.75822520256042</v>
       </c>
       <c r="H634" t="n">
         <v>3308</v>
@@ -18784,7 +18784,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G635" t="n">
-        <v>1.72696781158447</v>
+        <v>1.72696769237518</v>
       </c>
       <c r="H635" t="n">
         <v>2340</v>
@@ -18813,7 +18813,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G636" t="n">
-        <v>1.75041079521179</v>
+        <v>1.7504106760025</v>
       </c>
       <c r="H636" t="n">
         <v>116</v>
@@ -18871,7 +18871,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G638" t="n">
-        <v>1.82073986530304</v>
+        <v>1.82073962688446</v>
       </c>
       <c r="H638" t="n">
         <v>1300</v>
@@ -18987,7 +18987,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G642" t="n">
-        <v>1.75041079521179</v>
+        <v>1.7504106760025</v>
       </c>
       <c r="H642" t="n">
         <v>870</v>
@@ -19045,7 +19045,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G644" t="n">
-        <v>1.74259638786316</v>
+        <v>1.74259662628174</v>
       </c>
       <c r="H644" t="n">
         <v>1986</v>
@@ -19190,7 +19190,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G649" t="n">
-        <v>1.70352470874786</v>
+        <v>1.70352482795715</v>
       </c>
       <c r="H649" t="n">
         <v>1910</v>
@@ -19306,7 +19306,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G653" t="n">
-        <v>1.66445314884186</v>
+        <v>1.66445302963257</v>
       </c>
       <c r="H653" t="n">
         <v>1170</v>
@@ -19335,7 +19335,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G654" t="n">
-        <v>1.66445314884186</v>
+        <v>1.66445302963257</v>
       </c>
       <c r="H654" t="n">
         <v>891</v>
@@ -19364,7 +19364,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G655" t="n">
-        <v>1.61756718158722</v>
+        <v>1.61756706237793</v>
       </c>
       <c r="H655" t="n">
         <v>2957</v>
@@ -19393,7 +19393,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G656" t="n">
-        <v>1.61756718158722</v>
+        <v>1.61756706237793</v>
       </c>
       <c r="H656" t="n">
         <v>4076</v>
@@ -19422,7 +19422,7 @@
         <v>2</v>
       </c>
       <c r="G657" t="n">
-        <v>1.56286692619324</v>
+        <v>1.56286680698395</v>
       </c>
       <c r="H657" t="n">
         <v>7242</v>
@@ -19509,7 +19509,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G660" t="n">
-        <v>1.64101016521454</v>
+        <v>1.64101004600525</v>
       </c>
       <c r="H660" t="n">
         <v>2150</v>
@@ -19596,7 +19596,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G663" t="n">
-        <v>1.48472356796265</v>
+        <v>1.48472344875336</v>
       </c>
       <c r="H663" t="n">
         <v>210</v>
@@ -19625,7 +19625,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G664" t="n">
-        <v>1.55505263805389</v>
+        <v>1.5550525188446</v>
       </c>
       <c r="H664" t="n">
         <v>7681</v>
@@ -19654,7 +19654,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G665" t="n">
-        <v>2.06298422813416</v>
+        <v>2.06298446655273</v>
       </c>
       <c r="H665" t="n">
         <v>130384</v>
@@ -19683,7 +19683,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G666" t="n">
-        <v>1.92232620716095</v>
+        <v>1.92232632637024</v>
       </c>
       <c r="H666" t="n">
         <v>446846</v>
@@ -19741,7 +19741,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G668" t="n">
-        <v>1.88325476646423</v>
+        <v>1.88325464725494</v>
       </c>
       <c r="H668" t="n">
         <v>20273</v>
@@ -19770,7 +19770,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G669" t="n">
-        <v>1.92232620716095</v>
+        <v>1.92232632637024</v>
       </c>
       <c r="H669" t="n">
         <v>32286</v>
@@ -19799,7 +19799,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G670" t="n">
-        <v>1.99265480041504</v>
+        <v>1.99265515804291</v>
       </c>
       <c r="H670" t="n">
         <v>78330</v>
@@ -19828,7 +19828,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G671" t="n">
-        <v>1.93014061450958</v>
+        <v>1.930140376091</v>
       </c>
       <c r="H671" t="n">
         <v>41175</v>
@@ -19857,7 +19857,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G672" t="n">
-        <v>1.89888322353363</v>
+        <v>1.89888334274292</v>
       </c>
       <c r="H672" t="n">
         <v>10847</v>
@@ -19886,7 +19886,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G673" t="n">
-        <v>1.92232620716095</v>
+        <v>1.92232632637024</v>
       </c>
       <c r="H673" t="n">
         <v>37391</v>
@@ -19915,7 +19915,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G674" t="n">
-        <v>1.97702634334564</v>
+        <v>1.97702646255493</v>
       </c>
       <c r="H674" t="n">
         <v>10462</v>
@@ -19944,7 +19944,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G675" t="n">
-        <v>1.891068816185</v>
+        <v>1.89106869697571</v>
       </c>
       <c r="H675" t="n">
         <v>16914</v>
@@ -19973,7 +19973,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G676" t="n">
-        <v>1.91451179981232</v>
+        <v>1.91451215744019</v>
       </c>
       <c r="H676" t="n">
         <v>18044</v>
@@ -20002,7 +20002,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G677" t="n">
-        <v>1.88325476646423</v>
+        <v>1.88325464725494</v>
       </c>
       <c r="H677" t="n">
         <v>24276</v>
@@ -20060,7 +20060,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G679" t="n">
-        <v>1.85981166362762</v>
+        <v>1.85981178283691</v>
       </c>
       <c r="H679" t="n">
         <v>1203</v>
@@ -20147,7 +20147,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G682" t="n">
-        <v>1.70352470874786</v>
+        <v>1.70352482795715</v>
       </c>
       <c r="H682" t="n">
         <v>21460</v>
@@ -20176,7 +20176,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G683" t="n">
-        <v>1.91451179981232</v>
+        <v>1.91451215744019</v>
       </c>
       <c r="H683" t="n">
         <v>82840</v>
@@ -20205,7 +20205,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G684" t="n">
-        <v>1.82073986530304</v>
+        <v>1.82073962688446</v>
       </c>
       <c r="H684" t="n">
         <v>79297</v>
@@ -20379,7 +20379,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G690" t="n">
-        <v>1.75041079521179</v>
+        <v>1.7504106760025</v>
       </c>
       <c r="H690" t="n">
         <v>2392</v>
@@ -20437,7 +20437,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G692" t="n">
-        <v>1.70352470874786</v>
+        <v>1.70352482795715</v>
       </c>
       <c r="H692" t="n">
         <v>29415</v>
@@ -20466,7 +20466,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G693" t="n">
-        <v>1.66445314884186</v>
+        <v>1.66445302963257</v>
       </c>
       <c r="H693" t="n">
         <v>31190</v>
@@ -20495,7 +20495,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G694" t="n">
-        <v>1.66445314884186</v>
+        <v>1.66445302963257</v>
       </c>
       <c r="H694" t="n">
         <v>9856</v>
@@ -20640,7 +20640,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G699" t="n">
-        <v>1.74259638786316</v>
+        <v>1.74259662628174</v>
       </c>
       <c r="H699" t="n">
         <v>125437</v>
@@ -20698,7 +20698,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G701" t="n">
-        <v>1.70352470874786</v>
+        <v>1.70352482795715</v>
       </c>
       <c r="H701" t="n">
         <v>20038</v>
@@ -20727,7 +20727,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G702" t="n">
-        <v>1.69571042060852</v>
+        <v>1.69571053981781</v>
       </c>
       <c r="H702" t="n">
         <v>42863</v>
@@ -20814,7 +20814,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G705" t="n">
-        <v>1.69571042060852</v>
+        <v>1.69571053981781</v>
       </c>
       <c r="H705" t="n">
         <v>9685</v>
@@ -20901,7 +20901,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G708" t="n">
-        <v>1.64101016521454</v>
+        <v>1.64101004600525</v>
       </c>
       <c r="H708" t="n">
         <v>1684</v>
@@ -21075,7 +21075,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G714" t="n">
-        <v>1.64101016521454</v>
+        <v>1.64101004600525</v>
       </c>
       <c r="H714" t="n">
         <v>318</v>
@@ -21104,7 +21104,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G715" t="n">
-        <v>1.61756718158722</v>
+        <v>1.61756706237793</v>
       </c>
       <c r="H715" t="n">
         <v>5893</v>
@@ -21133,7 +21133,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G716" t="n">
-        <v>1.61756718158722</v>
+        <v>1.61756706237793</v>
       </c>
       <c r="H716" t="n">
         <v>15324</v>
@@ -21191,7 +21191,7 @@
         <v>2</v>
       </c>
       <c r="G718" t="n">
-        <v>1.56286692619324</v>
+        <v>1.56286680698395</v>
       </c>
       <c r="H718" t="n">
         <v>6637</v>
@@ -21220,7 +21220,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G719" t="n">
-        <v>1.54723823070526</v>
+        <v>1.54723811149597</v>
       </c>
       <c r="H719" t="n">
         <v>9044</v>
@@ -21249,7 +21249,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G720" t="n">
-        <v>1.57068109512329</v>
+        <v>1.57068121433258</v>
       </c>
       <c r="H720" t="n">
         <v>7076</v>
@@ -21278,7 +21278,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G721" t="n">
-        <v>1.54723823070526</v>
+        <v>1.54723811149597</v>
       </c>
       <c r="H721" t="n">
         <v>4279</v>
@@ -21307,7 +21307,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G722" t="n">
-        <v>1.61756718158722</v>
+        <v>1.61756706237793</v>
       </c>
       <c r="H722" t="n">
         <v>3905</v>
@@ -21510,7 +21510,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G729" t="n">
-        <v>1.57068109512329</v>
+        <v>1.57068121433258</v>
       </c>
       <c r="H729" t="n">
         <v>530</v>
@@ -21539,7 +21539,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G730" t="n">
-        <v>1.57068109512329</v>
+        <v>1.57068121433258</v>
       </c>
       <c r="H730" t="n">
         <v>1325</v>
@@ -21568,7 +21568,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G731" t="n">
-        <v>1.54723823070526</v>
+        <v>1.54723811149597</v>
       </c>
       <c r="H731" t="n">
         <v>2640</v>
@@ -21626,7 +21626,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G733" t="n">
-        <v>1.54723823070526</v>
+        <v>1.54723811149597</v>
       </c>
       <c r="H733" t="n">
         <v>10612</v>
@@ -21655,7 +21655,7 @@
         <v>2</v>
       </c>
       <c r="G734" t="n">
-        <v>1.56286692619324</v>
+        <v>1.56286680698395</v>
       </c>
       <c r="H734" t="n">
         <v>1000</v>
@@ -21684,7 +21684,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G735" t="n">
-        <v>1.55505263805389</v>
+        <v>1.5550525188446</v>
       </c>
       <c r="H735" t="n">
         <v>5470</v>
@@ -21974,7 +21974,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G745" t="n">
-        <v>1.54723823070526</v>
+        <v>1.54723811149597</v>
       </c>
       <c r="H745" t="n">
         <v>6604</v>
@@ -22177,7 +22177,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G752" t="n">
-        <v>1.52379512786865</v>
+        <v>1.52379524707794</v>
       </c>
       <c r="H752" t="n">
         <v>2112</v>
@@ -22206,7 +22206,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G753" t="n">
-        <v>1.52379512786865</v>
+        <v>1.52379524707794</v>
       </c>
       <c r="H753" t="n">
         <v>2730</v>
@@ -22235,7 +22235,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G754" t="n">
-        <v>1.52379512786865</v>
+        <v>1.52379524707794</v>
       </c>
       <c r="H754" t="n">
         <v>116</v>
@@ -22264,7 +22264,7 @@
         <v>2</v>
       </c>
       <c r="G755" t="n">
-        <v>1.56286692619324</v>
+        <v>1.56286680698395</v>
       </c>
       <c r="H755" t="n">
         <v>4200</v>
@@ -22293,7 +22293,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G756" t="n">
-        <v>1.53942382335663</v>
+        <v>1.53942394256592</v>
       </c>
       <c r="H756" t="n">
         <v>2030</v>
@@ -22351,7 +22351,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G758" t="n">
-        <v>1.48472356796265</v>
+        <v>1.48472344875336</v>
       </c>
       <c r="H758" t="n">
         <v>3743</v>
@@ -22380,7 +22380,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G759" t="n">
-        <v>1.48472356796265</v>
+        <v>1.48472344875336</v>
       </c>
       <c r="H759" t="n">
         <v>4807</v>
@@ -22409,7 +22409,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G760" t="n">
-        <v>1.57068109512329</v>
+        <v>1.57068121433258</v>
       </c>
       <c r="H760" t="n">
         <v>3200</v>
@@ -22467,7 +22467,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G762" t="n">
-        <v>1.47690904140472</v>
+        <v>1.47690916061401</v>
       </c>
       <c r="H762" t="n">
         <v>4134</v>
@@ -22554,7 +22554,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G765" t="n">
-        <v>1.74259638786316</v>
+        <v>1.74259662628174</v>
       </c>
       <c r="H765" t="n">
         <v>62191</v>
@@ -22583,7 +22583,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G766" t="n">
-        <v>1.55505263805389</v>
+        <v>1.5550525188446</v>
       </c>
       <c r="H766" t="n">
         <v>117476</v>
@@ -22641,7 +22641,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G768" t="n">
-        <v>1.55505263805389</v>
+        <v>1.5550525188446</v>
       </c>
       <c r="H768" t="n">
         <v>5714</v>
@@ -22786,7 +22786,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G773" t="n">
-        <v>1.55505263805389</v>
+        <v>1.5550525188446</v>
       </c>
       <c r="H773" t="n">
         <v>8089</v>
@@ -22844,7 +22844,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G775" t="n">
-        <v>1.55505263805389</v>
+        <v>1.5550525188446</v>
       </c>
       <c r="H775" t="n">
         <v>2807</v>
@@ -22902,7 +22902,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G777" t="n">
-        <v>1.53942382335663</v>
+        <v>1.53942394256592</v>
       </c>
       <c r="H777" t="n">
         <v>6542</v>
@@ -22931,7 +22931,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G778" t="n">
-        <v>1.53942382335663</v>
+        <v>1.53942394256592</v>
       </c>
       <c r="H778" t="n">
         <v>8387</v>
@@ -22960,7 +22960,7 @@
         <v>2</v>
       </c>
       <c r="G779" t="n">
-        <v>1.56286692619324</v>
+        <v>1.56286680698395</v>
       </c>
       <c r="H779" t="n">
         <v>770</v>
@@ -22989,7 +22989,7 @@
         <v>2</v>
       </c>
       <c r="G780" t="n">
-        <v>1.56286692619324</v>
+        <v>1.56286680698395</v>
       </c>
       <c r="H780" t="n">
         <v>1385</v>
@@ -23018,7 +23018,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G781" t="n">
-        <v>1.55505263805389</v>
+        <v>1.5550525188446</v>
       </c>
       <c r="H781" t="n">
         <v>1090</v>
@@ -23105,7 +23105,7 @@
         <v>2</v>
       </c>
       <c r="G784" t="n">
-        <v>1.56286692619324</v>
+        <v>1.56286680698395</v>
       </c>
       <c r="H784" t="n">
         <v>1630</v>
@@ -23134,7 +23134,7 @@
         <v>2</v>
       </c>
       <c r="G785" t="n">
-        <v>1.56286692619324</v>
+        <v>1.56286680698395</v>
       </c>
       <c r="H785" t="n">
         <v>3493</v>
@@ -23163,7 +23163,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G786" t="n">
-        <v>1.55505263805389</v>
+        <v>1.5550525188446</v>
       </c>
       <c r="H786" t="n">
         <v>3597</v>
@@ -23192,7 +23192,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G787" t="n">
-        <v>1.55505263805389</v>
+        <v>1.5550525188446</v>
       </c>
       <c r="H787" t="n">
         <v>375</v>
@@ -23221,7 +23221,7 @@
         <v>2</v>
       </c>
       <c r="G788" t="n">
-        <v>1.56286692619324</v>
+        <v>1.56286680698395</v>
       </c>
       <c r="H788" t="n">
         <v>400</v>
@@ -23250,7 +23250,7 @@
         <v>2</v>
       </c>
       <c r="G789" t="n">
-        <v>1.56286692619324</v>
+        <v>1.56286680698395</v>
       </c>
       <c r="H789" t="n">
         <v>540</v>
@@ -23279,7 +23279,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G790" t="n">
-        <v>1.55505263805389</v>
+        <v>1.5550525188446</v>
       </c>
       <c r="H790" t="n">
         <v>935</v>
@@ -23308,7 +23308,7 @@
         <v>2</v>
       </c>
       <c r="G791" t="n">
-        <v>1.56286692619324</v>
+        <v>1.56286680698395</v>
       </c>
       <c r="H791" t="n">
         <v>88</v>
@@ -23337,7 +23337,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G792" t="n">
-        <v>1.54723823070526</v>
+        <v>1.54723811149597</v>
       </c>
       <c r="H792" t="n">
         <v>3760</v>
@@ -23366,7 +23366,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G793" t="n">
-        <v>1.54723823070526</v>
+        <v>1.54723811149597</v>
       </c>
       <c r="H793" t="n">
         <v>1646</v>
@@ -23395,7 +23395,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G794" t="n">
-        <v>1.54723823070526</v>
+        <v>1.54723811149597</v>
       </c>
       <c r="H794" t="n">
         <v>3700</v>
@@ -23424,7 +23424,7 @@
         <v>2</v>
       </c>
       <c r="G795" t="n">
-        <v>1.56286692619324</v>
+        <v>1.56286680698395</v>
       </c>
       <c r="H795" t="n">
         <v>8735</v>
@@ -23453,7 +23453,7 @@
         <v>2</v>
       </c>
       <c r="G796" t="n">
-        <v>1.56286692619324</v>
+        <v>1.56286680698395</v>
       </c>
       <c r="H796" t="n">
         <v>8350</v>
@@ -23482,7 +23482,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G797" t="n">
-        <v>1.57068109512329</v>
+        <v>1.57068121433258</v>
       </c>
       <c r="H797" t="n">
         <v>8209</v>
@@ -23569,7 +23569,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G800" t="n">
-        <v>1.53942382335663</v>
+        <v>1.53942394256592</v>
       </c>
       <c r="H800" t="n">
         <v>7026</v>
@@ -23598,7 +23598,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G801" t="n">
-        <v>1.54723823070526</v>
+        <v>1.54723811149597</v>
       </c>
       <c r="H801" t="n">
         <v>4800</v>
@@ -23627,7 +23627,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G802" t="n">
-        <v>1.55505263805389</v>
+        <v>1.5550525188446</v>
       </c>
       <c r="H802" t="n">
         <v>11782</v>
@@ -23685,7 +23685,7 @@
         <v>2</v>
       </c>
       <c r="G804" t="n">
-        <v>1.56286692619324</v>
+        <v>1.56286680698395</v>
       </c>
       <c r="H804" t="n">
         <v>715</v>
@@ -23830,7 +23830,7 @@
         <v>2</v>
       </c>
       <c r="G809" t="n">
-        <v>1.56286692619324</v>
+        <v>1.56286680698395</v>
       </c>
       <c r="H809" t="n">
         <v>100</v>
@@ -23859,7 +23859,7 @@
         <v>2</v>
       </c>
       <c r="G810" t="n">
-        <v>1.56286692619324</v>
+        <v>1.56286680698395</v>
       </c>
       <c r="H810" t="n">
         <v>2902</v>
@@ -23888,7 +23888,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G811" t="n">
-        <v>1.55505263805389</v>
+        <v>1.5550525188446</v>
       </c>
       <c r="H811" t="n">
         <v>1500</v>
@@ -23917,7 +23917,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G812" t="n">
-        <v>1.55505263805389</v>
+        <v>1.5550525188446</v>
       </c>
       <c r="H812" t="n">
         <v>3468</v>
@@ -23946,7 +23946,7 @@
         <v>2</v>
       </c>
       <c r="G813" t="n">
-        <v>1.56286692619324</v>
+        <v>1.56286680698395</v>
       </c>
       <c r="H813" t="n">
         <v>3779</v>
@@ -23975,7 +23975,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G814" t="n">
-        <v>1.57068109512329</v>
+        <v>1.57068121433258</v>
       </c>
       <c r="H814" t="n">
         <v>19292</v>
@@ -24004,7 +24004,7 @@
         <v>2</v>
       </c>
       <c r="G815" t="n">
-        <v>1.56286692619324</v>
+        <v>1.56286680698395</v>
       </c>
       <c r="H815" t="n">
         <v>4107</v>
@@ -24033,7 +24033,7 @@
         <v>2</v>
       </c>
       <c r="G816" t="n">
-        <v>1.56286692619324</v>
+        <v>1.56286680698395</v>
       </c>
       <c r="H816" t="n">
         <v>8835</v>
@@ -24149,7 +24149,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G820" t="n">
-        <v>1.64101016521454</v>
+        <v>1.64101004600525</v>
       </c>
       <c r="H820" t="n">
         <v>7169</v>
@@ -24207,7 +24207,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G822" t="n">
-        <v>1.61756718158722</v>
+        <v>1.61756706237793</v>
       </c>
       <c r="H822" t="n">
         <v>271</v>
@@ -24381,7 +24381,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G828" t="n">
-        <v>1.891068816185</v>
+        <v>1.89106869697571</v>
       </c>
       <c r="H828" t="n">
         <v>164712</v>
@@ -24555,7 +24555,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G834" t="n">
-        <v>1.64101016521454</v>
+        <v>1.64101004600525</v>
       </c>
       <c r="H834" t="n">
         <v>9584</v>
@@ -24700,7 +24700,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G839" t="n">
-        <v>1.64101016521454</v>
+        <v>1.64101004600525</v>
       </c>
       <c r="H839" t="n">
         <v>10970</v>
@@ -24758,7 +24758,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G841" t="n">
-        <v>1.64101016521454</v>
+        <v>1.64101004600525</v>
       </c>
       <c r="H841" t="n">
         <v>17557</v>
@@ -25077,7 +25077,7 @@
         <v>2</v>
       </c>
       <c r="G852" t="n">
-        <v>1.56286692619324</v>
+        <v>1.56286680698395</v>
       </c>
       <c r="H852" t="n">
         <v>14569</v>
@@ -25193,7 +25193,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G856" t="n">
-        <v>1.54723823070526</v>
+        <v>1.54723811149597</v>
       </c>
       <c r="H856" t="n">
         <v>6091</v>
@@ -25309,7 +25309,7 @@
         <v>2</v>
       </c>
       <c r="G860" t="n">
-        <v>1.56286692619324</v>
+        <v>1.56286680698395</v>
       </c>
       <c r="H860" t="n">
         <v>500</v>
@@ -25338,7 +25338,7 @@
         <v>2</v>
       </c>
       <c r="G861" t="n">
-        <v>1.56286692619324</v>
+        <v>1.56286680698395</v>
       </c>
       <c r="H861" t="n">
         <v>0</v>
@@ -25541,7 +25541,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G868" t="n">
-        <v>1.46909475326538</v>
+        <v>1.46909487247467</v>
       </c>
       <c r="H868" t="n">
         <v>28560</v>
@@ -25599,7 +25599,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G870" t="n">
-        <v>1.46909475326538</v>
+        <v>1.46909487247467</v>
       </c>
       <c r="H870" t="n">
         <v>3044</v>
@@ -25686,7 +25686,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G873" t="n">
-        <v>1.46909475326538</v>
+        <v>1.46909487247467</v>
       </c>
       <c r="H873" t="n">
         <v>710</v>
@@ -25715,7 +25715,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G874" t="n">
-        <v>1.48472356796265</v>
+        <v>1.48472344875336</v>
       </c>
       <c r="H874" t="n">
         <v>750</v>
@@ -25860,7 +25860,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G879" t="n">
-        <v>1.48472356796265</v>
+        <v>1.48472344875336</v>
       </c>
       <c r="H879" t="n">
         <v>2150</v>
@@ -25889,7 +25889,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G880" t="n">
-        <v>1.46909475326538</v>
+        <v>1.46909487247467</v>
       </c>
       <c r="H880" t="n">
         <v>22334</v>
@@ -25947,7 +25947,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G882" t="n">
-        <v>1.43783748149872</v>
+        <v>1.43783760070801</v>
       </c>
       <c r="H882" t="n">
         <v>3065</v>
@@ -26034,7 +26034,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G885" t="n">
-        <v>1.43783748149872</v>
+        <v>1.43783760070801</v>
       </c>
       <c r="H885" t="n">
         <v>29</v>
@@ -26063,7 +26063,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G886" t="n">
-        <v>1.46909475326538</v>
+        <v>1.46909487247467</v>
       </c>
       <c r="H886" t="n">
         <v>4151</v>
@@ -26092,7 +26092,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G887" t="n">
-        <v>1.48472356796265</v>
+        <v>1.48472344875336</v>
       </c>
       <c r="H887" t="n">
         <v>341707</v>
@@ -26121,7 +26121,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G888" t="n">
-        <v>1.48472356796265</v>
+        <v>1.48472344875336</v>
       </c>
       <c r="H888" t="n">
         <v>16005</v>
@@ -26295,7 +26295,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G894" t="n">
-        <v>1.48472356796265</v>
+        <v>1.48472344875336</v>
       </c>
       <c r="H894" t="n">
         <v>20473</v>
@@ -26382,7 +26382,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G897" t="n">
-        <v>1.54723823070526</v>
+        <v>1.54723811149597</v>
       </c>
       <c r="H897" t="n">
         <v>12400</v>
@@ -26498,7 +26498,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G901" t="n">
-        <v>1.54723823070526</v>
+        <v>1.54723811149597</v>
       </c>
       <c r="H901" t="n">
         <v>5238</v>
@@ -26788,7 +26788,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G911" t="n">
-        <v>1.48472356796265</v>
+        <v>1.48472344875336</v>
       </c>
       <c r="H911" t="n">
         <v>50</v>
@@ -26991,7 +26991,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G918" t="n">
-        <v>1.46909475326538</v>
+        <v>1.46909487247467</v>
       </c>
       <c r="H918" t="n">
         <v>9855</v>
@@ -27078,7 +27078,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G921" t="n">
-        <v>1.48472356796265</v>
+        <v>1.48472344875336</v>
       </c>
       <c r="H921" t="n">
         <v>1357</v>
@@ -27107,7 +27107,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G922" t="n">
-        <v>1.46909475326538</v>
+        <v>1.46909487247467</v>
       </c>
       <c r="H922" t="n">
         <v>577</v>
@@ -27136,7 +27136,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G923" t="n">
-        <v>1.46909475326538</v>
+        <v>1.46909487247467</v>
       </c>
       <c r="H923" t="n">
         <v>1678</v>
@@ -27194,7 +27194,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G925" t="n">
-        <v>1.48472356796265</v>
+        <v>1.48472344875336</v>
       </c>
       <c r="H925" t="n">
         <v>10370</v>
@@ -27339,7 +27339,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G930" t="n">
-        <v>1.48472356796265</v>
+        <v>1.48472344875336</v>
       </c>
       <c r="H930" t="n">
         <v>4310</v>
@@ -27368,7 +27368,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G931" t="n">
-        <v>1.48472356796265</v>
+        <v>1.48472344875336</v>
       </c>
       <c r="H931" t="n">
         <v>634</v>
@@ -27397,7 +27397,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G932" t="n">
-        <v>1.46909475326538</v>
+        <v>1.46909487247467</v>
       </c>
       <c r="H932" t="n">
         <v>7581</v>
@@ -27455,7 +27455,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G934" t="n">
-        <v>1.46909475326538</v>
+        <v>1.46909487247467</v>
       </c>
       <c r="H934" t="n">
         <v>4422</v>
@@ -27687,7 +27687,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G942" t="n">
-        <v>1.48472356796265</v>
+        <v>1.48472344875336</v>
       </c>
       <c r="H942" t="n">
         <v>10270</v>
@@ -27832,7 +27832,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G947" t="n">
-        <v>1.48472356796265</v>
+        <v>1.48472344875336</v>
       </c>
       <c r="H947" t="n">
         <v>7679</v>
@@ -28064,7 +28064,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G955" t="n">
-        <v>1.48472356796265</v>
+        <v>1.48472344875336</v>
       </c>
       <c r="H955" t="n">
         <v>8758</v>
@@ -28093,7 +28093,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G956" t="n">
-        <v>1.46909475326538</v>
+        <v>1.46909487247467</v>
       </c>
       <c r="H956" t="n">
         <v>14201</v>
@@ -28122,7 +28122,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G957" t="n">
-        <v>1.46909475326538</v>
+        <v>1.46909487247467</v>
       </c>
       <c r="H957" t="n">
         <v>24615</v>
@@ -28209,7 +28209,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G960" t="n">
-        <v>1.46909475326538</v>
+        <v>1.46909487247467</v>
       </c>
       <c r="H960" t="n">
         <v>61673</v>
@@ -28238,7 +28238,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G961" t="n">
-        <v>1.46909475326538</v>
+        <v>1.46909487247467</v>
       </c>
       <c r="H961" t="n">
         <v>5222</v>
@@ -28296,7 +28296,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G963" t="n">
-        <v>1.48472356796265</v>
+        <v>1.48472344875336</v>
       </c>
       <c r="H963" t="n">
         <v>9765</v>
@@ -28325,7 +28325,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G964" t="n">
-        <v>1.48472356796265</v>
+        <v>1.48472344875336</v>
       </c>
       <c r="H964" t="n">
         <v>11563</v>
@@ -28354,7 +28354,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G965" t="n">
-        <v>1.48472356796265</v>
+        <v>1.48472344875336</v>
       </c>
       <c r="H965" t="n">
         <v>4432</v>
@@ -28383,7 +28383,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G966" t="n">
-        <v>1.46909475326538</v>
+        <v>1.46909487247467</v>
       </c>
       <c r="H966" t="n">
         <v>10446</v>
@@ -28412,7 +28412,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G967" t="n">
-        <v>1.46909475326538</v>
+        <v>1.46909487247467</v>
       </c>
       <c r="H967" t="n">
         <v>320</v>
@@ -28441,7 +28441,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G968" t="n">
-        <v>1.46909475326538</v>
+        <v>1.46909487247467</v>
       </c>
       <c r="H968" t="n">
         <v>3588</v>
@@ -28470,7 +28470,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G969" t="n">
-        <v>1.43783748149872</v>
+        <v>1.43783760070801</v>
       </c>
       <c r="H969" t="n">
         <v>21430</v>
@@ -28499,7 +28499,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G970" t="n">
-        <v>1.43783748149872</v>
+        <v>1.43783760070801</v>
       </c>
       <c r="H970" t="n">
         <v>484</v>
@@ -28528,7 +28528,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G971" t="n">
-        <v>1.43783748149872</v>
+        <v>1.43783760070801</v>
       </c>
       <c r="H971" t="n">
         <v>1075</v>
@@ -28557,7 +28557,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G972" t="n">
-        <v>1.43783748149872</v>
+        <v>1.43783760070801</v>
       </c>
       <c r="H972" t="n">
         <v>500</v>
@@ -28586,7 +28586,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G973" t="n">
-        <v>1.42220878601074</v>
+        <v>1.42220890522003</v>
       </c>
       <c r="H973" t="n">
         <v>30</v>
@@ -28644,7 +28644,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G975" t="n">
-        <v>1.43783748149872</v>
+        <v>1.43783760070801</v>
       </c>
       <c r="H975" t="n">
         <v>2000</v>
@@ -28673,7 +28673,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G976" t="n">
-        <v>1.42220878601074</v>
+        <v>1.42220890522003</v>
       </c>
       <c r="H976" t="n">
         <v>8943</v>
@@ -28702,7 +28702,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G977" t="n">
-        <v>1.42220878601074</v>
+        <v>1.42220890522003</v>
       </c>
       <c r="H977" t="n">
         <v>2955</v>
@@ -28731,7 +28731,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G978" t="n">
-        <v>1.43783748149872</v>
+        <v>1.43783760070801</v>
       </c>
       <c r="H978" t="n">
         <v>4265</v>
@@ -28789,7 +28789,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G980" t="n">
-        <v>1.43783748149872</v>
+        <v>1.43783760070801</v>
       </c>
       <c r="H980" t="n">
         <v>560</v>
@@ -28818,7 +28818,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G981" t="n">
-        <v>1.43783748149872</v>
+        <v>1.43783760070801</v>
       </c>
       <c r="H981" t="n">
         <v>3315</v>
@@ -28905,7 +28905,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G984" t="n">
-        <v>1.42220878601074</v>
+        <v>1.42220890522003</v>
       </c>
       <c r="H984" t="n">
         <v>2400</v>
@@ -28934,7 +28934,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G985" t="n">
-        <v>1.42220878601074</v>
+        <v>1.42220890522003</v>
       </c>
       <c r="H985" t="n">
         <v>7856</v>
@@ -28963,7 +28963,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G986" t="n">
-        <v>1.42220878601074</v>
+        <v>1.42220890522003</v>
       </c>
       <c r="H986" t="n">
         <v>28690</v>
@@ -29021,7 +29021,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G988" t="n">
-        <v>1.43783748149872</v>
+        <v>1.43783760070801</v>
       </c>
       <c r="H988" t="n">
         <v>3235</v>
@@ -29079,7 +29079,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G990" t="n">
-        <v>1.43783748149872</v>
+        <v>1.43783760070801</v>
       </c>
       <c r="H990" t="n">
         <v>377</v>
@@ -29108,7 +29108,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G991" t="n">
-        <v>1.43783748149872</v>
+        <v>1.43783760070801</v>
       </c>
       <c r="H991" t="n">
         <v>1621</v>
@@ -29137,7 +29137,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G992" t="n">
-        <v>1.43783748149872</v>
+        <v>1.43783760070801</v>
       </c>
       <c r="H992" t="n">
         <v>4633</v>
@@ -29166,7 +29166,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G993" t="n">
-        <v>1.42220878601074</v>
+        <v>1.42220890522003</v>
       </c>
       <c r="H993" t="n">
         <v>2550</v>
@@ -29195,7 +29195,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G994" t="n">
-        <v>1.42220878601074</v>
+        <v>1.42220890522003</v>
       </c>
       <c r="H994" t="n">
         <v>2459</v>
@@ -29224,7 +29224,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G995" t="n">
-        <v>1.3909512758255</v>
+        <v>1.39095151424408</v>
       </c>
       <c r="H995" t="n">
         <v>4445</v>
@@ -29253,7 +29253,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G996" t="n">
-        <v>1.42220878601074</v>
+        <v>1.42220890522003</v>
       </c>
       <c r="H996" t="n">
         <v>739</v>
@@ -29427,7 +29427,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G1002" t="n">
-        <v>1.43783748149872</v>
+        <v>1.43783760070801</v>
       </c>
       <c r="H1002" t="n">
         <v>29959</v>
@@ -29485,7 +29485,7 @@
         <v>2</v>
       </c>
       <c r="G1004" t="n">
-        <v>1.56286692619324</v>
+        <v>1.56286680698395</v>
       </c>
       <c r="H1004" t="n">
         <v>526368</v>
@@ -29514,7 +29514,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G1005" t="n">
-        <v>1.48472356796265</v>
+        <v>1.48472344875336</v>
       </c>
       <c r="H1005" t="n">
         <v>203908</v>
@@ -29572,7 +29572,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G1007" t="n">
-        <v>1.46909475326538</v>
+        <v>1.46909487247467</v>
       </c>
       <c r="H1007" t="n">
         <v>168703</v>
@@ -29601,7 +29601,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G1008" t="n">
-        <v>1.42220878601074</v>
+        <v>1.42220890522003</v>
       </c>
       <c r="H1008" t="n">
         <v>24714</v>
@@ -29717,7 +29717,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G1012" t="n">
-        <v>1.43783748149872</v>
+        <v>1.43783760070801</v>
       </c>
       <c r="H1012" t="n">
         <v>26843</v>
@@ -29746,7 +29746,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G1013" t="n">
-        <v>1.43783748149872</v>
+        <v>1.43783760070801</v>
       </c>
       <c r="H1013" t="n">
         <v>8510</v>
@@ -29775,7 +29775,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G1014" t="n">
-        <v>1.46909475326538</v>
+        <v>1.46909487247467</v>
       </c>
       <c r="H1014" t="n">
         <v>11951</v>
@@ -29833,7 +29833,7 @@
         <v>1.84019994735718</v>
       </c>
       <c r="G1016" t="n">
-        <v>1.43799364566803</v>
+        <v>1.43799376487732</v>
       </c>
       <c r="H1016" t="n">
         <v>22250</v>
@@ -29949,7 +29949,7 @@
         <v>1.81679999828339</v>
       </c>
       <c r="G1020" t="n">
-        <v>1.41970825195312</v>
+        <v>1.41970813274384</v>
       </c>
       <c r="H1020" t="n">
         <v>54639</v>
@@ -29978,7 +29978,7 @@
         <v>1.77359998226166</v>
       </c>
       <c r="G1021" t="n">
-        <v>1.38595032691956</v>
+        <v>1.38595020771027</v>
       </c>
       <c r="H1021" t="n">
         <v>10862</v>
@@ -30123,7 +30123,7 @@
         <v>1.74119997024536</v>
       </c>
       <c r="G1026" t="n">
-        <v>1.36063182353973</v>
+        <v>1.36063170433044</v>
       </c>
       <c r="H1026" t="n">
         <v>42274</v>
@@ -30181,7 +30181,7 @@
         <v>1.70500004291534</v>
       </c>
       <c r="G1028" t="n">
-        <v>1.33234393596649</v>
+        <v>1.33234405517578</v>
       </c>
       <c r="H1028" t="n">
         <v>21254</v>
@@ -30268,7 +30268,7 @@
         <v>1.73239994049072</v>
       </c>
       <c r="G1031" t="n">
-        <v>1.35375535488129</v>
+        <v>1.353755235672</v>
       </c>
       <c r="H1031" t="n">
         <v>8694</v>
@@ -30326,7 +30326,7 @@
         <v>1.70099997520447</v>
       </c>
       <c r="G1033" t="n">
-        <v>1.32921814918518</v>
+        <v>1.32921826839447</v>
       </c>
       <c r="H1033" t="n">
         <v>15378</v>
@@ -30384,7 +30384,7 @@
         <v>1.68099999427795</v>
       </c>
       <c r="G1035" t="n">
-        <v>1.31358969211578</v>
+        <v>1.31358957290649</v>
       </c>
       <c r="H1035" t="n">
         <v>15612</v>
@@ -30471,7 +30471,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1038" t="n">
-        <v>1.25029361248016</v>
+        <v>1.25029349327087</v>
       </c>
       <c r="H1038" t="n">
         <v>7984</v>
@@ -30529,7 +30529,7 @@
         <v>1.52020001411438</v>
       </c>
       <c r="G1040" t="n">
-        <v>1.18793511390686</v>
+        <v>1.18793499469757</v>
       </c>
       <c r="H1040" t="n">
         <v>32531</v>
@@ -30558,7 +30558,7 @@
         <v>1.57720005512238</v>
       </c>
       <c r="G1041" t="n">
-        <v>1.23247683048248</v>
+        <v>1.23247671127319</v>
       </c>
       <c r="H1041" t="n">
         <v>45218</v>
@@ -30587,7 +30587,7 @@
         <v>1.60580003261566</v>
       </c>
       <c r="G1042" t="n">
-        <v>1.25482571125031</v>
+        <v>1.25482583045959</v>
       </c>
       <c r="H1042" t="n">
         <v>57252</v>
@@ -30616,7 +30616,7 @@
         <v>1.61819994449615</v>
       </c>
       <c r="G1043" t="n">
-        <v>1.26451551914215</v>
+        <v>1.26451539993286</v>
       </c>
       <c r="H1043" t="n">
         <v>5812</v>
@@ -30703,7 +30703,7 @@
         <v>1.63779997825623</v>
       </c>
       <c r="G1046" t="n">
-        <v>1.27983164787292</v>
+        <v>1.27983176708221</v>
       </c>
       <c r="H1046" t="n">
         <v>22878</v>
@@ -30732,7 +30732,7 @@
         <v>1.66260004043579</v>
       </c>
       <c r="G1047" t="n">
-        <v>1.29921114444733</v>
+        <v>1.29921126365662</v>
       </c>
       <c r="H1047" t="n">
         <v>23626</v>
@@ -30761,7 +30761,7 @@
         <v>1.68579995632172</v>
       </c>
       <c r="G1048" t="n">
-        <v>1.31734049320221</v>
+        <v>1.31734037399292</v>
       </c>
       <c r="H1048" t="n">
         <v>10382</v>
@@ -30790,7 +30790,7 @@
         <v>1.67980003356934</v>
       </c>
       <c r="G1049" t="n">
-        <v>1.31265187263489</v>
+        <v>1.3126517534256</v>
       </c>
       <c r="H1049" t="n">
         <v>5718</v>
@@ -30819,7 +30819,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1050" t="n">
-        <v>1.30499386787415</v>
+        <v>1.30499374866486</v>
       </c>
       <c r="H1050" t="n">
         <v>5237</v>
@@ -30877,7 +30877,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1052" t="n">
-        <v>1.30499386787415</v>
+        <v>1.30499374866486</v>
       </c>
       <c r="H1052" t="n">
         <v>3328</v>
@@ -30964,7 +30964,7 @@
         <v>1.61479997634888</v>
       </c>
       <c r="G1055" t="n">
-        <v>1.26185858249664</v>
+        <v>1.26185870170593</v>
       </c>
       <c r="H1055" t="n">
         <v>3537</v>
@@ -31051,7 +31051,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G1058" t="n">
-        <v>1.17996454238892</v>
+        <v>1.17996442317963</v>
       </c>
       <c r="H1058" t="n">
         <v>26123</v>
@@ -31080,7 +31080,7 @@
         <v>1.55980002880096</v>
       </c>
       <c r="G1059" t="n">
-        <v>1.2188800573349</v>
+        <v>1.21887993812561</v>
       </c>
       <c r="H1059" t="n">
         <v>21083</v>
@@ -31138,7 +31138,7 @@
         <v>1.49779999256134</v>
       </c>
       <c r="G1061" t="n">
-        <v>1.17043089866638</v>
+        <v>1.17043101787567</v>
       </c>
       <c r="H1061" t="n">
         <v>16113</v>
@@ -31167,7 +31167,7 @@
         <v>1.35800004005432</v>
       </c>
       <c r="G1062" t="n">
-        <v>1.06118655204773</v>
+        <v>1.06118667125702</v>
       </c>
       <c r="H1062" t="n">
         <v>18498</v>
@@ -31283,7 +31283,7 @@
         <v>0.939999997615814</v>
       </c>
       <c r="G1066" t="n">
-        <v>0.73454737663269</v>
+        <v>0.734547436237335</v>
       </c>
       <c r="H1066" t="n">
         <v>21386</v>
@@ -31341,7 +31341,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G1068" t="n">
-        <v>0.773619115352631</v>
+        <v>0.773619055747986</v>
       </c>
       <c r="H1068" t="n">
         <v>15083</v>
@@ -31370,7 +31370,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G1069" t="n">
-        <v>0.773619115352631</v>
+        <v>0.773619055747986</v>
       </c>
       <c r="H1069" t="n">
         <v>7200</v>
@@ -31399,7 +31399,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G1070" t="n">
-        <v>0.773619115352631</v>
+        <v>0.773619055747986</v>
       </c>
       <c r="H1070" t="n">
         <v>1500</v>
@@ -31486,7 +31486,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G1073" t="n">
-        <v>0.968977391719818</v>
+        <v>0.968977510929108</v>
       </c>
       <c r="H1073" t="n">
         <v>6985</v>
@@ -31515,7 +31515,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G1074" t="n">
-        <v>1.0940066576004</v>
+        <v>1.09400677680969</v>
       </c>
       <c r="H1074" t="n">
         <v>7710</v>
@@ -31544,7 +31544,7 @@
         <v>1.54499995708466</v>
       </c>
       <c r="G1075" t="n">
-        <v>1.20731472969055</v>
+        <v>1.20731461048126</v>
       </c>
       <c r="H1075" t="n">
         <v>70566</v>
@@ -31602,7 +31602,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G1077" t="n">
-        <v>1.24247920513153</v>
+        <v>1.24247908592224</v>
       </c>
       <c r="H1077" t="n">
         <v>15463</v>
@@ -31631,7 +31631,7 @@
         <v>1.61500000953674</v>
       </c>
       <c r="G1078" t="n">
-        <v>1.26201510429382</v>
+        <v>1.26201486587524</v>
       </c>
       <c r="H1078" t="n">
         <v>5525</v>
@@ -31660,7 +31660,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1079" t="n">
-        <v>1.25029361248016</v>
+        <v>1.25029349327087</v>
       </c>
       <c r="H1079" t="n">
         <v>7119</v>
@@ -31718,7 +31718,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G1081" t="n">
-        <v>1.21122181415558</v>
+        <v>1.21122169494629</v>
       </c>
       <c r="H1081" t="n">
         <v>11021</v>
@@ -31776,7 +31776,7 @@
         <v>1.58800005912781</v>
       </c>
       <c r="G1083" t="n">
-        <v>1.24091625213623</v>
+        <v>1.24091637134552</v>
       </c>
       <c r="H1083" t="n">
         <v>22509</v>
@@ -31805,7 +31805,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G1084" t="n">
-        <v>1.25810790061951</v>
+        <v>1.25810778141022</v>
       </c>
       <c r="H1084" t="n">
         <v>29539</v>
@@ -31921,7 +31921,7 @@
         <v>1.52999997138977</v>
       </c>
       <c r="G1088" t="n">
-        <v>1.1955931186676</v>
+        <v>1.19559299945831</v>
       </c>
       <c r="H1088" t="n">
         <v>8558</v>
@@ -31979,7 +31979,7 @@
         <v>1.56959998607635</v>
       </c>
       <c r="G1090" t="n">
-        <v>1.22653782367706</v>
+        <v>1.22653794288635</v>
       </c>
       <c r="H1090" t="n">
         <v>15691</v>
@@ -32037,7 +32037,7 @@
         <v>1.51059997081757</v>
       </c>
       <c r="G1092" t="n">
-        <v>1.18043327331543</v>
+        <v>1.18043339252472</v>
       </c>
       <c r="H1092" t="n">
         <v>10176</v>
@@ -32066,7 +32066,7 @@
         <v>1.53840005397797</v>
       </c>
       <c r="G1093" t="n">
-        <v>1.20215713977814</v>
+        <v>1.20215737819672</v>
       </c>
       <c r="H1093" t="n">
         <v>6653</v>
@@ -32124,7 +32124,7 @@
         <v>1.42999994754791</v>
       </c>
       <c r="G1095" t="n">
-        <v>1.11744964122772</v>
+        <v>1.1174498796463</v>
       </c>
       <c r="H1095" t="n">
         <v>6692</v>
@@ -32240,7 +32240,7 @@
         <v>1.42980003356934</v>
       </c>
       <c r="G1099" t="n">
-        <v>1.11729347705841</v>
+        <v>1.1172935962677</v>
       </c>
       <c r="H1099" t="n">
         <v>10201</v>
@@ -32269,7 +32269,7 @@
         <v>1.42980003356934</v>
       </c>
       <c r="G1100" t="n">
-        <v>1.11729347705841</v>
+        <v>1.1172935962677</v>
       </c>
       <c r="H1100" t="n">
         <v>0</v>
@@ -32327,7 +32327,7 @@
         <v>1.44400000572205</v>
       </c>
       <c r="G1102" t="n">
-        <v>1.12838983535767</v>
+        <v>1.12838971614838</v>
       </c>
       <c r="H1102" t="n">
         <v>44823</v>
@@ -32356,7 +32356,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G1103" t="n">
-        <v>1.07837808132172</v>
+        <v>1.07837820053101</v>
       </c>
       <c r="H1103" t="n">
         <v>39674</v>
@@ -32443,7 +32443,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1106" t="n">
-        <v>1.04712069034576</v>
+        <v>1.04712080955505</v>
       </c>
       <c r="H1106" t="n">
         <v>11729</v>
@@ -32472,7 +32472,7 @@
         <v>1.34080004692078</v>
       </c>
       <c r="G1107" t="n">
-        <v>1.04774606227875</v>
+        <v>1.04774594306946</v>
       </c>
       <c r="H1107" t="n">
         <v>27019</v>
@@ -32501,7 +32501,7 @@
         <v>1.30019998550415</v>
       </c>
       <c r="G1108" t="n">
-        <v>1.0160197019577</v>
+        <v>1.01601982116699</v>
       </c>
       <c r="H1108" t="n">
         <v>1305</v>
@@ -32588,7 +32588,7 @@
         <v>1.24500000476837</v>
       </c>
       <c r="G1111" t="n">
-        <v>0.97288453578949</v>
+        <v>0.972884654998779</v>
       </c>
       <c r="H1111" t="n">
         <v>16126</v>
@@ -32646,7 +32646,7 @@
         <v>1.23800003528595</v>
       </c>
       <c r="G1113" t="n">
-        <v>0.967414736747742</v>
+        <v>0.967414557933807</v>
       </c>
       <c r="H1113" t="n">
         <v>18476</v>
@@ -32675,7 +32675,7 @@
         <v>1.23039996623993</v>
       </c>
       <c r="G1114" t="n">
-        <v>0.961475729942322</v>
+        <v>0.961475670337677</v>
       </c>
       <c r="H1114" t="n">
         <v>12655</v>
@@ -32791,7 +32791,7 @@
         <v>1.31719994544983</v>
       </c>
       <c r="G1118" t="n">
-        <v>1.02930414676666</v>
+        <v>1.02930402755737</v>
       </c>
       <c r="H1118" t="n">
         <v>20471</v>
@@ -32849,7 +32849,7 @@
         <v>1.2791999578476</v>
       </c>
       <c r="G1120" t="n">
-        <v>0.999609649181366</v>
+        <v>0.999609529972076</v>
       </c>
       <c r="H1120" t="n">
         <v>25760</v>
@@ -32878,7 +32878,7 @@
         <v>1.2771999835968</v>
       </c>
       <c r="G1121" t="n">
-        <v>0.99804675579071</v>
+        <v>0.998046875</v>
       </c>
       <c r="H1121" t="n">
         <v>64712</v>
@@ -32907,7 +32907,7 @@
         <v>1.33940005302429</v>
       </c>
       <c r="G1122" t="n">
-        <v>1.04665184020996</v>
+        <v>1.04665195941925</v>
       </c>
       <c r="H1122" t="n">
         <v>68249</v>
@@ -32965,7 +32965,7 @@
         <v>1.31900000572205</v>
       </c>
       <c r="G1124" t="n">
-        <v>1.03071081638336</v>
+        <v>1.03071069717407</v>
       </c>
       <c r="H1124" t="n">
         <v>11224</v>
@@ -32994,7 +32994,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G1125" t="n">
-        <v>1.07837808132172</v>
+        <v>1.07837820053101</v>
       </c>
       <c r="H1125" t="n">
         <v>43721</v>
@@ -33081,7 +33081,7 @@
         <v>1.34979999065399</v>
       </c>
       <c r="G1128" t="n">
-        <v>1.05477869510651</v>
+        <v>1.0547788143158</v>
       </c>
       <c r="H1128" t="n">
         <v>30907</v>
@@ -33110,7 +33110,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G1129" t="n">
-        <v>1.03149211406708</v>
+        <v>1.03149223327637</v>
       </c>
       <c r="H1129" t="n">
         <v>23471</v>
@@ -33197,7 +33197,7 @@
         <v>1.32280004024506</v>
       </c>
       <c r="G1132" t="n">
-        <v>1.03368008136749</v>
+        <v>1.03368020057678</v>
       </c>
       <c r="H1132" t="n">
         <v>4792</v>
@@ -33226,7 +33226,7 @@
         <v>1.29820001125336</v>
       </c>
       <c r="G1133" t="n">
-        <v>1.01445686817169</v>
+        <v>1.0144567489624</v>
       </c>
       <c r="H1133" t="n">
         <v>4011</v>
@@ -33255,7 +33255,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1134" t="n">
-        <v>1.04712069034576</v>
+        <v>1.04712080955505</v>
       </c>
       <c r="H1134" t="n">
         <v>6000</v>
@@ -33284,7 +33284,7 @@
         <v>1.2960000038147</v>
       </c>
       <c r="G1135" t="n">
-        <v>1.01273787021637</v>
+        <v>1.01273775100708</v>
       </c>
       <c r="H1135" t="n">
         <v>2329</v>
@@ -33313,7 +33313,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G1136" t="n">
-        <v>1.03149211406708</v>
+        <v>1.03149223327637</v>
       </c>
       <c r="H1136" t="n">
         <v>3100</v>
@@ -33429,7 +33429,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1140" t="n">
-        <v>1.03930640220642</v>
+        <v>1.03930652141571</v>
       </c>
       <c r="H1140" t="n">
         <v>4250</v>
@@ -33516,7 +33516,7 @@
         <v>1.30900001525879</v>
       </c>
       <c r="G1143" t="n">
-        <v>1.02289640903473</v>
+        <v>1.02289628982544</v>
       </c>
       <c r="H1143" t="n">
         <v>1000</v>
@@ -33545,7 +33545,7 @@
         <v>1.30499994754791</v>
       </c>
       <c r="G1144" t="n">
-        <v>1.01977050304413</v>
+        <v>1.01977062225342</v>
       </c>
       <c r="H1144" t="n">
         <v>3677</v>
@@ -33632,7 +33632,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1147" t="n">
-        <v>0.992420375347137</v>
+        <v>0.992420434951782</v>
       </c>
       <c r="H1147" t="n">
         <v>5704</v>
@@ -33661,7 +33661,7 @@
         <v>1.26499998569489</v>
       </c>
       <c r="G1148" t="n">
-        <v>0.988513171672821</v>
+        <v>0.988513231277466</v>
       </c>
       <c r="H1148" t="n">
         <v>1022</v>
@@ -33748,7 +33748,7 @@
         <v>1.29299998283386</v>
       </c>
       <c r="G1151" t="n">
-        <v>1.01039326190948</v>
+        <v>1.01039350032806</v>
       </c>
       <c r="H1151" t="n">
         <v>4302</v>
@@ -33777,7 +33777,7 @@
         <v>1.29180002212524</v>
       </c>
       <c r="G1152" t="n">
-        <v>1.00945568084717</v>
+        <v>1.00945556163788</v>
       </c>
       <c r="H1152" t="n">
         <v>8200</v>
@@ -33806,7 +33806,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1153" t="n">
-        <v>0.992420375347137</v>
+        <v>0.992420434951782</v>
       </c>
       <c r="H1153" t="n">
         <v>2410</v>
@@ -33835,7 +33835,7 @@
         <v>1.25440001487732</v>
       </c>
       <c r="G1154" t="n">
-        <v>0.980230212211609</v>
+        <v>0.980230093002319</v>
       </c>
       <c r="H1154" t="n">
         <v>5500</v>
@@ -33864,7 +33864,7 @@
         <v>1.28880000114441</v>
       </c>
       <c r="G1155" t="n">
-        <v>1.00711143016815</v>
+        <v>1.00711131095886</v>
       </c>
       <c r="H1155" t="n">
         <v>5122</v>
@@ -33893,7 +33893,7 @@
         <v>1.26199996471405</v>
       </c>
       <c r="G1156" t="n">
-        <v>0.98616898059845</v>
+        <v>0.98616886138916</v>
       </c>
       <c r="H1156" t="n">
         <v>9776</v>
@@ -33922,7 +33922,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G1157" t="n">
-        <v>1.02367770671844</v>
+        <v>1.02367758750916</v>
       </c>
       <c r="H1157" t="n">
         <v>40638</v>
@@ -33951,7 +33951,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G1158" t="n">
-        <v>1.03149211406708</v>
+        <v>1.03149223327637</v>
       </c>
       <c r="H1158" t="n">
         <v>25837</v>
@@ -33980,7 +33980,7 @@
         <v>1.29499995708466</v>
       </c>
       <c r="G1159" t="n">
-        <v>1.01195633411407</v>
+        <v>1.01195621490479</v>
       </c>
       <c r="H1159" t="n">
         <v>21359</v>
@@ -34038,7 +34038,7 @@
         <v>1.28939998149872</v>
       </c>
       <c r="G1161" t="n">
-        <v>1.00758016109467</v>
+        <v>1.00758028030396</v>
       </c>
       <c r="H1161" t="n">
         <v>160</v>
@@ -34125,7 +34125,7 @@
         <v>1.23099994659424</v>
       </c>
       <c r="G1164" t="n">
-        <v>0.96194452047348</v>
+        <v>0.961944580078125</v>
       </c>
       <c r="H1164" t="n">
         <v>10525</v>
@@ -34154,7 +34154,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1165" t="n">
-        <v>0.992420375347137</v>
+        <v>0.992420434951782</v>
       </c>
       <c r="H1165" t="n">
         <v>10014</v>
@@ -34183,7 +34183,7 @@
         <v>1.27900004386902</v>
       </c>
       <c r="G1166" t="n">
-        <v>0.99945330619812</v>
+        <v>0.999453365802765</v>
       </c>
       <c r="H1166" t="n">
         <v>19032</v>
@@ -34212,7 +34212,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1167" t="n">
-        <v>0.992420375347137</v>
+        <v>0.992420434951782</v>
       </c>
       <c r="H1167" t="n">
         <v>18852</v>
@@ -34328,7 +34328,7 @@
         <v>1.24339997768402</v>
       </c>
       <c r="G1171" t="n">
-        <v>0.971634387969971</v>
+        <v>0.971634268760681</v>
       </c>
       <c r="H1171" t="n">
         <v>4563</v>
@@ -34357,7 +34357,7 @@
         <v>1.22060000896454</v>
       </c>
       <c r="G1172" t="n">
-        <v>0.95381772518158</v>
+        <v>0.95381760597229</v>
       </c>
       <c r="H1172" t="n">
         <v>2356</v>
@@ -34386,7 +34386,7 @@
         <v>1.22060000896454</v>
       </c>
       <c r="G1173" t="n">
-        <v>0.95381772518158</v>
+        <v>0.95381760597229</v>
       </c>
       <c r="H1173" t="n">
         <v>0</v>
@@ -34444,7 +34444,7 @@
         <v>1.22200000286102</v>
       </c>
       <c r="G1175" t="n">
-        <v>0.954911589622498</v>
+        <v>0.954911708831787</v>
       </c>
       <c r="H1175" t="n">
         <v>800</v>
@@ -34473,7 +34473,7 @@
         <v>1.22019994258881</v>
       </c>
       <c r="G1176" t="n">
-        <v>0.953504979610443</v>
+        <v>0.953504920005798</v>
       </c>
       <c r="H1176" t="n">
         <v>1000</v>
@@ -34502,7 +34502,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1177" t="n">
-        <v>0.953348875045776</v>
+        <v>0.953348815441132</v>
       </c>
       <c r="H1177" t="n">
         <v>1300</v>
@@ -34531,7 +34531,7 @@
         <v>1.23479998111725</v>
       </c>
       <c r="G1178" t="n">
-        <v>0.964913964271545</v>
+        <v>0.964913904666901</v>
       </c>
       <c r="H1178" t="n">
         <v>5677</v>
@@ -34560,7 +34560,7 @@
         <v>1.21700000762939</v>
       </c>
       <c r="G1179" t="n">
-        <v>0.951004445552826</v>
+        <v>0.951004385948181</v>
       </c>
       <c r="H1179" t="n">
         <v>1896</v>
@@ -34618,7 +34618,7 @@
         <v>1.23580002784729</v>
       </c>
       <c r="G1181" t="n">
-        <v>0.96569550037384</v>
+        <v>0.965695321559906</v>
       </c>
       <c r="H1181" t="n">
         <v>2300</v>
@@ -34647,7 +34647,7 @@
         <v>1.24399995803833</v>
       </c>
       <c r="G1182" t="n">
-        <v>0.972103118896484</v>
+        <v>0.97210305929184</v>
       </c>
       <c r="H1182" t="n">
         <v>2300</v>
@@ -34676,7 +34676,7 @@
         <v>1.24399995803833</v>
       </c>
       <c r="G1183" t="n">
-        <v>0.972103118896484</v>
+        <v>0.97210305929184</v>
       </c>
       <c r="H1183" t="n">
         <v>1000</v>
@@ -34734,7 +34734,7 @@
         <v>1.20500004291534</v>
       </c>
       <c r="G1185" t="n">
-        <v>0.941627383232117</v>
+        <v>0.941627323627472</v>
       </c>
       <c r="H1185" t="n">
         <v>6534</v>
@@ -34792,7 +34792,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1187" t="n">
-        <v>0.953348875045776</v>
+        <v>0.953348815441132</v>
       </c>
       <c r="H1187" t="n">
         <v>9105</v>
@@ -34821,7 +34821,7 @@
         <v>1.20019996166229</v>
       </c>
       <c r="G1188" t="n">
-        <v>0.937876403331757</v>
+        <v>0.937876462936401</v>
       </c>
       <c r="H1188" t="n">
         <v>10090</v>
@@ -34850,7 +34850,7 @@
         <v>1.22019994258881</v>
       </c>
       <c r="G1189" t="n">
-        <v>0.953504979610443</v>
+        <v>0.953504920005798</v>
       </c>
       <c r="H1189" t="n">
         <v>7534</v>
@@ -34908,7 +34908,7 @@
         <v>1.23959994316101</v>
       </c>
       <c r="G1191" t="n">
-        <v>0.968664884567261</v>
+        <v>0.968664824962616</v>
       </c>
       <c r="H1191" t="n">
         <v>1101</v>
@@ -34966,7 +34966,7 @@
         <v>1.21319997310638</v>
       </c>
       <c r="G1193" t="n">
-        <v>0.94803512096405</v>
+        <v>0.948034882545471</v>
       </c>
       <c r="H1193" t="n">
         <v>5835</v>
@@ -34995,7 +34995,7 @@
         <v>1.22800004482269</v>
       </c>
       <c r="G1194" t="n">
-        <v>0.959600329399109</v>
+        <v>0.959600210189819</v>
       </c>
       <c r="H1194" t="n">
         <v>24707</v>
@@ -35024,7 +35024,7 @@
         <v>1.24279999732971</v>
       </c>
       <c r="G1195" t="n">
-        <v>0.971165418624878</v>
+        <v>0.971165478229523</v>
       </c>
       <c r="H1195" t="n">
         <v>23798</v>
@@ -35053,7 +35053,7 @@
         <v>1.24199998378754</v>
       </c>
       <c r="G1196" t="n">
-        <v>0.970540225505829</v>
+        <v>0.970540285110474</v>
       </c>
       <c r="H1196" t="n">
         <v>22960</v>
@@ -35082,7 +35082,7 @@
         <v>1.24399995803833</v>
       </c>
       <c r="G1197" t="n">
-        <v>0.972103118896484</v>
+        <v>0.97210305929184</v>
       </c>
       <c r="H1197" t="n">
         <v>28501</v>
@@ -35169,7 +35169,7 @@
         <v>1.19120001792908</v>
       </c>
       <c r="G1200" t="n">
-        <v>0.930843353271484</v>
+        <v>0.930843412876129</v>
       </c>
       <c r="H1200" t="n">
         <v>13624</v>
@@ -35198,7 +35198,7 @@
         <v>1.19120001792908</v>
       </c>
       <c r="G1201" t="n">
-        <v>0.930843353271484</v>
+        <v>0.930843412876129</v>
       </c>
       <c r="H1201" t="n">
         <v>0</v>
@@ -35227,7 +35227,7 @@
         <v>1.22940003871918</v>
       </c>
       <c r="G1202" t="n">
-        <v>0.960694253444672</v>
+        <v>0.960694313049316</v>
       </c>
       <c r="H1202" t="n">
         <v>930</v>
@@ -35314,7 +35314,7 @@
         <v>1.24199998378754</v>
       </c>
       <c r="G1205" t="n">
-        <v>0.970540225505829</v>
+        <v>0.970540285110474</v>
       </c>
       <c r="H1205" t="n">
         <v>5811</v>
@@ -35343,7 +35343,7 @@
         <v>1.2117999792099</v>
       </c>
       <c r="G1206" t="n">
-        <v>0.946941077709198</v>
+        <v>0.946941018104553</v>
       </c>
       <c r="H1206" t="n">
         <v>27456</v>
@@ -35372,7 +35372,7 @@
         <v>1.21119999885559</v>
       </c>
       <c r="G1207" t="n">
-        <v>0.946472108364105</v>
+        <v>0.94647216796875</v>
       </c>
       <c r="H1207" t="n">
         <v>11015</v>
@@ -35459,7 +35459,7 @@
         <v>1.19900000095367</v>
       </c>
       <c r="G1210" t="n">
-        <v>0.936938583850861</v>
+        <v>0.93693870306015</v>
       </c>
       <c r="H1210" t="n">
         <v>3</v>
@@ -35488,7 +35488,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G1211" t="n">
-        <v>0.968977391719818</v>
+        <v>0.968977510929108</v>
       </c>
       <c r="H1211" t="n">
         <v>39741</v>
@@ -35517,7 +35517,7 @@
         <v>1.20060002803802</v>
       </c>
       <c r="G1212" t="n">
-        <v>0.938188970088959</v>
+        <v>0.938188910484314</v>
       </c>
       <c r="H1212" t="n">
         <v>13237</v>
@@ -35575,7 +35575,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G1214" t="n">
-        <v>1.02367770671844</v>
+        <v>1.02367758750916</v>
       </c>
       <c r="H1214" t="n">
         <v>84862</v>
@@ -35604,7 +35604,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1215" t="n">
-        <v>0.984605967998505</v>
+        <v>0.984606087207794</v>
       </c>
       <c r="H1215" t="n">
         <v>32688</v>
@@ -35633,7 +35633,7 @@
         <v>1.26579999923706</v>
       </c>
       <c r="G1216" t="n">
-        <v>0.98913848400116</v>
+        <v>0.989138424396515</v>
       </c>
       <c r="H1216" t="n">
         <v>35063</v>
@@ -35691,7 +35691,7 @@
         <v>1.24020004272461</v>
       </c>
       <c r="G1218" t="n">
-        <v>0.969133615493774</v>
+        <v>0.969133853912354</v>
       </c>
       <c r="H1218" t="n">
         <v>4530</v>
@@ -35778,7 +35778,7 @@
         <v>1.25539994239807</v>
       </c>
       <c r="G1221" t="n">
-        <v>0.981011390686035</v>
+        <v>0.981011509895325</v>
       </c>
       <c r="H1221" t="n">
         <v>4670</v>
@@ -35807,7 +35807,7 @@
         <v>1.22599995136261</v>
       </c>
       <c r="G1222" t="n">
-        <v>0.958037376403809</v>
+        <v>0.958037316799164</v>
       </c>
       <c r="H1222" t="n">
         <v>119</v>
@@ -35836,7 +35836,7 @@
         <v>1.22599995136261</v>
       </c>
       <c r="G1223" t="n">
-        <v>0.958037376403809</v>
+        <v>0.958037316799164</v>
       </c>
       <c r="H1223" t="n">
         <v>0</v>
@@ -35865,7 +35865,7 @@
         <v>1.22599995136261</v>
       </c>
       <c r="G1224" t="n">
-        <v>0.958037376403809</v>
+        <v>0.958037316799164</v>
       </c>
       <c r="H1224" t="n">
         <v>0</v>
@@ -35894,7 +35894,7 @@
         <v>1.23039996623993</v>
       </c>
       <c r="G1225" t="n">
-        <v>0.961475729942322</v>
+        <v>0.961475670337677</v>
       </c>
       <c r="H1225" t="n">
         <v>3067</v>
@@ -35952,7 +35952,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1227" t="n">
-        <v>0.937720060348511</v>
+        <v>0.937720239162445</v>
       </c>
       <c r="H1227" t="n">
         <v>6525</v>
@@ -35981,7 +35981,7 @@
         <v>1.17519998550415</v>
       </c>
       <c r="G1228" t="n">
-        <v>0.918340563774109</v>
+        <v>0.918340504169464</v>
       </c>
       <c r="H1228" t="n">
         <v>8221</v>
@@ -36010,7 +36010,7 @@
         <v>1.192999958992</v>
       </c>
       <c r="G1229" t="n">
-        <v>0.932250022888184</v>
+        <v>0.932250082492828</v>
       </c>
       <c r="H1229" t="n">
         <v>712</v>
@@ -36097,7 +36097,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G1232" t="n">
-        <v>0.961163103580475</v>
+        <v>0.96116316318512</v>
       </c>
       <c r="H1232" t="n">
         <v>6056</v>
@@ -36126,7 +36126,7 @@
         <v>1.19159996509552</v>
       </c>
       <c r="G1233" t="n">
-        <v>0.931155979633331</v>
+        <v>0.931156039237976</v>
       </c>
       <c r="H1233" t="n">
         <v>510</v>
@@ -36155,7 +36155,7 @@
         <v>1.19099998474121</v>
       </c>
       <c r="G1234" t="n">
-        <v>0.930687189102173</v>
+        <v>0.930687129497528</v>
       </c>
       <c r="H1234" t="n">
         <v>2006</v>
@@ -36184,7 +36184,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G1235" t="n">
-        <v>0.961163103580475</v>
+        <v>0.96116316318512</v>
       </c>
       <c r="H1235" t="n">
         <v>16103</v>
@@ -36213,7 +36213,7 @@
         <v>1.19799995422363</v>
       </c>
       <c r="G1236" t="n">
-        <v>0.936157166957855</v>
+        <v>0.93615710735321</v>
       </c>
       <c r="H1236" t="n">
         <v>37918</v>
@@ -36242,7 +36242,7 @@
         <v>1.23800003528595</v>
       </c>
       <c r="G1237" t="n">
-        <v>0.967414736747742</v>
+        <v>0.967414557933807</v>
       </c>
       <c r="H1237" t="n">
         <v>7311</v>
@@ -36271,7 +36271,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1238" t="n">
-        <v>0.953348875045776</v>
+        <v>0.953348815441132</v>
       </c>
       <c r="H1238" t="n">
         <v>3720</v>
@@ -36300,7 +36300,7 @@
         <v>1.26800000667572</v>
       </c>
       <c r="G1239" t="n">
-        <v>0.990857481956482</v>
+        <v>0.990857660770416</v>
       </c>
       <c r="H1239" t="n">
         <v>129144</v>
@@ -36358,7 +36358,7 @@
         <v>1.27320003509521</v>
       </c>
       <c r="G1241" t="n">
-        <v>0.994921028614044</v>
+        <v>0.994920969009399</v>
       </c>
       <c r="H1241" t="n">
         <v>41792</v>
@@ -36387,7 +36387,7 @@
         <v>1.27320003509521</v>
       </c>
       <c r="G1242" t="n">
-        <v>0.994921028614044</v>
+        <v>0.994920969009399</v>
       </c>
       <c r="H1242" t="n">
         <v>13700</v>
@@ -36445,7 +36445,7 @@
         <v>1.26639997959137</v>
       </c>
       <c r="G1244" t="n">
-        <v>0.989607214927673</v>
+        <v>0.989607334136963</v>
       </c>
       <c r="H1244" t="n">
         <v>32132</v>
@@ -36503,7 +36503,7 @@
         <v>1.46099996566772</v>
       </c>
       <c r="G1246" t="n">
-        <v>1.14167416095734</v>
+        <v>1.14167428016663</v>
       </c>
       <c r="H1246" t="n">
         <v>196814</v>
@@ -36532,7 +36532,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G1247" t="n">
-        <v>1.24247920513153</v>
+        <v>1.24247908592224</v>
       </c>
       <c r="H1247" t="n">
         <v>197270</v>
@@ -36590,7 +36590,7 @@
         <v>1.59200000762939</v>
       </c>
       <c r="G1249" t="n">
-        <v>1.24404191970825</v>
+        <v>1.24404203891754</v>
       </c>
       <c r="H1249" t="n">
         <v>77714</v>
@@ -36648,7 +36648,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G1251" t="n">
-        <v>1.31280815601349</v>
+        <v>1.3128080368042</v>
       </c>
       <c r="H1251" t="n">
         <v>57237</v>
@@ -36677,7 +36677,7 @@
         <v>1.67980003356934</v>
       </c>
       <c r="G1252" t="n">
-        <v>1.31265187263489</v>
+        <v>1.3126517534256</v>
       </c>
       <c r="H1252" t="n">
         <v>36963</v>
@@ -36706,7 +36706,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G1253" t="n">
-        <v>1.31280815601349</v>
+        <v>1.3128080368042</v>
       </c>
       <c r="H1253" t="n">
         <v>6137</v>
@@ -36735,7 +36735,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1254" t="n">
-        <v>1.30499386787415</v>
+        <v>1.30499374866486</v>
       </c>
       <c r="H1254" t="n">
         <v>28012</v>
@@ -36764,7 +36764,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G1255" t="n">
-        <v>1.31280815601349</v>
+        <v>1.3128080368042</v>
       </c>
       <c r="H1255" t="n">
         <v>9259</v>
@@ -36822,7 +36822,7 @@
         <v>1.72500002384186</v>
       </c>
       <c r="G1257" t="n">
-        <v>1.34797263145447</v>
+        <v>1.34797275066376</v>
       </c>
       <c r="H1257" t="n">
         <v>18428</v>
@@ -36967,7 +36967,7 @@
         <v>1.74119997024536</v>
       </c>
       <c r="G1262" t="n">
-        <v>1.36063182353973</v>
+        <v>1.36063170433044</v>
       </c>
       <c r="H1262" t="n">
         <v>7273</v>
@@ -37083,7 +37083,7 @@
         <v>1.72940003871918</v>
       </c>
       <c r="G1266" t="n">
-        <v>1.35141098499298</v>
+        <v>1.35141086578369</v>
       </c>
       <c r="H1266" t="n">
         <v>28267</v>
@@ -37112,7 +37112,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G1267" t="n">
-        <v>1.3909512758255</v>
+        <v>1.39095151424408</v>
       </c>
       <c r="H1267" t="n">
         <v>141202</v>
@@ -37141,7 +37141,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G1268" t="n">
-        <v>1.45658135414124</v>
+        <v>1.45658147335052</v>
       </c>
       <c r="H1268" t="n">
         <v>42786</v>
@@ -37170,7 +37170,7 @@
         <v>1.74979996681213</v>
       </c>
       <c r="G1269" t="n">
-        <v>1.46478497982025</v>
+        <v>1.46478509902954</v>
       </c>
       <c r="H1269" t="n">
         <v>33596</v>
@@ -37228,7 +37228,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G1271" t="n">
-        <v>1.45658135414124</v>
+        <v>1.45658147335052</v>
       </c>
       <c r="H1271" t="n">
         <v>53971</v>
@@ -37489,7 +37489,7 @@
         <v>1.66600000858307</v>
       </c>
       <c r="G1280" t="n">
-        <v>1.39463472366333</v>
+        <v>1.39463484287262</v>
       </c>
       <c r="H1280" t="n">
         <v>32262</v>
@@ -37518,7 +37518,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G1281" t="n">
-        <v>1.37286972999573</v>
+        <v>1.37286984920502</v>
       </c>
       <c r="H1281" t="n">
         <v>16602</v>
@@ -37634,7 +37634,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G1285" t="n">
-        <v>1.37286972999573</v>
+        <v>1.37286984920502</v>
       </c>
       <c r="H1285" t="n">
         <v>21352</v>
@@ -37663,7 +37663,7 @@
         <v>1.60060000419617</v>
       </c>
       <c r="G1286" t="n">
-        <v>1.33988749980927</v>
+        <v>1.33988761901855</v>
       </c>
       <c r="H1286" t="n">
         <v>27968</v>
@@ -37721,7 +37721,7 @@
         <v>1.60199999809265</v>
       </c>
       <c r="G1288" t="n">
-        <v>1.34105932712555</v>
+        <v>1.34105944633484</v>
       </c>
       <c r="H1288" t="n">
         <v>26307</v>
@@ -37866,7 +37866,7 @@
         <v>1.60199999809265</v>
       </c>
       <c r="G1293" t="n">
-        <v>1.34105932712555</v>
+        <v>1.34105944633484</v>
       </c>
       <c r="H1293" t="n">
         <v>1484</v>
@@ -38040,7 +38040,7 @@
         <v>1.77939999103546</v>
       </c>
       <c r="G1299" t="n">
-        <v>1.48956370353699</v>
+        <v>1.48956382274628</v>
       </c>
       <c r="H1299" t="n">
         <v>20620</v>
@@ -38069,7 +38069,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G1300" t="n">
-        <v>1.49006593227386</v>
+        <v>1.49006605148315</v>
       </c>
       <c r="H1300" t="n">
         <v>15871</v>
@@ -38127,7 +38127,7 @@
         <v>1.7688000202179</v>
       </c>
       <c r="G1302" t="n">
-        <v>1.48069036006927</v>
+        <v>1.48069024085999</v>
       </c>
       <c r="H1302" t="n">
         <v>40491</v>
@@ -38185,7 +38185,7 @@
         <v>1.74399995803833</v>
       </c>
       <c r="G1304" t="n">
-        <v>1.45992982387543</v>
+        <v>1.45992970466614</v>
       </c>
       <c r="H1304" t="n">
         <v>70208</v>
@@ -38417,7 +38417,7 @@
         <v>1.88979995250702</v>
       </c>
       <c r="G1312" t="n">
-        <v>1.58198118209839</v>
+        <v>1.58198130130768</v>
       </c>
       <c r="H1312" t="n">
         <v>7026</v>
@@ -38591,7 +38591,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G1318" t="n">
-        <v>1.62400460243225</v>
+        <v>1.62400448322296</v>
       </c>
       <c r="H1318" t="n">
         <v>11052</v>
@@ -38620,7 +38620,7 @@
         <v>1.97979998588562</v>
       </c>
       <c r="G1319" t="n">
-        <v>1.65732181072235</v>
+        <v>1.65732169151306</v>
       </c>
       <c r="H1319" t="n">
         <v>18867</v>
@@ -38678,7 +38678,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G1321" t="n">
-        <v>1.65748918056488</v>
+        <v>1.65748906135559</v>
       </c>
       <c r="H1321" t="n">
         <v>17248</v>
@@ -38736,7 +38736,7 @@
         <v>1.96440005302429</v>
       </c>
       <c r="G1323" t="n">
-        <v>1.64443016052246</v>
+        <v>1.64443004131317</v>
       </c>
       <c r="H1323" t="n">
         <v>7944</v>
@@ -38794,7 +38794,7 @@
         <v>1.92120003700256</v>
       </c>
       <c r="G1325" t="n">
-        <v>1.60826683044434</v>
+        <v>1.60826671123505</v>
       </c>
       <c r="H1325" t="n">
         <v>17616</v>
@@ -38910,7 +38910,7 @@
         <v>1.95959997177124</v>
       </c>
       <c r="G1329" t="n">
-        <v>1.64041197299957</v>
+        <v>1.64041185379028</v>
       </c>
       <c r="H1329" t="n">
         <v>3100</v>
@@ -39374,7 +39374,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G1345" t="n">
-        <v>1.65748918056488</v>
+        <v>1.65748906135559</v>
       </c>
       <c r="H1345" t="n">
         <v>50151</v>
@@ -39490,7 +39490,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G1349" t="n">
-        <v>1.65748918056488</v>
+        <v>1.65748906135559</v>
       </c>
       <c r="H1349" t="n">
         <v>45371</v>
@@ -39606,7 +39606,7 @@
         <v>1.85500001907349</v>
       </c>
       <c r="G1353" t="n">
-        <v>1.552849650383</v>
+        <v>1.55284976959229</v>
       </c>
       <c r="H1353" t="n">
         <v>21990</v>
@@ -39635,7 +39635,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G1354" t="n">
-        <v>1.59051990509033</v>
+        <v>1.59051978588104</v>
       </c>
       <c r="H1354" t="n">
         <v>15319</v>
@@ -39722,7 +39722,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G1357" t="n">
-        <v>1.55703520774841</v>
+        <v>1.5570353269577</v>
       </c>
       <c r="H1357" t="n">
         <v>10646</v>
@@ -39809,7 +39809,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G1360" t="n">
-        <v>1.59051990509033</v>
+        <v>1.59051978588104</v>
       </c>
       <c r="H1360" t="n">
         <v>13059</v>
@@ -39867,7 +39867,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G1362" t="n">
-        <v>1.59051990509033</v>
+        <v>1.59051978588104</v>
       </c>
       <c r="H1362" t="n">
         <v>7070</v>
@@ -39925,7 +39925,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G1364" t="n">
-        <v>1.59051990509033</v>
+        <v>1.59051978588104</v>
       </c>
       <c r="H1364" t="n">
         <v>4035</v>
@@ -39954,7 +39954,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G1365" t="n">
-        <v>1.59051990509033</v>
+        <v>1.59051978588104</v>
       </c>
       <c r="H1365" t="n">
         <v>1022</v>
@@ -39983,7 +39983,7 @@
         <v>1.85500001907349</v>
       </c>
       <c r="G1366" t="n">
-        <v>1.552849650383</v>
+        <v>1.55284976959229</v>
       </c>
       <c r="H1366" t="n">
         <v>32969</v>
@@ -40041,7 +40041,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G1368" t="n">
-        <v>1.59051990509033</v>
+        <v>1.59051978588104</v>
       </c>
       <c r="H1368" t="n">
         <v>25050</v>
@@ -40070,7 +40070,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G1369" t="n">
-        <v>1.55703520774841</v>
+        <v>1.5570353269577</v>
       </c>
       <c r="H1369" t="n">
         <v>6264</v>
@@ -40128,7 +40128,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G1371" t="n">
-        <v>1.55703520774841</v>
+        <v>1.5570353269577</v>
       </c>
       <c r="H1371" t="n">
         <v>5678</v>
@@ -40244,7 +40244,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G1375" t="n">
-        <v>1.55703520774841</v>
+        <v>1.5570353269577</v>
       </c>
       <c r="H1375" t="n">
         <v>5724</v>
@@ -40360,7 +40360,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G1379" t="n">
-        <v>1.89188170433044</v>
+        <v>1.89188158512115</v>
       </c>
       <c r="H1379" t="n">
         <v>317280</v>
@@ -40389,7 +40389,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1380" t="n">
-        <v>1.80817019939423</v>
+        <v>1.80817008018494</v>
       </c>
       <c r="H1380" t="n">
         <v>114976</v>
@@ -40708,7 +40708,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1391" t="n">
-        <v>1.80817019939423</v>
+        <v>1.80817008018494</v>
       </c>
       <c r="H1391" t="n">
         <v>20155</v>
@@ -40737,7 +40737,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G1392" t="n">
-        <v>1.76631414890289</v>
+        <v>1.76631426811218</v>
       </c>
       <c r="H1392" t="n">
         <v>3519</v>
@@ -40766,7 +40766,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1393" t="n">
-        <v>1.80817019939423</v>
+        <v>1.80817008018494</v>
       </c>
       <c r="H1393" t="n">
         <v>10650</v>
@@ -40911,7 +40911,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G1398" t="n">
-        <v>1.76631414890289</v>
+        <v>1.76631426811218</v>
       </c>
       <c r="H1398" t="n">
         <v>4485</v>
@@ -41201,7 +41201,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G1408" t="n">
-        <v>1.70771610736847</v>
+        <v>1.70771598815918</v>
       </c>
       <c r="H1408" t="n">
         <v>1758</v>
@@ -41288,7 +41288,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G1411" t="n">
-        <v>1.70771610736847</v>
+        <v>1.70771598815918</v>
       </c>
       <c r="H1411" t="n">
         <v>36540</v>
@@ -41404,7 +41404,7 @@
         <v>1.99500000476837</v>
       </c>
       <c r="G1415" t="n">
-        <v>1.67004585266113</v>
+        <v>1.67004597187042</v>
       </c>
       <c r="H1415" t="n">
         <v>1050</v>
@@ -41433,7 +41433,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G1416" t="n">
-        <v>1.65748918056488</v>
+        <v>1.65748906135559</v>
       </c>
       <c r="H1416" t="n">
         <v>5</v>
@@ -41520,7 +41520,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G1419" t="n">
-        <v>1.77468526363373</v>
+        <v>1.77468514442444</v>
       </c>
       <c r="H1419" t="n">
         <v>15638</v>
@@ -41578,7 +41578,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1421" t="n">
-        <v>1.80817019939423</v>
+        <v>1.80817008018494</v>
       </c>
       <c r="H1421" t="n">
         <v>41767</v>
@@ -41723,7 +41723,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G1426" t="n">
-        <v>1.83328354358673</v>
+        <v>1.83328366279602</v>
       </c>
       <c r="H1426" t="n">
         <v>5861</v>
@@ -41839,7 +41839,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G1430" t="n">
-        <v>1.83328354358673</v>
+        <v>1.83328366279602</v>
       </c>
       <c r="H1430" t="n">
         <v>2450</v>
@@ -42187,7 +42187,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1442" t="n">
-        <v>1.80817019939423</v>
+        <v>1.80817008018494</v>
       </c>
       <c r="H1442" t="n">
         <v>3900</v>
@@ -42216,7 +42216,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G1443" t="n">
-        <v>1.83328354358673</v>
+        <v>1.83328366279602</v>
       </c>
       <c r="H1443" t="n">
         <v>7310</v>
@@ -42245,7 +42245,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G1444" t="n">
-        <v>1.83328354358673</v>
+        <v>1.83328366279602</v>
       </c>
       <c r="H1444" t="n">
         <v>0</v>
@@ -42361,7 +42361,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G1448" t="n">
-        <v>1.76631414890289</v>
+        <v>1.76631426811218</v>
       </c>
       <c r="H1448" t="n">
         <v>6157</v>
@@ -42506,7 +42506,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G1453" t="n">
-        <v>1.77468526363373</v>
+        <v>1.77468514442444</v>
       </c>
       <c r="H1453" t="n">
         <v>5250</v>
@@ -42593,7 +42593,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G1456" t="n">
-        <v>1.83328354358673</v>
+        <v>1.83328366279602</v>
       </c>
       <c r="H1456" t="n">
         <v>33296</v>
@@ -43086,7 +43086,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G1473" t="n">
-        <v>2.13464522361755</v>
+        <v>2.13464498519897</v>
       </c>
       <c r="H1473" t="n">
         <v>33269</v>
@@ -43115,7 +43115,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G1474" t="n">
-        <v>2.10953187942505</v>
+        <v>2.10953164100647</v>
       </c>
       <c r="H1474" t="n">
         <v>11143</v>
@@ -43202,7 +43202,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G1477" t="n">
-        <v>2.18487191200256</v>
+        <v>2.18487215042114</v>
       </c>
       <c r="H1477" t="n">
         <v>44426</v>
@@ -43405,7 +43405,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G1484" t="n">
-        <v>2.18487191200256</v>
+        <v>2.18487215042114</v>
       </c>
       <c r="H1484" t="n">
         <v>432</v>
@@ -43434,7 +43434,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G1485" t="n">
-        <v>2.18487191200256</v>
+        <v>2.18487215042114</v>
       </c>
       <c r="H1485" t="n">
         <v>5778</v>
@@ -43463,7 +43463,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G1486" t="n">
-        <v>2.18487191200256</v>
+        <v>2.18487215042114</v>
       </c>
       <c r="H1486" t="n">
         <v>5915</v>
@@ -43492,7 +43492,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G1487" t="n">
-        <v>2.18487191200256</v>
+        <v>2.18487215042114</v>
       </c>
       <c r="H1487" t="n">
         <v>4544</v>
@@ -43608,7 +43608,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G1491" t="n">
-        <v>2.13464522361755</v>
+        <v>2.13464498519897</v>
       </c>
       <c r="H1491" t="n">
         <v>11546</v>
@@ -43724,7 +43724,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G1495" t="n">
-        <v>2.26021265983582</v>
+        <v>2.26021242141724</v>
       </c>
       <c r="H1495" t="n">
         <v>31872</v>
@@ -43985,7 +43985,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G1504" t="n">
-        <v>2.24346995353699</v>
+        <v>2.24347019195557</v>
       </c>
       <c r="H1504" t="n">
         <v>44721</v>
@@ -44101,7 +44101,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G1508" t="n">
-        <v>2.26021265983582</v>
+        <v>2.26021242141724</v>
       </c>
       <c r="H1508" t="n">
         <v>11295</v>
@@ -44159,7 +44159,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G1510" t="n">
-        <v>2.26021265983582</v>
+        <v>2.26021242141724</v>
       </c>
       <c r="H1510" t="n">
         <v>3332</v>
@@ -44333,7 +44333,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G1516" t="n">
-        <v>2.26021265983582</v>
+        <v>2.26021242141724</v>
       </c>
       <c r="H1516" t="n">
         <v>39885</v>
@@ -44362,7 +44362,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G1517" t="n">
-        <v>2.5448317527771</v>
+        <v>2.54483199119568</v>
       </c>
       <c r="H1517" t="n">
         <v>82221</v>
@@ -44391,7 +44391,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G1518" t="n">
-        <v>2.62017250061035</v>
+        <v>2.62017226219177</v>
       </c>
       <c r="H1518" t="n">
         <v>151266</v>
@@ -44449,7 +44449,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G1520" t="n">
-        <v>2.67039942741394</v>
+        <v>2.67039918899536</v>
       </c>
       <c r="H1520" t="n">
         <v>70441</v>
@@ -44478,7 +44478,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G1521" t="n">
-        <v>2.71225523948669</v>
+        <v>2.71225500106812</v>
       </c>
       <c r="H1521" t="n">
         <v>58192</v>
@@ -44652,7 +44652,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G1527" t="n">
-        <v>3.10569930076599</v>
+        <v>3.10569953918457</v>
       </c>
       <c r="H1527" t="n">
         <v>40326</v>
@@ -44884,7 +44884,7 @@
         <v>3.5</v>
       </c>
       <c r="G1535" t="n">
-        <v>2.92990493774414</v>
+        <v>2.92990517616272</v>
       </c>
       <c r="H1535" t="n">
         <v>5651</v>
@@ -44913,7 +44913,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G1536" t="n">
-        <v>2.89642071723938</v>
+        <v>2.8964204788208</v>
       </c>
       <c r="H1536" t="n">
         <v>9495</v>
@@ -44971,7 +44971,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1538" t="n">
-        <v>2.84619355201721</v>
+        <v>2.84619379043579</v>
       </c>
       <c r="H1538" t="n">
         <v>13330</v>
@@ -45087,7 +45087,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G1542" t="n">
-        <v>2.89642071723938</v>
+        <v>2.8964204788208</v>
       </c>
       <c r="H1542" t="n">
         <v>56699</v>
@@ -45348,7 +45348,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G1551" t="n">
-        <v>3.22289562225342</v>
+        <v>3.22289538383484</v>
       </c>
       <c r="H1551" t="n">
         <v>94238</v>
@@ -80096,6 +80096,35 @@
         <v>1001</v>
       </c>
       <c r="I2749" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2750">
+      <c r="A2750" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2750" s="1" t="n">
+        <v>46321.3333333333</v>
+      </c>
+      <c r="C2750" t="n">
+        <v>0.398000001907349</v>
+      </c>
+      <c r="D2750" t="n">
+        <v>0.400000005960464</v>
+      </c>
+      <c r="E2750" t="n">
+        <v>0.398000001907349</v>
+      </c>
+      <c r="F2750" t="n">
+        <v>0.400000005960464</v>
+      </c>
+      <c r="G2750" t="n">
+        <v>0.400000005960464</v>
+      </c>
+      <c r="H2750" t="n">
+        <v>11003</v>
+      </c>
+      <c r="I2750" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ZUC.MI.xlsx
+++ b/data/ZUC.MI.xlsx
@@ -427,7 +427,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G2" t="n">
-        <v>3.01633310317993</v>
+        <v>3.01633286476135</v>
       </c>
       <c r="H2" t="n">
         <v>42345</v>
@@ -485,7 +485,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G4" t="n">
-        <v>2.96163272857666</v>
+        <v>2.96163249015808</v>
       </c>
       <c r="H4" t="n">
         <v>12680</v>
@@ -514,7 +514,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G5" t="n">
-        <v>2.85223197937012</v>
+        <v>2.85223174095154</v>
       </c>
       <c r="H5" t="n">
         <v>41852</v>
@@ -601,7 +601,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G8" t="n">
-        <v>2.85223197937012</v>
+        <v>2.85223174095154</v>
       </c>
       <c r="H8" t="n">
         <v>11271</v>
@@ -630,7 +630,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G9" t="n">
-        <v>2.85223197937012</v>
+        <v>2.85223174095154</v>
       </c>
       <c r="H9" t="n">
         <v>22577</v>
@@ -688,7 +688,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G11" t="n">
-        <v>2.77408838272095</v>
+        <v>2.77408885955811</v>
       </c>
       <c r="H11" t="n">
         <v>14530</v>
@@ -775,7 +775,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G14" t="n">
-        <v>2.39900040626526</v>
+        <v>2.39900064468384</v>
       </c>
       <c r="H14" t="n">
         <v>17223</v>
@@ -833,7 +833,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G16" t="n">
-        <v>2.39118599891663</v>
+        <v>2.39118623733521</v>
       </c>
       <c r="H16" t="n">
         <v>21477</v>
@@ -978,7 +978,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G21" t="n">
-        <v>2.3286714553833</v>
+        <v>2.32867169380188</v>
       </c>
       <c r="H21" t="n">
         <v>6070</v>
@@ -1007,7 +1007,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G22" t="n">
-        <v>2.30522847175598</v>
+        <v>2.30522871017456</v>
       </c>
       <c r="H22" t="n">
         <v>7688</v>
@@ -1065,7 +1065,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G24" t="n">
-        <v>2.16457056999207</v>
+        <v>2.16457033157349</v>
       </c>
       <c r="H24" t="n">
         <v>15034</v>
@@ -1094,7 +1094,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G25" t="n">
-        <v>1.78948259353638</v>
+        <v>1.78948247432709</v>
       </c>
       <c r="H25" t="n">
         <v>29015</v>
@@ -1210,7 +1210,7 @@
         <v>1</v>
       </c>
       <c r="G29" t="n">
-        <v>0.781433403491974</v>
+        <v>0.781433463096619</v>
       </c>
       <c r="H29" t="n">
         <v>16056</v>
@@ -1268,7 +1268,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G31" t="n">
-        <v>1.71915352344513</v>
+        <v>1.71915376186371</v>
       </c>
       <c r="H31" t="n">
         <v>23390</v>
@@ -1297,7 +1297,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G32" t="n">
-        <v>1.64101004600525</v>
+        <v>1.64101016521454</v>
       </c>
       <c r="H32" t="n">
         <v>80086</v>
@@ -1442,7 +1442,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G37" t="n">
-        <v>2.71157383918762</v>
+        <v>2.7115740776062</v>
       </c>
       <c r="H37" t="n">
         <v>25045</v>
@@ -1500,7 +1500,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G39" t="n">
-        <v>2.44588661193848</v>
+        <v>2.44588685035706</v>
       </c>
       <c r="H39" t="n">
         <v>23320</v>
@@ -1529,7 +1529,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G40" t="n">
-        <v>2.37555766105652</v>
+        <v>2.37555742263794</v>
       </c>
       <c r="H40" t="n">
         <v>26653</v>
@@ -1587,7 +1587,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G42" t="n">
-        <v>2.45370078086853</v>
+        <v>2.45370101928711</v>
       </c>
       <c r="H42" t="n">
         <v>6497</v>
@@ -1674,7 +1674,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G45" t="n">
-        <v>2.77408838272095</v>
+        <v>2.77408885955811</v>
       </c>
       <c r="H45" t="n">
         <v>276654</v>
@@ -1761,7 +1761,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G48" t="n">
-        <v>2.52402973175049</v>
+        <v>2.52402997016907</v>
       </c>
       <c r="H48" t="n">
         <v>14408</v>
@@ -1848,7 +1848,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G51" t="n">
-        <v>2.54747271537781</v>
+        <v>2.54747295379639</v>
       </c>
       <c r="H51" t="n">
         <v>16194</v>
@@ -2080,7 +2080,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G59" t="n">
-        <v>2.22708535194397</v>
+        <v>2.22708511352539</v>
       </c>
       <c r="H59" t="n">
         <v>10942</v>
@@ -2109,7 +2109,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G60" t="n">
-        <v>2.15675640106201</v>
+        <v>2.15675616264343</v>
       </c>
       <c r="H60" t="n">
         <v>5903</v>
@@ -2138,7 +2138,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G61" t="n">
-        <v>2.08642745018005</v>
+        <v>2.08642721176147</v>
       </c>
       <c r="H61" t="n">
         <v>24791</v>
@@ -2167,7 +2167,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G62" t="n">
-        <v>2.05517029762268</v>
+        <v>2.0551700592041</v>
       </c>
       <c r="H62" t="n">
         <v>7073</v>
@@ -2196,7 +2196,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G63" t="n">
-        <v>2.07079839706421</v>
+        <v>2.07079863548279</v>
       </c>
       <c r="H63" t="n">
         <v>3910</v>
@@ -2254,7 +2254,7 @@
         <v>2.5</v>
       </c>
       <c r="G65" t="n">
-        <v>1.95358347892761</v>
+        <v>1.95358335971832</v>
       </c>
       <c r="H65" t="n">
         <v>4420</v>
@@ -2283,7 +2283,7 @@
         <v>2.5</v>
       </c>
       <c r="G66" t="n">
-        <v>1.95358347892761</v>
+        <v>1.95358335971832</v>
       </c>
       <c r="H66" t="n">
         <v>8536</v>
@@ -2312,7 +2312,7 @@
         <v>2.5</v>
       </c>
       <c r="G67" t="n">
-        <v>1.95358347892761</v>
+        <v>1.95358335971832</v>
       </c>
       <c r="H67" t="n">
         <v>400</v>
@@ -2341,7 +2341,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G68" t="n">
-        <v>1.86762571334839</v>
+        <v>1.86762595176697</v>
       </c>
       <c r="H68" t="n">
         <v>5688</v>
@@ -2370,7 +2370,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G69" t="n">
-        <v>1.83636856079102</v>
+        <v>1.83636832237244</v>
       </c>
       <c r="H69" t="n">
         <v>7190</v>
@@ -2399,7 +2399,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G70" t="n">
-        <v>1.82073962688446</v>
+        <v>1.82073974609375</v>
       </c>
       <c r="H70" t="n">
         <v>19067</v>
@@ -2428,7 +2428,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G71" t="n">
-        <v>1.81292545795441</v>
+        <v>1.8129255771637</v>
       </c>
       <c r="H71" t="n">
         <v>7528</v>
@@ -2457,7 +2457,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G72" t="n">
-        <v>1.80511116981506</v>
+        <v>1.80511105060577</v>
       </c>
       <c r="H72" t="n">
         <v>6071</v>
@@ -2515,7 +2515,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G74" t="n">
-        <v>1.91451215744019</v>
+        <v>1.91451179981232</v>
       </c>
       <c r="H74" t="n">
         <v>27553</v>
@@ -2544,7 +2544,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G75" t="n">
-        <v>1.84418261051178</v>
+        <v>1.84418284893036</v>
       </c>
       <c r="H75" t="n">
         <v>12321</v>
@@ -2573,7 +2573,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G76" t="n">
-        <v>1.87544047832489</v>
+        <v>1.87544012069702</v>
       </c>
       <c r="H76" t="n">
         <v>16625</v>
@@ -2602,7 +2602,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G77" t="n">
-        <v>1.80511116981506</v>
+        <v>1.80511105060577</v>
       </c>
       <c r="H77" t="n">
         <v>15224</v>
@@ -2631,7 +2631,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G78" t="n">
-        <v>1.77385365962982</v>
+        <v>1.7738538980484</v>
       </c>
       <c r="H78" t="n">
         <v>12767</v>
@@ -2660,7 +2660,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G79" t="n">
-        <v>1.7504106760025</v>
+        <v>1.75041079521179</v>
       </c>
       <c r="H79" t="n">
         <v>18881</v>
@@ -2689,7 +2689,7 @@
         <v>2.25</v>
       </c>
       <c r="G80" t="n">
-        <v>1.75822520256042</v>
+        <v>1.75822496414185</v>
       </c>
       <c r="H80" t="n">
         <v>4825</v>
@@ -2718,7 +2718,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G81" t="n">
-        <v>1.7504106760025</v>
+        <v>1.75041079521179</v>
       </c>
       <c r="H81" t="n">
         <v>11995</v>
@@ -2747,7 +2747,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G82" t="n">
-        <v>1.85981178283691</v>
+        <v>1.85981154441833</v>
       </c>
       <c r="H82" t="n">
         <v>17718</v>
@@ -2776,7 +2776,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G83" t="n">
-        <v>1.85981178283691</v>
+        <v>1.85981154441833</v>
       </c>
       <c r="H83" t="n">
         <v>1959</v>
@@ -2805,7 +2805,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G84" t="n">
-        <v>1.85981178283691</v>
+        <v>1.85981154441833</v>
       </c>
       <c r="H84" t="n">
         <v>1535</v>
@@ -2834,7 +2834,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G85" t="n">
-        <v>1.83636856079102</v>
+        <v>1.83636832237244</v>
       </c>
       <c r="H85" t="n">
         <v>1560</v>
@@ -2863,7 +2863,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G86" t="n">
-        <v>1.78166818618774</v>
+        <v>1.78166806697845</v>
       </c>
       <c r="H86" t="n">
         <v>2070</v>
@@ -2950,7 +2950,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G89" t="n">
-        <v>1.78948259353638</v>
+        <v>1.78948247432709</v>
       </c>
       <c r="H89" t="n">
         <v>13120</v>
@@ -2979,7 +2979,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G90" t="n">
-        <v>1.70352482795715</v>
+        <v>1.70352494716644</v>
       </c>
       <c r="H90" t="n">
         <v>5489</v>
@@ -3008,7 +3008,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G91" t="n">
-        <v>1.71915352344513</v>
+        <v>1.71915376186371</v>
       </c>
       <c r="H91" t="n">
         <v>12134</v>
@@ -3066,7 +3066,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G93" t="n">
-        <v>1.70352482795715</v>
+        <v>1.70352494716644</v>
       </c>
       <c r="H93" t="n">
         <v>5250</v>
@@ -3095,7 +3095,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G94" t="n">
-        <v>1.69571053981781</v>
+        <v>1.69571042060852</v>
       </c>
       <c r="H94" t="n">
         <v>7592</v>
@@ -3124,7 +3124,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G95" t="n">
-        <v>1.71915352344513</v>
+        <v>1.71915376186371</v>
       </c>
       <c r="H95" t="n">
         <v>1431</v>
@@ -3182,7 +3182,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G97" t="n">
-        <v>1.71915352344513</v>
+        <v>1.71915376186371</v>
       </c>
       <c r="H97" t="n">
         <v>10382</v>
@@ -3211,7 +3211,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G98" t="n">
-        <v>2.21927094459534</v>
+        <v>2.21927070617676</v>
       </c>
       <c r="H98" t="n">
         <v>189197</v>
@@ -3240,7 +3240,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G99" t="n">
-        <v>2.26615715026855</v>
+        <v>2.26615691184998</v>
       </c>
       <c r="H99" t="n">
         <v>221937</v>
@@ -3269,7 +3269,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G100" t="n">
-        <v>2.08642745018005</v>
+        <v>2.08642721176147</v>
       </c>
       <c r="H100" t="n">
         <v>131201</v>
@@ -3385,7 +3385,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G104" t="n">
-        <v>1.93795502185822</v>
+        <v>1.93795490264893</v>
       </c>
       <c r="H104" t="n">
         <v>28640</v>
@@ -3414,7 +3414,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G105" t="n">
-        <v>1.88325464725494</v>
+        <v>1.88325452804565</v>
       </c>
       <c r="H105" t="n">
         <v>30798</v>
@@ -3472,7 +3472,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G107" t="n">
-        <v>1.74259662628174</v>
+        <v>1.74259638786316</v>
       </c>
       <c r="H107" t="n">
         <v>29505</v>
@@ -3501,7 +3501,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G108" t="n">
-        <v>1.71915352344513</v>
+        <v>1.71915376186371</v>
       </c>
       <c r="H108" t="n">
         <v>19258</v>
@@ -3530,7 +3530,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G109" t="n">
-        <v>1.71133935451508</v>
+        <v>1.71133947372437</v>
       </c>
       <c r="H109" t="n">
         <v>13938</v>
@@ -3559,7 +3559,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G110" t="n">
-        <v>1.71915352344513</v>
+        <v>1.71915376186371</v>
       </c>
       <c r="H110" t="n">
         <v>31434</v>
@@ -3588,7 +3588,7 @@
         <v>2.25</v>
       </c>
       <c r="G111" t="n">
-        <v>1.75822520256042</v>
+        <v>1.75822496414185</v>
       </c>
       <c r="H111" t="n">
         <v>12997</v>
@@ -3617,7 +3617,7 @@
         <v>2.25</v>
       </c>
       <c r="G112" t="n">
-        <v>1.75822520256042</v>
+        <v>1.75822496414185</v>
       </c>
       <c r="H112" t="n">
         <v>6892</v>
@@ -3646,7 +3646,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G113" t="n">
-        <v>1.69571053981781</v>
+        <v>1.69571042060852</v>
       </c>
       <c r="H113" t="n">
         <v>7676</v>
@@ -3704,7 +3704,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G115" t="n">
-        <v>1.58630979061127</v>
+        <v>1.58630967140198</v>
       </c>
       <c r="H115" t="n">
         <v>15973</v>
@@ -3733,7 +3733,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G116" t="n">
-        <v>1.60193848609924</v>
+        <v>1.60193836688995</v>
       </c>
       <c r="H116" t="n">
         <v>15987</v>
@@ -3791,7 +3791,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G118" t="n">
-        <v>1.54723811149597</v>
+        <v>1.54723823070526</v>
       </c>
       <c r="H118" t="n">
         <v>2966</v>
@@ -3820,7 +3820,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G119" t="n">
-        <v>1.64101004600525</v>
+        <v>1.64101016521454</v>
       </c>
       <c r="H119" t="n">
         <v>7103</v>
@@ -3965,7 +3965,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G124" t="n">
-        <v>1.46909487247467</v>
+        <v>1.46909475326538</v>
       </c>
       <c r="H124" t="n">
         <v>33327</v>
@@ -4139,7 +4139,7 @@
         <v>2.25</v>
       </c>
       <c r="G130" t="n">
-        <v>1.75822520256042</v>
+        <v>1.75822496414185</v>
       </c>
       <c r="H130" t="n">
         <v>83797</v>
@@ -4313,7 +4313,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G136" t="n">
-        <v>1.41439437866211</v>
+        <v>1.4143944978714</v>
       </c>
       <c r="H136" t="n">
         <v>17202</v>
@@ -4371,7 +4371,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G138" t="n">
-        <v>1.41439437866211</v>
+        <v>1.4143944978714</v>
       </c>
       <c r="H138" t="n">
         <v>9467</v>
@@ -4429,7 +4429,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G140" t="n">
-        <v>1.41439437866211</v>
+        <v>1.4143944978714</v>
       </c>
       <c r="H140" t="n">
         <v>22023</v>
@@ -4458,7 +4458,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G141" t="n">
-        <v>1.47690916061401</v>
+        <v>1.47690904140472</v>
       </c>
       <c r="H141" t="n">
         <v>16351</v>
@@ -4487,7 +4487,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G142" t="n">
-        <v>1.46909487247467</v>
+        <v>1.46909475326538</v>
       </c>
       <c r="H142" t="n">
         <v>23001</v>
@@ -4603,7 +4603,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G146" t="n">
-        <v>1.43002319335938</v>
+        <v>1.43002307415009</v>
       </c>
       <c r="H146" t="n">
         <v>5668</v>
@@ -4661,7 +4661,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G148" t="n">
-        <v>1.43002319335938</v>
+        <v>1.43002307415009</v>
       </c>
       <c r="H148" t="n">
         <v>3047</v>
@@ -4719,7 +4719,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G150" t="n">
-        <v>1.43002319335938</v>
+        <v>1.43002307415009</v>
       </c>
       <c r="H150" t="n">
         <v>3668</v>
@@ -4748,7 +4748,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G151" t="n">
-        <v>1.43002319335938</v>
+        <v>1.43002307415009</v>
       </c>
       <c r="H151" t="n">
         <v>20454</v>
@@ -4835,7 +4835,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G154" t="n">
-        <v>1.46909487247467</v>
+        <v>1.46909475326538</v>
       </c>
       <c r="H154" t="n">
         <v>6731</v>
@@ -4864,7 +4864,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G155" t="n">
-        <v>1.50035214424133</v>
+        <v>1.50035226345062</v>
       </c>
       <c r="H155" t="n">
         <v>11333</v>
@@ -4893,7 +4893,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G156" t="n">
-        <v>1.49253785610199</v>
+        <v>1.49253797531128</v>
       </c>
       <c r="H156" t="n">
         <v>5721</v>
@@ -4922,7 +4922,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G157" t="n">
-        <v>1.50816655158997</v>
+        <v>1.50816643238068</v>
       </c>
       <c r="H157" t="n">
         <v>300</v>
@@ -4951,7 +4951,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G158" t="n">
-        <v>1.50035214424133</v>
+        <v>1.50035226345062</v>
       </c>
       <c r="H158" t="n">
         <v>230</v>
@@ -5038,7 +5038,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G161" t="n">
-        <v>1.47690916061401</v>
+        <v>1.47690904140472</v>
       </c>
       <c r="H161" t="n">
         <v>4796</v>
@@ -5096,7 +5096,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G163" t="n">
-        <v>1.46909487247467</v>
+        <v>1.46909475326538</v>
       </c>
       <c r="H163" t="n">
         <v>3375</v>
@@ -5183,7 +5183,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G166" t="n">
-        <v>1.46909487247467</v>
+        <v>1.46909475326538</v>
       </c>
       <c r="H166" t="n">
         <v>3815</v>
@@ -5212,7 +5212,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G167" t="n">
-        <v>1.46909487247467</v>
+        <v>1.46909475326538</v>
       </c>
       <c r="H167" t="n">
         <v>100</v>
@@ -5241,7 +5241,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G168" t="n">
-        <v>1.46909487247467</v>
+        <v>1.46909475326538</v>
       </c>
       <c r="H168" t="n">
         <v>600</v>
@@ -5270,7 +5270,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G169" t="n">
-        <v>1.47690916061401</v>
+        <v>1.47690904140472</v>
       </c>
       <c r="H169" t="n">
         <v>12338</v>
@@ -5328,7 +5328,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G171" t="n">
-        <v>1.47690916061401</v>
+        <v>1.47690904140472</v>
       </c>
       <c r="H171" t="n">
         <v>7601</v>
@@ -5357,7 +5357,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G172" t="n">
-        <v>1.47690916061401</v>
+        <v>1.47690904140472</v>
       </c>
       <c r="H172" t="n">
         <v>2406</v>
@@ -5415,7 +5415,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G174" t="n">
-        <v>1.54723811149597</v>
+        <v>1.54723823070526</v>
       </c>
       <c r="H174" t="n">
         <v>47810</v>
@@ -5444,7 +5444,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G175" t="n">
-        <v>1.49253785610199</v>
+        <v>1.49253797531128</v>
       </c>
       <c r="H175" t="n">
         <v>8883</v>
@@ -5502,7 +5502,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G177" t="n">
-        <v>1.52379524707794</v>
+        <v>1.52379512786865</v>
       </c>
       <c r="H177" t="n">
         <v>51119</v>
@@ -5531,7 +5531,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G178" t="n">
-        <v>1.49253785610199</v>
+        <v>1.49253797531128</v>
       </c>
       <c r="H178" t="n">
         <v>7365</v>
@@ -5647,7 +5647,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G182" t="n">
-        <v>1.47690916061401</v>
+        <v>1.47690904140472</v>
       </c>
       <c r="H182" t="n">
         <v>1510</v>
@@ -5676,7 +5676,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G183" t="n">
-        <v>1.41439437866211</v>
+        <v>1.4143944978714</v>
       </c>
       <c r="H183" t="n">
         <v>13615</v>
@@ -5734,7 +5734,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G185" t="n">
-        <v>1.43783760070801</v>
+        <v>1.43783736228943</v>
       </c>
       <c r="H185" t="n">
         <v>3980</v>
@@ -5792,7 +5792,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G187" t="n">
-        <v>1.60975289344788</v>
+        <v>1.6097526550293</v>
       </c>
       <c r="H187" t="n">
         <v>206627</v>
@@ -5821,7 +5821,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G188" t="n">
-        <v>1.66445302963257</v>
+        <v>1.66445326805115</v>
       </c>
       <c r="H188" t="n">
         <v>64466</v>
@@ -5879,7 +5879,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G190" t="n">
-        <v>1.52379524707794</v>
+        <v>1.52379512786865</v>
       </c>
       <c r="H190" t="n">
         <v>29552</v>
@@ -5908,7 +5908,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G191" t="n">
-        <v>1.52379524707794</v>
+        <v>1.52379512786865</v>
       </c>
       <c r="H191" t="n">
         <v>10729</v>
@@ -6111,7 +6111,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G198" t="n">
-        <v>1.46909487247467</v>
+        <v>1.46909475326538</v>
       </c>
       <c r="H198" t="n">
         <v>7517</v>
@@ -6227,7 +6227,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G202" t="n">
-        <v>1.47690916061401</v>
+        <v>1.47690904140472</v>
       </c>
       <c r="H202" t="n">
         <v>7610</v>
@@ -6285,7 +6285,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G204" t="n">
-        <v>1.53160953521729</v>
+        <v>1.531609416008</v>
       </c>
       <c r="H204" t="n">
         <v>8646</v>
@@ -6314,7 +6314,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G205" t="n">
-        <v>1.50816655158997</v>
+        <v>1.50816643238068</v>
       </c>
       <c r="H205" t="n">
         <v>23070</v>
@@ -6401,7 +6401,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G208" t="n">
-        <v>1.54723811149597</v>
+        <v>1.54723823070526</v>
       </c>
       <c r="H208" t="n">
         <v>30696</v>
@@ -6430,7 +6430,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G209" t="n">
-        <v>1.54723811149597</v>
+        <v>1.54723823070526</v>
       </c>
       <c r="H209" t="n">
         <v>5243</v>
@@ -6459,7 +6459,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G210" t="n">
-        <v>1.52379524707794</v>
+        <v>1.52379512786865</v>
       </c>
       <c r="H210" t="n">
         <v>3092</v>
@@ -6517,7 +6517,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G212" t="n">
-        <v>1.54723811149597</v>
+        <v>1.54723823070526</v>
       </c>
       <c r="H212" t="n">
         <v>600</v>
@@ -6604,7 +6604,7 @@
         <v>2</v>
       </c>
       <c r="G215" t="n">
-        <v>1.56286680698395</v>
+        <v>1.56286692619324</v>
       </c>
       <c r="H215" t="n">
         <v>7270</v>
@@ -6633,7 +6633,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G216" t="n">
-        <v>1.50816655158997</v>
+        <v>1.50816643238068</v>
       </c>
       <c r="H216" t="n">
         <v>15002</v>
@@ -6662,7 +6662,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G217" t="n">
-        <v>1.52379524707794</v>
+        <v>1.52379512786865</v>
       </c>
       <c r="H217" t="n">
         <v>9361</v>
@@ -6720,7 +6720,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G219" t="n">
-        <v>1.53160953521729</v>
+        <v>1.531609416008</v>
       </c>
       <c r="H219" t="n">
         <v>16116</v>
@@ -6778,7 +6778,7 @@
         <v>2</v>
       </c>
       <c r="G221" t="n">
-        <v>1.56286680698395</v>
+        <v>1.56286692619324</v>
       </c>
       <c r="H221" t="n">
         <v>25291</v>
@@ -6894,7 +6894,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G225" t="n">
-        <v>1.58630979061127</v>
+        <v>1.58630967140198</v>
       </c>
       <c r="H225" t="n">
         <v>24397</v>
@@ -6923,7 +6923,7 @@
         <v>2</v>
       </c>
       <c r="G226" t="n">
-        <v>1.56286680698395</v>
+        <v>1.56286692619324</v>
       </c>
       <c r="H226" t="n">
         <v>13694</v>
@@ -7010,7 +7010,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G229" t="n">
-        <v>1.46909487247467</v>
+        <v>1.46909475326538</v>
       </c>
       <c r="H229" t="n">
         <v>18045</v>
@@ -7039,7 +7039,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G230" t="n">
-        <v>1.49253785610199</v>
+        <v>1.49253797531128</v>
       </c>
       <c r="H230" t="n">
         <v>3975</v>
@@ -7126,7 +7126,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G233" t="n">
-        <v>1.52379524707794</v>
+        <v>1.52379512786865</v>
       </c>
       <c r="H233" t="n">
         <v>6905</v>
@@ -7155,7 +7155,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G234" t="n">
-        <v>1.41439437866211</v>
+        <v>1.4143944978714</v>
       </c>
       <c r="H234" t="n">
         <v>15984</v>
@@ -7184,7 +7184,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G235" t="n">
-        <v>1.43002319335938</v>
+        <v>1.43002307415009</v>
       </c>
       <c r="H235" t="n">
         <v>7002</v>
@@ -7242,7 +7242,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G237" t="n">
-        <v>1.47690916061401</v>
+        <v>1.47690904140472</v>
       </c>
       <c r="H237" t="n">
         <v>3415</v>
@@ -7271,7 +7271,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G238" t="n">
-        <v>1.43783760070801</v>
+        <v>1.43783736228943</v>
       </c>
       <c r="H238" t="n">
         <v>1692</v>
@@ -7300,7 +7300,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G239" t="n">
-        <v>1.46909487247467</v>
+        <v>1.46909475326538</v>
       </c>
       <c r="H239" t="n">
         <v>4746</v>
@@ -7358,7 +7358,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G241" t="n">
-        <v>1.52379524707794</v>
+        <v>1.52379512786865</v>
       </c>
       <c r="H241" t="n">
         <v>5500</v>
@@ -7387,7 +7387,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G242" t="n">
-        <v>1.52379524707794</v>
+        <v>1.52379512786865</v>
       </c>
       <c r="H242" t="n">
         <v>6897</v>
@@ -7416,7 +7416,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G243" t="n">
-        <v>1.50035214424133</v>
+        <v>1.50035226345062</v>
       </c>
       <c r="H243" t="n">
         <v>2774</v>
@@ -7445,7 +7445,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G244" t="n">
-        <v>1.50035214424133</v>
+        <v>1.50035226345062</v>
       </c>
       <c r="H244" t="n">
         <v>2142</v>
@@ -7474,7 +7474,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G245" t="n">
-        <v>1.49253785610199</v>
+        <v>1.49253797531128</v>
       </c>
       <c r="H245" t="n">
         <v>6756</v>
@@ -7503,7 +7503,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G246" t="n">
-        <v>1.50035214424133</v>
+        <v>1.50035226345062</v>
       </c>
       <c r="H246" t="n">
         <v>6837</v>
@@ -7532,7 +7532,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G247" t="n">
-        <v>1.50035214424133</v>
+        <v>1.50035226345062</v>
       </c>
       <c r="H247" t="n">
         <v>9596</v>
@@ -7561,7 +7561,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G248" t="n">
-        <v>1.50035214424133</v>
+        <v>1.50035226345062</v>
       </c>
       <c r="H248" t="n">
         <v>3796</v>
@@ -7619,7 +7619,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G250" t="n">
-        <v>1.50035214424133</v>
+        <v>1.50035226345062</v>
       </c>
       <c r="H250" t="n">
         <v>16130</v>
@@ -7648,7 +7648,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G251" t="n">
-        <v>1.50816655158997</v>
+        <v>1.50816643238068</v>
       </c>
       <c r="H251" t="n">
         <v>4699</v>
@@ -7677,7 +7677,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G252" t="n">
-        <v>1.49253785610199</v>
+        <v>1.49253797531128</v>
       </c>
       <c r="H252" t="n">
         <v>8020</v>
@@ -7706,7 +7706,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G253" t="n">
-        <v>1.47690916061401</v>
+        <v>1.47690904140472</v>
       </c>
       <c r="H253" t="n">
         <v>5630</v>
@@ -7735,7 +7735,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G254" t="n">
-        <v>1.50035214424133</v>
+        <v>1.50035226345062</v>
       </c>
       <c r="H254" t="n">
         <v>10860</v>
@@ -7764,7 +7764,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G255" t="n">
-        <v>1.49253785610199</v>
+        <v>1.49253797531128</v>
       </c>
       <c r="H255" t="n">
         <v>45713</v>
@@ -7822,7 +7822,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G257" t="n">
-        <v>1.54723811149597</v>
+        <v>1.54723823070526</v>
       </c>
       <c r="H257" t="n">
         <v>41048</v>
@@ -7851,7 +7851,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G258" t="n">
-        <v>1.83636856079102</v>
+        <v>1.83636832237244</v>
       </c>
       <c r="H258" t="n">
         <v>125566</v>
@@ -7880,7 +7880,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G259" t="n">
-        <v>1.77385365962982</v>
+        <v>1.7738538980484</v>
       </c>
       <c r="H259" t="n">
         <v>144770</v>
@@ -7909,7 +7909,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G260" t="n">
-        <v>1.76603949069977</v>
+        <v>1.76603937149048</v>
       </c>
       <c r="H260" t="n">
         <v>45306</v>
@@ -7967,7 +7967,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G262" t="n">
-        <v>1.72696769237518</v>
+        <v>1.72696805000305</v>
       </c>
       <c r="H262" t="n">
         <v>17933</v>
@@ -8083,7 +8083,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G266" t="n">
-        <v>1.60193848609924</v>
+        <v>1.60193836688995</v>
       </c>
       <c r="H266" t="n">
         <v>12204</v>
@@ -8112,7 +8112,7 @@
         <v>2.25</v>
       </c>
       <c r="G267" t="n">
-        <v>1.75822520256042</v>
+        <v>1.75822496414185</v>
       </c>
       <c r="H267" t="n">
         <v>48617</v>
@@ -8141,7 +8141,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G268" t="n">
-        <v>1.71133935451508</v>
+        <v>1.71133947372437</v>
       </c>
       <c r="H268" t="n">
         <v>79014</v>
@@ -8170,7 +8170,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G269" t="n">
-        <v>1.66445302963257</v>
+        <v>1.66445326805115</v>
       </c>
       <c r="H269" t="n">
         <v>20304</v>
@@ -8199,7 +8199,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G270" t="n">
-        <v>1.64101004600525</v>
+        <v>1.64101016521454</v>
       </c>
       <c r="H270" t="n">
         <v>10671</v>
@@ -8286,7 +8286,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G273" t="n">
-        <v>2.54747271537781</v>
+        <v>2.54747295379639</v>
       </c>
       <c r="H273" t="n">
         <v>419311</v>
@@ -8315,7 +8315,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G274" t="n">
-        <v>2.78190302848816</v>
+        <v>2.78190279006958</v>
       </c>
       <c r="H274" t="n">
         <v>248750</v>
@@ -8373,7 +8373,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G276" t="n">
-        <v>2.54747271537781</v>
+        <v>2.54747295379639</v>
       </c>
       <c r="H276" t="n">
         <v>186391</v>
@@ -8402,7 +8402,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G277" t="n">
-        <v>2.31304264068604</v>
+        <v>2.31304311752319</v>
       </c>
       <c r="H277" t="n">
         <v>178115</v>
@@ -8431,7 +8431,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G278" t="n">
-        <v>2.36774301528931</v>
+        <v>2.36774325370789</v>
       </c>
       <c r="H278" t="n">
         <v>155933</v>
@@ -8489,7 +8489,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G280" t="n">
-        <v>2.36774301528931</v>
+        <v>2.36774325370789</v>
       </c>
       <c r="H280" t="n">
         <v>42641</v>
@@ -8518,7 +8518,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G281" t="n">
-        <v>2.26615715026855</v>
+        <v>2.26615691184998</v>
       </c>
       <c r="H281" t="n">
         <v>36137</v>
@@ -8547,7 +8547,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G282" t="n">
-        <v>2.66468811035156</v>
+        <v>2.66468787193298</v>
       </c>
       <c r="H282" t="n">
         <v>180543</v>
@@ -8692,7 +8692,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G287" t="n">
-        <v>2.53184413909912</v>
+        <v>2.5318443775177</v>
       </c>
       <c r="H287" t="n">
         <v>175902</v>
@@ -8808,7 +8808,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G291" t="n">
-        <v>2.45370078086853</v>
+        <v>2.45370101928711</v>
       </c>
       <c r="H291" t="n">
         <v>62585</v>
@@ -8866,7 +8866,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G293" t="n">
-        <v>2.30522847175598</v>
+        <v>2.30522871017456</v>
       </c>
       <c r="H293" t="n">
         <v>63123</v>
@@ -8895,7 +8895,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G294" t="n">
-        <v>2.21927094459534</v>
+        <v>2.21927070617676</v>
       </c>
       <c r="H294" t="n">
         <v>88001</v>
@@ -9040,7 +9040,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G299" t="n">
-        <v>2.18801355361938</v>
+        <v>2.18801331520081</v>
       </c>
       <c r="H299" t="n">
         <v>145545</v>
@@ -9069,7 +9069,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G300" t="n">
-        <v>2.16457056999207</v>
+        <v>2.16457033157349</v>
       </c>
       <c r="H300" t="n">
         <v>48238</v>
@@ -9098,7 +9098,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G301" t="n">
-        <v>2.11768460273743</v>
+        <v>2.11768484115601</v>
       </c>
       <c r="H301" t="n">
         <v>31779</v>
@@ -9127,7 +9127,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G302" t="n">
-        <v>2.10987019538879</v>
+        <v>2.10987043380737</v>
       </c>
       <c r="H302" t="n">
         <v>17255</v>
@@ -9185,7 +9185,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G304" t="n">
-        <v>2.08642745018005</v>
+        <v>2.08642721176147</v>
       </c>
       <c r="H304" t="n">
         <v>19530</v>
@@ -9214,7 +9214,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G305" t="n">
-        <v>2.08642745018005</v>
+        <v>2.08642721176147</v>
       </c>
       <c r="H305" t="n">
         <v>13542</v>
@@ -9272,7 +9272,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G307" t="n">
-        <v>2.11768460273743</v>
+        <v>2.11768484115601</v>
       </c>
       <c r="H307" t="n">
         <v>94727</v>
@@ -9301,7 +9301,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G308" t="n">
-        <v>2.18801355361938</v>
+        <v>2.18801331520081</v>
       </c>
       <c r="H308" t="n">
         <v>36108</v>
@@ -9330,7 +9330,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G309" t="n">
-        <v>2.16457056999207</v>
+        <v>2.16457033157349</v>
       </c>
       <c r="H309" t="n">
         <v>14321</v>
@@ -9359,7 +9359,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G310" t="n">
-        <v>2.11768460273743</v>
+        <v>2.11768484115601</v>
       </c>
       <c r="H310" t="n">
         <v>7325</v>
@@ -9388,7 +9388,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G311" t="n">
-        <v>2.13331317901611</v>
+        <v>2.13331341743469</v>
       </c>
       <c r="H311" t="n">
         <v>20423</v>
@@ -9446,7 +9446,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G313" t="n">
-        <v>2.14112782478333</v>
+        <v>2.14112758636475</v>
       </c>
       <c r="H313" t="n">
         <v>5822</v>
@@ -9475,7 +9475,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G314" t="n">
-        <v>2.19582796096802</v>
+        <v>2.19582772254944</v>
       </c>
       <c r="H314" t="n">
         <v>90558</v>
@@ -9533,7 +9533,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G316" t="n">
-        <v>2.31304264068604</v>
+        <v>2.31304311752319</v>
       </c>
       <c r="H316" t="n">
         <v>166647</v>
@@ -9736,7 +9736,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G323" t="n">
-        <v>2.26615715026855</v>
+        <v>2.26615691184998</v>
       </c>
       <c r="H323" t="n">
         <v>66785</v>
@@ -9765,7 +9765,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G324" t="n">
-        <v>2.24271392822266</v>
+        <v>2.24271368980408</v>
       </c>
       <c r="H324" t="n">
         <v>19757</v>
@@ -9794,7 +9794,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G325" t="n">
-        <v>2.36774301528931</v>
+        <v>2.36774325370789</v>
       </c>
       <c r="H325" t="n">
         <v>123555</v>
@@ -9823,7 +9823,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G326" t="n">
-        <v>2.3286714553833</v>
+        <v>2.32867169380188</v>
       </c>
       <c r="H326" t="n">
         <v>34122</v>
@@ -9852,7 +9852,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G327" t="n">
-        <v>2.31304264068604</v>
+        <v>2.31304311752319</v>
       </c>
       <c r="H327" t="n">
         <v>15378</v>
@@ -9939,7 +9939,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G330" t="n">
-        <v>2.26615715026855</v>
+        <v>2.26615691184998</v>
       </c>
       <c r="H330" t="n">
         <v>9551</v>
@@ -9997,7 +9997,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G332" t="n">
-        <v>2.19582796096802</v>
+        <v>2.19582772254944</v>
       </c>
       <c r="H332" t="n">
         <v>23745</v>
@@ -10026,7 +10026,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G333" t="n">
-        <v>2.25834274291992</v>
+        <v>2.25834250450134</v>
       </c>
       <c r="H333" t="n">
         <v>41046</v>
@@ -10055,7 +10055,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G334" t="n">
-        <v>2.30522847175598</v>
+        <v>2.30522871017456</v>
       </c>
       <c r="H334" t="n">
         <v>27597</v>
@@ -10113,7 +10113,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G336" t="n">
-        <v>2.36774301528931</v>
+        <v>2.36774325370789</v>
       </c>
       <c r="H336" t="n">
         <v>60523</v>
@@ -10142,7 +10142,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G337" t="n">
-        <v>2.30522847175598</v>
+        <v>2.30522871017456</v>
       </c>
       <c r="H337" t="n">
         <v>70691</v>
@@ -10171,7 +10171,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G338" t="n">
-        <v>2.31304264068604</v>
+        <v>2.31304311752319</v>
       </c>
       <c r="H338" t="n">
         <v>35872</v>
@@ -10200,7 +10200,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G339" t="n">
-        <v>2.3286714553833</v>
+        <v>2.32867169380188</v>
       </c>
       <c r="H339" t="n">
         <v>58353</v>
@@ -10229,7 +10229,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G340" t="n">
-        <v>2.26615715026855</v>
+        <v>2.26615691184998</v>
       </c>
       <c r="H340" t="n">
         <v>69321</v>
@@ -10258,7 +10258,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G341" t="n">
-        <v>2.25834274291992</v>
+        <v>2.25834250450134</v>
       </c>
       <c r="H341" t="n">
         <v>19671</v>
@@ -10287,7 +10287,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G342" t="n">
-        <v>2.25834274291992</v>
+        <v>2.25834250450134</v>
       </c>
       <c r="H342" t="n">
         <v>9250</v>
@@ -10374,7 +10374,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G345" t="n">
-        <v>2.40681481361389</v>
+        <v>2.40681505203247</v>
       </c>
       <c r="H345" t="n">
         <v>126337</v>
@@ -10403,7 +10403,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G346" t="n">
-        <v>2.39900040626526</v>
+        <v>2.39900064468384</v>
       </c>
       <c r="H346" t="n">
         <v>45418</v>
@@ -10490,7 +10490,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G349" t="n">
-        <v>2.28960013389587</v>
+        <v>2.28959989547729</v>
       </c>
       <c r="H349" t="n">
         <v>69457</v>
@@ -10548,7 +10548,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G351" t="n">
-        <v>2.30522847175598</v>
+        <v>2.30522871017456</v>
       </c>
       <c r="H351" t="n">
         <v>10524</v>
@@ -10577,7 +10577,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G352" t="n">
-        <v>2.25834274291992</v>
+        <v>2.25834250450134</v>
       </c>
       <c r="H352" t="n">
         <v>34161</v>
@@ -10606,7 +10606,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G353" t="n">
-        <v>2.26615715026855</v>
+        <v>2.26615691184998</v>
       </c>
       <c r="H353" t="n">
         <v>11227</v>
@@ -10664,7 +10664,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G355" t="n">
-        <v>2.30522847175598</v>
+        <v>2.30522871017456</v>
       </c>
       <c r="H355" t="n">
         <v>6469</v>
@@ -10722,7 +10722,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G357" t="n">
-        <v>2.3286714553833</v>
+        <v>2.32867169380188</v>
       </c>
       <c r="H357" t="n">
         <v>14916</v>
@@ -10751,7 +10751,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G358" t="n">
-        <v>2.37555766105652</v>
+        <v>2.37555742263794</v>
       </c>
       <c r="H358" t="n">
         <v>129387</v>
@@ -10780,7 +10780,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G359" t="n">
-        <v>2.30522847175598</v>
+        <v>2.30522871017456</v>
       </c>
       <c r="H359" t="n">
         <v>21418</v>
@@ -10809,7 +10809,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G360" t="n">
-        <v>2.31304264068604</v>
+        <v>2.31304311752319</v>
       </c>
       <c r="H360" t="n">
         <v>6391</v>
@@ -10838,7 +10838,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G361" t="n">
-        <v>2.30522847175598</v>
+        <v>2.30522871017456</v>
       </c>
       <c r="H361" t="n">
         <v>12853</v>
@@ -10867,7 +10867,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G362" t="n">
-        <v>2.39900040626526</v>
+        <v>2.39900064468384</v>
       </c>
       <c r="H362" t="n">
         <v>53897</v>
@@ -10925,7 +10925,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G364" t="n">
-        <v>2.28960013389587</v>
+        <v>2.28959989547729</v>
       </c>
       <c r="H364" t="n">
         <v>9629</v>
@@ -10954,7 +10954,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G365" t="n">
-        <v>2.19582796096802</v>
+        <v>2.19582772254944</v>
       </c>
       <c r="H365" t="n">
         <v>66685</v>
@@ -10983,7 +10983,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G366" t="n">
-        <v>2.19582796096802</v>
+        <v>2.19582772254944</v>
       </c>
       <c r="H366" t="n">
         <v>21330</v>
@@ -11012,7 +11012,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G367" t="n">
-        <v>2.22708535194397</v>
+        <v>2.22708511352539</v>
       </c>
       <c r="H367" t="n">
         <v>8955</v>
@@ -11041,7 +11041,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G368" t="n">
-        <v>2.22708535194397</v>
+        <v>2.22708511352539</v>
       </c>
       <c r="H368" t="n">
         <v>5899</v>
@@ -11070,7 +11070,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G369" t="n">
-        <v>2.19582796096802</v>
+        <v>2.19582772254944</v>
       </c>
       <c r="H369" t="n">
         <v>25375</v>
@@ -11099,7 +11099,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G370" t="n">
-        <v>2.19582796096802</v>
+        <v>2.19582772254944</v>
       </c>
       <c r="H370" t="n">
         <v>2922</v>
@@ -11128,7 +11128,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G371" t="n">
-        <v>2.20364236831665</v>
+        <v>2.20364212989807</v>
       </c>
       <c r="H371" t="n">
         <v>6831</v>
@@ -11157,7 +11157,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G372" t="n">
-        <v>2.22708535194397</v>
+        <v>2.22708511352539</v>
       </c>
       <c r="H372" t="n">
         <v>12004</v>
@@ -11186,7 +11186,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G373" t="n">
-        <v>2.20364236831665</v>
+        <v>2.20364212989807</v>
       </c>
       <c r="H373" t="n">
         <v>664</v>
@@ -11244,7 +11244,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G375" t="n">
-        <v>2.20364236831665</v>
+        <v>2.20364212989807</v>
       </c>
       <c r="H375" t="n">
         <v>2860</v>
@@ -11273,7 +11273,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G376" t="n">
-        <v>2.18801355361938</v>
+        <v>2.18801331520081</v>
       </c>
       <c r="H376" t="n">
         <v>4715</v>
@@ -11302,7 +11302,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G377" t="n">
-        <v>2.22708535194397</v>
+        <v>2.22708511352539</v>
       </c>
       <c r="H377" t="n">
         <v>4658</v>
@@ -11331,7 +11331,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G378" t="n">
-        <v>2.21927094459534</v>
+        <v>2.21927070617676</v>
       </c>
       <c r="H378" t="n">
         <v>6809</v>
@@ -11360,7 +11360,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G379" t="n">
-        <v>2.22708535194397</v>
+        <v>2.22708511352539</v>
       </c>
       <c r="H379" t="n">
         <v>7003</v>
@@ -11389,7 +11389,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G380" t="n">
-        <v>2.20364236831665</v>
+        <v>2.20364212989807</v>
       </c>
       <c r="H380" t="n">
         <v>5030</v>
@@ -11418,7 +11418,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G381" t="n">
-        <v>2.21927094459534</v>
+        <v>2.21927070617676</v>
       </c>
       <c r="H381" t="n">
         <v>34021</v>
@@ -11476,7 +11476,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G383" t="n">
-        <v>2.25834274291992</v>
+        <v>2.25834250450134</v>
       </c>
       <c r="H383" t="n">
         <v>38535</v>
@@ -11505,7 +11505,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G384" t="n">
-        <v>2.2348997592926</v>
+        <v>2.23489952087402</v>
       </c>
       <c r="H384" t="n">
         <v>7914</v>
@@ -11534,7 +11534,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G385" t="n">
-        <v>2.2348997592926</v>
+        <v>2.23489952087402</v>
       </c>
       <c r="H385" t="n">
         <v>2794</v>
@@ -11563,7 +11563,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G386" t="n">
-        <v>2.25834274291992</v>
+        <v>2.25834250450134</v>
       </c>
       <c r="H386" t="n">
         <v>100</v>
@@ -11592,7 +11592,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G387" t="n">
-        <v>2.24271392822266</v>
+        <v>2.24271368980408</v>
       </c>
       <c r="H387" t="n">
         <v>6947</v>
@@ -11621,7 +11621,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G388" t="n">
-        <v>2.22708535194397</v>
+        <v>2.22708511352539</v>
       </c>
       <c r="H388" t="n">
         <v>100</v>
@@ -11650,7 +11650,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G389" t="n">
-        <v>2.18019938468933</v>
+        <v>2.18019890785217</v>
       </c>
       <c r="H389" t="n">
         <v>20929</v>
@@ -11679,7 +11679,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G390" t="n">
-        <v>2.19582796096802</v>
+        <v>2.19582772254944</v>
       </c>
       <c r="H390" t="n">
         <v>6870</v>
@@ -11708,7 +11708,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G391" t="n">
-        <v>2.2348997592926</v>
+        <v>2.23489952087402</v>
       </c>
       <c r="H391" t="n">
         <v>13073</v>
@@ -11737,7 +11737,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G392" t="n">
-        <v>2.22708535194397</v>
+        <v>2.22708511352539</v>
       </c>
       <c r="H392" t="n">
         <v>4464</v>
@@ -11766,7 +11766,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G393" t="n">
-        <v>2.28960013389587</v>
+        <v>2.28959989547729</v>
       </c>
       <c r="H393" t="n">
         <v>490568</v>
@@ -11795,7 +11795,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G394" t="n">
-        <v>2.25052809715271</v>
+        <v>2.25052833557129</v>
       </c>
       <c r="H394" t="n">
         <v>49928</v>
@@ -11824,7 +11824,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G395" t="n">
-        <v>2.26615715026855</v>
+        <v>2.26615691184998</v>
       </c>
       <c r="H395" t="n">
         <v>27151</v>
@@ -11853,7 +11853,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G396" t="n">
-        <v>2.22708535194397</v>
+        <v>2.22708511352539</v>
       </c>
       <c r="H396" t="n">
         <v>21203</v>
@@ -11911,7 +11911,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G398" t="n">
-        <v>2.2348997592926</v>
+        <v>2.23489952087402</v>
       </c>
       <c r="H398" t="n">
         <v>19480</v>
@@ -11940,7 +11940,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G399" t="n">
-        <v>2.25834274291992</v>
+        <v>2.25834250450134</v>
       </c>
       <c r="H399" t="n">
         <v>9326</v>
@@ -11969,7 +11969,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G400" t="n">
-        <v>2.25052809715271</v>
+        <v>2.25052833557129</v>
       </c>
       <c r="H400" t="n">
         <v>125043</v>
@@ -12056,7 +12056,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G403" t="n">
-        <v>2.28960013389587</v>
+        <v>2.28959989547729</v>
       </c>
       <c r="H403" t="n">
         <v>3440</v>
@@ -12114,7 +12114,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G405" t="n">
-        <v>2.26615715026855</v>
+        <v>2.26615691184998</v>
       </c>
       <c r="H405" t="n">
         <v>3645</v>
@@ -12143,7 +12143,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G406" t="n">
-        <v>2.24271392822266</v>
+        <v>2.24271368980408</v>
       </c>
       <c r="H406" t="n">
         <v>10421</v>
@@ -12172,7 +12172,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G407" t="n">
-        <v>2.26615715026855</v>
+        <v>2.26615691184998</v>
       </c>
       <c r="H407" t="n">
         <v>13225</v>
@@ -12201,7 +12201,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G408" t="n">
-        <v>2.28960013389587</v>
+        <v>2.28959989547729</v>
       </c>
       <c r="H408" t="n">
         <v>16796</v>
@@ -12230,7 +12230,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G409" t="n">
-        <v>2.25052809715271</v>
+        <v>2.25052833557129</v>
       </c>
       <c r="H409" t="n">
         <v>3826</v>
@@ -12288,7 +12288,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G411" t="n">
-        <v>2.26615715026855</v>
+        <v>2.26615691184998</v>
       </c>
       <c r="H411" t="n">
         <v>4008</v>
@@ -12317,7 +12317,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G412" t="n">
-        <v>2.25052809715271</v>
+        <v>2.25052833557129</v>
       </c>
       <c r="H412" t="n">
         <v>13597</v>
@@ -12346,7 +12346,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G413" t="n">
-        <v>2.24271392822266</v>
+        <v>2.24271368980408</v>
       </c>
       <c r="H413" t="n">
         <v>8588</v>
@@ -12375,7 +12375,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G414" t="n">
-        <v>2.22708535194397</v>
+        <v>2.22708511352539</v>
       </c>
       <c r="H414" t="n">
         <v>16306</v>
@@ -12404,7 +12404,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G415" t="n">
-        <v>2.22708535194397</v>
+        <v>2.22708511352539</v>
       </c>
       <c r="H415" t="n">
         <v>4789</v>
@@ -12433,7 +12433,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G416" t="n">
-        <v>2.25052809715271</v>
+        <v>2.25052833557129</v>
       </c>
       <c r="H416" t="n">
         <v>4039</v>
@@ -12462,7 +12462,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G417" t="n">
-        <v>2.25834274291992</v>
+        <v>2.25834250450134</v>
       </c>
       <c r="H417" t="n">
         <v>1700</v>
@@ -12520,7 +12520,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G419" t="n">
-        <v>2.25052809715271</v>
+        <v>2.25052833557129</v>
       </c>
       <c r="H419" t="n">
         <v>6100</v>
@@ -12549,7 +12549,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G420" t="n">
-        <v>2.24271392822266</v>
+        <v>2.24271368980408</v>
       </c>
       <c r="H420" t="n">
         <v>4693</v>
@@ -12578,7 +12578,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G421" t="n">
-        <v>2.25052809715271</v>
+        <v>2.25052833557129</v>
       </c>
       <c r="H421" t="n">
         <v>5308</v>
@@ -12607,7 +12607,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G422" t="n">
-        <v>2.25052809715271</v>
+        <v>2.25052833557129</v>
       </c>
       <c r="H422" t="n">
         <v>13271</v>
@@ -12636,7 +12636,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G423" t="n">
-        <v>2.25834274291992</v>
+        <v>2.25834250450134</v>
       </c>
       <c r="H423" t="n">
         <v>19254</v>
@@ -12665,7 +12665,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G424" t="n">
-        <v>2.25834274291992</v>
+        <v>2.25834250450134</v>
       </c>
       <c r="H424" t="n">
         <v>2892</v>
@@ -12694,7 +12694,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G425" t="n">
-        <v>2.24271392822266</v>
+        <v>2.24271368980408</v>
       </c>
       <c r="H425" t="n">
         <v>22550</v>
@@ -12723,7 +12723,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G426" t="n">
-        <v>2.28960013389587</v>
+        <v>2.28959989547729</v>
       </c>
       <c r="H426" t="n">
         <v>16488</v>
@@ -12752,7 +12752,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G427" t="n">
-        <v>2.28960013389587</v>
+        <v>2.28959989547729</v>
       </c>
       <c r="H427" t="n">
         <v>33109</v>
@@ -12839,7 +12839,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G430" t="n">
-        <v>2.26615715026855</v>
+        <v>2.26615691184998</v>
       </c>
       <c r="H430" t="n">
         <v>3551</v>
@@ -12897,7 +12897,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G432" t="n">
-        <v>2.28960013389587</v>
+        <v>2.28959989547729</v>
       </c>
       <c r="H432" t="n">
         <v>7635</v>
@@ -12926,7 +12926,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G433" t="n">
-        <v>2.28960013389587</v>
+        <v>2.28959989547729</v>
       </c>
       <c r="H433" t="n">
         <v>12703</v>
@@ -12955,7 +12955,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G434" t="n">
-        <v>2.30522847175598</v>
+        <v>2.30522871017456</v>
       </c>
       <c r="H434" t="n">
         <v>3559</v>
@@ -12984,7 +12984,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G435" t="n">
-        <v>2.28960013389587</v>
+        <v>2.28959989547729</v>
       </c>
       <c r="H435" t="n">
         <v>6499</v>
@@ -13100,7 +13100,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G439" t="n">
-        <v>2.30522847175598</v>
+        <v>2.30522871017456</v>
       </c>
       <c r="H439" t="n">
         <v>7059</v>
@@ -13245,7 +13245,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G444" t="n">
-        <v>2.42244338989258</v>
+        <v>2.42244362831116</v>
       </c>
       <c r="H444" t="n">
         <v>158865</v>
@@ -13303,7 +13303,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G446" t="n">
-        <v>2.3286714553833</v>
+        <v>2.32867169380188</v>
       </c>
       <c r="H446" t="n">
         <v>38929</v>
@@ -13332,7 +13332,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G447" t="n">
-        <v>2.28960013389587</v>
+        <v>2.28959989547729</v>
       </c>
       <c r="H447" t="n">
         <v>18719</v>
@@ -13390,7 +13390,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G449" t="n">
-        <v>2.31304264068604</v>
+        <v>2.31304311752319</v>
       </c>
       <c r="H449" t="n">
         <v>8698</v>
@@ -13419,7 +13419,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G450" t="n">
-        <v>2.28960013389587</v>
+        <v>2.28959989547729</v>
       </c>
       <c r="H450" t="n">
         <v>5156</v>
@@ -13506,7 +13506,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G453" t="n">
-        <v>2.25834274291992</v>
+        <v>2.25834250450134</v>
       </c>
       <c r="H453" t="n">
         <v>12264</v>
@@ -13535,7 +13535,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G454" t="n">
-        <v>2.25834274291992</v>
+        <v>2.25834250450134</v>
       </c>
       <c r="H454" t="n">
         <v>3217</v>
@@ -13564,7 +13564,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G455" t="n">
-        <v>2.25052809715271</v>
+        <v>2.25052833557129</v>
       </c>
       <c r="H455" t="n">
         <v>4720</v>
@@ -13622,7 +13622,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G457" t="n">
-        <v>2.26615715026855</v>
+        <v>2.26615691184998</v>
       </c>
       <c r="H457" t="n">
         <v>12905</v>
@@ -13651,7 +13651,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G458" t="n">
-        <v>2.26615715026855</v>
+        <v>2.26615691184998</v>
       </c>
       <c r="H458" t="n">
         <v>5857</v>
@@ -13709,7 +13709,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G460" t="n">
-        <v>2.26615715026855</v>
+        <v>2.26615691184998</v>
       </c>
       <c r="H460" t="n">
         <v>5248</v>
@@ -13767,7 +13767,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G462" t="n">
-        <v>2.25834274291992</v>
+        <v>2.25834250450134</v>
       </c>
       <c r="H462" t="n">
         <v>11311</v>
@@ -13825,7 +13825,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G464" t="n">
-        <v>2.25834274291992</v>
+        <v>2.25834250450134</v>
       </c>
       <c r="H464" t="n">
         <v>893</v>
@@ -13854,7 +13854,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G465" t="n">
-        <v>2.25052809715271</v>
+        <v>2.25052833557129</v>
       </c>
       <c r="H465" t="n">
         <v>7854</v>
@@ -13883,7 +13883,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G466" t="n">
-        <v>2.24271392822266</v>
+        <v>2.24271368980408</v>
       </c>
       <c r="H466" t="n">
         <v>8835</v>
@@ -13912,7 +13912,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G467" t="n">
-        <v>2.25052809715271</v>
+        <v>2.25052833557129</v>
       </c>
       <c r="H467" t="n">
         <v>6429</v>
@@ -13941,7 +13941,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G468" t="n">
-        <v>2.24271392822266</v>
+        <v>2.24271368980408</v>
       </c>
       <c r="H468" t="n">
         <v>4382</v>
@@ -13970,7 +13970,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G469" t="n">
-        <v>2.24271392822266</v>
+        <v>2.24271368980408</v>
       </c>
       <c r="H469" t="n">
         <v>5207</v>
@@ -13999,7 +13999,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G470" t="n">
-        <v>2.25052809715271</v>
+        <v>2.25052833557129</v>
       </c>
       <c r="H470" t="n">
         <v>4682</v>
@@ -14028,7 +14028,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G471" t="n">
-        <v>2.25834274291992</v>
+        <v>2.25834250450134</v>
       </c>
       <c r="H471" t="n">
         <v>5598</v>
@@ -14057,7 +14057,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G472" t="n">
-        <v>2.24271392822266</v>
+        <v>2.24271368980408</v>
       </c>
       <c r="H472" t="n">
         <v>5970</v>
@@ -14086,7 +14086,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G473" t="n">
-        <v>2.25834274291992</v>
+        <v>2.25834250450134</v>
       </c>
       <c r="H473" t="n">
         <v>2692</v>
@@ -14144,7 +14144,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G475" t="n">
-        <v>2.26615715026855</v>
+        <v>2.26615691184998</v>
       </c>
       <c r="H475" t="n">
         <v>6319</v>
@@ -14173,7 +14173,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G476" t="n">
-        <v>2.26615715026855</v>
+        <v>2.26615691184998</v>
       </c>
       <c r="H476" t="n">
         <v>11654</v>
@@ -14202,7 +14202,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G477" t="n">
-        <v>2.26615715026855</v>
+        <v>2.26615691184998</v>
       </c>
       <c r="H477" t="n">
         <v>9741</v>
@@ -14231,7 +14231,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G478" t="n">
-        <v>2.25052809715271</v>
+        <v>2.25052833557129</v>
       </c>
       <c r="H478" t="n">
         <v>13054</v>
@@ -14260,7 +14260,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G479" t="n">
-        <v>2.21927094459534</v>
+        <v>2.21927070617676</v>
       </c>
       <c r="H479" t="n">
         <v>14483</v>
@@ -14289,7 +14289,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G480" t="n">
-        <v>2.18801355361938</v>
+        <v>2.18801331520081</v>
       </c>
       <c r="H480" t="n">
         <v>127127</v>
@@ -14318,7 +14318,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G481" t="n">
-        <v>2.11768460273743</v>
+        <v>2.11768484115601</v>
       </c>
       <c r="H481" t="n">
         <v>18942</v>
@@ -14347,7 +14347,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G482" t="n">
-        <v>2.05517029762268</v>
+        <v>2.0551700592041</v>
       </c>
       <c r="H482" t="n">
         <v>33954</v>
@@ -14376,7 +14376,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G483" t="n">
-        <v>2.05517029762268</v>
+        <v>2.0551700592041</v>
       </c>
       <c r="H483" t="n">
         <v>1310</v>
@@ -14434,7 +14434,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G485" t="n">
-        <v>2.04735517501831</v>
+        <v>2.04735541343689</v>
       </c>
       <c r="H485" t="n">
         <v>5465</v>
@@ -14463,7 +14463,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G486" t="n">
-        <v>2.07079839706421</v>
+        <v>2.07079863548279</v>
       </c>
       <c r="H486" t="n">
         <v>9534</v>
@@ -14492,7 +14492,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G487" t="n">
-        <v>2.05517029762268</v>
+        <v>2.0551700592041</v>
       </c>
       <c r="H487" t="n">
         <v>7884</v>
@@ -14521,7 +14521,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G488" t="n">
-        <v>2.09424161911011</v>
+        <v>2.09424138069153</v>
       </c>
       <c r="H488" t="n">
         <v>6344</v>
@@ -14608,7 +14608,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G491" t="n">
-        <v>2.05517029762268</v>
+        <v>2.0551700592041</v>
       </c>
       <c r="H491" t="n">
         <v>4461</v>
@@ -14695,7 +14695,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G494" t="n">
-        <v>2.02391242980957</v>
+        <v>2.02391266822815</v>
       </c>
       <c r="H494" t="n">
         <v>4454</v>
@@ -14724,7 +14724,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G495" t="n">
-        <v>2.02391242980957</v>
+        <v>2.02391266822815</v>
       </c>
       <c r="H495" t="n">
         <v>1453</v>
@@ -15391,7 +15391,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G518" t="n">
-        <v>2.09424161911011</v>
+        <v>2.09424138069153</v>
       </c>
       <c r="H518" t="n">
         <v>112388</v>
@@ -15420,7 +15420,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G519" t="n">
-        <v>2.08642745018005</v>
+        <v>2.08642721176147</v>
       </c>
       <c r="H519" t="n">
         <v>11274</v>
@@ -15507,7 +15507,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G522" t="n">
-        <v>2.05517029762268</v>
+        <v>2.0551700592041</v>
       </c>
       <c r="H522" t="n">
         <v>2500</v>
@@ -15536,7 +15536,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G523" t="n">
-        <v>2.08642745018005</v>
+        <v>2.08642721176147</v>
       </c>
       <c r="H523" t="n">
         <v>9758</v>
@@ -15594,7 +15594,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G525" t="n">
-        <v>2.05517029762268</v>
+        <v>2.0551700592041</v>
       </c>
       <c r="H525" t="n">
         <v>14380</v>
@@ -15623,7 +15623,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G526" t="n">
-        <v>2.04735517501831</v>
+        <v>2.04735541343689</v>
       </c>
       <c r="H526" t="n">
         <v>13140</v>
@@ -15652,7 +15652,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G527" t="n">
-        <v>2.04735517501831</v>
+        <v>2.04735541343689</v>
       </c>
       <c r="H527" t="n">
         <v>1930</v>
@@ -15681,7 +15681,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G528" t="n">
-        <v>2.05517029762268</v>
+        <v>2.0551700592041</v>
       </c>
       <c r="H528" t="n">
         <v>4970</v>
@@ -15710,7 +15710,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G529" t="n">
-        <v>2.04735517501831</v>
+        <v>2.04735541343689</v>
       </c>
       <c r="H529" t="n">
         <v>6486</v>
@@ -15739,7 +15739,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G530" t="n">
-        <v>2.08642745018005</v>
+        <v>2.08642721176147</v>
       </c>
       <c r="H530" t="n">
         <v>11459</v>
@@ -16000,7 +16000,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G539" t="n">
-        <v>1.98484086990356</v>
+        <v>1.98484075069427</v>
       </c>
       <c r="H539" t="n">
         <v>4051</v>
@@ -16058,7 +16058,7 @@
         <v>2.5</v>
       </c>
       <c r="G541" t="n">
-        <v>1.95358347892761</v>
+        <v>1.95358335971832</v>
       </c>
       <c r="H541" t="n">
         <v>1628</v>
@@ -16087,7 +16087,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G542" t="n">
-        <v>1.89106869697571</v>
+        <v>1.891068816185</v>
       </c>
       <c r="H542" t="n">
         <v>4966</v>
@@ -16145,7 +16145,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G544" t="n">
-        <v>1.89106869697571</v>
+        <v>1.891068816185</v>
       </c>
       <c r="H544" t="n">
         <v>1977</v>
@@ -16174,7 +16174,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G545" t="n">
-        <v>1.98484086990356</v>
+        <v>1.98484075069427</v>
       </c>
       <c r="H545" t="n">
         <v>7157</v>
@@ -16203,7 +16203,7 @@
         <v>2.5</v>
       </c>
       <c r="G546" t="n">
-        <v>1.95358347892761</v>
+        <v>1.95358335971832</v>
       </c>
       <c r="H546" t="n">
         <v>13540</v>
@@ -16232,7 +16232,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G547" t="n">
-        <v>1.96921217441559</v>
+        <v>1.96921193599701</v>
       </c>
       <c r="H547" t="n">
         <v>4409</v>
@@ -16261,7 +16261,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G548" t="n">
-        <v>1.96921217441559</v>
+        <v>1.96921193599701</v>
       </c>
       <c r="H548" t="n">
         <v>2935</v>
@@ -16290,7 +16290,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G549" t="n">
-        <v>1.93795502185822</v>
+        <v>1.93795490264893</v>
       </c>
       <c r="H549" t="n">
         <v>78</v>
@@ -16319,7 +16319,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G550" t="n">
-        <v>2.04735517501831</v>
+        <v>2.04735541343689</v>
       </c>
       <c r="H550" t="n">
         <v>12782</v>
@@ -16377,7 +16377,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G552" t="n">
-        <v>2.02391242980957</v>
+        <v>2.02391266822815</v>
       </c>
       <c r="H552" t="n">
         <v>3342</v>
@@ -16435,7 +16435,7 @@
         <v>2.5</v>
       </c>
       <c r="G554" t="n">
-        <v>1.95358347892761</v>
+        <v>1.95358335971832</v>
       </c>
       <c r="H554" t="n">
         <v>801</v>
@@ -16464,7 +16464,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G555" t="n">
-        <v>1.87544047832489</v>
+        <v>1.87544012069702</v>
       </c>
       <c r="H555" t="n">
         <v>11021</v>
@@ -16493,7 +16493,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G556" t="n">
-        <v>1.86762571334839</v>
+        <v>1.86762595176697</v>
       </c>
       <c r="H556" t="n">
         <v>3914</v>
@@ -16522,7 +16522,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G557" t="n">
-        <v>1.87544047832489</v>
+        <v>1.87544012069702</v>
       </c>
       <c r="H557" t="n">
         <v>9292</v>
@@ -16551,7 +16551,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G558" t="n">
-        <v>1.88325464725494</v>
+        <v>1.88325452804565</v>
       </c>
       <c r="H558" t="n">
         <v>7999</v>
@@ -16580,7 +16580,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G559" t="n">
-        <v>1.87544047832489</v>
+        <v>1.87544012069702</v>
       </c>
       <c r="H559" t="n">
         <v>2957</v>
@@ -16609,7 +16609,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G560" t="n">
-        <v>1.89888334274292</v>
+        <v>1.89888298511505</v>
       </c>
       <c r="H560" t="n">
         <v>4094</v>
@@ -16638,7 +16638,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G561" t="n">
-        <v>1.89888334274292</v>
+        <v>1.89888298511505</v>
       </c>
       <c r="H561" t="n">
         <v>2899</v>
@@ -16667,7 +16667,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G562" t="n">
-        <v>1.88325464725494</v>
+        <v>1.88325452804565</v>
       </c>
       <c r="H562" t="n">
         <v>12511</v>
@@ -16754,7 +16754,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G565" t="n">
-        <v>1.91451215744019</v>
+        <v>1.91451179981232</v>
       </c>
       <c r="H565" t="n">
         <v>930</v>
@@ -16783,7 +16783,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G566" t="n">
-        <v>1.87544047832489</v>
+        <v>1.87544012069702</v>
       </c>
       <c r="H566" t="n">
         <v>3211</v>
@@ -16812,7 +16812,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G567" t="n">
-        <v>1.87544047832489</v>
+        <v>1.87544012069702</v>
       </c>
       <c r="H567" t="n">
         <v>2215</v>
@@ -16841,7 +16841,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G568" t="n">
-        <v>1.86762571334839</v>
+        <v>1.86762595176697</v>
       </c>
       <c r="H568" t="n">
         <v>5620</v>
@@ -16870,7 +16870,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G569" t="n">
-        <v>1.84418261051178</v>
+        <v>1.84418284893036</v>
       </c>
       <c r="H569" t="n">
         <v>2584</v>
@@ -17131,7 +17131,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G578" t="n">
-        <v>2.05517029762268</v>
+        <v>2.0551700592041</v>
       </c>
       <c r="H578" t="n">
         <v>3757</v>
@@ -17189,7 +17189,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G580" t="n">
-        <v>2.04735517501831</v>
+        <v>2.04735541343689</v>
       </c>
       <c r="H580" t="n">
         <v>2057</v>
@@ -17247,7 +17247,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G582" t="n">
-        <v>1.98484086990356</v>
+        <v>1.98484075069427</v>
       </c>
       <c r="H582" t="n">
         <v>5772</v>
@@ -17276,7 +17276,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G583" t="n">
-        <v>1.98484086990356</v>
+        <v>1.98484075069427</v>
       </c>
       <c r="H583" t="n">
         <v>817</v>
@@ -17305,7 +17305,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G584" t="n">
-        <v>1.96139800548553</v>
+        <v>1.96139788627625</v>
       </c>
       <c r="H584" t="n">
         <v>534</v>
@@ -17363,7 +17363,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G586" t="n">
-        <v>2.02391242980957</v>
+        <v>2.02391266822815</v>
       </c>
       <c r="H586" t="n">
         <v>4748</v>
@@ -17421,7 +17421,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G588" t="n">
-        <v>1.96921217441559</v>
+        <v>1.96921193599701</v>
       </c>
       <c r="H588" t="n">
         <v>1223</v>
@@ -17479,7 +17479,7 @@
         <v>2.5</v>
       </c>
       <c r="G590" t="n">
-        <v>1.95358347892761</v>
+        <v>1.95358335971832</v>
       </c>
       <c r="H590" t="n">
         <v>6559</v>
@@ -17508,7 +17508,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G591" t="n">
-        <v>1.93795502185822</v>
+        <v>1.93795490264893</v>
       </c>
       <c r="H591" t="n">
         <v>11871</v>
@@ -17537,7 +17537,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G592" t="n">
-        <v>1.96921217441559</v>
+        <v>1.96921193599701</v>
       </c>
       <c r="H592" t="n">
         <v>100</v>
@@ -17566,7 +17566,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G593" t="n">
-        <v>1.89888334274292</v>
+        <v>1.89888298511505</v>
       </c>
       <c r="H593" t="n">
         <v>219</v>
@@ -17595,7 +17595,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G594" t="n">
-        <v>1.96921217441559</v>
+        <v>1.96921193599701</v>
       </c>
       <c r="H594" t="n">
         <v>28</v>
@@ -17624,7 +17624,7 @@
         <v>2.5</v>
       </c>
       <c r="G595" t="n">
-        <v>1.95358347892761</v>
+        <v>1.95358335971832</v>
       </c>
       <c r="H595" t="n">
         <v>2570</v>
@@ -17653,7 +17653,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G596" t="n">
-        <v>1.930140376091</v>
+        <v>1.93014049530029</v>
       </c>
       <c r="H596" t="n">
         <v>321</v>
@@ -17682,7 +17682,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G597" t="n">
-        <v>1.930140376091</v>
+        <v>1.93014049530029</v>
       </c>
       <c r="H597" t="n">
         <v>1300</v>
@@ -17711,7 +17711,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G598" t="n">
-        <v>1.93795502185822</v>
+        <v>1.93795490264893</v>
       </c>
       <c r="H598" t="n">
         <v>301</v>
@@ -17740,7 +17740,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G599" t="n">
-        <v>1.91451215744019</v>
+        <v>1.91451179981232</v>
       </c>
       <c r="H599" t="n">
         <v>16585</v>
@@ -17827,7 +17827,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G602" t="n">
-        <v>1.89106869697571</v>
+        <v>1.891068816185</v>
       </c>
       <c r="H602" t="n">
         <v>3186</v>
@@ -17885,7 +17885,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G604" t="n">
-        <v>1.93795502185822</v>
+        <v>1.93795490264893</v>
       </c>
       <c r="H604" t="n">
         <v>100</v>
@@ -17914,7 +17914,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G605" t="n">
-        <v>1.89106869697571</v>
+        <v>1.891068816185</v>
       </c>
       <c r="H605" t="n">
         <v>12977</v>
@@ -17943,7 +17943,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G606" t="n">
-        <v>1.87544047832489</v>
+        <v>1.87544012069702</v>
       </c>
       <c r="H606" t="n">
         <v>311</v>
@@ -17972,7 +17972,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G607" t="n">
-        <v>1.87544047832489</v>
+        <v>1.87544012069702</v>
       </c>
       <c r="H607" t="n">
         <v>1604</v>
@@ -18001,7 +18001,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G608" t="n">
-        <v>1.87544047832489</v>
+        <v>1.87544012069702</v>
       </c>
       <c r="H608" t="n">
         <v>5380</v>
@@ -18030,7 +18030,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G609" t="n">
-        <v>1.85199701786041</v>
+        <v>1.8519971370697</v>
       </c>
       <c r="H609" t="n">
         <v>700</v>
@@ -18059,7 +18059,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G610" t="n">
-        <v>1.84418261051178</v>
+        <v>1.84418284893036</v>
       </c>
       <c r="H610" t="n">
         <v>4036</v>
@@ -18088,7 +18088,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G611" t="n">
-        <v>1.84418261051178</v>
+        <v>1.84418284893036</v>
       </c>
       <c r="H611" t="n">
         <v>937</v>
@@ -18117,7 +18117,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G612" t="n">
-        <v>1.85981178283691</v>
+        <v>1.85981154441833</v>
       </c>
       <c r="H612" t="n">
         <v>992</v>
@@ -18146,7 +18146,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G613" t="n">
-        <v>1.78166818618774</v>
+        <v>1.78166806697845</v>
       </c>
       <c r="H613" t="n">
         <v>2844</v>
@@ -18204,7 +18204,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G615" t="n">
-        <v>1.88325464725494</v>
+        <v>1.88325452804565</v>
       </c>
       <c r="H615" t="n">
         <v>100</v>
@@ -18233,7 +18233,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G616" t="n">
-        <v>1.88325464725494</v>
+        <v>1.88325452804565</v>
       </c>
       <c r="H616" t="n">
         <v>0</v>
@@ -18262,7 +18262,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G617" t="n">
-        <v>1.87544047832489</v>
+        <v>1.87544012069702</v>
       </c>
       <c r="H617" t="n">
         <v>1865</v>
@@ -18291,7 +18291,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G618" t="n">
-        <v>1.84418261051178</v>
+        <v>1.84418284893036</v>
       </c>
       <c r="H618" t="n">
         <v>2111</v>
@@ -18320,7 +18320,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G619" t="n">
-        <v>1.89106869697571</v>
+        <v>1.891068816185</v>
       </c>
       <c r="H619" t="n">
         <v>4395</v>
@@ -18349,7 +18349,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G620" t="n">
-        <v>1.82073962688446</v>
+        <v>1.82073974609375</v>
       </c>
       <c r="H620" t="n">
         <v>2510</v>
@@ -18378,7 +18378,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G621" t="n">
-        <v>1.86762571334839</v>
+        <v>1.86762595176697</v>
       </c>
       <c r="H621" t="n">
         <v>16907</v>
@@ -18407,7 +18407,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G622" t="n">
-        <v>1.84418261051178</v>
+        <v>1.84418284893036</v>
       </c>
       <c r="H622" t="n">
         <v>1654</v>
@@ -18465,7 +18465,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G624" t="n">
-        <v>1.86762571334839</v>
+        <v>1.86762595176697</v>
       </c>
       <c r="H624" t="n">
         <v>5391</v>
@@ -18494,7 +18494,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G625" t="n">
-        <v>1.91451215744019</v>
+        <v>1.91451179981232</v>
       </c>
       <c r="H625" t="n">
         <v>1010</v>
@@ -18523,7 +18523,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G626" t="n">
-        <v>1.86762571334839</v>
+        <v>1.86762595176697</v>
       </c>
       <c r="H626" t="n">
         <v>4224</v>
@@ -18552,7 +18552,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G627" t="n">
-        <v>1.82073962688446</v>
+        <v>1.82073974609375</v>
       </c>
       <c r="H627" t="n">
         <v>5337</v>
@@ -18581,7 +18581,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G628" t="n">
-        <v>1.85199701786041</v>
+        <v>1.8519971370697</v>
       </c>
       <c r="H628" t="n">
         <v>767</v>
@@ -18610,7 +18610,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G629" t="n">
-        <v>1.83636856079102</v>
+        <v>1.83636832237244</v>
       </c>
       <c r="H629" t="n">
         <v>2700</v>
@@ -18639,7 +18639,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G630" t="n">
-        <v>1.84418261051178</v>
+        <v>1.84418284893036</v>
       </c>
       <c r="H630" t="n">
         <v>470</v>
@@ -18697,7 +18697,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G632" t="n">
-        <v>1.76603949069977</v>
+        <v>1.76603937149048</v>
       </c>
       <c r="H632" t="n">
         <v>2150</v>
@@ -18726,7 +18726,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G633" t="n">
-        <v>1.76603949069977</v>
+        <v>1.76603937149048</v>
       </c>
       <c r="H633" t="n">
         <v>0</v>
@@ -18755,7 +18755,7 @@
         <v>2.25</v>
       </c>
       <c r="G634" t="n">
-        <v>1.75822520256042</v>
+        <v>1.75822496414185</v>
       </c>
       <c r="H634" t="n">
         <v>3308</v>
@@ -18784,7 +18784,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G635" t="n">
-        <v>1.72696769237518</v>
+        <v>1.72696805000305</v>
       </c>
       <c r="H635" t="n">
         <v>2340</v>
@@ -18813,7 +18813,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G636" t="n">
-        <v>1.7504106760025</v>
+        <v>1.75041079521179</v>
       </c>
       <c r="H636" t="n">
         <v>116</v>
@@ -18842,7 +18842,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G637" t="n">
-        <v>1.78166818618774</v>
+        <v>1.78166806697845</v>
       </c>
       <c r="H637" t="n">
         <v>4216</v>
@@ -18871,7 +18871,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G638" t="n">
-        <v>1.82073962688446</v>
+        <v>1.82073974609375</v>
       </c>
       <c r="H638" t="n">
         <v>1300</v>
@@ -18929,7 +18929,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G640" t="n">
-        <v>1.71915352344513</v>
+        <v>1.71915376186371</v>
       </c>
       <c r="H640" t="n">
         <v>7930</v>
@@ -18958,7 +18958,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G641" t="n">
-        <v>1.71915352344513</v>
+        <v>1.71915376186371</v>
       </c>
       <c r="H641" t="n">
         <v>7808</v>
@@ -18987,7 +18987,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G642" t="n">
-        <v>1.7504106760025</v>
+        <v>1.75041079521179</v>
       </c>
       <c r="H642" t="n">
         <v>870</v>
@@ -19016,7 +19016,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G643" t="n">
-        <v>1.71915352344513</v>
+        <v>1.71915376186371</v>
       </c>
       <c r="H643" t="n">
         <v>3579</v>
@@ -19045,7 +19045,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G644" t="n">
-        <v>1.74259662628174</v>
+        <v>1.74259638786316</v>
       </c>
       <c r="H644" t="n">
         <v>1986</v>
@@ -19074,7 +19074,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G645" t="n">
-        <v>1.71915352344513</v>
+        <v>1.71915376186371</v>
       </c>
       <c r="H645" t="n">
         <v>380</v>
@@ -19103,7 +19103,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G646" t="n">
-        <v>1.71915352344513</v>
+        <v>1.71915376186371</v>
       </c>
       <c r="H646" t="n">
         <v>7131</v>
@@ -19132,7 +19132,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G647" t="n">
-        <v>1.71915352344513</v>
+        <v>1.71915376186371</v>
       </c>
       <c r="H647" t="n">
         <v>1204</v>
@@ -19161,7 +19161,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G648" t="n">
-        <v>1.71915352344513</v>
+        <v>1.71915376186371</v>
       </c>
       <c r="H648" t="n">
         <v>4223</v>
@@ -19190,7 +19190,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G649" t="n">
-        <v>1.70352482795715</v>
+        <v>1.70352494716644</v>
       </c>
       <c r="H649" t="n">
         <v>1910</v>
@@ -19219,7 +19219,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G650" t="n">
-        <v>1.71915352344513</v>
+        <v>1.71915376186371</v>
       </c>
       <c r="H650" t="n">
         <v>1700</v>
@@ -19306,7 +19306,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G653" t="n">
-        <v>1.66445302963257</v>
+        <v>1.66445326805115</v>
       </c>
       <c r="H653" t="n">
         <v>1170</v>
@@ -19335,7 +19335,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G654" t="n">
-        <v>1.66445302963257</v>
+        <v>1.66445326805115</v>
       </c>
       <c r="H654" t="n">
         <v>891</v>
@@ -19422,7 +19422,7 @@
         <v>2</v>
       </c>
       <c r="G657" t="n">
-        <v>1.56286680698395</v>
+        <v>1.56286692619324</v>
       </c>
       <c r="H657" t="n">
         <v>7242</v>
@@ -19451,7 +19451,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G658" t="n">
-        <v>1.5941241979599</v>
+        <v>1.59412407875061</v>
       </c>
       <c r="H658" t="n">
         <v>5786</v>
@@ -19480,7 +19480,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G659" t="n">
-        <v>1.60193848609924</v>
+        <v>1.60193836688995</v>
       </c>
       <c r="H659" t="n">
         <v>9353</v>
@@ -19509,7 +19509,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G660" t="n">
-        <v>1.64101004600525</v>
+        <v>1.64101016521454</v>
       </c>
       <c r="H660" t="n">
         <v>2150</v>
@@ -19538,7 +19538,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G661" t="n">
-        <v>1.60193848609924</v>
+        <v>1.60193836688995</v>
       </c>
       <c r="H661" t="n">
         <v>790</v>
@@ -19567,7 +19567,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G662" t="n">
-        <v>1.60975289344788</v>
+        <v>1.6097526550293</v>
       </c>
       <c r="H662" t="n">
         <v>1581</v>
@@ -19741,7 +19741,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G668" t="n">
-        <v>1.88325464725494</v>
+        <v>1.88325452804565</v>
       </c>
       <c r="H668" t="n">
         <v>20273</v>
@@ -19828,7 +19828,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G671" t="n">
-        <v>1.930140376091</v>
+        <v>1.93014049530029</v>
       </c>
       <c r="H671" t="n">
         <v>41175</v>
@@ -19857,7 +19857,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G672" t="n">
-        <v>1.89888334274292</v>
+        <v>1.89888298511505</v>
       </c>
       <c r="H672" t="n">
         <v>10847</v>
@@ -19944,7 +19944,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G675" t="n">
-        <v>1.89106869697571</v>
+        <v>1.891068816185</v>
       </c>
       <c r="H675" t="n">
         <v>16914</v>
@@ -19973,7 +19973,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G676" t="n">
-        <v>1.91451215744019</v>
+        <v>1.91451179981232</v>
       </c>
       <c r="H676" t="n">
         <v>18044</v>
@@ -20002,7 +20002,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G677" t="n">
-        <v>1.88325464725494</v>
+        <v>1.88325452804565</v>
       </c>
       <c r="H677" t="n">
         <v>24276</v>
@@ -20060,7 +20060,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G679" t="n">
-        <v>1.85981178283691</v>
+        <v>1.85981154441833</v>
       </c>
       <c r="H679" t="n">
         <v>1203</v>
@@ -20118,7 +20118,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G681" t="n">
-        <v>1.76603949069977</v>
+        <v>1.76603937149048</v>
       </c>
       <c r="H681" t="n">
         <v>6126</v>
@@ -20147,7 +20147,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G682" t="n">
-        <v>1.70352482795715</v>
+        <v>1.70352494716644</v>
       </c>
       <c r="H682" t="n">
         <v>21460</v>
@@ -20176,7 +20176,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G683" t="n">
-        <v>1.91451215744019</v>
+        <v>1.91451179981232</v>
       </c>
       <c r="H683" t="n">
         <v>82840</v>
@@ -20205,7 +20205,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G684" t="n">
-        <v>1.82073962688446</v>
+        <v>1.82073974609375</v>
       </c>
       <c r="H684" t="n">
         <v>79297</v>
@@ -20234,7 +20234,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G685" t="n">
-        <v>1.76603949069977</v>
+        <v>1.76603937149048</v>
       </c>
       <c r="H685" t="n">
         <v>13837</v>
@@ -20263,7 +20263,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G686" t="n">
-        <v>1.78166818618774</v>
+        <v>1.78166806697845</v>
       </c>
       <c r="H686" t="n">
         <v>16568</v>
@@ -20292,7 +20292,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G687" t="n">
-        <v>1.76603949069977</v>
+        <v>1.76603937149048</v>
       </c>
       <c r="H687" t="n">
         <v>11052</v>
@@ -20321,7 +20321,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G688" t="n">
-        <v>1.76603949069977</v>
+        <v>1.76603937149048</v>
       </c>
       <c r="H688" t="n">
         <v>8342</v>
@@ -20350,7 +20350,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G689" t="n">
-        <v>1.78166818618774</v>
+        <v>1.78166806697845</v>
       </c>
       <c r="H689" t="n">
         <v>4504</v>
@@ -20379,7 +20379,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G690" t="n">
-        <v>1.7504106760025</v>
+        <v>1.75041079521179</v>
       </c>
       <c r="H690" t="n">
         <v>2392</v>
@@ -20408,7 +20408,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G691" t="n">
-        <v>1.71915352344513</v>
+        <v>1.71915376186371</v>
       </c>
       <c r="H691" t="n">
         <v>22928</v>
@@ -20437,7 +20437,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G692" t="n">
-        <v>1.70352482795715</v>
+        <v>1.70352494716644</v>
       </c>
       <c r="H692" t="n">
         <v>29415</v>
@@ -20466,7 +20466,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G693" t="n">
-        <v>1.66445302963257</v>
+        <v>1.66445326805115</v>
       </c>
       <c r="H693" t="n">
         <v>31190</v>
@@ -20495,7 +20495,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G694" t="n">
-        <v>1.66445302963257</v>
+        <v>1.66445326805115</v>
       </c>
       <c r="H694" t="n">
         <v>9856</v>
@@ -20640,7 +20640,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G699" t="n">
-        <v>1.74259662628174</v>
+        <v>1.74259638786316</v>
       </c>
       <c r="H699" t="n">
         <v>125437</v>
@@ -20669,7 +20669,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G700" t="n">
-        <v>1.78166818618774</v>
+        <v>1.78166806697845</v>
       </c>
       <c r="H700" t="n">
         <v>16469</v>
@@ -20698,7 +20698,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G701" t="n">
-        <v>1.70352482795715</v>
+        <v>1.70352494716644</v>
       </c>
       <c r="H701" t="n">
         <v>20038</v>
@@ -20727,7 +20727,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G702" t="n">
-        <v>1.69571053981781</v>
+        <v>1.69571042060852</v>
       </c>
       <c r="H702" t="n">
         <v>42863</v>
@@ -20785,7 +20785,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G704" t="n">
-        <v>1.71133935451508</v>
+        <v>1.71133947372437</v>
       </c>
       <c r="H704" t="n">
         <v>104789</v>
@@ -20814,7 +20814,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G705" t="n">
-        <v>1.69571053981781</v>
+        <v>1.69571042060852</v>
       </c>
       <c r="H705" t="n">
         <v>9685</v>
@@ -20843,7 +20843,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G706" t="n">
-        <v>1.68789625167847</v>
+        <v>1.68789613246918</v>
       </c>
       <c r="H706" t="n">
         <v>4340</v>
@@ -20901,7 +20901,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G708" t="n">
-        <v>1.64101004600525</v>
+        <v>1.64101016521454</v>
       </c>
       <c r="H708" t="n">
         <v>1684</v>
@@ -20930,7 +20930,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G709" t="n">
-        <v>1.68789625167847</v>
+        <v>1.68789613246918</v>
       </c>
       <c r="H709" t="n">
         <v>23100</v>
@@ -21075,7 +21075,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G714" t="n">
-        <v>1.64101004600525</v>
+        <v>1.64101016521454</v>
       </c>
       <c r="H714" t="n">
         <v>318</v>
@@ -21162,7 +21162,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G717" t="n">
-        <v>1.58630979061127</v>
+        <v>1.58630967140198</v>
       </c>
       <c r="H717" t="n">
         <v>4983</v>
@@ -21191,7 +21191,7 @@
         <v>2</v>
       </c>
       <c r="G718" t="n">
-        <v>1.56286680698395</v>
+        <v>1.56286692619324</v>
       </c>
       <c r="H718" t="n">
         <v>6637</v>
@@ -21220,7 +21220,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G719" t="n">
-        <v>1.54723811149597</v>
+        <v>1.54723823070526</v>
       </c>
       <c r="H719" t="n">
         <v>9044</v>
@@ -21278,7 +21278,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G721" t="n">
-        <v>1.54723811149597</v>
+        <v>1.54723823070526</v>
       </c>
       <c r="H721" t="n">
         <v>4279</v>
@@ -21336,7 +21336,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G723" t="n">
-        <v>1.60193848609924</v>
+        <v>1.60193836688995</v>
       </c>
       <c r="H723" t="n">
         <v>33</v>
@@ -21365,7 +21365,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G724" t="n">
-        <v>1.60193848609924</v>
+        <v>1.60193836688995</v>
       </c>
       <c r="H724" t="n">
         <v>1593</v>
@@ -21394,7 +21394,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G725" t="n">
-        <v>1.60193848609924</v>
+        <v>1.60193836688995</v>
       </c>
       <c r="H725" t="n">
         <v>772</v>
@@ -21423,7 +21423,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G726" t="n">
-        <v>1.60193848609924</v>
+        <v>1.60193836688995</v>
       </c>
       <c r="H726" t="n">
         <v>1638</v>
@@ -21452,7 +21452,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G727" t="n">
-        <v>1.60193848609924</v>
+        <v>1.60193836688995</v>
       </c>
       <c r="H727" t="n">
         <v>0</v>
@@ -21481,7 +21481,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G728" t="n">
-        <v>1.5941241979599</v>
+        <v>1.59412407875061</v>
       </c>
       <c r="H728" t="n">
         <v>2500</v>
@@ -21568,7 +21568,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G731" t="n">
-        <v>1.54723811149597</v>
+        <v>1.54723823070526</v>
       </c>
       <c r="H731" t="n">
         <v>2640</v>
@@ -21597,7 +21597,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G732" t="n">
-        <v>1.60193848609924</v>
+        <v>1.60193836688995</v>
       </c>
       <c r="H732" t="n">
         <v>686</v>
@@ -21626,7 +21626,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G733" t="n">
-        <v>1.54723811149597</v>
+        <v>1.54723823070526</v>
       </c>
       <c r="H733" t="n">
         <v>10612</v>
@@ -21655,7 +21655,7 @@
         <v>2</v>
       </c>
       <c r="G734" t="n">
-        <v>1.56286680698395</v>
+        <v>1.56286692619324</v>
       </c>
       <c r="H734" t="n">
         <v>1000</v>
@@ -21713,7 +21713,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G736" t="n">
-        <v>1.53160953521729</v>
+        <v>1.531609416008</v>
       </c>
       <c r="H736" t="n">
         <v>1180</v>
@@ -21742,7 +21742,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G737" t="n">
-        <v>1.50816655158997</v>
+        <v>1.50816643238068</v>
       </c>
       <c r="H737" t="n">
         <v>2610</v>
@@ -21771,7 +21771,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G738" t="n">
-        <v>1.50035214424133</v>
+        <v>1.50035226345062</v>
       </c>
       <c r="H738" t="n">
         <v>3783</v>
@@ -21800,7 +21800,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G739" t="n">
-        <v>1.49253785610199</v>
+        <v>1.49253797531128</v>
       </c>
       <c r="H739" t="n">
         <v>1588</v>
@@ -21829,7 +21829,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G740" t="n">
-        <v>1.53160953521729</v>
+        <v>1.531609416008</v>
       </c>
       <c r="H740" t="n">
         <v>1201</v>
@@ -21858,7 +21858,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G741" t="n">
-        <v>1.50035214424133</v>
+        <v>1.50035226345062</v>
       </c>
       <c r="H741" t="n">
         <v>1657</v>
@@ -21887,7 +21887,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G742" t="n">
-        <v>1.50816655158997</v>
+        <v>1.50816643238068</v>
       </c>
       <c r="H742" t="n">
         <v>8117</v>
@@ -21916,7 +21916,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G743" t="n">
-        <v>1.60975289344788</v>
+        <v>1.6097526550293</v>
       </c>
       <c r="H743" t="n">
         <v>83441</v>
@@ -21974,7 +21974,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G745" t="n">
-        <v>1.54723811149597</v>
+        <v>1.54723823070526</v>
       </c>
       <c r="H745" t="n">
         <v>6604</v>
@@ -22003,7 +22003,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G746" t="n">
-        <v>1.5941241979599</v>
+        <v>1.59412407875061</v>
       </c>
       <c r="H746" t="n">
         <v>4010</v>
@@ -22032,7 +22032,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G747" t="n">
-        <v>1.58630979061127</v>
+        <v>1.58630967140198</v>
       </c>
       <c r="H747" t="n">
         <v>1818</v>
@@ -22061,7 +22061,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G748" t="n">
-        <v>1.58630979061127</v>
+        <v>1.58630967140198</v>
       </c>
       <c r="H748" t="n">
         <v>5636</v>
@@ -22090,7 +22090,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G749" t="n">
-        <v>1.58630979061127</v>
+        <v>1.58630967140198</v>
       </c>
       <c r="H749" t="n">
         <v>4728</v>
@@ -22177,7 +22177,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G752" t="n">
-        <v>1.52379524707794</v>
+        <v>1.52379512786865</v>
       </c>
       <c r="H752" t="n">
         <v>2112</v>
@@ -22206,7 +22206,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G753" t="n">
-        <v>1.52379524707794</v>
+        <v>1.52379512786865</v>
       </c>
       <c r="H753" t="n">
         <v>2730</v>
@@ -22235,7 +22235,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G754" t="n">
-        <v>1.52379524707794</v>
+        <v>1.52379512786865</v>
       </c>
       <c r="H754" t="n">
         <v>116</v>
@@ -22264,7 +22264,7 @@
         <v>2</v>
       </c>
       <c r="G755" t="n">
-        <v>1.56286680698395</v>
+        <v>1.56286692619324</v>
       </c>
       <c r="H755" t="n">
         <v>4200</v>
@@ -22322,7 +22322,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G757" t="n">
-        <v>1.50816655158997</v>
+        <v>1.50816643238068</v>
       </c>
       <c r="H757" t="n">
         <v>390</v>
@@ -22438,7 +22438,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G761" t="n">
-        <v>1.49253785610199</v>
+        <v>1.49253797531128</v>
       </c>
       <c r="H761" t="n">
         <v>6174</v>
@@ -22467,7 +22467,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G762" t="n">
-        <v>1.47690916061401</v>
+        <v>1.47690904140472</v>
       </c>
       <c r="H762" t="n">
         <v>4134</v>
@@ -22525,7 +22525,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G764" t="n">
-        <v>1.50816655158997</v>
+        <v>1.50816643238068</v>
       </c>
       <c r="H764" t="n">
         <v>2240</v>
@@ -22554,7 +22554,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G765" t="n">
-        <v>1.74259662628174</v>
+        <v>1.74259638786316</v>
       </c>
       <c r="H765" t="n">
         <v>62191</v>
@@ -22612,7 +22612,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G767" t="n">
-        <v>1.58630979061127</v>
+        <v>1.58630967140198</v>
       </c>
       <c r="H767" t="n">
         <v>8040</v>
@@ -22670,7 +22670,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G769" t="n">
-        <v>1.58630979061127</v>
+        <v>1.58630967140198</v>
       </c>
       <c r="H769" t="n">
         <v>1450</v>
@@ -22699,7 +22699,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G770" t="n">
-        <v>1.58630979061127</v>
+        <v>1.58630967140198</v>
       </c>
       <c r="H770" t="n">
         <v>1250</v>
@@ -22728,7 +22728,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G771" t="n">
-        <v>1.58630979061127</v>
+        <v>1.58630967140198</v>
       </c>
       <c r="H771" t="n">
         <v>505</v>
@@ -22757,7 +22757,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G772" t="n">
-        <v>1.58630979061127</v>
+        <v>1.58630967140198</v>
       </c>
       <c r="H772" t="n">
         <v>0</v>
@@ -22873,7 +22873,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G776" t="n">
-        <v>1.53160953521729</v>
+        <v>1.531609416008</v>
       </c>
       <c r="H776" t="n">
         <v>5415</v>
@@ -22960,7 +22960,7 @@
         <v>2</v>
       </c>
       <c r="G779" t="n">
-        <v>1.56286680698395</v>
+        <v>1.56286692619324</v>
       </c>
       <c r="H779" t="n">
         <v>770</v>
@@ -22989,7 +22989,7 @@
         <v>2</v>
       </c>
       <c r="G780" t="n">
-        <v>1.56286680698395</v>
+        <v>1.56286692619324</v>
       </c>
       <c r="H780" t="n">
         <v>1385</v>
@@ -23047,7 +23047,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G782" t="n">
-        <v>1.53160953521729</v>
+        <v>1.531609416008</v>
       </c>
       <c r="H782" t="n">
         <v>5650</v>
@@ -23076,7 +23076,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G783" t="n">
-        <v>1.53160953521729</v>
+        <v>1.531609416008</v>
       </c>
       <c r="H783" t="n">
         <v>9208</v>
@@ -23105,7 +23105,7 @@
         <v>2</v>
       </c>
       <c r="G784" t="n">
-        <v>1.56286680698395</v>
+        <v>1.56286692619324</v>
       </c>
       <c r="H784" t="n">
         <v>1630</v>
@@ -23134,7 +23134,7 @@
         <v>2</v>
       </c>
       <c r="G785" t="n">
-        <v>1.56286680698395</v>
+        <v>1.56286692619324</v>
       </c>
       <c r="H785" t="n">
         <v>3493</v>
@@ -23221,7 +23221,7 @@
         <v>2</v>
       </c>
       <c r="G788" t="n">
-        <v>1.56286680698395</v>
+        <v>1.56286692619324</v>
       </c>
       <c r="H788" t="n">
         <v>400</v>
@@ -23250,7 +23250,7 @@
         <v>2</v>
       </c>
       <c r="G789" t="n">
-        <v>1.56286680698395</v>
+        <v>1.56286692619324</v>
       </c>
       <c r="H789" t="n">
         <v>540</v>
@@ -23308,7 +23308,7 @@
         <v>2</v>
       </c>
       <c r="G791" t="n">
-        <v>1.56286680698395</v>
+        <v>1.56286692619324</v>
       </c>
       <c r="H791" t="n">
         <v>88</v>
@@ -23337,7 +23337,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G792" t="n">
-        <v>1.54723811149597</v>
+        <v>1.54723823070526</v>
       </c>
       <c r="H792" t="n">
         <v>3760</v>
@@ -23366,7 +23366,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G793" t="n">
-        <v>1.54723811149597</v>
+        <v>1.54723823070526</v>
       </c>
       <c r="H793" t="n">
         <v>1646</v>
@@ -23395,7 +23395,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G794" t="n">
-        <v>1.54723811149597</v>
+        <v>1.54723823070526</v>
       </c>
       <c r="H794" t="n">
         <v>3700</v>
@@ -23424,7 +23424,7 @@
         <v>2</v>
       </c>
       <c r="G795" t="n">
-        <v>1.56286680698395</v>
+        <v>1.56286692619324</v>
       </c>
       <c r="H795" t="n">
         <v>8735</v>
@@ -23453,7 +23453,7 @@
         <v>2</v>
       </c>
       <c r="G796" t="n">
-        <v>1.56286680698395</v>
+        <v>1.56286692619324</v>
       </c>
       <c r="H796" t="n">
         <v>8350</v>
@@ -23540,7 +23540,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G799" t="n">
-        <v>1.5941241979599</v>
+        <v>1.59412407875061</v>
       </c>
       <c r="H799" t="n">
         <v>10202</v>
@@ -23598,7 +23598,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G801" t="n">
-        <v>1.54723811149597</v>
+        <v>1.54723823070526</v>
       </c>
       <c r="H801" t="n">
         <v>4800</v>
@@ -23656,7 +23656,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G803" t="n">
-        <v>1.58630979061127</v>
+        <v>1.58630967140198</v>
       </c>
       <c r="H803" t="n">
         <v>3550</v>
@@ -23685,7 +23685,7 @@
         <v>2</v>
       </c>
       <c r="G804" t="n">
-        <v>1.56286680698395</v>
+        <v>1.56286692619324</v>
       </c>
       <c r="H804" t="n">
         <v>715</v>
@@ -23714,7 +23714,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G805" t="n">
-        <v>1.5941241979599</v>
+        <v>1.59412407875061</v>
       </c>
       <c r="H805" t="n">
         <v>4829</v>
@@ -23743,7 +23743,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G806" t="n">
-        <v>1.58630979061127</v>
+        <v>1.58630967140198</v>
       </c>
       <c r="H806" t="n">
         <v>9021</v>
@@ -23772,7 +23772,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G807" t="n">
-        <v>1.60975289344788</v>
+        <v>1.6097526550293</v>
       </c>
       <c r="H807" t="n">
         <v>6800</v>
@@ -23801,7 +23801,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G808" t="n">
-        <v>1.58630979061127</v>
+        <v>1.58630967140198</v>
       </c>
       <c r="H808" t="n">
         <v>6622</v>
@@ -23830,7 +23830,7 @@
         <v>2</v>
       </c>
       <c r="G809" t="n">
-        <v>1.56286680698395</v>
+        <v>1.56286692619324</v>
       </c>
       <c r="H809" t="n">
         <v>100</v>
@@ -23859,7 +23859,7 @@
         <v>2</v>
       </c>
       <c r="G810" t="n">
-        <v>1.56286680698395</v>
+        <v>1.56286692619324</v>
       </c>
       <c r="H810" t="n">
         <v>2902</v>
@@ -23946,7 +23946,7 @@
         <v>2</v>
       </c>
       <c r="G813" t="n">
-        <v>1.56286680698395</v>
+        <v>1.56286692619324</v>
       </c>
       <c r="H813" t="n">
         <v>3779</v>
@@ -24004,7 +24004,7 @@
         <v>2</v>
       </c>
       <c r="G815" t="n">
-        <v>1.56286680698395</v>
+        <v>1.56286692619324</v>
       </c>
       <c r="H815" t="n">
         <v>4107</v>
@@ -24033,7 +24033,7 @@
         <v>2</v>
       </c>
       <c r="G816" t="n">
-        <v>1.56286680698395</v>
+        <v>1.56286692619324</v>
       </c>
       <c r="H816" t="n">
         <v>8835</v>
@@ -24091,7 +24091,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G818" t="n">
-        <v>1.60975289344788</v>
+        <v>1.6097526550293</v>
       </c>
       <c r="H818" t="n">
         <v>32403</v>
@@ -24120,7 +24120,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G819" t="n">
-        <v>1.58630979061127</v>
+        <v>1.58630967140198</v>
       </c>
       <c r="H819" t="n">
         <v>15326</v>
@@ -24149,7 +24149,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G820" t="n">
-        <v>1.64101004600525</v>
+        <v>1.64101016521454</v>
       </c>
       <c r="H820" t="n">
         <v>7169</v>
@@ -24294,7 +24294,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G825" t="n">
-        <v>1.58630979061127</v>
+        <v>1.58630967140198</v>
       </c>
       <c r="H825" t="n">
         <v>1500</v>
@@ -24323,7 +24323,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G826" t="n">
-        <v>1.5941241979599</v>
+        <v>1.59412407875061</v>
       </c>
       <c r="H826" t="n">
         <v>4684</v>
@@ -24381,7 +24381,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G828" t="n">
-        <v>1.89106869697571</v>
+        <v>1.891068816185</v>
       </c>
       <c r="H828" t="n">
         <v>164712</v>
@@ -24555,7 +24555,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G834" t="n">
-        <v>1.64101004600525</v>
+        <v>1.64101016521454</v>
       </c>
       <c r="H834" t="n">
         <v>9584</v>
@@ -24584,7 +24584,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G835" t="n">
-        <v>1.60975289344788</v>
+        <v>1.6097526550293</v>
       </c>
       <c r="H835" t="n">
         <v>57779</v>
@@ -24700,7 +24700,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G839" t="n">
-        <v>1.64101004600525</v>
+        <v>1.64101016521454</v>
       </c>
       <c r="H839" t="n">
         <v>10970</v>
@@ -24729,7 +24729,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G840" t="n">
-        <v>1.5941241979599</v>
+        <v>1.59412407875061</v>
       </c>
       <c r="H840" t="n">
         <v>22366</v>
@@ -24758,7 +24758,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G841" t="n">
-        <v>1.64101004600525</v>
+        <v>1.64101016521454</v>
       </c>
       <c r="H841" t="n">
         <v>17557</v>
@@ -24787,7 +24787,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G842" t="n">
-        <v>1.5941241979599</v>
+        <v>1.59412407875061</v>
       </c>
       <c r="H842" t="n">
         <v>34014</v>
@@ -24845,7 +24845,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G844" t="n">
-        <v>1.60975289344788</v>
+        <v>1.6097526550293</v>
       </c>
       <c r="H844" t="n">
         <v>39333</v>
@@ -24903,7 +24903,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G846" t="n">
-        <v>1.60975289344788</v>
+        <v>1.6097526550293</v>
       </c>
       <c r="H846" t="n">
         <v>9208</v>
@@ -24961,7 +24961,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G848" t="n">
-        <v>1.60975289344788</v>
+        <v>1.6097526550293</v>
       </c>
       <c r="H848" t="n">
         <v>10001</v>
@@ -24990,7 +24990,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G849" t="n">
-        <v>1.5941241979599</v>
+        <v>1.59412407875061</v>
       </c>
       <c r="H849" t="n">
         <v>8778</v>
@@ -25019,7 +25019,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G850" t="n">
-        <v>1.5941241979599</v>
+        <v>1.59412407875061</v>
       </c>
       <c r="H850" t="n">
         <v>1999</v>
@@ -25077,7 +25077,7 @@
         <v>2</v>
       </c>
       <c r="G852" t="n">
-        <v>1.56286680698395</v>
+        <v>1.56286692619324</v>
       </c>
       <c r="H852" t="n">
         <v>14569</v>
@@ -25106,7 +25106,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G853" t="n">
-        <v>1.53160953521729</v>
+        <v>1.531609416008</v>
       </c>
       <c r="H853" t="n">
         <v>9826</v>
@@ -25135,7 +25135,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G854" t="n">
-        <v>1.5941241979599</v>
+        <v>1.59412407875061</v>
       </c>
       <c r="H854" t="n">
         <v>10243</v>
@@ -25164,7 +25164,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G855" t="n">
-        <v>1.53160953521729</v>
+        <v>1.531609416008</v>
       </c>
       <c r="H855" t="n">
         <v>30431</v>
@@ -25193,7 +25193,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G856" t="n">
-        <v>1.54723811149597</v>
+        <v>1.54723823070526</v>
       </c>
       <c r="H856" t="n">
         <v>6091</v>
@@ -25222,7 +25222,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G857" t="n">
-        <v>1.53160953521729</v>
+        <v>1.531609416008</v>
       </c>
       <c r="H857" t="n">
         <v>8665</v>
@@ -25309,7 +25309,7 @@
         <v>2</v>
       </c>
       <c r="G860" t="n">
-        <v>1.56286680698395</v>
+        <v>1.56286692619324</v>
       </c>
       <c r="H860" t="n">
         <v>500</v>
@@ -25338,7 +25338,7 @@
         <v>2</v>
       </c>
       <c r="G861" t="n">
-        <v>1.56286680698395</v>
+        <v>1.56286692619324</v>
       </c>
       <c r="H861" t="n">
         <v>0</v>
@@ -25454,7 +25454,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G865" t="n">
-        <v>1.50035214424133</v>
+        <v>1.50035226345062</v>
       </c>
       <c r="H865" t="n">
         <v>6903</v>
@@ -25483,7 +25483,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G866" t="n">
-        <v>1.50035214424133</v>
+        <v>1.50035226345062</v>
       </c>
       <c r="H866" t="n">
         <v>8355</v>
@@ -25512,7 +25512,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G867" t="n">
-        <v>1.53160953521729</v>
+        <v>1.531609416008</v>
       </c>
       <c r="H867" t="n">
         <v>3500</v>
@@ -25541,7 +25541,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G868" t="n">
-        <v>1.46909487247467</v>
+        <v>1.46909475326538</v>
       </c>
       <c r="H868" t="n">
         <v>28560</v>
@@ -25599,7 +25599,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G870" t="n">
-        <v>1.46909487247467</v>
+        <v>1.46909475326538</v>
       </c>
       <c r="H870" t="n">
         <v>3044</v>
@@ -25628,7 +25628,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G871" t="n">
-        <v>1.50035214424133</v>
+        <v>1.50035226345062</v>
       </c>
       <c r="H871" t="n">
         <v>1918</v>
@@ -25657,7 +25657,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G872" t="n">
-        <v>1.50035214424133</v>
+        <v>1.50035226345062</v>
       </c>
       <c r="H872" t="n">
         <v>0</v>
@@ -25686,7 +25686,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G873" t="n">
-        <v>1.46909487247467</v>
+        <v>1.46909475326538</v>
       </c>
       <c r="H873" t="n">
         <v>710</v>
@@ -25831,7 +25831,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G878" t="n">
-        <v>1.53160953521729</v>
+        <v>1.531609416008</v>
       </c>
       <c r="H878" t="n">
         <v>2050</v>
@@ -25889,7 +25889,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G880" t="n">
-        <v>1.46909487247467</v>
+        <v>1.46909475326538</v>
       </c>
       <c r="H880" t="n">
         <v>22334</v>
@@ -25947,7 +25947,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G882" t="n">
-        <v>1.43783760070801</v>
+        <v>1.43783736228943</v>
       </c>
       <c r="H882" t="n">
         <v>3065</v>
@@ -26034,7 +26034,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G885" t="n">
-        <v>1.43783760070801</v>
+        <v>1.43783736228943</v>
       </c>
       <c r="H885" t="n">
         <v>29</v>
@@ -26063,7 +26063,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G886" t="n">
-        <v>1.46909487247467</v>
+        <v>1.46909475326538</v>
       </c>
       <c r="H886" t="n">
         <v>4151</v>
@@ -26237,7 +26237,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G892" t="n">
-        <v>1.53160953521729</v>
+        <v>1.531609416008</v>
       </c>
       <c r="H892" t="n">
         <v>6177</v>
@@ -26324,7 +26324,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G895" t="n">
-        <v>1.53160953521729</v>
+        <v>1.531609416008</v>
       </c>
       <c r="H895" t="n">
         <v>4132</v>
@@ -26353,7 +26353,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G896" t="n">
-        <v>1.53160953521729</v>
+        <v>1.531609416008</v>
       </c>
       <c r="H896" t="n">
         <v>15658</v>
@@ -26382,7 +26382,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G897" t="n">
-        <v>1.54723811149597</v>
+        <v>1.54723823070526</v>
       </c>
       <c r="H897" t="n">
         <v>12400</v>
@@ -26411,7 +26411,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G898" t="n">
-        <v>1.50035214424133</v>
+        <v>1.50035226345062</v>
       </c>
       <c r="H898" t="n">
         <v>9001</v>
@@ -26440,7 +26440,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G899" t="n">
-        <v>1.50035214424133</v>
+        <v>1.50035226345062</v>
       </c>
       <c r="H899" t="n">
         <v>5729</v>
@@ -26469,7 +26469,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G900" t="n">
-        <v>1.50035214424133</v>
+        <v>1.50035226345062</v>
       </c>
       <c r="H900" t="n">
         <v>4094</v>
@@ -26498,7 +26498,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G901" t="n">
-        <v>1.54723811149597</v>
+        <v>1.54723823070526</v>
       </c>
       <c r="H901" t="n">
         <v>5238</v>
@@ -26585,7 +26585,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G904" t="n">
-        <v>1.53160953521729</v>
+        <v>1.531609416008</v>
       </c>
       <c r="H904" t="n">
         <v>2250</v>
@@ -26614,7 +26614,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G905" t="n">
-        <v>1.53160953521729</v>
+        <v>1.531609416008</v>
       </c>
       <c r="H905" t="n">
         <v>3080</v>
@@ -26643,7 +26643,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G906" t="n">
-        <v>1.50035214424133</v>
+        <v>1.50035226345062</v>
       </c>
       <c r="H906" t="n">
         <v>3380</v>
@@ -26672,7 +26672,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G907" t="n">
-        <v>1.50035214424133</v>
+        <v>1.50035226345062</v>
       </c>
       <c r="H907" t="n">
         <v>17682</v>
@@ -26759,7 +26759,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G910" t="n">
-        <v>1.50035214424133</v>
+        <v>1.50035226345062</v>
       </c>
       <c r="H910" t="n">
         <v>2535</v>
@@ -26846,7 +26846,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G913" t="n">
-        <v>1.50035214424133</v>
+        <v>1.50035226345062</v>
       </c>
       <c r="H913" t="n">
         <v>1205</v>
@@ -26933,7 +26933,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G916" t="n">
-        <v>1.50035214424133</v>
+        <v>1.50035226345062</v>
       </c>
       <c r="H916" t="n">
         <v>1650</v>
@@ -26962,7 +26962,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G917" t="n">
-        <v>1.50035214424133</v>
+        <v>1.50035226345062</v>
       </c>
       <c r="H917" t="n">
         <v>8100</v>
@@ -26991,7 +26991,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G918" t="n">
-        <v>1.46909487247467</v>
+        <v>1.46909475326538</v>
       </c>
       <c r="H918" t="n">
         <v>9855</v>
@@ -27107,7 +27107,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G922" t="n">
-        <v>1.46909487247467</v>
+        <v>1.46909475326538</v>
       </c>
       <c r="H922" t="n">
         <v>577</v>
@@ -27136,7 +27136,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G923" t="n">
-        <v>1.46909487247467</v>
+        <v>1.46909475326538</v>
       </c>
       <c r="H923" t="n">
         <v>1678</v>
@@ -27223,7 +27223,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G926" t="n">
-        <v>1.50035214424133</v>
+        <v>1.50035226345062</v>
       </c>
       <c r="H926" t="n">
         <v>3414</v>
@@ -27252,7 +27252,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G927" t="n">
-        <v>1.50035214424133</v>
+        <v>1.50035226345062</v>
       </c>
       <c r="H927" t="n">
         <v>60</v>
@@ -27397,7 +27397,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G932" t="n">
-        <v>1.46909487247467</v>
+        <v>1.46909475326538</v>
       </c>
       <c r="H932" t="n">
         <v>7581</v>
@@ -27426,7 +27426,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G933" t="n">
-        <v>1.50035214424133</v>
+        <v>1.50035226345062</v>
       </c>
       <c r="H933" t="n">
         <v>10800</v>
@@ -27455,7 +27455,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G934" t="n">
-        <v>1.46909487247467</v>
+        <v>1.46909475326538</v>
       </c>
       <c r="H934" t="n">
         <v>4422</v>
@@ -27629,7 +27629,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G940" t="n">
-        <v>1.50035214424133</v>
+        <v>1.50035226345062</v>
       </c>
       <c r="H940" t="n">
         <v>3395</v>
@@ -27658,7 +27658,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G941" t="n">
-        <v>1.53160953521729</v>
+        <v>1.531609416008</v>
       </c>
       <c r="H941" t="n">
         <v>62485</v>
@@ -27890,7 +27890,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G949" t="n">
-        <v>1.50035214424133</v>
+        <v>1.50035226345062</v>
       </c>
       <c r="H949" t="n">
         <v>2380</v>
@@ -27919,7 +27919,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G950" t="n">
-        <v>1.50035214424133</v>
+        <v>1.50035226345062</v>
       </c>
       <c r="H950" t="n">
         <v>1118</v>
@@ -27948,7 +27948,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G951" t="n">
-        <v>1.50035214424133</v>
+        <v>1.50035226345062</v>
       </c>
       <c r="H951" t="n">
         <v>2270</v>
@@ -27977,7 +27977,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G952" t="n">
-        <v>1.50035214424133</v>
+        <v>1.50035226345062</v>
       </c>
       <c r="H952" t="n">
         <v>3602</v>
@@ -28006,7 +28006,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G953" t="n">
-        <v>1.50035214424133</v>
+        <v>1.50035226345062</v>
       </c>
       <c r="H953" t="n">
         <v>4131</v>
@@ -28035,7 +28035,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G954" t="n">
-        <v>1.50035214424133</v>
+        <v>1.50035226345062</v>
       </c>
       <c r="H954" t="n">
         <v>7140</v>
@@ -28093,7 +28093,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G956" t="n">
-        <v>1.46909487247467</v>
+        <v>1.46909475326538</v>
       </c>
       <c r="H956" t="n">
         <v>14201</v>
@@ -28122,7 +28122,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G957" t="n">
-        <v>1.46909487247467</v>
+        <v>1.46909475326538</v>
       </c>
       <c r="H957" t="n">
         <v>24615</v>
@@ -28209,7 +28209,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G960" t="n">
-        <v>1.46909487247467</v>
+        <v>1.46909475326538</v>
       </c>
       <c r="H960" t="n">
         <v>61673</v>
@@ -28238,7 +28238,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G961" t="n">
-        <v>1.46909487247467</v>
+        <v>1.46909475326538</v>
       </c>
       <c r="H961" t="n">
         <v>5222</v>
@@ -28383,7 +28383,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G966" t="n">
-        <v>1.46909487247467</v>
+        <v>1.46909475326538</v>
       </c>
       <c r="H966" t="n">
         <v>10446</v>
@@ -28412,7 +28412,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G967" t="n">
-        <v>1.46909487247467</v>
+        <v>1.46909475326538</v>
       </c>
       <c r="H967" t="n">
         <v>320</v>
@@ -28441,7 +28441,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G968" t="n">
-        <v>1.46909487247467</v>
+        <v>1.46909475326538</v>
       </c>
       <c r="H968" t="n">
         <v>3588</v>
@@ -28470,7 +28470,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G969" t="n">
-        <v>1.43783760070801</v>
+        <v>1.43783736228943</v>
       </c>
       <c r="H969" t="n">
         <v>21430</v>
@@ -28499,7 +28499,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G970" t="n">
-        <v>1.43783760070801</v>
+        <v>1.43783736228943</v>
       </c>
       <c r="H970" t="n">
         <v>484</v>
@@ -28528,7 +28528,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G971" t="n">
-        <v>1.43783760070801</v>
+        <v>1.43783736228943</v>
       </c>
       <c r="H971" t="n">
         <v>1075</v>
@@ -28557,7 +28557,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G972" t="n">
-        <v>1.43783760070801</v>
+        <v>1.43783736228943</v>
       </c>
       <c r="H972" t="n">
         <v>500</v>
@@ -28644,7 +28644,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G975" t="n">
-        <v>1.43783760070801</v>
+        <v>1.43783736228943</v>
       </c>
       <c r="H975" t="n">
         <v>2000</v>
@@ -28731,7 +28731,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G978" t="n">
-        <v>1.43783760070801</v>
+        <v>1.43783736228943</v>
       </c>
       <c r="H978" t="n">
         <v>4265</v>
@@ -28789,7 +28789,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G980" t="n">
-        <v>1.43783760070801</v>
+        <v>1.43783736228943</v>
       </c>
       <c r="H980" t="n">
         <v>560</v>
@@ -28818,7 +28818,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G981" t="n">
-        <v>1.43783760070801</v>
+        <v>1.43783736228943</v>
       </c>
       <c r="H981" t="n">
         <v>3315</v>
@@ -29021,7 +29021,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G988" t="n">
-        <v>1.43783760070801</v>
+        <v>1.43783736228943</v>
       </c>
       <c r="H988" t="n">
         <v>3235</v>
@@ -29079,7 +29079,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G990" t="n">
-        <v>1.43783760070801</v>
+        <v>1.43783736228943</v>
       </c>
       <c r="H990" t="n">
         <v>377</v>
@@ -29108,7 +29108,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G991" t="n">
-        <v>1.43783760070801</v>
+        <v>1.43783736228943</v>
       </c>
       <c r="H991" t="n">
         <v>1621</v>
@@ -29137,7 +29137,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G992" t="n">
-        <v>1.43783760070801</v>
+        <v>1.43783736228943</v>
       </c>
       <c r="H992" t="n">
         <v>4633</v>
@@ -29224,7 +29224,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G995" t="n">
-        <v>1.39095151424408</v>
+        <v>1.39095139503479</v>
       </c>
       <c r="H995" t="n">
         <v>4445</v>
@@ -29427,7 +29427,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G1002" t="n">
-        <v>1.43783760070801</v>
+        <v>1.43783736228943</v>
       </c>
       <c r="H1002" t="n">
         <v>29959</v>
@@ -29456,7 +29456,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1003" t="n">
-        <v>1.68789625167847</v>
+        <v>1.68789613246918</v>
       </c>
       <c r="H1003" t="n">
         <v>363297</v>
@@ -29485,7 +29485,7 @@
         <v>2</v>
       </c>
       <c r="G1004" t="n">
-        <v>1.56286680698395</v>
+        <v>1.56286692619324</v>
       </c>
       <c r="H1004" t="n">
         <v>526368</v>
@@ -29572,7 +29572,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G1007" t="n">
-        <v>1.46909487247467</v>
+        <v>1.46909475326538</v>
       </c>
       <c r="H1007" t="n">
         <v>168703</v>
@@ -29717,7 +29717,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G1012" t="n">
-        <v>1.43783760070801</v>
+        <v>1.43783736228943</v>
       </c>
       <c r="H1012" t="n">
         <v>26843</v>
@@ -29746,7 +29746,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G1013" t="n">
-        <v>1.43783760070801</v>
+        <v>1.43783736228943</v>
       </c>
       <c r="H1013" t="n">
         <v>8510</v>
@@ -29775,7 +29775,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G1014" t="n">
-        <v>1.46909487247467</v>
+        <v>1.46909475326538</v>
       </c>
       <c r="H1014" t="n">
         <v>11951</v>
@@ -29804,7 +29804,7 @@
         <v>1.86940002441406</v>
       </c>
       <c r="G1015" t="n">
-        <v>1.46081173419952</v>
+        <v>1.46081161499023</v>
       </c>
       <c r="H1015" t="n">
         <v>31731</v>
@@ -29862,7 +29862,7 @@
         <v>1.80480003356934</v>
       </c>
       <c r="G1017" t="n">
-        <v>1.41033101081848</v>
+        <v>1.41033113002777</v>
       </c>
       <c r="H1017" t="n">
         <v>6419</v>
@@ -29949,7 +29949,7 @@
         <v>1.81679999828339</v>
       </c>
       <c r="G1020" t="n">
-        <v>1.41970813274384</v>
+        <v>1.41970825195312</v>
       </c>
       <c r="H1020" t="n">
         <v>54639</v>
@@ -30007,7 +30007,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G1022" t="n">
-        <v>1.43002319335938</v>
+        <v>1.43002307415009</v>
       </c>
       <c r="H1022" t="n">
         <v>55375</v>
@@ -30036,7 +30036,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G1023" t="n">
-        <v>1.41439437866211</v>
+        <v>1.4143944978714</v>
       </c>
       <c r="H1023" t="n">
         <v>10822</v>
@@ -30152,7 +30152,7 @@
         <v>1.74600005149841</v>
       </c>
       <c r="G1027" t="n">
-        <v>1.36438286304474</v>
+        <v>1.36438274383545</v>
       </c>
       <c r="H1027" t="n">
         <v>3497</v>
@@ -30181,7 +30181,7 @@
         <v>1.70500004291534</v>
       </c>
       <c r="G1028" t="n">
-        <v>1.33234405517578</v>
+        <v>1.33234393596649</v>
       </c>
       <c r="H1028" t="n">
         <v>21254</v>
@@ -30210,7 +30210,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G1029" t="n">
-        <v>1.34406542778015</v>
+        <v>1.34406566619873</v>
       </c>
       <c r="H1029" t="n">
         <v>22344</v>
@@ -30326,7 +30326,7 @@
         <v>1.70099997520447</v>
       </c>
       <c r="G1033" t="n">
-        <v>1.32921826839447</v>
+        <v>1.32921814918518</v>
       </c>
       <c r="H1033" t="n">
         <v>15378</v>
@@ -30500,7 +30500,7 @@
         <v>1.57840001583099</v>
       </c>
       <c r="G1039" t="n">
-        <v>1.23341464996338</v>
+        <v>1.23341453075409</v>
       </c>
       <c r="H1039" t="n">
         <v>13283</v>
@@ -30529,7 +30529,7 @@
         <v>1.52020001411438</v>
       </c>
       <c r="G1040" t="n">
-        <v>1.18793499469757</v>
+        <v>1.18793511390686</v>
       </c>
       <c r="H1040" t="n">
         <v>32531</v>
@@ -30558,7 +30558,7 @@
         <v>1.57720005512238</v>
       </c>
       <c r="G1041" t="n">
-        <v>1.23247671127319</v>
+        <v>1.23247683048248</v>
       </c>
       <c r="H1041" t="n">
         <v>45218</v>
@@ -30616,7 +30616,7 @@
         <v>1.61819994449615</v>
       </c>
       <c r="G1043" t="n">
-        <v>1.26451539993286</v>
+        <v>1.26451551914215</v>
       </c>
       <c r="H1043" t="n">
         <v>5812</v>
@@ -30645,7 +30645,7 @@
         <v>1.63900005817413</v>
       </c>
       <c r="G1044" t="n">
-        <v>1.28076946735382</v>
+        <v>1.28076934814453</v>
       </c>
       <c r="H1044" t="n">
         <v>37874</v>
@@ -30703,7 +30703,7 @@
         <v>1.63779997825623</v>
       </c>
       <c r="G1046" t="n">
-        <v>1.27983176708221</v>
+        <v>1.27983164787292</v>
       </c>
       <c r="H1046" t="n">
         <v>22878</v>
@@ -30761,7 +30761,7 @@
         <v>1.68579995632172</v>
       </c>
       <c r="G1048" t="n">
-        <v>1.31734037399292</v>
+        <v>1.31734049320221</v>
       </c>
       <c r="H1048" t="n">
         <v>10382</v>
@@ -30993,7 +30993,7 @@
         <v>1.54159998893738</v>
       </c>
       <c r="G1056" t="n">
-        <v>1.20465779304504</v>
+        <v>1.20465767383575</v>
       </c>
       <c r="H1056" t="n">
         <v>6735</v>
@@ -31022,7 +31022,7 @@
         <v>1.58980000019073</v>
       </c>
       <c r="G1057" t="n">
-        <v>1.24232292175293</v>
+        <v>1.24232280254364</v>
       </c>
       <c r="H1057" t="n">
         <v>20662</v>
@@ -31080,7 +31080,7 @@
         <v>1.55980002880096</v>
       </c>
       <c r="G1059" t="n">
-        <v>1.21887993812561</v>
+        <v>1.2188800573349</v>
       </c>
       <c r="H1059" t="n">
         <v>21083</v>
@@ -31196,7 +31196,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G1063" t="n">
-        <v>0.883019745349884</v>
+        <v>0.883019685745239</v>
       </c>
       <c r="H1063" t="n">
         <v>14800</v>
@@ -31225,7 +31225,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G1064" t="n">
-        <v>0.883019745349884</v>
+        <v>0.883019685745239</v>
       </c>
       <c r="H1064" t="n">
         <v>10076</v>
@@ -31283,7 +31283,7 @@
         <v>0.939999997615814</v>
       </c>
       <c r="G1066" t="n">
-        <v>0.734547436237335</v>
+        <v>0.73454737663269</v>
       </c>
       <c r="H1066" t="n">
         <v>21386</v>
@@ -31341,7 +31341,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G1068" t="n">
-        <v>0.773619055747986</v>
+        <v>0.773619115352631</v>
       </c>
       <c r="H1068" t="n">
         <v>15083</v>
@@ -31370,7 +31370,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G1069" t="n">
-        <v>0.773619055747986</v>
+        <v>0.773619115352631</v>
       </c>
       <c r="H1069" t="n">
         <v>7200</v>
@@ -31399,7 +31399,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G1070" t="n">
-        <v>0.773619055747986</v>
+        <v>0.773619115352631</v>
       </c>
       <c r="H1070" t="n">
         <v>1500</v>
@@ -31457,7 +31457,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G1072" t="n">
-        <v>0.859576761722565</v>
+        <v>0.859576880931854</v>
       </c>
       <c r="H1072" t="n">
         <v>6459</v>
@@ -31486,7 +31486,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G1073" t="n">
-        <v>0.968977510929108</v>
+        <v>0.968977451324463</v>
       </c>
       <c r="H1073" t="n">
         <v>6985</v>
@@ -31515,7 +31515,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G1074" t="n">
-        <v>1.09400677680969</v>
+        <v>1.0940066576004</v>
       </c>
       <c r="H1074" t="n">
         <v>7710</v>
@@ -31573,7 +31573,7 @@
         <v>1.5958000421524</v>
       </c>
       <c r="G1076" t="n">
-        <v>1.24701142311096</v>
+        <v>1.24701154232025</v>
       </c>
       <c r="H1076" t="n">
         <v>28795</v>
@@ -31631,7 +31631,7 @@
         <v>1.61500000953674</v>
       </c>
       <c r="G1078" t="n">
-        <v>1.26201486587524</v>
+        <v>1.26201498508453</v>
       </c>
       <c r="H1078" t="n">
         <v>5525</v>
@@ -31718,7 +31718,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G1081" t="n">
-        <v>1.21122169494629</v>
+        <v>1.21122181415558</v>
       </c>
       <c r="H1081" t="n">
         <v>11021</v>
@@ -31921,7 +31921,7 @@
         <v>1.52999997138977</v>
       </c>
       <c r="G1088" t="n">
-        <v>1.19559299945831</v>
+        <v>1.1955931186676</v>
       </c>
       <c r="H1088" t="n">
         <v>8558</v>
@@ -31979,7 +31979,7 @@
         <v>1.56959998607635</v>
       </c>
       <c r="G1090" t="n">
-        <v>1.22653794288635</v>
+        <v>1.22653782367706</v>
       </c>
       <c r="H1090" t="n">
         <v>15691</v>
@@ -32008,7 +32008,7 @@
         <v>1.53519999980927</v>
       </c>
       <c r="G1091" t="n">
-        <v>1.19965660572052</v>
+        <v>1.19965672492981</v>
       </c>
       <c r="H1091" t="n">
         <v>7726</v>
@@ -32037,7 +32037,7 @@
         <v>1.51059997081757</v>
       </c>
       <c r="G1092" t="n">
-        <v>1.18043339252472</v>
+        <v>1.18043327331543</v>
       </c>
       <c r="H1092" t="n">
         <v>10176</v>
@@ -32066,7 +32066,7 @@
         <v>1.53840005397797</v>
       </c>
       <c r="G1093" t="n">
-        <v>1.20215737819672</v>
+        <v>1.20215713977814</v>
       </c>
       <c r="H1093" t="n">
         <v>6653</v>
@@ -32124,7 +32124,7 @@
         <v>1.42999994754791</v>
       </c>
       <c r="G1095" t="n">
-        <v>1.1174498796463</v>
+        <v>1.11744976043701</v>
       </c>
       <c r="H1095" t="n">
         <v>6692</v>
@@ -32153,7 +32153,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G1096" t="n">
-        <v>1.08619248867035</v>
+        <v>1.08619236946106</v>
       </c>
       <c r="H1096" t="n">
         <v>36445</v>
@@ -32182,7 +32182,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G1097" t="n">
-        <v>1.0549350976944</v>
+        <v>1.05493521690369</v>
       </c>
       <c r="H1097" t="n">
         <v>24618</v>
@@ -32211,7 +32211,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G1098" t="n">
-        <v>1.0549350976944</v>
+        <v>1.05493521690369</v>
       </c>
       <c r="H1098" t="n">
         <v>0</v>
@@ -32240,7 +32240,7 @@
         <v>1.42980003356934</v>
       </c>
       <c r="G1099" t="n">
-        <v>1.1172935962677</v>
+        <v>1.11729347705841</v>
       </c>
       <c r="H1099" t="n">
         <v>10201</v>
@@ -32269,7 +32269,7 @@
         <v>1.42980003356934</v>
       </c>
       <c r="G1100" t="n">
-        <v>1.1172935962677</v>
+        <v>1.11729347705841</v>
       </c>
       <c r="H1100" t="n">
         <v>0</v>
@@ -32327,7 +32327,7 @@
         <v>1.44400000572205</v>
       </c>
       <c r="G1102" t="n">
-        <v>1.12838971614838</v>
+        <v>1.12838983535767</v>
       </c>
       <c r="H1102" t="n">
         <v>44823</v>
@@ -32356,7 +32356,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G1103" t="n">
-        <v>1.07837820053101</v>
+        <v>1.07837808132172</v>
       </c>
       <c r="H1103" t="n">
         <v>39674</v>
@@ -32414,7 +32414,7 @@
         <v>1.3782000541687</v>
       </c>
       <c r="G1105" t="n">
-        <v>1.07697153091431</v>
+        <v>1.07697141170502</v>
       </c>
       <c r="H1105" t="n">
         <v>17647</v>
@@ -32443,7 +32443,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1106" t="n">
-        <v>1.04712080955505</v>
+        <v>1.04712069034576</v>
       </c>
       <c r="H1106" t="n">
         <v>11729</v>
@@ -32501,7 +32501,7 @@
         <v>1.30019998550415</v>
       </c>
       <c r="G1108" t="n">
-        <v>1.01601982116699</v>
+        <v>1.0160197019577</v>
       </c>
       <c r="H1108" t="n">
         <v>1305</v>
@@ -32559,7 +32559,7 @@
         <v>1.25279998779297</v>
       </c>
       <c r="G1110" t="n">
-        <v>0.978979825973511</v>
+        <v>0.978979766368866</v>
       </c>
       <c r="H1110" t="n">
         <v>24524</v>
@@ -32675,7 +32675,7 @@
         <v>1.23039996623993</v>
       </c>
       <c r="G1114" t="n">
-        <v>0.961475670337677</v>
+        <v>0.961475729942322</v>
       </c>
       <c r="H1114" t="n">
         <v>12655</v>
@@ -32704,7 +32704,7 @@
         <v>1.25</v>
       </c>
       <c r="G1115" t="n">
-        <v>0.976791739463806</v>
+        <v>0.976791679859161</v>
       </c>
       <c r="H1115" t="n">
         <v>34094</v>
@@ -32762,7 +32762,7 @@
         <v>1.3367999792099</v>
       </c>
       <c r="G1117" t="n">
-        <v>1.04462015628815</v>
+        <v>1.04462027549744</v>
       </c>
       <c r="H1117" t="n">
         <v>27003</v>
@@ -32849,7 +32849,7 @@
         <v>1.2791999578476</v>
       </c>
       <c r="G1120" t="n">
-        <v>0.999609529972076</v>
+        <v>0.999609589576721</v>
       </c>
       <c r="H1120" t="n">
         <v>25760</v>
@@ -32878,7 +32878,7 @@
         <v>1.2771999835968</v>
       </c>
       <c r="G1121" t="n">
-        <v>0.998046875</v>
+        <v>0.998046696186066</v>
       </c>
       <c r="H1121" t="n">
         <v>64712</v>
@@ -32907,7 +32907,7 @@
         <v>1.33940005302429</v>
       </c>
       <c r="G1122" t="n">
-        <v>1.04665195941925</v>
+        <v>1.04665207862854</v>
       </c>
       <c r="H1122" t="n">
         <v>68249</v>
@@ -32994,7 +32994,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G1125" t="n">
-        <v>1.07837820053101</v>
+        <v>1.07837808132172</v>
       </c>
       <c r="H1125" t="n">
         <v>43721</v>
@@ -33023,7 +33023,7 @@
         <v>1.35979998111725</v>
       </c>
       <c r="G1126" t="n">
-        <v>1.06259310245514</v>
+        <v>1.06259322166443</v>
       </c>
       <c r="H1126" t="n">
         <v>19347</v>
@@ -33081,7 +33081,7 @@
         <v>1.34979999065399</v>
       </c>
       <c r="G1128" t="n">
-        <v>1.0547788143158</v>
+        <v>1.05477893352509</v>
       </c>
       <c r="H1128" t="n">
         <v>30907</v>
@@ -33139,7 +33139,7 @@
         <v>1.29579997062683</v>
       </c>
       <c r="G1130" t="n">
-        <v>1.01258146762848</v>
+        <v>1.0125812292099</v>
       </c>
       <c r="H1130" t="n">
         <v>34473</v>
@@ -33197,7 +33197,7 @@
         <v>1.32280004024506</v>
       </c>
       <c r="G1132" t="n">
-        <v>1.03368020057678</v>
+        <v>1.03368008136749</v>
       </c>
       <c r="H1132" t="n">
         <v>4792</v>
@@ -33226,7 +33226,7 @@
         <v>1.29820001125336</v>
       </c>
       <c r="G1133" t="n">
-        <v>1.0144567489624</v>
+        <v>1.01445686817169</v>
       </c>
       <c r="H1133" t="n">
         <v>4011</v>
@@ -33255,7 +33255,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1134" t="n">
-        <v>1.04712080955505</v>
+        <v>1.04712069034576</v>
       </c>
       <c r="H1134" t="n">
         <v>6000</v>
@@ -33284,7 +33284,7 @@
         <v>1.2960000038147</v>
       </c>
       <c r="G1135" t="n">
-        <v>1.01273775100708</v>
+        <v>1.01273763179779</v>
       </c>
       <c r="H1135" t="n">
         <v>2329</v>
@@ -33632,7 +33632,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1147" t="n">
-        <v>0.992420434951782</v>
+        <v>0.992420375347137</v>
       </c>
       <c r="H1147" t="n">
         <v>5704</v>
@@ -33690,7 +33690,7 @@
         <v>1.26240003108978</v>
       </c>
       <c r="G1149" t="n">
-        <v>0.986481547355652</v>
+        <v>0.986481666564941</v>
       </c>
       <c r="H1149" t="n">
         <v>8000</v>
@@ -33748,7 +33748,7 @@
         <v>1.29299998283386</v>
       </c>
       <c r="G1151" t="n">
-        <v>1.01039350032806</v>
+        <v>1.01039338111877</v>
       </c>
       <c r="H1151" t="n">
         <v>4302</v>
@@ -33777,7 +33777,7 @@
         <v>1.29180002212524</v>
       </c>
       <c r="G1152" t="n">
-        <v>1.00945556163788</v>
+        <v>1.00945568084717</v>
       </c>
       <c r="H1152" t="n">
         <v>8200</v>
@@ -33806,7 +33806,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1153" t="n">
-        <v>0.992420434951782</v>
+        <v>0.992420375347137</v>
       </c>
       <c r="H1153" t="n">
         <v>2410</v>
@@ -33835,7 +33835,7 @@
         <v>1.25440001487732</v>
       </c>
       <c r="G1154" t="n">
-        <v>0.980230093002319</v>
+        <v>0.980230033397675</v>
       </c>
       <c r="H1154" t="n">
         <v>5500</v>
@@ -33922,7 +33922,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G1157" t="n">
-        <v>1.02367758750916</v>
+        <v>1.02367770671844</v>
       </c>
       <c r="H1157" t="n">
         <v>40638</v>
@@ -33980,7 +33980,7 @@
         <v>1.29499995708466</v>
       </c>
       <c r="G1159" t="n">
-        <v>1.01195621490479</v>
+        <v>1.01195633411407</v>
       </c>
       <c r="H1159" t="n">
         <v>21359</v>
@@ -34038,7 +34038,7 @@
         <v>1.28939998149872</v>
       </c>
       <c r="G1161" t="n">
-        <v>1.00758028030396</v>
+        <v>1.00758016109467</v>
       </c>
       <c r="H1161" t="n">
         <v>160</v>
@@ -34125,7 +34125,7 @@
         <v>1.23099994659424</v>
       </c>
       <c r="G1164" t="n">
-        <v>0.961944580078125</v>
+        <v>0.96194452047348</v>
       </c>
       <c r="H1164" t="n">
         <v>10525</v>
@@ -34154,7 +34154,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1165" t="n">
-        <v>0.992420434951782</v>
+        <v>0.992420375347137</v>
       </c>
       <c r="H1165" t="n">
         <v>10014</v>
@@ -34183,7 +34183,7 @@
         <v>1.27900004386902</v>
       </c>
       <c r="G1166" t="n">
-        <v>0.999453365802765</v>
+        <v>0.99945330619812</v>
       </c>
       <c r="H1166" t="n">
         <v>19032</v>
@@ -34212,7 +34212,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1167" t="n">
-        <v>0.992420434951782</v>
+        <v>0.992420375347137</v>
       </c>
       <c r="H1167" t="n">
         <v>18852</v>
@@ -34270,7 +34270,7 @@
         <v>1.25</v>
       </c>
       <c r="G1169" t="n">
-        <v>0.976791739463806</v>
+        <v>0.976791679859161</v>
       </c>
       <c r="H1169" t="n">
         <v>7000</v>
@@ -34299,7 +34299,7 @@
         <v>1.25</v>
       </c>
       <c r="G1170" t="n">
-        <v>0.976791739463806</v>
+        <v>0.976791679859161</v>
       </c>
       <c r="H1170" t="n">
         <v>0</v>
@@ -34328,7 +34328,7 @@
         <v>1.24339997768402</v>
       </c>
       <c r="G1171" t="n">
-        <v>0.971634268760681</v>
+        <v>0.971634328365326</v>
       </c>
       <c r="H1171" t="n">
         <v>4563</v>
@@ -34357,7 +34357,7 @@
         <v>1.22060000896454</v>
       </c>
       <c r="G1172" t="n">
-        <v>0.95381760597229</v>
+        <v>0.953817665576935</v>
       </c>
       <c r="H1172" t="n">
         <v>2356</v>
@@ -34386,7 +34386,7 @@
         <v>1.22060000896454</v>
       </c>
       <c r="G1173" t="n">
-        <v>0.95381760597229</v>
+        <v>0.953817665576935</v>
       </c>
       <c r="H1173" t="n">
         <v>0</v>
@@ -34444,7 +34444,7 @@
         <v>1.22200000286102</v>
       </c>
       <c r="G1175" t="n">
-        <v>0.954911708831787</v>
+        <v>0.954911649227142</v>
       </c>
       <c r="H1175" t="n">
         <v>800</v>
@@ -34473,7 +34473,7 @@
         <v>1.22019994258881</v>
       </c>
       <c r="G1176" t="n">
-        <v>0.953504920005798</v>
+        <v>0.953504979610443</v>
       </c>
       <c r="H1176" t="n">
         <v>1000</v>
@@ -34560,7 +34560,7 @@
         <v>1.21700000762939</v>
       </c>
       <c r="G1179" t="n">
-        <v>0.951004385948181</v>
+        <v>0.951004445552826</v>
       </c>
       <c r="H1179" t="n">
         <v>1896</v>
@@ -34589,7 +34589,7 @@
         <v>1.19500005245209</v>
       </c>
       <c r="G1180" t="n">
-        <v>0.933812856674194</v>
+        <v>0.933812975883484</v>
       </c>
       <c r="H1180" t="n">
         <v>1588</v>
@@ -34618,7 +34618,7 @@
         <v>1.23580002784729</v>
       </c>
       <c r="G1181" t="n">
-        <v>0.965695321559906</v>
+        <v>0.965695381164551</v>
       </c>
       <c r="H1181" t="n">
         <v>2300</v>
@@ -34647,7 +34647,7 @@
         <v>1.24399995803833</v>
       </c>
       <c r="G1182" t="n">
-        <v>0.97210305929184</v>
+        <v>0.972103178501129</v>
       </c>
       <c r="H1182" t="n">
         <v>2300</v>
@@ -34676,7 +34676,7 @@
         <v>1.24399995803833</v>
       </c>
       <c r="G1183" t="n">
-        <v>0.97210305929184</v>
+        <v>0.972103178501129</v>
       </c>
       <c r="H1183" t="n">
         <v>1000</v>
@@ -34734,7 +34734,7 @@
         <v>1.20500004291534</v>
       </c>
       <c r="G1185" t="n">
-        <v>0.941627323627472</v>
+        <v>0.941627264022827</v>
       </c>
       <c r="H1185" t="n">
         <v>6534</v>
@@ -34821,7 +34821,7 @@
         <v>1.20019996166229</v>
       </c>
       <c r="G1188" t="n">
-        <v>0.937876462936401</v>
+        <v>0.937876403331757</v>
       </c>
       <c r="H1188" t="n">
         <v>10090</v>
@@ -34850,7 +34850,7 @@
         <v>1.22019994258881</v>
       </c>
       <c r="G1189" t="n">
-        <v>0.953504920005798</v>
+        <v>0.953504979610443</v>
       </c>
       <c r="H1189" t="n">
         <v>7534</v>
@@ -34879,7 +34879,7 @@
         <v>1.26979994773865</v>
       </c>
       <c r="G1190" t="n">
-        <v>0.992264091968536</v>
+        <v>0.992264151573181</v>
       </c>
       <c r="H1190" t="n">
         <v>2250</v>
@@ -34908,7 +34908,7 @@
         <v>1.23959994316101</v>
       </c>
       <c r="G1191" t="n">
-        <v>0.968664824962616</v>
+        <v>0.968664765357971</v>
       </c>
       <c r="H1191" t="n">
         <v>1101</v>
@@ -34966,7 +34966,7 @@
         <v>1.21319997310638</v>
       </c>
       <c r="G1193" t="n">
-        <v>0.948034882545471</v>
+        <v>0.948034942150116</v>
       </c>
       <c r="H1193" t="n">
         <v>5835</v>
@@ -34995,7 +34995,7 @@
         <v>1.22800004482269</v>
       </c>
       <c r="G1194" t="n">
-        <v>0.959600210189819</v>
+        <v>0.959600269794464</v>
       </c>
       <c r="H1194" t="n">
         <v>24707</v>
@@ -35024,7 +35024,7 @@
         <v>1.24279999732971</v>
       </c>
       <c r="G1195" t="n">
-        <v>0.971165478229523</v>
+        <v>0.971165359020233</v>
       </c>
       <c r="H1195" t="n">
         <v>23798</v>
@@ -35053,7 +35053,7 @@
         <v>1.24199998378754</v>
       </c>
       <c r="G1196" t="n">
-        <v>0.970540285110474</v>
+        <v>0.970540404319763</v>
       </c>
       <c r="H1196" t="n">
         <v>22960</v>
@@ -35082,7 +35082,7 @@
         <v>1.24399995803833</v>
       </c>
       <c r="G1197" t="n">
-        <v>0.97210305929184</v>
+        <v>0.972103178501129</v>
       </c>
       <c r="H1197" t="n">
         <v>28501</v>
@@ -35169,7 +35169,7 @@
         <v>1.19120001792908</v>
       </c>
       <c r="G1200" t="n">
-        <v>0.930843412876129</v>
+        <v>0.930843472480774</v>
       </c>
       <c r="H1200" t="n">
         <v>13624</v>
@@ -35198,7 +35198,7 @@
         <v>1.19120001792908</v>
       </c>
       <c r="G1201" t="n">
-        <v>0.930843412876129</v>
+        <v>0.930843472480774</v>
       </c>
       <c r="H1201" t="n">
         <v>0</v>
@@ -35227,7 +35227,7 @@
         <v>1.22940003871918</v>
       </c>
       <c r="G1202" t="n">
-        <v>0.960694313049316</v>
+        <v>0.960694193840027</v>
       </c>
       <c r="H1202" t="n">
         <v>930</v>
@@ -35256,7 +35256,7 @@
         <v>1.19140005111694</v>
       </c>
       <c r="G1203" t="n">
-        <v>0.930999755859375</v>
+        <v>0.930999875068665</v>
       </c>
       <c r="H1203" t="n">
         <v>520</v>
@@ -35285,7 +35285,7 @@
         <v>1.22979998588562</v>
       </c>
       <c r="G1204" t="n">
-        <v>0.961006760597229</v>
+        <v>0.961006700992584</v>
       </c>
       <c r="H1204" t="n">
         <v>4250</v>
@@ -35314,7 +35314,7 @@
         <v>1.24199998378754</v>
       </c>
       <c r="G1205" t="n">
-        <v>0.970540285110474</v>
+        <v>0.970540404319763</v>
       </c>
       <c r="H1205" t="n">
         <v>5811</v>
@@ -35401,7 +35401,7 @@
         <v>1.19500005245209</v>
       </c>
       <c r="G1208" t="n">
-        <v>0.933812856674194</v>
+        <v>0.933812975883484</v>
       </c>
       <c r="H1208" t="n">
         <v>1086</v>
@@ -35430,7 +35430,7 @@
         <v>1.19500005245209</v>
       </c>
       <c r="G1209" t="n">
-        <v>0.933812856674194</v>
+        <v>0.933812975883484</v>
       </c>
       <c r="H1209" t="n">
         <v>7175</v>
@@ -35488,7 +35488,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G1211" t="n">
-        <v>0.968977510929108</v>
+        <v>0.968977451324463</v>
       </c>
       <c r="H1211" t="n">
         <v>39741</v>
@@ -35517,7 +35517,7 @@
         <v>1.20060002803802</v>
       </c>
       <c r="G1212" t="n">
-        <v>0.938188910484314</v>
+        <v>0.938188970088959</v>
       </c>
       <c r="H1212" t="n">
         <v>13237</v>
@@ -35575,7 +35575,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G1214" t="n">
-        <v>1.02367758750916</v>
+        <v>1.02367770671844</v>
       </c>
       <c r="H1214" t="n">
         <v>84862</v>
@@ -35604,7 +35604,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1215" t="n">
-        <v>0.984606087207794</v>
+        <v>0.984605967998505</v>
       </c>
       <c r="H1215" t="n">
         <v>32688</v>
@@ -35633,7 +35633,7 @@
         <v>1.26579999923706</v>
       </c>
       <c r="G1216" t="n">
-        <v>0.989138424396515</v>
+        <v>0.98913848400116</v>
       </c>
       <c r="H1216" t="n">
         <v>35063</v>
@@ -35662,7 +35662,7 @@
         <v>1.26540005207062</v>
       </c>
       <c r="G1217" t="n">
-        <v>0.988825857639313</v>
+        <v>0.988825917243958</v>
       </c>
       <c r="H1217" t="n">
         <v>20941</v>
@@ -35691,7 +35691,7 @@
         <v>1.24020004272461</v>
       </c>
       <c r="G1218" t="n">
-        <v>0.969133853912354</v>
+        <v>0.969133794307709</v>
       </c>
       <c r="H1218" t="n">
         <v>4530</v>
@@ -35807,7 +35807,7 @@
         <v>1.22599995136261</v>
       </c>
       <c r="G1222" t="n">
-        <v>0.958037316799164</v>
+        <v>0.958037436008453</v>
       </c>
       <c r="H1222" t="n">
         <v>119</v>
@@ -35836,7 +35836,7 @@
         <v>1.22599995136261</v>
       </c>
       <c r="G1223" t="n">
-        <v>0.958037316799164</v>
+        <v>0.958037436008453</v>
       </c>
       <c r="H1223" t="n">
         <v>0</v>
@@ -35865,7 +35865,7 @@
         <v>1.22599995136261</v>
       </c>
       <c r="G1224" t="n">
-        <v>0.958037316799164</v>
+        <v>0.958037436008453</v>
       </c>
       <c r="H1224" t="n">
         <v>0</v>
@@ -35894,7 +35894,7 @@
         <v>1.23039996623993</v>
       </c>
       <c r="G1225" t="n">
-        <v>0.961475670337677</v>
+        <v>0.961475729942322</v>
       </c>
       <c r="H1225" t="n">
         <v>3067</v>
@@ -35923,7 +35923,7 @@
         <v>1.25</v>
       </c>
       <c r="G1226" t="n">
-        <v>0.976791739463806</v>
+        <v>0.976791679859161</v>
       </c>
       <c r="H1226" t="n">
         <v>370</v>
@@ -35952,7 +35952,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1227" t="n">
-        <v>0.937720239162445</v>
+        <v>0.937720060348511</v>
       </c>
       <c r="H1227" t="n">
         <v>6525</v>
@@ -36010,7 +36010,7 @@
         <v>1.192999958992</v>
       </c>
       <c r="G1229" t="n">
-        <v>0.932250082492828</v>
+        <v>0.932250022888184</v>
       </c>
       <c r="H1229" t="n">
         <v>712</v>
@@ -36126,7 +36126,7 @@
         <v>1.19159996509552</v>
       </c>
       <c r="G1233" t="n">
-        <v>0.931156039237976</v>
+        <v>0.931155979633331</v>
       </c>
       <c r="H1233" t="n">
         <v>510</v>
@@ -36213,7 +36213,7 @@
         <v>1.19799995422363</v>
       </c>
       <c r="G1236" t="n">
-        <v>0.93615710735321</v>
+        <v>0.9361572265625</v>
       </c>
       <c r="H1236" t="n">
         <v>37918</v>
@@ -36300,7 +36300,7 @@
         <v>1.26800000667572</v>
       </c>
       <c r="G1239" t="n">
-        <v>0.990857660770416</v>
+        <v>0.990857541561127</v>
       </c>
       <c r="H1239" t="n">
         <v>129144</v>
@@ -36358,7 +36358,7 @@
         <v>1.27320003509521</v>
       </c>
       <c r="G1241" t="n">
-        <v>0.994920969009399</v>
+        <v>0.994921088218689</v>
       </c>
       <c r="H1241" t="n">
         <v>41792</v>
@@ -36387,7 +36387,7 @@
         <v>1.27320003509521</v>
       </c>
       <c r="G1242" t="n">
-        <v>0.994920969009399</v>
+        <v>0.994921088218689</v>
       </c>
       <c r="H1242" t="n">
         <v>13700</v>
@@ -36445,7 +36445,7 @@
         <v>1.26639997959137</v>
       </c>
       <c r="G1244" t="n">
-        <v>0.989607334136963</v>
+        <v>0.989607214927673</v>
       </c>
       <c r="H1244" t="n">
         <v>32132</v>
@@ -36474,7 +36474,7 @@
         <v>1.32840001583099</v>
       </c>
       <c r="G1245" t="n">
-        <v>1.03805613517761</v>
+        <v>1.0380562543869</v>
       </c>
       <c r="H1245" t="n">
         <v>67169</v>
@@ -36503,7 +36503,7 @@
         <v>1.46099996566772</v>
       </c>
       <c r="G1246" t="n">
-        <v>1.14167428016663</v>
+        <v>1.14167416095734</v>
       </c>
       <c r="H1246" t="n">
         <v>196814</v>
@@ -36561,7 +36561,7 @@
         <v>1.61300003528595</v>
       </c>
       <c r="G1248" t="n">
-        <v>1.26045215129852</v>
+        <v>1.26045227050781</v>
       </c>
       <c r="H1248" t="n">
         <v>112579</v>
@@ -36590,7 +36590,7 @@
         <v>1.59200000762939</v>
       </c>
       <c r="G1249" t="n">
-        <v>1.24404203891754</v>
+        <v>1.24404191970825</v>
       </c>
       <c r="H1249" t="n">
         <v>77714</v>
@@ -36793,7 +36793,7 @@
         <v>1.72060000896454</v>
       </c>
       <c r="G1256" t="n">
-        <v>1.34453439712524</v>
+        <v>1.34453427791595</v>
       </c>
       <c r="H1256" t="n">
         <v>88356</v>
@@ -36851,7 +36851,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G1258" t="n">
-        <v>1.41439437866211</v>
+        <v>1.4143944978714</v>
       </c>
       <c r="H1258" t="n">
         <v>159971</v>
@@ -36938,7 +36938,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G1261" t="n">
-        <v>1.34406542778015</v>
+        <v>1.34406566619873</v>
       </c>
       <c r="H1261" t="n">
         <v>16020</v>
@@ -36996,7 +36996,7 @@
         <v>1.7208000421524</v>
       </c>
       <c r="G1263" t="n">
-        <v>1.34469068050385</v>
+        <v>1.34469056129456</v>
       </c>
       <c r="H1263" t="n">
         <v>7468</v>
@@ -37025,7 +37025,7 @@
         <v>1.71019995212555</v>
       </c>
       <c r="G1264" t="n">
-        <v>1.33640742301941</v>
+        <v>1.33640730381012</v>
       </c>
       <c r="H1264" t="n">
         <v>18672</v>
@@ -37083,7 +37083,7 @@
         <v>1.72940003871918</v>
       </c>
       <c r="G1266" t="n">
-        <v>1.35141086578369</v>
+        <v>1.35141098499298</v>
       </c>
       <c r="H1266" t="n">
         <v>28267</v>
@@ -37112,7 +37112,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G1267" t="n">
-        <v>1.39095151424408</v>
+        <v>1.39095139503479</v>
       </c>
       <c r="H1267" t="n">
         <v>141202</v>
@@ -37170,7 +37170,7 @@
         <v>1.74979996681213</v>
       </c>
       <c r="G1269" t="n">
-        <v>1.46478509902954</v>
+        <v>1.46478521823883</v>
       </c>
       <c r="H1269" t="n">
         <v>33596</v>
@@ -37199,7 +37199,7 @@
         <v>1.73800003528595</v>
       </c>
       <c r="G1270" t="n">
-        <v>1.45490717887878</v>
+        <v>1.45490729808807</v>
       </c>
       <c r="H1270" t="n">
         <v>14911</v>
@@ -37257,7 +37257,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G1272" t="n">
-        <v>1.43983912467957</v>
+        <v>1.43983900547028</v>
       </c>
       <c r="H1272" t="n">
         <v>16994</v>
@@ -37286,7 +37286,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G1273" t="n">
-        <v>1.43983912467957</v>
+        <v>1.43983900547028</v>
       </c>
       <c r="H1273" t="n">
         <v>0</v>
@@ -37315,7 +37315,7 @@
         <v>1.69459998607635</v>
       </c>
       <c r="G1274" t="n">
-        <v>1.41857635974884</v>
+        <v>1.41857624053955</v>
       </c>
       <c r="H1274" t="n">
         <v>82713</v>
@@ -37344,7 +37344,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G1275" t="n">
-        <v>1.43983912467957</v>
+        <v>1.43983900547028</v>
       </c>
       <c r="H1275" t="n">
         <v>57560</v>
@@ -37518,7 +37518,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G1281" t="n">
-        <v>1.37286984920502</v>
+        <v>1.37286972999573</v>
       </c>
       <c r="H1281" t="n">
         <v>16602</v>
@@ -37576,7 +37576,7 @@
         <v>1.64800000190735</v>
       </c>
       <c r="G1283" t="n">
-        <v>1.37956666946411</v>
+        <v>1.3795667886734</v>
       </c>
       <c r="H1283" t="n">
         <v>12860</v>
@@ -37605,7 +37605,7 @@
         <v>1.66939997673035</v>
       </c>
       <c r="G1284" t="n">
-        <v>1.39748084545135</v>
+        <v>1.39748108386993</v>
       </c>
       <c r="H1284" t="n">
         <v>12668</v>
@@ -37634,7 +37634,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G1285" t="n">
-        <v>1.37286984920502</v>
+        <v>1.37286972999573</v>
       </c>
       <c r="H1285" t="n">
         <v>21352</v>
@@ -37663,7 +37663,7 @@
         <v>1.60060000419617</v>
       </c>
       <c r="G1286" t="n">
-        <v>1.33988761901855</v>
+        <v>1.33988738059998</v>
       </c>
       <c r="H1286" t="n">
         <v>27968</v>
@@ -37692,7 +37692,7 @@
         <v>1.6088000535965</v>
       </c>
       <c r="G1287" t="n">
-        <v>1.34675180912018</v>
+        <v>1.34675192832947</v>
       </c>
       <c r="H1287" t="n">
         <v>15942</v>
@@ -37721,7 +37721,7 @@
         <v>1.60199999809265</v>
       </c>
       <c r="G1288" t="n">
-        <v>1.34105944633484</v>
+        <v>1.34105932712555</v>
       </c>
       <c r="H1288" t="n">
         <v>26307</v>
@@ -37750,7 +37750,7 @@
         <v>1.62999999523163</v>
       </c>
       <c r="G1289" t="n">
-        <v>1.3644984960556</v>
+        <v>1.36449873447418</v>
       </c>
       <c r="H1289" t="n">
         <v>57500</v>
@@ -37779,7 +37779,7 @@
         <v>1.64820003509521</v>
       </c>
       <c r="G1290" t="n">
-        <v>1.37973403930664</v>
+        <v>1.37973415851593</v>
       </c>
       <c r="H1290" t="n">
         <v>301</v>
@@ -37866,7 +37866,7 @@
         <v>1.60199999809265</v>
       </c>
       <c r="G1293" t="n">
-        <v>1.34105944633484</v>
+        <v>1.34105932712555</v>
       </c>
       <c r="H1293" t="n">
         <v>1484</v>
@@ -37924,7 +37924,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G1295" t="n">
-        <v>1.40635442733765</v>
+        <v>1.40635454654694</v>
       </c>
       <c r="H1295" t="n">
         <v>92320</v>
@@ -37953,7 +37953,7 @@
         <v>1.71039998531342</v>
       </c>
       <c r="G1296" t="n">
-        <v>1.4318026304245</v>
+        <v>1.43180274963379</v>
       </c>
       <c r="H1296" t="n">
         <v>100876</v>
@@ -37982,7 +37982,7 @@
         <v>1.77799999713898</v>
       </c>
       <c r="G1297" t="n">
-        <v>1.48839175701141</v>
+        <v>1.4883918762207</v>
       </c>
       <c r="H1297" t="n">
         <v>90989</v>
@@ -38011,7 +38011,7 @@
         <v>1.75419998168945</v>
       </c>
       <c r="G1298" t="n">
-        <v>1.46846842765808</v>
+        <v>1.46846830844879</v>
       </c>
       <c r="H1298" t="n">
         <v>40624</v>
@@ -38040,7 +38040,7 @@
         <v>1.77939999103546</v>
       </c>
       <c r="G1299" t="n">
-        <v>1.48956382274628</v>
+        <v>1.48956370353699</v>
       </c>
       <c r="H1299" t="n">
         <v>20620</v>
@@ -38098,7 +38098,7 @@
         <v>1.80540001392365</v>
       </c>
       <c r="G1301" t="n">
-        <v>1.51132881641388</v>
+        <v>1.51132869720459</v>
       </c>
       <c r="H1301" t="n">
         <v>61944</v>
@@ -38127,7 +38127,7 @@
         <v>1.7688000202179</v>
       </c>
       <c r="G1302" t="n">
-        <v>1.48069024085999</v>
+        <v>1.48069036006927</v>
       </c>
       <c r="H1302" t="n">
         <v>40491</v>
@@ -38185,7 +38185,7 @@
         <v>1.74399995803833</v>
       </c>
       <c r="G1304" t="n">
-        <v>1.45992970466614</v>
+        <v>1.45992982387543</v>
       </c>
       <c r="H1304" t="n">
         <v>70208</v>
@@ -38214,7 +38214,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G1305" t="n">
-        <v>1.56540644168854</v>
+        <v>1.56540632247925</v>
       </c>
       <c r="H1305" t="n">
         <v>90063</v>
@@ -38243,7 +38243,7 @@
         <v>1.83259999752045</v>
       </c>
       <c r="G1306" t="n">
-        <v>1.53409826755524</v>
+        <v>1.53409814834595</v>
       </c>
       <c r="H1306" t="n">
         <v>15504</v>
@@ -38272,7 +38272,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G1307" t="n">
-        <v>1.57377755641937</v>
+        <v>1.57377743721008</v>
       </c>
       <c r="H1307" t="n">
         <v>25764</v>
@@ -38301,7 +38301,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G1308" t="n">
-        <v>1.57377755641937</v>
+        <v>1.57377743721008</v>
       </c>
       <c r="H1308" t="n">
         <v>6508</v>
@@ -38330,7 +38330,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G1309" t="n">
-        <v>1.56540644168854</v>
+        <v>1.56540632247925</v>
       </c>
       <c r="H1309" t="n">
         <v>5381</v>
@@ -38359,7 +38359,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G1310" t="n">
-        <v>1.56540644168854</v>
+        <v>1.56540632247925</v>
       </c>
       <c r="H1310" t="n">
         <v>6800</v>
@@ -38388,7 +38388,7 @@
         <v>1.87479996681213</v>
       </c>
       <c r="G1311" t="n">
-        <v>1.56942451000214</v>
+        <v>1.56942462921143</v>
       </c>
       <c r="H1311" t="n">
         <v>5785</v>
@@ -38446,7 +38446,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G1313" t="n">
-        <v>1.57377755641937</v>
+        <v>1.57377743721008</v>
       </c>
       <c r="H1313" t="n">
         <v>4995</v>
@@ -38533,7 +38533,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G1316" t="n">
-        <v>1.57377755641937</v>
+        <v>1.57377743721008</v>
       </c>
       <c r="H1316" t="n">
         <v>16667</v>
@@ -38562,7 +38562,7 @@
         <v>1.9423999786377</v>
       </c>
       <c r="G1317" t="n">
-        <v>1.62601363658905</v>
+        <v>1.62601351737976</v>
       </c>
       <c r="H1317" t="n">
         <v>154605</v>
@@ -38591,7 +38591,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G1318" t="n">
-        <v>1.62400448322296</v>
+        <v>1.62400460243225</v>
       </c>
       <c r="H1318" t="n">
         <v>11052</v>
@@ -38678,7 +38678,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G1321" t="n">
-        <v>1.65748906135559</v>
+        <v>1.65748918056488</v>
       </c>
       <c r="H1321" t="n">
         <v>17248</v>
@@ -38736,7 +38736,7 @@
         <v>1.96440005302429</v>
       </c>
       <c r="G1323" t="n">
-        <v>1.64443004131317</v>
+        <v>1.64443016052246</v>
       </c>
       <c r="H1323" t="n">
         <v>7944</v>
@@ -38765,7 +38765,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G1324" t="n">
-        <v>1.61563336849213</v>
+        <v>1.61563324928284</v>
       </c>
       <c r="H1324" t="n">
         <v>11644</v>
@@ -38794,7 +38794,7 @@
         <v>1.92120003700256</v>
       </c>
       <c r="G1325" t="n">
-        <v>1.60826671123505</v>
+        <v>1.60826683044434</v>
       </c>
       <c r="H1325" t="n">
         <v>17616</v>
@@ -38823,7 +38823,7 @@
         <v>1.94700002670288</v>
       </c>
       <c r="G1326" t="n">
-        <v>1.62986433506012</v>
+        <v>1.62986445426941</v>
       </c>
       <c r="H1326" t="n">
         <v>33486</v>
@@ -38910,7 +38910,7 @@
         <v>1.95959997177124</v>
       </c>
       <c r="G1329" t="n">
-        <v>1.64041185379028</v>
+        <v>1.64041197299957</v>
       </c>
       <c r="H1329" t="n">
         <v>3100</v>
@@ -39171,7 +39171,7 @@
         <v>1.93499994277954</v>
       </c>
       <c r="G1338" t="n">
-        <v>1.61981904506683</v>
+        <v>1.61981892585754</v>
       </c>
       <c r="H1338" t="n">
         <v>12311</v>
@@ -39200,7 +39200,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G1339" t="n">
-        <v>1.607262134552</v>
+        <v>1.60726225376129</v>
       </c>
       <c r="H1339" t="n">
         <v>1005</v>
@@ -39229,7 +39229,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G1340" t="n">
-        <v>1.607262134552</v>
+        <v>1.60726225376129</v>
       </c>
       <c r="H1340" t="n">
         <v>120</v>
@@ -39258,7 +39258,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G1341" t="n">
-        <v>1.607262134552</v>
+        <v>1.60726225376129</v>
       </c>
       <c r="H1341" t="n">
         <v>20929</v>
@@ -39287,7 +39287,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G1342" t="n">
-        <v>1.61563336849213</v>
+        <v>1.61563324928284</v>
       </c>
       <c r="H1342" t="n">
         <v>4847</v>
@@ -39316,7 +39316,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G1343" t="n">
-        <v>1.607262134552</v>
+        <v>1.60726225376129</v>
       </c>
       <c r="H1343" t="n">
         <v>14161</v>
@@ -39345,7 +39345,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G1344" t="n">
-        <v>1.69097375869751</v>
+        <v>1.6909738779068</v>
       </c>
       <c r="H1344" t="n">
         <v>155728</v>
@@ -39374,7 +39374,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G1345" t="n">
-        <v>1.65748906135559</v>
+        <v>1.65748918056488</v>
       </c>
       <c r="H1345" t="n">
         <v>50151</v>
@@ -39432,7 +39432,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G1347" t="n">
-        <v>1.69097375869751</v>
+        <v>1.6909738779068</v>
       </c>
       <c r="H1347" t="n">
         <v>31082</v>
@@ -39490,7 +39490,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G1349" t="n">
-        <v>1.65748906135559</v>
+        <v>1.65748918056488</v>
       </c>
       <c r="H1349" t="n">
         <v>45371</v>
@@ -39519,7 +39519,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G1350" t="n">
-        <v>1.607262134552</v>
+        <v>1.60726225376129</v>
       </c>
       <c r="H1350" t="n">
         <v>120787</v>
@@ -39577,7 +39577,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G1352" t="n">
-        <v>1.59889101982117</v>
+        <v>1.59889113903046</v>
       </c>
       <c r="H1352" t="n">
         <v>23824</v>
@@ -39606,7 +39606,7 @@
         <v>1.85500001907349</v>
       </c>
       <c r="G1353" t="n">
-        <v>1.55284976959229</v>
+        <v>1.552849650383</v>
       </c>
       <c r="H1353" t="n">
         <v>21990</v>
@@ -39693,7 +39693,7 @@
         <v>1.88499999046326</v>
       </c>
       <c r="G1356" t="n">
-        <v>1.57796311378479</v>
+        <v>1.57796323299408</v>
       </c>
       <c r="H1356" t="n">
         <v>10700</v>
@@ -39722,7 +39722,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G1357" t="n">
-        <v>1.5570353269577</v>
+        <v>1.55703544616699</v>
       </c>
       <c r="H1357" t="n">
         <v>10646</v>
@@ -39780,7 +39780,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G1359" t="n">
-        <v>1.56540644168854</v>
+        <v>1.56540632247925</v>
       </c>
       <c r="H1359" t="n">
         <v>4850</v>
@@ -39838,7 +39838,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G1361" t="n">
-        <v>1.607262134552</v>
+        <v>1.60726225376129</v>
       </c>
       <c r="H1361" t="n">
         <v>16896</v>
@@ -39896,7 +39896,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G1363" t="n">
-        <v>1.58214867115021</v>
+        <v>1.5821487903595</v>
       </c>
       <c r="H1363" t="n">
         <v>20795</v>
@@ -39983,7 +39983,7 @@
         <v>1.85500001907349</v>
       </c>
       <c r="G1366" t="n">
-        <v>1.55284976959229</v>
+        <v>1.552849650383</v>
       </c>
       <c r="H1366" t="n">
         <v>32969</v>
@@ -40070,7 +40070,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G1369" t="n">
-        <v>1.5570353269577</v>
+        <v>1.55703544616699</v>
       </c>
       <c r="H1369" t="n">
         <v>6264</v>
@@ -40128,7 +40128,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G1371" t="n">
-        <v>1.5570353269577</v>
+        <v>1.55703544616699</v>
       </c>
       <c r="H1371" t="n">
         <v>5678</v>
@@ -40186,7 +40186,7 @@
         <v>1.83500003814697</v>
       </c>
       <c r="G1373" t="n">
-        <v>1.53610742092133</v>
+        <v>1.53610754013062</v>
       </c>
       <c r="H1373" t="n">
         <v>6413</v>
@@ -40244,7 +40244,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G1375" t="n">
-        <v>1.5570353269577</v>
+        <v>1.55703544616699</v>
       </c>
       <c r="H1375" t="n">
         <v>5724</v>
@@ -40302,7 +40302,7 @@
         <v>1.86500000953674</v>
       </c>
       <c r="G1377" t="n">
-        <v>1.56122076511383</v>
+        <v>1.56122088432312</v>
       </c>
       <c r="H1377" t="n">
         <v>24781</v>
@@ -40418,7 +40418,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G1381" t="n">
-        <v>1.90862393379211</v>
+        <v>1.90862381458282</v>
       </c>
       <c r="H1381" t="n">
         <v>118880</v>
@@ -40476,7 +40476,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G1383" t="n">
-        <v>1.87513911724091</v>
+        <v>1.87513935565948</v>
       </c>
       <c r="H1383" t="n">
         <v>52913</v>
@@ -40505,7 +40505,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G1384" t="n">
-        <v>1.9002525806427</v>
+        <v>1.90025269985199</v>
       </c>
       <c r="H1384" t="n">
         <v>25190</v>
@@ -40737,7 +40737,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G1392" t="n">
-        <v>1.76631426811218</v>
+        <v>1.7663140296936</v>
       </c>
       <c r="H1392" t="n">
         <v>3519</v>
@@ -40824,7 +40824,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G1395" t="n">
-        <v>1.79142773151398</v>
+        <v>1.79142785072327</v>
       </c>
       <c r="H1395" t="n">
         <v>9872</v>
@@ -40911,7 +40911,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G1398" t="n">
-        <v>1.76631426811218</v>
+        <v>1.7663140296936</v>
       </c>
       <c r="H1398" t="n">
         <v>4485</v>
@@ -41114,7 +41114,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G1405" t="n">
-        <v>1.74957180023193</v>
+        <v>1.74957191944122</v>
       </c>
       <c r="H1405" t="n">
         <v>6593</v>
@@ -41201,7 +41201,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G1408" t="n">
-        <v>1.70771598815918</v>
+        <v>1.70771610736847</v>
       </c>
       <c r="H1408" t="n">
         <v>1758</v>
@@ -41288,7 +41288,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G1411" t="n">
-        <v>1.70771598815918</v>
+        <v>1.70771610736847</v>
       </c>
       <c r="H1411" t="n">
         <v>36540</v>
@@ -41317,7 +41317,7 @@
         <v>1.98500001430511</v>
       </c>
       <c r="G1412" t="n">
-        <v>1.6616747379303</v>
+        <v>1.66167485713959</v>
       </c>
       <c r="H1412" t="n">
         <v>10099</v>
@@ -41404,7 +41404,7 @@
         <v>1.99500000476837</v>
       </c>
       <c r="G1415" t="n">
-        <v>1.67004597187042</v>
+        <v>1.67004585266113</v>
       </c>
       <c r="H1415" t="n">
         <v>1050</v>
@@ -41433,7 +41433,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G1416" t="n">
-        <v>1.65748906135559</v>
+        <v>1.65748918056488</v>
       </c>
       <c r="H1416" t="n">
         <v>5</v>
@@ -41462,7 +41462,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G1417" t="n">
-        <v>1.69097375869751</v>
+        <v>1.6909738779068</v>
       </c>
       <c r="H1417" t="n">
         <v>5747</v>
@@ -41520,7 +41520,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G1419" t="n">
-        <v>1.77468514442444</v>
+        <v>1.77468526363373</v>
       </c>
       <c r="H1419" t="n">
         <v>15638</v>
@@ -41926,7 +41926,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G1433" t="n">
-        <v>1.79142773151398</v>
+        <v>1.79142785072327</v>
       </c>
       <c r="H1433" t="n">
         <v>12195</v>
@@ -42042,7 +42042,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G1437" t="n">
-        <v>1.85002565383911</v>
+        <v>1.8500257730484</v>
       </c>
       <c r="H1437" t="n">
         <v>2124</v>
@@ -42332,7 +42332,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G1447" t="n">
-        <v>1.79142773151398</v>
+        <v>1.79142785072327</v>
       </c>
       <c r="H1447" t="n">
         <v>1801</v>
@@ -42361,7 +42361,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G1448" t="n">
-        <v>1.76631426811218</v>
+        <v>1.7663140296936</v>
       </c>
       <c r="H1448" t="n">
         <v>6157</v>
@@ -42506,7 +42506,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G1453" t="n">
-        <v>1.77468514442444</v>
+        <v>1.77468526363373</v>
       </c>
       <c r="H1453" t="n">
         <v>5250</v>
@@ -42564,7 +42564,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G1455" t="n">
-        <v>1.79142773151398</v>
+        <v>1.79142785072327</v>
       </c>
       <c r="H1455" t="n">
         <v>8648</v>
@@ -42651,7 +42651,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G1458" t="n">
-        <v>1.86676824092865</v>
+        <v>1.86676800251007</v>
       </c>
       <c r="H1458" t="n">
         <v>13297</v>
@@ -42680,7 +42680,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G1459" t="n">
-        <v>1.87513911724091</v>
+        <v>1.87513935565948</v>
       </c>
       <c r="H1459" t="n">
         <v>10775</v>
@@ -42709,7 +42709,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G1460" t="n">
-        <v>1.87513911724091</v>
+        <v>1.87513935565948</v>
       </c>
       <c r="H1460" t="n">
         <v>12250</v>
@@ -42738,7 +42738,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G1461" t="n">
-        <v>1.9002525806427</v>
+        <v>1.90025269985199</v>
       </c>
       <c r="H1461" t="n">
         <v>22939</v>
@@ -42767,7 +42767,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G1462" t="n">
-        <v>2.19324278831482</v>
+        <v>2.1932430267334</v>
       </c>
       <c r="H1462" t="n">
         <v>497101</v>
@@ -42796,7 +42796,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G1463" t="n">
-        <v>2.20161461830139</v>
+        <v>2.20161437988281</v>
       </c>
       <c r="H1463" t="n">
         <v>261129</v>
@@ -42854,7 +42854,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G1465" t="n">
-        <v>2.16812944412231</v>
+        <v>2.16812968254089</v>
       </c>
       <c r="H1465" t="n">
         <v>38675</v>
@@ -42912,7 +42912,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G1467" t="n">
-        <v>2.07604718208313</v>
+        <v>2.07604694366455</v>
       </c>
       <c r="H1467" t="n">
         <v>8318</v>
@@ -42970,7 +42970,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G1469" t="n">
-        <v>2.07604718208313</v>
+        <v>2.07604694366455</v>
       </c>
       <c r="H1469" t="n">
         <v>10761</v>
@@ -42999,7 +42999,7 @@
         <v>2.5</v>
       </c>
       <c r="G1470" t="n">
-        <v>2.09278917312622</v>
+        <v>2.0927894115448</v>
       </c>
       <c r="H1470" t="n">
         <v>17544</v>
@@ -43057,7 +43057,7 @@
         <v>2.5</v>
       </c>
       <c r="G1472" t="n">
-        <v>2.09278917312622</v>
+        <v>2.0927894115448</v>
       </c>
       <c r="H1472" t="n">
         <v>16513</v>
@@ -43086,7 +43086,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G1473" t="n">
-        <v>2.13464498519897</v>
+        <v>2.13464522361755</v>
       </c>
       <c r="H1473" t="n">
         <v>33269</v>
@@ -43144,7 +43144,7 @@
         <v>2.5</v>
       </c>
       <c r="G1475" t="n">
-        <v>2.09278917312622</v>
+        <v>2.0927894115448</v>
       </c>
       <c r="H1475" t="n">
         <v>1995</v>
@@ -43231,7 +43231,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G1478" t="n">
-        <v>2.20161461830139</v>
+        <v>2.20161437988281</v>
       </c>
       <c r="H1478" t="n">
         <v>8945</v>
@@ -43347,7 +43347,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G1482" t="n">
-        <v>2.19324278831482</v>
+        <v>2.1932430267334</v>
       </c>
       <c r="H1482" t="n">
         <v>2227</v>
@@ -43521,7 +43521,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G1488" t="n">
-        <v>2.16812944412231</v>
+        <v>2.16812968254089</v>
       </c>
       <c r="H1488" t="n">
         <v>17680</v>
@@ -43608,7 +43608,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G1491" t="n">
-        <v>2.13464498519897</v>
+        <v>2.13464522361755</v>
       </c>
       <c r="H1491" t="n">
         <v>11546</v>
@@ -43637,7 +43637,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G1492" t="n">
-        <v>2.15138745307922</v>
+        <v>2.15138721466064</v>
       </c>
       <c r="H1492" t="n">
         <v>4814</v>
@@ -43695,7 +43695,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G1494" t="n">
-        <v>2.25184154510498</v>
+        <v>2.2518413066864</v>
       </c>
       <c r="H1494" t="n">
         <v>89679</v>
@@ -43811,7 +43811,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G1498" t="n">
-        <v>2.21835660934448</v>
+        <v>2.21835684776306</v>
       </c>
       <c r="H1498" t="n">
         <v>26546</v>
@@ -43840,7 +43840,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G1499" t="n">
-        <v>2.21835660934448</v>
+        <v>2.21835684776306</v>
       </c>
       <c r="H1499" t="n">
         <v>2484</v>
@@ -43898,7 +43898,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G1501" t="n">
-        <v>2.25184154510498</v>
+        <v>2.2518413066864</v>
       </c>
       <c r="H1501" t="n">
         <v>65037</v>
@@ -43927,7 +43927,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G1502" t="n">
-        <v>2.27695488929749</v>
+        <v>2.27695465087891</v>
       </c>
       <c r="H1502" t="n">
         <v>6864</v>
@@ -43956,7 +43956,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G1503" t="n">
-        <v>2.25184154510498</v>
+        <v>2.2518413066864</v>
       </c>
       <c r="H1503" t="n">
         <v>18385</v>
@@ -43985,7 +43985,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G1504" t="n">
-        <v>2.24347019195557</v>
+        <v>2.24347043037415</v>
       </c>
       <c r="H1504" t="n">
         <v>44721</v>
@@ -44014,7 +44014,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G1505" t="n">
-        <v>2.21835660934448</v>
+        <v>2.21835684776306</v>
       </c>
       <c r="H1505" t="n">
         <v>7243</v>
@@ -44043,7 +44043,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G1506" t="n">
-        <v>2.26858353614807</v>
+        <v>2.26858377456665</v>
       </c>
       <c r="H1506" t="n">
         <v>24102</v>
@@ -44072,7 +44072,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G1507" t="n">
-        <v>2.26858353614807</v>
+        <v>2.26858377456665</v>
       </c>
       <c r="H1507" t="n">
         <v>15920</v>
@@ -44130,7 +44130,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G1509" t="n">
-        <v>2.26858353614807</v>
+        <v>2.26858377456665</v>
       </c>
       <c r="H1509" t="n">
         <v>27905</v>
@@ -44188,7 +44188,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G1511" t="n">
-        <v>2.21835660934448</v>
+        <v>2.21835684776306</v>
       </c>
       <c r="H1511" t="n">
         <v>8611</v>
@@ -44217,7 +44217,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G1512" t="n">
-        <v>2.25184154510498</v>
+        <v>2.2518413066864</v>
       </c>
       <c r="H1512" t="n">
         <v>1609</v>
@@ -44246,7 +44246,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G1513" t="n">
-        <v>2.25184154510498</v>
+        <v>2.2518413066864</v>
       </c>
       <c r="H1513" t="n">
         <v>10947</v>
@@ -44275,7 +44275,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G1514" t="n">
-        <v>2.26858353614807</v>
+        <v>2.26858377456665</v>
       </c>
       <c r="H1514" t="n">
         <v>9007</v>
@@ -44304,7 +44304,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G1515" t="n">
-        <v>2.26858353614807</v>
+        <v>2.26858377456665</v>
       </c>
       <c r="H1515" t="n">
         <v>22258</v>
@@ -44420,7 +44420,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G1519" t="n">
-        <v>2.59505867958069</v>
+        <v>2.59505891799927</v>
       </c>
       <c r="H1519" t="n">
         <v>110398</v>
@@ -44536,7 +44536,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G1523" t="n">
-        <v>2.75411057472229</v>
+        <v>2.75411081314087</v>
       </c>
       <c r="H1523" t="n">
         <v>36741</v>
@@ -44565,7 +44565,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G1524" t="n">
-        <v>3.23963809013367</v>
+        <v>3.23963785171509</v>
       </c>
       <c r="H1524" t="n">
         <v>106501</v>
@@ -44652,7 +44652,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G1527" t="n">
-        <v>3.10569953918457</v>
+        <v>3.10569930076599</v>
       </c>
       <c r="H1527" t="n">
         <v>40326</v>
@@ -44710,7 +44710,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G1529" t="n">
-        <v>3.03035879135132</v>
+        <v>3.0303590297699</v>
       </c>
       <c r="H1529" t="n">
         <v>25973</v>
@@ -44855,7 +44855,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G1534" t="n">
-        <v>2.87967824935913</v>
+        <v>2.87967801094055</v>
       </c>
       <c r="H1534" t="n">
         <v>5863</v>
@@ -44884,7 +44884,7 @@
         <v>3.5</v>
       </c>
       <c r="G1535" t="n">
-        <v>2.92990517616272</v>
+        <v>2.92990493774414</v>
       </c>
       <c r="H1535" t="n">
         <v>5651</v>
@@ -44913,7 +44913,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G1536" t="n">
-        <v>2.8964204788208</v>
+        <v>2.89642071723938</v>
       </c>
       <c r="H1536" t="n">
         <v>9495</v>
@@ -44971,7 +44971,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1538" t="n">
-        <v>2.84619379043579</v>
+        <v>2.84619331359863</v>
       </c>
       <c r="H1538" t="n">
         <v>13330</v>
@@ -45029,7 +45029,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G1540" t="n">
-        <v>2.78759527206421</v>
+        <v>2.78759551048279</v>
       </c>
       <c r="H1540" t="n">
         <v>21833</v>
@@ -45058,7 +45058,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1541" t="n">
-        <v>2.80433773994446</v>
+        <v>2.80433750152588</v>
       </c>
       <c r="H1541" t="n">
         <v>9323</v>
@@ -45087,7 +45087,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G1542" t="n">
-        <v>2.8964204788208</v>
+        <v>2.89642071723938</v>
       </c>
       <c r="H1542" t="n">
         <v>56699</v>
@@ -45174,7 +45174,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G1545" t="n">
-        <v>3.03873038291931</v>
+        <v>3.03873014450073</v>
       </c>
       <c r="H1545" t="n">
         <v>46478</v>
@@ -45232,7 +45232,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G1547" t="n">
-        <v>3.04710149765015</v>
+        <v>3.04710125923157</v>
       </c>
       <c r="H1547" t="n">
         <v>27597</v>
@@ -45261,7 +45261,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G1548" t="n">
-        <v>3.12244153022766</v>
+        <v>3.12244176864624</v>
       </c>
       <c r="H1548" t="n">
         <v>31587</v>
@@ -45290,7 +45290,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G1549" t="n">
-        <v>3.1894109249115</v>
+        <v>3.18941068649292</v>
       </c>
       <c r="H1549" t="n">
         <v>55680</v>
@@ -45348,7 +45348,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G1551" t="n">
-        <v>3.22289538383484</v>
+        <v>3.22289562225342</v>
       </c>
       <c r="H1551" t="n">
         <v>94238</v>
@@ -45493,7 +45493,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G1556" t="n">
-        <v>3.21806406974792</v>
+        <v>3.2180643081665</v>
       </c>
       <c r="H1556" t="n">
         <v>26348</v>
@@ -45522,7 +45522,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G1557" t="n">
-        <v>3.15767168998718</v>
+        <v>3.1576714515686</v>
       </c>
       <c r="H1557" t="n">
         <v>14643</v>
@@ -45725,7 +45725,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1564" t="n">
-        <v>3.10590624809265</v>
+        <v>3.10590648651123</v>
       </c>
       <c r="H1564" t="n">
         <v>5841</v>
@@ -45783,7 +45783,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G1566" t="n">
-        <v>2.97649383544922</v>
+        <v>2.97649359703064</v>
       </c>
       <c r="H1566" t="n">
         <v>27030</v>
@@ -46015,7 +46015,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G1574" t="n">
-        <v>2.66590309143066</v>
+        <v>2.66590285301208</v>
       </c>
       <c r="H1574" t="n">
         <v>33185</v>
@@ -46044,7 +46044,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G1575" t="n">
-        <v>2.62276554107666</v>
+        <v>2.62276530265808</v>
       </c>
       <c r="H1575" t="n">
         <v>16919</v>
@@ -46218,7 +46218,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G1581" t="n">
-        <v>3.00237631797791</v>
+        <v>3.00237607955933</v>
       </c>
       <c r="H1581" t="n">
         <v>7369</v>
@@ -46247,7 +46247,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G1582" t="n">
-        <v>2.96786618232727</v>
+        <v>2.96786594390869</v>
       </c>
       <c r="H1582" t="n">
         <v>9819</v>
@@ -46421,7 +46421,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G1588" t="n">
-        <v>3.00237631797791</v>
+        <v>3.00237607955933</v>
       </c>
       <c r="H1588" t="n">
         <v>8197</v>
@@ -46595,7 +46595,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1594" t="n">
-        <v>2.93335628509521</v>
+        <v>2.93335604667664</v>
       </c>
       <c r="H1594" t="n">
         <v>1217</v>
@@ -46624,7 +46624,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1595" t="n">
-        <v>2.93335628509521</v>
+        <v>2.93335604667664</v>
       </c>
       <c r="H1595" t="n">
         <v>2971</v>
@@ -46711,7 +46711,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1598" t="n">
-        <v>2.93335628509521</v>
+        <v>2.93335604667664</v>
       </c>
       <c r="H1598" t="n">
         <v>2090</v>
@@ -46798,7 +46798,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1601" t="n">
-        <v>2.93335628509521</v>
+        <v>2.93335604667664</v>
       </c>
       <c r="H1601" t="n">
         <v>1039</v>
@@ -46827,7 +46827,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G1602" t="n">
-        <v>2.95061111450195</v>
+        <v>2.95061135292053</v>
       </c>
       <c r="H1602" t="n">
         <v>3240</v>
@@ -47001,7 +47001,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G1608" t="n">
-        <v>2.95061111450195</v>
+        <v>2.95061135292053</v>
       </c>
       <c r="H1608" t="n">
         <v>24178</v>
@@ -47059,7 +47059,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G1610" t="n">
-        <v>3.19792699813843</v>
+        <v>3.19792723655701</v>
       </c>
       <c r="H1610" t="n">
         <v>18822</v>
@@ -47088,7 +47088,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1611" t="n">
-        <v>3.05004596710205</v>
+        <v>3.05004620552063</v>
       </c>
       <c r="H1611" t="n">
         <v>18282</v>
@@ -47117,7 +47117,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1612" t="n">
-        <v>3.05004596710205</v>
+        <v>3.05004620552063</v>
       </c>
       <c r="H1612" t="n">
         <v>6535</v>
@@ -47146,7 +47146,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1613" t="n">
-        <v>3.05004596710205</v>
+        <v>3.05004620552063</v>
       </c>
       <c r="H1613" t="n">
         <v>6560</v>
@@ -47204,7 +47204,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G1615" t="n">
-        <v>2.98534798622131</v>
+        <v>2.98534822463989</v>
       </c>
       <c r="H1615" t="n">
         <v>5371</v>
@@ -47262,7 +47262,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G1617" t="n">
-        <v>3.01307559013367</v>
+        <v>3.01307582855225</v>
       </c>
       <c r="H1617" t="n">
         <v>1877</v>
@@ -47320,7 +47320,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G1619" t="n">
-        <v>3.06853127479553</v>
+        <v>3.06853103637695</v>
       </c>
       <c r="H1619" t="n">
         <v>5319</v>
@@ -47378,7 +47378,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G1621" t="n">
-        <v>2.93913555145264</v>
+        <v>2.93913531303406</v>
       </c>
       <c r="H1621" t="n">
         <v>7441</v>
@@ -47407,7 +47407,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G1622" t="n">
-        <v>3.06853127479553</v>
+        <v>3.06853103637695</v>
       </c>
       <c r="H1622" t="n">
         <v>9571</v>
@@ -47494,7 +47494,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G1625" t="n">
-        <v>3.01307559013367</v>
+        <v>3.01307582855225</v>
       </c>
       <c r="H1625" t="n">
         <v>720</v>
@@ -47523,7 +47523,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G1626" t="n">
-        <v>3.01307559013367</v>
+        <v>3.01307582855225</v>
       </c>
       <c r="H1626" t="n">
         <v>0</v>
@@ -47552,7 +47552,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G1627" t="n">
-        <v>2.98534798622131</v>
+        <v>2.98534822463989</v>
       </c>
       <c r="H1627" t="n">
         <v>2900</v>
@@ -47697,7 +47697,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G1632" t="n">
-        <v>2.93913555145264</v>
+        <v>2.93913531303406</v>
       </c>
       <c r="H1632" t="n">
         <v>2221</v>
@@ -47813,7 +47813,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G1636" t="n">
-        <v>2.88367986679077</v>
+        <v>2.88367962837219</v>
       </c>
       <c r="H1636" t="n">
         <v>4351</v>
@@ -48074,7 +48074,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G1645" t="n">
-        <v>2.44927930831909</v>
+        <v>2.44927954673767</v>
       </c>
       <c r="H1645" t="n">
         <v>4242</v>
@@ -48364,7 +48364,7 @@
         <v>2.75</v>
       </c>
       <c r="G1655" t="n">
-        <v>2.54170513153076</v>
+        <v>2.54170489311218</v>
       </c>
       <c r="H1655" t="n">
         <v>4443</v>
@@ -48422,7 +48422,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G1657" t="n">
-        <v>2.66185832023621</v>
+        <v>2.66185855865479</v>
       </c>
       <c r="H1657" t="n">
         <v>1365</v>
@@ -48538,7 +48538,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G1661" t="n">
-        <v>2.51397752761841</v>
+        <v>2.51397728919983</v>
       </c>
       <c r="H1661" t="n">
         <v>2782</v>
@@ -48596,7 +48596,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G1663" t="n">
-        <v>2.53246259689331</v>
+        <v>2.53246235847473</v>
       </c>
       <c r="H1663" t="n">
         <v>37694</v>
@@ -48625,7 +48625,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G1664" t="n">
-        <v>2.48624968528748</v>
+        <v>2.48624992370605</v>
       </c>
       <c r="H1664" t="n">
         <v>1765</v>
@@ -48712,7 +48712,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G1667" t="n">
-        <v>2.51397752761841</v>
+        <v>2.51397728919983</v>
       </c>
       <c r="H1667" t="n">
         <v>22439</v>
@@ -48741,7 +48741,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G1668" t="n">
-        <v>2.44927930831909</v>
+        <v>2.44927954673767</v>
       </c>
       <c r="H1668" t="n">
         <v>12455</v>
@@ -48857,7 +48857,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G1672" t="n">
-        <v>2.42155146598816</v>
+        <v>2.42155170440674</v>
       </c>
       <c r="H1672" t="n">
         <v>3460</v>
@@ -49147,7 +49147,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G1682" t="n">
-        <v>2.40306663513184</v>
+        <v>2.40306639671326</v>
       </c>
       <c r="H1682" t="n">
         <v>1410</v>
@@ -49495,7 +49495,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G1694" t="n">
-        <v>2.27367067337036</v>
+        <v>2.27367091178894</v>
       </c>
       <c r="H1694" t="n">
         <v>3905</v>
@@ -49611,7 +49611,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G1698" t="n">
-        <v>2.27367067337036</v>
+        <v>2.27367091178894</v>
       </c>
       <c r="H1698" t="n">
         <v>19</v>
@@ -49640,7 +49640,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G1699" t="n">
-        <v>2.26442837715149</v>
+        <v>2.26442813873291</v>
       </c>
       <c r="H1699" t="n">
         <v>580</v>
@@ -49669,7 +49669,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G1700" t="n">
-        <v>2.23670029640198</v>
+        <v>2.23670053482056</v>
       </c>
       <c r="H1700" t="n">
         <v>450</v>
@@ -49814,7 +49814,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G1705" t="n">
-        <v>2.20897269248962</v>
+        <v>2.2089729309082</v>
       </c>
       <c r="H1705" t="n">
         <v>1386</v>
@@ -49872,7 +49872,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G1707" t="n">
-        <v>2.26442837715149</v>
+        <v>2.26442813873291</v>
       </c>
       <c r="H1707" t="n">
         <v>190</v>
@@ -49901,7 +49901,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G1708" t="n">
-        <v>2.26442837715149</v>
+        <v>2.26442813873291</v>
       </c>
       <c r="H1708" t="n">
         <v>0</v>
@@ -49959,7 +49959,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G1710" t="n">
-        <v>2.28291320800781</v>
+        <v>2.28291344642639</v>
       </c>
       <c r="H1710" t="n">
         <v>900</v>
@@ -49988,7 +49988,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G1711" t="n">
-        <v>2.28291320800781</v>
+        <v>2.28291344642639</v>
       </c>
       <c r="H1711" t="n">
         <v>0</v>
@@ -50104,7 +50104,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G1715" t="n">
-        <v>2.23670029640198</v>
+        <v>2.23670053482056</v>
       </c>
       <c r="H1715" t="n">
         <v>11340</v>
@@ -50133,7 +50133,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G1716" t="n">
-        <v>2.28291320800781</v>
+        <v>2.28291344642639</v>
       </c>
       <c r="H1716" t="n">
         <v>8732</v>
@@ -50278,7 +50278,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G1721" t="n">
-        <v>2.0703341960907</v>
+        <v>2.07033443450928</v>
       </c>
       <c r="H1721" t="n">
         <v>201</v>
@@ -50336,7 +50336,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G1723" t="n">
-        <v>2.19048762321472</v>
+        <v>2.19048738479614</v>
       </c>
       <c r="H1723" t="n">
         <v>7034</v>
@@ -50423,7 +50423,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G1726" t="n">
-        <v>2.06109166145325</v>
+        <v>2.06109189987183</v>
       </c>
       <c r="H1726" t="n">
         <v>7464</v>
@@ -50684,7 +50684,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G1735" t="n">
-        <v>2.05184936523438</v>
+        <v>2.0518491268158</v>
       </c>
       <c r="H1735" t="n">
         <v>601</v>
@@ -50742,7 +50742,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1737" t="n">
-        <v>1.99639403820038</v>
+        <v>1.99639391899109</v>
       </c>
       <c r="H1737" t="n">
         <v>7242</v>
@@ -50945,7 +50945,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G1744" t="n">
-        <v>2.0703341960907</v>
+        <v>2.07033443450928</v>
       </c>
       <c r="H1744" t="n">
         <v>2600</v>
@@ -51032,7 +51032,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G1747" t="n">
-        <v>2.06109166145325</v>
+        <v>2.06109189987183</v>
       </c>
       <c r="H1747" t="n">
         <v>2976</v>
@@ -51148,7 +51148,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G1751" t="n">
-        <v>2.23670029640198</v>
+        <v>2.23670053482056</v>
       </c>
       <c r="H1751" t="n">
         <v>2433</v>
@@ -51293,7 +51293,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G1756" t="n">
-        <v>2.19048762321472</v>
+        <v>2.19048738479614</v>
       </c>
       <c r="H1756" t="n">
         <v>8634</v>
@@ -51322,7 +51322,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G1757" t="n">
-        <v>2.27367067337036</v>
+        <v>2.27367091178894</v>
       </c>
       <c r="H1757" t="n">
         <v>7714</v>
@@ -51351,7 +51351,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G1758" t="n">
-        <v>2.53246259689331</v>
+        <v>2.53246235847473</v>
       </c>
       <c r="H1758" t="n">
         <v>20349</v>
@@ -51467,7 +51467,7 @@
         <v>2.75</v>
       </c>
       <c r="G1762" t="n">
-        <v>2.54170513153076</v>
+        <v>2.54170489311218</v>
       </c>
       <c r="H1762" t="n">
         <v>6937</v>
@@ -51699,7 +51699,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G1770" t="n">
-        <v>2.51397752761841</v>
+        <v>2.51397728919983</v>
       </c>
       <c r="H1770" t="n">
         <v>9906</v>
@@ -51786,7 +51786,7 @@
         <v>2.75</v>
       </c>
       <c r="G1773" t="n">
-        <v>2.54170513153076</v>
+        <v>2.54170489311218</v>
       </c>
       <c r="H1773" t="n">
         <v>13690</v>
@@ -51844,7 +51844,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G1775" t="n">
-        <v>2.53246259689331</v>
+        <v>2.53246235847473</v>
       </c>
       <c r="H1775" t="n">
         <v>10845</v>
@@ -51873,7 +51873,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G1776" t="n">
-        <v>2.53246259689331</v>
+        <v>2.53246235847473</v>
       </c>
       <c r="H1776" t="n">
         <v>3910</v>
@@ -51902,7 +51902,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G1777" t="n">
-        <v>2.51397752761841</v>
+        <v>2.51397728919983</v>
       </c>
       <c r="H1777" t="n">
         <v>18536</v>
@@ -80125,6 +80125,35 @@
         <v>11003</v>
       </c>
       <c r="I2750" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2751">
+      <c r="A2751" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2751" s="1" t="n">
+        <v>46322.3333333333</v>
+      </c>
+      <c r="C2751" t="n">
+        <v>0.361999988555908</v>
+      </c>
+      <c r="D2751" t="n">
+        <v>0.409999996423721</v>
+      </c>
+      <c r="E2751" t="n">
+        <v>0.361999988555908</v>
+      </c>
+      <c r="F2751" t="n">
+        <v>0.409999996423721</v>
+      </c>
+      <c r="G2751" t="n">
+        <v>0.409999996423721</v>
+      </c>
+      <c r="H2751" t="n">
+        <v>3149</v>
+      </c>
+      <c r="I2751" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ZUC.MI.xlsx
+++ b/data/ZUC.MI.xlsx
@@ -456,7 +456,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G3" t="n">
-        <v>3.07884788513184</v>
+        <v>3.07884764671326</v>
       </c>
       <c r="H3" t="n">
         <v>28114</v>
@@ -485,7 +485,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G4" t="n">
-        <v>2.96163249015808</v>
+        <v>2.96163272857666</v>
       </c>
       <c r="H4" t="n">
         <v>12680</v>
@@ -514,7 +514,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G5" t="n">
-        <v>2.85223174095154</v>
+        <v>2.8522322177887</v>
       </c>
       <c r="H5" t="n">
         <v>41852</v>
@@ -601,7 +601,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G8" t="n">
-        <v>2.85223174095154</v>
+        <v>2.8522322177887</v>
       </c>
       <c r="H8" t="n">
         <v>11271</v>
@@ -630,7 +630,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G9" t="n">
-        <v>2.85223174095154</v>
+        <v>2.8522322177887</v>
       </c>
       <c r="H9" t="n">
         <v>22577</v>
@@ -688,7 +688,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G11" t="n">
-        <v>2.77408885955811</v>
+        <v>2.77408862113953</v>
       </c>
       <c r="H11" t="n">
         <v>14530</v>
@@ -717,7 +717,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G12" t="n">
-        <v>2.6256160736084</v>
+        <v>2.62561655044556</v>
       </c>
       <c r="H12" t="n">
         <v>16207</v>
@@ -804,7 +804,7 @@
         <v>3</v>
       </c>
       <c r="G15" t="n">
-        <v>2.34430027008057</v>
+        <v>2.34430003166199</v>
       </c>
       <c r="H15" t="n">
         <v>26367</v>
@@ -833,7 +833,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G16" t="n">
-        <v>2.39118623733521</v>
+        <v>2.39118599891663</v>
       </c>
       <c r="H16" t="n">
         <v>21477</v>
@@ -920,7 +920,7 @@
         <v>3</v>
       </c>
       <c r="G19" t="n">
-        <v>2.34430027008057</v>
+        <v>2.34430003166199</v>
       </c>
       <c r="H19" t="n">
         <v>7546</v>
@@ -978,7 +978,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G21" t="n">
-        <v>2.32867169380188</v>
+        <v>2.3286714553833</v>
       </c>
       <c r="H21" t="n">
         <v>6070</v>
@@ -1007,7 +1007,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G22" t="n">
-        <v>2.30522871017456</v>
+        <v>2.30522847175598</v>
       </c>
       <c r="H22" t="n">
         <v>7688</v>
@@ -1094,7 +1094,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G25" t="n">
-        <v>1.78948247432709</v>
+        <v>1.78948259353638</v>
       </c>
       <c r="H25" t="n">
         <v>29015</v>
@@ -1210,7 +1210,7 @@
         <v>1</v>
       </c>
       <c r="G29" t="n">
-        <v>0.781433463096619</v>
+        <v>0.781433403491974</v>
       </c>
       <c r="H29" t="n">
         <v>16056</v>
@@ -1239,7 +1239,7 @@
         <v>1.5</v>
       </c>
       <c r="G30" t="n">
-        <v>1.17215013504028</v>
+        <v>1.17215001583099</v>
       </c>
       <c r="H30" t="n">
         <v>11792</v>
@@ -1268,7 +1268,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G31" t="n">
-        <v>1.71915376186371</v>
+        <v>1.71915352344513</v>
       </c>
       <c r="H31" t="n">
         <v>23390</v>
@@ -1297,7 +1297,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G32" t="n">
-        <v>1.64101016521454</v>
+        <v>1.64101004600525</v>
       </c>
       <c r="H32" t="n">
         <v>80086</v>
@@ -1326,7 +1326,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G33" t="n">
-        <v>1.99265515804291</v>
+        <v>1.9926552772522</v>
       </c>
       <c r="H33" t="n">
         <v>23570</v>
@@ -1355,7 +1355,7 @@
         <v>3</v>
       </c>
       <c r="G34" t="n">
-        <v>2.34430027008057</v>
+        <v>2.34430003166199</v>
       </c>
       <c r="H34" t="n">
         <v>65915</v>
@@ -1413,7 +1413,7 @@
         <v>3</v>
       </c>
       <c r="G36" t="n">
-        <v>2.34430027008057</v>
+        <v>2.34430003166199</v>
       </c>
       <c r="H36" t="n">
         <v>20892</v>
@@ -1442,7 +1442,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G37" t="n">
-        <v>2.7115740776062</v>
+        <v>2.71157383918762</v>
       </c>
       <c r="H37" t="n">
         <v>25045</v>
@@ -1471,7 +1471,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G38" t="n">
-        <v>2.63343048095703</v>
+        <v>2.63343024253845</v>
       </c>
       <c r="H38" t="n">
         <v>44345</v>
@@ -1529,7 +1529,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G40" t="n">
-        <v>2.37555742263794</v>
+        <v>2.37555766105652</v>
       </c>
       <c r="H40" t="n">
         <v>26653</v>
@@ -1558,7 +1558,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G41" t="n">
-        <v>2.51621556282043</v>
+        <v>2.51621580123901</v>
       </c>
       <c r="H41" t="n">
         <v>12434</v>
@@ -1587,7 +1587,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G42" t="n">
-        <v>2.45370101928711</v>
+        <v>2.45370078086853</v>
       </c>
       <c r="H42" t="n">
         <v>6497</v>
@@ -1674,7 +1674,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G45" t="n">
-        <v>2.77408885955811</v>
+        <v>2.77408862113953</v>
       </c>
       <c r="H45" t="n">
         <v>276654</v>
@@ -1703,7 +1703,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G46" t="n">
-        <v>2.74283123016357</v>
+        <v>2.742830991745</v>
       </c>
       <c r="H46" t="n">
         <v>30985</v>
@@ -1790,7 +1790,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G49" t="n">
-        <v>2.57091569900513</v>
+        <v>2.57091593742371</v>
       </c>
       <c r="H49" t="n">
         <v>6727</v>
@@ -1906,7 +1906,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G53" t="n">
-        <v>2.43807220458984</v>
+        <v>2.43807196617126</v>
       </c>
       <c r="H53" t="n">
         <v>8203</v>
@@ -2051,7 +2051,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G58" t="n">
-        <v>2.27397131919861</v>
+        <v>2.27397155761719</v>
       </c>
       <c r="H58" t="n">
         <v>5139</v>
@@ -2080,7 +2080,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G59" t="n">
-        <v>2.22708511352539</v>
+        <v>2.22708535194397</v>
       </c>
       <c r="H59" t="n">
         <v>10942</v>
@@ -2167,7 +2167,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G62" t="n">
-        <v>2.0551700592041</v>
+        <v>2.05516982078552</v>
       </c>
       <c r="H62" t="n">
         <v>7073</v>
@@ -2254,7 +2254,7 @@
         <v>2.5</v>
       </c>
       <c r="G65" t="n">
-        <v>1.95358335971832</v>
+        <v>1.9535835981369</v>
       </c>
       <c r="H65" t="n">
         <v>4420</v>
@@ -2283,7 +2283,7 @@
         <v>2.5</v>
       </c>
       <c r="G66" t="n">
-        <v>1.95358335971832</v>
+        <v>1.9535835981369</v>
       </c>
       <c r="H66" t="n">
         <v>8536</v>
@@ -2312,7 +2312,7 @@
         <v>2.5</v>
       </c>
       <c r="G67" t="n">
-        <v>1.95358335971832</v>
+        <v>1.9535835981369</v>
       </c>
       <c r="H67" t="n">
         <v>400</v>
@@ -2341,7 +2341,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G68" t="n">
-        <v>1.86762595176697</v>
+        <v>1.86762571334839</v>
       </c>
       <c r="H68" t="n">
         <v>5688</v>
@@ -2370,7 +2370,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G69" t="n">
-        <v>1.83636832237244</v>
+        <v>1.83636844158173</v>
       </c>
       <c r="H69" t="n">
         <v>7190</v>
@@ -2428,7 +2428,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G71" t="n">
-        <v>1.8129255771637</v>
+        <v>1.81292545795441</v>
       </c>
       <c r="H71" t="n">
         <v>7528</v>
@@ -2457,7 +2457,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G72" t="n">
-        <v>1.80511105060577</v>
+        <v>1.80511116981506</v>
       </c>
       <c r="H72" t="n">
         <v>6071</v>
@@ -2486,7 +2486,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G73" t="n">
-        <v>1.94576930999756</v>
+        <v>1.94576907157898</v>
       </c>
       <c r="H73" t="n">
         <v>30047</v>
@@ -2515,7 +2515,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G74" t="n">
-        <v>1.91451179981232</v>
+        <v>1.91451191902161</v>
       </c>
       <c r="H74" t="n">
         <v>27553</v>
@@ -2544,7 +2544,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G75" t="n">
-        <v>1.84418284893036</v>
+        <v>1.84418272972107</v>
       </c>
       <c r="H75" t="n">
         <v>12321</v>
@@ -2573,7 +2573,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G76" t="n">
-        <v>1.87544012069702</v>
+        <v>1.87544023990631</v>
       </c>
       <c r="H76" t="n">
         <v>16625</v>
@@ -2602,7 +2602,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G77" t="n">
-        <v>1.80511105060577</v>
+        <v>1.80511116981506</v>
       </c>
       <c r="H77" t="n">
         <v>15224</v>
@@ -2631,7 +2631,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G78" t="n">
-        <v>1.7738538980484</v>
+        <v>1.77385365962982</v>
       </c>
       <c r="H78" t="n">
         <v>12767</v>
@@ -2660,7 +2660,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G79" t="n">
-        <v>1.75041079521179</v>
+        <v>1.75041091442108</v>
       </c>
       <c r="H79" t="n">
         <v>18881</v>
@@ -2689,7 +2689,7 @@
         <v>2.25</v>
       </c>
       <c r="G80" t="n">
-        <v>1.75822496414185</v>
+        <v>1.75822520256042</v>
       </c>
       <c r="H80" t="n">
         <v>4825</v>
@@ -2718,7 +2718,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G81" t="n">
-        <v>1.75041079521179</v>
+        <v>1.75041091442108</v>
       </c>
       <c r="H81" t="n">
         <v>11995</v>
@@ -2747,7 +2747,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G82" t="n">
-        <v>1.85981154441833</v>
+        <v>1.85981166362762</v>
       </c>
       <c r="H82" t="n">
         <v>17718</v>
@@ -2776,7 +2776,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G83" t="n">
-        <v>1.85981154441833</v>
+        <v>1.85981166362762</v>
       </c>
       <c r="H83" t="n">
         <v>1959</v>
@@ -2805,7 +2805,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G84" t="n">
-        <v>1.85981154441833</v>
+        <v>1.85981166362762</v>
       </c>
       <c r="H84" t="n">
         <v>1535</v>
@@ -2834,7 +2834,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G85" t="n">
-        <v>1.83636832237244</v>
+        <v>1.83636844158173</v>
       </c>
       <c r="H85" t="n">
         <v>1560</v>
@@ -2950,7 +2950,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G89" t="n">
-        <v>1.78948247432709</v>
+        <v>1.78948259353638</v>
       </c>
       <c r="H89" t="n">
         <v>13120</v>
@@ -2979,7 +2979,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G90" t="n">
-        <v>1.70352494716644</v>
+        <v>1.70352482795715</v>
       </c>
       <c r="H90" t="n">
         <v>5489</v>
@@ -3008,7 +3008,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G91" t="n">
-        <v>1.71915376186371</v>
+        <v>1.71915352344513</v>
       </c>
       <c r="H91" t="n">
         <v>12134</v>
@@ -3037,7 +3037,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G92" t="n">
-        <v>1.63319575786591</v>
+        <v>1.6331958770752</v>
       </c>
       <c r="H92" t="n">
         <v>15187</v>
@@ -3066,7 +3066,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G93" t="n">
-        <v>1.70352494716644</v>
+        <v>1.70352482795715</v>
       </c>
       <c r="H93" t="n">
         <v>5250</v>
@@ -3095,7 +3095,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G94" t="n">
-        <v>1.69571042060852</v>
+        <v>1.69571053981781</v>
       </c>
       <c r="H94" t="n">
         <v>7592</v>
@@ -3124,7 +3124,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G95" t="n">
-        <v>1.71915376186371</v>
+        <v>1.71915352344513</v>
       </c>
       <c r="H95" t="n">
         <v>1431</v>
@@ -3153,7 +3153,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G96" t="n">
-        <v>1.64882445335388</v>
+        <v>1.64882433414459</v>
       </c>
       <c r="H96" t="n">
         <v>2615</v>
@@ -3182,7 +3182,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G97" t="n">
-        <v>1.71915376186371</v>
+        <v>1.71915352344513</v>
       </c>
       <c r="H97" t="n">
         <v>10382</v>
@@ -3385,7 +3385,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G104" t="n">
-        <v>1.93795490264893</v>
+        <v>1.93795502185822</v>
       </c>
       <c r="H104" t="n">
         <v>28640</v>
@@ -3414,7 +3414,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G105" t="n">
-        <v>1.88325452804565</v>
+        <v>1.88325476646423</v>
       </c>
       <c r="H105" t="n">
         <v>30798</v>
@@ -3472,7 +3472,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G107" t="n">
-        <v>1.74259638786316</v>
+        <v>1.74259650707245</v>
       </c>
       <c r="H107" t="n">
         <v>29505</v>
@@ -3501,7 +3501,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G108" t="n">
-        <v>1.71915376186371</v>
+        <v>1.71915352344513</v>
       </c>
       <c r="H108" t="n">
         <v>19258</v>
@@ -3530,7 +3530,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G109" t="n">
-        <v>1.71133947372437</v>
+        <v>1.71133923530579</v>
       </c>
       <c r="H109" t="n">
         <v>13938</v>
@@ -3559,7 +3559,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G110" t="n">
-        <v>1.71915376186371</v>
+        <v>1.71915352344513</v>
       </c>
       <c r="H110" t="n">
         <v>31434</v>
@@ -3588,7 +3588,7 @@
         <v>2.25</v>
       </c>
       <c r="G111" t="n">
-        <v>1.75822496414185</v>
+        <v>1.75822520256042</v>
       </c>
       <c r="H111" t="n">
         <v>12997</v>
@@ -3617,7 +3617,7 @@
         <v>2.25</v>
       </c>
       <c r="G112" t="n">
-        <v>1.75822496414185</v>
+        <v>1.75822520256042</v>
       </c>
       <c r="H112" t="n">
         <v>6892</v>
@@ -3646,7 +3646,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G113" t="n">
-        <v>1.69571042060852</v>
+        <v>1.69571053981781</v>
       </c>
       <c r="H113" t="n">
         <v>7676</v>
@@ -3675,7 +3675,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G114" t="n">
-        <v>1.64882445335388</v>
+        <v>1.64882433414459</v>
       </c>
       <c r="H114" t="n">
         <v>16400</v>
@@ -3704,7 +3704,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G115" t="n">
-        <v>1.58630967140198</v>
+        <v>1.58630979061127</v>
       </c>
       <c r="H115" t="n">
         <v>15973</v>
@@ -3733,7 +3733,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G116" t="n">
-        <v>1.60193836688995</v>
+        <v>1.60193848609924</v>
       </c>
       <c r="H116" t="n">
         <v>15987</v>
@@ -3820,7 +3820,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G119" t="n">
-        <v>1.64101016521454</v>
+        <v>1.64101004600525</v>
       </c>
       <c r="H119" t="n">
         <v>7103</v>
@@ -3849,7 +3849,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G120" t="n">
-        <v>1.57849550247192</v>
+        <v>1.57849562168121</v>
       </c>
       <c r="H120" t="n">
         <v>26546</v>
@@ -3878,7 +3878,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G121" t="n">
-        <v>1.57849550247192</v>
+        <v>1.57849562168121</v>
       </c>
       <c r="H121" t="n">
         <v>5793</v>
@@ -3907,7 +3907,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G122" t="n">
-        <v>1.57849550247192</v>
+        <v>1.57849562168121</v>
       </c>
       <c r="H122" t="n">
         <v>255</v>
@@ -3936,7 +3936,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G123" t="n">
-        <v>1.57849550247192</v>
+        <v>1.57849562168121</v>
       </c>
       <c r="H123" t="n">
         <v>12438</v>
@@ -4139,7 +4139,7 @@
         <v>2.25</v>
       </c>
       <c r="G130" t="n">
-        <v>1.75822496414185</v>
+        <v>1.75822520256042</v>
       </c>
       <c r="H130" t="n">
         <v>83797</v>
@@ -4197,7 +4197,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G132" t="n">
-        <v>1.32843685150146</v>
+        <v>1.32843673229218</v>
       </c>
       <c r="H132" t="n">
         <v>54470</v>
@@ -4255,7 +4255,7 @@
         <v>1.75</v>
       </c>
       <c r="G134" t="n">
-        <v>1.36750853061676</v>
+        <v>1.36750841140747</v>
       </c>
       <c r="H134" t="n">
         <v>31791</v>
@@ -4313,7 +4313,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G136" t="n">
-        <v>1.4143944978714</v>
+        <v>1.41439437866211</v>
       </c>
       <c r="H136" t="n">
         <v>17202</v>
@@ -4371,7 +4371,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G138" t="n">
-        <v>1.4143944978714</v>
+        <v>1.41439437866211</v>
       </c>
       <c r="H138" t="n">
         <v>9467</v>
@@ -4429,7 +4429,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G140" t="n">
-        <v>1.4143944978714</v>
+        <v>1.41439437866211</v>
       </c>
       <c r="H140" t="n">
         <v>22023</v>
@@ -4458,7 +4458,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G141" t="n">
-        <v>1.47690904140472</v>
+        <v>1.47690916061401</v>
       </c>
       <c r="H141" t="n">
         <v>16351</v>
@@ -4603,7 +4603,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G146" t="n">
-        <v>1.43002307415009</v>
+        <v>1.43002319335938</v>
       </c>
       <c r="H146" t="n">
         <v>5668</v>
@@ -4661,7 +4661,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G148" t="n">
-        <v>1.43002307415009</v>
+        <v>1.43002319335938</v>
       </c>
       <c r="H148" t="n">
         <v>3047</v>
@@ -4719,7 +4719,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G150" t="n">
-        <v>1.43002307415009</v>
+        <v>1.43002319335938</v>
       </c>
       <c r="H150" t="n">
         <v>3668</v>
@@ -4748,7 +4748,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G151" t="n">
-        <v>1.43002307415009</v>
+        <v>1.43002319335938</v>
       </c>
       <c r="H151" t="n">
         <v>20454</v>
@@ -4864,7 +4864,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G155" t="n">
-        <v>1.50035226345062</v>
+        <v>1.50035202503204</v>
       </c>
       <c r="H155" t="n">
         <v>11333</v>
@@ -4893,7 +4893,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G156" t="n">
-        <v>1.49253797531128</v>
+        <v>1.4925377368927</v>
       </c>
       <c r="H156" t="n">
         <v>5721</v>
@@ -4951,7 +4951,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G158" t="n">
-        <v>1.50035226345062</v>
+        <v>1.50035202503204</v>
       </c>
       <c r="H158" t="n">
         <v>230</v>
@@ -5038,7 +5038,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G161" t="n">
-        <v>1.47690904140472</v>
+        <v>1.47690916061401</v>
       </c>
       <c r="H161" t="n">
         <v>4796</v>
@@ -5270,7 +5270,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G169" t="n">
-        <v>1.47690904140472</v>
+        <v>1.47690916061401</v>
       </c>
       <c r="H169" t="n">
         <v>12338</v>
@@ -5328,7 +5328,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G171" t="n">
-        <v>1.47690904140472</v>
+        <v>1.47690916061401</v>
       </c>
       <c r="H171" t="n">
         <v>7601</v>
@@ -5357,7 +5357,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G172" t="n">
-        <v>1.47690904140472</v>
+        <v>1.47690916061401</v>
       </c>
       <c r="H172" t="n">
         <v>2406</v>
@@ -5444,7 +5444,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G175" t="n">
-        <v>1.49253797531128</v>
+        <v>1.4925377368927</v>
       </c>
       <c r="H175" t="n">
         <v>8883</v>
@@ -5531,7 +5531,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G178" t="n">
-        <v>1.49253797531128</v>
+        <v>1.4925377368927</v>
       </c>
       <c r="H178" t="n">
         <v>7365</v>
@@ -5647,7 +5647,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G182" t="n">
-        <v>1.47690904140472</v>
+        <v>1.47690916061401</v>
       </c>
       <c r="H182" t="n">
         <v>1510</v>
@@ -5676,7 +5676,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G183" t="n">
-        <v>1.4143944978714</v>
+        <v>1.41439437866211</v>
       </c>
       <c r="H183" t="n">
         <v>13615</v>
@@ -5734,7 +5734,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G185" t="n">
-        <v>1.43783736228943</v>
+        <v>1.43783748149872</v>
       </c>
       <c r="H185" t="n">
         <v>3980</v>
@@ -5792,7 +5792,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G187" t="n">
-        <v>1.6097526550293</v>
+        <v>1.60975277423859</v>
       </c>
       <c r="H187" t="n">
         <v>206627</v>
@@ -5821,7 +5821,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G188" t="n">
-        <v>1.66445326805115</v>
+        <v>1.66445314884186</v>
       </c>
       <c r="H188" t="n">
         <v>64466</v>
@@ -6227,7 +6227,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G202" t="n">
-        <v>1.47690904140472</v>
+        <v>1.47690916061401</v>
       </c>
       <c r="H202" t="n">
         <v>7610</v>
@@ -6285,7 +6285,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G204" t="n">
-        <v>1.531609416008</v>
+        <v>1.53160953521729</v>
       </c>
       <c r="H204" t="n">
         <v>8646</v>
@@ -6488,7 +6488,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G211" t="n">
-        <v>1.53942394256592</v>
+        <v>1.53942382335663</v>
       </c>
       <c r="H211" t="n">
         <v>2400</v>
@@ -6604,7 +6604,7 @@
         <v>2</v>
       </c>
       <c r="G215" t="n">
-        <v>1.56286692619324</v>
+        <v>1.56286680698395</v>
       </c>
       <c r="H215" t="n">
         <v>7270</v>
@@ -6720,7 +6720,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G219" t="n">
-        <v>1.531609416008</v>
+        <v>1.53160953521729</v>
       </c>
       <c r="H219" t="n">
         <v>16116</v>
@@ -6778,7 +6778,7 @@
         <v>2</v>
       </c>
       <c r="G221" t="n">
-        <v>1.56286692619324</v>
+        <v>1.56286680698395</v>
       </c>
       <c r="H221" t="n">
         <v>25291</v>
@@ -6836,7 +6836,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G223" t="n">
-        <v>1.57849550247192</v>
+        <v>1.57849562168121</v>
       </c>
       <c r="H223" t="n">
         <v>95323</v>
@@ -6894,7 +6894,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G225" t="n">
-        <v>1.58630967140198</v>
+        <v>1.58630979061127</v>
       </c>
       <c r="H225" t="n">
         <v>24397</v>
@@ -6923,7 +6923,7 @@
         <v>2</v>
       </c>
       <c r="G226" t="n">
-        <v>1.56286692619324</v>
+        <v>1.56286680698395</v>
       </c>
       <c r="H226" t="n">
         <v>13694</v>
@@ -6952,7 +6952,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G227" t="n">
-        <v>1.53942394256592</v>
+        <v>1.53942382335663</v>
       </c>
       <c r="H227" t="n">
         <v>13085</v>
@@ -6981,7 +6981,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G228" t="n">
-        <v>1.53942394256592</v>
+        <v>1.53942382335663</v>
       </c>
       <c r="H228" t="n">
         <v>7625</v>
@@ -7039,7 +7039,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G230" t="n">
-        <v>1.49253797531128</v>
+        <v>1.4925377368927</v>
       </c>
       <c r="H230" t="n">
         <v>3975</v>
@@ -7155,7 +7155,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G234" t="n">
-        <v>1.4143944978714</v>
+        <v>1.41439437866211</v>
       </c>
       <c r="H234" t="n">
         <v>15984</v>
@@ -7184,7 +7184,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G235" t="n">
-        <v>1.43002307415009</v>
+        <v>1.43002319335938</v>
       </c>
       <c r="H235" t="n">
         <v>7002</v>
@@ -7242,7 +7242,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G237" t="n">
-        <v>1.47690904140472</v>
+        <v>1.47690916061401</v>
       </c>
       <c r="H237" t="n">
         <v>3415</v>
@@ -7271,7 +7271,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G238" t="n">
-        <v>1.43783736228943</v>
+        <v>1.43783748149872</v>
       </c>
       <c r="H238" t="n">
         <v>1692</v>
@@ -7416,7 +7416,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G243" t="n">
-        <v>1.50035226345062</v>
+        <v>1.50035202503204</v>
       </c>
       <c r="H243" t="n">
         <v>2774</v>
@@ -7445,7 +7445,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G244" t="n">
-        <v>1.50035226345062</v>
+        <v>1.50035202503204</v>
       </c>
       <c r="H244" t="n">
         <v>2142</v>
@@ -7474,7 +7474,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G245" t="n">
-        <v>1.49253797531128</v>
+        <v>1.4925377368927</v>
       </c>
       <c r="H245" t="n">
         <v>6756</v>
@@ -7503,7 +7503,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G246" t="n">
-        <v>1.50035226345062</v>
+        <v>1.50035202503204</v>
       </c>
       <c r="H246" t="n">
         <v>6837</v>
@@ -7532,7 +7532,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G247" t="n">
-        <v>1.50035226345062</v>
+        <v>1.50035202503204</v>
       </c>
       <c r="H247" t="n">
         <v>9596</v>
@@ -7561,7 +7561,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G248" t="n">
-        <v>1.50035226345062</v>
+        <v>1.50035202503204</v>
       </c>
       <c r="H248" t="n">
         <v>3796</v>
@@ -7619,7 +7619,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G250" t="n">
-        <v>1.50035226345062</v>
+        <v>1.50035202503204</v>
       </c>
       <c r="H250" t="n">
         <v>16130</v>
@@ -7677,7 +7677,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G252" t="n">
-        <v>1.49253797531128</v>
+        <v>1.4925377368927</v>
       </c>
       <c r="H252" t="n">
         <v>8020</v>
@@ -7706,7 +7706,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G253" t="n">
-        <v>1.47690904140472</v>
+        <v>1.47690916061401</v>
       </c>
       <c r="H253" t="n">
         <v>5630</v>
@@ -7735,7 +7735,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G254" t="n">
-        <v>1.50035226345062</v>
+        <v>1.50035202503204</v>
       </c>
       <c r="H254" t="n">
         <v>10860</v>
@@ -7764,7 +7764,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G255" t="n">
-        <v>1.49253797531128</v>
+        <v>1.4925377368927</v>
       </c>
       <c r="H255" t="n">
         <v>45713</v>
@@ -7793,7 +7793,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G256" t="n">
-        <v>1.53942394256592</v>
+        <v>1.53942382335663</v>
       </c>
       <c r="H256" t="n">
         <v>12280</v>
@@ -7851,7 +7851,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G258" t="n">
-        <v>1.83636832237244</v>
+        <v>1.83636844158173</v>
       </c>
       <c r="H258" t="n">
         <v>125566</v>
@@ -7880,7 +7880,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G259" t="n">
-        <v>1.7738538980484</v>
+        <v>1.77385365962982</v>
       </c>
       <c r="H259" t="n">
         <v>144770</v>
@@ -7909,7 +7909,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G260" t="n">
-        <v>1.76603937149048</v>
+        <v>1.76603949069977</v>
       </c>
       <c r="H260" t="n">
         <v>45306</v>
@@ -7967,7 +7967,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G262" t="n">
-        <v>1.72696805000305</v>
+        <v>1.72696781158447</v>
       </c>
       <c r="H262" t="n">
         <v>17933</v>
@@ -8025,7 +8025,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G264" t="n">
-        <v>1.64882445335388</v>
+        <v>1.64882433414459</v>
       </c>
       <c r="H264" t="n">
         <v>11388</v>
@@ -8054,7 +8054,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G265" t="n">
-        <v>1.63319575786591</v>
+        <v>1.6331958770752</v>
       </c>
       <c r="H265" t="n">
         <v>33628</v>
@@ -8083,7 +8083,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G266" t="n">
-        <v>1.60193836688995</v>
+        <v>1.60193848609924</v>
       </c>
       <c r="H266" t="n">
         <v>12204</v>
@@ -8112,7 +8112,7 @@
         <v>2.25</v>
       </c>
       <c r="G267" t="n">
-        <v>1.75822496414185</v>
+        <v>1.75822520256042</v>
       </c>
       <c r="H267" t="n">
         <v>48617</v>
@@ -8141,7 +8141,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G268" t="n">
-        <v>1.71133947372437</v>
+        <v>1.71133923530579</v>
       </c>
       <c r="H268" t="n">
         <v>79014</v>
@@ -8170,7 +8170,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G269" t="n">
-        <v>1.66445326805115</v>
+        <v>1.66445314884186</v>
       </c>
       <c r="H269" t="n">
         <v>20304</v>
@@ -8199,7 +8199,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G270" t="n">
-        <v>1.64101016521454</v>
+        <v>1.64101004600525</v>
       </c>
       <c r="H270" t="n">
         <v>10671</v>
@@ -8228,7 +8228,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G271" t="n">
-        <v>1.79729664325714</v>
+        <v>1.79729676246643</v>
       </c>
       <c r="H271" t="n">
         <v>110444</v>
@@ -8402,7 +8402,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G277" t="n">
-        <v>2.31304311752319</v>
+        <v>2.31304287910461</v>
       </c>
       <c r="H277" t="n">
         <v>178115</v>
@@ -8431,7 +8431,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G278" t="n">
-        <v>2.36774325370789</v>
+        <v>2.36774349212646</v>
       </c>
       <c r="H278" t="n">
         <v>155933</v>
@@ -8460,7 +8460,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G279" t="n">
-        <v>2.32085728645325</v>
+        <v>2.32085752487183</v>
       </c>
       <c r="H279" t="n">
         <v>23589</v>
@@ -8489,7 +8489,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G280" t="n">
-        <v>2.36774325370789</v>
+        <v>2.36774349212646</v>
       </c>
       <c r="H280" t="n">
         <v>42641</v>
@@ -8547,7 +8547,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G282" t="n">
-        <v>2.66468787193298</v>
+        <v>2.66468811035156</v>
       </c>
       <c r="H282" t="n">
         <v>180543</v>
@@ -8663,7 +8663,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G286" t="n">
-        <v>2.63343048095703</v>
+        <v>2.63343024253845</v>
       </c>
       <c r="H286" t="n">
         <v>258644</v>
@@ -8808,7 +8808,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G291" t="n">
-        <v>2.45370101928711</v>
+        <v>2.45370078086853</v>
       </c>
       <c r="H291" t="n">
         <v>62585</v>
@@ -8866,7 +8866,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G293" t="n">
-        <v>2.30522871017456</v>
+        <v>2.30522847175598</v>
       </c>
       <c r="H293" t="n">
         <v>63123</v>
@@ -8953,7 +8953,7 @@
         <v>2.75</v>
       </c>
       <c r="G296" t="n">
-        <v>2.14894199371338</v>
+        <v>2.1489417552948</v>
       </c>
       <c r="H296" t="n">
         <v>145249</v>
@@ -9011,7 +9011,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G298" t="n">
-        <v>2.10205602645874</v>
+        <v>2.10205578804016</v>
       </c>
       <c r="H298" t="n">
         <v>89125</v>
@@ -9040,7 +9040,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G299" t="n">
-        <v>2.18801331520081</v>
+        <v>2.18801379203796</v>
       </c>
       <c r="H299" t="n">
         <v>145545</v>
@@ -9098,7 +9098,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G301" t="n">
-        <v>2.11768484115601</v>
+        <v>2.11768460273743</v>
       </c>
       <c r="H301" t="n">
         <v>31779</v>
@@ -9127,7 +9127,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G302" t="n">
-        <v>2.10987043380737</v>
+        <v>2.10987019538879</v>
       </c>
       <c r="H302" t="n">
         <v>17255</v>
@@ -9156,7 +9156,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G303" t="n">
-        <v>2.10205602645874</v>
+        <v>2.10205578804016</v>
       </c>
       <c r="H303" t="n">
         <v>8034</v>
@@ -9243,7 +9243,7 @@
         <v>2.75</v>
       </c>
       <c r="G306" t="n">
-        <v>2.14894199371338</v>
+        <v>2.1489417552948</v>
       </c>
       <c r="H306" t="n">
         <v>29862</v>
@@ -9272,7 +9272,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G307" t="n">
-        <v>2.11768484115601</v>
+        <v>2.11768460273743</v>
       </c>
       <c r="H307" t="n">
         <v>94727</v>
@@ -9301,7 +9301,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G308" t="n">
-        <v>2.18801331520081</v>
+        <v>2.18801379203796</v>
       </c>
       <c r="H308" t="n">
         <v>36108</v>
@@ -9359,7 +9359,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G310" t="n">
-        <v>2.11768484115601</v>
+        <v>2.11768460273743</v>
       </c>
       <c r="H310" t="n">
         <v>7325</v>
@@ -9388,7 +9388,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G311" t="n">
-        <v>2.13331341743469</v>
+        <v>2.13331317901611</v>
       </c>
       <c r="H311" t="n">
         <v>20423</v>
@@ -9417,7 +9417,7 @@
         <v>2.75</v>
       </c>
       <c r="G312" t="n">
-        <v>2.14894199371338</v>
+        <v>2.1489417552948</v>
       </c>
       <c r="H312" t="n">
         <v>12417</v>
@@ -9533,7 +9533,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G316" t="n">
-        <v>2.31304311752319</v>
+        <v>2.31304287910461</v>
       </c>
       <c r="H316" t="n">
         <v>166647</v>
@@ -9562,7 +9562,7 @@
         <v>3</v>
       </c>
       <c r="G317" t="n">
-        <v>2.34430027008057</v>
+        <v>2.34430003166199</v>
       </c>
       <c r="H317" t="n">
         <v>64269</v>
@@ -9591,7 +9591,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G318" t="n">
-        <v>2.65687370300293</v>
+        <v>2.65687346458435</v>
       </c>
       <c r="H318" t="n">
         <v>288982</v>
@@ -9678,7 +9678,7 @@
         <v>3</v>
       </c>
       <c r="G321" t="n">
-        <v>2.34430027008057</v>
+        <v>2.34430003166199</v>
       </c>
       <c r="H321" t="n">
         <v>14413</v>
@@ -9707,7 +9707,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G322" t="n">
-        <v>2.32085728645325</v>
+        <v>2.32085752487183</v>
       </c>
       <c r="H322" t="n">
         <v>120703</v>
@@ -9765,7 +9765,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G324" t="n">
-        <v>2.24271368980408</v>
+        <v>2.24271392822266</v>
       </c>
       <c r="H324" t="n">
         <v>19757</v>
@@ -9794,7 +9794,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G325" t="n">
-        <v>2.36774325370789</v>
+        <v>2.36774349212646</v>
       </c>
       <c r="H325" t="n">
         <v>123555</v>
@@ -9823,7 +9823,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G326" t="n">
-        <v>2.32867169380188</v>
+        <v>2.3286714553833</v>
       </c>
       <c r="H326" t="n">
         <v>34122</v>
@@ -9852,7 +9852,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G327" t="n">
-        <v>2.31304311752319</v>
+        <v>2.31304287910461</v>
       </c>
       <c r="H327" t="n">
         <v>15378</v>
@@ -9881,7 +9881,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G328" t="n">
-        <v>2.27397131919861</v>
+        <v>2.27397155761719</v>
       </c>
       <c r="H328" t="n">
         <v>24472</v>
@@ -9910,7 +9910,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G329" t="n">
-        <v>2.27397131919861</v>
+        <v>2.27397155761719</v>
       </c>
       <c r="H329" t="n">
         <v>19303</v>
@@ -9968,7 +9968,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G331" t="n">
-        <v>2.27397131919861</v>
+        <v>2.27397155761719</v>
       </c>
       <c r="H331" t="n">
         <v>11915</v>
@@ -10026,7 +10026,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G333" t="n">
-        <v>2.25834250450134</v>
+        <v>2.25834274291992</v>
       </c>
       <c r="H333" t="n">
         <v>41046</v>
@@ -10055,7 +10055,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G334" t="n">
-        <v>2.30522871017456</v>
+        <v>2.30522847175598</v>
       </c>
       <c r="H334" t="n">
         <v>27597</v>
@@ -10113,7 +10113,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G336" t="n">
-        <v>2.36774325370789</v>
+        <v>2.36774349212646</v>
       </c>
       <c r="H336" t="n">
         <v>60523</v>
@@ -10142,7 +10142,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G337" t="n">
-        <v>2.30522871017456</v>
+        <v>2.30522847175598</v>
       </c>
       <c r="H337" t="n">
         <v>70691</v>
@@ -10171,7 +10171,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G338" t="n">
-        <v>2.31304311752319</v>
+        <v>2.31304287910461</v>
       </c>
       <c r="H338" t="n">
         <v>35872</v>
@@ -10200,7 +10200,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G339" t="n">
-        <v>2.32867169380188</v>
+        <v>2.3286714553833</v>
       </c>
       <c r="H339" t="n">
         <v>58353</v>
@@ -10258,7 +10258,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G341" t="n">
-        <v>2.25834250450134</v>
+        <v>2.25834274291992</v>
       </c>
       <c r="H341" t="n">
         <v>19671</v>
@@ -10287,7 +10287,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G342" t="n">
-        <v>2.25834250450134</v>
+        <v>2.25834274291992</v>
       </c>
       <c r="H342" t="n">
         <v>9250</v>
@@ -10374,7 +10374,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G345" t="n">
-        <v>2.40681505203247</v>
+        <v>2.40681481361389</v>
       </c>
       <c r="H345" t="n">
         <v>126337</v>
@@ -10490,7 +10490,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G349" t="n">
-        <v>2.28959989547729</v>
+        <v>2.28960013389587</v>
       </c>
       <c r="H349" t="n">
         <v>69457</v>
@@ -10519,7 +10519,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G350" t="n">
-        <v>2.33648586273193</v>
+        <v>2.33648610115051</v>
       </c>
       <c r="H350" t="n">
         <v>30279</v>
@@ -10548,7 +10548,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G351" t="n">
-        <v>2.30522871017456</v>
+        <v>2.30522847175598</v>
       </c>
       <c r="H351" t="n">
         <v>10524</v>
@@ -10577,7 +10577,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G352" t="n">
-        <v>2.25834250450134</v>
+        <v>2.25834274291992</v>
       </c>
       <c r="H352" t="n">
         <v>34161</v>
@@ -10635,7 +10635,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G354" t="n">
-        <v>2.27397131919861</v>
+        <v>2.27397155761719</v>
       </c>
       <c r="H354" t="n">
         <v>5260</v>
@@ -10664,7 +10664,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G355" t="n">
-        <v>2.30522871017456</v>
+        <v>2.30522847175598</v>
       </c>
       <c r="H355" t="n">
         <v>6469</v>
@@ -10722,7 +10722,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G357" t="n">
-        <v>2.32867169380188</v>
+        <v>2.3286714553833</v>
       </c>
       <c r="H357" t="n">
         <v>14916</v>
@@ -10751,7 +10751,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G358" t="n">
-        <v>2.37555742263794</v>
+        <v>2.37555766105652</v>
       </c>
       <c r="H358" t="n">
         <v>129387</v>
@@ -10780,7 +10780,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G359" t="n">
-        <v>2.30522871017456</v>
+        <v>2.30522847175598</v>
       </c>
       <c r="H359" t="n">
         <v>21418</v>
@@ -10809,7 +10809,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G360" t="n">
-        <v>2.31304311752319</v>
+        <v>2.31304287910461</v>
       </c>
       <c r="H360" t="n">
         <v>6391</v>
@@ -10838,7 +10838,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G361" t="n">
-        <v>2.30522871017456</v>
+        <v>2.30522847175598</v>
       </c>
       <c r="H361" t="n">
         <v>12853</v>
@@ -10925,7 +10925,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G364" t="n">
-        <v>2.28959989547729</v>
+        <v>2.28960013389587</v>
       </c>
       <c r="H364" t="n">
         <v>9629</v>
@@ -11012,7 +11012,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G367" t="n">
-        <v>2.22708511352539</v>
+        <v>2.22708535194397</v>
       </c>
       <c r="H367" t="n">
         <v>8955</v>
@@ -11041,7 +11041,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G368" t="n">
-        <v>2.22708511352539</v>
+        <v>2.22708535194397</v>
       </c>
       <c r="H368" t="n">
         <v>5899</v>
@@ -11157,7 +11157,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G372" t="n">
-        <v>2.22708511352539</v>
+        <v>2.22708535194397</v>
       </c>
       <c r="H372" t="n">
         <v>12004</v>
@@ -11273,7 +11273,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G376" t="n">
-        <v>2.18801331520081</v>
+        <v>2.18801379203796</v>
       </c>
       <c r="H376" t="n">
         <v>4715</v>
@@ -11302,7 +11302,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G377" t="n">
-        <v>2.22708511352539</v>
+        <v>2.22708535194397</v>
       </c>
       <c r="H377" t="n">
         <v>4658</v>
@@ -11360,7 +11360,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G379" t="n">
-        <v>2.22708511352539</v>
+        <v>2.22708535194397</v>
       </c>
       <c r="H379" t="n">
         <v>7003</v>
@@ -11476,7 +11476,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G383" t="n">
-        <v>2.25834250450134</v>
+        <v>2.25834274291992</v>
       </c>
       <c r="H383" t="n">
         <v>38535</v>
@@ -11563,7 +11563,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G386" t="n">
-        <v>2.25834250450134</v>
+        <v>2.25834274291992</v>
       </c>
       <c r="H386" t="n">
         <v>100</v>
@@ -11592,7 +11592,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G387" t="n">
-        <v>2.24271368980408</v>
+        <v>2.24271392822266</v>
       </c>
       <c r="H387" t="n">
         <v>6947</v>
@@ -11621,7 +11621,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G388" t="n">
-        <v>2.22708511352539</v>
+        <v>2.22708535194397</v>
       </c>
       <c r="H388" t="n">
         <v>100</v>
@@ -11737,7 +11737,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G392" t="n">
-        <v>2.22708511352539</v>
+        <v>2.22708535194397</v>
       </c>
       <c r="H392" t="n">
         <v>4464</v>
@@ -11766,7 +11766,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G393" t="n">
-        <v>2.28959989547729</v>
+        <v>2.28960013389587</v>
       </c>
       <c r="H393" t="n">
         <v>490568</v>
@@ -11795,7 +11795,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G394" t="n">
-        <v>2.25052833557129</v>
+        <v>2.25052809715271</v>
       </c>
       <c r="H394" t="n">
         <v>49928</v>
@@ -11853,7 +11853,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G396" t="n">
-        <v>2.22708511352539</v>
+        <v>2.22708535194397</v>
       </c>
       <c r="H396" t="n">
         <v>21203</v>
@@ -11940,7 +11940,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G399" t="n">
-        <v>2.25834250450134</v>
+        <v>2.25834274291992</v>
       </c>
       <c r="H399" t="n">
         <v>9326</v>
@@ -11969,7 +11969,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G400" t="n">
-        <v>2.25052833557129</v>
+        <v>2.25052809715271</v>
       </c>
       <c r="H400" t="n">
         <v>125043</v>
@@ -11998,7 +11998,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G401" t="n">
-        <v>2.27397131919861</v>
+        <v>2.27397155761719</v>
       </c>
       <c r="H401" t="n">
         <v>8887</v>
@@ -12027,7 +12027,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G402" t="n">
-        <v>2.28178548812866</v>
+        <v>2.28178572654724</v>
       </c>
       <c r="H402" t="n">
         <v>11823</v>
@@ -12056,7 +12056,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G403" t="n">
-        <v>2.28959989547729</v>
+        <v>2.28960013389587</v>
       </c>
       <c r="H403" t="n">
         <v>3440</v>
@@ -12085,7 +12085,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G404" t="n">
-        <v>2.28178548812866</v>
+        <v>2.28178572654724</v>
       </c>
       <c r="H404" t="n">
         <v>4961</v>
@@ -12143,7 +12143,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G406" t="n">
-        <v>2.24271368980408</v>
+        <v>2.24271392822266</v>
       </c>
       <c r="H406" t="n">
         <v>10421</v>
@@ -12201,7 +12201,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G408" t="n">
-        <v>2.28959989547729</v>
+        <v>2.28960013389587</v>
       </c>
       <c r="H408" t="n">
         <v>16796</v>
@@ -12230,7 +12230,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G409" t="n">
-        <v>2.25052833557129</v>
+        <v>2.25052809715271</v>
       </c>
       <c r="H409" t="n">
         <v>3826</v>
@@ -12259,7 +12259,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G410" t="n">
-        <v>2.27397131919861</v>
+        <v>2.27397155761719</v>
       </c>
       <c r="H410" t="n">
         <v>12237</v>
@@ -12317,7 +12317,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G412" t="n">
-        <v>2.25052833557129</v>
+        <v>2.25052809715271</v>
       </c>
       <c r="H412" t="n">
         <v>13597</v>
@@ -12346,7 +12346,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G413" t="n">
-        <v>2.24271368980408</v>
+        <v>2.24271392822266</v>
       </c>
       <c r="H413" t="n">
         <v>8588</v>
@@ -12375,7 +12375,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G414" t="n">
-        <v>2.22708511352539</v>
+        <v>2.22708535194397</v>
       </c>
       <c r="H414" t="n">
         <v>16306</v>
@@ -12404,7 +12404,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G415" t="n">
-        <v>2.22708511352539</v>
+        <v>2.22708535194397</v>
       </c>
       <c r="H415" t="n">
         <v>4789</v>
@@ -12433,7 +12433,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G416" t="n">
-        <v>2.25052833557129</v>
+        <v>2.25052809715271</v>
       </c>
       <c r="H416" t="n">
         <v>4039</v>
@@ -12462,7 +12462,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G417" t="n">
-        <v>2.25834250450134</v>
+        <v>2.25834274291992</v>
       </c>
       <c r="H417" t="n">
         <v>1700</v>
@@ -12491,7 +12491,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G418" t="n">
-        <v>2.27397131919861</v>
+        <v>2.27397155761719</v>
       </c>
       <c r="H418" t="n">
         <v>7095</v>
@@ -12520,7 +12520,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G419" t="n">
-        <v>2.25052833557129</v>
+        <v>2.25052809715271</v>
       </c>
       <c r="H419" t="n">
         <v>6100</v>
@@ -12549,7 +12549,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G420" t="n">
-        <v>2.24271368980408</v>
+        <v>2.24271392822266</v>
       </c>
       <c r="H420" t="n">
         <v>4693</v>
@@ -12578,7 +12578,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G421" t="n">
-        <v>2.25052833557129</v>
+        <v>2.25052809715271</v>
       </c>
       <c r="H421" t="n">
         <v>5308</v>
@@ -12607,7 +12607,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G422" t="n">
-        <v>2.25052833557129</v>
+        <v>2.25052809715271</v>
       </c>
       <c r="H422" t="n">
         <v>13271</v>
@@ -12636,7 +12636,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G423" t="n">
-        <v>2.25834250450134</v>
+        <v>2.25834274291992</v>
       </c>
       <c r="H423" t="n">
         <v>19254</v>
@@ -12665,7 +12665,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G424" t="n">
-        <v>2.25834250450134</v>
+        <v>2.25834274291992</v>
       </c>
       <c r="H424" t="n">
         <v>2892</v>
@@ -12694,7 +12694,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G425" t="n">
-        <v>2.24271368980408</v>
+        <v>2.24271392822266</v>
       </c>
       <c r="H425" t="n">
         <v>22550</v>
@@ -12723,7 +12723,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G426" t="n">
-        <v>2.28959989547729</v>
+        <v>2.28960013389587</v>
       </c>
       <c r="H426" t="n">
         <v>16488</v>
@@ -12752,7 +12752,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G427" t="n">
-        <v>2.28959989547729</v>
+        <v>2.28960013389587</v>
       </c>
       <c r="H427" t="n">
         <v>33109</v>
@@ -12781,7 +12781,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G428" t="n">
-        <v>2.28178548812866</v>
+        <v>2.28178572654724</v>
       </c>
       <c r="H428" t="n">
         <v>8669</v>
@@ -12810,7 +12810,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G429" t="n">
-        <v>2.27397131919861</v>
+        <v>2.27397155761719</v>
       </c>
       <c r="H429" t="n">
         <v>3175</v>
@@ -12868,7 +12868,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G431" t="n">
-        <v>2.27397131919861</v>
+        <v>2.27397155761719</v>
       </c>
       <c r="H431" t="n">
         <v>5595</v>
@@ -12897,7 +12897,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G432" t="n">
-        <v>2.28959989547729</v>
+        <v>2.28960013389587</v>
       </c>
       <c r="H432" t="n">
         <v>7635</v>
@@ -12926,7 +12926,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G433" t="n">
-        <v>2.28959989547729</v>
+        <v>2.28960013389587</v>
       </c>
       <c r="H433" t="n">
         <v>12703</v>
@@ -12955,7 +12955,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G434" t="n">
-        <v>2.30522871017456</v>
+        <v>2.30522847175598</v>
       </c>
       <c r="H434" t="n">
         <v>3559</v>
@@ -12984,7 +12984,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G435" t="n">
-        <v>2.28959989547729</v>
+        <v>2.28960013389587</v>
       </c>
       <c r="H435" t="n">
         <v>6499</v>
@@ -13013,7 +13013,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G436" t="n">
-        <v>2.28178548812866</v>
+        <v>2.28178572654724</v>
       </c>
       <c r="H436" t="n">
         <v>3312</v>
@@ -13042,7 +13042,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G437" t="n">
-        <v>2.27397131919861</v>
+        <v>2.27397155761719</v>
       </c>
       <c r="H437" t="n">
         <v>4699</v>
@@ -13071,7 +13071,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G438" t="n">
-        <v>2.28178548812866</v>
+        <v>2.28178572654724</v>
       </c>
       <c r="H438" t="n">
         <v>17639</v>
@@ -13100,7 +13100,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G439" t="n">
-        <v>2.30522871017456</v>
+        <v>2.30522847175598</v>
       </c>
       <c r="H439" t="n">
         <v>7059</v>
@@ -13158,7 +13158,7 @@
         <v>3</v>
       </c>
       <c r="G441" t="n">
-        <v>2.34430027008057</v>
+        <v>2.34430003166199</v>
       </c>
       <c r="H441" t="n">
         <v>42286</v>
@@ -13187,7 +13187,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G442" t="n">
-        <v>2.33648586273193</v>
+        <v>2.33648610115051</v>
       </c>
       <c r="H442" t="n">
         <v>35567</v>
@@ -13274,7 +13274,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G445" t="n">
-        <v>2.32085728645325</v>
+        <v>2.32085752487183</v>
       </c>
       <c r="H445" t="n">
         <v>109510</v>
@@ -13303,7 +13303,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G446" t="n">
-        <v>2.32867169380188</v>
+        <v>2.3286714553833</v>
       </c>
       <c r="H446" t="n">
         <v>38929</v>
@@ -13332,7 +13332,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G447" t="n">
-        <v>2.28959989547729</v>
+        <v>2.28960013389587</v>
       </c>
       <c r="H447" t="n">
         <v>18719</v>
@@ -13390,7 +13390,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G449" t="n">
-        <v>2.31304311752319</v>
+        <v>2.31304287910461</v>
       </c>
       <c r="H449" t="n">
         <v>8698</v>
@@ -13419,7 +13419,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G450" t="n">
-        <v>2.28959989547729</v>
+        <v>2.28960013389587</v>
       </c>
       <c r="H450" t="n">
         <v>5156</v>
@@ -13448,7 +13448,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G451" t="n">
-        <v>2.28178548812866</v>
+        <v>2.28178572654724</v>
       </c>
       <c r="H451" t="n">
         <v>11688</v>
@@ -13477,7 +13477,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G452" t="n">
-        <v>2.27397131919861</v>
+        <v>2.27397155761719</v>
       </c>
       <c r="H452" t="n">
         <v>4236</v>
@@ -13506,7 +13506,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G453" t="n">
-        <v>2.25834250450134</v>
+        <v>2.25834274291992</v>
       </c>
       <c r="H453" t="n">
         <v>12264</v>
@@ -13535,7 +13535,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G454" t="n">
-        <v>2.25834250450134</v>
+        <v>2.25834274291992</v>
       </c>
       <c r="H454" t="n">
         <v>3217</v>
@@ -13564,7 +13564,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G455" t="n">
-        <v>2.25052833557129</v>
+        <v>2.25052809715271</v>
       </c>
       <c r="H455" t="n">
         <v>4720</v>
@@ -13593,7 +13593,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G456" t="n">
-        <v>2.27397131919861</v>
+        <v>2.27397155761719</v>
       </c>
       <c r="H456" t="n">
         <v>23276</v>
@@ -13680,7 +13680,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G459" t="n">
-        <v>2.27397131919861</v>
+        <v>2.27397155761719</v>
       </c>
       <c r="H459" t="n">
         <v>4372</v>
@@ -13738,7 +13738,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G461" t="n">
-        <v>2.27397131919861</v>
+        <v>2.27397155761719</v>
       </c>
       <c r="H461" t="n">
         <v>2391</v>
@@ -13767,7 +13767,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G462" t="n">
-        <v>2.25834250450134</v>
+        <v>2.25834274291992</v>
       </c>
       <c r="H462" t="n">
         <v>11311</v>
@@ -13796,7 +13796,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G463" t="n">
-        <v>2.27397131919861</v>
+        <v>2.27397155761719</v>
       </c>
       <c r="H463" t="n">
         <v>891</v>
@@ -13825,7 +13825,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G464" t="n">
-        <v>2.25834250450134</v>
+        <v>2.25834274291992</v>
       </c>
       <c r="H464" t="n">
         <v>893</v>
@@ -13854,7 +13854,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G465" t="n">
-        <v>2.25052833557129</v>
+        <v>2.25052809715271</v>
       </c>
       <c r="H465" t="n">
         <v>7854</v>
@@ -13883,7 +13883,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G466" t="n">
-        <v>2.24271368980408</v>
+        <v>2.24271392822266</v>
       </c>
       <c r="H466" t="n">
         <v>8835</v>
@@ -13912,7 +13912,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G467" t="n">
-        <v>2.25052833557129</v>
+        <v>2.25052809715271</v>
       </c>
       <c r="H467" t="n">
         <v>6429</v>
@@ -13941,7 +13941,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G468" t="n">
-        <v>2.24271368980408</v>
+        <v>2.24271392822266</v>
       </c>
       <c r="H468" t="n">
         <v>4382</v>
@@ -13970,7 +13970,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G469" t="n">
-        <v>2.24271368980408</v>
+        <v>2.24271392822266</v>
       </c>
       <c r="H469" t="n">
         <v>5207</v>
@@ -13999,7 +13999,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G470" t="n">
-        <v>2.25052833557129</v>
+        <v>2.25052809715271</v>
       </c>
       <c r="H470" t="n">
         <v>4682</v>
@@ -14028,7 +14028,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G471" t="n">
-        <v>2.25834250450134</v>
+        <v>2.25834274291992</v>
       </c>
       <c r="H471" t="n">
         <v>5598</v>
@@ -14057,7 +14057,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G472" t="n">
-        <v>2.24271368980408</v>
+        <v>2.24271392822266</v>
       </c>
       <c r="H472" t="n">
         <v>5970</v>
@@ -14086,7 +14086,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G473" t="n">
-        <v>2.25834250450134</v>
+        <v>2.25834274291992</v>
       </c>
       <c r="H473" t="n">
         <v>2692</v>
@@ -14115,7 +14115,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G474" t="n">
-        <v>2.28178548812866</v>
+        <v>2.28178572654724</v>
       </c>
       <c r="H474" t="n">
         <v>36315</v>
@@ -14231,7 +14231,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G478" t="n">
-        <v>2.25052833557129</v>
+        <v>2.25052809715271</v>
       </c>
       <c r="H478" t="n">
         <v>13054</v>
@@ -14289,7 +14289,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G480" t="n">
-        <v>2.18801331520081</v>
+        <v>2.18801379203796</v>
       </c>
       <c r="H480" t="n">
         <v>127127</v>
@@ -14318,7 +14318,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G481" t="n">
-        <v>2.11768484115601</v>
+        <v>2.11768460273743</v>
       </c>
       <c r="H481" t="n">
         <v>18942</v>
@@ -14347,7 +14347,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G482" t="n">
-        <v>2.0551700592041</v>
+        <v>2.05516982078552</v>
       </c>
       <c r="H482" t="n">
         <v>33954</v>
@@ -14376,7 +14376,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G483" t="n">
-        <v>2.0551700592041</v>
+        <v>2.05516982078552</v>
       </c>
       <c r="H483" t="n">
         <v>1310</v>
@@ -14492,7 +14492,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G487" t="n">
-        <v>2.0551700592041</v>
+        <v>2.05516982078552</v>
       </c>
       <c r="H487" t="n">
         <v>7884</v>
@@ -14521,7 +14521,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G488" t="n">
-        <v>2.09424138069153</v>
+        <v>2.09424185752869</v>
       </c>
       <c r="H488" t="n">
         <v>6344</v>
@@ -14550,7 +14550,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G489" t="n">
-        <v>2.10205602645874</v>
+        <v>2.10205578804016</v>
       </c>
       <c r="H489" t="n">
         <v>1060</v>
@@ -14608,7 +14608,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G491" t="n">
-        <v>2.0551700592041</v>
+        <v>2.05516982078552</v>
       </c>
       <c r="H491" t="n">
         <v>4461</v>
@@ -14637,7 +14637,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G492" t="n">
-        <v>1.99265515804291</v>
+        <v>1.9926552772522</v>
       </c>
       <c r="H492" t="n">
         <v>39507</v>
@@ -14666,7 +14666,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G493" t="n">
-        <v>2.00828385353088</v>
+        <v>2.0082836151123</v>
       </c>
       <c r="H493" t="n">
         <v>38338</v>
@@ -14695,7 +14695,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G494" t="n">
-        <v>2.02391266822815</v>
+        <v>2.02391242980957</v>
       </c>
       <c r="H494" t="n">
         <v>4454</v>
@@ -14724,7 +14724,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G495" t="n">
-        <v>2.02391266822815</v>
+        <v>2.02391242980957</v>
       </c>
       <c r="H495" t="n">
         <v>1453</v>
@@ -14782,7 +14782,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G497" t="n">
-        <v>1.99265515804291</v>
+        <v>1.9926552772522</v>
       </c>
       <c r="H497" t="n">
         <v>2512</v>
@@ -14869,7 +14869,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G500" t="n">
-        <v>2.00828385353088</v>
+        <v>2.0082836151123</v>
       </c>
       <c r="H500" t="n">
         <v>1488</v>
@@ -14985,7 +14985,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G504" t="n">
-        <v>1.99265515804291</v>
+        <v>1.9926552772522</v>
       </c>
       <c r="H504" t="n">
         <v>3080</v>
@@ -15159,7 +15159,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G510" t="n">
-        <v>2.00828385353088</v>
+        <v>2.0082836151123</v>
       </c>
       <c r="H510" t="n">
         <v>2371</v>
@@ -15246,7 +15246,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G513" t="n">
-        <v>2.00828385353088</v>
+        <v>2.0082836151123</v>
       </c>
       <c r="H513" t="n">
         <v>4130</v>
@@ -15391,7 +15391,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G518" t="n">
-        <v>2.09424138069153</v>
+        <v>2.09424185752869</v>
       </c>
       <c r="H518" t="n">
         <v>112388</v>
@@ -15507,7 +15507,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G522" t="n">
-        <v>2.0551700592041</v>
+        <v>2.05516982078552</v>
       </c>
       <c r="H522" t="n">
         <v>2500</v>
@@ -15565,7 +15565,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G524" t="n">
-        <v>2.10205602645874</v>
+        <v>2.10205578804016</v>
       </c>
       <c r="H524" t="n">
         <v>450</v>
@@ -15594,7 +15594,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G525" t="n">
-        <v>2.0551700592041</v>
+        <v>2.05516982078552</v>
       </c>
       <c r="H525" t="n">
         <v>14380</v>
@@ -15681,7 +15681,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G528" t="n">
-        <v>2.0551700592041</v>
+        <v>2.05516982078552</v>
       </c>
       <c r="H528" t="n">
         <v>4970</v>
@@ -16000,7 +16000,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G539" t="n">
-        <v>1.98484075069427</v>
+        <v>1.98484098911285</v>
       </c>
       <c r="H539" t="n">
         <v>4051</v>
@@ -16058,7 +16058,7 @@
         <v>2.5</v>
       </c>
       <c r="G541" t="n">
-        <v>1.95358335971832</v>
+        <v>1.9535835981369</v>
       </c>
       <c r="H541" t="n">
         <v>1628</v>
@@ -16087,7 +16087,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G542" t="n">
-        <v>1.891068816185</v>
+        <v>1.89106905460358</v>
       </c>
       <c r="H542" t="n">
         <v>4966</v>
@@ -16116,7 +16116,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G543" t="n">
-        <v>1.92232632637024</v>
+        <v>1.92232596874237</v>
       </c>
       <c r="H543" t="n">
         <v>2000</v>
@@ -16145,7 +16145,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G544" t="n">
-        <v>1.891068816185</v>
+        <v>1.89106905460358</v>
       </c>
       <c r="H544" t="n">
         <v>1977</v>
@@ -16174,7 +16174,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G545" t="n">
-        <v>1.98484075069427</v>
+        <v>1.98484098911285</v>
       </c>
       <c r="H545" t="n">
         <v>7157</v>
@@ -16203,7 +16203,7 @@
         <v>2.5</v>
       </c>
       <c r="G546" t="n">
-        <v>1.95358335971832</v>
+        <v>1.9535835981369</v>
       </c>
       <c r="H546" t="n">
         <v>13540</v>
@@ -16232,7 +16232,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G547" t="n">
-        <v>1.96921193599701</v>
+        <v>1.96921241283417</v>
       </c>
       <c r="H547" t="n">
         <v>4409</v>
@@ -16261,7 +16261,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G548" t="n">
-        <v>1.96921193599701</v>
+        <v>1.96921241283417</v>
       </c>
       <c r="H548" t="n">
         <v>2935</v>
@@ -16290,7 +16290,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G549" t="n">
-        <v>1.93795490264893</v>
+        <v>1.93795502185822</v>
       </c>
       <c r="H549" t="n">
         <v>78</v>
@@ -16348,7 +16348,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G551" t="n">
-        <v>2.00828385353088</v>
+        <v>2.0082836151123</v>
       </c>
       <c r="H551" t="n">
         <v>4912</v>
@@ -16377,7 +16377,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G552" t="n">
-        <v>2.02391266822815</v>
+        <v>2.02391242980957</v>
       </c>
       <c r="H552" t="n">
         <v>3342</v>
@@ -16406,7 +16406,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G553" t="n">
-        <v>2.00828385353088</v>
+        <v>2.0082836151123</v>
       </c>
       <c r="H553" t="n">
         <v>3184</v>
@@ -16435,7 +16435,7 @@
         <v>2.5</v>
       </c>
       <c r="G554" t="n">
-        <v>1.95358335971832</v>
+        <v>1.9535835981369</v>
       </c>
       <c r="H554" t="n">
         <v>801</v>
@@ -16464,7 +16464,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G555" t="n">
-        <v>1.87544012069702</v>
+        <v>1.87544023990631</v>
       </c>
       <c r="H555" t="n">
         <v>11021</v>
@@ -16493,7 +16493,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G556" t="n">
-        <v>1.86762595176697</v>
+        <v>1.86762571334839</v>
       </c>
       <c r="H556" t="n">
         <v>3914</v>
@@ -16522,7 +16522,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G557" t="n">
-        <v>1.87544012069702</v>
+        <v>1.87544023990631</v>
       </c>
       <c r="H557" t="n">
         <v>9292</v>
@@ -16551,7 +16551,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G558" t="n">
-        <v>1.88325452804565</v>
+        <v>1.88325476646423</v>
       </c>
       <c r="H558" t="n">
         <v>7999</v>
@@ -16580,7 +16580,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G559" t="n">
-        <v>1.87544012069702</v>
+        <v>1.87544023990631</v>
       </c>
       <c r="H559" t="n">
         <v>2957</v>
@@ -16609,7 +16609,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G560" t="n">
-        <v>1.89888298511505</v>
+        <v>1.89888334274292</v>
       </c>
       <c r="H560" t="n">
         <v>4094</v>
@@ -16638,7 +16638,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G561" t="n">
-        <v>1.89888298511505</v>
+        <v>1.89888334274292</v>
       </c>
       <c r="H561" t="n">
         <v>2899</v>
@@ -16667,7 +16667,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G562" t="n">
-        <v>1.88325452804565</v>
+        <v>1.88325476646423</v>
       </c>
       <c r="H562" t="n">
         <v>12511</v>
@@ -16696,7 +16696,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G563" t="n">
-        <v>1.90669763088226</v>
+        <v>1.90669739246368</v>
       </c>
       <c r="H563" t="n">
         <v>3670</v>
@@ -16725,7 +16725,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G564" t="n">
-        <v>1.90669763088226</v>
+        <v>1.90669739246368</v>
       </c>
       <c r="H564" t="n">
         <v>290</v>
@@ -16754,7 +16754,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G565" t="n">
-        <v>1.91451179981232</v>
+        <v>1.91451191902161</v>
       </c>
       <c r="H565" t="n">
         <v>930</v>
@@ -16783,7 +16783,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G566" t="n">
-        <v>1.87544012069702</v>
+        <v>1.87544023990631</v>
       </c>
       <c r="H566" t="n">
         <v>3211</v>
@@ -16812,7 +16812,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G567" t="n">
-        <v>1.87544012069702</v>
+        <v>1.87544023990631</v>
       </c>
       <c r="H567" t="n">
         <v>2215</v>
@@ -16841,7 +16841,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G568" t="n">
-        <v>1.86762595176697</v>
+        <v>1.86762571334839</v>
       </c>
       <c r="H568" t="n">
         <v>5620</v>
@@ -16870,7 +16870,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G569" t="n">
-        <v>1.84418284893036</v>
+        <v>1.84418272972107</v>
       </c>
       <c r="H569" t="n">
         <v>2584</v>
@@ -16899,7 +16899,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G570" t="n">
-        <v>1.92232632637024</v>
+        <v>1.92232596874237</v>
       </c>
       <c r="H570" t="n">
         <v>34637</v>
@@ -16957,7 +16957,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G572" t="n">
-        <v>2.00828385353088</v>
+        <v>2.0082836151123</v>
       </c>
       <c r="H572" t="n">
         <v>19963</v>
@@ -17131,7 +17131,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G578" t="n">
-        <v>2.0551700592041</v>
+        <v>2.05516982078552</v>
       </c>
       <c r="H578" t="n">
         <v>3757</v>
@@ -17247,7 +17247,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G582" t="n">
-        <v>1.98484075069427</v>
+        <v>1.98484098911285</v>
       </c>
       <c r="H582" t="n">
         <v>5772</v>
@@ -17276,7 +17276,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G583" t="n">
-        <v>1.98484075069427</v>
+        <v>1.98484098911285</v>
       </c>
       <c r="H583" t="n">
         <v>817</v>
@@ -17305,7 +17305,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G584" t="n">
-        <v>1.96139788627625</v>
+        <v>1.96139764785767</v>
       </c>
       <c r="H584" t="n">
         <v>534</v>
@@ -17363,7 +17363,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G586" t="n">
-        <v>2.02391266822815</v>
+        <v>2.02391242980957</v>
       </c>
       <c r="H586" t="n">
         <v>4748</v>
@@ -17392,7 +17392,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G587" t="n">
-        <v>2.00828385353088</v>
+        <v>2.0082836151123</v>
       </c>
       <c r="H587" t="n">
         <v>4400</v>
@@ -17421,7 +17421,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G588" t="n">
-        <v>1.96921193599701</v>
+        <v>1.96921241283417</v>
       </c>
       <c r="H588" t="n">
         <v>1223</v>
@@ -17479,7 +17479,7 @@
         <v>2.5</v>
       </c>
       <c r="G590" t="n">
-        <v>1.95358335971832</v>
+        <v>1.9535835981369</v>
       </c>
       <c r="H590" t="n">
         <v>6559</v>
@@ -17508,7 +17508,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G591" t="n">
-        <v>1.93795490264893</v>
+        <v>1.93795502185822</v>
       </c>
       <c r="H591" t="n">
         <v>11871</v>
@@ -17537,7 +17537,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G592" t="n">
-        <v>1.96921193599701</v>
+        <v>1.96921241283417</v>
       </c>
       <c r="H592" t="n">
         <v>100</v>
@@ -17566,7 +17566,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G593" t="n">
-        <v>1.89888298511505</v>
+        <v>1.89888334274292</v>
       </c>
       <c r="H593" t="n">
         <v>219</v>
@@ -17595,7 +17595,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G594" t="n">
-        <v>1.96921193599701</v>
+        <v>1.96921241283417</v>
       </c>
       <c r="H594" t="n">
         <v>28</v>
@@ -17624,7 +17624,7 @@
         <v>2.5</v>
       </c>
       <c r="G595" t="n">
-        <v>1.95358335971832</v>
+        <v>1.9535835981369</v>
       </c>
       <c r="H595" t="n">
         <v>2570</v>
@@ -17653,7 +17653,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G596" t="n">
-        <v>1.93014049530029</v>
+        <v>1.93014073371887</v>
       </c>
       <c r="H596" t="n">
         <v>321</v>
@@ -17682,7 +17682,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G597" t="n">
-        <v>1.93014049530029</v>
+        <v>1.93014073371887</v>
       </c>
       <c r="H597" t="n">
         <v>1300</v>
@@ -17711,7 +17711,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G598" t="n">
-        <v>1.93795490264893</v>
+        <v>1.93795502185822</v>
       </c>
       <c r="H598" t="n">
         <v>301</v>
@@ -17740,7 +17740,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G599" t="n">
-        <v>1.91451179981232</v>
+        <v>1.91451191902161</v>
       </c>
       <c r="H599" t="n">
         <v>16585</v>
@@ -17769,7 +17769,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G600" t="n">
-        <v>1.94576930999756</v>
+        <v>1.94576907157898</v>
       </c>
       <c r="H600" t="n">
         <v>1103</v>
@@ -17798,7 +17798,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G601" t="n">
-        <v>1.94576930999756</v>
+        <v>1.94576907157898</v>
       </c>
       <c r="H601" t="n">
         <v>200</v>
@@ -17827,7 +17827,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G602" t="n">
-        <v>1.891068816185</v>
+        <v>1.89106905460358</v>
       </c>
       <c r="H602" t="n">
         <v>3186</v>
@@ -17856,7 +17856,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G603" t="n">
-        <v>1.94576930999756</v>
+        <v>1.94576907157898</v>
       </c>
       <c r="H603" t="n">
         <v>7397</v>
@@ -17885,7 +17885,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G604" t="n">
-        <v>1.93795490264893</v>
+        <v>1.93795502185822</v>
       </c>
       <c r="H604" t="n">
         <v>100</v>
@@ -17914,7 +17914,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G605" t="n">
-        <v>1.891068816185</v>
+        <v>1.89106905460358</v>
       </c>
       <c r="H605" t="n">
         <v>12977</v>
@@ -17943,7 +17943,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G606" t="n">
-        <v>1.87544012069702</v>
+        <v>1.87544023990631</v>
       </c>
       <c r="H606" t="n">
         <v>311</v>
@@ -17972,7 +17972,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G607" t="n">
-        <v>1.87544012069702</v>
+        <v>1.87544023990631</v>
       </c>
       <c r="H607" t="n">
         <v>1604</v>
@@ -18001,7 +18001,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G608" t="n">
-        <v>1.87544012069702</v>
+        <v>1.87544023990631</v>
       </c>
       <c r="H608" t="n">
         <v>5380</v>
@@ -18059,7 +18059,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G610" t="n">
-        <v>1.84418284893036</v>
+        <v>1.84418272972107</v>
       </c>
       <c r="H610" t="n">
         <v>4036</v>
@@ -18088,7 +18088,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G611" t="n">
-        <v>1.84418284893036</v>
+        <v>1.84418272972107</v>
       </c>
       <c r="H611" t="n">
         <v>937</v>
@@ -18117,7 +18117,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G612" t="n">
-        <v>1.85981154441833</v>
+        <v>1.85981166362762</v>
       </c>
       <c r="H612" t="n">
         <v>992</v>
@@ -18175,7 +18175,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G614" t="n">
-        <v>1.79729664325714</v>
+        <v>1.79729676246643</v>
       </c>
       <c r="H614" t="n">
         <v>10850</v>
@@ -18204,7 +18204,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G615" t="n">
-        <v>1.88325452804565</v>
+        <v>1.88325476646423</v>
       </c>
       <c r="H615" t="n">
         <v>100</v>
@@ -18233,7 +18233,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G616" t="n">
-        <v>1.88325452804565</v>
+        <v>1.88325476646423</v>
       </c>
       <c r="H616" t="n">
         <v>0</v>
@@ -18262,7 +18262,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G617" t="n">
-        <v>1.87544012069702</v>
+        <v>1.87544023990631</v>
       </c>
       <c r="H617" t="n">
         <v>1865</v>
@@ -18291,7 +18291,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G618" t="n">
-        <v>1.84418284893036</v>
+        <v>1.84418272972107</v>
       </c>
       <c r="H618" t="n">
         <v>2111</v>
@@ -18320,7 +18320,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G619" t="n">
-        <v>1.891068816185</v>
+        <v>1.89106905460358</v>
       </c>
       <c r="H619" t="n">
         <v>4395</v>
@@ -18378,7 +18378,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G621" t="n">
-        <v>1.86762595176697</v>
+        <v>1.86762571334839</v>
       </c>
       <c r="H621" t="n">
         <v>16907</v>
@@ -18407,7 +18407,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G622" t="n">
-        <v>1.84418284893036</v>
+        <v>1.84418272972107</v>
       </c>
       <c r="H622" t="n">
         <v>1654</v>
@@ -18436,7 +18436,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G623" t="n">
-        <v>1.92232632637024</v>
+        <v>1.92232596874237</v>
       </c>
       <c r="H623" t="n">
         <v>678</v>
@@ -18465,7 +18465,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G624" t="n">
-        <v>1.86762595176697</v>
+        <v>1.86762571334839</v>
       </c>
       <c r="H624" t="n">
         <v>5391</v>
@@ -18494,7 +18494,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G625" t="n">
-        <v>1.91451179981232</v>
+        <v>1.91451191902161</v>
       </c>
       <c r="H625" t="n">
         <v>1010</v>
@@ -18523,7 +18523,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G626" t="n">
-        <v>1.86762595176697</v>
+        <v>1.86762571334839</v>
       </c>
       <c r="H626" t="n">
         <v>4224</v>
@@ -18610,7 +18610,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G629" t="n">
-        <v>1.83636832237244</v>
+        <v>1.83636844158173</v>
       </c>
       <c r="H629" t="n">
         <v>2700</v>
@@ -18639,7 +18639,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G630" t="n">
-        <v>1.84418284893036</v>
+        <v>1.84418272972107</v>
       </c>
       <c r="H630" t="n">
         <v>470</v>
@@ -18668,7 +18668,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G631" t="n">
-        <v>1.79729664325714</v>
+        <v>1.79729676246643</v>
       </c>
       <c r="H631" t="n">
         <v>1387</v>
@@ -18697,7 +18697,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G632" t="n">
-        <v>1.76603937149048</v>
+        <v>1.76603949069977</v>
       </c>
       <c r="H632" t="n">
         <v>2150</v>
@@ -18726,7 +18726,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G633" t="n">
-        <v>1.76603937149048</v>
+        <v>1.76603949069977</v>
       </c>
       <c r="H633" t="n">
         <v>0</v>
@@ -18755,7 +18755,7 @@
         <v>2.25</v>
       </c>
       <c r="G634" t="n">
-        <v>1.75822496414185</v>
+        <v>1.75822520256042</v>
       </c>
       <c r="H634" t="n">
         <v>3308</v>
@@ -18784,7 +18784,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G635" t="n">
-        <v>1.72696805000305</v>
+        <v>1.72696781158447</v>
       </c>
       <c r="H635" t="n">
         <v>2340</v>
@@ -18813,7 +18813,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G636" t="n">
-        <v>1.75041079521179</v>
+        <v>1.75041091442108</v>
       </c>
       <c r="H636" t="n">
         <v>116</v>
@@ -18929,7 +18929,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G640" t="n">
-        <v>1.71915376186371</v>
+        <v>1.71915352344513</v>
       </c>
       <c r="H640" t="n">
         <v>7930</v>
@@ -18958,7 +18958,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G641" t="n">
-        <v>1.71915376186371</v>
+        <v>1.71915352344513</v>
       </c>
       <c r="H641" t="n">
         <v>7808</v>
@@ -18987,7 +18987,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G642" t="n">
-        <v>1.75041079521179</v>
+        <v>1.75041091442108</v>
       </c>
       <c r="H642" t="n">
         <v>870</v>
@@ -19016,7 +19016,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G643" t="n">
-        <v>1.71915376186371</v>
+        <v>1.71915352344513</v>
       </c>
       <c r="H643" t="n">
         <v>3579</v>
@@ -19045,7 +19045,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G644" t="n">
-        <v>1.74259638786316</v>
+        <v>1.74259650707245</v>
       </c>
       <c r="H644" t="n">
         <v>1986</v>
@@ -19074,7 +19074,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G645" t="n">
-        <v>1.71915376186371</v>
+        <v>1.71915352344513</v>
       </c>
       <c r="H645" t="n">
         <v>380</v>
@@ -19103,7 +19103,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G646" t="n">
-        <v>1.71915376186371</v>
+        <v>1.71915352344513</v>
       </c>
       <c r="H646" t="n">
         <v>7131</v>
@@ -19132,7 +19132,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G647" t="n">
-        <v>1.71915376186371</v>
+        <v>1.71915352344513</v>
       </c>
       <c r="H647" t="n">
         <v>1204</v>
@@ -19161,7 +19161,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G648" t="n">
-        <v>1.71915376186371</v>
+        <v>1.71915352344513</v>
       </c>
       <c r="H648" t="n">
         <v>4223</v>
@@ -19190,7 +19190,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G649" t="n">
-        <v>1.70352494716644</v>
+        <v>1.70352482795715</v>
       </c>
       <c r="H649" t="n">
         <v>1910</v>
@@ -19219,7 +19219,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G650" t="n">
-        <v>1.71915376186371</v>
+        <v>1.71915352344513</v>
       </c>
       <c r="H650" t="n">
         <v>1700</v>
@@ -19248,7 +19248,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G651" t="n">
-        <v>1.68008184432983</v>
+        <v>1.68008196353912</v>
       </c>
       <c r="H651" t="n">
         <v>2312</v>
@@ -19277,7 +19277,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G652" t="n">
-        <v>1.68008184432983</v>
+        <v>1.68008196353912</v>
       </c>
       <c r="H652" t="n">
         <v>3142</v>
@@ -19306,7 +19306,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G653" t="n">
-        <v>1.66445326805115</v>
+        <v>1.66445314884186</v>
       </c>
       <c r="H653" t="n">
         <v>1170</v>
@@ -19335,7 +19335,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G654" t="n">
-        <v>1.66445326805115</v>
+        <v>1.66445314884186</v>
       </c>
       <c r="H654" t="n">
         <v>891</v>
@@ -19422,7 +19422,7 @@
         <v>2</v>
       </c>
       <c r="G657" t="n">
-        <v>1.56286692619324</v>
+        <v>1.56286680698395</v>
       </c>
       <c r="H657" t="n">
         <v>7242</v>
@@ -19451,7 +19451,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G658" t="n">
-        <v>1.59412407875061</v>
+        <v>1.5941241979599</v>
       </c>
       <c r="H658" t="n">
         <v>5786</v>
@@ -19480,7 +19480,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G659" t="n">
-        <v>1.60193836688995</v>
+        <v>1.60193848609924</v>
       </c>
       <c r="H659" t="n">
         <v>9353</v>
@@ -19509,7 +19509,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G660" t="n">
-        <v>1.64101016521454</v>
+        <v>1.64101004600525</v>
       </c>
       <c r="H660" t="n">
         <v>2150</v>
@@ -19538,7 +19538,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G661" t="n">
-        <v>1.60193836688995</v>
+        <v>1.60193848609924</v>
       </c>
       <c r="H661" t="n">
         <v>790</v>
@@ -19567,7 +19567,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G662" t="n">
-        <v>1.6097526550293</v>
+        <v>1.60975277423859</v>
       </c>
       <c r="H662" t="n">
         <v>1581</v>
@@ -19683,7 +19683,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G666" t="n">
-        <v>1.92232632637024</v>
+        <v>1.92232596874237</v>
       </c>
       <c r="H666" t="n">
         <v>446846</v>
@@ -19741,7 +19741,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G668" t="n">
-        <v>1.88325452804565</v>
+        <v>1.88325476646423</v>
       </c>
       <c r="H668" t="n">
         <v>20273</v>
@@ -19770,7 +19770,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G669" t="n">
-        <v>1.92232632637024</v>
+        <v>1.92232596874237</v>
       </c>
       <c r="H669" t="n">
         <v>32286</v>
@@ -19799,7 +19799,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G670" t="n">
-        <v>1.99265515804291</v>
+        <v>1.9926552772522</v>
       </c>
       <c r="H670" t="n">
         <v>78330</v>
@@ -19828,7 +19828,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G671" t="n">
-        <v>1.93014049530029</v>
+        <v>1.93014073371887</v>
       </c>
       <c r="H671" t="n">
         <v>41175</v>
@@ -19857,7 +19857,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G672" t="n">
-        <v>1.89888298511505</v>
+        <v>1.89888334274292</v>
       </c>
       <c r="H672" t="n">
         <v>10847</v>
@@ -19886,7 +19886,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G673" t="n">
-        <v>1.92232632637024</v>
+        <v>1.92232596874237</v>
       </c>
       <c r="H673" t="n">
         <v>37391</v>
@@ -19944,7 +19944,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G675" t="n">
-        <v>1.891068816185</v>
+        <v>1.89106905460358</v>
       </c>
       <c r="H675" t="n">
         <v>16914</v>
@@ -19973,7 +19973,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G676" t="n">
-        <v>1.91451179981232</v>
+        <v>1.91451191902161</v>
       </c>
       <c r="H676" t="n">
         <v>18044</v>
@@ -20002,7 +20002,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G677" t="n">
-        <v>1.88325452804565</v>
+        <v>1.88325476646423</v>
       </c>
       <c r="H677" t="n">
         <v>24276</v>
@@ -20060,7 +20060,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G679" t="n">
-        <v>1.85981154441833</v>
+        <v>1.85981166362762</v>
       </c>
       <c r="H679" t="n">
         <v>1203</v>
@@ -20118,7 +20118,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G681" t="n">
-        <v>1.76603937149048</v>
+        <v>1.76603949069977</v>
       </c>
       <c r="H681" t="n">
         <v>6126</v>
@@ -20147,7 +20147,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G682" t="n">
-        <v>1.70352494716644</v>
+        <v>1.70352482795715</v>
       </c>
       <c r="H682" t="n">
         <v>21460</v>
@@ -20176,7 +20176,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G683" t="n">
-        <v>1.91451179981232</v>
+        <v>1.91451191902161</v>
       </c>
       <c r="H683" t="n">
         <v>82840</v>
@@ -20234,7 +20234,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G685" t="n">
-        <v>1.76603937149048</v>
+        <v>1.76603949069977</v>
       </c>
       <c r="H685" t="n">
         <v>13837</v>
@@ -20292,7 +20292,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G687" t="n">
-        <v>1.76603937149048</v>
+        <v>1.76603949069977</v>
       </c>
       <c r="H687" t="n">
         <v>11052</v>
@@ -20321,7 +20321,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G688" t="n">
-        <v>1.76603937149048</v>
+        <v>1.76603949069977</v>
       </c>
       <c r="H688" t="n">
         <v>8342</v>
@@ -20379,7 +20379,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G690" t="n">
-        <v>1.75041079521179</v>
+        <v>1.75041091442108</v>
       </c>
       <c r="H690" t="n">
         <v>2392</v>
@@ -20408,7 +20408,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G691" t="n">
-        <v>1.71915376186371</v>
+        <v>1.71915352344513</v>
       </c>
       <c r="H691" t="n">
         <v>22928</v>
@@ -20437,7 +20437,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G692" t="n">
-        <v>1.70352494716644</v>
+        <v>1.70352482795715</v>
       </c>
       <c r="H692" t="n">
         <v>29415</v>
@@ -20466,7 +20466,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G693" t="n">
-        <v>1.66445326805115</v>
+        <v>1.66445314884186</v>
       </c>
       <c r="H693" t="n">
         <v>31190</v>
@@ -20495,7 +20495,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G694" t="n">
-        <v>1.66445326805115</v>
+        <v>1.66445314884186</v>
       </c>
       <c r="H694" t="n">
         <v>9856</v>
@@ -20524,7 +20524,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G695" t="n">
-        <v>1.64882445335388</v>
+        <v>1.64882433414459</v>
       </c>
       <c r="H695" t="n">
         <v>5710</v>
@@ -20582,7 +20582,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G697" t="n">
-        <v>1.68008184432983</v>
+        <v>1.68008196353912</v>
       </c>
       <c r="H697" t="n">
         <v>5973</v>
@@ -20611,7 +20611,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G698" t="n">
-        <v>1.68008184432983</v>
+        <v>1.68008196353912</v>
       </c>
       <c r="H698" t="n">
         <v>6783</v>
@@ -20640,7 +20640,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G699" t="n">
-        <v>1.74259638786316</v>
+        <v>1.74259650707245</v>
       </c>
       <c r="H699" t="n">
         <v>125437</v>
@@ -20698,7 +20698,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G701" t="n">
-        <v>1.70352494716644</v>
+        <v>1.70352482795715</v>
       </c>
       <c r="H701" t="n">
         <v>20038</v>
@@ -20727,7 +20727,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G702" t="n">
-        <v>1.69571042060852</v>
+        <v>1.69571053981781</v>
       </c>
       <c r="H702" t="n">
         <v>42863</v>
@@ -20756,7 +20756,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G703" t="n">
-        <v>1.64882445335388</v>
+        <v>1.64882433414459</v>
       </c>
       <c r="H703" t="n">
         <v>2626</v>
@@ -20785,7 +20785,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G704" t="n">
-        <v>1.71133947372437</v>
+        <v>1.71133923530579</v>
       </c>
       <c r="H704" t="n">
         <v>104789</v>
@@ -20814,7 +20814,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G705" t="n">
-        <v>1.69571042060852</v>
+        <v>1.69571053981781</v>
       </c>
       <c r="H705" t="n">
         <v>9685</v>
@@ -20843,7 +20843,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G706" t="n">
-        <v>1.68789613246918</v>
+        <v>1.68789637088776</v>
       </c>
       <c r="H706" t="n">
         <v>4340</v>
@@ -20901,7 +20901,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G708" t="n">
-        <v>1.64101016521454</v>
+        <v>1.64101004600525</v>
       </c>
       <c r="H708" t="n">
         <v>1684</v>
@@ -20930,7 +20930,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G709" t="n">
-        <v>1.68789613246918</v>
+        <v>1.68789637088776</v>
       </c>
       <c r="H709" t="n">
         <v>23100</v>
@@ -20959,7 +20959,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G710" t="n">
-        <v>1.63319575786591</v>
+        <v>1.6331958770752</v>
       </c>
       <c r="H710" t="n">
         <v>5696</v>
@@ -20988,7 +20988,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G711" t="n">
-        <v>1.68008184432983</v>
+        <v>1.68008196353912</v>
       </c>
       <c r="H711" t="n">
         <v>1343</v>
@@ -21017,7 +21017,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G712" t="n">
-        <v>1.68008184432983</v>
+        <v>1.68008196353912</v>
       </c>
       <c r="H712" t="n">
         <v>1105</v>
@@ -21046,7 +21046,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G713" t="n">
-        <v>1.63319575786591</v>
+        <v>1.6331958770752</v>
       </c>
       <c r="H713" t="n">
         <v>1527</v>
@@ -21075,7 +21075,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G714" t="n">
-        <v>1.64101016521454</v>
+        <v>1.64101004600525</v>
       </c>
       <c r="H714" t="n">
         <v>318</v>
@@ -21162,7 +21162,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G717" t="n">
-        <v>1.58630967140198</v>
+        <v>1.58630979061127</v>
       </c>
       <c r="H717" t="n">
         <v>4983</v>
@@ -21191,7 +21191,7 @@
         <v>2</v>
       </c>
       <c r="G718" t="n">
-        <v>1.56286692619324</v>
+        <v>1.56286680698395</v>
       </c>
       <c r="H718" t="n">
         <v>6637</v>
@@ -21336,7 +21336,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G723" t="n">
-        <v>1.60193836688995</v>
+        <v>1.60193848609924</v>
       </c>
       <c r="H723" t="n">
         <v>33</v>
@@ -21365,7 +21365,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G724" t="n">
-        <v>1.60193836688995</v>
+        <v>1.60193848609924</v>
       </c>
       <c r="H724" t="n">
         <v>1593</v>
@@ -21394,7 +21394,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G725" t="n">
-        <v>1.60193836688995</v>
+        <v>1.60193848609924</v>
       </c>
       <c r="H725" t="n">
         <v>772</v>
@@ -21423,7 +21423,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G726" t="n">
-        <v>1.60193836688995</v>
+        <v>1.60193848609924</v>
       </c>
       <c r="H726" t="n">
         <v>1638</v>
@@ -21452,7 +21452,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G727" t="n">
-        <v>1.60193836688995</v>
+        <v>1.60193848609924</v>
       </c>
       <c r="H727" t="n">
         <v>0</v>
@@ -21481,7 +21481,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G728" t="n">
-        <v>1.59412407875061</v>
+        <v>1.5941241979599</v>
       </c>
       <c r="H728" t="n">
         <v>2500</v>
@@ -21597,7 +21597,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G732" t="n">
-        <v>1.60193836688995</v>
+        <v>1.60193848609924</v>
       </c>
       <c r="H732" t="n">
         <v>686</v>
@@ -21655,7 +21655,7 @@
         <v>2</v>
       </c>
       <c r="G734" t="n">
-        <v>1.56286692619324</v>
+        <v>1.56286680698395</v>
       </c>
       <c r="H734" t="n">
         <v>1000</v>
@@ -21713,7 +21713,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G736" t="n">
-        <v>1.531609416008</v>
+        <v>1.53160953521729</v>
       </c>
       <c r="H736" t="n">
         <v>1180</v>
@@ -21771,7 +21771,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G738" t="n">
-        <v>1.50035226345062</v>
+        <v>1.50035202503204</v>
       </c>
       <c r="H738" t="n">
         <v>3783</v>
@@ -21800,7 +21800,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G739" t="n">
-        <v>1.49253797531128</v>
+        <v>1.4925377368927</v>
       </c>
       <c r="H739" t="n">
         <v>1588</v>
@@ -21829,7 +21829,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G740" t="n">
-        <v>1.531609416008</v>
+        <v>1.53160953521729</v>
       </c>
       <c r="H740" t="n">
         <v>1201</v>
@@ -21858,7 +21858,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G741" t="n">
-        <v>1.50035226345062</v>
+        <v>1.50035202503204</v>
       </c>
       <c r="H741" t="n">
         <v>1657</v>
@@ -21916,7 +21916,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G743" t="n">
-        <v>1.6097526550293</v>
+        <v>1.60975277423859</v>
       </c>
       <c r="H743" t="n">
         <v>83441</v>
@@ -22003,7 +22003,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G746" t="n">
-        <v>1.59412407875061</v>
+        <v>1.5941241979599</v>
       </c>
       <c r="H746" t="n">
         <v>4010</v>
@@ -22032,7 +22032,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G747" t="n">
-        <v>1.58630967140198</v>
+        <v>1.58630979061127</v>
       </c>
       <c r="H747" t="n">
         <v>1818</v>
@@ -22061,7 +22061,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G748" t="n">
-        <v>1.58630967140198</v>
+        <v>1.58630979061127</v>
       </c>
       <c r="H748" t="n">
         <v>5636</v>
@@ -22090,7 +22090,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G749" t="n">
-        <v>1.58630967140198</v>
+        <v>1.58630979061127</v>
       </c>
       <c r="H749" t="n">
         <v>4728</v>
@@ -22148,7 +22148,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G751" t="n">
-        <v>1.57849550247192</v>
+        <v>1.57849562168121</v>
       </c>
       <c r="H751" t="n">
         <v>40</v>
@@ -22264,7 +22264,7 @@
         <v>2</v>
       </c>
       <c r="G755" t="n">
-        <v>1.56286692619324</v>
+        <v>1.56286680698395</v>
       </c>
       <c r="H755" t="n">
         <v>4200</v>
@@ -22293,7 +22293,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G756" t="n">
-        <v>1.53942394256592</v>
+        <v>1.53942382335663</v>
       </c>
       <c r="H756" t="n">
         <v>2030</v>
@@ -22438,7 +22438,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G761" t="n">
-        <v>1.49253797531128</v>
+        <v>1.4925377368927</v>
       </c>
       <c r="H761" t="n">
         <v>6174</v>
@@ -22467,7 +22467,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G762" t="n">
-        <v>1.47690904140472</v>
+        <v>1.47690916061401</v>
       </c>
       <c r="H762" t="n">
         <v>4134</v>
@@ -22554,7 +22554,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G765" t="n">
-        <v>1.74259638786316</v>
+        <v>1.74259650707245</v>
       </c>
       <c r="H765" t="n">
         <v>62191</v>
@@ -22612,7 +22612,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G767" t="n">
-        <v>1.58630967140198</v>
+        <v>1.58630979061127</v>
       </c>
       <c r="H767" t="n">
         <v>8040</v>
@@ -22670,7 +22670,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G769" t="n">
-        <v>1.58630967140198</v>
+        <v>1.58630979061127</v>
       </c>
       <c r="H769" t="n">
         <v>1450</v>
@@ -22699,7 +22699,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G770" t="n">
-        <v>1.58630967140198</v>
+        <v>1.58630979061127</v>
       </c>
       <c r="H770" t="n">
         <v>1250</v>
@@ -22728,7 +22728,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G771" t="n">
-        <v>1.58630967140198</v>
+        <v>1.58630979061127</v>
       </c>
       <c r="H771" t="n">
         <v>505</v>
@@ -22757,7 +22757,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G772" t="n">
-        <v>1.58630967140198</v>
+        <v>1.58630979061127</v>
       </c>
       <c r="H772" t="n">
         <v>0</v>
@@ -22815,7 +22815,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G774" t="n">
-        <v>1.57849550247192</v>
+        <v>1.57849562168121</v>
       </c>
       <c r="H774" t="n">
         <v>305</v>
@@ -22873,7 +22873,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G776" t="n">
-        <v>1.531609416008</v>
+        <v>1.53160953521729</v>
       </c>
       <c r="H776" t="n">
         <v>5415</v>
@@ -22902,7 +22902,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G777" t="n">
-        <v>1.53942394256592</v>
+        <v>1.53942382335663</v>
       </c>
       <c r="H777" t="n">
         <v>6542</v>
@@ -22931,7 +22931,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G778" t="n">
-        <v>1.53942394256592</v>
+        <v>1.53942382335663</v>
       </c>
       <c r="H778" t="n">
         <v>8387</v>
@@ -22960,7 +22960,7 @@
         <v>2</v>
       </c>
       <c r="G779" t="n">
-        <v>1.56286692619324</v>
+        <v>1.56286680698395</v>
       </c>
       <c r="H779" t="n">
         <v>770</v>
@@ -22989,7 +22989,7 @@
         <v>2</v>
       </c>
       <c r="G780" t="n">
-        <v>1.56286692619324</v>
+        <v>1.56286680698395</v>
       </c>
       <c r="H780" t="n">
         <v>1385</v>
@@ -23047,7 +23047,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G782" t="n">
-        <v>1.531609416008</v>
+        <v>1.53160953521729</v>
       </c>
       <c r="H782" t="n">
         <v>5650</v>
@@ -23076,7 +23076,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G783" t="n">
-        <v>1.531609416008</v>
+        <v>1.53160953521729</v>
       </c>
       <c r="H783" t="n">
         <v>9208</v>
@@ -23105,7 +23105,7 @@
         <v>2</v>
       </c>
       <c r="G784" t="n">
-        <v>1.56286692619324</v>
+        <v>1.56286680698395</v>
       </c>
       <c r="H784" t="n">
         <v>1630</v>
@@ -23134,7 +23134,7 @@
         <v>2</v>
       </c>
       <c r="G785" t="n">
-        <v>1.56286692619324</v>
+        <v>1.56286680698395</v>
       </c>
       <c r="H785" t="n">
         <v>3493</v>
@@ -23221,7 +23221,7 @@
         <v>2</v>
       </c>
       <c r="G788" t="n">
-        <v>1.56286692619324</v>
+        <v>1.56286680698395</v>
       </c>
       <c r="H788" t="n">
         <v>400</v>
@@ -23250,7 +23250,7 @@
         <v>2</v>
       </c>
       <c r="G789" t="n">
-        <v>1.56286692619324</v>
+        <v>1.56286680698395</v>
       </c>
       <c r="H789" t="n">
         <v>540</v>
@@ -23308,7 +23308,7 @@
         <v>2</v>
       </c>
       <c r="G791" t="n">
-        <v>1.56286692619324</v>
+        <v>1.56286680698395</v>
       </c>
       <c r="H791" t="n">
         <v>88</v>
@@ -23424,7 +23424,7 @@
         <v>2</v>
       </c>
       <c r="G795" t="n">
-        <v>1.56286692619324</v>
+        <v>1.56286680698395</v>
       </c>
       <c r="H795" t="n">
         <v>8735</v>
@@ -23453,7 +23453,7 @@
         <v>2</v>
       </c>
       <c r="G796" t="n">
-        <v>1.56286692619324</v>
+        <v>1.56286680698395</v>
       </c>
       <c r="H796" t="n">
         <v>8350</v>
@@ -23511,7 +23511,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G798" t="n">
-        <v>1.57849550247192</v>
+        <v>1.57849562168121</v>
       </c>
       <c r="H798" t="n">
         <v>382</v>
@@ -23540,7 +23540,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G799" t="n">
-        <v>1.59412407875061</v>
+        <v>1.5941241979599</v>
       </c>
       <c r="H799" t="n">
         <v>10202</v>
@@ -23569,7 +23569,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G800" t="n">
-        <v>1.53942394256592</v>
+        <v>1.53942382335663</v>
       </c>
       <c r="H800" t="n">
         <v>7026</v>
@@ -23656,7 +23656,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G803" t="n">
-        <v>1.58630967140198</v>
+        <v>1.58630979061127</v>
       </c>
       <c r="H803" t="n">
         <v>3550</v>
@@ -23685,7 +23685,7 @@
         <v>2</v>
       </c>
       <c r="G804" t="n">
-        <v>1.56286692619324</v>
+        <v>1.56286680698395</v>
       </c>
       <c r="H804" t="n">
         <v>715</v>
@@ -23714,7 +23714,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G805" t="n">
-        <v>1.59412407875061</v>
+        <v>1.5941241979599</v>
       </c>
       <c r="H805" t="n">
         <v>4829</v>
@@ -23743,7 +23743,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G806" t="n">
-        <v>1.58630967140198</v>
+        <v>1.58630979061127</v>
       </c>
       <c r="H806" t="n">
         <v>9021</v>
@@ -23772,7 +23772,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G807" t="n">
-        <v>1.6097526550293</v>
+        <v>1.60975277423859</v>
       </c>
       <c r="H807" t="n">
         <v>6800</v>
@@ -23801,7 +23801,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G808" t="n">
-        <v>1.58630967140198</v>
+        <v>1.58630979061127</v>
       </c>
       <c r="H808" t="n">
         <v>6622</v>
@@ -23830,7 +23830,7 @@
         <v>2</v>
       </c>
       <c r="G809" t="n">
-        <v>1.56286692619324</v>
+        <v>1.56286680698395</v>
       </c>
       <c r="H809" t="n">
         <v>100</v>
@@ -23859,7 +23859,7 @@
         <v>2</v>
       </c>
       <c r="G810" t="n">
-        <v>1.56286692619324</v>
+        <v>1.56286680698395</v>
       </c>
       <c r="H810" t="n">
         <v>2902</v>
@@ -23946,7 +23946,7 @@
         <v>2</v>
       </c>
       <c r="G813" t="n">
-        <v>1.56286692619324</v>
+        <v>1.56286680698395</v>
       </c>
       <c r="H813" t="n">
         <v>3779</v>
@@ -24004,7 +24004,7 @@
         <v>2</v>
       </c>
       <c r="G815" t="n">
-        <v>1.56286692619324</v>
+        <v>1.56286680698395</v>
       </c>
       <c r="H815" t="n">
         <v>4107</v>
@@ -24033,7 +24033,7 @@
         <v>2</v>
       </c>
       <c r="G816" t="n">
-        <v>1.56286692619324</v>
+        <v>1.56286680698395</v>
       </c>
       <c r="H816" t="n">
         <v>8835</v>
@@ -24062,7 +24062,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G817" t="n">
-        <v>1.68008184432983</v>
+        <v>1.68008196353912</v>
       </c>
       <c r="H817" t="n">
         <v>78580</v>
@@ -24091,7 +24091,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G818" t="n">
-        <v>1.6097526550293</v>
+        <v>1.60975277423859</v>
       </c>
       <c r="H818" t="n">
         <v>32403</v>
@@ -24120,7 +24120,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G819" t="n">
-        <v>1.58630967140198</v>
+        <v>1.58630979061127</v>
       </c>
       <c r="H819" t="n">
         <v>15326</v>
@@ -24149,7 +24149,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G820" t="n">
-        <v>1.64101016521454</v>
+        <v>1.64101004600525</v>
       </c>
       <c r="H820" t="n">
         <v>7169</v>
@@ -24236,7 +24236,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G823" t="n">
-        <v>1.57849550247192</v>
+        <v>1.57849562168121</v>
       </c>
       <c r="H823" t="n">
         <v>2086</v>
@@ -24265,7 +24265,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G824" t="n">
-        <v>1.57849550247192</v>
+        <v>1.57849562168121</v>
       </c>
       <c r="H824" t="n">
         <v>3797</v>
@@ -24294,7 +24294,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G825" t="n">
-        <v>1.58630967140198</v>
+        <v>1.58630979061127</v>
       </c>
       <c r="H825" t="n">
         <v>1500</v>
@@ -24323,7 +24323,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G826" t="n">
-        <v>1.59412407875061</v>
+        <v>1.5941241979599</v>
       </c>
       <c r="H826" t="n">
         <v>4684</v>
@@ -24381,7 +24381,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G828" t="n">
-        <v>1.891068816185</v>
+        <v>1.89106905460358</v>
       </c>
       <c r="H828" t="n">
         <v>164712</v>
@@ -24555,7 +24555,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G834" t="n">
-        <v>1.64101016521454</v>
+        <v>1.64101004600525</v>
       </c>
       <c r="H834" t="n">
         <v>9584</v>
@@ -24584,7 +24584,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G835" t="n">
-        <v>1.6097526550293</v>
+        <v>1.60975277423859</v>
       </c>
       <c r="H835" t="n">
         <v>57779</v>
@@ -24700,7 +24700,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G839" t="n">
-        <v>1.64101016521454</v>
+        <v>1.64101004600525</v>
       </c>
       <c r="H839" t="n">
         <v>10970</v>
@@ -24729,7 +24729,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G840" t="n">
-        <v>1.59412407875061</v>
+        <v>1.5941241979599</v>
       </c>
       <c r="H840" t="n">
         <v>22366</v>
@@ -24758,7 +24758,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G841" t="n">
-        <v>1.64101016521454</v>
+        <v>1.64101004600525</v>
       </c>
       <c r="H841" t="n">
         <v>17557</v>
@@ -24787,7 +24787,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G842" t="n">
-        <v>1.59412407875061</v>
+        <v>1.5941241979599</v>
       </c>
       <c r="H842" t="n">
         <v>34014</v>
@@ -24816,7 +24816,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G843" t="n">
-        <v>1.57849550247192</v>
+        <v>1.57849562168121</v>
       </c>
       <c r="H843" t="n">
         <v>5516</v>
@@ -24845,7 +24845,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G844" t="n">
-        <v>1.6097526550293</v>
+        <v>1.60975277423859</v>
       </c>
       <c r="H844" t="n">
         <v>39333</v>
@@ -24903,7 +24903,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G846" t="n">
-        <v>1.6097526550293</v>
+        <v>1.60975277423859</v>
       </c>
       <c r="H846" t="n">
         <v>9208</v>
@@ -24961,7 +24961,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G848" t="n">
-        <v>1.6097526550293</v>
+        <v>1.60975277423859</v>
       </c>
       <c r="H848" t="n">
         <v>10001</v>
@@ -24990,7 +24990,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G849" t="n">
-        <v>1.59412407875061</v>
+        <v>1.5941241979599</v>
       </c>
       <c r="H849" t="n">
         <v>8778</v>
@@ -25019,7 +25019,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G850" t="n">
-        <v>1.59412407875061</v>
+        <v>1.5941241979599</v>
       </c>
       <c r="H850" t="n">
         <v>1999</v>
@@ -25048,7 +25048,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G851" t="n">
-        <v>1.57849550247192</v>
+        <v>1.57849562168121</v>
       </c>
       <c r="H851" t="n">
         <v>3006</v>
@@ -25077,7 +25077,7 @@
         <v>2</v>
       </c>
       <c r="G852" t="n">
-        <v>1.56286692619324</v>
+        <v>1.56286680698395</v>
       </c>
       <c r="H852" t="n">
         <v>14569</v>
@@ -25106,7 +25106,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G853" t="n">
-        <v>1.531609416008</v>
+        <v>1.53160953521729</v>
       </c>
       <c r="H853" t="n">
         <v>9826</v>
@@ -25135,7 +25135,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G854" t="n">
-        <v>1.59412407875061</v>
+        <v>1.5941241979599</v>
       </c>
       <c r="H854" t="n">
         <v>10243</v>
@@ -25164,7 +25164,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G855" t="n">
-        <v>1.531609416008</v>
+        <v>1.53160953521729</v>
       </c>
       <c r="H855" t="n">
         <v>30431</v>
@@ -25222,7 +25222,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G857" t="n">
-        <v>1.531609416008</v>
+        <v>1.53160953521729</v>
       </c>
       <c r="H857" t="n">
         <v>8665</v>
@@ -25280,7 +25280,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G859" t="n">
-        <v>1.57849550247192</v>
+        <v>1.57849562168121</v>
       </c>
       <c r="H859" t="n">
         <v>7873</v>
@@ -25309,7 +25309,7 @@
         <v>2</v>
       </c>
       <c r="G860" t="n">
-        <v>1.56286692619324</v>
+        <v>1.56286680698395</v>
       </c>
       <c r="H860" t="n">
         <v>500</v>
@@ -25338,7 +25338,7 @@
         <v>2</v>
       </c>
       <c r="G861" t="n">
-        <v>1.56286692619324</v>
+        <v>1.56286680698395</v>
       </c>
       <c r="H861" t="n">
         <v>0</v>
@@ -25454,7 +25454,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G865" t="n">
-        <v>1.50035226345062</v>
+        <v>1.50035202503204</v>
       </c>
       <c r="H865" t="n">
         <v>6903</v>
@@ -25483,7 +25483,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G866" t="n">
-        <v>1.50035226345062</v>
+        <v>1.50035202503204</v>
       </c>
       <c r="H866" t="n">
         <v>8355</v>
@@ -25512,7 +25512,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G867" t="n">
-        <v>1.531609416008</v>
+        <v>1.53160953521729</v>
       </c>
       <c r="H867" t="n">
         <v>3500</v>
@@ -25628,7 +25628,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G871" t="n">
-        <v>1.50035226345062</v>
+        <v>1.50035202503204</v>
       </c>
       <c r="H871" t="n">
         <v>1918</v>
@@ -25657,7 +25657,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G872" t="n">
-        <v>1.50035226345062</v>
+        <v>1.50035202503204</v>
       </c>
       <c r="H872" t="n">
         <v>0</v>
@@ -25831,7 +25831,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G878" t="n">
-        <v>1.531609416008</v>
+        <v>1.53160953521729</v>
       </c>
       <c r="H878" t="n">
         <v>2050</v>
@@ -25947,7 +25947,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G882" t="n">
-        <v>1.43783736228943</v>
+        <v>1.43783748149872</v>
       </c>
       <c r="H882" t="n">
         <v>3065</v>
@@ -26034,7 +26034,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G885" t="n">
-        <v>1.43783736228943</v>
+        <v>1.43783748149872</v>
       </c>
       <c r="H885" t="n">
         <v>29</v>
@@ -26237,7 +26237,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G892" t="n">
-        <v>1.531609416008</v>
+        <v>1.53160953521729</v>
       </c>
       <c r="H892" t="n">
         <v>6177</v>
@@ -26324,7 +26324,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G895" t="n">
-        <v>1.531609416008</v>
+        <v>1.53160953521729</v>
       </c>
       <c r="H895" t="n">
         <v>4132</v>
@@ -26353,7 +26353,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G896" t="n">
-        <v>1.531609416008</v>
+        <v>1.53160953521729</v>
       </c>
       <c r="H896" t="n">
         <v>15658</v>
@@ -26411,7 +26411,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G898" t="n">
-        <v>1.50035226345062</v>
+        <v>1.50035202503204</v>
       </c>
       <c r="H898" t="n">
         <v>9001</v>
@@ -26440,7 +26440,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G899" t="n">
-        <v>1.50035226345062</v>
+        <v>1.50035202503204</v>
       </c>
       <c r="H899" t="n">
         <v>5729</v>
@@ -26469,7 +26469,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G900" t="n">
-        <v>1.50035226345062</v>
+        <v>1.50035202503204</v>
       </c>
       <c r="H900" t="n">
         <v>4094</v>
@@ -26585,7 +26585,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G904" t="n">
-        <v>1.531609416008</v>
+        <v>1.53160953521729</v>
       </c>
       <c r="H904" t="n">
         <v>2250</v>
@@ -26614,7 +26614,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G905" t="n">
-        <v>1.531609416008</v>
+        <v>1.53160953521729</v>
       </c>
       <c r="H905" t="n">
         <v>3080</v>
@@ -26643,7 +26643,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G906" t="n">
-        <v>1.50035226345062</v>
+        <v>1.50035202503204</v>
       </c>
       <c r="H906" t="n">
         <v>3380</v>
@@ -26672,7 +26672,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G907" t="n">
-        <v>1.50035226345062</v>
+        <v>1.50035202503204</v>
       </c>
       <c r="H907" t="n">
         <v>17682</v>
@@ -26759,7 +26759,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G910" t="n">
-        <v>1.50035226345062</v>
+        <v>1.50035202503204</v>
       </c>
       <c r="H910" t="n">
         <v>2535</v>
@@ -26846,7 +26846,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G913" t="n">
-        <v>1.50035226345062</v>
+        <v>1.50035202503204</v>
       </c>
       <c r="H913" t="n">
         <v>1205</v>
@@ -26933,7 +26933,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G916" t="n">
-        <v>1.50035226345062</v>
+        <v>1.50035202503204</v>
       </c>
       <c r="H916" t="n">
         <v>1650</v>
@@ -26962,7 +26962,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G917" t="n">
-        <v>1.50035226345062</v>
+        <v>1.50035202503204</v>
       </c>
       <c r="H917" t="n">
         <v>8100</v>
@@ -27223,7 +27223,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G926" t="n">
-        <v>1.50035226345062</v>
+        <v>1.50035202503204</v>
       </c>
       <c r="H926" t="n">
         <v>3414</v>
@@ -27252,7 +27252,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G927" t="n">
-        <v>1.50035226345062</v>
+        <v>1.50035202503204</v>
       </c>
       <c r="H927" t="n">
         <v>60</v>
@@ -27426,7 +27426,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G933" t="n">
-        <v>1.50035226345062</v>
+        <v>1.50035202503204</v>
       </c>
       <c r="H933" t="n">
         <v>10800</v>
@@ -27629,7 +27629,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G940" t="n">
-        <v>1.50035226345062</v>
+        <v>1.50035202503204</v>
       </c>
       <c r="H940" t="n">
         <v>3395</v>
@@ -27658,7 +27658,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G941" t="n">
-        <v>1.531609416008</v>
+        <v>1.53160953521729</v>
       </c>
       <c r="H941" t="n">
         <v>62485</v>
@@ -27890,7 +27890,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G949" t="n">
-        <v>1.50035226345062</v>
+        <v>1.50035202503204</v>
       </c>
       <c r="H949" t="n">
         <v>2380</v>
@@ -27919,7 +27919,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G950" t="n">
-        <v>1.50035226345062</v>
+        <v>1.50035202503204</v>
       </c>
       <c r="H950" t="n">
         <v>1118</v>
@@ -27948,7 +27948,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G951" t="n">
-        <v>1.50035226345062</v>
+        <v>1.50035202503204</v>
       </c>
       <c r="H951" t="n">
         <v>2270</v>
@@ -27977,7 +27977,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G952" t="n">
-        <v>1.50035226345062</v>
+        <v>1.50035202503204</v>
       </c>
       <c r="H952" t="n">
         <v>3602</v>
@@ -28006,7 +28006,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G953" t="n">
-        <v>1.50035226345062</v>
+        <v>1.50035202503204</v>
       </c>
       <c r="H953" t="n">
         <v>4131</v>
@@ -28035,7 +28035,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G954" t="n">
-        <v>1.50035226345062</v>
+        <v>1.50035202503204</v>
       </c>
       <c r="H954" t="n">
         <v>7140</v>
@@ -28470,7 +28470,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G969" t="n">
-        <v>1.43783736228943</v>
+        <v>1.43783748149872</v>
       </c>
       <c r="H969" t="n">
         <v>21430</v>
@@ -28499,7 +28499,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G970" t="n">
-        <v>1.43783736228943</v>
+        <v>1.43783748149872</v>
       </c>
       <c r="H970" t="n">
         <v>484</v>
@@ -28528,7 +28528,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G971" t="n">
-        <v>1.43783736228943</v>
+        <v>1.43783748149872</v>
       </c>
       <c r="H971" t="n">
         <v>1075</v>
@@ -28557,7 +28557,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G972" t="n">
-        <v>1.43783736228943</v>
+        <v>1.43783748149872</v>
       </c>
       <c r="H972" t="n">
         <v>500</v>
@@ -28644,7 +28644,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G975" t="n">
-        <v>1.43783736228943</v>
+        <v>1.43783748149872</v>
       </c>
       <c r="H975" t="n">
         <v>2000</v>
@@ -28731,7 +28731,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G978" t="n">
-        <v>1.43783736228943</v>
+        <v>1.43783748149872</v>
       </c>
       <c r="H978" t="n">
         <v>4265</v>
@@ -28789,7 +28789,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G980" t="n">
-        <v>1.43783736228943</v>
+        <v>1.43783748149872</v>
       </c>
       <c r="H980" t="n">
         <v>560</v>
@@ -28818,7 +28818,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G981" t="n">
-        <v>1.43783736228943</v>
+        <v>1.43783748149872</v>
       </c>
       <c r="H981" t="n">
         <v>3315</v>
@@ -29021,7 +29021,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G988" t="n">
-        <v>1.43783736228943</v>
+        <v>1.43783748149872</v>
       </c>
       <c r="H988" t="n">
         <v>3235</v>
@@ -29079,7 +29079,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G990" t="n">
-        <v>1.43783736228943</v>
+        <v>1.43783748149872</v>
       </c>
       <c r="H990" t="n">
         <v>377</v>
@@ -29108,7 +29108,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G991" t="n">
-        <v>1.43783736228943</v>
+        <v>1.43783748149872</v>
       </c>
       <c r="H991" t="n">
         <v>1621</v>
@@ -29137,7 +29137,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G992" t="n">
-        <v>1.43783736228943</v>
+        <v>1.43783748149872</v>
       </c>
       <c r="H992" t="n">
         <v>4633</v>
@@ -29340,7 +29340,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G999" t="n">
-        <v>1.3753228187561</v>
+        <v>1.37532293796539</v>
       </c>
       <c r="H999" t="n">
         <v>5008</v>
@@ -29398,7 +29398,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G1001" t="n">
-        <v>1.3753228187561</v>
+        <v>1.37532293796539</v>
       </c>
       <c r="H1001" t="n">
         <v>3675</v>
@@ -29427,7 +29427,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G1002" t="n">
-        <v>1.43783736228943</v>
+        <v>1.43783748149872</v>
       </c>
       <c r="H1002" t="n">
         <v>29959</v>
@@ -29456,7 +29456,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1003" t="n">
-        <v>1.68789613246918</v>
+        <v>1.68789637088776</v>
       </c>
       <c r="H1003" t="n">
         <v>363297</v>
@@ -29485,7 +29485,7 @@
         <v>2</v>
       </c>
       <c r="G1004" t="n">
-        <v>1.56286692619324</v>
+        <v>1.56286680698395</v>
       </c>
       <c r="H1004" t="n">
         <v>526368</v>
@@ -29717,7 +29717,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G1012" t="n">
-        <v>1.43783736228943</v>
+        <v>1.43783748149872</v>
       </c>
       <c r="H1012" t="n">
         <v>26843</v>
@@ -29746,7 +29746,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G1013" t="n">
-        <v>1.43783736228943</v>
+        <v>1.43783748149872</v>
       </c>
       <c r="H1013" t="n">
         <v>8510</v>
@@ -29862,7 +29862,7 @@
         <v>1.80480003356934</v>
       </c>
       <c r="G1017" t="n">
-        <v>1.41033113002777</v>
+        <v>1.41033101081848</v>
       </c>
       <c r="H1017" t="n">
         <v>6419</v>
@@ -29891,7 +29891,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G1018" t="n">
-        <v>1.35969412326813</v>
+        <v>1.35969424247742</v>
       </c>
       <c r="H1018" t="n">
         <v>21467</v>
@@ -29920,7 +29920,7 @@
         <v>1.76600003242493</v>
       </c>
       <c r="G1019" t="n">
-        <v>1.38001143932343</v>
+        <v>1.38001132011414</v>
       </c>
       <c r="H1019" t="n">
         <v>61548</v>
@@ -29978,7 +29978,7 @@
         <v>1.77359998226166</v>
       </c>
       <c r="G1021" t="n">
-        <v>1.38595020771027</v>
+        <v>1.38595032691956</v>
       </c>
       <c r="H1021" t="n">
         <v>10862</v>
@@ -30007,7 +30007,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G1022" t="n">
-        <v>1.43002307415009</v>
+        <v>1.43002319335938</v>
       </c>
       <c r="H1022" t="n">
         <v>55375</v>
@@ -30036,7 +30036,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G1023" t="n">
-        <v>1.4143944978714</v>
+        <v>1.41439437866211</v>
       </c>
       <c r="H1023" t="n">
         <v>10822</v>
@@ -30065,7 +30065,7 @@
         <v>1.81959998607635</v>
       </c>
       <c r="G1024" t="n">
-        <v>1.42189621925354</v>
+        <v>1.42189633846283</v>
       </c>
       <c r="H1024" t="n">
         <v>67133</v>
@@ -30094,7 +30094,7 @@
         <v>1.74860000610352</v>
       </c>
       <c r="G1025" t="n">
-        <v>1.36641442775726</v>
+        <v>1.36641454696655</v>
       </c>
       <c r="H1025" t="n">
         <v>53431</v>
@@ -30123,7 +30123,7 @@
         <v>1.74119997024536</v>
       </c>
       <c r="G1026" t="n">
-        <v>1.36063170433044</v>
+        <v>1.36063182353973</v>
       </c>
       <c r="H1026" t="n">
         <v>42274</v>
@@ -30181,7 +30181,7 @@
         <v>1.70500004291534</v>
       </c>
       <c r="G1028" t="n">
-        <v>1.33234393596649</v>
+        <v>1.33234405517578</v>
       </c>
       <c r="H1028" t="n">
         <v>21254</v>
@@ -30210,7 +30210,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G1029" t="n">
-        <v>1.34406566619873</v>
+        <v>1.34406542778015</v>
       </c>
       <c r="H1029" t="n">
         <v>22344</v>
@@ -30239,7 +30239,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G1030" t="n">
-        <v>1.33625113964081</v>
+        <v>1.3362512588501</v>
       </c>
       <c r="H1030" t="n">
         <v>3600</v>
@@ -30268,7 +30268,7 @@
         <v>1.73239994049072</v>
       </c>
       <c r="G1031" t="n">
-        <v>1.353755235672</v>
+        <v>1.35375511646271</v>
       </c>
       <c r="H1031" t="n">
         <v>8694</v>
@@ -30297,7 +30297,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G1032" t="n">
-        <v>1.35187983512878</v>
+        <v>1.35187995433807</v>
       </c>
       <c r="H1032" t="n">
         <v>850</v>
@@ -30326,7 +30326,7 @@
         <v>1.70099997520447</v>
       </c>
       <c r="G1033" t="n">
-        <v>1.32921814918518</v>
+        <v>1.32921826839447</v>
       </c>
       <c r="H1033" t="n">
         <v>15378</v>
@@ -30355,7 +30355,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G1034" t="n">
-        <v>1.33625113964081</v>
+        <v>1.3362512588501</v>
       </c>
       <c r="H1034" t="n">
         <v>4038</v>
@@ -30413,7 +30413,7 @@
         <v>1.66919994354248</v>
       </c>
       <c r="G1036" t="n">
-        <v>1.30436861515045</v>
+        <v>1.30436849594116</v>
       </c>
       <c r="H1036" t="n">
         <v>37285</v>
@@ -30558,7 +30558,7 @@
         <v>1.57720005512238</v>
       </c>
       <c r="G1041" t="n">
-        <v>1.23247683048248</v>
+        <v>1.23247671127319</v>
       </c>
       <c r="H1041" t="n">
         <v>45218</v>
@@ -30616,7 +30616,7 @@
         <v>1.61819994449615</v>
       </c>
       <c r="G1043" t="n">
-        <v>1.26451551914215</v>
+        <v>1.26451539993286</v>
       </c>
       <c r="H1043" t="n">
         <v>5812</v>
@@ -30790,7 +30790,7 @@
         <v>1.67980003356934</v>
       </c>
       <c r="G1049" t="n">
-        <v>1.3126517534256</v>
+        <v>1.31265199184418</v>
       </c>
       <c r="H1049" t="n">
         <v>5718</v>
@@ -30964,7 +30964,7 @@
         <v>1.61479997634888</v>
       </c>
       <c r="G1055" t="n">
-        <v>1.26185870170593</v>
+        <v>1.26185858249664</v>
       </c>
       <c r="H1055" t="n">
         <v>3537</v>
@@ -30993,7 +30993,7 @@
         <v>1.54159998893738</v>
       </c>
       <c r="G1056" t="n">
-        <v>1.20465767383575</v>
+        <v>1.20465779304504</v>
       </c>
       <c r="H1056" t="n">
         <v>6735</v>
@@ -31080,7 +31080,7 @@
         <v>1.55980002880096</v>
       </c>
       <c r="G1059" t="n">
-        <v>1.2188800573349</v>
+        <v>1.21887993812561</v>
       </c>
       <c r="H1059" t="n">
         <v>21083</v>
@@ -31109,7 +31109,7 @@
         <v>1.5</v>
       </c>
       <c r="G1060" t="n">
-        <v>1.17215013504028</v>
+        <v>1.17215001583099</v>
       </c>
       <c r="H1060" t="n">
         <v>1635</v>
@@ -31196,7 +31196,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G1063" t="n">
-        <v>0.883019685745239</v>
+        <v>0.883019745349884</v>
       </c>
       <c r="H1063" t="n">
         <v>14800</v>
@@ -31225,7 +31225,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G1064" t="n">
-        <v>0.883019685745239</v>
+        <v>0.883019745349884</v>
       </c>
       <c r="H1064" t="n">
         <v>10076</v>
@@ -31312,7 +31312,7 @@
         <v>0.997900009155273</v>
       </c>
       <c r="G1067" t="n">
-        <v>0.779792428016663</v>
+        <v>0.779792368412018</v>
       </c>
       <c r="H1067" t="n">
         <v>46633</v>
@@ -31428,7 +31428,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G1071" t="n">
-        <v>0.789247751235962</v>
+        <v>0.789247810840607</v>
       </c>
       <c r="H1071" t="n">
         <v>4000</v>
@@ -31457,7 +31457,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G1072" t="n">
-        <v>0.859576880931854</v>
+        <v>0.859576761722565</v>
       </c>
       <c r="H1072" t="n">
         <v>6459</v>
@@ -31486,7 +31486,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G1073" t="n">
-        <v>0.968977451324463</v>
+        <v>0.968977510929108</v>
       </c>
       <c r="H1073" t="n">
         <v>6985</v>
@@ -31515,7 +31515,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G1074" t="n">
-        <v>1.0940066576004</v>
+        <v>1.09400689601898</v>
       </c>
       <c r="H1074" t="n">
         <v>7710</v>
@@ -31573,7 +31573,7 @@
         <v>1.5958000421524</v>
       </c>
       <c r="G1076" t="n">
-        <v>1.24701154232025</v>
+        <v>1.24701142311096</v>
       </c>
       <c r="H1076" t="n">
         <v>28795</v>
@@ -31747,7 +31747,7 @@
         <v>1.49080002307892</v>
       </c>
       <c r="G1082" t="n">
-        <v>1.16496086120605</v>
+        <v>1.16496098041534</v>
       </c>
       <c r="H1082" t="n">
         <v>2750</v>
@@ -31805,7 +31805,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G1084" t="n">
-        <v>1.25810778141022</v>
+        <v>1.25810790061951</v>
       </c>
       <c r="H1084" t="n">
         <v>29539</v>
@@ -31834,7 +31834,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G1085" t="n">
-        <v>1.21903610229492</v>
+        <v>1.21903598308563</v>
       </c>
       <c r="H1085" t="n">
         <v>12132</v>
@@ -31921,7 +31921,7 @@
         <v>1.52999997138977</v>
       </c>
       <c r="G1088" t="n">
-        <v>1.1955931186676</v>
+        <v>1.19559299945831</v>
       </c>
       <c r="H1088" t="n">
         <v>8558</v>
@@ -31950,7 +31950,7 @@
         <v>1.60959994792938</v>
       </c>
       <c r="G1089" t="n">
-        <v>1.25779521465302</v>
+        <v>1.25779509544373</v>
       </c>
       <c r="H1089" t="n">
         <v>9302</v>
@@ -31979,7 +31979,7 @@
         <v>1.56959998607635</v>
       </c>
       <c r="G1090" t="n">
-        <v>1.22653782367706</v>
+        <v>1.22653794288635</v>
       </c>
       <c r="H1090" t="n">
         <v>15691</v>
@@ -32008,7 +32008,7 @@
         <v>1.53519999980927</v>
       </c>
       <c r="G1091" t="n">
-        <v>1.19965672492981</v>
+        <v>1.19965660572052</v>
       </c>
       <c r="H1091" t="n">
         <v>7726</v>
@@ -32037,7 +32037,7 @@
         <v>1.51059997081757</v>
       </c>
       <c r="G1092" t="n">
-        <v>1.18043327331543</v>
+        <v>1.18043339252472</v>
       </c>
       <c r="H1092" t="n">
         <v>10176</v>
@@ -32066,7 +32066,7 @@
         <v>1.53840005397797</v>
       </c>
       <c r="G1093" t="n">
-        <v>1.20215713977814</v>
+        <v>1.20215725898743</v>
       </c>
       <c r="H1093" t="n">
         <v>6653</v>
@@ -32153,7 +32153,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G1096" t="n">
-        <v>1.08619236946106</v>
+        <v>1.08619248867035</v>
       </c>
       <c r="H1096" t="n">
         <v>36445</v>
@@ -32182,7 +32182,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G1097" t="n">
-        <v>1.05493521690369</v>
+        <v>1.0549350976944</v>
       </c>
       <c r="H1097" t="n">
         <v>24618</v>
@@ -32211,7 +32211,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G1098" t="n">
-        <v>1.05493521690369</v>
+        <v>1.0549350976944</v>
       </c>
       <c r="H1098" t="n">
         <v>0</v>
@@ -32298,7 +32298,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G1101" t="n">
-        <v>1.06274950504303</v>
+        <v>1.06274938583374</v>
       </c>
       <c r="H1101" t="n">
         <v>17633</v>
@@ -32414,7 +32414,7 @@
         <v>1.3782000541687</v>
       </c>
       <c r="G1105" t="n">
-        <v>1.07697141170502</v>
+        <v>1.07697153091431</v>
       </c>
       <c r="H1105" t="n">
         <v>17647</v>
@@ -32443,7 +32443,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1106" t="n">
-        <v>1.04712069034576</v>
+        <v>1.04712092876434</v>
       </c>
       <c r="H1106" t="n">
         <v>11729</v>
@@ -32530,7 +32530,7 @@
         <v>1.26440000534058</v>
       </c>
       <c r="G1109" t="n">
-        <v>0.988044440746307</v>
+        <v>0.988044500350952</v>
       </c>
       <c r="H1109" t="n">
         <v>36450</v>
@@ -32588,7 +32588,7 @@
         <v>1.24500000476837</v>
       </c>
       <c r="G1111" t="n">
-        <v>0.972884654998779</v>
+        <v>0.97288453578949</v>
       </c>
       <c r="H1111" t="n">
         <v>16126</v>
@@ -32646,7 +32646,7 @@
         <v>1.23800003528595</v>
       </c>
       <c r="G1113" t="n">
-        <v>0.967414557933807</v>
+        <v>0.967414438724518</v>
       </c>
       <c r="H1113" t="n">
         <v>18476</v>
@@ -32675,7 +32675,7 @@
         <v>1.23039996623993</v>
       </c>
       <c r="G1114" t="n">
-        <v>0.961475729942322</v>
+        <v>0.961475670337677</v>
       </c>
       <c r="H1114" t="n">
         <v>12655</v>
@@ -32704,7 +32704,7 @@
         <v>1.25</v>
       </c>
       <c r="G1115" t="n">
-        <v>0.976791679859161</v>
+        <v>0.976791799068451</v>
       </c>
       <c r="H1115" t="n">
         <v>34094</v>
@@ -32762,7 +32762,7 @@
         <v>1.3367999792099</v>
       </c>
       <c r="G1117" t="n">
-        <v>1.04462027549744</v>
+        <v>1.04462015628815</v>
       </c>
       <c r="H1117" t="n">
         <v>27003</v>
@@ -32791,7 +32791,7 @@
         <v>1.31719994544983</v>
       </c>
       <c r="G1118" t="n">
-        <v>1.02930402755737</v>
+        <v>1.02930414676666</v>
       </c>
       <c r="H1118" t="n">
         <v>20471</v>
@@ -32849,7 +32849,7 @@
         <v>1.2791999578476</v>
       </c>
       <c r="G1120" t="n">
-        <v>0.999609589576721</v>
+        <v>0.999609649181366</v>
       </c>
       <c r="H1120" t="n">
         <v>25760</v>
@@ -32907,7 +32907,7 @@
         <v>1.33940005302429</v>
       </c>
       <c r="G1122" t="n">
-        <v>1.04665207862854</v>
+        <v>1.04665195941925</v>
       </c>
       <c r="H1122" t="n">
         <v>68249</v>
@@ -32936,7 +32936,7 @@
         <v>1.31359994411469</v>
       </c>
       <c r="G1123" t="n">
-        <v>1.02649092674255</v>
+        <v>1.02649080753326</v>
       </c>
       <c r="H1123" t="n">
         <v>10857</v>
@@ -33023,7 +33023,7 @@
         <v>1.35979998111725</v>
       </c>
       <c r="G1126" t="n">
-        <v>1.06259322166443</v>
+        <v>1.06259298324585</v>
       </c>
       <c r="H1126" t="n">
         <v>19347</v>
@@ -33052,7 +33052,7 @@
         <v>1.37399995326996</v>
       </c>
       <c r="G1127" t="n">
-        <v>1.07368957996368</v>
+        <v>1.07368946075439</v>
       </c>
       <c r="H1127" t="n">
         <v>9812</v>
@@ -33139,7 +33139,7 @@
         <v>1.29579997062683</v>
       </c>
       <c r="G1130" t="n">
-        <v>1.0125812292099</v>
+        <v>1.01258134841919</v>
       </c>
       <c r="H1130" t="n">
         <v>34473</v>
@@ -33197,7 +33197,7 @@
         <v>1.32280004024506</v>
       </c>
       <c r="G1132" t="n">
-        <v>1.03368008136749</v>
+        <v>1.03368020057678</v>
       </c>
       <c r="H1132" t="n">
         <v>4792</v>
@@ -33255,7 +33255,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1134" t="n">
-        <v>1.04712069034576</v>
+        <v>1.04712092876434</v>
       </c>
       <c r="H1134" t="n">
         <v>6000</v>
@@ -33371,7 +33371,7 @@
         <v>1.33980000019073</v>
       </c>
       <c r="G1138" t="n">
-        <v>1.04696452617645</v>
+        <v>1.04696440696716</v>
       </c>
       <c r="H1138" t="n">
         <v>20947</v>
@@ -33487,7 +33487,7 @@
         <v>1.29200005531311</v>
       </c>
       <c r="G1142" t="n">
-        <v>1.00961208343506</v>
+        <v>1.00961196422577</v>
       </c>
       <c r="H1142" t="n">
         <v>1000</v>
@@ -33516,7 +33516,7 @@
         <v>1.30900001525879</v>
       </c>
       <c r="G1143" t="n">
-        <v>1.02289628982544</v>
+        <v>1.02289640903473</v>
       </c>
       <c r="H1143" t="n">
         <v>1000</v>
@@ -33632,7 +33632,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1147" t="n">
-        <v>0.992420375347137</v>
+        <v>0.992420494556427</v>
       </c>
       <c r="H1147" t="n">
         <v>5704</v>
@@ -33690,7 +33690,7 @@
         <v>1.26240003108978</v>
       </c>
       <c r="G1149" t="n">
-        <v>0.986481666564941</v>
+        <v>0.986481487751007</v>
       </c>
       <c r="H1149" t="n">
         <v>8000</v>
@@ -33748,7 +33748,7 @@
         <v>1.29299998283386</v>
       </c>
       <c r="G1151" t="n">
-        <v>1.01039338111877</v>
+        <v>1.01039326190948</v>
       </c>
       <c r="H1151" t="n">
         <v>4302</v>
@@ -33806,7 +33806,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1153" t="n">
-        <v>0.992420375347137</v>
+        <v>0.992420494556427</v>
       </c>
       <c r="H1153" t="n">
         <v>2410</v>
@@ -33893,7 +33893,7 @@
         <v>1.26199996471405</v>
       </c>
       <c r="G1156" t="n">
-        <v>0.98616886138916</v>
+        <v>0.986168920993805</v>
       </c>
       <c r="H1156" t="n">
         <v>9776</v>
@@ -33980,7 +33980,7 @@
         <v>1.29499995708466</v>
       </c>
       <c r="G1159" t="n">
-        <v>1.01195633411407</v>
+        <v>1.01195621490479</v>
       </c>
       <c r="H1159" t="n">
         <v>21359</v>
@@ -34038,7 +34038,7 @@
         <v>1.28939998149872</v>
       </c>
       <c r="G1161" t="n">
-        <v>1.00758016109467</v>
+        <v>1.00758028030396</v>
       </c>
       <c r="H1161" t="n">
         <v>160</v>
@@ -34096,7 +34096,7 @@
         <v>1.23080003261566</v>
       </c>
       <c r="G1163" t="n">
-        <v>0.961788296699524</v>
+        <v>0.961788356304169</v>
       </c>
       <c r="H1163" t="n">
         <v>35956</v>
@@ -34154,7 +34154,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1165" t="n">
-        <v>0.992420375347137</v>
+        <v>0.992420494556427</v>
       </c>
       <c r="H1165" t="n">
         <v>10014</v>
@@ -34183,7 +34183,7 @@
         <v>1.27900004386902</v>
       </c>
       <c r="G1166" t="n">
-        <v>0.99945330619812</v>
+        <v>0.999453365802765</v>
       </c>
       <c r="H1166" t="n">
         <v>19032</v>
@@ -34212,7 +34212,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1167" t="n">
-        <v>0.992420375347137</v>
+        <v>0.992420494556427</v>
       </c>
       <c r="H1167" t="n">
         <v>18852</v>
@@ -34241,7 +34241,7 @@
         <v>1.22819995880127</v>
       </c>
       <c r="G1168" t="n">
-        <v>0.95975649356842</v>
+        <v>0.959756433963776</v>
       </c>
       <c r="H1168" t="n">
         <v>10446</v>
@@ -34270,7 +34270,7 @@
         <v>1.25</v>
       </c>
       <c r="G1169" t="n">
-        <v>0.976791679859161</v>
+        <v>0.976791799068451</v>
       </c>
       <c r="H1169" t="n">
         <v>7000</v>
@@ -34299,7 +34299,7 @@
         <v>1.25</v>
       </c>
       <c r="G1170" t="n">
-        <v>0.976791679859161</v>
+        <v>0.976791799068451</v>
       </c>
       <c r="H1170" t="n">
         <v>0</v>
@@ -34357,7 +34357,7 @@
         <v>1.22060000896454</v>
       </c>
       <c r="G1172" t="n">
-        <v>0.953817665576935</v>
+        <v>0.95381760597229</v>
       </c>
       <c r="H1172" t="n">
         <v>2356</v>
@@ -34386,7 +34386,7 @@
         <v>1.22060000896454</v>
       </c>
       <c r="G1173" t="n">
-        <v>0.953817665576935</v>
+        <v>0.95381760597229</v>
       </c>
       <c r="H1173" t="n">
         <v>0</v>
@@ -34415,7 +34415,7 @@
         <v>1.24979996681213</v>
       </c>
       <c r="G1174" t="n">
-        <v>0.97663551568985</v>
+        <v>0.976635456085205</v>
       </c>
       <c r="H1174" t="n">
         <v>1000</v>
@@ -34444,7 +34444,7 @@
         <v>1.22200000286102</v>
       </c>
       <c r="G1175" t="n">
-        <v>0.954911649227142</v>
+        <v>0.954911589622498</v>
       </c>
       <c r="H1175" t="n">
         <v>800</v>
@@ -34473,7 +34473,7 @@
         <v>1.22019994258881</v>
       </c>
       <c r="G1176" t="n">
-        <v>0.953504979610443</v>
+        <v>0.953504920005798</v>
       </c>
       <c r="H1176" t="n">
         <v>1000</v>
@@ -34502,7 +34502,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1177" t="n">
-        <v>0.953348815441132</v>
+        <v>0.953348696231842</v>
       </c>
       <c r="H1177" t="n">
         <v>1300</v>
@@ -34531,7 +34531,7 @@
         <v>1.23479998111725</v>
       </c>
       <c r="G1178" t="n">
-        <v>0.964913904666901</v>
+        <v>0.96491402387619</v>
       </c>
       <c r="H1178" t="n">
         <v>5677</v>
@@ -34560,7 +34560,7 @@
         <v>1.21700000762939</v>
       </c>
       <c r="G1179" t="n">
-        <v>0.951004445552826</v>
+        <v>0.951004385948181</v>
       </c>
       <c r="H1179" t="n">
         <v>1896</v>
@@ -34589,7 +34589,7 @@
         <v>1.19500005245209</v>
       </c>
       <c r="G1180" t="n">
-        <v>0.933812975883484</v>
+        <v>0.933812856674194</v>
       </c>
       <c r="H1180" t="n">
         <v>1588</v>
@@ -34618,7 +34618,7 @@
         <v>1.23580002784729</v>
       </c>
       <c r="G1181" t="n">
-        <v>0.965695381164551</v>
+        <v>0.96569550037384</v>
       </c>
       <c r="H1181" t="n">
         <v>2300</v>
@@ -34647,7 +34647,7 @@
         <v>1.24399995803833</v>
       </c>
       <c r="G1182" t="n">
-        <v>0.972103178501129</v>
+        <v>0.972103118896484</v>
       </c>
       <c r="H1182" t="n">
         <v>2300</v>
@@ -34676,7 +34676,7 @@
         <v>1.24399995803833</v>
       </c>
       <c r="G1183" t="n">
-        <v>0.972103178501129</v>
+        <v>0.972103118896484</v>
       </c>
       <c r="H1183" t="n">
         <v>1000</v>
@@ -34705,7 +34705,7 @@
         <v>1.20860004425049</v>
       </c>
       <c r="G1184" t="n">
-        <v>0.944440484046936</v>
+        <v>0.944440424442291</v>
       </c>
       <c r="H1184" t="n">
         <v>5980</v>
@@ -34734,7 +34734,7 @@
         <v>1.20500004291534</v>
       </c>
       <c r="G1185" t="n">
-        <v>0.941627264022827</v>
+        <v>0.941627383232117</v>
       </c>
       <c r="H1185" t="n">
         <v>6534</v>
@@ -34763,7 +34763,7 @@
         <v>1.20899999141693</v>
       </c>
       <c r="G1186" t="n">
-        <v>0.944752931594849</v>
+        <v>0.944752991199493</v>
       </c>
       <c r="H1186" t="n">
         <v>8300</v>
@@ -34792,7 +34792,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1187" t="n">
-        <v>0.953348815441132</v>
+        <v>0.953348696231842</v>
       </c>
       <c r="H1187" t="n">
         <v>9105</v>
@@ -34821,7 +34821,7 @@
         <v>1.20019996166229</v>
       </c>
       <c r="G1188" t="n">
-        <v>0.937876403331757</v>
+        <v>0.937876224517822</v>
       </c>
       <c r="H1188" t="n">
         <v>10090</v>
@@ -34850,7 +34850,7 @@
         <v>1.22019994258881</v>
       </c>
       <c r="G1189" t="n">
-        <v>0.953504979610443</v>
+        <v>0.953504920005798</v>
       </c>
       <c r="H1189" t="n">
         <v>7534</v>
@@ -34908,7 +34908,7 @@
         <v>1.23959994316101</v>
       </c>
       <c r="G1191" t="n">
-        <v>0.968664765357971</v>
+        <v>0.968664824962616</v>
       </c>
       <c r="H1191" t="n">
         <v>1101</v>
@@ -34937,7 +34937,7 @@
         <v>1.24979996681213</v>
       </c>
       <c r="G1192" t="n">
-        <v>0.97663551568985</v>
+        <v>0.976635456085205</v>
       </c>
       <c r="H1192" t="n">
         <v>7471</v>
@@ -35053,7 +35053,7 @@
         <v>1.24199998378754</v>
       </c>
       <c r="G1196" t="n">
-        <v>0.970540404319763</v>
+        <v>0.970540344715118</v>
       </c>
       <c r="H1196" t="n">
         <v>22960</v>
@@ -35082,7 +35082,7 @@
         <v>1.24399995803833</v>
       </c>
       <c r="G1197" t="n">
-        <v>0.972103178501129</v>
+        <v>0.972103118896484</v>
       </c>
       <c r="H1197" t="n">
         <v>28501</v>
@@ -35111,7 +35111,7 @@
         <v>1.23979997634888</v>
       </c>
       <c r="G1198" t="n">
-        <v>0.968821108341217</v>
+        <v>0.968821167945862</v>
       </c>
       <c r="H1198" t="n">
         <v>8654</v>
@@ -35140,7 +35140,7 @@
         <v>1.23979997634888</v>
       </c>
       <c r="G1199" t="n">
-        <v>0.968821108341217</v>
+        <v>0.968821167945862</v>
       </c>
       <c r="H1199" t="n">
         <v>11918</v>
@@ -35169,7 +35169,7 @@
         <v>1.19120001792908</v>
       </c>
       <c r="G1200" t="n">
-        <v>0.930843472480774</v>
+        <v>0.930843532085419</v>
       </c>
       <c r="H1200" t="n">
         <v>13624</v>
@@ -35198,7 +35198,7 @@
         <v>1.19120001792908</v>
       </c>
       <c r="G1201" t="n">
-        <v>0.930843472480774</v>
+        <v>0.930843532085419</v>
       </c>
       <c r="H1201" t="n">
         <v>0</v>
@@ -35227,7 +35227,7 @@
         <v>1.22940003871918</v>
       </c>
       <c r="G1202" t="n">
-        <v>0.960694193840027</v>
+        <v>0.960694253444672</v>
       </c>
       <c r="H1202" t="n">
         <v>930</v>
@@ -35285,7 +35285,7 @@
         <v>1.22979998588562</v>
       </c>
       <c r="G1204" t="n">
-        <v>0.961006700992584</v>
+        <v>0.961006641387939</v>
       </c>
       <c r="H1204" t="n">
         <v>4250</v>
@@ -35314,7 +35314,7 @@
         <v>1.24199998378754</v>
       </c>
       <c r="G1205" t="n">
-        <v>0.970540404319763</v>
+        <v>0.970540344715118</v>
       </c>
       <c r="H1205" t="n">
         <v>5811</v>
@@ -35343,7 +35343,7 @@
         <v>1.2117999792099</v>
       </c>
       <c r="G1206" t="n">
-        <v>0.946941018104553</v>
+        <v>0.946940958499908</v>
       </c>
       <c r="H1206" t="n">
         <v>27456</v>
@@ -35401,7 +35401,7 @@
         <v>1.19500005245209</v>
       </c>
       <c r="G1208" t="n">
-        <v>0.933812975883484</v>
+        <v>0.933812856674194</v>
       </c>
       <c r="H1208" t="n">
         <v>1086</v>
@@ -35430,7 +35430,7 @@
         <v>1.19500005245209</v>
       </c>
       <c r="G1209" t="n">
-        <v>0.933812975883484</v>
+        <v>0.933812856674194</v>
       </c>
       <c r="H1209" t="n">
         <v>7175</v>
@@ -35459,7 +35459,7 @@
         <v>1.19900000095367</v>
       </c>
       <c r="G1210" t="n">
-        <v>0.93693870306015</v>
+        <v>0.936938583850861</v>
       </c>
       <c r="H1210" t="n">
         <v>3</v>
@@ -35488,7 +35488,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G1211" t="n">
-        <v>0.968977451324463</v>
+        <v>0.968977510929108</v>
       </c>
       <c r="H1211" t="n">
         <v>39741</v>
@@ -35517,7 +35517,7 @@
         <v>1.20060002803802</v>
       </c>
       <c r="G1212" t="n">
-        <v>0.938188970088959</v>
+        <v>0.938189029693604</v>
       </c>
       <c r="H1212" t="n">
         <v>13237</v>
@@ -35604,7 +35604,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1215" t="n">
-        <v>0.984605967998505</v>
+        <v>0.984606206417084</v>
       </c>
       <c r="H1215" t="n">
         <v>32688</v>
@@ -35633,7 +35633,7 @@
         <v>1.26579999923706</v>
       </c>
       <c r="G1216" t="n">
-        <v>0.98913848400116</v>
+        <v>0.989138543605804</v>
       </c>
       <c r="H1216" t="n">
         <v>35063</v>
@@ -35662,7 +35662,7 @@
         <v>1.26540005207062</v>
       </c>
       <c r="G1217" t="n">
-        <v>0.988825917243958</v>
+        <v>0.988825798034668</v>
       </c>
       <c r="H1217" t="n">
         <v>20941</v>
@@ -35691,7 +35691,7 @@
         <v>1.24020004272461</v>
       </c>
       <c r="G1218" t="n">
-        <v>0.969133794307709</v>
+        <v>0.969133734703064</v>
       </c>
       <c r="H1218" t="n">
         <v>4530</v>
@@ -35778,7 +35778,7 @@
         <v>1.25539994239807</v>
       </c>
       <c r="G1221" t="n">
-        <v>0.981011509895325</v>
+        <v>0.981011390686035</v>
       </c>
       <c r="H1221" t="n">
         <v>4670</v>
@@ -35807,7 +35807,7 @@
         <v>1.22599995136261</v>
       </c>
       <c r="G1222" t="n">
-        <v>0.958037436008453</v>
+        <v>0.958037376403809</v>
       </c>
       <c r="H1222" t="n">
         <v>119</v>
@@ -35836,7 +35836,7 @@
         <v>1.22599995136261</v>
       </c>
       <c r="G1223" t="n">
-        <v>0.958037436008453</v>
+        <v>0.958037376403809</v>
       </c>
       <c r="H1223" t="n">
         <v>0</v>
@@ -35865,7 +35865,7 @@
         <v>1.22599995136261</v>
       </c>
       <c r="G1224" t="n">
-        <v>0.958037436008453</v>
+        <v>0.958037376403809</v>
       </c>
       <c r="H1224" t="n">
         <v>0</v>
@@ -35894,7 +35894,7 @@
         <v>1.23039996623993</v>
       </c>
       <c r="G1225" t="n">
-        <v>0.961475729942322</v>
+        <v>0.961475670337677</v>
       </c>
       <c r="H1225" t="n">
         <v>3067</v>
@@ -35923,7 +35923,7 @@
         <v>1.25</v>
       </c>
       <c r="G1226" t="n">
-        <v>0.976791679859161</v>
+        <v>0.976791799068451</v>
       </c>
       <c r="H1226" t="n">
         <v>370</v>
@@ -35952,7 +35952,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1227" t="n">
-        <v>0.937720060348511</v>
+        <v>0.937720119953156</v>
       </c>
       <c r="H1227" t="n">
         <v>6525</v>
@@ -35981,7 +35981,7 @@
         <v>1.17519998550415</v>
       </c>
       <c r="G1228" t="n">
-        <v>0.918340504169464</v>
+        <v>0.918340563774109</v>
       </c>
       <c r="H1228" t="n">
         <v>8221</v>
@@ -36010,7 +36010,7 @@
         <v>1.192999958992</v>
       </c>
       <c r="G1229" t="n">
-        <v>0.932250022888184</v>
+        <v>0.932250082492828</v>
       </c>
       <c r="H1229" t="n">
         <v>712</v>
@@ -36097,7 +36097,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G1232" t="n">
-        <v>0.96116316318512</v>
+        <v>0.961162984371185</v>
       </c>
       <c r="H1232" t="n">
         <v>6056</v>
@@ -36126,7 +36126,7 @@
         <v>1.19159996509552</v>
       </c>
       <c r="G1233" t="n">
-        <v>0.931155979633331</v>
+        <v>0.931156098842621</v>
       </c>
       <c r="H1233" t="n">
         <v>510</v>
@@ -36155,7 +36155,7 @@
         <v>1.19099998474121</v>
       </c>
       <c r="G1234" t="n">
-        <v>0.930687129497528</v>
+        <v>0.930687189102173</v>
       </c>
       <c r="H1234" t="n">
         <v>2006</v>
@@ -36184,7 +36184,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G1235" t="n">
-        <v>0.96116316318512</v>
+        <v>0.961162984371185</v>
       </c>
       <c r="H1235" t="n">
         <v>16103</v>
@@ -36213,7 +36213,7 @@
         <v>1.19799995422363</v>
       </c>
       <c r="G1236" t="n">
-        <v>0.9361572265625</v>
+        <v>0.936157166957855</v>
       </c>
       <c r="H1236" t="n">
         <v>37918</v>
@@ -36242,7 +36242,7 @@
         <v>1.23800003528595</v>
       </c>
       <c r="G1237" t="n">
-        <v>0.967414557933807</v>
+        <v>0.967414438724518</v>
       </c>
       <c r="H1237" t="n">
         <v>7311</v>
@@ -36271,7 +36271,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1238" t="n">
-        <v>0.953348815441132</v>
+        <v>0.953348696231842</v>
       </c>
       <c r="H1238" t="n">
         <v>3720</v>
@@ -36300,7 +36300,7 @@
         <v>1.26800000667572</v>
       </c>
       <c r="G1239" t="n">
-        <v>0.990857541561127</v>
+        <v>0.990857481956482</v>
       </c>
       <c r="H1239" t="n">
         <v>129144</v>
@@ -36561,7 +36561,7 @@
         <v>1.61300003528595</v>
       </c>
       <c r="G1248" t="n">
-        <v>1.26045227050781</v>
+        <v>1.26045215129852</v>
       </c>
       <c r="H1248" t="n">
         <v>112579</v>
@@ -36590,7 +36590,7 @@
         <v>1.59200000762939</v>
       </c>
       <c r="G1249" t="n">
-        <v>1.24404191970825</v>
+        <v>1.24404203891754</v>
       </c>
       <c r="H1249" t="n">
         <v>77714</v>
@@ -36619,7 +36619,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G1250" t="n">
-        <v>1.33625113964081</v>
+        <v>1.3362512588501</v>
       </c>
       <c r="H1250" t="n">
         <v>95910</v>
@@ -36648,7 +36648,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G1251" t="n">
-        <v>1.3128080368042</v>
+        <v>1.31280827522278</v>
       </c>
       <c r="H1251" t="n">
         <v>57237</v>
@@ -36677,7 +36677,7 @@
         <v>1.67980003356934</v>
       </c>
       <c r="G1252" t="n">
-        <v>1.3126517534256</v>
+        <v>1.31265199184418</v>
       </c>
       <c r="H1252" t="n">
         <v>36963</v>
@@ -36706,7 +36706,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G1253" t="n">
-        <v>1.3128080368042</v>
+        <v>1.31280827522278</v>
       </c>
       <c r="H1253" t="n">
         <v>6137</v>
@@ -36764,7 +36764,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G1255" t="n">
-        <v>1.3128080368042</v>
+        <v>1.31280827522278</v>
       </c>
       <c r="H1255" t="n">
         <v>9259</v>
@@ -36793,7 +36793,7 @@
         <v>1.72060000896454</v>
       </c>
       <c r="G1256" t="n">
-        <v>1.34453427791595</v>
+        <v>1.34453439712524</v>
       </c>
       <c r="H1256" t="n">
         <v>88356</v>
@@ -36822,7 +36822,7 @@
         <v>1.72500002384186</v>
       </c>
       <c r="G1257" t="n">
-        <v>1.34797275066376</v>
+        <v>1.34797263145447</v>
       </c>
       <c r="H1257" t="n">
         <v>18428</v>
@@ -36851,7 +36851,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G1258" t="n">
-        <v>1.4143944978714</v>
+        <v>1.41439437866211</v>
       </c>
       <c r="H1258" t="n">
         <v>159971</v>
@@ -36880,7 +36880,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G1259" t="n">
-        <v>1.32843685150146</v>
+        <v>1.32843673229218</v>
       </c>
       <c r="H1259" t="n">
         <v>147479</v>
@@ -36938,7 +36938,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G1261" t="n">
-        <v>1.34406566619873</v>
+        <v>1.34406542778015</v>
       </c>
       <c r="H1261" t="n">
         <v>16020</v>
@@ -36967,7 +36967,7 @@
         <v>1.74119997024536</v>
       </c>
       <c r="G1262" t="n">
-        <v>1.36063170433044</v>
+        <v>1.36063182353973</v>
       </c>
       <c r="H1262" t="n">
         <v>7273</v>
@@ -36996,7 +36996,7 @@
         <v>1.7208000421524</v>
       </c>
       <c r="G1263" t="n">
-        <v>1.34469056129456</v>
+        <v>1.34469068050385</v>
       </c>
       <c r="H1263" t="n">
         <v>7468</v>
@@ -37083,7 +37083,7 @@
         <v>1.72940003871918</v>
       </c>
       <c r="G1266" t="n">
-        <v>1.35141098499298</v>
+        <v>1.35141086578369</v>
       </c>
       <c r="H1266" t="n">
         <v>28267</v>
@@ -37170,7 +37170,7 @@
         <v>1.74979996681213</v>
       </c>
       <c r="G1269" t="n">
-        <v>1.46478521823883</v>
+        <v>1.46478509902954</v>
       </c>
       <c r="H1269" t="n">
         <v>33596</v>
@@ -37199,7 +37199,7 @@
         <v>1.73800003528595</v>
       </c>
       <c r="G1270" t="n">
-        <v>1.45490729808807</v>
+        <v>1.45490717887878</v>
       </c>
       <c r="H1270" t="n">
         <v>14911</v>
@@ -37489,7 +37489,7 @@
         <v>1.66600000858307</v>
       </c>
       <c r="G1280" t="n">
-        <v>1.39463484287262</v>
+        <v>1.39463472366333</v>
       </c>
       <c r="H1280" t="n">
         <v>32262</v>
@@ -37605,7 +37605,7 @@
         <v>1.66939997673035</v>
       </c>
       <c r="G1284" t="n">
-        <v>1.39748108386993</v>
+        <v>1.39748096466064</v>
       </c>
       <c r="H1284" t="n">
         <v>12668</v>
@@ -37750,7 +37750,7 @@
         <v>1.62999999523163</v>
       </c>
       <c r="G1289" t="n">
-        <v>1.36449873447418</v>
+        <v>1.36449861526489</v>
       </c>
       <c r="H1289" t="n">
         <v>57500</v>
@@ -37779,7 +37779,7 @@
         <v>1.64820003509521</v>
       </c>
       <c r="G1290" t="n">
-        <v>1.37973415851593</v>
+        <v>1.37973403930664</v>
       </c>
       <c r="H1290" t="n">
         <v>301</v>
@@ -38069,7 +38069,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G1300" t="n">
-        <v>1.49006605148315</v>
+        <v>1.49006593227386</v>
       </c>
       <c r="H1300" t="n">
         <v>15871</v>
@@ -38214,7 +38214,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G1305" t="n">
-        <v>1.56540632247925</v>
+        <v>1.56540644168854</v>
       </c>
       <c r="H1305" t="n">
         <v>90063</v>
@@ -38243,7 +38243,7 @@
         <v>1.83259999752045</v>
       </c>
       <c r="G1306" t="n">
-        <v>1.53409814834595</v>
+        <v>1.53409826755524</v>
       </c>
       <c r="H1306" t="n">
         <v>15504</v>
@@ -38272,7 +38272,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G1307" t="n">
-        <v>1.57377743721008</v>
+        <v>1.57377755641937</v>
       </c>
       <c r="H1307" t="n">
         <v>25764</v>
@@ -38301,7 +38301,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G1308" t="n">
-        <v>1.57377743721008</v>
+        <v>1.57377755641937</v>
       </c>
       <c r="H1308" t="n">
         <v>6508</v>
@@ -38330,7 +38330,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G1309" t="n">
-        <v>1.56540632247925</v>
+        <v>1.56540644168854</v>
       </c>
       <c r="H1309" t="n">
         <v>5381</v>
@@ -38359,7 +38359,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G1310" t="n">
-        <v>1.56540632247925</v>
+        <v>1.56540644168854</v>
       </c>
       <c r="H1310" t="n">
         <v>6800</v>
@@ -38446,7 +38446,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G1313" t="n">
-        <v>1.57377743721008</v>
+        <v>1.57377755641937</v>
       </c>
       <c r="H1313" t="n">
         <v>4995</v>
@@ -38533,7 +38533,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G1316" t="n">
-        <v>1.57377743721008</v>
+        <v>1.57377755641937</v>
       </c>
       <c r="H1316" t="n">
         <v>16667</v>
@@ -38765,7 +38765,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G1324" t="n">
-        <v>1.61563324928284</v>
+        <v>1.61563336849213</v>
       </c>
       <c r="H1324" t="n">
         <v>11644</v>
@@ -39200,7 +39200,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G1339" t="n">
-        <v>1.60726225376129</v>
+        <v>1.607262134552</v>
       </c>
       <c r="H1339" t="n">
         <v>1005</v>
@@ -39229,7 +39229,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G1340" t="n">
-        <v>1.60726225376129</v>
+        <v>1.607262134552</v>
       </c>
       <c r="H1340" t="n">
         <v>120</v>
@@ -39258,7 +39258,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G1341" t="n">
-        <v>1.60726225376129</v>
+        <v>1.607262134552</v>
       </c>
       <c r="H1341" t="n">
         <v>20929</v>
@@ -39287,7 +39287,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G1342" t="n">
-        <v>1.61563324928284</v>
+        <v>1.61563336849213</v>
       </c>
       <c r="H1342" t="n">
         <v>4847</v>
@@ -39316,7 +39316,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G1343" t="n">
-        <v>1.60726225376129</v>
+        <v>1.607262134552</v>
       </c>
       <c r="H1343" t="n">
         <v>14161</v>
@@ -39519,7 +39519,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G1350" t="n">
-        <v>1.60726225376129</v>
+        <v>1.607262134552</v>
       </c>
       <c r="H1350" t="n">
         <v>120787</v>
@@ -39577,7 +39577,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G1352" t="n">
-        <v>1.59889113903046</v>
+        <v>1.59889101982117</v>
       </c>
       <c r="H1352" t="n">
         <v>23824</v>
@@ -39606,7 +39606,7 @@
         <v>1.85500001907349</v>
       </c>
       <c r="G1353" t="n">
-        <v>1.552849650383</v>
+        <v>1.55284976959229</v>
       </c>
       <c r="H1353" t="n">
         <v>21990</v>
@@ -39635,7 +39635,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G1354" t="n">
-        <v>1.59051978588104</v>
+        <v>1.59051990509033</v>
       </c>
       <c r="H1354" t="n">
         <v>15319</v>
@@ -39693,7 +39693,7 @@
         <v>1.88499999046326</v>
       </c>
       <c r="G1356" t="n">
-        <v>1.57796323299408</v>
+        <v>1.57796311378479</v>
       </c>
       <c r="H1356" t="n">
         <v>10700</v>
@@ -39722,7 +39722,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G1357" t="n">
-        <v>1.55703544616699</v>
+        <v>1.5570353269577</v>
       </c>
       <c r="H1357" t="n">
         <v>10646</v>
@@ -39780,7 +39780,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G1359" t="n">
-        <v>1.56540632247925</v>
+        <v>1.56540644168854</v>
       </c>
       <c r="H1359" t="n">
         <v>4850</v>
@@ -39809,7 +39809,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G1360" t="n">
-        <v>1.59051978588104</v>
+        <v>1.59051990509033</v>
       </c>
       <c r="H1360" t="n">
         <v>13059</v>
@@ -39838,7 +39838,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G1361" t="n">
-        <v>1.60726225376129</v>
+        <v>1.607262134552</v>
       </c>
       <c r="H1361" t="n">
         <v>16896</v>
@@ -39867,7 +39867,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G1362" t="n">
-        <v>1.59051978588104</v>
+        <v>1.59051990509033</v>
       </c>
       <c r="H1362" t="n">
         <v>7070</v>
@@ -39925,7 +39925,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G1364" t="n">
-        <v>1.59051978588104</v>
+        <v>1.59051990509033</v>
       </c>
       <c r="H1364" t="n">
         <v>4035</v>
@@ -39954,7 +39954,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G1365" t="n">
-        <v>1.59051978588104</v>
+        <v>1.59051990509033</v>
       </c>
       <c r="H1365" t="n">
         <v>1022</v>
@@ -39983,7 +39983,7 @@
         <v>1.85500001907349</v>
       </c>
       <c r="G1366" t="n">
-        <v>1.552849650383</v>
+        <v>1.55284976959229</v>
       </c>
       <c r="H1366" t="n">
         <v>32969</v>
@@ -40041,7 +40041,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G1368" t="n">
-        <v>1.59051978588104</v>
+        <v>1.59051990509033</v>
       </c>
       <c r="H1368" t="n">
         <v>25050</v>
@@ -40070,7 +40070,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G1369" t="n">
-        <v>1.55703544616699</v>
+        <v>1.5570353269577</v>
       </c>
       <c r="H1369" t="n">
         <v>6264</v>
@@ -40128,7 +40128,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G1371" t="n">
-        <v>1.55703544616699</v>
+        <v>1.5570353269577</v>
       </c>
       <c r="H1371" t="n">
         <v>5678</v>
@@ -40186,7 +40186,7 @@
         <v>1.83500003814697</v>
       </c>
       <c r="G1373" t="n">
-        <v>1.53610754013062</v>
+        <v>1.53610742092133</v>
       </c>
       <c r="H1373" t="n">
         <v>6413</v>
@@ -40244,7 +40244,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G1375" t="n">
-        <v>1.55703544616699</v>
+        <v>1.5570353269577</v>
       </c>
       <c r="H1375" t="n">
         <v>5724</v>
@@ -40302,7 +40302,7 @@
         <v>1.86500000953674</v>
       </c>
       <c r="G1377" t="n">
-        <v>1.56122088432312</v>
+        <v>1.56122076511383</v>
       </c>
       <c r="H1377" t="n">
         <v>24781</v>
@@ -40389,7 +40389,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1380" t="n">
-        <v>1.80817008018494</v>
+        <v>1.80817019939423</v>
       </c>
       <c r="H1380" t="n">
         <v>114976</v>
@@ -40418,7 +40418,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G1381" t="n">
-        <v>1.90862381458282</v>
+        <v>1.90862369537354</v>
       </c>
       <c r="H1381" t="n">
         <v>118880</v>
@@ -40505,7 +40505,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G1384" t="n">
-        <v>1.90025269985199</v>
+        <v>1.9002525806427</v>
       </c>
       <c r="H1384" t="n">
         <v>25190</v>
@@ -40708,7 +40708,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1391" t="n">
-        <v>1.80817008018494</v>
+        <v>1.80817019939423</v>
       </c>
       <c r="H1391" t="n">
         <v>20155</v>
@@ -40766,7 +40766,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1393" t="n">
-        <v>1.80817008018494</v>
+        <v>1.80817019939423</v>
       </c>
       <c r="H1393" t="n">
         <v>10650</v>
@@ -40824,7 +40824,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G1395" t="n">
-        <v>1.79142785072327</v>
+        <v>1.79142773151398</v>
       </c>
       <c r="H1395" t="n">
         <v>9872</v>
@@ -40853,7 +40853,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1396" t="n">
-        <v>1.75794279575348</v>
+        <v>1.75794291496277</v>
       </c>
       <c r="H1396" t="n">
         <v>11946</v>
@@ -40882,7 +40882,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1397" t="n">
-        <v>1.75794279575348</v>
+        <v>1.75794291496277</v>
       </c>
       <c r="H1397" t="n">
         <v>17267</v>
@@ -40940,7 +40940,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1399" t="n">
-        <v>1.75794279575348</v>
+        <v>1.75794291496277</v>
       </c>
       <c r="H1399" t="n">
         <v>13274</v>
@@ -41578,7 +41578,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1421" t="n">
-        <v>1.80817008018494</v>
+        <v>1.80817019939423</v>
       </c>
       <c r="H1421" t="n">
         <v>41767</v>
@@ -41723,7 +41723,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G1426" t="n">
-        <v>1.83328366279602</v>
+        <v>1.83328354358673</v>
       </c>
       <c r="H1426" t="n">
         <v>5861</v>
@@ -41839,7 +41839,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G1430" t="n">
-        <v>1.83328366279602</v>
+        <v>1.83328354358673</v>
       </c>
       <c r="H1430" t="n">
         <v>2450</v>
@@ -41926,7 +41926,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G1433" t="n">
-        <v>1.79142785072327</v>
+        <v>1.79142773151398</v>
       </c>
       <c r="H1433" t="n">
         <v>12195</v>
@@ -42187,7 +42187,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1442" t="n">
-        <v>1.80817008018494</v>
+        <v>1.80817019939423</v>
       </c>
       <c r="H1442" t="n">
         <v>3900</v>
@@ -42216,7 +42216,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G1443" t="n">
-        <v>1.83328366279602</v>
+        <v>1.83328354358673</v>
       </c>
       <c r="H1443" t="n">
         <v>7310</v>
@@ -42245,7 +42245,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G1444" t="n">
-        <v>1.83328366279602</v>
+        <v>1.83328354358673</v>
       </c>
       <c r="H1444" t="n">
         <v>0</v>
@@ -42332,7 +42332,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G1447" t="n">
-        <v>1.79142785072327</v>
+        <v>1.79142773151398</v>
       </c>
       <c r="H1447" t="n">
         <v>1801</v>
@@ -42535,7 +42535,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1454" t="n">
-        <v>1.75794279575348</v>
+        <v>1.75794291496277</v>
       </c>
       <c r="H1454" t="n">
         <v>10200</v>
@@ -42564,7 +42564,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G1455" t="n">
-        <v>1.79142785072327</v>
+        <v>1.79142773151398</v>
       </c>
       <c r="H1455" t="n">
         <v>8648</v>
@@ -42593,7 +42593,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G1456" t="n">
-        <v>1.83328366279602</v>
+        <v>1.83328354358673</v>
       </c>
       <c r="H1456" t="n">
         <v>33296</v>
@@ -42651,7 +42651,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G1458" t="n">
-        <v>1.86676800251007</v>
+        <v>1.86676812171936</v>
       </c>
       <c r="H1458" t="n">
         <v>13297</v>
@@ -42738,7 +42738,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G1461" t="n">
-        <v>1.90025269985199</v>
+        <v>1.9002525806427</v>
       </c>
       <c r="H1461" t="n">
         <v>22939</v>
@@ -42912,7 +42912,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G1467" t="n">
-        <v>2.07604694366455</v>
+        <v>2.07604718208313</v>
       </c>
       <c r="H1467" t="n">
         <v>8318</v>
@@ -42970,7 +42970,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G1469" t="n">
-        <v>2.07604694366455</v>
+        <v>2.07604718208313</v>
       </c>
       <c r="H1469" t="n">
         <v>10761</v>
@@ -43028,7 +43028,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G1471" t="n">
-        <v>2.04256248474121</v>
+        <v>2.04256224632263</v>
       </c>
       <c r="H1471" t="n">
         <v>4161</v>
@@ -43115,7 +43115,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G1474" t="n">
-        <v>2.10953164100647</v>
+        <v>2.10953187942505</v>
       </c>
       <c r="H1474" t="n">
         <v>11143</v>
@@ -44391,7 +44391,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G1518" t="n">
-        <v>2.62017226219177</v>
+        <v>2.62017250061035</v>
       </c>
       <c r="H1518" t="n">
         <v>151266</v>
@@ -44478,7 +44478,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G1521" t="n">
-        <v>2.71225500106812</v>
+        <v>2.71225523948669</v>
       </c>
       <c r="H1521" t="n">
         <v>58192</v>
@@ -44652,7 +44652,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G1527" t="n">
-        <v>3.10569930076599</v>
+        <v>3.10569953918457</v>
       </c>
       <c r="H1527" t="n">
         <v>40326</v>
@@ -44710,7 +44710,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G1529" t="n">
-        <v>3.0303590297699</v>
+        <v>3.03035879135132</v>
       </c>
       <c r="H1529" t="n">
         <v>25973</v>
@@ -45029,7 +45029,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G1540" t="n">
-        <v>2.78759551048279</v>
+        <v>2.78759527206421</v>
       </c>
       <c r="H1540" t="n">
         <v>21833</v>
@@ -45058,7 +45058,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1541" t="n">
-        <v>2.80433750152588</v>
+        <v>2.80433773994446</v>
       </c>
       <c r="H1541" t="n">
         <v>9323</v>
@@ -45203,7 +45203,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G1546" t="n">
-        <v>3.00524544715881</v>
+        <v>3.00524568557739</v>
       </c>
       <c r="H1546" t="n">
         <v>18229</v>
@@ -45232,7 +45232,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G1547" t="n">
-        <v>3.04710125923157</v>
+        <v>3.04710149765015</v>
       </c>
       <c r="H1547" t="n">
         <v>27597</v>
@@ -45261,7 +45261,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G1548" t="n">
-        <v>3.12244176864624</v>
+        <v>3.12244153022766</v>
       </c>
       <c r="H1548" t="n">
         <v>31587</v>
@@ -45290,7 +45290,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G1549" t="n">
-        <v>3.18941068649292</v>
+        <v>3.1894109249115</v>
       </c>
       <c r="H1549" t="n">
         <v>55680</v>
@@ -45348,7 +45348,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G1551" t="n">
-        <v>3.22289562225342</v>
+        <v>3.222895860672</v>
       </c>
       <c r="H1551" t="n">
         <v>94238</v>
@@ -45493,7 +45493,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G1556" t="n">
-        <v>3.2180643081665</v>
+        <v>3.21806406974792</v>
       </c>
       <c r="H1556" t="n">
         <v>26348</v>
@@ -45522,7 +45522,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G1557" t="n">
-        <v>3.1576714515686</v>
+        <v>3.15767168998718</v>
       </c>
       <c r="H1557" t="n">
         <v>14643</v>
@@ -45725,7 +45725,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1564" t="n">
-        <v>3.10590648651123</v>
+        <v>3.10590624809265</v>
       </c>
       <c r="H1564" t="n">
         <v>5841</v>
@@ -45783,7 +45783,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G1566" t="n">
-        <v>2.97649359703064</v>
+        <v>2.97649383544922</v>
       </c>
       <c r="H1566" t="n">
         <v>27030</v>
@@ -46015,7 +46015,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G1574" t="n">
-        <v>2.66590285301208</v>
+        <v>2.66590309143066</v>
       </c>
       <c r="H1574" t="n">
         <v>33185</v>
@@ -46044,7 +46044,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G1575" t="n">
-        <v>2.62276530265808</v>
+        <v>2.62276554107666</v>
       </c>
       <c r="H1575" t="n">
         <v>16919</v>
@@ -46218,7 +46218,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G1581" t="n">
-        <v>3.00237607955933</v>
+        <v>3.00237631797791</v>
       </c>
       <c r="H1581" t="n">
         <v>7369</v>
@@ -46247,7 +46247,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G1582" t="n">
-        <v>2.96786594390869</v>
+        <v>2.96786618232727</v>
       </c>
       <c r="H1582" t="n">
         <v>9819</v>
@@ -46421,7 +46421,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G1588" t="n">
-        <v>3.00237607955933</v>
+        <v>3.00237631797791</v>
       </c>
       <c r="H1588" t="n">
         <v>8197</v>
@@ -46595,7 +46595,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1594" t="n">
-        <v>2.93335604667664</v>
+        <v>2.93335628509521</v>
       </c>
       <c r="H1594" t="n">
         <v>1217</v>
@@ -46624,7 +46624,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1595" t="n">
-        <v>2.93335604667664</v>
+        <v>2.93335628509521</v>
       </c>
       <c r="H1595" t="n">
         <v>2971</v>
@@ -46711,7 +46711,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1598" t="n">
-        <v>2.93335604667664</v>
+        <v>2.93335628509521</v>
       </c>
       <c r="H1598" t="n">
         <v>2090</v>
@@ -46798,7 +46798,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1601" t="n">
-        <v>2.93335604667664</v>
+        <v>2.93335628509521</v>
       </c>
       <c r="H1601" t="n">
         <v>1039</v>
@@ -46827,7 +46827,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G1602" t="n">
-        <v>2.95061135292053</v>
+        <v>2.95061111450195</v>
       </c>
       <c r="H1602" t="n">
         <v>3240</v>
@@ -47001,7 +47001,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G1608" t="n">
-        <v>2.95061135292053</v>
+        <v>2.95061111450195</v>
       </c>
       <c r="H1608" t="n">
         <v>24178</v>
@@ -47059,7 +47059,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G1610" t="n">
-        <v>3.19792723655701</v>
+        <v>3.19792699813843</v>
       </c>
       <c r="H1610" t="n">
         <v>18822</v>
@@ -47088,7 +47088,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1611" t="n">
-        <v>3.05004620552063</v>
+        <v>3.05004596710205</v>
       </c>
       <c r="H1611" t="n">
         <v>18282</v>
@@ -47117,7 +47117,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1612" t="n">
-        <v>3.05004620552063</v>
+        <v>3.05004596710205</v>
       </c>
       <c r="H1612" t="n">
         <v>6535</v>
@@ -47146,7 +47146,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1613" t="n">
-        <v>3.05004620552063</v>
+        <v>3.05004596710205</v>
       </c>
       <c r="H1613" t="n">
         <v>6560</v>
@@ -47204,7 +47204,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G1615" t="n">
-        <v>2.98534822463989</v>
+        <v>2.98534798622131</v>
       </c>
       <c r="H1615" t="n">
         <v>5371</v>
@@ -47262,7 +47262,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G1617" t="n">
-        <v>3.01307582855225</v>
+        <v>3.01307559013367</v>
       </c>
       <c r="H1617" t="n">
         <v>1877</v>
@@ -47320,7 +47320,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G1619" t="n">
-        <v>3.06853103637695</v>
+        <v>3.06853127479553</v>
       </c>
       <c r="H1619" t="n">
         <v>5319</v>
@@ -47378,7 +47378,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G1621" t="n">
-        <v>2.93913531303406</v>
+        <v>2.93913555145264</v>
       </c>
       <c r="H1621" t="n">
         <v>7441</v>
@@ -47407,7 +47407,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G1622" t="n">
-        <v>3.06853103637695</v>
+        <v>3.06853127479553</v>
       </c>
       <c r="H1622" t="n">
         <v>9571</v>
@@ -47494,7 +47494,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G1625" t="n">
-        <v>3.01307582855225</v>
+        <v>3.01307559013367</v>
       </c>
       <c r="H1625" t="n">
         <v>720</v>
@@ -47523,7 +47523,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G1626" t="n">
-        <v>3.01307582855225</v>
+        <v>3.01307559013367</v>
       </c>
       <c r="H1626" t="n">
         <v>0</v>
@@ -47552,7 +47552,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G1627" t="n">
-        <v>2.98534822463989</v>
+        <v>2.98534798622131</v>
       </c>
       <c r="H1627" t="n">
         <v>2900</v>
@@ -47697,7 +47697,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G1632" t="n">
-        <v>2.93913531303406</v>
+        <v>2.93913555145264</v>
       </c>
       <c r="H1632" t="n">
         <v>2221</v>
@@ -47813,7 +47813,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G1636" t="n">
-        <v>2.88367962837219</v>
+        <v>2.88367986679077</v>
       </c>
       <c r="H1636" t="n">
         <v>4351</v>
@@ -48074,7 +48074,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G1645" t="n">
-        <v>2.44927954673767</v>
+        <v>2.44927930831909</v>
       </c>
       <c r="H1645" t="n">
         <v>4242</v>
@@ -48364,7 +48364,7 @@
         <v>2.75</v>
       </c>
       <c r="G1655" t="n">
-        <v>2.54170489311218</v>
+        <v>2.54170513153076</v>
       </c>
       <c r="H1655" t="n">
         <v>4443</v>
@@ -48422,7 +48422,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G1657" t="n">
-        <v>2.66185855865479</v>
+        <v>2.66185832023621</v>
       </c>
       <c r="H1657" t="n">
         <v>1365</v>
@@ -48538,7 +48538,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G1661" t="n">
-        <v>2.51397728919983</v>
+        <v>2.51397752761841</v>
       </c>
       <c r="H1661" t="n">
         <v>2782</v>
@@ -48596,7 +48596,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G1663" t="n">
-        <v>2.53246235847473</v>
+        <v>2.53246259689331</v>
       </c>
       <c r="H1663" t="n">
         <v>37694</v>
@@ -48625,7 +48625,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G1664" t="n">
-        <v>2.48624992370605</v>
+        <v>2.48624968528748</v>
       </c>
       <c r="H1664" t="n">
         <v>1765</v>
@@ -48712,7 +48712,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G1667" t="n">
-        <v>2.51397728919983</v>
+        <v>2.51397752761841</v>
       </c>
       <c r="H1667" t="n">
         <v>22439</v>
@@ -48741,7 +48741,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G1668" t="n">
-        <v>2.44927954673767</v>
+        <v>2.44927930831909</v>
       </c>
       <c r="H1668" t="n">
         <v>12455</v>
@@ -48857,7 +48857,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G1672" t="n">
-        <v>2.42155170440674</v>
+        <v>2.42155146598816</v>
       </c>
       <c r="H1672" t="n">
         <v>3460</v>
@@ -49147,7 +49147,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G1682" t="n">
-        <v>2.40306639671326</v>
+        <v>2.40306663513184</v>
       </c>
       <c r="H1682" t="n">
         <v>1410</v>
@@ -49495,7 +49495,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G1694" t="n">
-        <v>2.27367091178894</v>
+        <v>2.27367067337036</v>
       </c>
       <c r="H1694" t="n">
         <v>3905</v>
@@ -49611,7 +49611,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G1698" t="n">
-        <v>2.27367091178894</v>
+        <v>2.27367067337036</v>
       </c>
       <c r="H1698" t="n">
         <v>19</v>
@@ -49640,7 +49640,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G1699" t="n">
-        <v>2.26442813873291</v>
+        <v>2.26442837715149</v>
       </c>
       <c r="H1699" t="n">
         <v>580</v>
@@ -49669,7 +49669,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G1700" t="n">
-        <v>2.23670053482056</v>
+        <v>2.23670029640198</v>
       </c>
       <c r="H1700" t="n">
         <v>450</v>
@@ -49814,7 +49814,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G1705" t="n">
-        <v>2.2089729309082</v>
+        <v>2.20897269248962</v>
       </c>
       <c r="H1705" t="n">
         <v>1386</v>
@@ -49872,7 +49872,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G1707" t="n">
-        <v>2.26442813873291</v>
+        <v>2.26442837715149</v>
       </c>
       <c r="H1707" t="n">
         <v>190</v>
@@ -49901,7 +49901,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G1708" t="n">
-        <v>2.26442813873291</v>
+        <v>2.26442837715149</v>
       </c>
       <c r="H1708" t="n">
         <v>0</v>
@@ -49959,7 +49959,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G1710" t="n">
-        <v>2.28291344642639</v>
+        <v>2.28291320800781</v>
       </c>
       <c r="H1710" t="n">
         <v>900</v>
@@ -49988,7 +49988,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G1711" t="n">
-        <v>2.28291344642639</v>
+        <v>2.28291320800781</v>
       </c>
       <c r="H1711" t="n">
         <v>0</v>
@@ -50104,7 +50104,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G1715" t="n">
-        <v>2.23670053482056</v>
+        <v>2.23670029640198</v>
       </c>
       <c r="H1715" t="n">
         <v>11340</v>
@@ -50133,7 +50133,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G1716" t="n">
-        <v>2.28291344642639</v>
+        <v>2.28291320800781</v>
       </c>
       <c r="H1716" t="n">
         <v>8732</v>
@@ -50278,7 +50278,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G1721" t="n">
-        <v>2.07033443450928</v>
+        <v>2.0703341960907</v>
       </c>
       <c r="H1721" t="n">
         <v>201</v>
@@ -50336,7 +50336,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G1723" t="n">
-        <v>2.19048738479614</v>
+        <v>2.19048762321472</v>
       </c>
       <c r="H1723" t="n">
         <v>7034</v>
@@ -50423,7 +50423,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G1726" t="n">
-        <v>2.06109189987183</v>
+        <v>2.06109166145325</v>
       </c>
       <c r="H1726" t="n">
         <v>7464</v>
@@ -50684,7 +50684,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G1735" t="n">
-        <v>2.0518491268158</v>
+        <v>2.05184936523438</v>
       </c>
       <c r="H1735" t="n">
         <v>601</v>
@@ -50742,7 +50742,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1737" t="n">
-        <v>1.99639391899109</v>
+        <v>1.99639403820038</v>
       </c>
       <c r="H1737" t="n">
         <v>7242</v>
@@ -50945,7 +50945,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G1744" t="n">
-        <v>2.07033443450928</v>
+        <v>2.0703341960907</v>
       </c>
       <c r="H1744" t="n">
         <v>2600</v>
@@ -51032,7 +51032,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G1747" t="n">
-        <v>2.06109189987183</v>
+        <v>2.06109166145325</v>
       </c>
       <c r="H1747" t="n">
         <v>2976</v>
@@ -51148,7 +51148,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G1751" t="n">
-        <v>2.23670053482056</v>
+        <v>2.23670029640198</v>
       </c>
       <c r="H1751" t="n">
         <v>2433</v>
@@ -51293,7 +51293,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G1756" t="n">
-        <v>2.19048738479614</v>
+        <v>2.19048762321472</v>
       </c>
       <c r="H1756" t="n">
         <v>8634</v>
@@ -51322,7 +51322,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G1757" t="n">
-        <v>2.27367091178894</v>
+        <v>2.27367067337036</v>
       </c>
       <c r="H1757" t="n">
         <v>7714</v>
@@ -51351,7 +51351,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G1758" t="n">
-        <v>2.53246235847473</v>
+        <v>2.53246259689331</v>
       </c>
       <c r="H1758" t="n">
         <v>20349</v>
@@ -51467,7 +51467,7 @@
         <v>2.75</v>
       </c>
       <c r="G1762" t="n">
-        <v>2.54170489311218</v>
+        <v>2.54170513153076</v>
       </c>
       <c r="H1762" t="n">
         <v>6937</v>
@@ -51699,7 +51699,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G1770" t="n">
-        <v>2.51397728919983</v>
+        <v>2.51397752761841</v>
       </c>
       <c r="H1770" t="n">
         <v>9906</v>
@@ -51786,7 +51786,7 @@
         <v>2.75</v>
       </c>
       <c r="G1773" t="n">
-        <v>2.54170489311218</v>
+        <v>2.54170513153076</v>
       </c>
       <c r="H1773" t="n">
         <v>13690</v>
@@ -51844,7 +51844,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G1775" t="n">
-        <v>2.53246235847473</v>
+        <v>2.53246259689331</v>
       </c>
       <c r="H1775" t="n">
         <v>10845</v>
@@ -51873,7 +51873,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G1776" t="n">
-        <v>2.53246235847473</v>
+        <v>2.53246259689331</v>
       </c>
       <c r="H1776" t="n">
         <v>3910</v>
@@ -51902,7 +51902,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G1777" t="n">
-        <v>2.51397728919983</v>
+        <v>2.51397752761841</v>
       </c>
       <c r="H1777" t="n">
         <v>18536</v>
